--- a/binance-usdt-perpetual-data/weeks/2026-03-09_2026-03-15/2026-03-12.xlsx
+++ b/binance-usdt-perpetual-data/weeks/2026-03-09_2026-03-15/2026-03-12.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H543"/>
+  <dimension ref="A1:J543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -434,6 +434,8 @@
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -477,6 +479,16 @@
           <t>change_00:45</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>price_01:00</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>change_01:00</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -505,6 +517,12 @@
       <c r="H2" s="2" t="n">
         <v>0.004252200662968277</v>
       </c>
+      <c r="I2" s="1" t="n">
+        <v>70534.10000000001</v>
+      </c>
+      <c r="J2" s="3" t="n">
+        <v>-0.00248762551265725</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -533,6 +551,12 @@
       <c r="H3" s="2" t="n">
         <v>0.006555063506739889</v>
       </c>
+      <c r="I3" s="1" t="n">
+        <v>2065.82</v>
+      </c>
+      <c r="J3" s="3" t="n">
+        <v>-0.001232854856722795</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -561,6 +585,12 @@
       <c r="H4" s="2" t="n">
         <v>0.007106244175209686</v>
       </c>
+      <c r="I4" s="1" t="n">
+        <v>86.38</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>-0.0008097165991903688</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -589,6 +619,12 @@
       <c r="H5" s="3" t="n">
         <v>-0.02724252491694345</v>
       </c>
+      <c r="I5" s="1" t="n">
+        <v>0.014573</v>
+      </c>
+      <c r="J5" s="3" t="n">
+        <v>-0.004576502732240511</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -617,6 +653,12 @@
       <c r="H6" s="2" t="n">
         <v>0.004863813229571899</v>
       </c>
+      <c r="I6" s="1" t="n">
+        <v>0.09293999999999999</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>-0.0003226847370119635</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -645,6 +687,12 @@
       <c r="H7" s="2" t="n">
         <v>0.004120879120879149</v>
       </c>
+      <c r="I7" s="1" t="n">
+        <v>1.3864</v>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>-0.001799985600115161</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -673,6 +721,12 @@
       <c r="H8" s="2" t="n">
         <v>0.0008260139321014904</v>
       </c>
+      <c r="I8" s="1" t="n">
+        <v>36.438</v>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>0.002448485515420115</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -701,6 +755,12 @@
       <c r="H9" s="2" t="n">
         <v>0.002548459340489578</v>
       </c>
+      <c r="I9" s="1" t="n">
+        <v>648.16</v>
+      </c>
+      <c r="J9" s="3" t="n">
+        <v>-0.001448158989369981</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -729,6 +789,12 @@
       <c r="H10" s="2" t="n">
         <v>0.02167328532005122</v>
       </c>
+      <c r="I10" s="1" t="n">
+        <v>15.091</v>
+      </c>
+      <c r="J10" s="3" t="n">
+        <v>-0.005797483365175635</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -757,6 +823,12 @@
       <c r="H11" s="2" t="n">
         <v>0.004487944616853654</v>
       </c>
+      <c r="I11" s="1" t="n">
+        <v>211.12</v>
+      </c>
+      <c r="J11" s="2" t="n">
+        <v>0.00346974666096306</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -785,6 +857,12 @@
       <c r="H12" s="2" t="n">
         <v>0.004017750059966484</v>
       </c>
+      <c r="I12" s="1" t="n">
+        <v>0.0033524</v>
+      </c>
+      <c r="J12" s="2" t="n">
+        <v>0.001134802604073339</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -813,6 +891,12 @@
       <c r="H13" s="3" t="n">
         <v>-0.0002696871628911289</v>
       </c>
+      <c r="I13" s="1" t="n">
+        <v>0.03706</v>
+      </c>
+      <c r="J13" s="3" t="n">
+        <v>-0.000269759913676723</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -841,6 +925,12 @@
       <c r="H14" s="2" t="n">
         <v>0.0007564296520422767</v>
       </c>
+      <c r="I14" s="1" t="n">
+        <v>2.614</v>
+      </c>
+      <c r="J14" s="3" t="n">
+        <v>-0.01209372637944068</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -869,6 +959,12 @@
       <c r="H15" s="2" t="n">
         <v>0.007613952052680278</v>
       </c>
+      <c r="I15" s="1" t="n">
+        <v>0.9771</v>
+      </c>
+      <c r="J15" s="3" t="n">
+        <v>-0.002246502603900725</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -897,6 +993,12 @@
       <c r="H16" s="3" t="n">
         <v>-0.01059135039717558</v>
       </c>
+      <c r="I16" s="1" t="n">
+        <v>0.05647</v>
+      </c>
+      <c r="J16" s="2" t="n">
+        <v>0.007493309545049005</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -925,6 +1027,12 @@
       <c r="H17" s="2" t="n">
         <v>0.003409090909090912</v>
       </c>
+      <c r="I17" s="1" t="n">
+        <v>0.882</v>
+      </c>
+      <c r="J17" s="3" t="n">
+        <v>-0.001132502831257079</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -953,6 +1061,12 @@
       <c r="H18" s="2" t="n">
         <v>0.006102212051868765</v>
       </c>
+      <c r="I18" s="1" t="n">
+        <v>0.2634</v>
+      </c>
+      <c r="J18" s="3" t="n">
+        <v>-0.001516300227444867</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -981,6 +1095,12 @@
       <c r="H19" s="2" t="n">
         <v>0.006940942663067685</v>
       </c>
+      <c r="I19" s="1" t="n">
+        <v>0.34003</v>
+      </c>
+      <c r="J19" s="2" t="n">
+        <v>0.001649630306065352</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1009,6 +1129,12 @@
       <c r="H20" s="2" t="n">
         <v>0.005833941035524447</v>
       </c>
+      <c r="I20" s="1" t="n">
+        <v>9.629</v>
+      </c>
+      <c r="J20" s="3" t="n">
+        <v>-0.002692905230450523</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1037,6 +1163,12 @@
       <c r="H21" s="3" t="n">
         <v>-0.0002500250025001648</v>
       </c>
+      <c r="I21" s="1" t="n">
+        <v>199.01</v>
+      </c>
+      <c r="J21" s="3" t="n">
+        <v>-0.004601610563697373</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1065,6 +1197,12 @@
       <c r="H22" s="2" t="n">
         <v>0.01244593945218656</v>
       </c>
+      <c r="I22" s="1" t="n">
+        <v>0.020611</v>
+      </c>
+      <c r="J22" s="3" t="n">
+        <v>-0.02173809862831649</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1093,6 +1231,12 @@
       <c r="H23" s="2" t="n">
         <v>0.002742611404875266</v>
       </c>
+      <c r="I23" s="1" t="n">
+        <v>456.84</v>
+      </c>
+      <c r="J23" s="3" t="n">
+        <v>-0.000393855848759369</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1121,6 +1265,12 @@
       <c r="H24" s="2" t="n">
         <v>0.001345428640013593</v>
       </c>
+      <c r="I24" s="1" t="n">
+        <v>5173.32</v>
+      </c>
+      <c r="J24" s="2" t="n">
+        <v>0.0001411285255548117</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1149,6 +1299,12 @@
       <c r="H25" s="2" t="n">
         <v>0.008008898776418151</v>
       </c>
+      <c r="I25" s="1" t="n">
+        <v>9.054</v>
+      </c>
+      <c r="J25" s="3" t="n">
+        <v>-0.0008828073273007194</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1177,6 +1333,12 @@
       <c r="H26" s="3" t="n">
         <v>-0.03339205637411921</v>
       </c>
+      <c r="I26" s="1" t="n">
+        <v>0.11796</v>
+      </c>
+      <c r="J26" s="3" t="n">
+        <v>-0.02278187391268331</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1205,6 +1367,12 @@
       <c r="H27" s="3" t="n">
         <v>-0.002427184466019319</v>
       </c>
+      <c r="I27" s="1" t="n">
+        <v>0.01217</v>
+      </c>
+      <c r="J27" s="3" t="n">
+        <v>-0.01297648012976483</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1233,6 +1401,12 @@
       <c r="H28" s="2" t="n">
         <v>0.003869969040247595</v>
       </c>
+      <c r="I28" s="1" t="n">
+        <v>1.298</v>
+      </c>
+      <c r="J28" s="2" t="n">
+        <v>0.0007710100231303871</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1261,6 +1435,12 @@
       <c r="H29" s="2" t="n">
         <v>0.02546573235344383</v>
       </c>
+      <c r="I29" s="1" t="n">
+        <v>0.0608</v>
+      </c>
+      <c r="J29" s="2" t="n">
+        <v>0.01333333333333337</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1289,6 +1469,12 @@
       <c r="H30" s="2" t="n">
         <v>0.003952569169960478</v>
       </c>
+      <c r="I30" s="1" t="n">
+        <v>1.523</v>
+      </c>
+      <c r="J30" s="3" t="n">
+        <v>-0.0006561679790026981</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1317,6 +1503,12 @@
       <c r="H31" s="2" t="n">
         <v>0.007916872835230277</v>
       </c>
+      <c r="I31" s="1" t="n">
+        <v>0.002043</v>
+      </c>
+      <c r="J31" s="2" t="n">
+        <v>0.00294550810014724</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1345,6 +1537,12 @@
       <c r="H32" s="2" t="n">
         <v>0.006208095356344679</v>
       </c>
+      <c r="I32" s="1" t="n">
+        <v>0.0403</v>
+      </c>
+      <c r="J32" s="3" t="n">
+        <v>-0.005429417571569545</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1373,6 +1571,12 @@
       <c r="H33" s="2" t="n">
         <v>0.005107252298263538</v>
       </c>
+      <c r="I33" s="1" t="n">
+        <v>0.0982</v>
+      </c>
+      <c r="J33" s="3" t="n">
+        <v>-0.00203252032520331</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1401,6 +1605,12 @@
       <c r="H34" s="2" t="n">
         <v>0.006704980842911803</v>
       </c>
+      <c r="I34" s="1" t="n">
+        <v>0.1049</v>
+      </c>
+      <c r="J34" s="3" t="n">
+        <v>-0.001902949571836401</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1429,6 +1639,12 @@
       <c r="H35" s="3" t="n">
         <v>-0.00882028665931645</v>
       </c>
+      <c r="I35" s="1" t="n">
+        <v>0.009039999999999999</v>
+      </c>
+      <c r="J35" s="2" t="n">
+        <v>0.005561735261401524</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1457,6 +1673,12 @@
       <c r="H36" s="2" t="n">
         <v>0.003925967470555279</v>
       </c>
+      <c r="I36" s="1" t="n">
+        <v>0.3571</v>
+      </c>
+      <c r="J36" s="3" t="n">
+        <v>-0.002513966480446961</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1485,6 +1707,12 @@
       <c r="H37" s="2" t="n">
         <v>0.002411714039621037</v>
       </c>
+      <c r="I37" s="1" t="n">
+        <v>0.005835</v>
+      </c>
+      <c r="J37" s="2" t="n">
+        <v>0.002749613335624596</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1513,6 +1741,12 @@
       <c r="H38" s="2" t="n">
         <v>0.0008731303621593196</v>
       </c>
+      <c r="I38" s="1" t="n">
+        <v>0.26342</v>
+      </c>
+      <c r="J38" s="3" t="n">
+        <v>-0.0008723686705860344</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1541,6 +1775,12 @@
       <c r="H39" s="2" t="n">
         <v>0.004538279400157737</v>
       </c>
+      <c r="I39" s="1" t="n">
+        <v>0.05074</v>
+      </c>
+      <c r="J39" s="3" t="n">
+        <v>-0.00333922608524841</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1569,6 +1809,12 @@
       <c r="H40" s="2" t="n">
         <v>0.01539299822912399</v>
       </c>
+      <c r="I40" s="1" t="n">
+        <v>0.14837</v>
+      </c>
+      <c r="J40" s="3" t="n">
+        <v>-0.004762543600751197</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1597,6 +1843,12 @@
       <c r="H41" s="2" t="n">
         <v>0.008373205741626869</v>
       </c>
+      <c r="I41" s="1" t="n">
+        <v>0.1684</v>
+      </c>
+      <c r="J41" s="3" t="n">
+        <v>-0.001186239620403355</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1625,6 +1877,12 @@
       <c r="H42" s="2" t="n">
         <v>0.008001438460846898</v>
       </c>
+      <c r="I42" s="1" t="n">
+        <v>111.96</v>
+      </c>
+      <c r="J42" s="3" t="n">
+        <v>-0.001427042454513118</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1653,6 +1911,12 @@
       <c r="H43" s="2" t="n">
         <v>0.05156225950438659</v>
       </c>
+      <c r="I43" s="1" t="n">
+        <v>0.6972</v>
+      </c>
+      <c r="J43" s="2" t="n">
+        <v>0.02049180327868854</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1681,6 +1945,12 @@
       <c r="H44" s="2" t="n">
         <v>0.004756677643615169</v>
       </c>
+      <c r="I44" s="1" t="n">
+        <v>54.81</v>
+      </c>
+      <c r="J44" s="3" t="n">
+        <v>-0.002002913328477776</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1709,6 +1979,12 @@
       <c r="H45" s="2" t="n">
         <v>0.01642872240262871</v>
       </c>
+      <c r="I45" s="1" t="n">
+        <v>0.52658</v>
+      </c>
+      <c r="J45" s="3" t="n">
+        <v>-0.004537033536239476</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1737,6 +2013,12 @@
       <c r="H46" s="2" t="n">
         <v>0.002992305500142478</v>
       </c>
+      <c r="I46" s="1" t="n">
+        <v>0.7037</v>
+      </c>
+      <c r="J46" s="3" t="n">
+        <v>-0.0002841312686460832</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1765,6 +2047,12 @@
       <c r="H47" s="2" t="n">
         <v>0.005394297456974147</v>
       </c>
+      <c r="I47" s="1" t="n">
+        <v>3.903</v>
+      </c>
+      <c r="J47" s="3" t="n">
+        <v>-0.00281042411854883</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1793,6 +2081,12 @@
       <c r="H48" s="2" t="n">
         <v>0.008695652173912995</v>
       </c>
+      <c r="I48" s="1" t="n">
+        <v>0.16004</v>
+      </c>
+      <c r="J48" s="3" t="n">
+        <v>-0.0002498750624688422</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1821,6 +2115,12 @@
       <c r="H49" s="2" t="n">
         <v>0.004643449419568863</v>
       </c>
+      <c r="I49" s="1" t="n">
+        <v>0.06039</v>
+      </c>
+      <c r="J49" s="3" t="n">
+        <v>-0.003136348629910906</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1849,6 +2149,12 @@
       <c r="H50" s="2" t="n">
         <v>0.005208333333333483</v>
       </c>
+      <c r="I50" s="1" t="n">
+        <v>0.0387</v>
+      </c>
+      <c r="J50" s="2" t="n">
+        <v>0.002590673575129428</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1877,6 +2183,12 @@
       <c r="H51" s="2" t="n">
         <v>0.001868549056827512</v>
       </c>
+      <c r="I51" s="1" t="n">
+        <v>0.33346</v>
+      </c>
+      <c r="J51" s="3" t="n">
+        <v>-0.01281861511590041</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1905,6 +2217,12 @@
       <c r="H52" s="2" t="n">
         <v>0.01140684410646397</v>
       </c>
+      <c r="I52" s="1" t="n">
+        <v>0.2925</v>
+      </c>
+      <c r="J52" s="3" t="n">
+        <v>-0.0003417634996583885</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1933,6 +2251,12 @@
       <c r="H53" s="2" t="n">
         <v>0.01269841269841271</v>
       </c>
+      <c r="I53" s="1" t="n">
+        <v>0.1587</v>
+      </c>
+      <c r="J53" s="3" t="n">
+        <v>-0.005015673981191193</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1961,6 +2285,12 @@
       <c r="H54" s="2" t="n">
         <v>0.000378709632995934</v>
       </c>
+      <c r="I54" s="1" t="n">
+        <v>0.29082</v>
+      </c>
+      <c r="J54" s="2" t="n">
+        <v>0.0008603778779640981</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1989,6 +2319,12 @@
       <c r="H55" s="2" t="n">
         <v>0.009125368524498098</v>
       </c>
+      <c r="I55" s="1" t="n">
+        <v>0.007163</v>
+      </c>
+      <c r="J55" s="3" t="n">
+        <v>-0.003478018920422906</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2017,6 +2353,12 @@
       <c r="H56" s="2" t="n">
         <v>0.02090090090090092</v>
       </c>
+      <c r="I56" s="1" t="n">
+        <v>0.02854</v>
+      </c>
+      <c r="J56" s="2" t="n">
+        <v>0.007412636780797684</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2045,6 +2387,12 @@
       <c r="H57" s="2" t="n">
         <v>0.005009541984732868</v>
       </c>
+      <c r="I57" s="1" t="n">
+        <v>0.04197</v>
+      </c>
+      <c r="J57" s="3" t="n">
+        <v>-0.003797768810823651</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2073,6 +2421,12 @@
       <c r="H58" s="2" t="n">
         <v>0.01559116500649628</v>
       </c>
+      <c r="I58" s="1" t="n">
+        <v>0.04641</v>
+      </c>
+      <c r="J58" s="3" t="n">
+        <v>-0.0104477611940298</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2101,6 +2455,12 @@
       <c r="H59" s="2" t="n">
         <v>0.007915567282321907</v>
       </c>
+      <c r="I59" s="1" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="J59" s="2" t="n">
+        <v>0.001308900523560211</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2129,6 +2489,12 @@
       <c r="H60" s="2" t="n">
         <v>0.005865102639296203</v>
       </c>
+      <c r="I60" s="1" t="n">
+        <v>0.00343</v>
+      </c>
+      <c r="J60" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2157,6 +2523,12 @@
       <c r="H61" s="2" t="n">
         <v>0.005201560468140411</v>
       </c>
+      <c r="I61" s="1" t="n">
+        <v>0.155</v>
+      </c>
+      <c r="J61" s="2" t="n">
+        <v>0.002587322121604214</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2185,6 +2557,12 @@
       <c r="H62" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="I62" s="1" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="J62" s="3" t="n">
+        <v>-0.003466204506065861</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2213,6 +2591,12 @@
       <c r="H63" s="2" t="n">
         <v>0.00848798733995095</v>
       </c>
+      <c r="I63" s="1" t="n">
+        <v>0.7004</v>
+      </c>
+      <c r="J63" s="3" t="n">
+        <v>-0.0008559201141225877</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2241,6 +2625,12 @@
       <c r="H64" s="2" t="n">
         <v>0.001364256480218282</v>
       </c>
+      <c r="I64" s="1" t="n">
+        <v>2.936</v>
+      </c>
+      <c r="J64" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2269,6 +2659,12 @@
       <c r="H65" s="3" t="n">
         <v>-0.001254705144291186</v>
       </c>
+      <c r="I65" s="1" t="n">
+        <v>0.02391</v>
+      </c>
+      <c r="J65" s="2" t="n">
+        <v>0.00125628140703527</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2297,6 +2693,12 @@
       <c r="H66" s="2" t="n">
         <v>0.006944444444444506</v>
       </c>
+      <c r="I66" s="1" t="n">
+        <v>0.1015</v>
+      </c>
+      <c r="J66" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2325,6 +2727,12 @@
       <c r="H67" s="2" t="n">
         <v>0.003521603684139236</v>
       </c>
+      <c r="I67" s="1" t="n">
+        <v>0.007398</v>
+      </c>
+      <c r="J67" s="3" t="n">
+        <v>-0.001484680793629333</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2353,6 +2761,12 @@
       <c r="H68" s="2" t="n">
         <v>0.008156606851549678</v>
       </c>
+      <c r="I68" s="1" t="n">
+        <v>18.59</v>
+      </c>
+      <c r="J68" s="2" t="n">
+        <v>0.002696871628910502</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2381,6 +2795,12 @@
       <c r="H69" s="2" t="n">
         <v>0.002593072791257534</v>
       </c>
+      <c r="I69" s="1" t="n">
+        <v>0.05363</v>
+      </c>
+      <c r="J69" s="3" t="n">
+        <v>-0.009237021984112331</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2409,6 +2829,12 @@
       <c r="H70" s="2" t="n">
         <v>0.004201680672268912</v>
       </c>
+      <c r="I70" s="1" t="n">
+        <v>0.238</v>
+      </c>
+      <c r="J70" s="3" t="n">
+        <v>-0.004184100418410046</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2437,6 +2863,12 @@
       <c r="H71" s="2" t="n">
         <v>0.01897632311977716</v>
       </c>
+      <c r="I71" s="1" t="n">
+        <v>5.964</v>
+      </c>
+      <c r="J71" s="2" t="n">
+        <v>0.01896463352127126</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2465,6 +2897,12 @@
       <c r="H72" s="3" t="n">
         <v>-0.001924001924001971</v>
       </c>
+      <c r="I72" s="1" t="n">
+        <v>0.002062</v>
+      </c>
+      <c r="J72" s="3" t="n">
+        <v>-0.006265060240963851</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2493,6 +2931,12 @@
       <c r="H73" s="2" t="n">
         <v>0.005969512845112396</v>
       </c>
+      <c r="I73" s="1" t="n">
+        <v>0.9441000000000001</v>
+      </c>
+      <c r="J73" s="2" t="n">
+        <v>0.0004238635159479358</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2521,6 +2965,12 @@
       <c r="H74" s="2" t="n">
         <v>0.003325020781379863</v>
       </c>
+      <c r="I74" s="1" t="n">
+        <v>0.1207</v>
+      </c>
+      <c r="J74" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2549,6 +2999,12 @@
       <c r="H75" s="2" t="n">
         <v>0.0003414523104939806</v>
       </c>
+      <c r="I75" s="1" t="n">
+        <v>350.16</v>
+      </c>
+      <c r="J75" s="3" t="n">
+        <v>-0.003982250540448223</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2577,6 +3033,12 @@
       <c r="H76" s="2" t="n">
         <v>0.004823151125401938</v>
       </c>
+      <c r="I76" s="1" t="n">
+        <v>0.11816</v>
+      </c>
+      <c r="J76" s="3" t="n">
+        <v>-0.004968421052631523</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2605,6 +3067,12 @@
       <c r="H77" s="2" t="n">
         <v>0.01104707012487986</v>
       </c>
+      <c r="I77" s="1" t="n">
+        <v>0.06306</v>
+      </c>
+      <c r="J77" s="3" t="n">
+        <v>-0.001425178147268296</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2633,6 +3101,12 @@
       <c r="H78" s="2" t="n">
         <v>0.005666631027477843</v>
       </c>
+      <c r="I78" s="1" t="n">
+        <v>0.09401</v>
+      </c>
+      <c r="J78" s="3" t="n">
+        <v>-0.0005315755900489939</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2661,6 +3135,12 @@
       <c r="H79" s="3" t="n">
         <v>-0.001913417842621437</v>
       </c>
+      <c r="I79" s="1" t="n">
+        <v>0.4125</v>
+      </c>
+      <c r="J79" s="3" t="n">
+        <v>-0.01150251617541343</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2689,6 +3169,12 @@
       <c r="H80" s="2" t="n">
         <v>0.006868822248282689</v>
       </c>
+      <c r="I80" s="1" t="n">
+        <v>0.006003</v>
+      </c>
+      <c r="J80" s="3" t="n">
+        <v>-0.001164725457570726</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2717,6 +3203,12 @@
       <c r="H81" s="3" t="n">
         <v>-0.003853564547206142</v>
       </c>
+      <c r="I81" s="1" t="n">
+        <v>0.1038</v>
+      </c>
+      <c r="J81" s="2" t="n">
+        <v>0.003868471953578313</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -2745,6 +3237,12 @@
       <c r="H82" s="2" t="n">
         <v>0.008875739644970394</v>
       </c>
+      <c r="I82" s="1" t="n">
+        <v>0.1022</v>
+      </c>
+      <c r="J82" s="3" t="n">
+        <v>-0.0009775171065493926</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -2773,6 +3271,12 @@
       <c r="H83" s="3" t="n">
         <v>-0.01333333333333332</v>
       </c>
+      <c r="I83" s="1" t="n">
+        <v>0.05953</v>
+      </c>
+      <c r="J83" s="2" t="n">
+        <v>0.01830311323982213</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -2801,6 +3305,12 @@
       <c r="H84" s="2" t="n">
         <v>0.006049661399548669</v>
       </c>
+      <c r="I84" s="1" t="n">
+        <v>1.1126</v>
+      </c>
+      <c r="J84" s="3" t="n">
+        <v>-0.00143600789804348</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -2829,6 +3339,12 @@
       <c r="H85" s="3" t="n">
         <v>-0.01985294117647055</v>
       </c>
+      <c r="I85" s="1" t="n">
+        <v>0.01325</v>
+      </c>
+      <c r="J85" s="3" t="n">
+        <v>-0.006001500375093789</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -2857,6 +3373,12 @@
       <c r="H86" s="2" t="n">
         <v>0.001194743130226952</v>
       </c>
+      <c r="I86" s="1" t="n">
+        <v>0.01673</v>
+      </c>
+      <c r="J86" s="3" t="n">
+        <v>-0.001789976133651685</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -2885,6 +3407,12 @@
       <c r="H87" s="2" t="n">
         <v>0.00532300992015491</v>
       </c>
+      <c r="I87" s="1" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="J87" s="3" t="n">
+        <v>-0.00120336943441634</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -2913,6 +3441,12 @@
       <c r="H88" s="3" t="n">
         <v>-0.009497837126198984</v>
       </c>
+      <c r="I88" s="1" t="n">
+        <v>2.1191</v>
+      </c>
+      <c r="J88" s="2" t="n">
+        <v>0.005933732080129202</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -2941,6 +3475,12 @@
       <c r="H89" s="3" t="n">
         <v>-0.01045599767644496</v>
       </c>
+      <c r="I89" s="1" t="n">
+        <v>0.006673</v>
+      </c>
+      <c r="J89" s="3" t="n">
+        <v>-0.02069269151746399</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -2969,6 +3509,12 @@
       <c r="H90" s="2" t="n">
         <v>0.001314060446780524</v>
       </c>
+      <c r="I90" s="1" t="n">
+        <v>15.23</v>
+      </c>
+      <c r="J90" s="3" t="n">
+        <v>-0.0006561679790026107</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -2997,6 +3543,12 @@
       <c r="H91" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="I91" s="1" t="n">
+        <v>0.000222</v>
+      </c>
+      <c r="J91" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3025,6 +3577,12 @@
       <c r="H92" s="3" t="n">
         <v>-0.004904734955668804</v>
       </c>
+      <c r="I92" s="1" t="n">
+        <v>0.05278</v>
+      </c>
+      <c r="J92" s="2" t="n">
+        <v>0.0005687203791469621</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3053,6 +3611,12 @@
       <c r="H93" s="2" t="n">
         <v>0.003724819460281358</v>
       </c>
+      <c r="I93" s="1" t="n">
+        <v>1.3185</v>
+      </c>
+      <c r="J93" s="3" t="n">
+        <v>-0.001438957891548025</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3081,6 +3645,12 @@
       <c r="H94" s="3" t="n">
         <v>-0.008359572078292788</v>
       </c>
+      <c r="I94" s="1" t="n">
+        <v>0.053768</v>
+      </c>
+      <c r="J94" s="3" t="n">
+        <v>-0.001615448890539352</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3109,6 +3679,12 @@
       <c r="H95" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="I95" s="1" t="n">
+        <v>0.2416</v>
+      </c>
+      <c r="J95" s="3" t="n">
+        <v>-0.002888980602558722</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3137,6 +3713,12 @@
       <c r="H96" s="2" t="n">
         <v>0.001291155584247964</v>
       </c>
+      <c r="I96" s="1" t="n">
+        <v>1.0845</v>
+      </c>
+      <c r="J96" s="3" t="n">
+        <v>-0.001105277701022464</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3165,6 +3747,12 @@
       <c r="H97" s="2" t="n">
         <v>0.006648416112632127</v>
       </c>
+      <c r="I97" s="1" t="n">
+        <v>0.2572</v>
+      </c>
+      <c r="J97" s="3" t="n">
+        <v>-0.000777000777000907</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3193,6 +3781,12 @@
       <c r="H98" s="2" t="n">
         <v>0.01081269619811647</v>
       </c>
+      <c r="I98" s="1" t="n">
+        <v>0.5773</v>
+      </c>
+      <c r="J98" s="3" t="n">
+        <v>-0.003968253968253914</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3221,6 +3815,12 @@
       <c r="H99" s="3" t="n">
         <v>-0.01301534210717671</v>
       </c>
+      <c r="I99" s="1" t="n">
+        <v>0.13572</v>
+      </c>
+      <c r="J99" s="3" t="n">
+        <v>-0.0001473405039044662</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3249,6 +3849,12 @@
       <c r="H100" s="2" t="n">
         <v>0.006583278472679355</v>
       </c>
+      <c r="I100" s="1" t="n">
+        <v>0.03046</v>
+      </c>
+      <c r="J100" s="3" t="n">
+        <v>-0.003924133420536251</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3277,6 +3883,12 @@
       <c r="H101" s="3" t="n">
         <v>-0.001955034213098731</v>
       </c>
+      <c r="I101" s="1" t="n">
+        <v>1.023</v>
+      </c>
+      <c r="J101" s="2" t="n">
+        <v>0.001958863858961804</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -3305,6 +3917,12 @@
       <c r="H102" s="2" t="n">
         <v>0.002724795640326864</v>
       </c>
+      <c r="I102" s="1" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="J102" s="3" t="n">
+        <v>-0.003623188405797111</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -3333,6 +3951,12 @@
       <c r="H103" s="2" t="n">
         <v>0.0005096839959226841</v>
       </c>
+      <c r="I103" s="1" t="n">
+        <v>0.01954</v>
+      </c>
+      <c r="J103" s="3" t="n">
+        <v>-0.004584819154355745</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -3361,6 +3985,12 @@
       <c r="H104" s="2" t="n">
         <v>0.004033613445378155</v>
       </c>
+      <c r="I104" s="1" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="J104" s="2" t="n">
+        <v>0.001004352192835659</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -3389,6 +4019,12 @@
       <c r="H105" s="2" t="n">
         <v>0.005931938807368021</v>
       </c>
+      <c r="I105" s="1" t="n">
+        <v>32.25</v>
+      </c>
+      <c r="J105" s="2" t="n">
+        <v>0.0009310986964618603</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -3417,6 +4053,12 @@
       <c r="H106" s="2" t="n">
         <v>0.01096892138939669</v>
       </c>
+      <c r="I106" s="1" t="n">
+        <v>0.1657</v>
+      </c>
+      <c r="J106" s="3" t="n">
+        <v>-0.001205545509343012</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -3445,6 +4087,12 @@
       <c r="H107" s="2" t="n">
         <v>0.003153153153153181</v>
       </c>
+      <c r="I107" s="1" t="n">
+        <v>0.4489</v>
+      </c>
+      <c r="J107" s="2" t="n">
+        <v>0.007858105074090712</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -3473,6 +4121,12 @@
       <c r="H108" s="2" t="n">
         <v>0.005100510051005205</v>
       </c>
+      <c r="I108" s="1" t="n">
+        <v>0.3355</v>
+      </c>
+      <c r="J108" s="2" t="n">
+        <v>0.001492537313432837</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -3501,6 +4155,12 @@
       <c r="H109" s="2" t="n">
         <v>0.007669365146996149</v>
       </c>
+      <c r="I109" s="1" t="n">
+        <v>0.235</v>
+      </c>
+      <c r="J109" s="3" t="n">
+        <v>-0.006342494714587744</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -3529,6 +4189,12 @@
       <c r="H110" s="2" t="n">
         <v>0.01195219123505973</v>
       </c>
+      <c r="I110" s="1" t="n">
+        <v>0.01522</v>
+      </c>
+      <c r="J110" s="3" t="n">
+        <v>-0.00131233595800531</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -3557,6 +4223,12 @@
       <c r="H111" s="2" t="n">
         <v>0.002730748225013717</v>
       </c>
+      <c r="I111" s="1" t="n">
+        <v>1.831</v>
+      </c>
+      <c r="J111" s="3" t="n">
+        <v>-0.002723311546841021</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -3585,6 +4257,12 @@
       <c r="H112" s="2" t="n">
         <v>0.004176455233620476</v>
       </c>
+      <c r="I112" s="1" t="n">
+        <v>0.0384</v>
+      </c>
+      <c r="J112" s="3" t="n">
+        <v>-0.001819599688068641</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -3613,6 +4291,12 @@
       <c r="H113" s="2" t="n">
         <v>0.0006994637444626053</v>
       </c>
+      <c r="I113" s="1" t="n">
+        <v>4.253</v>
+      </c>
+      <c r="J113" s="3" t="n">
+        <v>-0.009086672879776259</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -3641,6 +4325,12 @@
       <c r="H114" s="2" t="n">
         <v>0.002150826724021981</v>
       </c>
+      <c r="I114" s="1" t="n">
+        <v>0.007543</v>
+      </c>
+      <c r="J114" s="2" t="n">
+        <v>0.01180415828303158</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -3669,6 +4359,12 @@
       <c r="H115" s="2" t="n">
         <v>0.008768352365415984</v>
       </c>
+      <c r="I115" s="1" t="n">
+        <v>0.0989</v>
+      </c>
+      <c r="J115" s="3" t="n">
+        <v>-0.0004042854255103939</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -3697,6 +4393,12 @@
       <c r="H116" s="2" t="n">
         <v>0.004366812227074226</v>
       </c>
+      <c r="I116" s="1" t="n">
+        <v>0.08272</v>
+      </c>
+      <c r="J116" s="3" t="n">
+        <v>-0.0009661835748791877</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -3725,6 +4427,12 @@
       <c r="H117" s="2" t="n">
         <v>0.005369127516778491</v>
       </c>
+      <c r="I117" s="1" t="n">
+        <v>0.2992</v>
+      </c>
+      <c r="J117" s="3" t="n">
+        <v>-0.001335113484646048</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -3753,6 +4461,12 @@
       <c r="H118" s="2" t="n">
         <v>0.001318681318681418</v>
       </c>
+      <c r="I118" s="1" t="n">
+        <v>0.02274</v>
+      </c>
+      <c r="J118" s="3" t="n">
+        <v>-0.001755926251097535</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -3781,6 +4495,12 @@
       <c r="H119" s="3" t="n">
         <v>-0.003236245954692559</v>
       </c>
+      <c r="I119" s="1" t="n">
+        <v>0.154</v>
+      </c>
+      <c r="J119" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -3809,6 +4529,12 @@
       <c r="H120" s="3" t="n">
         <v>-0.004553734061930795</v>
       </c>
+      <c r="I120" s="1" t="n">
+        <v>0.004409</v>
+      </c>
+      <c r="J120" s="2" t="n">
+        <v>0.008462946020128021</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -3837,6 +4563,12 @@
       <c r="H121" s="3" t="n">
         <v>-0.002082369273484397</v>
       </c>
+      <c r="I121" s="1" t="n">
+        <v>0.4302</v>
+      </c>
+      <c r="J121" s="3" t="n">
+        <v>-0.002550428935775539</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -3865,6 +4597,12 @@
       <c r="H122" s="2" t="n">
         <v>0.002583979328165377</v>
       </c>
+      <c r="I122" s="1" t="n">
+        <v>0.776</v>
+      </c>
+      <c r="J122" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -3893,6 +4631,12 @@
       <c r="H123" s="2" t="n">
         <v>0.003492433061699589</v>
       </c>
+      <c r="I123" s="1" t="n">
+        <v>0.0863</v>
+      </c>
+      <c r="J123" s="2" t="n">
+        <v>0.001160092807424627</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -3921,6 +4665,12 @@
       <c r="H124" s="2" t="n">
         <v>0.01954397394136813</v>
       </c>
+      <c r="I124" s="1" t="n">
+        <v>0.01252</v>
+      </c>
+      <c r="J124" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -3949,6 +4699,12 @@
       <c r="H125" s="2" t="n">
         <v>0.004626297933586984</v>
       </c>
+      <c r="I125" s="1" t="n">
+        <v>0.09752</v>
+      </c>
+      <c r="J125" s="3" t="n">
+        <v>-0.002046663937781475</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -3977,6 +4733,12 @@
       <c r="H126" s="3" t="n">
         <v>-0.002112378538234112</v>
       </c>
+      <c r="I126" s="1" t="n">
+        <v>0.04701</v>
+      </c>
+      <c r="J126" s="3" t="n">
+        <v>-0.004868755292125193</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -4005,6 +4767,12 @@
       <c r="H127" s="2" t="n">
         <v>0.006369426751592512</v>
       </c>
+      <c r="I127" s="1" t="n">
+        <v>3.17e-05</v>
+      </c>
+      <c r="J127" s="2" t="n">
+        <v>0.003164556962025178</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -4033,6 +4801,12 @@
       <c r="H128" s="2" t="n">
         <v>0.002797202797202877</v>
       </c>
+      <c r="I128" s="1" t="n">
+        <v>0.5723</v>
+      </c>
+      <c r="J128" s="3" t="n">
+        <v>-0.002266387726638717</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -4061,6 +4835,12 @@
       <c r="H129" s="2" t="n">
         <v>0.002132520944402151</v>
       </c>
+      <c r="I129" s="1" t="n">
+        <v>0.06561</v>
+      </c>
+      <c r="J129" s="3" t="n">
+        <v>-0.002735978112175096</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -4089,6 +4869,12 @@
       <c r="H130" s="2" t="n">
         <v>0.001007895178901419</v>
       </c>
+      <c r="I130" s="1" t="n">
+        <v>0.0005978</v>
+      </c>
+      <c r="J130" s="2" t="n">
+        <v>0.003188454438664192</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -4117,6 +4903,12 @@
       <c r="H131" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="I131" s="1" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="J131" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -4145,6 +4937,12 @@
       <c r="H132" s="2" t="n">
         <v>0.009339559706470877</v>
       </c>
+      <c r="I132" s="1" t="n">
+        <v>0.3012</v>
+      </c>
+      <c r="J132" s="3" t="n">
+        <v>-0.004626569729015059</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -4173,6 +4971,12 @@
       <c r="H133" s="3" t="n">
         <v>-0.001499700059988045</v>
       </c>
+      <c r="I133" s="1" t="n">
+        <v>0.03318</v>
+      </c>
+      <c r="J133" s="3" t="n">
+        <v>-0.003304295584259507</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -4201,6 +5005,12 @@
       <c r="H134" s="2" t="n">
         <v>0.00130181569030487</v>
       </c>
+      <c r="I134" s="1" t="n">
+        <v>0.14559</v>
+      </c>
+      <c r="J134" s="3" t="n">
+        <v>-0.003763514438209901</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -4229,6 +5039,12 @@
       <c r="H135" s="2" t="n">
         <v>0.006809669731018005</v>
       </c>
+      <c r="I135" s="1" t="n">
+        <v>0.02962</v>
+      </c>
+      <c r="J135" s="2" t="n">
+        <v>0.001690902942171168</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -4257,6 +5073,12 @@
       <c r="H136" s="2" t="n">
         <v>0.01036825169824822</v>
       </c>
+      <c r="I136" s="1" t="n">
+        <v>28.13</v>
+      </c>
+      <c r="J136" s="3" t="n">
+        <v>-0.004600141542816793</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -4285,6 +5107,12 @@
       <c r="H137" s="2" t="n">
         <v>0.006111894687353101</v>
       </c>
+      <c r="I137" s="1" t="n">
+        <v>0.0004285</v>
+      </c>
+      <c r="J137" s="2" t="n">
+        <v>0.001168224299065449</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -4313,6 +5141,12 @@
       <c r="H138" s="2" t="n">
         <v>0.01185461956521734</v>
       </c>
+      <c r="I138" s="1" t="n">
+        <v>0.029084</v>
+      </c>
+      <c r="J138" s="3" t="n">
+        <v>-0.0236664540602236</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -4341,6 +5175,12 @@
       <c r="H139" s="3" t="n">
         <v>-0.002702140927042157</v>
       </c>
+      <c r="I139" s="1" t="n">
+        <v>0.09603</v>
+      </c>
+      <c r="J139" s="2" t="n">
+        <v>0.0007294706127553212</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -4369,6 +5209,12 @@
       <c r="H140" s="2" t="n">
         <v>0.02208380520951295</v>
       </c>
+      <c r="I140" s="1" t="n">
+        <v>0.358</v>
+      </c>
+      <c r="J140" s="3" t="n">
+        <v>-0.008310249307479232</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -4397,6 +5243,12 @@
       <c r="H141" s="2" t="n">
         <v>0.01599107474897731</v>
       </c>
+      <c r="I141" s="1" t="n">
+        <v>0.02721</v>
+      </c>
+      <c r="J141" s="3" t="n">
+        <v>-0.004026354319180051</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -4425,6 +5277,12 @@
       <c r="H142" s="2" t="n">
         <v>0.004055468341182689</v>
       </c>
+      <c r="I142" s="1" t="n">
+        <v>0.07691000000000001</v>
+      </c>
+      <c r="J142" s="2" t="n">
+        <v>0.002084690553746024</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -4453,6 +5311,12 @@
       <c r="H143" s="2" t="n">
         <v>0.006248579868211712</v>
       </c>
+      <c r="I143" s="1" t="n">
+        <v>0.08821</v>
+      </c>
+      <c r="J143" s="3" t="n">
+        <v>-0.004064581686801391</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -4481,6 +5345,12 @@
       <c r="H144" s="3" t="n">
         <v>-0.003954522985664864</v>
       </c>
+      <c r="I144" s="1" t="n">
+        <v>0.02024</v>
+      </c>
+      <c r="J144" s="2" t="n">
+        <v>0.004466501240694779</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -4509,6 +5379,12 @@
       <c r="H145" s="2" t="n">
         <v>0.0007004027315706245</v>
       </c>
+      <c r="I145" s="1" t="n">
+        <v>0.11388</v>
+      </c>
+      <c r="J145" s="3" t="n">
+        <v>-0.003674540682414731</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -4537,6 +5413,12 @@
       <c r="H146" s="2" t="n">
         <v>0.009302325581395432</v>
       </c>
+      <c r="I146" s="1" t="n">
+        <v>0.3034</v>
+      </c>
+      <c r="J146" s="3" t="n">
+        <v>-0.001316655694535917</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -4565,6 +5447,12 @@
       <c r="H147" s="3" t="n">
         <v>-0.008196721311475417</v>
       </c>
+      <c r="I147" s="1" t="n">
+        <v>0.122</v>
+      </c>
+      <c r="J147" s="2" t="n">
+        <v>0.008264462809917363</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -4593,6 +5481,12 @@
       <c r="H148" s="3" t="n">
         <v>-0.001533585522952608</v>
       </c>
+      <c r="I148" s="1" t="n">
+        <v>1.9456</v>
+      </c>
+      <c r="J148" s="3" t="n">
+        <v>-0.003891050583657614</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -4621,6 +5515,12 @@
       <c r="H149" s="2" t="n">
         <v>0.0004837149306675629</v>
       </c>
+      <c r="I149" s="1" t="n">
+        <v>0.06184</v>
+      </c>
+      <c r="J149" s="3" t="n">
+        <v>-0.00338436744560841</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -4649,6 +5549,12 @@
       <c r="H150" s="3" t="n">
         <v>-0.01084337349397588</v>
       </c>
+      <c r="I150" s="1" t="n">
+        <v>0.1647</v>
+      </c>
+      <c r="J150" s="2" t="n">
+        <v>0.003045066991473815</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -4677,6 +5583,12 @@
       <c r="H151" s="2" t="n">
         <v>0.007236544549977521</v>
       </c>
+      <c r="I151" s="1" t="n">
+        <v>6.674e-05</v>
+      </c>
+      <c r="J151" s="3" t="n">
+        <v>-0.00104774734321216</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -4705,6 +5617,12 @@
       <c r="H152" s="2" t="n">
         <v>0.005464480874316954</v>
       </c>
+      <c r="I152" s="1" t="n">
+        <v>0.01467</v>
+      </c>
+      <c r="J152" s="3" t="n">
+        <v>-0.003396739130434762</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -4733,6 +5651,12 @@
       <c r="H153" s="2" t="n">
         <v>0.007232401157184057</v>
       </c>
+      <c r="I153" s="1" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="J153" s="3" t="n">
+        <v>-0.00287218764959299</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -4761,6 +5685,12 @@
       <c r="H154" s="2" t="n">
         <v>0.002685464921114533</v>
       </c>
+      <c r="I154" s="1" t="n">
+        <v>0.0005974</v>
+      </c>
+      <c r="J154" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -4789,6 +5719,12 @@
       <c r="H155" s="2" t="n">
         <v>0.003745318352059859</v>
       </c>
+      <c r="I155" s="1" t="n">
+        <v>0.0401</v>
+      </c>
+      <c r="J155" s="3" t="n">
+        <v>-0.002487562189054797</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -4817,6 +5753,12 @@
       <c r="H156" s="2" t="n">
         <v>0.003719447396386855</v>
       </c>
+      <c r="I156" s="1" t="n">
+        <v>0.01887</v>
+      </c>
+      <c r="J156" s="3" t="n">
+        <v>-0.001058761249338231</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -4845,6 +5787,12 @@
       <c r="H157" s="2" t="n">
         <v>0.0001147842056932521</v>
       </c>
+      <c r="I157" s="1" t="n">
+        <v>0.08678</v>
+      </c>
+      <c r="J157" s="3" t="n">
+        <v>-0.004016986112705189</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -4873,6 +5821,12 @@
       <c r="H158" s="2" t="n">
         <v>0.008672285330401843</v>
       </c>
+      <c r="I158" s="1" t="n">
+        <v>0.008288</v>
+      </c>
+      <c r="J158" s="2" t="n">
+        <v>0.003632840881569449</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -4901,6 +5855,12 @@
       <c r="H159" s="2" t="n">
         <v>0.003218020917135964</v>
       </c>
+      <c r="I159" s="1" t="n">
+        <v>2.494</v>
+      </c>
+      <c r="J159" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -4929,6 +5889,12 @@
       <c r="H160" s="2" t="n">
         <v>0.005501847048652139</v>
       </c>
+      <c r="I160" s="1" t="n">
+        <v>1.2791</v>
+      </c>
+      <c r="J160" s="3" t="n">
+        <v>-0.0001563354959745173</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -4957,6 +5923,12 @@
       <c r="H161" s="3" t="n">
         <v>-0.003401360544217685</v>
       </c>
+      <c r="I161" s="1" t="n">
+        <v>0.007545</v>
+      </c>
+      <c r="J161" s="3" t="n">
+        <v>-0.009582567603045438</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -4985,6 +5957,12 @@
       <c r="H162" s="2" t="n">
         <v>0.01693227091633475</v>
       </c>
+      <c r="I162" s="1" t="n">
+        <v>0.00414</v>
+      </c>
+      <c r="J162" s="2" t="n">
+        <v>0.01371204701273252</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -5013,6 +5991,12 @@
       <c r="H163" s="2" t="n">
         <v>0.001042752867570416</v>
       </c>
+      <c r="I163" s="1" t="n">
+        <v>0.0959</v>
+      </c>
+      <c r="J163" s="3" t="n">
+        <v>-0.001041666666666697</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -5041,6 +6025,12 @@
       <c r="H164" s="2" t="n">
         <v>0.004218181818181838</v>
       </c>
+      <c r="I164" s="1" t="n">
+        <v>1.3783</v>
+      </c>
+      <c r="J164" s="3" t="n">
+        <v>-0.001810544611819197</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -5069,6 +6059,12 @@
       <c r="H165" s="2" t="n">
         <v>0.005094931196655745</v>
       </c>
+      <c r="I165" s="1" t="n">
+        <v>0.023226</v>
+      </c>
+      <c r="J165" s="2" t="n">
+        <v>0.006282223473852922</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -5097,6 +6093,12 @@
       <c r="H166" s="2" t="n">
         <v>0.004988913525498912</v>
       </c>
+      <c r="I166" s="1" t="n">
+        <v>0.005218</v>
+      </c>
+      <c r="J166" s="3" t="n">
+        <v>-0.04063246920389774</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -5125,6 +6127,12 @@
       <c r="H167" s="3" t="n">
         <v>-0.0001526018617428659</v>
       </c>
+      <c r="I167" s="1" t="n">
+        <v>0.06560000000000001</v>
+      </c>
+      <c r="J167" s="2" t="n">
+        <v>0.001221001221001383</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -5153,6 +6161,12 @@
       <c r="H168" s="2" t="n">
         <v>0.001055966209081193</v>
       </c>
+      <c r="I168" s="1" t="n">
+        <v>0.09470000000000001</v>
+      </c>
+      <c r="J168" s="3" t="n">
+        <v>-0.001054852320674989</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -5181,6 +6195,12 @@
       <c r="H169" s="3" t="n">
         <v>-0.0007808433107756961</v>
       </c>
+      <c r="I169" s="1" t="n">
+        <v>0.03833</v>
+      </c>
+      <c r="J169" s="3" t="n">
+        <v>-0.001562907007033018</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -5209,6 +6229,12 @@
       <c r="H170" s="2" t="n">
         <v>0.004233102864399554</v>
       </c>
+      <c r="I170" s="1" t="n">
+        <v>0.007115</v>
+      </c>
+      <c r="J170" s="3" t="n">
+        <v>-0.0002810172825629149</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -5237,6 +6263,12 @@
       <c r="H171" s="2" t="n">
         <v>0.008577343981070729</v>
       </c>
+      <c r="I171" s="1" t="n">
+        <v>0.3417</v>
+      </c>
+      <c r="J171" s="2" t="n">
+        <v>0.002052785923753602</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -5265,6 +6297,12 @@
       <c r="H172" s="2" t="n">
         <v>0.004993526909561704</v>
       </c>
+      <c r="I172" s="1" t="n">
+        <v>5.439</v>
+      </c>
+      <c r="J172" s="2" t="n">
+        <v>0.0009201324990798478</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -5293,6 +6331,12 @@
       <c r="H173" s="2" t="n">
         <v>0.006855373728438694</v>
       </c>
+      <c r="I173" s="1" t="n">
+        <v>0.0455</v>
+      </c>
+      <c r="J173" s="3" t="n">
+        <v>-0.0006589062156820173</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -5321,6 +6365,12 @@
       <c r="H174" s="2" t="n">
         <v>0.001277139208173728</v>
       </c>
+      <c r="I174" s="1" t="n">
+        <v>0.03912</v>
+      </c>
+      <c r="J174" s="3" t="n">
+        <v>-0.002040816326530529</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -5349,6 +6399,12 @@
       <c r="H175" s="2" t="n">
         <v>0.009384587619563249</v>
       </c>
+      <c r="I175" s="1" t="n">
+        <v>0.005563</v>
+      </c>
+      <c r="J175" s="3" t="n">
+        <v>-0.005363847666726202</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -5377,6 +6433,12 @@
       <c r="H176" s="2" t="n">
         <v>0.005291005291005305</v>
       </c>
+      <c r="I176" s="1" t="n">
+        <v>0.00759</v>
+      </c>
+      <c r="J176" s="3" t="n">
+        <v>-0.001315789473684157</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -5405,6 +6467,12 @@
       <c r="H177" s="2" t="n">
         <v>0.01036866359447005</v>
       </c>
+      <c r="I177" s="1" t="n">
+        <v>1.735</v>
+      </c>
+      <c r="J177" s="3" t="n">
+        <v>-0.01083238312428729</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -5433,6 +6501,12 @@
       <c r="H178" s="2" t="n">
         <v>0.006293347033136447</v>
       </c>
+      <c r="I178" s="1" t="n">
+        <v>15.663</v>
+      </c>
+      <c r="J178" s="3" t="n">
+        <v>-0.0004467134652201451</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -5461,6 +6535,12 @@
       <c r="H179" s="2" t="n">
         <v>0.003236245954692559</v>
       </c>
+      <c r="I179" s="1" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="J179" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -5489,6 +6569,12 @@
       <c r="H180" s="2" t="n">
         <v>0.0009564293304993928</v>
       </c>
+      <c r="I180" s="1" t="n">
+        <v>0.09571</v>
+      </c>
+      <c r="J180" s="2" t="n">
+        <v>0.01613759422444004</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -5517,6 +6603,12 @@
       <c r="H181" s="2" t="n">
         <v>0.002672367717797971</v>
       </c>
+      <c r="I181" s="1" t="n">
+        <v>0.1874</v>
+      </c>
+      <c r="J181" s="3" t="n">
+        <v>-0.001066098081023337</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -5545,6 +6637,12 @@
       <c r="H182" s="3" t="n">
         <v>-0.0005031024652021171</v>
       </c>
+      <c r="I182" s="1" t="n">
+        <v>0.05939</v>
+      </c>
+      <c r="J182" s="3" t="n">
+        <v>-0.003523489932885937</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -5573,6 +6671,12 @@
       <c r="H183" s="3" t="n">
         <v>-0.001652892561983404</v>
       </c>
+      <c r="I183" s="1" t="n">
+        <v>0.01207</v>
+      </c>
+      <c r="J183" s="3" t="n">
+        <v>-0.0008278145695363901</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -5601,6 +6705,12 @@
       <c r="H184" s="2" t="n">
         <v>0.005607476635514115</v>
       </c>
+      <c r="I184" s="1" t="n">
+        <v>0.02142</v>
+      </c>
+      <c r="J184" s="3" t="n">
+        <v>-0.004646840148698856</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -5629,6 +6739,12 @@
       <c r="H185" s="2" t="n">
         <v>0.005540166204986155</v>
       </c>
+      <c r="I185" s="1" t="n">
+        <v>0.363</v>
+      </c>
+      <c r="J185" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -5657,6 +6773,12 @@
       <c r="H186" s="3" t="n">
         <v>-0.001046983379138882</v>
       </c>
+      <c r="I186" s="1" t="n">
+        <v>0.007637</v>
+      </c>
+      <c r="J186" s="2" t="n">
+        <v>0.0005240403511069912</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -5685,6 +6807,12 @@
       <c r="H187" s="2" t="n">
         <v>0.004444444444444366</v>
       </c>
+      <c r="I187" s="1" t="n">
+        <v>0.2702</v>
+      </c>
+      <c r="J187" s="3" t="n">
+        <v>-0.003687315634218293</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -5713,6 +6841,12 @@
       <c r="H188" s="2" t="n">
         <v>0.006353761016601717</v>
       </c>
+      <c r="I188" s="1" t="n">
+        <v>0.04909</v>
+      </c>
+      <c r="J188" s="3" t="n">
+        <v>-0.0002036659877799618</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -5741,6 +6875,12 @@
       <c r="H189" s="2" t="n">
         <v>0.007078254030672308</v>
       </c>
+      <c r="I189" s="1" t="n">
+        <v>0.2559</v>
+      </c>
+      <c r="J189" s="3" t="n">
+        <v>-0.0007809449433814057</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -5769,6 +6909,12 @@
       <c r="H190" s="2" t="n">
         <v>0.002843433445885989</v>
       </c>
+      <c r="I190" s="1" t="n">
+        <v>0.5647</v>
+      </c>
+      <c r="J190" s="2" t="n">
+        <v>0.0007088428141058939</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -5797,6 +6943,12 @@
       <c r="H191" s="2" t="n">
         <v>0.005496335776149295</v>
       </c>
+      <c r="I191" s="1" t="n">
+        <v>6.029</v>
+      </c>
+      <c r="J191" s="3" t="n">
+        <v>-0.001325161504058308</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -5825,6 +6977,12 @@
       <c r="H192" s="3" t="n">
         <v>-0.0002862868594331205</v>
       </c>
+      <c r="I192" s="1" t="n">
+        <v>0.3497</v>
+      </c>
+      <c r="J192" s="2" t="n">
+        <v>0.001431844215349371</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -5853,6 +7011,12 @@
       <c r="H193" s="2" t="n">
         <v>0.001560062402495928</v>
       </c>
+      <c r="I193" s="1" t="n">
+        <v>0.06419999999999999</v>
+      </c>
+      <c r="J193" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -5881,6 +7045,12 @@
       <c r="H194" s="2" t="n">
         <v>0.009866511897852584</v>
       </c>
+      <c r="I194" s="1" t="n">
+        <v>0.01743</v>
+      </c>
+      <c r="J194" s="2" t="n">
+        <v>0.001724137931034612</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -5909,6 +7079,12 @@
       <c r="H195" s="2" t="n">
         <v>0.003466204506065942</v>
       </c>
+      <c r="I195" s="1" t="n">
+        <v>0.0008716</v>
+      </c>
+      <c r="J195" s="2" t="n">
+        <v>0.003569372481289604</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -5937,6 +7113,12 @@
       <c r="H196" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="I196" s="1" t="n">
+        <v>0.001019</v>
+      </c>
+      <c r="J196" s="2" t="n">
+        <v>0.0009823182711197601</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -5965,6 +7147,12 @@
       <c r="H197" s="2" t="n">
         <v>0.00497203231821002</v>
       </c>
+      <c r="I197" s="1" t="n">
+        <v>0.0001611</v>
+      </c>
+      <c r="J197" s="3" t="n">
+        <v>-0.00371057513914649</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -5993,6 +7181,12 @@
       <c r="H198" s="2" t="n">
         <v>0.003005085529357557</v>
       </c>
+      <c r="I198" s="1" t="n">
+        <v>4.335</v>
+      </c>
+      <c r="J198" s="3" t="n">
+        <v>-0.0009218713989399509</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -6021,6 +7215,12 @@
       <c r="H199" s="2" t="n">
         <v>0.008014796547472228</v>
       </c>
+      <c r="I199" s="1" t="n">
+        <v>0.1627</v>
+      </c>
+      <c r="J199" s="3" t="n">
+        <v>-0.004892966360856239</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -6049,6 +7249,12 @@
       <c r="H200" s="3" t="n">
         <v>-0.001014370245139464</v>
       </c>
+      <c r="I200" s="1" t="n">
+        <v>0.023819</v>
+      </c>
+      <c r="J200" s="2" t="n">
+        <v>0.007742426806566218</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -6077,6 +7283,12 @@
       <c r="H201" s="2" t="n">
         <v>0.01597340468661315</v>
       </c>
+      <c r="I201" s="1" t="n">
+        <v>0.12504</v>
+      </c>
+      <c r="J201" s="3" t="n">
+        <v>-0.002075019952114784</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -6105,6 +7317,12 @@
       <c r="H202" s="3" t="n">
         <v>-0.001447178002894422</v>
       </c>
+      <c r="I202" s="1" t="n">
+        <v>0.01378</v>
+      </c>
+      <c r="J202" s="3" t="n">
+        <v>-0.001449275362318782</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -6133,6 +7351,12 @@
       <c r="H203" s="3" t="n">
         <v>-0.004139274409544764</v>
       </c>
+      <c r="I203" s="1" t="n">
+        <v>0.04077</v>
+      </c>
+      <c r="J203" s="3" t="n">
+        <v>-0.003178484107579418</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -6161,6 +7385,12 @@
       <c r="H204" s="2" t="n">
         <v>0.003903200624512076</v>
       </c>
+      <c r="I204" s="1" t="n">
+        <v>0.02571</v>
+      </c>
+      <c r="J204" s="3" t="n">
+        <v>-0.0003888024883359095</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -6189,6 +7419,12 @@
       <c r="H205" s="2" t="n">
         <v>0.00536881419234366</v>
       </c>
+      <c r="I205" s="1" t="n">
+        <v>0.4305</v>
+      </c>
+      <c r="J205" s="3" t="n">
+        <v>-0.000464360343626732</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -6217,6 +7453,12 @@
       <c r="H206" s="2" t="n">
         <v>0.003498032356799309</v>
       </c>
+      <c r="I206" s="1" t="n">
+        <v>0.02285</v>
+      </c>
+      <c r="J206" s="3" t="n">
+        <v>-0.004357298474945658</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -6245,6 +7487,12 @@
       <c r="H207" s="2" t="n">
         <v>0.003853564547206169</v>
       </c>
+      <c r="I207" s="1" t="n">
+        <v>4.164</v>
+      </c>
+      <c r="J207" s="3" t="n">
+        <v>-0.0009596928982726602</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -6273,6 +7521,12 @@
       <c r="H208" s="3" t="n">
         <v>-0.0009459459459459543</v>
       </c>
+      <c r="I208" s="1" t="n">
+        <v>0.07392</v>
+      </c>
+      <c r="J208" s="3" t="n">
+        <v>-0.0001352630867035861</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -6301,6 +7555,12 @@
       <c r="H209" s="2" t="n">
         <v>0.001661129568106327</v>
       </c>
+      <c r="I209" s="1" t="n">
+        <v>0.04215</v>
+      </c>
+      <c r="J209" s="3" t="n">
+        <v>-0.001421464108031214</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -6329,6 +7589,12 @@
       <c r="H210" s="2" t="n">
         <v>0.002724795640326978</v>
       </c>
+      <c r="I210" s="1" t="n">
+        <v>0.184</v>
+      </c>
+      <c r="J210" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -6357,6 +7623,12 @@
       <c r="H211" s="2" t="n">
         <v>0.001255230125523107</v>
       </c>
+      <c r="I211" s="1" t="n">
+        <v>0.2389</v>
+      </c>
+      <c r="J211" s="3" t="n">
+        <v>-0.001671541997492735</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -6385,6 +7657,12 @@
       <c r="H212" s="2" t="n">
         <v>0.001442307692307884</v>
       </c>
+      <c r="I212" s="1" t="n">
+        <v>0.002077</v>
+      </c>
+      <c r="J212" s="3" t="n">
+        <v>-0.002880460873739972</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -6413,6 +7691,12 @@
       <c r="H213" s="2" t="n">
         <v>0.005411255411255416</v>
       </c>
+      <c r="I213" s="1" t="n">
+        <v>0.929</v>
+      </c>
+      <c r="J213" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -6441,6 +7725,12 @@
       <c r="H214" s="2" t="n">
         <v>0.005627857896588095</v>
       </c>
+      <c r="I214" s="1" t="n">
+        <v>0.005698</v>
+      </c>
+      <c r="J214" s="3" t="n">
+        <v>-0.003497726477789446</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -6469,6 +7759,12 @@
       <c r="H215" s="2" t="n">
         <v>0.002014652014651996</v>
       </c>
+      <c r="I215" s="1" t="n">
+        <v>0.05465</v>
+      </c>
+      <c r="J215" s="3" t="n">
+        <v>-0.001096691646865372</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -6497,6 +7793,12 @@
       <c r="H216" s="2" t="n">
         <v>0.003169572107765323</v>
       </c>
+      <c r="I216" s="1" t="n">
+        <v>0.06320000000000001</v>
+      </c>
+      <c r="J216" s="3" t="n">
+        <v>-0.001579778830963491</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -6525,6 +7827,12 @@
       <c r="H217" s="2" t="n">
         <v>0.004343105320303991</v>
       </c>
+      <c r="I217" s="1" t="n">
+        <v>0.09279999999999999</v>
+      </c>
+      <c r="J217" s="2" t="n">
+        <v>0.003243243243243186</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -6553,6 +7861,12 @@
       <c r="H218" s="2" t="n">
         <v>0.001745010360999149</v>
       </c>
+      <c r="I218" s="1" t="n">
+        <v>0.27502</v>
+      </c>
+      <c r="J218" s="3" t="n">
+        <v>-0.001923425875521794</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -6581,6 +7895,12 @@
       <c r="H219" s="2" t="n">
         <v>0.004638218923933289</v>
       </c>
+      <c r="I219" s="1" t="n">
+        <v>0.003244</v>
+      </c>
+      <c r="J219" s="3" t="n">
+        <v>-0.001538935056940668</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -6609,6 +7929,12 @@
       <c r="H220" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="I220" s="1" t="n">
+        <v>0.999374</v>
+      </c>
+      <c r="J220" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -6637,6 +7963,12 @@
       <c r="H221" s="2" t="n">
         <v>0.009401932619482873</v>
       </c>
+      <c r="I221" s="1" t="n">
+        <v>0.03866</v>
+      </c>
+      <c r="J221" s="2" t="n">
+        <v>0.0002587322121604932</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -6665,6 +7997,12 @@
       <c r="H222" s="2" t="n">
         <v>0.006063230835859733</v>
       </c>
+      <c r="I222" s="1" t="n">
+        <v>0.04648</v>
+      </c>
+      <c r="J222" s="2" t="n">
+        <v>0.0004304778303917173</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -6693,6 +8031,12 @@
       <c r="H223" s="2" t="n">
         <v>0.001910219675262577</v>
       </c>
+      <c r="I223" s="1" t="n">
+        <v>0.1048</v>
+      </c>
+      <c r="J223" s="3" t="n">
+        <v>-0.0009532888465203907</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -6721,6 +8065,12 @@
       <c r="H224" s="3" t="n">
         <v>-0.002568713074749496</v>
       </c>
+      <c r="I224" s="1" t="n">
+        <v>3.874</v>
+      </c>
+      <c r="J224" s="3" t="n">
+        <v>-0.002317795518928637</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -6749,6 +8099,12 @@
       <c r="H225" s="2" t="n">
         <v>0.007312813796114386</v>
       </c>
+      <c r="I225" s="1" t="n">
+        <v>0.0009210000000000001</v>
+      </c>
+      <c r="J225" s="3" t="n">
+        <v>-0.002058727922851871</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -6777,6 +8133,12 @@
       <c r="H226" s="3" t="n">
         <v>-0.000705052878966016</v>
       </c>
+      <c r="I226" s="1" t="n">
+        <v>0.008496999999999999</v>
+      </c>
+      <c r="J226" s="3" t="n">
+        <v>-0.000823142050799631</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -6805,6 +8167,12 @@
       <c r="H227" s="2" t="n">
         <v>0.001936108422071557</v>
       </c>
+      <c r="I227" s="1" t="n">
+        <v>0.04129</v>
+      </c>
+      <c r="J227" s="3" t="n">
+        <v>-0.00265700483091785</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -6833,6 +8201,12 @@
       <c r="H228" s="2" t="n">
         <v>0.003384094754653188</v>
       </c>
+      <c r="I228" s="1" t="n">
+        <v>0.03553</v>
+      </c>
+      <c r="J228" s="3" t="n">
+        <v>-0.001405283867341243</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -6861,6 +8235,12 @@
       <c r="H229" s="2" t="n">
         <v>0.006049960967993711</v>
       </c>
+      <c r="I229" s="1" t="n">
+        <v>0.05146</v>
+      </c>
+      <c r="J229" s="3" t="n">
+        <v>-0.001745877788554797</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -6889,6 +8269,12 @@
       <c r="H230" s="3" t="n">
         <v>-0.001160092807424622</v>
       </c>
+      <c r="I230" s="1" t="n">
+        <v>0.001714</v>
+      </c>
+      <c r="J230" s="3" t="n">
+        <v>-0.004645760743321706</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -6917,6 +8303,12 @@
       <c r="H231" s="3" t="n">
         <v>-0.005297473512632362</v>
       </c>
+      <c r="I231" s="1" t="n">
+        <v>0.04862</v>
+      </c>
+      <c r="J231" s="3" t="n">
+        <v>-0.004096681687832972</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -6945,6 +8337,12 @@
       <c r="H232" s="2" t="n">
         <v>0.01159554730983304</v>
       </c>
+      <c r="I232" s="1" t="n">
+        <v>0.02178</v>
+      </c>
+      <c r="J232" s="3" t="n">
+        <v>-0.001375515818431856</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -6973,6 +8371,12 @@
       <c r="H233" s="2" t="n">
         <v>0.001715560130382611</v>
       </c>
+      <c r="I233" s="1" t="n">
+        <v>0.0005843000000000001</v>
+      </c>
+      <c r="J233" s="2" t="n">
+        <v>0.0006850488097277097</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -7001,6 +8405,12 @@
       <c r="H234" s="3" t="n">
         <v>-0.004523670891745345</v>
       </c>
+      <c r="I234" s="1" t="n">
+        <v>0.22118</v>
+      </c>
+      <c r="J234" s="3" t="n">
+        <v>-0.004859173940430241</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -7029,6 +8439,12 @@
       <c r="H235" s="2" t="n">
         <v>0.005813953488372109</v>
       </c>
+      <c r="I235" s="1" t="n">
+        <v>0.01391</v>
+      </c>
+      <c r="J235" s="2" t="n">
+        <v>0.005057803468208137</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -7057,6 +8473,12 @@
       <c r="H236" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="I236" s="1" t="n">
+        <v>0.0413</v>
+      </c>
+      <c r="J236" s="2" t="n">
+        <v>0.002427184466019487</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -7085,6 +8507,12 @@
       <c r="H237" s="2" t="n">
         <v>0.002398081534772085</v>
       </c>
+      <c r="I237" s="1" t="n">
+        <v>0.00418</v>
+      </c>
+      <c r="J237" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -7113,6 +8541,12 @@
       <c r="H238" s="3" t="n">
         <v>-0.004000000000000115</v>
       </c>
+      <c r="I238" s="1" t="n">
+        <v>0.0248</v>
+      </c>
+      <c r="J238" s="3" t="n">
+        <v>-0.004016064257028089</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -7141,6 +8575,12 @@
       <c r="H239" s="2" t="n">
         <v>0.003369272237196745</v>
       </c>
+      <c r="I239" s="1" t="n">
+        <v>0.01486</v>
+      </c>
+      <c r="J239" s="3" t="n">
+        <v>-0.002014775016789826</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -7169,6 +8609,12 @@
       <c r="H240" s="2" t="n">
         <v>0.003842213114754053</v>
       </c>
+      <c r="I240" s="1" t="n">
+        <v>0.0003917</v>
+      </c>
+      <c r="J240" s="3" t="n">
+        <v>-0.0005103342689461722</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -7197,6 +8643,12 @@
       <c r="H241" s="2" t="n">
         <v>0.006060606060606023</v>
       </c>
+      <c r="I241" s="1" t="n">
+        <v>0.2662</v>
+      </c>
+      <c r="J241" s="2" t="n">
+        <v>0.002259036144578273</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -7225,6 +8677,12 @@
       <c r="H242" s="2" t="n">
         <v>0.01311605723370417</v>
       </c>
+      <c r="I242" s="1" t="n">
+        <v>0.07613</v>
+      </c>
+      <c r="J242" s="3" t="n">
+        <v>-0.004446188047600276</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -7253,6 +8711,12 @@
       <c r="H243" s="2" t="n">
         <v>0.006649616368286351</v>
       </c>
+      <c r="I243" s="1" t="n">
+        <v>0.01971</v>
+      </c>
+      <c r="J243" s="2" t="n">
+        <v>0.001524390243902377</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -7281,6 +8745,12 @@
       <c r="H244" s="3" t="n">
         <v>-0.006572982774252008</v>
       </c>
+      <c r="I244" s="1" t="n">
+        <v>0.08769</v>
+      </c>
+      <c r="J244" s="2" t="n">
+        <v>0.0003422313483915383</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -7309,6 +8779,12 @@
       <c r="H245" s="3" t="n">
         <v>-0.008743927827897409</v>
       </c>
+      <c r="I245" s="1" t="n">
+        <v>1.4299</v>
+      </c>
+      <c r="J245" s="2" t="n">
+        <v>0.001050126015121854</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -7337,6 +8813,12 @@
       <c r="H246" s="2" t="n">
         <v>0.00167597765363141</v>
       </c>
+      <c r="I246" s="1" t="n">
+        <v>0.01783</v>
+      </c>
+      <c r="J246" s="3" t="n">
+        <v>-0.005577244841048682</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -7365,6 +8847,12 @@
       <c r="H247" s="2" t="n">
         <v>0.004103967168262671</v>
       </c>
+      <c r="I247" s="1" t="n">
+        <v>0.006599</v>
+      </c>
+      <c r="J247" s="3" t="n">
+        <v>-0.001059642749016055</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -7393,6 +8881,12 @@
       <c r="H248" s="2" t="n">
         <v>0.02896416298478155</v>
       </c>
+      <c r="I248" s="1" t="n">
+        <v>0.004242</v>
+      </c>
+      <c r="J248" s="2" t="n">
+        <v>0.01192748091603046</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -7421,6 +8915,12 @@
       <c r="H249" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="I249" s="1" t="n">
+        <v>0.1095</v>
+      </c>
+      <c r="J249" s="3" t="n">
+        <v>-0.0009124087591241137</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -7449,6 +8949,12 @@
       <c r="H250" s="2" t="n">
         <v>0.002636976267213589</v>
       </c>
+      <c r="I250" s="1" t="n">
+        <v>0.03422</v>
+      </c>
+      <c r="J250" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -7477,6 +8983,12 @@
       <c r="H251" s="2" t="n">
         <v>0.002082369273484493</v>
       </c>
+      <c r="I251" s="1" t="n">
+        <v>0.04318</v>
+      </c>
+      <c r="J251" s="3" t="n">
+        <v>-0.003001616254906446</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -7505,6 +9017,12 @@
       <c r="H252" s="3" t="n">
         <v>-0.04656862745098034</v>
       </c>
+      <c r="I252" s="1" t="n">
+        <v>0.005866</v>
+      </c>
+      <c r="J252" s="2" t="n">
+        <v>0.005312767780634066</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -7533,6 +9051,12 @@
       <c r="H253" s="2" t="n">
         <v>0.003592814371257547</v>
       </c>
+      <c r="I253" s="1" t="n">
+        <v>0.01682</v>
+      </c>
+      <c r="J253" s="2" t="n">
+        <v>0.003579952267303164</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -7561,6 +9085,12 @@
       <c r="H254" s="2" t="n">
         <v>0.00920951650038378</v>
       </c>
+      <c r="I254" s="1" t="n">
+        <v>0.1301</v>
+      </c>
+      <c r="J254" s="3" t="n">
+        <v>-0.01064638783269971</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -7589,6 +9119,12 @@
       <c r="H255" s="2" t="n">
         <v>0.0009652509652510934</v>
       </c>
+      <c r="I255" s="1" t="n">
+        <v>0.02085</v>
+      </c>
+      <c r="J255" s="2" t="n">
+        <v>0.005303760848601687</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -7617,6 +9153,12 @@
       <c r="H256" s="2" t="n">
         <v>0.002865329512894032</v>
       </c>
+      <c r="I256" s="1" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="J256" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -7645,6 +9187,12 @@
       <c r="H257" s="2" t="n">
         <v>0.002365930599369126</v>
       </c>
+      <c r="I257" s="1" t="n">
+        <v>0.02538</v>
+      </c>
+      <c r="J257" s="3" t="n">
+        <v>-0.001573564122738074</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -7673,6 +9221,12 @@
       <c r="H258" s="3" t="n">
         <v>-0.0007431428185380285</v>
       </c>
+      <c r="I258" s="1" t="n">
+        <v>0.14805</v>
+      </c>
+      <c r="J258" s="2" t="n">
+        <v>0.0009465215333647047</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -7701,6 +9255,12 @@
       <c r="H259" s="3" t="n">
         <v>-0.0001963864886096438</v>
       </c>
+      <c r="I259" s="1" t="n">
+        <v>0.05087</v>
+      </c>
+      <c r="J259" s="3" t="n">
+        <v>-0.000785700255352551</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -7729,6 +9289,12 @@
       <c r="H260" s="2" t="n">
         <v>0.002659574468085082</v>
       </c>
+      <c r="I260" s="1" t="n">
+        <v>0.08284</v>
+      </c>
+      <c r="J260" s="3" t="n">
+        <v>-0.001205690860863309</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -7757,6 +9323,12 @@
       <c r="H261" s="2" t="n">
         <v>0.01729957805907182</v>
       </c>
+      <c r="I261" s="1" t="n">
+        <v>0.242</v>
+      </c>
+      <c r="J261" s="2" t="n">
+        <v>0.003732890916632037</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -7785,6 +9357,12 @@
       <c r="H262" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="I262" s="1" t="n">
+        <v>0.1423</v>
+      </c>
+      <c r="J262" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -7813,6 +9391,12 @@
       <c r="H263" s="3" t="n">
         <v>-0.0002579979360165908</v>
       </c>
+      <c r="I263" s="1" t="n">
+        <v>0.07754</v>
+      </c>
+      <c r="J263" s="2" t="n">
+        <v>0.0005161290322580435</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -7841,6 +9425,12 @@
       <c r="H264" s="2" t="n">
         <v>0.01758014477766288</v>
       </c>
+      <c r="I264" s="1" t="n">
+        <v>0.04031</v>
+      </c>
+      <c r="J264" s="2" t="n">
+        <v>0.0241361788617886</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -7869,6 +9459,12 @@
       <c r="H265" s="2" t="n">
         <v>0.0006514657980455761</v>
       </c>
+      <c r="I265" s="1" t="n">
+        <v>0.01536</v>
+      </c>
+      <c r="J265" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -7897,6 +9493,12 @@
       <c r="H266" s="2" t="n">
         <v>0.008387854386847794</v>
       </c>
+      <c r="I266" s="1" t="n">
+        <v>0.005992</v>
+      </c>
+      <c r="J266" s="3" t="n">
+        <v>-0.003160871735152208</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -7925,6 +9527,12 @@
       <c r="H267" s="2" t="n">
         <v>0.005918751681463491</v>
       </c>
+      <c r="I267" s="1" t="n">
+        <v>0.03737</v>
+      </c>
+      <c r="J267" s="3" t="n">
+        <v>-0.0005349023803155706</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -7953,6 +9561,12 @@
       <c r="H268" s="2" t="n">
         <v>0.00197173841603684</v>
       </c>
+      <c r="I268" s="1" t="n">
+        <v>0.03049</v>
+      </c>
+      <c r="J268" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -7981,6 +9595,12 @@
       <c r="H269" s="2" t="n">
         <v>0.004329578087033394</v>
       </c>
+      <c r="I269" s="1" t="n">
+        <v>0.22704</v>
+      </c>
+      <c r="J269" s="3" t="n">
+        <v>-0.001275678529010744</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -8009,6 +9629,12 @@
       <c r="H270" s="2" t="n">
         <v>0.0130576713819369</v>
       </c>
+      <c r="I270" s="1" t="n">
+        <v>0.927</v>
+      </c>
+      <c r="J270" s="3" t="n">
+        <v>-0.004296455424274977</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -8037,6 +9663,12 @@
       <c r="H271" s="2" t="n">
         <v>0.004252029377657393</v>
       </c>
+      <c r="I271" s="1" t="n">
+        <v>2.588</v>
+      </c>
+      <c r="J271" s="3" t="n">
+        <v>-0.003849114703618086</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -8065,6 +9697,12 @@
       <c r="H272" s="3" t="n">
         <v>-0.001084010840108432</v>
       </c>
+      <c r="I272" s="1" t="n">
+        <v>0.1839</v>
+      </c>
+      <c r="J272" s="3" t="n">
+        <v>-0.002170374389582114</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -8093,6 +9731,12 @@
       <c r="H273" s="2" t="n">
         <v>0.004233148811462005</v>
       </c>
+      <c r="I273" s="1" t="n">
+        <v>0.03083</v>
+      </c>
+      <c r="J273" s="3" t="n">
+        <v>-0.0003242542153047858</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -8121,6 +9765,12 @@
       <c r="H274" s="3" t="n">
         <v>-0.00472440944881896</v>
       </c>
+      <c r="I274" s="1" t="n">
+        <v>0.1902</v>
+      </c>
+      <c r="J274" s="2" t="n">
+        <v>0.003164556962025407</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -8149,6 +9799,12 @@
       <c r="H275" s="3" t="n">
         <v>-0.0005805515239477267</v>
       </c>
+      <c r="I275" s="1" t="n">
+        <v>0.06923</v>
+      </c>
+      <c r="J275" s="2" t="n">
+        <v>0.005373221028173037</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -8177,6 +9833,12 @@
       <c r="H276" s="2" t="n">
         <v>0.003470930953266253</v>
       </c>
+      <c r="I276" s="1" t="n">
+        <v>0.08082</v>
+      </c>
+      <c r="J276" s="3" t="n">
+        <v>-0.001605929586164191</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -8205,6 +9867,12 @@
       <c r="H277" s="2" t="n">
         <v>0.001903855306996715</v>
       </c>
+      <c r="I277" s="1" t="n">
+        <v>0.004092</v>
+      </c>
+      <c r="J277" s="3" t="n">
+        <v>-0.02802850356294538</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -8233,6 +9901,12 @@
       <c r="H278" s="2" t="n">
         <v>0.001290322580645162</v>
       </c>
+      <c r="I278" s="1" t="n">
+        <v>1.548</v>
+      </c>
+      <c r="J278" s="3" t="n">
+        <v>-0.002577319587628868</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -8261,6 +9935,12 @@
       <c r="H279" s="2" t="n">
         <v>0.005454545454545548</v>
       </c>
+      <c r="I279" s="1" t="n">
+        <v>0.01107</v>
+      </c>
+      <c r="J279" s="2" t="n">
+        <v>0.0009041591320071964</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -8289,6 +9969,12 @@
       <c r="H280" s="2" t="n">
         <v>0.005616543272912892</v>
       </c>
+      <c r="I280" s="1" t="n">
+        <v>0.03935</v>
+      </c>
+      <c r="J280" s="3" t="n">
+        <v>-0.001015486164000974</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -8317,6 +10003,12 @@
       <c r="H281" s="2" t="n">
         <v>0.008862105636299192</v>
       </c>
+      <c r="I281" s="1" t="n">
+        <v>0.08444</v>
+      </c>
+      <c r="J281" s="3" t="n">
+        <v>-0.01100960412274533</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -8345,6 +10037,12 @@
       <c r="H282" s="2" t="n">
         <v>0.003773584905660355</v>
       </c>
+      <c r="I282" s="1" t="n">
+        <v>0.0265</v>
+      </c>
+      <c r="J282" s="3" t="n">
+        <v>-0.003759398496240579</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -8373,6 +10071,12 @@
       <c r="H283" s="2" t="n">
         <v>0.002898168884204953</v>
       </c>
+      <c r="I283" s="1" t="n">
+        <v>0.07613</v>
+      </c>
+      <c r="J283" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -8401,6 +10105,12 @@
       <c r="H284" s="2" t="n">
         <v>0.002473716759431105</v>
       </c>
+      <c r="I284" s="1" t="n">
+        <v>0.001619</v>
+      </c>
+      <c r="J284" s="3" t="n">
+        <v>-0.001233806292412121</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -8429,6 +10139,12 @@
       <c r="H285" s="2" t="n">
         <v>0.003477396920019901</v>
       </c>
+      <c r="I285" s="1" t="n">
+        <v>0.202</v>
+      </c>
+      <c r="J285" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -8457,6 +10173,12 @@
       <c r="H286" s="2" t="n">
         <v>0.01030638058652665</v>
       </c>
+      <c r="I286" s="1" t="n">
+        <v>0.10738</v>
+      </c>
+      <c r="J286" s="3" t="n">
+        <v>-0.004173235648706223</v>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -8485,6 +10207,12 @@
       <c r="H287" s="2" t="n">
         <v>0.004086398131932319</v>
       </c>
+      <c r="I287" s="1" t="n">
+        <v>0.01717</v>
+      </c>
+      <c r="J287" s="3" t="n">
+        <v>-0.001744186046511557</v>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -8513,6 +10241,12 @@
       <c r="H288" s="2" t="n">
         <v>0.001960784313725524</v>
       </c>
+      <c r="I288" s="1" t="n">
+        <v>0.01525</v>
+      </c>
+      <c r="J288" s="3" t="n">
+        <v>-0.005218525766470986</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -8541,6 +10275,12 @@
       <c r="H289" s="3" t="n">
         <v>-0.00186799501868009</v>
       </c>
+      <c r="I289" s="1" t="n">
+        <v>0.01597</v>
+      </c>
+      <c r="J289" s="3" t="n">
+        <v>-0.003742981908920621</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -8569,6 +10309,12 @@
       <c r="H290" s="2" t="n">
         <v>0.004430660168364992</v>
       </c>
+      <c r="I290" s="1" t="n">
+        <v>2.267</v>
+      </c>
+      <c r="J290" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -8597,6 +10343,12 @@
       <c r="H291" s="2" t="n">
         <v>0.005677946854417447</v>
       </c>
+      <c r="I291" s="1" t="n">
+        <v>0.4415</v>
+      </c>
+      <c r="J291" s="3" t="n">
+        <v>-0.002935862691960305</v>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -8625,6 +10377,12 @@
       <c r="H292" s="2" t="n">
         <v>0.001728110599078407</v>
       </c>
+      <c r="I292" s="1" t="n">
+        <v>1.737</v>
+      </c>
+      <c r="J292" s="3" t="n">
+        <v>-0.001150086256469236</v>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -8653,6 +10411,12 @@
       <c r="H293" s="3" t="n">
         <v>-0.007121661721068234</v>
       </c>
+      <c r="I293" s="1" t="n">
+        <v>0.05074</v>
+      </c>
+      <c r="J293" s="2" t="n">
+        <v>0.010958358238693</v>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -8681,6 +10445,12 @@
       <c r="H294" s="2" t="n">
         <v>0.002524854031876399</v>
       </c>
+      <c r="I294" s="1" t="n">
+        <v>0.06343</v>
+      </c>
+      <c r="J294" s="3" t="n">
+        <v>-0.001574059499449124</v>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -8709,6 +10479,12 @@
       <c r="H295" s="2" t="n">
         <v>0.004878048780487791</v>
       </c>
+      <c r="I295" s="1" t="n">
+        <v>0.0004115</v>
+      </c>
+      <c r="J295" s="3" t="n">
+        <v>-0.001213592233009738</v>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -8737,6 +10513,12 @@
       <c r="H296" s="3" t="n">
         <v>-0.001117496807151984</v>
       </c>
+      <c r="I296" s="1" t="n">
+        <v>62.32</v>
+      </c>
+      <c r="J296" s="3" t="n">
+        <v>-0.003995525011986575</v>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -8765,6 +10547,12 @@
       <c r="H297" s="2" t="n">
         <v>0.003067484662576775</v>
       </c>
+      <c r="I297" s="1" t="n">
+        <v>0.0979</v>
+      </c>
+      <c r="J297" s="3" t="n">
+        <v>-0.00203873598369017</v>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -8793,6 +10581,12 @@
       <c r="H298" s="2" t="n">
         <v>0.00209424083769625</v>
       </c>
+      <c r="I298" s="1" t="n">
+        <v>0.0956</v>
+      </c>
+      <c r="J298" s="3" t="n">
+        <v>-0.001044932079414723</v>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -8821,6 +10615,12 @@
       <c r="H299" s="3" t="n">
         <v>-0.006720430107526859</v>
       </c>
+      <c r="I299" s="1" t="n">
+        <v>0.09554</v>
+      </c>
+      <c r="J299" s="3" t="n">
+        <v>-0.005516810658894584</v>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -8849,6 +10649,12 @@
       <c r="H300" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="I300" s="1" t="n">
+        <v>0.01844</v>
+      </c>
+      <c r="J300" s="3" t="n">
+        <v>-0.001624255549539728</v>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -8877,6 +10683,12 @@
       <c r="H301" s="2" t="n">
         <v>0.0022556390977444</v>
       </c>
+      <c r="I301" s="1" t="n">
+        <v>0.01332</v>
+      </c>
+      <c r="J301" s="3" t="n">
+        <v>-0.0007501875468866911</v>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -8905,6 +10717,12 @@
       <c r="H302" s="2" t="n">
         <v>0.001838657779820776</v>
       </c>
+      <c r="I302" s="1" t="n">
+        <v>0.004358</v>
+      </c>
+      <c r="J302" s="3" t="n">
+        <v>-0.000229410415232882</v>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -8933,6 +10751,12 @@
       <c r="H303" s="3" t="n">
         <v>-0.001069518716577682</v>
       </c>
+      <c r="I303" s="1" t="n">
+        <v>0.009379999999999999</v>
+      </c>
+      <c r="J303" s="2" t="n">
+        <v>0.004282655246252688</v>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -8961,6 +10785,12 @@
       <c r="H304" s="2" t="n">
         <v>0.002971137521222461</v>
       </c>
+      <c r="I304" s="1" t="n">
+        <v>4.721</v>
+      </c>
+      <c r="J304" s="3" t="n">
+        <v>-0.001057977147693587</v>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -8989,6 +10819,12 @@
       <c r="H305" s="2" t="n">
         <v>0.002827521206408998</v>
       </c>
+      <c r="I305" s="1" t="n">
+        <v>0.05303</v>
+      </c>
+      <c r="J305" s="3" t="n">
+        <v>-0.003195488721804446</v>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -9017,6 +10853,12 @@
       <c r="H306" s="3" t="n">
         <v>-0.0003423485107839641</v>
       </c>
+      <c r="I306" s="1" t="n">
+        <v>0.0582</v>
+      </c>
+      <c r="J306" s="3" t="n">
+        <v>-0.003424657534246555</v>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -9045,6 +10887,12 @@
       <c r="H307" s="2" t="n">
         <v>0.001138952164009144</v>
       </c>
+      <c r="I307" s="1" t="n">
+        <v>0.1753</v>
+      </c>
+      <c r="J307" s="3" t="n">
+        <v>-0.002844141069397044</v>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -9073,6 +10921,12 @@
       <c r="H308" s="2" t="n">
         <v>0.0002025931928686411</v>
       </c>
+      <c r="I308" s="1" t="n">
+        <v>0.04928</v>
+      </c>
+      <c r="J308" s="3" t="n">
+        <v>-0.001822969414624262</v>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -9101,6 +10955,12 @@
       <c r="H309" s="2" t="n">
         <v>0.002775208140610651</v>
       </c>
+      <c r="I309" s="1" t="n">
+        <v>0.5402</v>
+      </c>
+      <c r="J309" s="3" t="n">
+        <v>-0.003321033210332147</v>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -9129,6 +10989,12 @@
       <c r="H310" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="I310" s="1" t="n">
+        <v>0.00243</v>
+      </c>
+      <c r="J310" s="3" t="n">
+        <v>-0.004098360655737716</v>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -9157,6 +11023,12 @@
       <c r="H311" s="3" t="n">
         <v>-0.003476567932137397</v>
       </c>
+      <c r="I311" s="1" t="n">
+        <v>0.07139</v>
+      </c>
+      <c r="J311" s="3" t="n">
+        <v>-0.003767792352777091</v>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -9185,6 +11057,12 @@
       <c r="H312" s="2" t="n">
         <v>0.0005563591854901297</v>
       </c>
+      <c r="I312" s="1" t="n">
+        <v>0.009009</v>
+      </c>
+      <c r="J312" s="2" t="n">
+        <v>0.001890569395017755</v>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -9213,6 +11091,12 @@
       <c r="H313" s="2" t="n">
         <v>0.01216749181841061</v>
       </c>
+      <c r="I313" s="1" t="n">
+        <v>0.012201</v>
+      </c>
+      <c r="J313" s="2" t="n">
+        <v>0.01152379373238271</v>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -9241,6 +11125,12 @@
       <c r="H314" s="2" t="n">
         <v>0.00863557858376506</v>
       </c>
+      <c r="I314" s="1" t="n">
+        <v>0.02324</v>
+      </c>
+      <c r="J314" s="3" t="n">
+        <v>-0.005136986301369803</v>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -9269,6 +11159,12 @@
       <c r="H315" s="2" t="n">
         <v>0.002820874471086044</v>
       </c>
+      <c r="I315" s="1" t="n">
+        <v>0.00709</v>
+      </c>
+      <c r="J315" s="3" t="n">
+        <v>-0.002812939521800289</v>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -9297,6 +11193,12 @@
       <c r="H316" s="2" t="n">
         <v>0.001533742331288388</v>
       </c>
+      <c r="I316" s="1" t="n">
+        <v>0.2612</v>
+      </c>
+      <c r="J316" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -9325,6 +11227,12 @@
       <c r="H317" s="3" t="n">
         <v>-0.008928571428571343</v>
       </c>
+      <c r="I317" s="1" t="n">
+        <v>1.12e-05</v>
+      </c>
+      <c r="J317" s="2" t="n">
+        <v>0.009009009009008922</v>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -9353,6 +11261,12 @@
       <c r="H318" s="2" t="n">
         <v>0.002735770195303562</v>
       </c>
+      <c r="I318" s="1" t="n">
+        <v>0.052646</v>
+      </c>
+      <c r="J318" s="3" t="n">
+        <v>-0.002538840469874994</v>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -9381,6 +11295,12 @@
       <c r="H319" s="3" t="n">
         <v>-0.001051524710830662</v>
       </c>
+      <c r="I319" s="1" t="n">
+        <v>0.03811</v>
+      </c>
+      <c r="J319" s="2" t="n">
+        <v>0.002894736842105236</v>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -9409,6 +11329,12 @@
       <c r="H320" s="2" t="n">
         <v>0.00501622897609917</v>
       </c>
+      <c r="I320" s="1" t="n">
+        <v>0.006799</v>
+      </c>
+      <c r="J320" s="3" t="n">
+        <v>-0.001908396946564884</v>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -9437,6 +11363,12 @@
       <c r="H321" s="2" t="n">
         <v>0.001105705440070742</v>
       </c>
+      <c r="I321" s="1" t="n">
+        <v>4.512</v>
+      </c>
+      <c r="J321" s="3" t="n">
+        <v>-0.003313452617627693</v>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -9465,6 +11397,12 @@
       <c r="H322" s="2" t="n">
         <v>0.003144654088050317</v>
       </c>
+      <c r="I322" s="1" t="n">
+        <v>1.908</v>
+      </c>
+      <c r="J322" s="3" t="n">
+        <v>-0.003134796238244517</v>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -9493,6 +11431,12 @@
       <c r="H323" s="3" t="n">
         <v>-0.001412628902387408</v>
       </c>
+      <c r="I323" s="1" t="n">
+        <v>0.007068</v>
+      </c>
+      <c r="J323" s="3" t="n">
+        <v>-0.0001414627245720941</v>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -9521,6 +11465,12 @@
       <c r="H324" s="2" t="n">
         <v>0.005506607929515386</v>
       </c>
+      <c r="I324" s="1" t="n">
+        <v>0.01824</v>
+      </c>
+      <c r="J324" s="3" t="n">
+        <v>-0.001095290251916713</v>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -9549,6 +11499,12 @@
       <c r="H325" s="2" t="n">
         <v>0.003179261433113288</v>
       </c>
+      <c r="I325" s="1" t="n">
+        <v>0.4098</v>
+      </c>
+      <c r="J325" s="3" t="n">
+        <v>-0.0009751340809361567</v>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -9577,6 +11533,12 @@
       <c r="H326" s="2" t="n">
         <v>0.003744798890429974</v>
       </c>
+      <c r="I326" s="1" t="n">
+        <v>0.007214</v>
+      </c>
+      <c r="J326" s="3" t="n">
+        <v>-0.003178112477546007</v>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -9605,6 +11567,12 @@
       <c r="H327" s="3" t="n">
         <v>-0.004689942678478292</v>
       </c>
+      <c r="I327" s="1" t="n">
+        <v>0.1912</v>
+      </c>
+      <c r="J327" s="2" t="n">
+        <v>0.001047120418848198</v>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -9633,6 +11601,12 @@
       <c r="H328" s="2" t="n">
         <v>0.002572347266880983</v>
       </c>
+      <c r="I328" s="1" t="n">
+        <v>0.4748</v>
+      </c>
+      <c r="J328" s="2" t="n">
+        <v>0.01518067137053666</v>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -9661,6 +11635,12 @@
       <c r="H329" s="2" t="n">
         <v>0.0141054194506311</v>
       </c>
+      <c r="I329" s="1" t="n">
+        <v>0.01364</v>
+      </c>
+      <c r="J329" s="3" t="n">
+        <v>-0.001464128843338281</v>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -9689,6 +11669,12 @@
       <c r="H330" s="2" t="n">
         <v>0.001768346595932731</v>
       </c>
+      <c r="I330" s="1" t="n">
+        <v>0.1134</v>
+      </c>
+      <c r="J330" s="2" t="n">
+        <v>0.0008826125330979953</v>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -9717,6 +11703,12 @@
       <c r="H331" s="2" t="n">
         <v>0.007724601175482682</v>
       </c>
+      <c r="I331" s="1" t="n">
+        <v>0.5997</v>
+      </c>
+      <c r="J331" s="3" t="n">
+        <v>-0.0006665555740709148</v>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -9745,6 +11737,12 @@
       <c r="H332" s="3" t="n">
         <v>-0.001537022186581181</v>
       </c>
+      <c r="I332" s="1" t="n">
+        <v>0.29696</v>
+      </c>
+      <c r="J332" s="3" t="n">
+        <v>-0.006224482966334158</v>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -9773,6 +11771,12 @@
       <c r="H333" s="2" t="n">
         <v>0.001138790035587142</v>
       </c>
+      <c r="I333" s="1" t="n">
+        <v>0.06994</v>
+      </c>
+      <c r="J333" s="3" t="n">
+        <v>-0.005545286506469522</v>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -9801,6 +11805,12 @@
       <c r="H334" s="2" t="n">
         <v>0.02762758802584729</v>
       </c>
+      <c r="I334" s="1" t="n">
+        <v>0.15109</v>
+      </c>
+      <c r="J334" s="3" t="n">
+        <v>-0.0305421880012832</v>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -9829,6 +11839,12 @@
       <c r="H335" s="3" t="n">
         <v>-0.001915708812260503</v>
       </c>
+      <c r="I335" s="1" t="n">
+        <v>0.1564</v>
+      </c>
+      <c r="J335" s="2" t="n">
+        <v>0.0006397952655151423</v>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -9857,6 +11873,12 @@
       <c r="H336" s="2" t="n">
         <v>0.004025301897642359</v>
       </c>
+      <c r="I336" s="1" t="n">
+        <v>0.1739</v>
+      </c>
+      <c r="J336" s="3" t="n">
+        <v>-0.004009163802978271</v>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -9885,6 +11907,12 @@
       <c r="H337" s="2" t="n">
         <v>0.009980039920159793</v>
       </c>
+      <c r="I337" s="1" t="n">
+        <v>0.03981</v>
+      </c>
+      <c r="J337" s="3" t="n">
+        <v>-0.01655138339920958</v>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -9913,6 +11941,12 @@
       <c r="H338" s="2" t="n">
         <v>0.002083333333333281</v>
       </c>
+      <c r="I338" s="1" t="n">
+        <v>0.005295</v>
+      </c>
+      <c r="J338" s="2" t="n">
+        <v>0.0007560007560008564</v>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -9941,6 +11975,12 @@
       <c r="H339" s="2" t="n">
         <v>0.004890453834115811</v>
       </c>
+      <c r="I339" s="1" t="n">
+        <v>0.0514</v>
+      </c>
+      <c r="J339" s="2" t="n">
+        <v>0.0005839984426708633</v>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -9969,6 +12009,12 @@
       <c r="H340" s="2" t="n">
         <v>0.003437334743521898</v>
       </c>
+      <c r="I340" s="1" t="n">
+        <v>0.1509</v>
+      </c>
+      <c r="J340" s="3" t="n">
+        <v>-0.005928853754940607</v>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -9997,6 +12043,12 @@
       <c r="H341" s="2" t="n">
         <v>0.003035502177642825</v>
       </c>
+      <c r="I341" s="1" t="n">
+        <v>7.593</v>
+      </c>
+      <c r="J341" s="3" t="n">
+        <v>-0.0009210526315789044</v>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -10025,6 +12077,12 @@
       <c r="H342" s="3" t="n">
         <v>-0.003872505212987856</v>
       </c>
+      <c r="I342" s="1" t="n">
+        <v>0.3347</v>
+      </c>
+      <c r="J342" s="2" t="n">
+        <v>0.0008971291866029381</v>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -10053,6 +12111,12 @@
       <c r="H343" s="3" t="n">
         <v>-0.0005089058524172821</v>
       </c>
+      <c r="I343" s="1" t="n">
+        <v>0.01979</v>
+      </c>
+      <c r="J343" s="2" t="n">
+        <v>0.007637474541751393</v>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -10081,6 +12145,12 @@
       <c r="H344" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="I344" s="1" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J344" s="2" t="n">
+        <v>0.0009099181073704385</v>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -10109,6 +12179,12 @@
       <c r="H345" s="2" t="n">
         <v>0.00315208825847124</v>
       </c>
+      <c r="I345" s="1" t="n">
+        <v>1.271</v>
+      </c>
+      <c r="J345" s="3" t="n">
+        <v>-0.001571091908876671</v>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -10137,6 +12213,12 @@
       <c r="H346" s="3" t="n">
         <v>-0.00365454895172147</v>
       </c>
+      <c r="I346" s="1" t="n">
+        <v>0.005175</v>
+      </c>
+      <c r="J346" s="3" t="n">
+        <v>-0.000965250965250926</v>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -10165,6 +12247,12 @@
       <c r="H347" s="2" t="n">
         <v>0.006328001406222521</v>
       </c>
+      <c r="I347" s="1" t="n">
+        <v>0.05727</v>
+      </c>
+      <c r="J347" s="2" t="n">
+        <v>0.0003493449781659246</v>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -10193,6 +12281,12 @@
       <c r="H348" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="I348" s="1" t="n">
+        <v>0.1273</v>
+      </c>
+      <c r="J348" s="3" t="n">
+        <v>-0.006245120999219323</v>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -10221,6 +12315,12 @@
       <c r="H349" s="3" t="n">
         <v>-0.001034145967788199</v>
       </c>
+      <c r="I349" s="1" t="n">
+        <v>5207</v>
+      </c>
+      <c r="J349" s="3" t="n">
+        <v>-0.001782872917585296</v>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -10249,6 +12349,12 @@
       <c r="H350" s="2" t="n">
         <v>0.006062767475035664</v>
       </c>
+      <c r="I350" s="1" t="n">
+        <v>0.02822</v>
+      </c>
+      <c r="J350" s="2" t="n">
+        <v>0.000354484225451953</v>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -10277,6 +12383,12 @@
       <c r="H351" s="2" t="n">
         <v>0.006676557863501405</v>
       </c>
+      <c r="I351" s="1" t="n">
+        <v>0.001356</v>
+      </c>
+      <c r="J351" s="3" t="n">
+        <v>-0.0007369196757552808</v>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -10305,6 +12417,12 @@
       <c r="H352" s="2" t="n">
         <v>0.0006357279084551553</v>
       </c>
+      <c r="I352" s="1" t="n">
+        <v>0.01574</v>
+      </c>
+      <c r="J352" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -10333,6 +12451,12 @@
       <c r="H353" s="2" t="n">
         <v>0.001121794871794819</v>
       </c>
+      <c r="I353" s="1" t="n">
+        <v>6.245</v>
+      </c>
+      <c r="J353" s="3" t="n">
+        <v>-0.0003201536737633712</v>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -10361,6 +12485,12 @@
       <c r="H354" s="2" t="n">
         <v>0.002799160251924503</v>
       </c>
+      <c r="I354" s="1" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="J354" s="3" t="n">
+        <v>-0.002093510118632397</v>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -10389,6 +12519,12 @@
       <c r="H355" s="3" t="n">
         <v>-0.0007253384912959925</v>
       </c>
+      <c r="I355" s="1" t="n">
+        <v>0.04122</v>
+      </c>
+      <c r="J355" s="3" t="n">
+        <v>-0.002661504960077401</v>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -10417,6 +12553,12 @@
       <c r="H356" s="2" t="n">
         <v>0.007052186177715049</v>
       </c>
+      <c r="I356" s="1" t="n">
+        <v>0.11635</v>
+      </c>
+      <c r="J356" s="2" t="n">
+        <v>0.01846988795518208</v>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -10445,6 +12587,12 @@
       <c r="H357" s="2" t="n">
         <v>0.00786193672099717</v>
       </c>
+      <c r="I357" s="1" t="n">
+        <v>0.00522</v>
+      </c>
+      <c r="J357" s="3" t="n">
+        <v>-0.006849315068493234</v>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -10473,6 +12621,12 @@
       <c r="H358" s="2" t="n">
         <v>0.009729729729729708</v>
       </c>
+      <c r="I358" s="1" t="n">
+        <v>0.1852</v>
+      </c>
+      <c r="J358" s="3" t="n">
+        <v>-0.008565310492505302</v>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -10501,6 +12655,12 @@
       <c r="H359" s="2" t="n">
         <v>0.001849568434032026</v>
       </c>
+      <c r="I359" s="1" t="n">
+        <v>0.1627</v>
+      </c>
+      <c r="J359" s="2" t="n">
+        <v>0.001230769230769266</v>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -10529,6 +12689,12 @@
       <c r="H360" s="2" t="n">
         <v>0.001645510108133536</v>
       </c>
+      <c r="I360" s="1" t="n">
+        <v>0.08484999999999999</v>
+      </c>
+      <c r="J360" s="3" t="n">
+        <v>-0.004341703825393208</v>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -10557,6 +12723,12 @@
       <c r="H361" s="2" t="n">
         <v>0.0138017565872021</v>
       </c>
+      <c r="I361" s="1" t="n">
+        <v>0.007900000000000001</v>
+      </c>
+      <c r="J361" s="3" t="n">
+        <v>-0.02227722772277223</v>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -10585,6 +12757,12 @@
       <c r="H362" s="3" t="n">
         <v>-0.003060984224158284</v>
       </c>
+      <c r="I362" s="1" t="n">
+        <v>0.4216</v>
+      </c>
+      <c r="J362" s="3" t="n">
+        <v>-0.004251299008030287</v>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -10613,6 +12791,12 @@
       <c r="H363" s="2" t="n">
         <v>0.01382863340563983</v>
       </c>
+      <c r="I363" s="1" t="n">
+        <v>3.735</v>
+      </c>
+      <c r="J363" s="3" t="n">
+        <v>-0.001069804760631186</v>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -10641,6 +12825,12 @@
       <c r="H364" s="2" t="n">
         <v>0.002747252747252794</v>
       </c>
+      <c r="I364" s="1" t="n">
+        <v>0.01094</v>
+      </c>
+      <c r="J364" s="3" t="n">
+        <v>-0.0009132420091323829</v>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -10669,6 +12859,12 @@
       <c r="H365" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="I365" s="1" t="n">
+        <v>0.05507</v>
+      </c>
+      <c r="J365" s="2" t="n">
+        <v>0.002001455604075673</v>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -10697,6 +12893,12 @@
       <c r="H366" s="3" t="n">
         <v>-0.003139013452914826</v>
       </c>
+      <c r="I366" s="1" t="n">
+        <v>0.02277</v>
+      </c>
+      <c r="J366" s="2" t="n">
+        <v>0.02429149797570845</v>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -10725,6 +12927,12 @@
       <c r="H367" s="2" t="n">
         <v>0.005192878338278977</v>
       </c>
+      <c r="I367" s="1" t="n">
+        <v>0.001357</v>
+      </c>
+      <c r="J367" s="2" t="n">
+        <v>0.001476014760147477</v>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -10753,6 +12961,12 @@
       <c r="H368" s="3" t="n">
         <v>-0.001740341106856945</v>
       </c>
+      <c r="I368" s="1" t="n">
+        <v>0.2866</v>
+      </c>
+      <c r="J368" s="3" t="n">
+        <v>-0.0006973500697349302</v>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -10781,6 +12995,12 @@
       <c r="H369" s="3" t="n">
         <v>-0.00271002710027108</v>
       </c>
+      <c r="I369" s="1" t="n">
+        <v>0.01846</v>
+      </c>
+      <c r="J369" s="2" t="n">
+        <v>0.003260869565217447</v>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -10809,6 +13029,12 @@
       <c r="H370" s="3" t="n">
         <v>-0.02011195323723178</v>
       </c>
+      <c r="I370" s="1" t="n">
+        <v>0.19951</v>
+      </c>
+      <c r="J370" s="2" t="n">
+        <v>0.008594105454729181</v>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -10837,6 +13063,12 @@
       <c r="H371" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="I371" s="1" t="n">
+        <v>0.076</v>
+      </c>
+      <c r="J371" s="2" t="n">
+        <v>0.01333333333333335</v>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -10865,6 +13097,12 @@
       <c r="H372" s="2" t="n">
         <v>0.003820439350525287</v>
       </c>
+      <c r="I372" s="1" t="n">
+        <v>0.1051</v>
+      </c>
+      <c r="J372" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -10893,6 +13131,12 @@
       <c r="H373" s="3" t="n">
         <v>-0.0009095043201455889</v>
       </c>
+      <c r="I373" s="1" t="n">
+        <v>0.06579</v>
+      </c>
+      <c r="J373" s="3" t="n">
+        <v>-0.00182066454255796</v>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -10921,6 +13165,12 @@
       <c r="H374" s="2" t="n">
         <v>0.003575685339690007</v>
       </c>
+      <c r="I374" s="1" t="n">
+        <v>0.007576</v>
+      </c>
+      <c r="J374" s="3" t="n">
+        <v>-0.0002639218791237</v>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -10949,6 +13199,12 @@
       <c r="H375" s="2" t="n">
         <v>0.002525252525252422</v>
       </c>
+      <c r="I375" s="1" t="n">
+        <v>0.1589</v>
+      </c>
+      <c r="J375" s="2" t="n">
+        <v>0.0006297229219144632</v>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -10977,6 +13233,12 @@
       <c r="H376" s="2" t="n">
         <v>0.00473232771369416</v>
       </c>
+      <c r="I376" s="1" t="n">
+        <v>0.003404</v>
+      </c>
+      <c r="J376" s="2" t="n">
+        <v>0.002060641742714178</v>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -11005,6 +13267,12 @@
       <c r="H377" s="3" t="n">
         <v>-0.006249999999999962</v>
       </c>
+      <c r="I377" s="1" t="n">
+        <v>0.0159</v>
+      </c>
+      <c r="J377" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -11033,6 +13301,12 @@
       <c r="H378" s="3" t="n">
         <v>-0.01763668430335086</v>
       </c>
+      <c r="I378" s="1" t="n">
+        <v>0.01116</v>
+      </c>
+      <c r="J378" s="2" t="n">
+        <v>0.001795332136445169</v>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -11061,6 +13335,12 @@
       <c r="H379" s="2" t="n">
         <v>0.001829826166514106</v>
       </c>
+      <c r="I379" s="1" t="n">
+        <v>0.02167</v>
+      </c>
+      <c r="J379" s="3" t="n">
+        <v>-0.01050228310502288</v>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -11089,6 +13369,12 @@
       <c r="H380" s="2" t="n">
         <v>0.001604278074866245</v>
       </c>
+      <c r="I380" s="1" t="n">
+        <v>0.01877</v>
+      </c>
+      <c r="J380" s="2" t="n">
+        <v>0.002135611318739902</v>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -11117,6 +13403,12 @@
       <c r="H381" s="2" t="n">
         <v>0.00334728033472813</v>
       </c>
+      <c r="I381" s="1" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="J381" s="2" t="n">
+        <v>0.0008340283569640449</v>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -11145,6 +13437,12 @@
       <c r="H382" s="2" t="n">
         <v>0.004495159059474348</v>
       </c>
+      <c r="I382" s="1" t="n">
+        <v>0.02896</v>
+      </c>
+      <c r="J382" s="3" t="n">
+        <v>-0.003098106712564537</v>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -11173,6 +13471,12 @@
       <c r="H383" s="2" t="n">
         <v>0.003375268487265948</v>
       </c>
+      <c r="I383" s="1" t="n">
+        <v>0.006528</v>
+      </c>
+      <c r="J383" s="3" t="n">
+        <v>-0.001834862385321079</v>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -11201,6 +13505,12 @@
       <c r="H384" s="2" t="n">
         <v>0.0004786979415988317</v>
       </c>
+      <c r="I384" s="1" t="n">
+        <v>0.02091</v>
+      </c>
+      <c r="J384" s="2" t="n">
+        <v>0.0004784688995216776</v>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -11229,6 +13539,12 @@
       <c r="H385" s="3" t="n">
         <v>-0.001189060642092747</v>
       </c>
+      <c r="I385" s="1" t="n">
+        <v>2522</v>
+      </c>
+      <c r="J385" s="2" t="n">
+        <v>0.0007936507936507937</v>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -11257,6 +13573,12 @@
       <c r="H386" s="2" t="n">
         <v>0.002523977788995459</v>
       </c>
+      <c r="I386" s="1" t="n">
+        <v>0.1978</v>
+      </c>
+      <c r="J386" s="3" t="n">
+        <v>-0.004028197381671678</v>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -11285,6 +13607,12 @@
       <c r="H387" s="3" t="n">
         <v>-0.001874414245548352</v>
       </c>
+      <c r="I387" s="1" t="n">
+        <v>0.08494</v>
+      </c>
+      <c r="J387" s="3" t="n">
+        <v>-0.00305164319248822</v>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -11313,6 +13641,12 @@
       <c r="H388" s="2" t="n">
         <v>0.001994813484939077</v>
       </c>
+      <c r="I388" s="1" t="n">
+        <v>0.005012</v>
+      </c>
+      <c r="J388" s="3" t="n">
+        <v>-0.002189926338841275</v>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -11341,6 +13675,12 @@
       <c r="H389" s="2" t="n">
         <v>0.0004531037607611958</v>
       </c>
+      <c r="I389" s="1" t="n">
+        <v>0.02217</v>
+      </c>
+      <c r="J389" s="2" t="n">
+        <v>0.00407608695652173</v>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -11369,6 +13709,12 @@
       <c r="H390" s="2" t="n">
         <v>0.01980198019801986</v>
       </c>
+      <c r="I390" s="1" t="n">
+        <v>0.5094</v>
+      </c>
+      <c r="J390" s="2" t="n">
+        <v>0.009312462849217211</v>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -11397,6 +13743,12 @@
       <c r="H391" s="2" t="n">
         <v>0.008595988538682067</v>
       </c>
+      <c r="I391" s="1" t="n">
+        <v>0.0005985</v>
+      </c>
+      <c r="J391" s="2" t="n">
+        <v>0.0001671122994651541</v>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -11425,6 +13777,12 @@
       <c r="H392" s="2" t="n">
         <v>0.001370801919122631</v>
       </c>
+      <c r="I392" s="1" t="n">
+        <v>0.05838</v>
+      </c>
+      <c r="J392" s="3" t="n">
+        <v>-0.001026694045174496</v>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -11453,6 +13811,12 @@
       <c r="H393" s="2" t="n">
         <v>0.0007490636704119024</v>
       </c>
+      <c r="I393" s="1" t="n">
+        <v>0.2668</v>
+      </c>
+      <c r="J393" s="3" t="n">
+        <v>-0.001497005988023995</v>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -11481,6 +13845,12 @@
       <c r="H394" s="2" t="n">
         <v>0.003522205206738068</v>
       </c>
+      <c r="I394" s="1" t="n">
+        <v>0.006556</v>
+      </c>
+      <c r="J394" s="2" t="n">
+        <v>0.0004578055852282006</v>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -11509,6 +13879,12 @@
       <c r="H395" s="2" t="n">
         <v>0.006113537117903863</v>
       </c>
+      <c r="I395" s="1" t="n">
+        <v>0.1151</v>
+      </c>
+      <c r="J395" s="3" t="n">
+        <v>-0.0008680555555555804</v>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -11537,6 +13913,12 @@
       <c r="H396" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="I396" s="1" t="n">
+        <v>0.03085</v>
+      </c>
+      <c r="J396" s="3" t="n">
+        <v>-0.001618122977346325</v>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -11565,6 +13947,12 @@
       <c r="H397" s="2" t="n">
         <v>0.001982815598149521</v>
       </c>
+      <c r="I397" s="1" t="n">
+        <v>0.151</v>
+      </c>
+      <c r="J397" s="3" t="n">
+        <v>-0.003957783641161063</v>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -11593,6 +13981,12 @@
       <c r="H398" s="2" t="n">
         <v>0.00854961832061063</v>
       </c>
+      <c r="I398" s="1" t="n">
+        <v>0.003301</v>
+      </c>
+      <c r="J398" s="3" t="n">
+        <v>-0.0006055101422948326</v>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -11621,6 +14015,12 @@
       <c r="H399" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="I399" s="1" t="n">
+        <v>0.0187</v>
+      </c>
+      <c r="J399" s="3" t="n">
+        <v>-0.001601708489054927</v>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -11649,6 +14049,12 @@
       <c r="H400" s="2" t="n">
         <v>0.006205048653222362</v>
       </c>
+      <c r="I400" s="1" t="n">
+        <v>0.007061</v>
+      </c>
+      <c r="J400" s="3" t="n">
+        <v>-0.01037140854940439</v>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -11677,6 +14083,12 @@
       <c r="H401" s="2" t="n">
         <v>0.005479452054794497</v>
       </c>
+      <c r="I401" s="1" t="n">
+        <v>0.006952</v>
+      </c>
+      <c r="J401" s="3" t="n">
+        <v>-0.003011616234045631</v>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -11705,6 +14117,12 @@
       <c r="H402" s="2" t="n">
         <v>0.001246416552411765</v>
       </c>
+      <c r="I402" s="1" t="n">
+        <v>0.008011000000000001</v>
+      </c>
+      <c r="J402" s="3" t="n">
+        <v>-0.002738702850740626</v>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -11733,6 +14151,12 @@
       <c r="H403" s="2" t="n">
         <v>0.01109285127362364</v>
       </c>
+      <c r="I403" s="1" t="n">
+        <v>0.04916</v>
+      </c>
+      <c r="J403" s="3" t="n">
+        <v>-0.001219016659894302</v>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -11761,6 +14185,12 @@
       <c r="H404" s="2" t="n">
         <v>0.008812999173781351</v>
       </c>
+      <c r="I404" s="1" t="n">
+        <v>0.14828</v>
+      </c>
+      <c r="J404" s="2" t="n">
+        <v>0.0120120120120119</v>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -11789,6 +14219,12 @@
       <c r="H405" s="2" t="n">
         <v>0.002582159624413122</v>
       </c>
+      <c r="I405" s="1" t="n">
+        <v>0.04265</v>
+      </c>
+      <c r="J405" s="3" t="n">
+        <v>-0.00140482322641062</v>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -11817,6 +14253,12 @@
       <c r="H406" s="2" t="n">
         <v>0.002722513089005285</v>
       </c>
+      <c r="I406" s="1" t="n">
+        <v>0.4787</v>
+      </c>
+      <c r="J406" s="3" t="n">
+        <v>-0.0002088554720133438</v>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -11845,6 +14287,12 @@
       <c r="H407" s="3" t="n">
         <v>-0.002048760499897501</v>
       </c>
+      <c r="I407" s="1" t="n">
+        <v>0.0004855</v>
+      </c>
+      <c r="J407" s="3" t="n">
+        <v>-0.003284746458632804</v>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -11873,6 +14321,12 @@
       <c r="H408" s="2" t="n">
         <v>0.003289473684210535</v>
       </c>
+      <c r="I408" s="1" t="n">
+        <v>0.01232</v>
+      </c>
+      <c r="J408" s="2" t="n">
+        <v>0.009836065573770375</v>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -11901,6 +14355,12 @@
       <c r="H409" s="2" t="n">
         <v>0.006635071090047364</v>
       </c>
+      <c r="I409" s="1" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="J409" s="3" t="n">
+        <v>-0.001883239171374732</v>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -11929,6 +14389,12 @@
       <c r="H410" s="3" t="n">
         <v>-0.0007218479307026527</v>
       </c>
+      <c r="I410" s="1" t="n">
+        <v>0.04159</v>
+      </c>
+      <c r="J410" s="2" t="n">
+        <v>0.001444738743077402</v>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -11957,6 +14423,12 @@
       <c r="H411" s="2" t="n">
         <v>0.003030303030303023</v>
       </c>
+      <c r="I411" s="1" t="n">
+        <v>0.0298</v>
+      </c>
+      <c r="J411" s="2" t="n">
+        <v>0.0003356831151392948</v>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
@@ -11985,6 +14457,12 @@
       <c r="H412" s="2" t="n">
         <v>0.003292361720807782</v>
       </c>
+      <c r="I412" s="1" t="n">
+        <v>0.004569</v>
+      </c>
+      <c r="J412" s="3" t="n">
+        <v>-0.0004375410194706334</v>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -12013,6 +14491,12 @@
       <c r="H413" s="3" t="n">
         <v>-0.0007914523149979343</v>
       </c>
+      <c r="I413" s="1" t="n">
+        <v>0.2524</v>
+      </c>
+      <c r="J413" s="3" t="n">
+        <v>-0.0003960396039603524</v>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -12041,6 +14525,12 @@
       <c r="H414" s="2" t="n">
         <v>0.0007855459544384226</v>
       </c>
+      <c r="I414" s="1" t="n">
+        <v>1.283</v>
+      </c>
+      <c r="J414" s="2" t="n">
+        <v>0.007064364207221269</v>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -12069,6 +14559,12 @@
       <c r="H415" s="2" t="n">
         <v>0.006322052807735182</v>
       </c>
+      <c r="I415" s="1" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="J415" s="2" t="n">
+        <v>0.001478196600147821</v>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -12097,6 +14593,12 @@
       <c r="H416" s="3" t="n">
         <v>-0.00832049306625576</v>
       </c>
+      <c r="I416" s="1" t="n">
+        <v>0.03221</v>
+      </c>
+      <c r="J416" s="2" t="n">
+        <v>0.0009322560596644576</v>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -12125,6 +14627,12 @@
       <c r="H417" s="2" t="n">
         <v>0.005537377296753032</v>
       </c>
+      <c r="I417" s="1" t="n">
+        <v>0.03996</v>
+      </c>
+      <c r="J417" s="2" t="n">
+        <v>0.000250312891113969</v>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -12153,6 +14661,12 @@
       <c r="H418" s="3" t="n">
         <v>-0.001180637544273996</v>
       </c>
+      <c r="I418" s="1" t="n">
+        <v>0.0759</v>
+      </c>
+      <c r="J418" s="3" t="n">
+        <v>-0.003152088258471291</v>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -12181,6 +14695,12 @@
       <c r="H419" s="2" t="n">
         <v>0.001508295625942754</v>
       </c>
+      <c r="I419" s="1" t="n">
+        <v>0.00665</v>
+      </c>
+      <c r="J419" s="2" t="n">
+        <v>0.001506024096385481</v>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -12209,6 +14729,12 @@
       <c r="H420" s="2" t="n">
         <v>0.005656108597285072</v>
       </c>
+      <c r="I420" s="1" t="n">
+        <v>0.0885</v>
+      </c>
+      <c r="J420" s="3" t="n">
+        <v>-0.004499437570303841</v>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -12237,6 +14763,12 @@
       <c r="H421" s="2" t="n">
         <v>0.003732890916632037</v>
       </c>
+      <c r="I421" s="1" t="n">
+        <v>0.2426</v>
+      </c>
+      <c r="J421" s="2" t="n">
+        <v>0.002479338842975278</v>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
@@ -12265,6 +14797,12 @@
       <c r="H422" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="I422" s="1" t="n">
+        <v>0.0194</v>
+      </c>
+      <c r="J422" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -12293,6 +14831,12 @@
       <c r="H423" s="2" t="n">
         <v>0.001330671989354662</v>
       </c>
+      <c r="I423" s="1" t="n">
+        <v>0.1505</v>
+      </c>
+      <c r="J423" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -12321,6 +14865,12 @@
       <c r="H424" s="3" t="n">
         <v>-0.001902949571836264</v>
       </c>
+      <c r="I424" s="1" t="n">
+        <v>0.0002095</v>
+      </c>
+      <c r="J424" s="3" t="n">
+        <v>-0.001429933269780778</v>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -12349,6 +14899,12 @@
       <c r="H425" s="2" t="n">
         <v>0.003241491085899517</v>
       </c>
+      <c r="I425" s="1" t="n">
+        <v>1.236</v>
+      </c>
+      <c r="J425" s="3" t="n">
+        <v>-0.001615508885298871</v>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
@@ -12377,6 +14933,12 @@
       <c r="H426" s="2" t="n">
         <v>0.004989308624376261</v>
       </c>
+      <c r="I426" s="1" t="n">
+        <v>1.408</v>
+      </c>
+      <c r="J426" s="3" t="n">
+        <v>-0.001418439716312058</v>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -12405,6 +14967,12 @@
       <c r="H427" s="2" t="n">
         <v>0.002578648788034964</v>
       </c>
+      <c r="I427" s="1" t="n">
+        <v>0.01941</v>
+      </c>
+      <c r="J427" s="3" t="n">
+        <v>-0.001543209876543147</v>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
@@ -12433,6 +15001,12 @@
       <c r="H428" s="2" t="n">
         <v>0.003349063784442046</v>
       </c>
+      <c r="I428" s="1" t="n">
+        <v>0.06580999999999999</v>
+      </c>
+      <c r="J428" s="3" t="n">
+        <v>-0.001517220452131738</v>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
@@ -12461,6 +15035,12 @@
       <c r="H429" s="2" t="n">
         <v>0.001510574018126932</v>
       </c>
+      <c r="I429" s="1" t="n">
+        <v>0.1327</v>
+      </c>
+      <c r="J429" s="2" t="n">
+        <v>0.0007541478129714686</v>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
@@ -12489,6 +15069,12 @@
       <c r="H430" s="2" t="n">
         <v>0.0009009009009008642</v>
       </c>
+      <c r="I430" s="1" t="n">
+        <v>0.011118</v>
+      </c>
+      <c r="J430" s="2" t="n">
+        <v>0.0007200720072006595</v>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -12517,6 +15103,12 @@
       <c r="H431" s="2" t="n">
         <v>0.005269497139415754</v>
       </c>
+      <c r="I431" s="1" t="n">
+        <v>0.006679</v>
+      </c>
+      <c r="J431" s="2" t="n">
+        <v>0.0002995357196346062</v>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
@@ -12545,6 +15137,12 @@
       <c r="H432" s="2" t="n">
         <v>0.004002287021154982</v>
       </c>
+      <c r="I432" s="1" t="n">
+        <v>0.001758</v>
+      </c>
+      <c r="J432" s="2" t="n">
+        <v>0.001138952164009139</v>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
@@ -12573,6 +15171,12 @@
       <c r="H433" s="3" t="n">
         <v>-0.0150862068965517</v>
       </c>
+      <c r="I433" s="1" t="n">
+        <v>0.001372</v>
+      </c>
+      <c r="J433" s="2" t="n">
+        <v>0.0007293946024798803</v>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
@@ -12601,6 +15205,12 @@
       <c r="H434" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="I434" s="1" t="n">
+        <v>0.000408</v>
+      </c>
+      <c r="J434" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
@@ -12629,6 +15239,12 @@
       <c r="H435" s="2" t="n">
         <v>0.002926983624713308</v>
       </c>
+      <c r="I435" s="1" t="n">
+        <v>0.12663</v>
+      </c>
+      <c r="J435" s="3" t="n">
+        <v>-0.001183151916706194</v>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -12657,6 +15273,12 @@
       <c r="H436" s="2" t="n">
         <v>0.002199223803363564</v>
       </c>
+      <c r="I436" s="1" t="n">
+        <v>0.07742</v>
+      </c>
+      <c r="J436" s="3" t="n">
+        <v>-0.0006454111268877565</v>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
@@ -12685,6 +15307,12 @@
       <c r="H437" s="2" t="n">
         <v>0.009325114588272333</v>
       </c>
+      <c r="I437" s="1" t="n">
+        <v>0.6356000000000001</v>
+      </c>
+      <c r="J437" s="3" t="n">
+        <v>-0.004697776385843865</v>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -12713,6 +15341,12 @@
       <c r="H438" s="3" t="n">
         <v>-0.01518585675430637</v>
       </c>
+      <c r="I438" s="1" t="n">
+        <v>0.04352</v>
+      </c>
+      <c r="J438" s="2" t="n">
+        <v>0.001611047180667448</v>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
@@ -12741,6 +15375,12 @@
       <c r="H439" s="2" t="n">
         <v>0.00485575549842912</v>
       </c>
+      <c r="I439" s="1" t="n">
+        <v>0.07027</v>
+      </c>
+      <c r="J439" s="3" t="n">
+        <v>-0.001279135872655013</v>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
@@ -12769,6 +15409,12 @@
       <c r="H440" s="2" t="n">
         <v>0.001980198019801957</v>
       </c>
+      <c r="I440" s="1" t="n">
+        <v>0.001516</v>
+      </c>
+      <c r="J440" s="3" t="n">
+        <v>-0.001317523056653523</v>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -12797,6 +15443,12 @@
       <c r="H441" s="3" t="n">
         <v>-0.0004207426107079553</v>
       </c>
+      <c r="I441" s="1" t="n">
+        <v>0.009497999999999999</v>
+      </c>
+      <c r="J441" s="3" t="n">
+        <v>-0.0005261496369567291</v>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
@@ -12825,6 +15477,12 @@
       <c r="H442" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="I442" s="1" t="n">
+        <v>1.056</v>
+      </c>
+      <c r="J442" s="3" t="n">
+        <v>-0.005649717514124298</v>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
@@ -12853,6 +15511,12 @@
       <c r="H443" s="3" t="n">
         <v>-0.004516711833784977</v>
       </c>
+      <c r="I443" s="1" t="n">
+        <v>0.02202</v>
+      </c>
+      <c r="J443" s="3" t="n">
+        <v>-0.0009074410163339013</v>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
@@ -12881,6 +15545,12 @@
       <c r="H444" s="2" t="n">
         <v>0.009785770960063571</v>
       </c>
+      <c r="I444" s="1" t="n">
+        <v>0.0003784</v>
+      </c>
+      <c r="J444" s="3" t="n">
+        <v>-0.008905185961236324</v>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
@@ -12909,6 +15579,12 @@
       <c r="H445" s="2" t="n">
         <v>0.004277159965782843</v>
       </c>
+      <c r="I445" s="1" t="n">
+        <v>0.03521</v>
+      </c>
+      <c r="J445" s="3" t="n">
+        <v>-0.0002839295854628921</v>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
@@ -12937,6 +15613,12 @@
       <c r="H446" s="2" t="n">
         <v>0.001760770043432297</v>
       </c>
+      <c r="I446" s="1" t="n">
+        <v>0.0853</v>
+      </c>
+      <c r="J446" s="3" t="n">
+        <v>-0.0004687133817670304</v>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
@@ -12965,6 +15647,12 @@
       <c r="H447" s="2" t="n">
         <v>0.003707136237256722</v>
       </c>
+      <c r="I447" s="1" t="n">
+        <v>3.251</v>
+      </c>
+      <c r="J447" s="2" t="n">
+        <v>0.0006155740227761711</v>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
@@ -12993,6 +15681,12 @@
       <c r="H448" s="2" t="n">
         <v>0.001563966218329729</v>
       </c>
+      <c r="I448" s="1" t="n">
+        <v>0.06388000000000001</v>
+      </c>
+      <c r="J448" s="3" t="n">
+        <v>-0.002498438475952428</v>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
@@ -13021,6 +15715,12 @@
       <c r="H449" s="2" t="n">
         <v>0.0008242324335462837</v>
       </c>
+      <c r="I449" s="1" t="n">
+        <v>0.4851</v>
+      </c>
+      <c r="J449" s="3" t="n">
+        <v>-0.001235330450895707</v>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
@@ -13049,6 +15749,12 @@
       <c r="H450" s="3" t="n">
         <v>-0.003728362183755026</v>
       </c>
+      <c r="I450" s="1" t="n">
+        <v>0.03712</v>
+      </c>
+      <c r="J450" s="3" t="n">
+        <v>-0.007751937984496087</v>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -13077,6 +15783,12 @@
       <c r="H451" s="2" t="n">
         <v>0.001838235294117572</v>
       </c>
+      <c r="I451" s="1" t="n">
+        <v>0.00545</v>
+      </c>
+      <c r="J451" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
@@ -13105,6 +15817,12 @@
       <c r="H452" s="3" t="n">
         <v>-0.0008520306731042955</v>
       </c>
+      <c r="I452" s="1" t="n">
+        <v>0.10461</v>
+      </c>
+      <c r="J452" s="3" t="n">
+        <v>-0.008811824900511658</v>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
@@ -13133,6 +15851,12 @@
       <c r="H453" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="I453" s="1" t="n">
+        <v>0.01598</v>
+      </c>
+      <c r="J453" s="3" t="n">
+        <v>-0.002496878901373182</v>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
@@ -13161,6 +15885,12 @@
       <c r="H454" s="2" t="n">
         <v>0.01053370786516863</v>
       </c>
+      <c r="I454" s="1" t="n">
+        <v>2.878</v>
+      </c>
+      <c r="J454" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
@@ -13189,6 +15919,12 @@
       <c r="H455" s="2" t="n">
         <v>0.001118568232662193</v>
       </c>
+      <c r="I455" s="1" t="n">
+        <v>0.895</v>
+      </c>
+      <c r="J455" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
@@ -13217,6 +15953,12 @@
       <c r="H456" s="2" t="n">
         <v>0.001020061203672259</v>
       </c>
+      <c r="I456" s="1" t="n">
+        <v>2.942</v>
+      </c>
+      <c r="J456" s="3" t="n">
+        <v>-0.0006793478260868817</v>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -13245,6 +15987,12 @@
       <c r="H457" s="2" t="n">
         <v>0.003051881993896288</v>
       </c>
+      <c r="I457" s="1" t="n">
+        <v>0.00988</v>
+      </c>
+      <c r="J457" s="2" t="n">
+        <v>0.002028397565922838</v>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
@@ -13273,6 +16021,12 @@
       <c r="H458" s="2" t="n">
         <v>0.004030957755562725</v>
       </c>
+      <c r="I458" s="1" t="n">
+        <v>0.06232</v>
+      </c>
+      <c r="J458" s="2" t="n">
+        <v>0.0008029548739361078</v>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
@@ -13301,6 +16055,12 @@
       <c r="H459" s="2" t="n">
         <v>0.0006958942240779118</v>
       </c>
+      <c r="I459" s="1" t="n">
+        <v>0.01424</v>
+      </c>
+      <c r="J459" s="3" t="n">
+        <v>-0.009735744089012602</v>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
@@ -13329,6 +16089,12 @@
       <c r="H460" s="3" t="n">
         <v>-0.000687500000000037</v>
       </c>
+      <c r="I460" s="1" t="n">
+        <v>0.015966</v>
+      </c>
+      <c r="J460" s="3" t="n">
+        <v>-0.001438488961160718</v>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
@@ -13357,6 +16123,12 @@
       <c r="H461" s="2" t="n">
         <v>0.009140767824497097</v>
       </c>
+      <c r="I461" s="1" t="n">
+        <v>0.01661</v>
+      </c>
+      <c r="J461" s="2" t="n">
+        <v>0.003019323671497671</v>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
@@ -13385,6 +16157,12 @@
       <c r="H462" s="2" t="n">
         <v>0.002394636015325599</v>
       </c>
+      <c r="I462" s="1" t="n">
+        <v>0.0002093</v>
+      </c>
+      <c r="J462" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
@@ -13413,6 +16191,12 @@
       <c r="H463" s="2" t="n">
         <v>0.003051881993896182</v>
       </c>
+      <c r="I463" s="1" t="n">
+        <v>0.0988</v>
+      </c>
+      <c r="J463" s="2" t="n">
+        <v>0.002028397565922979</v>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
@@ -13441,6 +16225,12 @@
       <c r="H464" s="2" t="n">
         <v>0.003456221198156674</v>
       </c>
+      <c r="I464" s="1" t="n">
+        <v>0.02612</v>
+      </c>
+      <c r="J464" s="3" t="n">
+        <v>-0.0003827018752391731</v>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
@@ -13469,6 +16259,12 @@
       <c r="H465" s="2" t="n">
         <v>0.006657789613848162</v>
       </c>
+      <c r="I465" s="1" t="n">
+        <v>0.01513</v>
+      </c>
+      <c r="J465" s="2" t="n">
+        <v>0.0006613756613756345</v>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
@@ -13497,6 +16293,12 @@
       <c r="H466" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="I466" s="1" t="n">
+        <v>0.05473</v>
+      </c>
+      <c r="J466" s="2" t="n">
+        <v>0.0005484460694698765</v>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
@@ -13525,6 +16327,12 @@
       <c r="H467" s="2" t="n">
         <v>0.004091174751607283</v>
       </c>
+      <c r="I467" s="1" t="n">
+        <v>0.03428</v>
+      </c>
+      <c r="J467" s="3" t="n">
+        <v>-0.002328288707799874</v>
+      </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
@@ -13553,6 +16361,12 @@
       <c r="H468" s="2" t="n">
         <v>0.02484241750092702</v>
       </c>
+      <c r="I468" s="1" t="n">
+        <v>27.48</v>
+      </c>
+      <c r="J468" s="3" t="n">
+        <v>-0.005788712011577429</v>
+      </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
@@ -13581,6 +16395,12 @@
       <c r="H469" s="3" t="n">
         <v>-0.003733831177490279</v>
       </c>
+      <c r="I469" s="1" t="n">
+        <v>0.000746</v>
+      </c>
+      <c r="J469" s="3" t="n">
+        <v>-0.001472359791192575</v>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
@@ -13609,6 +16429,12 @@
       <c r="H470" s="2" t="n">
         <v>0.002283105022831052</v>
       </c>
+      <c r="I470" s="1" t="n">
+        <v>0.874</v>
+      </c>
+      <c r="J470" s="3" t="n">
+        <v>-0.004555808656036451</v>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
@@ -13637,6 +16463,12 @@
       <c r="H471" s="3" t="n">
         <v>-0.002020202020202113</v>
       </c>
+      <c r="I471" s="1" t="n">
+        <v>0.009849999999999999</v>
+      </c>
+      <c r="J471" s="3" t="n">
+        <v>-0.003036437246963615</v>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
@@ -13665,6 +16497,12 @@
       <c r="H472" s="3" t="n">
         <v>-0.002568493150684827</v>
       </c>
+      <c r="I472" s="1" t="n">
+        <v>0.04655</v>
+      </c>
+      <c r="J472" s="3" t="n">
+        <v>-0.001072961373390589</v>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -13693,6 +16531,12 @@
       <c r="H473" s="2" t="n">
         <v>0.00183284457478006</v>
       </c>
+      <c r="I473" s="1" t="n">
+        <v>0.2731</v>
+      </c>
+      <c r="J473" s="3" t="n">
+        <v>-0.0007317965605560848</v>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
@@ -13721,6 +16565,12 @@
       <c r="H474" s="3" t="n">
         <v>-0.002516010978956976</v>
       </c>
+      <c r="I474" s="1" t="n">
+        <v>0.0437</v>
+      </c>
+      <c r="J474" s="2" t="n">
+        <v>0.002063746847053423</v>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
@@ -13749,6 +16599,12 @@
       <c r="H475" s="2" t="n">
         <v>0.003564638783270023</v>
       </c>
+      <c r="I475" s="1" t="n">
+        <v>0.008454</v>
+      </c>
+      <c r="J475" s="2" t="n">
+        <v>0.0009471939379587174</v>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
@@ -13777,6 +16633,12 @@
       <c r="H476" s="2" t="n">
         <v>0.001226391954868811</v>
       </c>
+      <c r="I476" s="1" t="n">
+        <v>0.08147</v>
+      </c>
+      <c r="J476" s="3" t="n">
+        <v>-0.002082312591866775</v>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
@@ -13805,6 +16667,12 @@
       <c r="H477" s="2" t="n">
         <v>0.002954209748892256</v>
       </c>
+      <c r="I477" s="1" t="n">
+        <v>0.1358</v>
+      </c>
+      <c r="J477" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
@@ -13833,6 +16701,12 @@
       <c r="H478" s="2" t="n">
         <v>0.002271580010095941</v>
       </c>
+      <c r="I478" s="1" t="n">
+        <v>0.3972</v>
+      </c>
+      <c r="J478" s="2" t="n">
+        <v>0.0002518257365902518</v>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
@@ -13861,6 +16735,12 @@
       <c r="H479" s="2" t="n">
         <v>0.003458144526592088</v>
       </c>
+      <c r="I479" s="1" t="n">
+        <v>0.008433</v>
+      </c>
+      <c r="J479" s="2" t="n">
+        <v>0.002139037433154951</v>
+      </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
@@ -13889,6 +16769,12 @@
       <c r="H480" s="2" t="n">
         <v>0.0006273525721455203</v>
       </c>
+      <c r="I480" s="1" t="n">
+        <v>0.01592</v>
+      </c>
+      <c r="J480" s="3" t="n">
+        <v>-0.001880877742946632</v>
+      </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
@@ -13917,6 +16803,12 @@
       <c r="H481" s="2" t="n">
         <v>0.001689189189189256</v>
       </c>
+      <c r="I481" s="1" t="n">
+        <v>0.07725</v>
+      </c>
+      <c r="J481" s="2" t="n">
+        <v>0.002075496173303846</v>
+      </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
@@ -13945,6 +16837,12 @@
       <c r="H482" s="2" t="n">
         <v>0.002178217821782158</v>
       </c>
+      <c r="I482" s="1" t="n">
+        <v>0.05059</v>
+      </c>
+      <c r="J482" s="3" t="n">
+        <v>-0.0003951788184153168</v>
+      </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
@@ -13973,6 +16871,12 @@
       <c r="H483" s="2" t="n">
         <v>0.003102378490175855</v>
       </c>
+      <c r="I483" s="1" t="n">
+        <v>0.00971</v>
+      </c>
+      <c r="J483" s="2" t="n">
+        <v>0.001030927835051504</v>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
@@ -14001,6 +16905,12 @@
       <c r="H484" s="2" t="n">
         <v>0.001472103636095819</v>
       </c>
+      <c r="I484" s="1" t="n">
+        <v>0.06797</v>
+      </c>
+      <c r="J484" s="3" t="n">
+        <v>-0.0008819638394824433</v>
+      </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
@@ -14029,6 +16939,12 @@
       <c r="H485" s="3" t="n">
         <v>-0.001112347052280218</v>
       </c>
+      <c r="I485" s="1" t="n">
+        <v>0.0004487</v>
+      </c>
+      <c r="J485" s="3" t="n">
+        <v>-0.0006681514476614862</v>
+      </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
@@ -14057,6 +16973,12 @@
       <c r="H486" s="3" t="n">
         <v>-0.0008789552988448093</v>
       </c>
+      <c r="I486" s="1" t="n">
+        <v>0.07936</v>
+      </c>
+      <c r="J486" s="3" t="n">
+        <v>-0.002639185622722155</v>
+      </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
@@ -14085,6 +17007,12 @@
       <c r="H487" s="2" t="n">
         <v>0.001157407407407436</v>
       </c>
+      <c r="I487" s="1" t="n">
+        <v>0.000173</v>
+      </c>
+      <c r="J487" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
@@ -14113,6 +17041,12 @@
       <c r="H488" s="2" t="n">
         <v>0.00022815423226092</v>
       </c>
+      <c r="I488" s="1" t="n">
+        <v>0.08742999999999999</v>
+      </c>
+      <c r="J488" s="3" t="n">
+        <v>-0.002851277372262776</v>
+      </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
@@ -14141,6 +17075,12 @@
       <c r="H489" s="2" t="n">
         <v>0.002317741255794332</v>
       </c>
+      <c r="I489" s="1" t="n">
+        <v>0.04744</v>
+      </c>
+      <c r="J489" s="3" t="n">
+        <v>-0.002732814799243182</v>
+      </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
@@ -14169,6 +17109,12 @@
       <c r="H490" s="2" t="n">
         <v>0.006563402467839334</v>
       </c>
+      <c r="I490" s="1" t="n">
+        <v>0.03847</v>
+      </c>
+      <c r="J490" s="2" t="n">
+        <v>0.003390714658320245</v>
+      </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
@@ -14197,6 +17143,12 @@
       <c r="H491" s="2" t="n">
         <v>0.001027089485171354</v>
       </c>
+      <c r="I491" s="1" t="n">
+        <v>0.07776</v>
+      </c>
+      <c r="J491" s="3" t="n">
+        <v>-0.002693343593689904</v>
+      </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
@@ -14225,6 +17177,12 @@
       <c r="H492" s="2" t="n">
         <v>0.001889466225791356</v>
       </c>
+      <c r="I492" s="1" t="n">
+        <v>0.06358999999999999</v>
+      </c>
+      <c r="J492" s="3" t="n">
+        <v>-0.0006286342920008211</v>
+      </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
@@ -14253,6 +17211,12 @@
       <c r="H493" s="2" t="n">
         <v>0.001923076923077012</v>
       </c>
+      <c r="I493" s="1" t="n">
+        <v>0.00523</v>
+      </c>
+      <c r="J493" s="2" t="n">
+        <v>0.003838771593090221</v>
+      </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
@@ -14281,6 +17245,12 @@
       <c r="H494" s="2" t="n">
         <v>0.0007241129616219333</v>
       </c>
+      <c r="I494" s="1" t="n">
+        <v>0.2762</v>
+      </c>
+      <c r="J494" s="3" t="n">
+        <v>-0.0007235890014470984</v>
+      </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
@@ -14309,6 +17279,12 @@
       <c r="H495" s="2" t="n">
         <v>0.000943247916994254</v>
       </c>
+      <c r="I495" s="1" t="n">
+        <v>0.06358999999999999</v>
+      </c>
+      <c r="J495" s="3" t="n">
+        <v>-0.001256478718391874</v>
+      </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
@@ -14337,6 +17313,12 @@
       <c r="H496" s="2" t="n">
         <v>0.001364721937905001</v>
       </c>
+      <c r="I496" s="1" t="n">
+        <v>0.2928</v>
+      </c>
+      <c r="J496" s="3" t="n">
+        <v>-0.00238500851788749</v>
+      </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
@@ -14365,6 +17347,12 @@
       <c r="H497" s="3" t="n">
         <v>-0.01214321482223351</v>
       </c>
+      <c r="I497" s="1" t="n">
+        <v>0.07846</v>
+      </c>
+      <c r="J497" s="3" t="n">
+        <v>-0.005702699277657992</v>
+      </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
@@ -14393,6 +17381,12 @@
       <c r="H498" s="2" t="n">
         <v>0.0009699321047526951</v>
       </c>
+      <c r="I498" s="1" t="n">
+        <v>0.1031</v>
+      </c>
+      <c r="J498" s="3" t="n">
+        <v>-0.0009689922480620432</v>
+      </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
@@ -14421,6 +17415,12 @@
       <c r="H499" s="2" t="n">
         <v>0.004349927501208304</v>
       </c>
+      <c r="I499" s="1" t="n">
+        <v>0.0415</v>
+      </c>
+      <c r="J499" s="3" t="n">
+        <v>-0.001443695861405138</v>
+      </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
@@ -14449,6 +17449,12 @@
       <c r="H500" s="2" t="n">
         <v>0.00292468925176705</v>
       </c>
+      <c r="I500" s="1" t="n">
+        <v>0.0411</v>
+      </c>
+      <c r="J500" s="3" t="n">
+        <v>-0.001215066828675612</v>
+      </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
@@ -14477,6 +17483,12 @@
       <c r="H501" s="2" t="n">
         <v>0.001004016064257057</v>
       </c>
+      <c r="I501" s="1" t="n">
+        <v>0.09959999999999999</v>
+      </c>
+      <c r="J501" s="3" t="n">
+        <v>-0.001003009027081273</v>
+      </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
@@ -14505,6 +17517,12 @@
       <c r="H502" s="2" t="n">
         <v>0.0009082652134423144</v>
       </c>
+      <c r="I502" s="1" t="n">
+        <v>0.003307</v>
+      </c>
+      <c r="J502" s="2" t="n">
+        <v>0.0003024803387780196</v>
+      </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
@@ -14533,6 +17551,12 @@
       <c r="H503" s="3" t="n">
         <v>-0.001095290251916713</v>
       </c>
+      <c r="I503" s="1" t="n">
+        <v>0.0092</v>
+      </c>
+      <c r="J503" s="2" t="n">
+        <v>0.008771929824561427</v>
+      </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
@@ -14561,6 +17585,12 @@
       <c r="H504" s="2" t="n">
         <v>0.006993006993007105</v>
       </c>
+      <c r="I504" s="1" t="n">
+        <v>0.1577</v>
+      </c>
+      <c r="J504" s="3" t="n">
+        <v>-0.004419191919191958</v>
+      </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
@@ -14589,6 +17619,12 @@
       <c r="H505" s="2" t="n">
         <v>0.002291825821237758</v>
       </c>
+      <c r="I505" s="1" t="n">
+        <v>0.1312</v>
+      </c>
+      <c r="J505" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
@@ -14617,6 +17653,12 @@
       <c r="H506" s="2" t="n">
         <v>0.002972651605231746</v>
       </c>
+      <c r="I506" s="1" t="n">
+        <v>0.01685</v>
+      </c>
+      <c r="J506" s="3" t="n">
+        <v>-0.001185536455245951</v>
+      </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
@@ -14645,6 +17687,12 @@
       <c r="H507" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="I507" s="1" t="n">
+        <v>0.002884</v>
+      </c>
+      <c r="J507" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
@@ -14673,6 +17721,12 @@
       <c r="H508" s="2" t="n">
         <v>0.00362647325475975</v>
       </c>
+      <c r="I508" s="1" t="n">
+        <v>2.207</v>
+      </c>
+      <c r="J508" s="3" t="n">
+        <v>-0.003161698283649556</v>
+      </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
@@ -14701,6 +17755,12 @@
       <c r="H509" s="2" t="n">
         <v>0.002004738472753763</v>
       </c>
+      <c r="I509" s="1" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="J509" s="2" t="n">
+        <v>0.0003637686431429462</v>
+      </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
@@ -14729,6 +17789,12 @@
       <c r="H510" s="2" t="n">
         <v>0.006837606837606796</v>
       </c>
+      <c r="I510" s="1" t="n">
+        <v>0.02939</v>
+      </c>
+      <c r="J510" s="3" t="n">
+        <v>-0.002037351443123973</v>
+      </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
@@ -14757,6 +17823,12 @@
       <c r="H511" s="2" t="n">
         <v>0.001981669556601356</v>
       </c>
+      <c r="I511" s="1" t="n">
+        <v>0.04037</v>
+      </c>
+      <c r="J511" s="3" t="n">
+        <v>-0.001977750309023405</v>
+      </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
@@ -14785,6 +17857,12 @@
       <c r="H512" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="I512" s="1" t="n">
+        <v>0.08599999999999999</v>
+      </c>
+      <c r="J512" s="2" t="n">
+        <v>0.01176470588235279</v>
+      </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
@@ -14813,6 +17891,12 @@
       <c r="H513" s="2" t="n">
         <v>0.003518267929634639</v>
       </c>
+      <c r="I513" s="1" t="n">
+        <v>0.014804</v>
+      </c>
+      <c r="J513" s="3" t="n">
+        <v>-0.001887810140237341</v>
+      </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
@@ -14841,6 +17925,12 @@
       <c r="H514" s="2" t="n">
         <v>0.0005747126436782572</v>
       </c>
+      <c r="I514" s="1" t="n">
+        <v>0.1738</v>
+      </c>
+      <c r="J514" s="3" t="n">
+        <v>-0.001723147616312434</v>
+      </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
@@ -14869,6 +17959,12 @@
       <c r="H515" s="2" t="n">
         <v>0.0009310986964618516</v>
       </c>
+      <c r="I515" s="1" t="n">
+        <v>0.1073</v>
+      </c>
+      <c r="J515" s="3" t="n">
+        <v>-0.001860465116278994</v>
+      </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
@@ -14897,6 +17993,12 @@
       <c r="H516" s="3" t="n">
         <v>-0.003759398496240611</v>
       </c>
+      <c r="I516" s="1" t="n">
+        <v>0.00265</v>
+      </c>
+      <c r="J516" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
@@ -14925,6 +18027,12 @@
       <c r="H517" s="2" t="n">
         <v>0.007804370447450479</v>
       </c>
+      <c r="I517" s="1" t="n">
+        <v>0.007714</v>
+      </c>
+      <c r="J517" s="3" t="n">
+        <v>-0.004388229220443896</v>
+      </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
@@ -14953,6 +18061,12 @@
       <c r="H518" s="2" t="n">
         <v>0.001297858533419804</v>
       </c>
+      <c r="I518" s="1" t="n">
+        <v>0.01544</v>
+      </c>
+      <c r="J518" s="2" t="n">
+        <v>0.0006480881399871243</v>
+      </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
@@ -14981,6 +18095,12 @@
       <c r="H519" s="2" t="n">
         <v>0.005384238864414941</v>
       </c>
+      <c r="I519" s="1" t="n">
+        <v>0.004088</v>
+      </c>
+      <c r="J519" s="3" t="n">
+        <v>-0.004868549172346654</v>
+      </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
@@ -15009,6 +18129,12 @@
       <c r="H520" s="2" t="n">
         <v>0.0008635578583766259</v>
       </c>
+      <c r="I520" s="1" t="n">
+        <v>0.001158</v>
+      </c>
+      <c r="J520" s="3" t="n">
+        <v>-0.0008628127696291049</v>
+      </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
@@ -15037,6 +18163,12 @@
       <c r="H521" s="2" t="n">
         <v>0.002250562640660203</v>
       </c>
+      <c r="I521" s="1" t="n">
+        <v>0.01337</v>
+      </c>
+      <c r="J521" s="2" t="n">
+        <v>0.0007485029940119455</v>
+      </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
@@ -15065,6 +18197,12 @@
       <c r="H522" s="2" t="n">
         <v>0.0001462202076328411</v>
       </c>
+      <c r="I522" s="1" t="n">
+        <v>0.6845</v>
+      </c>
+      <c r="J522" s="2" t="n">
+        <v>0.000730994152046703</v>
+      </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
@@ -15093,6 +18231,12 @@
       <c r="H523" s="2" t="n">
         <v>0.002437275985662933</v>
       </c>
+      <c r="I523" s="1" t="n">
+        <v>0.06999</v>
+      </c>
+      <c r="J523" s="2" t="n">
+        <v>0.001001144164759734</v>
+      </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
@@ -15121,6 +18265,12 @@
       <c r="H524" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="I524" s="1" t="n">
+        <v>0.01151</v>
+      </c>
+      <c r="J524" s="3" t="n">
+        <v>-0.002599653379549438</v>
+      </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
@@ -15149,6 +18299,12 @@
       <c r="H525" s="2" t="n">
         <v>0.0006142506142505893</v>
       </c>
+      <c r="I525" s="1" t="n">
+        <v>0.01635</v>
+      </c>
+      <c r="J525" s="2" t="n">
+        <v>0.003683241252302089</v>
+      </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
@@ -15177,6 +18333,12 @@
       <c r="H526" s="2" t="n">
         <v>0.0008084668528592294</v>
       </c>
+      <c r="I526" s="1" t="n">
+        <v>0.13621</v>
+      </c>
+      <c r="J526" s="2" t="n">
+        <v>0.0002937504589849782</v>
+      </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
@@ -15205,6 +18367,12 @@
       <c r="H527" s="2" t="n">
         <v>0.002331002331002236</v>
       </c>
+      <c r="I527" s="1" t="n">
+        <v>0.04293</v>
+      </c>
+      <c r="J527" s="3" t="n">
+        <v>-0.001627906976744039</v>
+      </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
@@ -15233,6 +18401,12 @@
       <c r="H528" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="I528" s="1" t="n">
+        <v>0.272</v>
+      </c>
+      <c r="J528" s="2" t="n">
+        <v>0.001841620626151014</v>
+      </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
@@ -15261,6 +18435,12 @@
       <c r="H529" s="2" t="n">
         <v>0.002364394993045879</v>
       </c>
+      <c r="I529" s="1" t="n">
+        <v>0.000722</v>
+      </c>
+      <c r="J529" s="2" t="n">
+        <v>0.001803801859303424</v>
+      </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
@@ -15289,6 +18469,12 @@
       <c r="H530" s="2" t="n">
         <v>0.0009615384615385892</v>
       </c>
+      <c r="I530" s="1" t="n">
+        <v>0.004159</v>
+      </c>
+      <c r="J530" s="3" t="n">
+        <v>-0.001200768491834725</v>
+      </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
@@ -15317,6 +18503,12 @@
       <c r="H531" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="I531" s="1" t="n">
+        <v>1.313</v>
+      </c>
+      <c r="J531" s="2" t="n">
+        <v>0.003822629969418879</v>
+      </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
@@ -15345,6 +18537,12 @@
       <c r="H532" s="3" t="n">
         <v>-0.003392705682782116</v>
       </c>
+      <c r="I532" s="1" t="n">
+        <v>0.1176</v>
+      </c>
+      <c r="J532" s="2" t="n">
+        <v>0.0008510638297872584</v>
+      </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
@@ -15373,6 +18571,12 @@
       <c r="H533" s="2" t="n">
         <v>0.003937746109131725</v>
       </c>
+      <c r="I533" s="1" t="n">
+        <v>0.05347</v>
+      </c>
+      <c r="J533" s="3" t="n">
+        <v>-0.00130743369443408</v>
+      </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
@@ -15401,6 +18605,12 @@
       <c r="H534" s="2" t="n">
         <v>0.001330671989354662</v>
       </c>
+      <c r="I534" s="1" t="n">
+        <v>0.1502</v>
+      </c>
+      <c r="J534" s="3" t="n">
+        <v>-0.00199335548172754</v>
+      </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
@@ -15429,6 +18639,12 @@
       <c r="H535" s="2" t="n">
         <v>0.003521126760563441</v>
       </c>
+      <c r="I535" s="1" t="n">
+        <v>0.01708</v>
+      </c>
+      <c r="J535" s="3" t="n">
+        <v>-0.001169590643274806</v>
+      </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
@@ -15457,6 +18673,12 @@
       <c r="H536" s="2" t="n">
         <v>0.003026634382566462</v>
       </c>
+      <c r="I536" s="1" t="n">
+        <v>0.00497</v>
+      </c>
+      <c r="J536" s="3" t="n">
+        <v>-0.000201166767250077</v>
+      </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
@@ -15485,6 +18707,12 @@
       <c r="H537" s="2" t="n">
         <v>0.002759572266298803</v>
       </c>
+      <c r="I537" s="1" t="n">
+        <v>0.2909</v>
+      </c>
+      <c r="J537" s="2" t="n">
+        <v>0.0006879944960439558</v>
+      </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
@@ -15513,6 +18741,12 @@
       <c r="H538" s="2" t="n">
         <v>0.003808073115003917</v>
       </c>
+      <c r="I538" s="1" t="n">
+        <v>0.01324</v>
+      </c>
+      <c r="J538" s="2" t="n">
+        <v>0.004552352048558367</v>
+      </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
@@ -15541,6 +18775,12 @@
       <c r="H539" s="2" t="n">
         <v>0.003274662300450275</v>
       </c>
+      <c r="I539" s="1" t="n">
+        <v>0.02464</v>
+      </c>
+      <c r="J539" s="2" t="n">
+        <v>0.005303957568339379</v>
+      </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
@@ -15569,6 +18809,12 @@
       <c r="H540" s="2" t="n">
         <v>0.001941404871161295</v>
       </c>
+      <c r="I540" s="1" t="n">
+        <v>0.05675</v>
+      </c>
+      <c r="J540" s="3" t="n">
+        <v>-0.0003522987493394255</v>
+      </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
@@ -15597,6 +18843,12 @@
       <c r="H541" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="I541" s="1" t="n">
+        <v>0.0116</v>
+      </c>
+      <c r="J541" s="2" t="n">
+        <v>0.008695652173912992</v>
+      </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
@@ -15625,6 +18877,12 @@
       <c r="H542" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="I542" s="1" t="n">
+        <v>1.11e-05</v>
+      </c>
+      <c r="J542" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
@@ -15652,6 +18910,12 @@
       </c>
       <c r="H543" s="2" t="n">
         <v>0.002458344714558834</v>
+      </c>
+      <c r="I543" s="1" t="n">
+        <v>0.003661</v>
+      </c>
+      <c r="J543" s="3" t="n">
+        <v>-0.002452316076294249</v>
       </c>
     </row>
   </sheetData>

--- a/binance-usdt-perpetual-data/weeks/2026-03-09_2026-03-15/2026-03-12.xlsx
+++ b/binance-usdt-perpetual-data/weeks/2026-03-09_2026-03-15/2026-03-12.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J543"/>
+  <dimension ref="A1:L543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -436,6 +436,8 @@
     <col width="18" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -489,6 +491,16 @@
           <t>change_01:00</t>
         </is>
       </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>price_01:15</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>change_01:15</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -523,6 +535,12 @@
       <c r="J2" s="3" t="n">
         <v>-0.00248762551265725</v>
       </c>
+      <c r="K2" s="1" t="n">
+        <v>70826.5</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>0.004145512596035027</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -557,6 +575,12 @@
       <c r="J3" s="3" t="n">
         <v>-0.001232854856722795</v>
       </c>
+      <c r="K3" s="1" t="n">
+        <v>2070.26</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>0.002149267603179393</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -591,6 +615,12 @@
       <c r="J4" s="3" t="n">
         <v>-0.0008097165991903688</v>
       </c>
+      <c r="K4" s="1" t="n">
+        <v>86.56999999999999</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>0.002199583236860358</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -625,6 +655,12 @@
       <c r="J5" s="3" t="n">
         <v>-0.004576502732240511</v>
       </c>
+      <c r="K5" s="1" t="n">
+        <v>0.014864</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>0.01996843477664183</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -659,6 +695,12 @@
       <c r="J6" s="3" t="n">
         <v>-0.0003226847370119635</v>
       </c>
+      <c r="K6" s="1" t="n">
+        <v>0.09338</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>0.004734237142242413</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -693,6 +735,12 @@
       <c r="J7" s="3" t="n">
         <v>-0.001799985600115161</v>
       </c>
+      <c r="K7" s="1" t="n">
+        <v>1.3905</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>0.002957299480669354</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -727,6 +775,12 @@
       <c r="J8" s="2" t="n">
         <v>0.002448485515420115</v>
       </c>
+      <c r="K8" s="1" t="n">
+        <v>36.406</v>
+      </c>
+      <c r="L8" s="3" t="n">
+        <v>-0.0008782040726714852</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -761,6 +815,12 @@
       <c r="J9" s="3" t="n">
         <v>-0.001448158989369981</v>
       </c>
+      <c r="K9" s="1" t="n">
+        <v>650.4299999999999</v>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>0.003502221673660797</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -795,6 +855,12 @@
       <c r="J10" s="3" t="n">
         <v>-0.005797483365175635</v>
       </c>
+      <c r="K10" s="1" t="n">
+        <v>14.952</v>
+      </c>
+      <c r="L10" s="3" t="n">
+        <v>-0.009210787886819916</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -829,6 +895,12 @@
       <c r="J11" s="2" t="n">
         <v>0.00346974666096306</v>
       </c>
+      <c r="K11" s="1" t="n">
+        <v>210.62</v>
+      </c>
+      <c r="L11" s="3" t="n">
+        <v>-0.002368321333838575</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -863,6 +935,12 @@
       <c r="J12" s="2" t="n">
         <v>0.001134802604073339</v>
       </c>
+      <c r="K12" s="1" t="n">
+        <v>0.0033632</v>
+      </c>
+      <c r="L12" s="2" t="n">
+        <v>0.003221572604700994</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -897,6 +975,12 @@
       <c r="J13" s="3" t="n">
         <v>-0.000269759913676723</v>
       </c>
+      <c r="K13" s="1" t="n">
+        <v>0.03744</v>
+      </c>
+      <c r="L13" s="2" t="n">
+        <v>0.01025364274150023</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -931,6 +1015,12 @@
       <c r="J14" s="3" t="n">
         <v>-0.01209372637944068</v>
       </c>
+      <c r="K14" s="1" t="n">
+        <v>2.627</v>
+      </c>
+      <c r="L14" s="2" t="n">
+        <v>0.004973221117061936</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -965,6 +1055,12 @@
       <c r="J15" s="3" t="n">
         <v>-0.002246502603900725</v>
       </c>
+      <c r="K15" s="1" t="n">
+        <v>0.9833</v>
+      </c>
+      <c r="L15" s="2" t="n">
+        <v>0.006345307542728465</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -999,6 +1095,12 @@
       <c r="J16" s="2" t="n">
         <v>0.007493309545049005</v>
       </c>
+      <c r="K16" s="1" t="n">
+        <v>0.05626</v>
+      </c>
+      <c r="L16" s="3" t="n">
+        <v>-0.003718788737382714</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1033,6 +1135,12 @@
       <c r="J17" s="3" t="n">
         <v>-0.001132502831257079</v>
       </c>
+      <c r="K17" s="1" t="n">
+        <v>0.884</v>
+      </c>
+      <c r="L17" s="2" t="n">
+        <v>0.002267573696145127</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1067,6 +1175,12 @@
       <c r="J18" s="3" t="n">
         <v>-0.001516300227444867</v>
       </c>
+      <c r="K18" s="1" t="n">
+        <v>0.2644</v>
+      </c>
+      <c r="L18" s="2" t="n">
+        <v>0.003796507213363708</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1101,6 +1215,12 @@
       <c r="J19" s="2" t="n">
         <v>0.001649630306065352</v>
       </c>
+      <c r="K19" s="1" t="n">
+        <v>0.34388</v>
+      </c>
+      <c r="L19" s="2" t="n">
+        <v>0.01132253036496786</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1135,6 +1255,12 @@
       <c r="J20" s="3" t="n">
         <v>-0.002692905230450523</v>
       </c>
+      <c r="K20" s="1" t="n">
+        <v>9.676</v>
+      </c>
+      <c r="L20" s="2" t="n">
+        <v>0.004881088378855603</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1169,6 +1295,12 @@
       <c r="J21" s="3" t="n">
         <v>-0.004601610563697373</v>
       </c>
+      <c r="K21" s="1" t="n">
+        <v>199.3</v>
+      </c>
+      <c r="L21" s="2" t="n">
+        <v>0.001457213205366667</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1203,6 +1335,12 @@
       <c r="J22" s="3" t="n">
         <v>-0.02173809862831649</v>
       </c>
+      <c r="K22" s="1" t="n">
+        <v>0.020614</v>
+      </c>
+      <c r="L22" s="2" t="n">
+        <v>0.0001455533453010301</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1237,6 +1375,12 @@
       <c r="J23" s="3" t="n">
         <v>-0.000393855848759369</v>
       </c>
+      <c r="K23" s="1" t="n">
+        <v>456.46</v>
+      </c>
+      <c r="L23" s="3" t="n">
+        <v>-0.0008318010682076776</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1271,6 +1415,12 @@
       <c r="J24" s="2" t="n">
         <v>0.0001411285255548117</v>
       </c>
+      <c r="K24" s="1" t="n">
+        <v>5173.41</v>
+      </c>
+      <c r="L24" s="2" t="n">
+        <v>1.739695205402827e-05</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1305,6 +1455,12 @@
       <c r="J25" s="3" t="n">
         <v>-0.0008828073273007194</v>
       </c>
+      <c r="K25" s="1" t="n">
+        <v>9.073</v>
+      </c>
+      <c r="L25" s="2" t="n">
+        <v>0.00209851999116414</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1339,6 +1495,12 @@
       <c r="J26" s="3" t="n">
         <v>-0.02278187391268331</v>
       </c>
+      <c r="K26" s="1" t="n">
+        <v>0.11459</v>
+      </c>
+      <c r="L26" s="3" t="n">
+        <v>-0.02856900644286197</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1373,6 +1535,12 @@
       <c r="J27" s="3" t="n">
         <v>-0.01297648012976483</v>
       </c>
+      <c r="K27" s="1" t="n">
+        <v>0.01237</v>
+      </c>
+      <c r="L27" s="2" t="n">
+        <v>0.01643385373870177</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1407,6 +1575,12 @@
       <c r="J28" s="2" t="n">
         <v>0.0007710100231303871</v>
       </c>
+      <c r="K28" s="1" t="n">
+        <v>1.296</v>
+      </c>
+      <c r="L28" s="3" t="n">
+        <v>-0.001540832049306627</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1441,6 +1615,12 @@
       <c r="J29" s="2" t="n">
         <v>0.01333333333333337</v>
       </c>
+      <c r="K29" s="1" t="n">
+        <v>0.0608</v>
+      </c>
+      <c r="L29" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1475,6 +1655,12 @@
       <c r="J30" s="3" t="n">
         <v>-0.0006561679790026981</v>
       </c>
+      <c r="K30" s="1" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="L30" s="2" t="n">
+        <v>0.004596191726854969</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1509,6 +1695,12 @@
       <c r="J31" s="2" t="n">
         <v>0.00294550810014724</v>
       </c>
+      <c r="K31" s="1" t="n">
+        <v>0.002036</v>
+      </c>
+      <c r="L31" s="3" t="n">
+        <v>-0.003426333822809624</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1543,6 +1735,12 @@
       <c r="J32" s="3" t="n">
         <v>-0.005429417571569545</v>
       </c>
+      <c r="K32" s="1" t="n">
+        <v>0.04051</v>
+      </c>
+      <c r="L32" s="2" t="n">
+        <v>0.005210918114143794</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1577,6 +1775,12 @@
       <c r="J33" s="3" t="n">
         <v>-0.00203252032520331</v>
       </c>
+      <c r="K33" s="1" t="n">
+        <v>0.0982</v>
+      </c>
+      <c r="L33" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1611,6 +1815,12 @@
       <c r="J34" s="3" t="n">
         <v>-0.001902949571836401</v>
       </c>
+      <c r="K34" s="1" t="n">
+        <v>0.1052</v>
+      </c>
+      <c r="L34" s="2" t="n">
+        <v>0.002859866539561569</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1645,6 +1855,12 @@
       <c r="J35" s="2" t="n">
         <v>0.005561735261401524</v>
       </c>
+      <c r="K35" s="1" t="n">
+        <v>0.008959999999999999</v>
+      </c>
+      <c r="L35" s="3" t="n">
+        <v>-0.008849557522123918</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1679,6 +1895,12 @@
       <c r="J36" s="3" t="n">
         <v>-0.002513966480446961</v>
       </c>
+      <c r="K36" s="1" t="n">
+        <v>0.3582</v>
+      </c>
+      <c r="L36" s="2" t="n">
+        <v>0.00308036964435745</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1713,6 +1935,12 @@
       <c r="J37" s="2" t="n">
         <v>0.002749613335624596</v>
       </c>
+      <c r="K37" s="1" t="n">
+        <v>0.005838</v>
+      </c>
+      <c r="L37" s="2" t="n">
+        <v>0.0005141388174807881</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1747,6 +1975,12 @@
       <c r="J38" s="3" t="n">
         <v>-0.0008723686705860344</v>
       </c>
+      <c r="K38" s="1" t="n">
+        <v>0.26349</v>
+      </c>
+      <c r="L38" s="2" t="n">
+        <v>0.0002657353276137518</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1781,6 +2015,12 @@
       <c r="J39" s="3" t="n">
         <v>-0.00333922608524841</v>
       </c>
+      <c r="K39" s="1" t="n">
+        <v>0.05049</v>
+      </c>
+      <c r="L39" s="3" t="n">
+        <v>-0.004927079227433981</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1815,6 +2055,12 @@
       <c r="J40" s="3" t="n">
         <v>-0.004762543600751197</v>
       </c>
+      <c r="K40" s="1" t="n">
+        <v>0.14977</v>
+      </c>
+      <c r="L40" s="2" t="n">
+        <v>0.009435869784996864</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1849,6 +2095,12 @@
       <c r="J41" s="3" t="n">
         <v>-0.001186239620403355</v>
       </c>
+      <c r="K41" s="1" t="n">
+        <v>0.1692</v>
+      </c>
+      <c r="L41" s="2" t="n">
+        <v>0.004750593824228</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1883,6 +2135,12 @@
       <c r="J42" s="3" t="n">
         <v>-0.001427042454513118</v>
       </c>
+      <c r="K42" s="1" t="n">
+        <v>112.54</v>
+      </c>
+      <c r="L42" s="2" t="n">
+        <v>0.005180421579135517</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1917,6 +2175,12 @@
       <c r="J43" s="2" t="n">
         <v>0.02049180327868854</v>
       </c>
+      <c r="K43" s="1" t="n">
+        <v>0.7215</v>
+      </c>
+      <c r="L43" s="2" t="n">
+        <v>0.0348537005163511</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1951,6 +2215,12 @@
       <c r="J44" s="3" t="n">
         <v>-0.002002913328477776</v>
       </c>
+      <c r="K44" s="1" t="n">
+        <v>54.71</v>
+      </c>
+      <c r="L44" s="3" t="n">
+        <v>-0.001824484583105299</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1985,6 +2255,12 @@
       <c r="J45" s="3" t="n">
         <v>-0.004537033536239476</v>
       </c>
+      <c r="K45" s="1" t="n">
+        <v>0.53009</v>
+      </c>
+      <c r="L45" s="2" t="n">
+        <v>0.006665653841771244</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2019,6 +2295,12 @@
       <c r="J46" s="3" t="n">
         <v>-0.0002841312686460832</v>
       </c>
+      <c r="K46" s="1" t="n">
+        <v>0.7050999999999999</v>
+      </c>
+      <c r="L46" s="2" t="n">
+        <v>0.001989484155179703</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2053,6 +2335,12 @@
       <c r="J47" s="3" t="n">
         <v>-0.00281042411854883</v>
       </c>
+      <c r="K47" s="1" t="n">
+        <v>3.911</v>
+      </c>
+      <c r="L47" s="2" t="n">
+        <v>0.002049705354855241</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2087,6 +2375,12 @@
       <c r="J48" s="3" t="n">
         <v>-0.0002498750624688422</v>
       </c>
+      <c r="K48" s="1" t="n">
+        <v>0.16028</v>
+      </c>
+      <c r="L48" s="2" t="n">
+        <v>0.001499625093726681</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2121,6 +2415,12 @@
       <c r="J49" s="3" t="n">
         <v>-0.003136348629910906</v>
       </c>
+      <c r="K49" s="1" t="n">
+        <v>0.05941</v>
+      </c>
+      <c r="L49" s="3" t="n">
+        <v>-0.01622785229342609</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2155,6 +2455,12 @@
       <c r="J50" s="2" t="n">
         <v>0.002590673575129428</v>
       </c>
+      <c r="K50" s="1" t="n">
+        <v>0.0386</v>
+      </c>
+      <c r="L50" s="3" t="n">
+        <v>-0.002583979328165269</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2189,6 +2495,12 @@
       <c r="J51" s="3" t="n">
         <v>-0.01281861511590041</v>
       </c>
+      <c r="K51" s="1" t="n">
+        <v>0.33396</v>
+      </c>
+      <c r="L51" s="2" t="n">
+        <v>0.001499430216517725</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2223,6 +2535,12 @@
       <c r="J52" s="3" t="n">
         <v>-0.0003417634996583885</v>
       </c>
+      <c r="K52" s="1" t="n">
+        <v>0.2941</v>
+      </c>
+      <c r="L52" s="2" t="n">
+        <v>0.005470085470085437</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2257,6 +2575,12 @@
       <c r="J53" s="3" t="n">
         <v>-0.005015673981191193</v>
       </c>
+      <c r="K53" s="1" t="n">
+        <v>0.1583</v>
+      </c>
+      <c r="L53" s="3" t="n">
+        <v>-0.00252047889098936</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2291,6 +2615,12 @@
       <c r="J54" s="2" t="n">
         <v>0.0008603778779640981</v>
       </c>
+      <c r="K54" s="1" t="n">
+        <v>0.29149</v>
+      </c>
+      <c r="L54" s="2" t="n">
+        <v>0.002303830548105371</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2325,6 +2655,12 @@
       <c r="J55" s="3" t="n">
         <v>-0.003478018920422906</v>
       </c>
+      <c r="K55" s="1" t="n">
+        <v>0.007168</v>
+      </c>
+      <c r="L55" s="2" t="n">
+        <v>0.000698031551026078</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2359,6 +2695,12 @@
       <c r="J56" s="2" t="n">
         <v>0.007412636780797684</v>
       </c>
+      <c r="K56" s="1" t="n">
+        <v>0.02841</v>
+      </c>
+      <c r="L56" s="3" t="n">
+        <v>-0.004555010511562655</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2393,6 +2735,12 @@
       <c r="J57" s="3" t="n">
         <v>-0.003797768810823651</v>
       </c>
+      <c r="K57" s="1" t="n">
+        <v>0.04203</v>
+      </c>
+      <c r="L57" s="2" t="n">
+        <v>0.001429592566118598</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2427,6 +2775,12 @@
       <c r="J58" s="3" t="n">
         <v>-0.0104477611940298</v>
       </c>
+      <c r="K58" s="1" t="n">
+        <v>0.04685</v>
+      </c>
+      <c r="L58" s="2" t="n">
+        <v>0.009480715363068366</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2461,6 +2815,12 @@
       <c r="J59" s="2" t="n">
         <v>0.001308900523560211</v>
       </c>
+      <c r="K59" s="1" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="L59" s="2" t="n">
+        <v>0.006535947712418306</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2495,6 +2855,12 @@
       <c r="J60" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="K60" s="1" t="n">
+        <v>0.00344</v>
+      </c>
+      <c r="L60" s="2" t="n">
+        <v>0.00291545189504374</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2529,6 +2895,12 @@
       <c r="J61" s="2" t="n">
         <v>0.002587322121604214</v>
       </c>
+      <c r="K61" s="1" t="n">
+        <v>0.155</v>
+      </c>
+      <c r="L61" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2563,6 +2935,12 @@
       <c r="J62" s="3" t="n">
         <v>-0.003466204506065861</v>
       </c>
+      <c r="K62" s="1" t="n">
+        <v>1.151</v>
+      </c>
+      <c r="L62" s="2" t="n">
+        <v>0.0008695652173914017</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2597,6 +2975,12 @@
       <c r="J63" s="3" t="n">
         <v>-0.0008559201141225877</v>
       </c>
+      <c r="K63" s="1" t="n">
+        <v>0.7003</v>
+      </c>
+      <c r="L63" s="3" t="n">
+        <v>-0.0001427755568246559</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2631,6 +3015,12 @@
       <c r="J64" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="K64" s="1" t="n">
+        <v>2.945</v>
+      </c>
+      <c r="L64" s="2" t="n">
+        <v>0.003065395095367812</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2665,6 +3055,12 @@
       <c r="J65" s="2" t="n">
         <v>0.00125628140703527</v>
       </c>
+      <c r="K65" s="1" t="n">
+        <v>0.02401</v>
+      </c>
+      <c r="L65" s="2" t="n">
+        <v>0.00418235048097028</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2699,6 +3095,12 @@
       <c r="J66" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="K66" s="1" t="n">
+        <v>0.1016</v>
+      </c>
+      <c r="L66" s="2" t="n">
+        <v>0.0009852216748767388</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2733,6 +3135,12 @@
       <c r="J67" s="3" t="n">
         <v>-0.001484680793629333</v>
       </c>
+      <c r="K67" s="1" t="n">
+        <v>0.007285</v>
+      </c>
+      <c r="L67" s="3" t="n">
+        <v>-0.01527439848607735</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2767,6 +3175,12 @@
       <c r="J68" s="2" t="n">
         <v>0.002696871628910502</v>
       </c>
+      <c r="K68" s="1" t="n">
+        <v>18.56</v>
+      </c>
+      <c r="L68" s="3" t="n">
+        <v>-0.001613770844540136</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2801,6 +3215,12 @@
       <c r="J69" s="3" t="n">
         <v>-0.009237021984112331</v>
       </c>
+      <c r="K69" s="1" t="n">
+        <v>0.05388</v>
+      </c>
+      <c r="L69" s="2" t="n">
+        <v>0.004661570016781656</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2835,6 +3255,12 @@
       <c r="J70" s="3" t="n">
         <v>-0.004184100418410046</v>
       </c>
+      <c r="K70" s="1" t="n">
+        <v>0.238</v>
+      </c>
+      <c r="L70" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2869,6 +3295,12 @@
       <c r="J71" s="2" t="n">
         <v>0.01896463352127126</v>
       </c>
+      <c r="K71" s="1" t="n">
+        <v>5.791</v>
+      </c>
+      <c r="L71" s="3" t="n">
+        <v>-0.0290073775989269</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2903,6 +3335,12 @@
       <c r="J72" s="3" t="n">
         <v>-0.006265060240963851</v>
       </c>
+      <c r="K72" s="1" t="n">
+        <v>0.001948</v>
+      </c>
+      <c r="L72" s="3" t="n">
+        <v>-0.05528612997090201</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2937,6 +3375,12 @@
       <c r="J73" s="2" t="n">
         <v>0.0004238635159479358</v>
       </c>
+      <c r="K73" s="1" t="n">
+        <v>0.9496</v>
+      </c>
+      <c r="L73" s="2" t="n">
+        <v>0.005825654062069642</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2971,6 +3415,12 @@
       <c r="J74" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="K74" s="1" t="n">
+        <v>0.1212</v>
+      </c>
+      <c r="L74" s="2" t="n">
+        <v>0.004142502071251039</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3005,6 +3455,12 @@
       <c r="J75" s="3" t="n">
         <v>-0.003982250540448223</v>
       </c>
+      <c r="K75" s="1" t="n">
+        <v>351.7</v>
+      </c>
+      <c r="L75" s="2" t="n">
+        <v>0.004397989490518516</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3039,6 +3495,12 @@
       <c r="J76" s="3" t="n">
         <v>-0.004968421052631523</v>
       </c>
+      <c r="K76" s="1" t="n">
+        <v>0.11848</v>
+      </c>
+      <c r="L76" s="2" t="n">
+        <v>0.002708192281652005</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3073,6 +3535,12 @@
       <c r="J77" s="3" t="n">
         <v>-0.001425178147268296</v>
       </c>
+      <c r="K77" s="1" t="n">
+        <v>0.06287</v>
+      </c>
+      <c r="L77" s="3" t="n">
+        <v>-0.003013003488741034</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3107,6 +3575,12 @@
       <c r="J78" s="3" t="n">
         <v>-0.0005315755900489939</v>
       </c>
+      <c r="K78" s="1" t="n">
+        <v>0.09415999999999999</v>
+      </c>
+      <c r="L78" s="2" t="n">
+        <v>0.001595574938836266</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3141,6 +3615,12 @@
       <c r="J79" s="3" t="n">
         <v>-0.01150251617541343</v>
       </c>
+      <c r="K79" s="1" t="n">
+        <v>0.4153</v>
+      </c>
+      <c r="L79" s="2" t="n">
+        <v>0.006787878787878848</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3175,6 +3655,12 @@
       <c r="J80" s="3" t="n">
         <v>-0.001164725457570726</v>
       </c>
+      <c r="K80" s="1" t="n">
+        <v>0.006011</v>
+      </c>
+      <c r="L80" s="2" t="n">
+        <v>0.001332666999833449</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3209,6 +3695,12 @@
       <c r="J81" s="2" t="n">
         <v>0.003868471953578313</v>
       </c>
+      <c r="K81" s="1" t="n">
+        <v>0.1032</v>
+      </c>
+      <c r="L81" s="3" t="n">
+        <v>-0.00578034682080928</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3243,6 +3735,12 @@
       <c r="J82" s="3" t="n">
         <v>-0.0009775171065493926</v>
       </c>
+      <c r="K82" s="1" t="n">
+        <v>0.1023</v>
+      </c>
+      <c r="L82" s="2" t="n">
+        <v>0.0009784735812133354</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3277,6 +3775,12 @@
       <c r="J83" s="2" t="n">
         <v>0.01830311323982213</v>
       </c>
+      <c r="K83" s="1" t="n">
+        <v>0.06283</v>
+      </c>
+      <c r="L83" s="2" t="n">
+        <v>0.05543423483957664</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3311,6 +3815,12 @@
       <c r="J84" s="3" t="n">
         <v>-0.00143600789804348</v>
       </c>
+      <c r="K84" s="1" t="n">
+        <v>1.1207</v>
+      </c>
+      <c r="L84" s="2" t="n">
+        <v>0.007280244472406971</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3345,6 +3855,12 @@
       <c r="J85" s="3" t="n">
         <v>-0.006001500375093789</v>
       </c>
+      <c r="K85" s="1" t="n">
+        <v>0.0133</v>
+      </c>
+      <c r="L85" s="2" t="n">
+        <v>0.003773584905660355</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3379,6 +3895,12 @@
       <c r="J86" s="3" t="n">
         <v>-0.001789976133651685</v>
       </c>
+      <c r="K86" s="1" t="n">
+        <v>0.01679</v>
+      </c>
+      <c r="L86" s="2" t="n">
+        <v>0.003586371787208669</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3413,6 +3935,12 @@
       <c r="J87" s="3" t="n">
         <v>-0.00120336943441634</v>
       </c>
+      <c r="K87" s="1" t="n">
+        <v>8.308</v>
+      </c>
+      <c r="L87" s="2" t="n">
+        <v>0.0009638554216866408</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3447,6 +3975,12 @@
       <c r="J88" s="2" t="n">
         <v>0.005933732080129202</v>
       </c>
+      <c r="K88" s="1" t="n">
+        <v>2.1271</v>
+      </c>
+      <c r="L88" s="2" t="n">
+        <v>0.003775187579632867</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3481,6 +4015,12 @@
       <c r="J89" s="3" t="n">
         <v>-0.02069269151746399</v>
       </c>
+      <c r="K89" s="1" t="n">
+        <v>0.006703</v>
+      </c>
+      <c r="L89" s="2" t="n">
+        <v>0.004495729057395421</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3515,6 +4055,12 @@
       <c r="J90" s="3" t="n">
         <v>-0.0006561679790026107</v>
       </c>
+      <c r="K90" s="1" t="n">
+        <v>15.24</v>
+      </c>
+      <c r="L90" s="2" t="n">
+        <v>0.0006565988181221133</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3549,6 +4095,12 @@
       <c r="J91" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="K91" s="1" t="n">
+        <v>0.000225</v>
+      </c>
+      <c r="L91" s="2" t="n">
+        <v>0.01351351351351348</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3583,6 +4135,12 @@
       <c r="J92" s="2" t="n">
         <v>0.0005687203791469621</v>
       </c>
+      <c r="K92" s="1" t="n">
+        <v>0.05237</v>
+      </c>
+      <c r="L92" s="3" t="n">
+        <v>-0.007768093974990539</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3617,6 +4175,12 @@
       <c r="J93" s="3" t="n">
         <v>-0.001438957891548025</v>
       </c>
+      <c r="K93" s="1" t="n">
+        <v>1.3216</v>
+      </c>
+      <c r="L93" s="2" t="n">
+        <v>0.002351156617368299</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3651,6 +4215,12 @@
       <c r="J94" s="3" t="n">
         <v>-0.001615448890539352</v>
       </c>
+      <c r="K94" s="1" t="n">
+        <v>0.054134</v>
+      </c>
+      <c r="L94" s="2" t="n">
+        <v>0.00680702276446954</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3685,6 +4255,12 @@
       <c r="J95" s="3" t="n">
         <v>-0.002888980602558722</v>
       </c>
+      <c r="K95" s="1" t="n">
+        <v>0.2422</v>
+      </c>
+      <c r="L95" s="2" t="n">
+        <v>0.002483443708609228</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3719,6 +4295,12 @@
       <c r="J96" s="3" t="n">
         <v>-0.001105277701022464</v>
       </c>
+      <c r="K96" s="1" t="n">
+        <v>1.0834</v>
+      </c>
+      <c r="L96" s="3" t="n">
+        <v>-0.001014292300599448</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3753,6 +4335,12 @@
       <c r="J97" s="3" t="n">
         <v>-0.000777000777000907</v>
       </c>
+      <c r="K97" s="1" t="n">
+        <v>0.2583</v>
+      </c>
+      <c r="L97" s="2" t="n">
+        <v>0.004276827371695139</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3787,6 +4375,12 @@
       <c r="J98" s="3" t="n">
         <v>-0.003968253968253914</v>
       </c>
+      <c r="K98" s="1" t="n">
+        <v>0.5786</v>
+      </c>
+      <c r="L98" s="2" t="n">
+        <v>0.002251862116750334</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3821,6 +4415,12 @@
       <c r="J99" s="3" t="n">
         <v>-0.0001473405039044662</v>
       </c>
+      <c r="K99" s="1" t="n">
+        <v>0.13478</v>
+      </c>
+      <c r="L99" s="3" t="n">
+        <v>-0.006926024167403451</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3855,6 +4455,12 @@
       <c r="J100" s="3" t="n">
         <v>-0.003924133420536251</v>
       </c>
+      <c r="K100" s="1" t="n">
+        <v>0.03062</v>
+      </c>
+      <c r="L100" s="2" t="n">
+        <v>0.005252790544977032</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3889,6 +4495,12 @@
       <c r="J101" s="2" t="n">
         <v>0.001958863858961804</v>
       </c>
+      <c r="K101" s="1" t="n">
+        <v>1.028</v>
+      </c>
+      <c r="L101" s="2" t="n">
+        <v>0.004887585532746937</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -3923,6 +4535,12 @@
       <c r="J102" s="3" t="n">
         <v>-0.003623188405797111</v>
       </c>
+      <c r="K102" s="1" t="n">
+        <v>0.02206</v>
+      </c>
+      <c r="L102" s="2" t="n">
+        <v>0.002727272727272774</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -3957,6 +4575,12 @@
       <c r="J103" s="3" t="n">
         <v>-0.004584819154355745</v>
       </c>
+      <c r="K103" s="1" t="n">
+        <v>0.01966</v>
+      </c>
+      <c r="L103" s="2" t="n">
+        <v>0.006141248720573289</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -3991,6 +4615,12 @@
       <c r="J104" s="2" t="n">
         <v>0.001004352192835659</v>
       </c>
+      <c r="K104" s="1" t="n">
+        <v>2.991</v>
+      </c>
+      <c r="L104" s="2" t="n">
+        <v>0.0003344481605350802</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -4025,6 +4655,12 @@
       <c r="J105" s="2" t="n">
         <v>0.0009310986964618603</v>
       </c>
+      <c r="K105" s="1" t="n">
+        <v>32.28</v>
+      </c>
+      <c r="L105" s="2" t="n">
+        <v>0.0009302325581395702</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -4059,6 +4695,12 @@
       <c r="J106" s="3" t="n">
         <v>-0.001205545509343012</v>
       </c>
+      <c r="K106" s="1" t="n">
+        <v>0.1659</v>
+      </c>
+      <c r="L106" s="2" t="n">
+        <v>0.001207000603500336</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -4093,6 +4735,12 @@
       <c r="J107" s="2" t="n">
         <v>0.007858105074090712</v>
       </c>
+      <c r="K107" s="1" t="n">
+        <v>0.4578</v>
+      </c>
+      <c r="L107" s="2" t="n">
+        <v>0.01982624192470475</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -4127,6 +4775,12 @@
       <c r="J108" s="2" t="n">
         <v>0.001492537313432837</v>
       </c>
+      <c r="K108" s="1" t="n">
+        <v>0.3363</v>
+      </c>
+      <c r="L108" s="2" t="n">
+        <v>0.002384500745156386</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -4161,6 +4815,12 @@
       <c r="J109" s="3" t="n">
         <v>-0.006342494714587744</v>
       </c>
+      <c r="K109" s="1" t="n">
+        <v>0.2331</v>
+      </c>
+      <c r="L109" s="3" t="n">
+        <v>-0.008085106382978661</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -4195,6 +4855,12 @@
       <c r="J110" s="3" t="n">
         <v>-0.00131233595800531</v>
       </c>
+      <c r="K110" s="1" t="n">
+        <v>0.01506</v>
+      </c>
+      <c r="L110" s="3" t="n">
+        <v>-0.01051248357424433</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -4229,6 +4895,12 @@
       <c r="J111" s="3" t="n">
         <v>-0.002723311546841021</v>
       </c>
+      <c r="K111" s="1" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="L111" s="3" t="n">
+        <v>-0.0005461496450026706</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -4263,6 +4935,12 @@
       <c r="J112" s="3" t="n">
         <v>-0.001819599688068641</v>
       </c>
+      <c r="K112" s="1" t="n">
+        <v>0.03843</v>
+      </c>
+      <c r="L112" s="2" t="n">
+        <v>0.0007812500000000586</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -4297,6 +4975,12 @@
       <c r="J113" s="3" t="n">
         <v>-0.009086672879776259</v>
       </c>
+      <c r="K113" s="1" t="n">
+        <v>4.266</v>
+      </c>
+      <c r="L113" s="2" t="n">
+        <v>0.003056665882906161</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -4331,6 +5015,12 @@
       <c r="J114" s="2" t="n">
         <v>0.01180415828303158</v>
       </c>
+      <c r="K114" s="1" t="n">
+        <v>0.007655</v>
+      </c>
+      <c r="L114" s="2" t="n">
+        <v>0.01484820363250698</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -4365,6 +5055,12 @@
       <c r="J115" s="3" t="n">
         <v>-0.0004042854255103939</v>
       </c>
+      <c r="K115" s="1" t="n">
+        <v>0.09882000000000001</v>
+      </c>
+      <c r="L115" s="3" t="n">
+        <v>-0.0008088978766430409</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -4399,6 +5095,12 @@
       <c r="J116" s="3" t="n">
         <v>-0.0009661835748791877</v>
       </c>
+      <c r="K116" s="1" t="n">
+        <v>0.08293</v>
+      </c>
+      <c r="L116" s="2" t="n">
+        <v>0.002538684719535806</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -4433,6 +5135,12 @@
       <c r="J117" s="3" t="n">
         <v>-0.001335113484646048</v>
       </c>
+      <c r="K117" s="1" t="n">
+        <v>0.3003</v>
+      </c>
+      <c r="L117" s="2" t="n">
+        <v>0.00367647058823526</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -4467,6 +5175,12 @@
       <c r="J118" s="3" t="n">
         <v>-0.001755926251097535</v>
       </c>
+      <c r="K118" s="1" t="n">
+        <v>0.02269</v>
+      </c>
+      <c r="L118" s="3" t="n">
+        <v>-0.002198768689533924</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -4501,6 +5215,12 @@
       <c r="J119" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="K119" s="1" t="n">
+        <v>0.1544</v>
+      </c>
+      <c r="L119" s="2" t="n">
+        <v>0.002597402597402672</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -4535,6 +5255,12 @@
       <c r="J120" s="2" t="n">
         <v>0.008462946020128021</v>
       </c>
+      <c r="K120" s="1" t="n">
+        <v>0.004433</v>
+      </c>
+      <c r="L120" s="2" t="n">
+        <v>0.005443411204354862</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -4569,6 +5295,12 @@
       <c r="J121" s="3" t="n">
         <v>-0.002550428935775539</v>
       </c>
+      <c r="K121" s="1" t="n">
+        <v>0.4341</v>
+      </c>
+      <c r="L121" s="2" t="n">
+        <v>0.009065550906554995</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -4603,6 +5335,12 @@
       <c r="J122" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="K122" s="1" t="n">
+        <v>0.778</v>
+      </c>
+      <c r="L122" s="2" t="n">
+        <v>0.002577319587628868</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -4637,6 +5375,12 @@
       <c r="J123" s="2" t="n">
         <v>0.001160092807424627</v>
       </c>
+      <c r="K123" s="1" t="n">
+        <v>0.08649999999999999</v>
+      </c>
+      <c r="L123" s="2" t="n">
+        <v>0.002317497103128527</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4671,6 +5415,12 @@
       <c r="J124" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="K124" s="1" t="n">
+        <v>0.01259</v>
+      </c>
+      <c r="L124" s="2" t="n">
+        <v>0.005591054313099091</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -4705,6 +5455,12 @@
       <c r="J125" s="3" t="n">
         <v>-0.002046663937781475</v>
       </c>
+      <c r="K125" s="1" t="n">
+        <v>0.09768</v>
+      </c>
+      <c r="L125" s="2" t="n">
+        <v>0.001640689089417631</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -4739,6 +5495,12 @@
       <c r="J126" s="3" t="n">
         <v>-0.004868755292125193</v>
       </c>
+      <c r="K126" s="1" t="n">
+        <v>0.04701</v>
+      </c>
+      <c r="L126" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -4773,6 +5535,12 @@
       <c r="J127" s="2" t="n">
         <v>0.003164556962025178</v>
       </c>
+      <c r="K127" s="1" t="n">
+        <v>3.19e-05</v>
+      </c>
+      <c r="L127" s="2" t="n">
+        <v>0.00630914826498438</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -4807,6 +5575,12 @@
       <c r="J128" s="3" t="n">
         <v>-0.002266387726638717</v>
       </c>
+      <c r="K128" s="1" t="n">
+        <v>0.575</v>
+      </c>
+      <c r="L128" s="2" t="n">
+        <v>0.004717805346845928</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -4841,6 +5615,12 @@
       <c r="J129" s="3" t="n">
         <v>-0.002735978112175096</v>
       </c>
+      <c r="K129" s="1" t="n">
+        <v>0.0658</v>
+      </c>
+      <c r="L129" s="2" t="n">
+        <v>0.002895900015241514</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -4875,6 +5655,12 @@
       <c r="J130" s="2" t="n">
         <v>0.003188454438664192</v>
       </c>
+      <c r="K130" s="1" t="n">
+        <v>0.000601</v>
+      </c>
+      <c r="L130" s="2" t="n">
+        <v>0.005352960856473686</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -4909,6 +5695,12 @@
       <c r="J131" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="K131" s="1" t="n">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="L131" s="2" t="n">
+        <v>0.01149425287356323</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -4943,6 +5735,12 @@
       <c r="J132" s="3" t="n">
         <v>-0.004626569729015059</v>
       </c>
+      <c r="K132" s="1" t="n">
+        <v>0.302</v>
+      </c>
+      <c r="L132" s="2" t="n">
+        <v>0.002656042496679838</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -4977,6 +5775,12 @@
       <c r="J133" s="3" t="n">
         <v>-0.003304295584259507</v>
       </c>
+      <c r="K133" s="1" t="n">
+        <v>0.03332</v>
+      </c>
+      <c r="L133" s="2" t="n">
+        <v>0.004219409282700459</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -5011,6 +5815,12 @@
       <c r="J134" s="3" t="n">
         <v>-0.003763514438209901</v>
       </c>
+      <c r="K134" s="1" t="n">
+        <v>0.14473</v>
+      </c>
+      <c r="L134" s="3" t="n">
+        <v>-0.005906999107081528</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -5045,6 +5855,12 @@
       <c r="J135" s="2" t="n">
         <v>0.001690902942171168</v>
       </c>
+      <c r="K135" s="1" t="n">
+        <v>0.02962</v>
+      </c>
+      <c r="L135" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -5079,6 +5895,12 @@
       <c r="J136" s="3" t="n">
         <v>-0.004600141542816793</v>
       </c>
+      <c r="K136" s="1" t="n">
+        <v>28.27</v>
+      </c>
+      <c r="L136" s="2" t="n">
+        <v>0.004976892996800589</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -5113,6 +5935,12 @@
       <c r="J137" s="2" t="n">
         <v>0.001168224299065449</v>
       </c>
+      <c r="K137" s="1" t="n">
+        <v>0.0004303</v>
+      </c>
+      <c r="L137" s="2" t="n">
+        <v>0.00420070011668609</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -5147,6 +5975,12 @@
       <c r="J138" s="3" t="n">
         <v>-0.0236664540602236</v>
       </c>
+      <c r="K138" s="1" t="n">
+        <v>0.029488</v>
+      </c>
+      <c r="L138" s="2" t="n">
+        <v>0.01389079906477794</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -5181,6 +6015,12 @@
       <c r="J139" s="2" t="n">
         <v>0.0007294706127553212</v>
       </c>
+      <c r="K139" s="1" t="n">
+        <v>0.09611</v>
+      </c>
+      <c r="L139" s="2" t="n">
+        <v>0.0008330729980214177</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -5215,6 +6055,12 @@
       <c r="J140" s="3" t="n">
         <v>-0.008310249307479232</v>
       </c>
+      <c r="K140" s="1" t="n">
+        <v>0.3571</v>
+      </c>
+      <c r="L140" s="3" t="n">
+        <v>-0.002513966480446961</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -5249,6 +6095,12 @@
       <c r="J141" s="3" t="n">
         <v>-0.004026354319180051</v>
       </c>
+      <c r="K141" s="1" t="n">
+        <v>0.02718</v>
+      </c>
+      <c r="L141" s="3" t="n">
+        <v>-0.001102535832414636</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -5283,6 +6135,12 @@
       <c r="J142" s="2" t="n">
         <v>0.002084690553746024</v>
       </c>
+      <c r="K142" s="1" t="n">
+        <v>0.07702000000000001</v>
+      </c>
+      <c r="L142" s="2" t="n">
+        <v>0.001430243141334014</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -5317,6 +6175,12 @@
       <c r="J143" s="3" t="n">
         <v>-0.004064581686801391</v>
       </c>
+      <c r="K143" s="1" t="n">
+        <v>0.08888</v>
+      </c>
+      <c r="L143" s="2" t="n">
+        <v>0.007595510713071125</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -5351,6 +6215,12 @@
       <c r="J144" s="2" t="n">
         <v>0.004466501240694779</v>
       </c>
+      <c r="K144" s="1" t="n">
+        <v>0.02033</v>
+      </c>
+      <c r="L144" s="2" t="n">
+        <v>0.004446640316205524</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -5385,6 +6255,12 @@
       <c r="J145" s="3" t="n">
         <v>-0.003674540682414731</v>
       </c>
+      <c r="K145" s="1" t="n">
+        <v>0.11368</v>
+      </c>
+      <c r="L145" s="3" t="n">
+        <v>-0.00175623463294689</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -5419,6 +6295,12 @@
       <c r="J146" s="3" t="n">
         <v>-0.001316655694535917</v>
       </c>
+      <c r="K146" s="1" t="n">
+        <v>0.3043</v>
+      </c>
+      <c r="L146" s="2" t="n">
+        <v>0.002966381015161542</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -5453,6 +6335,12 @@
       <c r="J147" s="2" t="n">
         <v>0.008264462809917363</v>
       </c>
+      <c r="K147" s="1" t="n">
+        <v>0.123</v>
+      </c>
+      <c r="L147" s="2" t="n">
+        <v>0.008196721311475417</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -5487,6 +6375,12 @@
       <c r="J148" s="3" t="n">
         <v>-0.003891050583657614</v>
       </c>
+      <c r="K148" s="1" t="n">
+        <v>1.9559</v>
+      </c>
+      <c r="L148" s="2" t="n">
+        <v>0.005293996710526303</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -5521,6 +6415,12 @@
       <c r="J149" s="3" t="n">
         <v>-0.00338436744560841</v>
       </c>
+      <c r="K149" s="1" t="n">
+        <v>0.06198</v>
+      </c>
+      <c r="L149" s="2" t="n">
+        <v>0.002263906856403642</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -5555,6 +6455,12 @@
       <c r="J150" s="2" t="n">
         <v>0.003045066991473815</v>
       </c>
+      <c r="K150" s="1" t="n">
+        <v>0.1653</v>
+      </c>
+      <c r="L150" s="2" t="n">
+        <v>0.003642987249544562</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -5589,6 +6495,12 @@
       <c r="J151" s="3" t="n">
         <v>-0.00104774734321216</v>
       </c>
+      <c r="K151" s="1" t="n">
+        <v>6.685e-05</v>
+      </c>
+      <c r="L151" s="2" t="n">
+        <v>0.001648186994306222</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -5623,6 +6535,12 @@
       <c r="J152" s="3" t="n">
         <v>-0.003396739130434762</v>
       </c>
+      <c r="K152" s="1" t="n">
+        <v>0.01488</v>
+      </c>
+      <c r="L152" s="2" t="n">
+        <v>0.01431492842535788</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -5657,6 +6575,12 @@
       <c r="J153" s="3" t="n">
         <v>-0.00287218764959299</v>
       </c>
+      <c r="K153" s="1" t="n">
+        <v>0.02086</v>
+      </c>
+      <c r="L153" s="2" t="n">
+        <v>0.00144023043686984</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -5691,6 +6615,12 @@
       <c r="J154" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="K154" s="1" t="n">
+        <v>0.0005976</v>
+      </c>
+      <c r="L154" s="2" t="n">
+        <v>0.0003347840642785485</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -5725,6 +6655,12 @@
       <c r="J155" s="3" t="n">
         <v>-0.002487562189054797</v>
       </c>
+      <c r="K155" s="1" t="n">
+        <v>0.04014</v>
+      </c>
+      <c r="L155" s="2" t="n">
+        <v>0.0009975062344140975</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -5759,6 +6695,12 @@
       <c r="J156" s="3" t="n">
         <v>-0.001058761249338231</v>
       </c>
+      <c r="K156" s="1" t="n">
+        <v>0.0189</v>
+      </c>
+      <c r="L156" s="2" t="n">
+        <v>0.001589825119236819</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -5793,6 +6735,12 @@
       <c r="J157" s="3" t="n">
         <v>-0.004016986112705189</v>
       </c>
+      <c r="K157" s="1" t="n">
+        <v>0.08628</v>
+      </c>
+      <c r="L157" s="3" t="n">
+        <v>-0.005761696243374055</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -5827,6 +6775,12 @@
       <c r="J158" s="2" t="n">
         <v>0.003632840881569449</v>
       </c>
+      <c r="K158" s="1" t="n">
+        <v>0.008305</v>
+      </c>
+      <c r="L158" s="2" t="n">
+        <v>0.002051158301158259</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -5861,6 +6815,12 @@
       <c r="J159" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="K159" s="1" t="n">
+        <v>2.497</v>
+      </c>
+      <c r="L159" s="2" t="n">
+        <v>0.001202886928628576</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -5895,6 +6855,12 @@
       <c r="J160" s="3" t="n">
         <v>-0.0001563354959745173</v>
       </c>
+      <c r="K160" s="1" t="n">
+        <v>1.2838</v>
+      </c>
+      <c r="L160" s="2" t="n">
+        <v>0.003674458603705847</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -5929,6 +6895,12 @@
       <c r="J161" s="3" t="n">
         <v>-0.009582567603045438</v>
       </c>
+      <c r="K161" s="1" t="n">
+        <v>0.007544</v>
+      </c>
+      <c r="L161" s="3" t="n">
+        <v>-0.0001325381047050054</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -5963,6 +6935,12 @@
       <c r="J162" s="2" t="n">
         <v>0.01371204701273252</v>
       </c>
+      <c r="K162" s="1" t="n">
+        <v>0.00418</v>
+      </c>
+      <c r="L162" s="2" t="n">
+        <v>0.009661835748792296</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -5997,6 +6975,12 @@
       <c r="J163" s="3" t="n">
         <v>-0.001041666666666697</v>
       </c>
+      <c r="K163" s="1" t="n">
+        <v>0.096</v>
+      </c>
+      <c r="L163" s="2" t="n">
+        <v>0.001042752867570416</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -6031,6 +7015,12 @@
       <c r="J164" s="3" t="n">
         <v>-0.001810544611819197</v>
       </c>
+      <c r="K164" s="1" t="n">
+        <v>1.382</v>
+      </c>
+      <c r="L164" s="2" t="n">
+        <v>0.002684466371617075</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -6065,6 +7055,12 @@
       <c r="J165" s="2" t="n">
         <v>0.006282223473852922</v>
       </c>
+      <c r="K165" s="1" t="n">
+        <v>0.023214</v>
+      </c>
+      <c r="L165" s="3" t="n">
+        <v>-0.000516662361147059</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -6099,6 +7095,12 @@
       <c r="J166" s="3" t="n">
         <v>-0.04063246920389774</v>
       </c>
+      <c r="K166" s="1" t="n">
+        <v>0.005194</v>
+      </c>
+      <c r="L166" s="3" t="n">
+        <v>-0.004599463395937252</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -6133,6 +7135,12 @@
       <c r="J167" s="2" t="n">
         <v>0.001221001221001383</v>
       </c>
+      <c r="K167" s="1" t="n">
+        <v>0.06560000000000001</v>
+      </c>
+      <c r="L167" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -6167,6 +7175,12 @@
       <c r="J168" s="3" t="n">
         <v>-0.001054852320674989</v>
       </c>
+      <c r="K168" s="1" t="n">
+        <v>0.0948</v>
+      </c>
+      <c r="L168" s="2" t="n">
+        <v>0.001055966209081193</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -6201,6 +7215,12 @@
       <c r="J169" s="3" t="n">
         <v>-0.001562907007033018</v>
       </c>
+      <c r="K169" s="1" t="n">
+        <v>0.03815</v>
+      </c>
+      <c r="L169" s="3" t="n">
+        <v>-0.004696060527002338</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -6235,6 +7255,12 @@
       <c r="J170" s="3" t="n">
         <v>-0.0002810172825629149</v>
       </c>
+      <c r="K170" s="1" t="n">
+        <v>0.007128</v>
+      </c>
+      <c r="L170" s="2" t="n">
+        <v>0.001827125790583274</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -6269,6 +7295,12 @@
       <c r="J171" s="2" t="n">
         <v>0.002052785923753602</v>
       </c>
+      <c r="K171" s="1" t="n">
+        <v>0.3428</v>
+      </c>
+      <c r="L171" s="2" t="n">
+        <v>0.003219198127011969</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -6303,6 +7335,12 @@
       <c r="J172" s="2" t="n">
         <v>0.0009201324990798478</v>
       </c>
+      <c r="K172" s="1" t="n">
+        <v>5.447</v>
+      </c>
+      <c r="L172" s="2" t="n">
+        <v>0.001470858613715758</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -6337,6 +7375,12 @@
       <c r="J173" s="3" t="n">
         <v>-0.0006589062156820173</v>
       </c>
+      <c r="K173" s="1" t="n">
+        <v>0.04559</v>
+      </c>
+      <c r="L173" s="2" t="n">
+        <v>0.001978021978021974</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -6371,6 +7415,12 @@
       <c r="J174" s="3" t="n">
         <v>-0.002040816326530529</v>
       </c>
+      <c r="K174" s="1" t="n">
+        <v>0.03909</v>
+      </c>
+      <c r="L174" s="3" t="n">
+        <v>-0.0007668711656442292</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -6405,6 +7455,12 @@
       <c r="J175" s="3" t="n">
         <v>-0.005363847666726202</v>
       </c>
+      <c r="K175" s="1" t="n">
+        <v>0.005629</v>
+      </c>
+      <c r="L175" s="2" t="n">
+        <v>0.01186410210318175</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -6439,6 +7495,12 @@
       <c r="J176" s="3" t="n">
         <v>-0.001315789473684157</v>
       </c>
+      <c r="K176" s="1" t="n">
+        <v>0.00759</v>
+      </c>
+      <c r="L176" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -6473,6 +7535,12 @@
       <c r="J177" s="3" t="n">
         <v>-0.01083238312428729</v>
       </c>
+      <c r="K177" s="1" t="n">
+        <v>1.743</v>
+      </c>
+      <c r="L177" s="2" t="n">
+        <v>0.004610951008645537</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -6507,6 +7575,12 @@
       <c r="J178" s="3" t="n">
         <v>-0.0004467134652201451</v>
       </c>
+      <c r="K178" s="1" t="n">
+        <v>15.668</v>
+      </c>
+      <c r="L178" s="2" t="n">
+        <v>0.0003192236480877868</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -6541,6 +7615,12 @@
       <c r="J179" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="K179" s="1" t="n">
+        <v>0.309</v>
+      </c>
+      <c r="L179" s="3" t="n">
+        <v>-0.003225806451612906</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -6575,6 +7655,12 @@
       <c r="J180" s="2" t="n">
         <v>0.01613759422444004</v>
       </c>
+      <c r="K180" s="1" t="n">
+        <v>0.09678</v>
+      </c>
+      <c r="L180" s="2" t="n">
+        <v>0.01117960505694286</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -6609,6 +7695,12 @@
       <c r="J181" s="3" t="n">
         <v>-0.001066098081023337</v>
       </c>
+      <c r="K181" s="1" t="n">
+        <v>0.1876</v>
+      </c>
+      <c r="L181" s="2" t="n">
+        <v>0.001067235859124749</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -6643,6 +7735,12 @@
       <c r="J182" s="3" t="n">
         <v>-0.003523489932885937</v>
       </c>
+      <c r="K182" s="1" t="n">
+        <v>0.05935</v>
+      </c>
+      <c r="L182" s="3" t="n">
+        <v>-0.0006735140596059668</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -6677,6 +7775,12 @@
       <c r="J183" s="3" t="n">
         <v>-0.0008278145695363901</v>
       </c>
+      <c r="K183" s="1" t="n">
+        <v>0.01207</v>
+      </c>
+      <c r="L183" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -6711,6 +7815,12 @@
       <c r="J184" s="3" t="n">
         <v>-0.004646840148698856</v>
       </c>
+      <c r="K184" s="1" t="n">
+        <v>0.02155</v>
+      </c>
+      <c r="L184" s="2" t="n">
+        <v>0.006069094304388336</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -6745,6 +7855,12 @@
       <c r="J185" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="K185" s="1" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="L185" s="3" t="n">
+        <v>-0.002754820936639121</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -6779,6 +7895,12 @@
       <c r="J186" s="2" t="n">
         <v>0.0005240403511069912</v>
       </c>
+      <c r="K186" s="1" t="n">
+        <v>0.007636</v>
+      </c>
+      <c r="L186" s="3" t="n">
+        <v>-0.0001309414691631878</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -6813,6 +7935,12 @@
       <c r="J187" s="3" t="n">
         <v>-0.003687315634218293</v>
       </c>
+      <c r="K187" s="1" t="n">
+        <v>0.2695</v>
+      </c>
+      <c r="L187" s="3" t="n">
+        <v>-0.002590673575129454</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -6847,6 +7975,12 @@
       <c r="J188" s="3" t="n">
         <v>-0.0002036659877799618</v>
       </c>
+      <c r="K188" s="1" t="n">
+        <v>0.04906</v>
+      </c>
+      <c r="L188" s="3" t="n">
+        <v>-0.0006111224281931605</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -6881,6 +8015,12 @@
       <c r="J189" s="3" t="n">
         <v>-0.0007809449433814057</v>
       </c>
+      <c r="K189" s="1" t="n">
+        <v>0.256</v>
+      </c>
+      <c r="L189" s="2" t="n">
+        <v>0.0003907776475185189</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -6915,6 +8055,12 @@
       <c r="J190" s="2" t="n">
         <v>0.0007088428141058939</v>
       </c>
+      <c r="K190" s="1" t="n">
+        <v>0.5672</v>
+      </c>
+      <c r="L190" s="2" t="n">
+        <v>0.004427129449265199</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -6949,6 +8095,12 @@
       <c r="J191" s="3" t="n">
         <v>-0.001325161504058308</v>
       </c>
+      <c r="K191" s="1" t="n">
+        <v>6.039</v>
+      </c>
+      <c r="L191" s="2" t="n">
+        <v>0.001658649859014727</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -6983,6 +8135,12 @@
       <c r="J192" s="2" t="n">
         <v>0.001431844215349371</v>
       </c>
+      <c r="K192" s="1" t="n">
+        <v>0.3496</v>
+      </c>
+      <c r="L192" s="3" t="n">
+        <v>-0.0002859593937660537</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -7017,6 +8175,12 @@
       <c r="J193" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="K193" s="1" t="n">
+        <v>0.0643</v>
+      </c>
+      <c r="L193" s="2" t="n">
+        <v>0.001557632398753939</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -7051,6 +8215,12 @@
       <c r="J194" s="2" t="n">
         <v>0.001724137931034612</v>
       </c>
+      <c r="K194" s="1" t="n">
+        <v>0.01751</v>
+      </c>
+      <c r="L194" s="2" t="n">
+        <v>0.004589787722317855</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -7085,6 +8255,12 @@
       <c r="J195" s="2" t="n">
         <v>0.003569372481289604</v>
       </c>
+      <c r="K195" s="1" t="n">
+        <v>0.0008649</v>
+      </c>
+      <c r="L195" s="3" t="n">
+        <v>-0.007687012391005048</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -7119,6 +8295,12 @@
       <c r="J196" s="2" t="n">
         <v>0.0009823182711197601</v>
       </c>
+      <c r="K196" s="1" t="n">
+        <v>0.001018</v>
+      </c>
+      <c r="L196" s="3" t="n">
+        <v>-0.0009813542688909872</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -7153,6 +8335,12 @@
       <c r="J197" s="3" t="n">
         <v>-0.00371057513914649</v>
       </c>
+      <c r="K197" s="1" t="n">
+        <v>0.0001613</v>
+      </c>
+      <c r="L197" s="2" t="n">
+        <v>0.001241464928615628</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -7187,6 +8375,12 @@
       <c r="J198" s="3" t="n">
         <v>-0.0009218713989399509</v>
       </c>
+      <c r="K198" s="1" t="n">
+        <v>4.344</v>
+      </c>
+      <c r="L198" s="2" t="n">
+        <v>0.002076124567474127</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -7221,6 +8415,12 @@
       <c r="J199" s="3" t="n">
         <v>-0.004892966360856239</v>
       </c>
+      <c r="K199" s="1" t="n">
+        <v>0.1631</v>
+      </c>
+      <c r="L199" s="2" t="n">
+        <v>0.002458512599876974</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -7255,6 +8455,12 @@
       <c r="J200" s="2" t="n">
         <v>0.007742426806566218</v>
       </c>
+      <c r="K200" s="1" t="n">
+        <v>0.023825</v>
+      </c>
+      <c r="L200" s="2" t="n">
+        <v>0.0002518997439018877</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -7289,6 +8495,12 @@
       <c r="J201" s="3" t="n">
         <v>-0.002075019952114784</v>
       </c>
+      <c r="K201" s="1" t="n">
+        <v>0.12388</v>
+      </c>
+      <c r="L201" s="3" t="n">
+        <v>-0.009277031349968075</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -7323,6 +8535,12 @@
       <c r="J202" s="3" t="n">
         <v>-0.001449275362318782</v>
       </c>
+      <c r="K202" s="1" t="n">
+        <v>0.01379</v>
+      </c>
+      <c r="L202" s="2" t="n">
+        <v>0.0007256894049346584</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -7357,6 +8575,12 @@
       <c r="J203" s="3" t="n">
         <v>-0.003178484107579418</v>
       </c>
+      <c r="K203" s="1" t="n">
+        <v>0.04089</v>
+      </c>
+      <c r="L203" s="2" t="n">
+        <v>0.002943340691685113</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -7391,6 +8615,12 @@
       <c r="J204" s="3" t="n">
         <v>-0.0003888024883359095</v>
       </c>
+      <c r="K204" s="1" t="n">
+        <v>0.02574</v>
+      </c>
+      <c r="L204" s="2" t="n">
+        <v>0.001166861143523873</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -7425,6 +8655,12 @@
       <c r="J205" s="3" t="n">
         <v>-0.000464360343626732</v>
       </c>
+      <c r="K205" s="1" t="n">
+        <v>0.4315</v>
+      </c>
+      <c r="L205" s="2" t="n">
+        <v>0.002322880371660862</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -7459,6 +8695,12 @@
       <c r="J206" s="3" t="n">
         <v>-0.004357298474945658</v>
       </c>
+      <c r="K206" s="1" t="n">
+        <v>0.02297</v>
+      </c>
+      <c r="L206" s="2" t="n">
+        <v>0.00525164113785567</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -7493,6 +8735,12 @@
       <c r="J207" s="3" t="n">
         <v>-0.0009596928982726602</v>
       </c>
+      <c r="K207" s="1" t="n">
+        <v>4.166</v>
+      </c>
+      <c r="L207" s="2" t="n">
+        <v>0.0004803073967340702</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -7527,6 +8775,12 @@
       <c r="J208" s="3" t="n">
         <v>-0.0001352630867035861</v>
       </c>
+      <c r="K208" s="1" t="n">
+        <v>0.07378999999999999</v>
+      </c>
+      <c r="L208" s="3" t="n">
+        <v>-0.001758658008658078</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -7561,6 +8815,12 @@
       <c r="J209" s="3" t="n">
         <v>-0.001421464108031214</v>
       </c>
+      <c r="K209" s="1" t="n">
+        <v>0.04214</v>
+      </c>
+      <c r="L209" s="3" t="n">
+        <v>-0.000237247924080737</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -7595,6 +8855,12 @@
       <c r="J210" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="K210" s="1" t="n">
+        <v>0.1846</v>
+      </c>
+      <c r="L210" s="2" t="n">
+        <v>0.003260869565217334</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -7629,6 +8895,12 @@
       <c r="J211" s="3" t="n">
         <v>-0.001671541997492735</v>
       </c>
+      <c r="K211" s="1" t="n">
+        <v>0.2389</v>
+      </c>
+      <c r="L211" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -7663,6 +8935,12 @@
       <c r="J212" s="3" t="n">
         <v>-0.002880460873739972</v>
       </c>
+      <c r="K212" s="1" t="n">
+        <v>0.002083</v>
+      </c>
+      <c r="L212" s="2" t="n">
+        <v>0.002888781896966954</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -7697,6 +8975,12 @@
       <c r="J213" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="K213" s="1" t="n">
+        <v>0.9330000000000001</v>
+      </c>
+      <c r="L213" s="2" t="n">
+        <v>0.004305705059203449</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -7731,6 +9015,12 @@
       <c r="J214" s="3" t="n">
         <v>-0.003497726477789446</v>
       </c>
+      <c r="K214" s="1" t="n">
+        <v>0.005709</v>
+      </c>
+      <c r="L214" s="2" t="n">
+        <v>0.001930501930501882</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -7765,6 +9055,12 @@
       <c r="J215" s="3" t="n">
         <v>-0.001096691646865372</v>
       </c>
+      <c r="K215" s="1" t="n">
+        <v>0.05473</v>
+      </c>
+      <c r="L215" s="2" t="n">
+        <v>0.001463860933211412</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -7799,6 +9095,12 @@
       <c r="J216" s="3" t="n">
         <v>-0.001579778830963491</v>
       </c>
+      <c r="K216" s="1" t="n">
+        <v>0.0634</v>
+      </c>
+      <c r="L216" s="2" t="n">
+        <v>0.003164556962025187</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -7833,6 +9135,12 @@
       <c r="J217" s="2" t="n">
         <v>0.003243243243243186</v>
       </c>
+      <c r="K217" s="1" t="n">
+        <v>0.0927</v>
+      </c>
+      <c r="L217" s="3" t="n">
+        <v>-0.001077586206896433</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -7867,6 +9175,12 @@
       <c r="J218" s="3" t="n">
         <v>-0.001923425875521794</v>
       </c>
+      <c r="K218" s="1" t="n">
+        <v>0.27432</v>
+      </c>
+      <c r="L218" s="3" t="n">
+        <v>-0.002545269434950107</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -7901,6 +9215,12 @@
       <c r="J219" s="3" t="n">
         <v>-0.001538935056940668</v>
       </c>
+      <c r="K219" s="1" t="n">
+        <v>0.003254</v>
+      </c>
+      <c r="L219" s="2" t="n">
+        <v>0.003082614056720107</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -7935,6 +9255,12 @@
       <c r="J220" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="K220" s="1" t="n">
+        <v>0.999374</v>
+      </c>
+      <c r="L220" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -7969,6 +9295,12 @@
       <c r="J221" s="2" t="n">
         <v>0.0002587322121604932</v>
       </c>
+      <c r="K221" s="1" t="n">
+        <v>0.0389</v>
+      </c>
+      <c r="L221" s="2" t="n">
+        <v>0.006207966890843176</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -8003,6 +9335,12 @@
       <c r="J222" s="2" t="n">
         <v>0.0004304778303917173</v>
       </c>
+      <c r="K222" s="1" t="n">
+        <v>0.04659</v>
+      </c>
+      <c r="L222" s="2" t="n">
+        <v>0.002366609294320116</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -8037,6 +9375,12 @@
       <c r="J223" s="3" t="n">
         <v>-0.0009532888465203907</v>
       </c>
+      <c r="K223" s="1" t="n">
+        <v>0.1053</v>
+      </c>
+      <c r="L223" s="2" t="n">
+        <v>0.004770992366412218</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -8071,6 +9415,12 @@
       <c r="J224" s="3" t="n">
         <v>-0.002317795518928637</v>
       </c>
+      <c r="K224" s="1" t="n">
+        <v>3.875</v>
+      </c>
+      <c r="L224" s="2" t="n">
+        <v>0.0002581311306143236</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -8105,6 +9455,12 @@
       <c r="J225" s="3" t="n">
         <v>-0.002058727922851871</v>
       </c>
+      <c r="K225" s="1" t="n">
+        <v>0.0009229</v>
+      </c>
+      <c r="L225" s="2" t="n">
+        <v>0.002062975027144399</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -8139,6 +9495,12 @@
       <c r="J226" s="3" t="n">
         <v>-0.000823142050799631</v>
       </c>
+      <c r="K226" s="1" t="n">
+        <v>0.008473</v>
+      </c>
+      <c r="L226" s="3" t="n">
+        <v>-0.002824526303401167</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -8173,6 +9535,12 @@
       <c r="J227" s="3" t="n">
         <v>-0.00265700483091785</v>
       </c>
+      <c r="K227" s="1" t="n">
+        <v>0.04132</v>
+      </c>
+      <c r="L227" s="2" t="n">
+        <v>0.0007265681763139319</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -8207,6 +9575,12 @@
       <c r="J228" s="3" t="n">
         <v>-0.001405283867341243</v>
       </c>
+      <c r="K228" s="1" t="n">
+        <v>0.03576</v>
+      </c>
+      <c r="L228" s="2" t="n">
+        <v>0.006473402758232509</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -8241,6 +9615,12 @@
       <c r="J229" s="3" t="n">
         <v>-0.001745877788554797</v>
       </c>
+      <c r="K229" s="1" t="n">
+        <v>0.05153</v>
+      </c>
+      <c r="L229" s="2" t="n">
+        <v>0.001360279828993405</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -8275,6 +9655,12 @@
       <c r="J230" s="3" t="n">
         <v>-0.004645760743321706</v>
       </c>
+      <c r="K230" s="1" t="n">
+        <v>0.00172</v>
+      </c>
+      <c r="L230" s="2" t="n">
+        <v>0.00350058343057172</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -8309,6 +9695,12 @@
       <c r="J231" s="3" t="n">
         <v>-0.004096681687832972</v>
       </c>
+      <c r="K231" s="1" t="n">
+        <v>0.04876</v>
+      </c>
+      <c r="L231" s="2" t="n">
+        <v>0.002879473467708788</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -8343,6 +9735,12 @@
       <c r="J232" s="3" t="n">
         <v>-0.001375515818431856</v>
       </c>
+      <c r="K232" s="1" t="n">
+        <v>0.02175</v>
+      </c>
+      <c r="L232" s="3" t="n">
+        <v>-0.001377410468319662</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -8377,6 +9775,12 @@
       <c r="J233" s="2" t="n">
         <v>0.0006850488097277097</v>
       </c>
+      <c r="K233" s="1" t="n">
+        <v>0.0005845</v>
+      </c>
+      <c r="L233" s="2" t="n">
+        <v>0.0003422899195616916</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -8411,6 +9815,12 @@
       <c r="J234" s="3" t="n">
         <v>-0.004859173940430241</v>
       </c>
+      <c r="K234" s="1" t="n">
+        <v>0.22057</v>
+      </c>
+      <c r="L234" s="3" t="n">
+        <v>-0.002757934713807756</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -8445,6 +9855,12 @@
       <c r="J235" s="2" t="n">
         <v>0.005057803468208137</v>
       </c>
+      <c r="K235" s="1" t="n">
+        <v>0.01395</v>
+      </c>
+      <c r="L235" s="2" t="n">
+        <v>0.00287562904385335</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -8479,6 +9895,12 @@
       <c r="J236" s="2" t="n">
         <v>0.002427184466019487</v>
       </c>
+      <c r="K236" s="1" t="n">
+        <v>0.0412</v>
+      </c>
+      <c r="L236" s="3" t="n">
+        <v>-0.002421307506053338</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -8513,6 +9935,12 @@
       <c r="J237" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="K237" s="1" t="n">
+        <v>0.00419</v>
+      </c>
+      <c r="L237" s="2" t="n">
+        <v>0.002392344497607766</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -8547,6 +9975,12 @@
       <c r="J238" s="3" t="n">
         <v>-0.004016064257028089</v>
       </c>
+      <c r="K238" s="1" t="n">
+        <v>0.0249</v>
+      </c>
+      <c r="L238" s="2" t="n">
+        <v>0.004032258064516105</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -8581,6 +10015,12 @@
       <c r="J239" s="3" t="n">
         <v>-0.002014775016789826</v>
       </c>
+      <c r="K239" s="1" t="n">
+        <v>0.0149</v>
+      </c>
+      <c r="L239" s="2" t="n">
+        <v>0.002691790040376858</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -8615,6 +10055,12 @@
       <c r="J240" s="3" t="n">
         <v>-0.0005103342689461722</v>
       </c>
+      <c r="K240" s="1" t="n">
+        <v>0.0003915</v>
+      </c>
+      <c r="L240" s="3" t="n">
+        <v>-0.0005105948429920982</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -8649,6 +10095,12 @@
       <c r="J241" s="2" t="n">
         <v>0.002259036144578273</v>
       </c>
+      <c r="K241" s="1" t="n">
+        <v>0.2665</v>
+      </c>
+      <c r="L241" s="2" t="n">
+        <v>0.001126972201352451</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -8683,6 +10135,12 @@
       <c r="J242" s="3" t="n">
         <v>-0.004446188047600276</v>
       </c>
+      <c r="K242" s="1" t="n">
+        <v>0.07668999999999999</v>
+      </c>
+      <c r="L242" s="2" t="n">
+        <v>0.007355838696965599</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -8717,6 +10175,12 @@
       <c r="J243" s="2" t="n">
         <v>0.001524390243902377</v>
       </c>
+      <c r="K243" s="1" t="n">
+        <v>0.01991</v>
+      </c>
+      <c r="L243" s="2" t="n">
+        <v>0.01014713343480478</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -8751,6 +10215,12 @@
       <c r="J244" s="2" t="n">
         <v>0.0003422313483915383</v>
       </c>
+      <c r="K244" s="1" t="n">
+        <v>0.08767</v>
+      </c>
+      <c r="L244" s="3" t="n">
+        <v>-0.0002280761774433359</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -8785,6 +10255,12 @@
       <c r="J245" s="2" t="n">
         <v>0.001050126015121854</v>
       </c>
+      <c r="K245" s="1" t="n">
+        <v>1.4244</v>
+      </c>
+      <c r="L245" s="3" t="n">
+        <v>-0.00384642282677099</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -8819,6 +10295,12 @@
       <c r="J246" s="3" t="n">
         <v>-0.005577244841048682</v>
       </c>
+      <c r="K246" s="1" t="n">
+        <v>0.01791</v>
+      </c>
+      <c r="L246" s="2" t="n">
+        <v>0.004486819966348862</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -8853,6 +10335,12 @@
       <c r="J247" s="3" t="n">
         <v>-0.001059642749016055</v>
       </c>
+      <c r="K247" s="1" t="n">
+        <v>0.006602</v>
+      </c>
+      <c r="L247" s="2" t="n">
+        <v>0.0004546143355054399</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -8887,6 +10375,12 @@
       <c r="J248" s="2" t="n">
         <v>0.01192748091603046</v>
       </c>
+      <c r="K248" s="1" t="n">
+        <v>0.004141</v>
+      </c>
+      <c r="L248" s="3" t="n">
+        <v>-0.0238095238095239</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -8921,6 +10415,12 @@
       <c r="J249" s="3" t="n">
         <v>-0.0009124087591241137</v>
       </c>
+      <c r="K249" s="1" t="n">
+        <v>0.1096</v>
+      </c>
+      <c r="L249" s="2" t="n">
+        <v>0.0009132420091324463</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -8955,6 +10455,12 @@
       <c r="J250" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="K250" s="1" t="n">
+        <v>0.03424</v>
+      </c>
+      <c r="L250" s="2" t="n">
+        <v>0.0005844535359438687</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -8989,6 +10495,12 @@
       <c r="J251" s="3" t="n">
         <v>-0.003001616254906446</v>
       </c>
+      <c r="K251" s="1" t="n">
+        <v>0.04311</v>
+      </c>
+      <c r="L251" s="3" t="n">
+        <v>-0.001621120889300616</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -9023,6 +10535,12 @@
       <c r="J252" s="2" t="n">
         <v>0.005312767780634066</v>
       </c>
+      <c r="K252" s="1" t="n">
+        <v>0.005955</v>
+      </c>
+      <c r="L252" s="2" t="n">
+        <v>0.01517217865666562</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -9057,6 +10575,12 @@
       <c r="J253" s="2" t="n">
         <v>0.003579952267303164</v>
       </c>
+      <c r="K253" s="1" t="n">
+        <v>0.01674</v>
+      </c>
+      <c r="L253" s="3" t="n">
+        <v>-0.004756242568370999</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -9091,6 +10615,12 @@
       <c r="J254" s="3" t="n">
         <v>-0.01064638783269971</v>
       </c>
+      <c r="K254" s="1" t="n">
+        <v>0.1299</v>
+      </c>
+      <c r="L254" s="3" t="n">
+        <v>-0.001537279016141474</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -9125,6 +10655,12 @@
       <c r="J255" s="2" t="n">
         <v>0.005303760848601687</v>
       </c>
+      <c r="K255" s="1" t="n">
+        <v>0.0209</v>
+      </c>
+      <c r="L255" s="2" t="n">
+        <v>0.002398081534772085</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -9159,6 +10695,12 @@
       <c r="J256" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="K256" s="1" t="n">
+        <v>0.02105</v>
+      </c>
+      <c r="L256" s="2" t="n">
+        <v>0.002380952380952284</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -9193,6 +10735,12 @@
       <c r="J257" s="3" t="n">
         <v>-0.001573564122738074</v>
       </c>
+      <c r="K257" s="1" t="n">
+        <v>0.02545</v>
+      </c>
+      <c r="L257" s="2" t="n">
+        <v>0.002758077226162357</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -9227,6 +10775,12 @@
       <c r="J258" s="2" t="n">
         <v>0.0009465215333647047</v>
       </c>
+      <c r="K258" s="1" t="n">
+        <v>0.14814</v>
+      </c>
+      <c r="L258" s="2" t="n">
+        <v>0.0006079027355623556</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -9261,6 +10815,12 @@
       <c r="J259" s="3" t="n">
         <v>-0.000785700255352551</v>
       </c>
+      <c r="K259" s="1" t="n">
+        <v>0.05095</v>
+      </c>
+      <c r="L259" s="2" t="n">
+        <v>0.001572636131315189</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -9295,6 +10855,12 @@
       <c r="J260" s="3" t="n">
         <v>-0.001205690860863309</v>
       </c>
+      <c r="K260" s="1" t="n">
+        <v>0.08298999999999999</v>
+      </c>
+      <c r="L260" s="2" t="n">
+        <v>0.001810719459198423</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -9329,6 +10895,12 @@
       <c r="J261" s="2" t="n">
         <v>0.003732890916632037</v>
       </c>
+      <c r="K261" s="1" t="n">
+        <v>0.2387</v>
+      </c>
+      <c r="L261" s="3" t="n">
+        <v>-0.01363636363636363</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -9363,6 +10935,12 @@
       <c r="J262" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="K262" s="1" t="n">
+        <v>0.1425</v>
+      </c>
+      <c r="L262" s="2" t="n">
+        <v>0.001405481377371595</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -9397,6 +10975,12 @@
       <c r="J263" s="2" t="n">
         <v>0.0005161290322580435</v>
       </c>
+      <c r="K263" s="1" t="n">
+        <v>0.07734000000000001</v>
+      </c>
+      <c r="L263" s="3" t="n">
+        <v>-0.00257931390250183</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -9431,6 +11015,12 @@
       <c r="J264" s="2" t="n">
         <v>0.0241361788617886</v>
       </c>
+      <c r="K264" s="1" t="n">
+        <v>0.04045</v>
+      </c>
+      <c r="L264" s="2" t="n">
+        <v>0.003473083602083881</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -9465,6 +11055,12 @@
       <c r="J265" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="K265" s="1" t="n">
+        <v>0.01532</v>
+      </c>
+      <c r="L265" s="3" t="n">
+        <v>-0.002604166666666673</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -9499,6 +11095,12 @@
       <c r="J266" s="3" t="n">
         <v>-0.003160871735152208</v>
       </c>
+      <c r="K266" s="1" t="n">
+        <v>0.005972</v>
+      </c>
+      <c r="L266" s="3" t="n">
+        <v>-0.003337783711615496</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -9533,6 +11135,12 @@
       <c r="J267" s="3" t="n">
         <v>-0.0005349023803155706</v>
       </c>
+      <c r="K267" s="1" t="n">
+        <v>0.03721</v>
+      </c>
+      <c r="L267" s="3" t="n">
+        <v>-0.004281509232004293</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -9567,6 +11175,12 @@
       <c r="J268" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="K268" s="1" t="n">
+        <v>0.03054</v>
+      </c>
+      <c r="L268" s="2" t="n">
+        <v>0.001639881928501195</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -9601,6 +11215,12 @@
       <c r="J269" s="3" t="n">
         <v>-0.001275678529010744</v>
       </c>
+      <c r="K269" s="1" t="n">
+        <v>0.2274</v>
+      </c>
+      <c r="L269" s="2" t="n">
+        <v>0.001585623678646931</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -9635,6 +11255,12 @@
       <c r="J270" s="3" t="n">
         <v>-0.004296455424274977</v>
       </c>
+      <c r="K270" s="1" t="n">
+        <v>0.924</v>
+      </c>
+      <c r="L270" s="3" t="n">
+        <v>-0.003236245954692559</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -9669,6 +11295,12 @@
       <c r="J271" s="3" t="n">
         <v>-0.003849114703618086</v>
       </c>
+      <c r="K271" s="1" t="n">
+        <v>2.592</v>
+      </c>
+      <c r="L271" s="2" t="n">
+        <v>0.001545595054095828</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -9703,6 +11335,12 @@
       <c r="J272" s="3" t="n">
         <v>-0.002170374389582114</v>
       </c>
+      <c r="K272" s="1" t="n">
+        <v>0.1844</v>
+      </c>
+      <c r="L272" s="2" t="n">
+        <v>0.002718868950516587</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -9737,6 +11375,12 @@
       <c r="J273" s="3" t="n">
         <v>-0.0003242542153047858</v>
       </c>
+      <c r="K273" s="1" t="n">
+        <v>0.03091</v>
+      </c>
+      <c r="L273" s="2" t="n">
+        <v>0.002594875121634778</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -9771,6 +11415,12 @@
       <c r="J274" s="2" t="n">
         <v>0.003164556962025407</v>
       </c>
+      <c r="K274" s="1" t="n">
+        <v>0.1909</v>
+      </c>
+      <c r="L274" s="2" t="n">
+        <v>0.003680336487907352</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -9805,6 +11455,12 @@
       <c r="J275" s="2" t="n">
         <v>0.005373221028173037</v>
       </c>
+      <c r="K275" s="1" t="n">
+        <v>0.06955</v>
+      </c>
+      <c r="L275" s="2" t="n">
+        <v>0.004622273580817577</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -9839,6 +11495,12 @@
       <c r="J276" s="3" t="n">
         <v>-0.001605929586164191</v>
       </c>
+      <c r="K276" s="1" t="n">
+        <v>0.08085000000000001</v>
+      </c>
+      <c r="L276" s="2" t="n">
+        <v>0.0003711952487008444</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -9873,6 +11535,12 @@
       <c r="J277" s="3" t="n">
         <v>-0.02802850356294538</v>
       </c>
+      <c r="K277" s="1" t="n">
+        <v>0.003926</v>
+      </c>
+      <c r="L277" s="3" t="n">
+        <v>-0.04056695992179871</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -9907,6 +11575,12 @@
       <c r="J278" s="3" t="n">
         <v>-0.002577319587628868</v>
       </c>
+      <c r="K278" s="1" t="n">
+        <v>1.551</v>
+      </c>
+      <c r="L278" s="2" t="n">
+        <v>0.001937984496123961</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -9941,6 +11615,12 @@
       <c r="J279" s="2" t="n">
         <v>0.0009041591320071964</v>
       </c>
+      <c r="K279" s="1" t="n">
+        <v>0.01104</v>
+      </c>
+      <c r="L279" s="3" t="n">
+        <v>-0.002710027100271049</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -9975,6 +11655,12 @@
       <c r="J280" s="3" t="n">
         <v>-0.001015486164000974</v>
       </c>
+      <c r="K280" s="1" t="n">
+        <v>0.03953</v>
+      </c>
+      <c r="L280" s="2" t="n">
+        <v>0.004574332909783979</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -10009,6 +11695,12 @@
       <c r="J281" s="3" t="n">
         <v>-0.01100960412274533</v>
       </c>
+      <c r="K281" s="1" t="n">
+        <v>0.08365</v>
+      </c>
+      <c r="L281" s="3" t="n">
+        <v>-0.009355755566082414</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -10043,6 +11735,12 @@
       <c r="J282" s="3" t="n">
         <v>-0.003759398496240579</v>
       </c>
+      <c r="K282" s="1" t="n">
+        <v>0.0265</v>
+      </c>
+      <c r="L282" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -10077,6 +11775,12 @@
       <c r="J283" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="K283" s="1" t="n">
+        <v>0.07632</v>
+      </c>
+      <c r="L283" s="2" t="n">
+        <v>0.002495730986470455</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -10111,6 +11815,12 @@
       <c r="J284" s="3" t="n">
         <v>-0.001233806292412121</v>
       </c>
+      <c r="K284" s="1" t="n">
+        <v>0.001619</v>
+      </c>
+      <c r="L284" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -10145,6 +11855,12 @@
       <c r="J285" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="K285" s="1" t="n">
+        <v>0.2023</v>
+      </c>
+      <c r="L285" s="2" t="n">
+        <v>0.001485148514851459</v>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -10179,6 +11895,12 @@
       <c r="J286" s="3" t="n">
         <v>-0.004173235648706223</v>
       </c>
+      <c r="K286" s="1" t="n">
+        <v>0.10644</v>
+      </c>
+      <c r="L286" s="3" t="n">
+        <v>-0.008753957906500246</v>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -10213,6 +11935,12 @@
       <c r="J287" s="3" t="n">
         <v>-0.001744186046511557</v>
       </c>
+      <c r="K287" s="1" t="n">
+        <v>0.01727</v>
+      </c>
+      <c r="L287" s="2" t="n">
+        <v>0.005824111822946965</v>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -10247,6 +11975,12 @@
       <c r="J288" s="3" t="n">
         <v>-0.005218525766470986</v>
       </c>
+      <c r="K288" s="1" t="n">
+        <v>0.01522</v>
+      </c>
+      <c r="L288" s="3" t="n">
+        <v>-0.001967213114754132</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -10281,6 +12015,12 @@
       <c r="J289" s="3" t="n">
         <v>-0.003742981908920621</v>
       </c>
+      <c r="K289" s="1" t="n">
+        <v>0.01597</v>
+      </c>
+      <c r="L289" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -10315,6 +12055,12 @@
       <c r="J290" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="K290" s="1" t="n">
+        <v>2.266</v>
+      </c>
+      <c r="L290" s="3" t="n">
+        <v>-0.0004411116012350639</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -10349,6 +12095,12 @@
       <c r="J291" s="3" t="n">
         <v>-0.002935862691960305</v>
       </c>
+      <c r="K291" s="1" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="L291" s="3" t="n">
+        <v>-0.003397508493771237</v>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -10383,6 +12135,12 @@
       <c r="J292" s="3" t="n">
         <v>-0.001150086256469236</v>
       </c>
+      <c r="K292" s="1" t="n">
+        <v>1.735</v>
+      </c>
+      <c r="L292" s="3" t="n">
+        <v>-0.001151410477835349</v>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -10417,6 +12175,12 @@
       <c r="J293" s="2" t="n">
         <v>0.010958358238693</v>
       </c>
+      <c r="K293" s="1" t="n">
+        <v>0.05062</v>
+      </c>
+      <c r="L293" s="3" t="n">
+        <v>-0.002364998029168349</v>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -10451,6 +12215,12 @@
       <c r="J294" s="3" t="n">
         <v>-0.001574059499449124</v>
       </c>
+      <c r="K294" s="1" t="n">
+        <v>0.0635</v>
+      </c>
+      <c r="L294" s="2" t="n">
+        <v>0.001103578748226401</v>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -10485,6 +12255,12 @@
       <c r="J295" s="3" t="n">
         <v>-0.001213592233009738</v>
       </c>
+      <c r="K295" s="1" t="n">
+        <v>0.0004132</v>
+      </c>
+      <c r="L295" s="2" t="n">
+        <v>0.004131227217497063</v>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -10519,6 +12295,12 @@
       <c r="J296" s="3" t="n">
         <v>-0.003995525011986575</v>
       </c>
+      <c r="K296" s="1" t="n">
+        <v>62.42</v>
+      </c>
+      <c r="L296" s="2" t="n">
+        <v>0.001604621309371011</v>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -10553,6 +12335,12 @@
       <c r="J297" s="3" t="n">
         <v>-0.00203873598369017</v>
       </c>
+      <c r="K297" s="1" t="n">
+        <v>0.0979</v>
+      </c>
+      <c r="L297" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -10587,6 +12375,12 @@
       <c r="J298" s="3" t="n">
         <v>-0.001044932079414723</v>
       </c>
+      <c r="K298" s="1" t="n">
+        <v>0.0955</v>
+      </c>
+      <c r="L298" s="3" t="n">
+        <v>-0.00104602510460254</v>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -10621,6 +12415,12 @@
       <c r="J299" s="3" t="n">
         <v>-0.005516810658894584</v>
       </c>
+      <c r="K299" s="1" t="n">
+        <v>0.09594</v>
+      </c>
+      <c r="L299" s="2" t="n">
+        <v>0.004186728072011698</v>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -10655,6 +12455,12 @@
       <c r="J300" s="3" t="n">
         <v>-0.001624255549539728</v>
       </c>
+      <c r="K300" s="1" t="n">
+        <v>0.01852</v>
+      </c>
+      <c r="L300" s="2" t="n">
+        <v>0.00433839479392607</v>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -10689,6 +12495,12 @@
       <c r="J301" s="3" t="n">
         <v>-0.0007501875468866911</v>
       </c>
+      <c r="K301" s="1" t="n">
+        <v>0.01336</v>
+      </c>
+      <c r="L301" s="2" t="n">
+        <v>0.003003003003003011</v>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -10723,6 +12535,12 @@
       <c r="J302" s="3" t="n">
         <v>-0.000229410415232882</v>
       </c>
+      <c r="K302" s="1" t="n">
+        <v>0.00436</v>
+      </c>
+      <c r="L302" s="2" t="n">
+        <v>0.0004589261128958847</v>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -10757,6 +12575,12 @@
       <c r="J303" s="2" t="n">
         <v>0.004282655246252688</v>
       </c>
+      <c r="K303" s="1" t="n">
+        <v>0.009339999999999999</v>
+      </c>
+      <c r="L303" s="3" t="n">
+        <v>-0.004264392324093828</v>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -10791,6 +12615,12 @@
       <c r="J304" s="3" t="n">
         <v>-0.001057977147693587</v>
       </c>
+      <c r="K304" s="1" t="n">
+        <v>4.734</v>
+      </c>
+      <c r="L304" s="2" t="n">
+        <v>0.00275365388688835</v>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -10825,6 +12655,12 @@
       <c r="J305" s="3" t="n">
         <v>-0.003195488721804446</v>
       </c>
+      <c r="K305" s="1" t="n">
+        <v>0.05296</v>
+      </c>
+      <c r="L305" s="3" t="n">
+        <v>-0.001320007542900257</v>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -10859,6 +12695,12 @@
       <c r="J306" s="3" t="n">
         <v>-0.003424657534246555</v>
       </c>
+      <c r="K306" s="1" t="n">
+        <v>0.05832</v>
+      </c>
+      <c r="L306" s="2" t="n">
+        <v>0.002061855670103009</v>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -10893,6 +12735,12 @@
       <c r="J307" s="3" t="n">
         <v>-0.002844141069397044</v>
       </c>
+      <c r="K307" s="1" t="n">
+        <v>0.1755</v>
+      </c>
+      <c r="L307" s="2" t="n">
+        <v>0.001140901312036383</v>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -10927,6 +12775,12 @@
       <c r="J308" s="3" t="n">
         <v>-0.001822969414624262</v>
       </c>
+      <c r="K308" s="1" t="n">
+        <v>0.04936</v>
+      </c>
+      <c r="L308" s="2" t="n">
+        <v>0.001623376623376698</v>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -10961,6 +12815,12 @@
       <c r="J309" s="3" t="n">
         <v>-0.003321033210332147</v>
       </c>
+      <c r="K309" s="1" t="n">
+        <v>0.5409</v>
+      </c>
+      <c r="L309" s="2" t="n">
+        <v>0.001295816364309578</v>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -10995,6 +12855,12 @@
       <c r="J310" s="3" t="n">
         <v>-0.004098360655737716</v>
       </c>
+      <c r="K310" s="1" t="n">
+        <v>0.00244</v>
+      </c>
+      <c r="L310" s="2" t="n">
+        <v>0.00411522633744857</v>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -11029,6 +12895,12 @@
       <c r="J311" s="3" t="n">
         <v>-0.003767792352777091</v>
       </c>
+      <c r="K311" s="1" t="n">
+        <v>0.07147000000000001</v>
+      </c>
+      <c r="L311" s="2" t="n">
+        <v>0.001120605126768604</v>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -11063,6 +12935,12 @@
       <c r="J312" s="2" t="n">
         <v>0.001890569395017755</v>
       </c>
+      <c r="K312" s="1" t="n">
+        <v>0.009022000000000001</v>
+      </c>
+      <c r="L312" s="2" t="n">
+        <v>0.001443001443001538</v>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -11097,6 +12975,12 @@
       <c r="J313" s="2" t="n">
         <v>0.01152379373238271</v>
       </c>
+      <c r="K313" s="1" t="n">
+        <v>0.012076</v>
+      </c>
+      <c r="L313" s="3" t="n">
+        <v>-0.01024506188017377</v>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -11131,6 +13015,12 @@
       <c r="J314" s="3" t="n">
         <v>-0.005136986301369803</v>
       </c>
+      <c r="K314" s="1" t="n">
+        <v>0.02309</v>
+      </c>
+      <c r="L314" s="3" t="n">
+        <v>-0.006454388984509502</v>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -11165,6 +13055,12 @@
       <c r="J315" s="3" t="n">
         <v>-0.002812939521800289</v>
       </c>
+      <c r="K315" s="1" t="n">
+        <v>0.00711</v>
+      </c>
+      <c r="L315" s="2" t="n">
+        <v>0.002820874471086044</v>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -11199,6 +13095,12 @@
       <c r="J316" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="K316" s="1" t="n">
+        <v>0.2612</v>
+      </c>
+      <c r="L316" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -11233,6 +13135,12 @@
       <c r="J317" s="2" t="n">
         <v>0.009009009009008922</v>
       </c>
+      <c r="K317" s="1" t="n">
+        <v>1.11e-05</v>
+      </c>
+      <c r="L317" s="3" t="n">
+        <v>-0.008928571428571343</v>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -11267,6 +13175,12 @@
       <c r="J318" s="3" t="n">
         <v>-0.002538840469874994</v>
       </c>
+      <c r="K318" s="1" t="n">
+        <v>0.052432</v>
+      </c>
+      <c r="L318" s="3" t="n">
+        <v>-0.004064886221175378</v>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -11301,6 +13215,12 @@
       <c r="J319" s="2" t="n">
         <v>0.002894736842105236</v>
       </c>
+      <c r="K319" s="1" t="n">
+        <v>0.0382</v>
+      </c>
+      <c r="L319" s="2" t="n">
+        <v>0.002361584885856726</v>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -11335,6 +13255,12 @@
       <c r="J320" s="3" t="n">
         <v>-0.001908396946564884</v>
       </c>
+      <c r="K320" s="1" t="n">
+        <v>0.006809</v>
+      </c>
+      <c r="L320" s="2" t="n">
+        <v>0.001470804530077893</v>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -11369,6 +13295,12 @@
       <c r="J321" s="3" t="n">
         <v>-0.003313452617627693</v>
       </c>
+      <c r="K321" s="1" t="n">
+        <v>4.533</v>
+      </c>
+      <c r="L321" s="2" t="n">
+        <v>0.004654255319149113</v>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -11403,6 +13335,12 @@
       <c r="J322" s="3" t="n">
         <v>-0.003134796238244517</v>
       </c>
+      <c r="K322" s="1" t="n">
+        <v>1.909</v>
+      </c>
+      <c r="L322" s="2" t="n">
+        <v>0.0005241090146751111</v>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -11437,6 +13375,12 @@
       <c r="J323" s="3" t="n">
         <v>-0.0001414627245720941</v>
       </c>
+      <c r="K323" s="1" t="n">
+        <v>0.007074</v>
+      </c>
+      <c r="L323" s="2" t="n">
+        <v>0.0008488964346350873</v>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -11471,6 +13415,12 @@
       <c r="J324" s="3" t="n">
         <v>-0.001095290251916713</v>
       </c>
+      <c r="K324" s="1" t="n">
+        <v>0.0183</v>
+      </c>
+      <c r="L324" s="2" t="n">
+        <v>0.003289473684210583</v>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -11505,6 +13455,12 @@
       <c r="J325" s="3" t="n">
         <v>-0.0009751340809361567</v>
       </c>
+      <c r="K325" s="1" t="n">
+        <v>0.4098</v>
+      </c>
+      <c r="L325" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -11539,6 +13495,12 @@
       <c r="J326" s="3" t="n">
         <v>-0.003178112477546007</v>
       </c>
+      <c r="K326" s="1" t="n">
+        <v>0.007248</v>
+      </c>
+      <c r="L326" s="2" t="n">
+        <v>0.004713057942888852</v>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -11573,6 +13535,12 @@
       <c r="J327" s="2" t="n">
         <v>0.001047120418848198</v>
       </c>
+      <c r="K327" s="1" t="n">
+        <v>0.1899</v>
+      </c>
+      <c r="L327" s="3" t="n">
+        <v>-0.006799163179916295</v>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -11607,6 +13575,12 @@
       <c r="J328" s="2" t="n">
         <v>0.01518067137053666</v>
       </c>
+      <c r="K328" s="1" t="n">
+        <v>0.4732</v>
+      </c>
+      <c r="L328" s="3" t="n">
+        <v>-0.003369839932603181</v>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -11641,6 +13615,12 @@
       <c r="J329" s="3" t="n">
         <v>-0.001464128843338281</v>
       </c>
+      <c r="K329" s="1" t="n">
+        <v>0.01356</v>
+      </c>
+      <c r="L329" s="3" t="n">
+        <v>-0.005865102639296203</v>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -11675,6 +13655,12 @@
       <c r="J330" s="2" t="n">
         <v>0.0008826125330979953</v>
       </c>
+      <c r="K330" s="1" t="n">
+        <v>0.1136</v>
+      </c>
+      <c r="L330" s="2" t="n">
+        <v>0.001763668430335147</v>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -11709,6 +13695,12 @@
       <c r="J331" s="3" t="n">
         <v>-0.0006665555740709148</v>
       </c>
+      <c r="K331" s="1" t="n">
+        <v>0.6002999999999999</v>
+      </c>
+      <c r="L331" s="2" t="n">
+        <v>0.001000500250124952</v>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -11743,6 +13735,12 @@
       <c r="J332" s="3" t="n">
         <v>-0.006224482966334158</v>
       </c>
+      <c r="K332" s="1" t="n">
+        <v>0.2995</v>
+      </c>
+      <c r="L332" s="2" t="n">
+        <v>0.008553340517241334</v>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -11777,6 +13775,12 @@
       <c r="J333" s="3" t="n">
         <v>-0.005545286506469522</v>
       </c>
+      <c r="K333" s="1" t="n">
+        <v>0.0703</v>
+      </c>
+      <c r="L333" s="2" t="n">
+        <v>0.005147269087789523</v>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -11811,6 +13815,12 @@
       <c r="J334" s="3" t="n">
         <v>-0.0305421880012832</v>
       </c>
+      <c r="K334" s="1" t="n">
+        <v>0.15049</v>
+      </c>
+      <c r="L334" s="3" t="n">
+        <v>-0.003971143027334631</v>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -11845,6 +13855,12 @@
       <c r="J335" s="2" t="n">
         <v>0.0006397952655151423</v>
       </c>
+      <c r="K335" s="1" t="n">
+        <v>0.1564</v>
+      </c>
+      <c r="L335" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -11879,6 +13895,12 @@
       <c r="J336" s="3" t="n">
         <v>-0.004009163802978271</v>
       </c>
+      <c r="K336" s="1" t="n">
+        <v>0.174</v>
+      </c>
+      <c r="L336" s="2" t="n">
+        <v>0.0005750431282345543</v>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -11913,6 +13935,12 @@
       <c r="J337" s="3" t="n">
         <v>-0.01655138339920958</v>
       </c>
+      <c r="K337" s="1" t="n">
+        <v>0.04008</v>
+      </c>
+      <c r="L337" s="2" t="n">
+        <v>0.00678221552373774</v>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -11947,6 +13975,12 @@
       <c r="J338" s="2" t="n">
         <v>0.0007560007560008564</v>
       </c>
+      <c r="K338" s="1" t="n">
+        <v>0.005296</v>
+      </c>
+      <c r="L338" s="2" t="n">
+        <v>0.0001888574126534717</v>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -11981,6 +14015,12 @@
       <c r="J339" s="2" t="n">
         <v>0.0005839984426708633</v>
       </c>
+      <c r="K339" s="1" t="n">
+        <v>0.0514</v>
+      </c>
+      <c r="L339" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -12015,6 +14055,12 @@
       <c r="J340" s="3" t="n">
         <v>-0.005928853754940607</v>
       </c>
+      <c r="K340" s="1" t="n">
+        <v>0.15128</v>
+      </c>
+      <c r="L340" s="2" t="n">
+        <v>0.002518223989396895</v>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -12049,6 +14095,12 @@
       <c r="J341" s="3" t="n">
         <v>-0.0009210526315789044</v>
       </c>
+      <c r="K341" s="1" t="n">
+        <v>7.603</v>
+      </c>
+      <c r="L341" s="2" t="n">
+        <v>0.001317002502304726</v>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -12083,6 +14135,12 @@
       <c r="J342" s="2" t="n">
         <v>0.0008971291866029381</v>
       </c>
+      <c r="K342" s="1" t="n">
+        <v>0.3294</v>
+      </c>
+      <c r="L342" s="3" t="n">
+        <v>-0.01583507618763063</v>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -12117,6 +14175,12 @@
       <c r="J343" s="2" t="n">
         <v>0.007637474541751393</v>
       </c>
+      <c r="K343" s="1" t="n">
+        <v>0.01982</v>
+      </c>
+      <c r="L343" s="2" t="n">
+        <v>0.001515917129863681</v>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -12151,6 +14215,12 @@
       <c r="J344" s="2" t="n">
         <v>0.0009099181073704385</v>
       </c>
+      <c r="K344" s="1" t="n">
+        <v>2.205</v>
+      </c>
+      <c r="L344" s="2" t="n">
+        <v>0.002272727272727224</v>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -12185,6 +14255,12 @@
       <c r="J345" s="3" t="n">
         <v>-0.001571091908876671</v>
       </c>
+      <c r="K345" s="1" t="n">
+        <v>1.272</v>
+      </c>
+      <c r="L345" s="2" t="n">
+        <v>0.0007867820613690889</v>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -12219,6 +14295,12 @@
       <c r="J346" s="3" t="n">
         <v>-0.000965250965250926</v>
       </c>
+      <c r="K346" s="1" t="n">
+        <v>0.005184</v>
+      </c>
+      <c r="L346" s="2" t="n">
+        <v>0.001739130434782672</v>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -12253,6 +14335,12 @@
       <c r="J347" s="2" t="n">
         <v>0.0003493449781659246</v>
       </c>
+      <c r="K347" s="1" t="n">
+        <v>0.05726</v>
+      </c>
+      <c r="L347" s="3" t="n">
+        <v>-0.0001746114894360584</v>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -12287,6 +14375,12 @@
       <c r="J348" s="3" t="n">
         <v>-0.006245120999219323</v>
       </c>
+      <c r="K348" s="1" t="n">
+        <v>0.1271</v>
+      </c>
+      <c r="L348" s="3" t="n">
+        <v>-0.001571091908876714</v>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -12321,6 +14415,12 @@
       <c r="J349" s="3" t="n">
         <v>-0.001782872917585296</v>
       </c>
+      <c r="K349" s="1" t="n">
+        <v>5216.3</v>
+      </c>
+      <c r="L349" s="2" t="n">
+        <v>0.001786057230651082</v>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -12355,6 +14455,12 @@
       <c r="J350" s="2" t="n">
         <v>0.000354484225451953</v>
       </c>
+      <c r="K350" s="1" t="n">
+        <v>0.02825</v>
+      </c>
+      <c r="L350" s="2" t="n">
+        <v>0.001063075832742815</v>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -12389,6 +14495,12 @@
       <c r="J351" s="3" t="n">
         <v>-0.0007369196757552808</v>
       </c>
+      <c r="K351" s="1" t="n">
+        <v>0.001361</v>
+      </c>
+      <c r="L351" s="2" t="n">
+        <v>0.003687315634218299</v>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -12423,6 +14535,12 @@
       <c r="J352" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="K352" s="1" t="n">
+        <v>0.01602</v>
+      </c>
+      <c r="L352" s="2" t="n">
+        <v>0.01778907242693768</v>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -12457,6 +14575,12 @@
       <c r="J353" s="3" t="n">
         <v>-0.0003201536737633712</v>
       </c>
+      <c r="K353" s="1" t="n">
+        <v>6.297</v>
+      </c>
+      <c r="L353" s="2" t="n">
+        <v>0.008326661329063187</v>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -12491,6 +14615,12 @@
       <c r="J354" s="3" t="n">
         <v>-0.002093510118632397</v>
       </c>
+      <c r="K354" s="1" t="n">
+        <v>0.2861</v>
+      </c>
+      <c r="L354" s="2" t="n">
+        <v>0.0003496503496505053</v>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -12525,6 +14655,12 @@
       <c r="J355" s="3" t="n">
         <v>-0.002661504960077401</v>
       </c>
+      <c r="K355" s="1" t="n">
+        <v>0.04151</v>
+      </c>
+      <c r="L355" s="2" t="n">
+        <v>0.007035419699175123</v>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -12559,6 +14695,12 @@
       <c r="J356" s="2" t="n">
         <v>0.01846988795518208</v>
       </c>
+      <c r="K356" s="1" t="n">
+        <v>0.11474</v>
+      </c>
+      <c r="L356" s="3" t="n">
+        <v>-0.01383755908895574</v>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -12593,6 +14735,12 @@
       <c r="J357" s="3" t="n">
         <v>-0.006849315068493234</v>
       </c>
+      <c r="K357" s="1" t="n">
+        <v>0.005227</v>
+      </c>
+      <c r="L357" s="2" t="n">
+        <v>0.001340996168582387</v>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -12627,6 +14775,12 @@
       <c r="J358" s="3" t="n">
         <v>-0.008565310492505302</v>
       </c>
+      <c r="K358" s="1" t="n">
+        <v>0.1859</v>
+      </c>
+      <c r="L358" s="2" t="n">
+        <v>0.003779697624190098</v>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -12661,6 +14815,12 @@
       <c r="J359" s="2" t="n">
         <v>0.001230769230769266</v>
       </c>
+      <c r="K359" s="1" t="n">
+        <v>0.1624</v>
+      </c>
+      <c r="L359" s="3" t="n">
+        <v>-0.001843884449907944</v>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -12695,6 +14855,12 @@
       <c r="J360" s="3" t="n">
         <v>-0.004341703825393208</v>
       </c>
+      <c r="K360" s="1" t="n">
+        <v>0.08468000000000001</v>
+      </c>
+      <c r="L360" s="3" t="n">
+        <v>-0.002003535651148964</v>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -12729,6 +14895,12 @@
       <c r="J361" s="3" t="n">
         <v>-0.02227722772277223</v>
       </c>
+      <c r="K361" s="1" t="n">
+        <v>0.00792</v>
+      </c>
+      <c r="L361" s="2" t="n">
+        <v>0.00253164556962015</v>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -12763,6 +14935,12 @@
       <c r="J362" s="3" t="n">
         <v>-0.004251299008030287</v>
       </c>
+      <c r="K362" s="1" t="n">
+        <v>0.425</v>
+      </c>
+      <c r="L362" s="2" t="n">
+        <v>0.008064516129032293</v>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -12797,6 +14975,12 @@
       <c r="J363" s="3" t="n">
         <v>-0.001069804760631186</v>
       </c>
+      <c r="K363" s="1" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="L363" s="2" t="n">
+        <v>0.01472556894243645</v>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -12831,6 +15015,12 @@
       <c r="J364" s="3" t="n">
         <v>-0.0009132420091323829</v>
       </c>
+      <c r="K364" s="1" t="n">
+        <v>0.01094</v>
+      </c>
+      <c r="L364" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -12865,6 +15055,12 @@
       <c r="J365" s="2" t="n">
         <v>0.002001455604075673</v>
       </c>
+      <c r="K365" s="1" t="n">
+        <v>0.05488</v>
+      </c>
+      <c r="L365" s="3" t="n">
+        <v>-0.003450154349010399</v>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -12899,6 +15095,12 @@
       <c r="J366" s="2" t="n">
         <v>0.02429149797570845</v>
       </c>
+      <c r="K366" s="1" t="n">
+        <v>0.02297</v>
+      </c>
+      <c r="L366" s="2" t="n">
+        <v>0.008783487044356709</v>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -12933,6 +15135,12 @@
       <c r="J367" s="2" t="n">
         <v>0.001476014760147477</v>
       </c>
+      <c r="K367" s="1" t="n">
+        <v>0.001367</v>
+      </c>
+      <c r="L367" s="2" t="n">
+        <v>0.007369196757553447</v>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -12967,6 +15175,12 @@
       <c r="J368" s="3" t="n">
         <v>-0.0006973500697349302</v>
       </c>
+      <c r="K368" s="1" t="n">
+        <v>0.2864</v>
+      </c>
+      <c r="L368" s="3" t="n">
+        <v>-0.0006978367062108635</v>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -13001,6 +15215,12 @@
       <c r="J369" s="2" t="n">
         <v>0.003260869565217447</v>
       </c>
+      <c r="K369" s="1" t="n">
+        <v>0.01849</v>
+      </c>
+      <c r="L369" s="2" t="n">
+        <v>0.001625135427952263</v>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -13035,6 +15255,12 @@
       <c r="J370" s="2" t="n">
         <v>0.008594105454729181</v>
       </c>
+      <c r="K370" s="1" t="n">
+        <v>0.19937</v>
+      </c>
+      <c r="L370" s="3" t="n">
+        <v>-0.0007017192120695767</v>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -13069,6 +15295,12 @@
       <c r="J371" s="2" t="n">
         <v>0.01333333333333335</v>
       </c>
+      <c r="K371" s="1" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="L371" s="3" t="n">
+        <v>-0.01315789473684212</v>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -13103,6 +15335,12 @@
       <c r="J372" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="K372" s="1" t="n">
+        <v>0.1051</v>
+      </c>
+      <c r="L372" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -13137,6 +15375,12 @@
       <c r="J373" s="3" t="n">
         <v>-0.00182066454255796</v>
       </c>
+      <c r="K373" s="1" t="n">
+        <v>0.06610000000000001</v>
+      </c>
+      <c r="L373" s="2" t="n">
+        <v>0.004711962304301637</v>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -13171,6 +15415,12 @@
       <c r="J374" s="3" t="n">
         <v>-0.0002639218791237</v>
       </c>
+      <c r="K374" s="1" t="n">
+        <v>0.007596</v>
+      </c>
+      <c r="L374" s="2" t="n">
+        <v>0.00263991552270328</v>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -13205,6 +15455,12 @@
       <c r="J375" s="2" t="n">
         <v>0.0006297229219144632</v>
       </c>
+      <c r="K375" s="1" t="n">
+        <v>0.1593</v>
+      </c>
+      <c r="L375" s="2" t="n">
+        <v>0.002517306482064089</v>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -13239,6 +15495,12 @@
       <c r="J376" s="2" t="n">
         <v>0.002060641742714178</v>
       </c>
+      <c r="K376" s="1" t="n">
+        <v>0.003425</v>
+      </c>
+      <c r="L376" s="2" t="n">
+        <v>0.006169212690951876</v>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -13273,6 +15535,12 @@
       <c r="J377" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="K377" s="1" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="L377" s="2" t="n">
+        <v>0.00628930817610059</v>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -13307,6 +15575,12 @@
       <c r="J378" s="2" t="n">
         <v>0.001795332136445169</v>
       </c>
+      <c r="K378" s="1" t="n">
+        <v>0.01117</v>
+      </c>
+      <c r="L378" s="2" t="n">
+        <v>0.0008960573476702144</v>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -13341,6 +15615,12 @@
       <c r="J379" s="3" t="n">
         <v>-0.01050228310502288</v>
       </c>
+      <c r="K379" s="1" t="n">
+        <v>0.02176</v>
+      </c>
+      <c r="L379" s="2" t="n">
+        <v>0.00415320719889263</v>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -13375,6 +15655,12 @@
       <c r="J380" s="2" t="n">
         <v>0.002135611318739902</v>
       </c>
+      <c r="K380" s="1" t="n">
+        <v>0.0188</v>
+      </c>
+      <c r="L380" s="2" t="n">
+        <v>0.001598295151838159</v>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -13409,6 +15695,12 @@
       <c r="J381" s="2" t="n">
         <v>0.0008340283569640449</v>
       </c>
+      <c r="K381" s="1" t="n">
+        <v>0.1198</v>
+      </c>
+      <c r="L381" s="3" t="n">
+        <v>-0.001666666666666599</v>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -13443,6 +15735,12 @@
       <c r="J382" s="3" t="n">
         <v>-0.003098106712564537</v>
       </c>
+      <c r="K382" s="1" t="n">
+        <v>0.02905</v>
+      </c>
+      <c r="L382" s="2" t="n">
+        <v>0.003107734806629828</v>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -13477,6 +15775,12 @@
       <c r="J383" s="3" t="n">
         <v>-0.001834862385321079</v>
       </c>
+      <c r="K383" s="1" t="n">
+        <v>0.006537</v>
+      </c>
+      <c r="L383" s="2" t="n">
+        <v>0.001378676470588285</v>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -13511,6 +15815,12 @@
       <c r="J384" s="2" t="n">
         <v>0.0004784688995216776</v>
       </c>
+      <c r="K384" s="1" t="n">
+        <v>0.02076</v>
+      </c>
+      <c r="L384" s="3" t="n">
+        <v>-0.007173601147776223</v>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -13545,6 +15855,12 @@
       <c r="J385" s="2" t="n">
         <v>0.0007936507936507937</v>
       </c>
+      <c r="K385" s="1" t="n">
+        <v>2529</v>
+      </c>
+      <c r="L385" s="2" t="n">
+        <v>0.002775574940523394</v>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -13579,6 +15895,12 @@
       <c r="J386" s="3" t="n">
         <v>-0.004028197381671678</v>
       </c>
+      <c r="K386" s="1" t="n">
+        <v>0.1974</v>
+      </c>
+      <c r="L386" s="3" t="n">
+        <v>-0.002022244691607742</v>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -13613,6 +15935,12 @@
       <c r="J387" s="3" t="n">
         <v>-0.00305164319248822</v>
       </c>
+      <c r="K387" s="1" t="n">
+        <v>0.08518000000000001</v>
+      </c>
+      <c r="L387" s="2" t="n">
+        <v>0.002825523899223029</v>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -13647,6 +15975,12 @@
       <c r="J388" s="3" t="n">
         <v>-0.002189926338841275</v>
       </c>
+      <c r="K388" s="1" t="n">
+        <v>0.005023</v>
+      </c>
+      <c r="L388" s="2" t="n">
+        <v>0.002194732641659961</v>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -13681,6 +16015,12 @@
       <c r="J389" s="2" t="n">
         <v>0.00407608695652173</v>
       </c>
+      <c r="K389" s="1" t="n">
+        <v>0.02242</v>
+      </c>
+      <c r="L389" s="2" t="n">
+        <v>0.01127649977447001</v>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -13715,6 +16055,12 @@
       <c r="J390" s="2" t="n">
         <v>0.009312462849217211</v>
       </c>
+      <c r="K390" s="1" t="n">
+        <v>0.5083</v>
+      </c>
+      <c r="L390" s="3" t="n">
+        <v>-0.002159403219473871</v>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -13749,6 +16095,12 @@
       <c r="J391" s="2" t="n">
         <v>0.0001671122994651541</v>
       </c>
+      <c r="K391" s="1" t="n">
+        <v>0.0005997</v>
+      </c>
+      <c r="L391" s="2" t="n">
+        <v>0.00200501253132837</v>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -13783,6 +16135,12 @@
       <c r="J392" s="3" t="n">
         <v>-0.001026694045174496</v>
       </c>
+      <c r="K392" s="1" t="n">
+        <v>0.05846</v>
+      </c>
+      <c r="L392" s="2" t="n">
+        <v>0.001370332305584048</v>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -13817,6 +16175,12 @@
       <c r="J393" s="3" t="n">
         <v>-0.001497005988023995</v>
       </c>
+      <c r="K393" s="1" t="n">
+        <v>0.2669</v>
+      </c>
+      <c r="L393" s="2" t="n">
+        <v>0.0003748125937033152</v>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -13851,6 +16215,12 @@
       <c r="J394" s="2" t="n">
         <v>0.0004578055852282006</v>
       </c>
+      <c r="K394" s="1" t="n">
+        <v>0.006519</v>
+      </c>
+      <c r="L394" s="3" t="n">
+        <v>-0.005643685173886604</v>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -13885,6 +16255,12 @@
       <c r="J395" s="3" t="n">
         <v>-0.0008680555555555804</v>
       </c>
+      <c r="K395" s="1" t="n">
+        <v>0.1152</v>
+      </c>
+      <c r="L395" s="2" t="n">
+        <v>0.0008688097306690084</v>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -13919,6 +16295,12 @@
       <c r="J396" s="3" t="n">
         <v>-0.001618122977346325</v>
       </c>
+      <c r="K396" s="1" t="n">
+        <v>0.03081</v>
+      </c>
+      <c r="L396" s="3" t="n">
+        <v>-0.001296596434359753</v>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -13953,6 +16335,12 @@
       <c r="J397" s="3" t="n">
         <v>-0.003957783641161063</v>
       </c>
+      <c r="K397" s="1" t="n">
+        <v>0.1508</v>
+      </c>
+      <c r="L397" s="3" t="n">
+        <v>-0.001324503311258316</v>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -13987,6 +16375,12 @@
       <c r="J398" s="3" t="n">
         <v>-0.0006055101422948326</v>
       </c>
+      <c r="K398" s="1" t="n">
+        <v>0.003302</v>
+      </c>
+      <c r="L398" s="2" t="n">
+        <v>0.0003029385034837016</v>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -14021,6 +16415,12 @@
       <c r="J399" s="3" t="n">
         <v>-0.001601708489054927</v>
       </c>
+      <c r="K399" s="1" t="n">
+        <v>0.01873</v>
+      </c>
+      <c r="L399" s="2" t="n">
+        <v>0.001604278074866245</v>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -14055,6 +16455,12 @@
       <c r="J400" s="3" t="n">
         <v>-0.01037140854940439</v>
       </c>
+      <c r="K400" s="1" t="n">
+        <v>0.007035</v>
+      </c>
+      <c r="L400" s="3" t="n">
+        <v>-0.003682197988953403</v>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -14089,6 +16495,12 @@
       <c r="J401" s="3" t="n">
         <v>-0.003011616234045631</v>
       </c>
+      <c r="K401" s="1" t="n">
+        <v>0.006937</v>
+      </c>
+      <c r="L401" s="3" t="n">
+        <v>-0.002157652474108207</v>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -14123,6 +16535,12 @@
       <c r="J402" s="3" t="n">
         <v>-0.002738702850740626</v>
       </c>
+      <c r="K402" s="1" t="n">
+        <v>0.007993</v>
+      </c>
+      <c r="L402" s="3" t="n">
+        <v>-0.002246910498065242</v>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -14157,6 +16575,12 @@
       <c r="J403" s="3" t="n">
         <v>-0.001219016659894302</v>
       </c>
+      <c r="K403" s="1" t="n">
+        <v>0.04912</v>
+      </c>
+      <c r="L403" s="3" t="n">
+        <v>-0.0008136696501221584</v>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -14191,6 +16615,12 @@
       <c r="J404" s="2" t="n">
         <v>0.0120120120120119</v>
       </c>
+      <c r="K404" s="1" t="n">
+        <v>0.14983</v>
+      </c>
+      <c r="L404" s="2" t="n">
+        <v>0.01045319665497704</v>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -14225,6 +16655,12 @@
       <c r="J405" s="3" t="n">
         <v>-0.00140482322641062</v>
       </c>
+      <c r="K405" s="1" t="n">
+        <v>0.04255</v>
+      </c>
+      <c r="L405" s="3" t="n">
+        <v>-0.002344665885111439</v>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -14259,6 +16695,12 @@
       <c r="J406" s="3" t="n">
         <v>-0.0002088554720133438</v>
       </c>
+      <c r="K406" s="1" t="n">
+        <v>0.4785</v>
+      </c>
+      <c r="L406" s="3" t="n">
+        <v>-0.000417798203467795</v>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -14293,6 +16735,12 @@
       <c r="J407" s="3" t="n">
         <v>-0.003284746458632804</v>
       </c>
+      <c r="K407" s="1" t="n">
+        <v>0.0004871</v>
+      </c>
+      <c r="L407" s="2" t="n">
+        <v>0.00329557157569524</v>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -14327,6 +16775,12 @@
       <c r="J408" s="2" t="n">
         <v>0.009836065573770375</v>
       </c>
+      <c r="K408" s="1" t="n">
+        <v>0.01233</v>
+      </c>
+      <c r="L408" s="2" t="n">
+        <v>0.0008116883116884195</v>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -14361,6 +16815,12 @@
       <c r="J409" s="3" t="n">
         <v>-0.001883239171374732</v>
       </c>
+      <c r="K409" s="1" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="L409" s="2" t="n">
+        <v>0.006289308176100634</v>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -14395,6 +16855,12 @@
       <c r="J410" s="2" t="n">
         <v>0.001444738743077402</v>
       </c>
+      <c r="K410" s="1" t="n">
+        <v>0.04167</v>
+      </c>
+      <c r="L410" s="2" t="n">
+        <v>0.001923539312334617</v>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -14429,6 +16895,12 @@
       <c r="J411" s="2" t="n">
         <v>0.0003356831151392948</v>
       </c>
+      <c r="K411" s="1" t="n">
+        <v>0.02975</v>
+      </c>
+      <c r="L411" s="3" t="n">
+        <v>-0.001677852348993337</v>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
@@ -14463,6 +16935,12 @@
       <c r="J412" s="3" t="n">
         <v>-0.0004375410194706334</v>
       </c>
+      <c r="K412" s="1" t="n">
+        <v>0.004582</v>
+      </c>
+      <c r="L412" s="2" t="n">
+        <v>0.002845261545195883</v>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -14497,6 +16975,12 @@
       <c r="J413" s="3" t="n">
         <v>-0.0003960396039603524</v>
       </c>
+      <c r="K413" s="1" t="n">
+        <v>0.2516</v>
+      </c>
+      <c r="L413" s="3" t="n">
+        <v>-0.003169572107765542</v>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -14531,6 +17015,12 @@
       <c r="J414" s="2" t="n">
         <v>0.007064364207221269</v>
       </c>
+      <c r="K414" s="1" t="n">
+        <v>1.281</v>
+      </c>
+      <c r="L414" s="3" t="n">
+        <v>-0.00155884645362432</v>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -14565,6 +17055,12 @@
       <c r="J415" s="2" t="n">
         <v>0.001478196600147821</v>
       </c>
+      <c r="K415" s="1" t="n">
+        <v>2.717</v>
+      </c>
+      <c r="L415" s="2" t="n">
+        <v>0.002583025830258346</v>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -14599,6 +17095,12 @@
       <c r="J416" s="2" t="n">
         <v>0.0009322560596644576</v>
       </c>
+      <c r="K416" s="1" t="n">
+        <v>0.03219</v>
+      </c>
+      <c r="L416" s="3" t="n">
+        <v>-0.0006209251785159634</v>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -14633,6 +17135,12 @@
       <c r="J417" s="2" t="n">
         <v>0.000250312891113969</v>
       </c>
+      <c r="K417" s="1" t="n">
+        <v>0.04013</v>
+      </c>
+      <c r="L417" s="2" t="n">
+        <v>0.004254254254254167</v>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -14667,6 +17175,12 @@
       <c r="J418" s="3" t="n">
         <v>-0.003152088258471291</v>
       </c>
+      <c r="K418" s="1" t="n">
+        <v>0.07599</v>
+      </c>
+      <c r="L418" s="2" t="n">
+        <v>0.001185770750988231</v>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -14701,6 +17215,12 @@
       <c r="J419" s="2" t="n">
         <v>0.001506024096385481</v>
       </c>
+      <c r="K419" s="1" t="n">
+        <v>0.00666</v>
+      </c>
+      <c r="L419" s="2" t="n">
+        <v>0.00150375939849631</v>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -14735,6 +17255,12 @@
       <c r="J420" s="3" t="n">
         <v>-0.004499437570303841</v>
       </c>
+      <c r="K420" s="1" t="n">
+        <v>0.0886</v>
+      </c>
+      <c r="L420" s="2" t="n">
+        <v>0.001129943502824891</v>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -14769,6 +17295,12 @@
       <c r="J421" s="2" t="n">
         <v>0.002479338842975278</v>
       </c>
+      <c r="K421" s="1" t="n">
+        <v>0.2435</v>
+      </c>
+      <c r="L421" s="2" t="n">
+        <v>0.00370981038746902</v>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
@@ -14803,6 +17335,12 @@
       <c r="J422" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="K422" s="1" t="n">
+        <v>0.0194</v>
+      </c>
+      <c r="L422" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -14837,6 +17375,12 @@
       <c r="J423" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="K423" s="1" t="n">
+        <v>0.1507</v>
+      </c>
+      <c r="L423" s="2" t="n">
+        <v>0.001328903654485088</v>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -14871,6 +17415,12 @@
       <c r="J424" s="3" t="n">
         <v>-0.001429933269780778</v>
       </c>
+      <c r="K424" s="1" t="n">
+        <v>0.0002087</v>
+      </c>
+      <c r="L424" s="3" t="n">
+        <v>-0.00381861575178994</v>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -14905,6 +17455,12 @@
       <c r="J425" s="3" t="n">
         <v>-0.001615508885298871</v>
       </c>
+      <c r="K425" s="1" t="n">
+        <v>1.237</v>
+      </c>
+      <c r="L425" s="2" t="n">
+        <v>0.0008090614886732297</v>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
@@ -14939,6 +17495,12 @@
       <c r="J426" s="3" t="n">
         <v>-0.001418439716312058</v>
       </c>
+      <c r="K426" s="1" t="n">
+        <v>1.409</v>
+      </c>
+      <c r="L426" s="2" t="n">
+        <v>0.0007102272727273522</v>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -14973,6 +17535,12 @@
       <c r="J427" s="3" t="n">
         <v>-0.001543209876543147</v>
       </c>
+      <c r="K427" s="1" t="n">
+        <v>0.01943</v>
+      </c>
+      <c r="L427" s="2" t="n">
+        <v>0.001030396702730509</v>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
@@ -15007,6 +17575,12 @@
       <c r="J428" s="3" t="n">
         <v>-0.001517220452131738</v>
       </c>
+      <c r="K428" s="1" t="n">
+        <v>0.06583</v>
+      </c>
+      <c r="L428" s="2" t="n">
+        <v>0.0003039051815834391</v>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
@@ -15041,6 +17615,12 @@
       <c r="J429" s="2" t="n">
         <v>0.0007541478129714686</v>
       </c>
+      <c r="K429" s="1" t="n">
+        <v>0.1327</v>
+      </c>
+      <c r="L429" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
@@ -15075,6 +17655,12 @@
       <c r="J430" s="2" t="n">
         <v>0.0007200720072006595</v>
       </c>
+      <c r="K430" s="1" t="n">
+        <v>0.011121</v>
+      </c>
+      <c r="L430" s="2" t="n">
+        <v>0.0002698327037238052</v>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -15109,6 +17695,12 @@
       <c r="J431" s="2" t="n">
         <v>0.0002995357196346062</v>
       </c>
+      <c r="K431" s="1" t="n">
+        <v>0.006672</v>
+      </c>
+      <c r="L431" s="3" t="n">
+        <v>-0.001048061086989079</v>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
@@ -15143,6 +17735,12 @@
       <c r="J432" s="2" t="n">
         <v>0.001138952164009139</v>
       </c>
+      <c r="K432" s="1" t="n">
+        <v>0.001759</v>
+      </c>
+      <c r="L432" s="2" t="n">
+        <v>0.0005688282138793606</v>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
@@ -15177,6 +17775,12 @@
       <c r="J433" s="2" t="n">
         <v>0.0007293946024798803</v>
       </c>
+      <c r="K433" s="1" t="n">
+        <v>0.001369</v>
+      </c>
+      <c r="L433" s="3" t="n">
+        <v>-0.002186588921282773</v>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
@@ -15211,6 +17815,12 @@
       <c r="J434" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="K434" s="1" t="n">
+        <v>0.000409</v>
+      </c>
+      <c r="L434" s="2" t="n">
+        <v>0.002450980392156922</v>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
@@ -15245,6 +17855,12 @@
       <c r="J435" s="3" t="n">
         <v>-0.001183151916706194</v>
       </c>
+      <c r="K435" s="1" t="n">
+        <v>0.12632</v>
+      </c>
+      <c r="L435" s="3" t="n">
+        <v>-0.002448077074942784</v>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -15279,6 +17895,12 @@
       <c r="J436" s="3" t="n">
         <v>-0.0006454111268877565</v>
       </c>
+      <c r="K436" s="1" t="n">
+        <v>0.07782</v>
+      </c>
+      <c r="L436" s="2" t="n">
+        <v>0.005166623611469873</v>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
@@ -15313,6 +17935,12 @@
       <c r="J437" s="3" t="n">
         <v>-0.004697776385843865</v>
       </c>
+      <c r="K437" s="1" t="n">
+        <v>0.6337</v>
+      </c>
+      <c r="L437" s="3" t="n">
+        <v>-0.002989301447451247</v>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -15347,6 +17975,12 @@
       <c r="J438" s="2" t="n">
         <v>0.001611047180667448</v>
       </c>
+      <c r="K438" s="1" t="n">
+        <v>0.04345</v>
+      </c>
+      <c r="L438" s="3" t="n">
+        <v>-0.001608455882352955</v>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
@@ -15381,6 +18015,12 @@
       <c r="J439" s="3" t="n">
         <v>-0.001279135872655013</v>
       </c>
+      <c r="K439" s="1" t="n">
+        <v>0.07041</v>
+      </c>
+      <c r="L439" s="2" t="n">
+        <v>0.001992315355059076</v>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
@@ -15415,6 +18055,12 @@
       <c r="J440" s="3" t="n">
         <v>-0.001317523056653523</v>
       </c>
+      <c r="K440" s="1" t="n">
+        <v>0.001517</v>
+      </c>
+      <c r="L440" s="2" t="n">
+        <v>0.0006596306068601029</v>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -15449,6 +18095,12 @@
       <c r="J441" s="3" t="n">
         <v>-0.0005261496369567291</v>
       </c>
+      <c r="K441" s="1" t="n">
+        <v>0.009488</v>
+      </c>
+      <c r="L441" s="3" t="n">
+        <v>-0.00105285323225938</v>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
@@ -15483,6 +18135,12 @@
       <c r="J442" s="3" t="n">
         <v>-0.005649717514124298</v>
       </c>
+      <c r="K442" s="1" t="n">
+        <v>1.061</v>
+      </c>
+      <c r="L442" s="2" t="n">
+        <v>0.004734848484848383</v>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
@@ -15517,6 +18175,12 @@
       <c r="J443" s="3" t="n">
         <v>-0.0009074410163339013</v>
       </c>
+      <c r="K443" s="1" t="n">
+        <v>0.02202</v>
+      </c>
+      <c r="L443" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
@@ -15551,6 +18215,12 @@
       <c r="J444" s="3" t="n">
         <v>-0.008905185961236324</v>
       </c>
+      <c r="K444" s="1" t="n">
+        <v>0.0003818</v>
+      </c>
+      <c r="L444" s="2" t="n">
+        <v>0.008985200845666038</v>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
@@ -15585,6 +18255,12 @@
       <c r="J445" s="3" t="n">
         <v>-0.0002839295854628921</v>
       </c>
+      <c r="K445" s="1" t="n">
+        <v>0.03555</v>
+      </c>
+      <c r="L445" s="2" t="n">
+        <v>0.009656347628514628</v>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
@@ -15619,6 +18295,12 @@
       <c r="J446" s="3" t="n">
         <v>-0.0004687133817670304</v>
       </c>
+      <c r="K446" s="1" t="n">
+        <v>0.08587</v>
+      </c>
+      <c r="L446" s="2" t="n">
+        <v>0.006682297772567422</v>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
@@ -15653,6 +18335,12 @@
       <c r="J447" s="2" t="n">
         <v>0.0006155740227761711</v>
       </c>
+      <c r="K447" s="1" t="n">
+        <v>3.261</v>
+      </c>
+      <c r="L447" s="2" t="n">
+        <v>0.00307597662257774</v>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
@@ -15687,6 +18375,12 @@
       <c r="J448" s="3" t="n">
         <v>-0.002498438475952428</v>
       </c>
+      <c r="K448" s="1" t="n">
+        <v>0.06405</v>
+      </c>
+      <c r="L448" s="2" t="n">
+        <v>0.002661239824671095</v>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
@@ -15721,6 +18415,12 @@
       <c r="J449" s="3" t="n">
         <v>-0.001235330450895707</v>
       </c>
+      <c r="K449" s="1" t="n">
+        <v>0.4849</v>
+      </c>
+      <c r="L449" s="3" t="n">
+        <v>-0.0004122861265717955</v>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
@@ -15755,6 +18455,12 @@
       <c r="J450" s="3" t="n">
         <v>-0.007751937984496087</v>
       </c>
+      <c r="K450" s="1" t="n">
+        <v>0.03732</v>
+      </c>
+      <c r="L450" s="2" t="n">
+        <v>0.005387931034482726</v>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -15789,6 +18495,12 @@
       <c r="J451" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="K451" s="1" t="n">
+        <v>0.00546</v>
+      </c>
+      <c r="L451" s="2" t="n">
+        <v>0.001834862385321026</v>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
@@ -15823,6 +18535,12 @@
       <c r="J452" s="3" t="n">
         <v>-0.008811824900511658</v>
       </c>
+      <c r="K452" s="1" t="n">
+        <v>0.10469</v>
+      </c>
+      <c r="L452" s="2" t="n">
+        <v>0.0007647452442406139</v>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
@@ -15857,6 +18575,12 @@
       <c r="J453" s="3" t="n">
         <v>-0.002496878901373182</v>
       </c>
+      <c r="K453" s="1" t="n">
+        <v>0.01602</v>
+      </c>
+      <c r="L453" s="2" t="n">
+        <v>0.002503128911138821</v>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
@@ -15891,6 +18615,12 @@
       <c r="J454" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="K454" s="1" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="L454" s="2" t="n">
+        <v>0.01111883252258514</v>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
@@ -15925,6 +18655,12 @@
       <c r="J455" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="K455" s="1" t="n">
+        <v>0.895</v>
+      </c>
+      <c r="L455" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
@@ -15959,6 +18695,12 @@
       <c r="J456" s="3" t="n">
         <v>-0.0006793478260868817</v>
       </c>
+      <c r="K456" s="1" t="n">
+        <v>2.943</v>
+      </c>
+      <c r="L456" s="2" t="n">
+        <v>0.0003399048266485009</v>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -15993,6 +18735,12 @@
       <c r="J457" s="2" t="n">
         <v>0.002028397565922838</v>
       </c>
+      <c r="K457" s="1" t="n">
+        <v>0.009860000000000001</v>
+      </c>
+      <c r="L457" s="3" t="n">
+        <v>-0.002024291497975626</v>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
@@ -16027,6 +18775,12 @@
       <c r="J458" s="2" t="n">
         <v>0.0008029548739361078</v>
       </c>
+      <c r="K458" s="1" t="n">
+        <v>0.06205</v>
+      </c>
+      <c r="L458" s="3" t="n">
+        <v>-0.004332477535301659</v>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
@@ -16061,6 +18815,12 @@
       <c r="J459" s="3" t="n">
         <v>-0.009735744089012602</v>
       </c>
+      <c r="K459" s="1" t="n">
+        <v>0.01429</v>
+      </c>
+      <c r="L459" s="2" t="n">
+        <v>0.003511235955056281</v>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
@@ -16095,6 +18855,12 @@
       <c r="J460" s="3" t="n">
         <v>-0.001438488961160718</v>
       </c>
+      <c r="K460" s="1" t="n">
+        <v>0.015996</v>
+      </c>
+      <c r="L460" s="2" t="n">
+        <v>0.001878992859827056</v>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
@@ -16129,6 +18895,12 @@
       <c r="J461" s="2" t="n">
         <v>0.003019323671497671</v>
       </c>
+      <c r="K461" s="1" t="n">
+        <v>0.0167</v>
+      </c>
+      <c r="L461" s="2" t="n">
+        <v>0.005418422636965671</v>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
@@ -16163,6 +18935,12 @@
       <c r="J462" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="K462" s="1" t="n">
+        <v>0.0002096</v>
+      </c>
+      <c r="L462" s="2" t="n">
+        <v>0.001433349259436251</v>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
@@ -16197,6 +18975,12 @@
       <c r="J463" s="2" t="n">
         <v>0.002028397565922979</v>
       </c>
+      <c r="K463" s="1" t="n">
+        <v>0.09959999999999999</v>
+      </c>
+      <c r="L463" s="2" t="n">
+        <v>0.008097165991902786</v>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
@@ -16231,6 +19015,12 @@
       <c r="J464" s="3" t="n">
         <v>-0.0003827018752391731</v>
       </c>
+      <c r="K464" s="1" t="n">
+        <v>0.02623</v>
+      </c>
+      <c r="L464" s="2" t="n">
+        <v>0.004211332312404249</v>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
@@ -16265,6 +19055,12 @@
       <c r="J465" s="2" t="n">
         <v>0.0006613756613756345</v>
       </c>
+      <c r="K465" s="1" t="n">
+        <v>0.01521</v>
+      </c>
+      <c r="L465" s="2" t="n">
+        <v>0.005287508261731673</v>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
@@ -16299,6 +19095,12 @@
       <c r="J466" s="2" t="n">
         <v>0.0005484460694698765</v>
       </c>
+      <c r="K466" s="1" t="n">
+        <v>0.05469</v>
+      </c>
+      <c r="L466" s="3" t="n">
+        <v>-0.0007308605883427438</v>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
@@ -16333,6 +19135,12 @@
       <c r="J467" s="3" t="n">
         <v>-0.002328288707799874</v>
       </c>
+      <c r="K467" s="1" t="n">
+        <v>0.03446</v>
+      </c>
+      <c r="L467" s="2" t="n">
+        <v>0.005250875145857632</v>
+      </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
@@ -16367,6 +19175,12 @@
       <c r="J468" s="3" t="n">
         <v>-0.005788712011577429</v>
       </c>
+      <c r="K468" s="1" t="n">
+        <v>27.58</v>
+      </c>
+      <c r="L468" s="2" t="n">
+        <v>0.003639010189228452</v>
+      </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
@@ -16401,6 +19215,12 @@
       <c r="J469" s="3" t="n">
         <v>-0.001472359791192575</v>
       </c>
+      <c r="K469" s="1" t="n">
+        <v>0.0007486</v>
+      </c>
+      <c r="L469" s="2" t="n">
+        <v>0.003485254691688947</v>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
@@ -16435,6 +19255,12 @@
       <c r="J470" s="3" t="n">
         <v>-0.004555808656036451</v>
       </c>
+      <c r="K470" s="1" t="n">
+        <v>0.872</v>
+      </c>
+      <c r="L470" s="3" t="n">
+        <v>-0.002288329519450803</v>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
@@ -16469,6 +19295,12 @@
       <c r="J471" s="3" t="n">
         <v>-0.003036437246963615</v>
       </c>
+      <c r="K471" s="1" t="n">
+        <v>0.009900000000000001</v>
+      </c>
+      <c r="L471" s="2" t="n">
+        <v>0.005076142131979841</v>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
@@ -16503,6 +19335,12 @@
       <c r="J472" s="3" t="n">
         <v>-0.001072961373390589</v>
       </c>
+      <c r="K472" s="1" t="n">
+        <v>0.04662</v>
+      </c>
+      <c r="L472" s="2" t="n">
+        <v>0.001503759398496254</v>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -16537,6 +19375,12 @@
       <c r="J473" s="3" t="n">
         <v>-0.0007317965605560848</v>
       </c>
+      <c r="K473" s="1" t="n">
+        <v>0.2735</v>
+      </c>
+      <c r="L473" s="2" t="n">
+        <v>0.001464664957890924</v>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
@@ -16571,6 +19415,12 @@
       <c r="J474" s="2" t="n">
         <v>0.002063746847053423</v>
       </c>
+      <c r="K474" s="1" t="n">
+        <v>0.04371</v>
+      </c>
+      <c r="L474" s="2" t="n">
+        <v>0.0002288329519449914</v>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
@@ -16605,6 +19455,12 @@
       <c r="J475" s="2" t="n">
         <v>0.0009471939379587174</v>
       </c>
+      <c r="K475" s="1" t="n">
+        <v>0.008472</v>
+      </c>
+      <c r="L475" s="2" t="n">
+        <v>0.002129169623846777</v>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
@@ -16639,6 +19495,12 @@
       <c r="J476" s="3" t="n">
         <v>-0.002082312591866775</v>
       </c>
+      <c r="K476" s="1" t="n">
+        <v>0.08155</v>
+      </c>
+      <c r="L476" s="2" t="n">
+        <v>0.0009819565484226922</v>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
@@ -16673,6 +19535,12 @@
       <c r="J477" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="K477" s="1" t="n">
+        <v>0.1364</v>
+      </c>
+      <c r="L477" s="2" t="n">
+        <v>0.004418262150220835</v>
+      </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
@@ -16707,6 +19575,12 @@
       <c r="J478" s="2" t="n">
         <v>0.0002518257365902518</v>
       </c>
+      <c r="K478" s="1" t="n">
+        <v>0.3978</v>
+      </c>
+      <c r="L478" s="2" t="n">
+        <v>0.001510574018126862</v>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
@@ -16741,6 +19615,12 @@
       <c r="J479" s="2" t="n">
         <v>0.002139037433154951</v>
       </c>
+      <c r="K479" s="1" t="n">
+        <v>0.008436000000000001</v>
+      </c>
+      <c r="L479" s="2" t="n">
+        <v>0.0003557452863751056</v>
+      </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
@@ -16775,6 +19655,12 @@
       <c r="J480" s="3" t="n">
         <v>-0.001880877742946632</v>
       </c>
+      <c r="K480" s="1" t="n">
+        <v>0.0159</v>
+      </c>
+      <c r="L480" s="3" t="n">
+        <v>-0.001256281407035125</v>
+      </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
@@ -16809,6 +19695,12 @@
       <c r="J481" s="2" t="n">
         <v>0.002075496173303846</v>
       </c>
+      <c r="K481" s="1" t="n">
+        <v>0.07728</v>
+      </c>
+      <c r="L481" s="2" t="n">
+        <v>0.0003883495145631359</v>
+      </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
@@ -16843,6 +19735,12 @@
       <c r="J482" s="3" t="n">
         <v>-0.0003951788184153168</v>
       </c>
+      <c r="K482" s="1" t="n">
+        <v>0.05049</v>
+      </c>
+      <c r="L482" s="3" t="n">
+        <v>-0.001976675232259396</v>
+      </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
@@ -16877,6 +19775,12 @@
       <c r="J483" s="2" t="n">
         <v>0.001030927835051504</v>
       </c>
+      <c r="K483" s="1" t="n">
+        <v>0.0097</v>
+      </c>
+      <c r="L483" s="3" t="n">
+        <v>-0.001029866117404695</v>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
@@ -16911,6 +19815,12 @@
       <c r="J484" s="3" t="n">
         <v>-0.0008819638394824433</v>
       </c>
+      <c r="K484" s="1" t="n">
+        <v>0.06798</v>
+      </c>
+      <c r="L484" s="2" t="n">
+        <v>0.0001471237310577626</v>
+      </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
@@ -16945,6 +19855,12 @@
       <c r="J485" s="3" t="n">
         <v>-0.0006681514476614862</v>
       </c>
+      <c r="K485" s="1" t="n">
+        <v>0.0004494</v>
+      </c>
+      <c r="L485" s="2" t="n">
+        <v>0.001560062402496017</v>
+      </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
@@ -16979,6 +19895,12 @@
       <c r="J486" s="3" t="n">
         <v>-0.002639185622722155</v>
       </c>
+      <c r="K486" s="1" t="n">
+        <v>0.07933999999999999</v>
+      </c>
+      <c r="L486" s="3" t="n">
+        <v>-0.0002520161290323353</v>
+      </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
@@ -17013,6 +19935,12 @@
       <c r="J487" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="K487" s="1" t="n">
+        <v>0.000173</v>
+      </c>
+      <c r="L487" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
@@ -17047,6 +19975,12 @@
       <c r="J488" s="3" t="n">
         <v>-0.002851277372262776</v>
       </c>
+      <c r="K488" s="1" t="n">
+        <v>0.08759</v>
+      </c>
+      <c r="L488" s="2" t="n">
+        <v>0.001830035456937062</v>
+      </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
@@ -17081,6 +20015,12 @@
       <c r="J489" s="3" t="n">
         <v>-0.002732814799243182</v>
       </c>
+      <c r="K489" s="1" t="n">
+        <v>0.0475</v>
+      </c>
+      <c r="L489" s="2" t="n">
+        <v>0.001264755480607031</v>
+      </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
@@ -17115,6 +20055,12 @@
       <c r="J490" s="2" t="n">
         <v>0.003390714658320245</v>
       </c>
+      <c r="K490" s="1" t="n">
+        <v>0.03803</v>
+      </c>
+      <c r="L490" s="3" t="n">
+        <v>-0.01143748375357411</v>
+      </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
@@ -17149,6 +20095,12 @@
       <c r="J491" s="3" t="n">
         <v>-0.002693343593689904</v>
       </c>
+      <c r="K491" s="1" t="n">
+        <v>0.07775</v>
+      </c>
+      <c r="L491" s="3" t="n">
+        <v>-0.0001286008230452176</v>
+      </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
@@ -17183,6 +20135,12 @@
       <c r="J492" s="3" t="n">
         <v>-0.0006286342920008211</v>
       </c>
+      <c r="K492" s="1" t="n">
+        <v>0.06301</v>
+      </c>
+      <c r="L492" s="3" t="n">
+        <v>-0.009120930963988005</v>
+      </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
@@ -17217,6 +20175,12 @@
       <c r="J493" s="2" t="n">
         <v>0.003838771593090221</v>
       </c>
+      <c r="K493" s="1" t="n">
+        <v>0.00524</v>
+      </c>
+      <c r="L493" s="2" t="n">
+        <v>0.001912045889101261</v>
+      </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
@@ -17251,6 +20215,12 @@
       <c r="J494" s="3" t="n">
         <v>-0.0007235890014470984</v>
       </c>
+      <c r="K494" s="1" t="n">
+        <v>0.2764</v>
+      </c>
+      <c r="L494" s="2" t="n">
+        <v>0.0007241129616219333</v>
+      </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
@@ -17285,6 +20255,12 @@
       <c r="J495" s="3" t="n">
         <v>-0.001256478718391874</v>
       </c>
+      <c r="K495" s="1" t="n">
+        <v>0.06371</v>
+      </c>
+      <c r="L495" s="2" t="n">
+        <v>0.001887089164963186</v>
+      </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
@@ -17319,6 +20295,12 @@
       <c r="J496" s="3" t="n">
         <v>-0.00238500851788749</v>
       </c>
+      <c r="K496" s="1" t="n">
+        <v>0.2931</v>
+      </c>
+      <c r="L496" s="2" t="n">
+        <v>0.001024590163934503</v>
+      </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
@@ -17353,6 +20335,12 @@
       <c r="J497" s="3" t="n">
         <v>-0.005702699277657992</v>
       </c>
+      <c r="K497" s="1" t="n">
+        <v>0.07867</v>
+      </c>
+      <c r="L497" s="2" t="n">
+        <v>0.002676523069079809</v>
+      </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
@@ -17387,6 +20375,12 @@
       <c r="J498" s="3" t="n">
         <v>-0.0009689922480620432</v>
       </c>
+      <c r="K498" s="1" t="n">
+        <v>0.1032</v>
+      </c>
+      <c r="L498" s="2" t="n">
+        <v>0.0009699321047526951</v>
+      </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
@@ -17421,6 +20415,12 @@
       <c r="J499" s="3" t="n">
         <v>-0.001443695861405138</v>
       </c>
+      <c r="K499" s="1" t="n">
+        <v>0.04175</v>
+      </c>
+      <c r="L499" s="2" t="n">
+        <v>0.006024096385542173</v>
+      </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
@@ -17455,6 +20455,12 @@
       <c r="J500" s="3" t="n">
         <v>-0.001215066828675612</v>
       </c>
+      <c r="K500" s="1" t="n">
+        <v>0.04107</v>
+      </c>
+      <c r="L500" s="3" t="n">
+        <v>-0.000729927007299156</v>
+      </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
@@ -17489,6 +20495,12 @@
       <c r="J501" s="3" t="n">
         <v>-0.001003009027081273</v>
       </c>
+      <c r="K501" s="1" t="n">
+        <v>0.0994</v>
+      </c>
+      <c r="L501" s="3" t="n">
+        <v>-0.002008032128513975</v>
+      </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
@@ -17523,6 +20535,12 @@
       <c r="J502" s="2" t="n">
         <v>0.0003024803387780196</v>
       </c>
+      <c r="K502" s="1" t="n">
+        <v>0.003305</v>
+      </c>
+      <c r="L502" s="3" t="n">
+        <v>-0.0006047777441789634</v>
+      </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
@@ -17557,6 +20575,12 @@
       <c r="J503" s="2" t="n">
         <v>0.008771929824561427</v>
       </c>
+      <c r="K503" s="1" t="n">
+        <v>0.00932</v>
+      </c>
+      <c r="L503" s="2" t="n">
+        <v>0.0130434782608696</v>
+      </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
@@ -17591,6 +20615,12 @@
       <c r="J504" s="3" t="n">
         <v>-0.004419191919191958</v>
       </c>
+      <c r="K504" s="1" t="n">
+        <v>0.1592</v>
+      </c>
+      <c r="L504" s="2" t="n">
+        <v>0.009511731135066591</v>
+      </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
@@ -17625,6 +20655,12 @@
       <c r="J505" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="K505" s="1" t="n">
+        <v>0.1313</v>
+      </c>
+      <c r="L505" s="2" t="n">
+        <v>0.0007621951219511355</v>
+      </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
@@ -17659,6 +20695,12 @@
       <c r="J506" s="3" t="n">
         <v>-0.001185536455245951</v>
       </c>
+      <c r="K506" s="1" t="n">
+        <v>0.01697</v>
+      </c>
+      <c r="L506" s="2" t="n">
+        <v>0.007121661721068165</v>
+      </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
@@ -17693,6 +20735,12 @@
       <c r="J507" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="K507" s="1" t="n">
+        <v>0.00289</v>
+      </c>
+      <c r="L507" s="2" t="n">
+        <v>0.002080443828016769</v>
+      </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
@@ -17727,6 +20775,12 @@
       <c r="J508" s="3" t="n">
         <v>-0.003161698283649556</v>
       </c>
+      <c r="K508" s="1" t="n">
+        <v>2.212</v>
+      </c>
+      <c r="L508" s="2" t="n">
+        <v>0.002265518803806224</v>
+      </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
@@ -17761,6 +20815,12 @@
       <c r="J509" s="2" t="n">
         <v>0.0003637686431429462</v>
       </c>
+      <c r="K509" s="1" t="n">
+        <v>0.05504</v>
+      </c>
+      <c r="L509" s="2" t="n">
+        <v>0.0007272727272726976</v>
+      </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
@@ -17795,6 +20855,12 @@
       <c r="J510" s="3" t="n">
         <v>-0.002037351443123973</v>
       </c>
+      <c r="K510" s="1" t="n">
+        <v>0.0295</v>
+      </c>
+      <c r="L510" s="2" t="n">
+        <v>0.003742769649540626</v>
+      </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
@@ -17829,6 +20895,12 @@
       <c r="J511" s="3" t="n">
         <v>-0.001977750309023405</v>
       </c>
+      <c r="K511" s="1" t="n">
+        <v>0.04048</v>
+      </c>
+      <c r="L511" s="2" t="n">
+        <v>0.00272479564032695</v>
+      </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
@@ -17863,6 +20935,12 @@
       <c r="J512" s="2" t="n">
         <v>0.01176470588235279</v>
       </c>
+      <c r="K512" s="1" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="L512" s="2" t="n">
+        <v>0.0116279069767442</v>
+      </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
@@ -17897,6 +20975,12 @@
       <c r="J513" s="3" t="n">
         <v>-0.001887810140237341</v>
       </c>
+      <c r="K513" s="1" t="n">
+        <v>0.014863</v>
+      </c>
+      <c r="L513" s="2" t="n">
+        <v>0.003985409348824644</v>
+      </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
@@ -17931,6 +21015,12 @@
       <c r="J514" s="3" t="n">
         <v>-0.001723147616312434</v>
       </c>
+      <c r="K514" s="1" t="n">
+        <v>0.1745</v>
+      </c>
+      <c r="L514" s="2" t="n">
+        <v>0.00402761795166846</v>
+      </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
@@ -17965,6 +21055,12 @@
       <c r="J515" s="3" t="n">
         <v>-0.001860465116278994</v>
       </c>
+      <c r="K515" s="1" t="n">
+        <v>0.1076</v>
+      </c>
+      <c r="L515" s="2" t="n">
+        <v>0.002795899347623436</v>
+      </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
@@ -17999,6 +21095,12 @@
       <c r="J516" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="K516" s="1" t="n">
+        <v>0.00267</v>
+      </c>
+      <c r="L516" s="2" t="n">
+        <v>0.007547169811320775</v>
+      </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
@@ -18033,6 +21135,12 @@
       <c r="J517" s="3" t="n">
         <v>-0.004388229220443896</v>
       </c>
+      <c r="K517" s="1" t="n">
+        <v>0.007724</v>
+      </c>
+      <c r="L517" s="2" t="n">
+        <v>0.00129634430904843</v>
+      </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
@@ -18067,6 +21175,12 @@
       <c r="J518" s="2" t="n">
         <v>0.0006480881399871243</v>
       </c>
+      <c r="K518" s="1" t="n">
+        <v>0.0154</v>
+      </c>
+      <c r="L518" s="3" t="n">
+        <v>-0.00259067357512954</v>
+      </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
@@ -18101,6 +21215,12 @@
       <c r="J519" s="3" t="n">
         <v>-0.004868549172346654</v>
       </c>
+      <c r="K519" s="1" t="n">
+        <v>0.004107</v>
+      </c>
+      <c r="L519" s="2" t="n">
+        <v>0.004647749510763403</v>
+      </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
@@ -18135,6 +21255,12 @@
       <c r="J520" s="3" t="n">
         <v>-0.0008628127696291049</v>
       </c>
+      <c r="K520" s="1" t="n">
+        <v>0.001157</v>
+      </c>
+      <c r="L520" s="3" t="n">
+        <v>-0.0008635578583764387</v>
+      </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
@@ -18169,6 +21295,12 @@
       <c r="J521" s="2" t="n">
         <v>0.0007485029940119455</v>
       </c>
+      <c r="K521" s="1" t="n">
+        <v>0.0134</v>
+      </c>
+      <c r="L521" s="2" t="n">
+        <v>0.002243829468960398</v>
+      </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
@@ -18203,6 +21335,12 @@
       <c r="J522" s="2" t="n">
         <v>0.000730994152046703</v>
       </c>
+      <c r="K522" s="1" t="n">
+        <v>0.6861</v>
+      </c>
+      <c r="L522" s="2" t="n">
+        <v>0.002337472607742945</v>
+      </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
@@ -18237,6 +21375,12 @@
       <c r="J523" s="2" t="n">
         <v>0.001001144164759734</v>
       </c>
+      <c r="K523" s="1" t="n">
+        <v>0.07008</v>
+      </c>
+      <c r="L523" s="2" t="n">
+        <v>0.001285897985426586</v>
+      </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
@@ -18271,6 +21415,12 @@
       <c r="J524" s="3" t="n">
         <v>-0.002599653379549438</v>
       </c>
+      <c r="K524" s="1" t="n">
+        <v>0.01154</v>
+      </c>
+      <c r="L524" s="2" t="n">
+        <v>0.002606429192006995</v>
+      </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
@@ -18305,6 +21455,12 @@
       <c r="J525" s="2" t="n">
         <v>0.003683241252302089</v>
       </c>
+      <c r="K525" s="1" t="n">
+        <v>0.0164</v>
+      </c>
+      <c r="L525" s="2" t="n">
+        <v>0.003058103975535256</v>
+      </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
@@ -18339,6 +21495,12 @@
       <c r="J526" s="2" t="n">
         <v>0.0002937504589849782</v>
       </c>
+      <c r="K526" s="1" t="n">
+        <v>0.13563</v>
+      </c>
+      <c r="L526" s="3" t="n">
+        <v>-0.004258130827398849</v>
+      </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
@@ -18373,6 +21535,12 @@
       <c r="J527" s="3" t="n">
         <v>-0.001627906976744039</v>
       </c>
+      <c r="K527" s="1" t="n">
+        <v>0.04304</v>
+      </c>
+      <c r="L527" s="2" t="n">
+        <v>0.002562310738411344</v>
+      </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
@@ -18407,6 +21575,12 @@
       <c r="J528" s="2" t="n">
         <v>0.001841620626151014</v>
       </c>
+      <c r="K528" s="1" t="n">
+        <v>0.2723</v>
+      </c>
+      <c r="L528" s="2" t="n">
+        <v>0.001102941176470467</v>
+      </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
@@ -18441,6 +21615,12 @@
       <c r="J529" s="2" t="n">
         <v>0.001803801859303424</v>
       </c>
+      <c r="K529" s="1" t="n">
+        <v>0.000723</v>
+      </c>
+      <c r="L529" s="2" t="n">
+        <v>0.001385041551246571</v>
+      </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
@@ -18475,6 +21655,12 @@
       <c r="J530" s="3" t="n">
         <v>-0.001200768491834725</v>
       </c>
+      <c r="K530" s="1" t="n">
+        <v>0.004174</v>
+      </c>
+      <c r="L530" s="2" t="n">
+        <v>0.003606636210627407</v>
+      </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
@@ -18509,6 +21695,12 @@
       <c r="J531" s="2" t="n">
         <v>0.003822629969418879</v>
       </c>
+      <c r="K531" s="1" t="n">
+        <v>1.314</v>
+      </c>
+      <c r="L531" s="2" t="n">
+        <v>0.0007616146230008469</v>
+      </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
@@ -18543,6 +21735,12 @@
       <c r="J532" s="2" t="n">
         <v>0.0008510638297872584</v>
       </c>
+      <c r="K532" s="1" t="n">
+        <v>0.1175</v>
+      </c>
+      <c r="L532" s="3" t="n">
+        <v>-0.0008503401360544461</v>
+      </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
@@ -18577,6 +21775,12 @@
       <c r="J533" s="3" t="n">
         <v>-0.00130743369443408</v>
       </c>
+      <c r="K533" s="1" t="n">
+        <v>0.05343</v>
+      </c>
+      <c r="L533" s="3" t="n">
+        <v>-0.0007480830372171007</v>
+      </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
@@ -18611,6 +21815,12 @@
       <c r="J534" s="3" t="n">
         <v>-0.00199335548172754</v>
       </c>
+      <c r="K534" s="1" t="n">
+        <v>0.1504</v>
+      </c>
+      <c r="L534" s="2" t="n">
+        <v>0.001331557922769679</v>
+      </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
@@ -18645,6 +21855,12 @@
       <c r="J535" s="3" t="n">
         <v>-0.001169590643274806</v>
       </c>
+      <c r="K535" s="1" t="n">
+        <v>0.01714</v>
+      </c>
+      <c r="L535" s="2" t="n">
+        <v>0.003512880562060746</v>
+      </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
@@ -18679,6 +21895,12 @@
       <c r="J536" s="3" t="n">
         <v>-0.000201166767250077</v>
       </c>
+      <c r="K536" s="1" t="n">
+        <v>0.00498</v>
+      </c>
+      <c r="L536" s="2" t="n">
+        <v>0.002012072434607738</v>
+      </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
@@ -18713,6 +21935,12 @@
       <c r="J537" s="2" t="n">
         <v>0.0006879944960439558</v>
       </c>
+      <c r="K537" s="1" t="n">
+        <v>0.2913</v>
+      </c>
+      <c r="L537" s="2" t="n">
+        <v>0.001375042970092855</v>
+      </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
@@ -18747,6 +21975,12 @@
       <c r="J538" s="2" t="n">
         <v>0.004552352048558367</v>
       </c>
+      <c r="K538" s="1" t="n">
+        <v>0.01327</v>
+      </c>
+      <c r="L538" s="2" t="n">
+        <v>0.002265861027190371</v>
+      </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
@@ -18781,6 +22015,12 @@
       <c r="J539" s="2" t="n">
         <v>0.005303957568339379</v>
       </c>
+      <c r="K539" s="1" t="n">
+        <v>0.02459</v>
+      </c>
+      <c r="L539" s="3" t="n">
+        <v>-0.002029220779220697</v>
+      </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
@@ -18815,6 +22055,12 @@
       <c r="J540" s="3" t="n">
         <v>-0.0003522987493394255</v>
       </c>
+      <c r="K540" s="1" t="n">
+        <v>0.05687</v>
+      </c>
+      <c r="L540" s="2" t="n">
+        <v>0.002114537444933835</v>
+      </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
@@ -18849,6 +22095,12 @@
       <c r="J541" s="2" t="n">
         <v>0.008695652173912992</v>
       </c>
+      <c r="K541" s="1" t="n">
+        <v>0.0116</v>
+      </c>
+      <c r="L541" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
@@ -18883,6 +22135,12 @@
       <c r="J542" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="K542" s="1" t="n">
+        <v>1.12e-05</v>
+      </c>
+      <c r="L542" s="2" t="n">
+        <v>0.009009009009008922</v>
+      </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
@@ -18916,6 +22174,12 @@
       </c>
       <c r="J543" s="3" t="n">
         <v>-0.002452316076294249</v>
+      </c>
+      <c r="K543" s="1" t="n">
+        <v>0.003675</v>
+      </c>
+      <c r="L543" s="2" t="n">
+        <v>0.003824091778202592</v>
       </c>
     </row>
   </sheetData>

--- a/binance-usdt-perpetual-data/weeks/2026-03-09_2026-03-15/2026-03-12.xlsx
+++ b/binance-usdt-perpetual-data/weeks/2026-03-09_2026-03-15/2026-03-12.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L543"/>
+  <dimension ref="A1:N543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -438,6 +438,8 @@
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="13" customWidth="1" min="11" max="11"/>
     <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -501,6 +503,16 @@
           <t>change_01:15</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>price_01:30</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>change_01:30</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -541,6 +553,12 @@
       <c r="L2" s="2" t="n">
         <v>0.004145512596035027</v>
       </c>
+      <c r="M2" s="1" t="n">
+        <v>71207.2</v>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>0.005375106775006489</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -581,6 +599,12 @@
       <c r="L3" s="2" t="n">
         <v>0.002149267603179393</v>
       </c>
+      <c r="M3" s="1" t="n">
+        <v>2081.63</v>
+      </c>
+      <c r="N3" s="2" t="n">
+        <v>0.005492063798749862</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -621,6 +645,12 @@
       <c r="L4" s="2" t="n">
         <v>0.002199583236860358</v>
       </c>
+      <c r="M4" s="1" t="n">
+        <v>87.63</v>
+      </c>
+      <c r="N4" s="2" t="n">
+        <v>0.01224442647568444</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -661,6 +691,12 @@
       <c r="L5" s="2" t="n">
         <v>0.01996843477664183</v>
       </c>
+      <c r="M5" s="1" t="n">
+        <v>0.014638</v>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>-0.0152045209903122</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -701,6 +737,12 @@
       <c r="L6" s="2" t="n">
         <v>0.004734237142242413</v>
       </c>
+      <c r="M6" s="1" t="n">
+        <v>0.09383</v>
+      </c>
+      <c r="N6" s="2" t="n">
+        <v>0.004819019061897537</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -741,6 +783,12 @@
       <c r="L7" s="2" t="n">
         <v>0.002957299480669354</v>
       </c>
+      <c r="M7" s="1" t="n">
+        <v>1.3985</v>
+      </c>
+      <c r="N7" s="2" t="n">
+        <v>0.005753326141675661</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -781,6 +829,12 @@
       <c r="L8" s="3" t="n">
         <v>-0.0008782040726714852</v>
       </c>
+      <c r="M8" s="1" t="n">
+        <v>36.697</v>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>0.007993187936054604</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -821,6 +875,12 @@
       <c r="L9" s="2" t="n">
         <v>0.003502221673660797</v>
       </c>
+      <c r="M9" s="1" t="n">
+        <v>654.61</v>
+      </c>
+      <c r="N9" s="2" t="n">
+        <v>0.006426517842043055</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -861,6 +921,12 @@
       <c r="L10" s="3" t="n">
         <v>-0.009210787886819916</v>
       </c>
+      <c r="M10" s="1" t="n">
+        <v>14.575</v>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>-0.02521401819154633</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -901,6 +967,12 @@
       <c r="L11" s="3" t="n">
         <v>-0.002368321333838575</v>
       </c>
+      <c r="M11" s="1" t="n">
+        <v>212.66</v>
+      </c>
+      <c r="N11" s="2" t="n">
+        <v>0.009685689868008699</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -941,6 +1013,12 @@
       <c r="L12" s="2" t="n">
         <v>0.003221572604700994</v>
       </c>
+      <c r="M12" s="1" t="n">
+        <v>0.0033784</v>
+      </c>
+      <c r="N12" s="2" t="n">
+        <v>0.004519505233111433</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -981,6 +1059,12 @@
       <c r="L13" s="2" t="n">
         <v>0.01025364274150023</v>
       </c>
+      <c r="M13" s="1" t="n">
+        <v>0.03689</v>
+      </c>
+      <c r="N13" s="3" t="n">
+        <v>-0.01469017094017099</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1021,6 +1105,12 @@
       <c r="L14" s="2" t="n">
         <v>0.004973221117061936</v>
       </c>
+      <c r="M14" s="1" t="n">
+        <v>2.632</v>
+      </c>
+      <c r="N14" s="2" t="n">
+        <v>0.001903311762466821</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1061,6 +1151,12 @@
       <c r="L15" s="2" t="n">
         <v>0.006345307542728465</v>
       </c>
+      <c r="M15" s="1" t="n">
+        <v>0.9876</v>
+      </c>
+      <c r="N15" s="2" t="n">
+        <v>0.004373029594223616</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1101,6 +1197,12 @@
       <c r="L16" s="3" t="n">
         <v>-0.003718788737382714</v>
       </c>
+      <c r="M16" s="1" t="n">
+        <v>0.05603</v>
+      </c>
+      <c r="N16" s="3" t="n">
+        <v>-0.004088162104514648</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1141,6 +1243,12 @@
       <c r="L17" s="2" t="n">
         <v>0.002267573696145127</v>
       </c>
+      <c r="M17" s="1" t="n">
+        <v>0.886</v>
+      </c>
+      <c r="N17" s="2" t="n">
+        <v>0.002262443438914029</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1181,6 +1289,12 @@
       <c r="L18" s="2" t="n">
         <v>0.003796507213363708</v>
       </c>
+      <c r="M18" s="1" t="n">
+        <v>0.2655</v>
+      </c>
+      <c r="N18" s="2" t="n">
+        <v>0.004160363086232942</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1221,6 +1335,12 @@
       <c r="L19" s="2" t="n">
         <v>0.01132253036496786</v>
       </c>
+      <c r="M19" s="1" t="n">
+        <v>0.34216</v>
+      </c>
+      <c r="N19" s="3" t="n">
+        <v>-0.005001744794695822</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1261,6 +1381,12 @@
       <c r="L20" s="2" t="n">
         <v>0.004881088378855603</v>
       </c>
+      <c r="M20" s="1" t="n">
+        <v>9.715</v>
+      </c>
+      <c r="N20" s="2" t="n">
+        <v>0.00403059115336913</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1301,6 +1427,12 @@
       <c r="L21" s="2" t="n">
         <v>0.001457213205366667</v>
       </c>
+      <c r="M21" s="1" t="n">
+        <v>200.01</v>
+      </c>
+      <c r="N21" s="2" t="n">
+        <v>0.00356246864024074</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1341,6 +1473,12 @@
       <c r="L22" s="2" t="n">
         <v>0.0001455533453010301</v>
       </c>
+      <c r="M22" s="1" t="n">
+        <v>0.021003</v>
+      </c>
+      <c r="N22" s="2" t="n">
+        <v>0.01887067041816243</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1381,6 +1519,12 @@
       <c r="L23" s="3" t="n">
         <v>-0.0008318010682076776</v>
       </c>
+      <c r="M23" s="1" t="n">
+        <v>458.07</v>
+      </c>
+      <c r="N23" s="2" t="n">
+        <v>0.003527143670858375</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1421,6 +1565,12 @@
       <c r="L24" s="2" t="n">
         <v>1.739695205402827e-05</v>
       </c>
+      <c r="M24" s="1" t="n">
+        <v>5169.55</v>
+      </c>
+      <c r="N24" s="3" t="n">
+        <v>-0.0007461229633838557</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1461,6 +1611,12 @@
       <c r="L25" s="2" t="n">
         <v>0.00209851999116414</v>
       </c>
+      <c r="M25" s="1" t="n">
+        <v>9.128</v>
+      </c>
+      <c r="N25" s="2" t="n">
+        <v>0.006061942025790776</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1501,6 +1657,12 @@
       <c r="L26" s="3" t="n">
         <v>-0.02856900644286197</v>
       </c>
+      <c r="M26" s="1" t="n">
+        <v>0.11894</v>
+      </c>
+      <c r="N26" s="2" t="n">
+        <v>0.03796142769875213</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1541,6 +1703,12 @@
       <c r="L27" s="2" t="n">
         <v>0.01643385373870177</v>
       </c>
+      <c r="M27" s="1" t="n">
+        <v>0.01235</v>
+      </c>
+      <c r="N27" s="3" t="n">
+        <v>-0.001616814874696922</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1581,6 +1749,12 @@
       <c r="L28" s="3" t="n">
         <v>-0.001540832049306627</v>
       </c>
+      <c r="M28" s="1" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="N28" s="2" t="n">
+        <v>0.003086419753086422</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1621,6 +1795,12 @@
       <c r="L29" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="M29" s="1" t="n">
+        <v>0.06073</v>
+      </c>
+      <c r="N29" s="3" t="n">
+        <v>-0.001151315789473694</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1661,6 +1841,12 @@
       <c r="L30" s="2" t="n">
         <v>0.004596191726854969</v>
       </c>
+      <c r="M30" s="1" t="n">
+        <v>1.531</v>
+      </c>
+      <c r="N30" s="2" t="n">
+        <v>0.000653594771241758</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1701,6 +1887,12 @@
       <c r="L31" s="3" t="n">
         <v>-0.003426333822809624</v>
       </c>
+      <c r="M31" s="1" t="n">
+        <v>0.002056</v>
+      </c>
+      <c r="N31" s="2" t="n">
+        <v>0.009823182711198454</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1741,6 +1933,12 @@
       <c r="L32" s="2" t="n">
         <v>0.005210918114143794</v>
       </c>
+      <c r="M32" s="1" t="n">
+        <v>0.04071</v>
+      </c>
+      <c r="N32" s="2" t="n">
+        <v>0.004937052579610114</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1781,6 +1979,12 @@
       <c r="L33" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="M33" s="1" t="n">
+        <v>0.0988</v>
+      </c>
+      <c r="N33" s="2" t="n">
+        <v>0.006109979633401256</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1821,6 +2025,12 @@
       <c r="L34" s="2" t="n">
         <v>0.002859866539561569</v>
       </c>
+      <c r="M34" s="1" t="n">
+        <v>0.1054</v>
+      </c>
+      <c r="N34" s="2" t="n">
+        <v>0.001901140684410569</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1861,6 +2071,12 @@
       <c r="L35" s="3" t="n">
         <v>-0.008849557522123918</v>
       </c>
+      <c r="M35" s="1" t="n">
+        <v>0.008920000000000001</v>
+      </c>
+      <c r="N35" s="3" t="n">
+        <v>-0.004464285714285533</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1901,6 +2117,12 @@
       <c r="L36" s="2" t="n">
         <v>0.00308036964435745</v>
       </c>
+      <c r="M36" s="1" t="n">
+        <v>0.3592</v>
+      </c>
+      <c r="N36" s="2" t="n">
+        <v>0.002791736460078171</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1941,6 +2163,12 @@
       <c r="L37" s="2" t="n">
         <v>0.0005141388174807881</v>
       </c>
+      <c r="M37" s="1" t="n">
+        <v>0.005854</v>
+      </c>
+      <c r="N37" s="2" t="n">
+        <v>0.002740664611168126</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1981,6 +2209,12 @@
       <c r="L38" s="2" t="n">
         <v>0.0002657353276137518</v>
       </c>
+      <c r="M38" s="1" t="n">
+        <v>0.26182</v>
+      </c>
+      <c r="N38" s="3" t="n">
+        <v>-0.006338001442179987</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2021,6 +2255,12 @@
       <c r="L39" s="3" t="n">
         <v>-0.004927079227433981</v>
       </c>
+      <c r="M39" s="1" t="n">
+        <v>0.05033</v>
+      </c>
+      <c r="N39" s="3" t="n">
+        <v>-0.003168944345414942</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2061,6 +2301,12 @@
       <c r="L40" s="2" t="n">
         <v>0.009435869784996864</v>
       </c>
+      <c r="M40" s="1" t="n">
+        <v>0.15008</v>
+      </c>
+      <c r="N40" s="2" t="n">
+        <v>0.002069840421980401</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2101,6 +2347,12 @@
       <c r="L41" s="2" t="n">
         <v>0.004750593824228</v>
       </c>
+      <c r="M41" s="1" t="n">
+        <v>0.1699</v>
+      </c>
+      <c r="N41" s="2" t="n">
+        <v>0.004137115839243535</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2141,6 +2393,12 @@
       <c r="L42" s="2" t="n">
         <v>0.005180421579135517</v>
       </c>
+      <c r="M42" s="1" t="n">
+        <v>112.57</v>
+      </c>
+      <c r="N42" s="2" t="n">
+        <v>0.0002665718855516876</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2181,6 +2439,12 @@
       <c r="L43" s="2" t="n">
         <v>0.0348537005163511</v>
       </c>
+      <c r="M43" s="1" t="n">
+        <v>0.7019</v>
+      </c>
+      <c r="N43" s="3" t="n">
+        <v>-0.02716562716562725</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2221,6 +2485,12 @@
       <c r="L44" s="3" t="n">
         <v>-0.001824484583105299</v>
       </c>
+      <c r="M44" s="1" t="n">
+        <v>55.02</v>
+      </c>
+      <c r="N44" s="2" t="n">
+        <v>0.005666240175470705</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2261,6 +2531,12 @@
       <c r="L45" s="2" t="n">
         <v>0.006665653841771244</v>
       </c>
+      <c r="M45" s="1" t="n">
+        <v>0.52977</v>
+      </c>
+      <c r="N45" s="3" t="n">
+        <v>-0.0006036710747231356</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2301,6 +2577,12 @@
       <c r="L46" s="2" t="n">
         <v>0.001989484155179703</v>
       </c>
+      <c r="M46" s="1" t="n">
+        <v>0.7058</v>
+      </c>
+      <c r="N46" s="2" t="n">
+        <v>0.0009927669834066573</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2341,6 +2623,12 @@
       <c r="L47" s="2" t="n">
         <v>0.002049705354855241</v>
       </c>
+      <c r="M47" s="1" t="n">
+        <v>3.927</v>
+      </c>
+      <c r="N47" s="2" t="n">
+        <v>0.004091025313219129</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2381,6 +2669,12 @@
       <c r="L48" s="2" t="n">
         <v>0.001499625093726681</v>
       </c>
+      <c r="M48" s="1" t="n">
+        <v>0.16055</v>
+      </c>
+      <c r="N48" s="2" t="n">
+        <v>0.001684552033940557</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2421,6 +2715,12 @@
       <c r="L49" s="3" t="n">
         <v>-0.01622785229342609</v>
       </c>
+      <c r="M49" s="1" t="n">
+        <v>0.0602</v>
+      </c>
+      <c r="N49" s="2" t="n">
+        <v>0.01329742467598046</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2461,6 +2761,12 @@
       <c r="L50" s="3" t="n">
         <v>-0.002583979328165269</v>
       </c>
+      <c r="M50" s="1" t="n">
+        <v>0.0388</v>
+      </c>
+      <c r="N50" s="2" t="n">
+        <v>0.005181347150259035</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2501,6 +2807,12 @@
       <c r="L51" s="2" t="n">
         <v>0.001499430216517725</v>
       </c>
+      <c r="M51" s="1" t="n">
+        <v>0.33217</v>
+      </c>
+      <c r="N51" s="3" t="n">
+        <v>-0.005359923344112943</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2541,6 +2853,12 @@
       <c r="L52" s="2" t="n">
         <v>0.005470085470085437</v>
       </c>
+      <c r="M52" s="1" t="n">
+        <v>0.2946</v>
+      </c>
+      <c r="N52" s="2" t="n">
+        <v>0.001700102006120369</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2581,6 +2899,12 @@
       <c r="L53" s="3" t="n">
         <v>-0.00252047889098936</v>
       </c>
+      <c r="M53" s="1" t="n">
+        <v>0.1587</v>
+      </c>
+      <c r="N53" s="2" t="n">
+        <v>0.002526847757422688</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2621,6 +2945,12 @@
       <c r="L54" s="2" t="n">
         <v>0.002303830548105371</v>
       </c>
+      <c r="M54" s="1" t="n">
+        <v>0.29158</v>
+      </c>
+      <c r="N54" s="2" t="n">
+        <v>0.0003087584479741294</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2661,6 +2991,12 @@
       <c r="L55" s="2" t="n">
         <v>0.000698031551026078</v>
       </c>
+      <c r="M55" s="1" t="n">
+        <v>0.00721</v>
+      </c>
+      <c r="N55" s="2" t="n">
+        <v>0.005859375000000052</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2701,6 +3037,12 @@
       <c r="L56" s="3" t="n">
         <v>-0.004555010511562655</v>
       </c>
+      <c r="M56" s="1" t="n">
+        <v>0.02842</v>
+      </c>
+      <c r="N56" s="2" t="n">
+        <v>0.0003519887363604221</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2741,6 +3083,12 @@
       <c r="L57" s="2" t="n">
         <v>0.001429592566118598</v>
       </c>
+      <c r="M57" s="1" t="n">
+        <v>0.04215</v>
+      </c>
+      <c r="N57" s="2" t="n">
+        <v>0.002855103497501833</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2781,6 +3129,12 @@
       <c r="L58" s="2" t="n">
         <v>0.009480715363068366</v>
       </c>
+      <c r="M58" s="1" t="n">
+        <v>0.04548</v>
+      </c>
+      <c r="N58" s="3" t="n">
+        <v>-0.02924226254002141</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2821,6 +3175,12 @@
       <c r="L59" s="2" t="n">
         <v>0.006535947712418306</v>
       </c>
+      <c r="M59" s="1" t="n">
+        <v>1.542</v>
+      </c>
+      <c r="N59" s="2" t="n">
+        <v>0.0012987012987013</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2861,6 +3221,12 @@
       <c r="L60" s="2" t="n">
         <v>0.00291545189504374</v>
       </c>
+      <c r="M60" s="1" t="n">
+        <v>0.00345</v>
+      </c>
+      <c r="N60" s="2" t="n">
+        <v>0.002906976744186054</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2901,6 +3267,12 @@
       <c r="L61" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="M61" s="1" t="n">
+        <v>0.1563</v>
+      </c>
+      <c r="N61" s="2" t="n">
+        <v>0.00838709677419352</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2941,6 +3313,12 @@
       <c r="L62" s="2" t="n">
         <v>0.0008695652173914017</v>
       </c>
+      <c r="M62" s="1" t="n">
+        <v>1.152</v>
+      </c>
+      <c r="N62" s="2" t="n">
+        <v>0.0008688097306688878</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2981,6 +3359,12 @@
       <c r="L63" s="3" t="n">
         <v>-0.0001427755568246559</v>
       </c>
+      <c r="M63" s="1" t="n">
+        <v>0.7027</v>
+      </c>
+      <c r="N63" s="2" t="n">
+        <v>0.003427102670284103</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3021,6 +3405,12 @@
       <c r="L64" s="2" t="n">
         <v>0.003065395095367812</v>
       </c>
+      <c r="M64" s="1" t="n">
+        <v>2.962</v>
+      </c>
+      <c r="N64" s="2" t="n">
+        <v>0.005772495755517945</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3061,6 +3451,12 @@
       <c r="L65" s="2" t="n">
         <v>0.00418235048097028</v>
       </c>
+      <c r="M65" s="1" t="n">
+        <v>0.02402</v>
+      </c>
+      <c r="N65" s="2" t="n">
+        <v>0.0004164931278633733</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3101,6 +3497,12 @@
       <c r="L66" s="2" t="n">
         <v>0.0009852216748767388</v>
       </c>
+      <c r="M66" s="1" t="n">
+        <v>0.102</v>
+      </c>
+      <c r="N66" s="2" t="n">
+        <v>0.003937007874015725</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3141,6 +3543,12 @@
       <c r="L67" s="3" t="n">
         <v>-0.01527439848607735</v>
       </c>
+      <c r="M67" s="1" t="n">
+        <v>0.007307</v>
+      </c>
+      <c r="N67" s="2" t="n">
+        <v>0.003019903912148294</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3181,6 +3589,12 @@
       <c r="L68" s="3" t="n">
         <v>-0.001613770844540136</v>
       </c>
+      <c r="M68" s="1" t="n">
+        <v>18.79</v>
+      </c>
+      <c r="N68" s="2" t="n">
+        <v>0.01239224137931037</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3221,6 +3635,12 @@
       <c r="L69" s="2" t="n">
         <v>0.004661570016781656</v>
       </c>
+      <c r="M69" s="1" t="n">
+        <v>0.054</v>
+      </c>
+      <c r="N69" s="2" t="n">
+        <v>0.002227171492204938</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3261,6 +3681,12 @@
       <c r="L70" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="M70" s="1" t="n">
+        <v>0.239</v>
+      </c>
+      <c r="N70" s="2" t="n">
+        <v>0.004201680672268912</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3301,6 +3727,12 @@
       <c r="L71" s="3" t="n">
         <v>-0.0290073775989269</v>
       </c>
+      <c r="M71" s="1" t="n">
+        <v>5.957</v>
+      </c>
+      <c r="N71" s="2" t="n">
+        <v>0.02866517009152124</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3341,6 +3773,12 @@
       <c r="L72" s="3" t="n">
         <v>-0.05528612997090201</v>
       </c>
+      <c r="M72" s="1" t="n">
+        <v>0.001909</v>
+      </c>
+      <c r="N72" s="3" t="n">
+        <v>-0.02002053388090348</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3381,6 +3819,12 @@
       <c r="L73" s="2" t="n">
         <v>0.005825654062069642</v>
       </c>
+      <c r="M73" s="1" t="n">
+        <v>0.9435</v>
+      </c>
+      <c r="N73" s="3" t="n">
+        <v>-0.006423757371524847</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3421,6 +3865,12 @@
       <c r="L74" s="2" t="n">
         <v>0.004142502071251039</v>
       </c>
+      <c r="M74" s="1" t="n">
+        <v>0.1213</v>
+      </c>
+      <c r="N74" s="2" t="n">
+        <v>0.0008250825082508487</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3461,6 +3911,12 @@
       <c r="L75" s="2" t="n">
         <v>0.004397989490518516</v>
       </c>
+      <c r="M75" s="1" t="n">
+        <v>352.2</v>
+      </c>
+      <c r="N75" s="2" t="n">
+        <v>0.001421666192777936</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3501,6 +3957,12 @@
       <c r="L76" s="2" t="n">
         <v>0.002708192281652005</v>
       </c>
+      <c r="M76" s="1" t="n">
+        <v>0.11941</v>
+      </c>
+      <c r="N76" s="2" t="n">
+        <v>0.007849426063470629</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3541,6 +4003,12 @@
       <c r="L77" s="3" t="n">
         <v>-0.003013003488741034</v>
       </c>
+      <c r="M77" s="1" t="n">
+        <v>0.06301</v>
+      </c>
+      <c r="N77" s="2" t="n">
+        <v>0.002226817241927808</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3581,6 +4049,12 @@
       <c r="L78" s="2" t="n">
         <v>0.001595574938836266</v>
       </c>
+      <c r="M78" s="1" t="n">
+        <v>0.09443</v>
+      </c>
+      <c r="N78" s="2" t="n">
+        <v>0.002867459643160645</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3621,6 +4095,12 @@
       <c r="L79" s="2" t="n">
         <v>0.006787878787878848</v>
       </c>
+      <c r="M79" s="1" t="n">
+        <v>0.4127</v>
+      </c>
+      <c r="N79" s="3" t="n">
+        <v>-0.006260534553334918</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3661,6 +4141,12 @@
       <c r="L80" s="2" t="n">
         <v>0.001332666999833449</v>
       </c>
+      <c r="M80" s="1" t="n">
+        <v>0.006043</v>
+      </c>
+      <c r="N80" s="2" t="n">
+        <v>0.00532357344867741</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3701,6 +4187,12 @@
       <c r="L81" s="3" t="n">
         <v>-0.00578034682080928</v>
       </c>
+      <c r="M81" s="1" t="n">
+        <v>0.1046</v>
+      </c>
+      <c r="N81" s="2" t="n">
+        <v>0.0135658914728682</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3741,6 +4233,12 @@
       <c r="L82" s="2" t="n">
         <v>0.0009784735812133354</v>
       </c>
+      <c r="M82" s="1" t="n">
+        <v>0.1023</v>
+      </c>
+      <c r="N82" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3781,6 +4279,12 @@
       <c r="L83" s="2" t="n">
         <v>0.05543423483957664</v>
       </c>
+      <c r="M83" s="1" t="n">
+        <v>0.06152</v>
+      </c>
+      <c r="N83" s="3" t="n">
+        <v>-0.02084991246219957</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3821,6 +4325,12 @@
       <c r="L84" s="2" t="n">
         <v>0.007280244472406971</v>
       </c>
+      <c r="M84" s="1" t="n">
+        <v>1.1242</v>
+      </c>
+      <c r="N84" s="2" t="n">
+        <v>0.003123048094940714</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3861,6 +4371,12 @@
       <c r="L85" s="2" t="n">
         <v>0.003773584905660355</v>
       </c>
+      <c r="M85" s="1" t="n">
+        <v>0.01338</v>
+      </c>
+      <c r="N85" s="2" t="n">
+        <v>0.006015037593984978</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3901,6 +4417,12 @@
       <c r="L86" s="2" t="n">
         <v>0.003586371787208669</v>
       </c>
+      <c r="M86" s="1" t="n">
+        <v>0.01689</v>
+      </c>
+      <c r="N86" s="2" t="n">
+        <v>0.005955926146515748</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3941,6 +4463,12 @@
       <c r="L87" s="2" t="n">
         <v>0.0009638554216866408</v>
       </c>
+      <c r="M87" s="1" t="n">
+        <v>8.348000000000001</v>
+      </c>
+      <c r="N87" s="2" t="n">
+        <v>0.004814636494944743</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3981,6 +4509,12 @@
       <c r="L88" s="2" t="n">
         <v>0.003775187579632867</v>
       </c>
+      <c r="M88" s="1" t="n">
+        <v>2.1395</v>
+      </c>
+      <c r="N88" s="2" t="n">
+        <v>0.005829533167222964</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -4021,6 +4555,12 @@
       <c r="L89" s="2" t="n">
         <v>0.004495729057395421</v>
       </c>
+      <c r="M89" s="1" t="n">
+        <v>0.006778</v>
+      </c>
+      <c r="N89" s="2" t="n">
+        <v>0.01118901984186191</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -4061,6 +4601,12 @@
       <c r="L90" s="2" t="n">
         <v>0.0006565988181221133</v>
       </c>
+      <c r="M90" s="1" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="N90" s="2" t="n">
+        <v>0.003937007874015781</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -4101,6 +4647,12 @@
       <c r="L91" s="2" t="n">
         <v>0.01351351351351348</v>
       </c>
+      <c r="M91" s="1" t="n">
+        <v>0.000224</v>
+      </c>
+      <c r="N91" s="3" t="n">
+        <v>-0.004444444444444432</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -4141,6 +4693,12 @@
       <c r="L92" s="3" t="n">
         <v>-0.007768093974990539</v>
       </c>
+      <c r="M92" s="1" t="n">
+        <v>0.05358</v>
+      </c>
+      <c r="N92" s="2" t="n">
+        <v>0.02310483101012035</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -4181,6 +4739,12 @@
       <c r="L93" s="2" t="n">
         <v>0.002351156617368299</v>
       </c>
+      <c r="M93" s="1" t="n">
+        <v>1.3257</v>
+      </c>
+      <c r="N93" s="2" t="n">
+        <v>0.003102300242130745</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -4221,6 +4785,12 @@
       <c r="L94" s="2" t="n">
         <v>0.00680702276446954</v>
       </c>
+      <c r="M94" s="1" t="n">
+        <v>0.054071</v>
+      </c>
+      <c r="N94" s="3" t="n">
+        <v>-0.001163778771197409</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -4261,6 +4831,12 @@
       <c r="L95" s="2" t="n">
         <v>0.002483443708609228</v>
       </c>
+      <c r="M95" s="1" t="n">
+        <v>0.2425</v>
+      </c>
+      <c r="N95" s="2" t="n">
+        <v>0.001238645747316246</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -4301,6 +4877,12 @@
       <c r="L96" s="3" t="n">
         <v>-0.001014292300599448</v>
       </c>
+      <c r="M96" s="1" t="n">
+        <v>1.0822</v>
+      </c>
+      <c r="N96" s="3" t="n">
+        <v>-0.001107624146206265</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -4341,6 +4923,12 @@
       <c r="L97" s="2" t="n">
         <v>0.004276827371695139</v>
       </c>
+      <c r="M97" s="1" t="n">
+        <v>0.2591</v>
+      </c>
+      <c r="N97" s="2" t="n">
+        <v>0.003097173828881235</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -4381,6 +4969,12 @@
       <c r="L98" s="2" t="n">
         <v>0.002251862116750334</v>
       </c>
+      <c r="M98" s="1" t="n">
+        <v>0.5879</v>
+      </c>
+      <c r="N98" s="2" t="n">
+        <v>0.01607328033183542</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -4421,6 +5015,12 @@
       <c r="L99" s="3" t="n">
         <v>-0.006926024167403451</v>
       </c>
+      <c r="M99" s="1" t="n">
+        <v>0.13512</v>
+      </c>
+      <c r="N99" s="2" t="n">
+        <v>0.002522629470247657</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -4461,6 +5061,12 @@
       <c r="L100" s="2" t="n">
         <v>0.005252790544977032</v>
       </c>
+      <c r="M100" s="1" t="n">
+        <v>0.0307</v>
+      </c>
+      <c r="N100" s="2" t="n">
+        <v>0.002612671456564344</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -4501,6 +5107,12 @@
       <c r="L101" s="2" t="n">
         <v>0.004887585532746937</v>
       </c>
+      <c r="M101" s="1" t="n">
+        <v>1.034</v>
+      </c>
+      <c r="N101" s="2" t="n">
+        <v>0.005836575875486387</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -4541,6 +5153,12 @@
       <c r="L102" s="2" t="n">
         <v>0.002727272727272774</v>
       </c>
+      <c r="M102" s="1" t="n">
+        <v>0.02214</v>
+      </c>
+      <c r="N102" s="2" t="n">
+        <v>0.003626473254759756</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -4581,6 +5199,12 @@
       <c r="L103" s="2" t="n">
         <v>0.006141248720573289</v>
       </c>
+      <c r="M103" s="1" t="n">
+        <v>0.01962</v>
+      </c>
+      <c r="N103" s="3" t="n">
+        <v>-0.002034587995930918</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -4621,6 +5245,12 @@
       <c r="L104" s="2" t="n">
         <v>0.0003344481605350802</v>
       </c>
+      <c r="M104" s="1" t="n">
+        <v>3.004</v>
+      </c>
+      <c r="N104" s="2" t="n">
+        <v>0.004346372450685356</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -4661,6 +5291,12 @@
       <c r="L105" s="2" t="n">
         <v>0.0009302325581395702</v>
       </c>
+      <c r="M105" s="1" t="n">
+        <v>32.48</v>
+      </c>
+      <c r="N105" s="2" t="n">
+        <v>0.006195786864931714</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -4701,6 +5337,12 @@
       <c r="L106" s="2" t="n">
         <v>0.001207000603500336</v>
       </c>
+      <c r="M106" s="1" t="n">
+        <v>0.1668</v>
+      </c>
+      <c r="N106" s="2" t="n">
+        <v>0.005424954792043472</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -4741,6 +5383,12 @@
       <c r="L107" s="2" t="n">
         <v>0.01982624192470475</v>
       </c>
+      <c r="M107" s="1" t="n">
+        <v>0.4581</v>
+      </c>
+      <c r="N107" s="2" t="n">
+        <v>0.0006553079947575852</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -4781,6 +5429,12 @@
       <c r="L108" s="2" t="n">
         <v>0.002384500745156386</v>
       </c>
+      <c r="M108" s="1" t="n">
+        <v>0.3369</v>
+      </c>
+      <c r="N108" s="2" t="n">
+        <v>0.001784121320249746</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -4821,6 +5475,12 @@
       <c r="L109" s="3" t="n">
         <v>-0.008085106382978661</v>
       </c>
+      <c r="M109" s="1" t="n">
+        <v>0.2339</v>
+      </c>
+      <c r="N109" s="2" t="n">
+        <v>0.003432003432003411</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -4861,6 +5521,12 @@
       <c r="L110" s="3" t="n">
         <v>-0.01051248357424433</v>
       </c>
+      <c r="M110" s="1" t="n">
+        <v>0.0151</v>
+      </c>
+      <c r="N110" s="2" t="n">
+        <v>0.002656042496679954</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -4901,6 +5567,12 @@
       <c r="L111" s="3" t="n">
         <v>-0.0005461496450026706</v>
       </c>
+      <c r="M111" s="1" t="n">
+        <v>1.839</v>
+      </c>
+      <c r="N111" s="2" t="n">
+        <v>0.004918032786885189</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -4941,6 +5613,12 @@
       <c r="L112" s="2" t="n">
         <v>0.0007812500000000586</v>
       </c>
+      <c r="M112" s="1" t="n">
+        <v>0.03842</v>
+      </c>
+      <c r="N112" s="3" t="n">
+        <v>-0.0002602133749673724</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -4981,6 +5659,12 @@
       <c r="L113" s="2" t="n">
         <v>0.003056665882906161</v>
       </c>
+      <c r="M113" s="1" t="n">
+        <v>4.259</v>
+      </c>
+      <c r="N113" s="3" t="n">
+        <v>-0.001640881387716754</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -5021,6 +5705,12 @@
       <c r="L114" s="2" t="n">
         <v>0.01484820363250698</v>
       </c>
+      <c r="M114" s="1" t="n">
+        <v>0.007587</v>
+      </c>
+      <c r="N114" s="3" t="n">
+        <v>-0.008883082952318792</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -5061,6 +5751,12 @@
       <c r="L115" s="3" t="n">
         <v>-0.0008088978766430409</v>
       </c>
+      <c r="M115" s="1" t="n">
+        <v>0.09977</v>
+      </c>
+      <c r="N115" s="2" t="n">
+        <v>0.009613438575187132</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -5101,6 +5797,12 @@
       <c r="L116" s="2" t="n">
         <v>0.002538684719535806</v>
       </c>
+      <c r="M116" s="1" t="n">
+        <v>0.08314000000000001</v>
+      </c>
+      <c r="N116" s="2" t="n">
+        <v>0.002532256119618978</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -5141,6 +5843,12 @@
       <c r="L117" s="2" t="n">
         <v>0.00367647058823526</v>
       </c>
+      <c r="M117" s="1" t="n">
+        <v>0.3024</v>
+      </c>
+      <c r="N117" s="2" t="n">
+        <v>0.006993006993006962</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -5181,6 +5889,12 @@
       <c r="L118" s="3" t="n">
         <v>-0.002198768689533924</v>
       </c>
+      <c r="M118" s="1" t="n">
+        <v>0.0227</v>
+      </c>
+      <c r="N118" s="2" t="n">
+        <v>0.0004407227853681385</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -5221,6 +5935,12 @@
       <c r="L119" s="2" t="n">
         <v>0.002597402597402672</v>
       </c>
+      <c r="M119" s="1" t="n">
+        <v>0.1542</v>
+      </c>
+      <c r="N119" s="3" t="n">
+        <v>-0.001295336787564804</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -5261,6 +5981,12 @@
       <c r="L120" s="2" t="n">
         <v>0.005443411204354862</v>
       </c>
+      <c r="M120" s="1" t="n">
+        <v>0.004674</v>
+      </c>
+      <c r="N120" s="2" t="n">
+        <v>0.05436498984886079</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -5301,6 +6027,12 @@
       <c r="L121" s="2" t="n">
         <v>0.009065550906554995</v>
       </c>
+      <c r="M121" s="1" t="n">
+        <v>0.4327</v>
+      </c>
+      <c r="N121" s="3" t="n">
+        <v>-0.003225063349458679</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -5341,6 +6073,12 @@
       <c r="L122" s="2" t="n">
         <v>0.002577319587628868</v>
       </c>
+      <c r="M122" s="1" t="n">
+        <v>0.779</v>
+      </c>
+      <c r="N122" s="2" t="n">
+        <v>0.001285347043701801</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -5381,6 +6119,12 @@
       <c r="L123" s="2" t="n">
         <v>0.002317497103128527</v>
       </c>
+      <c r="M123" s="1" t="n">
+        <v>0.0867</v>
+      </c>
+      <c r="N123" s="2" t="n">
+        <v>0.002312138728323766</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -5421,6 +6165,12 @@
       <c r="L124" s="2" t="n">
         <v>0.005591054313099091</v>
       </c>
+      <c r="M124" s="1" t="n">
+        <v>0.01243</v>
+      </c>
+      <c r="N124" s="3" t="n">
+        <v>-0.01270849880857827</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -5461,6 +6211,12 @@
       <c r="L125" s="2" t="n">
         <v>0.001640689089417631</v>
       </c>
+      <c r="M125" s="1" t="n">
+        <v>0.09779</v>
+      </c>
+      <c r="N125" s="2" t="n">
+        <v>0.001126126126126116</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -5501,6 +6257,12 @@
       <c r="L126" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="M126" s="1" t="n">
+        <v>0.04702</v>
+      </c>
+      <c r="N126" s="2" t="n">
+        <v>0.000212720697723806</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -5541,6 +6303,12 @@
       <c r="L127" s="2" t="n">
         <v>0.00630914826498438</v>
       </c>
+      <c r="M127" s="1" t="n">
+        <v>3.25e-05</v>
+      </c>
+      <c r="N127" s="2" t="n">
+        <v>0.0188087774294669</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -5581,6 +6349,12 @@
       <c r="L128" s="2" t="n">
         <v>0.004717805346845928</v>
       </c>
+      <c r="M128" s="1" t="n">
+        <v>0.5746</v>
+      </c>
+      <c r="N128" s="3" t="n">
+        <v>-0.0006956521739129669</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -5621,6 +6395,12 @@
       <c r="L129" s="2" t="n">
         <v>0.002895900015241514</v>
       </c>
+      <c r="M129" s="1" t="n">
+        <v>0.06584</v>
+      </c>
+      <c r="N129" s="2" t="n">
+        <v>0.0006079027355622852</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -5661,6 +6441,12 @@
       <c r="L130" s="2" t="n">
         <v>0.005352960856473686</v>
       </c>
+      <c r="M130" s="1" t="n">
+        <v>0.0006062</v>
+      </c>
+      <c r="N130" s="2" t="n">
+        <v>0.008652246256239631</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -5701,6 +6487,12 @@
       <c r="L131" s="2" t="n">
         <v>0.01149425287356323</v>
       </c>
+      <c r="M131" s="1" t="n">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="N131" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -5741,6 +6533,12 @@
       <c r="L132" s="2" t="n">
         <v>0.002656042496679838</v>
       </c>
+      <c r="M132" s="1" t="n">
+        <v>0.3024</v>
+      </c>
+      <c r="N132" s="2" t="n">
+        <v>0.001324503311258316</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -5781,6 +6579,12 @@
       <c r="L133" s="2" t="n">
         <v>0.004219409282700459</v>
       </c>
+      <c r="M133" s="1" t="n">
+        <v>0.03323</v>
+      </c>
+      <c r="N133" s="3" t="n">
+        <v>-0.002701080432172863</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -5821,6 +6625,12 @@
       <c r="L134" s="3" t="n">
         <v>-0.005906999107081528</v>
       </c>
+      <c r="M134" s="1" t="n">
+        <v>0.14493</v>
+      </c>
+      <c r="N134" s="2" t="n">
+        <v>0.001381883507220381</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -5861,6 +6671,12 @@
       <c r="L135" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="M135" s="1" t="n">
+        <v>0.02976</v>
+      </c>
+      <c r="N135" s="2" t="n">
+        <v>0.00472653612424042</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -5901,6 +6717,12 @@
       <c r="L136" s="2" t="n">
         <v>0.004976892996800589</v>
       </c>
+      <c r="M136" s="1" t="n">
+        <v>28.33</v>
+      </c>
+      <c r="N136" s="2" t="n">
+        <v>0.002122391227449548</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -5941,6 +6763,12 @@
       <c r="L137" s="2" t="n">
         <v>0.00420070011668609</v>
       </c>
+      <c r="M137" s="1" t="n">
+        <v>0.0004327</v>
+      </c>
+      <c r="N137" s="2" t="n">
+        <v>0.005577504066930058</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -5981,6 +6809,12 @@
       <c r="L138" s="2" t="n">
         <v>0.01389079906477794</v>
       </c>
+      <c r="M138" s="1" t="n">
+        <v>0.029488</v>
+      </c>
+      <c r="N138" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -6021,6 +6855,12 @@
       <c r="L139" s="2" t="n">
         <v>0.0008330729980214177</v>
       </c>
+      <c r="M139" s="1" t="n">
+        <v>0.09594</v>
+      </c>
+      <c r="N139" s="3" t="n">
+        <v>-0.0017688065757986</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -6061,6 +6901,12 @@
       <c r="L140" s="3" t="n">
         <v>-0.002513966480446961</v>
       </c>
+      <c r="M140" s="1" t="n">
+        <v>0.3559</v>
+      </c>
+      <c r="N140" s="3" t="n">
+        <v>-0.003360403248389748</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -6101,6 +6947,12 @@
       <c r="L141" s="3" t="n">
         <v>-0.001102535832414636</v>
       </c>
+      <c r="M141" s="1" t="n">
+        <v>0.02707</v>
+      </c>
+      <c r="N141" s="3" t="n">
+        <v>-0.004047093451066924</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -6141,6 +6993,12 @@
       <c r="L142" s="2" t="n">
         <v>0.001430243141334014</v>
       </c>
+      <c r="M142" s="1" t="n">
+        <v>0.07779</v>
+      </c>
+      <c r="N142" s="2" t="n">
+        <v>0.009997403271877342</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -6181,6 +7039,12 @@
       <c r="L143" s="2" t="n">
         <v>0.007595510713071125</v>
       </c>
+      <c r="M143" s="1" t="n">
+        <v>0.08875</v>
+      </c>
+      <c r="N143" s="3" t="n">
+        <v>-0.00146264626462652</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -6221,6 +7085,12 @@
       <c r="L144" s="2" t="n">
         <v>0.004446640316205524</v>
       </c>
+      <c r="M144" s="1" t="n">
+        <v>0.02034</v>
+      </c>
+      <c r="N144" s="2" t="n">
+        <v>0.0004918839153959465</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -6261,6 +7131,12 @@
       <c r="L145" s="3" t="n">
         <v>-0.00175623463294689</v>
       </c>
+      <c r="M145" s="1" t="n">
+        <v>0.11416</v>
+      </c>
+      <c r="N145" s="2" t="n">
+        <v>0.00422237860661501</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -6301,6 +7177,12 @@
       <c r="L146" s="2" t="n">
         <v>0.002966381015161542</v>
       </c>
+      <c r="M146" s="1" t="n">
+        <v>0.3069</v>
+      </c>
+      <c r="N146" s="2" t="n">
+        <v>0.008544199802826129</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -6341,6 +7223,12 @@
       <c r="L147" s="2" t="n">
         <v>0.008196721311475417</v>
       </c>
+      <c r="M147" s="1" t="n">
+        <v>0.123</v>
+      </c>
+      <c r="N147" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -6381,6 +7269,12 @@
       <c r="L148" s="2" t="n">
         <v>0.005293996710526303</v>
       </c>
+      <c r="M148" s="1" t="n">
+        <v>1.9667</v>
+      </c>
+      <c r="N148" s="2" t="n">
+        <v>0.005521754690935079</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -6421,6 +7315,12 @@
       <c r="L149" s="2" t="n">
         <v>0.002263906856403642</v>
       </c>
+      <c r="M149" s="1" t="n">
+        <v>0.06186</v>
+      </c>
+      <c r="N149" s="3" t="n">
+        <v>-0.001936108422071669</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -6461,6 +7361,12 @@
       <c r="L150" s="2" t="n">
         <v>0.003642987249544562</v>
       </c>
+      <c r="M150" s="1" t="n">
+        <v>0.1619</v>
+      </c>
+      <c r="N150" s="3" t="n">
+        <v>-0.02056866303690269</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -6501,6 +7407,12 @@
       <c r="L151" s="2" t="n">
         <v>0.001648186994306222</v>
       </c>
+      <c r="M151" s="1" t="n">
+        <v>6.717e-05</v>
+      </c>
+      <c r="N151" s="2" t="n">
+        <v>0.00478683620044872</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -6541,6 +7453,12 @@
       <c r="L152" s="2" t="n">
         <v>0.01431492842535788</v>
       </c>
+      <c r="M152" s="1" t="n">
+        <v>0.01475</v>
+      </c>
+      <c r="N152" s="3" t="n">
+        <v>-0.008736559139785056</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -6581,6 +7499,12 @@
       <c r="L153" s="2" t="n">
         <v>0.00144023043686984</v>
       </c>
+      <c r="M153" s="1" t="n">
+        <v>0.02098</v>
+      </c>
+      <c r="N153" s="2" t="n">
+        <v>0.005752636625119778</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -6621,6 +7545,12 @@
       <c r="L154" s="2" t="n">
         <v>0.0003347840642785485</v>
       </c>
+      <c r="M154" s="1" t="n">
+        <v>0.0005954000000000001</v>
+      </c>
+      <c r="N154" s="3" t="n">
+        <v>-0.003681392235609011</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -6661,6 +7591,12 @@
       <c r="L155" s="2" t="n">
         <v>0.0009975062344140975</v>
       </c>
+      <c r="M155" s="1" t="n">
+        <v>0.04028</v>
+      </c>
+      <c r="N155" s="2" t="n">
+        <v>0.003487792725460917</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -6701,6 +7637,12 @@
       <c r="L156" s="2" t="n">
         <v>0.001589825119236819</v>
       </c>
+      <c r="M156" s="1" t="n">
+        <v>0.01893</v>
+      </c>
+      <c r="N156" s="2" t="n">
+        <v>0.001587301587301523</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -6741,6 +7683,12 @@
       <c r="L157" s="3" t="n">
         <v>-0.005761696243374055</v>
       </c>
+      <c r="M157" s="1" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="N157" s="2" t="n">
+        <v>0.008344923504867855</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -6781,6 +7729,12 @@
       <c r="L158" s="2" t="n">
         <v>0.002051158301158259</v>
       </c>
+      <c r="M158" s="1" t="n">
+        <v>0.008394</v>
+      </c>
+      <c r="N158" s="2" t="n">
+        <v>0.01071643588199886</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -6821,6 +7775,12 @@
       <c r="L159" s="2" t="n">
         <v>0.001202886928628576</v>
       </c>
+      <c r="M159" s="1" t="n">
+        <v>2.498</v>
+      </c>
+      <c r="N159" s="2" t="n">
+        <v>0.0004004805766921642</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -6861,6 +7821,12 @@
       <c r="L160" s="2" t="n">
         <v>0.003674458603705847</v>
       </c>
+      <c r="M160" s="1" t="n">
+        <v>1.2865</v>
+      </c>
+      <c r="N160" s="2" t="n">
+        <v>0.002103131328867366</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -6901,6 +7867,12 @@
       <c r="L161" s="3" t="n">
         <v>-0.0001325381047050054</v>
       </c>
+      <c r="M161" s="1" t="n">
+        <v>0.007523</v>
+      </c>
+      <c r="N161" s="3" t="n">
+        <v>-0.002783669141039261</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -6941,6 +7913,12 @@
       <c r="L162" s="2" t="n">
         <v>0.009661835748792296</v>
       </c>
+      <c r="M162" s="1" t="n">
+        <v>0.004132</v>
+      </c>
+      <c r="N162" s="3" t="n">
+        <v>-0.01148325358851661</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -6981,6 +7959,12 @@
       <c r="L163" s="2" t="n">
         <v>0.001042752867570416</v>
       </c>
+      <c r="M163" s="1" t="n">
+        <v>0.09619999999999999</v>
+      </c>
+      <c r="N163" s="2" t="n">
+        <v>0.002083333333333248</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -7021,6 +8005,12 @@
       <c r="L164" s="2" t="n">
         <v>0.002684466371617075</v>
       </c>
+      <c r="M164" s="1" t="n">
+        <v>1.3879</v>
+      </c>
+      <c r="N164" s="2" t="n">
+        <v>0.004269175108538362</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -7061,6 +8051,12 @@
       <c r="L165" s="3" t="n">
         <v>-0.000516662361147059</v>
       </c>
+      <c r="M165" s="1" t="n">
+        <v>0.02353</v>
+      </c>
+      <c r="N165" s="2" t="n">
+        <v>0.01361247523046439</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -7101,6 +8097,12 @@
       <c r="L166" s="3" t="n">
         <v>-0.004599463395937252</v>
       </c>
+      <c r="M166" s="1" t="n">
+        <v>0.005097</v>
+      </c>
+      <c r="N166" s="3" t="n">
+        <v>-0.01867539468617633</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -7141,6 +8143,12 @@
       <c r="L167" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="M167" s="1" t="n">
+        <v>0.06594999999999999</v>
+      </c>
+      <c r="N167" s="2" t="n">
+        <v>0.005335365853658371</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -7181,6 +8189,12 @@
       <c r="L168" s="2" t="n">
         <v>0.001055966209081193</v>
       </c>
+      <c r="M168" s="1" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="N168" s="2" t="n">
+        <v>0.002109704641350272</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -7221,6 +8235,12 @@
       <c r="L169" s="3" t="n">
         <v>-0.004696060527002338</v>
       </c>
+      <c r="M169" s="1" t="n">
+        <v>0.0382</v>
+      </c>
+      <c r="N169" s="2" t="n">
+        <v>0.001310615989514928</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -7261,6 +8281,12 @@
       <c r="L170" s="2" t="n">
         <v>0.001827125790583274</v>
       </c>
+      <c r="M170" s="1" t="n">
+        <v>0.007155</v>
+      </c>
+      <c r="N170" s="2" t="n">
+        <v>0.003787878787878804</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -7301,6 +8327,12 @@
       <c r="L171" s="2" t="n">
         <v>0.003219198127011969</v>
       </c>
+      <c r="M171" s="1" t="n">
+        <v>0.3435</v>
+      </c>
+      <c r="N171" s="2" t="n">
+        <v>0.00204200700116696</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -7341,6 +8373,12 @@
       <c r="L172" s="2" t="n">
         <v>0.001470858613715758</v>
       </c>
+      <c r="M172" s="1" t="n">
+        <v>5.476</v>
+      </c>
+      <c r="N172" s="2" t="n">
+        <v>0.005324031577014855</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -7381,6 +8419,12 @@
       <c r="L173" s="2" t="n">
         <v>0.001978021978021974</v>
       </c>
+      <c r="M173" s="1" t="n">
+        <v>0.04582</v>
+      </c>
+      <c r="N173" s="2" t="n">
+        <v>0.005044966001316101</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -7421,6 +8465,12 @@
       <c r="L174" s="3" t="n">
         <v>-0.0007668711656442292</v>
       </c>
+      <c r="M174" s="1" t="n">
+        <v>0.03911</v>
+      </c>
+      <c r="N174" s="2" t="n">
+        <v>0.000511639805576853</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -7461,6 +8511,12 @@
       <c r="L175" s="2" t="n">
         <v>0.01186410210318175</v>
       </c>
+      <c r="M175" s="1" t="n">
+        <v>0.005589</v>
+      </c>
+      <c r="N175" s="3" t="n">
+        <v>-0.007106057914372021</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -7501,6 +8557,12 @@
       <c r="L176" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="M176" s="1" t="n">
+        <v>0.00761</v>
+      </c>
+      <c r="N176" s="2" t="n">
+        <v>0.002635046113306875</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -7541,6 +8603,12 @@
       <c r="L177" s="2" t="n">
         <v>0.004610951008645537</v>
       </c>
+      <c r="M177" s="1" t="n">
+        <v>1.755</v>
+      </c>
+      <c r="N177" s="2" t="n">
+        <v>0.006884681583476642</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -7581,6 +8649,12 @@
       <c r="L178" s="2" t="n">
         <v>0.0003192236480877868</v>
       </c>
+      <c r="M178" s="1" t="n">
+        <v>15.689</v>
+      </c>
+      <c r="N178" s="2" t="n">
+        <v>0.001340311462854276</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -7621,6 +8695,12 @@
       <c r="L179" s="3" t="n">
         <v>-0.003225806451612906</v>
       </c>
+      <c r="M179" s="1" t="n">
+        <v>0.311</v>
+      </c>
+      <c r="N179" s="2" t="n">
+        <v>0.006472491909385119</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -7661,6 +8741,12 @@
       <c r="L180" s="2" t="n">
         <v>0.01117960505694286</v>
       </c>
+      <c r="M180" s="1" t="n">
+        <v>0.09698</v>
+      </c>
+      <c r="N180" s="2" t="n">
+        <v>0.002066542674106136</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -7701,6 +8787,12 @@
       <c r="L181" s="2" t="n">
         <v>0.001067235859124749</v>
       </c>
+      <c r="M181" s="1" t="n">
+        <v>0.1877</v>
+      </c>
+      <c r="N181" s="2" t="n">
+        <v>0.0005330490405118164</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -7741,6 +8833,12 @@
       <c r="L182" s="3" t="n">
         <v>-0.0006735140596059668</v>
       </c>
+      <c r="M182" s="1" t="n">
+        <v>0.05941</v>
+      </c>
+      <c r="N182" s="2" t="n">
+        <v>0.001010951979780919</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -7781,6 +8879,12 @@
       <c r="L183" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="M183" s="1" t="n">
+        <v>0.01204</v>
+      </c>
+      <c r="N183" s="3" t="n">
+        <v>-0.002485501242750664</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -7821,6 +8925,12 @@
       <c r="L184" s="2" t="n">
         <v>0.006069094304388336</v>
       </c>
+      <c r="M184" s="1" t="n">
+        <v>0.02158</v>
+      </c>
+      <c r="N184" s="2" t="n">
+        <v>0.001392111368909456</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -7861,6 +8971,12 @@
       <c r="L185" s="3" t="n">
         <v>-0.002754820936639121</v>
       </c>
+      <c r="M185" s="1" t="n">
+        <v>0.364</v>
+      </c>
+      <c r="N185" s="2" t="n">
+        <v>0.005524861878453044</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -7901,6 +9017,12 @@
       <c r="L186" s="3" t="n">
         <v>-0.0001309414691631878</v>
       </c>
+      <c r="M186" s="1" t="n">
+        <v>0.007657</v>
+      </c>
+      <c r="N186" s="2" t="n">
+        <v>0.002750130958616987</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -7941,6 +9063,12 @@
       <c r="L187" s="3" t="n">
         <v>-0.002590673575129454</v>
       </c>
+      <c r="M187" s="1" t="n">
+        <v>0.2703</v>
+      </c>
+      <c r="N187" s="2" t="n">
+        <v>0.002968460111317133</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -7981,6 +9109,12 @@
       <c r="L188" s="3" t="n">
         <v>-0.0006111224281931605</v>
       </c>
+      <c r="M188" s="1" t="n">
+        <v>0.04939</v>
+      </c>
+      <c r="N188" s="2" t="n">
+        <v>0.006726457399103218</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -8021,6 +9155,12 @@
       <c r="L189" s="2" t="n">
         <v>0.0003907776475185189</v>
       </c>
+      <c r="M189" s="1" t="n">
+        <v>0.2572</v>
+      </c>
+      <c r="N189" s="2" t="n">
+        <v>0.004687499999999917</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -8061,6 +9201,12 @@
       <c r="L190" s="2" t="n">
         <v>0.004427129449265199</v>
       </c>
+      <c r="M190" s="1" t="n">
+        <v>0.5682</v>
+      </c>
+      <c r="N190" s="2" t="n">
+        <v>0.001763046544428774</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -8101,6 +9247,12 @@
       <c r="L191" s="2" t="n">
         <v>0.001658649859014727</v>
       </c>
+      <c r="M191" s="1" t="n">
+        <v>6.065</v>
+      </c>
+      <c r="N191" s="2" t="n">
+        <v>0.004305348567643764</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -8141,6 +9293,12 @@
       <c r="L192" s="3" t="n">
         <v>-0.0002859593937660537</v>
       </c>
+      <c r="M192" s="1" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="N192" s="2" t="n">
+        <v>0.004004576659038778</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -8181,6 +9339,12 @@
       <c r="L193" s="2" t="n">
         <v>0.001557632398753939</v>
       </c>
+      <c r="M193" s="1" t="n">
+        <v>0.06419999999999999</v>
+      </c>
+      <c r="N193" s="3" t="n">
+        <v>-0.001555209953343746</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -8221,6 +9385,12 @@
       <c r="L194" s="2" t="n">
         <v>0.004589787722317855</v>
       </c>
+      <c r="M194" s="1" t="n">
+        <v>0.01758</v>
+      </c>
+      <c r="N194" s="2" t="n">
+        <v>0.003997715591090642</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -8261,6 +9431,12 @@
       <c r="L195" s="3" t="n">
         <v>-0.007687012391005048</v>
       </c>
+      <c r="M195" s="1" t="n">
+        <v>0.0008645</v>
+      </c>
+      <c r="N195" s="3" t="n">
+        <v>-0.0004624812117007859</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -8301,6 +9477,12 @@
       <c r="L196" s="3" t="n">
         <v>-0.0009813542688909872</v>
       </c>
+      <c r="M196" s="1" t="n">
+        <v>0.001016</v>
+      </c>
+      <c r="N196" s="3" t="n">
+        <v>-0.001964636542239733</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -8341,6 +9523,12 @@
       <c r="L197" s="2" t="n">
         <v>0.001241464928615628</v>
       </c>
+      <c r="M197" s="1" t="n">
+        <v>0.0001619</v>
+      </c>
+      <c r="N197" s="2" t="n">
+        <v>0.003719776813391287</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -8381,6 +9569,12 @@
       <c r="L198" s="2" t="n">
         <v>0.002076124567474127</v>
       </c>
+      <c r="M198" s="1" t="n">
+        <v>4.357</v>
+      </c>
+      <c r="N198" s="2" t="n">
+        <v>0.002992633517495373</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -8421,6 +9615,12 @@
       <c r="L199" s="2" t="n">
         <v>0.002458512599876974</v>
       </c>
+      <c r="M199" s="1" t="n">
+        <v>0.1638</v>
+      </c>
+      <c r="N199" s="2" t="n">
+        <v>0.00429184549356227</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -8461,6 +9661,12 @@
       <c r="L200" s="2" t="n">
         <v>0.0002518997439018877</v>
       </c>
+      <c r="M200" s="1" t="n">
+        <v>0.023873</v>
+      </c>
+      <c r="N200" s="2" t="n">
+        <v>0.002014690451206692</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -8501,6 +9707,12 @@
       <c r="L201" s="3" t="n">
         <v>-0.009277031349968075</v>
       </c>
+      <c r="M201" s="1" t="n">
+        <v>0.12367</v>
+      </c>
+      <c r="N201" s="3" t="n">
+        <v>-0.001695188892476605</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -8541,6 +9753,12 @@
       <c r="L202" s="2" t="n">
         <v>0.0007256894049346584</v>
       </c>
+      <c r="M202" s="1" t="n">
+        <v>0.01382</v>
+      </c>
+      <c r="N202" s="2" t="n">
+        <v>0.002175489485134192</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -8581,6 +9799,12 @@
       <c r="L203" s="2" t="n">
         <v>0.002943340691685113</v>
       </c>
+      <c r="M203" s="1" t="n">
+        <v>0.04111</v>
+      </c>
+      <c r="N203" s="2" t="n">
+        <v>0.005380288579114648</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -8621,6 +9845,12 @@
       <c r="L204" s="2" t="n">
         <v>0.001166861143523873</v>
       </c>
+      <c r="M204" s="1" t="n">
+        <v>0.02586</v>
+      </c>
+      <c r="N204" s="2" t="n">
+        <v>0.004662004662004742</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -8661,6 +9891,12 @@
       <c r="L205" s="2" t="n">
         <v>0.002322880371660862</v>
       </c>
+      <c r="M205" s="1" t="n">
+        <v>0.4345</v>
+      </c>
+      <c r="N205" s="2" t="n">
+        <v>0.006952491309385869</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -8701,6 +9937,12 @@
       <c r="L206" s="2" t="n">
         <v>0.00525164113785567</v>
       </c>
+      <c r="M206" s="1" t="n">
+        <v>0.02302</v>
+      </c>
+      <c r="N206" s="2" t="n">
+        <v>0.002176752285589811</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -8741,6 +9983,12 @@
       <c r="L207" s="2" t="n">
         <v>0.0004803073967340702</v>
       </c>
+      <c r="M207" s="1" t="n">
+        <v>4.173</v>
+      </c>
+      <c r="N207" s="2" t="n">
+        <v>0.001680268843014804</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -8781,6 +10029,12 @@
       <c r="L208" s="3" t="n">
         <v>-0.001758658008658078</v>
       </c>
+      <c r="M208" s="1" t="n">
+        <v>0.07381</v>
+      </c>
+      <c r="N208" s="2" t="n">
+        <v>0.0002710394362380557</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -8821,6 +10075,12 @@
       <c r="L209" s="3" t="n">
         <v>-0.000237247924080737</v>
       </c>
+      <c r="M209" s="1" t="n">
+        <v>0.04232</v>
+      </c>
+      <c r="N209" s="2" t="n">
+        <v>0.00427147603227353</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -8861,6 +10121,12 @@
       <c r="L210" s="2" t="n">
         <v>0.003260869565217334</v>
       </c>
+      <c r="M210" s="1" t="n">
+        <v>0.1852</v>
+      </c>
+      <c r="N210" s="2" t="n">
+        <v>0.003250270855904752</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -8901,6 +10167,12 @@
       <c r="L211" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="M211" s="1" t="n">
+        <v>0.2386</v>
+      </c>
+      <c r="N211" s="3" t="n">
+        <v>-0.001255755546253641</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -8941,6 +10213,12 @@
       <c r="L212" s="2" t="n">
         <v>0.002888781896966954</v>
       </c>
+      <c r="M212" s="1" t="n">
+        <v>0.002094</v>
+      </c>
+      <c r="N212" s="2" t="n">
+        <v>0.005280844935189498</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -8981,6 +10259,12 @@
       <c r="L213" s="2" t="n">
         <v>0.004305705059203449</v>
       </c>
+      <c r="M213" s="1" t="n">
+        <v>0.9350000000000001</v>
+      </c>
+      <c r="N213" s="2" t="n">
+        <v>0.002143622722400859</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -9021,6 +10305,12 @@
       <c r="L214" s="2" t="n">
         <v>0.001930501930501882</v>
       </c>
+      <c r="M214" s="1" t="n">
+        <v>0.005744</v>
+      </c>
+      <c r="N214" s="2" t="n">
+        <v>0.006130670870555318</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -9061,6 +10351,12 @@
       <c r="L215" s="2" t="n">
         <v>0.001463860933211412</v>
       </c>
+      <c r="M215" s="1" t="n">
+        <v>0.05494</v>
+      </c>
+      <c r="N215" s="2" t="n">
+        <v>0.003837018088799595</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -9101,6 +10397,12 @@
       <c r="L216" s="2" t="n">
         <v>0.003164556962025187</v>
       </c>
+      <c r="M216" s="1" t="n">
+        <v>0.0634</v>
+      </c>
+      <c r="N216" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -9141,6 +10443,12 @@
       <c r="L217" s="3" t="n">
         <v>-0.001077586206896433</v>
       </c>
+      <c r="M217" s="1" t="n">
+        <v>0.0929</v>
+      </c>
+      <c r="N217" s="2" t="n">
+        <v>0.002157497303128283</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -9181,6 +10489,12 @@
       <c r="L218" s="3" t="n">
         <v>-0.002545269434950107</v>
       </c>
+      <c r="M218" s="1" t="n">
+        <v>0.27579</v>
+      </c>
+      <c r="N218" s="2" t="n">
+        <v>0.005358705161854663</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -9221,6 +10535,12 @@
       <c r="L219" s="2" t="n">
         <v>0.003082614056720107</v>
       </c>
+      <c r="M219" s="1" t="n">
+        <v>0.003273</v>
+      </c>
+      <c r="N219" s="2" t="n">
+        <v>0.005838967424708027</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -9261,6 +10581,12 @@
       <c r="L220" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="M220" s="1" t="n">
+        <v>0.999373</v>
+      </c>
+      <c r="N220" s="3" t="n">
+        <v>-1.000626392150242e-06</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -9301,6 +10627,12 @@
       <c r="L221" s="2" t="n">
         <v>0.006207966890843176</v>
       </c>
+      <c r="M221" s="1" t="n">
+        <v>0.03961</v>
+      </c>
+      <c r="N221" s="2" t="n">
+        <v>0.01825192802056561</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -9341,6 +10673,12 @@
       <c r="L222" s="2" t="n">
         <v>0.002366609294320116</v>
       </c>
+      <c r="M222" s="1" t="n">
+        <v>0.04674</v>
+      </c>
+      <c r="N222" s="2" t="n">
+        <v>0.003219575016097819</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -9381,6 +10719,12 @@
       <c r="L223" s="2" t="n">
         <v>0.004770992366412218</v>
       </c>
+      <c r="M223" s="1" t="n">
+        <v>0.1055</v>
+      </c>
+      <c r="N223" s="2" t="n">
+        <v>0.001899335232668488</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -9421,6 +10765,12 @@
       <c r="L224" s="2" t="n">
         <v>0.0002581311306143236</v>
       </c>
+      <c r="M224" s="1" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="N224" s="2" t="n">
+        <v>0.006451612903225784</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -9461,6 +10811,12 @@
       <c r="L225" s="2" t="n">
         <v>0.002062975027144399</v>
       </c>
+      <c r="M225" s="1" t="n">
+        <v>0.0009269</v>
+      </c>
+      <c r="N225" s="2" t="n">
+        <v>0.004334164048109208</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -9501,6 +10857,12 @@
       <c r="L226" s="3" t="n">
         <v>-0.002824526303401167</v>
       </c>
+      <c r="M226" s="1" t="n">
+        <v>0.008484999999999999</v>
+      </c>
+      <c r="N226" s="2" t="n">
+        <v>0.001416263424997033</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -9541,6 +10903,12 @@
       <c r="L227" s="2" t="n">
         <v>0.0007265681763139319</v>
       </c>
+      <c r="M227" s="1" t="n">
+        <v>0.0414</v>
+      </c>
+      <c r="N227" s="2" t="n">
+        <v>0.001936108422071557</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -9581,6 +10949,12 @@
       <c r="L228" s="2" t="n">
         <v>0.006473402758232509</v>
       </c>
+      <c r="M228" s="1" t="n">
+        <v>0.0358</v>
+      </c>
+      <c r="N228" s="2" t="n">
+        <v>0.001118568232662147</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -9621,6 +10995,12 @@
       <c r="L229" s="2" t="n">
         <v>0.001360279828993405</v>
       </c>
+      <c r="M229" s="1" t="n">
+        <v>0.0516</v>
+      </c>
+      <c r="N229" s="2" t="n">
+        <v>0.001358431981370088</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -9661,6 +11041,12 @@
       <c r="L230" s="2" t="n">
         <v>0.00350058343057172</v>
       </c>
+      <c r="M230" s="1" t="n">
+        <v>0.00172</v>
+      </c>
+      <c r="N230" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -9701,6 +11087,12 @@
       <c r="L231" s="2" t="n">
         <v>0.002879473467708788</v>
       </c>
+      <c r="M231" s="1" t="n">
+        <v>0.0485</v>
+      </c>
+      <c r="N231" s="3" t="n">
+        <v>-0.00533223954060698</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -9741,6 +11133,12 @@
       <c r="L232" s="3" t="n">
         <v>-0.001377410468319662</v>
       </c>
+      <c r="M232" s="1" t="n">
+        <v>0.02189</v>
+      </c>
+      <c r="N232" s="2" t="n">
+        <v>0.00643678160919546</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -9781,6 +11179,12 @@
       <c r="L233" s="2" t="n">
         <v>0.0003422899195616916</v>
       </c>
+      <c r="M233" s="1" t="n">
+        <v>0.0005867</v>
+      </c>
+      <c r="N233" s="2" t="n">
+        <v>0.003763900769888886</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -9821,6 +11225,12 @@
       <c r="L234" s="3" t="n">
         <v>-0.002757934713807756</v>
       </c>
+      <c r="M234" s="1" t="n">
+        <v>0.22202</v>
+      </c>
+      <c r="N234" s="2" t="n">
+        <v>0.006573876773813333</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -9861,6 +11271,12 @@
       <c r="L235" s="2" t="n">
         <v>0.00287562904385335</v>
       </c>
+      <c r="M235" s="1" t="n">
+        <v>0.01383</v>
+      </c>
+      <c r="N235" s="3" t="n">
+        <v>-0.008602150537634431</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -9901,6 +11317,12 @@
       <c r="L236" s="3" t="n">
         <v>-0.002421307506053338</v>
       </c>
+      <c r="M236" s="1" t="n">
+        <v>0.0414</v>
+      </c>
+      <c r="N236" s="2" t="n">
+        <v>0.004854368932038806</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -9941,6 +11363,12 @@
       <c r="L237" s="2" t="n">
         <v>0.002392344497607766</v>
       </c>
+      <c r="M237" s="1" t="n">
+        <v>0.0042</v>
+      </c>
+      <c r="N237" s="2" t="n">
+        <v>0.002386634844868638</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -9981,6 +11409,12 @@
       <c r="L238" s="2" t="n">
         <v>0.004032258064516105</v>
       </c>
+      <c r="M238" s="1" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="N238" s="2" t="n">
+        <v>0.004016064257028227</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -10021,6 +11455,12 @@
       <c r="L239" s="2" t="n">
         <v>0.002691790040376858</v>
       </c>
+      <c r="M239" s="1" t="n">
+        <v>0.01491</v>
+      </c>
+      <c r="N239" s="2" t="n">
+        <v>0.0006711409395972881</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -10061,6 +11501,12 @@
       <c r="L240" s="3" t="n">
         <v>-0.0005105948429920982</v>
       </c>
+      <c r="M240" s="1" t="n">
+        <v>0.0003921</v>
+      </c>
+      <c r="N240" s="2" t="n">
+        <v>0.001532567049808466</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -10101,6 +11547,12 @@
       <c r="L241" s="2" t="n">
         <v>0.001126972201352451</v>
       </c>
+      <c r="M241" s="1" t="n">
+        <v>0.2676</v>
+      </c>
+      <c r="N241" s="2" t="n">
+        <v>0.004127579737335797</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -10141,6 +11593,12 @@
       <c r="L242" s="2" t="n">
         <v>0.007355838696965599</v>
       </c>
+      <c r="M242" s="1" t="n">
+        <v>0.07630000000000001</v>
+      </c>
+      <c r="N242" s="3" t="n">
+        <v>-0.005085408788629386</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -10181,6 +11639,12 @@
       <c r="L243" s="2" t="n">
         <v>0.01014713343480478</v>
       </c>
+      <c r="M243" s="1" t="n">
+        <v>0.01976</v>
+      </c>
+      <c r="N243" s="3" t="n">
+        <v>-0.007533902561526912</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -10221,6 +11685,12 @@
       <c r="L244" s="3" t="n">
         <v>-0.0002280761774433359</v>
       </c>
+      <c r="M244" s="1" t="n">
+        <v>0.08759</v>
+      </c>
+      <c r="N244" s="3" t="n">
+        <v>-0.0009125128322116658</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -10261,6 +11731,12 @@
       <c r="L245" s="3" t="n">
         <v>-0.00384642282677099</v>
       </c>
+      <c r="M245" s="1" t="n">
+        <v>1.4234</v>
+      </c>
+      <c r="N245" s="3" t="n">
+        <v>-0.0007020499859590788</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -10301,6 +11777,12 @@
       <c r="L246" s="2" t="n">
         <v>0.004486819966348862</v>
       </c>
+      <c r="M246" s="1" t="n">
+        <v>0.0179</v>
+      </c>
+      <c r="N246" s="3" t="n">
+        <v>-0.000558347292015611</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -10341,6 +11823,12 @@
       <c r="L247" s="2" t="n">
         <v>0.0004546143355054399</v>
       </c>
+      <c r="M247" s="1" t="n">
+        <v>0.006633</v>
+      </c>
+      <c r="N247" s="2" t="n">
+        <v>0.004695546803998755</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -10381,6 +11869,12 @@
       <c r="L248" s="3" t="n">
         <v>-0.0238095238095239</v>
       </c>
+      <c r="M248" s="1" t="n">
+        <v>0.004157</v>
+      </c>
+      <c r="N248" s="2" t="n">
+        <v>0.00386380101424786</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -10421,6 +11915,12 @@
       <c r="L249" s="2" t="n">
         <v>0.0009132420091324463</v>
       </c>
+      <c r="M249" s="1" t="n">
+        <v>0.1099</v>
+      </c>
+      <c r="N249" s="2" t="n">
+        <v>0.002737226277372214</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -10461,6 +11961,12 @@
       <c r="L250" s="2" t="n">
         <v>0.0005844535359438687</v>
       </c>
+      <c r="M250" s="1" t="n">
+        <v>0.03444</v>
+      </c>
+      <c r="N250" s="2" t="n">
+        <v>0.005841121495327068</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -10501,6 +12007,12 @@
       <c r="L251" s="3" t="n">
         <v>-0.001621120889300616</v>
       </c>
+      <c r="M251" s="1" t="n">
+        <v>0.04319</v>
+      </c>
+      <c r="N251" s="2" t="n">
+        <v>0.001855717930874431</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -10541,6 +12053,12 @@
       <c r="L252" s="2" t="n">
         <v>0.01517217865666562</v>
       </c>
+      <c r="M252" s="1" t="n">
+        <v>0.00617</v>
+      </c>
+      <c r="N252" s="2" t="n">
+        <v>0.03610411418975649</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -10581,6 +12099,12 @@
       <c r="L253" s="3" t="n">
         <v>-0.004756242568370999</v>
       </c>
+      <c r="M253" s="1" t="n">
+        <v>0.01682</v>
+      </c>
+      <c r="N253" s="2" t="n">
+        <v>0.004778972520908017</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -10621,6 +12145,12 @@
       <c r="L254" s="3" t="n">
         <v>-0.001537279016141474</v>
       </c>
+      <c r="M254" s="1" t="n">
+        <v>0.1306</v>
+      </c>
+      <c r="N254" s="2" t="n">
+        <v>0.005388760585065483</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -10661,6 +12191,12 @@
       <c r="L255" s="2" t="n">
         <v>0.002398081534772085</v>
       </c>
+      <c r="M255" s="1" t="n">
+        <v>0.02086</v>
+      </c>
+      <c r="N255" s="3" t="n">
+        <v>-0.001913875598086047</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -10701,6 +12237,12 @@
       <c r="L256" s="2" t="n">
         <v>0.002380952380952284</v>
       </c>
+      <c r="M256" s="1" t="n">
+        <v>0.02106</v>
+      </c>
+      <c r="N256" s="2" t="n">
+        <v>0.0004750593824227835</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -10741,6 +12283,12 @@
       <c r="L257" s="2" t="n">
         <v>0.002758077226162357</v>
       </c>
+      <c r="M257" s="1" t="n">
+        <v>0.0255</v>
+      </c>
+      <c r="N257" s="2" t="n">
+        <v>0.001964636542239606</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -10781,6 +12329,12 @@
       <c r="L258" s="2" t="n">
         <v>0.0006079027355623556</v>
       </c>
+      <c r="M258" s="1" t="n">
+        <v>0.14853</v>
+      </c>
+      <c r="N258" s="2" t="n">
+        <v>0.00263264479546376</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -10821,6 +12375,12 @@
       <c r="L259" s="2" t="n">
         <v>0.001572636131315189</v>
       </c>
+      <c r="M259" s="1" t="n">
+        <v>0.05105</v>
+      </c>
+      <c r="N259" s="2" t="n">
+        <v>0.001962708537782059</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -10861,6 +12421,12 @@
       <c r="L260" s="2" t="n">
         <v>0.001810719459198423</v>
       </c>
+      <c r="M260" s="1" t="n">
+        <v>0.08308</v>
+      </c>
+      <c r="N260" s="2" t="n">
+        <v>0.00108446800819384</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -10901,6 +12467,12 @@
       <c r="L261" s="3" t="n">
         <v>-0.01363636363636363</v>
       </c>
+      <c r="M261" s="1" t="n">
+        <v>0.2397</v>
+      </c>
+      <c r="N261" s="2" t="n">
+        <v>0.004189359028068709</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -10941,6 +12513,12 @@
       <c r="L262" s="2" t="n">
         <v>0.001405481377371595</v>
       </c>
+      <c r="M262" s="1" t="n">
+        <v>0.1424</v>
+      </c>
+      <c r="N262" s="3" t="n">
+        <v>-0.000701754385964835</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -10981,6 +12559,12 @@
       <c r="L263" s="3" t="n">
         <v>-0.00257931390250183</v>
       </c>
+      <c r="M263" s="1" t="n">
+        <v>0.07736</v>
+      </c>
+      <c r="N263" s="2" t="n">
+        <v>0.0002585983966898402</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -11021,6 +12605,12 @@
       <c r="L264" s="2" t="n">
         <v>0.003473083602083881</v>
       </c>
+      <c r="M264" s="1" t="n">
+        <v>0.03977</v>
+      </c>
+      <c r="N264" s="3" t="n">
+        <v>-0.01681087762669963</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -11061,6 +12651,12 @@
       <c r="L265" s="3" t="n">
         <v>-0.002604166666666673</v>
       </c>
+      <c r="M265" s="1" t="n">
+        <v>0.01536</v>
+      </c>
+      <c r="N265" s="2" t="n">
+        <v>0.00261096605744126</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -11101,6 +12697,12 @@
       <c r="L266" s="3" t="n">
         <v>-0.003337783711615496</v>
       </c>
+      <c r="M266" s="1" t="n">
+        <v>0.005958</v>
+      </c>
+      <c r="N266" s="3" t="n">
+        <v>-0.002344273275284683</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -11141,6 +12743,12 @@
       <c r="L267" s="3" t="n">
         <v>-0.004281509232004293</v>
       </c>
+      <c r="M267" s="1" t="n">
+        <v>0.03718</v>
+      </c>
+      <c r="N267" s="3" t="n">
+        <v>-0.0008062348830960023</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -11181,6 +12789,12 @@
       <c r="L268" s="2" t="n">
         <v>0.001639881928501195</v>
       </c>
+      <c r="M268" s="1" t="n">
+        <v>0.03062</v>
+      </c>
+      <c r="N268" s="2" t="n">
+        <v>0.002619515389652921</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -11221,6 +12835,12 @@
       <c r="L269" s="2" t="n">
         <v>0.001585623678646931</v>
       </c>
+      <c r="M269" s="1" t="n">
+        <v>0.22831</v>
+      </c>
+      <c r="N269" s="2" t="n">
+        <v>0.004001759014951724</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -11261,6 +12881,12 @@
       <c r="L270" s="3" t="n">
         <v>-0.003236245954692559</v>
       </c>
+      <c r="M270" s="1" t="n">
+        <v>0.927</v>
+      </c>
+      <c r="N270" s="2" t="n">
+        <v>0.00324675324675325</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -11301,6 +12927,12 @@
       <c r="L271" s="2" t="n">
         <v>0.001545595054095828</v>
       </c>
+      <c r="M271" s="1" t="n">
+        <v>2.597</v>
+      </c>
+      <c r="N271" s="2" t="n">
+        <v>0.001929012345678971</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -11341,6 +12973,12 @@
       <c r="L272" s="2" t="n">
         <v>0.002718868950516587</v>
       </c>
+      <c r="M272" s="1" t="n">
+        <v>0.1854</v>
+      </c>
+      <c r="N272" s="2" t="n">
+        <v>0.005422993492407813</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -11381,6 +13019,12 @@
       <c r="L273" s="2" t="n">
         <v>0.002594875121634778</v>
       </c>
+      <c r="M273" s="1" t="n">
+        <v>0.031</v>
+      </c>
+      <c r="N273" s="2" t="n">
+        <v>0.002911679068262692</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -11421,6 +13065,12 @@
       <c r="L274" s="2" t="n">
         <v>0.003680336487907352</v>
       </c>
+      <c r="M274" s="1" t="n">
+        <v>0.1914</v>
+      </c>
+      <c r="N274" s="2" t="n">
+        <v>0.002619172341540076</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -11461,6 +13111,12 @@
       <c r="L275" s="2" t="n">
         <v>0.004622273580817577</v>
       </c>
+      <c r="M275" s="1" t="n">
+        <v>0.06985</v>
+      </c>
+      <c r="N275" s="2" t="n">
+        <v>0.004313443565779939</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -11501,6 +13157,12 @@
       <c r="L276" s="2" t="n">
         <v>0.0003711952487008444</v>
       </c>
+      <c r="M276" s="1" t="n">
+        <v>0.08096</v>
+      </c>
+      <c r="N276" s="2" t="n">
+        <v>0.001360544217687062</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -11541,6 +13203,12 @@
       <c r="L277" s="3" t="n">
         <v>-0.04056695992179871</v>
       </c>
+      <c r="M277" s="1" t="n">
+        <v>0.003965</v>
+      </c>
+      <c r="N277" s="2" t="n">
+        <v>0.00993377483443708</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -11581,6 +13249,12 @@
       <c r="L278" s="2" t="n">
         <v>0.001937984496123961</v>
       </c>
+      <c r="M278" s="1" t="n">
+        <v>1.553</v>
+      </c>
+      <c r="N278" s="2" t="n">
+        <v>0.00128949065119278</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -11621,6 +13295,12 @@
       <c r="L279" s="3" t="n">
         <v>-0.002710027100271049</v>
       </c>
+      <c r="M279" s="1" t="n">
+        <v>0.01105</v>
+      </c>
+      <c r="N279" s="2" t="n">
+        <v>0.0009057971014493956</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -11661,6 +13341,12 @@
       <c r="L280" s="2" t="n">
         <v>0.004574332909783979</v>
       </c>
+      <c r="M280" s="1" t="n">
+        <v>0.04015</v>
+      </c>
+      <c r="N280" s="2" t="n">
+        <v>0.01568429041234494</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -11701,6 +13387,12 @@
       <c r="L281" s="3" t="n">
         <v>-0.009355755566082414</v>
       </c>
+      <c r="M281" s="1" t="n">
+        <v>0.08376</v>
+      </c>
+      <c r="N281" s="2" t="n">
+        <v>0.001315002988643144</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -11741,6 +13433,12 @@
       <c r="L282" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="M282" s="1" t="n">
+        <v>0.0265</v>
+      </c>
+      <c r="N282" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -11781,6 +13479,12 @@
       <c r="L283" s="2" t="n">
         <v>0.002495730986470455</v>
       </c>
+      <c r="M283" s="1" t="n">
+        <v>0.07652</v>
+      </c>
+      <c r="N283" s="2" t="n">
+        <v>0.002620545073375337</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -11821,6 +13525,12 @@
       <c r="L284" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="M284" s="1" t="n">
+        <v>0.001626</v>
+      </c>
+      <c r="N284" s="2" t="n">
+        <v>0.004323656578134689</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -11861,6 +13571,12 @@
       <c r="L285" s="2" t="n">
         <v>0.001485148514851459</v>
       </c>
+      <c r="M285" s="1" t="n">
+        <v>0.2026</v>
+      </c>
+      <c r="N285" s="2" t="n">
+        <v>0.001482946119624294</v>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -11901,6 +13617,12 @@
       <c r="L286" s="3" t="n">
         <v>-0.008753957906500246</v>
       </c>
+      <c r="M286" s="1" t="n">
+        <v>0.10643</v>
+      </c>
+      <c r="N286" s="3" t="n">
+        <v>-9.394964299145059e-05</v>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -11941,6 +13663,12 @@
       <c r="L287" s="2" t="n">
         <v>0.005824111822946965</v>
       </c>
+      <c r="M287" s="1" t="n">
+        <v>0.0173</v>
+      </c>
+      <c r="N287" s="2" t="n">
+        <v>0.001737116386797845</v>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -11981,6 +13709,12 @@
       <c r="L288" s="3" t="n">
         <v>-0.001967213114754132</v>
       </c>
+      <c r="M288" s="1" t="n">
+        <v>0.0152</v>
+      </c>
+      <c r="N288" s="3" t="n">
+        <v>-0.001314060446780498</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -12021,6 +13755,12 @@
       <c r="L289" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="M289" s="1" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="N289" s="2" t="n">
+        <v>0.001878522229179635</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -12061,6 +13801,12 @@
       <c r="L290" s="3" t="n">
         <v>-0.0004411116012350639</v>
       </c>
+      <c r="M290" s="1" t="n">
+        <v>2.273</v>
+      </c>
+      <c r="N290" s="2" t="n">
+        <v>0.003089143865842947</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -12101,6 +13847,12 @@
       <c r="L291" s="3" t="n">
         <v>-0.003397508493771237</v>
       </c>
+      <c r="M291" s="1" t="n">
+        <v>0.4404</v>
+      </c>
+      <c r="N291" s="2" t="n">
+        <v>0.0009090909090909351</v>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -12141,6 +13893,12 @@
       <c r="L292" s="3" t="n">
         <v>-0.001151410477835349</v>
       </c>
+      <c r="M292" s="1" t="n">
+        <v>1.739</v>
+      </c>
+      <c r="N292" s="2" t="n">
+        <v>0.002305475504322768</v>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -12181,6 +13939,12 @@
       <c r="L293" s="3" t="n">
         <v>-0.002364998029168349</v>
       </c>
+      <c r="M293" s="1" t="n">
+        <v>0.05065</v>
+      </c>
+      <c r="N293" s="2" t="n">
+        <v>0.0005926511260371839</v>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -12221,6 +13985,12 @@
       <c r="L294" s="2" t="n">
         <v>0.001103578748226401</v>
       </c>
+      <c r="M294" s="1" t="n">
+        <v>0.06356000000000001</v>
+      </c>
+      <c r="N294" s="2" t="n">
+        <v>0.0009448818897638503</v>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -12261,6 +14031,12 @@
       <c r="L295" s="2" t="n">
         <v>0.004131227217497063</v>
       </c>
+      <c r="M295" s="1" t="n">
+        <v>0.0004156</v>
+      </c>
+      <c r="N295" s="2" t="n">
+        <v>0.005808325266214918</v>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -12301,6 +14077,12 @@
       <c r="L296" s="2" t="n">
         <v>0.001604621309371011</v>
       </c>
+      <c r="M296" s="1" t="n">
+        <v>62.6</v>
+      </c>
+      <c r="N296" s="2" t="n">
+        <v>0.002883691124639534</v>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -12341,6 +14123,12 @@
       <c r="L297" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="M297" s="1" t="n">
+        <v>0.0982</v>
+      </c>
+      <c r="N297" s="2" t="n">
+        <v>0.003064351378958067</v>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -12381,6 +14169,12 @@
       <c r="L298" s="3" t="n">
         <v>-0.00104602510460254</v>
       </c>
+      <c r="M298" s="1" t="n">
+        <v>0.096</v>
+      </c>
+      <c r="N298" s="2" t="n">
+        <v>0.005235602094240842</v>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -12421,6 +14215,12 @@
       <c r="L299" s="2" t="n">
         <v>0.004186728072011698</v>
       </c>
+      <c r="M299" s="1" t="n">
+        <v>0.09634</v>
+      </c>
+      <c r="N299" s="2" t="n">
+        <v>0.004169272461955364</v>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -12461,6 +14261,12 @@
       <c r="L300" s="2" t="n">
         <v>0.00433839479392607</v>
       </c>
+      <c r="M300" s="1" t="n">
+        <v>0.0186</v>
+      </c>
+      <c r="N300" s="2" t="n">
+        <v>0.0043196544276458</v>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -12501,6 +14307,12 @@
       <c r="L301" s="2" t="n">
         <v>0.003003003003003011</v>
       </c>
+      <c r="M301" s="1" t="n">
+        <v>0.0134</v>
+      </c>
+      <c r="N301" s="2" t="n">
+        <v>0.002994011976047912</v>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -12541,6 +14353,12 @@
       <c r="L302" s="2" t="n">
         <v>0.0004589261128958847</v>
       </c>
+      <c r="M302" s="1" t="n">
+        <v>0.004368</v>
+      </c>
+      <c r="N302" s="2" t="n">
+        <v>0.001834862385321145</v>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -12581,6 +14399,12 @@
       <c r="L303" s="3" t="n">
         <v>-0.004264392324093828</v>
       </c>
+      <c r="M303" s="1" t="n">
+        <v>0.009350000000000001</v>
+      </c>
+      <c r="N303" s="2" t="n">
+        <v>0.001070663811563311</v>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -12621,6 +14445,12 @@
       <c r="L304" s="2" t="n">
         <v>0.00275365388688835</v>
       </c>
+      <c r="M304" s="1" t="n">
+        <v>4.735</v>
+      </c>
+      <c r="N304" s="2" t="n">
+        <v>0.0002112378538234757</v>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -12661,6 +14491,12 @@
       <c r="L305" s="3" t="n">
         <v>-0.001320007542900257</v>
       </c>
+      <c r="M305" s="1" t="n">
+        <v>0.053</v>
+      </c>
+      <c r="N305" s="2" t="n">
+        <v>0.0007552870090634133</v>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -12701,6 +14537,12 @@
       <c r="L306" s="2" t="n">
         <v>0.002061855670103009</v>
       </c>
+      <c r="M306" s="1" t="n">
+        <v>0.0584</v>
+      </c>
+      <c r="N306" s="2" t="n">
+        <v>0.001371742112482916</v>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -12741,6 +14583,12 @@
       <c r="L307" s="2" t="n">
         <v>0.001140901312036383</v>
       </c>
+      <c r="M307" s="1" t="n">
+        <v>0.1754</v>
+      </c>
+      <c r="N307" s="3" t="n">
+        <v>-0.0005698005698005071</v>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -12781,6 +14629,12 @@
       <c r="L308" s="2" t="n">
         <v>0.001623376623376698</v>
       </c>
+      <c r="M308" s="1" t="n">
+        <v>0.0495</v>
+      </c>
+      <c r="N308" s="2" t="n">
+        <v>0.002836304700162099</v>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -12821,6 +14675,12 @@
       <c r="L309" s="2" t="n">
         <v>0.001295816364309578</v>
       </c>
+      <c r="M309" s="1" t="n">
+        <v>0.5431</v>
+      </c>
+      <c r="N309" s="2" t="n">
+        <v>0.004067295248659604</v>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -12861,6 +14721,12 @@
       <c r="L310" s="2" t="n">
         <v>0.00411522633744857</v>
       </c>
+      <c r="M310" s="1" t="n">
+        <v>0.00245</v>
+      </c>
+      <c r="N310" s="2" t="n">
+        <v>0.004098360655737716</v>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -12901,6 +14767,12 @@
       <c r="L311" s="2" t="n">
         <v>0.001120605126768604</v>
       </c>
+      <c r="M311" s="1" t="n">
+        <v>0.07083</v>
+      </c>
+      <c r="N311" s="3" t="n">
+        <v>-0.008954806212396832</v>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -12941,6 +14813,12 @@
       <c r="L312" s="2" t="n">
         <v>0.001443001443001538</v>
       </c>
+      <c r="M312" s="1" t="n">
+        <v>0.009032999999999999</v>
+      </c>
+      <c r="N312" s="2" t="n">
+        <v>0.00121924185324749</v>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -12981,6 +14859,12 @@
       <c r="L313" s="3" t="n">
         <v>-0.01024506188017377</v>
       </c>
+      <c r="M313" s="1" t="n">
+        <v>0.012058</v>
+      </c>
+      <c r="N313" s="3" t="n">
+        <v>-0.001490559788009329</v>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -13021,6 +14905,12 @@
       <c r="L314" s="3" t="n">
         <v>-0.006454388984509502</v>
       </c>
+      <c r="M314" s="1" t="n">
+        <v>0.02335</v>
+      </c>
+      <c r="N314" s="2" t="n">
+        <v>0.01126028583802511</v>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -13061,6 +14951,12 @@
       <c r="L315" s="2" t="n">
         <v>0.002820874471086044</v>
       </c>
+      <c r="M315" s="1" t="n">
+        <v>0.00711</v>
+      </c>
+      <c r="N315" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -13101,6 +14997,12 @@
       <c r="L316" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="M316" s="1" t="n">
+        <v>0.2617</v>
+      </c>
+      <c r="N316" s="2" t="n">
+        <v>0.001914241960183769</v>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -13141,6 +15043,12 @@
       <c r="L317" s="3" t="n">
         <v>-0.008928571428571343</v>
       </c>
+      <c r="M317" s="1" t="n">
+        <v>1.11e-05</v>
+      </c>
+      <c r="N317" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -13181,6 +15089,12 @@
       <c r="L318" s="3" t="n">
         <v>-0.004064886221175378</v>
       </c>
+      <c r="M318" s="1" t="n">
+        <v>0.05257</v>
+      </c>
+      <c r="N318" s="2" t="n">
+        <v>0.002631980469942005</v>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -13221,6 +15135,12 @@
       <c r="L319" s="2" t="n">
         <v>0.002361584885856726</v>
       </c>
+      <c r="M319" s="1" t="n">
+        <v>0.03821</v>
+      </c>
+      <c r="N319" s="2" t="n">
+        <v>0.000261780104712122</v>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -13261,6 +15181,12 @@
       <c r="L320" s="2" t="n">
         <v>0.001470804530077893</v>
       </c>
+      <c r="M320" s="1" t="n">
+        <v>0.006824</v>
+      </c>
+      <c r="N320" s="2" t="n">
+        <v>0.002202966661771223</v>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -13301,6 +15227,12 @@
       <c r="L321" s="2" t="n">
         <v>0.004654255319149113</v>
       </c>
+      <c r="M321" s="1" t="n">
+        <v>4.542</v>
+      </c>
+      <c r="N321" s="2" t="n">
+        <v>0.001985440105890018</v>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -13341,6 +15273,12 @@
       <c r="L322" s="2" t="n">
         <v>0.0005241090146751111</v>
       </c>
+      <c r="M322" s="1" t="n">
+        <v>1.923</v>
+      </c>
+      <c r="N322" s="2" t="n">
+        <v>0.007333682556312212</v>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -13381,6 +15319,12 @@
       <c r="L323" s="2" t="n">
         <v>0.0008488964346350873</v>
       </c>
+      <c r="M323" s="1" t="n">
+        <v>0.007066</v>
+      </c>
+      <c r="N323" s="3" t="n">
+        <v>-0.0011309018942607</v>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -13421,6 +15365,12 @@
       <c r="L324" s="2" t="n">
         <v>0.003289473684210583</v>
       </c>
+      <c r="M324" s="1" t="n">
+        <v>0.01842</v>
+      </c>
+      <c r="N324" s="2" t="n">
+        <v>0.00655737704918025</v>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -13461,6 +15411,12 @@
       <c r="L325" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="M325" s="1" t="n">
+        <v>0.411</v>
+      </c>
+      <c r="N325" s="2" t="n">
+        <v>0.002928257686676376</v>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -13501,6 +15457,12 @@
       <c r="L326" s="2" t="n">
         <v>0.004713057942888852</v>
       </c>
+      <c r="M326" s="1" t="n">
+        <v>0.00723</v>
+      </c>
+      <c r="N326" s="3" t="n">
+        <v>-0.002483443708609242</v>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -13541,6 +15503,12 @@
       <c r="L327" s="3" t="n">
         <v>-0.006799163179916295</v>
       </c>
+      <c r="M327" s="1" t="n">
+        <v>0.1888</v>
+      </c>
+      <c r="N327" s="3" t="n">
+        <v>-0.005792522380200198</v>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -13581,6 +15549,12 @@
       <c r="L328" s="3" t="n">
         <v>-0.003369839932603181</v>
       </c>
+      <c r="M328" s="1" t="n">
+        <v>0.4723</v>
+      </c>
+      <c r="N328" s="3" t="n">
+        <v>-0.001901944209636543</v>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -13621,6 +15595,12 @@
       <c r="L329" s="3" t="n">
         <v>-0.005865102639296203</v>
       </c>
+      <c r="M329" s="1" t="n">
+        <v>0.01353</v>
+      </c>
+      <c r="N329" s="3" t="n">
+        <v>-0.002212389380530884</v>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -13661,6 +15641,12 @@
       <c r="L330" s="2" t="n">
         <v>0.001763668430335147</v>
       </c>
+      <c r="M330" s="1" t="n">
+        <v>0.1139</v>
+      </c>
+      <c r="N330" s="2" t="n">
+        <v>0.002640845070422488</v>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -13701,6 +15687,12 @@
       <c r="L331" s="2" t="n">
         <v>0.001000500250124952</v>
       </c>
+      <c r="M331" s="1" t="n">
+        <v>0.6061</v>
+      </c>
+      <c r="N331" s="2" t="n">
+        <v>0.009661835748792317</v>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -13741,6 +15733,12 @@
       <c r="L332" s="2" t="n">
         <v>0.008553340517241334</v>
       </c>
+      <c r="M332" s="1" t="n">
+        <v>0.30234</v>
+      </c>
+      <c r="N332" s="2" t="n">
+        <v>0.0094824707846411</v>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -13781,6 +15779,12 @@
       <c r="L333" s="2" t="n">
         <v>0.005147269087789523</v>
       </c>
+      <c r="M333" s="1" t="n">
+        <v>0.0706</v>
+      </c>
+      <c r="N333" s="2" t="n">
+        <v>0.004267425320056824</v>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -13821,6 +15825,12 @@
       <c r="L334" s="3" t="n">
         <v>-0.003971143027334631</v>
       </c>
+      <c r="M334" s="1" t="n">
+        <v>0.15458</v>
+      </c>
+      <c r="N334" s="2" t="n">
+        <v>0.02717788557379216</v>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -13861,6 +15871,12 @@
       <c r="L335" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="M335" s="1" t="n">
+        <v>0.1566</v>
+      </c>
+      <c r="N335" s="2" t="n">
+        <v>0.001278772378516483</v>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -13901,6 +15917,12 @@
       <c r="L336" s="2" t="n">
         <v>0.0005750431282345543</v>
       </c>
+      <c r="M336" s="1" t="n">
+        <v>0.1747</v>
+      </c>
+      <c r="N336" s="2" t="n">
+        <v>0.004022988505747162</v>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -13941,6 +15963,12 @@
       <c r="L337" s="2" t="n">
         <v>0.00678221552373774</v>
       </c>
+      <c r="M337" s="1" t="n">
+        <v>0.04008</v>
+      </c>
+      <c r="N337" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -13981,6 +16009,12 @@
       <c r="L338" s="2" t="n">
         <v>0.0001888574126534717</v>
       </c>
+      <c r="M338" s="1" t="n">
+        <v>0.005292</v>
+      </c>
+      <c r="N338" s="3" t="n">
+        <v>-0.0007552870090635443</v>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -14021,6 +16055,12 @@
       <c r="L339" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="M339" s="1" t="n">
+        <v>0.05175</v>
+      </c>
+      <c r="N339" s="2" t="n">
+        <v>0.006809338521400703</v>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -14061,6 +16101,12 @@
       <c r="L340" s="2" t="n">
         <v>0.002518223989396895</v>
       </c>
+      <c r="M340" s="1" t="n">
+        <v>0.15154</v>
+      </c>
+      <c r="N340" s="2" t="n">
+        <v>0.001718667371761041</v>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -14101,6 +16147,12 @@
       <c r="L341" s="2" t="n">
         <v>0.001317002502304726</v>
       </c>
+      <c r="M341" s="1" t="n">
+        <v>7.605</v>
+      </c>
+      <c r="N341" s="2" t="n">
+        <v>0.0002630540576089265</v>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -14141,6 +16193,12 @@
       <c r="L342" s="3" t="n">
         <v>-0.01583507618763063</v>
       </c>
+      <c r="M342" s="1" t="n">
+        <v>0.3293</v>
+      </c>
+      <c r="N342" s="3" t="n">
+        <v>-0.0003035822707955206</v>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -14181,6 +16239,12 @@
       <c r="L343" s="2" t="n">
         <v>0.001515917129863681</v>
       </c>
+      <c r="M343" s="1" t="n">
+        <v>0.01985</v>
+      </c>
+      <c r="N343" s="2" t="n">
+        <v>0.001513622603430816</v>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -14221,6 +16285,12 @@
       <c r="L344" s="2" t="n">
         <v>0.002272727272727224</v>
       </c>
+      <c r="M344" s="1" t="n">
+        <v>2.206</v>
+      </c>
+      <c r="N344" s="2" t="n">
+        <v>0.000453514739228975</v>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -14261,6 +16331,12 @@
       <c r="L345" s="2" t="n">
         <v>0.0007867820613690889</v>
       </c>
+      <c r="M345" s="1" t="n">
+        <v>1.273</v>
+      </c>
+      <c r="N345" s="2" t="n">
+        <v>0.000786163522012492</v>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -14301,6 +16377,12 @@
       <c r="L346" s="2" t="n">
         <v>0.001739130434782672</v>
       </c>
+      <c r="M346" s="1" t="n">
+        <v>0.00518</v>
+      </c>
+      <c r="N346" s="3" t="n">
+        <v>-0.0007716049382717074</v>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -14341,6 +16423,12 @@
       <c r="L347" s="3" t="n">
         <v>-0.0001746114894360584</v>
       </c>
+      <c r="M347" s="1" t="n">
+        <v>0.05732</v>
+      </c>
+      <c r="N347" s="2" t="n">
+        <v>0.001047851903597703</v>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -14381,6 +16469,12 @@
       <c r="L348" s="3" t="n">
         <v>-0.001571091908876714</v>
       </c>
+      <c r="M348" s="1" t="n">
+        <v>0.1273</v>
+      </c>
+      <c r="N348" s="2" t="n">
+        <v>0.001573564122738047</v>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -14421,6 +16515,12 @@
       <c r="L349" s="2" t="n">
         <v>0.001786057230651082</v>
       </c>
+      <c r="M349" s="1" t="n">
+        <v>5211.8</v>
+      </c>
+      <c r="N349" s="3" t="n">
+        <v>-0.0008626804439928685</v>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -14461,6 +16561,12 @@
       <c r="L350" s="2" t="n">
         <v>0.001063075832742815</v>
       </c>
+      <c r="M350" s="1" t="n">
+        <v>0.02824</v>
+      </c>
+      <c r="N350" s="3" t="n">
+        <v>-0.0003539823008849413</v>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -14501,6 +16607,12 @@
       <c r="L351" s="2" t="n">
         <v>0.003687315634218299</v>
       </c>
+      <c r="M351" s="1" t="n">
+        <v>0.00138</v>
+      </c>
+      <c r="N351" s="2" t="n">
+        <v>0.01396032329169722</v>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -14541,6 +16653,12 @@
       <c r="L352" s="2" t="n">
         <v>0.01778907242693768</v>
       </c>
+      <c r="M352" s="1" t="n">
+        <v>0.01587</v>
+      </c>
+      <c r="N352" s="3" t="n">
+        <v>-0.009363295880149865</v>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -14581,6 +16699,12 @@
       <c r="L353" s="2" t="n">
         <v>0.008326661329063187</v>
       </c>
+      <c r="M353" s="1" t="n">
+        <v>6.304</v>
+      </c>
+      <c r="N353" s="2" t="n">
+        <v>0.001111640463712968</v>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -14621,6 +16745,12 @@
       <c r="L354" s="2" t="n">
         <v>0.0003496503496505053</v>
       </c>
+      <c r="M354" s="1" t="n">
+        <v>0.2868</v>
+      </c>
+      <c r="N354" s="2" t="n">
+        <v>0.002446696959105132</v>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -14661,6 +16791,12 @@
       <c r="L355" s="2" t="n">
         <v>0.007035419699175123</v>
       </c>
+      <c r="M355" s="1" t="n">
+        <v>0.04151</v>
+      </c>
+      <c r="N355" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -14701,6 +16837,12 @@
       <c r="L356" s="3" t="n">
         <v>-0.01383755908895574</v>
       </c>
+      <c r="M356" s="1" t="n">
+        <v>0.11458</v>
+      </c>
+      <c r="N356" s="3" t="n">
+        <v>-0.001394457033292605</v>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -14741,6 +16883,12 @@
       <c r="L357" s="2" t="n">
         <v>0.001340996168582387</v>
       </c>
+      <c r="M357" s="1" t="n">
+        <v>0.005208</v>
+      </c>
+      <c r="N357" s="3" t="n">
+        <v>-0.003634972259422215</v>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -14781,6 +16929,12 @@
       <c r="L358" s="2" t="n">
         <v>0.003779697624190098</v>
       </c>
+      <c r="M358" s="1" t="n">
+        <v>0.1864</v>
+      </c>
+      <c r="N358" s="2" t="n">
+        <v>0.002689618074233461</v>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -14821,6 +16975,12 @@
       <c r="L359" s="3" t="n">
         <v>-0.001843884449907944</v>
       </c>
+      <c r="M359" s="1" t="n">
+        <v>0.1625</v>
+      </c>
+      <c r="N359" s="2" t="n">
+        <v>0.0006157635467981327</v>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -14861,6 +17021,12 @@
       <c r="L360" s="3" t="n">
         <v>-0.002003535651148964</v>
       </c>
+      <c r="M360" s="1" t="n">
+        <v>0.08452</v>
+      </c>
+      <c r="N360" s="3" t="n">
+        <v>-0.001889466225791301</v>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -14901,6 +17067,12 @@
       <c r="L361" s="2" t="n">
         <v>0.00253164556962015</v>
       </c>
+      <c r="M361" s="1" t="n">
+        <v>0.007990000000000001</v>
+      </c>
+      <c r="N361" s="2" t="n">
+        <v>0.008838383838383916</v>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -14941,6 +17113,12 @@
       <c r="L362" s="2" t="n">
         <v>0.008064516129032293</v>
       </c>
+      <c r="M362" s="1" t="n">
+        <v>0.4257</v>
+      </c>
+      <c r="N362" s="2" t="n">
+        <v>0.001647058823529492</v>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -14981,6 +17159,12 @@
       <c r="L363" s="2" t="n">
         <v>0.01472556894243645</v>
       </c>
+      <c r="M363" s="1" t="n">
+        <v>3.798</v>
+      </c>
+      <c r="N363" s="2" t="n">
+        <v>0.002110817941952508</v>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -15021,6 +17205,12 @@
       <c r="L364" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="M364" s="1" t="n">
+        <v>0.01096</v>
+      </c>
+      <c r="N364" s="2" t="n">
+        <v>0.001828153564899377</v>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -15061,6 +17251,12 @@
       <c r="L365" s="3" t="n">
         <v>-0.003450154349010399</v>
       </c>
+      <c r="M365" s="1" t="n">
+        <v>0.05503</v>
+      </c>
+      <c r="N365" s="2" t="n">
+        <v>0.002733236151603577</v>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -15101,6 +17297,12 @@
       <c r="L366" s="2" t="n">
         <v>0.008783487044356709</v>
       </c>
+      <c r="M366" s="1" t="n">
+        <v>0.02253</v>
+      </c>
+      <c r="N366" s="3" t="n">
+        <v>-0.01915542011319109</v>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -15141,6 +17343,12 @@
       <c r="L367" s="2" t="n">
         <v>0.007369196757553447</v>
       </c>
+      <c r="M367" s="1" t="n">
+        <v>0.001366</v>
+      </c>
+      <c r="N367" s="3" t="n">
+        <v>-0.0007315288953913064</v>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -15181,6 +17389,12 @@
       <c r="L368" s="3" t="n">
         <v>-0.0006978367062108635</v>
       </c>
+      <c r="M368" s="1" t="n">
+        <v>0.2869</v>
+      </c>
+      <c r="N368" s="2" t="n">
+        <v>0.001745810055865923</v>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -15221,6 +17435,12 @@
       <c r="L369" s="2" t="n">
         <v>0.001625135427952263</v>
       </c>
+      <c r="M369" s="1" t="n">
+        <v>0.01856</v>
+      </c>
+      <c r="N369" s="2" t="n">
+        <v>0.003785830178474885</v>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -15261,6 +17481,12 @@
       <c r="L370" s="3" t="n">
         <v>-0.0007017192120695767</v>
       </c>
+      <c r="M370" s="1" t="n">
+        <v>0.19829</v>
+      </c>
+      <c r="N370" s="3" t="n">
+        <v>-0.005417063750815056</v>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -15301,6 +17527,12 @@
       <c r="L371" s="3" t="n">
         <v>-0.01315789473684212</v>
       </c>
+      <c r="M371" s="1" t="n">
+        <v>0.076</v>
+      </c>
+      <c r="N371" s="2" t="n">
+        <v>0.01333333333333335</v>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -15341,6 +17573,12 @@
       <c r="L372" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="M372" s="1" t="n">
+        <v>0.1056</v>
+      </c>
+      <c r="N372" s="2" t="n">
+        <v>0.00475737392959087</v>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -15381,6 +17619,12 @@
       <c r="L373" s="2" t="n">
         <v>0.004711962304301637</v>
       </c>
+      <c r="M373" s="1" t="n">
+        <v>0.06669</v>
+      </c>
+      <c r="N373" s="2" t="n">
+        <v>0.008925869894099747</v>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -15421,6 +17665,12 @@
       <c r="L374" s="2" t="n">
         <v>0.00263991552270328</v>
       </c>
+      <c r="M374" s="1" t="n">
+        <v>0.007596</v>
+      </c>
+      <c r="N374" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -15461,6 +17711,12 @@
       <c r="L375" s="2" t="n">
         <v>0.002517306482064089</v>
       </c>
+      <c r="M375" s="1" t="n">
+        <v>0.1595</v>
+      </c>
+      <c r="N375" s="2" t="n">
+        <v>0.001255492780916546</v>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -15501,6 +17757,12 @@
       <c r="L376" s="2" t="n">
         <v>0.006169212690951876</v>
       </c>
+      <c r="M376" s="1" t="n">
+        <v>0.003435</v>
+      </c>
+      <c r="N376" s="2" t="n">
+        <v>0.002919708029197088</v>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -15541,6 +17803,12 @@
       <c r="L377" s="2" t="n">
         <v>0.00628930817610059</v>
       </c>
+      <c r="M377" s="1" t="n">
+        <v>0.0161</v>
+      </c>
+      <c r="N377" s="2" t="n">
+        <v>0.006249999999999962</v>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -15581,6 +17849,12 @@
       <c r="L378" s="2" t="n">
         <v>0.0008960573476702144</v>
       </c>
+      <c r="M378" s="1" t="n">
+        <v>0.01123</v>
+      </c>
+      <c r="N378" s="2" t="n">
+        <v>0.005371530886302689</v>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -15621,6 +17895,12 @@
       <c r="L379" s="2" t="n">
         <v>0.00415320719889263</v>
       </c>
+      <c r="M379" s="1" t="n">
+        <v>0.02159</v>
+      </c>
+      <c r="N379" s="3" t="n">
+        <v>-0.0078125</v>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -15661,6 +17941,12 @@
       <c r="L380" s="2" t="n">
         <v>0.001598295151838159</v>
       </c>
+      <c r="M380" s="1" t="n">
+        <v>0.0189</v>
+      </c>
+      <c r="N380" s="2" t="n">
+        <v>0.005319148936170181</v>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -15701,6 +17987,12 @@
       <c r="L381" s="3" t="n">
         <v>-0.001666666666666599</v>
       </c>
+      <c r="M381" s="1" t="n">
+        <v>0.1203</v>
+      </c>
+      <c r="N381" s="2" t="n">
+        <v>0.004173622704507516</v>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -15741,6 +18033,12 @@
       <c r="L382" s="2" t="n">
         <v>0.003107734806629828</v>
       </c>
+      <c r="M382" s="1" t="n">
+        <v>0.02917</v>
+      </c>
+      <c r="N382" s="2" t="n">
+        <v>0.004130808950086129</v>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -15781,6 +18079,12 @@
       <c r="L383" s="2" t="n">
         <v>0.001378676470588285</v>
       </c>
+      <c r="M383" s="1" t="n">
+        <v>0.006532</v>
+      </c>
+      <c r="N383" s="3" t="n">
+        <v>-0.0007648768548264744</v>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -15821,6 +18125,12 @@
       <c r="L384" s="3" t="n">
         <v>-0.007173601147776223</v>
       </c>
+      <c r="M384" s="1" t="n">
+        <v>0.02089</v>
+      </c>
+      <c r="N384" s="2" t="n">
+        <v>0.006262042389209931</v>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -15861,6 +18171,12 @@
       <c r="L385" s="2" t="n">
         <v>0.002775574940523394</v>
       </c>
+      <c r="M385" s="1" t="n">
+        <v>2537</v>
+      </c>
+      <c r="N385" s="2" t="n">
+        <v>0.003163305654408857</v>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -15901,6 +18217,12 @@
       <c r="L386" s="3" t="n">
         <v>-0.002022244691607742</v>
       </c>
+      <c r="M386" s="1" t="n">
+        <v>0.1973</v>
+      </c>
+      <c r="N386" s="3" t="n">
+        <v>-0.0005065856129685359</v>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -15941,6 +18263,12 @@
       <c r="L387" s="2" t="n">
         <v>0.002825523899223029</v>
       </c>
+      <c r="M387" s="1" t="n">
+        <v>0.08519</v>
+      </c>
+      <c r="N387" s="2" t="n">
+        <v>0.00011739845034041</v>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -15981,6 +18309,12 @@
       <c r="L388" s="2" t="n">
         <v>0.002194732641659961</v>
       </c>
+      <c r="M388" s="1" t="n">
+        <v>0.005024</v>
+      </c>
+      <c r="N388" s="2" t="n">
+        <v>0.0001990842126219655</v>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -16021,6 +18355,12 @@
       <c r="L389" s="2" t="n">
         <v>0.01127649977447001</v>
       </c>
+      <c r="M389" s="1" t="n">
+        <v>0.02246</v>
+      </c>
+      <c r="N389" s="2" t="n">
+        <v>0.001784121320249859</v>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -16061,6 +18401,12 @@
       <c r="L390" s="3" t="n">
         <v>-0.002159403219473871</v>
       </c>
+      <c r="M390" s="1" t="n">
+        <v>0.5044999999999999</v>
+      </c>
+      <c r="N390" s="3" t="n">
+        <v>-0.007475900059020314</v>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -16101,6 +18447,12 @@
       <c r="L391" s="2" t="n">
         <v>0.00200501253132837</v>
       </c>
+      <c r="M391" s="1" t="n">
+        <v>0.0006036</v>
+      </c>
+      <c r="N391" s="2" t="n">
+        <v>0.006503251625812974</v>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -16141,6 +18493,12 @@
       <c r="L392" s="2" t="n">
         <v>0.001370332305584048</v>
       </c>
+      <c r="M392" s="1" t="n">
+        <v>0.05861</v>
+      </c>
+      <c r="N392" s="2" t="n">
+        <v>0.002565856996236817</v>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -16181,6 +18539,12 @@
       <c r="L393" s="2" t="n">
         <v>0.0003748125937033152</v>
       </c>
+      <c r="M393" s="1" t="n">
+        <v>0.2676</v>
+      </c>
+      <c r="N393" s="2" t="n">
+        <v>0.002622705133008536</v>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -16221,6 +18585,12 @@
       <c r="L394" s="3" t="n">
         <v>-0.005643685173886604</v>
       </c>
+      <c r="M394" s="1" t="n">
+        <v>0.00656</v>
+      </c>
+      <c r="N394" s="2" t="n">
+        <v>0.006289308176100666</v>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -16261,6 +18631,12 @@
       <c r="L395" s="2" t="n">
         <v>0.0008688097306690084</v>
       </c>
+      <c r="M395" s="1" t="n">
+        <v>0.1153</v>
+      </c>
+      <c r="N395" s="2" t="n">
+        <v>0.0008680555555555804</v>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -16301,6 +18677,12 @@
       <c r="L396" s="3" t="n">
         <v>-0.001296596434359753</v>
       </c>
+      <c r="M396" s="1" t="n">
+        <v>0.03086</v>
+      </c>
+      <c r="N396" s="2" t="n">
+        <v>0.001622849724115481</v>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -16341,6 +18723,12 @@
       <c r="L397" s="3" t="n">
         <v>-0.001324503311258316</v>
       </c>
+      <c r="M397" s="1" t="n">
+        <v>0.1508</v>
+      </c>
+      <c r="N397" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -16381,6 +18769,12 @@
       <c r="L398" s="2" t="n">
         <v>0.0003029385034837016</v>
       </c>
+      <c r="M398" s="1" t="n">
+        <v>0.003311</v>
+      </c>
+      <c r="N398" s="2" t="n">
+        <v>0.002725620835857155</v>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -16421,6 +18815,12 @@
       <c r="L399" s="2" t="n">
         <v>0.001604278074866245</v>
       </c>
+      <c r="M399" s="1" t="n">
+        <v>0.01874</v>
+      </c>
+      <c r="N399" s="2" t="n">
+        <v>0.0005339028296849756</v>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -16461,6 +18861,12 @@
       <c r="L400" s="3" t="n">
         <v>-0.003682197988953403</v>
       </c>
+      <c r="M400" s="1" t="n">
+        <v>0.007052</v>
+      </c>
+      <c r="N400" s="2" t="n">
+        <v>0.002416488983653237</v>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -16501,6 +18907,12 @@
       <c r="L401" s="3" t="n">
         <v>-0.002157652474108207</v>
       </c>
+      <c r="M401" s="1" t="n">
+        <v>0.007022</v>
+      </c>
+      <c r="N401" s="2" t="n">
+        <v>0.01225313536110711</v>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -16541,6 +18953,12 @@
       <c r="L402" s="3" t="n">
         <v>-0.002246910498065242</v>
       </c>
+      <c r="M402" s="1" t="n">
+        <v>0.008030000000000001</v>
+      </c>
+      <c r="N402" s="2" t="n">
+        <v>0.004629050419116799</v>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -16581,6 +18999,12 @@
       <c r="L403" s="3" t="n">
         <v>-0.0008136696501221584</v>
       </c>
+      <c r="M403" s="1" t="n">
+        <v>0.04919</v>
+      </c>
+      <c r="N403" s="2" t="n">
+        <v>0.001425081433224768</v>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -16621,6 +19045,12 @@
       <c r="L404" s="2" t="n">
         <v>0.01045319665497704</v>
       </c>
+      <c r="M404" s="1" t="n">
+        <v>0.14927</v>
+      </c>
+      <c r="N404" s="3" t="n">
+        <v>-0.003737569245144345</v>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -16661,6 +19091,12 @@
       <c r="L405" s="3" t="n">
         <v>-0.002344665885111439</v>
       </c>
+      <c r="M405" s="1" t="n">
+        <v>0.04331</v>
+      </c>
+      <c r="N405" s="2" t="n">
+        <v>0.01786133960047013</v>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -16701,6 +19137,12 @@
       <c r="L406" s="3" t="n">
         <v>-0.000417798203467795</v>
       </c>
+      <c r="M406" s="1" t="n">
+        <v>0.4802</v>
+      </c>
+      <c r="N406" s="2" t="n">
+        <v>0.003552769070010522</v>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -16741,6 +19183,12 @@
       <c r="L407" s="2" t="n">
         <v>0.00329557157569524</v>
       </c>
+      <c r="M407" s="1" t="n">
+        <v>0.0004908</v>
+      </c>
+      <c r="N407" s="2" t="n">
+        <v>0.007595976185588137</v>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -16781,6 +19229,12 @@
       <c r="L408" s="2" t="n">
         <v>0.0008116883116884195</v>
       </c>
+      <c r="M408" s="1" t="n">
+        <v>0.01233</v>
+      </c>
+      <c r="N408" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -16821,6 +19275,12 @@
       <c r="L409" s="2" t="n">
         <v>0.006289308176100634</v>
       </c>
+      <c r="M409" s="1" t="n">
+        <v>0.3185</v>
+      </c>
+      <c r="N409" s="3" t="n">
+        <v>-0.004687500000000004</v>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -16861,6 +19321,12 @@
       <c r="L410" s="2" t="n">
         <v>0.001923539312334617</v>
       </c>
+      <c r="M410" s="1" t="n">
+        <v>0.04176</v>
+      </c>
+      <c r="N410" s="2" t="n">
+        <v>0.00215982721382289</v>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -16901,6 +19367,12 @@
       <c r="L411" s="3" t="n">
         <v>-0.001677852348993337</v>
       </c>
+      <c r="M411" s="1" t="n">
+        <v>0.0298</v>
+      </c>
+      <c r="N411" s="2" t="n">
+        <v>0.001680672268907611</v>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
@@ -16941,6 +19413,12 @@
       <c r="L412" s="2" t="n">
         <v>0.002845261545195883</v>
       </c>
+      <c r="M412" s="1" t="n">
+        <v>0.004585</v>
+      </c>
+      <c r="N412" s="2" t="n">
+        <v>0.0006547359231775493</v>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -16981,6 +19459,12 @@
       <c r="L413" s="3" t="n">
         <v>-0.003169572107765542</v>
       </c>
+      <c r="M413" s="1" t="n">
+        <v>0.2519</v>
+      </c>
+      <c r="N413" s="2" t="n">
+        <v>0.001192368839427752</v>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -17021,6 +19505,12 @@
       <c r="L414" s="3" t="n">
         <v>-0.00155884645362432</v>
       </c>
+      <c r="M414" s="1" t="n">
+        <v>1.281</v>
+      </c>
+      <c r="N414" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -17061,6 +19551,12 @@
       <c r="L415" s="2" t="n">
         <v>0.002583025830258346</v>
       </c>
+      <c r="M415" s="1" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="N415" s="2" t="n">
+        <v>0.00846521899153483</v>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -17101,6 +19597,12 @@
       <c r="L416" s="3" t="n">
         <v>-0.0006209251785159634</v>
       </c>
+      <c r="M416" s="1" t="n">
+        <v>0.03219</v>
+      </c>
+      <c r="N416" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -17141,6 +19643,12 @@
       <c r="L417" s="2" t="n">
         <v>0.004254254254254167</v>
       </c>
+      <c r="M417" s="1" t="n">
+        <v>0.04011</v>
+      </c>
+      <c r="N417" s="3" t="n">
+        <v>-0.0004983802641415197</v>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -17181,6 +19689,12 @@
       <c r="L418" s="2" t="n">
         <v>0.001185770750988231</v>
       </c>
+      <c r="M418" s="1" t="n">
+        <v>0.07624</v>
+      </c>
+      <c r="N418" s="2" t="n">
+        <v>0.00328990656665351</v>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -17221,6 +19735,12 @@
       <c r="L419" s="2" t="n">
         <v>0.00150375939849631</v>
       </c>
+      <c r="M419" s="1" t="n">
+        <v>0.00667</v>
+      </c>
+      <c r="N419" s="2" t="n">
+        <v>0.00150150150150144</v>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -17261,6 +19781,12 @@
       <c r="L420" s="2" t="n">
         <v>0.001129943502824891</v>
       </c>
+      <c r="M420" s="1" t="n">
+        <v>0.0888</v>
+      </c>
+      <c r="N420" s="2" t="n">
+        <v>0.002257336343115189</v>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -17301,6 +19827,12 @@
       <c r="L421" s="2" t="n">
         <v>0.00370981038746902</v>
       </c>
+      <c r="M421" s="1" t="n">
+        <v>0.2439</v>
+      </c>
+      <c r="N421" s="2" t="n">
+        <v>0.001642710472279308</v>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
@@ -17341,6 +19873,12 @@
       <c r="L422" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="M422" s="1" t="n">
+        <v>0.0196</v>
+      </c>
+      <c r="N422" s="2" t="n">
+        <v>0.0103092783505154</v>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -17381,6 +19919,12 @@
       <c r="L423" s="2" t="n">
         <v>0.001328903654485088</v>
       </c>
+      <c r="M423" s="1" t="n">
+        <v>0.1509</v>
+      </c>
+      <c r="N423" s="2" t="n">
+        <v>0.001327140013271438</v>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -17421,6 +19965,12 @@
       <c r="L424" s="3" t="n">
         <v>-0.00381861575178994</v>
       </c>
+      <c r="M424" s="1" t="n">
+        <v>0.0002096</v>
+      </c>
+      <c r="N424" s="2" t="n">
+        <v>0.004312410158121681</v>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -17461,6 +20011,12 @@
       <c r="L425" s="2" t="n">
         <v>0.0008090614886732297</v>
       </c>
+      <c r="M425" s="1" t="n">
+        <v>1.241</v>
+      </c>
+      <c r="N425" s="2" t="n">
+        <v>0.003233629749393697</v>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
@@ -17501,6 +20057,12 @@
       <c r="L426" s="2" t="n">
         <v>0.0007102272727273522</v>
       </c>
+      <c r="M426" s="1" t="n">
+        <v>1.411</v>
+      </c>
+      <c r="N426" s="2" t="n">
+        <v>0.001419446415897801</v>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -17541,6 +20103,12 @@
       <c r="L427" s="2" t="n">
         <v>0.001030396702730509</v>
       </c>
+      <c r="M427" s="1" t="n">
+        <v>0.01945</v>
+      </c>
+      <c r="N427" s="2" t="n">
+        <v>0.0010293360782295</v>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
@@ -17581,6 +20149,12 @@
       <c r="L428" s="2" t="n">
         <v>0.0003039051815834391</v>
       </c>
+      <c r="M428" s="1" t="n">
+        <v>0.06597</v>
+      </c>
+      <c r="N428" s="2" t="n">
+        <v>0.002126689958985284</v>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
@@ -17621,6 +20195,12 @@
       <c r="L429" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="M429" s="1" t="n">
+        <v>0.1329</v>
+      </c>
+      <c r="N429" s="2" t="n">
+        <v>0.00150715900527489</v>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
@@ -17661,6 +20241,12 @@
       <c r="L430" s="2" t="n">
         <v>0.0002698327037238052</v>
       </c>
+      <c r="M430" s="1" t="n">
+        <v>0.01112</v>
+      </c>
+      <c r="N430" s="3" t="n">
+        <v>-8.991997122569913e-05</v>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -17701,6 +20287,12 @@
       <c r="L431" s="3" t="n">
         <v>-0.001048061086989079</v>
       </c>
+      <c r="M431" s="1" t="n">
+        <v>0.006694</v>
+      </c>
+      <c r="N431" s="2" t="n">
+        <v>0.003297362110311798</v>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
@@ -17741,6 +20333,12 @@
       <c r="L432" s="2" t="n">
         <v>0.0005688282138793606</v>
       </c>
+      <c r="M432" s="1" t="n">
+        <v>0.001765</v>
+      </c>
+      <c r="N432" s="2" t="n">
+        <v>0.00341102899374653</v>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
@@ -17781,6 +20379,12 @@
       <c r="L433" s="3" t="n">
         <v>-0.002186588921282773</v>
       </c>
+      <c r="M433" s="1" t="n">
+        <v>0.001366</v>
+      </c>
+      <c r="N433" s="3" t="n">
+        <v>-0.002191380569758922</v>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
@@ -17821,6 +20425,12 @@
       <c r="L434" s="2" t="n">
         <v>0.002450980392156922</v>
       </c>
+      <c r="M434" s="1" t="n">
+        <v>0.00041</v>
+      </c>
+      <c r="N434" s="2" t="n">
+        <v>0.002444987775061051</v>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
@@ -17861,6 +20471,12 @@
       <c r="L435" s="3" t="n">
         <v>-0.002448077074942784</v>
       </c>
+      <c r="M435" s="1" t="n">
+        <v>0.1269</v>
+      </c>
+      <c r="N435" s="2" t="n">
+        <v>0.004591513616212991</v>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -17901,6 +20517,12 @@
       <c r="L436" s="2" t="n">
         <v>0.005166623611469873</v>
       </c>
+      <c r="M436" s="1" t="n">
+        <v>0.07807</v>
+      </c>
+      <c r="N436" s="2" t="n">
+        <v>0.003212541763042922</v>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
@@ -17941,6 +20563,12 @@
       <c r="L437" s="3" t="n">
         <v>-0.002989301447451247</v>
       </c>
+      <c r="M437" s="1" t="n">
+        <v>0.6358</v>
+      </c>
+      <c r="N437" s="2" t="n">
+        <v>0.003313870916837605</v>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -17981,6 +20609,12 @@
       <c r="L438" s="3" t="n">
         <v>-0.001608455882352955</v>
       </c>
+      <c r="M438" s="1" t="n">
+        <v>0.04368</v>
+      </c>
+      <c r="N438" s="2" t="n">
+        <v>0.005293440736478575</v>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
@@ -18021,6 +20655,12 @@
       <c r="L439" s="2" t="n">
         <v>0.001992315355059076</v>
       </c>
+      <c r="M439" s="1" t="n">
+        <v>0.07063</v>
+      </c>
+      <c r="N439" s="2" t="n">
+        <v>0.003124556170998409</v>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
@@ -18061,6 +20701,12 @@
       <c r="L440" s="2" t="n">
         <v>0.0006596306068601029</v>
       </c>
+      <c r="M440" s="1" t="n">
+        <v>0.001522</v>
+      </c>
+      <c r="N440" s="2" t="n">
+        <v>0.003295978905735012</v>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -18101,6 +20747,12 @@
       <c r="L441" s="3" t="n">
         <v>-0.00105285323225938</v>
       </c>
+      <c r="M441" s="1" t="n">
+        <v>0.009501000000000001</v>
+      </c>
+      <c r="N441" s="2" t="n">
+        <v>0.001370151770657763</v>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
@@ -18141,6 +20793,12 @@
       <c r="L442" s="2" t="n">
         <v>0.004734848484848383</v>
       </c>
+      <c r="M442" s="1" t="n">
+        <v>1.062</v>
+      </c>
+      <c r="N442" s="2" t="n">
+        <v>0.0009425070688031216</v>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
@@ -18181,6 +20839,12 @@
       <c r="L443" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="M443" s="1" t="n">
+        <v>0.02199</v>
+      </c>
+      <c r="N443" s="3" t="n">
+        <v>-0.00136239782016359</v>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
@@ -18221,6 +20885,12 @@
       <c r="L444" s="2" t="n">
         <v>0.008985200845666038</v>
       </c>
+      <c r="M444" s="1" t="n">
+        <v>0.0003813</v>
+      </c>
+      <c r="N444" s="3" t="n">
+        <v>-0.001309586170770068</v>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
@@ -18261,6 +20931,12 @@
       <c r="L445" s="2" t="n">
         <v>0.009656347628514628</v>
       </c>
+      <c r="M445" s="1" t="n">
+        <v>0.03558</v>
+      </c>
+      <c r="N445" s="2" t="n">
+        <v>0.0008438818565401476</v>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
@@ -18301,6 +20977,12 @@
       <c r="L446" s="2" t="n">
         <v>0.006682297772567422</v>
       </c>
+      <c r="M446" s="1" t="n">
+        <v>0.08548</v>
+      </c>
+      <c r="N446" s="3" t="n">
+        <v>-0.004541749155700494</v>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
@@ -18341,6 +21023,12 @@
       <c r="L447" s="2" t="n">
         <v>0.00307597662257774</v>
       </c>
+      <c r="M447" s="1" t="n">
+        <v>3.273</v>
+      </c>
+      <c r="N447" s="2" t="n">
+        <v>0.003679852805887767</v>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
@@ -18381,6 +21069,12 @@
       <c r="L448" s="2" t="n">
         <v>0.002661239824671095</v>
       </c>
+      <c r="M448" s="1" t="n">
+        <v>0.06407</v>
+      </c>
+      <c r="N448" s="2" t="n">
+        <v>0.0003122560499610636</v>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
@@ -18421,6 +21115,12 @@
       <c r="L449" s="3" t="n">
         <v>-0.0004122861265717955</v>
       </c>
+      <c r="M449" s="1" t="n">
+        <v>0.488</v>
+      </c>
+      <c r="N449" s="2" t="n">
+        <v>0.006393070736234258</v>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
@@ -18461,6 +21161,12 @@
       <c r="L450" s="2" t="n">
         <v>0.005387931034482726</v>
       </c>
+      <c r="M450" s="1" t="n">
+        <v>0.03714</v>
+      </c>
+      <c r="N450" s="3" t="n">
+        <v>-0.004823151125401919</v>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -18501,6 +21207,12 @@
       <c r="L451" s="2" t="n">
         <v>0.001834862385321026</v>
       </c>
+      <c r="M451" s="1" t="n">
+        <v>0.00548</v>
+      </c>
+      <c r="N451" s="2" t="n">
+        <v>0.003663003663003673</v>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
@@ -18541,6 +21253,12 @@
       <c r="L452" s="2" t="n">
         <v>0.0007647452442406139</v>
       </c>
+      <c r="M452" s="1" t="n">
+        <v>0.10444</v>
+      </c>
+      <c r="N452" s="3" t="n">
+        <v>-0.002388002674562998</v>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
@@ -18581,6 +21299,12 @@
       <c r="L453" s="2" t="n">
         <v>0.002503128911138821</v>
       </c>
+      <c r="M453" s="1" t="n">
+        <v>0.01606</v>
+      </c>
+      <c r="N453" s="2" t="n">
+        <v>0.002496878901373398</v>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
@@ -18621,6 +21345,12 @@
       <c r="L454" s="2" t="n">
         <v>0.01111883252258514</v>
       </c>
+      <c r="M454" s="1" t="n">
+        <v>2.838</v>
+      </c>
+      <c r="N454" s="3" t="n">
+        <v>-0.02474226804123713</v>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
@@ -18661,6 +21391,12 @@
       <c r="L455" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="M455" s="1" t="n">
+        <v>0.899</v>
+      </c>
+      <c r="N455" s="2" t="n">
+        <v>0.004469273743016764</v>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
@@ -18701,6 +21437,12 @@
       <c r="L456" s="2" t="n">
         <v>0.0003399048266485009</v>
       </c>
+      <c r="M456" s="1" t="n">
+        <v>2.957</v>
+      </c>
+      <c r="N456" s="2" t="n">
+        <v>0.00475705062861019</v>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -18741,6 +21483,12 @@
       <c r="L457" s="3" t="n">
         <v>-0.002024291497975626</v>
       </c>
+      <c r="M457" s="1" t="n">
+        <v>0.00988</v>
+      </c>
+      <c r="N457" s="2" t="n">
+        <v>0.002028397565922838</v>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
@@ -18781,6 +21529,12 @@
       <c r="L458" s="3" t="n">
         <v>-0.004332477535301659</v>
       </c>
+      <c r="M458" s="1" t="n">
+        <v>0.06214</v>
+      </c>
+      <c r="N458" s="2" t="n">
+        <v>0.001450443190975017</v>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
@@ -18821,6 +21575,12 @@
       <c r="L459" s="2" t="n">
         <v>0.003511235955056281</v>
       </c>
+      <c r="M459" s="1" t="n">
+        <v>0.01433</v>
+      </c>
+      <c r="N459" s="2" t="n">
+        <v>0.00279916025192443</v>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
@@ -18861,6 +21621,12 @@
       <c r="L460" s="2" t="n">
         <v>0.001878992859827056</v>
       </c>
+      <c r="M460" s="1" t="n">
+        <v>0.01599</v>
+      </c>
+      <c r="N460" s="3" t="n">
+        <v>-0.0003750937734433022</v>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
@@ -18901,6 +21667,12 @@
       <c r="L461" s="2" t="n">
         <v>0.005418422636965671</v>
       </c>
+      <c r="M461" s="1" t="n">
+        <v>0.01669</v>
+      </c>
+      <c r="N461" s="3" t="n">
+        <v>-0.0005988023952095564</v>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
@@ -18941,6 +21713,12 @@
       <c r="L462" s="2" t="n">
         <v>0.001433349259436251</v>
       </c>
+      <c r="M462" s="1" t="n">
+        <v>0.0002113</v>
+      </c>
+      <c r="N462" s="2" t="n">
+        <v>0.008110687022900831</v>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
@@ -18981,6 +21759,12 @@
       <c r="L463" s="2" t="n">
         <v>0.008097165991902786</v>
       </c>
+      <c r="M463" s="1" t="n">
+        <v>0.0988</v>
+      </c>
+      <c r="N463" s="3" t="n">
+        <v>-0.008032128514056177</v>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
@@ -19021,6 +21805,12 @@
       <c r="L464" s="2" t="n">
         <v>0.004211332312404249</v>
       </c>
+      <c r="M464" s="1" t="n">
+        <v>0.0262</v>
+      </c>
+      <c r="N464" s="3" t="n">
+        <v>-0.001143728555089545</v>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
@@ -19061,6 +21851,12 @@
       <c r="L465" s="2" t="n">
         <v>0.005287508261731673</v>
       </c>
+      <c r="M465" s="1" t="n">
+        <v>0.01512</v>
+      </c>
+      <c r="N465" s="3" t="n">
+        <v>-0.005917159763313596</v>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
@@ -19101,6 +21897,12 @@
       <c r="L466" s="3" t="n">
         <v>-0.0007308605883427438</v>
       </c>
+      <c r="M466" s="1" t="n">
+        <v>0.05469</v>
+      </c>
+      <c r="N466" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
@@ -19141,6 +21943,12 @@
       <c r="L467" s="2" t="n">
         <v>0.005250875145857632</v>
       </c>
+      <c r="M467" s="1" t="n">
+        <v>0.03446</v>
+      </c>
+      <c r="N467" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
@@ -19181,6 +21989,12 @@
       <c r="L468" s="2" t="n">
         <v>0.003639010189228452</v>
       </c>
+      <c r="M468" s="1" t="n">
+        <v>27.56</v>
+      </c>
+      <c r="N468" s="3" t="n">
+        <v>-0.0007251631617113697</v>
+      </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
@@ -19221,6 +22035,12 @@
       <c r="L469" s="2" t="n">
         <v>0.003485254691688947</v>
       </c>
+      <c r="M469" s="1" t="n">
+        <v>0.0007468</v>
+      </c>
+      <c r="N469" s="3" t="n">
+        <v>-0.002404488378306085</v>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
@@ -19261,6 +22081,12 @@
       <c r="L470" s="3" t="n">
         <v>-0.002288329519450803</v>
       </c>
+      <c r="M470" s="1" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="N470" s="2" t="n">
+        <v>0.003440366972477067</v>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
@@ -19301,6 +22127,12 @@
       <c r="L471" s="2" t="n">
         <v>0.005076142131979841</v>
       </c>
+      <c r="M471" s="1" t="n">
+        <v>0.00991</v>
+      </c>
+      <c r="N471" s="2" t="n">
+        <v>0.001010101010100969</v>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
@@ -19341,6 +22173,12 @@
       <c r="L472" s="2" t="n">
         <v>0.001503759398496254</v>
       </c>
+      <c r="M472" s="1" t="n">
+        <v>0.04668</v>
+      </c>
+      <c r="N472" s="2" t="n">
+        <v>0.001287001287001234</v>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -19381,6 +22219,12 @@
       <c r="L473" s="2" t="n">
         <v>0.001464664957890924</v>
       </c>
+      <c r="M473" s="1" t="n">
+        <v>0.2748</v>
+      </c>
+      <c r="N473" s="2" t="n">
+        <v>0.004753199268738456</v>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
@@ -19421,6 +22265,12 @@
       <c r="L474" s="2" t="n">
         <v>0.0002288329519449914</v>
       </c>
+      <c r="M474" s="1" t="n">
+        <v>0.04376</v>
+      </c>
+      <c r="N474" s="2" t="n">
+        <v>0.001143902997025885</v>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
@@ -19461,6 +22311,12 @@
       <c r="L475" s="2" t="n">
         <v>0.002129169623846777</v>
       </c>
+      <c r="M475" s="1" t="n">
+        <v>0.008488000000000001</v>
+      </c>
+      <c r="N475" s="2" t="n">
+        <v>0.001888574126534512</v>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
@@ -19501,6 +22357,12 @@
       <c r="L476" s="2" t="n">
         <v>0.0009819565484226922</v>
       </c>
+      <c r="M476" s="1" t="n">
+        <v>0.08165</v>
+      </c>
+      <c r="N476" s="2" t="n">
+        <v>0.001226241569589244</v>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
@@ -19541,6 +22403,12 @@
       <c r="L477" s="2" t="n">
         <v>0.004418262150220835</v>
       </c>
+      <c r="M477" s="1" t="n">
+        <v>0.1364</v>
+      </c>
+      <c r="N477" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
@@ -19581,6 +22449,12 @@
       <c r="L478" s="2" t="n">
         <v>0.001510574018126862</v>
       </c>
+      <c r="M478" s="1" t="n">
+        <v>0.3993</v>
+      </c>
+      <c r="N478" s="2" t="n">
+        <v>0.003770739064856715</v>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
@@ -19621,6 +22495,12 @@
       <c r="L479" s="2" t="n">
         <v>0.0003557452863751056</v>
       </c>
+      <c r="M479" s="1" t="n">
+        <v>0.008477999999999999</v>
+      </c>
+      <c r="N479" s="2" t="n">
+        <v>0.004978662873399553</v>
+      </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
@@ -19661,6 +22541,12 @@
       <c r="L480" s="3" t="n">
         <v>-0.001256281407035125</v>
       </c>
+      <c r="M480" s="1" t="n">
+        <v>0.01592</v>
+      </c>
+      <c r="N480" s="2" t="n">
+        <v>0.001257861635220075</v>
+      </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
@@ -19701,6 +22587,12 @@
       <c r="L481" s="2" t="n">
         <v>0.0003883495145631359</v>
       </c>
+      <c r="M481" s="1" t="n">
+        <v>0.07772</v>
+      </c>
+      <c r="N481" s="2" t="n">
+        <v>0.00569358178053825</v>
+      </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
@@ -19741,6 +22633,12 @@
       <c r="L482" s="3" t="n">
         <v>-0.001976675232259396</v>
       </c>
+      <c r="M482" s="1" t="n">
+        <v>0.05064</v>
+      </c>
+      <c r="N482" s="2" t="n">
+        <v>0.002970885323826448</v>
+      </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
@@ -19781,6 +22679,12 @@
       <c r="L483" s="3" t="n">
         <v>-0.001029866117404695</v>
       </c>
+      <c r="M483" s="1" t="n">
+        <v>0.00974</v>
+      </c>
+      <c r="N483" s="2" t="n">
+        <v>0.004123711340206196</v>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
@@ -19821,6 +22725,12 @@
       <c r="L484" s="2" t="n">
         <v>0.0001471237310577626</v>
       </c>
+      <c r="M484" s="1" t="n">
+        <v>0.06804</v>
+      </c>
+      <c r="N484" s="2" t="n">
+        <v>0.0008826125330980362</v>
+      </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
@@ -19861,6 +22771,12 @@
       <c r="L485" s="2" t="n">
         <v>0.001560062402496017</v>
       </c>
+      <c r="M485" s="1" t="n">
+        <v>0.0004488</v>
+      </c>
+      <c r="N485" s="3" t="n">
+        <v>-0.001335113484646107</v>
+      </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
@@ -19901,6 +22817,12 @@
       <c r="L486" s="3" t="n">
         <v>-0.0002520161290323353</v>
       </c>
+      <c r="M486" s="1" t="n">
+        <v>0.07924</v>
+      </c>
+      <c r="N486" s="3" t="n">
+        <v>-0.001260398285858193</v>
+      </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
@@ -19941,6 +22863,12 @@
       <c r="L487" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="M487" s="1" t="n">
+        <v>0.0001735</v>
+      </c>
+      <c r="N487" s="2" t="n">
+        <v>0.002890173410404538</v>
+      </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
@@ -19981,6 +22909,12 @@
       <c r="L488" s="2" t="n">
         <v>0.001830035456937062</v>
       </c>
+      <c r="M488" s="1" t="n">
+        <v>0.08724</v>
+      </c>
+      <c r="N488" s="3" t="n">
+        <v>-0.003995889941774211</v>
+      </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
@@ -20021,6 +22955,12 @@
       <c r="L489" s="2" t="n">
         <v>0.001264755480607031</v>
       </c>
+      <c r="M489" s="1" t="n">
+        <v>0.04744</v>
+      </c>
+      <c r="N489" s="3" t="n">
+        <v>-0.001263157894736791</v>
+      </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
@@ -20061,6 +23001,12 @@
       <c r="L490" s="3" t="n">
         <v>-0.01143748375357411</v>
       </c>
+      <c r="M490" s="1" t="n">
+        <v>0.03848</v>
+      </c>
+      <c r="N490" s="2" t="n">
+        <v>0.01183276360767812</v>
+      </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
@@ -20101,6 +23047,12 @@
       <c r="L491" s="3" t="n">
         <v>-0.0001286008230452176</v>
       </c>
+      <c r="M491" s="1" t="n">
+        <v>0.07807</v>
+      </c>
+      <c r="N491" s="2" t="n">
+        <v>0.004115755627009657</v>
+      </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
@@ -20141,6 +23093,12 @@
       <c r="L492" s="3" t="n">
         <v>-0.009120930963988005</v>
       </c>
+      <c r="M492" s="1" t="n">
+        <v>0.06297</v>
+      </c>
+      <c r="N492" s="3" t="n">
+        <v>-0.0006348198698619008</v>
+      </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
@@ -20181,6 +23139,12 @@
       <c r="L493" s="2" t="n">
         <v>0.001912045889101261</v>
       </c>
+      <c r="M493" s="1" t="n">
+        <v>0.00528</v>
+      </c>
+      <c r="N493" s="2" t="n">
+        <v>0.007633587786259563</v>
+      </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
@@ -20221,6 +23185,12 @@
       <c r="L494" s="2" t="n">
         <v>0.0007241129616219333</v>
       </c>
+      <c r="M494" s="1" t="n">
+        <v>0.277</v>
+      </c>
+      <c r="N494" s="2" t="n">
+        <v>0.002170767004341697</v>
+      </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
@@ -20261,6 +23231,12 @@
       <c r="L495" s="2" t="n">
         <v>0.001887089164963186</v>
       </c>
+      <c r="M495" s="1" t="n">
+        <v>0.06382</v>
+      </c>
+      <c r="N495" s="2" t="n">
+        <v>0.001726573536336509</v>
+      </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
@@ -20301,6 +23277,12 @@
       <c r="L496" s="2" t="n">
         <v>0.001024590163934503</v>
       </c>
+      <c r="M496" s="1" t="n">
+        <v>0.2937</v>
+      </c>
+      <c r="N496" s="2" t="n">
+        <v>0.002047082906857691</v>
+      </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
@@ -20341,6 +23323,12 @@
       <c r="L497" s="2" t="n">
         <v>0.002676523069079809</v>
       </c>
+      <c r="M497" s="1" t="n">
+        <v>0.07863000000000001</v>
+      </c>
+      <c r="N497" s="3" t="n">
+        <v>-0.0005084530316511804</v>
+      </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
@@ -20381,6 +23369,12 @@
       <c r="L498" s="2" t="n">
         <v>0.0009699321047526951</v>
       </c>
+      <c r="M498" s="1" t="n">
+        <v>0.1035</v>
+      </c>
+      <c r="N498" s="2" t="n">
+        <v>0.002906976744185995</v>
+      </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
@@ -20421,6 +23415,12 @@
       <c r="L499" s="2" t="n">
         <v>0.006024096385542173</v>
       </c>
+      <c r="M499" s="1" t="n">
+        <v>0.04168</v>
+      </c>
+      <c r="N499" s="3" t="n">
+        <v>-0.001676646706586841</v>
+      </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
@@ -20461,6 +23461,12 @@
       <c r="L500" s="3" t="n">
         <v>-0.000729927007299156</v>
       </c>
+      <c r="M500" s="1" t="n">
+        <v>0.04097</v>
+      </c>
+      <c r="N500" s="3" t="n">
+        <v>-0.002434867299732234</v>
+      </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
@@ -20501,6 +23507,12 @@
       <c r="L501" s="3" t="n">
         <v>-0.002008032128513975</v>
       </c>
+      <c r="M501" s="1" t="n">
+        <v>0.09959999999999999</v>
+      </c>
+      <c r="N501" s="2" t="n">
+        <v>0.002012072434607564</v>
+      </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
@@ -20541,6 +23553,12 @@
       <c r="L502" s="3" t="n">
         <v>-0.0006047777441789634</v>
       </c>
+      <c r="M502" s="1" t="n">
+        <v>0.003312</v>
+      </c>
+      <c r="N502" s="2" t="n">
+        <v>0.002118003025718495</v>
+      </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
@@ -20581,6 +23599,12 @@
       <c r="L503" s="2" t="n">
         <v>0.0130434782608696</v>
       </c>
+      <c r="M503" s="1" t="n">
+        <v>0.009350000000000001</v>
+      </c>
+      <c r="N503" s="2" t="n">
+        <v>0.003218884120171729</v>
+      </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
@@ -20621,6 +23645,12 @@
       <c r="L504" s="2" t="n">
         <v>0.009511731135066591</v>
       </c>
+      <c r="M504" s="1" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="N504" s="2" t="n">
+        <v>0.005025125628140673</v>
+      </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
@@ -20661,6 +23691,12 @@
       <c r="L505" s="2" t="n">
         <v>0.0007621951219511355</v>
       </c>
+      <c r="M505" s="1" t="n">
+        <v>0.1315</v>
+      </c>
+      <c r="N505" s="2" t="n">
+        <v>0.001523229246001567</v>
+      </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
@@ -20701,6 +23737,12 @@
       <c r="L506" s="2" t="n">
         <v>0.007121661721068165</v>
       </c>
+      <c r="M506" s="1" t="n">
+        <v>0.01695</v>
+      </c>
+      <c r="N506" s="3" t="n">
+        <v>-0.001178550383028827</v>
+      </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
@@ -20741,6 +23783,12 @@
       <c r="L507" s="2" t="n">
         <v>0.002080443828016769</v>
       </c>
+      <c r="M507" s="1" t="n">
+        <v>0.002897</v>
+      </c>
+      <c r="N507" s="2" t="n">
+        <v>0.002422145328719594</v>
+      </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
@@ -20781,6 +23829,12 @@
       <c r="L508" s="2" t="n">
         <v>0.002265518803806224</v>
       </c>
+      <c r="M508" s="1" t="n">
+        <v>2.226</v>
+      </c>
+      <c r="N508" s="2" t="n">
+        <v>0.006329113924050537</v>
+      </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
@@ -20821,6 +23875,12 @@
       <c r="L509" s="2" t="n">
         <v>0.0007272727272726976</v>
       </c>
+      <c r="M509" s="1" t="n">
+        <v>0.05507</v>
+      </c>
+      <c r="N509" s="2" t="n">
+        <v>0.0005450581395349246</v>
+      </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
@@ -20861,6 +23921,12 @@
       <c r="L510" s="2" t="n">
         <v>0.003742769649540626</v>
       </c>
+      <c r="M510" s="1" t="n">
+        <v>0.02935</v>
+      </c>
+      <c r="N510" s="3" t="n">
+        <v>-0.005084745762711775</v>
+      </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
@@ -20901,6 +23967,12 @@
       <c r="L511" s="2" t="n">
         <v>0.00272479564032695</v>
       </c>
+      <c r="M511" s="1" t="n">
+        <v>0.04042</v>
+      </c>
+      <c r="N511" s="3" t="n">
+        <v>-0.001482213438735289</v>
+      </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
@@ -20941,6 +24013,12 @@
       <c r="L512" s="2" t="n">
         <v>0.0116279069767442</v>
       </c>
+      <c r="M512" s="1" t="n">
+        <v>0.08599999999999999</v>
+      </c>
+      <c r="N512" s="3" t="n">
+        <v>-0.01149425287356323</v>
+      </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
@@ -20981,6 +24059,12 @@
       <c r="L513" s="2" t="n">
         <v>0.003985409348824644</v>
       </c>
+      <c r="M513" s="1" t="n">
+        <v>0.015006</v>
+      </c>
+      <c r="N513" s="2" t="n">
+        <v>0.009621207024153991</v>
+      </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
@@ -21021,6 +24105,12 @@
       <c r="L514" s="2" t="n">
         <v>0.00402761795166846</v>
       </c>
+      <c r="M514" s="1" t="n">
+        <v>0.1746</v>
+      </c>
+      <c r="N514" s="2" t="n">
+        <v>0.0005730659025788926</v>
+      </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
@@ -21061,6 +24151,12 @@
       <c r="L515" s="2" t="n">
         <v>0.002795899347623436</v>
       </c>
+      <c r="M515" s="1" t="n">
+        <v>0.1079</v>
+      </c>
+      <c r="N515" s="2" t="n">
+        <v>0.002788104089219282</v>
+      </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
@@ -21101,6 +24197,12 @@
       <c r="L516" s="2" t="n">
         <v>0.007547169811320775</v>
       </c>
+      <c r="M516" s="1" t="n">
+        <v>0.00268</v>
+      </c>
+      <c r="N516" s="2" t="n">
+        <v>0.003745318352059935</v>
+      </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
@@ -21141,6 +24243,12 @@
       <c r="L517" s="2" t="n">
         <v>0.00129634430904843</v>
       </c>
+      <c r="M517" s="1" t="n">
+        <v>0.007757</v>
+      </c>
+      <c r="N517" s="2" t="n">
+        <v>0.004272397721387888</v>
+      </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
@@ -21181,6 +24289,12 @@
       <c r="L518" s="3" t="n">
         <v>-0.00259067357512954</v>
       </c>
+      <c r="M518" s="1" t="n">
+        <v>0.01542</v>
+      </c>
+      <c r="N518" s="2" t="n">
+        <v>0.001298701298701246</v>
+      </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
@@ -21221,6 +24335,12 @@
       <c r="L519" s="2" t="n">
         <v>0.004647749510763403</v>
       </c>
+      <c r="M519" s="1" t="n">
+        <v>0.00411</v>
+      </c>
+      <c r="N519" s="2" t="n">
+        <v>0.0007304601899195351</v>
+      </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
@@ -21261,6 +24381,12 @@
       <c r="L520" s="3" t="n">
         <v>-0.0008635578583764387</v>
       </c>
+      <c r="M520" s="1" t="n">
+        <v>0.00116</v>
+      </c>
+      <c r="N520" s="2" t="n">
+        <v>0.002592912705272225</v>
+      </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
@@ -21301,6 +24427,12 @@
       <c r="L521" s="2" t="n">
         <v>0.002243829468960398</v>
       </c>
+      <c r="M521" s="1" t="n">
+        <v>0.01338</v>
+      </c>
+      <c r="N521" s="3" t="n">
+        <v>-0.001492537313432904</v>
+      </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
@@ -21341,6 +24473,12 @@
       <c r="L522" s="2" t="n">
         <v>0.002337472607742945</v>
       </c>
+      <c r="M522" s="1" t="n">
+        <v>0.6882</v>
+      </c>
+      <c r="N522" s="2" t="n">
+        <v>0.003060778312199374</v>
+      </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
@@ -21381,6 +24519,12 @@
       <c r="L523" s="2" t="n">
         <v>0.001285897985426586</v>
       </c>
+      <c r="M523" s="1" t="n">
+        <v>0.06995</v>
+      </c>
+      <c r="N523" s="3" t="n">
+        <v>-0.001855022831050301</v>
+      </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
@@ -21421,6 +24565,12 @@
       <c r="L524" s="2" t="n">
         <v>0.002606429192006995</v>
       </c>
+      <c r="M524" s="1" t="n">
+        <v>0.0116</v>
+      </c>
+      <c r="N524" s="2" t="n">
+        <v>0.005199306759098726</v>
+      </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
@@ -21461,6 +24611,12 @@
       <c r="L525" s="2" t="n">
         <v>0.003058103975535256</v>
       </c>
+      <c r="M525" s="1" t="n">
+        <v>0.01641</v>
+      </c>
+      <c r="N525" s="2" t="n">
+        <v>0.0006097560975609507</v>
+      </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
@@ -21501,6 +24657,12 @@
       <c r="L526" s="3" t="n">
         <v>-0.004258130827398849</v>
       </c>
+      <c r="M526" s="1" t="n">
+        <v>0.13553</v>
+      </c>
+      <c r="N526" s="3" t="n">
+        <v>-0.0007373000073729189</v>
+      </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
@@ -21541,6 +24703,12 @@
       <c r="L527" s="2" t="n">
         <v>0.002562310738411344</v>
       </c>
+      <c r="M527" s="1" t="n">
+        <v>0.04314</v>
+      </c>
+      <c r="N527" s="2" t="n">
+        <v>0.002323420074349348</v>
+      </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
@@ -21581,6 +24749,12 @@
       <c r="L528" s="2" t="n">
         <v>0.001102941176470467</v>
       </c>
+      <c r="M528" s="1" t="n">
+        <v>0.2729</v>
+      </c>
+      <c r="N528" s="2" t="n">
+        <v>0.002203452074917332</v>
+      </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
@@ -21621,6 +24795,12 @@
       <c r="L529" s="2" t="n">
         <v>0.001385041551246571</v>
       </c>
+      <c r="M529" s="1" t="n">
+        <v>0.0007291</v>
+      </c>
+      <c r="N529" s="2" t="n">
+        <v>0.008437067773167339</v>
+      </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
@@ -21661,6 +24841,12 @@
       <c r="L530" s="2" t="n">
         <v>0.003606636210627407</v>
       </c>
+      <c r="M530" s="1" t="n">
+        <v>0.004191</v>
+      </c>
+      <c r="N530" s="2" t="n">
+        <v>0.004072831816003959</v>
+      </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
@@ -21701,6 +24887,12 @@
       <c r="L531" s="2" t="n">
         <v>0.0007616146230008469</v>
       </c>
+      <c r="M531" s="1" t="n">
+        <v>1.316</v>
+      </c>
+      <c r="N531" s="2" t="n">
+        <v>0.001522070015220701</v>
+      </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
@@ -21741,6 +24933,12 @@
       <c r="L532" s="3" t="n">
         <v>-0.0008503401360544461</v>
       </c>
+      <c r="M532" s="1" t="n">
+        <v>0.1182</v>
+      </c>
+      <c r="N532" s="2" t="n">
+        <v>0.005957446808510691</v>
+      </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
@@ -21781,6 +24979,12 @@
       <c r="L533" s="3" t="n">
         <v>-0.0007480830372171007</v>
       </c>
+      <c r="M533" s="1" t="n">
+        <v>0.05371</v>
+      </c>
+      <c r="N533" s="2" t="n">
+        <v>0.005240501590866601</v>
+      </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
@@ -21821,6 +25025,12 @@
       <c r="L534" s="2" t="n">
         <v>0.001331557922769679</v>
       </c>
+      <c r="M534" s="1" t="n">
+        <v>0.1498</v>
+      </c>
+      <c r="N534" s="3" t="n">
+        <v>-0.003989361702127774</v>
+      </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
@@ -21861,6 +25071,12 @@
       <c r="L535" s="2" t="n">
         <v>0.003512880562060746</v>
       </c>
+      <c r="M535" s="1" t="n">
+        <v>0.01716</v>
+      </c>
+      <c r="N535" s="2" t="n">
+        <v>0.001166861143524076</v>
+      </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
@@ -21901,6 +25117,12 @@
       <c r="L536" s="2" t="n">
         <v>0.002012072434607738</v>
       </c>
+      <c r="M536" s="1" t="n">
+        <v>0.004985</v>
+      </c>
+      <c r="N536" s="2" t="n">
+        <v>0.001004016064256987</v>
+      </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
@@ -21941,6 +25163,12 @@
       <c r="L537" s="2" t="n">
         <v>0.001375042970092855</v>
       </c>
+      <c r="M537" s="1" t="n">
+        <v>0.2918</v>
+      </c>
+      <c r="N537" s="2" t="n">
+        <v>0.001716443529007897</v>
+      </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
@@ -21981,6 +25209,12 @@
       <c r="L538" s="2" t="n">
         <v>0.002265861027190371</v>
       </c>
+      <c r="M538" s="1" t="n">
+        <v>0.01327</v>
+      </c>
+      <c r="N538" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
@@ -22021,6 +25255,12 @@
       <c r="L539" s="3" t="n">
         <v>-0.002029220779220697</v>
       </c>
+      <c r="M539" s="1" t="n">
+        <v>0.02471</v>
+      </c>
+      <c r="N539" s="2" t="n">
+        <v>0.004880032533550166</v>
+      </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
@@ -22061,6 +25301,12 @@
       <c r="L540" s="2" t="n">
         <v>0.002114537444933835</v>
       </c>
+      <c r="M540" s="1" t="n">
+        <v>0.05696</v>
+      </c>
+      <c r="N540" s="2" t="n">
+        <v>0.001582556708282043</v>
+      </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
@@ -22101,6 +25347,12 @@
       <c r="L541" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="M541" s="1" t="n">
+        <v>0.0116</v>
+      </c>
+      <c r="N541" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
@@ -22141,6 +25393,12 @@
       <c r="L542" s="2" t="n">
         <v>0.009009009009008922</v>
       </c>
+      <c r="M542" s="1" t="n">
+        <v>1.11e-05</v>
+      </c>
+      <c r="N542" s="3" t="n">
+        <v>-0.008928571428571343</v>
+      </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
@@ -22180,6 +25438,12 @@
       </c>
       <c r="L543" s="2" t="n">
         <v>0.003824091778202592</v>
+      </c>
+      <c r="M543" s="1" t="n">
+        <v>0.003682</v>
+      </c>
+      <c r="N543" s="2" t="n">
+        <v>0.001904761904761922</v>
       </c>
     </row>
   </sheetData>

--- a/binance-usdt-perpetual-data/weeks/2026-03-09_2026-03-15/2026-03-12.xlsx
+++ b/binance-usdt-perpetual-data/weeks/2026-03-09_2026-03-15/2026-03-12.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N543"/>
+  <dimension ref="A1:P543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -440,6 +440,8 @@
     <col width="18" customWidth="1" min="12" max="12"/>
     <col width="13" customWidth="1" min="13" max="13"/>
     <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -513,6 +515,16 @@
           <t>change_01:30</t>
         </is>
       </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>price_01:45</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>change_01:45</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -559,6 +571,12 @@
       <c r="N2" s="2" t="n">
         <v>0.005375106775006489</v>
       </c>
+      <c r="O2" s="1" t="n">
+        <v>70802.7</v>
+      </c>
+      <c r="P2" s="3" t="n">
+        <v>-0.005680605332045075</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -605,6 +623,12 @@
       <c r="N3" s="2" t="n">
         <v>0.005492063798749862</v>
       </c>
+      <c r="O3" s="1" t="n">
+        <v>2068.88</v>
+      </c>
+      <c r="P3" s="3" t="n">
+        <v>-0.006125007806382498</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -651,6 +675,12 @@
       <c r="N4" s="2" t="n">
         <v>0.01224442647568444</v>
       </c>
+      <c r="O4" s="1" t="n">
+        <v>87.22</v>
+      </c>
+      <c r="P4" s="3" t="n">
+        <v>-0.004678762980714329</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -697,6 +727,12 @@
       <c r="N5" s="3" t="n">
         <v>-0.0152045209903122</v>
       </c>
+      <c r="O5" s="1" t="n">
+        <v>0.014079</v>
+      </c>
+      <c r="P5" s="3" t="n">
+        <v>-0.03818827708703378</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -743,6 +779,12 @@
       <c r="N6" s="2" t="n">
         <v>0.004819019061897537</v>
       </c>
+      <c r="O6" s="1" t="n">
+        <v>0.0936</v>
+      </c>
+      <c r="P6" s="3" t="n">
+        <v>-0.002451241607161826</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -789,6 +831,12 @@
       <c r="N7" s="2" t="n">
         <v>0.005753326141675661</v>
       </c>
+      <c r="O7" s="1" t="n">
+        <v>1.3972</v>
+      </c>
+      <c r="P7" s="3" t="n">
+        <v>-0.0009295673936360949</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -835,6 +883,12 @@
       <c r="N8" s="2" t="n">
         <v>0.007993187936054604</v>
       </c>
+      <c r="O8" s="1" t="n">
+        <v>36.296</v>
+      </c>
+      <c r="P8" s="3" t="n">
+        <v>-0.01092732375943547</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -881,6 +935,12 @@
       <c r="N9" s="2" t="n">
         <v>0.006426517842043055</v>
       </c>
+      <c r="O9" s="1" t="n">
+        <v>652.25</v>
+      </c>
+      <c r="P9" s="3" t="n">
+        <v>-0.00360520004277358</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -927,6 +987,12 @@
       <c r="N10" s="3" t="n">
         <v>-0.02521401819154633</v>
       </c>
+      <c r="O10" s="1" t="n">
+        <v>14.686</v>
+      </c>
+      <c r="P10" s="2" t="n">
+        <v>0.00761578044596917</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -973,6 +1039,12 @@
       <c r="N11" s="2" t="n">
         <v>0.009685689868008699</v>
       </c>
+      <c r="O11" s="1" t="n">
+        <v>211.76</v>
+      </c>
+      <c r="P11" s="3" t="n">
+        <v>-0.004232107589579637</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1019,6 +1091,12 @@
       <c r="N12" s="2" t="n">
         <v>0.004519505233111433</v>
       </c>
+      <c r="O12" s="1" t="n">
+        <v>0.0033577</v>
+      </c>
+      <c r="P12" s="3" t="n">
+        <v>-0.006127160786171037</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1065,6 +1143,12 @@
       <c r="N13" s="3" t="n">
         <v>-0.01469017094017099</v>
       </c>
+      <c r="O13" s="1" t="n">
+        <v>0.03718</v>
+      </c>
+      <c r="P13" s="2" t="n">
+        <v>0.007861208999728886</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1111,6 +1195,12 @@
       <c r="N14" s="2" t="n">
         <v>0.001903311762466821</v>
       </c>
+      <c r="O14" s="1" t="n">
+        <v>2.593</v>
+      </c>
+      <c r="P14" s="3" t="n">
+        <v>-0.01481762917933136</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1157,6 +1247,12 @@
       <c r="N15" s="2" t="n">
         <v>0.004373029594223616</v>
       </c>
+      <c r="O15" s="1" t="n">
+        <v>0.9823</v>
+      </c>
+      <c r="P15" s="3" t="n">
+        <v>-0.005366545159983882</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1203,6 +1299,12 @@
       <c r="N16" s="3" t="n">
         <v>-0.004088162104514648</v>
       </c>
+      <c r="O16" s="1" t="n">
+        <v>0.05641</v>
+      </c>
+      <c r="P16" s="2" t="n">
+        <v>0.006782081028020674</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1249,6 +1351,12 @@
       <c r="N17" s="2" t="n">
         <v>0.002262443438914029</v>
       </c>
+      <c r="O17" s="1" t="n">
+        <v>0.882</v>
+      </c>
+      <c r="P17" s="3" t="n">
+        <v>-0.004514672686230252</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1295,6 +1403,12 @@
       <c r="N18" s="2" t="n">
         <v>0.004160363086232942</v>
       </c>
+      <c r="O18" s="1" t="n">
+        <v>0.2645</v>
+      </c>
+      <c r="P18" s="3" t="n">
+        <v>-0.003766478342749533</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1341,6 +1455,12 @@
       <c r="N19" s="3" t="n">
         <v>-0.005001744794695822</v>
       </c>
+      <c r="O19" s="1" t="n">
+        <v>0.34577</v>
+      </c>
+      <c r="P19" s="2" t="n">
+        <v>0.01055061959317279</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1387,6 +1507,12 @@
       <c r="N20" s="2" t="n">
         <v>0.00403059115336913</v>
       </c>
+      <c r="O20" s="1" t="n">
+        <v>9.651999999999999</v>
+      </c>
+      <c r="P20" s="3" t="n">
+        <v>-0.006484817292846177</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1433,6 +1559,12 @@
       <c r="N21" s="2" t="n">
         <v>0.00356246864024074</v>
       </c>
+      <c r="O21" s="1" t="n">
+        <v>198.73</v>
+      </c>
+      <c r="P21" s="3" t="n">
+        <v>-0.006399680015999206</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1479,6 +1611,12 @@
       <c r="N22" s="2" t="n">
         <v>0.01887067041816243</v>
       </c>
+      <c r="O22" s="1" t="n">
+        <v>0.020751</v>
+      </c>
+      <c r="P22" s="3" t="n">
+        <v>-0.0119982859591488</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1525,6 +1663,12 @@
       <c r="N23" s="2" t="n">
         <v>0.003527143670858375</v>
       </c>
+      <c r="O23" s="1" t="n">
+        <v>457.55</v>
+      </c>
+      <c r="P23" s="3" t="n">
+        <v>-0.001135197677210867</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1571,6 +1715,12 @@
       <c r="N24" s="3" t="n">
         <v>-0.0007461229633838557</v>
       </c>
+      <c r="O24" s="1" t="n">
+        <v>5160.66</v>
+      </c>
+      <c r="P24" s="3" t="n">
+        <v>-0.001719685465852991</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1617,6 +1767,12 @@
       <c r="N25" s="2" t="n">
         <v>0.006061942025790776</v>
       </c>
+      <c r="O25" s="1" t="n">
+        <v>9.074</v>
+      </c>
+      <c r="P25" s="3" t="n">
+        <v>-0.005915863277826497</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1663,6 +1819,12 @@
       <c r="N26" s="2" t="n">
         <v>0.03796142769875213</v>
       </c>
+      <c r="O26" s="1" t="n">
+        <v>0.11787</v>
+      </c>
+      <c r="P26" s="3" t="n">
+        <v>-0.008996132503783432</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1709,6 +1871,12 @@
       <c r="N27" s="3" t="n">
         <v>-0.001616814874696922</v>
       </c>
+      <c r="O27" s="1" t="n">
+        <v>0.01209</v>
+      </c>
+      <c r="P27" s="3" t="n">
+        <v>-0.02105263157894735</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1755,6 +1923,12 @@
       <c r="N28" s="2" t="n">
         <v>0.003086419753086422</v>
       </c>
+      <c r="O28" s="1" t="n">
+        <v>1.289</v>
+      </c>
+      <c r="P28" s="3" t="n">
+        <v>-0.008461538461538555</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1801,6 +1975,12 @@
       <c r="N29" s="3" t="n">
         <v>-0.001151315789473694</v>
       </c>
+      <c r="O29" s="1" t="n">
+        <v>0.05931</v>
+      </c>
+      <c r="P29" s="3" t="n">
+        <v>-0.02338218343487564</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1847,6 +2027,12 @@
       <c r="N30" s="2" t="n">
         <v>0.000653594771241758</v>
       </c>
+      <c r="O30" s="1" t="n">
+        <v>1.521</v>
+      </c>
+      <c r="P30" s="3" t="n">
+        <v>-0.006531678641410849</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1893,6 +2079,12 @@
       <c r="N31" s="2" t="n">
         <v>0.009823182711198454</v>
       </c>
+      <c r="O31" s="1" t="n">
+        <v>0.002043</v>
+      </c>
+      <c r="P31" s="3" t="n">
+        <v>-0.006322957198443575</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1939,6 +2131,12 @@
       <c r="N32" s="2" t="n">
         <v>0.004937052579610114</v>
       </c>
+      <c r="O32" s="1" t="n">
+        <v>0.04046</v>
+      </c>
+      <c r="P32" s="3" t="n">
+        <v>-0.006140997297961194</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1985,6 +2183,12 @@
       <c r="N33" s="2" t="n">
         <v>0.006109979633401256</v>
       </c>
+      <c r="O33" s="1" t="n">
+        <v>0.0985</v>
+      </c>
+      <c r="P33" s="3" t="n">
+        <v>-0.003036437246963509</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2031,6 +2235,12 @@
       <c r="N34" s="2" t="n">
         <v>0.001901140684410569</v>
       </c>
+      <c r="O34" s="1" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="P34" s="3" t="n">
+        <v>-0.003795066413662216</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2077,6 +2287,12 @@
       <c r="N35" s="3" t="n">
         <v>-0.004464285714285533</v>
       </c>
+      <c r="O35" s="1" t="n">
+        <v>0.008750000000000001</v>
+      </c>
+      <c r="P35" s="3" t="n">
+        <v>-0.01905829596412556</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2123,6 +2339,12 @@
       <c r="N36" s="2" t="n">
         <v>0.002791736460078171</v>
       </c>
+      <c r="O36" s="1" t="n">
+        <v>0.3568</v>
+      </c>
+      <c r="P36" s="3" t="n">
+        <v>-0.006681514476614736</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2169,6 +2391,12 @@
       <c r="N37" s="2" t="n">
         <v>0.002740664611168126</v>
       </c>
+      <c r="O37" s="1" t="n">
+        <v>0.005826</v>
+      </c>
+      <c r="P37" s="3" t="n">
+        <v>-0.004783054321831269</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2215,6 +2443,12 @@
       <c r="N38" s="3" t="n">
         <v>-0.006338001442179987</v>
       </c>
+      <c r="O38" s="1" t="n">
+        <v>0.26208</v>
+      </c>
+      <c r="P38" s="2" t="n">
+        <v>0.0009930486593842428</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2261,6 +2495,12 @@
       <c r="N39" s="3" t="n">
         <v>-0.003168944345414942</v>
       </c>
+      <c r="O39" s="1" t="n">
+        <v>0.05075</v>
+      </c>
+      <c r="P39" s="2" t="n">
+        <v>0.008344923504867945</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2307,6 +2547,12 @@
       <c r="N40" s="2" t="n">
         <v>0.002069840421980401</v>
       </c>
+      <c r="O40" s="1" t="n">
+        <v>0.14915</v>
+      </c>
+      <c r="P40" s="3" t="n">
+        <v>-0.006196695095948737</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2353,6 +2599,12 @@
       <c r="N41" s="2" t="n">
         <v>0.004137115839243535</v>
       </c>
+      <c r="O41" s="1" t="n">
+        <v>0.1684</v>
+      </c>
+      <c r="P41" s="3" t="n">
+        <v>-0.008828722778104776</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2399,6 +2651,12 @@
       <c r="N42" s="2" t="n">
         <v>0.0002665718855516876</v>
       </c>
+      <c r="O42" s="1" t="n">
+        <v>112</v>
+      </c>
+      <c r="P42" s="3" t="n">
+        <v>-0.005063516034467383</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2445,6 +2703,12 @@
       <c r="N43" s="3" t="n">
         <v>-0.02716562716562725</v>
       </c>
+      <c r="O43" s="1" t="n">
+        <v>0.6942</v>
+      </c>
+      <c r="P43" s="3" t="n">
+        <v>-0.01097022367858659</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2491,6 +2755,12 @@
       <c r="N44" s="2" t="n">
         <v>0.005666240175470705</v>
       </c>
+      <c r="O44" s="1" t="n">
+        <v>54.89</v>
+      </c>
+      <c r="P44" s="3" t="n">
+        <v>-0.002362777171937524</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2537,6 +2807,12 @@
       <c r="N45" s="3" t="n">
         <v>-0.0006036710747231356</v>
       </c>
+      <c r="O45" s="1" t="n">
+        <v>0.52188</v>
+      </c>
+      <c r="P45" s="3" t="n">
+        <v>-0.01489325556373512</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2583,6 +2859,12 @@
       <c r="N46" s="2" t="n">
         <v>0.0009927669834066573</v>
       </c>
+      <c r="O46" s="1" t="n">
+        <v>0.7034</v>
+      </c>
+      <c r="P46" s="3" t="n">
+        <v>-0.003400396712949784</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2629,6 +2911,12 @@
       <c r="N47" s="2" t="n">
         <v>0.004091025313219129</v>
       </c>
+      <c r="O47" s="1" t="n">
+        <v>3.902</v>
+      </c>
+      <c r="P47" s="3" t="n">
+        <v>-0.00636618283677105</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2675,6 +2963,12 @@
       <c r="N48" s="2" t="n">
         <v>0.001684552033940557</v>
       </c>
+      <c r="O48" s="1" t="n">
+        <v>0.1602</v>
+      </c>
+      <c r="P48" s="3" t="n">
+        <v>-0.002180006228589158</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2721,6 +3015,12 @@
       <c r="N49" s="2" t="n">
         <v>0.01329742467598046</v>
       </c>
+      <c r="O49" s="1" t="n">
+        <v>0.05931</v>
+      </c>
+      <c r="P49" s="3" t="n">
+        <v>-0.0147840531561461</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2767,6 +3067,12 @@
       <c r="N50" s="2" t="n">
         <v>0.005181347150259035</v>
       </c>
+      <c r="O50" s="1" t="n">
+        <v>0.0387</v>
+      </c>
+      <c r="P50" s="3" t="n">
+        <v>-0.00257731958762894</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2813,6 +3119,12 @@
       <c r="N51" s="3" t="n">
         <v>-0.005359923344112943</v>
       </c>
+      <c r="O51" s="1" t="n">
+        <v>0.31529</v>
+      </c>
+      <c r="P51" s="3" t="n">
+        <v>-0.05081735256043594</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2859,6 +3171,12 @@
       <c r="N52" s="2" t="n">
         <v>0.001700102006120369</v>
       </c>
+      <c r="O52" s="1" t="n">
+        <v>0.2941</v>
+      </c>
+      <c r="P52" s="3" t="n">
+        <v>-0.001697216564833674</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2905,6 +3223,12 @@
       <c r="N53" s="2" t="n">
         <v>0.002526847757422688</v>
       </c>
+      <c r="O53" s="1" t="n">
+        <v>0.158</v>
+      </c>
+      <c r="P53" s="3" t="n">
+        <v>-0.004410838059231293</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2951,6 +3275,12 @@
       <c r="N54" s="2" t="n">
         <v>0.0003087584479741294</v>
       </c>
+      <c r="O54" s="1" t="n">
+        <v>0.29105</v>
+      </c>
+      <c r="P54" s="3" t="n">
+        <v>-0.001817682968653647</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2997,6 +3327,12 @@
       <c r="N55" s="2" t="n">
         <v>0.005859375000000052</v>
       </c>
+      <c r="O55" s="1" t="n">
+        <v>0.007145</v>
+      </c>
+      <c r="P55" s="3" t="n">
+        <v>-0.009015256588072115</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3043,6 +3379,12 @@
       <c r="N56" s="2" t="n">
         <v>0.0003519887363604221</v>
       </c>
+      <c r="O56" s="1" t="n">
+        <v>0.02823</v>
+      </c>
+      <c r="P56" s="3" t="n">
+        <v>-0.006685432793807149</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3089,6 +3431,12 @@
       <c r="N57" s="2" t="n">
         <v>0.002855103497501833</v>
       </c>
+      <c r="O57" s="1" t="n">
+        <v>0.04229</v>
+      </c>
+      <c r="P57" s="2" t="n">
+        <v>0.003321470937129329</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3135,6 +3483,12 @@
       <c r="N58" s="3" t="n">
         <v>-0.02924226254002141</v>
       </c>
+      <c r="O58" s="1" t="n">
+        <v>0.04605</v>
+      </c>
+      <c r="P58" s="2" t="n">
+        <v>0.01253298153034303</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3181,6 +3535,12 @@
       <c r="N59" s="2" t="n">
         <v>0.0012987012987013</v>
       </c>
+      <c r="O59" s="1" t="n">
+        <v>1.538</v>
+      </c>
+      <c r="P59" s="3" t="n">
+        <v>-0.002594033722438394</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3227,6 +3587,12 @@
       <c r="N60" s="2" t="n">
         <v>0.002906976744186054</v>
       </c>
+      <c r="O60" s="1" t="n">
+        <v>0.00342</v>
+      </c>
+      <c r="P60" s="3" t="n">
+        <v>-0.008695652173913066</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3273,6 +3639,12 @@
       <c r="N61" s="2" t="n">
         <v>0.00838709677419352</v>
       </c>
+      <c r="O61" s="1" t="n">
+        <v>0.1548</v>
+      </c>
+      <c r="P61" s="3" t="n">
+        <v>-0.009596928982725537</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3319,6 +3691,12 @@
       <c r="N62" s="2" t="n">
         <v>0.0008688097306688878</v>
       </c>
+      <c r="O62" s="1" t="n">
+        <v>1.147</v>
+      </c>
+      <c r="P62" s="3" t="n">
+        <v>-0.004340277777777685</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3365,6 +3743,12 @@
       <c r="N63" s="2" t="n">
         <v>0.003427102670284103</v>
       </c>
+      <c r="O63" s="1" t="n">
+        <v>0.6968</v>
+      </c>
+      <c r="P63" s="3" t="n">
+        <v>-0.008396186139177482</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3411,6 +3795,12 @@
       <c r="N64" s="2" t="n">
         <v>0.005772495755517945</v>
       </c>
+      <c r="O64" s="1" t="n">
+        <v>2.946</v>
+      </c>
+      <c r="P64" s="3" t="n">
+        <v>-0.005401755570560437</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3457,6 +3847,12 @@
       <c r="N65" s="2" t="n">
         <v>0.0004164931278633733</v>
       </c>
+      <c r="O65" s="1" t="n">
+        <v>0.02387</v>
+      </c>
+      <c r="P65" s="3" t="n">
+        <v>-0.006244796003330592</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3503,6 +3899,12 @@
       <c r="N66" s="2" t="n">
         <v>0.003937007874015725</v>
       </c>
+      <c r="O66" s="1" t="n">
+        <v>0.1012</v>
+      </c>
+      <c r="P66" s="3" t="n">
+        <v>-0.007843137254901914</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3549,6 +3951,12 @@
       <c r="N67" s="2" t="n">
         <v>0.003019903912148294</v>
       </c>
+      <c r="O67" s="1" t="n">
+        <v>0.007312</v>
+      </c>
+      <c r="P67" s="2" t="n">
+        <v>0.0006842753524017786</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3595,6 +4003,12 @@
       <c r="N68" s="2" t="n">
         <v>0.01239224137931037</v>
       </c>
+      <c r="O68" s="1" t="n">
+        <v>18.93</v>
+      </c>
+      <c r="P68" s="2" t="n">
+        <v>0.00745077168706762</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3641,6 +4055,12 @@
       <c r="N69" s="2" t="n">
         <v>0.002227171492204938</v>
       </c>
+      <c r="O69" s="1" t="n">
+        <v>0.05402</v>
+      </c>
+      <c r="P69" s="2" t="n">
+        <v>0.0003703703703703553</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3687,6 +4107,12 @@
       <c r="N70" s="2" t="n">
         <v>0.004201680672268912</v>
       </c>
+      <c r="O70" s="1" t="n">
+        <v>0.238</v>
+      </c>
+      <c r="P70" s="3" t="n">
+        <v>-0.004184100418410046</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3733,6 +4159,12 @@
       <c r="N71" s="2" t="n">
         <v>0.02866517009152124</v>
       </c>
+      <c r="O71" s="1" t="n">
+        <v>5.845</v>
+      </c>
+      <c r="P71" s="3" t="n">
+        <v>-0.01880141010575795</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3779,6 +4211,12 @@
       <c r="N72" s="3" t="n">
         <v>-0.02002053388090348</v>
       </c>
+      <c r="O72" s="1" t="n">
+        <v>0.001884</v>
+      </c>
+      <c r="P72" s="3" t="n">
+        <v>-0.0130958617077004</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3825,6 +4263,12 @@
       <c r="N73" s="3" t="n">
         <v>-0.006423757371524847</v>
       </c>
+      <c r="O73" s="1" t="n">
+        <v>0.9378</v>
+      </c>
+      <c r="P73" s="3" t="n">
+        <v>-0.0060413354531002</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3871,6 +4315,12 @@
       <c r="N74" s="2" t="n">
         <v>0.0008250825082508487</v>
       </c>
+      <c r="O74" s="1" t="n">
+        <v>0.1202</v>
+      </c>
+      <c r="P74" s="3" t="n">
+        <v>-0.009068425391591127</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3917,6 +4367,12 @@
       <c r="N75" s="2" t="n">
         <v>0.001421666192777936</v>
       </c>
+      <c r="O75" s="1" t="n">
+        <v>352.28</v>
+      </c>
+      <c r="P75" s="2" t="n">
+        <v>0.000227143668370199</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3963,6 +4419,12 @@
       <c r="N76" s="2" t="n">
         <v>0.007849426063470629</v>
       </c>
+      <c r="O76" s="1" t="n">
+        <v>0.11841</v>
+      </c>
+      <c r="P76" s="3" t="n">
+        <v>-0.008374507997655146</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4009,6 +4471,12 @@
       <c r="N77" s="2" t="n">
         <v>0.002226817241927808</v>
       </c>
+      <c r="O77" s="1" t="n">
+        <v>0.06239</v>
+      </c>
+      <c r="P77" s="3" t="n">
+        <v>-0.009839707982859793</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -4055,6 +4523,12 @@
       <c r="N78" s="2" t="n">
         <v>0.002867459643160645</v>
       </c>
+      <c r="O78" s="1" t="n">
+        <v>0.09418</v>
+      </c>
+      <c r="P78" s="3" t="n">
+        <v>-0.002647463729746905</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -4101,6 +4575,12 @@
       <c r="N79" s="3" t="n">
         <v>-0.006260534553334918</v>
       </c>
+      <c r="O79" s="1" t="n">
+        <v>0.4059</v>
+      </c>
+      <c r="P79" s="3" t="n">
+        <v>-0.01647685970438582</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -4147,6 +4627,12 @@
       <c r="N80" s="2" t="n">
         <v>0.00532357344867741</v>
       </c>
+      <c r="O80" s="1" t="n">
+        <v>0.00601</v>
+      </c>
+      <c r="P80" s="3" t="n">
+        <v>-0.005460863809366216</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -4193,6 +4679,12 @@
       <c r="N81" s="2" t="n">
         <v>0.0135658914728682</v>
       </c>
+      <c r="O81" s="1" t="n">
+        <v>0.1029</v>
+      </c>
+      <c r="P81" s="3" t="n">
+        <v>-0.01625239005736131</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -4239,6 +4731,12 @@
       <c r="N82" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="O82" s="1" t="n">
+        <v>0.1021</v>
+      </c>
+      <c r="P82" s="3" t="n">
+        <v>-0.001955034213098785</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -4285,6 +4783,12 @@
       <c r="N83" s="3" t="n">
         <v>-0.02084991246219957</v>
       </c>
+      <c r="O83" s="1" t="n">
+        <v>0.06153</v>
+      </c>
+      <c r="P83" s="2" t="n">
+        <v>0.0001625487646294386</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -4331,6 +4835,12 @@
       <c r="N84" s="2" t="n">
         <v>0.003123048094940714</v>
       </c>
+      <c r="O84" s="1" t="n">
+        <v>1.1206</v>
+      </c>
+      <c r="P84" s="3" t="n">
+        <v>-0.003202277174879957</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -4377,6 +4887,12 @@
       <c r="N85" s="2" t="n">
         <v>0.006015037593984978</v>
       </c>
+      <c r="O85" s="1" t="n">
+        <v>0.01325</v>
+      </c>
+      <c r="P85" s="3" t="n">
+        <v>-0.00971599402092675</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -4423,6 +4939,12 @@
       <c r="N86" s="2" t="n">
         <v>0.005955926146515748</v>
       </c>
+      <c r="O86" s="1" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="P86" s="3" t="n">
+        <v>-0.005328596802841907</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -4469,6 +4991,12 @@
       <c r="N87" s="2" t="n">
         <v>0.004814636494944743</v>
       </c>
+      <c r="O87" s="1" t="n">
+        <v>8.303000000000001</v>
+      </c>
+      <c r="P87" s="3" t="n">
+        <v>-0.005390512697652124</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -4515,6 +5043,12 @@
       <c r="N88" s="2" t="n">
         <v>0.005829533167222964</v>
       </c>
+      <c r="O88" s="1" t="n">
+        <v>2.1272</v>
+      </c>
+      <c r="P88" s="3" t="n">
+        <v>-0.005749006777284298</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -4561,6 +5095,12 @@
       <c r="N89" s="2" t="n">
         <v>0.01118901984186191</v>
       </c>
+      <c r="O89" s="1" t="n">
+        <v>0.006796</v>
+      </c>
+      <c r="P89" s="2" t="n">
+        <v>0.002655650634405398</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -4607,6 +5147,12 @@
       <c r="N90" s="2" t="n">
         <v>0.003937007874015781</v>
       </c>
+      <c r="O90" s="1" t="n">
+        <v>15.31</v>
+      </c>
+      <c r="P90" s="2" t="n">
+        <v>0.0006535947712418161</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -4653,6 +5199,12 @@
       <c r="N91" s="3" t="n">
         <v>-0.004444444444444432</v>
       </c>
+      <c r="O91" s="1" t="n">
+        <v>0.000223</v>
+      </c>
+      <c r="P91" s="3" t="n">
+        <v>-0.004464285714285702</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -4699,6 +5251,12 @@
       <c r="N92" s="2" t="n">
         <v>0.02310483101012035</v>
       </c>
+      <c r="O92" s="1" t="n">
+        <v>0.05291</v>
+      </c>
+      <c r="P92" s="3" t="n">
+        <v>-0.01250466592011952</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -4745,6 +5303,12 @@
       <c r="N93" s="2" t="n">
         <v>0.003102300242130745</v>
       </c>
+      <c r="O93" s="1" t="n">
+        <v>1.325</v>
+      </c>
+      <c r="P93" s="3" t="n">
+        <v>-0.0005280229312816964</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -4791,6 +5355,12 @@
       <c r="N94" s="3" t="n">
         <v>-0.001163778771197409</v>
       </c>
+      <c r="O94" s="1" t="n">
+        <v>0.054571</v>
+      </c>
+      <c r="P94" s="2" t="n">
+        <v>0.009247101033825903</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -4837,6 +5407,12 @@
       <c r="N95" s="2" t="n">
         <v>0.001238645747316246</v>
       </c>
+      <c r="O95" s="1" t="n">
+        <v>0.2417</v>
+      </c>
+      <c r="P95" s="3" t="n">
+        <v>-0.003298969072164929</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -4883,6 +5459,12 @@
       <c r="N96" s="3" t="n">
         <v>-0.001107624146206265</v>
       </c>
+      <c r="O96" s="1" t="n">
+        <v>1.0785</v>
+      </c>
+      <c r="P96" s="3" t="n">
+        <v>-0.003418961374976933</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -4929,6 +5511,12 @@
       <c r="N97" s="2" t="n">
         <v>0.003097173828881235</v>
       </c>
+      <c r="O97" s="1" t="n">
+        <v>0.2577</v>
+      </c>
+      <c r="P97" s="3" t="n">
+        <v>-0.005403319181783143</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -4975,6 +5563,12 @@
       <c r="N98" s="2" t="n">
         <v>0.01607328033183542</v>
       </c>
+      <c r="O98" s="1" t="n">
+        <v>0.5859</v>
+      </c>
+      <c r="P98" s="3" t="n">
+        <v>-0.003401939105290019</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -5021,6 +5615,12 @@
       <c r="N99" s="2" t="n">
         <v>0.002522629470247657</v>
       </c>
+      <c r="O99" s="1" t="n">
+        <v>0.13718</v>
+      </c>
+      <c r="P99" s="2" t="n">
+        <v>0.0152457075192422</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -5067,6 +5667,12 @@
       <c r="N100" s="2" t="n">
         <v>0.002612671456564344</v>
       </c>
+      <c r="O100" s="1" t="n">
+        <v>0.0305</v>
+      </c>
+      <c r="P100" s="3" t="n">
+        <v>-0.006514657980456099</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -5113,6 +5719,12 @@
       <c r="N101" s="2" t="n">
         <v>0.005836575875486387</v>
       </c>
+      <c r="O101" s="1" t="n">
+        <v>1.029</v>
+      </c>
+      <c r="P101" s="3" t="n">
+        <v>-0.004835589941973032</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -5159,6 +5771,12 @@
       <c r="N102" s="2" t="n">
         <v>0.003626473254759756</v>
       </c>
+      <c r="O102" s="1" t="n">
+        <v>0.02195</v>
+      </c>
+      <c r="P102" s="3" t="n">
+        <v>-0.008581752484191473</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -5205,6 +5823,12 @@
       <c r="N103" s="3" t="n">
         <v>-0.002034587995930918</v>
       </c>
+      <c r="O103" s="1" t="n">
+        <v>0.01953</v>
+      </c>
+      <c r="P103" s="3" t="n">
+        <v>-0.004587155963302742</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -5251,6 +5875,12 @@
       <c r="N104" s="2" t="n">
         <v>0.004346372450685356</v>
       </c>
+      <c r="O104" s="1" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="P104" s="3" t="n">
+        <v>-0.004660452729693672</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -5297,6 +5927,12 @@
       <c r="N105" s="2" t="n">
         <v>0.006195786864931714</v>
       </c>
+      <c r="O105" s="1" t="n">
+        <v>32.47</v>
+      </c>
+      <c r="P105" s="3" t="n">
+        <v>-0.0003078817733989536</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -5343,6 +5979,12 @@
       <c r="N106" s="2" t="n">
         <v>0.005424954792043472</v>
       </c>
+      <c r="O106" s="1" t="n">
+        <v>0.1661</v>
+      </c>
+      <c r="P106" s="3" t="n">
+        <v>-0.004196642685851356</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -5389,6 +6031,12 @@
       <c r="N107" s="2" t="n">
         <v>0.0006553079947575852</v>
       </c>
+      <c r="O107" s="1" t="n">
+        <v>0.4649</v>
+      </c>
+      <c r="P107" s="2" t="n">
+        <v>0.01484392054136645</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -5435,6 +6083,12 @@
       <c r="N108" s="2" t="n">
         <v>0.001784121320249746</v>
       </c>
+      <c r="O108" s="1" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="P108" s="3" t="n">
+        <v>-0.005639655684179156</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -5481,6 +6135,12 @@
       <c r="N109" s="2" t="n">
         <v>0.003432003432003411</v>
       </c>
+      <c r="O109" s="1" t="n">
+        <v>0.2318</v>
+      </c>
+      <c r="P109" s="3" t="n">
+        <v>-0.008978195810175249</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -5527,6 +6187,12 @@
       <c r="N110" s="2" t="n">
         <v>0.002656042496679954</v>
       </c>
+      <c r="O110" s="1" t="n">
+        <v>0.01507</v>
+      </c>
+      <c r="P110" s="3" t="n">
+        <v>-0.001986754966887451</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -5573,6 +6239,12 @@
       <c r="N111" s="2" t="n">
         <v>0.004918032786885189</v>
       </c>
+      <c r="O111" s="1" t="n">
+        <v>1.835</v>
+      </c>
+      <c r="P111" s="3" t="n">
+        <v>-0.00217509516041327</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -5619,6 +6291,12 @@
       <c r="N112" s="3" t="n">
         <v>-0.0002602133749673724</v>
       </c>
+      <c r="O112" s="1" t="n">
+        <v>0.03851</v>
+      </c>
+      <c r="P112" s="2" t="n">
+        <v>0.002342529932326908</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -5665,6 +6343,12 @@
       <c r="N113" s="3" t="n">
         <v>-0.001640881387716754</v>
       </c>
+      <c r="O113" s="1" t="n">
+        <v>4.272</v>
+      </c>
+      <c r="P113" s="2" t="n">
+        <v>0.003052359708851819</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -5711,6 +6395,12 @@
       <c r="N114" s="3" t="n">
         <v>-0.008883082952318792</v>
       </c>
+      <c r="O114" s="1" t="n">
+        <v>0.007441</v>
+      </c>
+      <c r="P114" s="3" t="n">
+        <v>-0.01924344273098725</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -5757,6 +6447,12 @@
       <c r="N115" s="2" t="n">
         <v>0.009613438575187132</v>
       </c>
+      <c r="O115" s="1" t="n">
+        <v>0.09907000000000001</v>
+      </c>
+      <c r="P115" s="3" t="n">
+        <v>-0.007016137115365263</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -5803,6 +6499,12 @@
       <c r="N116" s="2" t="n">
         <v>0.002532256119618978</v>
       </c>
+      <c r="O116" s="1" t="n">
+        <v>0.08276</v>
+      </c>
+      <c r="P116" s="3" t="n">
+        <v>-0.004570603800817962</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -5849,6 +6551,12 @@
       <c r="N117" s="2" t="n">
         <v>0.006993006993006962</v>
       </c>
+      <c r="O117" s="1" t="n">
+        <v>0.3001</v>
+      </c>
+      <c r="P117" s="3" t="n">
+        <v>-0.007605820105820186</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -5895,6 +6603,12 @@
       <c r="N118" s="2" t="n">
         <v>0.0004407227853681385</v>
       </c>
+      <c r="O118" s="1" t="n">
+        <v>0.02264</v>
+      </c>
+      <c r="P118" s="3" t="n">
+        <v>-0.002643171806167446</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -5941,6 +6655,12 @@
       <c r="N119" s="3" t="n">
         <v>-0.001295336787564804</v>
       </c>
+      <c r="O119" s="1" t="n">
+        <v>0.154</v>
+      </c>
+      <c r="P119" s="3" t="n">
+        <v>-0.001297016861219233</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -5987,6 +6707,12 @@
       <c r="N120" s="2" t="n">
         <v>0.05436498984886079</v>
       </c>
+      <c r="O120" s="1" t="n">
+        <v>0.004796</v>
+      </c>
+      <c r="P120" s="2" t="n">
+        <v>0.02610183996576802</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -6033,6 +6759,12 @@
       <c r="N121" s="3" t="n">
         <v>-0.003225063349458679</v>
       </c>
+      <c r="O121" s="1" t="n">
+        <v>0.433</v>
+      </c>
+      <c r="P121" s="2" t="n">
+        <v>0.0006933210076265831</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -6079,6 +6811,12 @@
       <c r="N122" s="2" t="n">
         <v>0.001285347043701801</v>
       </c>
+      <c r="O122" s="1" t="n">
+        <v>0.777</v>
+      </c>
+      <c r="P122" s="3" t="n">
+        <v>-0.002567394094993583</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -6125,6 +6863,12 @@
       <c r="N123" s="2" t="n">
         <v>0.002312138728323766</v>
       </c>
+      <c r="O123" s="1" t="n">
+        <v>0.0864</v>
+      </c>
+      <c r="P123" s="3" t="n">
+        <v>-0.003460207612456686</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -6171,6 +6915,12 @@
       <c r="N124" s="3" t="n">
         <v>-0.01270849880857827</v>
       </c>
+      <c r="O124" s="1" t="n">
+        <v>0.01231</v>
+      </c>
+      <c r="P124" s="3" t="n">
+        <v>-0.00965406275140791</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -6217,6 +6967,12 @@
       <c r="N125" s="2" t="n">
         <v>0.001126126126126116</v>
       </c>
+      <c r="O125" s="1" t="n">
+        <v>0.09733</v>
+      </c>
+      <c r="P125" s="3" t="n">
+        <v>-0.004703957459862993</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -6263,6 +7019,12 @@
       <c r="N126" s="2" t="n">
         <v>0.000212720697723806</v>
       </c>
+      <c r="O126" s="1" t="n">
+        <v>0.04672</v>
+      </c>
+      <c r="P126" s="3" t="n">
+        <v>-0.006380263717567028</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -6309,6 +7071,12 @@
       <c r="N127" s="2" t="n">
         <v>0.0188087774294669</v>
       </c>
+      <c r="O127" s="1" t="n">
+        <v>3.18e-05</v>
+      </c>
+      <c r="P127" s="3" t="n">
+        <v>-0.02153846153846144</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -6355,6 +7123,12 @@
       <c r="N128" s="3" t="n">
         <v>-0.0006956521739129669</v>
       </c>
+      <c r="O128" s="1" t="n">
+        <v>0.5651</v>
+      </c>
+      <c r="P128" s="3" t="n">
+        <v>-0.01653324051514089</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -6401,6 +7175,12 @@
       <c r="N129" s="2" t="n">
         <v>0.0006079027355622852</v>
       </c>
+      <c r="O129" s="1" t="n">
+        <v>0.06549000000000001</v>
+      </c>
+      <c r="P129" s="3" t="n">
+        <v>-0.005315917375455487</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -6447,6 +7227,12 @@
       <c r="N130" s="2" t="n">
         <v>0.008652246256239631</v>
       </c>
+      <c r="O130" s="1" t="n">
+        <v>0.0006061</v>
+      </c>
+      <c r="P130" s="3" t="n">
+        <v>-0.0001649620587264075</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -6493,6 +7279,12 @@
       <c r="N131" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="O131" s="1" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="P131" s="3" t="n">
+        <v>-0.01136363636363637</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -6539,6 +7331,12 @@
       <c r="N132" s="2" t="n">
         <v>0.001324503311258316</v>
       </c>
+      <c r="O132" s="1" t="n">
+        <v>0.3006</v>
+      </c>
+      <c r="P132" s="3" t="n">
+        <v>-0.005952380952381031</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -6585,6 +7383,12 @@
       <c r="N133" s="3" t="n">
         <v>-0.002701080432172863</v>
       </c>
+      <c r="O133" s="1" t="n">
+        <v>0.03312</v>
+      </c>
+      <c r="P133" s="3" t="n">
+        <v>-0.003310261811616188</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -6631,6 +7435,12 @@
       <c r="N134" s="2" t="n">
         <v>0.001381883507220381</v>
       </c>
+      <c r="O134" s="1" t="n">
+        <v>0.14436</v>
+      </c>
+      <c r="P134" s="3" t="n">
+        <v>-0.00393293314013672</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -6677,6 +7487,12 @@
       <c r="N135" s="2" t="n">
         <v>0.00472653612424042</v>
       </c>
+      <c r="O135" s="1" t="n">
+        <v>0.02954</v>
+      </c>
+      <c r="P135" s="3" t="n">
+        <v>-0.007392473118279618</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -6723,6 +7539,12 @@
       <c r="N136" s="2" t="n">
         <v>0.002122391227449548</v>
       </c>
+      <c r="O136" s="1" t="n">
+        <v>28.26</v>
+      </c>
+      <c r="P136" s="3" t="n">
+        <v>-0.002470878926932465</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -6769,6 +7591,12 @@
       <c r="N137" s="2" t="n">
         <v>0.005577504066930058</v>
       </c>
+      <c r="O137" s="1" t="n">
+        <v>0.0004299</v>
+      </c>
+      <c r="P137" s="3" t="n">
+        <v>-0.006470996071180989</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -6815,6 +7643,12 @@
       <c r="N138" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="O138" s="1" t="n">
+        <v>0.0295</v>
+      </c>
+      <c r="P138" s="2" t="n">
+        <v>0.0004069451980465994</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -6861,6 +7695,12 @@
       <c r="N139" s="3" t="n">
         <v>-0.0017688065757986</v>
       </c>
+      <c r="O139" s="1" t="n">
+        <v>0.09607</v>
+      </c>
+      <c r="P139" s="2" t="n">
+        <v>0.001355013550135555</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -6907,6 +7747,12 @@
       <c r="N140" s="3" t="n">
         <v>-0.003360403248389748</v>
       </c>
+      <c r="O140" s="1" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="P140" s="2" t="n">
+        <v>0.0002809778027535515</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -6953,6 +7799,12 @@
       <c r="N141" s="3" t="n">
         <v>-0.004047093451066924</v>
       </c>
+      <c r="O141" s="1" t="n">
+        <v>0.02632</v>
+      </c>
+      <c r="P141" s="3" t="n">
+        <v>-0.02770594754340601</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -6999,6 +7851,12 @@
       <c r="N142" s="2" t="n">
         <v>0.009997403271877342</v>
       </c>
+      <c r="O142" s="1" t="n">
+        <v>0.07770000000000001</v>
+      </c>
+      <c r="P142" s="3" t="n">
+        <v>-0.001156961048977926</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -7045,6 +7903,12 @@
       <c r="N143" s="3" t="n">
         <v>-0.00146264626462652</v>
       </c>
+      <c r="O143" s="1" t="n">
+        <v>0.08871999999999999</v>
+      </c>
+      <c r="P143" s="3" t="n">
+        <v>-0.0003380281690141098</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -7091,6 +7955,12 @@
       <c r="N144" s="2" t="n">
         <v>0.0004918839153959465</v>
       </c>
+      <c r="O144" s="1" t="n">
+        <v>0.02036</v>
+      </c>
+      <c r="P144" s="2" t="n">
+        <v>0.000983284169124837</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -7137,6 +8007,12 @@
       <c r="N145" s="2" t="n">
         <v>0.00422237860661501</v>
       </c>
+      <c r="O145" s="1" t="n">
+        <v>0.11422</v>
+      </c>
+      <c r="P145" s="2" t="n">
+        <v>0.0005255781359495839</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -7183,6 +8059,12 @@
       <c r="N146" s="2" t="n">
         <v>0.008544199802826129</v>
       </c>
+      <c r="O146" s="1" t="n">
+        <v>0.3022</v>
+      </c>
+      <c r="P146" s="3" t="n">
+        <v>-0.01531443466927332</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -7229,6 +8111,12 @@
       <c r="N147" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="O147" s="1" t="n">
+        <v>0.122</v>
+      </c>
+      <c r="P147" s="3" t="n">
+        <v>-0.008130081300813016</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -7275,6 +8163,12 @@
       <c r="N148" s="2" t="n">
         <v>0.005521754690935079</v>
       </c>
+      <c r="O148" s="1" t="n">
+        <v>1.9534</v>
+      </c>
+      <c r="P148" s="3" t="n">
+        <v>-0.006762597244114439</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -7321,6 +8215,12 @@
       <c r="N149" s="3" t="n">
         <v>-0.001936108422071669</v>
       </c>
+      <c r="O149" s="1" t="n">
+        <v>0.06155</v>
+      </c>
+      <c r="P149" s="3" t="n">
+        <v>-0.005011315874555412</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -7367,6 +8267,12 @@
       <c r="N150" s="3" t="n">
         <v>-0.02056866303690269</v>
       </c>
+      <c r="O150" s="1" t="n">
+        <v>0.1614</v>
+      </c>
+      <c r="P150" s="3" t="n">
+        <v>-0.003088326127239039</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -7413,6 +8319,12 @@
       <c r="N151" s="2" t="n">
         <v>0.00478683620044872</v>
       </c>
+      <c r="O151" s="1" t="n">
+        <v>6.669999999999999e-05</v>
+      </c>
+      <c r="P151" s="3" t="n">
+        <v>-0.006997171356260244</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -7459,6 +8371,12 @@
       <c r="N152" s="3" t="n">
         <v>-0.008736559139785056</v>
       </c>
+      <c r="O152" s="1" t="n">
+        <v>0.01472</v>
+      </c>
+      <c r="P152" s="3" t="n">
+        <v>-0.002033898305084663</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -7505,6 +8423,12 @@
       <c r="N153" s="2" t="n">
         <v>0.005752636625119778</v>
       </c>
+      <c r="O153" s="1" t="n">
+        <v>0.02089</v>
+      </c>
+      <c r="P153" s="3" t="n">
+        <v>-0.004289799809342221</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -7551,6 +8475,12 @@
       <c r="N154" s="3" t="n">
         <v>-0.003681392235609011</v>
       </c>
+      <c r="O154" s="1" t="n">
+        <v>0.0005938</v>
+      </c>
+      <c r="P154" s="3" t="n">
+        <v>-0.002687269062814979</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -7597,6 +8527,12 @@
       <c r="N155" s="2" t="n">
         <v>0.003487792725460917</v>
       </c>
+      <c r="O155" s="1" t="n">
+        <v>0.04014</v>
+      </c>
+      <c r="P155" s="3" t="n">
+        <v>-0.003475670307845115</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -7643,6 +8579,12 @@
       <c r="N156" s="2" t="n">
         <v>0.001587301587301523</v>
       </c>
+      <c r="O156" s="1" t="n">
+        <v>0.01888</v>
+      </c>
+      <c r="P156" s="3" t="n">
+        <v>-0.002641310089804436</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -7689,6 +8631,12 @@
       <c r="N157" s="2" t="n">
         <v>0.008344923504867855</v>
       </c>
+      <c r="O157" s="1" t="n">
+        <v>0.08704000000000001</v>
+      </c>
+      <c r="P157" s="2" t="n">
+        <v>0.0004597701149426696</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -7735,6 +8683,12 @@
       <c r="N158" s="2" t="n">
         <v>0.01071643588199886</v>
       </c>
+      <c r="O158" s="1" t="n">
+        <v>0.008345</v>
+      </c>
+      <c r="P158" s="3" t="n">
+        <v>-0.005837502978317898</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -7781,6 +8735,12 @@
       <c r="N159" s="2" t="n">
         <v>0.0004004805766921642</v>
       </c>
+      <c r="O159" s="1" t="n">
+        <v>2.483</v>
+      </c>
+      <c r="P159" s="3" t="n">
+        <v>-0.006004803843074509</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -7827,6 +8787,12 @@
       <c r="N160" s="2" t="n">
         <v>0.002103131328867366</v>
       </c>
+      <c r="O160" s="1" t="n">
+        <v>1.281</v>
+      </c>
+      <c r="P160" s="3" t="n">
+        <v>-0.004275165176836425</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -7873,6 +8839,12 @@
       <c r="N161" s="3" t="n">
         <v>-0.002783669141039261</v>
       </c>
+      <c r="O161" s="1" t="n">
+        <v>0.007524</v>
+      </c>
+      <c r="P161" s="2" t="n">
+        <v>0.0001329256945367716</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -7919,6 +8891,12 @@
       <c r="N162" s="3" t="n">
         <v>-0.01148325358851661</v>
       </c>
+      <c r="O162" s="1" t="n">
+        <v>0.004231</v>
+      </c>
+      <c r="P162" s="2" t="n">
+        <v>0.02395934172313652</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -7965,6 +8943,12 @@
       <c r="N163" s="2" t="n">
         <v>0.002083333333333248</v>
       </c>
+      <c r="O163" s="1" t="n">
+        <v>0.096</v>
+      </c>
+      <c r="P163" s="3" t="n">
+        <v>-0.002079002079001995</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -8011,6 +8995,12 @@
       <c r="N164" s="2" t="n">
         <v>0.004269175108538362</v>
       </c>
+      <c r="O164" s="1" t="n">
+        <v>1.3836</v>
+      </c>
+      <c r="P164" s="3" t="n">
+        <v>-0.003098205922616882</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -8057,6 +9047,12 @@
       <c r="N165" s="2" t="n">
         <v>0.01361247523046439</v>
       </c>
+      <c r="O165" s="1" t="n">
+        <v>0.023511</v>
+      </c>
+      <c r="P165" s="3" t="n">
+        <v>-0.0008074798130045978</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -8103,6 +9099,12 @@
       <c r="N166" s="3" t="n">
         <v>-0.01867539468617633</v>
       </c>
+      <c r="O166" s="1" t="n">
+        <v>0.005041</v>
+      </c>
+      <c r="P166" s="3" t="n">
+        <v>-0.01098685501275253</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -8149,6 +9151,12 @@
       <c r="N167" s="2" t="n">
         <v>0.005335365853658371</v>
       </c>
+      <c r="O167" s="1" t="n">
+        <v>0.06569999999999999</v>
+      </c>
+      <c r="P167" s="3" t="n">
+        <v>-0.003790750568612589</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -8195,6 +9203,12 @@
       <c r="N168" s="2" t="n">
         <v>0.002109704641350272</v>
       </c>
+      <c r="O168" s="1" t="n">
+        <v>0.09520000000000001</v>
+      </c>
+      <c r="P168" s="2" t="n">
+        <v>0.002105263157894797</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -8241,6 +9255,12 @@
       <c r="N169" s="2" t="n">
         <v>0.001310615989514928</v>
       </c>
+      <c r="O169" s="1" t="n">
+        <v>0.03815</v>
+      </c>
+      <c r="P169" s="3" t="n">
+        <v>-0.001308900523560065</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -8287,6 +9307,12 @@
       <c r="N170" s="2" t="n">
         <v>0.003787878787878804</v>
       </c>
+      <c r="O170" s="1" t="n">
+        <v>0.007116</v>
+      </c>
+      <c r="P170" s="3" t="n">
+        <v>-0.005450733752620542</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -8333,6 +9359,12 @@
       <c r="N171" s="2" t="n">
         <v>0.00204200700116696</v>
       </c>
+      <c r="O171" s="1" t="n">
+        <v>0.341</v>
+      </c>
+      <c r="P171" s="3" t="n">
+        <v>-0.007278020378457066</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -8379,6 +9411,12 @@
       <c r="N172" s="2" t="n">
         <v>0.005324031577014855</v>
       </c>
+      <c r="O172" s="1" t="n">
+        <v>5.449</v>
+      </c>
+      <c r="P172" s="3" t="n">
+        <v>-0.004930606281957658</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -8425,6 +9463,12 @@
       <c r="N173" s="2" t="n">
         <v>0.005044966001316101</v>
       </c>
+      <c r="O173" s="1" t="n">
+        <v>0.0454</v>
+      </c>
+      <c r="P173" s="3" t="n">
+        <v>-0.009166302924487052</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -8471,6 +9515,12 @@
       <c r="N174" s="2" t="n">
         <v>0.000511639805576853</v>
       </c>
+      <c r="O174" s="1" t="n">
+        <v>0.039</v>
+      </c>
+      <c r="P174" s="3" t="n">
+        <v>-0.002812579902838123</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -8517,6 +9567,12 @@
       <c r="N175" s="3" t="n">
         <v>-0.007106057914372021</v>
       </c>
+      <c r="O175" s="1" t="n">
+        <v>0.005571</v>
+      </c>
+      <c r="P175" s="3" t="n">
+        <v>-0.003220611916264052</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -8563,6 +9619,12 @@
       <c r="N176" s="2" t="n">
         <v>0.002635046113306875</v>
       </c>
+      <c r="O176" s="1" t="n">
+        <v>0.00755</v>
+      </c>
+      <c r="P176" s="3" t="n">
+        <v>-0.007884362680683219</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -8609,6 +9671,12 @@
       <c r="N177" s="2" t="n">
         <v>0.006884681583476642</v>
       </c>
+      <c r="O177" s="1" t="n">
+        <v>1.744</v>
+      </c>
+      <c r="P177" s="3" t="n">
+        <v>-0.00626780626780621</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -8655,6 +9723,12 @@
       <c r="N178" s="2" t="n">
         <v>0.001340311462854276</v>
       </c>
+      <c r="O178" s="1" t="n">
+        <v>15.618</v>
+      </c>
+      <c r="P178" s="3" t="n">
+        <v>-0.004525463700681989</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -8701,6 +9775,12 @@
       <c r="N179" s="2" t="n">
         <v>0.006472491909385119</v>
       </c>
+      <c r="O179" s="1" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="P179" s="3" t="n">
+        <v>-0.003215434083601289</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -8747,6 +9827,12 @@
       <c r="N180" s="2" t="n">
         <v>0.002066542674106136</v>
       </c>
+      <c r="O180" s="1" t="n">
+        <v>0.09694999999999999</v>
+      </c>
+      <c r="P180" s="3" t="n">
+        <v>-0.0003093421323984559</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -8793,6 +9879,12 @@
       <c r="N181" s="2" t="n">
         <v>0.0005330490405118164</v>
       </c>
+      <c r="O181" s="1" t="n">
+        <v>0.1871</v>
+      </c>
+      <c r="P181" s="3" t="n">
+        <v>-0.00319659030367617</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -8839,6 +9931,12 @@
       <c r="N182" s="2" t="n">
         <v>0.001010951979780919</v>
       </c>
+      <c r="O182" s="1" t="n">
+        <v>0.05935</v>
+      </c>
+      <c r="P182" s="3" t="n">
+        <v>-0.001009930988049109</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -8885,6 +9983,12 @@
       <c r="N183" s="3" t="n">
         <v>-0.002485501242750664</v>
       </c>
+      <c r="O183" s="1" t="n">
+        <v>0.01201</v>
+      </c>
+      <c r="P183" s="3" t="n">
+        <v>-0.002491694352159511</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -8931,6 +10035,12 @@
       <c r="N184" s="2" t="n">
         <v>0.001392111368909456</v>
       </c>
+      <c r="O184" s="1" t="n">
+        <v>0.02144</v>
+      </c>
+      <c r="P184" s="3" t="n">
+        <v>-0.006487488415199156</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -8977,6 +10087,12 @@
       <c r="N185" s="2" t="n">
         <v>0.005524861878453044</v>
       </c>
+      <c r="O185" s="1" t="n">
+        <v>0.363</v>
+      </c>
+      <c r="P185" s="3" t="n">
+        <v>-0.00274725274725275</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -9023,6 +10139,12 @@
       <c r="N186" s="2" t="n">
         <v>0.002750130958616987</v>
       </c>
+      <c r="O186" s="1" t="n">
+        <v>0.007621</v>
+      </c>
+      <c r="P186" s="3" t="n">
+        <v>-0.00470158025336288</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -9069,6 +10191,12 @@
       <c r="N187" s="2" t="n">
         <v>0.002968460111317133</v>
       </c>
+      <c r="O187" s="1" t="n">
+        <v>0.2686</v>
+      </c>
+      <c r="P187" s="3" t="n">
+        <v>-0.006289308176100553</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -9115,6 +10243,12 @@
       <c r="N188" s="2" t="n">
         <v>0.006726457399103218</v>
       </c>
+      <c r="O188" s="1" t="n">
+        <v>0.0491</v>
+      </c>
+      <c r="P188" s="3" t="n">
+        <v>-0.005871633933994847</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -9161,6 +10295,12 @@
       <c r="N189" s="2" t="n">
         <v>0.004687499999999917</v>
       </c>
+      <c r="O189" s="1" t="n">
+        <v>0.2556</v>
+      </c>
+      <c r="P189" s="3" t="n">
+        <v>-0.006220839813374768</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -9207,6 +10347,12 @@
       <c r="N190" s="2" t="n">
         <v>0.001763046544428774</v>
       </c>
+      <c r="O190" s="1" t="n">
+        <v>0.5673</v>
+      </c>
+      <c r="P190" s="3" t="n">
+        <v>-0.001583949313621985</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -9253,6 +10399,12 @@
       <c r="N191" s="2" t="n">
         <v>0.004305348567643764</v>
       </c>
+      <c r="O191" s="1" t="n">
+        <v>6.032</v>
+      </c>
+      <c r="P191" s="3" t="n">
+        <v>-0.005441055234954717</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -9299,6 +10451,12 @@
       <c r="N192" s="2" t="n">
         <v>0.004004576659038778</v>
       </c>
+      <c r="O192" s="1" t="n">
+        <v>0.3507</v>
+      </c>
+      <c r="P192" s="3" t="n">
+        <v>-0.0008547008547007606</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -9345,6 +10503,12 @@
       <c r="N193" s="3" t="n">
         <v>-0.001555209953343746</v>
       </c>
+      <c r="O193" s="1" t="n">
+        <v>0.0639</v>
+      </c>
+      <c r="P193" s="3" t="n">
+        <v>-0.0046728971962616</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -9391,6 +10555,12 @@
       <c r="N194" s="2" t="n">
         <v>0.003997715591090642</v>
       </c>
+      <c r="O194" s="1" t="n">
+        <v>0.01743</v>
+      </c>
+      <c r="P194" s="3" t="n">
+        <v>-0.008532423208190977</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -9437,6 +10607,12 @@
       <c r="N195" s="3" t="n">
         <v>-0.0004624812117007859</v>
       </c>
+      <c r="O195" s="1" t="n">
+        <v>0.0008494</v>
+      </c>
+      <c r="P195" s="3" t="n">
+        <v>-0.01746674378253324</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -9483,6 +10659,12 @@
       <c r="N196" s="3" t="n">
         <v>-0.001964636542239733</v>
       </c>
+      <c r="O196" s="1" t="n">
+        <v>0.001012</v>
+      </c>
+      <c r="P196" s="3" t="n">
+        <v>-0.00393700787401563</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -9529,6 +10711,12 @@
       <c r="N197" s="2" t="n">
         <v>0.003719776813391287</v>
       </c>
+      <c r="O197" s="1" t="n">
+        <v>0.0001615</v>
+      </c>
+      <c r="P197" s="3" t="n">
+        <v>-0.002470660901791289</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -9575,6 +10763,12 @@
       <c r="N198" s="2" t="n">
         <v>0.002992633517495373</v>
       </c>
+      <c r="O198" s="1" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="P198" s="3" t="n">
+        <v>-0.006196924489327549</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -9621,6 +10815,12 @@
       <c r="N199" s="2" t="n">
         <v>0.00429184549356227</v>
       </c>
+      <c r="O199" s="1" t="n">
+        <v>0.1631</v>
+      </c>
+      <c r="P199" s="3" t="n">
+        <v>-0.004273504273504311</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -9667,6 +10867,12 @@
       <c r="N200" s="2" t="n">
         <v>0.002014690451206692</v>
       </c>
+      <c r="O200" s="1" t="n">
+        <v>0.023831</v>
+      </c>
+      <c r="P200" s="3" t="n">
+        <v>-0.001759309680391945</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -9713,6 +10919,12 @@
       <c r="N201" s="3" t="n">
         <v>-0.001695188892476605</v>
       </c>
+      <c r="O201" s="1" t="n">
+        <v>0.1226</v>
+      </c>
+      <c r="P201" s="3" t="n">
+        <v>-0.008652057896013596</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -9759,6 +10971,12 @@
       <c r="N202" s="2" t="n">
         <v>0.002175489485134192</v>
       </c>
+      <c r="O202" s="1" t="n">
+        <v>0.01379</v>
+      </c>
+      <c r="P202" s="3" t="n">
+        <v>-0.002170767004341571</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -9805,6 +11023,12 @@
       <c r="N203" s="2" t="n">
         <v>0.005380288579114648</v>
       </c>
+      <c r="O203" s="1" t="n">
+        <v>0.04087</v>
+      </c>
+      <c r="P203" s="3" t="n">
+        <v>-0.005837995621503384</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -9851,6 +11075,12 @@
       <c r="N204" s="2" t="n">
         <v>0.004662004662004742</v>
       </c>
+      <c r="O204" s="1" t="n">
+        <v>0.02575</v>
+      </c>
+      <c r="P204" s="3" t="n">
+        <v>-0.004253673627223606</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -9897,6 +11127,12 @@
       <c r="N205" s="2" t="n">
         <v>0.006952491309385869</v>
       </c>
+      <c r="O205" s="1" t="n">
+        <v>0.4319</v>
+      </c>
+      <c r="P205" s="3" t="n">
+        <v>-0.005983889528193305</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -9943,6 +11179,12 @@
       <c r="N206" s="2" t="n">
         <v>0.002176752285589811</v>
       </c>
+      <c r="O206" s="1" t="n">
+        <v>0.02293</v>
+      </c>
+      <c r="P206" s="3" t="n">
+        <v>-0.003909643788010417</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -9989,6 +11231,12 @@
       <c r="N207" s="2" t="n">
         <v>0.001680268843014804</v>
       </c>
+      <c r="O207" s="1" t="n">
+        <v>4.157</v>
+      </c>
+      <c r="P207" s="3" t="n">
+        <v>-0.003834172058471127</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -10035,6 +11283,12 @@
       <c r="N208" s="2" t="n">
         <v>0.0002710394362380557</v>
       </c>
+      <c r="O208" s="1" t="n">
+        <v>0.07353999999999999</v>
+      </c>
+      <c r="P208" s="3" t="n">
+        <v>-0.003658040915865145</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -10081,6 +11335,12 @@
       <c r="N209" s="2" t="n">
         <v>0.00427147603227353</v>
       </c>
+      <c r="O209" s="1" t="n">
+        <v>0.04209</v>
+      </c>
+      <c r="P209" s="3" t="n">
+        <v>-0.005434782608695676</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -10127,6 +11387,12 @@
       <c r="N210" s="2" t="n">
         <v>0.003250270855904752</v>
       </c>
+      <c r="O210" s="1" t="n">
+        <v>0.1843</v>
+      </c>
+      <c r="P210" s="3" t="n">
+        <v>-0.004859611231101576</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -10173,6 +11439,12 @@
       <c r="N211" s="3" t="n">
         <v>-0.001255755546253641</v>
       </c>
+      <c r="O211" s="1" t="n">
+        <v>0.2368</v>
+      </c>
+      <c r="P211" s="3" t="n">
+        <v>-0.007544006705783722</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -10219,6 +11491,12 @@
       <c r="N212" s="2" t="n">
         <v>0.005280844935189498</v>
       </c>
+      <c r="O212" s="1" t="n">
+        <v>0.002083</v>
+      </c>
+      <c r="P212" s="3" t="n">
+        <v>-0.00525310410697217</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -10265,6 +11543,12 @@
       <c r="N213" s="2" t="n">
         <v>0.002143622722400859</v>
       </c>
+      <c r="O213" s="1" t="n">
+        <v>0.9320000000000001</v>
+      </c>
+      <c r="P213" s="3" t="n">
+        <v>-0.003208556149732623</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -10311,6 +11595,12 @@
       <c r="N214" s="2" t="n">
         <v>0.006130670870555318</v>
       </c>
+      <c r="O214" s="1" t="n">
+        <v>0.005718</v>
+      </c>
+      <c r="P214" s="3" t="n">
+        <v>-0.004526462395543172</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -10357,6 +11647,12 @@
       <c r="N215" s="2" t="n">
         <v>0.003837018088799595</v>
       </c>
+      <c r="O215" s="1" t="n">
+        <v>0.05469</v>
+      </c>
+      <c r="P215" s="3" t="n">
+        <v>-0.004550418638514747</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -10403,6 +11699,12 @@
       <c r="N216" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="O216" s="1" t="n">
+        <v>0.0631</v>
+      </c>
+      <c r="P216" s="3" t="n">
+        <v>-0.004731861198738087</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -10449,6 +11751,12 @@
       <c r="N217" s="2" t="n">
         <v>0.002157497303128283</v>
       </c>
+      <c r="O217" s="1" t="n">
+        <v>0.0925</v>
+      </c>
+      <c r="P217" s="3" t="n">
+        <v>-0.004305705059203419</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -10495,6 +11803,12 @@
       <c r="N218" s="2" t="n">
         <v>0.005358705161854663</v>
       </c>
+      <c r="O218" s="1" t="n">
+        <v>0.27643</v>
+      </c>
+      <c r="P218" s="2" t="n">
+        <v>0.00232060625838511</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -10541,6 +11855,12 @@
       <c r="N219" s="2" t="n">
         <v>0.005838967424708027</v>
       </c>
+      <c r="O219" s="1" t="n">
+        <v>0.003252</v>
+      </c>
+      <c r="P219" s="3" t="n">
+        <v>-0.006416131989000841</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -10587,6 +11907,12 @@
       <c r="N220" s="3" t="n">
         <v>-1.000626392150242e-06</v>
       </c>
+      <c r="O220" s="1" t="n">
+        <v>0.999374</v>
+      </c>
+      <c r="P220" s="2" t="n">
+        <v>1.00062739340442e-06</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -10633,6 +11959,12 @@
       <c r="N221" s="2" t="n">
         <v>0.01825192802056561</v>
       </c>
+      <c r="O221" s="1" t="n">
+        <v>0.03906</v>
+      </c>
+      <c r="P221" s="3" t="n">
+        <v>-0.01388538247917197</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -10679,6 +12011,12 @@
       <c r="N222" s="2" t="n">
         <v>0.003219575016097819</v>
       </c>
+      <c r="O222" s="1" t="n">
+        <v>0.04644</v>
+      </c>
+      <c r="P222" s="3" t="n">
+        <v>-0.006418485237483841</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -10725,6 +12063,12 @@
       <c r="N223" s="2" t="n">
         <v>0.001899335232668488</v>
       </c>
+      <c r="O223" s="1" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="P223" s="3" t="n">
+        <v>-0.004739336492891</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -10771,6 +12115,12 @@
       <c r="N224" s="2" t="n">
         <v>0.006451612903225784</v>
       </c>
+      <c r="O224" s="1" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="P224" s="2" t="n">
+        <v>0.005128205128205133</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -10817,6 +12167,12 @@
       <c r="N225" s="2" t="n">
         <v>0.004334164048109208</v>
       </c>
+      <c r="O225" s="1" t="n">
+        <v>0.000922</v>
+      </c>
+      <c r="P225" s="3" t="n">
+        <v>-0.005286438666522888</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -10863,6 +12219,12 @@
       <c r="N226" s="2" t="n">
         <v>0.001416263424997033</v>
       </c>
+      <c r="O226" s="1" t="n">
+        <v>0.008484</v>
+      </c>
+      <c r="P226" s="3" t="n">
+        <v>-0.0001178550383028009</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -10909,6 +12271,12 @@
       <c r="N227" s="2" t="n">
         <v>0.001936108422071557</v>
       </c>
+      <c r="O227" s="1" t="n">
+        <v>0.04132</v>
+      </c>
+      <c r="P227" s="3" t="n">
+        <v>-0.001932367149758375</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -10955,6 +12323,12 @@
       <c r="N228" s="2" t="n">
         <v>0.001118568232662147</v>
       </c>
+      <c r="O228" s="1" t="n">
+        <v>0.03575</v>
+      </c>
+      <c r="P228" s="3" t="n">
+        <v>-0.001396648044692778</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -11001,6 +12375,12 @@
       <c r="N229" s="2" t="n">
         <v>0.001358431981370088</v>
       </c>
+      <c r="O229" s="1" t="n">
+        <v>0.05133</v>
+      </c>
+      <c r="P229" s="3" t="n">
+        <v>-0.005232558139534872</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -11047,6 +12427,12 @@
       <c r="N230" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="O230" s="1" t="n">
+        <v>0.001717</v>
+      </c>
+      <c r="P230" s="3" t="n">
+        <v>-0.001744186046511607</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -11093,6 +12479,12 @@
       <c r="N231" s="3" t="n">
         <v>-0.00533223954060698</v>
       </c>
+      <c r="O231" s="1" t="n">
+        <v>0.04832</v>
+      </c>
+      <c r="P231" s="3" t="n">
+        <v>-0.003711340206185559</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -11139,6 +12531,12 @@
       <c r="N232" s="2" t="n">
         <v>0.00643678160919546</v>
       </c>
+      <c r="O232" s="1" t="n">
+        <v>0.02167</v>
+      </c>
+      <c r="P232" s="3" t="n">
+        <v>-0.01005025125628147</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -11185,6 +12583,12 @@
       <c r="N233" s="2" t="n">
         <v>0.003763900769888886</v>
       </c>
+      <c r="O233" s="1" t="n">
+        <v>0.000584</v>
+      </c>
+      <c r="P233" s="3" t="n">
+        <v>-0.004602011249360851</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -11231,6 +12635,12 @@
       <c r="N234" s="2" t="n">
         <v>0.006573876773813333</v>
       </c>
+      <c r="O234" s="1" t="n">
+        <v>0.2207</v>
+      </c>
+      <c r="P234" s="3" t="n">
+        <v>-0.005945410323394234</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -11277,6 +12687,12 @@
       <c r="N235" s="3" t="n">
         <v>-0.008602150537634431</v>
       </c>
+      <c r="O235" s="1" t="n">
+        <v>0.01384</v>
+      </c>
+      <c r="P235" s="2" t="n">
+        <v>0.0007230657989876784</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -11323,6 +12739,12 @@
       <c r="N236" s="2" t="n">
         <v>0.004854368932038806</v>
       </c>
+      <c r="O236" s="1" t="n">
+        <v>0.0412</v>
+      </c>
+      <c r="P236" s="3" t="n">
+        <v>-0.004830917874396106</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -11369,6 +12791,12 @@
       <c r="N237" s="2" t="n">
         <v>0.002386634844868638</v>
       </c>
+      <c r="O237" s="1" t="n">
+        <v>0.00418</v>
+      </c>
+      <c r="P237" s="3" t="n">
+        <v>-0.004761904761904774</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -11415,6 +12843,12 @@
       <c r="N238" s="2" t="n">
         <v>0.004016064257028227</v>
       </c>
+      <c r="O238" s="1" t="n">
+        <v>0.0249</v>
+      </c>
+      <c r="P238" s="3" t="n">
+        <v>-0.004000000000000115</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -11461,6 +12895,12 @@
       <c r="N239" s="2" t="n">
         <v>0.0006711409395972881</v>
       </c>
+      <c r="O239" s="1" t="n">
+        <v>0.01488</v>
+      </c>
+      <c r="P239" s="3" t="n">
+        <v>-0.002012072434607564</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -11507,6 +12947,12 @@
       <c r="N240" s="2" t="n">
         <v>0.001532567049808466</v>
       </c>
+      <c r="O240" s="1" t="n">
+        <v>0.0003907</v>
+      </c>
+      <c r="P240" s="3" t="n">
+        <v>-0.003570517725070084</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -11553,6 +12999,12 @@
       <c r="N241" s="2" t="n">
         <v>0.004127579737335797</v>
       </c>
+      <c r="O241" s="1" t="n">
+        <v>0.2675</v>
+      </c>
+      <c r="P241" s="3" t="n">
+        <v>-0.000373692077727911</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -11599,6 +13051,12 @@
       <c r="N242" s="3" t="n">
         <v>-0.005085408788629386</v>
       </c>
+      <c r="O242" s="1" t="n">
+        <v>0.07607999999999999</v>
+      </c>
+      <c r="P242" s="3" t="n">
+        <v>-0.002883355176933314</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -11645,6 +13103,12 @@
       <c r="N243" s="3" t="n">
         <v>-0.007533902561526912</v>
       </c>
+      <c r="O243" s="1" t="n">
+        <v>0.01964</v>
+      </c>
+      <c r="P243" s="3" t="n">
+        <v>-0.006072874493927054</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -11691,6 +13155,12 @@
       <c r="N244" s="3" t="n">
         <v>-0.0009125128322116658</v>
       </c>
+      <c r="O244" s="1" t="n">
+        <v>0.08655</v>
+      </c>
+      <c r="P244" s="3" t="n">
+        <v>-0.01187350154127183</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -11737,6 +13207,12 @@
       <c r="N245" s="3" t="n">
         <v>-0.0007020499859590788</v>
       </c>
+      <c r="O245" s="1" t="n">
+        <v>1.4288</v>
+      </c>
+      <c r="P245" s="2" t="n">
+        <v>0.003793733314598898</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -11783,6 +13259,12 @@
       <c r="N246" s="3" t="n">
         <v>-0.000558347292015611</v>
       </c>
+      <c r="O246" s="1" t="n">
+        <v>0.01784</v>
+      </c>
+      <c r="P246" s="3" t="n">
+        <v>-0.003351955307262434</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -11829,6 +13311,12 @@
       <c r="N247" s="2" t="n">
         <v>0.004695546803998755</v>
       </c>
+      <c r="O247" s="1" t="n">
+        <v>0.006606</v>
+      </c>
+      <c r="P247" s="3" t="n">
+        <v>-0.004070556309362297</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -11875,6 +13363,12 @@
       <c r="N248" s="2" t="n">
         <v>0.00386380101424786</v>
       </c>
+      <c r="O248" s="1" t="n">
+        <v>0.004156</v>
+      </c>
+      <c r="P248" s="3" t="n">
+        <v>-0.0002405580947799213</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -11921,6 +13415,12 @@
       <c r="N249" s="2" t="n">
         <v>0.002737226277372214</v>
       </c>
+      <c r="O249" s="1" t="n">
+        <v>0.1097</v>
+      </c>
+      <c r="P249" s="3" t="n">
+        <v>-0.001819836214740599</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -11967,6 +13467,12 @@
       <c r="N250" s="2" t="n">
         <v>0.005841121495327068</v>
       </c>
+      <c r="O250" s="1" t="n">
+        <v>0.03424</v>
+      </c>
+      <c r="P250" s="3" t="n">
+        <v>-0.005807200929152114</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -12013,6 +13519,12 @@
       <c r="N251" s="2" t="n">
         <v>0.001855717930874431</v>
       </c>
+      <c r="O251" s="1" t="n">
+        <v>0.04321</v>
+      </c>
+      <c r="P251" s="2" t="n">
+        <v>0.0004630701551284831</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -12059,6 +13571,12 @@
       <c r="N252" s="2" t="n">
         <v>0.03610411418975649</v>
       </c>
+      <c r="O252" s="1" t="n">
+        <v>0.00628</v>
+      </c>
+      <c r="P252" s="2" t="n">
+        <v>0.0178282009724473</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -12105,6 +13623,12 @@
       <c r="N253" s="2" t="n">
         <v>0.004778972520908017</v>
       </c>
+      <c r="O253" s="1" t="n">
+        <v>0.01686</v>
+      </c>
+      <c r="P253" s="2" t="n">
+        <v>0.002378121284185397</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -12151,6 +13675,12 @@
       <c r="N254" s="2" t="n">
         <v>0.005388760585065483</v>
       </c>
+      <c r="O254" s="1" t="n">
+        <v>0.1302</v>
+      </c>
+      <c r="P254" s="3" t="n">
+        <v>-0.003062787136293903</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -12197,6 +13727,12 @@
       <c r="N255" s="3" t="n">
         <v>-0.001913875598086047</v>
       </c>
+      <c r="O255" s="1" t="n">
+        <v>0.02094</v>
+      </c>
+      <c r="P255" s="2" t="n">
+        <v>0.003835091083413241</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -12243,6 +13779,12 @@
       <c r="N256" s="2" t="n">
         <v>0.0004750593824227835</v>
       </c>
+      <c r="O256" s="1" t="n">
+        <v>0.02103</v>
+      </c>
+      <c r="P256" s="3" t="n">
+        <v>-0.001424501424501366</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -12289,6 +13831,12 @@
       <c r="N257" s="2" t="n">
         <v>0.001964636542239606</v>
       </c>
+      <c r="O257" s="1" t="n">
+        <v>0.02544</v>
+      </c>
+      <c r="P257" s="3" t="n">
+        <v>-0.002352941176470493</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -12335,6 +13883,12 @@
       <c r="N258" s="2" t="n">
         <v>0.00263264479546376</v>
       </c>
+      <c r="O258" s="1" t="n">
+        <v>0.14871</v>
+      </c>
+      <c r="P258" s="2" t="n">
+        <v>0.001211876388608453</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -12381,6 +13935,12 @@
       <c r="N259" s="2" t="n">
         <v>0.001962708537782059</v>
       </c>
+      <c r="O259" s="1" t="n">
+        <v>0.05093</v>
+      </c>
+      <c r="P259" s="3" t="n">
+        <v>-0.002350636630754067</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -12427,6 +13987,12 @@
       <c r="N260" s="2" t="n">
         <v>0.00108446800819384</v>
       </c>
+      <c r="O260" s="1" t="n">
+        <v>0.08309</v>
+      </c>
+      <c r="P260" s="2" t="n">
+        <v>0.0001203659123735691</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -12473,6 +14039,12 @@
       <c r="N261" s="2" t="n">
         <v>0.004189359028068709</v>
       </c>
+      <c r="O261" s="1" t="n">
+        <v>0.2458</v>
+      </c>
+      <c r="P261" s="2" t="n">
+        <v>0.0254484772632457</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -12519,6 +14091,12 @@
       <c r="N262" s="3" t="n">
         <v>-0.000701754385964835</v>
       </c>
+      <c r="O262" s="1" t="n">
+        <v>0.1418</v>
+      </c>
+      <c r="P262" s="3" t="n">
+        <v>-0.004213483146067342</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -12565,6 +14143,12 @@
       <c r="N263" s="2" t="n">
         <v>0.0002585983966898402</v>
       </c>
+      <c r="O263" s="1" t="n">
+        <v>0.0772</v>
+      </c>
+      <c r="P263" s="3" t="n">
+        <v>-0.002068252326783783</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -12611,6 +14195,12 @@
       <c r="N264" s="3" t="n">
         <v>-0.01681087762669963</v>
       </c>
+      <c r="O264" s="1" t="n">
+        <v>0.03948</v>
+      </c>
+      <c r="P264" s="3" t="n">
+        <v>-0.007291928589388951</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -12657,6 +14247,12 @@
       <c r="N265" s="2" t="n">
         <v>0.00261096605744126</v>
       </c>
+      <c r="O265" s="1" t="n">
+        <v>0.01527</v>
+      </c>
+      <c r="P265" s="3" t="n">
+        <v>-0.005859374999999987</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -12703,6 +14299,12 @@
       <c r="N266" s="3" t="n">
         <v>-0.002344273275284683</v>
       </c>
+      <c r="O266" s="1" t="n">
+        <v>0.00592</v>
+      </c>
+      <c r="P266" s="3" t="n">
+        <v>-0.006377979187646834</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -12749,6 +14351,12 @@
       <c r="N267" s="3" t="n">
         <v>-0.0008062348830960023</v>
       </c>
+      <c r="O267" s="1" t="n">
+        <v>0.03708</v>
+      </c>
+      <c r="P267" s="3" t="n">
+        <v>-0.002689618074233349</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -12795,6 +14403,12 @@
       <c r="N268" s="2" t="n">
         <v>0.002619515389652921</v>
       </c>
+      <c r="O268" s="1" t="n">
+        <v>0.03056</v>
+      </c>
+      <c r="P268" s="3" t="n">
+        <v>-0.001959503592423286</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -12841,6 +14455,12 @@
       <c r="N269" s="2" t="n">
         <v>0.004001759014951724</v>
       </c>
+      <c r="O269" s="1" t="n">
+        <v>0.22731</v>
+      </c>
+      <c r="P269" s="3" t="n">
+        <v>-0.004380009636021203</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -12887,6 +14507,12 @@
       <c r="N270" s="2" t="n">
         <v>0.00324675324675325</v>
       </c>
+      <c r="O270" s="1" t="n">
+        <v>0.921</v>
+      </c>
+      <c r="P270" s="3" t="n">
+        <v>-0.006472491909385119</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -12933,6 +14559,12 @@
       <c r="N271" s="2" t="n">
         <v>0.001929012345678971</v>
       </c>
+      <c r="O271" s="1" t="n">
+        <v>2.581</v>
+      </c>
+      <c r="P271" s="3" t="n">
+        <v>-0.006160954948016949</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -12979,6 +14611,12 @@
       <c r="N272" s="2" t="n">
         <v>0.005422993492407813</v>
       </c>
+      <c r="O272" s="1" t="n">
+        <v>0.1846</v>
+      </c>
+      <c r="P272" s="3" t="n">
+        <v>-0.004314994606256866</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -13025,6 +14663,12 @@
       <c r="N273" s="2" t="n">
         <v>0.002911679068262692</v>
       </c>
+      <c r="O273" s="1" t="n">
+        <v>0.03089</v>
+      </c>
+      <c r="P273" s="3" t="n">
+        <v>-0.003548387096774161</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -13071,6 +14715,12 @@
       <c r="N274" s="2" t="n">
         <v>0.002619172341540076</v>
       </c>
+      <c r="O274" s="1" t="n">
+        <v>0.1906</v>
+      </c>
+      <c r="P274" s="3" t="n">
+        <v>-0.004179728317659327</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -13117,6 +14767,12 @@
       <c r="N275" s="2" t="n">
         <v>0.004313443565779939</v>
       </c>
+      <c r="O275" s="1" t="n">
+        <v>0.06963</v>
+      </c>
+      <c r="P275" s="3" t="n">
+        <v>-0.00314960629921257</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -13163,6 +14819,12 @@
       <c r="N276" s="2" t="n">
         <v>0.001360544217687062</v>
       </c>
+      <c r="O276" s="1" t="n">
+        <v>0.08073</v>
+      </c>
+      <c r="P276" s="3" t="n">
+        <v>-0.002840909090909189</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -13209,6 +14871,12 @@
       <c r="N277" s="2" t="n">
         <v>0.00993377483443708</v>
       </c>
+      <c r="O277" s="1" t="n">
+        <v>0.004017</v>
+      </c>
+      <c r="P277" s="2" t="n">
+        <v>0.01311475409836065</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -13255,6 +14923,12 @@
       <c r="N278" s="2" t="n">
         <v>0.00128949065119278</v>
       </c>
+      <c r="O278" s="1" t="n">
+        <v>1.552</v>
+      </c>
+      <c r="P278" s="3" t="n">
+        <v>-0.0006439150032195041</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -13301,6 +14975,12 @@
       <c r="N279" s="2" t="n">
         <v>0.0009057971014493956</v>
       </c>
+      <c r="O279" s="1" t="n">
+        <v>0.01102</v>
+      </c>
+      <c r="P279" s="3" t="n">
+        <v>-0.002714932126696879</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -13347,6 +15027,12 @@
       <c r="N280" s="2" t="n">
         <v>0.01568429041234494</v>
       </c>
+      <c r="O280" s="1" t="n">
+        <v>0.04034</v>
+      </c>
+      <c r="P280" s="2" t="n">
+        <v>0.004732254047322607</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -13393,6 +15079,12 @@
       <c r="N281" s="2" t="n">
         <v>0.001315002988643144</v>
       </c>
+      <c r="O281" s="1" t="n">
+        <v>0.08358</v>
+      </c>
+      <c r="P281" s="3" t="n">
+        <v>-0.002148997134670482</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -13439,6 +15131,12 @@
       <c r="N282" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="O282" s="1" t="n">
+        <v>0.0265</v>
+      </c>
+      <c r="P282" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -13485,6 +15183,12 @@
       <c r="N283" s="2" t="n">
         <v>0.002620545073375337</v>
       </c>
+      <c r="O283" s="1" t="n">
+        <v>0.07622</v>
+      </c>
+      <c r="P283" s="3" t="n">
+        <v>-0.003920543648719401</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -13531,6 +15235,12 @@
       <c r="N284" s="2" t="n">
         <v>0.004323656578134689</v>
       </c>
+      <c r="O284" s="1" t="n">
+        <v>0.001616</v>
+      </c>
+      <c r="P284" s="3" t="n">
+        <v>-0.006150061500615022</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -13577,6 +15287,12 @@
       <c r="N285" s="2" t="n">
         <v>0.001482946119624294</v>
       </c>
+      <c r="O285" s="1" t="n">
+        <v>0.202</v>
+      </c>
+      <c r="P285" s="3" t="n">
+        <v>-0.002961500493583364</v>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -13623,6 +15339,12 @@
       <c r="N286" s="3" t="n">
         <v>-9.394964299145059e-05</v>
       </c>
+      <c r="O286" s="1" t="n">
+        <v>0.10609</v>
+      </c>
+      <c r="P286" s="3" t="n">
+        <v>-0.003194587992107424</v>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -13669,6 +15391,12 @@
       <c r="N287" s="2" t="n">
         <v>0.001737116386797845</v>
       </c>
+      <c r="O287" s="1" t="n">
+        <v>0.01729</v>
+      </c>
+      <c r="P287" s="3" t="n">
+        <v>-0.0005780346820809014</v>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -13715,6 +15443,12 @@
       <c r="N288" s="3" t="n">
         <v>-0.001314060446780498</v>
       </c>
+      <c r="O288" s="1" t="n">
+        <v>0.01516</v>
+      </c>
+      <c r="P288" s="3" t="n">
+        <v>-0.002631578947368428</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -13761,6 +15495,12 @@
       <c r="N289" s="2" t="n">
         <v>0.001878522229179635</v>
       </c>
+      <c r="O289" s="1" t="n">
+        <v>0.01598</v>
+      </c>
+      <c r="P289" s="3" t="n">
+        <v>-0.001249999999999949</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -13807,6 +15547,12 @@
       <c r="N290" s="2" t="n">
         <v>0.003089143865842947</v>
       </c>
+      <c r="O290" s="1" t="n">
+        <v>2.271</v>
+      </c>
+      <c r="P290" s="3" t="n">
+        <v>-0.0008798944126705779</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -13853,6 +15599,12 @@
       <c r="N291" s="2" t="n">
         <v>0.0009090909090909351</v>
       </c>
+      <c r="O291" s="1" t="n">
+        <v>0.4394</v>
+      </c>
+      <c r="P291" s="3" t="n">
+        <v>-0.002270663033605815</v>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -13899,6 +15651,12 @@
       <c r="N292" s="2" t="n">
         <v>0.002305475504322768</v>
       </c>
+      <c r="O292" s="1" t="n">
+        <v>1.736</v>
+      </c>
+      <c r="P292" s="3" t="n">
+        <v>-0.001725129384703918</v>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -13945,6 +15703,12 @@
       <c r="N293" s="2" t="n">
         <v>0.0005926511260371839</v>
       </c>
+      <c r="O293" s="1" t="n">
+        <v>0.05043</v>
+      </c>
+      <c r="P293" s="3" t="n">
+        <v>-0.004343534057255636</v>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -13991,6 +15755,12 @@
       <c r="N294" s="2" t="n">
         <v>0.0009448818897638503</v>
       </c>
+      <c r="O294" s="1" t="n">
+        <v>0.06333999999999999</v>
+      </c>
+      <c r="P294" s="3" t="n">
+        <v>-0.003461296412838449</v>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -14037,6 +15807,12 @@
       <c r="N295" s="2" t="n">
         <v>0.005808325266214918</v>
       </c>
+      <c r="O295" s="1" t="n">
+        <v>0.0004153</v>
+      </c>
+      <c r="P295" s="3" t="n">
+        <v>-0.0007218479307026162</v>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -14083,6 +15859,12 @@
       <c r="N296" s="2" t="n">
         <v>0.002883691124639534</v>
       </c>
+      <c r="O296" s="1" t="n">
+        <v>62.33</v>
+      </c>
+      <c r="P296" s="3" t="n">
+        <v>-0.004313099041533596</v>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -14129,6 +15911,12 @@
       <c r="N297" s="2" t="n">
         <v>0.003064351378958067</v>
       </c>
+      <c r="O297" s="1" t="n">
+        <v>0.0978</v>
+      </c>
+      <c r="P297" s="3" t="n">
+        <v>-0.00407331975560079</v>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -14175,6 +15963,12 @@
       <c r="N298" s="2" t="n">
         <v>0.005235602094240842</v>
       </c>
+      <c r="O298" s="1" t="n">
+        <v>0.0955</v>
+      </c>
+      <c r="P298" s="3" t="n">
+        <v>-0.005208333333333338</v>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -14221,6 +16015,12 @@
       <c r="N299" s="2" t="n">
         <v>0.004169272461955364</v>
       </c>
+      <c r="O299" s="1" t="n">
+        <v>0.09585</v>
+      </c>
+      <c r="P299" s="3" t="n">
+        <v>-0.005086153207390393</v>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -14267,6 +16067,12 @@
       <c r="N300" s="2" t="n">
         <v>0.0043196544276458</v>
       </c>
+      <c r="O300" s="1" t="n">
+        <v>0.0186</v>
+      </c>
+      <c r="P300" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -14313,6 +16119,12 @@
       <c r="N301" s="2" t="n">
         <v>0.002994011976047912</v>
       </c>
+      <c r="O301" s="1" t="n">
+        <v>0.01333</v>
+      </c>
+      <c r="P301" s="3" t="n">
+        <v>-0.005223880597014972</v>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -14359,6 +16171,12 @@
       <c r="N302" s="2" t="n">
         <v>0.001834862385321145</v>
       </c>
+      <c r="O302" s="1" t="n">
+        <v>0.004348</v>
+      </c>
+      <c r="P302" s="3" t="n">
+        <v>-0.00457875457875459</v>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -14405,6 +16223,12 @@
       <c r="N303" s="2" t="n">
         <v>0.001070663811563311</v>
       </c>
+      <c r="O303" s="1" t="n">
+        <v>0.00932</v>
+      </c>
+      <c r="P303" s="3" t="n">
+        <v>-0.003208556149732675</v>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -14451,6 +16275,12 @@
       <c r="N304" s="2" t="n">
         <v>0.0002112378538234757</v>
       </c>
+      <c r="O304" s="1" t="n">
+        <v>4.715</v>
+      </c>
+      <c r="P304" s="3" t="n">
+        <v>-0.004223864836325334</v>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -14497,6 +16327,12 @@
       <c r="N305" s="2" t="n">
         <v>0.0007552870090634133</v>
       </c>
+      <c r="O305" s="1" t="n">
+        <v>0.05262</v>
+      </c>
+      <c r="P305" s="3" t="n">
+        <v>-0.007169811320754687</v>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -14543,6 +16379,12 @@
       <c r="N306" s="2" t="n">
         <v>0.001371742112482916</v>
       </c>
+      <c r="O306" s="1" t="n">
+        <v>0.05819</v>
+      </c>
+      <c r="P306" s="3" t="n">
+        <v>-0.003595890410958936</v>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -14589,6 +16431,12 @@
       <c r="N307" s="3" t="n">
         <v>-0.0005698005698005071</v>
       </c>
+      <c r="O307" s="1" t="n">
+        <v>0.1745</v>
+      </c>
+      <c r="P307" s="3" t="n">
+        <v>-0.005131128848346704</v>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -14635,6 +16483,12 @@
       <c r="N308" s="2" t="n">
         <v>0.002836304700162099</v>
       </c>
+      <c r="O308" s="1" t="n">
+        <v>0.04961</v>
+      </c>
+      <c r="P308" s="2" t="n">
+        <v>0.002222222222222202</v>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -14681,6 +16535,12 @@
       <c r="N309" s="2" t="n">
         <v>0.004067295248659604</v>
       </c>
+      <c r="O309" s="1" t="n">
+        <v>0.5413</v>
+      </c>
+      <c r="P309" s="3" t="n">
+        <v>-0.003314306757503266</v>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -14727,6 +16587,12 @@
       <c r="N310" s="2" t="n">
         <v>0.004098360655737716</v>
       </c>
+      <c r="O310" s="1" t="n">
+        <v>0.00243</v>
+      </c>
+      <c r="P310" s="3" t="n">
+        <v>-0.008163265306122471</v>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -14773,6 +16639,12 @@
       <c r="N311" s="3" t="n">
         <v>-0.008954806212396832</v>
       </c>
+      <c r="O311" s="1" t="n">
+        <v>0.0706</v>
+      </c>
+      <c r="P311" s="3" t="n">
+        <v>-0.003247211633488747</v>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -14819,6 +16691,12 @@
       <c r="N312" s="2" t="n">
         <v>0.00121924185324749</v>
       </c>
+      <c r="O312" s="1" t="n">
+        <v>0.008978999999999999</v>
+      </c>
+      <c r="P312" s="3" t="n">
+        <v>-0.005978080371969471</v>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -14865,6 +16743,12 @@
       <c r="N313" s="3" t="n">
         <v>-0.001490559788009329</v>
       </c>
+      <c r="O313" s="1" t="n">
+        <v>0.012082</v>
+      </c>
+      <c r="P313" s="2" t="n">
+        <v>0.001990379830817835</v>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -14911,6 +16795,12 @@
       <c r="N314" s="2" t="n">
         <v>0.01126028583802511</v>
       </c>
+      <c r="O314" s="1" t="n">
+        <v>0.02327</v>
+      </c>
+      <c r="P314" s="3" t="n">
+        <v>-0.00342612419700215</v>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -14957,6 +16847,12 @@
       <c r="N315" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="O315" s="1" t="n">
+        <v>0.0071</v>
+      </c>
+      <c r="P315" s="3" t="n">
+        <v>-0.001406469760900083</v>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -15003,6 +16899,12 @@
       <c r="N316" s="2" t="n">
         <v>0.001914241960183769</v>
       </c>
+      <c r="O316" s="1" t="n">
+        <v>0.2602</v>
+      </c>
+      <c r="P316" s="3" t="n">
+        <v>-0.005731753916698515</v>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -15049,6 +16951,12 @@
       <c r="N317" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="O317" s="1" t="n">
+        <v>1.11e-05</v>
+      </c>
+      <c r="P317" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -15095,6 +17003,12 @@
       <c r="N318" s="2" t="n">
         <v>0.002631980469942005</v>
       </c>
+      <c r="O318" s="1" t="n">
+        <v>0.05252</v>
+      </c>
+      <c r="P318" s="3" t="n">
+        <v>-0.0009511128019783419</v>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -15141,6 +17055,12 @@
       <c r="N319" s="2" t="n">
         <v>0.000261780104712122</v>
       </c>
+      <c r="O319" s="1" t="n">
+        <v>0.0382</v>
+      </c>
+      <c r="P319" s="3" t="n">
+        <v>-0.0002617115938236865</v>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -15187,6 +17107,12 @@
       <c r="N320" s="2" t="n">
         <v>0.002202966661771223</v>
       </c>
+      <c r="O320" s="1" t="n">
+        <v>0.006789</v>
+      </c>
+      <c r="P320" s="3" t="n">
+        <v>-0.005128956623681171</v>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -15233,6 +17159,12 @@
       <c r="N321" s="2" t="n">
         <v>0.001985440105890018</v>
       </c>
+      <c r="O321" s="1" t="n">
+        <v>4.514</v>
+      </c>
+      <c r="P321" s="3" t="n">
+        <v>-0.006164685160722057</v>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -15279,6 +17211,12 @@
       <c r="N322" s="2" t="n">
         <v>0.007333682556312212</v>
       </c>
+      <c r="O322" s="1" t="n">
+        <v>1.913</v>
+      </c>
+      <c r="P322" s="3" t="n">
+        <v>-0.005200208008320337</v>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -15325,6 +17263,12 @@
       <c r="N323" s="3" t="n">
         <v>-0.0011309018942607</v>
       </c>
+      <c r="O323" s="1" t="n">
+        <v>0.007049</v>
+      </c>
+      <c r="P323" s="3" t="n">
+        <v>-0.00240588734786308</v>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -15371,6 +17315,12 @@
       <c r="N324" s="2" t="n">
         <v>0.00655737704918025</v>
       </c>
+      <c r="O324" s="1" t="n">
+        <v>0.01836</v>
+      </c>
+      <c r="P324" s="3" t="n">
+        <v>-0.00325732899022788</v>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -15417,6 +17367,12 @@
       <c r="N325" s="2" t="n">
         <v>0.002928257686676376</v>
       </c>
+      <c r="O325" s="1" t="n">
+        <v>0.4079</v>
+      </c>
+      <c r="P325" s="3" t="n">
+        <v>-0.00754257907542577</v>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -15463,6 +17419,12 @@
       <c r="N326" s="3" t="n">
         <v>-0.002483443708609242</v>
       </c>
+      <c r="O326" s="1" t="n">
+        <v>0.007171</v>
+      </c>
+      <c r="P326" s="3" t="n">
+        <v>-0.008160442600276627</v>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -15509,6 +17471,12 @@
       <c r="N327" s="3" t="n">
         <v>-0.005792522380200198</v>
       </c>
+      <c r="O327" s="1" t="n">
+        <v>0.1878</v>
+      </c>
+      <c r="P327" s="3" t="n">
+        <v>-0.00529661016949153</v>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -15555,6 +17523,12 @@
       <c r="N328" s="3" t="n">
         <v>-0.001901944209636543</v>
       </c>
+      <c r="O328" s="1" t="n">
+        <v>0.4682</v>
+      </c>
+      <c r="P328" s="3" t="n">
+        <v>-0.008680923142070703</v>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -15601,6 +17575,12 @@
       <c r="N329" s="3" t="n">
         <v>-0.002212389380530884</v>
       </c>
+      <c r="O329" s="1" t="n">
+        <v>0.01347</v>
+      </c>
+      <c r="P329" s="3" t="n">
+        <v>-0.004434589800443534</v>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -15647,6 +17627,12 @@
       <c r="N330" s="2" t="n">
         <v>0.002640845070422488</v>
       </c>
+      <c r="O330" s="1" t="n">
+        <v>0.1132</v>
+      </c>
+      <c r="P330" s="3" t="n">
+        <v>-0.006145741878841143</v>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -15693,6 +17679,12 @@
       <c r="N331" s="2" t="n">
         <v>0.009661835748792317</v>
       </c>
+      <c r="O331" s="1" t="n">
+        <v>0.603</v>
+      </c>
+      <c r="P331" s="3" t="n">
+        <v>-0.005114667546609457</v>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -15739,6 +17731,12 @@
       <c r="N332" s="2" t="n">
         <v>0.0094824707846411</v>
       </c>
+      <c r="O332" s="1" t="n">
+        <v>0.30555</v>
+      </c>
+      <c r="P332" s="2" t="n">
+        <v>0.01061718594959314</v>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -15785,6 +17783,12 @@
       <c r="N333" s="2" t="n">
         <v>0.004267425320056824</v>
       </c>
+      <c r="O333" s="1" t="n">
+        <v>0.07005</v>
+      </c>
+      <c r="P333" s="3" t="n">
+        <v>-0.007790368271954603</v>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -15831,6 +17835,12 @@
       <c r="N334" s="2" t="n">
         <v>0.02717788557379216</v>
       </c>
+      <c r="O334" s="1" t="n">
+        <v>0.15138</v>
+      </c>
+      <c r="P334" s="3" t="n">
+        <v>-0.02070125501358525</v>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -15877,6 +17887,12 @@
       <c r="N335" s="2" t="n">
         <v>0.001278772378516483</v>
       </c>
+      <c r="O335" s="1" t="n">
+        <v>0.156</v>
+      </c>
+      <c r="P335" s="3" t="n">
+        <v>-0.003831417624521005</v>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -15923,6 +17939,12 @@
       <c r="N336" s="2" t="n">
         <v>0.004022988505747162</v>
       </c>
+      <c r="O336" s="1" t="n">
+        <v>0.1736</v>
+      </c>
+      <c r="P336" s="3" t="n">
+        <v>-0.006296508299942701</v>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -15969,6 +17991,12 @@
       <c r="N337" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="O337" s="1" t="n">
+        <v>0.04009</v>
+      </c>
+      <c r="P337" s="2" t="n">
+        <v>0.0002495009980040684</v>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -16015,6 +18043,12 @@
       <c r="N338" s="3" t="n">
         <v>-0.0007552870090635443</v>
       </c>
+      <c r="O338" s="1" t="n">
+        <v>0.005275</v>
+      </c>
+      <c r="P338" s="3" t="n">
+        <v>-0.003212396069538861</v>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -16061,6 +18095,12 @@
       <c r="N339" s="2" t="n">
         <v>0.006809338521400703</v>
       </c>
+      <c r="O339" s="1" t="n">
+        <v>0.0513</v>
+      </c>
+      <c r="P339" s="3" t="n">
+        <v>-0.008695652173913025</v>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -16107,6 +18147,12 @@
       <c r="N340" s="2" t="n">
         <v>0.001718667371761041</v>
       </c>
+      <c r="O340" s="1" t="n">
+        <v>0.15154</v>
+      </c>
+      <c r="P340" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -16153,6 +18199,12 @@
       <c r="N341" s="2" t="n">
         <v>0.0002630540576089265</v>
       </c>
+      <c r="O341" s="1" t="n">
+        <v>7.601</v>
+      </c>
+      <c r="P341" s="3" t="n">
+        <v>-0.0005259697567390464</v>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -16199,6 +18251,12 @@
       <c r="N342" s="3" t="n">
         <v>-0.0003035822707955206</v>
       </c>
+      <c r="O342" s="1" t="n">
+        <v>0.329</v>
+      </c>
+      <c r="P342" s="3" t="n">
+        <v>-0.000911023382933395</v>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -16245,6 +18303,12 @@
       <c r="N343" s="2" t="n">
         <v>0.001513622603430816</v>
       </c>
+      <c r="O343" s="1" t="n">
+        <v>0.01974</v>
+      </c>
+      <c r="P343" s="3" t="n">
+        <v>-0.005541561712846296</v>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -16291,6 +18355,12 @@
       <c r="N344" s="2" t="n">
         <v>0.000453514739228975</v>
       </c>
+      <c r="O344" s="1" t="n">
+        <v>2.174</v>
+      </c>
+      <c r="P344" s="3" t="n">
+        <v>-0.014505893019039</v>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -16337,6 +18407,12 @@
       <c r="N345" s="2" t="n">
         <v>0.000786163522012492</v>
       </c>
+      <c r="O345" s="1" t="n">
+        <v>1.265</v>
+      </c>
+      <c r="P345" s="3" t="n">
+        <v>-0.006284367635506683</v>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -16383,6 +18459,12 @@
       <c r="N346" s="3" t="n">
         <v>-0.0007716049382717074</v>
       </c>
+      <c r="O346" s="1" t="n">
+        <v>0.005157</v>
+      </c>
+      <c r="P346" s="3" t="n">
+        <v>-0.00444015444015436</v>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -16429,6 +18511,12 @@
       <c r="N347" s="2" t="n">
         <v>0.001047851903597703</v>
       </c>
+      <c r="O347" s="1" t="n">
+        <v>0.05706</v>
+      </c>
+      <c r="P347" s="3" t="n">
+        <v>-0.004535938590369911</v>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -16475,6 +18563,12 @@
       <c r="N348" s="2" t="n">
         <v>0.001573564122738047</v>
       </c>
+      <c r="O348" s="1" t="n">
+        <v>0.1271</v>
+      </c>
+      <c r="P348" s="3" t="n">
+        <v>-0.001571091908876714</v>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -16521,6 +18615,12 @@
       <c r="N349" s="3" t="n">
         <v>-0.0008626804439928685</v>
       </c>
+      <c r="O349" s="1" t="n">
+        <v>5207.3</v>
+      </c>
+      <c r="P349" s="3" t="n">
+        <v>-0.0008634253041175793</v>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -16567,6 +18667,12 @@
       <c r="N350" s="3" t="n">
         <v>-0.0003539823008849413</v>
       </c>
+      <c r="O350" s="1" t="n">
+        <v>0.02817</v>
+      </c>
+      <c r="P350" s="3" t="n">
+        <v>-0.002478753541076509</v>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -16613,6 +18719,12 @@
       <c r="N351" s="2" t="n">
         <v>0.01396032329169722</v>
       </c>
+      <c r="O351" s="1" t="n">
+        <v>0.001385</v>
+      </c>
+      <c r="P351" s="2" t="n">
+        <v>0.003623188405797111</v>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -16659,6 +18771,12 @@
       <c r="N352" s="3" t="n">
         <v>-0.009363295880149865</v>
       </c>
+      <c r="O352" s="1" t="n">
+        <v>0.01577</v>
+      </c>
+      <c r="P352" s="3" t="n">
+        <v>-0.006301197227473182</v>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -16705,6 +18823,12 @@
       <c r="N353" s="2" t="n">
         <v>0.001111640463712968</v>
       </c>
+      <c r="O353" s="1" t="n">
+        <v>6.248</v>
+      </c>
+      <c r="P353" s="3" t="n">
+        <v>-0.008883248730964475</v>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -16751,6 +18875,12 @@
       <c r="N354" s="2" t="n">
         <v>0.002446696959105132</v>
       </c>
+      <c r="O354" s="1" t="n">
+        <v>0.2866</v>
+      </c>
+      <c r="P354" s="3" t="n">
+        <v>-0.0006973500697349302</v>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -16797,6 +18927,12 @@
       <c r="N355" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="O355" s="1" t="n">
+        <v>0.04133</v>
+      </c>
+      <c r="P355" s="3" t="n">
+        <v>-0.00433630450493856</v>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -16843,6 +18979,12 @@
       <c r="N356" s="3" t="n">
         <v>-0.001394457033292605</v>
       </c>
+      <c r="O356" s="1" t="n">
+        <v>0.11396</v>
+      </c>
+      <c r="P356" s="3" t="n">
+        <v>-0.005411066503752797</v>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -16889,6 +19031,12 @@
       <c r="N357" s="3" t="n">
         <v>-0.003634972259422215</v>
       </c>
+      <c r="O357" s="1" t="n">
+        <v>0.00521</v>
+      </c>
+      <c r="P357" s="2" t="n">
+        <v>0.0003840245775730156</v>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -16935,6 +19083,12 @@
       <c r="N358" s="2" t="n">
         <v>0.002689618074233461</v>
       </c>
+      <c r="O358" s="1" t="n">
+        <v>0.1854</v>
+      </c>
+      <c r="P358" s="3" t="n">
+        <v>-0.005364806866952794</v>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -16981,6 +19135,12 @@
       <c r="N359" s="2" t="n">
         <v>0.0006157635467981327</v>
       </c>
+      <c r="O359" s="1" t="n">
+        <v>0.1627</v>
+      </c>
+      <c r="P359" s="2" t="n">
+        <v>0.001230769230769266</v>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -17027,6 +19187,12 @@
       <c r="N360" s="3" t="n">
         <v>-0.001889466225791301</v>
       </c>
+      <c r="O360" s="1" t="n">
+        <v>0.08492</v>
+      </c>
+      <c r="P360" s="2" t="n">
+        <v>0.004732607666824391</v>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -17073,6 +19239,12 @@
       <c r="N361" s="2" t="n">
         <v>0.008838383838383916</v>
       </c>
+      <c r="O361" s="1" t="n">
+        <v>0.00775</v>
+      </c>
+      <c r="P361" s="3" t="n">
+        <v>-0.03003754693366716</v>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -17119,6 +19291,12 @@
       <c r="N362" s="2" t="n">
         <v>0.001647058823529492</v>
       </c>
+      <c r="O362" s="1" t="n">
+        <v>0.425</v>
+      </c>
+      <c r="P362" s="3" t="n">
+        <v>-0.001644350481559864</v>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -17165,6 +19343,12 @@
       <c r="N363" s="2" t="n">
         <v>0.002110817941952508</v>
       </c>
+      <c r="O363" s="1" t="n">
+        <v>3.778</v>
+      </c>
+      <c r="P363" s="3" t="n">
+        <v>-0.005265929436545555</v>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -17211,6 +19395,12 @@
       <c r="N364" s="2" t="n">
         <v>0.001828153564899377</v>
       </c>
+      <c r="O364" s="1" t="n">
+        <v>0.01097</v>
+      </c>
+      <c r="P364" s="2" t="n">
+        <v>0.0009124087591242088</v>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -17257,6 +19447,12 @@
       <c r="N365" s="2" t="n">
         <v>0.002733236151603577</v>
       </c>
+      <c r="O365" s="1" t="n">
+        <v>0.05484</v>
+      </c>
+      <c r="P365" s="3" t="n">
+        <v>-0.003452662184263178</v>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -17303,6 +19499,12 @@
       <c r="N366" s="3" t="n">
         <v>-0.01915542011319109</v>
       </c>
+      <c r="O366" s="1" t="n">
+        <v>0.0226</v>
+      </c>
+      <c r="P366" s="2" t="n">
+        <v>0.003106968486462368</v>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -17349,6 +19551,12 @@
       <c r="N367" s="3" t="n">
         <v>-0.0007315288953913064</v>
       </c>
+      <c r="O367" s="1" t="n">
+        <v>0.001358</v>
+      </c>
+      <c r="P367" s="3" t="n">
+        <v>-0.005856515373352839</v>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -17395,6 +19603,12 @@
       <c r="N368" s="2" t="n">
         <v>0.001745810055865923</v>
       </c>
+      <c r="O368" s="1" t="n">
+        <v>0.2851</v>
+      </c>
+      <c r="P368" s="3" t="n">
+        <v>-0.006273963053328576</v>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -17441,6 +19655,12 @@
       <c r="N369" s="2" t="n">
         <v>0.003785830178474885</v>
       </c>
+      <c r="O369" s="1" t="n">
+        <v>0.01861</v>
+      </c>
+      <c r="P369" s="2" t="n">
+        <v>0.002693965517241456</v>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -17487,6 +19707,12 @@
       <c r="N370" s="3" t="n">
         <v>-0.005417063750815056</v>
       </c>
+      <c r="O370" s="1" t="n">
+        <v>0.19797</v>
+      </c>
+      <c r="P370" s="3" t="n">
+        <v>-0.001613797972666231</v>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -17533,6 +19759,12 @@
       <c r="N371" s="2" t="n">
         <v>0.01333333333333335</v>
       </c>
+      <c r="O371" s="1" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="P371" s="3" t="n">
+        <v>-0.01315789473684212</v>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -17579,6 +19811,12 @@
       <c r="N372" s="2" t="n">
         <v>0.00475737392959087</v>
       </c>
+      <c r="O372" s="1" t="n">
+        <v>0.1052</v>
+      </c>
+      <c r="P372" s="3" t="n">
+        <v>-0.003787878787878765</v>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -17625,6 +19863,12 @@
       <c r="N373" s="2" t="n">
         <v>0.008925869894099747</v>
       </c>
+      <c r="O373" s="1" t="n">
+        <v>0.06633</v>
+      </c>
+      <c r="P373" s="3" t="n">
+        <v>-0.005398110661268544</v>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -17671,6 +19915,12 @@
       <c r="N374" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="O374" s="1" t="n">
+        <v>0.007598</v>
+      </c>
+      <c r="P374" s="2" t="n">
+        <v>0.0002632964718271982</v>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -17717,6 +19967,12 @@
       <c r="N375" s="2" t="n">
         <v>0.001255492780916546</v>
       </c>
+      <c r="O375" s="1" t="n">
+        <v>0.1587</v>
+      </c>
+      <c r="P375" s="3" t="n">
+        <v>-0.005015673981191193</v>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -17763,6 +20019,12 @@
       <c r="N376" s="2" t="n">
         <v>0.002919708029197088</v>
       </c>
+      <c r="O376" s="1" t="n">
+        <v>0.003401</v>
+      </c>
+      <c r="P376" s="3" t="n">
+        <v>-0.009898107714701652</v>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -17809,6 +20071,12 @@
       <c r="N377" s="2" t="n">
         <v>0.006249999999999962</v>
       </c>
+      <c r="O377" s="1" t="n">
+        <v>0.0162</v>
+      </c>
+      <c r="P377" s="2" t="n">
+        <v>0.006211180124223565</v>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -17855,6 +20123,12 @@
       <c r="N378" s="2" t="n">
         <v>0.005371530886302689</v>
       </c>
+      <c r="O378" s="1" t="n">
+        <v>0.01116</v>
+      </c>
+      <c r="P378" s="3" t="n">
+        <v>-0.006233303650935051</v>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -17901,6 +20175,12 @@
       <c r="N379" s="3" t="n">
         <v>-0.0078125</v>
       </c>
+      <c r="O379" s="1" t="n">
+        <v>0.02137</v>
+      </c>
+      <c r="P379" s="3" t="n">
+        <v>-0.01018990273274671</v>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -17947,6 +20227,12 @@
       <c r="N380" s="2" t="n">
         <v>0.005319148936170181</v>
       </c>
+      <c r="O380" s="1" t="n">
+        <v>0.01876</v>
+      </c>
+      <c r="P380" s="3" t="n">
+        <v>-0.007407407407407473</v>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -17993,6 +20279,12 @@
       <c r="N381" s="2" t="n">
         <v>0.004173622704507516</v>
       </c>
+      <c r="O381" s="1" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="P381" s="3" t="n">
+        <v>-0.002493765586034984</v>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -18039,6 +20331,12 @@
       <c r="N382" s="2" t="n">
         <v>0.004130808950086129</v>
       </c>
+      <c r="O382" s="1" t="n">
+        <v>0.02927</v>
+      </c>
+      <c r="P382" s="2" t="n">
+        <v>0.003428179636612938</v>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -18085,6 +20383,12 @@
       <c r="N383" s="3" t="n">
         <v>-0.0007648768548264744</v>
       </c>
+      <c r="O383" s="1" t="n">
+        <v>0.006521</v>
+      </c>
+      <c r="P383" s="3" t="n">
+        <v>-0.001684017146356357</v>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -18131,6 +20435,12 @@
       <c r="N384" s="2" t="n">
         <v>0.006262042389209931</v>
       </c>
+      <c r="O384" s="1" t="n">
+        <v>0.02091</v>
+      </c>
+      <c r="P384" s="2" t="n">
+        <v>0.0009573958831978294</v>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -18177,6 +20487,12 @@
       <c r="N385" s="2" t="n">
         <v>0.003163305654408857</v>
       </c>
+      <c r="O385" s="1" t="n">
+        <v>2526</v>
+      </c>
+      <c r="P385" s="3" t="n">
+        <v>-0.004335829720141899</v>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -18223,6 +20539,12 @@
       <c r="N386" s="3" t="n">
         <v>-0.0005065856129685359</v>
       </c>
+      <c r="O386" s="1" t="n">
+        <v>0.1969</v>
+      </c>
+      <c r="P386" s="3" t="n">
+        <v>-0.002027369488089262</v>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -18269,6 +20591,12 @@
       <c r="N387" s="2" t="n">
         <v>0.00011739845034041</v>
       </c>
+      <c r="O387" s="1" t="n">
+        <v>0.0849</v>
+      </c>
+      <c r="P387" s="3" t="n">
+        <v>-0.003404155417302484</v>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -18315,6 +20643,12 @@
       <c r="N388" s="2" t="n">
         <v>0.0001990842126219655</v>
       </c>
+      <c r="O388" s="1" t="n">
+        <v>0.005006</v>
+      </c>
+      <c r="P388" s="3" t="n">
+        <v>-0.003582802547770658</v>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -18361,6 +20695,12 @@
       <c r="N389" s="2" t="n">
         <v>0.001784121320249859</v>
       </c>
+      <c r="O389" s="1" t="n">
+        <v>0.02237</v>
+      </c>
+      <c r="P389" s="3" t="n">
+        <v>-0.00400712377560106</v>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -18407,6 +20747,12 @@
       <c r="N390" s="3" t="n">
         <v>-0.007475900059020314</v>
       </c>
+      <c r="O390" s="1" t="n">
+        <v>0.5031</v>
+      </c>
+      <c r="P390" s="3" t="n">
+        <v>-0.002775024777006852</v>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -18453,6 +20799,12 @@
       <c r="N391" s="2" t="n">
         <v>0.006503251625812974</v>
       </c>
+      <c r="O391" s="1" t="n">
+        <v>0.0006018</v>
+      </c>
+      <c r="P391" s="3" t="n">
+        <v>-0.002982107355864883</v>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -18499,6 +20851,12 @@
       <c r="N392" s="2" t="n">
         <v>0.002565856996236817</v>
       </c>
+      <c r="O392" s="1" t="n">
+        <v>0.05843</v>
+      </c>
+      <c r="P392" s="3" t="n">
+        <v>-0.003071148268213609</v>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -18545,6 +20903,12 @@
       <c r="N393" s="2" t="n">
         <v>0.002622705133008536</v>
       </c>
+      <c r="O393" s="1" t="n">
+        <v>0.267</v>
+      </c>
+      <c r="P393" s="3" t="n">
+        <v>-0.002242152466367674</v>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -18591,6 +20955,12 @@
       <c r="N394" s="2" t="n">
         <v>0.006289308176100666</v>
       </c>
+      <c r="O394" s="1" t="n">
+        <v>0.006551</v>
+      </c>
+      <c r="P394" s="3" t="n">
+        <v>-0.001371951219512113</v>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -18637,6 +21007,12 @@
       <c r="N395" s="2" t="n">
         <v>0.0008680555555555804</v>
       </c>
+      <c r="O395" s="1" t="n">
+        <v>0.115</v>
+      </c>
+      <c r="P395" s="3" t="n">
+        <v>-0.002601908065914958</v>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -18683,6 +21059,12 @@
       <c r="N396" s="2" t="n">
         <v>0.001622849724115481</v>
       </c>
+      <c r="O396" s="1" t="n">
+        <v>0.0308</v>
+      </c>
+      <c r="P396" s="3" t="n">
+        <v>-0.001944264419961036</v>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -18729,6 +21111,12 @@
       <c r="N397" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="O397" s="1" t="n">
+        <v>0.1501</v>
+      </c>
+      <c r="P397" s="3" t="n">
+        <v>-0.004641909814323465</v>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -18775,6 +21163,12 @@
       <c r="N398" s="2" t="n">
         <v>0.002725620835857155</v>
       </c>
+      <c r="O398" s="1" t="n">
+        <v>0.003308</v>
+      </c>
+      <c r="P398" s="3" t="n">
+        <v>-0.0009060706735125232</v>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -18821,6 +21215,12 @@
       <c r="N399" s="2" t="n">
         <v>0.0005339028296849756</v>
       </c>
+      <c r="O399" s="1" t="n">
+        <v>0.01873</v>
+      </c>
+      <c r="P399" s="3" t="n">
+        <v>-0.0005336179295624115</v>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -18867,6 +21267,12 @@
       <c r="N400" s="2" t="n">
         <v>0.002416488983653237</v>
       </c>
+      <c r="O400" s="1" t="n">
+        <v>0.007065</v>
+      </c>
+      <c r="P400" s="2" t="n">
+        <v>0.001843448667044809</v>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -18913,6 +21319,12 @@
       <c r="N401" s="2" t="n">
         <v>0.01225313536110711</v>
       </c>
+      <c r="O401" s="1" t="n">
+        <v>0.007009</v>
+      </c>
+      <c r="P401" s="3" t="n">
+        <v>-0.001851324409000284</v>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -18959,6 +21371,12 @@
       <c r="N402" s="2" t="n">
         <v>0.004629050419116799</v>
       </c>
+      <c r="O402" s="1" t="n">
+        <v>0.008023000000000001</v>
+      </c>
+      <c r="P402" s="3" t="n">
+        <v>-0.0008717310087173177</v>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -19005,6 +21423,12 @@
       <c r="N403" s="2" t="n">
         <v>0.001425081433224768</v>
       </c>
+      <c r="O403" s="1" t="n">
+        <v>0.04874</v>
+      </c>
+      <c r="P403" s="3" t="n">
+        <v>-0.009148200853832059</v>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -19051,6 +21475,12 @@
       <c r="N404" s="3" t="n">
         <v>-0.003737569245144345</v>
       </c>
+      <c r="O404" s="1" t="n">
+        <v>0.14896</v>
+      </c>
+      <c r="P404" s="3" t="n">
+        <v>-0.002076773631674179</v>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -19097,6 +21527,12 @@
       <c r="N405" s="2" t="n">
         <v>0.01786133960047013</v>
       </c>
+      <c r="O405" s="1" t="n">
+        <v>0.04303</v>
+      </c>
+      <c r="P405" s="3" t="n">
+        <v>-0.006465019625952493</v>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -19143,6 +21579,12 @@
       <c r="N406" s="2" t="n">
         <v>0.003552769070010522</v>
       </c>
+      <c r="O406" s="1" t="n">
+        <v>0.4775</v>
+      </c>
+      <c r="P406" s="3" t="n">
+        <v>-0.005622657226155843</v>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -19189,6 +21631,12 @@
       <c r="N407" s="2" t="n">
         <v>0.007595976185588137</v>
       </c>
+      <c r="O407" s="1" t="n">
+        <v>0.0004902</v>
+      </c>
+      <c r="P407" s="3" t="n">
+        <v>-0.001222493887530592</v>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -19235,6 +21683,12 @@
       <c r="N408" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="O408" s="1" t="n">
+        <v>0.0123</v>
+      </c>
+      <c r="P408" s="3" t="n">
+        <v>-0.002433090024330942</v>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -19281,6 +21735,12 @@
       <c r="N409" s="3" t="n">
         <v>-0.004687500000000004</v>
       </c>
+      <c r="O409" s="1" t="n">
+        <v>0.3184</v>
+      </c>
+      <c r="P409" s="3" t="n">
+        <v>-0.0003139717425431365</v>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -19327,6 +21787,12 @@
       <c r="N410" s="2" t="n">
         <v>0.00215982721382289</v>
       </c>
+      <c r="O410" s="1" t="n">
+        <v>0.04164</v>
+      </c>
+      <c r="P410" s="3" t="n">
+        <v>-0.002873563218390687</v>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -19373,6 +21839,12 @@
       <c r="N411" s="2" t="n">
         <v>0.001680672268907611</v>
       </c>
+      <c r="O411" s="1" t="n">
+        <v>0.02964</v>
+      </c>
+      <c r="P411" s="3" t="n">
+        <v>-0.005369127516778538</v>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
@@ -19419,6 +21891,12 @@
       <c r="N412" s="2" t="n">
         <v>0.0006547359231775493</v>
       </c>
+      <c r="O412" s="1" t="n">
+        <v>0.00457</v>
+      </c>
+      <c r="P412" s="3" t="n">
+        <v>-0.003271537622682528</v>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -19465,6 +21943,12 @@
       <c r="N413" s="2" t="n">
         <v>0.001192368839427752</v>
       </c>
+      <c r="O413" s="1" t="n">
+        <v>0.2505</v>
+      </c>
+      <c r="P413" s="3" t="n">
+        <v>-0.005557761016276349</v>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -19511,6 +21995,12 @@
       <c r="N414" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="O414" s="1" t="n">
+        <v>1.278</v>
+      </c>
+      <c r="P414" s="3" t="n">
+        <v>-0.002341920374707175</v>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -19557,6 +22047,12 @@
       <c r="N415" s="2" t="n">
         <v>0.00846521899153483</v>
       </c>
+      <c r="O415" s="1" t="n">
+        <v>2.716</v>
+      </c>
+      <c r="P415" s="3" t="n">
+        <v>-0.008759124087591249</v>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -19603,6 +22099,12 @@
       <c r="N416" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="O416" s="1" t="n">
+        <v>0.03219</v>
+      </c>
+      <c r="P416" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -19649,6 +22151,12 @@
       <c r="N417" s="3" t="n">
         <v>-0.0004983802641415197</v>
       </c>
+      <c r="O417" s="1" t="n">
+        <v>0.04014</v>
+      </c>
+      <c r="P417" s="2" t="n">
+        <v>0.0007479431563201757</v>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -19695,6 +22203,12 @@
       <c r="N418" s="2" t="n">
         <v>0.00328990656665351</v>
       </c>
+      <c r="O418" s="1" t="n">
+        <v>0.07591000000000001</v>
+      </c>
+      <c r="P418" s="3" t="n">
+        <v>-0.004328436516264388</v>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -19741,6 +22255,12 @@
       <c r="N419" s="2" t="n">
         <v>0.00150150150150144</v>
       </c>
+      <c r="O419" s="1" t="n">
+        <v>0.00665</v>
+      </c>
+      <c r="P419" s="3" t="n">
+        <v>-0.002998500749625196</v>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -19787,6 +22307,12 @@
       <c r="N420" s="2" t="n">
         <v>0.002257336343115189</v>
       </c>
+      <c r="O420" s="1" t="n">
+        <v>0.08840000000000001</v>
+      </c>
+      <c r="P420" s="3" t="n">
+        <v>-0.004504504504504477</v>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -19833,6 +22359,12 @@
       <c r="N421" s="2" t="n">
         <v>0.001642710472279308</v>
       </c>
+      <c r="O421" s="1" t="n">
+        <v>0.2401</v>
+      </c>
+      <c r="P421" s="3" t="n">
+        <v>-0.01558015580155801</v>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
@@ -19879,6 +22411,12 @@
       <c r="N422" s="2" t="n">
         <v>0.0103092783505154</v>
       </c>
+      <c r="O422" s="1" t="n">
+        <v>0.0194</v>
+      </c>
+      <c r="P422" s="3" t="n">
+        <v>-0.010204081632653</v>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -19925,6 +22463,12 @@
       <c r="N423" s="2" t="n">
         <v>0.001327140013271438</v>
       </c>
+      <c r="O423" s="1" t="n">
+        <v>0.1505</v>
+      </c>
+      <c r="P423" s="3" t="n">
+        <v>-0.00265076209410213</v>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -19971,6 +22515,12 @@
       <c r="N424" s="2" t="n">
         <v>0.004312410158121681</v>
       </c>
+      <c r="O424" s="1" t="n">
+        <v>0.0002088</v>
+      </c>
+      <c r="P424" s="3" t="n">
+        <v>-0.003816793893129734</v>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -20017,6 +22567,12 @@
       <c r="N425" s="2" t="n">
         <v>0.003233629749393697</v>
       </c>
+      <c r="O425" s="1" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="P425" s="3" t="n">
+        <v>-0.0008058017727639901</v>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
@@ -20063,6 +22619,12 @@
       <c r="N426" s="2" t="n">
         <v>0.001419446415897801</v>
       </c>
+      <c r="O426" s="1" t="n">
+        <v>1.413</v>
+      </c>
+      <c r="P426" s="2" t="n">
+        <v>0.001417434443656982</v>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -20109,6 +22671,12 @@
       <c r="N427" s="2" t="n">
         <v>0.0010293360782295</v>
       </c>
+      <c r="O427" s="1" t="n">
+        <v>0.01938</v>
+      </c>
+      <c r="P427" s="3" t="n">
+        <v>-0.003598971722364892</v>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
@@ -20155,6 +22723,12 @@
       <c r="N428" s="2" t="n">
         <v>0.002126689958985284</v>
       </c>
+      <c r="O428" s="1" t="n">
+        <v>0.06584</v>
+      </c>
+      <c r="P428" s="3" t="n">
+        <v>-0.001970592693648705</v>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
@@ -20201,6 +22775,12 @@
       <c r="N429" s="2" t="n">
         <v>0.00150715900527489</v>
       </c>
+      <c r="O429" s="1" t="n">
+        <v>0.1322</v>
+      </c>
+      <c r="P429" s="3" t="n">
+        <v>-0.005267118133935128</v>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
@@ -20247,6 +22827,12 @@
       <c r="N430" s="3" t="n">
         <v>-8.991997122569913e-05</v>
       </c>
+      <c r="O430" s="1" t="n">
+        <v>0.011086</v>
+      </c>
+      <c r="P430" s="3" t="n">
+        <v>-0.00305755395683447</v>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -20293,6 +22879,12 @@
       <c r="N431" s="2" t="n">
         <v>0.003297362110311798</v>
       </c>
+      <c r="O431" s="1" t="n">
+        <v>0.006665</v>
+      </c>
+      <c r="P431" s="3" t="n">
+        <v>-0.004332237824917894</v>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
@@ -20339,6 +22931,12 @@
       <c r="N432" s="2" t="n">
         <v>0.00341102899374653</v>
       </c>
+      <c r="O432" s="1" t="n">
+        <v>0.001754</v>
+      </c>
+      <c r="P432" s="3" t="n">
+        <v>-0.006232294617563829</v>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
@@ -20385,6 +22983,12 @@
       <c r="N433" s="3" t="n">
         <v>-0.002191380569758922</v>
       </c>
+      <c r="O433" s="1" t="n">
+        <v>0.001357</v>
+      </c>
+      <c r="P433" s="3" t="n">
+        <v>-0.006588579795022043</v>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
@@ -20431,6 +23035,12 @@
       <c r="N434" s="2" t="n">
         <v>0.002444987775061051</v>
       </c>
+      <c r="O434" s="1" t="n">
+        <v>0.00041</v>
+      </c>
+      <c r="P434" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
@@ -20477,6 +23087,12 @@
       <c r="N435" s="2" t="n">
         <v>0.004591513616212991</v>
       </c>
+      <c r="O435" s="1" t="n">
+        <v>0.12658</v>
+      </c>
+      <c r="P435" s="3" t="n">
+        <v>-0.002521670606777105</v>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -20523,6 +23139,12 @@
       <c r="N436" s="2" t="n">
         <v>0.003212541763042922</v>
       </c>
+      <c r="O436" s="1" t="n">
+        <v>0.07776</v>
+      </c>
+      <c r="P436" s="3" t="n">
+        <v>-0.003970795439989813</v>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
@@ -20569,6 +23191,12 @@
       <c r="N437" s="2" t="n">
         <v>0.003313870916837605</v>
       </c>
+      <c r="O437" s="1" t="n">
+        <v>0.6329</v>
+      </c>
+      <c r="P437" s="3" t="n">
+        <v>-0.004561182761874825</v>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -20615,6 +23243,12 @@
       <c r="N438" s="2" t="n">
         <v>0.005293440736478575</v>
       </c>
+      <c r="O438" s="1" t="n">
+        <v>0.04369</v>
+      </c>
+      <c r="P438" s="2" t="n">
+        <v>0.0002289377289377991</v>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
@@ -20661,6 +23295,12 @@
       <c r="N439" s="2" t="n">
         <v>0.003124556170998409</v>
       </c>
+      <c r="O439" s="1" t="n">
+        <v>0.07043000000000001</v>
+      </c>
+      <c r="P439" s="3" t="n">
+        <v>-0.00283165793572125</v>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
@@ -20707,6 +23347,12 @@
       <c r="N440" s="2" t="n">
         <v>0.003295978905735012</v>
       </c>
+      <c r="O440" s="1" t="n">
+        <v>0.001514</v>
+      </c>
+      <c r="P440" s="3" t="n">
+        <v>-0.005256241787122193</v>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -20753,6 +23399,12 @@
       <c r="N441" s="2" t="n">
         <v>0.001370151770657763</v>
       </c>
+      <c r="O441" s="1" t="n">
+        <v>0.009464</v>
+      </c>
+      <c r="P441" s="3" t="n">
+        <v>-0.003894326912956591</v>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
@@ -20799,6 +23451,12 @@
       <c r="N442" s="2" t="n">
         <v>0.0009425070688031216</v>
       </c>
+      <c r="O442" s="1" t="n">
+        <v>1.058</v>
+      </c>
+      <c r="P442" s="3" t="n">
+        <v>-0.003766478342749533</v>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
@@ -20845,6 +23503,12 @@
       <c r="N443" s="3" t="n">
         <v>-0.00136239782016359</v>
       </c>
+      <c r="O443" s="1" t="n">
+        <v>0.02196</v>
+      </c>
+      <c r="P443" s="3" t="n">
+        <v>-0.001364256480218226</v>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
@@ -20891,6 +23555,12 @@
       <c r="N444" s="3" t="n">
         <v>-0.001309586170770068</v>
       </c>
+      <c r="O444" s="1" t="n">
+        <v>0.0003791</v>
+      </c>
+      <c r="P444" s="3" t="n">
+        <v>-0.005769735116706004</v>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
@@ -20937,6 +23607,12 @@
       <c r="N445" s="2" t="n">
         <v>0.0008438818565401476</v>
       </c>
+      <c r="O445" s="1" t="n">
+        <v>0.03547</v>
+      </c>
+      <c r="P445" s="3" t="n">
+        <v>-0.003091624508150618</v>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
@@ -20983,6 +23659,12 @@
       <c r="N446" s="3" t="n">
         <v>-0.004541749155700494</v>
       </c>
+      <c r="O446" s="1" t="n">
+        <v>0.08486</v>
+      </c>
+      <c r="P446" s="3" t="n">
+        <v>-0.007253158633598451</v>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
@@ -21029,6 +23711,12 @@
       <c r="N447" s="2" t="n">
         <v>0.003679852805887767</v>
       </c>
+      <c r="O447" s="1" t="n">
+        <v>3.256</v>
+      </c>
+      <c r="P447" s="3" t="n">
+        <v>-0.005194011610143706</v>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
@@ -21075,6 +23763,12 @@
       <c r="N448" s="2" t="n">
         <v>0.0003122560499610636</v>
       </c>
+      <c r="O448" s="1" t="n">
+        <v>0.06398</v>
+      </c>
+      <c r="P448" s="3" t="n">
+        <v>-0.001404713594506114</v>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
@@ -21121,6 +23815,12 @@
       <c r="N449" s="2" t="n">
         <v>0.006393070736234258</v>
       </c>
+      <c r="O449" s="1" t="n">
+        <v>0.487</v>
+      </c>
+      <c r="P449" s="3" t="n">
+        <v>-0.002049180327868854</v>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
@@ -21167,6 +23867,12 @@
       <c r="N450" s="3" t="n">
         <v>-0.004823151125401919</v>
       </c>
+      <c r="O450" s="1" t="n">
+        <v>0.03712</v>
+      </c>
+      <c r="P450" s="3" t="n">
+        <v>-0.0005385029617662678</v>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -21213,6 +23919,12 @@
       <c r="N451" s="2" t="n">
         <v>0.003663003663003673</v>
       </c>
+      <c r="O451" s="1" t="n">
+        <v>0.00546</v>
+      </c>
+      <c r="P451" s="3" t="n">
+        <v>-0.00364963503649636</v>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
@@ -21259,6 +23971,12 @@
       <c r="N452" s="3" t="n">
         <v>-0.002388002674562998</v>
       </c>
+      <c r="O452" s="1" t="n">
+        <v>0.10375</v>
+      </c>
+      <c r="P452" s="3" t="n">
+        <v>-0.006606664113366622</v>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
@@ -21305,6 +24023,12 @@
       <c r="N453" s="2" t="n">
         <v>0.002496878901373398</v>
       </c>
+      <c r="O453" s="1" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="P453" s="3" t="n">
+        <v>-0.003735990037359964</v>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
@@ -21351,6 +24075,12 @@
       <c r="N454" s="3" t="n">
         <v>-0.02474226804123713</v>
       </c>
+      <c r="O454" s="1" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="P454" s="2" t="n">
+        <v>0.004228329809725162</v>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
@@ -21397,6 +24127,12 @@
       <c r="N455" s="2" t="n">
         <v>0.004469273743016764</v>
       </c>
+      <c r="O455" s="1" t="n">
+        <v>0.895</v>
+      </c>
+      <c r="P455" s="3" t="n">
+        <v>-0.004449388209121249</v>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
@@ -21443,6 +24179,12 @@
       <c r="N456" s="2" t="n">
         <v>0.00475705062861019</v>
       </c>
+      <c r="O456" s="1" t="n">
+        <v>2.953</v>
+      </c>
+      <c r="P456" s="3" t="n">
+        <v>-0.001352722353736897</v>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -21489,6 +24231,12 @@
       <c r="N457" s="2" t="n">
         <v>0.002028397565922838</v>
       </c>
+      <c r="O457" s="1" t="n">
+        <v>0.00987</v>
+      </c>
+      <c r="P457" s="3" t="n">
+        <v>-0.001012145748987813</v>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
@@ -21535,6 +24283,12 @@
       <c r="N458" s="2" t="n">
         <v>0.001450443190975017</v>
       </c>
+      <c r="O458" s="1" t="n">
+        <v>0.06188</v>
+      </c>
+      <c r="P458" s="3" t="n">
+        <v>-0.004184100418410094</v>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
@@ -21581,6 +24335,12 @@
       <c r="N459" s="2" t="n">
         <v>0.00279916025192443</v>
       </c>
+      <c r="O459" s="1" t="n">
+        <v>0.01428</v>
+      </c>
+      <c r="P459" s="3" t="n">
+        <v>-0.003489183531053833</v>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
@@ -21627,6 +24387,12 @@
       <c r="N460" s="3" t="n">
         <v>-0.0003750937734433022</v>
       </c>
+      <c r="O460" s="1" t="n">
+        <v>0.015968</v>
+      </c>
+      <c r="P460" s="3" t="n">
+        <v>-0.001375859912445352</v>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
@@ -21673,6 +24439,12 @@
       <c r="N461" s="3" t="n">
         <v>-0.0005988023952095564</v>
       </c>
+      <c r="O461" s="1" t="n">
+        <v>0.01656</v>
+      </c>
+      <c r="P461" s="3" t="n">
+        <v>-0.007789095266626821</v>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
@@ -21719,6 +24491,12 @@
       <c r="N462" s="2" t="n">
         <v>0.008110687022900831</v>
       </c>
+      <c r="O462" s="1" t="n">
+        <v>0.0002104</v>
+      </c>
+      <c r="P462" s="3" t="n">
+        <v>-0.004259346900142081</v>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
@@ -21765,6 +24543,12 @@
       <c r="N463" s="3" t="n">
         <v>-0.008032128514056177</v>
       </c>
+      <c r="O463" s="1" t="n">
+        <v>0.0989</v>
+      </c>
+      <c r="P463" s="2" t="n">
+        <v>0.001012145748987883</v>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
@@ -21811,6 +24595,12 @@
       <c r="N464" s="3" t="n">
         <v>-0.001143728555089545</v>
       </c>
+      <c r="O464" s="1" t="n">
+        <v>0.02611</v>
+      </c>
+      <c r="P464" s="3" t="n">
+        <v>-0.003435114503816786</v>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
@@ -21857,6 +24647,12 @@
       <c r="N465" s="3" t="n">
         <v>-0.005917159763313596</v>
       </c>
+      <c r="O465" s="1" t="n">
+        <v>0.01502</v>
+      </c>
+      <c r="P465" s="3" t="n">
+        <v>-0.006613756613756573</v>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
@@ -21903,6 +24699,12 @@
       <c r="N466" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="O466" s="1" t="n">
+        <v>0.0547</v>
+      </c>
+      <c r="P466" s="2" t="n">
+        <v>0.0001828487840555151</v>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
@@ -21949,6 +24751,12 @@
       <c r="N467" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="O467" s="1" t="n">
+        <v>0.03438</v>
+      </c>
+      <c r="P467" s="3" t="n">
+        <v>-0.002321532211259337</v>
+      </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
@@ -21995,6 +24803,12 @@
       <c r="N468" s="3" t="n">
         <v>-0.0007251631617113697</v>
       </c>
+      <c r="O468" s="1" t="n">
+        <v>27.42</v>
+      </c>
+      <c r="P468" s="3" t="n">
+        <v>-0.005079825834542708</v>
+      </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
@@ -22041,6 +24855,12 @@
       <c r="N469" s="3" t="n">
         <v>-0.002404488378306085</v>
       </c>
+      <c r="O469" s="1" t="n">
+        <v>0.0007458</v>
+      </c>
+      <c r="P469" s="3" t="n">
+        <v>-0.001339046598821671</v>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
@@ -22087,6 +24907,12 @@
       <c r="N470" s="2" t="n">
         <v>0.003440366972477067</v>
       </c>
+      <c r="O470" s="1" t="n">
+        <v>0.874</v>
+      </c>
+      <c r="P470" s="3" t="n">
+        <v>-0.001142857142857144</v>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
@@ -22133,6 +24959,12 @@
       <c r="N471" s="2" t="n">
         <v>0.001010101010100969</v>
       </c>
+      <c r="O471" s="1" t="n">
+        <v>0.00988</v>
+      </c>
+      <c r="P471" s="3" t="n">
+        <v>-0.003027245206861807</v>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
@@ -22179,6 +25011,12 @@
       <c r="N472" s="2" t="n">
         <v>0.001287001287001234</v>
       </c>
+      <c r="O472" s="1" t="n">
+        <v>0.04652</v>
+      </c>
+      <c r="P472" s="3" t="n">
+        <v>-0.003427592116538141</v>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -22225,6 +25063,12 @@
       <c r="N473" s="2" t="n">
         <v>0.004753199268738456</v>
       </c>
+      <c r="O473" s="1" t="n">
+        <v>0.274</v>
+      </c>
+      <c r="P473" s="3" t="n">
+        <v>-0.002911208151382705</v>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
@@ -22271,6 +25115,12 @@
       <c r="N474" s="2" t="n">
         <v>0.001143902997025885</v>
       </c>
+      <c r="O474" s="1" t="n">
+        <v>0.04348</v>
+      </c>
+      <c r="P474" s="3" t="n">
+        <v>-0.006398537477148137</v>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
@@ -22317,6 +25167,12 @@
       <c r="N475" s="2" t="n">
         <v>0.001888574126534512</v>
       </c>
+      <c r="O475" s="1" t="n">
+        <v>0.008453</v>
+      </c>
+      <c r="P475" s="3" t="n">
+        <v>-0.004123468426013231</v>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
@@ -22363,6 +25219,12 @@
       <c r="N476" s="2" t="n">
         <v>0.001226241569589244</v>
       </c>
+      <c r="O476" s="1" t="n">
+        <v>0.08151</v>
+      </c>
+      <c r="P476" s="3" t="n">
+        <v>-0.001714635639926531</v>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
@@ -22409,6 +25271,12 @@
       <c r="N477" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="O477" s="1" t="n">
+        <v>0.1359</v>
+      </c>
+      <c r="P477" s="3" t="n">
+        <v>-0.003665689149560121</v>
+      </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
@@ -22455,6 +25323,12 @@
       <c r="N478" s="2" t="n">
         <v>0.003770739064856715</v>
       </c>
+      <c r="O478" s="1" t="n">
+        <v>0.3961</v>
+      </c>
+      <c r="P478" s="3" t="n">
+        <v>-0.008014024542950115</v>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
@@ -22501,6 +25375,12 @@
       <c r="N479" s="2" t="n">
         <v>0.004978662873399553</v>
       </c>
+      <c r="O479" s="1" t="n">
+        <v>0.008437</v>
+      </c>
+      <c r="P479" s="3" t="n">
+        <v>-0.004836046237320049</v>
+      </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
@@ -22547,6 +25427,12 @@
       <c r="N480" s="2" t="n">
         <v>0.001257861635220075</v>
       </c>
+      <c r="O480" s="1" t="n">
+        <v>0.01586</v>
+      </c>
+      <c r="P480" s="3" t="n">
+        <v>-0.003768844221105592</v>
+      </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
@@ -22593,6 +25479,12 @@
       <c r="N481" s="2" t="n">
         <v>0.00569358178053825</v>
       </c>
+      <c r="O481" s="1" t="n">
+        <v>0.07809000000000001</v>
+      </c>
+      <c r="P481" s="2" t="n">
+        <v>0.00476067936181175</v>
+      </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
@@ -22639,6 +25531,12 @@
       <c r="N482" s="2" t="n">
         <v>0.002970885323826448</v>
       </c>
+      <c r="O482" s="1" t="n">
+        <v>0.05034</v>
+      </c>
+      <c r="P482" s="3" t="n">
+        <v>-0.00592417061611364</v>
+      </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
@@ -22685,6 +25583,12 @@
       <c r="N483" s="2" t="n">
         <v>0.004123711340206196</v>
       </c>
+      <c r="O483" s="1" t="n">
+        <v>0.00966</v>
+      </c>
+      <c r="P483" s="3" t="n">
+        <v>-0.008213552361396325</v>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
@@ -22731,6 +25635,12 @@
       <c r="N484" s="2" t="n">
         <v>0.0008826125330980362</v>
       </c>
+      <c r="O484" s="1" t="n">
+        <v>0.06797</v>
+      </c>
+      <c r="P484" s="3" t="n">
+        <v>-0.001028806584362149</v>
+      </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
@@ -22777,6 +25687,12 @@
       <c r="N485" s="3" t="n">
         <v>-0.001335113484646107</v>
       </c>
+      <c r="O485" s="1" t="n">
+        <v>0.0004499</v>
+      </c>
+      <c r="P485" s="2" t="n">
+        <v>0.002450980392156802</v>
+      </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
@@ -22823,6 +25739,12 @@
       <c r="N486" s="3" t="n">
         <v>-0.001260398285858193</v>
       </c>
+      <c r="O486" s="1" t="n">
+        <v>0.07878</v>
+      </c>
+      <c r="P486" s="3" t="n">
+        <v>-0.005805148914689576</v>
+      </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
@@ -22869,6 +25791,12 @@
       <c r="N487" s="2" t="n">
         <v>0.002890173410404538</v>
       </c>
+      <c r="O487" s="1" t="n">
+        <v>0.0001729</v>
+      </c>
+      <c r="P487" s="3" t="n">
+        <v>-0.003458213256484078</v>
+      </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
@@ -22915,6 +25843,12 @@
       <c r="N488" s="3" t="n">
         <v>-0.003995889941774211</v>
       </c>
+      <c r="O488" s="1" t="n">
+        <v>0.08727</v>
+      </c>
+      <c r="P488" s="2" t="n">
+        <v>0.0003438789546080037</v>
+      </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
@@ -22961,6 +25895,12 @@
       <c r="N489" s="3" t="n">
         <v>-0.001263157894736791</v>
       </c>
+      <c r="O489" s="1" t="n">
+        <v>0.04743</v>
+      </c>
+      <c r="P489" s="3" t="n">
+        <v>-0.000210792580101245</v>
+      </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
@@ -23007,6 +25947,12 @@
       <c r="N490" s="2" t="n">
         <v>0.01183276360767812</v>
       </c>
+      <c r="O490" s="1" t="n">
+        <v>0.03864</v>
+      </c>
+      <c r="P490" s="2" t="n">
+        <v>0.004158004158004169</v>
+      </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
@@ -23053,6 +25999,12 @@
       <c r="N491" s="2" t="n">
         <v>0.004115755627009657</v>
       </c>
+      <c r="O491" s="1" t="n">
+        <v>0.07775</v>
+      </c>
+      <c r="P491" s="3" t="n">
+        <v>-0.004098885615473304</v>
+      </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
@@ -23099,6 +26051,12 @@
       <c r="N492" s="3" t="n">
         <v>-0.0006348198698619008</v>
       </c>
+      <c r="O492" s="1" t="n">
+        <v>0.06296</v>
+      </c>
+      <c r="P492" s="3" t="n">
+        <v>-0.0001588057805303498</v>
+      </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
@@ -23145,6 +26103,12 @@
       <c r="N493" s="2" t="n">
         <v>0.007633587786259563</v>
       </c>
+      <c r="O493" s="1" t="n">
+        <v>0.00527</v>
+      </c>
+      <c r="P493" s="3" t="n">
+        <v>-0.001893939393939317</v>
+      </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
@@ -23191,6 +26155,12 @@
       <c r="N494" s="2" t="n">
         <v>0.002170767004341697</v>
       </c>
+      <c r="O494" s="1" t="n">
+        <v>0.2758</v>
+      </c>
+      <c r="P494" s="3" t="n">
+        <v>-0.004332129963899041</v>
+      </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
@@ -23237,6 +26207,12 @@
       <c r="N495" s="2" t="n">
         <v>0.001726573536336509</v>
       </c>
+      <c r="O495" s="1" t="n">
+        <v>0.06372</v>
+      </c>
+      <c r="P495" s="3" t="n">
+        <v>-0.001566906925728657</v>
+      </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
@@ -23283,6 +26259,12 @@
       <c r="N496" s="2" t="n">
         <v>0.002047082906857691</v>
       </c>
+      <c r="O496" s="1" t="n">
+        <v>0.2922</v>
+      </c>
+      <c r="P496" s="3" t="n">
+        <v>-0.005107252298263538</v>
+      </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
@@ -23329,6 +26311,12 @@
       <c r="N497" s="3" t="n">
         <v>-0.0005084530316511804</v>
       </c>
+      <c r="O497" s="1" t="n">
+        <v>0.08280999999999999</v>
+      </c>
+      <c r="P497" s="2" t="n">
+        <v>0.05316037135953185</v>
+      </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
@@ -23375,6 +26363,12 @@
       <c r="N498" s="2" t="n">
         <v>0.002906976744185995</v>
       </c>
+      <c r="O498" s="1" t="n">
+        <v>0.1032</v>
+      </c>
+      <c r="P498" s="3" t="n">
+        <v>-0.00289855072463763</v>
+      </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
@@ -23421,6 +26415,12 @@
       <c r="N499" s="3" t="n">
         <v>-0.001676646706586841</v>
       </c>
+      <c r="O499" s="1" t="n">
+        <v>0.04146</v>
+      </c>
+      <c r="P499" s="3" t="n">
+        <v>-0.005278310940499158</v>
+      </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
@@ -23467,6 +26467,12 @@
       <c r="N500" s="3" t="n">
         <v>-0.002434867299732234</v>
       </c>
+      <c r="O500" s="1" t="n">
+        <v>0.0404</v>
+      </c>
+      <c r="P500" s="3" t="n">
+        <v>-0.01391261898950454</v>
+      </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
@@ -23513,6 +26519,12 @@
       <c r="N501" s="2" t="n">
         <v>0.002012072434607564</v>
       </c>
+      <c r="O501" s="1" t="n">
+        <v>0.0989</v>
+      </c>
+      <c r="P501" s="3" t="n">
+        <v>-0.00702811244979912</v>
+      </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
@@ -23559,6 +26571,12 @@
       <c r="N502" s="2" t="n">
         <v>0.002118003025718495</v>
       </c>
+      <c r="O502" s="1" t="n">
+        <v>0.0033</v>
+      </c>
+      <c r="P502" s="3" t="n">
+        <v>-0.003623188405797059</v>
+      </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
@@ -23605,6 +26623,12 @@
       <c r="N503" s="2" t="n">
         <v>0.003218884120171729</v>
       </c>
+      <c r="O503" s="1" t="n">
+        <v>0.009339999999999999</v>
+      </c>
+      <c r="P503" s="3" t="n">
+        <v>-0.001069518716577682</v>
+      </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
@@ -23651,6 +26675,12 @@
       <c r="N504" s="2" t="n">
         <v>0.005025125628140673</v>
       </c>
+      <c r="O504" s="1" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="P504" s="3" t="n">
+        <v>-0.008750000000000077</v>
+      </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
@@ -23697,6 +26727,12 @@
       <c r="N505" s="2" t="n">
         <v>0.001523229246001567</v>
       </c>
+      <c r="O505" s="1" t="n">
+        <v>0.131</v>
+      </c>
+      <c r="P505" s="3" t="n">
+        <v>-0.003802281368821296</v>
+      </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
@@ -23743,6 +26779,12 @@
       <c r="N506" s="3" t="n">
         <v>-0.001178550383028827</v>
       </c>
+      <c r="O506" s="1" t="n">
+        <v>0.01688</v>
+      </c>
+      <c r="P506" s="3" t="n">
+        <v>-0.00412979351032452</v>
+      </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
@@ -23789,6 +26831,12 @@
       <c r="N507" s="2" t="n">
         <v>0.002422145328719594</v>
       </c>
+      <c r="O507" s="1" t="n">
+        <v>0.002882</v>
+      </c>
+      <c r="P507" s="3" t="n">
+        <v>-0.005177770107007188</v>
+      </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
@@ -23835,6 +26883,12 @@
       <c r="N508" s="2" t="n">
         <v>0.006329113924050537</v>
       </c>
+      <c r="O508" s="1" t="n">
+        <v>2.217</v>
+      </c>
+      <c r="P508" s="3" t="n">
+        <v>-0.004043126684636072</v>
+      </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
@@ -23881,6 +26935,12 @@
       <c r="N509" s="2" t="n">
         <v>0.0005450581395349246</v>
       </c>
+      <c r="O509" s="1" t="n">
+        <v>0.05466</v>
+      </c>
+      <c r="P509" s="3" t="n">
+        <v>-0.007445069911022346</v>
+      </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
@@ -23927,6 +26987,12 @@
       <c r="N510" s="3" t="n">
         <v>-0.005084745762711775</v>
       </c>
+      <c r="O510" s="1" t="n">
+        <v>0.02925</v>
+      </c>
+      <c r="P510" s="3" t="n">
+        <v>-0.003407155025553642</v>
+      </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
@@ -23973,6 +27039,12 @@
       <c r="N511" s="3" t="n">
         <v>-0.001482213438735289</v>
       </c>
+      <c r="O511" s="1" t="n">
+        <v>0.04035</v>
+      </c>
+      <c r="P511" s="3" t="n">
+        <v>-0.001731815932706596</v>
+      </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
@@ -24019,6 +27091,12 @@
       <c r="N512" s="3" t="n">
         <v>-0.01149425287356323</v>
       </c>
+      <c r="O512" s="1" t="n">
+        <v>0.08599999999999999</v>
+      </c>
+      <c r="P512" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
@@ -24065,6 +27143,12 @@
       <c r="N513" s="2" t="n">
         <v>0.009621207024153991</v>
       </c>
+      <c r="O513" s="1" t="n">
+        <v>0.016159</v>
+      </c>
+      <c r="P513" s="2" t="n">
+        <v>0.07683593229374913</v>
+      </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
@@ -24111,6 +27195,12 @@
       <c r="N514" s="2" t="n">
         <v>0.0005730659025788926</v>
       </c>
+      <c r="O514" s="1" t="n">
+        <v>0.1737</v>
+      </c>
+      <c r="P514" s="3" t="n">
+        <v>-0.0051546391752578</v>
+      </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
@@ -24157,6 +27247,12 @@
       <c r="N515" s="2" t="n">
         <v>0.002788104089219282</v>
       </c>
+      <c r="O515" s="1" t="n">
+        <v>0.1075</v>
+      </c>
+      <c r="P515" s="3" t="n">
+        <v>-0.003707136237256697</v>
+      </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
@@ -24203,6 +27299,12 @@
       <c r="N516" s="2" t="n">
         <v>0.003745318352059935</v>
       </c>
+      <c r="O516" s="1" t="n">
+        <v>0.00266</v>
+      </c>
+      <c r="P516" s="3" t="n">
+        <v>-0.007462686567164198</v>
+      </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
@@ -24249,6 +27351,12 @@
       <c r="N517" s="2" t="n">
         <v>0.004272397721387888</v>
       </c>
+      <c r="O517" s="1" t="n">
+        <v>0.007717</v>
+      </c>
+      <c r="P517" s="3" t="n">
+        <v>-0.005156632718834615</v>
+      </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
@@ -24295,6 +27403,12 @@
       <c r="N518" s="2" t="n">
         <v>0.001298701298701246</v>
       </c>
+      <c r="O518" s="1" t="n">
+        <v>0.01542</v>
+      </c>
+      <c r="P518" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
@@ -24341,6 +27455,12 @@
       <c r="N519" s="2" t="n">
         <v>0.0007304601899195351</v>
       </c>
+      <c r="O519" s="1" t="n">
+        <v>0.00418</v>
+      </c>
+      <c r="P519" s="2" t="n">
+        <v>0.01703163017031624</v>
+      </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
@@ -24387,6 +27507,12 @@
       <c r="N520" s="2" t="n">
         <v>0.002592912705272225</v>
       </c>
+      <c r="O520" s="1" t="n">
+        <v>0.001157</v>
+      </c>
+      <c r="P520" s="3" t="n">
+        <v>-0.002586206896551693</v>
+      </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
@@ -24433,6 +27559,12 @@
       <c r="N521" s="3" t="n">
         <v>-0.001492537313432904</v>
       </c>
+      <c r="O521" s="1" t="n">
+        <v>0.01335</v>
+      </c>
+      <c r="P521" s="3" t="n">
+        <v>-0.002242152466367622</v>
+      </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
@@ -24479,6 +27611,12 @@
       <c r="N522" s="2" t="n">
         <v>0.003060778312199374</v>
       </c>
+      <c r="O522" s="1" t="n">
+        <v>0.6866</v>
+      </c>
+      <c r="P522" s="3" t="n">
+        <v>-0.002324905550712069</v>
+      </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
@@ -24525,6 +27663,12 @@
       <c r="N523" s="3" t="n">
         <v>-0.001855022831050301</v>
       </c>
+      <c r="O523" s="1" t="n">
+        <v>0.06994</v>
+      </c>
+      <c r="P523" s="3" t="n">
+        <v>-0.0001429592566118102</v>
+      </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
@@ -24571,6 +27715,12 @@
       <c r="N524" s="2" t="n">
         <v>0.005199306759098726</v>
       </c>
+      <c r="O524" s="1" t="n">
+        <v>0.01156</v>
+      </c>
+      <c r="P524" s="3" t="n">
+        <v>-0.003448275862068825</v>
+      </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
@@ -24617,6 +27767,12 @@
       <c r="N525" s="2" t="n">
         <v>0.0006097560975609507</v>
       </c>
+      <c r="O525" s="1" t="n">
+        <v>0.01635</v>
+      </c>
+      <c r="P525" s="3" t="n">
+        <v>-0.003656307129798966</v>
+      </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
@@ -24663,6 +27819,12 @@
       <c r="N526" s="3" t="n">
         <v>-0.0007373000073729189</v>
       </c>
+      <c r="O526" s="1" t="n">
+        <v>0.13461</v>
+      </c>
+      <c r="P526" s="3" t="n">
+        <v>-0.006788164981922851</v>
+      </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
@@ -24709,6 +27871,12 @@
       <c r="N527" s="2" t="n">
         <v>0.002323420074349348</v>
       </c>
+      <c r="O527" s="1" t="n">
+        <v>0.04304</v>
+      </c>
+      <c r="P527" s="3" t="n">
+        <v>-0.002318034306907648</v>
+      </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
@@ -24755,6 +27923,12 @@
       <c r="N528" s="2" t="n">
         <v>0.002203452074917332</v>
       </c>
+      <c r="O528" s="1" t="n">
+        <v>0.2719</v>
+      </c>
+      <c r="P528" s="3" t="n">
+        <v>-0.003664345914254309</v>
+      </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
@@ -24801,6 +27975,12 @@
       <c r="N529" s="2" t="n">
         <v>0.008437067773167339</v>
       </c>
+      <c r="O529" s="1" t="n">
+        <v>0.0007257</v>
+      </c>
+      <c r="P529" s="3" t="n">
+        <v>-0.004663283500205698</v>
+      </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
@@ -24847,6 +28027,12 @@
       <c r="N530" s="2" t="n">
         <v>0.004072831816003959</v>
       </c>
+      <c r="O530" s="1" t="n">
+        <v>0.004145</v>
+      </c>
+      <c r="P530" s="3" t="n">
+        <v>-0.01097590073968027</v>
+      </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
@@ -24893,6 +28079,12 @@
       <c r="N531" s="2" t="n">
         <v>0.001522070015220701</v>
       </c>
+      <c r="O531" s="1" t="n">
+        <v>1.313</v>
+      </c>
+      <c r="P531" s="3" t="n">
+        <v>-0.002279635258358749</v>
+      </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
@@ -24939,6 +28131,12 @@
       <c r="N532" s="2" t="n">
         <v>0.005957446808510691</v>
       </c>
+      <c r="O532" s="1" t="n">
+        <v>0.1177</v>
+      </c>
+      <c r="P532" s="3" t="n">
+        <v>-0.004230118443316416</v>
+      </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
@@ -24985,6 +28183,12 @@
       <c r="N533" s="2" t="n">
         <v>0.005240501590866601</v>
       </c>
+      <c r="O533" s="1" t="n">
+        <v>0.05338</v>
+      </c>
+      <c r="P533" s="3" t="n">
+        <v>-0.006144107242599216</v>
+      </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
@@ -25031,6 +28235,12 @@
       <c r="N534" s="3" t="n">
         <v>-0.003989361702127774</v>
       </c>
+      <c r="O534" s="1" t="n">
+        <v>0.1498</v>
+      </c>
+      <c r="P534" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
@@ -25077,6 +28287,12 @@
       <c r="N535" s="2" t="n">
         <v>0.001166861143524076</v>
       </c>
+      <c r="O535" s="1" t="n">
+        <v>0.01703</v>
+      </c>
+      <c r="P535" s="3" t="n">
+        <v>-0.007575757575757671</v>
+      </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
@@ -25123,6 +28339,12 @@
       <c r="N536" s="2" t="n">
         <v>0.001004016064256987</v>
       </c>
+      <c r="O536" s="1" t="n">
+        <v>0.004984</v>
+      </c>
+      <c r="P536" s="3" t="n">
+        <v>-0.0002006018054162754</v>
+      </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
@@ -25169,6 +28391,12 @@
       <c r="N537" s="2" t="n">
         <v>0.001716443529007897</v>
       </c>
+      <c r="O537" s="1" t="n">
+        <v>0.2914</v>
+      </c>
+      <c r="P537" s="3" t="n">
+        <v>-0.001370801919122726</v>
+      </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
@@ -25215,6 +28443,12 @@
       <c r="N538" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="O538" s="1" t="n">
+        <v>0.01326</v>
+      </c>
+      <c r="P538" s="3" t="n">
+        <v>-0.0007535795026376282</v>
+      </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
@@ -25261,6 +28495,12 @@
       <c r="N539" s="2" t="n">
         <v>0.004880032533550166</v>
       </c>
+      <c r="O539" s="1" t="n">
+        <v>0.02483</v>
+      </c>
+      <c r="P539" s="2" t="n">
+        <v>0.004856333468231568</v>
+      </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
@@ -25307,6 +28547,12 @@
       <c r="N540" s="2" t="n">
         <v>0.001582556708282043</v>
       </c>
+      <c r="O540" s="1" t="n">
+        <v>0.05684</v>
+      </c>
+      <c r="P540" s="3" t="n">
+        <v>-0.002106741573033622</v>
+      </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
@@ -25353,6 +28599,12 @@
       <c r="N541" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="O541" s="1" t="n">
+        <v>0.0115</v>
+      </c>
+      <c r="P541" s="3" t="n">
+        <v>-0.008620689655172362</v>
+      </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
@@ -25399,6 +28651,12 @@
       <c r="N542" s="3" t="n">
         <v>-0.008928571428571343</v>
       </c>
+      <c r="O542" s="1" t="n">
+        <v>1.11e-05</v>
+      </c>
+      <c r="P542" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
@@ -25444,6 +28702,12 @@
       </c>
       <c r="N543" s="2" t="n">
         <v>0.001904761904761922</v>
+      </c>
+      <c r="O543" s="1" t="n">
+        <v>0.003685</v>
+      </c>
+      <c r="P543" s="2" t="n">
+        <v>0.0008147745790331245</v>
       </c>
     </row>
   </sheetData>

--- a/binance-usdt-perpetual-data/weeks/2026-03-09_2026-03-15/2026-03-12.xlsx
+++ b/binance-usdt-perpetual-data/weeks/2026-03-09_2026-03-15/2026-03-12.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P543"/>
+  <dimension ref="A1:R543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -442,6 +442,8 @@
     <col width="18" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="18" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="18" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -525,6 +527,16 @@
           <t>change_01:45</t>
         </is>
       </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>price_02:00</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>change_02:00</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -577,6 +589,12 @@
       <c r="P2" s="3" t="n">
         <v>-0.005680605332045075</v>
       </c>
+      <c r="Q2" s="1" t="n">
+        <v>70753.5</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>-0.0006948887542423819</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -629,6 +647,12 @@
       <c r="P3" s="3" t="n">
         <v>-0.006125007806382498</v>
       </c>
+      <c r="Q3" s="1" t="n">
+        <v>2067.3</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>-0.0007636982328602563</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -681,6 +705,12 @@
       <c r="P4" s="3" t="n">
         <v>-0.004678762980714329</v>
       </c>
+      <c r="Q4" s="1" t="n">
+        <v>87.22</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -733,6 +763,12 @@
       <c r="P5" s="3" t="n">
         <v>-0.03818827708703378</v>
       </c>
+      <c r="Q5" s="1" t="n">
+        <v>0.01445</v>
+      </c>
+      <c r="R5" s="2" t="n">
+        <v>0.0263513033596136</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -785,6 +821,12 @@
       <c r="P6" s="3" t="n">
         <v>-0.002451241607161826</v>
       </c>
+      <c r="Q6" s="1" t="n">
+        <v>0.09364</v>
+      </c>
+      <c r="R6" s="2" t="n">
+        <v>0.0004273504273504099</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -837,6 +879,12 @@
       <c r="P7" s="3" t="n">
         <v>-0.0009295673936360949</v>
       </c>
+      <c r="Q7" s="1" t="n">
+        <v>1.3969</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>-0.0002147151445748404</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -889,6 +937,12 @@
       <c r="P8" s="3" t="n">
         <v>-0.01092732375943547</v>
       </c>
+      <c r="Q8" s="1" t="n">
+        <v>36.087</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>-0.005758210271104146</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -941,6 +995,12 @@
       <c r="P9" s="3" t="n">
         <v>-0.00360520004277358</v>
       </c>
+      <c r="Q9" s="1" t="n">
+        <v>651.89</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>-0.0005519356075124777</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -993,6 +1053,12 @@
       <c r="P10" s="2" t="n">
         <v>0.00761578044596917</v>
       </c>
+      <c r="Q10" s="1" t="n">
+        <v>14.279</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>-0.02771346860956013</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1045,6 +1111,12 @@
       <c r="P11" s="3" t="n">
         <v>-0.004232107589579637</v>
       </c>
+      <c r="Q11" s="1" t="n">
+        <v>211.69</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>-0.0003305629013977766</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1097,6 +1169,12 @@
       <c r="P12" s="3" t="n">
         <v>-0.006127160786171037</v>
       </c>
+      <c r="Q12" s="1" t="n">
+        <v>0.0033665</v>
+      </c>
+      <c r="R12" s="2" t="n">
+        <v>0.002620841647556427</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1149,6 +1227,12 @@
       <c r="P13" s="2" t="n">
         <v>0.007861208999728886</v>
       </c>
+      <c r="Q13" s="1" t="n">
+        <v>0.03652</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>-0.01775147928994085</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1201,6 +1285,12 @@
       <c r="P14" s="3" t="n">
         <v>-0.01481762917933136</v>
       </c>
+      <c r="Q14" s="1" t="n">
+        <v>2.597</v>
+      </c>
+      <c r="R14" s="2" t="n">
+        <v>0.001542614731970692</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1253,6 +1343,12 @@
       <c r="P15" s="3" t="n">
         <v>-0.005366545159983882</v>
       </c>
+      <c r="Q15" s="1" t="n">
+        <v>0.9792999999999999</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>-0.003054056805456585</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1305,6 +1401,12 @@
       <c r="P16" s="2" t="n">
         <v>0.006782081028020674</v>
       </c>
+      <c r="Q16" s="1" t="n">
+        <v>0.05614</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>-0.004786385392660865</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1357,6 +1459,12 @@
       <c r="P17" s="3" t="n">
         <v>-0.004514672686230252</v>
       </c>
+      <c r="Q17" s="1" t="n">
+        <v>0.881</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>-0.001133786848072563</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1409,6 +1517,12 @@
       <c r="P18" s="3" t="n">
         <v>-0.003766478342749533</v>
       </c>
+      <c r="Q18" s="1" t="n">
+        <v>0.2647</v>
+      </c>
+      <c r="R18" s="2" t="n">
+        <v>0.0007561436672967031</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1461,6 +1575,12 @@
       <c r="P19" s="2" t="n">
         <v>0.01055061959317279</v>
       </c>
+      <c r="Q19" s="1" t="n">
+        <v>0.34723</v>
+      </c>
+      <c r="R19" s="2" t="n">
+        <v>0.004222460016774044</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1513,6 +1633,12 @@
       <c r="P20" s="3" t="n">
         <v>-0.006484817292846177</v>
       </c>
+      <c r="Q20" s="1" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="R20" s="2" t="n">
+        <v>0.001554082055532591</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1565,6 +1691,12 @@
       <c r="P21" s="3" t="n">
         <v>-0.006399680015999206</v>
       </c>
+      <c r="Q21" s="1" t="n">
+        <v>199.08</v>
+      </c>
+      <c r="R21" s="2" t="n">
+        <v>0.001761183515322411</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1617,6 +1749,12 @@
       <c r="P22" s="3" t="n">
         <v>-0.0119982859591488</v>
       </c>
+      <c r="Q22" s="1" t="n">
+        <v>0.020598</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>-0.007373138643920626</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1669,6 +1807,12 @@
       <c r="P23" s="3" t="n">
         <v>-0.001135197677210867</v>
       </c>
+      <c r="Q23" s="1" t="n">
+        <v>456.63</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>-0.002010709212108001</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1721,6 +1865,12 @@
       <c r="P24" s="3" t="n">
         <v>-0.001719685465852991</v>
       </c>
+      <c r="Q24" s="1" t="n">
+        <v>5167.17</v>
+      </c>
+      <c r="R24" s="2" t="n">
+        <v>0.001261466556603268</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1773,6 +1923,12 @@
       <c r="P25" s="3" t="n">
         <v>-0.005915863277826497</v>
       </c>
+      <c r="Q25" s="1" t="n">
+        <v>9.079000000000001</v>
+      </c>
+      <c r="R25" s="2" t="n">
+        <v>0.000551024906325852</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1825,6 +1981,12 @@
       <c r="P26" s="3" t="n">
         <v>-0.008996132503783432</v>
       </c>
+      <c r="Q26" s="1" t="n">
+        <v>0.11802</v>
+      </c>
+      <c r="R26" s="2" t="n">
+        <v>0.001272588444896898</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1877,6 +2039,12 @@
       <c r="P27" s="3" t="n">
         <v>-0.02105263157894735</v>
       </c>
+      <c r="Q27" s="1" t="n">
+        <v>0.01211</v>
+      </c>
+      <c r="R27" s="2" t="n">
+        <v>0.00165425971877578</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1929,6 +2097,12 @@
       <c r="P28" s="3" t="n">
         <v>-0.008461538461538555</v>
       </c>
+      <c r="Q28" s="1" t="n">
+        <v>1.292</v>
+      </c>
+      <c r="R28" s="2" t="n">
+        <v>0.002327385570209553</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1981,6 +2155,12 @@
       <c r="P29" s="3" t="n">
         <v>-0.02338218343487564</v>
       </c>
+      <c r="Q29" s="1" t="n">
+        <v>0.06475</v>
+      </c>
+      <c r="R29" s="2" t="n">
+        <v>0.0917214634968808</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2033,6 +2213,12 @@
       <c r="P30" s="3" t="n">
         <v>-0.006531678641410849</v>
       </c>
+      <c r="Q30" s="1" t="n">
+        <v>1.527</v>
+      </c>
+      <c r="R30" s="2" t="n">
+        <v>0.00394477317554241</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2085,6 +2271,12 @@
       <c r="P31" s="3" t="n">
         <v>-0.006322957198443575</v>
       </c>
+      <c r="Q31" s="1" t="n">
+        <v>0.002027</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>-0.007831620166421907</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2137,6 +2329,12 @@
       <c r="P32" s="3" t="n">
         <v>-0.006140997297961194</v>
       </c>
+      <c r="Q32" s="1" t="n">
+        <v>0.04035</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>-0.002718734552644733</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2189,6 +2387,12 @@
       <c r="P33" s="3" t="n">
         <v>-0.003036437246963509</v>
       </c>
+      <c r="Q33" s="1" t="n">
+        <v>0.0987</v>
+      </c>
+      <c r="R33" s="2" t="n">
+        <v>0.002030456852791795</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2241,6 +2445,12 @@
       <c r="P34" s="3" t="n">
         <v>-0.003795066413662216</v>
       </c>
+      <c r="Q34" s="1" t="n">
+        <v>0.1045</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>-0.004761904761904767</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2293,6 +2503,12 @@
       <c r="P35" s="3" t="n">
         <v>-0.01905829596412556</v>
       </c>
+      <c r="Q35" s="1" t="n">
+        <v>0.00874</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>-0.001142857142857295</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2345,6 +2561,12 @@
       <c r="P36" s="3" t="n">
         <v>-0.006681514476614736</v>
       </c>
+      <c r="Q36" s="1" t="n">
+        <v>0.3577</v>
+      </c>
+      <c r="R36" s="2" t="n">
+        <v>0.00252242152466371</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2397,6 +2619,12 @@
       <c r="P37" s="3" t="n">
         <v>-0.004783054321831269</v>
       </c>
+      <c r="Q37" s="1" t="n">
+        <v>0.005837</v>
+      </c>
+      <c r="R37" s="2" t="n">
+        <v>0.001888087881908787</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2449,6 +2677,12 @@
       <c r="P38" s="2" t="n">
         <v>0.0009930486593842428</v>
       </c>
+      <c r="Q38" s="1" t="n">
+        <v>0.262</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>-0.0003052503052501869</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2501,6 +2735,12 @@
       <c r="P39" s="2" t="n">
         <v>0.008344923504867945</v>
       </c>
+      <c r="Q39" s="1" t="n">
+        <v>0.05039</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>-0.007093596059113421</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2553,6 +2793,12 @@
       <c r="P40" s="3" t="n">
         <v>-0.006196695095948737</v>
       </c>
+      <c r="Q40" s="1" t="n">
+        <v>0.14835</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>-0.005363727790814584</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2605,6 +2851,12 @@
       <c r="P41" s="3" t="n">
         <v>-0.008828722778104776</v>
       </c>
+      <c r="Q41" s="1" t="n">
+        <v>0.1687</v>
+      </c>
+      <c r="R41" s="2" t="n">
+        <v>0.001781472684085479</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2657,6 +2909,12 @@
       <c r="P42" s="3" t="n">
         <v>-0.005063516034467383</v>
       </c>
+      <c r="Q42" s="1" t="n">
+        <v>111.88</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>-0.001071428571428612</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2709,6 +2967,12 @@
       <c r="P43" s="3" t="n">
         <v>-0.01097022367858659</v>
       </c>
+      <c r="Q43" s="1" t="n">
+        <v>0.7114</v>
+      </c>
+      <c r="R43" s="2" t="n">
+        <v>0.02477672140593488</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2761,6 +3025,12 @@
       <c r="P44" s="3" t="n">
         <v>-0.002362777171937524</v>
       </c>
+      <c r="Q44" s="1" t="n">
+        <v>54.88</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>-0.0001821825469119696</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2813,6 +3083,12 @@
       <c r="P45" s="3" t="n">
         <v>-0.01489325556373512</v>
       </c>
+      <c r="Q45" s="1" t="n">
+        <v>0.51761</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>-0.008181957538131364</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2865,6 +3141,12 @@
       <c r="P46" s="3" t="n">
         <v>-0.003400396712949784</v>
       </c>
+      <c r="Q46" s="1" t="n">
+        <v>0.7039</v>
+      </c>
+      <c r="R46" s="2" t="n">
+        <v>0.0007108330963888895</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2917,6 +3199,12 @@
       <c r="P47" s="3" t="n">
         <v>-0.00636618283677105</v>
       </c>
+      <c r="Q47" s="1" t="n">
+        <v>3.911</v>
+      </c>
+      <c r="R47" s="2" t="n">
+        <v>0.002306509482316734</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2969,6 +3257,12 @@
       <c r="P48" s="3" t="n">
         <v>-0.002180006228589158</v>
       </c>
+      <c r="Q48" s="1" t="n">
+        <v>0.16008</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>-0.0007490636704120411</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3021,6 +3315,12 @@
       <c r="P49" s="3" t="n">
         <v>-0.0147840531561461</v>
       </c>
+      <c r="Q49" s="1" t="n">
+        <v>0.05941</v>
+      </c>
+      <c r="R49" s="2" t="n">
+        <v>0.001686056314280828</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3073,6 +3373,12 @@
       <c r="P50" s="3" t="n">
         <v>-0.00257731958762894</v>
       </c>
+      <c r="Q50" s="1" t="n">
+        <v>0.0387</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3125,6 +3431,12 @@
       <c r="P51" s="3" t="n">
         <v>-0.05081735256043594</v>
       </c>
+      <c r="Q51" s="1" t="n">
+        <v>0.31455</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>-0.002347045577087819</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3177,6 +3489,12 @@
       <c r="P52" s="3" t="n">
         <v>-0.001697216564833674</v>
       </c>
+      <c r="Q52" s="1" t="n">
+        <v>0.2929</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>-0.00408024481468881</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3229,6 +3547,12 @@
       <c r="P53" s="3" t="n">
         <v>-0.004410838059231293</v>
       </c>
+      <c r="Q53" s="1" t="n">
+        <v>0.1585</v>
+      </c>
+      <c r="R53" s="2" t="n">
+        <v>0.003164556962025319</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3281,6 +3605,12 @@
       <c r="P54" s="3" t="n">
         <v>-0.001817682968653647</v>
       </c>
+      <c r="Q54" s="1" t="n">
+        <v>0.29056</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>-0.001683559525854631</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3333,6 +3663,12 @@
       <c r="P55" s="3" t="n">
         <v>-0.009015256588072115</v>
       </c>
+      <c r="Q55" s="1" t="n">
+        <v>0.007138</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>-0.0009797060881735565</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3385,6 +3721,12 @@
       <c r="P56" s="3" t="n">
         <v>-0.006685432793807149</v>
       </c>
+      <c r="Q56" s="1" t="n">
+        <v>0.02805</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>-0.006376195536663233</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3437,6 +3779,12 @@
       <c r="P57" s="2" t="n">
         <v>0.003321470937129329</v>
       </c>
+      <c r="Q57" s="1" t="n">
+        <v>0.04221</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>-0.001891700165523851</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3489,6 +3837,12 @@
       <c r="P58" s="2" t="n">
         <v>0.01253298153034303</v>
       </c>
+      <c r="Q58" s="1" t="n">
+        <v>0.04707</v>
+      </c>
+      <c r="R58" s="2" t="n">
+        <v>0.02214983713355049</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3541,6 +3895,12 @@
       <c r="P59" s="3" t="n">
         <v>-0.002594033722438394</v>
       </c>
+      <c r="Q59" s="1" t="n">
+        <v>1.537</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>-0.000650195058517628</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3593,6 +3953,12 @@
       <c r="P60" s="3" t="n">
         <v>-0.008695652173913066</v>
       </c>
+      <c r="Q60" s="1" t="n">
+        <v>0.00344</v>
+      </c>
+      <c r="R60" s="2" t="n">
+        <v>0.005847953216374284</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3645,6 +4011,12 @@
       <c r="P61" s="3" t="n">
         <v>-0.009596928982725537</v>
       </c>
+      <c r="Q61" s="1" t="n">
+        <v>0.1548</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3697,6 +4069,12 @@
       <c r="P62" s="3" t="n">
         <v>-0.004340277777777685</v>
       </c>
+      <c r="Q62" s="1" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="R62" s="2" t="n">
+        <v>0.002615518744550908</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3749,6 +4127,12 @@
       <c r="P63" s="3" t="n">
         <v>-0.008396186139177482</v>
       </c>
+      <c r="Q63" s="1" t="n">
+        <v>0.6973</v>
+      </c>
+      <c r="R63" s="2" t="n">
+        <v>0.000717566016073559</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3801,6 +4185,12 @@
       <c r="P64" s="3" t="n">
         <v>-0.005401755570560437</v>
       </c>
+      <c r="Q64" s="1" t="n">
+        <v>2.931</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>-0.00509164969450106</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3853,6 +4243,12 @@
       <c r="P65" s="3" t="n">
         <v>-0.006244796003330592</v>
       </c>
+      <c r="Q65" s="1" t="n">
+        <v>0.02381</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>-0.002513615416841121</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3905,6 +4301,12 @@
       <c r="P66" s="3" t="n">
         <v>-0.007843137254901914</v>
       </c>
+      <c r="Q66" s="1" t="n">
+        <v>0.1012</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3957,6 +4359,12 @@
       <c r="P67" s="2" t="n">
         <v>0.0006842753524017786</v>
       </c>
+      <c r="Q67" s="1" t="n">
+        <v>0.007299</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>-0.001777899343544857</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -4009,6 +4417,12 @@
       <c r="P68" s="2" t="n">
         <v>0.00745077168706762</v>
       </c>
+      <c r="Q68" s="1" t="n">
+        <v>18.92</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>-0.0005282620179608036</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -4061,6 +4475,12 @@
       <c r="P69" s="2" t="n">
         <v>0.0003703703703703553</v>
       </c>
+      <c r="Q69" s="1" t="n">
+        <v>0.05386</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>-0.002961865975564614</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4113,6 +4533,12 @@
       <c r="P70" s="3" t="n">
         <v>-0.004184100418410046</v>
       </c>
+      <c r="Q70" s="1" t="n">
+        <v>0.237</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>-0.004201680672268912</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4165,6 +4591,12 @@
       <c r="P71" s="3" t="n">
         <v>-0.01880141010575795</v>
       </c>
+      <c r="Q71" s="1" t="n">
+        <v>5.805</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>-0.006843455945252359</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -4217,6 +4649,12 @@
       <c r="P72" s="3" t="n">
         <v>-0.0130958617077004</v>
       </c>
+      <c r="Q72" s="1" t="n">
+        <v>0.00188</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>-0.002123142250530837</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4269,6 +4707,12 @@
       <c r="P73" s="3" t="n">
         <v>-0.0060413354531002</v>
       </c>
+      <c r="Q73" s="1" t="n">
+        <v>0.9395</v>
+      </c>
+      <c r="R73" s="2" t="n">
+        <v>0.001812753252292637</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -4321,6 +4765,12 @@
       <c r="P74" s="3" t="n">
         <v>-0.009068425391591127</v>
       </c>
+      <c r="Q74" s="1" t="n">
+        <v>0.1204</v>
+      </c>
+      <c r="R74" s="2" t="n">
+        <v>0.00166389351081524</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4373,6 +4823,12 @@
       <c r="P75" s="2" t="n">
         <v>0.000227143668370199</v>
       </c>
+      <c r="Q75" s="1" t="n">
+        <v>351.37</v>
+      </c>
+      <c r="R75" s="3" t="n">
+        <v>-0.002583172476439106</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4425,6 +4881,12 @@
       <c r="P76" s="3" t="n">
         <v>-0.008374507997655146</v>
       </c>
+      <c r="Q76" s="1" t="n">
+        <v>0.11915</v>
+      </c>
+      <c r="R76" s="2" t="n">
+        <v>0.006249472172958404</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4477,6 +4939,12 @@
       <c r="P77" s="3" t="n">
         <v>-0.009839707982859793</v>
       </c>
+      <c r="Q77" s="1" t="n">
+        <v>0.06256</v>
+      </c>
+      <c r="R77" s="2" t="n">
+        <v>0.002724795640327031</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -4529,6 +4997,12 @@
       <c r="P78" s="3" t="n">
         <v>-0.002647463729746905</v>
       </c>
+      <c r="Q78" s="1" t="n">
+        <v>0.0944</v>
+      </c>
+      <c r="R78" s="2" t="n">
+        <v>0.002335952431514101</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -4581,6 +5055,12 @@
       <c r="P79" s="3" t="n">
         <v>-0.01647685970438582</v>
       </c>
+      <c r="Q79" s="1" t="n">
+        <v>0.4051</v>
+      </c>
+      <c r="R79" s="3" t="n">
+        <v>-0.001970928800197013</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -4633,6 +5113,12 @@
       <c r="P80" s="3" t="n">
         <v>-0.005460863809366216</v>
       </c>
+      <c r="Q80" s="1" t="n">
+        <v>0.006016</v>
+      </c>
+      <c r="R80" s="2" t="n">
+        <v>0.000998336106489173</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -4685,6 +5171,12 @@
       <c r="P81" s="3" t="n">
         <v>-0.01625239005736131</v>
       </c>
+      <c r="Q81" s="1" t="n">
+        <v>0.1047</v>
+      </c>
+      <c r="R81" s="2" t="n">
+        <v>0.01749271137026235</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -4737,6 +5229,12 @@
       <c r="P82" s="3" t="n">
         <v>-0.001955034213098785</v>
       </c>
+      <c r="Q82" s="1" t="n">
+        <v>0.1018</v>
+      </c>
+      <c r="R82" s="3" t="n">
+        <v>-0.002938295788442652</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -4789,6 +5287,12 @@
       <c r="P83" s="2" t="n">
         <v>0.0001625487646294386</v>
       </c>
+      <c r="Q83" s="1" t="n">
+        <v>0.06067</v>
+      </c>
+      <c r="R83" s="3" t="n">
+        <v>-0.01397692182675117</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -4841,6 +5345,12 @@
       <c r="P84" s="3" t="n">
         <v>-0.003202277174879957</v>
       </c>
+      <c r="Q84" s="1" t="n">
+        <v>1.1277</v>
+      </c>
+      <c r="R84" s="2" t="n">
+        <v>0.006335891486703448</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -4893,6 +5403,12 @@
       <c r="P85" s="3" t="n">
         <v>-0.00971599402092675</v>
       </c>
+      <c r="Q85" s="1" t="n">
+        <v>0.01318</v>
+      </c>
+      <c r="R85" s="3" t="n">
+        <v>-0.005283018867924444</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -4945,6 +5461,12 @@
       <c r="P86" s="3" t="n">
         <v>-0.005328596802841907</v>
       </c>
+      <c r="Q86" s="1" t="n">
+        <v>0.01689</v>
+      </c>
+      <c r="R86" s="2" t="n">
+        <v>0.005357142857142846</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -4997,6 +5519,12 @@
       <c r="P87" s="3" t="n">
         <v>-0.005390512697652124</v>
       </c>
+      <c r="Q87" s="1" t="n">
+        <v>8.298999999999999</v>
+      </c>
+      <c r="R87" s="3" t="n">
+        <v>-0.0004817535830424347</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -5049,6 +5577,12 @@
       <c r="P88" s="3" t="n">
         <v>-0.005749006777284298</v>
       </c>
+      <c r="Q88" s="1" t="n">
+        <v>2.1311</v>
+      </c>
+      <c r="R88" s="2" t="n">
+        <v>0.001833396013538827</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -5101,6 +5635,12 @@
       <c r="P89" s="2" t="n">
         <v>0.002655650634405398</v>
       </c>
+      <c r="Q89" s="1" t="n">
+        <v>0.006827</v>
+      </c>
+      <c r="R89" s="2" t="n">
+        <v>0.00456150676868743</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -5153,6 +5693,12 @@
       <c r="P90" s="2" t="n">
         <v>0.0006535947712418161</v>
       </c>
+      <c r="Q90" s="1" t="n">
+        <v>15.26</v>
+      </c>
+      <c r="R90" s="3" t="n">
+        <v>-0.003265839320705468</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -5205,6 +5751,12 @@
       <c r="P91" s="3" t="n">
         <v>-0.004464285714285702</v>
       </c>
+      <c r="Q91" s="1" t="n">
+        <v>0.000224</v>
+      </c>
+      <c r="R91" s="2" t="n">
+        <v>0.004484304932735414</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -5257,6 +5809,12 @@
       <c r="P92" s="3" t="n">
         <v>-0.01250466592011952</v>
       </c>
+      <c r="Q92" s="1" t="n">
+        <v>0.05203</v>
+      </c>
+      <c r="R92" s="3" t="n">
+        <v>-0.01663201663201661</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -5309,6 +5867,12 @@
       <c r="P93" s="3" t="n">
         <v>-0.0005280229312816964</v>
       </c>
+      <c r="Q93" s="1" t="n">
+        <v>1.3263</v>
+      </c>
+      <c r="R93" s="2" t="n">
+        <v>0.0009811320754717578</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -5361,6 +5925,12 @@
       <c r="P94" s="2" t="n">
         <v>0.009247101033825903</v>
       </c>
+      <c r="Q94" s="1" t="n">
+        <v>0.054221</v>
+      </c>
+      <c r="R94" s="3" t="n">
+        <v>-0.00641366293452572</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -5413,6 +5983,12 @@
       <c r="P95" s="3" t="n">
         <v>-0.003298969072164929</v>
       </c>
+      <c r="Q95" s="1" t="n">
+        <v>0.242</v>
+      </c>
+      <c r="R95" s="2" t="n">
+        <v>0.001241208109226292</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -5465,6 +6041,12 @@
       <c r="P96" s="3" t="n">
         <v>-0.003418961374976933</v>
       </c>
+      <c r="Q96" s="1" t="n">
+        <v>1.0765</v>
+      </c>
+      <c r="R96" s="3" t="n">
+        <v>-0.001854427445526195</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -5517,6 +6099,12 @@
       <c r="P97" s="3" t="n">
         <v>-0.005403319181783143</v>
       </c>
+      <c r="Q97" s="1" t="n">
+        <v>0.2567</v>
+      </c>
+      <c r="R97" s="3" t="n">
+        <v>-0.003880481179666282</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -5569,6 +6157,12 @@
       <c r="P98" s="3" t="n">
         <v>-0.003401939105290019</v>
       </c>
+      <c r="Q98" s="1" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="R98" s="3" t="n">
+        <v>-0.01006997781191332</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -5621,6 +6215,12 @@
       <c r="P99" s="2" t="n">
         <v>0.0152457075192422</v>
       </c>
+      <c r="Q99" s="1" t="n">
+        <v>0.13663</v>
+      </c>
+      <c r="R99" s="3" t="n">
+        <v>-0.00400933080623994</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -5673,6 +6273,12 @@
       <c r="P100" s="3" t="n">
         <v>-0.006514657980456099</v>
       </c>
+      <c r="Q100" s="1" t="n">
+        <v>0.03061</v>
+      </c>
+      <c r="R100" s="2" t="n">
+        <v>0.003606557377049147</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -5725,6 +6331,12 @@
       <c r="P101" s="3" t="n">
         <v>-0.004835589941973032</v>
       </c>
+      <c r="Q101" s="1" t="n">
+        <v>1.031</v>
+      </c>
+      <c r="R101" s="2" t="n">
+        <v>0.001943634596695823</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -5777,6 +6389,12 @@
       <c r="P102" s="3" t="n">
         <v>-0.008581752484191473</v>
       </c>
+      <c r="Q102" s="1" t="n">
+        <v>0.02199</v>
+      </c>
+      <c r="R102" s="2" t="n">
+        <v>0.001822323462414504</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -5829,6 +6447,12 @@
       <c r="P103" s="3" t="n">
         <v>-0.004587155963302742</v>
       </c>
+      <c r="Q103" s="1" t="n">
+        <v>0.01954</v>
+      </c>
+      <c r="R103" s="2" t="n">
+        <v>0.0005120327700972654</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -5881,6 +6505,12 @@
       <c r="P104" s="3" t="n">
         <v>-0.004660452729693672</v>
       </c>
+      <c r="Q104" s="1" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="R104" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -5933,6 +6563,12 @@
       <c r="P105" s="3" t="n">
         <v>-0.0003078817733989536</v>
       </c>
+      <c r="Q105" s="1" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="R105" s="2" t="n">
+        <v>0.0009239297813366535</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -5985,6 +6621,12 @@
       <c r="P106" s="3" t="n">
         <v>-0.004196642685851356</v>
       </c>
+      <c r="Q106" s="1" t="n">
+        <v>0.1661</v>
+      </c>
+      <c r="R106" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -6037,6 +6679,12 @@
       <c r="P107" s="2" t="n">
         <v>0.01484392054136645</v>
       </c>
+      <c r="Q107" s="1" t="n">
+        <v>0.4614</v>
+      </c>
+      <c r="R107" s="3" t="n">
+        <v>-0.007528500752850082</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -6089,6 +6737,12 @@
       <c r="P108" s="3" t="n">
         <v>-0.005639655684179156</v>
       </c>
+      <c r="Q108" s="1" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="R108" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -6141,6 +6795,12 @@
       <c r="P109" s="3" t="n">
         <v>-0.008978195810175249</v>
       </c>
+      <c r="Q109" s="1" t="n">
+        <v>0.2319</v>
+      </c>
+      <c r="R109" s="2" t="n">
+        <v>0.0004314063848144477</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -6193,6 +6853,12 @@
       <c r="P110" s="3" t="n">
         <v>-0.001986754966887451</v>
       </c>
+      <c r="Q110" s="1" t="n">
+        <v>0.01508</v>
+      </c>
+      <c r="R110" s="2" t="n">
+        <v>0.0006635700066356731</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -6245,6 +6911,12 @@
       <c r="P111" s="3" t="n">
         <v>-0.00217509516041327</v>
       </c>
+      <c r="Q111" s="1" t="n">
+        <v>1.837</v>
+      </c>
+      <c r="R111" s="2" t="n">
+        <v>0.001089918256130791</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -6297,6 +6969,12 @@
       <c r="P112" s="2" t="n">
         <v>0.002342529932326908</v>
       </c>
+      <c r="Q112" s="1" t="n">
+        <v>0.03837</v>
+      </c>
+      <c r="R112" s="3" t="n">
+        <v>-0.003635419371591826</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -6349,6 +7027,12 @@
       <c r="P113" s="2" t="n">
         <v>0.003052359708851819</v>
       </c>
+      <c r="Q113" s="1" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="R113" s="2" t="n">
+        <v>0.001872659176029964</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -6401,6 +7085,12 @@
       <c r="P114" s="3" t="n">
         <v>-0.01924344273098725</v>
       </c>
+      <c r="Q114" s="1" t="n">
+        <v>0.007605</v>
+      </c>
+      <c r="R114" s="2" t="n">
+        <v>0.02204004838059402</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -6453,6 +7143,12 @@
       <c r="P115" s="3" t="n">
         <v>-0.007016137115365263</v>
       </c>
+      <c r="Q115" s="1" t="n">
+        <v>0.09898999999999999</v>
+      </c>
+      <c r="R115" s="3" t="n">
+        <v>-0.0008075098415263008</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -6505,6 +7201,12 @@
       <c r="P116" s="3" t="n">
         <v>-0.004570603800817962</v>
       </c>
+      <c r="Q116" s="1" t="n">
+        <v>0.0828</v>
+      </c>
+      <c r="R116" s="2" t="n">
+        <v>0.0004833252779120151</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -6557,6 +7259,12 @@
       <c r="P117" s="3" t="n">
         <v>-0.007605820105820186</v>
       </c>
+      <c r="Q117" s="1" t="n">
+        <v>0.3005</v>
+      </c>
+      <c r="R117" s="2" t="n">
+        <v>0.001332889036987709</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -6609,6 +7317,12 @@
       <c r="P118" s="3" t="n">
         <v>-0.002643171806167446</v>
       </c>
+      <c r="Q118" s="1" t="n">
+        <v>0.02266</v>
+      </c>
+      <c r="R118" s="2" t="n">
+        <v>0.0008833922261483739</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -6661,6 +7375,12 @@
       <c r="P119" s="3" t="n">
         <v>-0.001297016861219233</v>
       </c>
+      <c r="Q119" s="1" t="n">
+        <v>0.1545</v>
+      </c>
+      <c r="R119" s="2" t="n">
+        <v>0.00324675324675325</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -6713,6 +7433,12 @@
       <c r="P120" s="2" t="n">
         <v>0.02610183996576802</v>
       </c>
+      <c r="Q120" s="1" t="n">
+        <v>0.004573</v>
+      </c>
+      <c r="R120" s="3" t="n">
+        <v>-0.04649708090075065</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -6765,6 +7491,12 @@
       <c r="P121" s="2" t="n">
         <v>0.0006933210076265831</v>
       </c>
+      <c r="Q121" s="1" t="n">
+        <v>0.433</v>
+      </c>
+      <c r="R121" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -6817,6 +7549,12 @@
       <c r="P122" s="3" t="n">
         <v>-0.002567394094993583</v>
       </c>
+      <c r="Q122" s="1" t="n">
+        <v>0.777</v>
+      </c>
+      <c r="R122" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -6869,6 +7607,12 @@
       <c r="P123" s="3" t="n">
         <v>-0.003460207612456686</v>
       </c>
+      <c r="Q123" s="1" t="n">
+        <v>0.0864</v>
+      </c>
+      <c r="R123" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -6921,6 +7665,12 @@
       <c r="P124" s="3" t="n">
         <v>-0.00965406275140791</v>
       </c>
+      <c r="Q124" s="1" t="n">
+        <v>0.01228</v>
+      </c>
+      <c r="R124" s="3" t="n">
+        <v>-0.002437043054427337</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -6973,6 +7723,12 @@
       <c r="P125" s="3" t="n">
         <v>-0.004703957459862993</v>
       </c>
+      <c r="Q125" s="1" t="n">
+        <v>0.09744</v>
+      </c>
+      <c r="R125" s="2" t="n">
+        <v>0.00113017569094831</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -7025,6 +7781,12 @@
       <c r="P126" s="3" t="n">
         <v>-0.006380263717567028</v>
       </c>
+      <c r="Q126" s="1" t="n">
+        <v>0.04672</v>
+      </c>
+      <c r="R126" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -7077,6 +7839,12 @@
       <c r="P127" s="3" t="n">
         <v>-0.02153846153846144</v>
       </c>
+      <c r="Q127" s="1" t="n">
+        <v>3.22e-05</v>
+      </c>
+      <c r="R127" s="2" t="n">
+        <v>0.01257861635220114</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -7129,6 +7897,12 @@
       <c r="P128" s="3" t="n">
         <v>-0.01653324051514089</v>
       </c>
+      <c r="Q128" s="1" t="n">
+        <v>0.5651</v>
+      </c>
+      <c r="R128" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -7181,6 +7955,12 @@
       <c r="P129" s="3" t="n">
         <v>-0.005315917375455487</v>
       </c>
+      <c r="Q129" s="1" t="n">
+        <v>0.06526</v>
+      </c>
+      <c r="R129" s="3" t="n">
+        <v>-0.003511986562834142</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -7233,6 +8013,12 @@
       <c r="P130" s="3" t="n">
         <v>-0.0001649620587264075</v>
       </c>
+      <c r="Q130" s="1" t="n">
+        <v>0.0006110999999999999</v>
+      </c>
+      <c r="R130" s="2" t="n">
+        <v>0.008249463784853826</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -7285,6 +8071,12 @@
       <c r="P131" s="3" t="n">
         <v>-0.01136363636363637</v>
       </c>
+      <c r="Q131" s="1" t="n">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="R131" s="2" t="n">
+        <v>0.01149425287356323</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -7337,6 +8129,12 @@
       <c r="P132" s="3" t="n">
         <v>-0.005952380952381031</v>
       </c>
+      <c r="Q132" s="1" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="R132" s="3" t="n">
+        <v>-0.001996007984031901</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -7389,6 +8187,12 @@
       <c r="P133" s="3" t="n">
         <v>-0.003310261811616188</v>
       </c>
+      <c r="Q133" s="1" t="n">
+        <v>0.03314</v>
+      </c>
+      <c r="R133" s="2" t="n">
+        <v>0.0006038647342997018</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -7441,6 +8245,12 @@
       <c r="P134" s="3" t="n">
         <v>-0.00393293314013672</v>
       </c>
+      <c r="Q134" s="1" t="n">
+        <v>0.14449</v>
+      </c>
+      <c r="R134" s="2" t="n">
+        <v>0.0009005264616238501</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -7493,6 +8303,12 @@
       <c r="P135" s="3" t="n">
         <v>-0.007392473118279618</v>
       </c>
+      <c r="Q135" s="1" t="n">
+        <v>0.02957</v>
+      </c>
+      <c r="R135" s="2" t="n">
+        <v>0.001015572105619458</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -7545,6 +8361,12 @@
       <c r="P136" s="3" t="n">
         <v>-0.002470878926932465</v>
       </c>
+      <c r="Q136" s="1" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="R136" s="3" t="n">
+        <v>-0.002123142250530866</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -7597,6 +8419,12 @@
       <c r="P137" s="3" t="n">
         <v>-0.006470996071180989</v>
       </c>
+      <c r="Q137" s="1" t="n">
+        <v>0.0004305</v>
+      </c>
+      <c r="R137" s="2" t="n">
+        <v>0.001395673412421527</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -7649,6 +8477,12 @@
       <c r="P138" s="2" t="n">
         <v>0.0004069451980465994</v>
       </c>
+      <c r="Q138" s="1" t="n">
+        <v>0.029429</v>
+      </c>
+      <c r="R138" s="3" t="n">
+        <v>-0.002406779661016887</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -7701,6 +8535,12 @@
       <c r="P139" s="2" t="n">
         <v>0.001355013550135555</v>
       </c>
+      <c r="Q139" s="1" t="n">
+        <v>0.09633</v>
+      </c>
+      <c r="R139" s="2" t="n">
+        <v>0.002706359945872763</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -7753,6 +8593,12 @@
       <c r="P140" s="2" t="n">
         <v>0.0002809778027535515</v>
       </c>
+      <c r="Q140" s="1" t="n">
+        <v>0.3566</v>
+      </c>
+      <c r="R140" s="2" t="n">
+        <v>0.001685393258426937</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -7805,6 +8651,12 @@
       <c r="P141" s="3" t="n">
         <v>-0.02770594754340601</v>
       </c>
+      <c r="Q141" s="1" t="n">
+        <v>0.02643</v>
+      </c>
+      <c r="R141" s="2" t="n">
+        <v>0.004179331306990843</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -7857,6 +8709,12 @@
       <c r="P142" s="3" t="n">
         <v>-0.001156961048977926</v>
       </c>
+      <c r="Q142" s="1" t="n">
+        <v>0.07794</v>
+      </c>
+      <c r="R142" s="2" t="n">
+        <v>0.003088803088802963</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -7909,6 +8767,12 @@
       <c r="P143" s="3" t="n">
         <v>-0.0003380281690141098</v>
       </c>
+      <c r="Q143" s="1" t="n">
+        <v>0.08859</v>
+      </c>
+      <c r="R143" s="3" t="n">
+        <v>-0.001465284039675285</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -7961,6 +8825,12 @@
       <c r="P144" s="2" t="n">
         <v>0.000983284169124837</v>
       </c>
+      <c r="Q144" s="1" t="n">
+        <v>0.02026</v>
+      </c>
+      <c r="R144" s="3" t="n">
+        <v>-0.004911591355599185</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -8013,6 +8883,12 @@
       <c r="P145" s="2" t="n">
         <v>0.0005255781359495839</v>
       </c>
+      <c r="Q145" s="1" t="n">
+        <v>0.11423</v>
+      </c>
+      <c r="R145" s="2" t="n">
+        <v>8.75503414462977e-05</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -8065,6 +8941,12 @@
       <c r="P146" s="3" t="n">
         <v>-0.01531443466927332</v>
       </c>
+      <c r="Q146" s="1" t="n">
+        <v>0.3029</v>
+      </c>
+      <c r="R146" s="2" t="n">
+        <v>0.002316346790205091</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -8117,6 +8999,12 @@
       <c r="P147" s="3" t="n">
         <v>-0.008130081300813016</v>
       </c>
+      <c r="Q147" s="1" t="n">
+        <v>0.123</v>
+      </c>
+      <c r="R147" s="2" t="n">
+        <v>0.008196721311475417</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -8169,6 +9057,12 @@
       <c r="P148" s="3" t="n">
         <v>-0.006762597244114439</v>
       </c>
+      <c r="Q148" s="1" t="n">
+        <v>1.959</v>
+      </c>
+      <c r="R148" s="2" t="n">
+        <v>0.002866796355073231</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -8221,6 +9115,12 @@
       <c r="P149" s="3" t="n">
         <v>-0.005011315874555412</v>
       </c>
+      <c r="Q149" s="1" t="n">
+        <v>0.06166</v>
+      </c>
+      <c r="R149" s="2" t="n">
+        <v>0.00178716490658</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -8273,6 +9173,12 @@
       <c r="P150" s="3" t="n">
         <v>-0.003088326127239039</v>
       </c>
+      <c r="Q150" s="1" t="n">
+        <v>0.1649</v>
+      </c>
+      <c r="R150" s="2" t="n">
+        <v>0.02168525402726148</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -8325,6 +9231,12 @@
       <c r="P151" s="3" t="n">
         <v>-0.006997171356260244</v>
       </c>
+      <c r="Q151" s="1" t="n">
+        <v>6.676e-05</v>
+      </c>
+      <c r="R151" s="2" t="n">
+        <v>0.0008995502248877001</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -8377,6 +9289,12 @@
       <c r="P152" s="3" t="n">
         <v>-0.002033898305084663</v>
       </c>
+      <c r="Q152" s="1" t="n">
+        <v>0.01477</v>
+      </c>
+      <c r="R152" s="2" t="n">
+        <v>0.003396739130434762</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -8429,6 +9347,12 @@
       <c r="P153" s="3" t="n">
         <v>-0.004289799809342221</v>
       </c>
+      <c r="Q153" s="1" t="n">
+        <v>0.02088</v>
+      </c>
+      <c r="R153" s="3" t="n">
+        <v>-0.0004786979415988317</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -8481,6 +9405,12 @@
       <c r="P154" s="3" t="n">
         <v>-0.002687269062814979</v>
       </c>
+      <c r="Q154" s="1" t="n">
+        <v>0.0005948</v>
+      </c>
+      <c r="R154" s="2" t="n">
+        <v>0.001684068710003409</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -8533,6 +9463,12 @@
       <c r="P155" s="3" t="n">
         <v>-0.003475670307845115</v>
       </c>
+      <c r="Q155" s="1" t="n">
+        <v>0.04019</v>
+      </c>
+      <c r="R155" s="2" t="n">
+        <v>0.001245640259093037</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -8585,6 +9521,12 @@
       <c r="P156" s="3" t="n">
         <v>-0.002641310089804436</v>
       </c>
+      <c r="Q156" s="1" t="n">
+        <v>0.01888</v>
+      </c>
+      <c r="R156" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -8637,6 +9579,12 @@
       <c r="P157" s="2" t="n">
         <v>0.0004597701149426696</v>
       </c>
+      <c r="Q157" s="1" t="n">
+        <v>0.08673</v>
+      </c>
+      <c r="R157" s="3" t="n">
+        <v>-0.003561580882352995</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -8689,6 +9637,12 @@
       <c r="P158" s="3" t="n">
         <v>-0.005837502978317898</v>
       </c>
+      <c r="Q158" s="1" t="n">
+        <v>0.008446</v>
+      </c>
+      <c r="R158" s="2" t="n">
+        <v>0.01210305572198926</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -8741,6 +9695,12 @@
       <c r="P159" s="3" t="n">
         <v>-0.006004803843074509</v>
       </c>
+      <c r="Q159" s="1" t="n">
+        <v>2.488</v>
+      </c>
+      <c r="R159" s="2" t="n">
+        <v>0.00201369311316951</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -8793,6 +9753,12 @@
       <c r="P160" s="3" t="n">
         <v>-0.004275165176836425</v>
       </c>
+      <c r="Q160" s="1" t="n">
+        <v>1.2795</v>
+      </c>
+      <c r="R160" s="3" t="n">
+        <v>-0.001170960187353501</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -8845,6 +9811,12 @@
       <c r="P161" s="2" t="n">
         <v>0.0001329256945367716</v>
       </c>
+      <c r="Q161" s="1" t="n">
+        <v>0.007516</v>
+      </c>
+      <c r="R161" s="3" t="n">
+        <v>-0.001063264221158984</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -8897,6 +9869,12 @@
       <c r="P162" s="2" t="n">
         <v>0.02395934172313652</v>
       </c>
+      <c r="Q162" s="1" t="n">
+        <v>0.004142</v>
+      </c>
+      <c r="R162" s="3" t="n">
+        <v>-0.02103521626093135</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -8949,6 +9927,12 @@
       <c r="P163" s="3" t="n">
         <v>-0.002079002079001995</v>
       </c>
+      <c r="Q163" s="1" t="n">
+        <v>0.09619999999999999</v>
+      </c>
+      <c r="R163" s="2" t="n">
+        <v>0.002083333333333248</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -9001,6 +9985,12 @@
       <c r="P164" s="3" t="n">
         <v>-0.003098205922616882</v>
       </c>
+      <c r="Q164" s="1" t="n">
+        <v>1.382</v>
+      </c>
+      <c r="R164" s="3" t="n">
+        <v>-0.001156403584851146</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -9053,6 +10043,12 @@
       <c r="P165" s="3" t="n">
         <v>-0.0008074798130045978</v>
       </c>
+      <c r="Q165" s="1" t="n">
+        <v>0.023474</v>
+      </c>
+      <c r="R165" s="3" t="n">
+        <v>-0.001573731444855698</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -9105,6 +10101,12 @@
       <c r="P166" s="3" t="n">
         <v>-0.01098685501275253</v>
       </c>
+      <c r="Q166" s="1" t="n">
+        <v>0.005107</v>
+      </c>
+      <c r="R166" s="2" t="n">
+        <v>0.01309264034913709</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -9157,6 +10159,12 @@
       <c r="P167" s="3" t="n">
         <v>-0.003790750568612589</v>
       </c>
+      <c r="Q167" s="1" t="n">
+        <v>0.06616</v>
+      </c>
+      <c r="R167" s="2" t="n">
+        <v>0.007001522070015253</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -9209,6 +10217,12 @@
       <c r="P168" s="2" t="n">
         <v>0.002105263157894797</v>
       </c>
+      <c r="Q168" s="1" t="n">
+        <v>0.0951</v>
+      </c>
+      <c r="R168" s="3" t="n">
+        <v>-0.001050420168067257</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -9261,6 +10275,12 @@
       <c r="P169" s="3" t="n">
         <v>-0.001308900523560065</v>
       </c>
+      <c r="Q169" s="1" t="n">
+        <v>0.0381</v>
+      </c>
+      <c r="R169" s="3" t="n">
+        <v>-0.00131061598951511</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -9313,6 +10333,12 @@
       <c r="P170" s="3" t="n">
         <v>-0.005450733752620542</v>
       </c>
+      <c r="Q170" s="1" t="n">
+        <v>0.007124</v>
+      </c>
+      <c r="R170" s="2" t="n">
+        <v>0.00112422709387299</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -9365,6 +10391,12 @@
       <c r="P171" s="3" t="n">
         <v>-0.007278020378457066</v>
       </c>
+      <c r="Q171" s="1" t="n">
+        <v>0.341</v>
+      </c>
+      <c r="R171" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -9417,6 +10449,12 @@
       <c r="P172" s="3" t="n">
         <v>-0.004930606281957658</v>
       </c>
+      <c r="Q172" s="1" t="n">
+        <v>5.449</v>
+      </c>
+      <c r="R172" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -9469,6 +10507,12 @@
       <c r="P173" s="3" t="n">
         <v>-0.009166302924487052</v>
       </c>
+      <c r="Q173" s="1" t="n">
+        <v>0.04544</v>
+      </c>
+      <c r="R173" s="2" t="n">
+        <v>0.000881057268722431</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -9521,6 +10565,12 @@
       <c r="P174" s="3" t="n">
         <v>-0.002812579902838123</v>
       </c>
+      <c r="Q174" s="1" t="n">
+        <v>0.039</v>
+      </c>
+      <c r="R174" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -9573,6 +10623,12 @@
       <c r="P175" s="3" t="n">
         <v>-0.003220611916264052</v>
       </c>
+      <c r="Q175" s="1" t="n">
+        <v>0.005598</v>
+      </c>
+      <c r="R175" s="2" t="n">
+        <v>0.004846526655896472</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -9625,6 +10681,12 @@
       <c r="P176" s="3" t="n">
         <v>-0.007884362680683219</v>
       </c>
+      <c r="Q176" s="1" t="n">
+        <v>0.00756</v>
+      </c>
+      <c r="R176" s="2" t="n">
+        <v>0.001324503311258224</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -9677,6 +10739,12 @@
       <c r="P177" s="3" t="n">
         <v>-0.00626780626780621</v>
       </c>
+      <c r="Q177" s="1" t="n">
+        <v>1.755</v>
+      </c>
+      <c r="R177" s="2" t="n">
+        <v>0.006307339449541227</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -9729,6 +10797,12 @@
       <c r="P178" s="3" t="n">
         <v>-0.004525463700681989</v>
       </c>
+      <c r="Q178" s="1" t="n">
+        <v>15.617</v>
+      </c>
+      <c r="R178" s="3" t="n">
+        <v>-6.402868485077768e-05</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -9781,6 +10855,12 @@
       <c r="P179" s="3" t="n">
         <v>-0.003215434083601289</v>
       </c>
+      <c r="Q179" s="1" t="n">
+        <v>0.311</v>
+      </c>
+      <c r="R179" s="2" t="n">
+        <v>0.003225806451612906</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -9833,6 +10913,12 @@
       <c r="P180" s="3" t="n">
         <v>-0.0003093421323984559</v>
       </c>
+      <c r="Q180" s="1" t="n">
+        <v>0.09728000000000001</v>
+      </c>
+      <c r="R180" s="2" t="n">
+        <v>0.003403816400206404</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -9885,6 +10971,12 @@
       <c r="P181" s="3" t="n">
         <v>-0.00319659030367617</v>
       </c>
+      <c r="Q181" s="1" t="n">
+        <v>0.1871</v>
+      </c>
+      <c r="R181" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -9937,6 +11029,12 @@
       <c r="P182" s="3" t="n">
         <v>-0.001009930988049109</v>
       </c>
+      <c r="Q182" s="1" t="n">
+        <v>0.0594</v>
+      </c>
+      <c r="R182" s="2" t="n">
+        <v>0.0008424599831508245</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -9989,6 +11087,12 @@
       <c r="P183" s="3" t="n">
         <v>-0.002491694352159511</v>
       </c>
+      <c r="Q183" s="1" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="R183" s="3" t="n">
+        <v>-0.0008326394671107071</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -10041,6 +11145,12 @@
       <c r="P184" s="3" t="n">
         <v>-0.006487488415199156</v>
       </c>
+      <c r="Q184" s="1" t="n">
+        <v>0.0214</v>
+      </c>
+      <c r="R184" s="3" t="n">
+        <v>-0.001865671641791131</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -10093,6 +11203,12 @@
       <c r="P185" s="3" t="n">
         <v>-0.00274725274725275</v>
       </c>
+      <c r="Q185" s="1" t="n">
+        <v>0.364</v>
+      </c>
+      <c r="R185" s="2" t="n">
+        <v>0.002754820936639121</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -10145,6 +11261,12 @@
       <c r="P186" s="3" t="n">
         <v>-0.00470158025336288</v>
       </c>
+      <c r="Q186" s="1" t="n">
+        <v>0.007652</v>
+      </c>
+      <c r="R186" s="2" t="n">
+        <v>0.00406770764991468</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -10197,6 +11319,12 @@
       <c r="P187" s="3" t="n">
         <v>-0.006289308176100553</v>
       </c>
+      <c r="Q187" s="1" t="n">
+        <v>0.2681</v>
+      </c>
+      <c r="R187" s="3" t="n">
+        <v>-0.001861504095309011</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -10249,6 +11377,12 @@
       <c r="P188" s="3" t="n">
         <v>-0.005871633933994847</v>
       </c>
+      <c r="Q188" s="1" t="n">
+        <v>0.04914</v>
+      </c>
+      <c r="R188" s="2" t="n">
+        <v>0.0008146639511202711</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -10301,6 +11435,12 @@
       <c r="P189" s="3" t="n">
         <v>-0.006220839813374768</v>
       </c>
+      <c r="Q189" s="1" t="n">
+        <v>0.2551</v>
+      </c>
+      <c r="R189" s="3" t="n">
+        <v>-0.001956181533646324</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -10353,6 +11493,12 @@
       <c r="P190" s="3" t="n">
         <v>-0.001583949313621985</v>
       </c>
+      <c r="Q190" s="1" t="n">
+        <v>0.5685</v>
+      </c>
+      <c r="R190" s="2" t="n">
+        <v>0.002115282919090391</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -10405,6 +11551,12 @@
       <c r="P191" s="3" t="n">
         <v>-0.005441055234954717</v>
       </c>
+      <c r="Q191" s="1" t="n">
+        <v>6.027</v>
+      </c>
+      <c r="R191" s="3" t="n">
+        <v>-0.0008289124668434837</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -10457,6 +11609,12 @@
       <c r="P192" s="3" t="n">
         <v>-0.0008547008547007606</v>
       </c>
+      <c r="Q192" s="1" t="n">
+        <v>0.3515</v>
+      </c>
+      <c r="R192" s="2" t="n">
+        <v>0.002281151981750691</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -10509,6 +11667,12 @@
       <c r="P193" s="3" t="n">
         <v>-0.0046728971962616</v>
       </c>
+      <c r="Q193" s="1" t="n">
+        <v>0.0639</v>
+      </c>
+      <c r="R193" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -10561,6 +11725,12 @@
       <c r="P194" s="3" t="n">
         <v>-0.008532423208190977</v>
       </c>
+      <c r="Q194" s="1" t="n">
+        <v>0.01743</v>
+      </c>
+      <c r="R194" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -10613,6 +11783,12 @@
       <c r="P195" s="3" t="n">
         <v>-0.01746674378253324</v>
       </c>
+      <c r="Q195" s="1" t="n">
+        <v>0.0008497999999999999</v>
+      </c>
+      <c r="R195" s="2" t="n">
+        <v>0.0004709206498703806</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -10665,6 +11841,12 @@
       <c r="P196" s="3" t="n">
         <v>-0.00393700787401563</v>
       </c>
+      <c r="Q196" s="1" t="n">
+        <v>0.001013</v>
+      </c>
+      <c r="R196" s="2" t="n">
+        <v>0.0009881422924900355</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -10717,6 +11899,12 @@
       <c r="P197" s="3" t="n">
         <v>-0.002470660901791289</v>
       </c>
+      <c r="Q197" s="1" t="n">
+        <v>0.0001619</v>
+      </c>
+      <c r="R197" s="2" t="n">
+        <v>0.002476780185758574</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -10769,6 +11957,12 @@
       <c r="P198" s="3" t="n">
         <v>-0.006196924489327549</v>
       </c>
+      <c r="Q198" s="1" t="n">
+        <v>4.327</v>
+      </c>
+      <c r="R198" s="3" t="n">
+        <v>-0.0006928406466512964</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -10821,6 +12015,12 @@
       <c r="P199" s="3" t="n">
         <v>-0.004273504273504311</v>
       </c>
+      <c r="Q199" s="1" t="n">
+        <v>0.1629</v>
+      </c>
+      <c r="R199" s="3" t="n">
+        <v>-0.001226241569589244</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -10873,6 +12073,12 @@
       <c r="P200" s="3" t="n">
         <v>-0.001759309680391945</v>
       </c>
+      <c r="Q200" s="1" t="n">
+        <v>0.023769</v>
+      </c>
+      <c r="R200" s="3" t="n">
+        <v>-0.002601653308715665</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -10925,6 +12131,12 @@
       <c r="P201" s="3" t="n">
         <v>-0.008652057896013596</v>
       </c>
+      <c r="Q201" s="1" t="n">
+        <v>0.12276</v>
+      </c>
+      <c r="R201" s="2" t="n">
+        <v>0.001305057096247908</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -10977,6 +12189,12 @@
       <c r="P202" s="3" t="n">
         <v>-0.002170767004341571</v>
       </c>
+      <c r="Q202" s="1" t="n">
+        <v>0.01382</v>
+      </c>
+      <c r="R202" s="2" t="n">
+        <v>0.002175489485134192</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -11029,6 +12247,12 @@
       <c r="P203" s="3" t="n">
         <v>-0.005837995621503384</v>
       </c>
+      <c r="Q203" s="1" t="n">
+        <v>0.04103</v>
+      </c>
+      <c r="R203" s="2" t="n">
+        <v>0.003914851969659907</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -11081,6 +12305,12 @@
       <c r="P204" s="3" t="n">
         <v>-0.004253673627223606</v>
       </c>
+      <c r="Q204" s="1" t="n">
+        <v>0.0258</v>
+      </c>
+      <c r="R204" s="2" t="n">
+        <v>0.00194174757281559</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -11133,6 +12363,12 @@
       <c r="P205" s="3" t="n">
         <v>-0.005983889528193305</v>
       </c>
+      <c r="Q205" s="1" t="n">
+        <v>0.432</v>
+      </c>
+      <c r="R205" s="2" t="n">
+        <v>0.0002315350775642255</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -11185,6 +12421,12 @@
       <c r="P206" s="3" t="n">
         <v>-0.003909643788010417</v>
       </c>
+      <c r="Q206" s="1" t="n">
+        <v>0.02293</v>
+      </c>
+      <c r="R206" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -11237,6 +12479,12 @@
       <c r="P207" s="3" t="n">
         <v>-0.003834172058471127</v>
       </c>
+      <c r="Q207" s="1" t="n">
+        <v>4.163</v>
+      </c>
+      <c r="R207" s="2" t="n">
+        <v>0.001443348568679391</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -11289,6 +12537,12 @@
       <c r="P208" s="3" t="n">
         <v>-0.003658040915865145</v>
       </c>
+      <c r="Q208" s="1" t="n">
+        <v>0.07367</v>
+      </c>
+      <c r="R208" s="2" t="n">
+        <v>0.001767745444656039</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -11341,6 +12595,12 @@
       <c r="P209" s="3" t="n">
         <v>-0.005434782608695676</v>
       </c>
+      <c r="Q209" s="1" t="n">
+        <v>0.04206</v>
+      </c>
+      <c r="R209" s="3" t="n">
+        <v>-0.0007127583749109586</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -11393,6 +12653,12 @@
       <c r="P210" s="3" t="n">
         <v>-0.004859611231101576</v>
       </c>
+      <c r="Q210" s="1" t="n">
+        <v>0.1851</v>
+      </c>
+      <c r="R210" s="2" t="n">
+        <v>0.00434074877916438</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -11445,6 +12711,12 @@
       <c r="P211" s="3" t="n">
         <v>-0.007544006705783722</v>
       </c>
+      <c r="Q211" s="1" t="n">
+        <v>0.2364</v>
+      </c>
+      <c r="R211" s="3" t="n">
+        <v>-0.001689189189189237</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -11497,6 +12769,12 @@
       <c r="P212" s="3" t="n">
         <v>-0.00525310410697217</v>
       </c>
+      <c r="Q212" s="1" t="n">
+        <v>0.002075</v>
+      </c>
+      <c r="R212" s="3" t="n">
+        <v>-0.003840614498319824</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -11549,6 +12827,12 @@
       <c r="P213" s="3" t="n">
         <v>-0.003208556149732623</v>
       </c>
+      <c r="Q213" s="1" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="R213" s="3" t="n">
+        <v>-0.002145922746781118</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -11601,6 +12885,12 @@
       <c r="P214" s="3" t="n">
         <v>-0.004526462395543172</v>
       </c>
+      <c r="Q214" s="1" t="n">
+        <v>0.005716</v>
+      </c>
+      <c r="R214" s="3" t="n">
+        <v>-0.0003497726477789901</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -11653,6 +12943,12 @@
       <c r="P215" s="3" t="n">
         <v>-0.004550418638514747</v>
       </c>
+      <c r="Q215" s="1" t="n">
+        <v>0.05468</v>
+      </c>
+      <c r="R215" s="3" t="n">
+        <v>-0.000182848784055642</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -11705,6 +13001,12 @@
       <c r="P216" s="3" t="n">
         <v>-0.004731861198738087</v>
       </c>
+      <c r="Q216" s="1" t="n">
+        <v>0.06320000000000001</v>
+      </c>
+      <c r="R216" s="2" t="n">
+        <v>0.001584786053882771</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -11757,6 +13059,12 @@
       <c r="P217" s="3" t="n">
         <v>-0.004305705059203419</v>
       </c>
+      <c r="Q217" s="1" t="n">
+        <v>0.0927</v>
+      </c>
+      <c r="R217" s="2" t="n">
+        <v>0.002162162162162224</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -11809,6 +13117,12 @@
       <c r="P218" s="2" t="n">
         <v>0.00232060625838511</v>
       </c>
+      <c r="Q218" s="1" t="n">
+        <v>0.27664</v>
+      </c>
+      <c r="R218" s="2" t="n">
+        <v>0.0007596859964547551</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -11861,6 +13175,12 @@
       <c r="P219" s="3" t="n">
         <v>-0.006416131989000841</v>
       </c>
+      <c r="Q219" s="1" t="n">
+        <v>0.003256</v>
+      </c>
+      <c r="R219" s="2" t="n">
+        <v>0.001230012300123031</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -11913,6 +13233,12 @@
       <c r="P220" s="2" t="n">
         <v>1.00062739340442e-06</v>
       </c>
+      <c r="Q220" s="1" t="n">
+        <v>0.999373</v>
+      </c>
+      <c r="R220" s="3" t="n">
+        <v>-1.000626392150242e-06</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -11965,6 +13291,12 @@
       <c r="P221" s="3" t="n">
         <v>-0.01388538247917197</v>
       </c>
+      <c r="Q221" s="1" t="n">
+        <v>0.03879</v>
+      </c>
+      <c r="R221" s="3" t="n">
+        <v>-0.00691244239631335</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -12017,6 +13349,12 @@
       <c r="P222" s="3" t="n">
         <v>-0.006418485237483841</v>
       </c>
+      <c r="Q222" s="1" t="n">
+        <v>0.04648</v>
+      </c>
+      <c r="R222" s="2" t="n">
+        <v>0.0008613264427217564</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -12069,6 +13407,12 @@
       <c r="P223" s="3" t="n">
         <v>-0.004739336492891</v>
       </c>
+      <c r="Q223" s="1" t="n">
+        <v>0.1054</v>
+      </c>
+      <c r="R223" s="2" t="n">
+        <v>0.003809523809523787</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -12121,6 +13465,12 @@
       <c r="P224" s="2" t="n">
         <v>0.005128205128205133</v>
       </c>
+      <c r="Q224" s="1" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="R224" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -12173,6 +13523,12 @@
       <c r="P225" s="3" t="n">
         <v>-0.005286438666522888</v>
       </c>
+      <c r="Q225" s="1" t="n">
+        <v>0.000923</v>
+      </c>
+      <c r="R225" s="2" t="n">
+        <v>0.001084598698481588</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -12225,6 +13581,12 @@
       <c r="P226" s="3" t="n">
         <v>-0.0001178550383028009</v>
       </c>
+      <c r="Q226" s="1" t="n">
+        <v>0.008492</v>
+      </c>
+      <c r="R226" s="2" t="n">
+        <v>0.0009429514380008636</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -12277,6 +13639,12 @@
       <c r="P227" s="3" t="n">
         <v>-0.001932367149758375</v>
       </c>
+      <c r="Q227" s="1" t="n">
+        <v>0.04137</v>
+      </c>
+      <c r="R227" s="2" t="n">
+        <v>0.001210067763794639</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -12329,6 +13697,12 @@
       <c r="P228" s="3" t="n">
         <v>-0.001396648044692778</v>
       </c>
+      <c r="Q228" s="1" t="n">
+        <v>0.03561</v>
+      </c>
+      <c r="R228" s="3" t="n">
+        <v>-0.003916083916083756</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -12381,6 +13755,12 @@
       <c r="P229" s="3" t="n">
         <v>-0.005232558139534872</v>
       </c>
+      <c r="Q229" s="1" t="n">
+        <v>0.05127</v>
+      </c>
+      <c r="R229" s="3" t="n">
+        <v>-0.001168907071887737</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -12433,6 +13813,12 @@
       <c r="P230" s="3" t="n">
         <v>-0.001744186046511607</v>
       </c>
+      <c r="Q230" s="1" t="n">
+        <v>0.001722</v>
+      </c>
+      <c r="R230" s="2" t="n">
+        <v>0.002912055911473508</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -12485,6 +13871,12 @@
       <c r="P231" s="3" t="n">
         <v>-0.003711340206185559</v>
       </c>
+      <c r="Q231" s="1" t="n">
+        <v>0.0487</v>
+      </c>
+      <c r="R231" s="2" t="n">
+        <v>0.007864238410595994</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -12537,6 +13929,12 @@
       <c r="P232" s="3" t="n">
         <v>-0.01005025125628147</v>
       </c>
+      <c r="Q232" s="1" t="n">
+        <v>0.02165</v>
+      </c>
+      <c r="R232" s="3" t="n">
+        <v>-0.0009229349330871798</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -12589,6 +13987,12 @@
       <c r="P233" s="3" t="n">
         <v>-0.004602011249360851</v>
       </c>
+      <c r="Q233" s="1" t="n">
+        <v>0.000584</v>
+      </c>
+      <c r="R233" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -12641,6 +14045,12 @@
       <c r="P234" s="3" t="n">
         <v>-0.005945410323394234</v>
       </c>
+      <c r="Q234" s="1" t="n">
+        <v>0.21962</v>
+      </c>
+      <c r="R234" s="3" t="n">
+        <v>-0.004893520616221104</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -12693,6 +14103,12 @@
       <c r="P235" s="2" t="n">
         <v>0.0007230657989876784</v>
       </c>
+      <c r="Q235" s="1" t="n">
+        <v>0.01392</v>
+      </c>
+      <c r="R235" s="2" t="n">
+        <v>0.005780346820809264</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -12745,6 +14161,12 @@
       <c r="P236" s="3" t="n">
         <v>-0.004830917874396106</v>
       </c>
+      <c r="Q236" s="1" t="n">
+        <v>0.0412</v>
+      </c>
+      <c r="R236" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -12797,6 +14219,12 @@
       <c r="P237" s="3" t="n">
         <v>-0.004761904761904774</v>
       </c>
+      <c r="Q237" s="1" t="n">
+        <v>0.0042</v>
+      </c>
+      <c r="R237" s="2" t="n">
+        <v>0.004784688995215324</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -12849,6 +14277,12 @@
       <c r="P238" s="3" t="n">
         <v>-0.004000000000000115</v>
       </c>
+      <c r="Q238" s="1" t="n">
+        <v>0.0249</v>
+      </c>
+      <c r="R238" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -12901,6 +14335,12 @@
       <c r="P239" s="3" t="n">
         <v>-0.002012072434607564</v>
       </c>
+      <c r="Q239" s="1" t="n">
+        <v>0.01485</v>
+      </c>
+      <c r="R239" s="3" t="n">
+        <v>-0.002016129032258099</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -12953,6 +14393,12 @@
       <c r="P240" s="3" t="n">
         <v>-0.003570517725070084</v>
       </c>
+      <c r="Q240" s="1" t="n">
+        <v>0.0003913</v>
+      </c>
+      <c r="R240" s="2" t="n">
+        <v>0.001535705144612272</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -13005,6 +14451,12 @@
       <c r="P241" s="3" t="n">
         <v>-0.000373692077727911</v>
       </c>
+      <c r="Q241" s="1" t="n">
+        <v>0.2689</v>
+      </c>
+      <c r="R241" s="2" t="n">
+        <v>0.005233644859812922</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -13057,6 +14509,12 @@
       <c r="P242" s="3" t="n">
         <v>-0.002883355176933314</v>
       </c>
+      <c r="Q242" s="1" t="n">
+        <v>0.07668999999999999</v>
+      </c>
+      <c r="R242" s="2" t="n">
+        <v>0.008017875920084115</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -13109,6 +14567,12 @@
       <c r="P243" s="3" t="n">
         <v>-0.006072874493927054</v>
       </c>
+      <c r="Q243" s="1" t="n">
+        <v>0.01973</v>
+      </c>
+      <c r="R243" s="2" t="n">
+        <v>0.004582484725050906</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -13161,6 +14625,12 @@
       <c r="P244" s="3" t="n">
         <v>-0.01187350154127183</v>
       </c>
+      <c r="Q244" s="1" t="n">
+        <v>0.08699</v>
+      </c>
+      <c r="R244" s="2" t="n">
+        <v>0.005083766608896544</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -13213,6 +14683,12 @@
       <c r="P245" s="2" t="n">
         <v>0.003793733314598898</v>
       </c>
+      <c r="Q245" s="1" t="n">
+        <v>1.4304</v>
+      </c>
+      <c r="R245" s="2" t="n">
+        <v>0.00111982082866729</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -13265,6 +14741,12 @@
       <c r="P246" s="3" t="n">
         <v>-0.003351955307262434</v>
       </c>
+      <c r="Q246" s="1" t="n">
+        <v>0.01777</v>
+      </c>
+      <c r="R246" s="3" t="n">
+        <v>-0.003923766816143532</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -13317,6 +14799,12 @@
       <c r="P247" s="3" t="n">
         <v>-0.004070556309362297</v>
       </c>
+      <c r="Q247" s="1" t="n">
+        <v>0.006604</v>
+      </c>
+      <c r="R247" s="3" t="n">
+        <v>-0.0003027550711474819</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -13369,6 +14857,12 @@
       <c r="P248" s="3" t="n">
         <v>-0.0002405580947799213</v>
       </c>
+      <c r="Q248" s="1" t="n">
+        <v>0.00417</v>
+      </c>
+      <c r="R248" s="2" t="n">
+        <v>0.003368623676612157</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -13421,6 +14915,12 @@
       <c r="P249" s="3" t="n">
         <v>-0.001819836214740599</v>
       </c>
+      <c r="Q249" s="1" t="n">
+        <v>0.1097</v>
+      </c>
+      <c r="R249" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -13473,6 +14973,12 @@
       <c r="P250" s="3" t="n">
         <v>-0.005807200929152114</v>
       </c>
+      <c r="Q250" s="1" t="n">
+        <v>0.03426</v>
+      </c>
+      <c r="R250" s="2" t="n">
+        <v>0.0005841121495326865</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -13525,6 +15031,12 @@
       <c r="P251" s="2" t="n">
         <v>0.0004630701551284831</v>
       </c>
+      <c r="Q251" s="1" t="n">
+        <v>0.04338</v>
+      </c>
+      <c r="R251" s="2" t="n">
+        <v>0.003934274473501585</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -13577,6 +15089,12 @@
       <c r="P252" s="2" t="n">
         <v>0.0178282009724473</v>
       </c>
+      <c r="Q252" s="1" t="n">
+        <v>0.006118</v>
+      </c>
+      <c r="R252" s="3" t="n">
+        <v>-0.02579617834394901</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -13629,6 +15147,12 @@
       <c r="P253" s="2" t="n">
         <v>0.002378121284185397</v>
       </c>
+      <c r="Q253" s="1" t="n">
+        <v>0.01685</v>
+      </c>
+      <c r="R253" s="3" t="n">
+        <v>-0.0005931198102016366</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -13681,6 +15205,12 @@
       <c r="P254" s="3" t="n">
         <v>-0.003062787136293903</v>
       </c>
+      <c r="Q254" s="1" t="n">
+        <v>0.1298</v>
+      </c>
+      <c r="R254" s="3" t="n">
+        <v>-0.003072196620583805</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -13733,6 +15263,12 @@
       <c r="P255" s="2" t="n">
         <v>0.003835091083413241</v>
       </c>
+      <c r="Q255" s="1" t="n">
+        <v>0.02098</v>
+      </c>
+      <c r="R255" s="2" t="n">
+        <v>0.001910219675262577</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -13785,6 +15321,12 @@
       <c r="P256" s="3" t="n">
         <v>-0.001424501424501366</v>
       </c>
+      <c r="Q256" s="1" t="n">
+        <v>0.02102</v>
+      </c>
+      <c r="R256" s="3" t="n">
+        <v>-0.0004755111745125817</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -13837,6 +15379,12 @@
       <c r="P257" s="3" t="n">
         <v>-0.002352941176470493</v>
       </c>
+      <c r="Q257" s="1" t="n">
+        <v>0.02534</v>
+      </c>
+      <c r="R257" s="3" t="n">
+        <v>-0.003930817610062869</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -13889,6 +15437,12 @@
       <c r="P258" s="2" t="n">
         <v>0.001211876388608453</v>
       </c>
+      <c r="Q258" s="1" t="n">
+        <v>0.14904</v>
+      </c>
+      <c r="R258" s="2" t="n">
+        <v>0.002219084123461751</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -13941,6 +15495,12 @@
       <c r="P259" s="3" t="n">
         <v>-0.002350636630754067</v>
       </c>
+      <c r="Q259" s="1" t="n">
+        <v>0.05092</v>
+      </c>
+      <c r="R259" s="3" t="n">
+        <v>-0.0001963479285294141</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -13993,6 +15553,12 @@
       <c r="P260" s="2" t="n">
         <v>0.0001203659123735691</v>
       </c>
+      <c r="Q260" s="1" t="n">
+        <v>0.08327</v>
+      </c>
+      <c r="R260" s="2" t="n">
+        <v>0.002166325670959196</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -14045,6 +15611,12 @@
       <c r="P261" s="2" t="n">
         <v>0.0254484772632457</v>
       </c>
+      <c r="Q261" s="1" t="n">
+        <v>0.245</v>
+      </c>
+      <c r="R261" s="3" t="n">
+        <v>-0.003254678600488182</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -14097,6 +15669,12 @@
       <c r="P262" s="3" t="n">
         <v>-0.004213483146067342</v>
       </c>
+      <c r="Q262" s="1" t="n">
+        <v>0.1425</v>
+      </c>
+      <c r="R262" s="2" t="n">
+        <v>0.004936530324400412</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -14149,6 +15727,12 @@
       <c r="P263" s="3" t="n">
         <v>-0.002068252326783783</v>
       </c>
+      <c r="Q263" s="1" t="n">
+        <v>0.07703</v>
+      </c>
+      <c r="R263" s="3" t="n">
+        <v>-0.002202072538860149</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -14201,6 +15785,12 @@
       <c r="P264" s="3" t="n">
         <v>-0.007291928589388951</v>
       </c>
+      <c r="Q264" s="1" t="n">
+        <v>0.03956</v>
+      </c>
+      <c r="R264" s="2" t="n">
+        <v>0.002026342451874284</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -14253,6 +15843,12 @@
       <c r="P265" s="3" t="n">
         <v>-0.005859374999999987</v>
       </c>
+      <c r="Q265" s="1" t="n">
+        <v>0.01532</v>
+      </c>
+      <c r="R265" s="2" t="n">
+        <v>0.003274394237066123</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -14305,6 +15901,12 @@
       <c r="P266" s="3" t="n">
         <v>-0.006377979187646834</v>
       </c>
+      <c r="Q266" s="1" t="n">
+        <v>0.005932</v>
+      </c>
+      <c r="R266" s="2" t="n">
+        <v>0.002027027027027003</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -14357,6 +15959,12 @@
       <c r="P267" s="3" t="n">
         <v>-0.002689618074233349</v>
       </c>
+      <c r="Q267" s="1" t="n">
+        <v>0.03722</v>
+      </c>
+      <c r="R267" s="2" t="n">
+        <v>0.003775620280474682</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -14409,6 +16017,12 @@
       <c r="P268" s="3" t="n">
         <v>-0.001959503592423286</v>
       </c>
+      <c r="Q268" s="1" t="n">
+        <v>0.03058</v>
+      </c>
+      <c r="R268" s="2" t="n">
+        <v>0.0006544502617800781</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -14461,6 +16075,12 @@
       <c r="P269" s="3" t="n">
         <v>-0.004380009636021203</v>
       </c>
+      <c r="Q269" s="1" t="n">
+        <v>0.22732</v>
+      </c>
+      <c r="R269" s="2" t="n">
+        <v>4.399278518315184e-05</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -14513,6 +16133,12 @@
       <c r="P270" s="3" t="n">
         <v>-0.006472491909385119</v>
       </c>
+      <c r="Q270" s="1" t="n">
+        <v>0.925</v>
+      </c>
+      <c r="R270" s="2" t="n">
+        <v>0.004343105320304021</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -14565,6 +16191,12 @@
       <c r="P271" s="3" t="n">
         <v>-0.006160954948016949</v>
       </c>
+      <c r="Q271" s="1" t="n">
+        <v>2.582</v>
+      </c>
+      <c r="R271" s="2" t="n">
+        <v>0.000387446726075122</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -14617,6 +16249,12 @@
       <c r="P272" s="3" t="n">
         <v>-0.004314994606256866</v>
       </c>
+      <c r="Q272" s="1" t="n">
+        <v>0.1847</v>
+      </c>
+      <c r="R272" s="2" t="n">
+        <v>0.0005417118093175338</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -14669,6 +16307,12 @@
       <c r="P273" s="3" t="n">
         <v>-0.003548387096774161</v>
       </c>
+      <c r="Q273" s="1" t="n">
+        <v>0.03102</v>
+      </c>
+      <c r="R273" s="2" t="n">
+        <v>0.004208481709290973</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -14721,6 +16365,12 @@
       <c r="P274" s="3" t="n">
         <v>-0.004179728317659327</v>
       </c>
+      <c r="Q274" s="1" t="n">
+        <v>0.1914</v>
+      </c>
+      <c r="R274" s="2" t="n">
+        <v>0.004197271773347299</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -14773,6 +16423,12 @@
       <c r="P275" s="3" t="n">
         <v>-0.00314960629921257</v>
       </c>
+      <c r="Q275" s="1" t="n">
+        <v>0.06905</v>
+      </c>
+      <c r="R275" s="3" t="n">
+        <v>-0.008329742926899284</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -14825,6 +16481,12 @@
       <c r="P276" s="3" t="n">
         <v>-0.002840909090909189</v>
       </c>
+      <c r="Q276" s="1" t="n">
+        <v>0.08048</v>
+      </c>
+      <c r="R276" s="3" t="n">
+        <v>-0.003096742227177013</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -14877,6 +16539,12 @@
       <c r="P277" s="2" t="n">
         <v>0.01311475409836065</v>
       </c>
+      <c r="Q277" s="1" t="n">
+        <v>0.003974</v>
+      </c>
+      <c r="R277" s="3" t="n">
+        <v>-0.01070450585013683</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -14929,6 +16597,12 @@
       <c r="P278" s="3" t="n">
         <v>-0.0006439150032195041</v>
       </c>
+      <c r="Q278" s="1" t="n">
+        <v>1.553</v>
+      </c>
+      <c r="R278" s="2" t="n">
+        <v>0.0006443298969071455</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -14981,6 +16655,12 @@
       <c r="P279" s="3" t="n">
         <v>-0.002714932126696879</v>
       </c>
+      <c r="Q279" s="1" t="n">
+        <v>0.01104</v>
+      </c>
+      <c r="R279" s="2" t="n">
+        <v>0.001814882032667803</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -15033,6 +16713,12 @@
       <c r="P280" s="2" t="n">
         <v>0.004732254047322607</v>
       </c>
+      <c r="Q280" s="1" t="n">
+        <v>0.04003</v>
+      </c>
+      <c r="R280" s="3" t="n">
+        <v>-0.007684680218145706</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -15085,6 +16771,12 @@
       <c r="P281" s="3" t="n">
         <v>-0.002148997134670482</v>
       </c>
+      <c r="Q281" s="1" t="n">
+        <v>0.08365</v>
+      </c>
+      <c r="R281" s="2" t="n">
+        <v>0.000837520938023458</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -15137,6 +16829,12 @@
       <c r="P282" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="Q282" s="1" t="n">
+        <v>0.0265</v>
+      </c>
+      <c r="R282" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -15189,6 +16887,12 @@
       <c r="P283" s="3" t="n">
         <v>-0.003920543648719401</v>
       </c>
+      <c r="Q283" s="1" t="n">
+        <v>0.07616000000000001</v>
+      </c>
+      <c r="R283" s="3" t="n">
+        <v>-0.0007871949619521205</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -15241,6 +16945,12 @@
       <c r="P284" s="3" t="n">
         <v>-0.006150061500615022</v>
       </c>
+      <c r="Q284" s="1" t="n">
+        <v>0.001617</v>
+      </c>
+      <c r="R284" s="2" t="n">
+        <v>0.0006188118811880668</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -15293,6 +17003,12 @@
       <c r="P285" s="3" t="n">
         <v>-0.002961500493583364</v>
       </c>
+      <c r="Q285" s="1" t="n">
+        <v>0.2023</v>
+      </c>
+      <c r="R285" s="2" t="n">
+        <v>0.001485148514851459</v>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -15345,6 +17061,12 @@
       <c r="P286" s="3" t="n">
         <v>-0.003194587992107424</v>
       </c>
+      <c r="Q286" s="1" t="n">
+        <v>0.10657</v>
+      </c>
+      <c r="R286" s="2" t="n">
+        <v>0.004524460363841967</v>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -15397,6 +17119,12 @@
       <c r="P287" s="3" t="n">
         <v>-0.0005780346820809014</v>
       </c>
+      <c r="Q287" s="1" t="n">
+        <v>0.01732</v>
+      </c>
+      <c r="R287" s="2" t="n">
+        <v>0.001735106998264822</v>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -15449,6 +17177,12 @@
       <c r="P288" s="3" t="n">
         <v>-0.002631578947368428</v>
       </c>
+      <c r="Q288" s="1" t="n">
+        <v>0.0151</v>
+      </c>
+      <c r="R288" s="3" t="n">
+        <v>-0.003957783641160903</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -15501,6 +17235,12 @@
       <c r="P289" s="3" t="n">
         <v>-0.001249999999999949</v>
       </c>
+      <c r="Q289" s="1" t="n">
+        <v>0.01604</v>
+      </c>
+      <c r="R289" s="2" t="n">
+        <v>0.003754693366708232</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -15553,6 +17293,12 @@
       <c r="P290" s="3" t="n">
         <v>-0.0008798944126705779</v>
       </c>
+      <c r="Q290" s="1" t="n">
+        <v>2.266</v>
+      </c>
+      <c r="R290" s="3" t="n">
+        <v>-0.002201673271686435</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -15605,6 +17351,12 @@
       <c r="P291" s="3" t="n">
         <v>-0.002270663033605815</v>
       </c>
+      <c r="Q291" s="1" t="n">
+        <v>0.4392</v>
+      </c>
+      <c r="R291" s="3" t="n">
+        <v>-0.0004551661356395846</v>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -15657,6 +17409,12 @@
       <c r="P292" s="3" t="n">
         <v>-0.001725129384703918</v>
       </c>
+      <c r="Q292" s="1" t="n">
+        <v>1.733</v>
+      </c>
+      <c r="R292" s="3" t="n">
+        <v>-0.001728110599078279</v>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -15709,6 +17467,12 @@
       <c r="P293" s="3" t="n">
         <v>-0.004343534057255636</v>
       </c>
+      <c r="Q293" s="1" t="n">
+        <v>0.05065</v>
+      </c>
+      <c r="R293" s="2" t="n">
+        <v>0.004362482649216696</v>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -15761,6 +17525,12 @@
       <c r="P294" s="3" t="n">
         <v>-0.003461296412838449</v>
       </c>
+      <c r="Q294" s="1" t="n">
+        <v>0.0635</v>
+      </c>
+      <c r="R294" s="2" t="n">
+        <v>0.002526049889485434</v>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -15813,6 +17583,12 @@
       <c r="P295" s="3" t="n">
         <v>-0.0007218479307026162</v>
       </c>
+      <c r="Q295" s="1" t="n">
+        <v>0.0004142</v>
+      </c>
+      <c r="R295" s="3" t="n">
+        <v>-0.002648687695641769</v>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -15865,6 +17641,12 @@
       <c r="P296" s="3" t="n">
         <v>-0.004313099041533596</v>
       </c>
+      <c r="Q296" s="1" t="n">
+        <v>62.32</v>
+      </c>
+      <c r="R296" s="3" t="n">
+        <v>-0.0001604363869725335</v>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -15917,6 +17699,12 @@
       <c r="P297" s="3" t="n">
         <v>-0.00407331975560079</v>
       </c>
+      <c r="Q297" s="1" t="n">
+        <v>0.0979</v>
+      </c>
+      <c r="R297" s="2" t="n">
+        <v>0.001022494887525592</v>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -15969,6 +17757,12 @@
       <c r="P298" s="3" t="n">
         <v>-0.005208333333333338</v>
       </c>
+      <c r="Q298" s="1" t="n">
+        <v>0.0956</v>
+      </c>
+      <c r="R298" s="2" t="n">
+        <v>0.001047120418848198</v>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -16021,6 +17815,12 @@
       <c r="P299" s="3" t="n">
         <v>-0.005086153207390393</v>
       </c>
+      <c r="Q299" s="1" t="n">
+        <v>0.09622</v>
+      </c>
+      <c r="R299" s="2" t="n">
+        <v>0.003860198226395361</v>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -16073,6 +17873,12 @@
       <c r="P300" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="Q300" s="1" t="n">
+        <v>0.01866</v>
+      </c>
+      <c r="R300" s="2" t="n">
+        <v>0.003225806451612959</v>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -16125,6 +17931,12 @@
       <c r="P301" s="3" t="n">
         <v>-0.005223880597014972</v>
       </c>
+      <c r="Q301" s="1" t="n">
+        <v>0.01335</v>
+      </c>
+      <c r="R301" s="2" t="n">
+        <v>0.001500375093773512</v>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -16177,6 +17989,12 @@
       <c r="P302" s="3" t="n">
         <v>-0.00457875457875459</v>
       </c>
+      <c r="Q302" s="1" t="n">
+        <v>0.004345</v>
+      </c>
+      <c r="R302" s="3" t="n">
+        <v>-0.0006899724011040474</v>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -16229,6 +18047,12 @@
       <c r="P303" s="3" t="n">
         <v>-0.003208556149732675</v>
       </c>
+      <c r="Q303" s="1" t="n">
+        <v>0.00928</v>
+      </c>
+      <c r="R303" s="3" t="n">
+        <v>-0.004291845493562243</v>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -16281,6 +18105,12 @@
       <c r="P304" s="3" t="n">
         <v>-0.004223864836325334</v>
       </c>
+      <c r="Q304" s="1" t="n">
+        <v>4.719</v>
+      </c>
+      <c r="R304" s="2" t="n">
+        <v>0.000848356309650148</v>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -16333,6 +18163,12 @@
       <c r="P305" s="3" t="n">
         <v>-0.007169811320754687</v>
       </c>
+      <c r="Q305" s="1" t="n">
+        <v>0.05261</v>
+      </c>
+      <c r="R305" s="3" t="n">
+        <v>-0.0001900418091980818</v>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -16385,6 +18221,12 @@
       <c r="P306" s="3" t="n">
         <v>-0.003595890410958936</v>
       </c>
+      <c r="Q306" s="1" t="n">
+        <v>0.05818</v>
+      </c>
+      <c r="R306" s="3" t="n">
+        <v>-0.0001718508334764757</v>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -16437,6 +18279,12 @@
       <c r="P307" s="3" t="n">
         <v>-0.005131128848346704</v>
       </c>
+      <c r="Q307" s="1" t="n">
+        <v>0.1743</v>
+      </c>
+      <c r="R307" s="3" t="n">
+        <v>-0.001146131805157467</v>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -16489,6 +18337,12 @@
       <c r="P308" s="2" t="n">
         <v>0.002222222222222202</v>
       </c>
+      <c r="Q308" s="1" t="n">
+        <v>0.0501</v>
+      </c>
+      <c r="R308" s="2" t="n">
+        <v>0.00987704091916947</v>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -16541,6 +18395,12 @@
       <c r="P309" s="3" t="n">
         <v>-0.003314306757503266</v>
       </c>
+      <c r="Q309" s="1" t="n">
+        <v>0.5424</v>
+      </c>
+      <c r="R309" s="2" t="n">
+        <v>0.002032144836504692</v>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -16593,6 +18453,12 @@
       <c r="P310" s="3" t="n">
         <v>-0.008163265306122471</v>
       </c>
+      <c r="Q310" s="1" t="n">
+        <v>0.00244</v>
+      </c>
+      <c r="R310" s="2" t="n">
+        <v>0.00411522633744857</v>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -16645,6 +18511,12 @@
       <c r="P311" s="3" t="n">
         <v>-0.003247211633488747</v>
       </c>
+      <c r="Q311" s="1" t="n">
+        <v>0.07062</v>
+      </c>
+      <c r="R311" s="2" t="n">
+        <v>0.0002832861189802567</v>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -16697,6 +18569,12 @@
       <c r="P312" s="3" t="n">
         <v>-0.005978080371969471</v>
       </c>
+      <c r="Q312" s="1" t="n">
+        <v>0.008970000000000001</v>
+      </c>
+      <c r="R312" s="3" t="n">
+        <v>-0.001002338790511036</v>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -16749,6 +18627,12 @@
       <c r="P313" s="2" t="n">
         <v>0.001990379830817835</v>
       </c>
+      <c r="Q313" s="1" t="n">
+        <v>0.012036</v>
+      </c>
+      <c r="R313" s="3" t="n">
+        <v>-0.003807316669425666</v>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -16801,6 +18685,12 @@
       <c r="P314" s="3" t="n">
         <v>-0.00342612419700215</v>
       </c>
+      <c r="Q314" s="1" t="n">
+        <v>0.02323</v>
+      </c>
+      <c r="R314" s="3" t="n">
+        <v>-0.001718951439621761</v>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -16853,6 +18743,12 @@
       <c r="P315" s="3" t="n">
         <v>-0.001406469760900083</v>
       </c>
+      <c r="Q315" s="1" t="n">
+        <v>0.0071</v>
+      </c>
+      <c r="R315" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -16905,6 +18801,12 @@
       <c r="P316" s="3" t="n">
         <v>-0.005731753916698515</v>
       </c>
+      <c r="Q316" s="1" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="R316" s="3" t="n">
+        <v>-0.0007686395080706303</v>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -16957,6 +18859,12 @@
       <c r="P317" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="Q317" s="1" t="n">
+        <v>1.11e-05</v>
+      </c>
+      <c r="R317" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -17009,6 +18917,12 @@
       <c r="P318" s="3" t="n">
         <v>-0.0009511128019783419</v>
       </c>
+      <c r="Q318" s="1" t="n">
+        <v>0.052478</v>
+      </c>
+      <c r="R318" s="3" t="n">
+        <v>-0.0007996953541508068</v>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -17061,6 +18975,12 @@
       <c r="P319" s="3" t="n">
         <v>-0.0002617115938236865</v>
       </c>
+      <c r="Q319" s="1" t="n">
+        <v>0.03816</v>
+      </c>
+      <c r="R319" s="3" t="n">
+        <v>-0.001047120418848125</v>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -17113,6 +19033,12 @@
       <c r="P320" s="3" t="n">
         <v>-0.005128956623681171</v>
       </c>
+      <c r="Q320" s="1" t="n">
+        <v>0.006789</v>
+      </c>
+      <c r="R320" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -17165,6 +19091,12 @@
       <c r="P321" s="3" t="n">
         <v>-0.006164685160722057</v>
       </c>
+      <c r="Q321" s="1" t="n">
+        <v>4.524</v>
+      </c>
+      <c r="R321" s="2" t="n">
+        <v>0.002215330084182496</v>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -17217,6 +19149,12 @@
       <c r="P322" s="3" t="n">
         <v>-0.005200208008320337</v>
       </c>
+      <c r="Q322" s="1" t="n">
+        <v>1.924</v>
+      </c>
+      <c r="R322" s="2" t="n">
+        <v>0.005750130684788237</v>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -17269,6 +19207,12 @@
       <c r="P323" s="3" t="n">
         <v>-0.00240588734786308</v>
       </c>
+      <c r="Q323" s="1" t="n">
+        <v>0.007065</v>
+      </c>
+      <c r="R323" s="2" t="n">
+        <v>0.002269825507164192</v>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -17321,6 +19265,12 @@
       <c r="P324" s="3" t="n">
         <v>-0.00325732899022788</v>
       </c>
+      <c r="Q324" s="1" t="n">
+        <v>0.01841</v>
+      </c>
+      <c r="R324" s="2" t="n">
+        <v>0.002723311546840847</v>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -17373,6 +19323,12 @@
       <c r="P325" s="3" t="n">
         <v>-0.00754257907542577</v>
       </c>
+      <c r="Q325" s="1" t="n">
+        <v>0.409</v>
+      </c>
+      <c r="R325" s="2" t="n">
+        <v>0.002696739396910983</v>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -17425,6 +19381,12 @@
       <c r="P326" s="3" t="n">
         <v>-0.008160442600276627</v>
       </c>
+      <c r="Q326" s="1" t="n">
+        <v>0.007186</v>
+      </c>
+      <c r="R326" s="2" t="n">
+        <v>0.002091758471621725</v>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -17477,6 +19439,12 @@
       <c r="P327" s="3" t="n">
         <v>-0.00529661016949153</v>
       </c>
+      <c r="Q327" s="1" t="n">
+        <v>0.1893</v>
+      </c>
+      <c r="R327" s="2" t="n">
+        <v>0.007987220447284352</v>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -17529,6 +19497,12 @@
       <c r="P328" s="3" t="n">
         <v>-0.008680923142070703</v>
       </c>
+      <c r="Q328" s="1" t="n">
+        <v>0.4615</v>
+      </c>
+      <c r="R328" s="3" t="n">
+        <v>-0.01431012387868429</v>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -17581,6 +19555,12 @@
       <c r="P329" s="3" t="n">
         <v>-0.004434589800443534</v>
       </c>
+      <c r="Q329" s="1" t="n">
+        <v>0.01345</v>
+      </c>
+      <c r="R329" s="3" t="n">
+        <v>-0.001484780994803206</v>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -17633,6 +19613,12 @@
       <c r="P330" s="3" t="n">
         <v>-0.006145741878841143</v>
       </c>
+      <c r="Q330" s="1" t="n">
+        <v>0.1132</v>
+      </c>
+      <c r="R330" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -17685,6 +19671,12 @@
       <c r="P331" s="3" t="n">
         <v>-0.005114667546609457</v>
       </c>
+      <c r="Q331" s="1" t="n">
+        <v>0.603</v>
+      </c>
+      <c r="R331" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -17737,6 +19729,12 @@
       <c r="P332" s="2" t="n">
         <v>0.01061718594959314</v>
       </c>
+      <c r="Q332" s="1" t="n">
+        <v>0.30628</v>
+      </c>
+      <c r="R332" s="2" t="n">
+        <v>0.002389134347897262</v>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -17789,6 +19787,12 @@
       <c r="P333" s="3" t="n">
         <v>-0.007790368271954603</v>
       </c>
+      <c r="Q333" s="1" t="n">
+        <v>0.07026</v>
+      </c>
+      <c r="R333" s="2" t="n">
+        <v>0.0029978586723769</v>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -17841,6 +19845,12 @@
       <c r="P334" s="3" t="n">
         <v>-0.02070125501358525</v>
       </c>
+      <c r="Q334" s="1" t="n">
+        <v>0.15071</v>
+      </c>
+      <c r="R334" s="3" t="n">
+        <v>-0.004425947945567289</v>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -17893,6 +19903,12 @@
       <c r="P335" s="3" t="n">
         <v>-0.003831417624521005</v>
       </c>
+      <c r="Q335" s="1" t="n">
+        <v>0.1562</v>
+      </c>
+      <c r="R335" s="2" t="n">
+        <v>0.001282051282051319</v>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -17945,6 +19961,12 @@
       <c r="P336" s="3" t="n">
         <v>-0.006296508299942701</v>
       </c>
+      <c r="Q336" s="1" t="n">
+        <v>0.1741</v>
+      </c>
+      <c r="R336" s="2" t="n">
+        <v>0.002880184331797237</v>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -17997,6 +20019,12 @@
       <c r="P337" s="2" t="n">
         <v>0.0002495009980040684</v>
       </c>
+      <c r="Q337" s="1" t="n">
+        <v>0.04021</v>
+      </c>
+      <c r="R337" s="2" t="n">
+        <v>0.00299326515340489</v>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -18049,6 +20077,12 @@
       <c r="P338" s="3" t="n">
         <v>-0.003212396069538861</v>
       </c>
+      <c r="Q338" s="1" t="n">
+        <v>0.005278</v>
+      </c>
+      <c r="R338" s="2" t="n">
+        <v>0.0005687203791468305</v>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -18101,6 +20135,12 @@
       <c r="P339" s="3" t="n">
         <v>-0.008695652173913025</v>
       </c>
+      <c r="Q339" s="1" t="n">
+        <v>0.05137</v>
+      </c>
+      <c r="R339" s="2" t="n">
+        <v>0.001364522417154008</v>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -18153,6 +20193,12 @@
       <c r="P340" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="Q340" s="1" t="n">
+        <v>0.15121</v>
+      </c>
+      <c r="R340" s="3" t="n">
+        <v>-0.002177642866569862</v>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -18205,6 +20251,12 @@
       <c r="P341" s="3" t="n">
         <v>-0.0005259697567390464</v>
       </c>
+      <c r="Q341" s="1" t="n">
+        <v>7.588</v>
+      </c>
+      <c r="R341" s="3" t="n">
+        <v>-0.001710301276147862</v>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -18257,6 +20309,12 @@
       <c r="P342" s="3" t="n">
         <v>-0.000911023382933395</v>
       </c>
+      <c r="Q342" s="1" t="n">
+        <v>0.3283</v>
+      </c>
+      <c r="R342" s="3" t="n">
+        <v>-0.002127659574468188</v>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -18309,6 +20367,12 @@
       <c r="P343" s="3" t="n">
         <v>-0.005541561712846296</v>
       </c>
+      <c r="Q343" s="1" t="n">
+        <v>0.01979</v>
+      </c>
+      <c r="R343" s="2" t="n">
+        <v>0.002532928064842855</v>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -18361,6 +20425,12 @@
       <c r="P344" s="3" t="n">
         <v>-0.014505893019039</v>
       </c>
+      <c r="Q344" s="1" t="n">
+        <v>2.177</v>
+      </c>
+      <c r="R344" s="2" t="n">
+        <v>0.001379944802207964</v>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -18413,6 +20483,12 @@
       <c r="P345" s="3" t="n">
         <v>-0.006284367635506683</v>
       </c>
+      <c r="Q345" s="1" t="n">
+        <v>1.264</v>
+      </c>
+      <c r="R345" s="3" t="n">
+        <v>-0.0007905138339920079</v>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -18465,6 +20541,12 @@
       <c r="P346" s="3" t="n">
         <v>-0.00444015444015436</v>
       </c>
+      <c r="Q346" s="1" t="n">
+        <v>0.005152</v>
+      </c>
+      <c r="R346" s="3" t="n">
+        <v>-0.0009695559433778934</v>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -18517,6 +20599,12 @@
       <c r="P347" s="3" t="n">
         <v>-0.004535938590369911</v>
       </c>
+      <c r="Q347" s="1" t="n">
+        <v>0.05702</v>
+      </c>
+      <c r="R347" s="3" t="n">
+        <v>-0.0007010164738871078</v>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -18569,6 +20657,12 @@
       <c r="P348" s="3" t="n">
         <v>-0.001571091908876714</v>
       </c>
+      <c r="Q348" s="1" t="n">
+        <v>0.1271</v>
+      </c>
+      <c r="R348" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -18621,6 +20715,12 @@
       <c r="P349" s="3" t="n">
         <v>-0.0008634253041175793</v>
       </c>
+      <c r="Q349" s="1" t="n">
+        <v>5204.4</v>
+      </c>
+      <c r="R349" s="3" t="n">
+        <v>-0.0005569104910415274</v>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -18673,6 +20773,12 @@
       <c r="P350" s="3" t="n">
         <v>-0.002478753541076509</v>
       </c>
+      <c r="Q350" s="1" t="n">
+        <v>0.02804</v>
+      </c>
+      <c r="R350" s="3" t="n">
+        <v>-0.004614838480653236</v>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -18725,6 +20831,12 @@
       <c r="P351" s="2" t="n">
         <v>0.003623188405797111</v>
       </c>
+      <c r="Q351" s="1" t="n">
+        <v>0.001387</v>
+      </c>
+      <c r="R351" s="2" t="n">
+        <v>0.001444043321299674</v>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -18777,6 +20889,12 @@
       <c r="P352" s="3" t="n">
         <v>-0.006301197227473182</v>
       </c>
+      <c r="Q352" s="1" t="n">
+        <v>0.01568</v>
+      </c>
+      <c r="R352" s="3" t="n">
+        <v>-0.005707038681039937</v>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -18829,6 +20947,12 @@
       <c r="P353" s="3" t="n">
         <v>-0.008883248730964475</v>
       </c>
+      <c r="Q353" s="1" t="n">
+        <v>6.251</v>
+      </c>
+      <c r="R353" s="2" t="n">
+        <v>0.0004801536491677519</v>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -18881,6 +21005,12 @@
       <c r="P354" s="3" t="n">
         <v>-0.0006973500697349302</v>
       </c>
+      <c r="Q354" s="1" t="n">
+        <v>0.2868</v>
+      </c>
+      <c r="R354" s="2" t="n">
+        <v>0.0006978367062106698</v>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -18933,6 +21063,12 @@
       <c r="P355" s="3" t="n">
         <v>-0.00433630450493856</v>
       </c>
+      <c r="Q355" s="1" t="n">
+        <v>0.04142</v>
+      </c>
+      <c r="R355" s="2" t="n">
+        <v>0.002177594967336071</v>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -18985,6 +21121,12 @@
       <c r="P356" s="3" t="n">
         <v>-0.005411066503752797</v>
       </c>
+      <c r="Q356" s="1" t="n">
+        <v>0.114</v>
+      </c>
+      <c r="R356" s="2" t="n">
+        <v>0.0003510003510003367</v>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -19037,6 +21179,12 @@
       <c r="P357" s="2" t="n">
         <v>0.0003840245775730156</v>
       </c>
+      <c r="Q357" s="1" t="n">
+        <v>0.005257</v>
+      </c>
+      <c r="R357" s="2" t="n">
+        <v>0.009021113243762027</v>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -19089,6 +21237,12 @@
       <c r="P358" s="3" t="n">
         <v>-0.005364806866952794</v>
       </c>
+      <c r="Q358" s="1" t="n">
+        <v>0.1852</v>
+      </c>
+      <c r="R358" s="3" t="n">
+        <v>-0.001078748651564216</v>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -19141,6 +21295,12 @@
       <c r="P359" s="2" t="n">
         <v>0.001230769230769266</v>
       </c>
+      <c r="Q359" s="1" t="n">
+        <v>0.1627</v>
+      </c>
+      <c r="R359" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -19193,6 +21353,12 @@
       <c r="P360" s="2" t="n">
         <v>0.004732607666824391</v>
       </c>
+      <c r="Q360" s="1" t="n">
+        <v>0.0849</v>
+      </c>
+      <c r="R360" s="3" t="n">
+        <v>-0.0002355157795571391</v>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -19245,6 +21411,12 @@
       <c r="P361" s="3" t="n">
         <v>-0.03003754693366716</v>
       </c>
+      <c r="Q361" s="1" t="n">
+        <v>0.00766</v>
+      </c>
+      <c r="R361" s="3" t="n">
+        <v>-0.01161290322580643</v>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -19297,6 +21469,12 @@
       <c r="P362" s="3" t="n">
         <v>-0.001644350481559864</v>
       </c>
+      <c r="Q362" s="1" t="n">
+        <v>0.424</v>
+      </c>
+      <c r="R362" s="3" t="n">
+        <v>-0.00235294117647059</v>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -19349,6 +21527,12 @@
       <c r="P363" s="3" t="n">
         <v>-0.005265929436545555</v>
       </c>
+      <c r="Q363" s="1" t="n">
+        <v>3.768</v>
+      </c>
+      <c r="R363" s="3" t="n">
+        <v>-0.002646903123345747</v>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -19401,6 +21585,12 @@
       <c r="P364" s="2" t="n">
         <v>0.0009124087591242088</v>
       </c>
+      <c r="Q364" s="1" t="n">
+        <v>0.01097</v>
+      </c>
+      <c r="R364" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -19453,6 +21643,12 @@
       <c r="P365" s="3" t="n">
         <v>-0.003452662184263178</v>
       </c>
+      <c r="Q365" s="1" t="n">
+        <v>0.05496</v>
+      </c>
+      <c r="R365" s="2" t="n">
+        <v>0.002188183807439862</v>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -19505,6 +21701,12 @@
       <c r="P366" s="2" t="n">
         <v>0.003106968486462368</v>
       </c>
+      <c r="Q366" s="1" t="n">
+        <v>0.02285</v>
+      </c>
+      <c r="R366" s="2" t="n">
+        <v>0.01106194690265488</v>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -19557,6 +21759,12 @@
       <c r="P367" s="3" t="n">
         <v>-0.005856515373352839</v>
       </c>
+      <c r="Q367" s="1" t="n">
+        <v>0.001368</v>
+      </c>
+      <c r="R367" s="2" t="n">
+        <v>0.007363770250368207</v>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -19609,6 +21817,12 @@
       <c r="P368" s="3" t="n">
         <v>-0.006273963053328576</v>
       </c>
+      <c r="Q368" s="1" t="n">
+        <v>0.2855</v>
+      </c>
+      <c r="R368" s="2" t="n">
+        <v>0.001403016485443549</v>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -19661,6 +21875,12 @@
       <c r="P369" s="2" t="n">
         <v>0.002693965517241456</v>
       </c>
+      <c r="Q369" s="1" t="n">
+        <v>0.01849</v>
+      </c>
+      <c r="R369" s="3" t="n">
+        <v>-0.00644814615797969</v>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -19713,6 +21933,12 @@
       <c r="P370" s="3" t="n">
         <v>-0.001613797972666231</v>
       </c>
+      <c r="Q370" s="1" t="n">
+        <v>0.19806</v>
+      </c>
+      <c r="R370" s="2" t="n">
+        <v>0.0004546143355054136</v>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -19765,6 +21991,12 @@
       <c r="P371" s="3" t="n">
         <v>-0.01315789473684212</v>
       </c>
+      <c r="Q371" s="1" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="R371" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -19817,6 +22049,12 @@
       <c r="P372" s="3" t="n">
         <v>-0.003787878787878765</v>
       </c>
+      <c r="Q372" s="1" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="R372" s="3" t="n">
+        <v>-0.001901140684410701</v>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -19869,6 +22107,12 @@
       <c r="P373" s="3" t="n">
         <v>-0.005398110661268544</v>
       </c>
+      <c r="Q373" s="1" t="n">
+        <v>0.06622</v>
+      </c>
+      <c r="R373" s="3" t="n">
+        <v>-0.001658374792703136</v>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -19921,6 +22165,12 @@
       <c r="P374" s="2" t="n">
         <v>0.0002632964718271982</v>
       </c>
+      <c r="Q374" s="1" t="n">
+        <v>0.007611</v>
+      </c>
+      <c r="R374" s="2" t="n">
+        <v>0.00171097657278231</v>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -19973,6 +22223,12 @@
       <c r="P375" s="3" t="n">
         <v>-0.005015673981191193</v>
       </c>
+      <c r="Q375" s="1" t="n">
+        <v>0.1587</v>
+      </c>
+      <c r="R375" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -20025,6 +22281,12 @@
       <c r="P376" s="3" t="n">
         <v>-0.009898107714701652</v>
       </c>
+      <c r="Q376" s="1" t="n">
+        <v>0.00342</v>
+      </c>
+      <c r="R376" s="2" t="n">
+        <v>0.005586592178770926</v>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -20077,6 +22339,12 @@
       <c r="P377" s="2" t="n">
         <v>0.006211180124223565</v>
       </c>
+      <c r="Q377" s="1" t="n">
+        <v>0.0162</v>
+      </c>
+      <c r="R377" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -20129,6 +22397,12 @@
       <c r="P378" s="3" t="n">
         <v>-0.006233303650935051</v>
       </c>
+      <c r="Q378" s="1" t="n">
+        <v>0.01136</v>
+      </c>
+      <c r="R378" s="2" t="n">
+        <v>0.01792114695340507</v>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -20181,6 +22455,12 @@
       <c r="P379" s="3" t="n">
         <v>-0.01018990273274671</v>
       </c>
+      <c r="Q379" s="1" t="n">
+        <v>0.02143</v>
+      </c>
+      <c r="R379" s="2" t="n">
+        <v>0.002807674309780113</v>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -20233,6 +22513,12 @@
       <c r="P380" s="3" t="n">
         <v>-0.007407407407407473</v>
       </c>
+      <c r="Q380" s="1" t="n">
+        <v>0.01882</v>
+      </c>
+      <c r="R380" s="2" t="n">
+        <v>0.003198294243070417</v>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -20285,6 +22571,12 @@
       <c r="P381" s="3" t="n">
         <v>-0.002493765586034984</v>
       </c>
+      <c r="Q381" s="1" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="R381" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -20337,6 +22629,12 @@
       <c r="P382" s="2" t="n">
         <v>0.003428179636612938</v>
       </c>
+      <c r="Q382" s="1" t="n">
+        <v>0.02917</v>
+      </c>
+      <c r="R382" s="3" t="n">
+        <v>-0.00341646737273657</v>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -20389,6 +22687,12 @@
       <c r="P383" s="3" t="n">
         <v>-0.001684017146356357</v>
       </c>
+      <c r="Q383" s="1" t="n">
+        <v>0.006529</v>
+      </c>
+      <c r="R383" s="2" t="n">
+        <v>0.001226805704646556</v>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -20441,6 +22745,12 @@
       <c r="P384" s="2" t="n">
         <v>0.0009573958831978294</v>
       </c>
+      <c r="Q384" s="1" t="n">
+        <v>0.0209</v>
+      </c>
+      <c r="R384" s="3" t="n">
+        <v>-0.0004782400765185586</v>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -20493,6 +22803,12 @@
       <c r="P385" s="3" t="n">
         <v>-0.004335829720141899</v>
       </c>
+      <c r="Q385" s="1" t="n">
+        <v>2531</v>
+      </c>
+      <c r="R385" s="2" t="n">
+        <v>0.001979414093428345</v>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -20545,6 +22861,12 @@
       <c r="P386" s="3" t="n">
         <v>-0.002027369488089262</v>
       </c>
+      <c r="Q386" s="1" t="n">
+        <v>0.1975</v>
+      </c>
+      <c r="R386" s="2" t="n">
+        <v>0.003047232097511514</v>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -20597,6 +22919,12 @@
       <c r="P387" s="3" t="n">
         <v>-0.003404155417302484</v>
       </c>
+      <c r="Q387" s="1" t="n">
+        <v>0.08484</v>
+      </c>
+      <c r="R387" s="3" t="n">
+        <v>-0.0007067137809187808</v>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -20649,6 +22977,12 @@
       <c r="P388" s="3" t="n">
         <v>-0.003582802547770658</v>
       </c>
+      <c r="Q388" s="1" t="n">
+        <v>0.005009</v>
+      </c>
+      <c r="R388" s="2" t="n">
+        <v>0.0005992808629645222</v>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -20701,6 +23035,12 @@
       <c r="P389" s="3" t="n">
         <v>-0.00400712377560106</v>
       </c>
+      <c r="Q389" s="1" t="n">
+        <v>0.02249</v>
+      </c>
+      <c r="R389" s="2" t="n">
+        <v>0.005364327223960598</v>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -20753,6 +23093,12 @@
       <c r="P390" s="3" t="n">
         <v>-0.002775024777006852</v>
       </c>
+      <c r="Q390" s="1" t="n">
+        <v>0.5028</v>
+      </c>
+      <c r="R390" s="3" t="n">
+        <v>-0.0005963029218842516</v>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -20805,6 +23151,12 @@
       <c r="P391" s="3" t="n">
         <v>-0.002982107355864883</v>
       </c>
+      <c r="Q391" s="1" t="n">
+        <v>0.0006038</v>
+      </c>
+      <c r="R391" s="2" t="n">
+        <v>0.003323363243602607</v>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -20857,6 +23209,12 @@
       <c r="P392" s="3" t="n">
         <v>-0.003071148268213609</v>
       </c>
+      <c r="Q392" s="1" t="n">
+        <v>0.05846</v>
+      </c>
+      <c r="R392" s="2" t="n">
+        <v>0.000513434879342723</v>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -20909,6 +23267,12 @@
       <c r="P393" s="3" t="n">
         <v>-0.002242152466367674</v>
       </c>
+      <c r="Q393" s="1" t="n">
+        <v>0.2674</v>
+      </c>
+      <c r="R393" s="2" t="n">
+        <v>0.001498127340824013</v>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -20961,6 +23325,12 @@
       <c r="P394" s="3" t="n">
         <v>-0.001371951219512113</v>
       </c>
+      <c r="Q394" s="1" t="n">
+        <v>0.006543</v>
+      </c>
+      <c r="R394" s="3" t="n">
+        <v>-0.001221187604945839</v>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -21013,6 +23383,12 @@
       <c r="P395" s="3" t="n">
         <v>-0.002601908065914958</v>
       </c>
+      <c r="Q395" s="1" t="n">
+        <v>0.1147</v>
+      </c>
+      <c r="R395" s="3" t="n">
+        <v>-0.002608695652173988</v>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -21065,6 +23441,12 @@
       <c r="P396" s="3" t="n">
         <v>-0.001944264419961036</v>
       </c>
+      <c r="Q396" s="1" t="n">
+        <v>0.03083</v>
+      </c>
+      <c r="R396" s="2" t="n">
+        <v>0.0009740259740259343</v>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -21117,6 +23499,12 @@
       <c r="P397" s="3" t="n">
         <v>-0.004641909814323465</v>
       </c>
+      <c r="Q397" s="1" t="n">
+        <v>0.1507</v>
+      </c>
+      <c r="R397" s="2" t="n">
+        <v>0.003997335109926644</v>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -21169,6 +23557,12 @@
       <c r="P398" s="3" t="n">
         <v>-0.0009060706735125232</v>
       </c>
+      <c r="Q398" s="1" t="n">
+        <v>0.003305</v>
+      </c>
+      <c r="R398" s="3" t="n">
+        <v>-0.0009068923821039795</v>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -21221,6 +23615,12 @@
       <c r="P399" s="3" t="n">
         <v>-0.0005336179295624115</v>
       </c>
+      <c r="Q399" s="1" t="n">
+        <v>0.01861</v>
+      </c>
+      <c r="R399" s="3" t="n">
+        <v>-0.006406833956219892</v>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -21273,6 +23673,12 @@
       <c r="P400" s="2" t="n">
         <v>0.001843448667044809</v>
       </c>
+      <c r="Q400" s="1" t="n">
+        <v>0.007092</v>
+      </c>
+      <c r="R400" s="2" t="n">
+        <v>0.00382165605095543</v>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -21325,6 +23731,12 @@
       <c r="P401" s="3" t="n">
         <v>-0.001851324409000284</v>
       </c>
+      <c r="Q401" s="1" t="n">
+        <v>0.007001</v>
+      </c>
+      <c r="R401" s="3" t="n">
+        <v>-0.001141389641888904</v>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -21377,6 +23789,12 @@
       <c r="P402" s="3" t="n">
         <v>-0.0008717310087173177</v>
       </c>
+      <c r="Q402" s="1" t="n">
+        <v>0.008036</v>
+      </c>
+      <c r="R402" s="2" t="n">
+        <v>0.001620341518135251</v>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -21429,6 +23847,12 @@
       <c r="P403" s="3" t="n">
         <v>-0.009148200853832059</v>
       </c>
+      <c r="Q403" s="1" t="n">
+        <v>0.04868</v>
+      </c>
+      <c r="R403" s="3" t="n">
+        <v>-0.001231021748050832</v>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -21481,6 +23905,12 @@
       <c r="P404" s="3" t="n">
         <v>-0.002076773631674179</v>
       </c>
+      <c r="Q404" s="1" t="n">
+        <v>0.14743</v>
+      </c>
+      <c r="R404" s="3" t="n">
+        <v>-0.01027121374865738</v>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -21533,6 +23963,12 @@
       <c r="P405" s="3" t="n">
         <v>-0.006465019625952493</v>
       </c>
+      <c r="Q405" s="1" t="n">
+        <v>0.04299</v>
+      </c>
+      <c r="R405" s="3" t="n">
+        <v>-0.0009295840111549703</v>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -21585,6 +24021,12 @@
       <c r="P406" s="3" t="n">
         <v>-0.005622657226155843</v>
       </c>
+      <c r="Q406" s="1" t="n">
+        <v>0.4785</v>
+      </c>
+      <c r="R406" s="2" t="n">
+        <v>0.002094240837696337</v>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -21637,6 +24079,12 @@
       <c r="P407" s="3" t="n">
         <v>-0.001222493887530592</v>
       </c>
+      <c r="Q407" s="1" t="n">
+        <v>0.0004922</v>
+      </c>
+      <c r="R407" s="2" t="n">
+        <v>0.004079967360261217</v>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -21689,6 +24137,12 @@
       <c r="P408" s="3" t="n">
         <v>-0.002433090024330942</v>
       </c>
+      <c r="Q408" s="1" t="n">
+        <v>0.01231</v>
+      </c>
+      <c r="R408" s="2" t="n">
+        <v>0.0008130081300812676</v>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -21741,6 +24195,12 @@
       <c r="P409" s="3" t="n">
         <v>-0.0003139717425431365</v>
       </c>
+      <c r="Q409" s="1" t="n">
+        <v>0.3181</v>
+      </c>
+      <c r="R409" s="3" t="n">
+        <v>-0.0009422110552764525</v>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -21793,6 +24253,12 @@
       <c r="P410" s="3" t="n">
         <v>-0.002873563218390687</v>
       </c>
+      <c r="Q410" s="1" t="n">
+        <v>0.04162</v>
+      </c>
+      <c r="R410" s="3" t="n">
+        <v>-0.0004803073967340567</v>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -21845,6 +24311,12 @@
       <c r="P411" s="3" t="n">
         <v>-0.005369127516778538</v>
       </c>
+      <c r="Q411" s="1" t="n">
+        <v>0.02965</v>
+      </c>
+      <c r="R411" s="2" t="n">
+        <v>0.000337381916329271</v>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
@@ -21897,6 +24369,12 @@
       <c r="P412" s="3" t="n">
         <v>-0.003271537622682528</v>
       </c>
+      <c r="Q412" s="1" t="n">
+        <v>0.004576</v>
+      </c>
+      <c r="R412" s="2" t="n">
+        <v>0.001312910284463879</v>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -21949,6 +24427,12 @@
       <c r="P413" s="3" t="n">
         <v>-0.005557761016276349</v>
       </c>
+      <c r="Q413" s="1" t="n">
+        <v>0.2508</v>
+      </c>
+      <c r="R413" s="2" t="n">
+        <v>0.001197604790419251</v>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -22001,6 +24485,12 @@
       <c r="P414" s="3" t="n">
         <v>-0.002341920374707175</v>
       </c>
+      <c r="Q414" s="1" t="n">
+        <v>1.277</v>
+      </c>
+      <c r="R414" s="3" t="n">
+        <v>-0.0007824726134586165</v>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -22053,6 +24543,12 @@
       <c r="P415" s="3" t="n">
         <v>-0.008759124087591249</v>
       </c>
+      <c r="Q415" s="1" t="n">
+        <v>2.721</v>
+      </c>
+      <c r="R415" s="2" t="n">
+        <v>0.001840942562592008</v>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -22105,6 +24601,12 @@
       <c r="P416" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="Q416" s="1" t="n">
+        <v>0.03223</v>
+      </c>
+      <c r="R416" s="2" t="n">
+        <v>0.001242621932277054</v>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -22157,6 +24659,12 @@
       <c r="P417" s="2" t="n">
         <v>0.0007479431563201757</v>
       </c>
+      <c r="Q417" s="1" t="n">
+        <v>0.04002</v>
+      </c>
+      <c r="R417" s="3" t="n">
+        <v>-0.002989536621823668</v>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -22209,6 +24717,12 @@
       <c r="P418" s="3" t="n">
         <v>-0.004328436516264388</v>
       </c>
+      <c r="Q418" s="1" t="n">
+        <v>0.07607</v>
+      </c>
+      <c r="R418" s="2" t="n">
+        <v>0.002107759188512626</v>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -22261,6 +24775,12 @@
       <c r="P419" s="3" t="n">
         <v>-0.002998500749625196</v>
       </c>
+      <c r="Q419" s="1" t="n">
+        <v>0.00662</v>
+      </c>
+      <c r="R419" s="3" t="n">
+        <v>-0.004511278195488668</v>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -22313,6 +24833,12 @@
       <c r="P420" s="3" t="n">
         <v>-0.004504504504504477</v>
       </c>
+      <c r="Q420" s="1" t="n">
+        <v>0.0885</v>
+      </c>
+      <c r="R420" s="2" t="n">
+        <v>0.001131221719456889</v>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -22365,6 +24891,12 @@
       <c r="P421" s="3" t="n">
         <v>-0.01558015580155801</v>
       </c>
+      <c r="Q421" s="1" t="n">
+        <v>0.2412</v>
+      </c>
+      <c r="R421" s="2" t="n">
+        <v>0.004581424406497251</v>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
@@ -22417,6 +24949,12 @@
       <c r="P422" s="3" t="n">
         <v>-0.010204081632653</v>
       </c>
+      <c r="Q422" s="1" t="n">
+        <v>0.0194</v>
+      </c>
+      <c r="R422" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -22469,6 +25007,12 @@
       <c r="P423" s="3" t="n">
         <v>-0.00265076209410213</v>
       </c>
+      <c r="Q423" s="1" t="n">
+        <v>0.1507</v>
+      </c>
+      <c r="R423" s="2" t="n">
+        <v>0.001328903654485088</v>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -22521,6 +25065,12 @@
       <c r="P424" s="3" t="n">
         <v>-0.003816793893129734</v>
       </c>
+      <c r="Q424" s="1" t="n">
+        <v>0.0002088</v>
+      </c>
+      <c r="R424" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -22573,6 +25123,12 @@
       <c r="P425" s="3" t="n">
         <v>-0.0008058017727639901</v>
       </c>
+      <c r="Q425" s="1" t="n">
+        <v>1.238</v>
+      </c>
+      <c r="R425" s="3" t="n">
+        <v>-0.001612903225806453</v>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
@@ -22625,6 +25181,12 @@
       <c r="P426" s="2" t="n">
         <v>0.001417434443656982</v>
       </c>
+      <c r="Q426" s="1" t="n">
+        <v>1.411</v>
+      </c>
+      <c r="R426" s="3" t="n">
+        <v>-0.001415428167020525</v>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -22677,6 +25239,12 @@
       <c r="P427" s="3" t="n">
         <v>-0.003598971722364892</v>
       </c>
+      <c r="Q427" s="1" t="n">
+        <v>0.01939</v>
+      </c>
+      <c r="R427" s="2" t="n">
+        <v>0.0005159958720330027</v>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
@@ -22729,6 +25297,12 @@
       <c r="P428" s="3" t="n">
         <v>-0.001970592693648705</v>
       </c>
+      <c r="Q428" s="1" t="n">
+        <v>0.0658</v>
+      </c>
+      <c r="R428" s="3" t="n">
+        <v>-0.0006075334143377639</v>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
@@ -22781,6 +25355,12 @@
       <c r="P429" s="3" t="n">
         <v>-0.005267118133935128</v>
       </c>
+      <c r="Q429" s="1" t="n">
+        <v>0.1324</v>
+      </c>
+      <c r="R429" s="2" t="n">
+        <v>0.001512859304084553</v>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
@@ -22833,6 +25413,12 @@
       <c r="P430" s="3" t="n">
         <v>-0.00305755395683447</v>
       </c>
+      <c r="Q430" s="1" t="n">
+        <v>0.011037</v>
+      </c>
+      <c r="R430" s="3" t="n">
+        <v>-0.004419989175536752</v>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -22885,6 +25471,12 @@
       <c r="P431" s="3" t="n">
         <v>-0.004332237824917894</v>
       </c>
+      <c r="Q431" s="1" t="n">
+        <v>0.006675</v>
+      </c>
+      <c r="R431" s="2" t="n">
+        <v>0.001500375093773512</v>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
@@ -22937,6 +25529,12 @@
       <c r="P432" s="3" t="n">
         <v>-0.006232294617563829</v>
       </c>
+      <c r="Q432" s="1" t="n">
+        <v>0.001763</v>
+      </c>
+      <c r="R432" s="2" t="n">
+        <v>0.0051311288483467</v>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
@@ -22989,6 +25587,12 @@
       <c r="P433" s="3" t="n">
         <v>-0.006588579795022043</v>
       </c>
+      <c r="Q433" s="1" t="n">
+        <v>0.001356</v>
+      </c>
+      <c r="R433" s="3" t="n">
+        <v>-0.0007369196757552808</v>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
@@ -23041,6 +25645,12 @@
       <c r="P434" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="Q434" s="1" t="n">
+        <v>0.000411</v>
+      </c>
+      <c r="R434" s="2" t="n">
+        <v>0.002439024390243962</v>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
@@ -23093,6 +25703,12 @@
       <c r="P435" s="3" t="n">
         <v>-0.002521670606777105</v>
       </c>
+      <c r="Q435" s="1" t="n">
+        <v>0.12669</v>
+      </c>
+      <c r="R435" s="2" t="n">
+        <v>0.000869015642281553</v>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -23145,6 +25761,12 @@
       <c r="P436" s="3" t="n">
         <v>-0.003970795439989813</v>
       </c>
+      <c r="Q436" s="1" t="n">
+        <v>0.07772</v>
+      </c>
+      <c r="R436" s="3" t="n">
+        <v>-0.0005144032921810491</v>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
@@ -23197,6 +25819,12 @@
       <c r="P437" s="3" t="n">
         <v>-0.004561182761874825</v>
       </c>
+      <c r="Q437" s="1" t="n">
+        <v>0.632</v>
+      </c>
+      <c r="R437" s="3" t="n">
+        <v>-0.001422025596460755</v>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -23249,6 +25877,12 @@
       <c r="P438" s="2" t="n">
         <v>0.0002289377289377991</v>
       </c>
+      <c r="Q438" s="1" t="n">
+        <v>0.0436</v>
+      </c>
+      <c r="R438" s="3" t="n">
+        <v>-0.002059967956054012</v>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
@@ -23301,6 +25935,12 @@
       <c r="P439" s="3" t="n">
         <v>-0.00283165793572125</v>
       </c>
+      <c r="Q439" s="1" t="n">
+        <v>0.07035</v>
+      </c>
+      <c r="R439" s="3" t="n">
+        <v>-0.001135879596762894</v>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
@@ -23353,6 +25993,12 @@
       <c r="P440" s="3" t="n">
         <v>-0.005256241787122193</v>
       </c>
+      <c r="Q440" s="1" t="n">
+        <v>0.001514</v>
+      </c>
+      <c r="R440" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -23405,6 +26051,12 @@
       <c r="P441" s="3" t="n">
         <v>-0.003894326912956591</v>
       </c>
+      <c r="Q441" s="1" t="n">
+        <v>0.009438999999999999</v>
+      </c>
+      <c r="R441" s="3" t="n">
+        <v>-0.002641589180050794</v>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
@@ -23457,6 +26109,12 @@
       <c r="P442" s="3" t="n">
         <v>-0.003766478342749533</v>
       </c>
+      <c r="Q442" s="1" t="n">
+        <v>1.062</v>
+      </c>
+      <c r="R442" s="2" t="n">
+        <v>0.003780718336483935</v>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
@@ -23509,6 +26167,12 @@
       <c r="P443" s="3" t="n">
         <v>-0.001364256480218226</v>
       </c>
+      <c r="Q443" s="1" t="n">
+        <v>0.02191</v>
+      </c>
+      <c r="R443" s="3" t="n">
+        <v>-0.002276867030965457</v>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
@@ -23561,6 +26225,12 @@
       <c r="P444" s="3" t="n">
         <v>-0.005769735116706004</v>
       </c>
+      <c r="Q444" s="1" t="n">
+        <v>0.0003781</v>
+      </c>
+      <c r="R444" s="3" t="n">
+        <v>-0.002637826431020903</v>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
@@ -23613,6 +26283,12 @@
       <c r="P445" s="3" t="n">
         <v>-0.003091624508150618</v>
       </c>
+      <c r="Q445" s="1" t="n">
+        <v>0.03532</v>
+      </c>
+      <c r="R445" s="3" t="n">
+        <v>-0.004228925852833501</v>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
@@ -23665,6 +26341,12 @@
       <c r="P446" s="3" t="n">
         <v>-0.007253158633598451</v>
       </c>
+      <c r="Q446" s="1" t="n">
+        <v>0.08481</v>
+      </c>
+      <c r="R446" s="3" t="n">
+        <v>-0.000589205750648225</v>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
@@ -23717,6 +26399,12 @@
       <c r="P447" s="3" t="n">
         <v>-0.005194011610143706</v>
       </c>
+      <c r="Q447" s="1" t="n">
+        <v>3.282</v>
+      </c>
+      <c r="R447" s="2" t="n">
+        <v>0.007985257985258062</v>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
@@ -23769,6 +26457,12 @@
       <c r="P448" s="3" t="n">
         <v>-0.001404713594506114</v>
       </c>
+      <c r="Q448" s="1" t="n">
+        <v>0.06383999999999999</v>
+      </c>
+      <c r="R448" s="3" t="n">
+        <v>-0.002188183807439844</v>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
@@ -23821,6 +26515,12 @@
       <c r="P449" s="3" t="n">
         <v>-0.002049180327868854</v>
       </c>
+      <c r="Q449" s="1" t="n">
+        <v>0.4868</v>
+      </c>
+      <c r="R449" s="3" t="n">
+        <v>-0.00041067761806977</v>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
@@ -23873,6 +26573,12 @@
       <c r="P450" s="3" t="n">
         <v>-0.0005385029617662678</v>
       </c>
+      <c r="Q450" s="1" t="n">
+        <v>0.03727</v>
+      </c>
+      <c r="R450" s="2" t="n">
+        <v>0.004040948275861998</v>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -23925,6 +26631,12 @@
       <c r="P451" s="3" t="n">
         <v>-0.00364963503649636</v>
       </c>
+      <c r="Q451" s="1" t="n">
+        <v>0.00546</v>
+      </c>
+      <c r="R451" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
@@ -23977,6 +26689,12 @@
       <c r="P452" s="3" t="n">
         <v>-0.006606664113366622</v>
       </c>
+      <c r="Q452" s="1" t="n">
+        <v>0.10389</v>
+      </c>
+      <c r="R452" s="2" t="n">
+        <v>0.001349397590361458</v>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
@@ -24029,6 +26747,12 @@
       <c r="P453" s="3" t="n">
         <v>-0.003735990037359964</v>
       </c>
+      <c r="Q453" s="1" t="n">
+        <v>0.01602</v>
+      </c>
+      <c r="R453" s="2" t="n">
+        <v>0.001249999999999949</v>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
@@ -24081,6 +26805,12 @@
       <c r="P454" s="2" t="n">
         <v>0.004228329809725162</v>
       </c>
+      <c r="Q454" s="1" t="n">
+        <v>2.861</v>
+      </c>
+      <c r="R454" s="2" t="n">
+        <v>0.00385964912280706</v>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
@@ -24133,6 +26863,12 @@
       <c r="P455" s="3" t="n">
         <v>-0.004449388209121249</v>
       </c>
+      <c r="Q455" s="1" t="n">
+        <v>0.895</v>
+      </c>
+      <c r="R455" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
@@ -24185,6 +26921,12 @@
       <c r="P456" s="3" t="n">
         <v>-0.001352722353736897</v>
       </c>
+      <c r="Q456" s="1" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="R456" s="3" t="n">
+        <v>-0.001015916017609099</v>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -24237,6 +26979,12 @@
       <c r="P457" s="3" t="n">
         <v>-0.001012145748987813</v>
       </c>
+      <c r="Q457" s="1" t="n">
+        <v>0.009860000000000001</v>
+      </c>
+      <c r="R457" s="3" t="n">
+        <v>-0.001013171225937142</v>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
@@ -24289,6 +27037,12 @@
       <c r="P458" s="3" t="n">
         <v>-0.004184100418410094</v>
       </c>
+      <c r="Q458" s="1" t="n">
+        <v>0.06199</v>
+      </c>
+      <c r="R458" s="2" t="n">
+        <v>0.001777634130575403</v>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
@@ -24341,6 +27095,12 @@
       <c r="P459" s="3" t="n">
         <v>-0.003489183531053833</v>
       </c>
+      <c r="Q459" s="1" t="n">
+        <v>0.01428</v>
+      </c>
+      <c r="R459" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
@@ -24393,6 +27153,12 @@
       <c r="P460" s="3" t="n">
         <v>-0.001375859912445352</v>
       </c>
+      <c r="Q460" s="1" t="n">
+        <v>0.015995</v>
+      </c>
+      <c r="R460" s="2" t="n">
+        <v>0.001690881763527007</v>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
@@ -24445,6 +27211,12 @@
       <c r="P461" s="3" t="n">
         <v>-0.007789095266626821</v>
       </c>
+      <c r="Q461" s="1" t="n">
+        <v>0.01654</v>
+      </c>
+      <c r="R461" s="3" t="n">
+        <v>-0.001207729468598985</v>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
@@ -24497,6 +27269,12 @@
       <c r="P462" s="3" t="n">
         <v>-0.004259346900142081</v>
       </c>
+      <c r="Q462" s="1" t="n">
+        <v>0.0002103</v>
+      </c>
+      <c r="R462" s="3" t="n">
+        <v>-0.0004752851711026732</v>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
@@ -24549,6 +27327,12 @@
       <c r="P463" s="2" t="n">
         <v>0.001012145748987883</v>
       </c>
+      <c r="Q463" s="1" t="n">
+        <v>0.099</v>
+      </c>
+      <c r="R463" s="2" t="n">
+        <v>0.001011122345803871</v>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
@@ -24601,6 +27385,12 @@
       <c r="P464" s="3" t="n">
         <v>-0.003435114503816786</v>
       </c>
+      <c r="Q464" s="1" t="n">
+        <v>0.02613</v>
+      </c>
+      <c r="R464" s="2" t="n">
+        <v>0.0007659900421294211</v>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
@@ -24653,6 +27443,12 @@
       <c r="P465" s="3" t="n">
         <v>-0.006613756613756573</v>
       </c>
+      <c r="Q465" s="1" t="n">
+        <v>0.01529</v>
+      </c>
+      <c r="R465" s="2" t="n">
+        <v>0.01797603195739011</v>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
@@ -24705,6 +27501,12 @@
       <c r="P466" s="2" t="n">
         <v>0.0001828487840555151</v>
       </c>
+      <c r="Q466" s="1" t="n">
+        <v>0.05461</v>
+      </c>
+      <c r="R466" s="3" t="n">
+        <v>-0.001645338208409503</v>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
@@ -24757,6 +27559,12 @@
       <c r="P467" s="3" t="n">
         <v>-0.002321532211259337</v>
       </c>
+      <c r="Q467" s="1" t="n">
+        <v>0.03431</v>
+      </c>
+      <c r="R467" s="3" t="n">
+        <v>-0.002036067481093677</v>
+      </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
@@ -24809,6 +27617,12 @@
       <c r="P468" s="3" t="n">
         <v>-0.005079825834542708</v>
       </c>
+      <c r="Q468" s="1" t="n">
+        <v>27.38</v>
+      </c>
+      <c r="R468" s="3" t="n">
+        <v>-0.001458789204959982</v>
+      </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
@@ -24861,6 +27675,12 @@
       <c r="P469" s="3" t="n">
         <v>-0.001339046598821671</v>
       </c>
+      <c r="Q469" s="1" t="n">
+        <v>0.0007481</v>
+      </c>
+      <c r="R469" s="2" t="n">
+        <v>0.003083936712255298</v>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
@@ -24913,6 +27733,12 @@
       <c r="P470" s="3" t="n">
         <v>-0.001142857142857144</v>
       </c>
+      <c r="Q470" s="1" t="n">
+        <v>0.874</v>
+      </c>
+      <c r="R470" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
@@ -24965,6 +27791,12 @@
       <c r="P471" s="3" t="n">
         <v>-0.003027245206861807</v>
       </c>
+      <c r="Q471" s="1" t="n">
+        <v>0.009900000000000001</v>
+      </c>
+      <c r="R471" s="2" t="n">
+        <v>0.002024291497975802</v>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
@@ -25017,6 +27849,12 @@
       <c r="P472" s="3" t="n">
         <v>-0.003427592116538141</v>
       </c>
+      <c r="Q472" s="1" t="n">
+        <v>0.04646</v>
+      </c>
+      <c r="R472" s="3" t="n">
+        <v>-0.001289767841788425</v>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -25069,6 +27907,12 @@
       <c r="P473" s="3" t="n">
         <v>-0.002911208151382705</v>
       </c>
+      <c r="Q473" s="1" t="n">
+        <v>0.274</v>
+      </c>
+      <c r="R473" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
@@ -25121,6 +27965,12 @@
       <c r="P474" s="3" t="n">
         <v>-0.006398537477148137</v>
       </c>
+      <c r="Q474" s="1" t="n">
+        <v>0.04376</v>
+      </c>
+      <c r="R474" s="2" t="n">
+        <v>0.006439742410303645</v>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
@@ -25173,6 +28023,12 @@
       <c r="P475" s="3" t="n">
         <v>-0.004123468426013231</v>
       </c>
+      <c r="Q475" s="1" t="n">
+        <v>0.008458</v>
+      </c>
+      <c r="R475" s="2" t="n">
+        <v>0.0005915059742103154</v>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
@@ -25225,6 +28081,12 @@
       <c r="P476" s="3" t="n">
         <v>-0.001714635639926531</v>
       </c>
+      <c r="Q476" s="1" t="n">
+        <v>0.08180999999999999</v>
+      </c>
+      <c r="R476" s="2" t="n">
+        <v>0.003680529996319405</v>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
@@ -25277,6 +28139,12 @@
       <c r="P477" s="3" t="n">
         <v>-0.003665689149560121</v>
       </c>
+      <c r="Q477" s="1" t="n">
+        <v>0.1358</v>
+      </c>
+      <c r="R477" s="3" t="n">
+        <v>-0.0007358351729211846</v>
+      </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
@@ -25329,6 +28197,12 @@
       <c r="P478" s="3" t="n">
         <v>-0.008014024542950115</v>
       </c>
+      <c r="Q478" s="1" t="n">
+        <v>0.3967</v>
+      </c>
+      <c r="R478" s="2" t="n">
+        <v>0.00151476899772782</v>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
@@ -25381,6 +28255,12 @@
       <c r="P479" s="3" t="n">
         <v>-0.004836046237320049</v>
       </c>
+      <c r="Q479" s="1" t="n">
+        <v>0.008495000000000001</v>
+      </c>
+      <c r="R479" s="2" t="n">
+        <v>0.006874481450752727</v>
+      </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
@@ -25433,6 +28313,12 @@
       <c r="P480" s="3" t="n">
         <v>-0.003768844221105592</v>
       </c>
+      <c r="Q480" s="1" t="n">
+        <v>0.01585</v>
+      </c>
+      <c r="R480" s="3" t="n">
+        <v>-0.0006305170239596212</v>
+      </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
@@ -25485,6 +28371,12 @@
       <c r="P481" s="2" t="n">
         <v>0.00476067936181175</v>
       </c>
+      <c r="Q481" s="1" t="n">
+        <v>0.07788</v>
+      </c>
+      <c r="R481" s="3" t="n">
+        <v>-0.002689204763734176</v>
+      </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
@@ -25537,6 +28429,12 @@
       <c r="P482" s="3" t="n">
         <v>-0.00592417061611364</v>
       </c>
+      <c r="Q482" s="1" t="n">
+        <v>0.05028</v>
+      </c>
+      <c r="R482" s="3" t="n">
+        <v>-0.001191895113230125</v>
+      </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
@@ -25589,6 +28487,12 @@
       <c r="P483" s="3" t="n">
         <v>-0.008213552361396325</v>
       </c>
+      <c r="Q483" s="1" t="n">
+        <v>0.0097</v>
+      </c>
+      <c r="R483" s="2" t="n">
+        <v>0.004140786749482412</v>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
@@ -25641,6 +28545,12 @@
       <c r="P484" s="3" t="n">
         <v>-0.001028806584362149</v>
       </c>
+      <c r="Q484" s="1" t="n">
+        <v>0.06788</v>
+      </c>
+      <c r="R484" s="3" t="n">
+        <v>-0.001324113579520476</v>
+      </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
@@ -25693,6 +28603,12 @@
       <c r="P485" s="2" t="n">
         <v>0.002450980392156802</v>
       </c>
+      <c r="Q485" s="1" t="n">
+        <v>0.0004483</v>
+      </c>
+      <c r="R485" s="3" t="n">
+        <v>-0.003556345854634329</v>
+      </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
@@ -25745,6 +28661,12 @@
       <c r="P486" s="3" t="n">
         <v>-0.005805148914689576</v>
       </c>
+      <c r="Q486" s="1" t="n">
+        <v>0.07901</v>
+      </c>
+      <c r="R486" s="2" t="n">
+        <v>0.002919522721502844</v>
+      </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
@@ -25797,6 +28719,12 @@
       <c r="P487" s="3" t="n">
         <v>-0.003458213256484078</v>
       </c>
+      <c r="Q487" s="1" t="n">
+        <v>0.0001728</v>
+      </c>
+      <c r="R487" s="3" t="n">
+        <v>-0.0005783689994216451</v>
+      </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
@@ -25849,6 +28777,12 @@
       <c r="P488" s="2" t="n">
         <v>0.0003438789546080037</v>
       </c>
+      <c r="Q488" s="1" t="n">
+        <v>0.08782</v>
+      </c>
+      <c r="R488" s="2" t="n">
+        <v>0.006302280279592012</v>
+      </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
@@ -25901,6 +28835,12 @@
       <c r="P489" s="3" t="n">
         <v>-0.000210792580101245</v>
       </c>
+      <c r="Q489" s="1" t="n">
+        <v>0.04756</v>
+      </c>
+      <c r="R489" s="2" t="n">
+        <v>0.002740881298756023</v>
+      </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
@@ -25953,6 +28893,12 @@
       <c r="P490" s="2" t="n">
         <v>0.004158004158004169</v>
       </c>
+      <c r="Q490" s="1" t="n">
+        <v>0.03896</v>
+      </c>
+      <c r="R490" s="2" t="n">
+        <v>0.008281573498964825</v>
+      </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
@@ -26005,6 +28951,12 @@
       <c r="P491" s="3" t="n">
         <v>-0.004098885615473304</v>
       </c>
+      <c r="Q491" s="1" t="n">
+        <v>0.07808</v>
+      </c>
+      <c r="R491" s="2" t="n">
+        <v>0.004244372990353659</v>
+      </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
@@ -26057,6 +29009,12 @@
       <c r="P492" s="3" t="n">
         <v>-0.0001588057805303498</v>
       </c>
+      <c r="Q492" s="1" t="n">
+        <v>0.06301</v>
+      </c>
+      <c r="R492" s="2" t="n">
+        <v>0.0007941550190596329</v>
+      </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
@@ -26109,6 +29067,12 @@
       <c r="P493" s="3" t="n">
         <v>-0.001893939393939317</v>
       </c>
+      <c r="Q493" s="1" t="n">
+        <v>0.00527</v>
+      </c>
+      <c r="R493" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
@@ -26161,6 +29125,12 @@
       <c r="P494" s="3" t="n">
         <v>-0.004332129963899041</v>
       </c>
+      <c r="Q494" s="1" t="n">
+        <v>0.2747</v>
+      </c>
+      <c r="R494" s="3" t="n">
+        <v>-0.003988397389412581</v>
+      </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
@@ -26213,6 +29183,12 @@
       <c r="P495" s="3" t="n">
         <v>-0.001566906925728657</v>
       </c>
+      <c r="Q495" s="1" t="n">
+        <v>0.0636</v>
+      </c>
+      <c r="R495" s="3" t="n">
+        <v>-0.001883239171374688</v>
+      </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
@@ -26265,6 +29241,12 @@
       <c r="P496" s="3" t="n">
         <v>-0.005107252298263538</v>
       </c>
+      <c r="Q496" s="1" t="n">
+        <v>0.2917</v>
+      </c>
+      <c r="R496" s="3" t="n">
+        <v>-0.001711156741957565</v>
+      </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
@@ -26317,6 +29299,12 @@
       <c r="P497" s="2" t="n">
         <v>0.05316037135953185</v>
       </c>
+      <c r="Q497" s="1" t="n">
+        <v>0.07872999999999999</v>
+      </c>
+      <c r="R497" s="3" t="n">
+        <v>-0.04926941190677455</v>
+      </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
@@ -26369,6 +29357,12 @@
       <c r="P498" s="3" t="n">
         <v>-0.00289855072463763</v>
       </c>
+      <c r="Q498" s="1" t="n">
+        <v>0.1032</v>
+      </c>
+      <c r="R498" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
@@ -26421,6 +29415,12 @@
       <c r="P499" s="3" t="n">
         <v>-0.005278310940499158</v>
       </c>
+      <c r="Q499" s="1" t="n">
+        <v>0.04153</v>
+      </c>
+      <c r="R499" s="2" t="n">
+        <v>0.001688374336710097</v>
+      </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
@@ -26473,6 +29473,12 @@
       <c r="P500" s="3" t="n">
         <v>-0.01391261898950454</v>
       </c>
+      <c r="Q500" s="1" t="n">
+        <v>0.04024</v>
+      </c>
+      <c r="R500" s="3" t="n">
+        <v>-0.003960396039603971</v>
+      </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
@@ -26525,6 +29531,12 @@
       <c r="P501" s="3" t="n">
         <v>-0.00702811244979912</v>
       </c>
+      <c r="Q501" s="1" t="n">
+        <v>0.0989</v>
+      </c>
+      <c r="R501" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
@@ -26577,6 +29589,12 @@
       <c r="P502" s="3" t="n">
         <v>-0.003623188405797059</v>
       </c>
+      <c r="Q502" s="1" t="n">
+        <v>0.003303</v>
+      </c>
+      <c r="R502" s="2" t="n">
+        <v>0.0009090909090908984</v>
+      </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
@@ -26629,6 +29647,12 @@
       <c r="P503" s="3" t="n">
         <v>-0.001069518716577682</v>
       </c>
+      <c r="Q503" s="1" t="n">
+        <v>0.00927</v>
+      </c>
+      <c r="R503" s="3" t="n">
+        <v>-0.007494646680942065</v>
+      </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
@@ -26681,6 +29705,12 @@
       <c r="P504" s="3" t="n">
         <v>-0.008750000000000077</v>
       </c>
+      <c r="Q504" s="1" t="n">
+        <v>0.1592</v>
+      </c>
+      <c r="R504" s="2" t="n">
+        <v>0.00378310214375799</v>
+      </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
@@ -26733,6 +29763,12 @@
       <c r="P505" s="3" t="n">
         <v>-0.003802281368821296</v>
       </c>
+      <c r="Q505" s="1" t="n">
+        <v>0.131</v>
+      </c>
+      <c r="R505" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
@@ -26785,6 +29821,12 @@
       <c r="P506" s="3" t="n">
         <v>-0.00412979351032452</v>
       </c>
+      <c r="Q506" s="1" t="n">
+        <v>0.01689</v>
+      </c>
+      <c r="R506" s="2" t="n">
+        <v>0.0005924170616113503</v>
+      </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
@@ -26837,6 +29879,12 @@
       <c r="P507" s="3" t="n">
         <v>-0.005177770107007188</v>
       </c>
+      <c r="Q507" s="1" t="n">
+        <v>0.002885</v>
+      </c>
+      <c r="R507" s="2" t="n">
+        <v>0.00104094378903538</v>
+      </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
@@ -26889,6 +29937,12 @@
       <c r="P508" s="3" t="n">
         <v>-0.004043126684636072</v>
       </c>
+      <c r="Q508" s="1" t="n">
+        <v>2.215</v>
+      </c>
+      <c r="R508" s="3" t="n">
+        <v>-0.0009021199819577013</v>
+      </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
@@ -26941,6 +29995,12 @@
       <c r="P509" s="3" t="n">
         <v>-0.007445069911022346</v>
       </c>
+      <c r="Q509" s="1" t="n">
+        <v>0.05466</v>
+      </c>
+      <c r="R509" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
@@ -26993,6 +30053,12 @@
       <c r="P510" s="3" t="n">
         <v>-0.003407155025553642</v>
       </c>
+      <c r="Q510" s="1" t="n">
+        <v>0.02931</v>
+      </c>
+      <c r="R510" s="2" t="n">
+        <v>0.002051282051281968</v>
+      </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
@@ -27045,6 +30111,12 @@
       <c r="P511" s="3" t="n">
         <v>-0.001731815932706596</v>
       </c>
+      <c r="Q511" s="1" t="n">
+        <v>0.04037</v>
+      </c>
+      <c r="R511" s="2" t="n">
+        <v>0.0004956629491946995</v>
+      </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
@@ -27097,6 +30169,12 @@
       <c r="P512" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="Q512" s="1" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="R512" s="3" t="n">
+        <v>-0.01162790697674404</v>
+      </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
@@ -27149,6 +30227,12 @@
       <c r="P513" s="2" t="n">
         <v>0.07683593229374913</v>
       </c>
+      <c r="Q513" s="1" t="n">
+        <v>0.015487</v>
+      </c>
+      <c r="R513" s="3" t="n">
+        <v>-0.04158673185221851</v>
+      </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
@@ -27201,6 +30285,12 @@
       <c r="P514" s="3" t="n">
         <v>-0.0051546391752578</v>
       </c>
+      <c r="Q514" s="1" t="n">
+        <v>0.1738</v>
+      </c>
+      <c r="R514" s="2" t="n">
+        <v>0.0005757052389177706</v>
+      </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
@@ -27253,6 +30343,12 @@
       <c r="P515" s="3" t="n">
         <v>-0.003707136237256697</v>
       </c>
+      <c r="Q515" s="1" t="n">
+        <v>0.1076</v>
+      </c>
+      <c r="R515" s="2" t="n">
+        <v>0.0009302325581395615</v>
+      </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
@@ -27305,6 +30401,12 @@
       <c r="P516" s="3" t="n">
         <v>-0.007462686567164198</v>
       </c>
+      <c r="Q516" s="1" t="n">
+        <v>0.00266</v>
+      </c>
+      <c r="R516" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
@@ -27357,6 +30459,12 @@
       <c r="P517" s="3" t="n">
         <v>-0.005156632718834615</v>
       </c>
+      <c r="Q517" s="1" t="n">
+        <v>0.007711</v>
+      </c>
+      <c r="R517" s="3" t="n">
+        <v>-0.0007775042114811364</v>
+      </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
@@ -27409,6 +30517,12 @@
       <c r="P518" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="Q518" s="1" t="n">
+        <v>0.01546</v>
+      </c>
+      <c r="R518" s="2" t="n">
+        <v>0.002594033722438399</v>
+      </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
@@ -27461,6 +30575,12 @@
       <c r="P519" s="2" t="n">
         <v>0.01703163017031624</v>
       </c>
+      <c r="Q519" s="1" t="n">
+        <v>0.00419</v>
+      </c>
+      <c r="R519" s="2" t="n">
+        <v>0.002392344497607766</v>
+      </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
@@ -27513,6 +30633,12 @@
       <c r="P520" s="3" t="n">
         <v>-0.002586206896551693</v>
       </c>
+      <c r="Q520" s="1" t="n">
+        <v>0.001158</v>
+      </c>
+      <c r="R520" s="2" t="n">
+        <v>0.0008643042350906792</v>
+      </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
@@ -27565,6 +30691,12 @@
       <c r="P521" s="3" t="n">
         <v>-0.002242152466367622</v>
       </c>
+      <c r="Q521" s="1" t="n">
+        <v>0.01338</v>
+      </c>
+      <c r="R521" s="2" t="n">
+        <v>0.002247191011235863</v>
+      </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
@@ -27617,6 +30749,12 @@
       <c r="P522" s="3" t="n">
         <v>-0.002324905550712069</v>
       </c>
+      <c r="Q522" s="1" t="n">
+        <v>0.6878</v>
+      </c>
+      <c r="R522" s="2" t="n">
+        <v>0.001747742499271743</v>
+      </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
@@ -27669,6 +30807,12 @@
       <c r="P523" s="3" t="n">
         <v>-0.0001429592566118102</v>
       </c>
+      <c r="Q523" s="1" t="n">
+        <v>0.07033</v>
+      </c>
+      <c r="R523" s="2" t="n">
+        <v>0.005576208178438682</v>
+      </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
@@ -27721,6 +30865,12 @@
       <c r="P524" s="3" t="n">
         <v>-0.003448275862068825</v>
       </c>
+      <c r="Q524" s="1" t="n">
+        <v>0.01157</v>
+      </c>
+      <c r="R524" s="2" t="n">
+        <v>0.0008650519031141515</v>
+      </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
@@ -27773,6 +30923,12 @@
       <c r="P525" s="3" t="n">
         <v>-0.003656307129798966</v>
       </c>
+      <c r="Q525" s="1" t="n">
+        <v>0.01642</v>
+      </c>
+      <c r="R525" s="2" t="n">
+        <v>0.004281345565749274</v>
+      </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
@@ -27825,6 +30981,12 @@
       <c r="P526" s="3" t="n">
         <v>-0.006788164981922851</v>
       </c>
+      <c r="Q526" s="1" t="n">
+        <v>0.13425</v>
+      </c>
+      <c r="R526" s="3" t="n">
+        <v>-0.002674392689993308</v>
+      </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
@@ -27877,6 +31039,12 @@
       <c r="P527" s="3" t="n">
         <v>-0.002318034306907648</v>
       </c>
+      <c r="Q527" s="1" t="n">
+        <v>0.043</v>
+      </c>
+      <c r="R527" s="3" t="n">
+        <v>-0.0009293680297399003</v>
+      </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
@@ -27929,6 +31097,12 @@
       <c r="P528" s="3" t="n">
         <v>-0.003664345914254309</v>
       </c>
+      <c r="Q528" s="1" t="n">
+        <v>0.2725</v>
+      </c>
+      <c r="R528" s="2" t="n">
+        <v>0.002206693637366844</v>
+      </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
@@ -27981,6 +31155,12 @@
       <c r="P529" s="3" t="n">
         <v>-0.004663283500205698</v>
       </c>
+      <c r="Q529" s="1" t="n">
+        <v>0.0007252</v>
+      </c>
+      <c r="R529" s="3" t="n">
+        <v>-0.0006889899407469566</v>
+      </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
@@ -28033,6 +31213,12 @@
       <c r="P530" s="3" t="n">
         <v>-0.01097590073968027</v>
       </c>
+      <c r="Q530" s="1" t="n">
+        <v>0.004139</v>
+      </c>
+      <c r="R530" s="3" t="n">
+        <v>-0.001447527141133879</v>
+      </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
@@ -28085,6 +31271,12 @@
       <c r="P531" s="3" t="n">
         <v>-0.002279635258358749</v>
       </c>
+      <c r="Q531" s="1" t="n">
+        <v>1.313</v>
+      </c>
+      <c r="R531" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
@@ -28137,6 +31329,12 @@
       <c r="P532" s="3" t="n">
         <v>-0.004230118443316416</v>
       </c>
+      <c r="Q532" s="1" t="n">
+        <v>0.1179</v>
+      </c>
+      <c r="R532" s="2" t="n">
+        <v>0.001699235344095206</v>
+      </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
@@ -28189,6 +31387,12 @@
       <c r="P533" s="3" t="n">
         <v>-0.006144107242599216</v>
       </c>
+      <c r="Q533" s="1" t="n">
+        <v>0.05335</v>
+      </c>
+      <c r="R533" s="3" t="n">
+        <v>-0.000562008242787473</v>
+      </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
@@ -28241,6 +31445,12 @@
       <c r="P534" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="Q534" s="1" t="n">
+        <v>0.1497</v>
+      </c>
+      <c r="R534" s="3" t="n">
+        <v>-0.000667556742323024</v>
+      </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
@@ -28293,6 +31503,12 @@
       <c r="P535" s="3" t="n">
         <v>-0.007575757575757671</v>
       </c>
+      <c r="Q535" s="1" t="n">
+        <v>0.01705</v>
+      </c>
+      <c r="R535" s="2" t="n">
+        <v>0.001174398120962959</v>
+      </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
@@ -28345,6 +31561,12 @@
       <c r="P536" s="3" t="n">
         <v>-0.0002006018054162754</v>
       </c>
+      <c r="Q536" s="1" t="n">
+        <v>0.004987</v>
+      </c>
+      <c r="R536" s="2" t="n">
+        <v>0.0006019261637239964</v>
+      </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
@@ -28397,6 +31619,12 @@
       <c r="P537" s="3" t="n">
         <v>-0.001370801919122726</v>
       </c>
+      <c r="Q537" s="1" t="n">
+        <v>0.2921</v>
+      </c>
+      <c r="R537" s="2" t="n">
+        <v>0.002402196293754406</v>
+      </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
@@ -28449,6 +31677,12 @@
       <c r="P538" s="3" t="n">
         <v>-0.0007535795026376282</v>
       </c>
+      <c r="Q538" s="1" t="n">
+        <v>0.01331</v>
+      </c>
+      <c r="R538" s="2" t="n">
+        <v>0.00377073906485682</v>
+      </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
@@ -28501,6 +31735,12 @@
       <c r="P539" s="2" t="n">
         <v>0.004856333468231568</v>
       </c>
+      <c r="Q539" s="1" t="n">
+        <v>0.02476</v>
+      </c>
+      <c r="R539" s="3" t="n">
+        <v>-0.002819170358437399</v>
+      </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
@@ -28553,6 +31793,12 @@
       <c r="P540" s="3" t="n">
         <v>-0.002106741573033622</v>
       </c>
+      <c r="Q540" s="1" t="n">
+        <v>0.05683</v>
+      </c>
+      <c r="R540" s="3" t="n">
+        <v>-0.000175932441942348</v>
+      </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
@@ -28605,6 +31851,12 @@
       <c r="P541" s="3" t="n">
         <v>-0.008620689655172362</v>
       </c>
+      <c r="Q541" s="1" t="n">
+        <v>0.0116</v>
+      </c>
+      <c r="R541" s="2" t="n">
+        <v>0.008695652173912992</v>
+      </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
@@ -28657,6 +31909,12 @@
       <c r="P542" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="Q542" s="1" t="n">
+        <v>1.12e-05</v>
+      </c>
+      <c r="R542" s="2" t="n">
+        <v>0.009009009009008922</v>
+      </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
@@ -28708,6 +31966,12 @@
       </c>
       <c r="P543" s="2" t="n">
         <v>0.0008147745790331245</v>
+      </c>
+      <c r="Q543" s="1" t="n">
+        <v>0.003671</v>
+      </c>
+      <c r="R543" s="3" t="n">
+        <v>-0.003799185888738161</v>
       </c>
     </row>
   </sheetData>

--- a/binance-usdt-perpetual-data/weeks/2026-03-09_2026-03-15/2026-03-12.xlsx
+++ b/binance-usdt-perpetual-data/weeks/2026-03-09_2026-03-15/2026-03-12.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R543"/>
+  <dimension ref="A1:T543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -444,6 +444,8 @@
     <col width="18" customWidth="1" min="16" max="16"/>
     <col width="13" customWidth="1" min="17" max="17"/>
     <col width="18" customWidth="1" min="18" max="18"/>
+    <col width="13" customWidth="1" min="19" max="19"/>
+    <col width="18" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -537,6 +539,16 @@
           <t>change_02:00</t>
         </is>
       </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>price_02:15</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>change_02:15</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -595,6 +607,12 @@
       <c r="R2" s="3" t="n">
         <v>-0.0006948887542423819</v>
       </c>
+      <c r="S2" s="1" t="n">
+        <v>70707.2</v>
+      </c>
+      <c r="T2" s="3" t="n">
+        <v>-0.0006543845887483009</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -653,6 +671,12 @@
       <c r="R3" s="3" t="n">
         <v>-0.0007636982328602563</v>
       </c>
+      <c r="S3" s="1" t="n">
+        <v>2067.4</v>
+      </c>
+      <c r="T3" s="2" t="n">
+        <v>4.837227301306489e-05</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -711,6 +735,12 @@
       <c r="R4" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="S4" s="1" t="n">
+        <v>87.77</v>
+      </c>
+      <c r="T4" s="2" t="n">
+        <v>0.006305893143774331</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -769,6 +799,12 @@
       <c r="R5" s="2" t="n">
         <v>0.0263513033596136</v>
       </c>
+      <c r="S5" s="1" t="n">
+        <v>0.013833</v>
+      </c>
+      <c r="T5" s="3" t="n">
+        <v>-0.04269896193771623</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -827,6 +863,12 @@
       <c r="R6" s="2" t="n">
         <v>0.0004273504273504099</v>
       </c>
+      <c r="S6" s="1" t="n">
+        <v>0.09394</v>
+      </c>
+      <c r="T6" s="2" t="n">
+        <v>0.003203759077317329</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -885,6 +927,12 @@
       <c r="R7" s="3" t="n">
         <v>-0.0002147151445748404</v>
       </c>
+      <c r="S7" s="1" t="n">
+        <v>1.3995</v>
+      </c>
+      <c r="T7" s="2" t="n">
+        <v>0.001861264227933235</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -943,6 +991,12 @@
       <c r="R8" s="3" t="n">
         <v>-0.005758210271104146</v>
       </c>
+      <c r="S8" s="1" t="n">
+        <v>36.11</v>
+      </c>
+      <c r="T8" s="2" t="n">
+        <v>0.000637348629700339</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1001,6 +1055,12 @@
       <c r="R9" s="3" t="n">
         <v>-0.0005519356075124777</v>
       </c>
+      <c r="S9" s="1" t="n">
+        <v>652.8200000000001</v>
+      </c>
+      <c r="T9" s="2" t="n">
+        <v>0.001426621055699679</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1059,6 +1119,12 @@
       <c r="R10" s="3" t="n">
         <v>-0.02771346860956013</v>
       </c>
+      <c r="S10" s="1" t="n">
+        <v>14.291</v>
+      </c>
+      <c r="T10" s="2" t="n">
+        <v>0.0008403949856432842</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1117,6 +1183,12 @@
       <c r="R11" s="3" t="n">
         <v>-0.0003305629013977766</v>
       </c>
+      <c r="S11" s="1" t="n">
+        <v>212.2</v>
+      </c>
+      <c r="T11" s="2" t="n">
+        <v>0.002409183239642831</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1175,6 +1247,12 @@
       <c r="R12" s="2" t="n">
         <v>0.002620841647556427</v>
       </c>
+      <c r="S12" s="1" t="n">
+        <v>0.003372</v>
+      </c>
+      <c r="T12" s="2" t="n">
+        <v>0.001633744244764551</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1233,6 +1311,12 @@
       <c r="R13" s="3" t="n">
         <v>-0.01775147928994085</v>
       </c>
+      <c r="S13" s="1" t="n">
+        <v>0.03693</v>
+      </c>
+      <c r="T13" s="2" t="n">
+        <v>0.01122672508214679</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1291,6 +1375,12 @@
       <c r="R14" s="2" t="n">
         <v>0.001542614731970692</v>
       </c>
+      <c r="S14" s="1" t="n">
+        <v>2.608</v>
+      </c>
+      <c r="T14" s="2" t="n">
+        <v>0.004235656526761695</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1349,6 +1439,12 @@
       <c r="R15" s="3" t="n">
         <v>-0.003054056805456585</v>
       </c>
+      <c r="S15" s="1" t="n">
+        <v>0.9818</v>
+      </c>
+      <c r="T15" s="2" t="n">
+        <v>0.002552843868069088</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1407,6 +1503,12 @@
       <c r="R16" s="3" t="n">
         <v>-0.004786385392660865</v>
       </c>
+      <c r="S16" s="1" t="n">
+        <v>0.05635</v>
+      </c>
+      <c r="T16" s="2" t="n">
+        <v>0.003740648379052278</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1465,6 +1567,12 @@
       <c r="R17" s="3" t="n">
         <v>-0.001133786848072563</v>
       </c>
+      <c r="S17" s="1" t="n">
+        <v>0.883</v>
+      </c>
+      <c r="T17" s="2" t="n">
+        <v>0.002270147559591376</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1523,6 +1631,12 @@
       <c r="R18" s="2" t="n">
         <v>0.0007561436672967031</v>
       </c>
+      <c r="S18" s="1" t="n">
+        <v>0.2653</v>
+      </c>
+      <c r="T18" s="2" t="n">
+        <v>0.002266717038156364</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1581,6 +1695,12 @@
       <c r="R19" s="2" t="n">
         <v>0.004222460016774044</v>
       </c>
+      <c r="S19" s="1" t="n">
+        <v>0.34536</v>
+      </c>
+      <c r="T19" s="3" t="n">
+        <v>-0.005385479365262169</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1639,6 +1759,12 @@
       <c r="R20" s="2" t="n">
         <v>0.001554082055532591</v>
       </c>
+      <c r="S20" s="1" t="n">
+        <v>9.702999999999999</v>
+      </c>
+      <c r="T20" s="2" t="n">
+        <v>0.003724009516913167</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1697,6 +1823,12 @@
       <c r="R21" s="2" t="n">
         <v>0.001761183515322411</v>
       </c>
+      <c r="S21" s="1" t="n">
+        <v>199.47</v>
+      </c>
+      <c r="T21" s="2" t="n">
+        <v>0.00195901145268227</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1755,6 +1887,12 @@
       <c r="R22" s="3" t="n">
         <v>-0.007373138643920626</v>
       </c>
+      <c r="S22" s="1" t="n">
+        <v>0.020679</v>
+      </c>
+      <c r="T22" s="2" t="n">
+        <v>0.003932420623361381</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1813,6 +1951,12 @@
       <c r="R23" s="3" t="n">
         <v>-0.002010709212108001</v>
       </c>
+      <c r="S23" s="1" t="n">
+        <v>457.59</v>
+      </c>
+      <c r="T23" s="2" t="n">
+        <v>0.00210235858353586</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1871,6 +2015,12 @@
       <c r="R24" s="2" t="n">
         <v>0.001261466556603268</v>
       </c>
+      <c r="S24" s="1" t="n">
+        <v>5170.19</v>
+      </c>
+      <c r="T24" s="2" t="n">
+        <v>0.0005844591913948113</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1929,6 +2079,12 @@
       <c r="R25" s="2" t="n">
         <v>0.000551024906325852</v>
       </c>
+      <c r="S25" s="1" t="n">
+        <v>9.087999999999999</v>
+      </c>
+      <c r="T25" s="2" t="n">
+        <v>0.0009912986011673714</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1987,6 +2143,12 @@
       <c r="R26" s="2" t="n">
         <v>0.001272588444896898</v>
       </c>
+      <c r="S26" s="1" t="n">
+        <v>0.11948</v>
+      </c>
+      <c r="T26" s="2" t="n">
+        <v>0.01237078461277752</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2045,6 +2207,12 @@
       <c r="R27" s="2" t="n">
         <v>0.00165425971877578</v>
       </c>
+      <c r="S27" s="1" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="T27" s="3" t="n">
+        <v>-0.009083402146985879</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2103,6 +2271,12 @@
       <c r="R28" s="2" t="n">
         <v>0.002327385570209553</v>
       </c>
+      <c r="S28" s="1" t="n">
+        <v>1.295</v>
+      </c>
+      <c r="T28" s="2" t="n">
+        <v>0.002321981424148523</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2161,6 +2335,12 @@
       <c r="R29" s="2" t="n">
         <v>0.0917214634968808</v>
       </c>
+      <c r="S29" s="1" t="n">
+        <v>0.06433999999999999</v>
+      </c>
+      <c r="T29" s="3" t="n">
+        <v>-0.006332046332046449</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2219,6 +2399,12 @@
       <c r="R30" s="2" t="n">
         <v>0.00394477317554241</v>
       </c>
+      <c r="S30" s="1" t="n">
+        <v>1.535</v>
+      </c>
+      <c r="T30" s="2" t="n">
+        <v>0.005239030779305833</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2277,6 +2463,12 @@
       <c r="R31" s="3" t="n">
         <v>-0.007831620166421907</v>
       </c>
+      <c r="S31" s="1" t="n">
+        <v>0.002033</v>
+      </c>
+      <c r="T31" s="2" t="n">
+        <v>0.002960039467192861</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2335,6 +2527,12 @@
       <c r="R32" s="3" t="n">
         <v>-0.002718734552644733</v>
       </c>
+      <c r="S32" s="1" t="n">
+        <v>0.04044</v>
+      </c>
+      <c r="T32" s="2" t="n">
+        <v>0.00223048327137546</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2393,6 +2591,12 @@
       <c r="R33" s="2" t="n">
         <v>0.002030456852791795</v>
       </c>
+      <c r="S33" s="1" t="n">
+        <v>0.0987</v>
+      </c>
+      <c r="T33" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2451,6 +2655,12 @@
       <c r="R34" s="3" t="n">
         <v>-0.004761904761904767</v>
       </c>
+      <c r="S34" s="1" t="n">
+        <v>0.1048</v>
+      </c>
+      <c r="T34" s="2" t="n">
+        <v>0.002870813397129269</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2509,6 +2719,12 @@
       <c r="R35" s="3" t="n">
         <v>-0.001142857142857295</v>
       </c>
+      <c r="S35" s="1" t="n">
+        <v>0.008670000000000001</v>
+      </c>
+      <c r="T35" s="3" t="n">
+        <v>-0.008009153318077675</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2567,6 +2783,12 @@
       <c r="R36" s="2" t="n">
         <v>0.00252242152466371</v>
       </c>
+      <c r="S36" s="1" t="n">
+        <v>0.3586</v>
+      </c>
+      <c r="T36" s="2" t="n">
+        <v>0.002516074923119811</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2625,6 +2847,12 @@
       <c r="R37" s="2" t="n">
         <v>0.001888087881908787</v>
       </c>
+      <c r="S37" s="1" t="n">
+        <v>0.00584</v>
+      </c>
+      <c r="T37" s="2" t="n">
+        <v>0.0005139626520472042</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2683,6 +2911,12 @@
       <c r="R38" s="3" t="n">
         <v>-0.0003052503052501869</v>
       </c>
+      <c r="S38" s="1" t="n">
+        <v>0.26158</v>
+      </c>
+      <c r="T38" s="3" t="n">
+        <v>-0.001603053435114624</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2741,6 +2975,12 @@
       <c r="R39" s="3" t="n">
         <v>-0.007093596059113421</v>
       </c>
+      <c r="S39" s="1" t="n">
+        <v>0.05022</v>
+      </c>
+      <c r="T39" s="3" t="n">
+        <v>-0.003373685255010847</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2799,6 +3039,12 @@
       <c r="R40" s="3" t="n">
         <v>-0.005363727790814584</v>
       </c>
+      <c r="S40" s="1" t="n">
+        <v>0.14986</v>
+      </c>
+      <c r="T40" s="2" t="n">
+        <v>0.01017863161442523</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2857,6 +3103,12 @@
       <c r="R41" s="2" t="n">
         <v>0.001781472684085479</v>
       </c>
+      <c r="S41" s="1" t="n">
+        <v>0.1698</v>
+      </c>
+      <c r="T41" s="2" t="n">
+        <v>0.006520450503853099</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2915,6 +3167,12 @@
       <c r="R42" s="3" t="n">
         <v>-0.001071428571428612</v>
       </c>
+      <c r="S42" s="1" t="n">
+        <v>112.11</v>
+      </c>
+      <c r="T42" s="2" t="n">
+        <v>0.002055774043618198</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2973,6 +3231,12 @@
       <c r="R43" s="2" t="n">
         <v>0.02477672140593488</v>
       </c>
+      <c r="S43" s="1" t="n">
+        <v>0.9183</v>
+      </c>
+      <c r="T43" s="2" t="n">
+        <v>0.2908349732921</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -3031,6 +3295,12 @@
       <c r="R44" s="3" t="n">
         <v>-0.0001821825469119696</v>
       </c>
+      <c r="S44" s="1" t="n">
+        <v>54.97</v>
+      </c>
+      <c r="T44" s="2" t="n">
+        <v>0.001639941690962032</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -3089,6 +3359,12 @@
       <c r="R45" s="3" t="n">
         <v>-0.008181957538131364</v>
       </c>
+      <c r="S45" s="1" t="n">
+        <v>0.52008</v>
+      </c>
+      <c r="T45" s="2" t="n">
+        <v>0.004771932536079234</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -3147,6 +3423,12 @@
       <c r="R46" s="2" t="n">
         <v>0.0007108330963888895</v>
       </c>
+      <c r="S46" s="1" t="n">
+        <v>0.7034</v>
+      </c>
+      <c r="T46" s="3" t="n">
+        <v>-0.000710328171615208</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -3205,6 +3487,12 @@
       <c r="R47" s="2" t="n">
         <v>0.002306509482316734</v>
       </c>
+      <c r="S47" s="1" t="n">
+        <v>3.923</v>
+      </c>
+      <c r="T47" s="2" t="n">
+        <v>0.003068268984914347</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3263,6 +3551,12 @@
       <c r="R48" s="3" t="n">
         <v>-0.0007490636704120411</v>
       </c>
+      <c r="S48" s="1" t="n">
+        <v>0.1599</v>
+      </c>
+      <c r="T48" s="3" t="n">
+        <v>-0.00112443778110953</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3321,6 +3615,12 @@
       <c r="R49" s="2" t="n">
         <v>0.001686056314280828</v>
       </c>
+      <c r="S49" s="1" t="n">
+        <v>0.06049</v>
+      </c>
+      <c r="T49" s="2" t="n">
+        <v>0.01817875778488478</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3379,6 +3679,12 @@
       <c r="R50" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="S50" s="1" t="n">
+        <v>0.0387</v>
+      </c>
+      <c r="T50" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3437,6 +3743,12 @@
       <c r="R51" s="3" t="n">
         <v>-0.002347045577087819</v>
       </c>
+      <c r="S51" s="1" t="n">
+        <v>0.29937</v>
+      </c>
+      <c r="T51" s="3" t="n">
+        <v>-0.04825941821649967</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3495,6 +3807,12 @@
       <c r="R52" s="3" t="n">
         <v>-0.00408024481468881</v>
       </c>
+      <c r="S52" s="1" t="n">
+        <v>0.2925</v>
+      </c>
+      <c r="T52" s="3" t="n">
+        <v>-0.001365653806760025</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3553,6 +3871,12 @@
       <c r="R53" s="2" t="n">
         <v>0.003164556962025319</v>
       </c>
+      <c r="S53" s="1" t="n">
+        <v>0.1582</v>
+      </c>
+      <c r="T53" s="3" t="n">
+        <v>-0.001892744479495235</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3611,6 +3935,12 @@
       <c r="R54" s="3" t="n">
         <v>-0.001683559525854631</v>
       </c>
+      <c r="S54" s="1" t="n">
+        <v>0.29106</v>
+      </c>
+      <c r="T54" s="2" t="n">
+        <v>0.00172081497797357</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3669,6 +3999,12 @@
       <c r="R55" s="3" t="n">
         <v>-0.0009797060881735565</v>
       </c>
+      <c r="S55" s="1" t="n">
+        <v>0.007154</v>
+      </c>
+      <c r="T55" s="2" t="n">
+        <v>0.00224152423648074</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3727,6 +4063,12 @@
       <c r="R56" s="3" t="n">
         <v>-0.006376195536663233</v>
       </c>
+      <c r="S56" s="1" t="n">
+        <v>0.02793</v>
+      </c>
+      <c r="T56" s="3" t="n">
+        <v>-0.00427807486631011</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3785,6 +4127,12 @@
       <c r="R57" s="3" t="n">
         <v>-0.001891700165523851</v>
       </c>
+      <c r="S57" s="1" t="n">
+        <v>0.04209</v>
+      </c>
+      <c r="T57" s="3" t="n">
+        <v>-0.002842928216062429</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3843,6 +4191,12 @@
       <c r="R58" s="2" t="n">
         <v>0.02214983713355049</v>
       </c>
+      <c r="S58" s="1" t="n">
+        <v>0.04997</v>
+      </c>
+      <c r="T58" s="2" t="n">
+        <v>0.06161036753770979</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3901,6 +4255,12 @@
       <c r="R59" s="3" t="n">
         <v>-0.000650195058517628</v>
       </c>
+      <c r="S59" s="1" t="n">
+        <v>1.537</v>
+      </c>
+      <c r="T59" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3959,6 +4319,12 @@
       <c r="R60" s="2" t="n">
         <v>0.005847953216374284</v>
       </c>
+      <c r="S60" s="1" t="n">
+        <v>0.00344</v>
+      </c>
+      <c r="T60" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -4017,6 +4383,12 @@
       <c r="R61" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="S61" s="1" t="n">
+        <v>0.1554</v>
+      </c>
+      <c r="T61" s="2" t="n">
+        <v>0.003875968992248173</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -4075,6 +4447,12 @@
       <c r="R62" s="2" t="n">
         <v>0.002615518744550908</v>
       </c>
+      <c r="S62" s="1" t="n">
+        <v>1.146</v>
+      </c>
+      <c r="T62" s="3" t="n">
+        <v>-0.003478260869565221</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -4133,6 +4511,12 @@
       <c r="R63" s="2" t="n">
         <v>0.000717566016073559</v>
       </c>
+      <c r="S63" s="1" t="n">
+        <v>0.6999</v>
+      </c>
+      <c r="T63" s="2" t="n">
+        <v>0.003728667718342085</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -4191,6 +4575,12 @@
       <c r="R64" s="3" t="n">
         <v>-0.00509164969450106</v>
       </c>
+      <c r="S64" s="1" t="n">
+        <v>2.937</v>
+      </c>
+      <c r="T64" s="2" t="n">
+        <v>0.002047082906857654</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -4249,6 +4639,12 @@
       <c r="R65" s="3" t="n">
         <v>-0.002513615416841121</v>
       </c>
+      <c r="S65" s="1" t="n">
+        <v>0.0239</v>
+      </c>
+      <c r="T65" s="2" t="n">
+        <v>0.003779924401511961</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -4307,6 +4703,12 @@
       <c r="R66" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="S66" s="1" t="n">
+        <v>0.1013</v>
+      </c>
+      <c r="T66" s="2" t="n">
+        <v>0.0009881422924901469</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -4365,6 +4767,12 @@
       <c r="R67" s="3" t="n">
         <v>-0.001777899343544857</v>
       </c>
+      <c r="S67" s="1" t="n">
+        <v>0.007326</v>
+      </c>
+      <c r="T67" s="2" t="n">
+        <v>0.003699136868064134</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -4423,6 +4831,12 @@
       <c r="R68" s="3" t="n">
         <v>-0.0005282620179608036</v>
       </c>
+      <c r="S68" s="1" t="n">
+        <v>18.79</v>
+      </c>
+      <c r="T68" s="3" t="n">
+        <v>-0.006871035940803517</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -4481,6 +4895,12 @@
       <c r="R69" s="3" t="n">
         <v>-0.002961865975564614</v>
       </c>
+      <c r="S69" s="1" t="n">
+        <v>0.05397</v>
+      </c>
+      <c r="T69" s="2" t="n">
+        <v>0.002042331971778667</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4539,6 +4959,12 @@
       <c r="R70" s="3" t="n">
         <v>-0.004201680672268912</v>
       </c>
+      <c r="S70" s="1" t="n">
+        <v>0.238</v>
+      </c>
+      <c r="T70" s="2" t="n">
+        <v>0.004219409282700426</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4597,6 +5023,12 @@
       <c r="R71" s="3" t="n">
         <v>-0.006843455945252359</v>
       </c>
+      <c r="S71" s="1" t="n">
+        <v>5.791</v>
+      </c>
+      <c r="T71" s="3" t="n">
+        <v>-0.002411714039620904</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -4655,6 +5087,12 @@
       <c r="R72" s="3" t="n">
         <v>-0.002123142250530837</v>
       </c>
+      <c r="S72" s="1" t="n">
+        <v>0.001862</v>
+      </c>
+      <c r="T72" s="3" t="n">
+        <v>-0.009574468085106385</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4713,6 +5151,12 @@
       <c r="R73" s="2" t="n">
         <v>0.001812753252292637</v>
       </c>
+      <c r="S73" s="1" t="n">
+        <v>0.9421</v>
+      </c>
+      <c r="T73" s="2" t="n">
+        <v>0.002767429483768011</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -4771,6 +5215,12 @@
       <c r="R74" s="2" t="n">
         <v>0.00166389351081524</v>
       </c>
+      <c r="S74" s="1" t="n">
+        <v>0.1205</v>
+      </c>
+      <c r="T74" s="2" t="n">
+        <v>0.00083056478405318</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4829,6 +5279,12 @@
       <c r="R75" s="3" t="n">
         <v>-0.002583172476439106</v>
       </c>
+      <c r="S75" s="1" t="n">
+        <v>351.76</v>
+      </c>
+      <c r="T75" s="2" t="n">
+        <v>0.001109941087742227</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4887,6 +5343,12 @@
       <c r="R76" s="2" t="n">
         <v>0.006249472172958404</v>
       </c>
+      <c r="S76" s="1" t="n">
+        <v>0.11926</v>
+      </c>
+      <c r="T76" s="2" t="n">
+        <v>0.0009232060428031807</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4945,6 +5407,12 @@
       <c r="R77" s="2" t="n">
         <v>0.002724795640327031</v>
       </c>
+      <c r="S77" s="1" t="n">
+        <v>0.06277000000000001</v>
+      </c>
+      <c r="T77" s="2" t="n">
+        <v>0.003356777493606168</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -5003,6 +5471,12 @@
       <c r="R78" s="2" t="n">
         <v>0.002335952431514101</v>
       </c>
+      <c r="S78" s="1" t="n">
+        <v>0.09464</v>
+      </c>
+      <c r="T78" s="2" t="n">
+        <v>0.002542372881355976</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -5061,6 +5535,12 @@
       <c r="R79" s="3" t="n">
         <v>-0.001970928800197013</v>
       </c>
+      <c r="S79" s="1" t="n">
+        <v>0.4052</v>
+      </c>
+      <c r="T79" s="2" t="n">
+        <v>0.0002468526289804714</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -5119,6 +5599,12 @@
       <c r="R80" s="2" t="n">
         <v>0.000998336106489173</v>
       </c>
+      <c r="S80" s="1" t="n">
+        <v>0.006026</v>
+      </c>
+      <c r="T80" s="2" t="n">
+        <v>0.001662234042553268</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -5177,6 +5663,12 @@
       <c r="R81" s="2" t="n">
         <v>0.01749271137026235</v>
       </c>
+      <c r="S81" s="1" t="n">
+        <v>0.1041</v>
+      </c>
+      <c r="T81" s="3" t="n">
+        <v>-0.005730659025787998</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -5235,6 +5727,12 @@
       <c r="R82" s="3" t="n">
         <v>-0.002938295788442652</v>
       </c>
+      <c r="S82" s="1" t="n">
+        <v>0.1019</v>
+      </c>
+      <c r="T82" s="2" t="n">
+        <v>0.0009823182711198709</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -5293,6 +5791,12 @@
       <c r="R83" s="3" t="n">
         <v>-0.01397692182675117</v>
       </c>
+      <c r="S83" s="1" t="n">
+        <v>0.06088</v>
+      </c>
+      <c r="T83" s="2" t="n">
+        <v>0.003461348277567083</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -5351,6 +5855,12 @@
       <c r="R84" s="2" t="n">
         <v>0.006335891486703448</v>
       </c>
+      <c r="S84" s="1" t="n">
+        <v>1.1215</v>
+      </c>
+      <c r="T84" s="3" t="n">
+        <v>-0.005497916112441238</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -5409,6 +5919,12 @@
       <c r="R85" s="3" t="n">
         <v>-0.005283018867924444</v>
       </c>
+      <c r="S85" s="1" t="n">
+        <v>0.01315</v>
+      </c>
+      <c r="T85" s="3" t="n">
+        <v>-0.00227617602427925</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -5467,6 +5983,12 @@
       <c r="R86" s="2" t="n">
         <v>0.005357142857142846</v>
       </c>
+      <c r="S86" s="1" t="n">
+        <v>0.01683</v>
+      </c>
+      <c r="T86" s="3" t="n">
+        <v>-0.003552397868561135</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -5525,6 +6047,12 @@
       <c r="R87" s="3" t="n">
         <v>-0.0004817535830424347</v>
       </c>
+      <c r="S87" s="1" t="n">
+        <v>8.314</v>
+      </c>
+      <c r="T87" s="2" t="n">
+        <v>0.001807446680322999</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -5583,6 +6111,12 @@
       <c r="R88" s="2" t="n">
         <v>0.001833396013538827</v>
       </c>
+      <c r="S88" s="1" t="n">
+        <v>2.1397</v>
+      </c>
+      <c r="T88" s="2" t="n">
+        <v>0.004035474637511117</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -5641,6 +6175,12 @@
       <c r="R89" s="2" t="n">
         <v>0.00456150676868743</v>
       </c>
+      <c r="S89" s="1" t="n">
+        <v>0.006903</v>
+      </c>
+      <c r="T89" s="2" t="n">
+        <v>0.01113226893218113</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -5699,6 +6239,12 @@
       <c r="R90" s="3" t="n">
         <v>-0.003265839320705468</v>
       </c>
+      <c r="S90" s="1" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="T90" s="2" t="n">
+        <v>0.002621231979030205</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -5757,6 +6303,12 @@
       <c r="R91" s="2" t="n">
         <v>0.004484304932735414</v>
       </c>
+      <c r="S91" s="1" t="n">
+        <v>0.000223</v>
+      </c>
+      <c r="T91" s="3" t="n">
+        <v>-0.004464285714285702</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -5815,6 +6367,12 @@
       <c r="R92" s="3" t="n">
         <v>-0.01663201663201661</v>
       </c>
+      <c r="S92" s="1" t="n">
+        <v>0.05166</v>
+      </c>
+      <c r="T92" s="3" t="n">
+        <v>-0.007111281952719629</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -5873,6 +6431,12 @@
       <c r="R93" s="2" t="n">
         <v>0.0009811320754717578</v>
       </c>
+      <c r="S93" s="1" t="n">
+        <v>1.3243</v>
+      </c>
+      <c r="T93" s="3" t="n">
+        <v>-0.001507954459775316</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -5931,6 +6495,12 @@
       <c r="R94" s="3" t="n">
         <v>-0.00641366293452572</v>
       </c>
+      <c r="S94" s="1" t="n">
+        <v>0.054177</v>
+      </c>
+      <c r="T94" s="3" t="n">
+        <v>-0.0008114937017022082</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -5989,6 +6559,12 @@
       <c r="R95" s="2" t="n">
         <v>0.001241208109226292</v>
       </c>
+      <c r="S95" s="1" t="n">
+        <v>0.2423</v>
+      </c>
+      <c r="T95" s="2" t="n">
+        <v>0.001239669421487581</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -6047,6 +6623,12 @@
       <c r="R96" s="3" t="n">
         <v>-0.001854427445526195</v>
       </c>
+      <c r="S96" s="1" t="n">
+        <v>1.0746</v>
+      </c>
+      <c r="T96" s="3" t="n">
+        <v>-0.001764979098931735</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -6105,6 +6687,12 @@
       <c r="R97" s="3" t="n">
         <v>-0.003880481179666282</v>
       </c>
+      <c r="S97" s="1" t="n">
+        <v>0.2574</v>
+      </c>
+      <c r="T97" s="2" t="n">
+        <v>0.00272691858200247</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -6163,6 +6751,12 @@
       <c r="R98" s="3" t="n">
         <v>-0.01006997781191332</v>
       </c>
+      <c r="S98" s="1" t="n">
+        <v>0.5777</v>
+      </c>
+      <c r="T98" s="3" t="n">
+        <v>-0.003965517241379257</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -6221,6 +6815,12 @@
       <c r="R99" s="3" t="n">
         <v>-0.00400933080623994</v>
       </c>
+      <c r="S99" s="1" t="n">
+        <v>0.13626</v>
+      </c>
+      <c r="T99" s="3" t="n">
+        <v>-0.002708043621459484</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -6279,6 +6879,12 @@
       <c r="R100" s="2" t="n">
         <v>0.003606557377049147</v>
       </c>
+      <c r="S100" s="1" t="n">
+        <v>0.03068</v>
+      </c>
+      <c r="T100" s="2" t="n">
+        <v>0.002286834367853663</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -6337,6 +6943,12 @@
       <c r="R101" s="2" t="n">
         <v>0.001943634596695823</v>
       </c>
+      <c r="S101" s="1" t="n">
+        <v>1.039</v>
+      </c>
+      <c r="T101" s="2" t="n">
+        <v>0.007759456838021346</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -6395,6 +7007,12 @@
       <c r="R102" s="2" t="n">
         <v>0.001822323462414504</v>
       </c>
+      <c r="S102" s="1" t="n">
+        <v>0.02212</v>
+      </c>
+      <c r="T102" s="2" t="n">
+        <v>0.005911778080945959</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -6453,6 +7071,12 @@
       <c r="R103" s="2" t="n">
         <v>0.0005120327700972654</v>
       </c>
+      <c r="S103" s="1" t="n">
+        <v>0.01959</v>
+      </c>
+      <c r="T103" s="2" t="n">
+        <v>0.002558853633572233</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -6511,6 +7135,12 @@
       <c r="R104" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="S104" s="1" t="n">
+        <v>2.997</v>
+      </c>
+      <c r="T104" s="2" t="n">
+        <v>0.00234113712374571</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -6569,6 +7199,12 @@
       <c r="R105" s="2" t="n">
         <v>0.0009239297813366535</v>
       </c>
+      <c r="S105" s="1" t="n">
+        <v>32.55</v>
+      </c>
+      <c r="T105" s="2" t="n">
+        <v>0.001538461538461451</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -6627,6 +7263,12 @@
       <c r="R106" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="S106" s="1" t="n">
+        <v>0.1666</v>
+      </c>
+      <c r="T106" s="2" t="n">
+        <v>0.003010234798314271</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -6685,6 +7327,12 @@
       <c r="R107" s="3" t="n">
         <v>-0.007528500752850082</v>
       </c>
+      <c r="S107" s="1" t="n">
+        <v>0.4651</v>
+      </c>
+      <c r="T107" s="2" t="n">
+        <v>0.008019072388383262</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -6743,6 +7391,12 @@
       <c r="R108" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="S108" s="1" t="n">
+        <v>0.3358</v>
+      </c>
+      <c r="T108" s="2" t="n">
+        <v>0.00238805970149244</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -6801,6 +7455,12 @@
       <c r="R109" s="2" t="n">
         <v>0.0004314063848144477</v>
       </c>
+      <c r="S109" s="1" t="n">
+        <v>0.2264</v>
+      </c>
+      <c r="T109" s="3" t="n">
+        <v>-0.02371711944803797</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -6859,6 +7519,12 @@
       <c r="R110" s="2" t="n">
         <v>0.0006635700066356731</v>
       </c>
+      <c r="S110" s="1" t="n">
+        <v>0.01517</v>
+      </c>
+      <c r="T110" s="2" t="n">
+        <v>0.005968169761273197</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -6917,6 +7583,12 @@
       <c r="R111" s="2" t="n">
         <v>0.001089918256130791</v>
       </c>
+      <c r="S111" s="1" t="n">
+        <v>1.834</v>
+      </c>
+      <c r="T111" s="3" t="n">
+        <v>-0.001633097441480616</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -6975,6 +7647,12 @@
       <c r="R112" s="3" t="n">
         <v>-0.003635419371591826</v>
       </c>
+      <c r="S112" s="1" t="n">
+        <v>0.03839</v>
+      </c>
+      <c r="T112" s="2" t="n">
+        <v>0.0005212405525149644</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -7033,6 +7711,12 @@
       <c r="R113" s="2" t="n">
         <v>0.001872659176029964</v>
       </c>
+      <c r="S113" s="1" t="n">
+        <v>4.295</v>
+      </c>
+      <c r="T113" s="2" t="n">
+        <v>0.003504672897196187</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -7091,6 +7775,12 @@
       <c r="R114" s="2" t="n">
         <v>0.02204004838059402</v>
       </c>
+      <c r="S114" s="1" t="n">
+        <v>0.007571</v>
+      </c>
+      <c r="T114" s="3" t="n">
+        <v>-0.004470742932281417</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -7149,6 +7839,12 @@
       <c r="R115" s="3" t="n">
         <v>-0.0008075098415263008</v>
       </c>
+      <c r="S115" s="1" t="n">
+        <v>0.09923</v>
+      </c>
+      <c r="T115" s="2" t="n">
+        <v>0.002424487321951754</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -7207,6 +7903,12 @@
       <c r="R116" s="2" t="n">
         <v>0.0004833252779120151</v>
       </c>
+      <c r="S116" s="1" t="n">
+        <v>0.08304</v>
+      </c>
+      <c r="T116" s="2" t="n">
+        <v>0.002898550724637731</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -7265,6 +7967,12 @@
       <c r="R117" s="2" t="n">
         <v>0.001332889036987709</v>
       </c>
+      <c r="S117" s="1" t="n">
+        <v>0.3009</v>
+      </c>
+      <c r="T117" s="2" t="n">
+        <v>0.001331114808652284</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -7323,6 +8031,12 @@
       <c r="R118" s="2" t="n">
         <v>0.0008833922261483739</v>
       </c>
+      <c r="S118" s="1" t="n">
+        <v>0.02261</v>
+      </c>
+      <c r="T118" s="3" t="n">
+        <v>-0.002206531332744835</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -7381,6 +8095,12 @@
       <c r="R119" s="2" t="n">
         <v>0.00324675324675325</v>
       </c>
+      <c r="S119" s="1" t="n">
+        <v>0.1542</v>
+      </c>
+      <c r="T119" s="3" t="n">
+        <v>-0.0019417475728155</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -7439,6 +8159,12 @@
       <c r="R120" s="3" t="n">
         <v>-0.04649708090075065</v>
       </c>
+      <c r="S120" s="1" t="n">
+        <v>0.00448</v>
+      </c>
+      <c r="T120" s="3" t="n">
+        <v>-0.02033675923901163</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -7497,6 +8223,12 @@
       <c r="R121" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="S121" s="1" t="n">
+        <v>0.4392</v>
+      </c>
+      <c r="T121" s="2" t="n">
+        <v>0.01431870669745955</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -7555,6 +8287,12 @@
       <c r="R122" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="S122" s="1" t="n">
+        <v>0.778</v>
+      </c>
+      <c r="T122" s="2" t="n">
+        <v>0.001287001287001288</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -7613,6 +8351,12 @@
       <c r="R123" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="S123" s="1" t="n">
+        <v>0.0866</v>
+      </c>
+      <c r="T123" s="2" t="n">
+        <v>0.002314814814814721</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -7671,6 +8415,12 @@
       <c r="R124" s="3" t="n">
         <v>-0.002437043054427337</v>
       </c>
+      <c r="S124" s="1" t="n">
+        <v>0.01235</v>
+      </c>
+      <c r="T124" s="2" t="n">
+        <v>0.005700325732899073</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -7729,6 +8479,12 @@
       <c r="R125" s="2" t="n">
         <v>0.00113017569094831</v>
       </c>
+      <c r="S125" s="1" t="n">
+        <v>0.09764</v>
+      </c>
+      <c r="T125" s="2" t="n">
+        <v>0.00205254515599349</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -7787,6 +8543,12 @@
       <c r="R126" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="S126" s="1" t="n">
+        <v>0.04681</v>
+      </c>
+      <c r="T126" s="2" t="n">
+        <v>0.001926369863013694</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -7845,6 +8607,12 @@
       <c r="R127" s="2" t="n">
         <v>0.01257861635220114</v>
       </c>
+      <c r="S127" s="1" t="n">
+        <v>3.25e-05</v>
+      </c>
+      <c r="T127" s="2" t="n">
+        <v>0.009316770186335421</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -7903,6 +8671,12 @@
       <c r="R128" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="S128" s="1" t="n">
+        <v>0.5643</v>
+      </c>
+      <c r="T128" s="3" t="n">
+        <v>-0.001415678640948545</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -7961,6 +8735,12 @@
       <c r="R129" s="3" t="n">
         <v>-0.003511986562834142</v>
       </c>
+      <c r="S129" s="1" t="n">
+        <v>0.06516</v>
+      </c>
+      <c r="T129" s="3" t="n">
+        <v>-0.00153233220962309</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -8019,6 +8799,12 @@
       <c r="R130" s="2" t="n">
         <v>0.008249463784853826</v>
       </c>
+      <c r="S130" s="1" t="n">
+        <v>0.0006072</v>
+      </c>
+      <c r="T130" s="3" t="n">
+        <v>-0.006381934216985653</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -8077,6 +8863,12 @@
       <c r="R131" s="2" t="n">
         <v>0.01149425287356323</v>
       </c>
+      <c r="S131" s="1" t="n">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="T131" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -8135,6 +8927,12 @@
       <c r="R132" s="3" t="n">
         <v>-0.001996007984031901</v>
       </c>
+      <c r="S132" s="1" t="n">
+        <v>0.3009</v>
+      </c>
+      <c r="T132" s="2" t="n">
+        <v>0.00300000000000004</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -8193,6 +8991,12 @@
       <c r="R133" s="2" t="n">
         <v>0.0006038647342997018</v>
       </c>
+      <c r="S133" s="1" t="n">
+        <v>0.03366</v>
+      </c>
+      <c r="T133" s="2" t="n">
+        <v>0.01569100784550391</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -8251,6 +9055,12 @@
       <c r="R134" s="2" t="n">
         <v>0.0009005264616238501</v>
       </c>
+      <c r="S134" s="1" t="n">
+        <v>0.14443</v>
+      </c>
+      <c r="T134" s="3" t="n">
+        <v>-0.0004152536507717108</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -8309,6 +9119,12 @@
       <c r="R135" s="2" t="n">
         <v>0.001015572105619458</v>
       </c>
+      <c r="S135" s="1" t="n">
+        <v>0.0297</v>
+      </c>
+      <c r="T135" s="2" t="n">
+        <v>0.004396347649644966</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -8367,6 +9183,12 @@
       <c r="R136" s="3" t="n">
         <v>-0.002123142250530866</v>
       </c>
+      <c r="S136" s="1" t="n">
+        <v>28.23</v>
+      </c>
+      <c r="T136" s="2" t="n">
+        <v>0.001063829787234083</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -8425,6 +9247,12 @@
       <c r="R137" s="2" t="n">
         <v>0.001395673412421527</v>
       </c>
+      <c r="S137" s="1" t="n">
+        <v>0.0004335</v>
+      </c>
+      <c r="T137" s="2" t="n">
+        <v>0.006968641114982622</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -8483,6 +9311,12 @@
       <c r="R138" s="3" t="n">
         <v>-0.002406779661016887</v>
       </c>
+      <c r="S138" s="1" t="n">
+        <v>0.029454</v>
+      </c>
+      <c r="T138" s="2" t="n">
+        <v>0.0008495021917156789</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -8541,6 +9375,12 @@
       <c r="R139" s="2" t="n">
         <v>0.002706359945872763</v>
       </c>
+      <c r="S139" s="1" t="n">
+        <v>0.09621</v>
+      </c>
+      <c r="T139" s="3" t="n">
+        <v>-0.001245717844908078</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -8599,6 +9439,12 @@
       <c r="R140" s="2" t="n">
         <v>0.001685393258426937</v>
       </c>
+      <c r="S140" s="1" t="n">
+        <v>0.3619</v>
+      </c>
+      <c r="T140" s="2" t="n">
+        <v>0.01486259113853064</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -8657,6 +9503,12 @@
       <c r="R141" s="2" t="n">
         <v>0.004179331306990843</v>
       </c>
+      <c r="S141" s="1" t="n">
+        <v>0.02632</v>
+      </c>
+      <c r="T141" s="3" t="n">
+        <v>-0.004161937192584147</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -8715,6 +9567,12 @@
       <c r="R142" s="2" t="n">
         <v>0.003088803088802963</v>
       </c>
+      <c r="S142" s="1" t="n">
+        <v>0.07858999999999999</v>
+      </c>
+      <c r="T142" s="2" t="n">
+        <v>0.008339748524506002</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -8773,6 +9631,12 @@
       <c r="R143" s="3" t="n">
         <v>-0.001465284039675285</v>
       </c>
+      <c r="S143" s="1" t="n">
+        <v>0.08840000000000001</v>
+      </c>
+      <c r="T143" s="3" t="n">
+        <v>-0.002144711592730508</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -8831,6 +9695,12 @@
       <c r="R144" s="3" t="n">
         <v>-0.004911591355599185</v>
       </c>
+      <c r="S144" s="1" t="n">
+        <v>0.02047</v>
+      </c>
+      <c r="T144" s="2" t="n">
+        <v>0.01036525172754187</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -8889,6 +9759,12 @@
       <c r="R145" s="2" t="n">
         <v>8.75503414462977e-05</v>
       </c>
+      <c r="S145" s="1" t="n">
+        <v>0.11459</v>
+      </c>
+      <c r="T145" s="2" t="n">
+        <v>0.003151536373982309</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -8947,6 +9823,12 @@
       <c r="R146" s="2" t="n">
         <v>0.002316346790205091</v>
       </c>
+      <c r="S146" s="1" t="n">
+        <v>0.3037</v>
+      </c>
+      <c r="T146" s="2" t="n">
+        <v>0.002641135688346064</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -9005,6 +9887,12 @@
       <c r="R147" s="2" t="n">
         <v>0.008196721311475417</v>
       </c>
+      <c r="S147" s="1" t="n">
+        <v>0.123</v>
+      </c>
+      <c r="T147" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -9063,6 +9951,12 @@
       <c r="R148" s="2" t="n">
         <v>0.002866796355073231</v>
       </c>
+      <c r="S148" s="1" t="n">
+        <v>1.9495</v>
+      </c>
+      <c r="T148" s="3" t="n">
+        <v>-0.00484941296579891</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -9121,6 +10015,12 @@
       <c r="R149" s="2" t="n">
         <v>0.00178716490658</v>
       </c>
+      <c r="S149" s="1" t="n">
+        <v>0.0618</v>
+      </c>
+      <c r="T149" s="2" t="n">
+        <v>0.002270515731430445</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -9179,6 +10079,12 @@
       <c r="R150" s="2" t="n">
         <v>0.02168525402726148</v>
       </c>
+      <c r="S150" s="1" t="n">
+        <v>0.1639</v>
+      </c>
+      <c r="T150" s="3" t="n">
+        <v>-0.006064281382656161</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -9237,6 +10143,12 @@
       <c r="R151" s="2" t="n">
         <v>0.0008995502248877001</v>
       </c>
+      <c r="S151" s="1" t="n">
+        <v>6.697e-05</v>
+      </c>
+      <c r="T151" s="2" t="n">
+        <v>0.003145596165368479</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -9295,6 +10207,12 @@
       <c r="R152" s="2" t="n">
         <v>0.003396739130434762</v>
       </c>
+      <c r="S152" s="1" t="n">
+        <v>0.01473</v>
+      </c>
+      <c r="T152" s="3" t="n">
+        <v>-0.002708192281652005</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -9353,6 +10271,12 @@
       <c r="R153" s="3" t="n">
         <v>-0.0004786979415988317</v>
       </c>
+      <c r="S153" s="1" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="T153" s="2" t="n">
+        <v>0.005747126436781707</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -9411,6 +10335,12 @@
       <c r="R154" s="2" t="n">
         <v>0.001684068710003409</v>
       </c>
+      <c r="S154" s="1" t="n">
+        <v>0.0005967</v>
+      </c>
+      <c r="T154" s="2" t="n">
+        <v>0.003194351042367169</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -9469,6 +10399,12 @@
       <c r="R155" s="2" t="n">
         <v>0.001245640259093037</v>
       </c>
+      <c r="S155" s="1" t="n">
+        <v>0.04024</v>
+      </c>
+      <c r="T155" s="2" t="n">
+        <v>0.001244090569793517</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -9527,6 +10463,12 @@
       <c r="R156" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="S156" s="1" t="n">
+        <v>0.01889</v>
+      </c>
+      <c r="T156" s="2" t="n">
+        <v>0.000529661016949131</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -9585,6 +10527,12 @@
       <c r="R157" s="3" t="n">
         <v>-0.003561580882352995</v>
       </c>
+      <c r="S157" s="1" t="n">
+        <v>0.08679000000000001</v>
+      </c>
+      <c r="T157" s="2" t="n">
+        <v>0.0006918021445867001</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -9643,6 +10591,12 @@
       <c r="R158" s="2" t="n">
         <v>0.01210305572198926</v>
       </c>
+      <c r="S158" s="1" t="n">
+        <v>0.008281999999999999</v>
+      </c>
+      <c r="T158" s="3" t="n">
+        <v>-0.01941747572815545</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -9701,6 +10655,12 @@
       <c r="R159" s="2" t="n">
         <v>0.00201369311316951</v>
       </c>
+      <c r="S159" s="1" t="n">
+        <v>2.497</v>
+      </c>
+      <c r="T159" s="2" t="n">
+        <v>0.003617363344051406</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -9759,6 +10719,12 @@
       <c r="R160" s="3" t="n">
         <v>-0.001170960187353501</v>
       </c>
+      <c r="S160" s="1" t="n">
+        <v>1.2822</v>
+      </c>
+      <c r="T160" s="2" t="n">
+        <v>0.002110199296600176</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -9817,6 +10783,12 @@
       <c r="R161" s="3" t="n">
         <v>-0.001063264221158984</v>
       </c>
+      <c r="S161" s="1" t="n">
+        <v>0.007509</v>
+      </c>
+      <c r="T161" s="3" t="n">
+        <v>-0.0009313464608834568</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -9875,6 +10847,12 @@
       <c r="R162" s="3" t="n">
         <v>-0.02103521626093135</v>
       </c>
+      <c r="S162" s="1" t="n">
+        <v>0.004142</v>
+      </c>
+      <c r="T162" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -9933,6 +10911,12 @@
       <c r="R163" s="2" t="n">
         <v>0.002083333333333248</v>
       </c>
+      <c r="S163" s="1" t="n">
+        <v>0.09619999999999999</v>
+      </c>
+      <c r="T163" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -9991,6 +10975,12 @@
       <c r="R164" s="3" t="n">
         <v>-0.001156403584851146</v>
       </c>
+      <c r="S164" s="1" t="n">
+        <v>1.3849</v>
+      </c>
+      <c r="T164" s="2" t="n">
+        <v>0.002098408104196907</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -10049,6 +11039,12 @@
       <c r="R165" s="3" t="n">
         <v>-0.001573731444855698</v>
       </c>
+      <c r="S165" s="1" t="n">
+        <v>0.023543</v>
+      </c>
+      <c r="T165" s="2" t="n">
+        <v>0.002939422339609913</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -10107,6 +11103,12 @@
       <c r="R166" s="2" t="n">
         <v>0.01309264034913709</v>
       </c>
+      <c r="S166" s="1" t="n">
+        <v>0.005159</v>
+      </c>
+      <c r="T166" s="2" t="n">
+        <v>0.01018210299588799</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -10165,6 +11167,12 @@
       <c r="R167" s="2" t="n">
         <v>0.007001522070015253</v>
       </c>
+      <c r="S167" s="1" t="n">
+        <v>0.0667</v>
+      </c>
+      <c r="T167" s="2" t="n">
+        <v>0.008162031438935895</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -10223,6 +11231,12 @@
       <c r="R168" s="3" t="n">
         <v>-0.001050420168067257</v>
       </c>
+      <c r="S168" s="1" t="n">
+        <v>0.0949</v>
+      </c>
+      <c r="T168" s="3" t="n">
+        <v>-0.002103049421661469</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -10281,6 +11295,12 @@
       <c r="R169" s="3" t="n">
         <v>-0.00131061598951511</v>
       </c>
+      <c r="S169" s="1" t="n">
+        <v>0.03805</v>
+      </c>
+      <c r="T169" s="3" t="n">
+        <v>-0.001312335958005287</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -10339,6 +11359,12 @@
       <c r="R170" s="2" t="n">
         <v>0.00112422709387299</v>
       </c>
+      <c r="S170" s="1" t="n">
+        <v>0.007142</v>
+      </c>
+      <c r="T170" s="2" t="n">
+        <v>0.002526670409882059</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -10397,6 +11423,12 @@
       <c r="R171" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="S171" s="1" t="n">
+        <v>0.341</v>
+      </c>
+      <c r="T171" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -10455,6 +11487,12 @@
       <c r="R172" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="S172" s="1" t="n">
+        <v>5.452</v>
+      </c>
+      <c r="T172" s="2" t="n">
+        <v>0.0005505597357313478</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -10513,6 +11551,12 @@
       <c r="R173" s="2" t="n">
         <v>0.000881057268722431</v>
       </c>
+      <c r="S173" s="1" t="n">
+        <v>0.04561</v>
+      </c>
+      <c r="T173" s="2" t="n">
+        <v>0.003741197183098515</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -10571,6 +11615,12 @@
       <c r="R174" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="S174" s="1" t="n">
+        <v>0.03899</v>
+      </c>
+      <c r="T174" s="3" t="n">
+        <v>-0.0002564102564103349</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -10629,6 +11679,12 @@
       <c r="R175" s="2" t="n">
         <v>0.004846526655896472</v>
       </c>
+      <c r="S175" s="1" t="n">
+        <v>0.005622</v>
+      </c>
+      <c r="T175" s="2" t="n">
+        <v>0.004287245444801819</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -10687,6 +11743,12 @@
       <c r="R176" s="2" t="n">
         <v>0.001324503311258224</v>
       </c>
+      <c r="S176" s="1" t="n">
+        <v>0.00755</v>
+      </c>
+      <c r="T176" s="3" t="n">
+        <v>-0.001322751322751269</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -10745,6 +11807,12 @@
       <c r="R177" s="2" t="n">
         <v>0.006307339449541227</v>
       </c>
+      <c r="S177" s="1" t="n">
+        <v>1.777</v>
+      </c>
+      <c r="T177" s="2" t="n">
+        <v>0.01253561253561255</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -10803,6 +11871,12 @@
       <c r="R178" s="3" t="n">
         <v>-6.402868485077768e-05</v>
       </c>
+      <c r="S178" s="1" t="n">
+        <v>15.677</v>
+      </c>
+      <c r="T178" s="2" t="n">
+        <v>0.003841967087148538</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -10861,6 +11935,12 @@
       <c r="R179" s="2" t="n">
         <v>0.003225806451612906</v>
       </c>
+      <c r="S179" s="1" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="T179" s="2" t="n">
+        <v>0.003215434083601289</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -10919,6 +11999,12 @@
       <c r="R180" s="2" t="n">
         <v>0.003403816400206404</v>
       </c>
+      <c r="S180" s="1" t="n">
+        <v>0.09795</v>
+      </c>
+      <c r="T180" s="2" t="n">
+        <v>0.006887335526315687</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -10977,6 +12063,12 @@
       <c r="R181" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="S181" s="1" t="n">
+        <v>0.1875</v>
+      </c>
+      <c r="T181" s="2" t="n">
+        <v>0.002137894174238437</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -11035,6 +12127,12 @@
       <c r="R182" s="2" t="n">
         <v>0.0008424599831508245</v>
       </c>
+      <c r="S182" s="1" t="n">
+        <v>0.0592</v>
+      </c>
+      <c r="T182" s="3" t="n">
+        <v>-0.003367003367003346</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -11093,6 +12191,12 @@
       <c r="R183" s="3" t="n">
         <v>-0.0008326394671107071</v>
       </c>
+      <c r="S183" s="1" t="n">
+        <v>0.01203</v>
+      </c>
+      <c r="T183" s="2" t="n">
+        <v>0.002500000000000043</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -11151,6 +12255,12 @@
       <c r="R184" s="3" t="n">
         <v>-0.001865671641791131</v>
       </c>
+      <c r="S184" s="1" t="n">
+        <v>0.02145</v>
+      </c>
+      <c r="T184" s="2" t="n">
+        <v>0.002336448598130908</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -11209,6 +12319,12 @@
       <c r="R185" s="2" t="n">
         <v>0.002754820936639121</v>
       </c>
+      <c r="S185" s="1" t="n">
+        <v>0.365</v>
+      </c>
+      <c r="T185" s="2" t="n">
+        <v>0.00274725274725275</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -11267,6 +12383,12 @@
       <c r="R186" s="2" t="n">
         <v>0.00406770764991468</v>
       </c>
+      <c r="S186" s="1" t="n">
+        <v>0.007649</v>
+      </c>
+      <c r="T186" s="3" t="n">
+        <v>-0.0003920543648718676</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -11325,6 +12447,12 @@
       <c r="R187" s="3" t="n">
         <v>-0.001861504095309011</v>
       </c>
+      <c r="S187" s="1" t="n">
+        <v>0.2683</v>
+      </c>
+      <c r="T187" s="2" t="n">
+        <v>0.0007459903021259902</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -11383,6 +12511,12 @@
       <c r="R188" s="2" t="n">
         <v>0.0008146639511202711</v>
       </c>
+      <c r="S188" s="1" t="n">
+        <v>0.04929</v>
+      </c>
+      <c r="T188" s="2" t="n">
+        <v>0.003052503052502999</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -11441,6 +12575,12 @@
       <c r="R189" s="3" t="n">
         <v>-0.001956181533646324</v>
       </c>
+      <c r="S189" s="1" t="n">
+        <v>0.2558</v>
+      </c>
+      <c r="T189" s="2" t="n">
+        <v>0.00274402195217575</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -11499,6 +12639,12 @@
       <c r="R190" s="2" t="n">
         <v>0.002115282919090391</v>
       </c>
+      <c r="S190" s="1" t="n">
+        <v>0.5693</v>
+      </c>
+      <c r="T190" s="2" t="n">
+        <v>0.001407211961301711</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -11557,6 +12703,12 @@
       <c r="R191" s="3" t="n">
         <v>-0.0008289124668434837</v>
       </c>
+      <c r="S191" s="1" t="n">
+        <v>6.036</v>
+      </c>
+      <c r="T191" s="2" t="n">
+        <v>0.001493280238924747</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -11615,6 +12767,12 @@
       <c r="R192" s="2" t="n">
         <v>0.002281151981750691</v>
       </c>
+      <c r="S192" s="1" t="n">
+        <v>0.3496</v>
+      </c>
+      <c r="T192" s="3" t="n">
+        <v>-0.005405405405405284</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -11673,6 +12831,12 @@
       <c r="R193" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="S193" s="1" t="n">
+        <v>0.0641</v>
+      </c>
+      <c r="T193" s="2" t="n">
+        <v>0.003129890453834206</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -11731,6 +12895,12 @@
       <c r="R194" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="S194" s="1" t="n">
+        <v>0.0174</v>
+      </c>
+      <c r="T194" s="3" t="n">
+        <v>-0.00172117039586932</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -11789,6 +12959,12 @@
       <c r="R195" s="2" t="n">
         <v>0.0004709206498703806</v>
       </c>
+      <c r="S195" s="1" t="n">
+        <v>0.0008503</v>
+      </c>
+      <c r="T195" s="2" t="n">
+        <v>0.0005883737349965479</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -11847,6 +13023,12 @@
       <c r="R196" s="2" t="n">
         <v>0.0009881422924900355</v>
       </c>
+      <c r="S196" s="1" t="n">
+        <v>0.001093</v>
+      </c>
+      <c r="T196" s="2" t="n">
+        <v>0.07897334649555775</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -11905,6 +13087,12 @@
       <c r="R197" s="2" t="n">
         <v>0.002476780185758574</v>
       </c>
+      <c r="S197" s="1" t="n">
+        <v>0.0001625</v>
+      </c>
+      <c r="T197" s="2" t="n">
+        <v>0.003705991352686766</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -11963,6 +13151,12 @@
       <c r="R198" s="3" t="n">
         <v>-0.0006928406466512964</v>
       </c>
+      <c r="S198" s="1" t="n">
+        <v>4.342</v>
+      </c>
+      <c r="T198" s="2" t="n">
+        <v>0.003466605038132582</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -12021,6 +13215,12 @@
       <c r="R199" s="3" t="n">
         <v>-0.001226241569589244</v>
       </c>
+      <c r="S199" s="1" t="n">
+        <v>0.1627</v>
+      </c>
+      <c r="T199" s="3" t="n">
+        <v>-0.00122774708410054</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -12079,6 +13279,12 @@
       <c r="R200" s="3" t="n">
         <v>-0.002601653308715665</v>
       </c>
+      <c r="S200" s="1" t="n">
+        <v>0.023566</v>
+      </c>
+      <c r="T200" s="3" t="n">
+        <v>-0.008540535992258754</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -12137,6 +13343,12 @@
       <c r="R201" s="2" t="n">
         <v>0.001305057096247908</v>
       </c>
+      <c r="S201" s="1" t="n">
+        <v>0.12347</v>
+      </c>
+      <c r="T201" s="2" t="n">
+        <v>0.005783642880417093</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -12195,6 +13407,12 @@
       <c r="R202" s="2" t="n">
         <v>0.002175489485134192</v>
       </c>
+      <c r="S202" s="1" t="n">
+        <v>0.01382</v>
+      </c>
+      <c r="T202" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -12253,6 +13471,12 @@
       <c r="R203" s="2" t="n">
         <v>0.003914851969659907</v>
       </c>
+      <c r="S203" s="1" t="n">
+        <v>0.04108</v>
+      </c>
+      <c r="T203" s="2" t="n">
+        <v>0.001218620521569618</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -12311,6 +13535,12 @@
       <c r="R204" s="2" t="n">
         <v>0.00194174757281559</v>
       </c>
+      <c r="S204" s="1" t="n">
+        <v>0.02581</v>
+      </c>
+      <c r="T204" s="2" t="n">
+        <v>0.0003875968992247904</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -12369,6 +13599,12 @@
       <c r="R205" s="2" t="n">
         <v>0.0002315350775642255</v>
       </c>
+      <c r="S205" s="1" t="n">
+        <v>0.4322</v>
+      </c>
+      <c r="T205" s="2" t="n">
+        <v>0.000462962962962912</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -12427,6 +13663,12 @@
       <c r="R206" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="S206" s="1" t="n">
+        <v>0.02298</v>
+      </c>
+      <c r="T206" s="2" t="n">
+        <v>0.002180549498473678</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -12485,6 +13727,12 @@
       <c r="R207" s="2" t="n">
         <v>0.001443348568679391</v>
       </c>
+      <c r="S207" s="1" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="T207" s="2" t="n">
+        <v>0.001681479702137803</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -12543,6 +13791,12 @@
       <c r="R208" s="2" t="n">
         <v>0.001767745444656039</v>
       </c>
+      <c r="S208" s="1" t="n">
+        <v>0.07371</v>
+      </c>
+      <c r="T208" s="2" t="n">
+        <v>0.0005429618569295285</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -12601,6 +13855,12 @@
       <c r="R209" s="3" t="n">
         <v>-0.0007127583749109586</v>
       </c>
+      <c r="S209" s="1" t="n">
+        <v>0.04212</v>
+      </c>
+      <c r="T209" s="2" t="n">
+        <v>0.001426533523537745</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -12659,6 +13919,12 @@
       <c r="R210" s="2" t="n">
         <v>0.00434074877916438</v>
       </c>
+      <c r="S210" s="1" t="n">
+        <v>0.1855</v>
+      </c>
+      <c r="T210" s="2" t="n">
+        <v>0.002160994057266405</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -12717,6 +13983,12 @@
       <c r="R211" s="3" t="n">
         <v>-0.001689189189189237</v>
       </c>
+      <c r="S211" s="1" t="n">
+        <v>0.2357</v>
+      </c>
+      <c r="T211" s="3" t="n">
+        <v>-0.002961082910321515</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -12775,6 +14047,12 @@
       <c r="R212" s="3" t="n">
         <v>-0.003840614498319824</v>
       </c>
+      <c r="S212" s="1" t="n">
+        <v>0.002075</v>
+      </c>
+      <c r="T212" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -12833,6 +14111,12 @@
       <c r="R213" s="3" t="n">
         <v>-0.002145922746781118</v>
       </c>
+      <c r="S213" s="1" t="n">
+        <v>0.9330000000000001</v>
+      </c>
+      <c r="T213" s="2" t="n">
+        <v>0.003225806451612906</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -12891,6 +14175,12 @@
       <c r="R214" s="3" t="n">
         <v>-0.0003497726477789901</v>
       </c>
+      <c r="S214" s="1" t="n">
+        <v>0.005711</v>
+      </c>
+      <c r="T214" s="3" t="n">
+        <v>-0.0008747375787263465</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -12949,6 +14239,12 @@
       <c r="R215" s="3" t="n">
         <v>-0.000182848784055642</v>
       </c>
+      <c r="S215" s="1" t="n">
+        <v>0.05478</v>
+      </c>
+      <c r="T215" s="2" t="n">
+        <v>0.001828822238478472</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -13007,6 +14303,12 @@
       <c r="R216" s="2" t="n">
         <v>0.001584786053882771</v>
       </c>
+      <c r="S216" s="1" t="n">
+        <v>0.0633</v>
+      </c>
+      <c r="T216" s="2" t="n">
+        <v>0.001582278481012484</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -13065,6 +14367,12 @@
       <c r="R217" s="2" t="n">
         <v>0.002162162162162224</v>
       </c>
+      <c r="S217" s="1" t="n">
+        <v>0.0927</v>
+      </c>
+      <c r="T217" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -13123,6 +14431,12 @@
       <c r="R218" s="2" t="n">
         <v>0.0007596859964547551</v>
       </c>
+      <c r="S218" s="1" t="n">
+        <v>0.27755</v>
+      </c>
+      <c r="T218" s="2" t="n">
+        <v>0.003289473684210605</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -13181,6 +14495,12 @@
       <c r="R219" s="2" t="n">
         <v>0.001230012300123031</v>
       </c>
+      <c r="S219" s="1" t="n">
+        <v>0.003274</v>
+      </c>
+      <c r="T219" s="2" t="n">
+        <v>0.005528255528255462</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -13239,6 +14559,12 @@
       <c r="R220" s="3" t="n">
         <v>-1.000626392150242e-06</v>
       </c>
+      <c r="S220" s="1" t="n">
+        <v>0.999373</v>
+      </c>
+      <c r="T220" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -13297,6 +14623,12 @@
       <c r="R221" s="3" t="n">
         <v>-0.00691244239631335</v>
       </c>
+      <c r="S221" s="1" t="n">
+        <v>0.03899</v>
+      </c>
+      <c r="T221" s="2" t="n">
+        <v>0.005155968032998164</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -13355,6 +14687,12 @@
       <c r="R222" s="2" t="n">
         <v>0.0008613264427217564</v>
       </c>
+      <c r="S222" s="1" t="n">
+        <v>0.0466</v>
+      </c>
+      <c r="T222" s="2" t="n">
+        <v>0.002581755593803831</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -13413,6 +14751,12 @@
       <c r="R223" s="2" t="n">
         <v>0.003809523809523787</v>
       </c>
+      <c r="S223" s="1" t="n">
+        <v>0.1054</v>
+      </c>
+      <c r="T223" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -13471,6 +14815,12 @@
       <c r="R224" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="S224" s="1" t="n">
+        <v>3.903</v>
+      </c>
+      <c r="T224" s="3" t="n">
+        <v>-0.004336734693877527</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -13529,6 +14879,12 @@
       <c r="R225" s="2" t="n">
         <v>0.001084598698481588</v>
       </c>
+      <c r="S225" s="1" t="n">
+        <v>0.0009222</v>
+      </c>
+      <c r="T225" s="3" t="n">
+        <v>-0.00086673889490793</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -13587,6 +14943,12 @@
       <c r="R226" s="2" t="n">
         <v>0.0009429514380008636</v>
       </c>
+      <c r="S226" s="1" t="n">
+        <v>0.008515</v>
+      </c>
+      <c r="T226" s="2" t="n">
+        <v>0.002708431464908202</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -13645,6 +15007,12 @@
       <c r="R227" s="2" t="n">
         <v>0.001210067763794639</v>
       </c>
+      <c r="S227" s="1" t="n">
+        <v>0.04134</v>
+      </c>
+      <c r="T227" s="3" t="n">
+        <v>-0.0007251631617112717</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -13703,6 +15071,12 @@
       <c r="R228" s="3" t="n">
         <v>-0.003916083916083756</v>
       </c>
+      <c r="S228" s="1" t="n">
+        <v>0.03564</v>
+      </c>
+      <c r="T228" s="2" t="n">
+        <v>0.0008424599831506686</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -13761,6 +15135,12 @@
       <c r="R229" s="3" t="n">
         <v>-0.001168907071887737</v>
       </c>
+      <c r="S229" s="1" t="n">
+        <v>0.0514</v>
+      </c>
+      <c r="T229" s="2" t="n">
+        <v>0.002535595865028246</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -13819,6 +15199,12 @@
       <c r="R230" s="2" t="n">
         <v>0.002912055911473508</v>
       </c>
+      <c r="S230" s="1" t="n">
+        <v>0.001739</v>
+      </c>
+      <c r="T230" s="2" t="n">
+        <v>0.009872241579558703</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -13877,6 +15263,12 @@
       <c r="R231" s="2" t="n">
         <v>0.007864238410595994</v>
       </c>
+      <c r="S231" s="1" t="n">
+        <v>0.0485</v>
+      </c>
+      <c r="T231" s="3" t="n">
+        <v>-0.004106776180698127</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -13935,6 +15327,12 @@
       <c r="R232" s="3" t="n">
         <v>-0.0009229349330871798</v>
       </c>
+      <c r="S232" s="1" t="n">
+        <v>0.02165</v>
+      </c>
+      <c r="T232" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -13993,6 +15391,12 @@
       <c r="R233" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="S233" s="1" t="n">
+        <v>0.0005855</v>
+      </c>
+      <c r="T233" s="2" t="n">
+        <v>0.002568493150684901</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -14051,6 +15455,12 @@
       <c r="R234" s="3" t="n">
         <v>-0.004893520616221104</v>
       </c>
+      <c r="S234" s="1" t="n">
+        <v>0.21915</v>
+      </c>
+      <c r="T234" s="3" t="n">
+        <v>-0.002140060103815673</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -14109,6 +15519,12 @@
       <c r="R235" s="2" t="n">
         <v>0.005780346820809264</v>
       </c>
+      <c r="S235" s="1" t="n">
+        <v>0.01401</v>
+      </c>
+      <c r="T235" s="2" t="n">
+        <v>0.006465517241379296</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -14167,6 +15583,12 @@
       <c r="R236" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="S236" s="1" t="n">
+        <v>0.0412</v>
+      </c>
+      <c r="T236" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -14225,6 +15647,12 @@
       <c r="R237" s="2" t="n">
         <v>0.004784688995215324</v>
       </c>
+      <c r="S237" s="1" t="n">
+        <v>0.0042</v>
+      </c>
+      <c r="T237" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -14283,6 +15711,12 @@
       <c r="R238" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="S238" s="1" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="T238" s="2" t="n">
+        <v>0.004016064257028227</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -14341,6 +15775,12 @@
       <c r="R239" s="3" t="n">
         <v>-0.002016129032258099</v>
       </c>
+      <c r="S239" s="1" t="n">
+        <v>0.01491</v>
+      </c>
+      <c r="T239" s="2" t="n">
+        <v>0.004040404040403993</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -14399,6 +15839,12 @@
       <c r="R240" s="2" t="n">
         <v>0.001535705144612272</v>
       </c>
+      <c r="S240" s="1" t="n">
+        <v>0.0003918</v>
+      </c>
+      <c r="T240" s="2" t="n">
+        <v>0.001277791975466286</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -14457,6 +15903,12 @@
       <c r="R241" s="2" t="n">
         <v>0.005233644859812922</v>
       </c>
+      <c r="S241" s="1" t="n">
+        <v>0.2695</v>
+      </c>
+      <c r="T241" s="2" t="n">
+        <v>0.00223131275567142</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -14515,6 +15967,12 @@
       <c r="R242" s="2" t="n">
         <v>0.008017875920084115</v>
       </c>
+      <c r="S242" s="1" t="n">
+        <v>0.07606</v>
+      </c>
+      <c r="T242" s="3" t="n">
+        <v>-0.008214891120093777</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -14573,6 +16031,12 @@
       <c r="R243" s="2" t="n">
         <v>0.004582484725050906</v>
       </c>
+      <c r="S243" s="1" t="n">
+        <v>0.01977</v>
+      </c>
+      <c r="T243" s="2" t="n">
+        <v>0.002027369488089121</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -14631,6 +16095,12 @@
       <c r="R244" s="2" t="n">
         <v>0.005083766608896544</v>
       </c>
+      <c r="S244" s="1" t="n">
+        <v>0.0868</v>
+      </c>
+      <c r="T244" s="3" t="n">
+        <v>-0.002184159098746934</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -14689,6 +16159,12 @@
       <c r="R245" s="2" t="n">
         <v>0.00111982082866729</v>
       </c>
+      <c r="S245" s="1" t="n">
+        <v>1.4329</v>
+      </c>
+      <c r="T245" s="2" t="n">
+        <v>0.001747762863534794</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -14747,6 +16223,12 @@
       <c r="R246" s="3" t="n">
         <v>-0.003923766816143532</v>
       </c>
+      <c r="S246" s="1" t="n">
+        <v>0.01778</v>
+      </c>
+      <c r="T246" s="2" t="n">
+        <v>0.0005627462014631172</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -14805,6 +16287,12 @@
       <c r="R247" s="3" t="n">
         <v>-0.0003027550711474819</v>
       </c>
+      <c r="S247" s="1" t="n">
+        <v>0.006622</v>
+      </c>
+      <c r="T247" s="2" t="n">
+        <v>0.002725620835857155</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -14863,6 +16351,12 @@
       <c r="R248" s="2" t="n">
         <v>0.003368623676612157</v>
       </c>
+      <c r="S248" s="1" t="n">
+        <v>0.00422</v>
+      </c>
+      <c r="T248" s="2" t="n">
+        <v>0.01199040767386084</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -14921,6 +16415,12 @@
       <c r="R249" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="S249" s="1" t="n">
+        <v>0.1097</v>
+      </c>
+      <c r="T249" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -14979,6 +16479,12 @@
       <c r="R250" s="2" t="n">
         <v>0.0005841121495326865</v>
       </c>
+      <c r="S250" s="1" t="n">
+        <v>0.03457</v>
+      </c>
+      <c r="T250" s="2" t="n">
+        <v>0.009048453006421419</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -15037,6 +16543,12 @@
       <c r="R251" s="2" t="n">
         <v>0.003934274473501585</v>
       </c>
+      <c r="S251" s="1" t="n">
+        <v>0.04327</v>
+      </c>
+      <c r="T251" s="3" t="n">
+        <v>-0.002535730751498363</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -15095,6 +16607,12 @@
       <c r="R252" s="3" t="n">
         <v>-0.02579617834394901</v>
       </c>
+      <c r="S252" s="1" t="n">
+        <v>0.006099</v>
+      </c>
+      <c r="T252" s="3" t="n">
+        <v>-0.003105590062111788</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -15153,6 +16671,12 @@
       <c r="R253" s="3" t="n">
         <v>-0.0005931198102016366</v>
       </c>
+      <c r="S253" s="1" t="n">
+        <v>0.01729</v>
+      </c>
+      <c r="T253" s="2" t="n">
+        <v>0.02611275964391688</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -15211,6 +16735,12 @@
       <c r="R254" s="3" t="n">
         <v>-0.003072196620583805</v>
       </c>
+      <c r="S254" s="1" t="n">
+        <v>0.1299</v>
+      </c>
+      <c r="T254" s="2" t="n">
+        <v>0.0007704160246532279</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -15269,6 +16799,12 @@
       <c r="R255" s="2" t="n">
         <v>0.001910219675262577</v>
       </c>
+      <c r="S255" s="1" t="n">
+        <v>0.02138</v>
+      </c>
+      <c r="T255" s="2" t="n">
+        <v>0.01906577693040996</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -15327,6 +16863,12 @@
       <c r="R256" s="3" t="n">
         <v>-0.0004755111745125817</v>
       </c>
+      <c r="S256" s="1" t="n">
+        <v>0.02108</v>
+      </c>
+      <c r="T256" s="2" t="n">
+        <v>0.002854424357754568</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -15385,6 +16927,12 @@
       <c r="R257" s="3" t="n">
         <v>-0.003930817610062869</v>
       </c>
+      <c r="S257" s="1" t="n">
+        <v>0.0253</v>
+      </c>
+      <c r="T257" s="3" t="n">
+        <v>-0.001578531965272369</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -15443,6 +16991,12 @@
       <c r="R258" s="2" t="n">
         <v>0.002219084123461751</v>
       </c>
+      <c r="S258" s="1" t="n">
+        <v>0.14976</v>
+      </c>
+      <c r="T258" s="2" t="n">
+        <v>0.004830917874396125</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -15501,6 +17055,12 @@
       <c r="R259" s="3" t="n">
         <v>-0.0001963479285294141</v>
       </c>
+      <c r="S259" s="1" t="n">
+        <v>0.05091</v>
+      </c>
+      <c r="T259" s="3" t="n">
+        <v>-0.0001963864886096438</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -15559,6 +17119,12 @@
       <c r="R260" s="2" t="n">
         <v>0.002166325670959196</v>
       </c>
+      <c r="S260" s="1" t="n">
+        <v>0.08332000000000001</v>
+      </c>
+      <c r="T260" s="2" t="n">
+        <v>0.0006004563468236865</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -15617,6 +17183,12 @@
       <c r="R261" s="3" t="n">
         <v>-0.003254678600488182</v>
       </c>
+      <c r="S261" s="1" t="n">
+        <v>0.2483</v>
+      </c>
+      <c r="T261" s="2" t="n">
+        <v>0.01346938775510203</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -15675,6 +17247,12 @@
       <c r="R262" s="2" t="n">
         <v>0.004936530324400412</v>
       </c>
+      <c r="S262" s="1" t="n">
+        <v>0.1433</v>
+      </c>
+      <c r="T262" s="2" t="n">
+        <v>0.005614035087719459</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -15733,6 +17311,12 @@
       <c r="R263" s="3" t="n">
         <v>-0.002202072538860149</v>
       </c>
+      <c r="S263" s="1" t="n">
+        <v>0.0769</v>
+      </c>
+      <c r="T263" s="3" t="n">
+        <v>-0.00168765416071667</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -15791,6 +17375,12 @@
       <c r="R264" s="2" t="n">
         <v>0.002026342451874284</v>
       </c>
+      <c r="S264" s="1" t="n">
+        <v>0.03964</v>
+      </c>
+      <c r="T264" s="2" t="n">
+        <v>0.002022244691607778</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -15849,6 +17439,12 @@
       <c r="R265" s="2" t="n">
         <v>0.003274394237066123</v>
       </c>
+      <c r="S265" s="1" t="n">
+        <v>0.01531</v>
+      </c>
+      <c r="T265" s="3" t="n">
+        <v>-0.0006527415143602868</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -15907,6 +17503,12 @@
       <c r="R266" s="2" t="n">
         <v>0.002027027027027003</v>
       </c>
+      <c r="S266" s="1" t="n">
+        <v>0.005945</v>
+      </c>
+      <c r="T266" s="2" t="n">
+        <v>0.002191503708698582</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -15965,6 +17567,12 @@
       <c r="R267" s="2" t="n">
         <v>0.003775620280474682</v>
       </c>
+      <c r="S267" s="1" t="n">
+        <v>0.03738</v>
+      </c>
+      <c r="T267" s="2" t="n">
+        <v>0.004298764105319545</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -16023,6 +17631,12 @@
       <c r="R268" s="2" t="n">
         <v>0.0006544502617800781</v>
       </c>
+      <c r="S268" s="1" t="n">
+        <v>0.03066</v>
+      </c>
+      <c r="T268" s="2" t="n">
+        <v>0.002616088947024206</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -16081,6 +17695,12 @@
       <c r="R269" s="2" t="n">
         <v>4.399278518315184e-05</v>
       </c>
+      <c r="S269" s="1" t="n">
+        <v>0.22623</v>
+      </c>
+      <c r="T269" s="3" t="n">
+        <v>-0.004795002639451028</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -16139,6 +17759,12 @@
       <c r="R270" s="2" t="n">
         <v>0.004343105320304021</v>
       </c>
+      <c r="S270" s="1" t="n">
+        <v>0.927</v>
+      </c>
+      <c r="T270" s="2" t="n">
+        <v>0.002162162162162164</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -16197,6 +17823,12 @@
       <c r="R271" s="2" t="n">
         <v>0.000387446726075122</v>
       </c>
+      <c r="S271" s="1" t="n">
+        <v>2.595</v>
+      </c>
+      <c r="T271" s="2" t="n">
+        <v>0.005034856700232512</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -16255,6 +17887,12 @@
       <c r="R272" s="2" t="n">
         <v>0.0005417118093175338</v>
       </c>
+      <c r="S272" s="1" t="n">
+        <v>0.185</v>
+      </c>
+      <c r="T272" s="2" t="n">
+        <v>0.001624255549539766</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -16313,6 +17951,12 @@
       <c r="R273" s="2" t="n">
         <v>0.004208481709290973</v>
       </c>
+      <c r="S273" s="1" t="n">
+        <v>0.03099</v>
+      </c>
+      <c r="T273" s="3" t="n">
+        <v>-0.0009671179883945448</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -16371,6 +18015,12 @@
       <c r="R274" s="2" t="n">
         <v>0.004197271773347299</v>
       </c>
+      <c r="S274" s="1" t="n">
+        <v>0.1919</v>
+      </c>
+      <c r="T274" s="2" t="n">
+        <v>0.002612330198537098</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -16429,6 +18079,12 @@
       <c r="R275" s="3" t="n">
         <v>-0.008329742926899284</v>
       </c>
+      <c r="S275" s="1" t="n">
+        <v>0.06897</v>
+      </c>
+      <c r="T275" s="3" t="n">
+        <v>-0.001158580738595174</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -16487,6 +18143,12 @@
       <c r="R276" s="3" t="n">
         <v>-0.003096742227177013</v>
       </c>
+      <c r="S276" s="1" t="n">
+        <v>0.08041</v>
+      </c>
+      <c r="T276" s="3" t="n">
+        <v>-0.0008697813121272443</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -16545,6 +18207,12 @@
       <c r="R277" s="3" t="n">
         <v>-0.01070450585013683</v>
       </c>
+      <c r="S277" s="1" t="n">
+        <v>0.003991</v>
+      </c>
+      <c r="T277" s="2" t="n">
+        <v>0.004277805737292313</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -16603,6 +18271,12 @@
       <c r="R278" s="2" t="n">
         <v>0.0006443298969071455</v>
       </c>
+      <c r="S278" s="1" t="n">
+        <v>1.555</v>
+      </c>
+      <c r="T278" s="2" t="n">
+        <v>0.001287830006439151</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -16661,6 +18335,12 @@
       <c r="R279" s="2" t="n">
         <v>0.001814882032667803</v>
       </c>
+      <c r="S279" s="1" t="n">
+        <v>0.01103</v>
+      </c>
+      <c r="T279" s="3" t="n">
+        <v>-0.0009057971014492385</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -16719,6 +18399,12 @@
       <c r="R280" s="3" t="n">
         <v>-0.007684680218145706</v>
       </c>
+      <c r="S280" s="1" t="n">
+        <v>0.03965</v>
+      </c>
+      <c r="T280" s="3" t="n">
+        <v>-0.009492880339745324</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -16777,6 +18463,12 @@
       <c r="R281" s="2" t="n">
         <v>0.000837520938023458</v>
       </c>
+      <c r="S281" s="1" t="n">
+        <v>0.08412</v>
+      </c>
+      <c r="T281" s="2" t="n">
+        <v>0.005618649133293463</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -16835,6 +18527,12 @@
       <c r="R282" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="S282" s="1" t="n">
+        <v>0.0266</v>
+      </c>
+      <c r="T282" s="2" t="n">
+        <v>0.003773584905660355</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -16893,6 +18591,12 @@
       <c r="R283" s="3" t="n">
         <v>-0.0007871949619521205</v>
       </c>
+      <c r="S283" s="1" t="n">
+        <v>0.07622</v>
+      </c>
+      <c r="T283" s="2" t="n">
+        <v>0.0007878151260502969</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -16951,6 +18655,12 @@
       <c r="R284" s="2" t="n">
         <v>0.0006188118811880668</v>
       </c>
+      <c r="S284" s="1" t="n">
+        <v>0.001615</v>
+      </c>
+      <c r="T284" s="3" t="n">
+        <v>-0.001236858379715553</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -17009,6 +18719,12 @@
       <c r="R285" s="2" t="n">
         <v>0.001485148514851459</v>
       </c>
+      <c r="S285" s="1" t="n">
+        <v>0.2026</v>
+      </c>
+      <c r="T285" s="2" t="n">
+        <v>0.001482946119624294</v>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -17067,6 +18783,12 @@
       <c r="R286" s="2" t="n">
         <v>0.004524460363841967</v>
       </c>
+      <c r="S286" s="1" t="n">
+        <v>0.10715</v>
+      </c>
+      <c r="T286" s="2" t="n">
+        <v>0.005442432204185017</v>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -17125,6 +18847,12 @@
       <c r="R287" s="2" t="n">
         <v>0.001735106998264822</v>
       </c>
+      <c r="S287" s="1" t="n">
+        <v>0.01733</v>
+      </c>
+      <c r="T287" s="2" t="n">
+        <v>0.000577367205542902</v>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -17183,6 +18911,12 @@
       <c r="R288" s="3" t="n">
         <v>-0.003957783641160903</v>
       </c>
+      <c r="S288" s="1" t="n">
+        <v>0.01512</v>
+      </c>
+      <c r="T288" s="2" t="n">
+        <v>0.001324503311258224</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -17241,6 +18975,12 @@
       <c r="R289" s="2" t="n">
         <v>0.003754693366708232</v>
       </c>
+      <c r="S289" s="1" t="n">
+        <v>0.01615</v>
+      </c>
+      <c r="T289" s="2" t="n">
+        <v>0.006857855361596164</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -17299,6 +19039,12 @@
       <c r="R290" s="3" t="n">
         <v>-0.002201673271686435</v>
       </c>
+      <c r="S290" s="1" t="n">
+        <v>2.267</v>
+      </c>
+      <c r="T290" s="2" t="n">
+        <v>0.0004413062665489364</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -17357,6 +19103,12 @@
       <c r="R291" s="3" t="n">
         <v>-0.0004551661356395846</v>
       </c>
+      <c r="S291" s="1" t="n">
+        <v>0.4392</v>
+      </c>
+      <c r="T291" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -17415,6 +19167,12 @@
       <c r="R292" s="3" t="n">
         <v>-0.001728110599078279</v>
       </c>
+      <c r="S292" s="1" t="n">
+        <v>1.726</v>
+      </c>
+      <c r="T292" s="3" t="n">
+        <v>-0.004039238315060656</v>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -17473,6 +19231,12 @@
       <c r="R293" s="2" t="n">
         <v>0.004362482649216696</v>
       </c>
+      <c r="S293" s="1" t="n">
+        <v>0.0505</v>
+      </c>
+      <c r="T293" s="3" t="n">
+        <v>-0.002961500493583364</v>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -17531,6 +19295,12 @@
       <c r="R294" s="2" t="n">
         <v>0.002526049889485434</v>
       </c>
+      <c r="S294" s="1" t="n">
+        <v>0.06345000000000001</v>
+      </c>
+      <c r="T294" s="3" t="n">
+        <v>-0.0007874015748030629</v>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -17589,6 +19359,12 @@
       <c r="R295" s="3" t="n">
         <v>-0.002648687695641769</v>
       </c>
+      <c r="S295" s="1" t="n">
+        <v>0.0004156</v>
+      </c>
+      <c r="T295" s="2" t="n">
+        <v>0.003380009657170531</v>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -17647,6 +19423,12 @@
       <c r="R296" s="3" t="n">
         <v>-0.0001604363869725335</v>
       </c>
+      <c r="S296" s="1" t="n">
+        <v>62.49</v>
+      </c>
+      <c r="T296" s="2" t="n">
+        <v>0.002727856225930708</v>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -17705,6 +19487,12 @@
       <c r="R297" s="2" t="n">
         <v>0.001022494887525592</v>
       </c>
+      <c r="S297" s="1" t="n">
+        <v>0.0978</v>
+      </c>
+      <c r="T297" s="3" t="n">
+        <v>-0.001021450459652736</v>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -17763,6 +19551,12 @@
       <c r="R298" s="2" t="n">
         <v>0.001047120418848198</v>
       </c>
+      <c r="S298" s="1" t="n">
+        <v>0.0958</v>
+      </c>
+      <c r="T298" s="2" t="n">
+        <v>0.002092050209204936</v>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -17821,6 +19615,12 @@
       <c r="R299" s="2" t="n">
         <v>0.003860198226395361</v>
       </c>
+      <c r="S299" s="1" t="n">
+        <v>0.09641</v>
+      </c>
+      <c r="T299" s="2" t="n">
+        <v>0.001974641446684636</v>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -17879,6 +19679,12 @@
       <c r="R300" s="2" t="n">
         <v>0.003225806451612959</v>
       </c>
+      <c r="S300" s="1" t="n">
+        <v>0.01872</v>
+      </c>
+      <c r="T300" s="2" t="n">
+        <v>0.003215434083601341</v>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -17937,6 +19743,12 @@
       <c r="R301" s="2" t="n">
         <v>0.001500375093773512</v>
       </c>
+      <c r="S301" s="1" t="n">
+        <v>0.01339</v>
+      </c>
+      <c r="T301" s="2" t="n">
+        <v>0.002996254681647948</v>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -17995,6 +19807,12 @@
       <c r="R302" s="3" t="n">
         <v>-0.0006899724011040474</v>
       </c>
+      <c r="S302" s="1" t="n">
+        <v>0.004364</v>
+      </c>
+      <c r="T302" s="2" t="n">
+        <v>0.004372842347525874</v>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -18053,6 +19871,12 @@
       <c r="R303" s="3" t="n">
         <v>-0.004291845493562243</v>
       </c>
+      <c r="S303" s="1" t="n">
+        <v>0.009310000000000001</v>
+      </c>
+      <c r="T303" s="2" t="n">
+        <v>0.00323275862068971</v>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -18111,6 +19935,12 @@
       <c r="R304" s="2" t="n">
         <v>0.000848356309650148</v>
       </c>
+      <c r="S304" s="1" t="n">
+        <v>4.714</v>
+      </c>
+      <c r="T304" s="3" t="n">
+        <v>-0.001059546514091946</v>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -18169,6 +19999,12 @@
       <c r="R305" s="3" t="n">
         <v>-0.0001900418091980818</v>
       </c>
+      <c r="S305" s="1" t="n">
+        <v>0.05304</v>
+      </c>
+      <c r="T305" s="2" t="n">
+        <v>0.008173351073940313</v>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -18227,6 +20063,12 @@
       <c r="R306" s="3" t="n">
         <v>-0.0001718508334764757</v>
       </c>
+      <c r="S306" s="1" t="n">
+        <v>0.0582</v>
+      </c>
+      <c r="T306" s="2" t="n">
+        <v>0.0003437607425231898</v>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -18285,6 +20127,12 @@
       <c r="R307" s="3" t="n">
         <v>-0.001146131805157467</v>
       </c>
+      <c r="S307" s="1" t="n">
+        <v>0.1744</v>
+      </c>
+      <c r="T307" s="2" t="n">
+        <v>0.0005737234652896671</v>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -18343,6 +20191,12 @@
       <c r="R308" s="2" t="n">
         <v>0.00987704091916947</v>
       </c>
+      <c r="S308" s="1" t="n">
+        <v>0.05031</v>
+      </c>
+      <c r="T308" s="2" t="n">
+        <v>0.004191616766467103</v>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -18401,6 +20255,12 @@
       <c r="R309" s="2" t="n">
         <v>0.002032144836504692</v>
       </c>
+      <c r="S309" s="1" t="n">
+        <v>0.5425</v>
+      </c>
+      <c r="T309" s="2" t="n">
+        <v>0.0001843657817108942</v>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -18459,6 +20319,12 @@
       <c r="R310" s="2" t="n">
         <v>0.00411522633744857</v>
       </c>
+      <c r="S310" s="1" t="n">
+        <v>0.00244</v>
+      </c>
+      <c r="T310" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -18517,6 +20383,12 @@
       <c r="R311" s="2" t="n">
         <v>0.0002832861189802567</v>
       </c>
+      <c r="S311" s="1" t="n">
+        <v>0.07088999999999999</v>
+      </c>
+      <c r="T311" s="2" t="n">
+        <v>0.003823279524213997</v>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -18575,6 +20447,12 @@
       <c r="R312" s="3" t="n">
         <v>-0.001002338790511036</v>
       </c>
+      <c r="S312" s="1" t="n">
+        <v>0.008978999999999999</v>
+      </c>
+      <c r="T312" s="2" t="n">
+        <v>0.001003344481605194</v>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -18633,6 +20511,12 @@
       <c r="R313" s="3" t="n">
         <v>-0.003807316669425666</v>
       </c>
+      <c r="S313" s="1" t="n">
+        <v>0.011995</v>
+      </c>
+      <c r="T313" s="3" t="n">
+        <v>-0.003406447324692537</v>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -18691,6 +20575,12 @@
       <c r="R314" s="3" t="n">
         <v>-0.001718951439621761</v>
       </c>
+      <c r="S314" s="1" t="n">
+        <v>0.02341</v>
+      </c>
+      <c r="T314" s="2" t="n">
+        <v>0.00774860094705121</v>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -18749,6 +20639,12 @@
       <c r="R315" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="S315" s="1" t="n">
+        <v>0.0071</v>
+      </c>
+      <c r="T315" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -18807,6 +20703,12 @@
       <c r="R316" s="3" t="n">
         <v>-0.0007686395080706303</v>
       </c>
+      <c r="S316" s="1" t="n">
+        <v>0.2607</v>
+      </c>
+      <c r="T316" s="2" t="n">
+        <v>0.002692307692307609</v>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -18865,6 +20767,12 @@
       <c r="R317" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="S317" s="1" t="n">
+        <v>1.11e-05</v>
+      </c>
+      <c r="T317" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -18923,6 +20831,12 @@
       <c r="R318" s="3" t="n">
         <v>-0.0007996953541508068</v>
       </c>
+      <c r="S318" s="1" t="n">
+        <v>0.052576</v>
+      </c>
+      <c r="T318" s="2" t="n">
+        <v>0.001867449216814682</v>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -18981,6 +20895,12 @@
       <c r="R319" s="3" t="n">
         <v>-0.001047120418848125</v>
       </c>
+      <c r="S319" s="1" t="n">
+        <v>0.03823</v>
+      </c>
+      <c r="T319" s="2" t="n">
+        <v>0.0018343815513627</v>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -19039,6 +20959,12 @@
       <c r="R320" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="S320" s="1" t="n">
+        <v>0.006794</v>
+      </c>
+      <c r="T320" s="2" t="n">
+        <v>0.0007364854912357927</v>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -19097,6 +21023,12 @@
       <c r="R321" s="2" t="n">
         <v>0.002215330084182496</v>
       </c>
+      <c r="S321" s="1" t="n">
+        <v>4.529</v>
+      </c>
+      <c r="T321" s="2" t="n">
+        <v>0.001105216622457978</v>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -19155,6 +21087,12 @@
       <c r="R322" s="2" t="n">
         <v>0.005750130684788237</v>
       </c>
+      <c r="S322" s="1" t="n">
+        <v>1.926</v>
+      </c>
+      <c r="T322" s="2" t="n">
+        <v>0.00103950103950104</v>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -19213,6 +21151,12 @@
       <c r="R323" s="2" t="n">
         <v>0.002269825507164192</v>
       </c>
+      <c r="S323" s="1" t="n">
+        <v>0.007079</v>
+      </c>
+      <c r="T323" s="2" t="n">
+        <v>0.001981599433828751</v>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -19271,6 +21215,12 @@
       <c r="R324" s="2" t="n">
         <v>0.002723311546840847</v>
       </c>
+      <c r="S324" s="1" t="n">
+        <v>0.01837</v>
+      </c>
+      <c r="T324" s="3" t="n">
+        <v>-0.002172732210754936</v>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -19329,6 +21279,12 @@
       <c r="R325" s="2" t="n">
         <v>0.002696739396910983</v>
       </c>
+      <c r="S325" s="1" t="n">
+        <v>0.4095</v>
+      </c>
+      <c r="T325" s="2" t="n">
+        <v>0.001222493887530563</v>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -19387,6 +21343,12 @@
       <c r="R326" s="2" t="n">
         <v>0.002091758471621725</v>
       </c>
+      <c r="S326" s="1" t="n">
+        <v>0.007205</v>
+      </c>
+      <c r="T326" s="2" t="n">
+        <v>0.002644030058446969</v>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -19445,6 +21407,12 @@
       <c r="R327" s="2" t="n">
         <v>0.007987220447284352</v>
       </c>
+      <c r="S327" s="1" t="n">
+        <v>0.1906</v>
+      </c>
+      <c r="T327" s="2" t="n">
+        <v>0.006867406233491789</v>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -19503,6 +21471,12 @@
       <c r="R328" s="3" t="n">
         <v>-0.01431012387868429</v>
       </c>
+      <c r="S328" s="1" t="n">
+        <v>0.4678</v>
+      </c>
+      <c r="T328" s="2" t="n">
+        <v>0.01365113759479951</v>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -19561,6 +21535,12 @@
       <c r="R329" s="3" t="n">
         <v>-0.001484780994803206</v>
       </c>
+      <c r="S329" s="1" t="n">
+        <v>0.01345</v>
+      </c>
+      <c r="T329" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -19619,6 +21599,12 @@
       <c r="R330" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="S330" s="1" t="n">
+        <v>0.1132</v>
+      </c>
+      <c r="T330" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -19677,6 +21663,12 @@
       <c r="R331" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="S331" s="1" t="n">
+        <v>0.6061</v>
+      </c>
+      <c r="T331" s="2" t="n">
+        <v>0.005140961857379754</v>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -19735,6 +21727,12 @@
       <c r="R332" s="2" t="n">
         <v>0.002389134347897262</v>
       </c>
+      <c r="S332" s="1" t="n">
+        <v>0.30492</v>
+      </c>
+      <c r="T332" s="3" t="n">
+        <v>-0.004440381350398238</v>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -19793,6 +21791,12 @@
       <c r="R333" s="2" t="n">
         <v>0.0029978586723769</v>
       </c>
+      <c r="S333" s="1" t="n">
+        <v>0.07043000000000001</v>
+      </c>
+      <c r="T333" s="2" t="n">
+        <v>0.002419584400797089</v>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -19851,6 +21855,12 @@
       <c r="R334" s="3" t="n">
         <v>-0.004425947945567289</v>
       </c>
+      <c r="S334" s="1" t="n">
+        <v>0.15068</v>
+      </c>
+      <c r="T334" s="3" t="n">
+        <v>-0.0001990577931126153</v>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -19909,6 +21919,12 @@
       <c r="R335" s="2" t="n">
         <v>0.001282051282051319</v>
       </c>
+      <c r="S335" s="1" t="n">
+        <v>0.1567</v>
+      </c>
+      <c r="T335" s="2" t="n">
+        <v>0.003201024327784894</v>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -19967,6 +21983,12 @@
       <c r="R336" s="2" t="n">
         <v>0.002880184331797237</v>
       </c>
+      <c r="S336" s="1" t="n">
+        <v>0.1738</v>
+      </c>
+      <c r="T336" s="3" t="n">
+        <v>-0.001723147616312434</v>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -20025,6 +22047,12 @@
       <c r="R337" s="2" t="n">
         <v>0.00299326515340489</v>
       </c>
+      <c r="S337" s="1" t="n">
+        <v>0.04051</v>
+      </c>
+      <c r="T337" s="2" t="n">
+        <v>0.00746083063914436</v>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -20083,6 +22111,12 @@
       <c r="R338" s="2" t="n">
         <v>0.0005687203791468305</v>
       </c>
+      <c r="S338" s="1" t="n">
+        <v>0.005285</v>
+      </c>
+      <c r="T338" s="2" t="n">
+        <v>0.001326259946949614</v>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -20141,6 +22175,12 @@
       <c r="R339" s="2" t="n">
         <v>0.001364522417154008</v>
       </c>
+      <c r="S339" s="1" t="n">
+        <v>0.0516</v>
+      </c>
+      <c r="T339" s="2" t="n">
+        <v>0.004477321393809637</v>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -20199,6 +22239,12 @@
       <c r="R340" s="3" t="n">
         <v>-0.002177642866569862</v>
       </c>
+      <c r="S340" s="1" t="n">
+        <v>0.15142</v>
+      </c>
+      <c r="T340" s="2" t="n">
+        <v>0.001388797037232908</v>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -20257,6 +22303,12 @@
       <c r="R341" s="3" t="n">
         <v>-0.001710301276147862</v>
       </c>
+      <c r="S341" s="1" t="n">
+        <v>7.608</v>
+      </c>
+      <c r="T341" s="2" t="n">
+        <v>0.002635740643120661</v>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -20315,6 +22367,12 @@
       <c r="R342" s="3" t="n">
         <v>-0.002127659574468188</v>
       </c>
+      <c r="S342" s="1" t="n">
+        <v>0.3283</v>
+      </c>
+      <c r="T342" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -20373,6 +22431,12 @@
       <c r="R343" s="2" t="n">
         <v>0.002532928064842855</v>
       </c>
+      <c r="S343" s="1" t="n">
+        <v>0.01984</v>
+      </c>
+      <c r="T343" s="2" t="n">
+        <v>0.002526528549772685</v>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -20431,6 +22495,12 @@
       <c r="R344" s="2" t="n">
         <v>0.001379944802207964</v>
       </c>
+      <c r="S344" s="1" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="T344" s="2" t="n">
+        <v>0.001378043178686318</v>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -20489,6 +22559,12 @@
       <c r="R345" s="3" t="n">
         <v>-0.0007905138339920079</v>
       </c>
+      <c r="S345" s="1" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="T345" s="2" t="n">
+        <v>0.004746835443037979</v>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -20547,6 +22623,12 @@
       <c r="R346" s="3" t="n">
         <v>-0.0009695559433778934</v>
       </c>
+      <c r="S346" s="1" t="n">
+        <v>0.005172</v>
+      </c>
+      <c r="T346" s="2" t="n">
+        <v>0.003881987577639761</v>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -20605,6 +22687,12 @@
       <c r="R347" s="3" t="n">
         <v>-0.0007010164738871078</v>
       </c>
+      <c r="S347" s="1" t="n">
+        <v>0.05721</v>
+      </c>
+      <c r="T347" s="2" t="n">
+        <v>0.003332164152928722</v>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -20663,6 +22751,12 @@
       <c r="R348" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="S348" s="1" t="n">
+        <v>0.1272</v>
+      </c>
+      <c r="T348" s="2" t="n">
+        <v>0.0007867820613691325</v>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -20721,6 +22815,12 @@
       <c r="R349" s="3" t="n">
         <v>-0.0005569104910415274</v>
       </c>
+      <c r="S349" s="1" t="n">
+        <v>5197.7</v>
+      </c>
+      <c r="T349" s="3" t="n">
+        <v>-0.001287372223503155</v>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -20779,6 +22879,12 @@
       <c r="R350" s="3" t="n">
         <v>-0.004614838480653236</v>
       </c>
+      <c r="S350" s="1" t="n">
+        <v>0.02792</v>
+      </c>
+      <c r="T350" s="3" t="n">
+        <v>-0.004279600570613359</v>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -20837,6 +22943,12 @@
       <c r="R351" s="2" t="n">
         <v>0.001444043321299674</v>
       </c>
+      <c r="S351" s="1" t="n">
+        <v>0.001393</v>
+      </c>
+      <c r="T351" s="2" t="n">
+        <v>0.004325883201153517</v>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -20895,6 +23007,12 @@
       <c r="R352" s="3" t="n">
         <v>-0.005707038681039937</v>
       </c>
+      <c r="S352" s="1" t="n">
+        <v>0.01572</v>
+      </c>
+      <c r="T352" s="2" t="n">
+        <v>0.002551020408163383</v>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -20953,6 +23071,12 @@
       <c r="R353" s="2" t="n">
         <v>0.0004801536491677519</v>
       </c>
+      <c r="S353" s="1" t="n">
+        <v>6.251</v>
+      </c>
+      <c r="T353" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -21011,6 +23135,12 @@
       <c r="R354" s="2" t="n">
         <v>0.0006978367062106698</v>
       </c>
+      <c r="S354" s="1" t="n">
+        <v>0.287</v>
+      </c>
+      <c r="T354" s="2" t="n">
+        <v>0.0006973500697349302</v>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -21069,6 +23199,12 @@
       <c r="R355" s="2" t="n">
         <v>0.002177594967336071</v>
       </c>
+      <c r="S355" s="1" t="n">
+        <v>0.04151</v>
+      </c>
+      <c r="T355" s="2" t="n">
+        <v>0.002172863351038141</v>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -21127,6 +23263,12 @@
       <c r="R356" s="2" t="n">
         <v>0.0003510003510003367</v>
       </c>
+      <c r="S356" s="1" t="n">
+        <v>0.11312</v>
+      </c>
+      <c r="T356" s="3" t="n">
+        <v>-0.007719298245614086</v>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -21185,6 +23327,12 @@
       <c r="R357" s="2" t="n">
         <v>0.009021113243762027</v>
       </c>
+      <c r="S357" s="1" t="n">
+        <v>0.005227</v>
+      </c>
+      <c r="T357" s="3" t="n">
+        <v>-0.005706676811869985</v>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -21243,6 +23391,12 @@
       <c r="R358" s="3" t="n">
         <v>-0.001078748651564216</v>
       </c>
+      <c r="S358" s="1" t="n">
+        <v>0.186</v>
+      </c>
+      <c r="T358" s="2" t="n">
+        <v>0.004319654427645762</v>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -21301,6 +23455,12 @@
       <c r="R359" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="S359" s="1" t="n">
+        <v>0.1629</v>
+      </c>
+      <c r="T359" s="2" t="n">
+        <v>0.001229256299938402</v>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -21359,6 +23519,12 @@
       <c r="R360" s="3" t="n">
         <v>-0.0002355157795571391</v>
       </c>
+      <c r="S360" s="1" t="n">
+        <v>0.08533</v>
+      </c>
+      <c r="T360" s="2" t="n">
+        <v>0.005064782096584215</v>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -21417,6 +23583,12 @@
       <c r="R361" s="3" t="n">
         <v>-0.01161290322580643</v>
       </c>
+      <c r="S361" s="1" t="n">
+        <v>0.00764</v>
+      </c>
+      <c r="T361" s="3" t="n">
+        <v>-0.00261096605744126</v>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -21475,6 +23647,12 @@
       <c r="R362" s="3" t="n">
         <v>-0.00235294117647059</v>
       </c>
+      <c r="S362" s="1" t="n">
+        <v>0.4257</v>
+      </c>
+      <c r="T362" s="2" t="n">
+        <v>0.004009433962264233</v>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -21533,6 +23711,12 @@
       <c r="R363" s="3" t="n">
         <v>-0.002646903123345747</v>
       </c>
+      <c r="S363" s="1" t="n">
+        <v>3.789</v>
+      </c>
+      <c r="T363" s="2" t="n">
+        <v>0.005573248407643405</v>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -21591,6 +23775,12 @@
       <c r="R364" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="S364" s="1" t="n">
+        <v>0.01101</v>
+      </c>
+      <c r="T364" s="2" t="n">
+        <v>0.003646308113035561</v>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -21649,6 +23839,12 @@
       <c r="R365" s="2" t="n">
         <v>0.002188183807439862</v>
       </c>
+      <c r="S365" s="1" t="n">
+        <v>0.05503</v>
+      </c>
+      <c r="T365" s="2" t="n">
+        <v>0.001273653566229997</v>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -21707,6 +23903,12 @@
       <c r="R366" s="2" t="n">
         <v>0.01106194690265488</v>
       </c>
+      <c r="S366" s="1" t="n">
+        <v>0.02326</v>
+      </c>
+      <c r="T366" s="2" t="n">
+        <v>0.01794310722100659</v>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -21765,6 +23967,12 @@
       <c r="R367" s="2" t="n">
         <v>0.007363770250368207</v>
       </c>
+      <c r="S367" s="1" t="n">
+        <v>0.001353</v>
+      </c>
+      <c r="T367" s="3" t="n">
+        <v>-0.01096491228070178</v>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -21823,6 +24031,12 @@
       <c r="R368" s="2" t="n">
         <v>0.001403016485443549</v>
       </c>
+      <c r="S368" s="1" t="n">
+        <v>0.2865</v>
+      </c>
+      <c r="T368" s="2" t="n">
+        <v>0.003502626970227674</v>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -21881,6 +24095,12 @@
       <c r="R369" s="3" t="n">
         <v>-0.00644814615797969</v>
       </c>
+      <c r="S369" s="1" t="n">
+        <v>0.01859</v>
+      </c>
+      <c r="T369" s="2" t="n">
+        <v>0.005408328826392612</v>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -21939,6 +24159,12 @@
       <c r="R370" s="2" t="n">
         <v>0.0004546143355054136</v>
       </c>
+      <c r="S370" s="1" t="n">
+        <v>0.19851</v>
+      </c>
+      <c r="T370" s="2" t="n">
+        <v>0.002272038776128336</v>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -21997,6 +24223,12 @@
       <c r="R371" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="S371" s="1" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="T371" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -22055,6 +24287,12 @@
       <c r="R372" s="3" t="n">
         <v>-0.001901140684410701</v>
       </c>
+      <c r="S372" s="1" t="n">
+        <v>0.1052</v>
+      </c>
+      <c r="T372" s="2" t="n">
+        <v>0.001904761904761959</v>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -22113,6 +24351,12 @@
       <c r="R373" s="3" t="n">
         <v>-0.001658374792703136</v>
       </c>
+      <c r="S373" s="1" t="n">
+        <v>0.0663</v>
+      </c>
+      <c r="T373" s="2" t="n">
+        <v>0.001208094231349996</v>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -22171,6 +24415,12 @@
       <c r="R374" s="2" t="n">
         <v>0.00171097657278231</v>
       </c>
+      <c r="S374" s="1" t="n">
+        <v>0.007616</v>
+      </c>
+      <c r="T374" s="2" t="n">
+        <v>0.0006569438969912842</v>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -22229,6 +24479,12 @@
       <c r="R375" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="S375" s="1" t="n">
+        <v>0.159</v>
+      </c>
+      <c r="T375" s="2" t="n">
+        <v>0.001890359168241933</v>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -22287,6 +24543,12 @@
       <c r="R376" s="2" t="n">
         <v>0.005586592178770926</v>
       </c>
+      <c r="S376" s="1" t="n">
+        <v>0.003405</v>
+      </c>
+      <c r="T376" s="3" t="n">
+        <v>-0.00438596491228065</v>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -22345,6 +24607,12 @@
       <c r="R377" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="S377" s="1" t="n">
+        <v>0.0162</v>
+      </c>
+      <c r="T377" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -22403,6 +24671,12 @@
       <c r="R378" s="2" t="n">
         <v>0.01792114695340507</v>
       </c>
+      <c r="S378" s="1" t="n">
+        <v>0.01145</v>
+      </c>
+      <c r="T378" s="2" t="n">
+        <v>0.007922535211267588</v>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -22461,6 +24735,12 @@
       <c r="R379" s="2" t="n">
         <v>0.002807674309780113</v>
       </c>
+      <c r="S379" s="1" t="n">
+        <v>0.02141</v>
+      </c>
+      <c r="T379" s="3" t="n">
+        <v>-0.0009332711152591066</v>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -22519,6 +24799,12 @@
       <c r="R380" s="2" t="n">
         <v>0.003198294243070417</v>
       </c>
+      <c r="S380" s="1" t="n">
+        <v>0.01878</v>
+      </c>
+      <c r="T380" s="3" t="n">
+        <v>-0.002125398512220955</v>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -22577,6 +24863,12 @@
       <c r="R381" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="S381" s="1" t="n">
+        <v>0.1204</v>
+      </c>
+      <c r="T381" s="2" t="n">
+        <v>0.003333333333333313</v>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -22635,6 +24927,12 @@
       <c r="R382" s="3" t="n">
         <v>-0.00341646737273657</v>
       </c>
+      <c r="S382" s="1" t="n">
+        <v>0.02965</v>
+      </c>
+      <c r="T382" s="2" t="n">
+        <v>0.01645526225574212</v>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -22693,6 +24991,12 @@
       <c r="R383" s="2" t="n">
         <v>0.001226805704646556</v>
       </c>
+      <c r="S383" s="1" t="n">
+        <v>0.006545</v>
+      </c>
+      <c r="T383" s="2" t="n">
+        <v>0.0024506049931076</v>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -22751,6 +25055,12 @@
       <c r="R384" s="3" t="n">
         <v>-0.0004782400765185586</v>
       </c>
+      <c r="S384" s="1" t="n">
+        <v>0.02086</v>
+      </c>
+      <c r="T384" s="3" t="n">
+        <v>-0.001913875598086047</v>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -22809,6 +25119,12 @@
       <c r="R385" s="2" t="n">
         <v>0.001979414093428345</v>
       </c>
+      <c r="S385" s="1" t="n">
+        <v>2537</v>
+      </c>
+      <c r="T385" s="2" t="n">
+        <v>0.002370604504148558</v>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -22867,6 +25183,12 @@
       <c r="R386" s="2" t="n">
         <v>0.003047232097511514</v>
       </c>
+      <c r="S386" s="1" t="n">
+        <v>0.1986</v>
+      </c>
+      <c r="T386" s="2" t="n">
+        <v>0.005569620253164506</v>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -22925,6 +25247,12 @@
       <c r="R387" s="3" t="n">
         <v>-0.0007067137809187808</v>
       </c>
+      <c r="S387" s="1" t="n">
+        <v>0.08499</v>
+      </c>
+      <c r="T387" s="2" t="n">
+        <v>0.001768033946251737</v>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -22983,6 +25311,12 @@
       <c r="R388" s="2" t="n">
         <v>0.0005992808629645222</v>
       </c>
+      <c r="S388" s="1" t="n">
+        <v>0.005008</v>
+      </c>
+      <c r="T388" s="3" t="n">
+        <v>-0.0001996406468357222</v>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -23041,6 +25375,12 @@
       <c r="R389" s="2" t="n">
         <v>0.005364327223960598</v>
       </c>
+      <c r="S389" s="1" t="n">
+        <v>0.02265</v>
+      </c>
+      <c r="T389" s="2" t="n">
+        <v>0.007114273010226786</v>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -23099,6 +25439,12 @@
       <c r="R390" s="3" t="n">
         <v>-0.0005963029218842516</v>
       </c>
+      <c r="S390" s="1" t="n">
+        <v>0.5043</v>
+      </c>
+      <c r="T390" s="2" t="n">
+        <v>0.002983293556085811</v>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -23157,6 +25503,12 @@
       <c r="R391" s="2" t="n">
         <v>0.003323363243602607</v>
       </c>
+      <c r="S391" s="1" t="n">
+        <v>0.0006043999999999999</v>
+      </c>
+      <c r="T391" s="2" t="n">
+        <v>0.000993706525339361</v>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -23215,6 +25567,12 @@
       <c r="R392" s="2" t="n">
         <v>0.000513434879342723</v>
       </c>
+      <c r="S392" s="1" t="n">
+        <v>0.05842</v>
+      </c>
+      <c r="T392" s="3" t="n">
+        <v>-0.0006842285323297703</v>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -23273,6 +25631,12 @@
       <c r="R393" s="2" t="n">
         <v>0.001498127340824013</v>
       </c>
+      <c r="S393" s="1" t="n">
+        <v>0.2683</v>
+      </c>
+      <c r="T393" s="2" t="n">
+        <v>0.003365744203440375</v>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -23331,6 +25695,12 @@
       <c r="R394" s="3" t="n">
         <v>-0.001221187604945839</v>
       </c>
+      <c r="S394" s="1" t="n">
+        <v>0.006577</v>
+      </c>
+      <c r="T394" s="2" t="n">
+        <v>0.005196393091853917</v>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -23389,6 +25759,12 @@
       <c r="R395" s="3" t="n">
         <v>-0.002608695652173988</v>
       </c>
+      <c r="S395" s="1" t="n">
+        <v>0.1148</v>
+      </c>
+      <c r="T395" s="2" t="n">
+        <v>0.0008718395815170258</v>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -23447,6 +25823,12 @@
       <c r="R396" s="2" t="n">
         <v>0.0009740259740259343</v>
       </c>
+      <c r="S396" s="1" t="n">
+        <v>0.03094</v>
+      </c>
+      <c r="T396" s="2" t="n">
+        <v>0.003567953292247778</v>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -23505,6 +25887,12 @@
       <c r="R397" s="2" t="n">
         <v>0.003997335109926644</v>
       </c>
+      <c r="S397" s="1" t="n">
+        <v>0.1508</v>
+      </c>
+      <c r="T397" s="2" t="n">
+        <v>0.000663570006635627</v>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -23563,6 +25951,12 @@
       <c r="R398" s="3" t="n">
         <v>-0.0009068923821039795</v>
       </c>
+      <c r="S398" s="1" t="n">
+        <v>0.003304</v>
+      </c>
+      <c r="T398" s="3" t="n">
+        <v>-0.0003025718608169842</v>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -23621,6 +26015,12 @@
       <c r="R399" s="3" t="n">
         <v>-0.006406833956219892</v>
       </c>
+      <c r="S399" s="1" t="n">
+        <v>0.01841</v>
+      </c>
+      <c r="T399" s="3" t="n">
+        <v>-0.01074691026329942</v>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -23679,6 +26079,12 @@
       <c r="R400" s="2" t="n">
         <v>0.00382165605095543</v>
       </c>
+      <c r="S400" s="1" t="n">
+        <v>0.007012</v>
+      </c>
+      <c r="T400" s="3" t="n">
+        <v>-0.0112803158488438</v>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -23737,6 +26143,12 @@
       <c r="R401" s="3" t="n">
         <v>-0.001141389641888904</v>
       </c>
+      <c r="S401" s="1" t="n">
+        <v>0.006987</v>
+      </c>
+      <c r="T401" s="3" t="n">
+        <v>-0.0019997143265248</v>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -23795,6 +26207,12 @@
       <c r="R402" s="2" t="n">
         <v>0.001620341518135251</v>
       </c>
+      <c r="S402" s="1" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="T402" s="3" t="n">
+        <v>-0.004479840716774462</v>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -23853,6 +26271,12 @@
       <c r="R403" s="3" t="n">
         <v>-0.001231021748050832</v>
       </c>
+      <c r="S403" s="1" t="n">
+        <v>0.04923</v>
+      </c>
+      <c r="T403" s="2" t="n">
+        <v>0.01129827444535748</v>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -23911,6 +26335,12 @@
       <c r="R404" s="3" t="n">
         <v>-0.01027121374865738</v>
       </c>
+      <c r="S404" s="1" t="n">
+        <v>0.14815</v>
+      </c>
+      <c r="T404" s="2" t="n">
+        <v>0.004883673607813867</v>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -23969,6 +26399,12 @@
       <c r="R405" s="3" t="n">
         <v>-0.0009295840111549703</v>
       </c>
+      <c r="S405" s="1" t="n">
+        <v>0.04295</v>
+      </c>
+      <c r="T405" s="3" t="n">
+        <v>-0.0009304489416142909</v>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -24027,6 +26463,12 @@
       <c r="R406" s="2" t="n">
         <v>0.002094240837696337</v>
       </c>
+      <c r="S406" s="1" t="n">
+        <v>0.4788</v>
+      </c>
+      <c r="T406" s="2" t="n">
+        <v>0.0006269592476489498</v>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -24085,6 +26527,12 @@
       <c r="R407" s="2" t="n">
         <v>0.004079967360261217</v>
       </c>
+      <c r="S407" s="1" t="n">
+        <v>0.0004927</v>
+      </c>
+      <c r="T407" s="2" t="n">
+        <v>0.001015847216578541</v>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -24143,6 +26591,12 @@
       <c r="R408" s="2" t="n">
         <v>0.0008130081300812676</v>
       </c>
+      <c r="S408" s="1" t="n">
+        <v>0.01234</v>
+      </c>
+      <c r="T408" s="2" t="n">
+        <v>0.002437043054427337</v>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -24201,6 +26655,12 @@
       <c r="R409" s="3" t="n">
         <v>-0.0009422110552764525</v>
       </c>
+      <c r="S409" s="1" t="n">
+        <v>0.3179</v>
+      </c>
+      <c r="T409" s="3" t="n">
+        <v>-0.0006287331027977931</v>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -24259,6 +26719,12 @@
       <c r="R410" s="3" t="n">
         <v>-0.0004803073967340567</v>
       </c>
+      <c r="S410" s="1" t="n">
+        <v>0.04167</v>
+      </c>
+      <c r="T410" s="2" t="n">
+        <v>0.001201345506967839</v>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -24317,6 +26783,12 @@
       <c r="R411" s="2" t="n">
         <v>0.000337381916329271</v>
       </c>
+      <c r="S411" s="1" t="n">
+        <v>0.02968</v>
+      </c>
+      <c r="T411" s="2" t="n">
+        <v>0.001011804384485742</v>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
@@ -24375,6 +26847,12 @@
       <c r="R412" s="2" t="n">
         <v>0.001312910284463879</v>
       </c>
+      <c r="S412" s="1" t="n">
+        <v>0.004576</v>
+      </c>
+      <c r="T412" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -24433,6 +26911,12 @@
       <c r="R413" s="2" t="n">
         <v>0.001197604790419251</v>
       </c>
+      <c r="S413" s="1" t="n">
+        <v>0.2507</v>
+      </c>
+      <c r="T413" s="3" t="n">
+        <v>-0.0003987240829347866</v>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -24491,6 +26975,12 @@
       <c r="R414" s="3" t="n">
         <v>-0.0007824726134586165</v>
       </c>
+      <c r="S414" s="1" t="n">
+        <v>1.279</v>
+      </c>
+      <c r="T414" s="2" t="n">
+        <v>0.001566170712607676</v>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -24549,6 +27039,12 @@
       <c r="R415" s="2" t="n">
         <v>0.001840942562592008</v>
       </c>
+      <c r="S415" s="1" t="n">
+        <v>2.726</v>
+      </c>
+      <c r="T415" s="2" t="n">
+        <v>0.001837559720690883</v>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -24607,6 +27103,12 @@
       <c r="R416" s="2" t="n">
         <v>0.001242621932277054</v>
       </c>
+      <c r="S416" s="1" t="n">
+        <v>0.03218</v>
+      </c>
+      <c r="T416" s="3" t="n">
+        <v>-0.001551349674216613</v>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -24665,6 +27167,12 @@
       <c r="R417" s="3" t="n">
         <v>-0.002989536621823668</v>
       </c>
+      <c r="S417" s="1" t="n">
+        <v>0.03983</v>
+      </c>
+      <c r="T417" s="3" t="n">
+        <v>-0.004747626186906613</v>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -24723,6 +27231,12 @@
       <c r="R418" s="2" t="n">
         <v>0.002107759188512626</v>
       </c>
+      <c r="S418" s="1" t="n">
+        <v>0.07607</v>
+      </c>
+      <c r="T418" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -24781,6 +27295,12 @@
       <c r="R419" s="3" t="n">
         <v>-0.004511278195488668</v>
       </c>
+      <c r="S419" s="1" t="n">
+        <v>0.00663</v>
+      </c>
+      <c r="T419" s="2" t="n">
+        <v>0.001510574018126827</v>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -24839,6 +27359,12 @@
       <c r="R420" s="2" t="n">
         <v>0.001131221719456889</v>
       </c>
+      <c r="S420" s="1" t="n">
+        <v>0.0885</v>
+      </c>
+      <c r="T420" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -24897,6 +27423,12 @@
       <c r="R421" s="2" t="n">
         <v>0.004581424406497251</v>
       </c>
+      <c r="S421" s="1" t="n">
+        <v>0.2396</v>
+      </c>
+      <c r="T421" s="3" t="n">
+        <v>-0.006633499170812564</v>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
@@ -24955,6 +27487,12 @@
       <c r="R422" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="S422" s="1" t="n">
+        <v>0.0194</v>
+      </c>
+      <c r="T422" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -25013,6 +27551,12 @@
       <c r="R423" s="2" t="n">
         <v>0.001328903654485088</v>
       </c>
+      <c r="S423" s="1" t="n">
+        <v>0.1509</v>
+      </c>
+      <c r="T423" s="2" t="n">
+        <v>0.001327140013271438</v>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -25071,6 +27615,12 @@
       <c r="R424" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="S424" s="1" t="n">
+        <v>0.0002084</v>
+      </c>
+      <c r="T424" s="3" t="n">
+        <v>-0.001915708812260583</v>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -25129,6 +27679,12 @@
       <c r="R425" s="3" t="n">
         <v>-0.001612903225806453</v>
       </c>
+      <c r="S425" s="1" t="n">
+        <v>1.238</v>
+      </c>
+      <c r="T425" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
@@ -25187,6 +27743,12 @@
       <c r="R426" s="3" t="n">
         <v>-0.001415428167020525</v>
       </c>
+      <c r="S426" s="1" t="n">
+        <v>1.413</v>
+      </c>
+      <c r="T426" s="2" t="n">
+        <v>0.001417434443656982</v>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -25245,6 +27807,12 @@
       <c r="R427" s="2" t="n">
         <v>0.0005159958720330027</v>
       </c>
+      <c r="S427" s="1" t="n">
+        <v>0.01945</v>
+      </c>
+      <c r="T427" s="2" t="n">
+        <v>0.003094378545641957</v>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
@@ -25303,6 +27871,12 @@
       <c r="R428" s="3" t="n">
         <v>-0.0006075334143377639</v>
       </c>
+      <c r="S428" s="1" t="n">
+        <v>0.06602</v>
+      </c>
+      <c r="T428" s="2" t="n">
+        <v>0.003343465045592674</v>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
@@ -25361,6 +27935,12 @@
       <c r="R429" s="2" t="n">
         <v>0.001512859304084553</v>
       </c>
+      <c r="S429" s="1" t="n">
+        <v>0.1322</v>
+      </c>
+      <c r="T429" s="3" t="n">
+        <v>-0.001510574018126722</v>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
@@ -25419,6 +27999,12 @@
       <c r="R430" s="3" t="n">
         <v>-0.004419989175536752</v>
       </c>
+      <c r="S430" s="1" t="n">
+        <v>0.011022</v>
+      </c>
+      <c r="T430" s="3" t="n">
+        <v>-0.001359064963305191</v>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -25477,6 +28063,12 @@
       <c r="R431" s="2" t="n">
         <v>0.001500375093773512</v>
       </c>
+      <c r="S431" s="1" t="n">
+        <v>0.006775</v>
+      </c>
+      <c r="T431" s="2" t="n">
+        <v>0.01498127340823961</v>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
@@ -25535,6 +28127,12 @@
       <c r="R432" s="2" t="n">
         <v>0.0051311288483467</v>
       </c>
+      <c r="S432" s="1" t="n">
+        <v>0.001768</v>
+      </c>
+      <c r="T432" s="2" t="n">
+        <v>0.002836074872376638</v>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
@@ -25593,6 +28191,12 @@
       <c r="R433" s="3" t="n">
         <v>-0.0007369196757552808</v>
       </c>
+      <c r="S433" s="1" t="n">
+        <v>0.001353</v>
+      </c>
+      <c r="T433" s="3" t="n">
+        <v>-0.002212389380530947</v>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
@@ -25651,6 +28255,12 @@
       <c r="R434" s="2" t="n">
         <v>0.002439024390243962</v>
       </c>
+      <c r="S434" s="1" t="n">
+        <v>0.00041</v>
+      </c>
+      <c r="T434" s="3" t="n">
+        <v>-0.002433090024330959</v>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
@@ -25709,6 +28319,12 @@
       <c r="R435" s="2" t="n">
         <v>0.000869015642281553</v>
       </c>
+      <c r="S435" s="1" t="n">
+        <v>0.1265</v>
+      </c>
+      <c r="T435" s="3" t="n">
+        <v>-0.001499723735101395</v>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -25767,6 +28383,12 @@
       <c r="R436" s="3" t="n">
         <v>-0.0005144032921810491</v>
       </c>
+      <c r="S436" s="1" t="n">
+        <v>0.07775</v>
+      </c>
+      <c r="T436" s="2" t="n">
+        <v>0.0003860010293361071</v>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
@@ -25825,6 +28447,12 @@
       <c r="R437" s="3" t="n">
         <v>-0.001422025596460755</v>
       </c>
+      <c r="S437" s="1" t="n">
+        <v>0.6291</v>
+      </c>
+      <c r="T437" s="3" t="n">
+        <v>-0.004588607594936731</v>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -25883,6 +28511,12 @@
       <c r="R438" s="3" t="n">
         <v>-0.002059967956054012</v>
       </c>
+      <c r="S438" s="1" t="n">
+        <v>0.04379</v>
+      </c>
+      <c r="T438" s="2" t="n">
+        <v>0.004357798165137676</v>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
@@ -25941,6 +28575,12 @@
       <c r="R439" s="3" t="n">
         <v>-0.001135879596762894</v>
       </c>
+      <c r="S439" s="1" t="n">
+        <v>0.07033</v>
+      </c>
+      <c r="T439" s="3" t="n">
+        <v>-0.0002842928216061442</v>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
@@ -25999,6 +28639,12 @@
       <c r="R440" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="S440" s="1" t="n">
+        <v>0.001513</v>
+      </c>
+      <c r="T440" s="3" t="n">
+        <v>-0.000660501981505889</v>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -26057,6 +28703,12 @@
       <c r="R441" s="3" t="n">
         <v>-0.002641589180050794</v>
       </c>
+      <c r="S441" s="1" t="n">
+        <v>0.009457</v>
+      </c>
+      <c r="T441" s="2" t="n">
+        <v>0.001906981671787335</v>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
@@ -26115,6 +28767,12 @@
       <c r="R442" s="2" t="n">
         <v>0.003780718336483935</v>
       </c>
+      <c r="S442" s="1" t="n">
+        <v>1.063</v>
+      </c>
+      <c r="T442" s="2" t="n">
+        <v>0.0009416195856872785</v>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
@@ -26173,6 +28831,12 @@
       <c r="R443" s="3" t="n">
         <v>-0.002276867030965457</v>
       </c>
+      <c r="S443" s="1" t="n">
+        <v>0.02199</v>
+      </c>
+      <c r="T443" s="2" t="n">
+        <v>0.003651300775901425</v>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
@@ -26231,6 +28895,12 @@
       <c r="R444" s="3" t="n">
         <v>-0.002637826431020903</v>
       </c>
+      <c r="S444" s="1" t="n">
+        <v>0.0003804</v>
+      </c>
+      <c r="T444" s="2" t="n">
+        <v>0.006083046813012435</v>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
@@ -26289,6 +28959,12 @@
       <c r="R445" s="3" t="n">
         <v>-0.004228925852833501</v>
       </c>
+      <c r="S445" s="1" t="n">
+        <v>0.0354</v>
+      </c>
+      <c r="T445" s="2" t="n">
+        <v>0.002265005662514261</v>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
@@ -26347,6 +29023,12 @@
       <c r="R446" s="3" t="n">
         <v>-0.000589205750648225</v>
       </c>
+      <c r="S446" s="1" t="n">
+        <v>0.08542</v>
+      </c>
+      <c r="T446" s="2" t="n">
+        <v>0.00719254804857917</v>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
@@ -26405,6 +29087,12 @@
       <c r="R447" s="2" t="n">
         <v>0.007985257985258062</v>
       </c>
+      <c r="S447" s="1" t="n">
+        <v>3.287</v>
+      </c>
+      <c r="T447" s="2" t="n">
+        <v>0.001523461304082844</v>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
@@ -26463,6 +29151,12 @@
       <c r="R448" s="3" t="n">
         <v>-0.002188183807439844</v>
       </c>
+      <c r="S448" s="1" t="n">
+        <v>0.0639</v>
+      </c>
+      <c r="T448" s="2" t="n">
+        <v>0.0009398496240602209</v>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
@@ -26521,6 +29215,12 @@
       <c r="R449" s="3" t="n">
         <v>-0.00041067761806977</v>
       </c>
+      <c r="S449" s="1" t="n">
+        <v>0.4869</v>
+      </c>
+      <c r="T449" s="2" t="n">
+        <v>0.000205423171733749</v>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
@@ -26579,6 +29279,12 @@
       <c r="R450" s="2" t="n">
         <v>0.004040948275861998</v>
       </c>
+      <c r="S450" s="1" t="n">
+        <v>0.03731</v>
+      </c>
+      <c r="T450" s="2" t="n">
+        <v>0.001073249262141275</v>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -26637,6 +29343,12 @@
       <c r="R451" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="S451" s="1" t="n">
+        <v>0.00548</v>
+      </c>
+      <c r="T451" s="2" t="n">
+        <v>0.003663003663003673</v>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
@@ -26695,6 +29407,12 @@
       <c r="R452" s="2" t="n">
         <v>0.001349397590361458</v>
       </c>
+      <c r="S452" s="1" t="n">
+        <v>0.10312</v>
+      </c>
+      <c r="T452" s="3" t="n">
+        <v>-0.007411685436519328</v>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
@@ -26753,6 +29471,12 @@
       <c r="R453" s="2" t="n">
         <v>0.001249999999999949</v>
       </c>
+      <c r="S453" s="1" t="n">
+        <v>0.01607</v>
+      </c>
+      <c r="T453" s="2" t="n">
+        <v>0.003121098626716694</v>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
@@ -26811,6 +29535,12 @@
       <c r="R454" s="2" t="n">
         <v>0.00385964912280706</v>
       </c>
+      <c r="S454" s="1" t="n">
+        <v>2.881</v>
+      </c>
+      <c r="T454" s="2" t="n">
+        <v>0.006990562740300445</v>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
@@ -26869,6 +29599,12 @@
       <c r="R455" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="S455" s="1" t="n">
+        <v>0.894</v>
+      </c>
+      <c r="T455" s="3" t="n">
+        <v>-0.001117318435754191</v>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
@@ -26927,6 +29663,12 @@
       <c r="R456" s="3" t="n">
         <v>-0.001015916017609099</v>
       </c>
+      <c r="S456" s="1" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="T456" s="3" t="n">
+        <v>-0.003389830508474654</v>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -26985,6 +29727,12 @@
       <c r="R457" s="3" t="n">
         <v>-0.001013171225937142</v>
       </c>
+      <c r="S457" s="1" t="n">
+        <v>0.009860000000000001</v>
+      </c>
+      <c r="T457" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
@@ -27043,6 +29791,12 @@
       <c r="R458" s="2" t="n">
         <v>0.001777634130575403</v>
       </c>
+      <c r="S458" s="1" t="n">
+        <v>0.06199</v>
+      </c>
+      <c r="T458" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
@@ -27101,6 +29855,12 @@
       <c r="R459" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="S459" s="1" t="n">
+        <v>0.0143</v>
+      </c>
+      <c r="T459" s="2" t="n">
+        <v>0.0014005602240897</v>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
@@ -27159,6 +29919,12 @@
       <c r="R460" s="2" t="n">
         <v>0.001690881763527007</v>
       </c>
+      <c r="S460" s="1" t="n">
+        <v>0.016006</v>
+      </c>
+      <c r="T460" s="2" t="n">
+        <v>0.0006877149109096964</v>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
@@ -27217,6 +29983,12 @@
       <c r="R461" s="3" t="n">
         <v>-0.001207729468598985</v>
       </c>
+      <c r="S461" s="1" t="n">
+        <v>0.01665</v>
+      </c>
+      <c r="T461" s="2" t="n">
+        <v>0.006650544135429411</v>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
@@ -27275,6 +30047,12 @@
       <c r="R462" s="3" t="n">
         <v>-0.0004752851711026732</v>
       </c>
+      <c r="S462" s="1" t="n">
+        <v>0.0002099</v>
+      </c>
+      <c r="T462" s="3" t="n">
+        <v>-0.001902044698050322</v>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
@@ -27333,6 +30111,12 @@
       <c r="R463" s="2" t="n">
         <v>0.001011122345803871</v>
       </c>
+      <c r="S463" s="1" t="n">
+        <v>0.0989</v>
+      </c>
+      <c r="T463" s="3" t="n">
+        <v>-0.001010101010101039</v>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
@@ -27391,6 +30175,12 @@
       <c r="R464" s="2" t="n">
         <v>0.0007659900421294211</v>
       </c>
+      <c r="S464" s="1" t="n">
+        <v>0.0262</v>
+      </c>
+      <c r="T464" s="2" t="n">
+        <v>0.002678913126674344</v>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
@@ -27449,6 +30239,12 @@
       <c r="R465" s="2" t="n">
         <v>0.01797603195739011</v>
       </c>
+      <c r="S465" s="1" t="n">
+        <v>0.01516</v>
+      </c>
+      <c r="T465" s="3" t="n">
+        <v>-0.008502289077828641</v>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
@@ -27507,6 +30303,12 @@
       <c r="R466" s="3" t="n">
         <v>-0.001645338208409503</v>
       </c>
+      <c r="S466" s="1" t="n">
+        <v>0.05469</v>
+      </c>
+      <c r="T466" s="2" t="n">
+        <v>0.001464933162424532</v>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
@@ -27565,6 +30367,12 @@
       <c r="R467" s="3" t="n">
         <v>-0.002036067481093677</v>
       </c>
+      <c r="S467" s="1" t="n">
+        <v>0.03448</v>
+      </c>
+      <c r="T467" s="2" t="n">
+        <v>0.004954823666569412</v>
+      </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
@@ -27623,6 +30431,12 @@
       <c r="R468" s="3" t="n">
         <v>-0.001458789204959982</v>
       </c>
+      <c r="S468" s="1" t="n">
+        <v>27.43</v>
+      </c>
+      <c r="T468" s="2" t="n">
+        <v>0.00182615047479915</v>
+      </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
@@ -27681,6 +30495,12 @@
       <c r="R469" s="2" t="n">
         <v>0.003083936712255298</v>
       </c>
+      <c r="S469" s="1" t="n">
+        <v>0.0007474</v>
+      </c>
+      <c r="T469" s="3" t="n">
+        <v>-0.0009357037829168175</v>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
@@ -27739,6 +30559,12 @@
       <c r="R470" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="S470" s="1" t="n">
+        <v>0.888</v>
+      </c>
+      <c r="T470" s="2" t="n">
+        <v>0.01601830663615562</v>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
@@ -27797,6 +30623,12 @@
       <c r="R471" s="2" t="n">
         <v>0.002024291497975802</v>
       </c>
+      <c r="S471" s="1" t="n">
+        <v>0.00988</v>
+      </c>
+      <c r="T471" s="3" t="n">
+        <v>-0.002020202020202113</v>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
@@ -27855,6 +30687,12 @@
       <c r="R472" s="3" t="n">
         <v>-0.001289767841788425</v>
       </c>
+      <c r="S472" s="1" t="n">
+        <v>0.04653</v>
+      </c>
+      <c r="T472" s="2" t="n">
+        <v>0.001506672406371085</v>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -27913,6 +30751,12 @@
       <c r="R473" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="S473" s="1" t="n">
+        <v>0.2741</v>
+      </c>
+      <c r="T473" s="2" t="n">
+        <v>0.0003649635036495948</v>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
@@ -27971,6 +30815,12 @@
       <c r="R474" s="2" t="n">
         <v>0.006439742410303645</v>
       </c>
+      <c r="S474" s="1" t="n">
+        <v>0.04392</v>
+      </c>
+      <c r="T474" s="2" t="n">
+        <v>0.003656307129798913</v>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
@@ -28029,6 +30879,12 @@
       <c r="R475" s="2" t="n">
         <v>0.0005915059742103154</v>
       </c>
+      <c r="S475" s="1" t="n">
+        <v>0.00847</v>
+      </c>
+      <c r="T475" s="2" t="n">
+        <v>0.001418775124142806</v>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
@@ -28087,6 +30943,12 @@
       <c r="R476" s="2" t="n">
         <v>0.003680529996319405</v>
       </c>
+      <c r="S476" s="1" t="n">
+        <v>0.08189</v>
+      </c>
+      <c r="T476" s="2" t="n">
+        <v>0.0009778755653344412</v>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
@@ -28145,6 +31007,12 @@
       <c r="R477" s="3" t="n">
         <v>-0.0007358351729211846</v>
       </c>
+      <c r="S477" s="1" t="n">
+        <v>0.1361</v>
+      </c>
+      <c r="T477" s="2" t="n">
+        <v>0.002209131075110417</v>
+      </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
@@ -28203,6 +31071,12 @@
       <c r="R478" s="2" t="n">
         <v>0.00151476899772782</v>
       </c>
+      <c r="S478" s="1" t="n">
+        <v>0.3968</v>
+      </c>
+      <c r="T478" s="2" t="n">
+        <v>0.0002520796571716385</v>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
@@ -28261,6 +31135,12 @@
       <c r="R479" s="2" t="n">
         <v>0.006874481450752727</v>
       </c>
+      <c r="S479" s="1" t="n">
+        <v>0.008663000000000001</v>
+      </c>
+      <c r="T479" s="2" t="n">
+        <v>0.01977633902295465</v>
+      </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
@@ -28319,6 +31199,12 @@
       <c r="R480" s="3" t="n">
         <v>-0.0006305170239596212</v>
       </c>
+      <c r="S480" s="1" t="n">
+        <v>0.01612</v>
+      </c>
+      <c r="T480" s="2" t="n">
+        <v>0.01703470031545738</v>
+      </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
@@ -28377,6 +31263,12 @@
       <c r="R481" s="3" t="n">
         <v>-0.002689204763734176</v>
       </c>
+      <c r="S481" s="1" t="n">
+        <v>0.07865999999999999</v>
+      </c>
+      <c r="T481" s="2" t="n">
+        <v>0.01001540832049293</v>
+      </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
@@ -28435,6 +31327,12 @@
       <c r="R482" s="3" t="n">
         <v>-0.001191895113230125</v>
       </c>
+      <c r="S482" s="1" t="n">
+        <v>0.05038</v>
+      </c>
+      <c r="T482" s="2" t="n">
+        <v>0.001988862370724003</v>
+      </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
@@ -28493,6 +31391,12 @@
       <c r="R483" s="2" t="n">
         <v>0.004140786749482412</v>
       </c>
+      <c r="S483" s="1" t="n">
+        <v>0.009719999999999999</v>
+      </c>
+      <c r="T483" s="2" t="n">
+        <v>0.002061855670103009</v>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
@@ -28551,6 +31455,12 @@
       <c r="R484" s="3" t="n">
         <v>-0.001324113579520476</v>
       </c>
+      <c r="S484" s="1" t="n">
+        <v>0.06805</v>
+      </c>
+      <c r="T484" s="2" t="n">
+        <v>0.00250441956393641</v>
+      </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
@@ -28609,6 +31519,12 @@
       <c r="R485" s="3" t="n">
         <v>-0.003556345854634329</v>
       </c>
+      <c r="S485" s="1" t="n">
+        <v>0.0004491</v>
+      </c>
+      <c r="T485" s="2" t="n">
+        <v>0.001784519295114922</v>
+      </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
@@ -28667,6 +31583,12 @@
       <c r="R486" s="2" t="n">
         <v>0.002919522721502844</v>
       </c>
+      <c r="S486" s="1" t="n">
+        <v>0.07948</v>
+      </c>
+      <c r="T486" s="2" t="n">
+        <v>0.005948614099481056</v>
+      </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
@@ -28725,6 +31647,12 @@
       <c r="R487" s="3" t="n">
         <v>-0.0005783689994216451</v>
       </c>
+      <c r="S487" s="1" t="n">
+        <v>0.0001731</v>
+      </c>
+      <c r="T487" s="2" t="n">
+        <v>0.001736111111111153</v>
+      </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
@@ -28783,6 +31711,12 @@
       <c r="R488" s="2" t="n">
         <v>0.006302280279592012</v>
       </c>
+      <c r="S488" s="1" t="n">
+        <v>0.08988</v>
+      </c>
+      <c r="T488" s="2" t="n">
+        <v>0.02345707128216814</v>
+      </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
@@ -28841,6 +31775,12 @@
       <c r="R489" s="2" t="n">
         <v>0.002740881298756023</v>
       </c>
+      <c r="S489" s="1" t="n">
+        <v>0.04773</v>
+      </c>
+      <c r="T489" s="2" t="n">
+        <v>0.003574432296047172</v>
+      </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
@@ -28899,6 +31839,12 @@
       <c r="R490" s="2" t="n">
         <v>0.008281573498964825</v>
       </c>
+      <c r="S490" s="1" t="n">
+        <v>0.0389</v>
+      </c>
+      <c r="T490" s="3" t="n">
+        <v>-0.001540041067761922</v>
+      </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
@@ -28957,6 +31903,12 @@
       <c r="R491" s="2" t="n">
         <v>0.004244372990353659</v>
       </c>
+      <c r="S491" s="1" t="n">
+        <v>0.07829</v>
+      </c>
+      <c r="T491" s="2" t="n">
+        <v>0.002689549180327893</v>
+      </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
@@ -29015,6 +31967,12 @@
       <c r="R492" s="2" t="n">
         <v>0.0007941550190596329</v>
       </c>
+      <c r="S492" s="1" t="n">
+        <v>0.06346</v>
+      </c>
+      <c r="T492" s="2" t="n">
+        <v>0.00714172353594677</v>
+      </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
@@ -29073,6 +32031,12 @@
       <c r="R493" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="S493" s="1" t="n">
+        <v>0.00526</v>
+      </c>
+      <c r="T493" s="3" t="n">
+        <v>-0.001897533206831207</v>
+      </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
@@ -29131,6 +32095,12 @@
       <c r="R494" s="3" t="n">
         <v>-0.003988397389412581</v>
       </c>
+      <c r="S494" s="1" t="n">
+        <v>0.2755</v>
+      </c>
+      <c r="T494" s="2" t="n">
+        <v>0.002912267928649519</v>
+      </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
@@ -29189,6 +32159,12 @@
       <c r="R495" s="3" t="n">
         <v>-0.001883239171374688</v>
       </c>
+      <c r="S495" s="1" t="n">
+        <v>0.06375</v>
+      </c>
+      <c r="T495" s="2" t="n">
+        <v>0.002358490566037694</v>
+      </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
@@ -29247,6 +32223,12 @@
       <c r="R496" s="3" t="n">
         <v>-0.001711156741957565</v>
       </c>
+      <c r="S496" s="1" t="n">
+        <v>0.2932</v>
+      </c>
+      <c r="T496" s="2" t="n">
+        <v>0.005142269454919442</v>
+      </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
@@ -29305,6 +32287,12 @@
       <c r="R497" s="3" t="n">
         <v>-0.04926941190677455</v>
       </c>
+      <c r="S497" s="1" t="n">
+        <v>0.07814</v>
+      </c>
+      <c r="T497" s="3" t="n">
+        <v>-0.007493966721707016</v>
+      </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
@@ -29363,6 +32351,12 @@
       <c r="R498" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="S498" s="1" t="n">
+        <v>0.1032</v>
+      </c>
+      <c r="T498" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
@@ -29421,6 +32415,12 @@
       <c r="R499" s="2" t="n">
         <v>0.001688374336710097</v>
       </c>
+      <c r="S499" s="1" t="n">
+        <v>0.04167</v>
+      </c>
+      <c r="T499" s="2" t="n">
+        <v>0.003371057067180381</v>
+      </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
@@ -29479,6 +32479,12 @@
       <c r="R500" s="3" t="n">
         <v>-0.003960396039603971</v>
       </c>
+      <c r="S500" s="1" t="n">
+        <v>0.03998</v>
+      </c>
+      <c r="T500" s="3" t="n">
+        <v>-0.006461232604373667</v>
+      </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
@@ -29537,6 +32543,12 @@
       <c r="R501" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="S501" s="1" t="n">
+        <v>0.0988</v>
+      </c>
+      <c r="T501" s="3" t="n">
+        <v>-0.001011122345803871</v>
+      </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
@@ -29595,6 +32607,12 @@
       <c r="R502" s="2" t="n">
         <v>0.0009090909090908984</v>
       </c>
+      <c r="S502" s="1" t="n">
+        <v>0.003307</v>
+      </c>
+      <c r="T502" s="2" t="n">
+        <v>0.001211020284589796</v>
+      </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
@@ -29653,6 +32671,12 @@
       <c r="R503" s="3" t="n">
         <v>-0.007494646680942065</v>
       </c>
+      <c r="S503" s="1" t="n">
+        <v>0.009140000000000001</v>
+      </c>
+      <c r="T503" s="3" t="n">
+        <v>-0.0140237324703344</v>
+      </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
@@ -29711,6 +32735,12 @@
       <c r="R504" s="2" t="n">
         <v>0.00378310214375799</v>
       </c>
+      <c r="S504" s="1" t="n">
+        <v>0.1593</v>
+      </c>
+      <c r="T504" s="2" t="n">
+        <v>0.0006281407035175188</v>
+      </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
@@ -29769,6 +32799,12 @@
       <c r="R505" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="S505" s="1" t="n">
+        <v>0.1311</v>
+      </c>
+      <c r="T505" s="2" t="n">
+        <v>0.0007633587786258701</v>
+      </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
@@ -29827,6 +32863,12 @@
       <c r="R506" s="2" t="n">
         <v>0.0005924170616113503</v>
       </c>
+      <c r="S506" s="1" t="n">
+        <v>0.01689</v>
+      </c>
+      <c r="T506" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
@@ -29885,6 +32927,12 @@
       <c r="R507" s="2" t="n">
         <v>0.00104094378903538</v>
       </c>
+      <c r="S507" s="1" t="n">
+        <v>0.002881</v>
+      </c>
+      <c r="T507" s="3" t="n">
+        <v>-0.001386481802426377</v>
+      </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
@@ -29943,6 +32991,12 @@
       <c r="R508" s="3" t="n">
         <v>-0.0009021199819577013</v>
       </c>
+      <c r="S508" s="1" t="n">
+        <v>2.219</v>
+      </c>
+      <c r="T508" s="2" t="n">
+        <v>0.001805869074492101</v>
+      </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
@@ -30001,6 +33055,12 @@
       <c r="R509" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="S509" s="1" t="n">
+        <v>0.05488</v>
+      </c>
+      <c r="T509" s="2" t="n">
+        <v>0.004024881083058872</v>
+      </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
@@ -30059,6 +33119,12 @@
       <c r="R510" s="2" t="n">
         <v>0.002051282051281968</v>
       </c>
+      <c r="S510" s="1" t="n">
+        <v>0.02938</v>
+      </c>
+      <c r="T510" s="2" t="n">
+        <v>0.002388263391334037</v>
+      </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
@@ -30117,6 +33183,12 @@
       <c r="R511" s="2" t="n">
         <v>0.0004956629491946995</v>
       </c>
+      <c r="S511" s="1" t="n">
+        <v>0.04038</v>
+      </c>
+      <c r="T511" s="2" t="n">
+        <v>0.0002477086945750836</v>
+      </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
@@ -30175,6 +33247,12 @@
       <c r="R512" s="3" t="n">
         <v>-0.01162790697674404</v>
       </c>
+      <c r="S512" s="1" t="n">
+        <v>0.089</v>
+      </c>
+      <c r="T512" s="2" t="n">
+        <v>0.04705882352941164</v>
+      </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
@@ -30233,6 +33311,12 @@
       <c r="R513" s="3" t="n">
         <v>-0.04158673185221851</v>
       </c>
+      <c r="S513" s="1" t="n">
+        <v>0.015164</v>
+      </c>
+      <c r="T513" s="3" t="n">
+        <v>-0.02085620197585073</v>
+      </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
@@ -30291,6 +33375,12 @@
       <c r="R514" s="2" t="n">
         <v>0.0005757052389177706</v>
       </c>
+      <c r="S514" s="1" t="n">
+        <v>0.1737</v>
+      </c>
+      <c r="T514" s="3" t="n">
+        <v>-0.0005753739930956084</v>
+      </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
@@ -30349,6 +33439,12 @@
       <c r="R515" s="2" t="n">
         <v>0.0009302325581395615</v>
       </c>
+      <c r="S515" s="1" t="n">
+        <v>0.1077</v>
+      </c>
+      <c r="T515" s="2" t="n">
+        <v>0.0009293680297398036</v>
+      </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
@@ -30407,6 +33503,12 @@
       <c r="R516" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="S516" s="1" t="n">
+        <v>0.00267</v>
+      </c>
+      <c r="T516" s="2" t="n">
+        <v>0.003759398496240611</v>
+      </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
@@ -30465,6 +33567,12 @@
       <c r="R517" s="3" t="n">
         <v>-0.0007775042114811364</v>
       </c>
+      <c r="S517" s="1" t="n">
+        <v>0.007717</v>
+      </c>
+      <c r="T517" s="2" t="n">
+        <v>0.0007781091946569744</v>
+      </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
@@ -30523,6 +33631,12 @@
       <c r="R518" s="2" t="n">
         <v>0.002594033722438399</v>
       </c>
+      <c r="S518" s="1" t="n">
+        <v>0.01557</v>
+      </c>
+      <c r="T518" s="2" t="n">
+        <v>0.007115135834411431</v>
+      </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
@@ -30581,6 +33695,12 @@
       <c r="R519" s="2" t="n">
         <v>0.002392344497607766</v>
       </c>
+      <c r="S519" s="1" t="n">
+        <v>0.004188</v>
+      </c>
+      <c r="T519" s="3" t="n">
+        <v>-0.0004773269689738103</v>
+      </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
@@ -30639,6 +33759,12 @@
       <c r="R520" s="2" t="n">
         <v>0.0008643042350906792</v>
       </c>
+      <c r="S520" s="1" t="n">
+        <v>0.001158</v>
+      </c>
+      <c r="T520" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
@@ -30697,6 +33823,12 @@
       <c r="R521" s="2" t="n">
         <v>0.002247191011235863</v>
       </c>
+      <c r="S521" s="1" t="n">
+        <v>0.01331</v>
+      </c>
+      <c r="T521" s="3" t="n">
+        <v>-0.005231689088191247</v>
+      </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
@@ -30755,6 +33887,12 @@
       <c r="R522" s="2" t="n">
         <v>0.001747742499271743</v>
       </c>
+      <c r="S522" s="1" t="n">
+        <v>0.6856</v>
+      </c>
+      <c r="T522" s="3" t="n">
+        <v>-0.003198604245420151</v>
+      </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
@@ -30813,6 +33951,12 @@
       <c r="R523" s="2" t="n">
         <v>0.005576208178438682</v>
       </c>
+      <c r="S523" s="1" t="n">
+        <v>0.07017</v>
+      </c>
+      <c r="T523" s="3" t="n">
+        <v>-0.002274989335987592</v>
+      </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
@@ -30871,6 +34015,12 @@
       <c r="R524" s="2" t="n">
         <v>0.0008650519031141515</v>
       </c>
+      <c r="S524" s="1" t="n">
+        <v>0.01167</v>
+      </c>
+      <c r="T524" s="2" t="n">
+        <v>0.008643042350907466</v>
+      </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
@@ -30929,6 +34079,12 @@
       <c r="R525" s="2" t="n">
         <v>0.004281345565749274</v>
       </c>
+      <c r="S525" s="1" t="n">
+        <v>0.01644</v>
+      </c>
+      <c r="T525" s="2" t="n">
+        <v>0.001218026796589475</v>
+      </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
@@ -30987,6 +34143,12 @@
       <c r="R526" s="3" t="n">
         <v>-0.002674392689993308</v>
       </c>
+      <c r="S526" s="1" t="n">
+        <v>0.13477</v>
+      </c>
+      <c r="T526" s="2" t="n">
+        <v>0.003873370577281137</v>
+      </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
@@ -31045,6 +34207,12 @@
       <c r="R527" s="3" t="n">
         <v>-0.0009293680297399003</v>
       </c>
+      <c r="S527" s="1" t="n">
+        <v>0.04303</v>
+      </c>
+      <c r="T527" s="2" t="n">
+        <v>0.0006976744186047034</v>
+      </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
@@ -31103,6 +34271,12 @@
       <c r="R528" s="2" t="n">
         <v>0.002206693637366844</v>
       </c>
+      <c r="S528" s="1" t="n">
+        <v>0.2722</v>
+      </c>
+      <c r="T528" s="3" t="n">
+        <v>-0.001100917431192743</v>
+      </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
@@ -31161,6 +34335,12 @@
       <c r="R529" s="3" t="n">
         <v>-0.0006889899407469566</v>
       </c>
+      <c r="S529" s="1" t="n">
+        <v>0.0007241</v>
+      </c>
+      <c r="T529" s="3" t="n">
+        <v>-0.001516822945394336</v>
+      </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
@@ -31219,6 +34399,12 @@
       <c r="R530" s="3" t="n">
         <v>-0.001447527141133879</v>
       </c>
+      <c r="S530" s="1" t="n">
+        <v>0.004167</v>
+      </c>
+      <c r="T530" s="2" t="n">
+        <v>0.006764919062575351</v>
+      </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
@@ -31277,6 +34463,12 @@
       <c r="R531" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="S531" s="1" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="T531" s="3" t="n">
+        <v>-0.0007616146230006777</v>
+      </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
@@ -31335,6 +34527,12 @@
       <c r="R532" s="2" t="n">
         <v>0.001699235344095206</v>
       </c>
+      <c r="S532" s="1" t="n">
+        <v>0.118</v>
+      </c>
+      <c r="T532" s="2" t="n">
+        <v>0.0008481764206954112</v>
+      </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
@@ -31393,6 +34591,12 @@
       <c r="R533" s="3" t="n">
         <v>-0.000562008242787473</v>
       </c>
+      <c r="S533" s="1" t="n">
+        <v>0.05358</v>
+      </c>
+      <c r="T533" s="2" t="n">
+        <v>0.004311152764761032</v>
+      </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
@@ -31451,6 +34655,12 @@
       <c r="R534" s="3" t="n">
         <v>-0.000667556742323024</v>
       </c>
+      <c r="S534" s="1" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="T534" s="2" t="n">
+        <v>0.002004008016032029</v>
+      </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
@@ -31509,6 +34719,12 @@
       <c r="R535" s="2" t="n">
         <v>0.001174398120962959</v>
       </c>
+      <c r="S535" s="1" t="n">
+        <v>0.01706</v>
+      </c>
+      <c r="T535" s="2" t="n">
+        <v>0.0005865102639295949</v>
+      </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
@@ -31567,6 +34783,12 @@
       <c r="R536" s="2" t="n">
         <v>0.0006019261637239964</v>
       </c>
+      <c r="S536" s="1" t="n">
+        <v>0.005011</v>
+      </c>
+      <c r="T536" s="2" t="n">
+        <v>0.004812512532584664</v>
+      </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
@@ -31625,6 +34847,12 @@
       <c r="R537" s="2" t="n">
         <v>0.002402196293754406</v>
       </c>
+      <c r="S537" s="1" t="n">
+        <v>0.2922</v>
+      </c>
+      <c r="T537" s="2" t="n">
+        <v>0.0003423485107839403</v>
+      </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
@@ -31683,6 +34911,12 @@
       <c r="R538" s="2" t="n">
         <v>0.00377073906485682</v>
       </c>
+      <c r="S538" s="1" t="n">
+        <v>0.01328</v>
+      </c>
+      <c r="T538" s="3" t="n">
+        <v>-0.002253944402704772</v>
+      </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
@@ -31741,6 +34975,12 @@
       <c r="R539" s="3" t="n">
         <v>-0.002819170358437399</v>
       </c>
+      <c r="S539" s="1" t="n">
+        <v>0.0252</v>
+      </c>
+      <c r="T539" s="2" t="n">
+        <v>0.01777059773828754</v>
+      </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
@@ -31799,6 +35039,12 @@
       <c r="R540" s="3" t="n">
         <v>-0.000175932441942348</v>
       </c>
+      <c r="S540" s="1" t="n">
+        <v>0.05685</v>
+      </c>
+      <c r="T540" s="2" t="n">
+        <v>0.0003519267992257467</v>
+      </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
@@ -31857,6 +35103,12 @@
       <c r="R541" s="2" t="n">
         <v>0.008695652173912992</v>
       </c>
+      <c r="S541" s="1" t="n">
+        <v>0.0116</v>
+      </c>
+      <c r="T541" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
@@ -31915,6 +35167,12 @@
       <c r="R542" s="2" t="n">
         <v>0.009009009009008922</v>
       </c>
+      <c r="S542" s="1" t="n">
+        <v>1.11e-05</v>
+      </c>
+      <c r="T542" s="3" t="n">
+        <v>-0.008928571428571343</v>
+      </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
@@ -31972,6 +35230,12 @@
       </c>
       <c r="R543" s="3" t="n">
         <v>-0.003799185888738161</v>
+      </c>
+      <c r="S543" s="1" t="n">
+        <v>0.003692</v>
+      </c>
+      <c r="T543" s="2" t="n">
+        <v>0.005720512122037643</v>
       </c>
     </row>
   </sheetData>

--- a/binance-usdt-perpetual-data/weeks/2026-03-09_2026-03-15/2026-03-12.xlsx
+++ b/binance-usdt-perpetual-data/weeks/2026-03-09_2026-03-15/2026-03-12.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T543"/>
+  <dimension ref="A1:V543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -446,6 +446,8 @@
     <col width="18" customWidth="1" min="18" max="18"/>
     <col width="13" customWidth="1" min="19" max="19"/>
     <col width="18" customWidth="1" min="20" max="20"/>
+    <col width="13" customWidth="1" min="21" max="21"/>
+    <col width="18" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -549,6 +551,16 @@
           <t>change_02:15</t>
         </is>
       </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>price_02:30</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>change_02:30</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -613,6 +625,12 @@
       <c r="T2" s="3" t="n">
         <v>-0.0006543845887483009</v>
       </c>
+      <c r="U2" s="1" t="n">
+        <v>70667.3</v>
+      </c>
+      <c r="V2" s="3" t="n">
+        <v>-0.0005642989681389473</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -677,6 +695,12 @@
       <c r="T3" s="2" t="n">
         <v>4.837227301306489e-05</v>
       </c>
+      <c r="U3" s="1" t="n">
+        <v>2072.23</v>
+      </c>
+      <c r="V3" s="2" t="n">
+        <v>0.002336267775950434</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -741,6 +765,12 @@
       <c r="T4" s="2" t="n">
         <v>0.006305893143774331</v>
       </c>
+      <c r="U4" s="1" t="n">
+        <v>87.59</v>
+      </c>
+      <c r="V4" s="3" t="n">
+        <v>-0.00205081462914427</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -805,6 +835,12 @@
       <c r="T5" s="3" t="n">
         <v>-0.04269896193771623</v>
       </c>
+      <c r="U5" s="1" t="n">
+        <v>0.013998</v>
+      </c>
+      <c r="V5" s="2" t="n">
+        <v>0.01192799826501845</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -869,6 +905,12 @@
       <c r="T6" s="2" t="n">
         <v>0.003203759077317329</v>
       </c>
+      <c r="U6" s="1" t="n">
+        <v>0.09413000000000001</v>
+      </c>
+      <c r="V6" s="2" t="n">
+        <v>0.00202256759633819</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -933,6 +975,12 @@
       <c r="T7" s="2" t="n">
         <v>0.001861264227933235</v>
       </c>
+      <c r="U7" s="1" t="n">
+        <v>1.4002</v>
+      </c>
+      <c r="V7" s="2" t="n">
+        <v>0.0005001786352268117</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -997,6 +1045,12 @@
       <c r="T8" s="2" t="n">
         <v>0.000637348629700339</v>
       </c>
+      <c r="U8" s="1" t="n">
+        <v>36.047</v>
+      </c>
+      <c r="V8" s="3" t="n">
+        <v>-0.001744669066740581</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1061,6 +1115,12 @@
       <c r="T9" s="2" t="n">
         <v>0.001426621055699679</v>
       </c>
+      <c r="U9" s="1" t="n">
+        <v>652.55</v>
+      </c>
+      <c r="V9" s="3" t="n">
+        <v>-0.0004135902699060928</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1125,6 +1185,12 @@
       <c r="T10" s="2" t="n">
         <v>0.0008403949856432842</v>
       </c>
+      <c r="U10" s="1" t="n">
+        <v>14.203</v>
+      </c>
+      <c r="V10" s="3" t="n">
+        <v>-0.00615772164299216</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1189,6 +1255,12 @@
       <c r="T11" s="2" t="n">
         <v>0.002409183239642831</v>
       </c>
+      <c r="U11" s="1" t="n">
+        <v>212.64</v>
+      </c>
+      <c r="V11" s="2" t="n">
+        <v>0.002073515551366625</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1253,6 +1325,12 @@
       <c r="T12" s="2" t="n">
         <v>0.001633744244764551</v>
       </c>
+      <c r="U12" s="1" t="n">
+        <v>0.0033711</v>
+      </c>
+      <c r="V12" s="3" t="n">
+        <v>-0.0002669039145907056</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1317,6 +1395,12 @@
       <c r="T13" s="2" t="n">
         <v>0.01122672508214679</v>
       </c>
+      <c r="U13" s="1" t="n">
+        <v>0.03692</v>
+      </c>
+      <c r="V13" s="3" t="n">
+        <v>-0.0002707825616029278</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1381,6 +1465,12 @@
       <c r="T14" s="2" t="n">
         <v>0.004235656526761695</v>
       </c>
+      <c r="U14" s="1" t="n">
+        <v>2.598</v>
+      </c>
+      <c r="V14" s="3" t="n">
+        <v>-0.003834355828220947</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1445,6 +1535,12 @@
       <c r="T15" s="2" t="n">
         <v>0.002552843868069088</v>
       </c>
+      <c r="U15" s="1" t="n">
+        <v>0.9821</v>
+      </c>
+      <c r="V15" s="2" t="n">
+        <v>0.0003055612140965237</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1509,6 +1605,12 @@
       <c r="T16" s="2" t="n">
         <v>0.003740648379052278</v>
       </c>
+      <c r="U16" s="1" t="n">
+        <v>0.05688</v>
+      </c>
+      <c r="V16" s="2" t="n">
+        <v>0.009405501330967217</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1573,6 +1675,12 @@
       <c r="T17" s="2" t="n">
         <v>0.002270147559591376</v>
       </c>
+      <c r="U17" s="1" t="n">
+        <v>0.885</v>
+      </c>
+      <c r="V17" s="2" t="n">
+        <v>0.002265005662514158</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1637,6 +1745,12 @@
       <c r="T18" s="2" t="n">
         <v>0.002266717038156364</v>
       </c>
+      <c r="U18" s="1" t="n">
+        <v>0.2655</v>
+      </c>
+      <c r="V18" s="2" t="n">
+        <v>0.00075386355069745</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1701,6 +1815,12 @@
       <c r="T19" s="3" t="n">
         <v>-0.005385479365262169</v>
       </c>
+      <c r="U19" s="1" t="n">
+        <v>0.35041</v>
+      </c>
+      <c r="V19" s="2" t="n">
+        <v>0.01462242297892054</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1765,6 +1885,12 @@
       <c r="T20" s="2" t="n">
         <v>0.003724009516913167</v>
       </c>
+      <c r="U20" s="1" t="n">
+        <v>9.714</v>
+      </c>
+      <c r="V20" s="2" t="n">
+        <v>0.001133669998969495</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1829,6 +1955,12 @@
       <c r="T21" s="2" t="n">
         <v>0.00195901145268227</v>
       </c>
+      <c r="U21" s="1" t="n">
+        <v>198.61</v>
+      </c>
+      <c r="V21" s="3" t="n">
+        <v>-0.004311425276983934</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1893,6 +2025,12 @@
       <c r="T22" s="2" t="n">
         <v>0.003932420623361381</v>
       </c>
+      <c r="U22" s="1" t="n">
+        <v>0.020972</v>
+      </c>
+      <c r="V22" s="2" t="n">
+        <v>0.01416896368296347</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1957,6 +2095,12 @@
       <c r="T23" s="2" t="n">
         <v>0.00210235858353586</v>
       </c>
+      <c r="U23" s="1" t="n">
+        <v>457.03</v>
+      </c>
+      <c r="V23" s="3" t="n">
+        <v>-0.001223802967722202</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2021,6 +2165,12 @@
       <c r="T24" s="2" t="n">
         <v>0.0005844591913948113</v>
       </c>
+      <c r="U24" s="1" t="n">
+        <v>5175.41</v>
+      </c>
+      <c r="V24" s="2" t="n">
+        <v>0.001009634075343509</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2085,6 +2235,12 @@
       <c r="T25" s="2" t="n">
         <v>0.0009912986011673714</v>
       </c>
+      <c r="U25" s="1" t="n">
+        <v>9.086</v>
+      </c>
+      <c r="V25" s="3" t="n">
+        <v>-0.0002200704225350893</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2149,6 +2305,12 @@
       <c r="T26" s="2" t="n">
         <v>0.01237078461277752</v>
       </c>
+      <c r="U26" s="1" t="n">
+        <v>0.12034</v>
+      </c>
+      <c r="V26" s="2" t="n">
+        <v>0.007197857381988615</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2213,6 +2375,12 @@
       <c r="T27" s="3" t="n">
         <v>-0.009083402146985879</v>
       </c>
+      <c r="U27" s="1" t="n">
+        <v>0.01185</v>
+      </c>
+      <c r="V27" s="3" t="n">
+        <v>-0.01250000000000007</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2277,6 +2445,12 @@
       <c r="T28" s="2" t="n">
         <v>0.002321981424148523</v>
       </c>
+      <c r="U28" s="1" t="n">
+        <v>1.296</v>
+      </c>
+      <c r="V28" s="2" t="n">
+        <v>0.0007722007722008586</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2341,6 +2515,12 @@
       <c r="T29" s="3" t="n">
         <v>-0.006332046332046449</v>
       </c>
+      <c r="U29" s="1" t="n">
+        <v>0.06223</v>
+      </c>
+      <c r="V29" s="3" t="n">
+        <v>-0.03279452906434557</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2405,6 +2585,12 @@
       <c r="T30" s="2" t="n">
         <v>0.005239030779305833</v>
       </c>
+      <c r="U30" s="1" t="n">
+        <v>1.531</v>
+      </c>
+      <c r="V30" s="3" t="n">
+        <v>-0.002605863192182413</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2469,6 +2655,12 @@
       <c r="T31" s="2" t="n">
         <v>0.002960039467192861</v>
       </c>
+      <c r="U31" s="1" t="n">
+        <v>0.002024</v>
+      </c>
+      <c r="V31" s="3" t="n">
+        <v>-0.004426955238563646</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2533,6 +2725,12 @@
       <c r="T32" s="2" t="n">
         <v>0.00223048327137546</v>
       </c>
+      <c r="U32" s="1" t="n">
+        <v>0.04048</v>
+      </c>
+      <c r="V32" s="2" t="n">
+        <v>0.0009891196834818327</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2597,6 +2795,12 @@
       <c r="T33" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="U33" s="1" t="n">
+        <v>0.0985</v>
+      </c>
+      <c r="V33" s="3" t="n">
+        <v>-0.002026342451874284</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2661,6 +2865,12 @@
       <c r="T34" s="2" t="n">
         <v>0.002870813397129269</v>
       </c>
+      <c r="U34" s="1" t="n">
+        <v>0.1052</v>
+      </c>
+      <c r="V34" s="2" t="n">
+        <v>0.003816793893129748</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2725,6 +2935,12 @@
       <c r="T35" s="3" t="n">
         <v>-0.008009153318077675</v>
       </c>
+      <c r="U35" s="1" t="n">
+        <v>0.00874</v>
+      </c>
+      <c r="V35" s="2" t="n">
+        <v>0.008073817762398948</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2789,6 +3005,12 @@
       <c r="T36" s="2" t="n">
         <v>0.002516074923119811</v>
       </c>
+      <c r="U36" s="1" t="n">
+        <v>0.3586</v>
+      </c>
+      <c r="V36" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2853,6 +3075,12 @@
       <c r="T37" s="2" t="n">
         <v>0.0005139626520472042</v>
       </c>
+      <c r="U37" s="1" t="n">
+        <v>0.005832</v>
+      </c>
+      <c r="V37" s="3" t="n">
+        <v>-0.001369863013698515</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2917,6 +3145,12 @@
       <c r="T38" s="3" t="n">
         <v>-0.001603053435114624</v>
       </c>
+      <c r="U38" s="1" t="n">
+        <v>0.26181</v>
+      </c>
+      <c r="V38" s="2" t="n">
+        <v>0.0008792721156051992</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2981,6 +3215,12 @@
       <c r="T39" s="3" t="n">
         <v>-0.003373685255010847</v>
       </c>
+      <c r="U39" s="1" t="n">
+        <v>0.05049</v>
+      </c>
+      <c r="V39" s="2" t="n">
+        <v>0.005376344086021494</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -3045,6 +3285,12 @@
       <c r="T40" s="2" t="n">
         <v>0.01017863161442523</v>
       </c>
+      <c r="U40" s="1" t="n">
+        <v>0.15157</v>
+      </c>
+      <c r="V40" s="2" t="n">
+        <v>0.01141064993994406</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -3109,6 +3355,12 @@
       <c r="T41" s="2" t="n">
         <v>0.006520450503853099</v>
       </c>
+      <c r="U41" s="1" t="n">
+        <v>0.1702</v>
+      </c>
+      <c r="V41" s="2" t="n">
+        <v>0.00235571260306233</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -3173,6 +3425,12 @@
       <c r="T42" s="2" t="n">
         <v>0.002055774043618198</v>
       </c>
+      <c r="U42" s="1" t="n">
+        <v>112.18</v>
+      </c>
+      <c r="V42" s="2" t="n">
+        <v>0.0006243867630006903</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -3237,6 +3495,12 @@
       <c r="T43" s="2" t="n">
         <v>0.2908349732921</v>
       </c>
+      <c r="U43" s="1" t="n">
+        <v>1.0043</v>
+      </c>
+      <c r="V43" s="2" t="n">
+        <v>0.0936513122073396</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -3301,6 +3565,12 @@
       <c r="T44" s="2" t="n">
         <v>0.001639941690962032</v>
       </c>
+      <c r="U44" s="1" t="n">
+        <v>55.09</v>
+      </c>
+      <c r="V44" s="2" t="n">
+        <v>0.002183008913953148</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -3365,6 +3635,12 @@
       <c r="T45" s="2" t="n">
         <v>0.004771932536079234</v>
       </c>
+      <c r="U45" s="1" t="n">
+        <v>0.5190399999999999</v>
+      </c>
+      <c r="V45" s="3" t="n">
+        <v>-0.001999692355022383</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -3429,6 +3705,12 @@
       <c r="T46" s="3" t="n">
         <v>-0.000710328171615208</v>
       </c>
+      <c r="U46" s="1" t="n">
+        <v>0.703</v>
+      </c>
+      <c r="V46" s="3" t="n">
+        <v>-0.0005686664771112694</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -3493,6 +3775,12 @@
       <c r="T47" s="2" t="n">
         <v>0.003068268984914347</v>
       </c>
+      <c r="U47" s="1" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="V47" s="2" t="n">
+        <v>0.001784348712719887</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3557,6 +3845,12 @@
       <c r="T48" s="3" t="n">
         <v>-0.00112443778110953</v>
       </c>
+      <c r="U48" s="1" t="n">
+        <v>0.16003</v>
+      </c>
+      <c r="V48" s="2" t="n">
+        <v>0.0008130081300814196</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3621,6 +3915,12 @@
       <c r="T49" s="2" t="n">
         <v>0.01817875778488478</v>
       </c>
+      <c r="U49" s="1" t="n">
+        <v>0.06105</v>
+      </c>
+      <c r="V49" s="2" t="n">
+        <v>0.009257728550173549</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3685,6 +3985,12 @@
       <c r="T50" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="U50" s="1" t="n">
+        <v>0.0387</v>
+      </c>
+      <c r="V50" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3749,6 +4055,12 @@
       <c r="T51" s="3" t="n">
         <v>-0.04825941821649967</v>
       </c>
+      <c r="U51" s="1" t="n">
+        <v>0.30219</v>
+      </c>
+      <c r="V51" s="2" t="n">
+        <v>0.009419781541236559</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3813,6 +4125,12 @@
       <c r="T52" s="3" t="n">
         <v>-0.001365653806760025</v>
       </c>
+      <c r="U52" s="1" t="n">
+        <v>0.2916</v>
+      </c>
+      <c r="V52" s="3" t="n">
+        <v>-0.003076923076922928</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3877,6 +4195,12 @@
       <c r="T53" s="3" t="n">
         <v>-0.001892744479495235</v>
       </c>
+      <c r="U53" s="1" t="n">
+        <v>0.159</v>
+      </c>
+      <c r="V53" s="2" t="n">
+        <v>0.005056890012642194</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3941,6 +4265,12 @@
       <c r="T54" s="2" t="n">
         <v>0.00172081497797357</v>
       </c>
+      <c r="U54" s="1" t="n">
+        <v>0.29072</v>
+      </c>
+      <c r="V54" s="3" t="n">
+        <v>-0.001168144025286906</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -4005,6 +4335,12 @@
       <c r="T55" s="2" t="n">
         <v>0.00224152423648074</v>
       </c>
+      <c r="U55" s="1" t="n">
+        <v>0.00716</v>
+      </c>
+      <c r="V55" s="2" t="n">
+        <v>0.0008386916410399678</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -4069,6 +4405,12 @@
       <c r="T56" s="3" t="n">
         <v>-0.00427807486631011</v>
       </c>
+      <c r="U56" s="1" t="n">
+        <v>0.02839</v>
+      </c>
+      <c r="V56" s="2" t="n">
+        <v>0.01646974579305401</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -4133,6 +4475,12 @@
       <c r="T57" s="3" t="n">
         <v>-0.002842928216062429</v>
       </c>
+      <c r="U57" s="1" t="n">
+        <v>0.04217</v>
+      </c>
+      <c r="V57" s="2" t="n">
+        <v>0.001900688999762336</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -4197,6 +4545,12 @@
       <c r="T58" s="2" t="n">
         <v>0.06161036753770979</v>
       </c>
+      <c r="U58" s="1" t="n">
+        <v>0.04943</v>
+      </c>
+      <c r="V58" s="3" t="n">
+        <v>-0.01080648389033418</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -4261,6 +4615,12 @@
       <c r="T59" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="U59" s="1" t="n">
+        <v>1.548</v>
+      </c>
+      <c r="V59" s="2" t="n">
+        <v>0.007156798959011139</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -4325,6 +4685,12 @@
       <c r="T60" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="U60" s="1" t="n">
+        <v>0.00344</v>
+      </c>
+      <c r="V60" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -4389,6 +4755,12 @@
       <c r="T61" s="2" t="n">
         <v>0.003875968992248173</v>
       </c>
+      <c r="U61" s="1" t="n">
+        <v>0.1554</v>
+      </c>
+      <c r="V61" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -4453,6 +4825,12 @@
       <c r="T62" s="3" t="n">
         <v>-0.003478260869565221</v>
       </c>
+      <c r="U62" s="1" t="n">
+        <v>1.145</v>
+      </c>
+      <c r="V62" s="3" t="n">
+        <v>-0.0008726003490400436</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -4517,6 +4895,12 @@
       <c r="T63" s="2" t="n">
         <v>0.003728667718342085</v>
       </c>
+      <c r="U63" s="1" t="n">
+        <v>0.7010999999999999</v>
+      </c>
+      <c r="V63" s="2" t="n">
+        <v>0.001714530647235289</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -4581,6 +4965,12 @@
       <c r="T64" s="2" t="n">
         <v>0.002047082906857654</v>
       </c>
+      <c r="U64" s="1" t="n">
+        <v>2.937</v>
+      </c>
+      <c r="V64" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -4645,6 +5035,12 @@
       <c r="T65" s="2" t="n">
         <v>0.003779924401511961</v>
       </c>
+      <c r="U65" s="1" t="n">
+        <v>0.02383</v>
+      </c>
+      <c r="V65" s="3" t="n">
+        <v>-0.002928870292887055</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -4709,6 +5105,12 @@
       <c r="T66" s="2" t="n">
         <v>0.0009881422924901469</v>
       </c>
+      <c r="U66" s="1" t="n">
+        <v>0.1016</v>
+      </c>
+      <c r="V66" s="2" t="n">
+        <v>0.002961500493583364</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -4773,6 +5175,12 @@
       <c r="T67" s="2" t="n">
         <v>0.003699136868064134</v>
       </c>
+      <c r="U67" s="1" t="n">
+        <v>0.007409</v>
+      </c>
+      <c r="V67" s="2" t="n">
+        <v>0.01132951132951129</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -4837,6 +5245,12 @@
       <c r="T68" s="3" t="n">
         <v>-0.006871035940803517</v>
       </c>
+      <c r="U68" s="1" t="n">
+        <v>19.27</v>
+      </c>
+      <c r="V68" s="2" t="n">
+        <v>0.0255455029270889</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -4901,6 +5315,12 @@
       <c r="T69" s="2" t="n">
         <v>0.002042331971778667</v>
       </c>
+      <c r="U69" s="1" t="n">
+        <v>0.05401</v>
+      </c>
+      <c r="V69" s="2" t="n">
+        <v>0.0007411524921253532</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4965,6 +5385,12 @@
       <c r="T70" s="2" t="n">
         <v>0.004219409282700426</v>
       </c>
+      <c r="U70" s="1" t="n">
+        <v>0.238</v>
+      </c>
+      <c r="V70" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -5029,6 +5455,12 @@
       <c r="T71" s="3" t="n">
         <v>-0.002411714039620904</v>
       </c>
+      <c r="U71" s="1" t="n">
+        <v>5.762</v>
+      </c>
+      <c r="V71" s="3" t="n">
+        <v>-0.005007770678639406</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -5093,6 +5525,12 @@
       <c r="T72" s="3" t="n">
         <v>-0.009574468085106385</v>
       </c>
+      <c r="U72" s="1" t="n">
+        <v>0.00187</v>
+      </c>
+      <c r="V72" s="2" t="n">
+        <v>0.004296455424274961</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -5157,6 +5595,12 @@
       <c r="T73" s="2" t="n">
         <v>0.002767429483768011</v>
       </c>
+      <c r="U73" s="1" t="n">
+        <v>0.9425</v>
+      </c>
+      <c r="V73" s="2" t="n">
+        <v>0.0004245833775607217</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -5221,6 +5665,12 @@
       <c r="T74" s="2" t="n">
         <v>0.00083056478405318</v>
       </c>
+      <c r="U74" s="1" t="n">
+        <v>0.1206</v>
+      </c>
+      <c r="V74" s="2" t="n">
+        <v>0.000829875518672223</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -5285,6 +5735,12 @@
       <c r="T75" s="2" t="n">
         <v>0.001109941087742227</v>
       </c>
+      <c r="U75" s="1" t="n">
+        <v>352.66</v>
+      </c>
+      <c r="V75" s="2" t="n">
+        <v>0.002558562656356704</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -5349,6 +5805,12 @@
       <c r="T76" s="2" t="n">
         <v>0.0009232060428031807</v>
       </c>
+      <c r="U76" s="1" t="n">
+        <v>0.11771</v>
+      </c>
+      <c r="V76" s="3" t="n">
+        <v>-0.01299681368438713</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -5413,6 +5875,12 @@
       <c r="T77" s="2" t="n">
         <v>0.003356777493606168</v>
       </c>
+      <c r="U77" s="1" t="n">
+        <v>0.06271</v>
+      </c>
+      <c r="V77" s="3" t="n">
+        <v>-0.0009558706388402818</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -5477,6 +5945,12 @@
       <c r="T78" s="2" t="n">
         <v>0.002542372881355976</v>
       </c>
+      <c r="U78" s="1" t="n">
+        <v>0.09447999999999999</v>
+      </c>
+      <c r="V78" s="3" t="n">
+        <v>-0.001690617075232538</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -5541,6 +6015,12 @@
       <c r="T79" s="2" t="n">
         <v>0.0002468526289804714</v>
       </c>
+      <c r="U79" s="1" t="n">
+        <v>0.4043</v>
+      </c>
+      <c r="V79" s="3" t="n">
+        <v>-0.002221125370187591</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -5605,6 +6085,12 @@
       <c r="T80" s="2" t="n">
         <v>0.001662234042553268</v>
       </c>
+      <c r="U80" s="1" t="n">
+        <v>0.006024</v>
+      </c>
+      <c r="V80" s="3" t="n">
+        <v>-0.0003318951211417633</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -5669,6 +6155,12 @@
       <c r="T81" s="3" t="n">
         <v>-0.005730659025787998</v>
       </c>
+      <c r="U81" s="1" t="n">
+        <v>0.1035</v>
+      </c>
+      <c r="V81" s="3" t="n">
+        <v>-0.005763688760806948</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -5733,6 +6225,12 @@
       <c r="T82" s="2" t="n">
         <v>0.0009823182711198709</v>
       </c>
+      <c r="U82" s="1" t="n">
+        <v>0.1019</v>
+      </c>
+      <c r="V82" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -5797,6 +6295,12 @@
       <c r="T83" s="2" t="n">
         <v>0.003461348277567083</v>
       </c>
+      <c r="U83" s="1" t="n">
+        <v>0.06121</v>
+      </c>
+      <c r="V83" s="2" t="n">
+        <v>0.005420499342969841</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -5861,6 +6365,12 @@
       <c r="T84" s="3" t="n">
         <v>-0.005497916112441238</v>
       </c>
+      <c r="U84" s="1" t="n">
+        <v>1.1241</v>
+      </c>
+      <c r="V84" s="2" t="n">
+        <v>0.002318323673651501</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -5925,6 +6435,12 @@
       <c r="T85" s="3" t="n">
         <v>-0.00227617602427925</v>
       </c>
+      <c r="U85" s="1" t="n">
+        <v>0.01307</v>
+      </c>
+      <c r="V85" s="3" t="n">
+        <v>-0.006083650190114085</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -5989,6 +6505,12 @@
       <c r="T86" s="3" t="n">
         <v>-0.003552397868561135</v>
       </c>
+      <c r="U86" s="1" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="V86" s="3" t="n">
+        <v>-0.001782531194296034</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -6053,6 +6575,12 @@
       <c r="T87" s="2" t="n">
         <v>0.001807446680322999</v>
       </c>
+      <c r="U87" s="1" t="n">
+        <v>8.327999999999999</v>
+      </c>
+      <c r="V87" s="2" t="n">
+        <v>0.001683906663459147</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -6117,6 +6645,12 @@
       <c r="T88" s="2" t="n">
         <v>0.004035474637511117</v>
       </c>
+      <c r="U88" s="1" t="n">
+        <v>2.1355</v>
+      </c>
+      <c r="V88" s="3" t="n">
+        <v>-0.001962891994204787</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -6181,6 +6715,12 @@
       <c r="T89" s="2" t="n">
         <v>0.01113226893218113</v>
       </c>
+      <c r="U89" s="1" t="n">
+        <v>0.007015</v>
+      </c>
+      <c r="V89" s="2" t="n">
+        <v>0.01622482978415183</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -6245,6 +6785,12 @@
       <c r="T90" s="2" t="n">
         <v>0.002621231979030205</v>
       </c>
+      <c r="U90" s="1" t="n">
+        <v>15.28</v>
+      </c>
+      <c r="V90" s="3" t="n">
+        <v>-0.001307189542483748</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -6309,6 +6855,12 @@
       <c r="T91" s="3" t="n">
         <v>-0.004464285714285702</v>
       </c>
+      <c r="U91" s="1" t="n">
+        <v>0.000225</v>
+      </c>
+      <c r="V91" s="2" t="n">
+        <v>0.008968609865470828</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -6373,6 +6925,12 @@
       <c r="T92" s="3" t="n">
         <v>-0.007111281952719629</v>
       </c>
+      <c r="U92" s="1" t="n">
+        <v>0.05224</v>
+      </c>
+      <c r="V92" s="2" t="n">
+        <v>0.01122725512969423</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -6437,6 +6995,12 @@
       <c r="T93" s="3" t="n">
         <v>-0.001507954459775316</v>
       </c>
+      <c r="U93" s="1" t="n">
+        <v>1.325</v>
+      </c>
+      <c r="V93" s="2" t="n">
+        <v>0.0005285811372045027</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -6501,6 +7065,12 @@
       <c r="T94" s="3" t="n">
         <v>-0.0008114937017022082</v>
       </c>
+      <c r="U94" s="1" t="n">
+        <v>0.054648</v>
+      </c>
+      <c r="V94" s="2" t="n">
+        <v>0.00869372611994018</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -6565,6 +7135,12 @@
       <c r="T95" s="2" t="n">
         <v>0.001239669421487581</v>
       </c>
+      <c r="U95" s="1" t="n">
+        <v>0.2412</v>
+      </c>
+      <c r="V95" s="3" t="n">
+        <v>-0.004539826661163805</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -6629,6 +7205,12 @@
       <c r="T96" s="3" t="n">
         <v>-0.001764979098931735</v>
       </c>
+      <c r="U96" s="1" t="n">
+        <v>1.0744</v>
+      </c>
+      <c r="V96" s="3" t="n">
+        <v>-0.0001861157640051908</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -6693,6 +7275,12 @@
       <c r="T97" s="2" t="n">
         <v>0.00272691858200247</v>
       </c>
+      <c r="U97" s="1" t="n">
+        <v>0.2573</v>
+      </c>
+      <c r="V97" s="3" t="n">
+        <v>-0.0003885003885005613</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -6757,6 +7345,12 @@
       <c r="T98" s="3" t="n">
         <v>-0.003965517241379257</v>
       </c>
+      <c r="U98" s="1" t="n">
+        <v>0.581</v>
+      </c>
+      <c r="V98" s="2" t="n">
+        <v>0.005712307425999602</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -6821,6 +7415,12 @@
       <c r="T99" s="3" t="n">
         <v>-0.002708043621459484</v>
       </c>
+      <c r="U99" s="1" t="n">
+        <v>0.13551</v>
+      </c>
+      <c r="V99" s="3" t="n">
+        <v>-0.00550418317921621</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -6885,6 +7485,12 @@
       <c r="T100" s="2" t="n">
         <v>0.002286834367853663</v>
       </c>
+      <c r="U100" s="1" t="n">
+        <v>0.03072</v>
+      </c>
+      <c r="V100" s="2" t="n">
+        <v>0.001303780964797974</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -6949,6 +7555,12 @@
       <c r="T101" s="2" t="n">
         <v>0.007759456838021346</v>
       </c>
+      <c r="U101" s="1" t="n">
+        <v>1.038</v>
+      </c>
+      <c r="V101" s="3" t="n">
+        <v>-0.0009624639076033589</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -7013,6 +7625,12 @@
       <c r="T102" s="2" t="n">
         <v>0.005911778080945959</v>
       </c>
+      <c r="U102" s="1" t="n">
+        <v>0.02207</v>
+      </c>
+      <c r="V102" s="3" t="n">
+        <v>-0.002260397830018148</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -7077,6 +7695,12 @@
       <c r="T103" s="2" t="n">
         <v>0.002558853633572233</v>
       </c>
+      <c r="U103" s="1" t="n">
+        <v>0.01952</v>
+      </c>
+      <c r="V103" s="3" t="n">
+        <v>-0.00357325165900973</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -7141,6 +7765,12 @@
       <c r="T104" s="2" t="n">
         <v>0.00234113712374571</v>
       </c>
+      <c r="U104" s="1" t="n">
+        <v>2.995</v>
+      </c>
+      <c r="V104" s="3" t="n">
+        <v>-0.0006673340006672605</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -7205,6 +7835,12 @@
       <c r="T105" s="2" t="n">
         <v>0.001538461538461451</v>
       </c>
+      <c r="U105" s="1" t="n">
+        <v>32.54</v>
+      </c>
+      <c r="V105" s="3" t="n">
+        <v>-0.0003072196620583106</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -7269,6 +7905,12 @@
       <c r="T106" s="2" t="n">
         <v>0.003010234798314271</v>
       </c>
+      <c r="U106" s="1" t="n">
+        <v>0.1663</v>
+      </c>
+      <c r="V106" s="3" t="n">
+        <v>-0.001800720288115214</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -7333,6 +7975,12 @@
       <c r="T107" s="2" t="n">
         <v>0.008019072388383262</v>
       </c>
+      <c r="U107" s="1" t="n">
+        <v>0.4666</v>
+      </c>
+      <c r="V107" s="2" t="n">
+        <v>0.003225112878950766</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -7397,6 +8045,12 @@
       <c r="T108" s="2" t="n">
         <v>0.00238805970149244</v>
       </c>
+      <c r="U108" s="1" t="n">
+        <v>0.3362</v>
+      </c>
+      <c r="V108" s="2" t="n">
+        <v>0.001191185229303191</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -7461,6 +8115,12 @@
       <c r="T109" s="3" t="n">
         <v>-0.02371711944803797</v>
       </c>
+      <c r="U109" s="1" t="n">
+        <v>0.2274</v>
+      </c>
+      <c r="V109" s="2" t="n">
+        <v>0.004416961130742054</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -7525,6 +8185,12 @@
       <c r="T110" s="2" t="n">
         <v>0.005968169761273197</v>
       </c>
+      <c r="U110" s="1" t="n">
+        <v>0.01522</v>
+      </c>
+      <c r="V110" s="2" t="n">
+        <v>0.003295978905734983</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -7589,6 +8255,12 @@
       <c r="T111" s="3" t="n">
         <v>-0.001633097441480616</v>
       </c>
+      <c r="U111" s="1" t="n">
+        <v>1.837</v>
+      </c>
+      <c r="V111" s="2" t="n">
+        <v>0.001635768811341271</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -7653,6 +8325,12 @@
       <c r="T112" s="2" t="n">
         <v>0.0005212405525149644</v>
       </c>
+      <c r="U112" s="1" t="n">
+        <v>0.03832</v>
+      </c>
+      <c r="V112" s="3" t="n">
+        <v>-0.001823391508205278</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -7717,6 +8395,12 @@
       <c r="T113" s="2" t="n">
         <v>0.003504672897196187</v>
       </c>
+      <c r="U113" s="1" t="n">
+        <v>4.299</v>
+      </c>
+      <c r="V113" s="2" t="n">
+        <v>0.0009313154831200111</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -7781,6 +8465,12 @@
       <c r="T114" s="3" t="n">
         <v>-0.004470742932281417</v>
       </c>
+      <c r="U114" s="1" t="n">
+        <v>0.007614</v>
+      </c>
+      <c r="V114" s="2" t="n">
+        <v>0.005679566767930327</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -7845,6 +8535,12 @@
       <c r="T115" s="2" t="n">
         <v>0.002424487321951754</v>
       </c>
+      <c r="U115" s="1" t="n">
+        <v>0.09993</v>
+      </c>
+      <c r="V115" s="2" t="n">
+        <v>0.007054318250529136</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -7909,6 +8605,12 @@
       <c r="T116" s="2" t="n">
         <v>0.002898550724637731</v>
       </c>
+      <c r="U116" s="1" t="n">
+        <v>0.08303000000000001</v>
+      </c>
+      <c r="V116" s="3" t="n">
+        <v>-0.000120423892100146</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -7973,6 +8675,12 @@
       <c r="T117" s="2" t="n">
         <v>0.001331114808652284</v>
       </c>
+      <c r="U117" s="1" t="n">
+        <v>0.3009</v>
+      </c>
+      <c r="V117" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -8037,6 +8745,12 @@
       <c r="T118" s="3" t="n">
         <v>-0.002206531332744835</v>
       </c>
+      <c r="U118" s="1" t="n">
+        <v>0.0226</v>
+      </c>
+      <c r="V118" s="3" t="n">
+        <v>-0.0004422821760284414</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -8101,6 +8815,12 @@
       <c r="T119" s="3" t="n">
         <v>-0.0019417475728155</v>
       </c>
+      <c r="U119" s="1" t="n">
+        <v>0.1538</v>
+      </c>
+      <c r="V119" s="3" t="n">
+        <v>-0.002594033722438466</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -8165,6 +8885,12 @@
       <c r="T120" s="3" t="n">
         <v>-0.02033675923901163</v>
       </c>
+      <c r="U120" s="1" t="n">
+        <v>0.00443</v>
+      </c>
+      <c r="V120" s="3" t="n">
+        <v>-0.01116071428571422</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -8229,6 +8955,12 @@
       <c r="T121" s="2" t="n">
         <v>0.01431870669745955</v>
       </c>
+      <c r="U121" s="1" t="n">
+        <v>0.4369</v>
+      </c>
+      <c r="V121" s="3" t="n">
+        <v>-0.00523679417122033</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -8293,6 +9025,12 @@
       <c r="T122" s="2" t="n">
         <v>0.001287001287001288</v>
       </c>
+      <c r="U122" s="1" t="n">
+        <v>0.778</v>
+      </c>
+      <c r="V122" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -8357,6 +9095,12 @@
       <c r="T123" s="2" t="n">
         <v>0.002314814814814721</v>
       </c>
+      <c r="U123" s="1" t="n">
+        <v>0.0866</v>
+      </c>
+      <c r="V123" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -8421,6 +9165,12 @@
       <c r="T124" s="2" t="n">
         <v>0.005700325732899073</v>
       </c>
+      <c r="U124" s="1" t="n">
+        <v>0.01233</v>
+      </c>
+      <c r="V124" s="3" t="n">
+        <v>-0.001619433198380501</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -8485,6 +9235,12 @@
       <c r="T125" s="2" t="n">
         <v>0.00205254515599349</v>
       </c>
+      <c r="U125" s="1" t="n">
+        <v>0.09758</v>
+      </c>
+      <c r="V125" s="3" t="n">
+        <v>-0.0006145022531749743</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -8549,6 +9305,12 @@
       <c r="T126" s="2" t="n">
         <v>0.001926369863013694</v>
       </c>
+      <c r="U126" s="1" t="n">
+        <v>0.04681</v>
+      </c>
+      <c r="V126" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -8613,6 +9375,12 @@
       <c r="T127" s="2" t="n">
         <v>0.009316770186335421</v>
       </c>
+      <c r="U127" s="1" t="n">
+        <v>3.26e-05</v>
+      </c>
+      <c r="V127" s="2" t="n">
+        <v>0.003076923076923152</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -8677,6 +9445,12 @@
       <c r="T128" s="3" t="n">
         <v>-0.001415678640948545</v>
       </c>
+      <c r="U128" s="1" t="n">
+        <v>0.5654</v>
+      </c>
+      <c r="V128" s="2" t="n">
+        <v>0.001949317738791405</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -8741,6 +9515,12 @@
       <c r="T129" s="3" t="n">
         <v>-0.00153233220962309</v>
       </c>
+      <c r="U129" s="1" t="n">
+        <v>0.06512</v>
+      </c>
+      <c r="V129" s="3" t="n">
+        <v>-0.0006138735420503126</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -8805,6 +9585,12 @@
       <c r="T130" s="3" t="n">
         <v>-0.006381934216985653</v>
       </c>
+      <c r="U130" s="1" t="n">
+        <v>0.0006118</v>
+      </c>
+      <c r="V130" s="2" t="n">
+        <v>0.007575757575757581</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -8869,6 +9655,12 @@
       <c r="T131" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="U131" s="1" t="n">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="V131" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -8933,6 +9725,12 @@
       <c r="T132" s="2" t="n">
         <v>0.00300000000000004</v>
       </c>
+      <c r="U132" s="1" t="n">
+        <v>0.3014</v>
+      </c>
+      <c r="V132" s="2" t="n">
+        <v>0.001661681621801264</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -8997,6 +9795,12 @@
       <c r="T133" s="2" t="n">
         <v>0.01569100784550391</v>
       </c>
+      <c r="U133" s="1" t="n">
+        <v>0.03375</v>
+      </c>
+      <c r="V133" s="2" t="n">
+        <v>0.002673796791443844</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -9061,6 +9865,12 @@
       <c r="T134" s="3" t="n">
         <v>-0.0004152536507717108</v>
       </c>
+      <c r="U134" s="1" t="n">
+        <v>0.14402</v>
+      </c>
+      <c r="V134" s="3" t="n">
+        <v>-0.002838745413002795</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -9125,6 +9935,12 @@
       <c r="T135" s="2" t="n">
         <v>0.004396347649644966</v>
       </c>
+      <c r="U135" s="1" t="n">
+        <v>0.0297</v>
+      </c>
+      <c r="V135" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -9189,6 +10005,12 @@
       <c r="T136" s="2" t="n">
         <v>0.001063829787234083</v>
       </c>
+      <c r="U136" s="1" t="n">
+        <v>28.23</v>
+      </c>
+      <c r="V136" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -9253,6 +10075,12 @@
       <c r="T137" s="2" t="n">
         <v>0.006968641114982622</v>
       </c>
+      <c r="U137" s="1" t="n">
+        <v>0.0004346</v>
+      </c>
+      <c r="V137" s="2" t="n">
+        <v>0.002537485582468218</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -9317,6 +10145,12 @@
       <c r="T138" s="2" t="n">
         <v>0.0008495021917156789</v>
       </c>
+      <c r="U138" s="1" t="n">
+        <v>0.029502</v>
+      </c>
+      <c r="V138" s="2" t="n">
+        <v>0.001629659808514953</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -9381,6 +10215,12 @@
       <c r="T139" s="3" t="n">
         <v>-0.001245717844908078</v>
       </c>
+      <c r="U139" s="1" t="n">
+        <v>0.0965</v>
+      </c>
+      <c r="V139" s="2" t="n">
+        <v>0.003014239684024515</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -9445,6 +10285,12 @@
       <c r="T140" s="2" t="n">
         <v>0.01486259113853064</v>
       </c>
+      <c r="U140" s="1" t="n">
+        <v>0.3618</v>
+      </c>
+      <c r="V140" s="3" t="n">
+        <v>-0.0002763194252555651</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -9509,6 +10355,12 @@
       <c r="T141" s="3" t="n">
         <v>-0.004161937192584147</v>
       </c>
+      <c r="U141" s="1" t="n">
+        <v>0.0263</v>
+      </c>
+      <c r="V141" s="3" t="n">
+        <v>-0.0007598784194528566</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -9573,6 +10425,12 @@
       <c r="T142" s="2" t="n">
         <v>0.008339748524506002</v>
       </c>
+      <c r="U142" s="1" t="n">
+        <v>0.07886</v>
+      </c>
+      <c r="V142" s="2" t="n">
+        <v>0.00343555159689536</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -9637,6 +10495,12 @@
       <c r="T143" s="3" t="n">
         <v>-0.002144711592730508</v>
       </c>
+      <c r="U143" s="1" t="n">
+        <v>0.08831</v>
+      </c>
+      <c r="V143" s="3" t="n">
+        <v>-0.001018099547511388</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -9701,6 +10565,12 @@
       <c r="T144" s="2" t="n">
         <v>0.01036525172754187</v>
       </c>
+      <c r="U144" s="1" t="n">
+        <v>0.02049</v>
+      </c>
+      <c r="V144" s="2" t="n">
+        <v>0.0009770395701027188</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -9765,6 +10635,12 @@
       <c r="T145" s="2" t="n">
         <v>0.003151536373982309</v>
       </c>
+      <c r="U145" s="1" t="n">
+        <v>0.11494</v>
+      </c>
+      <c r="V145" s="2" t="n">
+        <v>0.003054367745876631</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -9829,6 +10705,12 @@
       <c r="T146" s="2" t="n">
         <v>0.002641135688346064</v>
       </c>
+      <c r="U146" s="1" t="n">
+        <v>0.3034</v>
+      </c>
+      <c r="V146" s="3" t="n">
+        <v>-0.0009878169245967152</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -9893,6 +10775,12 @@
       <c r="T147" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="U147" s="1" t="n">
+        <v>0.123</v>
+      </c>
+      <c r="V147" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -9957,6 +10845,12 @@
       <c r="T148" s="3" t="n">
         <v>-0.00484941296579891</v>
       </c>
+      <c r="U148" s="1" t="n">
+        <v>1.9519</v>
+      </c>
+      <c r="V148" s="2" t="n">
+        <v>0.00123108489356243</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -10021,6 +10915,12 @@
       <c r="T149" s="2" t="n">
         <v>0.002270515731430445</v>
       </c>
+      <c r="U149" s="1" t="n">
+        <v>0.06174</v>
+      </c>
+      <c r="V149" s="3" t="n">
+        <v>-0.0009708737864077274</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -10085,6 +10985,12 @@
       <c r="T150" s="3" t="n">
         <v>-0.006064281382656161</v>
       </c>
+      <c r="U150" s="1" t="n">
+        <v>0.1637</v>
+      </c>
+      <c r="V150" s="3" t="n">
+        <v>-0.001220256253813167</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -10149,6 +11055,12 @@
       <c r="T151" s="2" t="n">
         <v>0.003145596165368479</v>
       </c>
+      <c r="U151" s="1" t="n">
+        <v>6.703e-05</v>
+      </c>
+      <c r="V151" s="2" t="n">
+        <v>0.0008959235478571902</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -10213,6 +11125,12 @@
       <c r="T152" s="3" t="n">
         <v>-0.002708192281652005</v>
       </c>
+      <c r="U152" s="1" t="n">
+        <v>0.01482</v>
+      </c>
+      <c r="V152" s="2" t="n">
+        <v>0.006109979633401209</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -10277,6 +11195,12 @@
       <c r="T153" s="2" t="n">
         <v>0.005747126436781707</v>
       </c>
+      <c r="U153" s="1" t="n">
+        <v>0.02099</v>
+      </c>
+      <c r="V153" s="3" t="n">
+        <v>-0.0004761904761904568</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -10341,6 +11265,12 @@
       <c r="T154" s="2" t="n">
         <v>0.003194351042367169</v>
       </c>
+      <c r="U154" s="1" t="n">
+        <v>0.0005952</v>
+      </c>
+      <c r="V154" s="3" t="n">
+        <v>-0.002513826043237778</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -10405,6 +11335,12 @@
       <c r="T155" s="2" t="n">
         <v>0.001244090569793517</v>
       </c>
+      <c r="U155" s="1" t="n">
+        <v>0.04022</v>
+      </c>
+      <c r="V155" s="3" t="n">
+        <v>-0.000497017892644115</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -10469,6 +11405,12 @@
       <c r="T156" s="2" t="n">
         <v>0.000529661016949131</v>
       </c>
+      <c r="U156" s="1" t="n">
+        <v>0.01887</v>
+      </c>
+      <c r="V156" s="3" t="n">
+        <v>-0.001058761249338231</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -10533,6 +11475,12 @@
       <c r="T157" s="2" t="n">
         <v>0.0006918021445867001</v>
       </c>
+      <c r="U157" s="1" t="n">
+        <v>0.08715000000000001</v>
+      </c>
+      <c r="V157" s="2" t="n">
+        <v>0.004147943311441401</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -10597,6 +11545,12 @@
       <c r="T158" s="3" t="n">
         <v>-0.01941747572815545</v>
       </c>
+      <c r="U158" s="1" t="n">
+        <v>0.008144</v>
+      </c>
+      <c r="V158" s="3" t="n">
+        <v>-0.0166626418739434</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -10661,6 +11615,12 @@
       <c r="T159" s="2" t="n">
         <v>0.003617363344051406</v>
       </c>
+      <c r="U159" s="1" t="n">
+        <v>2.497</v>
+      </c>
+      <c r="V159" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -10725,6 +11685,12 @@
       <c r="T160" s="2" t="n">
         <v>0.002110199296600176</v>
       </c>
+      <c r="U160" s="1" t="n">
+        <v>1.2825</v>
+      </c>
+      <c r="V160" s="2" t="n">
+        <v>0.000233972859148313</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -10789,6 +11755,12 @@
       <c r="T161" s="3" t="n">
         <v>-0.0009313464608834568</v>
       </c>
+      <c r="U161" s="1" t="n">
+        <v>0.007502</v>
+      </c>
+      <c r="V161" s="3" t="n">
+        <v>-0.0009322146757224746</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -10853,6 +11825,12 @@
       <c r="T162" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="U162" s="1" t="n">
+        <v>0.004293</v>
+      </c>
+      <c r="V162" s="2" t="n">
+        <v>0.03645581844519558</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -10917,6 +11895,12 @@
       <c r="T163" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="U163" s="1" t="n">
+        <v>0.0963</v>
+      </c>
+      <c r="V163" s="2" t="n">
+        <v>0.001039501039501069</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -10981,6 +11965,12 @@
       <c r="T164" s="2" t="n">
         <v>0.002098408104196907</v>
       </c>
+      <c r="U164" s="1" t="n">
+        <v>1.3839</v>
+      </c>
+      <c r="V164" s="3" t="n">
+        <v>-0.0007220737959420261</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -11045,6 +12035,12 @@
       <c r="T165" s="2" t="n">
         <v>0.002939422339609913</v>
       </c>
+      <c r="U165" s="1" t="n">
+        <v>0.023542</v>
+      </c>
+      <c r="V165" s="3" t="n">
+        <v>-4.247547041587733e-05</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -11109,6 +12105,12 @@
       <c r="T166" s="2" t="n">
         <v>0.01018210299588799</v>
       </c>
+      <c r="U166" s="1" t="n">
+        <v>0.005132</v>
+      </c>
+      <c r="V166" s="3" t="n">
+        <v>-0.005233572397751524</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -11173,6 +12175,12 @@
       <c r="T167" s="2" t="n">
         <v>0.008162031438935895</v>
       </c>
+      <c r="U167" s="1" t="n">
+        <v>0.06596</v>
+      </c>
+      <c r="V167" s="3" t="n">
+        <v>-0.01109445277361305</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -11237,6 +12245,12 @@
       <c r="T168" s="3" t="n">
         <v>-0.002103049421661469</v>
       </c>
+      <c r="U168" s="1" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="V168" s="2" t="n">
+        <v>0.001053740779768207</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -11301,6 +12315,12 @@
       <c r="T169" s="3" t="n">
         <v>-0.001312335958005287</v>
       </c>
+      <c r="U169" s="1" t="n">
+        <v>0.03805</v>
+      </c>
+      <c r="V169" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -11365,6 +12385,12 @@
       <c r="T170" s="2" t="n">
         <v>0.002526670409882059</v>
       </c>
+      <c r="U170" s="1" t="n">
+        <v>0.007143</v>
+      </c>
+      <c r="V170" s="2" t="n">
+        <v>0.0001400168020162605</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -11429,6 +12455,12 @@
       <c r="T171" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="U171" s="1" t="n">
+        <v>0.3411</v>
+      </c>
+      <c r="V171" s="2" t="n">
+        <v>0.0002932551319647771</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -11493,6 +12525,12 @@
       <c r="T172" s="2" t="n">
         <v>0.0005505597357313478</v>
       </c>
+      <c r="U172" s="1" t="n">
+        <v>5.447</v>
+      </c>
+      <c r="V172" s="3" t="n">
+        <v>-0.0009170946441672585</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -11557,6 +12595,12 @@
       <c r="T173" s="2" t="n">
         <v>0.003741197183098515</v>
       </c>
+      <c r="U173" s="1" t="n">
+        <v>0.04561</v>
+      </c>
+      <c r="V173" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -11621,6 +12665,12 @@
       <c r="T174" s="3" t="n">
         <v>-0.0002564102564103349</v>
       </c>
+      <c r="U174" s="1" t="n">
+        <v>0.03902</v>
+      </c>
+      <c r="V174" s="2" t="n">
+        <v>0.0007694280584765902</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -11685,6 +12735,12 @@
       <c r="T175" s="2" t="n">
         <v>0.004287245444801819</v>
       </c>
+      <c r="U175" s="1" t="n">
+        <v>0.005606</v>
+      </c>
+      <c r="V175" s="3" t="n">
+        <v>-0.002845962290999713</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -11749,6 +12805,12 @@
       <c r="T176" s="3" t="n">
         <v>-0.001322751322751269</v>
       </c>
+      <c r="U176" s="1" t="n">
+        <v>0.00756</v>
+      </c>
+      <c r="V176" s="2" t="n">
+        <v>0.001324503311258224</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -11813,6 +12875,12 @@
       <c r="T177" s="2" t="n">
         <v>0.01253561253561255</v>
       </c>
+      <c r="U177" s="1" t="n">
+        <v>1.783</v>
+      </c>
+      <c r="V177" s="2" t="n">
+        <v>0.003376477208778844</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -11877,6 +12945,12 @@
       <c r="T178" s="2" t="n">
         <v>0.003841967087148538</v>
       </c>
+      <c r="U178" s="1" t="n">
+        <v>15.708</v>
+      </c>
+      <c r="V178" s="2" t="n">
+        <v>0.001977419149071926</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -11941,6 +13015,12 @@
       <c r="T179" s="2" t="n">
         <v>0.003215434083601289</v>
       </c>
+      <c r="U179" s="1" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="V179" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -12005,6 +13085,12 @@
       <c r="T180" s="2" t="n">
         <v>0.006887335526315687</v>
       </c>
+      <c r="U180" s="1" t="n">
+        <v>0.09698</v>
+      </c>
+      <c r="V180" s="3" t="n">
+        <v>-0.009903011740684009</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -12069,6 +13155,12 @@
       <c r="T181" s="2" t="n">
         <v>0.002137894174238437</v>
       </c>
+      <c r="U181" s="1" t="n">
+        <v>0.1876</v>
+      </c>
+      <c r="V181" s="2" t="n">
+        <v>0.0005333333333332746</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -12133,6 +13225,12 @@
       <c r="T182" s="3" t="n">
         <v>-0.003367003367003346</v>
       </c>
+      <c r="U182" s="1" t="n">
+        <v>0.05921</v>
+      </c>
+      <c r="V182" s="2" t="n">
+        <v>0.0001689189189188534</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -12197,6 +13295,12 @@
       <c r="T183" s="2" t="n">
         <v>0.002500000000000043</v>
       </c>
+      <c r="U183" s="1" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="V183" s="3" t="n">
+        <v>-0.002493765586034955</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -12261,6 +13365,12 @@
       <c r="T184" s="2" t="n">
         <v>0.002336448598130908</v>
       </c>
+      <c r="U184" s="1" t="n">
+        <v>0.02141</v>
+      </c>
+      <c r="V184" s="3" t="n">
+        <v>-0.00186480186480195</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -12325,6 +13435,12 @@
       <c r="T185" s="2" t="n">
         <v>0.00274725274725275</v>
       </c>
+      <c r="U185" s="1" t="n">
+        <v>0.365</v>
+      </c>
+      <c r="V185" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -12389,6 +13505,12 @@
       <c r="T186" s="3" t="n">
         <v>-0.0003920543648718676</v>
       </c>
+      <c r="U186" s="1" t="n">
+        <v>0.007637</v>
+      </c>
+      <c r="V186" s="3" t="n">
+        <v>-0.001568832527127824</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -12453,6 +13575,12 @@
       <c r="T187" s="2" t="n">
         <v>0.0007459903021259902</v>
       </c>
+      <c r="U187" s="1" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="V187" s="2" t="n">
+        <v>0.006336190831159281</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -12517,6 +13645,12 @@
       <c r="T188" s="2" t="n">
         <v>0.003052503052502999</v>
       </c>
+      <c r="U188" s="1" t="n">
+        <v>0.04926</v>
+      </c>
+      <c r="V188" s="3" t="n">
+        <v>-0.0006086427267194613</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -12581,6 +13715,12 @@
       <c r="T189" s="2" t="n">
         <v>0.00274402195217575</v>
       </c>
+      <c r="U189" s="1" t="n">
+        <v>0.2565</v>
+      </c>
+      <c r="V189" s="2" t="n">
+        <v>0.00273651290070359</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -12645,6 +13785,12 @@
       <c r="T190" s="2" t="n">
         <v>0.001407211961301711</v>
       </c>
+      <c r="U190" s="1" t="n">
+        <v>0.5681</v>
+      </c>
+      <c r="V190" s="3" t="n">
+        <v>-0.00210785174776037</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -12709,6 +13855,12 @@
       <c r="T191" s="2" t="n">
         <v>0.001493280238924747</v>
       </c>
+      <c r="U191" s="1" t="n">
+        <v>6.046</v>
+      </c>
+      <c r="V191" s="2" t="n">
+        <v>0.001656726308813896</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -12773,6 +13925,12 @@
       <c r="T192" s="3" t="n">
         <v>-0.005405405405405284</v>
       </c>
+      <c r="U192" s="1" t="n">
+        <v>0.3508</v>
+      </c>
+      <c r="V192" s="2" t="n">
+        <v>0.003432494279176141</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -12837,6 +13995,12 @@
       <c r="T193" s="2" t="n">
         <v>0.003129890453834206</v>
       </c>
+      <c r="U193" s="1" t="n">
+        <v>0.06370000000000001</v>
+      </c>
+      <c r="V193" s="3" t="n">
+        <v>-0.006240249609984361</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -12901,6 +14065,12 @@
       <c r="T194" s="3" t="n">
         <v>-0.00172117039586932</v>
       </c>
+      <c r="U194" s="1" t="n">
+        <v>0.01732</v>
+      </c>
+      <c r="V194" s="3" t="n">
+        <v>-0.004597701149425299</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -12965,6 +14135,12 @@
       <c r="T195" s="2" t="n">
         <v>0.0005883737349965479</v>
       </c>
+      <c r="U195" s="1" t="n">
+        <v>0.0008445</v>
+      </c>
+      <c r="V195" s="3" t="n">
+        <v>-0.006821121956956407</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -13029,6 +14205,12 @@
       <c r="T196" s="2" t="n">
         <v>0.07897334649555775</v>
       </c>
+      <c r="U196" s="1" t="n">
+        <v>0.00108</v>
+      </c>
+      <c r="V196" s="3" t="n">
+        <v>-0.01189387008234217</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -13093,6 +14275,12 @@
       <c r="T197" s="2" t="n">
         <v>0.003705991352686766</v>
       </c>
+      <c r="U197" s="1" t="n">
+        <v>0.0001622</v>
+      </c>
+      <c r="V197" s="3" t="n">
+        <v>-0.001846153846153724</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -13157,6 +14345,12 @@
       <c r="T198" s="2" t="n">
         <v>0.003466605038132582</v>
       </c>
+      <c r="U198" s="1" t="n">
+        <v>4.335</v>
+      </c>
+      <c r="V198" s="3" t="n">
+        <v>-0.00161216029479495</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -13221,6 +14415,12 @@
       <c r="T199" s="3" t="n">
         <v>-0.00122774708410054</v>
       </c>
+      <c r="U199" s="1" t="n">
+        <v>0.1625</v>
+      </c>
+      <c r="V199" s="3" t="n">
+        <v>-0.001229256299938572</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -13285,6 +14485,12 @@
       <c r="T200" s="3" t="n">
         <v>-0.008540535992258754</v>
       </c>
+      <c r="U200" s="1" t="n">
+        <v>0.022996</v>
+      </c>
+      <c r="V200" s="3" t="n">
+        <v>-0.02418738861071039</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -13349,6 +14555,12 @@
       <c r="T201" s="2" t="n">
         <v>0.005783642880417093</v>
       </c>
+      <c r="U201" s="1" t="n">
+        <v>0.12339</v>
+      </c>
+      <c r="V201" s="3" t="n">
+        <v>-0.0006479306714181318</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -13413,6 +14625,12 @@
       <c r="T202" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="U202" s="1" t="n">
+        <v>0.01387</v>
+      </c>
+      <c r="V202" s="2" t="n">
+        <v>0.003617945007235868</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -13477,6 +14695,12 @@
       <c r="T203" s="2" t="n">
         <v>0.001218620521569618</v>
       </c>
+      <c r="U203" s="1" t="n">
+        <v>0.04117</v>
+      </c>
+      <c r="V203" s="2" t="n">
+        <v>0.002190847127555984</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -13541,6 +14765,12 @@
       <c r="T204" s="2" t="n">
         <v>0.0003875968992247904</v>
       </c>
+      <c r="U204" s="1" t="n">
+        <v>0.02579</v>
+      </c>
+      <c r="V204" s="3" t="n">
+        <v>-0.0007748934521502978</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -13605,6 +14835,12 @@
       <c r="T205" s="2" t="n">
         <v>0.000462962962962912</v>
       </c>
+      <c r="U205" s="1" t="n">
+        <v>0.432</v>
+      </c>
+      <c r="V205" s="3" t="n">
+        <v>-0.0004627487274409486</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -13669,6 +14905,12 @@
       <c r="T206" s="2" t="n">
         <v>0.002180549498473678</v>
       </c>
+      <c r="U206" s="1" t="n">
+        <v>0.02287</v>
+      </c>
+      <c r="V206" s="3" t="n">
+        <v>-0.00478677110530892</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -13733,6 +14975,12 @@
       <c r="T207" s="2" t="n">
         <v>0.001681479702137803</v>
       </c>
+      <c r="U207" s="1" t="n">
+        <v>4.178</v>
+      </c>
+      <c r="V207" s="2" t="n">
+        <v>0.001918465227817748</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -13797,6 +15045,12 @@
       <c r="T208" s="2" t="n">
         <v>0.0005429618569295285</v>
       </c>
+      <c r="U208" s="1" t="n">
+        <v>0.07371999999999999</v>
+      </c>
+      <c r="V208" s="2" t="n">
+        <v>0.0001356668023334164</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -13861,6 +15115,12 @@
       <c r="T209" s="2" t="n">
         <v>0.001426533523537745</v>
       </c>
+      <c r="U209" s="1" t="n">
+        <v>0.04205</v>
+      </c>
+      <c r="V209" s="3" t="n">
+        <v>-0.00166191832858501</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -13925,6 +15185,12 @@
       <c r="T210" s="2" t="n">
         <v>0.002160994057266405</v>
       </c>
+      <c r="U210" s="1" t="n">
+        <v>0.1854</v>
+      </c>
+      <c r="V210" s="3" t="n">
+        <v>-0.0005390835579514231</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -13989,6 +15255,12 @@
       <c r="T211" s="3" t="n">
         <v>-0.002961082910321515</v>
       </c>
+      <c r="U211" s="1" t="n">
+        <v>0.2353</v>
+      </c>
+      <c r="V211" s="3" t="n">
+        <v>-0.001697072549851437</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -14053,6 +15325,12 @@
       <c r="T212" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="U212" s="1" t="n">
+        <v>0.002082</v>
+      </c>
+      <c r="V212" s="2" t="n">
+        <v>0.003373493975903644</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -14117,6 +15395,12 @@
       <c r="T213" s="2" t="n">
         <v>0.003225806451612906</v>
       </c>
+      <c r="U213" s="1" t="n">
+        <v>0.9330000000000001</v>
+      </c>
+      <c r="V213" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -14181,6 +15465,12 @@
       <c r="T214" s="3" t="n">
         <v>-0.0008747375787263465</v>
       </c>
+      <c r="U214" s="1" t="n">
+        <v>0.005719</v>
+      </c>
+      <c r="V214" s="2" t="n">
+        <v>0.00140080546314134</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -14245,6 +15535,12 @@
       <c r="T215" s="2" t="n">
         <v>0.001828822238478472</v>
       </c>
+      <c r="U215" s="1" t="n">
+        <v>0.05474</v>
+      </c>
+      <c r="V215" s="3" t="n">
+        <v>-0.0007301935012779355</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -14309,6 +15605,12 @@
       <c r="T216" s="2" t="n">
         <v>0.001582278481012484</v>
       </c>
+      <c r="U216" s="1" t="n">
+        <v>0.06320000000000001</v>
+      </c>
+      <c r="V216" s="3" t="n">
+        <v>-0.001579778830963491</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -14373,6 +15675,12 @@
       <c r="T217" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="U217" s="1" t="n">
+        <v>0.09279999999999999</v>
+      </c>
+      <c r="V217" s="2" t="n">
+        <v>0.001078748651564067</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -14437,6 +15745,12 @@
       <c r="T218" s="2" t="n">
         <v>0.003289473684210605</v>
       </c>
+      <c r="U218" s="1" t="n">
+        <v>0.27665</v>
+      </c>
+      <c r="V218" s="3" t="n">
+        <v>-0.003242658980363941</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -14501,6 +15815,12 @@
       <c r="T219" s="2" t="n">
         <v>0.005528255528255462</v>
       </c>
+      <c r="U219" s="1" t="n">
+        <v>0.003273</v>
+      </c>
+      <c r="V219" s="3" t="n">
+        <v>-0.0003054367745877009</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -14565,6 +15885,12 @@
       <c r="T220" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="U220" s="1" t="n">
+        <v>0.999373</v>
+      </c>
+      <c r="V220" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -14629,6 +15955,12 @@
       <c r="T221" s="2" t="n">
         <v>0.005155968032998164</v>
       </c>
+      <c r="U221" s="1" t="n">
+        <v>0.03893</v>
+      </c>
+      <c r="V221" s="3" t="n">
+        <v>-0.001538856116953002</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -14693,6 +16025,12 @@
       <c r="T222" s="2" t="n">
         <v>0.002581755593803831</v>
       </c>
+      <c r="U222" s="1" t="n">
+        <v>0.04662</v>
+      </c>
+      <c r="V222" s="2" t="n">
+        <v>0.0004291845493562056</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -14757,6 +16095,12 @@
       <c r="T223" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="U223" s="1" t="n">
+        <v>0.1055</v>
+      </c>
+      <c r="V223" s="2" t="n">
+        <v>0.000948766603415587</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -14821,6 +16165,12 @@
       <c r="T224" s="3" t="n">
         <v>-0.004336734693877527</v>
       </c>
+      <c r="U224" s="1" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="V224" s="2" t="n">
+        <v>0.001793492185498365</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -14885,6 +16235,12 @@
       <c r="T225" s="3" t="n">
         <v>-0.00086673889490793</v>
       </c>
+      <c r="U225" s="1" t="n">
+        <v>0.0009239</v>
+      </c>
+      <c r="V225" s="2" t="n">
+        <v>0.001843417913684653</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -14949,6 +16305,12 @@
       <c r="T226" s="2" t="n">
         <v>0.002708431464908202</v>
       </c>
+      <c r="U226" s="1" t="n">
+        <v>0.008514000000000001</v>
+      </c>
+      <c r="V226" s="3" t="n">
+        <v>-0.0001174398120962144</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -15013,6 +16375,12 @@
       <c r="T227" s="3" t="n">
         <v>-0.0007251631617112717</v>
       </c>
+      <c r="U227" s="1" t="n">
+        <v>0.04134</v>
+      </c>
+      <c r="V227" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -15077,6 +16445,12 @@
       <c r="T228" s="2" t="n">
         <v>0.0008424599831506686</v>
       </c>
+      <c r="U228" s="1" t="n">
+        <v>0.03563</v>
+      </c>
+      <c r="V228" s="3" t="n">
+        <v>-0.0002805836139168385</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -15141,6 +16515,12 @@
       <c r="T229" s="2" t="n">
         <v>0.002535595865028246</v>
       </c>
+      <c r="U229" s="1" t="n">
+        <v>0.0515</v>
+      </c>
+      <c r="V229" s="2" t="n">
+        <v>0.001945525291828714</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -15205,6 +16585,12 @@
       <c r="T230" s="2" t="n">
         <v>0.009872241579558703</v>
       </c>
+      <c r="U230" s="1" t="n">
+        <v>0.00173</v>
+      </c>
+      <c r="V230" s="3" t="n">
+        <v>-0.005175388154111621</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -15269,6 +16655,12 @@
       <c r="T231" s="3" t="n">
         <v>-0.004106776180698127</v>
       </c>
+      <c r="U231" s="1" t="n">
+        <v>0.04856</v>
+      </c>
+      <c r="V231" s="2" t="n">
+        <v>0.001237113402061805</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -15333,6 +16725,12 @@
       <c r="T232" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="U232" s="1" t="n">
+        <v>0.02172</v>
+      </c>
+      <c r="V232" s="2" t="n">
+        <v>0.00323325635103929</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -15397,6 +16795,12 @@
       <c r="T233" s="2" t="n">
         <v>0.002568493150684901</v>
       </c>
+      <c r="U233" s="1" t="n">
+        <v>0.0005854</v>
+      </c>
+      <c r="V233" s="3" t="n">
+        <v>-0.0001707941929973496</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -15461,6 +16865,12 @@
       <c r="T234" s="3" t="n">
         <v>-0.002140060103815673</v>
       </c>
+      <c r="U234" s="1" t="n">
+        <v>0.21724</v>
+      </c>
+      <c r="V234" s="3" t="n">
+        <v>-0.008715491672370627</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -15525,6 +16935,12 @@
       <c r="T235" s="2" t="n">
         <v>0.006465517241379296</v>
       </c>
+      <c r="U235" s="1" t="n">
+        <v>0.01398</v>
+      </c>
+      <c r="V235" s="3" t="n">
+        <v>-0.002141327623126375</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -15589,6 +17005,12 @@
       <c r="T236" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="U236" s="1" t="n">
+        <v>0.0413</v>
+      </c>
+      <c r="V236" s="2" t="n">
+        <v>0.002427184466019487</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -15653,6 +17075,12 @@
       <c r="T237" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="U237" s="1" t="n">
+        <v>0.0042</v>
+      </c>
+      <c r="V237" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -15717,6 +17145,12 @@
       <c r="T238" s="2" t="n">
         <v>0.004016064257028227</v>
       </c>
+      <c r="U238" s="1" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="V238" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -15781,6 +17215,12 @@
       <c r="T239" s="2" t="n">
         <v>0.004040404040403993</v>
       </c>
+      <c r="U239" s="1" t="n">
+        <v>0.01496</v>
+      </c>
+      <c r="V239" s="2" t="n">
+        <v>0.00335345405767939</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -15845,6 +17285,12 @@
       <c r="T240" s="2" t="n">
         <v>0.001277791975466286</v>
       </c>
+      <c r="U240" s="1" t="n">
+        <v>0.0003922</v>
+      </c>
+      <c r="V240" s="2" t="n">
+        <v>0.001020929045431367</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -15909,6 +17355,12 @@
       <c r="T241" s="2" t="n">
         <v>0.00223131275567142</v>
       </c>
+      <c r="U241" s="1" t="n">
+        <v>0.2695</v>
+      </c>
+      <c r="V241" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -15973,6 +17425,12 @@
       <c r="T242" s="3" t="n">
         <v>-0.008214891120093777</v>
       </c>
+      <c r="U242" s="1" t="n">
+        <v>0.07606</v>
+      </c>
+      <c r="V242" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -16037,6 +17495,12 @@
       <c r="T243" s="2" t="n">
         <v>0.002027369488089121</v>
       </c>
+      <c r="U243" s="1" t="n">
+        <v>0.0198</v>
+      </c>
+      <c r="V243" s="2" t="n">
+        <v>0.001517450682852921</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -16101,6 +17565,12 @@
       <c r="T244" s="3" t="n">
         <v>-0.002184159098746934</v>
       </c>
+      <c r="U244" s="1" t="n">
+        <v>0.08694</v>
+      </c>
+      <c r="V244" s="2" t="n">
+        <v>0.001612903225806466</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -16165,6 +17635,12 @@
       <c r="T245" s="2" t="n">
         <v>0.001747762863534794</v>
       </c>
+      <c r="U245" s="1" t="n">
+        <v>1.439</v>
+      </c>
+      <c r="V245" s="2" t="n">
+        <v>0.00425710098401842</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -16229,6 +17705,12 @@
       <c r="T246" s="2" t="n">
         <v>0.0005627462014631172</v>
       </c>
+      <c r="U246" s="1" t="n">
+        <v>0.01777</v>
+      </c>
+      <c r="V246" s="3" t="n">
+        <v>-0.0005624296962879411</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -16293,6 +17775,12 @@
       <c r="T247" s="2" t="n">
         <v>0.002725620835857155</v>
       </c>
+      <c r="U247" s="1" t="n">
+        <v>0.006621</v>
+      </c>
+      <c r="V247" s="3" t="n">
+        <v>-0.0001510117789187757</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -16357,6 +17845,12 @@
       <c r="T248" s="2" t="n">
         <v>0.01199040767386084</v>
       </c>
+      <c r="U248" s="1" t="n">
+        <v>0.004168</v>
+      </c>
+      <c r="V248" s="3" t="n">
+        <v>-0.01232227488151658</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -16421,6 +17915,12 @@
       <c r="T249" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="U249" s="1" t="n">
+        <v>0.1097</v>
+      </c>
+      <c r="V249" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -16485,6 +17985,12 @@
       <c r="T250" s="2" t="n">
         <v>0.009048453006421419</v>
       </c>
+      <c r="U250" s="1" t="n">
+        <v>0.03447</v>
+      </c>
+      <c r="V250" s="3" t="n">
+        <v>-0.002892681515764996</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -16549,6 +18055,12 @@
       <c r="T251" s="3" t="n">
         <v>-0.002535730751498363</v>
       </c>
+      <c r="U251" s="1" t="n">
+        <v>0.04304</v>
+      </c>
+      <c r="V251" s="3" t="n">
+        <v>-0.005315461058470096</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -16613,6 +18125,12 @@
       <c r="T252" s="3" t="n">
         <v>-0.003105590062111788</v>
       </c>
+      <c r="U252" s="1" t="n">
+        <v>0.006091</v>
+      </c>
+      <c r="V252" s="3" t="n">
+        <v>-0.001311690441055943</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -16677,6 +18195,12 @@
       <c r="T253" s="2" t="n">
         <v>0.02611275964391688</v>
       </c>
+      <c r="U253" s="1" t="n">
+        <v>0.01749</v>
+      </c>
+      <c r="V253" s="2" t="n">
+        <v>0.01156737998843255</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -16741,6 +18265,12 @@
       <c r="T254" s="2" t="n">
         <v>0.0007704160246532279</v>
       </c>
+      <c r="U254" s="1" t="n">
+        <v>0.1296</v>
+      </c>
+      <c r="V254" s="3" t="n">
+        <v>-0.00230946882217086</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -16805,6 +18335,12 @@
       <c r="T255" s="2" t="n">
         <v>0.01906577693040996</v>
       </c>
+      <c r="U255" s="1" t="n">
+        <v>0.02119</v>
+      </c>
+      <c r="V255" s="3" t="n">
+        <v>-0.008886810102899869</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -16869,6 +18405,12 @@
       <c r="T256" s="2" t="n">
         <v>0.002854424357754568</v>
       </c>
+      <c r="U256" s="1" t="n">
+        <v>0.02105</v>
+      </c>
+      <c r="V256" s="3" t="n">
+        <v>-0.001423149905123446</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -16933,6 +18475,12 @@
       <c r="T257" s="3" t="n">
         <v>-0.001578531965272369</v>
       </c>
+      <c r="U257" s="1" t="n">
+        <v>0.02525</v>
+      </c>
+      <c r="V257" s="3" t="n">
+        <v>-0.001976284584980157</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -16997,6 +18545,12 @@
       <c r="T258" s="2" t="n">
         <v>0.004830917874396125</v>
       </c>
+      <c r="U258" s="1" t="n">
+        <v>0.15068</v>
+      </c>
+      <c r="V258" s="2" t="n">
+        <v>0.006143162393162421</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -17061,6 +18615,12 @@
       <c r="T259" s="3" t="n">
         <v>-0.0001963864886096438</v>
       </c>
+      <c r="U259" s="1" t="n">
+        <v>0.05083</v>
+      </c>
+      <c r="V259" s="3" t="n">
+        <v>-0.001571400510705102</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -17125,6 +18685,12 @@
       <c r="T260" s="2" t="n">
         <v>0.0006004563468236865</v>
       </c>
+      <c r="U260" s="1" t="n">
+        <v>0.08309</v>
+      </c>
+      <c r="V260" s="3" t="n">
+        <v>-0.002760441670667402</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -17189,6 +18755,12 @@
       <c r="T261" s="2" t="n">
         <v>0.01346938775510203</v>
       </c>
+      <c r="U261" s="1" t="n">
+        <v>0.2497</v>
+      </c>
+      <c r="V261" s="2" t="n">
+        <v>0.005638340716874798</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -17253,6 +18825,12 @@
       <c r="T262" s="2" t="n">
         <v>0.005614035087719459</v>
       </c>
+      <c r="U262" s="1" t="n">
+        <v>0.1439</v>
+      </c>
+      <c r="V262" s="2" t="n">
+        <v>0.004187020237264406</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -17317,6 +18895,12 @@
       <c r="T263" s="3" t="n">
         <v>-0.00168765416071667</v>
       </c>
+      <c r="U263" s="1" t="n">
+        <v>0.07698000000000001</v>
+      </c>
+      <c r="V263" s="2" t="n">
+        <v>0.001040312093628227</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -17381,6 +18965,12 @@
       <c r="T264" s="2" t="n">
         <v>0.002022244691607778</v>
       </c>
+      <c r="U264" s="1" t="n">
+        <v>0.03935</v>
+      </c>
+      <c r="V264" s="3" t="n">
+        <v>-0.007315842583249207</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -17445,6 +19035,12 @@
       <c r="T265" s="3" t="n">
         <v>-0.0006527415143602868</v>
       </c>
+      <c r="U265" s="1" t="n">
+        <v>0.0153</v>
+      </c>
+      <c r="V265" s="3" t="n">
+        <v>-0.0006531678641411709</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -17509,6 +19105,12 @@
       <c r="T266" s="2" t="n">
         <v>0.002191503708698582</v>
       </c>
+      <c r="U266" s="1" t="n">
+        <v>0.005954</v>
+      </c>
+      <c r="V266" s="2" t="n">
+        <v>0.00151387720773765</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -17573,6 +19175,12 @@
       <c r="T267" s="2" t="n">
         <v>0.004298764105319545</v>
       </c>
+      <c r="U267" s="1" t="n">
+        <v>0.03733</v>
+      </c>
+      <c r="V267" s="3" t="n">
+        <v>-0.001337613697164112</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -17637,6 +19245,12 @@
       <c r="T268" s="2" t="n">
         <v>0.002616088947024206</v>
       </c>
+      <c r="U268" s="1" t="n">
+        <v>0.03064</v>
+      </c>
+      <c r="V268" s="3" t="n">
+        <v>-0.0006523157208088449</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -17701,6 +19315,12 @@
       <c r="T269" s="3" t="n">
         <v>-0.004795002639451028</v>
       </c>
+      <c r="U269" s="1" t="n">
+        <v>0.22643</v>
+      </c>
+      <c r="V269" s="2" t="n">
+        <v>0.0008840560491535417</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -17765,6 +19385,12 @@
       <c r="T270" s="2" t="n">
         <v>0.002162162162162164</v>
       </c>
+      <c r="U270" s="1" t="n">
+        <v>0.925</v>
+      </c>
+      <c r="V270" s="3" t="n">
+        <v>-0.002157497303128373</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -17829,6 +19455,12 @@
       <c r="T271" s="2" t="n">
         <v>0.005034856700232512</v>
       </c>
+      <c r="U271" s="1" t="n">
+        <v>2.601</v>
+      </c>
+      <c r="V271" s="2" t="n">
+        <v>0.002312138728323616</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -17893,6 +19525,12 @@
       <c r="T272" s="2" t="n">
         <v>0.001624255549539766</v>
       </c>
+      <c r="U272" s="1" t="n">
+        <v>0.1851</v>
+      </c>
+      <c r="V272" s="2" t="n">
+        <v>0.000540540540540481</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -17957,6 +19595,12 @@
       <c r="T273" s="3" t="n">
         <v>-0.0009671179883945448</v>
       </c>
+      <c r="U273" s="1" t="n">
+        <v>0.03102</v>
+      </c>
+      <c r="V273" s="2" t="n">
+        <v>0.0009680542110357786</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -18021,6 +19665,12 @@
       <c r="T274" s="2" t="n">
         <v>0.002612330198537098</v>
       </c>
+      <c r="U274" s="1" t="n">
+        <v>0.1922</v>
+      </c>
+      <c r="V274" s="2" t="n">
+        <v>0.001563314226159575</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -18085,6 +19735,12 @@
       <c r="T275" s="3" t="n">
         <v>-0.001158580738595174</v>
       </c>
+      <c r="U275" s="1" t="n">
+        <v>0.06904</v>
+      </c>
+      <c r="V275" s="2" t="n">
+        <v>0.001014934029288105</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -18149,6 +19805,12 @@
       <c r="T276" s="3" t="n">
         <v>-0.0008697813121272443</v>
       </c>
+      <c r="U276" s="1" t="n">
+        <v>0.08037999999999999</v>
+      </c>
+      <c r="V276" s="3" t="n">
+        <v>-0.000373087924387542</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -18213,6 +19875,12 @@
       <c r="T277" s="2" t="n">
         <v>0.004277805737292313</v>
       </c>
+      <c r="U277" s="1" t="n">
+        <v>0.003998</v>
+      </c>
+      <c r="V277" s="2" t="n">
+        <v>0.001753946379353561</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -18277,6 +19945,12 @@
       <c r="T278" s="2" t="n">
         <v>0.001287830006439151</v>
       </c>
+      <c r="U278" s="1" t="n">
+        <v>1.554</v>
+      </c>
+      <c r="V278" s="3" t="n">
+        <v>-0.0006430868167201865</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -18341,6 +20015,12 @@
       <c r="T279" s="3" t="n">
         <v>-0.0009057971014492385</v>
       </c>
+      <c r="U279" s="1" t="n">
+        <v>0.01102</v>
+      </c>
+      <c r="V279" s="3" t="n">
+        <v>-0.0009066183136898996</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -18405,6 +20085,12 @@
       <c r="T280" s="3" t="n">
         <v>-0.009492880339745324</v>
       </c>
+      <c r="U280" s="1" t="n">
+        <v>0.04036</v>
+      </c>
+      <c r="V280" s="2" t="n">
+        <v>0.01790668348045403</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -18469,6 +20155,12 @@
       <c r="T281" s="2" t="n">
         <v>0.005618649133293463</v>
       </c>
+      <c r="U281" s="1" t="n">
+        <v>0.08383</v>
+      </c>
+      <c r="V281" s="3" t="n">
+        <v>-0.003447456015216341</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -18533,6 +20225,12 @@
       <c r="T282" s="2" t="n">
         <v>0.003773584905660355</v>
       </c>
+      <c r="U282" s="1" t="n">
+        <v>0.0267</v>
+      </c>
+      <c r="V282" s="2" t="n">
+        <v>0.003759398496240709</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -18597,6 +20295,12 @@
       <c r="T283" s="2" t="n">
         <v>0.0007878151260502969</v>
       </c>
+      <c r="U283" s="1" t="n">
+        <v>0.07643999999999999</v>
+      </c>
+      <c r="V283" s="2" t="n">
+        <v>0.0028863815271582</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -18661,6 +20365,12 @@
       <c r="T284" s="3" t="n">
         <v>-0.001236858379715553</v>
       </c>
+      <c r="U284" s="1" t="n">
+        <v>0.001613</v>
+      </c>
+      <c r="V284" s="3" t="n">
+        <v>-0.001238390092879153</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -18725,6 +20435,12 @@
       <c r="T285" s="2" t="n">
         <v>0.001482946119624294</v>
       </c>
+      <c r="U285" s="1" t="n">
+        <v>0.2023</v>
+      </c>
+      <c r="V285" s="3" t="n">
+        <v>-0.001480750246791682</v>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -18789,6 +20505,12 @@
       <c r="T286" s="2" t="n">
         <v>0.005442432204185017</v>
       </c>
+      <c r="U286" s="1" t="n">
+        <v>0.10699</v>
+      </c>
+      <c r="V286" s="3" t="n">
+        <v>-0.001493233784414312</v>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -18853,6 +20575,12 @@
       <c r="T287" s="2" t="n">
         <v>0.000577367205542902</v>
       </c>
+      <c r="U287" s="1" t="n">
+        <v>0.01734</v>
+      </c>
+      <c r="V287" s="2" t="n">
+        <v>0.0005770340450086319</v>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -18917,6 +20645,12 @@
       <c r="T288" s="2" t="n">
         <v>0.001324503311258224</v>
       </c>
+      <c r="U288" s="1" t="n">
+        <v>0.01507</v>
+      </c>
+      <c r="V288" s="3" t="n">
+        <v>-0.003306878306878287</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -18981,6 +20715,12 @@
       <c r="T289" s="2" t="n">
         <v>0.006857855361596164</v>
       </c>
+      <c r="U289" s="1" t="n">
+        <v>0.01617</v>
+      </c>
+      <c r="V289" s="2" t="n">
+        <v>0.001238390092879207</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -19045,6 +20785,12 @@
       <c r="T290" s="2" t="n">
         <v>0.0004413062665489364</v>
       </c>
+      <c r="U290" s="1" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="V290" s="2" t="n">
+        <v>0.001323334803705388</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -19109,6 +20855,12 @@
       <c r="T291" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="U291" s="1" t="n">
+        <v>0.4401</v>
+      </c>
+      <c r="V291" s="2" t="n">
+        <v>0.002049180327868879</v>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -19173,6 +20925,12 @@
       <c r="T292" s="3" t="n">
         <v>-0.004039238315060656</v>
       </c>
+      <c r="U292" s="1" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="V292" s="2" t="n">
+        <v>0.002317497103128623</v>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -19237,6 +20995,12 @@
       <c r="T293" s="3" t="n">
         <v>-0.002961500493583364</v>
       </c>
+      <c r="U293" s="1" t="n">
+        <v>0.04991</v>
+      </c>
+      <c r="V293" s="3" t="n">
+        <v>-0.01168316831683169</v>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -19301,6 +21065,12 @@
       <c r="T294" s="3" t="n">
         <v>-0.0007874015748030629</v>
       </c>
+      <c r="U294" s="1" t="n">
+        <v>0.06340999999999999</v>
+      </c>
+      <c r="V294" s="3" t="n">
+        <v>-0.0006304176516944404</v>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -19365,6 +21135,12 @@
       <c r="T295" s="2" t="n">
         <v>0.003380009657170531</v>
       </c>
+      <c r="U295" s="1" t="n">
+        <v>0.0004148</v>
+      </c>
+      <c r="V295" s="3" t="n">
+        <v>-0.001924927815206976</v>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -19429,6 +21205,12 @@
       <c r="T296" s="2" t="n">
         <v>0.002727856225930708</v>
       </c>
+      <c r="U296" s="1" t="n">
+        <v>62.59</v>
+      </c>
+      <c r="V296" s="2" t="n">
+        <v>0.001600256040966577</v>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -19493,6 +21275,12 @@
       <c r="T297" s="3" t="n">
         <v>-0.001021450459652736</v>
       </c>
+      <c r="U297" s="1" t="n">
+        <v>0.0977</v>
+      </c>
+      <c r="V297" s="3" t="n">
+        <v>-0.001022494887525592</v>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -19557,6 +21345,12 @@
       <c r="T298" s="2" t="n">
         <v>0.002092050209204936</v>
       </c>
+      <c r="U298" s="1" t="n">
+        <v>0.09569999999999999</v>
+      </c>
+      <c r="V298" s="3" t="n">
+        <v>-0.00104384133611694</v>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -19621,6 +21415,12 @@
       <c r="T299" s="2" t="n">
         <v>0.001974641446684636</v>
       </c>
+      <c r="U299" s="1" t="n">
+        <v>0.09674000000000001</v>
+      </c>
+      <c r="V299" s="2" t="n">
+        <v>0.00342288144383374</v>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -19685,6 +21485,12 @@
       <c r="T300" s="2" t="n">
         <v>0.003215434083601341</v>
       </c>
+      <c r="U300" s="1" t="n">
+        <v>0.01876</v>
+      </c>
+      <c r="V300" s="2" t="n">
+        <v>0.00213675213675205</v>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -19749,6 +21555,12 @@
       <c r="T301" s="2" t="n">
         <v>0.002996254681647948</v>
       </c>
+      <c r="U301" s="1" t="n">
+        <v>0.01334</v>
+      </c>
+      <c r="V301" s="3" t="n">
+        <v>-0.003734129947722287</v>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -19813,6 +21625,12 @@
       <c r="T302" s="2" t="n">
         <v>0.004372842347525874</v>
       </c>
+      <c r="U302" s="1" t="n">
+        <v>0.004363</v>
+      </c>
+      <c r="V302" s="3" t="n">
+        <v>-0.0002291475710357774</v>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -19877,6 +21695,12 @@
       <c r="T303" s="2" t="n">
         <v>0.00323275862068971</v>
       </c>
+      <c r="U303" s="1" t="n">
+        <v>0.00924</v>
+      </c>
+      <c r="V303" s="3" t="n">
+        <v>-0.007518796992481269</v>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -19941,6 +21765,12 @@
       <c r="T304" s="3" t="n">
         <v>-0.001059546514091946</v>
       </c>
+      <c r="U304" s="1" t="n">
+        <v>4.714</v>
+      </c>
+      <c r="V304" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -20005,6 +21835,12 @@
       <c r="T305" s="2" t="n">
         <v>0.008173351073940313</v>
       </c>
+      <c r="U305" s="1" t="n">
+        <v>0.05313</v>
+      </c>
+      <c r="V305" s="2" t="n">
+        <v>0.001696832579185517</v>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -20069,6 +21905,12 @@
       <c r="T306" s="2" t="n">
         <v>0.0003437607425231898</v>
       </c>
+      <c r="U306" s="1" t="n">
+        <v>0.05823</v>
+      </c>
+      <c r="V306" s="2" t="n">
+        <v>0.0005154639175256925</v>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -20133,6 +21975,12 @@
       <c r="T307" s="2" t="n">
         <v>0.0005737234652896671</v>
       </c>
+      <c r="U307" s="1" t="n">
+        <v>0.1745</v>
+      </c>
+      <c r="V307" s="2" t="n">
+        <v>0.0005733944954127809</v>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -20197,6 +22045,12 @@
       <c r="T308" s="2" t="n">
         <v>0.004191616766467103</v>
       </c>
+      <c r="U308" s="1" t="n">
+        <v>0.04974</v>
+      </c>
+      <c r="V308" s="3" t="n">
+        <v>-0.01132975551580205</v>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -20261,6 +22115,12 @@
       <c r="T309" s="2" t="n">
         <v>0.0001843657817108942</v>
       </c>
+      <c r="U309" s="1" t="n">
+        <v>0.5438</v>
+      </c>
+      <c r="V309" s="2" t="n">
+        <v>0.002396313364055241</v>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -20325,6 +22185,12 @@
       <c r="T310" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="U310" s="1" t="n">
+        <v>0.00243</v>
+      </c>
+      <c r="V310" s="3" t="n">
+        <v>-0.004098360655737716</v>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -20389,6 +22255,12 @@
       <c r="T311" s="2" t="n">
         <v>0.003823279524213997</v>
       </c>
+      <c r="U311" s="1" t="n">
+        <v>0.07087</v>
+      </c>
+      <c r="V311" s="3" t="n">
+        <v>-0.0002821272393848533</v>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -20453,6 +22325,12 @@
       <c r="T312" s="2" t="n">
         <v>0.001003344481605194</v>
       </c>
+      <c r="U312" s="1" t="n">
+        <v>0.008965000000000001</v>
+      </c>
+      <c r="V312" s="3" t="n">
+        <v>-0.001559193674128343</v>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -20517,6 +22395,12 @@
       <c r="T313" s="3" t="n">
         <v>-0.003406447324692537</v>
       </c>
+      <c r="U313" s="1" t="n">
+        <v>0.011982</v>
+      </c>
+      <c r="V313" s="3" t="n">
+        <v>-0.001083784910379396</v>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -20581,6 +22465,12 @@
       <c r="T314" s="2" t="n">
         <v>0.00774860094705121</v>
       </c>
+      <c r="U314" s="1" t="n">
+        <v>0.02336</v>
+      </c>
+      <c r="V314" s="3" t="n">
+        <v>-0.002135839384878319</v>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -20645,6 +22535,12 @@
       <c r="T315" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="U315" s="1" t="n">
+        <v>0.00712</v>
+      </c>
+      <c r="V315" s="2" t="n">
+        <v>0.002816901408450589</v>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -20709,6 +22605,12 @@
       <c r="T316" s="2" t="n">
         <v>0.002692307692307609</v>
       </c>
+      <c r="U316" s="1" t="n">
+        <v>0.2601</v>
+      </c>
+      <c r="V316" s="3" t="n">
+        <v>-0.002301495972382008</v>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -20773,6 +22675,12 @@
       <c r="T317" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="U317" s="1" t="n">
+        <v>1.11e-05</v>
+      </c>
+      <c r="V317" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -20837,6 +22745,12 @@
       <c r="T318" s="2" t="n">
         <v>0.001867449216814682</v>
       </c>
+      <c r="U318" s="1" t="n">
+        <v>0.052679</v>
+      </c>
+      <c r="V318" s="2" t="n">
+        <v>0.001959068776628099</v>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -20901,6 +22815,12 @@
       <c r="T319" s="2" t="n">
         <v>0.0018343815513627</v>
       </c>
+      <c r="U319" s="1" t="n">
+        <v>0.03826</v>
+      </c>
+      <c r="V319" s="2" t="n">
+        <v>0.0007847240387131114</v>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -20965,6 +22885,12 @@
       <c r="T320" s="2" t="n">
         <v>0.0007364854912357927</v>
       </c>
+      <c r="U320" s="1" t="n">
+        <v>0.006803</v>
+      </c>
+      <c r="V320" s="2" t="n">
+        <v>0.001324698263173436</v>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -21029,6 +22955,12 @@
       <c r="T321" s="2" t="n">
         <v>0.001105216622457978</v>
       </c>
+      <c r="U321" s="1" t="n">
+        <v>4.522</v>
+      </c>
+      <c r="V321" s="3" t="n">
+        <v>-0.001545595054095755</v>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -21093,6 +23025,12 @@
       <c r="T322" s="2" t="n">
         <v>0.00103950103950104</v>
       </c>
+      <c r="U322" s="1" t="n">
+        <v>1.927</v>
+      </c>
+      <c r="V322" s="2" t="n">
+        <v>0.0005192107995846895</v>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -21157,6 +23095,12 @@
       <c r="T323" s="2" t="n">
         <v>0.001981599433828751</v>
       </c>
+      <c r="U323" s="1" t="n">
+        <v>0.00716</v>
+      </c>
+      <c r="V323" s="2" t="n">
+        <v>0.0114422941093374</v>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -21221,6 +23165,12 @@
       <c r="T324" s="3" t="n">
         <v>-0.002172732210754936</v>
       </c>
+      <c r="U324" s="1" t="n">
+        <v>0.01841</v>
+      </c>
+      <c r="V324" s="2" t="n">
+        <v>0.002177463255307478</v>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -21285,6 +23235,12 @@
       <c r="T325" s="2" t="n">
         <v>0.001222493887530563</v>
       </c>
+      <c r="U325" s="1" t="n">
+        <v>0.4102</v>
+      </c>
+      <c r="V325" s="2" t="n">
+        <v>0.001709401709401792</v>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -21349,6 +23305,12 @@
       <c r="T326" s="2" t="n">
         <v>0.002644030058446969</v>
       </c>
+      <c r="U326" s="1" t="n">
+        <v>0.007198</v>
+      </c>
+      <c r="V326" s="3" t="n">
+        <v>-0.0009715475364329209</v>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -21413,6 +23375,12 @@
       <c r="T327" s="2" t="n">
         <v>0.006867406233491789</v>
       </c>
+      <c r="U327" s="1" t="n">
+        <v>0.1915</v>
+      </c>
+      <c r="V327" s="2" t="n">
+        <v>0.004721930745015803</v>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -21477,6 +23445,12 @@
       <c r="T328" s="2" t="n">
         <v>0.01365113759479951</v>
       </c>
+      <c r="U328" s="1" t="n">
+        <v>0.4689</v>
+      </c>
+      <c r="V328" s="2" t="n">
+        <v>0.002351432235998268</v>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -21541,6 +23515,12 @@
       <c r="T329" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="U329" s="1" t="n">
+        <v>0.01345</v>
+      </c>
+      <c r="V329" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -21605,6 +23585,12 @@
       <c r="T330" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="U330" s="1" t="n">
+        <v>0.1132</v>
+      </c>
+      <c r="V330" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -21669,6 +23655,12 @@
       <c r="T331" s="2" t="n">
         <v>0.005140961857379754</v>
       </c>
+      <c r="U331" s="1" t="n">
+        <v>0.6048</v>
+      </c>
+      <c r="V331" s="3" t="n">
+        <v>-0.002144860584061983</v>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -21733,6 +23725,12 @@
       <c r="T332" s="3" t="n">
         <v>-0.004440381350398238</v>
       </c>
+      <c r="U332" s="1" t="n">
+        <v>0.30464</v>
+      </c>
+      <c r="V332" s="3" t="n">
+        <v>-0.0009182736455463808</v>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -21797,6 +23795,12 @@
       <c r="T333" s="2" t="n">
         <v>0.002419584400797089</v>
       </c>
+      <c r="U333" s="1" t="n">
+        <v>0.07058</v>
+      </c>
+      <c r="V333" s="2" t="n">
+        <v>0.002129774243930106</v>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -21861,6 +23865,12 @@
       <c r="T334" s="3" t="n">
         <v>-0.0001990577931126153</v>
       </c>
+      <c r="U334" s="1" t="n">
+        <v>0.15027</v>
+      </c>
+      <c r="V334" s="3" t="n">
+        <v>-0.002720998141757509</v>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -21925,6 +23935,12 @@
       <c r="T335" s="2" t="n">
         <v>0.003201024327784894</v>
       </c>
+      <c r="U335" s="1" t="n">
+        <v>0.1566</v>
+      </c>
+      <c r="V335" s="3" t="n">
+        <v>-0.0006381620931717724</v>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -21989,6 +24005,12 @@
       <c r="T336" s="3" t="n">
         <v>-0.001723147616312434</v>
       </c>
+      <c r="U336" s="1" t="n">
+        <v>0.174</v>
+      </c>
+      <c r="V336" s="2" t="n">
+        <v>0.001150747986190897</v>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -22053,6 +24075,12 @@
       <c r="T337" s="2" t="n">
         <v>0.00746083063914436</v>
       </c>
+      <c r="U337" s="1" t="n">
+        <v>0.04016</v>
+      </c>
+      <c r="V337" s="3" t="n">
+        <v>-0.008639842014317358</v>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -22117,6 +24145,12 @@
       <c r="T338" s="2" t="n">
         <v>0.001326259946949614</v>
       </c>
+      <c r="U338" s="1" t="n">
+        <v>0.005294</v>
+      </c>
+      <c r="V338" s="2" t="n">
+        <v>0.001702932828760705</v>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -22181,6 +24215,12 @@
       <c r="T339" s="2" t="n">
         <v>0.004477321393809637</v>
       </c>
+      <c r="U339" s="1" t="n">
+        <v>0.05172</v>
+      </c>
+      <c r="V339" s="2" t="n">
+        <v>0.002325581395348877</v>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -22245,6 +24285,12 @@
       <c r="T340" s="2" t="n">
         <v>0.001388797037232908</v>
       </c>
+      <c r="U340" s="1" t="n">
+        <v>0.15113</v>
+      </c>
+      <c r="V340" s="3" t="n">
+        <v>-0.001915202747325403</v>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -22309,6 +24355,12 @@
       <c r="T341" s="2" t="n">
         <v>0.002635740643120661</v>
       </c>
+      <c r="U341" s="1" t="n">
+        <v>7.625</v>
+      </c>
+      <c r="V341" s="2" t="n">
+        <v>0.002234490010515293</v>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -22373,6 +24425,12 @@
       <c r="T342" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="U342" s="1" t="n">
+        <v>0.3276</v>
+      </c>
+      <c r="V342" s="3" t="n">
+        <v>-0.002132196162046843</v>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -22437,6 +24495,12 @@
       <c r="T343" s="2" t="n">
         <v>0.002526528549772685</v>
       </c>
+      <c r="U343" s="1" t="n">
+        <v>0.01995</v>
+      </c>
+      <c r="V343" s="2" t="n">
+        <v>0.005544354838709627</v>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -22501,6 +24565,12 @@
       <c r="T344" s="2" t="n">
         <v>0.001378043178686318</v>
       </c>
+      <c r="U344" s="1" t="n">
+        <v>2.177</v>
+      </c>
+      <c r="V344" s="3" t="n">
+        <v>-0.001376146788990878</v>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -22565,6 +24635,12 @@
       <c r="T345" s="2" t="n">
         <v>0.004746835443037979</v>
       </c>
+      <c r="U345" s="1" t="n">
+        <v>1.267</v>
+      </c>
+      <c r="V345" s="3" t="n">
+        <v>-0.002362204724409538</v>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -22629,6 +24705,12 @@
       <c r="T346" s="2" t="n">
         <v>0.003881987577639761</v>
       </c>
+      <c r="U346" s="1" t="n">
+        <v>0.005172</v>
+      </c>
+      <c r="V346" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -22693,6 +24775,12 @@
       <c r="T347" s="2" t="n">
         <v>0.003332164152928722</v>
       </c>
+      <c r="U347" s="1" t="n">
+        <v>0.05731</v>
+      </c>
+      <c r="V347" s="2" t="n">
+        <v>0.001747946163258222</v>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -22757,6 +24845,12 @@
       <c r="T348" s="2" t="n">
         <v>0.0007867820613691325</v>
       </c>
+      <c r="U348" s="1" t="n">
+        <v>0.1276</v>
+      </c>
+      <c r="V348" s="2" t="n">
+        <v>0.003144654088050186</v>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -22821,6 +24915,12 @@
       <c r="T349" s="3" t="n">
         <v>-0.001287372223503155</v>
       </c>
+      <c r="U349" s="1" t="n">
+        <v>5189.6</v>
+      </c>
+      <c r="V349" s="3" t="n">
+        <v>-0.001558381591857832</v>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -22885,6 +24985,12 @@
       <c r="T350" s="3" t="n">
         <v>-0.004279600570613359</v>
       </c>
+      <c r="U350" s="1" t="n">
+        <v>0.02789</v>
+      </c>
+      <c r="V350" s="3" t="n">
+        <v>-0.0010744985673352</v>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -22949,6 +25055,12 @@
       <c r="T351" s="2" t="n">
         <v>0.004325883201153517</v>
       </c>
+      <c r="U351" s="1" t="n">
+        <v>0.001389</v>
+      </c>
+      <c r="V351" s="3" t="n">
+        <v>-0.002871500358937459</v>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -23013,6 +25125,12 @@
       <c r="T352" s="2" t="n">
         <v>0.002551020408163383</v>
       </c>
+      <c r="U352" s="1" t="n">
+        <v>0.01571</v>
+      </c>
+      <c r="V352" s="3" t="n">
+        <v>-0.0006361323155218233</v>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -23077,6 +25195,12 @@
       <c r="T353" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="U353" s="1" t="n">
+        <v>6.254</v>
+      </c>
+      <c r="V353" s="2" t="n">
+        <v>0.0004799232122859103</v>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -23141,6 +25265,12 @@
       <c r="T354" s="2" t="n">
         <v>0.0006973500697349302</v>
       </c>
+      <c r="U354" s="1" t="n">
+        <v>0.2872</v>
+      </c>
+      <c r="V354" s="2" t="n">
+        <v>0.0006968641114983746</v>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -23205,6 +25335,12 @@
       <c r="T355" s="2" t="n">
         <v>0.002172863351038141</v>
       </c>
+      <c r="U355" s="1" t="n">
+        <v>0.04155</v>
+      </c>
+      <c r="V355" s="2" t="n">
+        <v>0.0009636232233196428</v>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -23269,6 +25405,12 @@
       <c r="T356" s="3" t="n">
         <v>-0.007719298245614086</v>
       </c>
+      <c r="U356" s="1" t="n">
+        <v>0.1131</v>
+      </c>
+      <c r="V356" s="3" t="n">
+        <v>-0.0001768033946251083</v>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -23333,6 +25475,12 @@
       <c r="T357" s="3" t="n">
         <v>-0.005706676811869985</v>
       </c>
+      <c r="U357" s="1" t="n">
+        <v>0.005227</v>
+      </c>
+      <c r="V357" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -23397,6 +25545,12 @@
       <c r="T358" s="2" t="n">
         <v>0.004319654427645762</v>
       </c>
+      <c r="U358" s="1" t="n">
+        <v>0.1854</v>
+      </c>
+      <c r="V358" s="3" t="n">
+        <v>-0.003225806451612846</v>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -23461,6 +25615,12 @@
       <c r="T359" s="2" t="n">
         <v>0.001229256299938402</v>
       </c>
+      <c r="U359" s="1" t="n">
+        <v>0.1627</v>
+      </c>
+      <c r="V359" s="3" t="n">
+        <v>-0.00122774708410054</v>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -23525,6 +25685,12 @@
       <c r="T360" s="2" t="n">
         <v>0.005064782096584215</v>
       </c>
+      <c r="U360" s="1" t="n">
+        <v>0.08523</v>
+      </c>
+      <c r="V360" s="3" t="n">
+        <v>-0.00117192077815543</v>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -23589,6 +25755,12 @@
       <c r="T361" s="3" t="n">
         <v>-0.00261096605744126</v>
       </c>
+      <c r="U361" s="1" t="n">
+        <v>0.00762</v>
+      </c>
+      <c r="V361" s="3" t="n">
+        <v>-0.002617801047120426</v>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -23653,6 +25825,12 @@
       <c r="T362" s="2" t="n">
         <v>0.004009433962264233</v>
       </c>
+      <c r="U362" s="1" t="n">
+        <v>0.4259</v>
+      </c>
+      <c r="V362" s="2" t="n">
+        <v>0.0004698144233027436</v>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -23717,6 +25895,12 @@
       <c r="T363" s="2" t="n">
         <v>0.005573248407643405</v>
       </c>
+      <c r="U363" s="1" t="n">
+        <v>3.772</v>
+      </c>
+      <c r="V363" s="3" t="n">
+        <v>-0.004486671945104341</v>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -23781,6 +25965,12 @@
       <c r="T364" s="2" t="n">
         <v>0.003646308113035561</v>
       </c>
+      <c r="U364" s="1" t="n">
+        <v>0.01102</v>
+      </c>
+      <c r="V364" s="2" t="n">
+        <v>0.000908265213442288</v>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -23845,6 +26035,12 @@
       <c r="T365" s="2" t="n">
         <v>0.001273653566229997</v>
       </c>
+      <c r="U365" s="1" t="n">
+        <v>0.05504</v>
+      </c>
+      <c r="V365" s="2" t="n">
+        <v>0.0001817190623295679</v>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -23909,6 +26105,12 @@
       <c r="T366" s="2" t="n">
         <v>0.01794310722100659</v>
       </c>
+      <c r="U366" s="1" t="n">
+        <v>0.02281</v>
+      </c>
+      <c r="V366" s="3" t="n">
+        <v>-0.01934651762682713</v>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -23973,6 +26175,12 @@
       <c r="T367" s="3" t="n">
         <v>-0.01096491228070178</v>
       </c>
+      <c r="U367" s="1" t="n">
+        <v>0.001363</v>
+      </c>
+      <c r="V367" s="2" t="n">
+        <v>0.007390983000739117</v>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -24037,6 +26245,12 @@
       <c r="T368" s="2" t="n">
         <v>0.003502626970227674</v>
       </c>
+      <c r="U368" s="1" t="n">
+        <v>0.2866</v>
+      </c>
+      <c r="V368" s="2" t="n">
+        <v>0.0003490401396162112</v>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -24101,6 +26315,12 @@
       <c r="T369" s="2" t="n">
         <v>0.005408328826392612</v>
       </c>
+      <c r="U369" s="1" t="n">
+        <v>0.01852</v>
+      </c>
+      <c r="V369" s="3" t="n">
+        <v>-0.003765465303926876</v>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -24165,6 +26385,12 @@
       <c r="T370" s="2" t="n">
         <v>0.002272038776128336</v>
       </c>
+      <c r="U370" s="1" t="n">
+        <v>0.19747</v>
+      </c>
+      <c r="V370" s="3" t="n">
+        <v>-0.005239030779305755</v>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -24229,6 +26455,12 @@
       <c r="T371" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="U371" s="1" t="n">
+        <v>0.076</v>
+      </c>
+      <c r="V371" s="2" t="n">
+        <v>0.01333333333333335</v>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -24293,6 +26525,12 @@
       <c r="T372" s="2" t="n">
         <v>0.001904761904761959</v>
       </c>
+      <c r="U372" s="1" t="n">
+        <v>0.1051</v>
+      </c>
+      <c r="V372" s="3" t="n">
+        <v>-0.0009505703422053504</v>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -24357,6 +26595,12 @@
       <c r="T373" s="2" t="n">
         <v>0.001208094231349996</v>
       </c>
+      <c r="U373" s="1" t="n">
+        <v>0.06636</v>
+      </c>
+      <c r="V373" s="2" t="n">
+        <v>0.0009049773755656787</v>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -24421,6 +26665,12 @@
       <c r="T374" s="2" t="n">
         <v>0.0006569438969912842</v>
       </c>
+      <c r="U374" s="1" t="n">
+        <v>0.007604</v>
+      </c>
+      <c r="V374" s="3" t="n">
+        <v>-0.001575630252100936</v>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -24485,6 +26735,12 @@
       <c r="T375" s="2" t="n">
         <v>0.001890359168241933</v>
       </c>
+      <c r="U375" s="1" t="n">
+        <v>0.1589</v>
+      </c>
+      <c r="V375" s="3" t="n">
+        <v>-0.0006289308176099936</v>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -24549,6 +26805,12 @@
       <c r="T376" s="3" t="n">
         <v>-0.00438596491228065</v>
       </c>
+      <c r="U376" s="1" t="n">
+        <v>0.003404</v>
+      </c>
+      <c r="V376" s="3" t="n">
+        <v>-0.0002936857562408613</v>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -24613,6 +26875,12 @@
       <c r="T377" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="U377" s="1" t="n">
+        <v>0.0164</v>
+      </c>
+      <c r="V377" s="2" t="n">
+        <v>0.01234567901234582</v>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -24677,6 +26945,12 @@
       <c r="T378" s="2" t="n">
         <v>0.007922535211267588</v>
       </c>
+      <c r="U378" s="1" t="n">
+        <v>0.01132</v>
+      </c>
+      <c r="V378" s="3" t="n">
+        <v>-0.01135371179039301</v>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -24741,6 +27015,12 @@
       <c r="T379" s="3" t="n">
         <v>-0.0009332711152591066</v>
       </c>
+      <c r="U379" s="1" t="n">
+        <v>0.02141</v>
+      </c>
+      <c r="V379" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -24805,6 +27085,12 @@
       <c r="T380" s="3" t="n">
         <v>-0.002125398512220955</v>
       </c>
+      <c r="U380" s="1" t="n">
+        <v>0.01886</v>
+      </c>
+      <c r="V380" s="2" t="n">
+        <v>0.004259850905218143</v>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -24869,6 +27155,12 @@
       <c r="T381" s="2" t="n">
         <v>0.003333333333333313</v>
       </c>
+      <c r="U381" s="1" t="n">
+        <v>0.1202</v>
+      </c>
+      <c r="V381" s="3" t="n">
+        <v>-0.001661129568106245</v>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -24933,6 +27225,12 @@
       <c r="T382" s="2" t="n">
         <v>0.01645526225574212</v>
       </c>
+      <c r="U382" s="1" t="n">
+        <v>0.02951</v>
+      </c>
+      <c r="V382" s="3" t="n">
+        <v>-0.004721753794266367</v>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -24997,6 +27295,12 @@
       <c r="T383" s="2" t="n">
         <v>0.0024506049931076</v>
       </c>
+      <c r="U383" s="1" t="n">
+        <v>0.00654</v>
+      </c>
+      <c r="V383" s="3" t="n">
+        <v>-0.0007639419404124975</v>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -25061,6 +27365,12 @@
       <c r="T384" s="3" t="n">
         <v>-0.001913875598086047</v>
       </c>
+      <c r="U384" s="1" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="V384" s="3" t="n">
+        <v>-0.001438159156279903</v>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -25125,6 +27435,12 @@
       <c r="T385" s="2" t="n">
         <v>0.002370604504148558</v>
       </c>
+      <c r="U385" s="1" t="n">
+        <v>2536</v>
+      </c>
+      <c r="V385" s="3" t="n">
+        <v>-0.0003941663381947182</v>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -25189,6 +27505,12 @@
       <c r="T386" s="2" t="n">
         <v>0.005569620253164506</v>
       </c>
+      <c r="U386" s="1" t="n">
+        <v>0.1983</v>
+      </c>
+      <c r="V386" s="3" t="n">
+        <v>-0.001510574018126862</v>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -25253,6 +27575,12 @@
       <c r="T387" s="2" t="n">
         <v>0.001768033946251737</v>
       </c>
+      <c r="U387" s="1" t="n">
+        <v>0.08495999999999999</v>
+      </c>
+      <c r="V387" s="3" t="n">
+        <v>-0.0003529827038475379</v>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -25317,6 +27645,12 @@
       <c r="T388" s="3" t="n">
         <v>-0.0001996406468357222</v>
       </c>
+      <c r="U388" s="1" t="n">
+        <v>0.004989</v>
+      </c>
+      <c r="V388" s="3" t="n">
+        <v>-0.003793929712460048</v>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -25381,6 +27715,12 @@
       <c r="T389" s="2" t="n">
         <v>0.007114273010226786</v>
       </c>
+      <c r="U389" s="1" t="n">
+        <v>0.02277</v>
+      </c>
+      <c r="V389" s="2" t="n">
+        <v>0.00529801324503305</v>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -25445,6 +27785,12 @@
       <c r="T390" s="2" t="n">
         <v>0.002983293556085811</v>
       </c>
+      <c r="U390" s="1" t="n">
+        <v>0.5056</v>
+      </c>
+      <c r="V390" s="2" t="n">
+        <v>0.0025778306563555</v>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -25509,6 +27855,12 @@
       <c r="T391" s="2" t="n">
         <v>0.000993706525339361</v>
       </c>
+      <c r="U391" s="1" t="n">
+        <v>0.0006043999999999999</v>
+      </c>
+      <c r="V391" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -25573,6 +27925,12 @@
       <c r="T392" s="3" t="n">
         <v>-0.0006842285323297703</v>
       </c>
+      <c r="U392" s="1" t="n">
+        <v>0.05837</v>
+      </c>
+      <c r="V392" s="3" t="n">
+        <v>-0.0008558712769599697</v>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -25637,6 +27995,12 @@
       <c r="T393" s="2" t="n">
         <v>0.003365744203440375</v>
       </c>
+      <c r="U393" s="1" t="n">
+        <v>0.269</v>
+      </c>
+      <c r="V393" s="2" t="n">
+        <v>0.002609019754006835</v>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -25701,6 +28065,12 @@
       <c r="T394" s="2" t="n">
         <v>0.005196393091853917</v>
       </c>
+      <c r="U394" s="1" t="n">
+        <v>0.006573</v>
+      </c>
+      <c r="V394" s="3" t="n">
+        <v>-0.0006081800212863815</v>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -25765,6 +28135,12 @@
       <c r="T395" s="2" t="n">
         <v>0.0008718395815170258</v>
       </c>
+      <c r="U395" s="1" t="n">
+        <v>0.1149</v>
+      </c>
+      <c r="V395" s="2" t="n">
+        <v>0.0008710801393728472</v>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -25829,6 +28205,12 @@
       <c r="T396" s="2" t="n">
         <v>0.003567953292247778</v>
       </c>
+      <c r="U396" s="1" t="n">
+        <v>0.03087</v>
+      </c>
+      <c r="V396" s="3" t="n">
+        <v>-0.002262443438913935</v>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -25893,6 +28275,12 @@
       <c r="T397" s="2" t="n">
         <v>0.000663570006635627</v>
       </c>
+      <c r="U397" s="1" t="n">
+        <v>0.1507</v>
+      </c>
+      <c r="V397" s="3" t="n">
+        <v>-0.0006631299734747281</v>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -25957,6 +28345,12 @@
       <c r="T398" s="3" t="n">
         <v>-0.0003025718608169842</v>
       </c>
+      <c r="U398" s="1" t="n">
+        <v>0.0033</v>
+      </c>
+      <c r="V398" s="3" t="n">
+        <v>-0.001210653753026664</v>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -26021,6 +28415,12 @@
       <c r="T399" s="3" t="n">
         <v>-0.01074691026329942</v>
       </c>
+      <c r="U399" s="1" t="n">
+        <v>0.01873</v>
+      </c>
+      <c r="V399" s="2" t="n">
+        <v>0.01738185768604024</v>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -26085,6 +28485,12 @@
       <c r="T400" s="3" t="n">
         <v>-0.0112803158488438</v>
       </c>
+      <c r="U400" s="1" t="n">
+        <v>0.00694</v>
+      </c>
+      <c r="V400" s="3" t="n">
+        <v>-0.01026811180832858</v>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -26149,6 +28555,12 @@
       <c r="T401" s="3" t="n">
         <v>-0.0019997143265248</v>
       </c>
+      <c r="U401" s="1" t="n">
+        <v>0.006993</v>
+      </c>
+      <c r="V401" s="2" t="n">
+        <v>0.0008587376556461899</v>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -26213,6 +28625,12 @@
       <c r="T402" s="3" t="n">
         <v>-0.004479840716774462</v>
       </c>
+      <c r="U402" s="1" t="n">
+        <v>0.008002</v>
+      </c>
+      <c r="V402" s="2" t="n">
+        <v>0.0002500000000000332</v>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -26277,6 +28695,12 @@
       <c r="T403" s="2" t="n">
         <v>0.01129827444535748</v>
       </c>
+      <c r="U403" s="1" t="n">
+        <v>0.04907</v>
+      </c>
+      <c r="V403" s="3" t="n">
+        <v>-0.003250050782043478</v>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -26341,6 +28765,12 @@
       <c r="T404" s="2" t="n">
         <v>0.004883673607813867</v>
       </c>
+      <c r="U404" s="1" t="n">
+        <v>0.14881</v>
+      </c>
+      <c r="V404" s="2" t="n">
+        <v>0.004454944313196043</v>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -26405,6 +28835,12 @@
       <c r="T405" s="3" t="n">
         <v>-0.0009304489416142909</v>
       </c>
+      <c r="U405" s="1" t="n">
+        <v>0.04281</v>
+      </c>
+      <c r="V405" s="3" t="n">
+        <v>-0.003259604190919703</v>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -26469,6 +28905,12 @@
       <c r="T406" s="2" t="n">
         <v>0.0006269592476489498</v>
       </c>
+      <c r="U406" s="1" t="n">
+        <v>0.4785</v>
+      </c>
+      <c r="V406" s="3" t="n">
+        <v>-0.0006265664160401472</v>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -26533,6 +28975,12 @@
       <c r="T407" s="2" t="n">
         <v>0.001015847216578541</v>
       </c>
+      <c r="U407" s="1" t="n">
+        <v>0.0004928000000000001</v>
+      </c>
+      <c r="V407" s="2" t="n">
+        <v>0.0002029632636493944</v>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -26597,6 +29045,12 @@
       <c r="T408" s="2" t="n">
         <v>0.002437043054427337</v>
       </c>
+      <c r="U408" s="1" t="n">
+        <v>0.01235</v>
+      </c>
+      <c r="V408" s="2" t="n">
+        <v>0.0008103727714748454</v>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -26661,6 +29115,12 @@
       <c r="T409" s="3" t="n">
         <v>-0.0006287331027977931</v>
       </c>
+      <c r="U409" s="1" t="n">
+        <v>0.3168</v>
+      </c>
+      <c r="V409" s="3" t="n">
+        <v>-0.003460207612456715</v>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -26725,6 +29185,12 @@
       <c r="T410" s="2" t="n">
         <v>0.001201345506967839</v>
       </c>
+      <c r="U410" s="1" t="n">
+        <v>0.04178</v>
+      </c>
+      <c r="V410" s="2" t="n">
+        <v>0.002639788816894624</v>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -26789,6 +29255,12 @@
       <c r="T411" s="2" t="n">
         <v>0.001011804384485742</v>
       </c>
+      <c r="U411" s="1" t="n">
+        <v>0.02968</v>
+      </c>
+      <c r="V411" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
@@ -26853,6 +29325,12 @@
       <c r="T412" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="U412" s="1" t="n">
+        <v>0.004576</v>
+      </c>
+      <c r="V412" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -26917,6 +29395,12 @@
       <c r="T413" s="3" t="n">
         <v>-0.0003987240829347866</v>
       </c>
+      <c r="U413" s="1" t="n">
+        <v>0.2515</v>
+      </c>
+      <c r="V413" s="2" t="n">
+        <v>0.003191065017949832</v>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -26981,6 +29465,12 @@
       <c r="T414" s="2" t="n">
         <v>0.001566170712607676</v>
       </c>
+      <c r="U414" s="1" t="n">
+        <v>1.279</v>
+      </c>
+      <c r="V414" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -27045,6 +29535,12 @@
       <c r="T415" s="2" t="n">
         <v>0.001837559720690883</v>
       </c>
+      <c r="U415" s="1" t="n">
+        <v>2.731</v>
+      </c>
+      <c r="V415" s="2" t="n">
+        <v>0.001834189288334517</v>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -27109,6 +29605,12 @@
       <c r="T416" s="3" t="n">
         <v>-0.001551349674216613</v>
       </c>
+      <c r="U416" s="1" t="n">
+        <v>0.03233</v>
+      </c>
+      <c r="V416" s="2" t="n">
+        <v>0.004661280298321857</v>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -27173,6 +29675,12 @@
       <c r="T417" s="3" t="n">
         <v>-0.004747626186906613</v>
       </c>
+      <c r="U417" s="1" t="n">
+        <v>0.03959</v>
+      </c>
+      <c r="V417" s="3" t="n">
+        <v>-0.006025608837559557</v>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -27237,6 +29745,12 @@
       <c r="T418" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="U418" s="1" t="n">
+        <v>0.07614</v>
+      </c>
+      <c r="V418" s="2" t="n">
+        <v>0.0009202050742737034</v>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -27301,6 +29815,12 @@
       <c r="T419" s="2" t="n">
         <v>0.001510574018126827</v>
       </c>
+      <c r="U419" s="1" t="n">
+        <v>0.00662</v>
+      </c>
+      <c r="V419" s="3" t="n">
+        <v>-0.001508295625942623</v>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -27365,6 +29885,12 @@
       <c r="T420" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="U420" s="1" t="n">
+        <v>0.0882</v>
+      </c>
+      <c r="V420" s="3" t="n">
+        <v>-0.003389830508474517</v>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -27429,6 +29955,12 @@
       <c r="T421" s="3" t="n">
         <v>-0.006633499170812564</v>
       </c>
+      <c r="U421" s="1" t="n">
+        <v>0.2396</v>
+      </c>
+      <c r="V421" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
@@ -27493,6 +30025,12 @@
       <c r="T422" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="U422" s="1" t="n">
+        <v>0.0195</v>
+      </c>
+      <c r="V422" s="2" t="n">
+        <v>0.005154639175257701</v>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -27557,6 +30095,12 @@
       <c r="T423" s="2" t="n">
         <v>0.001327140013271438</v>
       </c>
+      <c r="U423" s="1" t="n">
+        <v>0.1511</v>
+      </c>
+      <c r="V423" s="2" t="n">
+        <v>0.001325381047051065</v>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -27621,6 +30165,12 @@
       <c r="T424" s="3" t="n">
         <v>-0.001915708812260583</v>
       </c>
+      <c r="U424" s="1" t="n">
+        <v>0.0002091</v>
+      </c>
+      <c r="V424" s="2" t="n">
+        <v>0.003358925143953887</v>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -27685,6 +30235,12 @@
       <c r="T425" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="U425" s="1" t="n">
+        <v>1.237</v>
+      </c>
+      <c r="V425" s="3" t="n">
+        <v>-0.0008077544426493456</v>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
@@ -27749,6 +30305,12 @@
       <c r="T426" s="2" t="n">
         <v>0.001417434443656982</v>
       </c>
+      <c r="U426" s="1" t="n">
+        <v>1.413</v>
+      </c>
+      <c r="V426" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -27813,6 +30375,12 @@
       <c r="T427" s="2" t="n">
         <v>0.003094378545641957</v>
       </c>
+      <c r="U427" s="1" t="n">
+        <v>0.01944</v>
+      </c>
+      <c r="V427" s="3" t="n">
+        <v>-0.0005141388174806988</v>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
@@ -27877,6 +30445,12 @@
       <c r="T428" s="2" t="n">
         <v>0.003343465045592674</v>
       </c>
+      <c r="U428" s="1" t="n">
+        <v>0.06619</v>
+      </c>
+      <c r="V428" s="2" t="n">
+        <v>0.002574977279612292</v>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
@@ -27941,6 +30515,12 @@
       <c r="T429" s="3" t="n">
         <v>-0.001510574018126722</v>
       </c>
+      <c r="U429" s="1" t="n">
+        <v>0.132</v>
+      </c>
+      <c r="V429" s="3" t="n">
+        <v>-0.001512859304084763</v>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
@@ -28005,6 +30585,12 @@
       <c r="T430" s="3" t="n">
         <v>-0.001359064963305191</v>
       </c>
+      <c r="U430" s="1" t="n">
+        <v>0.011032</v>
+      </c>
+      <c r="V430" s="2" t="n">
+        <v>0.0009072763563781158</v>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -28069,6 +30655,12 @@
       <c r="T431" s="2" t="n">
         <v>0.01498127340823961</v>
       </c>
+      <c r="U431" s="1" t="n">
+        <v>0.006695</v>
+      </c>
+      <c r="V431" s="3" t="n">
+        <v>-0.01180811808118071</v>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
@@ -28133,6 +30725,12 @@
       <c r="T432" s="2" t="n">
         <v>0.002836074872376638</v>
       </c>
+      <c r="U432" s="1" t="n">
+        <v>0.001768</v>
+      </c>
+      <c r="V432" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
@@ -28197,6 +30795,12 @@
       <c r="T433" s="3" t="n">
         <v>-0.002212389380530947</v>
       </c>
+      <c r="U433" s="1" t="n">
+        <v>0.001362</v>
+      </c>
+      <c r="V433" s="2" t="n">
+        <v>0.00665188470066511</v>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
@@ -28261,6 +30865,12 @@
       <c r="T434" s="3" t="n">
         <v>-0.002433090024330959</v>
       </c>
+      <c r="U434" s="1" t="n">
+        <v>0.00041</v>
+      </c>
+      <c r="V434" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
@@ -28325,6 +30935,12 @@
       <c r="T435" s="3" t="n">
         <v>-0.001499723735101395</v>
       </c>
+      <c r="U435" s="1" t="n">
+        <v>0.12654</v>
+      </c>
+      <c r="V435" s="2" t="n">
+        <v>0.0003162055335969348</v>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -28389,6 +31005,12 @@
       <c r="T436" s="2" t="n">
         <v>0.0003860010293361071</v>
       </c>
+      <c r="U436" s="1" t="n">
+        <v>0.07771</v>
+      </c>
+      <c r="V436" s="3" t="n">
+        <v>-0.0005144694533761848</v>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
@@ -28453,6 +31075,12 @@
       <c r="T437" s="3" t="n">
         <v>-0.004588607594936731</v>
       </c>
+      <c r="U437" s="1" t="n">
+        <v>0.6297</v>
+      </c>
+      <c r="V437" s="2" t="n">
+        <v>0.0009537434430139007</v>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -28517,6 +31145,12 @@
       <c r="T438" s="2" t="n">
         <v>0.004357798165137676</v>
       </c>
+      <c r="U438" s="1" t="n">
+        <v>0.04374</v>
+      </c>
+      <c r="V438" s="3" t="n">
+        <v>-0.001141813199360617</v>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
@@ -28581,6 +31215,12 @@
       <c r="T439" s="3" t="n">
         <v>-0.0002842928216061442</v>
       </c>
+      <c r="U439" s="1" t="n">
+        <v>0.07005</v>
+      </c>
+      <c r="V439" s="3" t="n">
+        <v>-0.003981231337978139</v>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
@@ -28645,6 +31285,12 @@
       <c r="T440" s="3" t="n">
         <v>-0.000660501981505889</v>
       </c>
+      <c r="U440" s="1" t="n">
+        <v>0.001514</v>
+      </c>
+      <c r="V440" s="2" t="n">
+        <v>0.0006609385327164017</v>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -28709,6 +31355,12 @@
       <c r="T441" s="2" t="n">
         <v>0.001906981671787335</v>
       </c>
+      <c r="U441" s="1" t="n">
+        <v>0.009469999999999999</v>
+      </c>
+      <c r="V441" s="2" t="n">
+        <v>0.001374643121497211</v>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
@@ -28773,6 +31425,12 @@
       <c r="T442" s="2" t="n">
         <v>0.0009416195856872785</v>
       </c>
+      <c r="U442" s="1" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="V442" s="3" t="n">
+        <v>-0.00282220131702718</v>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
@@ -28837,6 +31495,12 @@
       <c r="T443" s="2" t="n">
         <v>0.003651300775901425</v>
       </c>
+      <c r="U443" s="1" t="n">
+        <v>0.02194</v>
+      </c>
+      <c r="V443" s="3" t="n">
+        <v>-0.002273760800363709</v>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
@@ -28901,6 +31565,12 @@
       <c r="T444" s="2" t="n">
         <v>0.006083046813012435</v>
       </c>
+      <c r="U444" s="1" t="n">
+        <v>0.0003809</v>
+      </c>
+      <c r="V444" s="2" t="n">
+        <v>0.001314405888538413</v>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
@@ -28965,6 +31635,12 @@
       <c r="T445" s="2" t="n">
         <v>0.002265005662514261</v>
       </c>
+      <c r="U445" s="1" t="n">
+        <v>0.03548</v>
+      </c>
+      <c r="V445" s="2" t="n">
+        <v>0.002259887005649625</v>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
@@ -29029,6 +31705,12 @@
       <c r="T446" s="2" t="n">
         <v>0.00719254804857917</v>
       </c>
+      <c r="U446" s="1" t="n">
+        <v>0.08547</v>
+      </c>
+      <c r="V446" s="2" t="n">
+        <v>0.0005853430110045467</v>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
@@ -29093,6 +31775,12 @@
       <c r="T447" s="2" t="n">
         <v>0.001523461304082844</v>
       </c>
+      <c r="U447" s="1" t="n">
+        <v>3.284</v>
+      </c>
+      <c r="V447" s="3" t="n">
+        <v>-0.0009126863401278107</v>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
@@ -29157,6 +31845,12 @@
       <c r="T448" s="2" t="n">
         <v>0.0009398496240602209</v>
       </c>
+      <c r="U448" s="1" t="n">
+        <v>0.06395000000000001</v>
+      </c>
+      <c r="V448" s="2" t="n">
+        <v>0.0007824726134586599</v>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
@@ -29221,6 +31915,12 @@
       <c r="T449" s="2" t="n">
         <v>0.000205423171733749</v>
       </c>
+      <c r="U449" s="1" t="n">
+        <v>0.4865</v>
+      </c>
+      <c r="V449" s="3" t="n">
+        <v>-0.000821523926884394</v>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
@@ -29285,6 +31985,12 @@
       <c r="T450" s="2" t="n">
         <v>0.001073249262141275</v>
       </c>
+      <c r="U450" s="1" t="n">
+        <v>0.03754</v>
+      </c>
+      <c r="V450" s="2" t="n">
+        <v>0.006164567140176738</v>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -29349,6 +32055,12 @@
       <c r="T451" s="2" t="n">
         <v>0.003663003663003673</v>
       </c>
+      <c r="U451" s="1" t="n">
+        <v>0.00548</v>
+      </c>
+      <c r="V451" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
@@ -29413,6 +32125,12 @@
       <c r="T452" s="3" t="n">
         <v>-0.007411685436519328</v>
       </c>
+      <c r="U452" s="1" t="n">
+        <v>0.10335</v>
+      </c>
+      <c r="V452" s="2" t="n">
+        <v>0.00223041117145068</v>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
@@ -29477,6 +32195,12 @@
       <c r="T453" s="2" t="n">
         <v>0.003121098626716694</v>
       </c>
+      <c r="U453" s="1" t="n">
+        <v>0.01609</v>
+      </c>
+      <c r="V453" s="2" t="n">
+        <v>0.001244555071561866</v>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
@@ -29541,6 +32265,12 @@
       <c r="T454" s="2" t="n">
         <v>0.006990562740300445</v>
       </c>
+      <c r="U454" s="1" t="n">
+        <v>2.893</v>
+      </c>
+      <c r="V454" s="2" t="n">
+        <v>0.004165220409580011</v>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
@@ -29605,6 +32335,12 @@
       <c r="T455" s="3" t="n">
         <v>-0.001117318435754191</v>
       </c>
+      <c r="U455" s="1" t="n">
+        <v>0.895</v>
+      </c>
+      <c r="V455" s="2" t="n">
+        <v>0.001118568232662193</v>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
@@ -29669,6 +32405,12 @@
       <c r="T456" s="3" t="n">
         <v>-0.003389830508474654</v>
       </c>
+      <c r="U456" s="1" t="n">
+        <v>2.946</v>
+      </c>
+      <c r="V456" s="2" t="n">
+        <v>0.00204081632653069</v>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -29733,6 +32475,12 @@
       <c r="T457" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="U457" s="1" t="n">
+        <v>0.009849999999999999</v>
+      </c>
+      <c r="V457" s="3" t="n">
+        <v>-0.001014198782961595</v>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
@@ -29797,6 +32545,12 @@
       <c r="T458" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="U458" s="1" t="n">
+        <v>0.06209</v>
+      </c>
+      <c r="V458" s="2" t="n">
+        <v>0.001613163413453717</v>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
@@ -29861,6 +32615,12 @@
       <c r="T459" s="2" t="n">
         <v>0.0014005602240897</v>
       </c>
+      <c r="U459" s="1" t="n">
+        <v>0.01429</v>
+      </c>
+      <c r="V459" s="3" t="n">
+        <v>-0.0006993006993006708</v>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
@@ -29925,6 +32685,12 @@
       <c r="T460" s="2" t="n">
         <v>0.0006877149109096964</v>
       </c>
+      <c r="U460" s="1" t="n">
+        <v>0.016002</v>
+      </c>
+      <c r="V460" s="3" t="n">
+        <v>-0.0002499062851431045</v>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
@@ -29989,6 +32755,12 @@
       <c r="T461" s="2" t="n">
         <v>0.006650544135429411</v>
       </c>
+      <c r="U461" s="1" t="n">
+        <v>0.01666</v>
+      </c>
+      <c r="V461" s="2" t="n">
+        <v>0.0006006006006005761</v>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
@@ -30053,6 +32825,12 @@
       <c r="T462" s="3" t="n">
         <v>-0.001902044698050322</v>
       </c>
+      <c r="U462" s="1" t="n">
+        <v>0.0002094</v>
+      </c>
+      <c r="V462" s="3" t="n">
+        <v>-0.002382086707956227</v>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
@@ -30117,6 +32895,12 @@
       <c r="T463" s="3" t="n">
         <v>-0.001010101010101039</v>
       </c>
+      <c r="U463" s="1" t="n">
+        <v>0.0989</v>
+      </c>
+      <c r="V463" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
@@ -30181,6 +32965,12 @@
       <c r="T464" s="2" t="n">
         <v>0.002678913126674344</v>
       </c>
+      <c r="U464" s="1" t="n">
+        <v>0.02618</v>
+      </c>
+      <c r="V464" s="3" t="n">
+        <v>-0.0007633587786260555</v>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
@@ -30245,6 +33035,12 @@
       <c r="T465" s="3" t="n">
         <v>-0.008502289077828641</v>
       </c>
+      <c r="U465" s="1" t="n">
+        <v>0.01508</v>
+      </c>
+      <c r="V465" s="3" t="n">
+        <v>-0.00527704485488128</v>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
@@ -30309,6 +33105,12 @@
       <c r="T466" s="2" t="n">
         <v>0.001464933162424532</v>
       </c>
+      <c r="U466" s="1" t="n">
+        <v>0.05478</v>
+      </c>
+      <c r="V466" s="2" t="n">
+        <v>0.001645639056500271</v>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
@@ -30373,6 +33175,12 @@
       <c r="T467" s="2" t="n">
         <v>0.004954823666569412</v>
       </c>
+      <c r="U467" s="1" t="n">
+        <v>0.03437</v>
+      </c>
+      <c r="V467" s="3" t="n">
+        <v>-0.003190255220417604</v>
+      </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
@@ -30437,6 +33245,12 @@
       <c r="T468" s="2" t="n">
         <v>0.00182615047479915</v>
       </c>
+      <c r="U468" s="1" t="n">
+        <v>27.49</v>
+      </c>
+      <c r="V468" s="2" t="n">
+        <v>0.002187386073641951</v>
+      </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
@@ -30501,6 +33315,12 @@
       <c r="T469" s="3" t="n">
         <v>-0.0009357037829168175</v>
       </c>
+      <c r="U469" s="1" t="n">
+        <v>0.0007474</v>
+      </c>
+      <c r="V469" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
@@ -30565,6 +33385,12 @@
       <c r="T470" s="2" t="n">
         <v>0.01601830663615562</v>
       </c>
+      <c r="U470" s="1" t="n">
+        <v>0.888</v>
+      </c>
+      <c r="V470" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
@@ -30629,6 +33455,12 @@
       <c r="T471" s="3" t="n">
         <v>-0.002020202020202113</v>
       </c>
+      <c r="U471" s="1" t="n">
+        <v>0.00988</v>
+      </c>
+      <c r="V471" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
@@ -30693,6 +33525,12 @@
       <c r="T472" s="2" t="n">
         <v>0.001506672406371085</v>
       </c>
+      <c r="U472" s="1" t="n">
+        <v>0.04649</v>
+      </c>
+      <c r="V472" s="3" t="n">
+        <v>-0.0008596604341286333</v>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -30757,6 +33595,12 @@
       <c r="T473" s="2" t="n">
         <v>0.0003649635036495948</v>
       </c>
+      <c r="U473" s="1" t="n">
+        <v>0.2738</v>
+      </c>
+      <c r="V473" s="3" t="n">
+        <v>-0.001094491061656412</v>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
@@ -30821,6 +33665,12 @@
       <c r="T474" s="2" t="n">
         <v>0.003656307129798913</v>
       </c>
+      <c r="U474" s="1" t="n">
+        <v>0.04383</v>
+      </c>
+      <c r="V474" s="3" t="n">
+        <v>-0.002049180327868848</v>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
@@ -30885,6 +33735,12 @@
       <c r="T475" s="2" t="n">
         <v>0.001418775124142806</v>
       </c>
+      <c r="U475" s="1" t="n">
+        <v>0.008455000000000001</v>
+      </c>
+      <c r="V475" s="3" t="n">
+        <v>-0.00177095631641079</v>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
@@ -30949,6 +33805,12 @@
       <c r="T476" s="2" t="n">
         <v>0.0009778755653344412</v>
       </c>
+      <c r="U476" s="1" t="n">
+        <v>0.08169999999999999</v>
+      </c>
+      <c r="V476" s="3" t="n">
+        <v>-0.002320185614849305</v>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
@@ -31013,6 +33875,12 @@
       <c r="T477" s="2" t="n">
         <v>0.002209131075110417</v>
       </c>
+      <c r="U477" s="1" t="n">
+        <v>0.1361</v>
+      </c>
+      <c r="V477" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
@@ -31077,6 +33945,12 @@
       <c r="T478" s="2" t="n">
         <v>0.0002520796571716385</v>
       </c>
+      <c r="U478" s="1" t="n">
+        <v>0.3967</v>
+      </c>
+      <c r="V478" s="3" t="n">
+        <v>-0.0002520161290322303</v>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
@@ -31141,6 +34015,12 @@
       <c r="T479" s="2" t="n">
         <v>0.01977633902295465</v>
       </c>
+      <c r="U479" s="1" t="n">
+        <v>0.008624</v>
+      </c>
+      <c r="V479" s="3" t="n">
+        <v>-0.004501904651968237</v>
+      </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
@@ -31205,6 +34085,12 @@
       <c r="T480" s="2" t="n">
         <v>0.01703470031545738</v>
       </c>
+      <c r="U480" s="1" t="n">
+        <v>0.01602</v>
+      </c>
+      <c r="V480" s="3" t="n">
+        <v>-0.006203473945409392</v>
+      </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
@@ -31269,6 +34155,12 @@
       <c r="T481" s="2" t="n">
         <v>0.01001540832049293</v>
       </c>
+      <c r="U481" s="1" t="n">
+        <v>0.07835</v>
+      </c>
+      <c r="V481" s="3" t="n">
+        <v>-0.003941011950165152</v>
+      </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
@@ -31333,6 +34225,12 @@
       <c r="T482" s="2" t="n">
         <v>0.001988862370724003</v>
       </c>
+      <c r="U482" s="1" t="n">
+        <v>0.05035</v>
+      </c>
+      <c r="V482" s="3" t="n">
+        <v>-0.0005954743946010768</v>
+      </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
@@ -31397,6 +34295,12 @@
       <c r="T483" s="2" t="n">
         <v>0.002061855670103009</v>
       </c>
+      <c r="U483" s="1" t="n">
+        <v>0.0097</v>
+      </c>
+      <c r="V483" s="3" t="n">
+        <v>-0.002057613168724196</v>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
@@ -31461,6 +34365,12 @@
       <c r="T484" s="2" t="n">
         <v>0.00250441956393641</v>
       </c>
+      <c r="U484" s="1" t="n">
+        <v>0.06807000000000001</v>
+      </c>
+      <c r="V484" s="2" t="n">
+        <v>0.0002939015429831906</v>
+      </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
@@ -31525,6 +34435,12 @@
       <c r="T485" s="2" t="n">
         <v>0.001784519295114922</v>
       </c>
+      <c r="U485" s="1" t="n">
+        <v>0.0004506</v>
+      </c>
+      <c r="V485" s="2" t="n">
+        <v>0.0033400133600534</v>
+      </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
@@ -31589,6 +34505,12 @@
       <c r="T486" s="2" t="n">
         <v>0.005948614099481056</v>
       </c>
+      <c r="U486" s="1" t="n">
+        <v>0.07922</v>
+      </c>
+      <c r="V486" s="3" t="n">
+        <v>-0.003271263210870613</v>
+      </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
@@ -31653,6 +34575,12 @@
       <c r="T487" s="2" t="n">
         <v>0.001736111111111153</v>
       </c>
+      <c r="U487" s="1" t="n">
+        <v>0.0001735</v>
+      </c>
+      <c r="V487" s="2" t="n">
+        <v>0.002310803004043805</v>
+      </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
@@ -31717,6 +34645,12 @@
       <c r="T488" s="2" t="n">
         <v>0.02345707128216814</v>
       </c>
+      <c r="U488" s="1" t="n">
+        <v>0.09014</v>
+      </c>
+      <c r="V488" s="2" t="n">
+        <v>0.002892745883400048</v>
+      </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
@@ -31781,6 +34715,12 @@
       <c r="T489" s="2" t="n">
         <v>0.003574432296047172</v>
       </c>
+      <c r="U489" s="1" t="n">
+        <v>0.04782</v>
+      </c>
+      <c r="V489" s="2" t="n">
+        <v>0.001885606536769323</v>
+      </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
@@ -31845,6 +34785,12 @@
       <c r="T490" s="3" t="n">
         <v>-0.001540041067761922</v>
       </c>
+      <c r="U490" s="1" t="n">
+        <v>0.03864</v>
+      </c>
+      <c r="V490" s="3" t="n">
+        <v>-0.006683804627249264</v>
+      </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
@@ -31909,6 +34855,12 @@
       <c r="T491" s="2" t="n">
         <v>0.002689549180327893</v>
       </c>
+      <c r="U491" s="1" t="n">
+        <v>0.07915999999999999</v>
+      </c>
+      <c r="V491" s="2" t="n">
+        <v>0.01111253033593046</v>
+      </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
@@ -31973,6 +34925,12 @@
       <c r="T492" s="2" t="n">
         <v>0.00714172353594677</v>
       </c>
+      <c r="U492" s="1" t="n">
+        <v>0.06344</v>
+      </c>
+      <c r="V492" s="3" t="n">
+        <v>-0.0003151591553735601</v>
+      </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
@@ -32037,6 +34995,12 @@
       <c r="T493" s="3" t="n">
         <v>-0.001897533206831207</v>
       </c>
+      <c r="U493" s="1" t="n">
+        <v>0.00522</v>
+      </c>
+      <c r="V493" s="3" t="n">
+        <v>-0.007604562737642605</v>
+      </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
@@ -32101,6 +35065,12 @@
       <c r="T494" s="2" t="n">
         <v>0.002912267928649519</v>
       </c>
+      <c r="U494" s="1" t="n">
+        <v>0.2757</v>
+      </c>
+      <c r="V494" s="2" t="n">
+        <v>0.0007259528130670706</v>
+      </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
@@ -32165,6 +35135,12 @@
       <c r="T495" s="2" t="n">
         <v>0.002358490566037694</v>
       </c>
+      <c r="U495" s="1" t="n">
+        <v>0.06372</v>
+      </c>
+      <c r="V495" s="3" t="n">
+        <v>-0.0004705882352941529</v>
+      </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
@@ -32229,6 +35205,12 @@
       <c r="T496" s="2" t="n">
         <v>0.005142269454919442</v>
       </c>
+      <c r="U496" s="1" t="n">
+        <v>0.293</v>
+      </c>
+      <c r="V496" s="3" t="n">
+        <v>-0.0006821282401092547</v>
+      </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
@@ -32293,6 +35275,12 @@
       <c r="T497" s="3" t="n">
         <v>-0.007493966721707016</v>
       </c>
+      <c r="U497" s="1" t="n">
+        <v>0.07994</v>
+      </c>
+      <c r="V497" s="2" t="n">
+        <v>0.02303557716918347</v>
+      </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
@@ -32357,6 +35345,12 @@
       <c r="T498" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="U498" s="1" t="n">
+        <v>0.1033</v>
+      </c>
+      <c r="V498" s="2" t="n">
+        <v>0.0009689922480620432</v>
+      </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
@@ -32421,6 +35415,12 @@
       <c r="T499" s="2" t="n">
         <v>0.003371057067180381</v>
       </c>
+      <c r="U499" s="1" t="n">
+        <v>0.04175</v>
+      </c>
+      <c r="V499" s="2" t="n">
+        <v>0.001919846412287105</v>
+      </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
@@ -32485,6 +35485,12 @@
       <c r="T500" s="3" t="n">
         <v>-0.006461232604373667</v>
       </c>
+      <c r="U500" s="1" t="n">
+        <v>0.03986</v>
+      </c>
+      <c r="V500" s="3" t="n">
+        <v>-0.003001500750375239</v>
+      </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
@@ -32549,6 +35555,12 @@
       <c r="T501" s="3" t="n">
         <v>-0.001011122345803871</v>
       </c>
+      <c r="U501" s="1" t="n">
+        <v>0.0987</v>
+      </c>
+      <c r="V501" s="3" t="n">
+        <v>-0.001012145748987883</v>
+      </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
@@ -32613,6 +35625,12 @@
       <c r="T502" s="2" t="n">
         <v>0.001211020284589796</v>
       </c>
+      <c r="U502" s="1" t="n">
+        <v>0.003311</v>
+      </c>
+      <c r="V502" s="2" t="n">
+        <v>0.001209555488358058</v>
+      </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
@@ -32677,6 +35695,12 @@
       <c r="T503" s="3" t="n">
         <v>-0.0140237324703344</v>
       </c>
+      <c r="U503" s="1" t="n">
+        <v>0.009129999999999999</v>
+      </c>
+      <c r="V503" s="3" t="n">
+        <v>-0.001094091903720058</v>
+      </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
@@ -32741,6 +35765,12 @@
       <c r="T504" s="2" t="n">
         <v>0.0006281407035175188</v>
       </c>
+      <c r="U504" s="1" t="n">
+        <v>0.1592</v>
+      </c>
+      <c r="V504" s="3" t="n">
+        <v>-0.0006277463904581857</v>
+      </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
@@ -32805,6 +35835,12 @@
       <c r="T505" s="2" t="n">
         <v>0.0007633587786258701</v>
       </c>
+      <c r="U505" s="1" t="n">
+        <v>0.1311</v>
+      </c>
+      <c r="V505" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
@@ -32869,6 +35905,12 @@
       <c r="T506" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="U506" s="1" t="n">
+        <v>0.01689</v>
+      </c>
+      <c r="V506" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
@@ -32933,6 +35975,12 @@
       <c r="T507" s="3" t="n">
         <v>-0.001386481802426377</v>
       </c>
+      <c r="U507" s="1" t="n">
+        <v>0.002868</v>
+      </c>
+      <c r="V507" s="3" t="n">
+        <v>-0.004512322110378338</v>
+      </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
@@ -32997,6 +36045,12 @@
       <c r="T508" s="2" t="n">
         <v>0.001805869074492101</v>
       </c>
+      <c r="U508" s="1" t="n">
+        <v>2.203</v>
+      </c>
+      <c r="V508" s="3" t="n">
+        <v>-0.007210455159981981</v>
+      </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
@@ -33061,6 +36115,12 @@
       <c r="T509" s="2" t="n">
         <v>0.004024881083058872</v>
       </c>
+      <c r="U509" s="1" t="n">
+        <v>0.05488</v>
+      </c>
+      <c r="V509" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
@@ -33125,6 +36185,12 @@
       <c r="T510" s="2" t="n">
         <v>0.002388263391334037</v>
       </c>
+      <c r="U510" s="1" t="n">
+        <v>0.0294</v>
+      </c>
+      <c r="V510" s="2" t="n">
+        <v>0.0006807351940095026</v>
+      </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
@@ -33189,6 +36255,12 @@
       <c r="T511" s="2" t="n">
         <v>0.0002477086945750836</v>
       </c>
+      <c r="U511" s="1" t="n">
+        <v>0.04038</v>
+      </c>
+      <c r="V511" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
@@ -33253,6 +36325,12 @@
       <c r="T512" s="2" t="n">
         <v>0.04705882352941164</v>
       </c>
+      <c r="U512" s="1" t="n">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="V512" s="3" t="n">
+        <v>-0.01123595505617979</v>
+      </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
@@ -33317,6 +36395,12 @@
       <c r="T513" s="3" t="n">
         <v>-0.02085620197585073</v>
       </c>
+      <c r="U513" s="1" t="n">
+        <v>0.015061</v>
+      </c>
+      <c r="V513" s="3" t="n">
+        <v>-0.006792403059878703</v>
+      </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
@@ -33381,6 +36465,12 @@
       <c r="T514" s="3" t="n">
         <v>-0.0005753739930956084</v>
       </c>
+      <c r="U514" s="1" t="n">
+        <v>0.174</v>
+      </c>
+      <c r="V514" s="2" t="n">
+        <v>0.001727115716752992</v>
+      </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
@@ -33445,6 +36535,12 @@
       <c r="T515" s="2" t="n">
         <v>0.0009293680297398036</v>
       </c>
+      <c r="U515" s="1" t="n">
+        <v>0.1076</v>
+      </c>
+      <c r="V515" s="3" t="n">
+        <v>-0.0009285051067781138</v>
+      </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
@@ -33509,6 +36605,12 @@
       <c r="T516" s="2" t="n">
         <v>0.003759398496240611</v>
       </c>
+      <c r="U516" s="1" t="n">
+        <v>0.00266</v>
+      </c>
+      <c r="V516" s="3" t="n">
+        <v>-0.003745318352059935</v>
+      </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
@@ -33573,6 +36675,12 @@
       <c r="T517" s="2" t="n">
         <v>0.0007781091946569744</v>
       </c>
+      <c r="U517" s="1" t="n">
+        <v>0.007715</v>
+      </c>
+      <c r="V517" s="3" t="n">
+        <v>-0.0002591680704937496</v>
+      </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
@@ -33637,6 +36745,12 @@
       <c r="T518" s="2" t="n">
         <v>0.007115135834411431</v>
       </c>
+      <c r="U518" s="1" t="n">
+        <v>0.01573</v>
+      </c>
+      <c r="V518" s="2" t="n">
+        <v>0.01027617212588314</v>
+      </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
@@ -33701,6 +36815,12 @@
       <c r="T519" s="3" t="n">
         <v>-0.0004773269689738103</v>
       </c>
+      <c r="U519" s="1" t="n">
+        <v>0.004203</v>
+      </c>
+      <c r="V519" s="2" t="n">
+        <v>0.00358166189111754</v>
+      </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
@@ -33765,6 +36885,12 @@
       <c r="T520" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="U520" s="1" t="n">
+        <v>0.001159</v>
+      </c>
+      <c r="V520" s="2" t="n">
+        <v>0.0008635578583766259</v>
+      </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
@@ -33829,6 +36955,12 @@
       <c r="T521" s="3" t="n">
         <v>-0.005231689088191247</v>
       </c>
+      <c r="U521" s="1" t="n">
+        <v>0.01333</v>
+      </c>
+      <c r="V521" s="2" t="n">
+        <v>0.001502629601803094</v>
+      </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
@@ -33893,6 +37025,12 @@
       <c r="T522" s="3" t="n">
         <v>-0.003198604245420151</v>
       </c>
+      <c r="U522" s="1" t="n">
+        <v>0.6860000000000001</v>
+      </c>
+      <c r="V522" s="2" t="n">
+        <v>0.000583430571762058</v>
+      </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
@@ -33957,6 +37095,12 @@
       <c r="T523" s="3" t="n">
         <v>-0.002274989335987592</v>
       </c>
+      <c r="U523" s="1" t="n">
+        <v>0.06992</v>
+      </c>
+      <c r="V523" s="3" t="n">
+        <v>-0.003562776115148927</v>
+      </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
@@ -34021,6 +37165,12 @@
       <c r="T524" s="2" t="n">
         <v>0.008643042350907466</v>
       </c>
+      <c r="U524" s="1" t="n">
+        <v>0.01169</v>
+      </c>
+      <c r="V524" s="2" t="n">
+        <v>0.001713796058269145</v>
+      </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
@@ -34085,6 +37235,12 @@
       <c r="T525" s="2" t="n">
         <v>0.001218026796589475</v>
       </c>
+      <c r="U525" s="1" t="n">
+        <v>0.01641</v>
+      </c>
+      <c r="V525" s="3" t="n">
+        <v>-0.001824817518248101</v>
+      </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
@@ -34149,6 +37305,12 @@
       <c r="T526" s="2" t="n">
         <v>0.003873370577281137</v>
       </c>
+      <c r="U526" s="1" t="n">
+        <v>0.1347</v>
+      </c>
+      <c r="V526" s="3" t="n">
+        <v>-0.0005194034280627328</v>
+      </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
@@ -34213,6 +37375,12 @@
       <c r="T527" s="2" t="n">
         <v>0.0006976744186047034</v>
       </c>
+      <c r="U527" s="1" t="n">
+        <v>0.04296</v>
+      </c>
+      <c r="V527" s="3" t="n">
+        <v>-0.001626772019521279</v>
+      </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
@@ -34277,6 +37445,12 @@
       <c r="T528" s="3" t="n">
         <v>-0.001100917431192743</v>
       </c>
+      <c r="U528" s="1" t="n">
+        <v>0.2732</v>
+      </c>
+      <c r="V528" s="2" t="n">
+        <v>0.003673769287288762</v>
+      </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
@@ -34341,6 +37515,12 @@
       <c r="T529" s="3" t="n">
         <v>-0.001516822945394336</v>
       </c>
+      <c r="U529" s="1" t="n">
+        <v>0.0007226999999999999</v>
+      </c>
+      <c r="V529" s="3" t="n">
+        <v>-0.001933434608479539</v>
+      </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
@@ -34405,6 +37585,12 @@
       <c r="T530" s="2" t="n">
         <v>0.006764919062575351</v>
       </c>
+      <c r="U530" s="1" t="n">
+        <v>0.004173</v>
+      </c>
+      <c r="V530" s="2" t="n">
+        <v>0.001439884809215246</v>
+      </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
@@ -34469,6 +37655,12 @@
       <c r="T531" s="3" t="n">
         <v>-0.0007616146230006777</v>
       </c>
+      <c r="U531" s="1" t="n">
+        <v>1.318</v>
+      </c>
+      <c r="V531" s="2" t="n">
+        <v>0.004573170731707321</v>
+      </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
@@ -34533,6 +37725,12 @@
       <c r="T532" s="2" t="n">
         <v>0.0008481764206954112</v>
       </c>
+      <c r="U532" s="1" t="n">
+        <v>0.1179</v>
+      </c>
+      <c r="V532" s="3" t="n">
+        <v>-0.0008474576271185508</v>
+      </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
@@ -34597,6 +37795,12 @@
       <c r="T533" s="2" t="n">
         <v>0.004311152764761032</v>
       </c>
+      <c r="U533" s="1" t="n">
+        <v>0.05356</v>
+      </c>
+      <c r="V533" s="3" t="n">
+        <v>-0.0003732736095557892</v>
+      </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
@@ -34661,6 +37865,12 @@
       <c r="T534" s="2" t="n">
         <v>0.002004008016032029</v>
       </c>
+      <c r="U534" s="1" t="n">
+        <v>0.1502</v>
+      </c>
+      <c r="V534" s="2" t="n">
+        <v>0.001333333333333372</v>
+      </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
@@ -34725,6 +37935,12 @@
       <c r="T535" s="2" t="n">
         <v>0.0005865102639295949</v>
       </c>
+      <c r="U535" s="1" t="n">
+        <v>0.01707</v>
+      </c>
+      <c r="V535" s="2" t="n">
+        <v>0.000586166471277819</v>
+      </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
@@ -34789,6 +38005,12 @@
       <c r="T536" s="2" t="n">
         <v>0.004812512532584664</v>
       </c>
+      <c r="U536" s="1" t="n">
+        <v>0.005018</v>
+      </c>
+      <c r="V536" s="2" t="n">
+        <v>0.001396926761125536</v>
+      </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
@@ -34853,6 +38075,12 @@
       <c r="T537" s="2" t="n">
         <v>0.0003423485107839403</v>
       </c>
+      <c r="U537" s="1" t="n">
+        <v>0.2917</v>
+      </c>
+      <c r="V537" s="3" t="n">
+        <v>-0.001711156741957565</v>
+      </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
@@ -34917,6 +38145,12 @@
       <c r="T538" s="3" t="n">
         <v>-0.002253944402704772</v>
       </c>
+      <c r="U538" s="1" t="n">
+        <v>0.01328</v>
+      </c>
+      <c r="V538" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
@@ -34981,6 +38215,12 @@
       <c r="T539" s="2" t="n">
         <v>0.01777059773828754</v>
       </c>
+      <c r="U539" s="1" t="n">
+        <v>0.02523</v>
+      </c>
+      <c r="V539" s="2" t="n">
+        <v>0.001190476190476142</v>
+      </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
@@ -35045,6 +38285,12 @@
       <c r="T540" s="2" t="n">
         <v>0.0003519267992257467</v>
       </c>
+      <c r="U540" s="1" t="n">
+        <v>0.0569</v>
+      </c>
+      <c r="V540" s="2" t="n">
+        <v>0.0008795074758135696</v>
+      </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
@@ -35109,6 +38355,12 @@
       <c r="T541" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="U541" s="1" t="n">
+        <v>0.0116</v>
+      </c>
+      <c r="V541" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
@@ -35173,6 +38425,12 @@
       <c r="T542" s="3" t="n">
         <v>-0.008928571428571343</v>
       </c>
+      <c r="U542" s="1" t="n">
+        <v>1.12e-05</v>
+      </c>
+      <c r="V542" s="2" t="n">
+        <v>0.009009009009008922</v>
+      </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
@@ -35236,6 +38494,12 @@
       </c>
       <c r="T543" s="2" t="n">
         <v>0.005720512122037643</v>
+      </c>
+      <c r="U543" s="1" t="n">
+        <v>0.003674</v>
+      </c>
+      <c r="V543" s="3" t="n">
+        <v>-0.004875406283856931</v>
       </c>
     </row>
   </sheetData>

--- a/binance-usdt-perpetual-data/weeks/2026-03-09_2026-03-15/2026-03-12.xlsx
+++ b/binance-usdt-perpetual-data/weeks/2026-03-09_2026-03-15/2026-03-12.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V543"/>
+  <dimension ref="A1:X543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -448,6 +448,8 @@
     <col width="18" customWidth="1" min="20" max="20"/>
     <col width="13" customWidth="1" min="21" max="21"/>
     <col width="18" customWidth="1" min="22" max="22"/>
+    <col width="13" customWidth="1" min="23" max="23"/>
+    <col width="18" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -561,6 +563,16 @@
           <t>change_02:30</t>
         </is>
       </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>price_02:45</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>change_02:45</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -631,6 +643,12 @@
       <c r="V2" s="3" t="n">
         <v>-0.0005642989681389473</v>
       </c>
+      <c r="W2" s="1" t="n">
+        <v>70472.60000000001</v>
+      </c>
+      <c r="X2" s="3" t="n">
+        <v>-0.002755163986737814</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -701,6 +719,12 @@
       <c r="V3" s="2" t="n">
         <v>0.002336267775950434</v>
       </c>
+      <c r="W3" s="1" t="n">
+        <v>2068.59</v>
+      </c>
+      <c r="X3" s="3" t="n">
+        <v>-0.001756561771617954</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -771,6 +795,12 @@
       <c r="V4" s="3" t="n">
         <v>-0.00205081462914427</v>
       </c>
+      <c r="W4" s="1" t="n">
+        <v>87.28</v>
+      </c>
+      <c r="X4" s="3" t="n">
+        <v>-0.003539216805571438</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -841,6 +871,12 @@
       <c r="V5" s="2" t="n">
         <v>0.01192799826501845</v>
       </c>
+      <c r="W5" s="1" t="n">
+        <v>0.014157</v>
+      </c>
+      <c r="X5" s="2" t="n">
+        <v>0.01135876553793395</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -911,6 +947,12 @@
       <c r="V6" s="2" t="n">
         <v>0.00202256759633819</v>
       </c>
+      <c r="W6" s="1" t="n">
+        <v>0.09396</v>
+      </c>
+      <c r="X6" s="3" t="n">
+        <v>-0.001806012960798932</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -981,6 +1023,12 @@
       <c r="V7" s="2" t="n">
         <v>0.0005001786352268117</v>
       </c>
+      <c r="W7" s="1" t="n">
+        <v>1.3991</v>
+      </c>
+      <c r="X7" s="3" t="n">
+        <v>-0.0007856020568489351</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1051,6 +1099,12 @@
       <c r="V8" s="3" t="n">
         <v>-0.001744669066740581</v>
       </c>
+      <c r="W8" s="1" t="n">
+        <v>36.136</v>
+      </c>
+      <c r="X8" s="2" t="n">
+        <v>0.002468998807113096</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1121,6 +1175,12 @@
       <c r="V9" s="3" t="n">
         <v>-0.0004135902699060928</v>
       </c>
+      <c r="W9" s="1" t="n">
+        <v>651.3</v>
+      </c>
+      <c r="X9" s="3" t="n">
+        <v>-0.001915562025898399</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1191,6 +1251,12 @@
       <c r="V10" s="3" t="n">
         <v>-0.00615772164299216</v>
       </c>
+      <c r="W10" s="1" t="n">
+        <v>14.434</v>
+      </c>
+      <c r="X10" s="2" t="n">
+        <v>0.01626416954164612</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1261,6 +1327,12 @@
       <c r="V11" s="2" t="n">
         <v>0.002073515551366625</v>
       </c>
+      <c r="W11" s="1" t="n">
+        <v>211.71</v>
+      </c>
+      <c r="X11" s="3" t="n">
+        <v>-0.004373589164785452</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1331,6 +1403,12 @@
       <c r="V12" s="3" t="n">
         <v>-0.0002669039145907056</v>
       </c>
+      <c r="W12" s="1" t="n">
+        <v>0.003371</v>
+      </c>
+      <c r="X12" s="3" t="n">
+        <v>-2.966390792331093e-05</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1401,6 +1479,12 @@
       <c r="V13" s="3" t="n">
         <v>-0.0002707825616029278</v>
       </c>
+      <c r="W13" s="1" t="n">
+        <v>0.03803</v>
+      </c>
+      <c r="X13" s="2" t="n">
+        <v>0.03006500541711809</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1471,6 +1555,12 @@
       <c r="V14" s="3" t="n">
         <v>-0.003834355828220947</v>
       </c>
+      <c r="W14" s="1" t="n">
+        <v>2.606</v>
+      </c>
+      <c r="X14" s="2" t="n">
+        <v>0.003079291762894537</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1541,6 +1631,12 @@
       <c r="V15" s="2" t="n">
         <v>0.0003055612140965237</v>
       </c>
+      <c r="W15" s="1" t="n">
+        <v>0.9837</v>
+      </c>
+      <c r="X15" s="2" t="n">
+        <v>0.001629161999796402</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1611,6 +1707,12 @@
       <c r="V16" s="2" t="n">
         <v>0.009405501330967217</v>
       </c>
+      <c r="W16" s="1" t="n">
+        <v>0.05686</v>
+      </c>
+      <c r="X16" s="3" t="n">
+        <v>-0.0003516174402250209</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1681,6 +1783,12 @@
       <c r="V17" s="2" t="n">
         <v>0.002265005662514158</v>
       </c>
+      <c r="W17" s="1" t="n">
+        <v>0.885</v>
+      </c>
+      <c r="X17" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1751,6 +1859,12 @@
       <c r="V18" s="2" t="n">
         <v>0.00075386355069745</v>
       </c>
+      <c r="W18" s="1" t="n">
+        <v>0.2655</v>
+      </c>
+      <c r="X18" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1821,6 +1935,12 @@
       <c r="V19" s="2" t="n">
         <v>0.01462242297892054</v>
       </c>
+      <c r="W19" s="1" t="n">
+        <v>0.35578</v>
+      </c>
+      <c r="X19" s="2" t="n">
+        <v>0.01532490511115546</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1891,6 +2011,12 @@
       <c r="V20" s="2" t="n">
         <v>0.001133669998969495</v>
       </c>
+      <c r="W20" s="1" t="n">
+        <v>9.696999999999999</v>
+      </c>
+      <c r="X20" s="3" t="n">
+        <v>-0.001750051472102248</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1961,6 +2087,12 @@
       <c r="V21" s="3" t="n">
         <v>-0.004311425276983934</v>
       </c>
+      <c r="W21" s="1" t="n">
+        <v>198.85</v>
+      </c>
+      <c r="X21" s="2" t="n">
+        <v>0.001208398368662105</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2031,6 +2163,12 @@
       <c r="V22" s="2" t="n">
         <v>0.01416896368296347</v>
       </c>
+      <c r="W22" s="1" t="n">
+        <v>0.020846</v>
+      </c>
+      <c r="X22" s="3" t="n">
+        <v>-0.00600801068090793</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2101,6 +2239,12 @@
       <c r="V23" s="3" t="n">
         <v>-0.001223802967722202</v>
       </c>
+      <c r="W23" s="1" t="n">
+        <v>456.42</v>
+      </c>
+      <c r="X23" s="3" t="n">
+        <v>-0.001334704505174621</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2171,6 +2315,12 @@
       <c r="V24" s="2" t="n">
         <v>0.001009634075343509</v>
       </c>
+      <c r="W24" s="1" t="n">
+        <v>5175.05</v>
+      </c>
+      <c r="X24" s="3" t="n">
+        <v>-6.955970638068725e-05</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2241,6 +2391,12 @@
       <c r="V25" s="3" t="n">
         <v>-0.0002200704225350893</v>
       </c>
+      <c r="W25" s="1" t="n">
+        <v>9.065</v>
+      </c>
+      <c r="X25" s="3" t="n">
+        <v>-0.002311248073960026</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2311,6 +2467,12 @@
       <c r="V26" s="2" t="n">
         <v>0.007197857381988615</v>
       </c>
+      <c r="W26" s="1" t="n">
+        <v>0.12102</v>
+      </c>
+      <c r="X26" s="2" t="n">
+        <v>0.005650656473325578</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2381,6 +2543,12 @@
       <c r="V27" s="3" t="n">
         <v>-0.01250000000000007</v>
       </c>
+      <c r="W27" s="1" t="n">
+        <v>0.01203</v>
+      </c>
+      <c r="X27" s="2" t="n">
+        <v>0.01518987341772163</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2451,6 +2619,12 @@
       <c r="V28" s="2" t="n">
         <v>0.0007722007722008586</v>
       </c>
+      <c r="W28" s="1" t="n">
+        <v>1.292</v>
+      </c>
+      <c r="X28" s="3" t="n">
+        <v>-0.003086419753086422</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2521,6 +2695,12 @@
       <c r="V29" s="3" t="n">
         <v>-0.03279452906434557</v>
       </c>
+      <c r="W29" s="1" t="n">
+        <v>0.06282</v>
+      </c>
+      <c r="X29" s="2" t="n">
+        <v>0.009480957737425683</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2591,6 +2771,12 @@
       <c r="V30" s="3" t="n">
         <v>-0.002605863192182413</v>
       </c>
+      <c r="W30" s="1" t="n">
+        <v>1.533</v>
+      </c>
+      <c r="X30" s="2" t="n">
+        <v>0.00130633572828217</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2661,6 +2847,12 @@
       <c r="V31" s="3" t="n">
         <v>-0.004426955238563646</v>
       </c>
+      <c r="W31" s="1" t="n">
+        <v>0.002009</v>
+      </c>
+      <c r="X31" s="3" t="n">
+        <v>-0.007411067193676015</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2731,6 +2923,12 @@
       <c r="V32" s="2" t="n">
         <v>0.0009891196834818327</v>
       </c>
+      <c r="W32" s="1" t="n">
+        <v>0.04017</v>
+      </c>
+      <c r="X32" s="3" t="n">
+        <v>-0.007658102766798535</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2801,6 +2999,12 @@
       <c r="V33" s="3" t="n">
         <v>-0.002026342451874284</v>
       </c>
+      <c r="W33" s="1" t="n">
+        <v>0.09810000000000001</v>
+      </c>
+      <c r="X33" s="3" t="n">
+        <v>-0.004060913705583731</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2871,6 +3075,12 @@
       <c r="V34" s="2" t="n">
         <v>0.003816793893129748</v>
       </c>
+      <c r="W34" s="1" t="n">
+        <v>0.1053</v>
+      </c>
+      <c r="X34" s="2" t="n">
+        <v>0.0009505703422053504</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2941,6 +3151,12 @@
       <c r="V35" s="2" t="n">
         <v>0.008073817762398948</v>
       </c>
+      <c r="W35" s="1" t="n">
+        <v>0.008920000000000001</v>
+      </c>
+      <c r="X35" s="2" t="n">
+        <v>0.02059496567505736</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3011,6 +3227,12 @@
       <c r="V36" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="W36" s="1" t="n">
+        <v>0.3577</v>
+      </c>
+      <c r="X36" s="3" t="n">
+        <v>-0.002509760178471713</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3081,6 +3303,12 @@
       <c r="V37" s="3" t="n">
         <v>-0.001369863013698515</v>
       </c>
+      <c r="W37" s="1" t="n">
+        <v>0.005819</v>
+      </c>
+      <c r="X37" s="3" t="n">
+        <v>-0.002229080932784635</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3151,6 +3379,12 @@
       <c r="V38" s="2" t="n">
         <v>0.0008792721156051992</v>
       </c>
+      <c r="W38" s="1" t="n">
+        <v>0.26192</v>
+      </c>
+      <c r="X38" s="2" t="n">
+        <v>0.0004201520186394675</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3221,6 +3455,12 @@
       <c r="V39" s="2" t="n">
         <v>0.005376344086021494</v>
       </c>
+      <c r="W39" s="1" t="n">
+        <v>0.05075</v>
+      </c>
+      <c r="X39" s="2" t="n">
+        <v>0.005149534561299332</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -3291,6 +3531,12 @@
       <c r="V40" s="2" t="n">
         <v>0.01141064993994406</v>
       </c>
+      <c r="W40" s="1" t="n">
+        <v>0.15024</v>
+      </c>
+      <c r="X40" s="3" t="n">
+        <v>-0.008774823513887958</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -3361,6 +3607,12 @@
       <c r="V41" s="2" t="n">
         <v>0.00235571260306233</v>
       </c>
+      <c r="W41" s="1" t="n">
+        <v>0.1702</v>
+      </c>
+      <c r="X41" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -3431,6 +3683,12 @@
       <c r="V42" s="2" t="n">
         <v>0.0006243867630006903</v>
       </c>
+      <c r="W42" s="1" t="n">
+        <v>111.98</v>
+      </c>
+      <c r="X42" s="3" t="n">
+        <v>-0.001782848992690344</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -3501,6 +3759,12 @@
       <c r="V43" s="2" t="n">
         <v>0.0936513122073396</v>
       </c>
+      <c r="W43" s="1" t="n">
+        <v>0.9272</v>
+      </c>
+      <c r="X43" s="3" t="n">
+        <v>-0.07676988947525634</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -3571,6 +3835,12 @@
       <c r="V44" s="2" t="n">
         <v>0.002183008913953148</v>
       </c>
+      <c r="W44" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="X44" s="3" t="n">
+        <v>-0.001633690324922915</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -3641,6 +3911,12 @@
       <c r="V45" s="3" t="n">
         <v>-0.001999692355022383</v>
       </c>
+      <c r="W45" s="1" t="n">
+        <v>0.517</v>
+      </c>
+      <c r="X45" s="3" t="n">
+        <v>-0.003930332922317993</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -3711,6 +3987,12 @@
       <c r="V46" s="3" t="n">
         <v>-0.0005686664771112694</v>
       </c>
+      <c r="W46" s="1" t="n">
+        <v>0.7019</v>
+      </c>
+      <c r="X46" s="3" t="n">
+        <v>-0.001564722617354182</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -3781,6 +4063,12 @@
       <c r="V47" s="2" t="n">
         <v>0.001784348712719887</v>
       </c>
+      <c r="W47" s="1" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="X47" s="3" t="n">
+        <v>-0.002544529262086573</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3851,6 +4139,12 @@
       <c r="V48" s="2" t="n">
         <v>0.0008130081300814196</v>
       </c>
+      <c r="W48" s="1" t="n">
+        <v>0.15986</v>
+      </c>
+      <c r="X48" s="3" t="n">
+        <v>-0.001062300818596535</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3921,6 +4215,12 @@
       <c r="V49" s="2" t="n">
         <v>0.009257728550173549</v>
       </c>
+      <c r="W49" s="1" t="n">
+        <v>0.06165</v>
+      </c>
+      <c r="X49" s="2" t="n">
+        <v>0.009828009828009882</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3991,6 +4291,12 @@
       <c r="V50" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="W50" s="1" t="n">
+        <v>0.0386</v>
+      </c>
+      <c r="X50" s="3" t="n">
+        <v>-0.002583979328165269</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -4061,6 +4367,12 @@
       <c r="V51" s="2" t="n">
         <v>0.009419781541236559</v>
       </c>
+      <c r="W51" s="1" t="n">
+        <v>0.30544</v>
+      </c>
+      <c r="X51" s="2" t="n">
+        <v>0.01075482312452422</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -4131,6 +4443,12 @@
       <c r="V52" s="3" t="n">
         <v>-0.003076923076922928</v>
       </c>
+      <c r="W52" s="1" t="n">
+        <v>0.2923</v>
+      </c>
+      <c r="X52" s="2" t="n">
+        <v>0.002400548696844919</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -4201,6 +4519,12 @@
       <c r="V53" s="2" t="n">
         <v>0.005056890012642194</v>
       </c>
+      <c r="W53" s="1" t="n">
+        <v>0.1588</v>
+      </c>
+      <c r="X53" s="3" t="n">
+        <v>-0.001257861635220162</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -4271,6 +4595,12 @@
       <c r="V54" s="3" t="n">
         <v>-0.001168144025286906</v>
       </c>
+      <c r="W54" s="1" t="n">
+        <v>0.28991</v>
+      </c>
+      <c r="X54" s="3" t="n">
+        <v>-0.002786186020913517</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -4341,6 +4671,12 @@
       <c r="V55" s="2" t="n">
         <v>0.0008386916410399678</v>
       </c>
+      <c r="W55" s="1" t="n">
+        <v>0.007134</v>
+      </c>
+      <c r="X55" s="3" t="n">
+        <v>-0.003631284916201115</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -4411,6 +4747,12 @@
       <c r="V56" s="2" t="n">
         <v>0.01646974579305401</v>
       </c>
+      <c r="W56" s="1" t="n">
+        <v>0.02847</v>
+      </c>
+      <c r="X56" s="2" t="n">
+        <v>0.002817893624515682</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -4481,6 +4823,12 @@
       <c r="V57" s="2" t="n">
         <v>0.001900688999762336</v>
       </c>
+      <c r="W57" s="1" t="n">
+        <v>0.04179</v>
+      </c>
+      <c r="X57" s="3" t="n">
+        <v>-0.009011145364002807</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -4551,6 +4899,12 @@
       <c r="V58" s="3" t="n">
         <v>-0.01080648389033418</v>
       </c>
+      <c r="W58" s="1" t="n">
+        <v>0.05016</v>
+      </c>
+      <c r="X58" s="2" t="n">
+        <v>0.01476835929597413</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -4621,6 +4975,12 @@
       <c r="V59" s="2" t="n">
         <v>0.007156798959011139</v>
       </c>
+      <c r="W59" s="1" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X59" s="2" t="n">
+        <v>0.001291989664082688</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -4691,6 +5051,12 @@
       <c r="V60" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="W60" s="1" t="n">
+        <v>0.00344</v>
+      </c>
+      <c r="X60" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -4761,6 +5127,12 @@
       <c r="V61" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="W61" s="1" t="n">
+        <v>0.1548</v>
+      </c>
+      <c r="X61" s="3" t="n">
+        <v>-0.003861003861003971</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -4831,6 +5203,12 @@
       <c r="V62" s="3" t="n">
         <v>-0.0008726003490400436</v>
       </c>
+      <c r="W62" s="1" t="n">
+        <v>1.145</v>
+      </c>
+      <c r="X62" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -4901,6 +5279,12 @@
       <c r="V63" s="2" t="n">
         <v>0.001714530647235289</v>
       </c>
+      <c r="W63" s="1" t="n">
+        <v>0.6994</v>
+      </c>
+      <c r="X63" s="3" t="n">
+        <v>-0.002424761089716052</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -4971,6 +5355,12 @@
       <c r="V64" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="W64" s="1" t="n">
+        <v>2.934</v>
+      </c>
+      <c r="X64" s="3" t="n">
+        <v>-0.001021450459652594</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -5041,6 +5431,12 @@
       <c r="V65" s="3" t="n">
         <v>-0.002928870292887055</v>
       </c>
+      <c r="W65" s="1" t="n">
+        <v>0.02376</v>
+      </c>
+      <c r="X65" s="3" t="n">
+        <v>-0.002937473772555628</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -5111,6 +5507,12 @@
       <c r="V66" s="2" t="n">
         <v>0.002961500493583364</v>
       </c>
+      <c r="W66" s="1" t="n">
+        <v>0.1015</v>
+      </c>
+      <c r="X66" s="3" t="n">
+        <v>-0.0009842519685038286</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -5181,6 +5583,12 @@
       <c r="V67" s="2" t="n">
         <v>0.01132951132951129</v>
       </c>
+      <c r="W67" s="1" t="n">
+        <v>0.00744</v>
+      </c>
+      <c r="X67" s="2" t="n">
+        <v>0.004184100418410129</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -5251,6 +5659,12 @@
       <c r="V68" s="2" t="n">
         <v>0.0255455029270889</v>
       </c>
+      <c r="W68" s="1" t="n">
+        <v>19.13</v>
+      </c>
+      <c r="X68" s="3" t="n">
+        <v>-0.007265179034769101</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -5321,6 +5735,12 @@
       <c r="V69" s="2" t="n">
         <v>0.0007411524921253532</v>
       </c>
+      <c r="W69" s="1" t="n">
+        <v>0.05408</v>
+      </c>
+      <c r="X69" s="2" t="n">
+        <v>0.001296056285872998</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -5391,6 +5811,12 @@
       <c r="V70" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="W70" s="1" t="n">
+        <v>0.234</v>
+      </c>
+      <c r="X70" s="3" t="n">
+        <v>-0.01680672268907553</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -5461,6 +5887,12 @@
       <c r="V71" s="3" t="n">
         <v>-0.005007770678639406</v>
       </c>
+      <c r="W71" s="1" t="n">
+        <v>5.723</v>
+      </c>
+      <c r="X71" s="3" t="n">
+        <v>-0.00676848316556746</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -5531,6 +5963,12 @@
       <c r="V72" s="2" t="n">
         <v>0.004296455424274961</v>
       </c>
+      <c r="W72" s="1" t="n">
+        <v>0.001866</v>
+      </c>
+      <c r="X72" s="3" t="n">
+        <v>-0.002139037433155017</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -5601,6 +6039,12 @@
       <c r="V73" s="2" t="n">
         <v>0.0004245833775607217</v>
       </c>
+      <c r="W73" s="1" t="n">
+        <v>0.9404</v>
+      </c>
+      <c r="X73" s="3" t="n">
+        <v>-0.002228116710875322</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -5671,6 +6115,12 @@
       <c r="V74" s="2" t="n">
         <v>0.000829875518672223</v>
       </c>
+      <c r="W74" s="1" t="n">
+        <v>0.1202</v>
+      </c>
+      <c r="X74" s="3" t="n">
+        <v>-0.003316749585406282</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -5741,6 +6191,12 @@
       <c r="V75" s="2" t="n">
         <v>0.002558562656356704</v>
       </c>
+      <c r="W75" s="1" t="n">
+        <v>352.64</v>
+      </c>
+      <c r="X75" s="3" t="n">
+        <v>-5.671184710496981e-05</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -5811,6 +6267,12 @@
       <c r="V76" s="3" t="n">
         <v>-0.01299681368438713</v>
       </c>
+      <c r="W76" s="1" t="n">
+        <v>0.1183</v>
+      </c>
+      <c r="X76" s="2" t="n">
+        <v>0.005012318409650898</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -5881,6 +6343,12 @@
       <c r="V77" s="3" t="n">
         <v>-0.0009558706388402818</v>
       </c>
+      <c r="W77" s="1" t="n">
+        <v>0.06278</v>
+      </c>
+      <c r="X77" s="2" t="n">
+        <v>0.001116249402009259</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -5951,6 +6419,12 @@
       <c r="V78" s="3" t="n">
         <v>-0.001690617075232538</v>
       </c>
+      <c r="W78" s="1" t="n">
+        <v>0.09472999999999999</v>
+      </c>
+      <c r="X78" s="2" t="n">
+        <v>0.002646062658763762</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -6021,6 +6495,12 @@
       <c r="V79" s="3" t="n">
         <v>-0.002221125370187591</v>
       </c>
+      <c r="W79" s="1" t="n">
+        <v>0.3985</v>
+      </c>
+      <c r="X79" s="3" t="n">
+        <v>-0.01434578283452875</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -6091,6 +6571,12 @@
       <c r="V80" s="3" t="n">
         <v>-0.0003318951211417633</v>
       </c>
+      <c r="W80" s="1" t="n">
+        <v>0.006011</v>
+      </c>
+      <c r="X80" s="3" t="n">
+        <v>-0.002158034528552455</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -6161,6 +6647,12 @@
       <c r="V81" s="3" t="n">
         <v>-0.005763688760806948</v>
       </c>
+      <c r="W81" s="1" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="X81" s="2" t="n">
+        <v>0.004830917874396139</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -6231,6 +6723,12 @@
       <c r="V82" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="W82" s="1" t="n">
+        <v>0.1014</v>
+      </c>
+      <c r="X82" s="3" t="n">
+        <v>-0.004906771344455352</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -6301,6 +6799,12 @@
       <c r="V83" s="2" t="n">
         <v>0.005420499342969841</v>
       </c>
+      <c r="W83" s="1" t="n">
+        <v>0.06169</v>
+      </c>
+      <c r="X83" s="2" t="n">
+        <v>0.007841855905897749</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -6371,6 +6875,12 @@
       <c r="V84" s="2" t="n">
         <v>0.002318323673651501</v>
       </c>
+      <c r="W84" s="1" t="n">
+        <v>1.1198</v>
+      </c>
+      <c r="X84" s="3" t="n">
+        <v>-0.003825282448180938</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -6441,6 +6951,12 @@
       <c r="V85" s="3" t="n">
         <v>-0.006083650190114085</v>
       </c>
+      <c r="W85" s="1" t="n">
+        <v>0.01306</v>
+      </c>
+      <c r="X85" s="3" t="n">
+        <v>-0.0007651109410864264</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -6511,6 +7027,12 @@
       <c r="V86" s="3" t="n">
         <v>-0.001782531194296034</v>
       </c>
+      <c r="W86" s="1" t="n">
+        <v>0.01678</v>
+      </c>
+      <c r="X86" s="3" t="n">
+        <v>-0.001190476190476142</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -6581,6 +7103,12 @@
       <c r="V87" s="2" t="n">
         <v>0.001683906663459147</v>
       </c>
+      <c r="W87" s="1" t="n">
+        <v>8.321999999999999</v>
+      </c>
+      <c r="X87" s="3" t="n">
+        <v>-0.0007204610951008919</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -6651,6 +7179,12 @@
       <c r="V88" s="3" t="n">
         <v>-0.001962891994204787</v>
       </c>
+      <c r="W88" s="1" t="n">
+        <v>2.1261</v>
+      </c>
+      <c r="X88" s="3" t="n">
+        <v>-0.004401779442753385</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -6721,6 +7255,12 @@
       <c r="V89" s="2" t="n">
         <v>0.01622482978415183</v>
       </c>
+      <c r="W89" s="1" t="n">
+        <v>0.007006</v>
+      </c>
+      <c r="X89" s="3" t="n">
+        <v>-0.001282965074839676</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -6791,6 +7331,12 @@
       <c r="V90" s="3" t="n">
         <v>-0.001307189542483748</v>
       </c>
+      <c r="W90" s="1" t="n">
+        <v>15.28</v>
+      </c>
+      <c r="X90" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -6861,6 +7407,12 @@
       <c r="V91" s="2" t="n">
         <v>0.008968609865470828</v>
       </c>
+      <c r="W91" s="1" t="n">
+        <v>0.000224</v>
+      </c>
+      <c r="X91" s="3" t="n">
+        <v>-0.004444444444444432</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -6931,6 +7483,12 @@
       <c r="V92" s="2" t="n">
         <v>0.01122725512969423</v>
       </c>
+      <c r="W92" s="1" t="n">
+        <v>0.05193</v>
+      </c>
+      <c r="X92" s="3" t="n">
+        <v>-0.005934150076569769</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -7001,6 +7559,12 @@
       <c r="V93" s="2" t="n">
         <v>0.0005285811372045027</v>
       </c>
+      <c r="W93" s="1" t="n">
+        <v>1.3273</v>
+      </c>
+      <c r="X93" s="2" t="n">
+        <v>0.00173584905660375</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -7071,6 +7635,12 @@
       <c r="V94" s="2" t="n">
         <v>0.00869372611994018</v>
       </c>
+      <c r="W94" s="1" t="n">
+        <v>0.054197</v>
+      </c>
+      <c r="X94" s="3" t="n">
+        <v>-0.008252818035426731</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -7141,6 +7711,12 @@
       <c r="V95" s="3" t="n">
         <v>-0.004539826661163805</v>
       </c>
+      <c r="W95" s="1" t="n">
+        <v>0.2406</v>
+      </c>
+      <c r="X95" s="3" t="n">
+        <v>-0.002487562189054683</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -7211,6 +7787,12 @@
       <c r="V96" s="3" t="n">
         <v>-0.0001861157640051908</v>
       </c>
+      <c r="W96" s="1" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X96" s="3" t="n">
+        <v>-0.004095309009679783</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -7281,6 +7863,12 @@
       <c r="V97" s="3" t="n">
         <v>-0.0003885003885005613</v>
       </c>
+      <c r="W97" s="1" t="n">
+        <v>0.2567</v>
+      </c>
+      <c r="X97" s="3" t="n">
+        <v>-0.002331908278274347</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -7351,6 +7939,12 @@
       <c r="V98" s="2" t="n">
         <v>0.005712307425999602</v>
       </c>
+      <c r="W98" s="1" t="n">
+        <v>0.579</v>
+      </c>
+      <c r="X98" s="3" t="n">
+        <v>-0.003442340791738385</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -7421,6 +8015,12 @@
       <c r="V99" s="3" t="n">
         <v>-0.00550418317921621</v>
       </c>
+      <c r="W99" s="1" t="n">
+        <v>0.13572</v>
+      </c>
+      <c r="X99" s="2" t="n">
+        <v>0.001549701129068082</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -7491,6 +8091,12 @@
       <c r="V100" s="2" t="n">
         <v>0.001303780964797974</v>
       </c>
+      <c r="W100" s="1" t="n">
+        <v>0.03084</v>
+      </c>
+      <c r="X100" s="2" t="n">
+        <v>0.003906249999999954</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -7561,6 +8167,12 @@
       <c r="V101" s="3" t="n">
         <v>-0.0009624639076033589</v>
       </c>
+      <c r="W101" s="1" t="n">
+        <v>1.041</v>
+      </c>
+      <c r="X101" s="2" t="n">
+        <v>0.00289017341040452</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -7631,6 +8243,12 @@
       <c r="V102" s="3" t="n">
         <v>-0.002260397830018148</v>
       </c>
+      <c r="W102" s="1" t="n">
+        <v>0.02209</v>
+      </c>
+      <c r="X102" s="2" t="n">
+        <v>0.0009062075215223917</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -7701,6 +8319,12 @@
       <c r="V103" s="3" t="n">
         <v>-0.00357325165900973</v>
       </c>
+      <c r="W103" s="1" t="n">
+        <v>0.01953</v>
+      </c>
+      <c r="X103" s="2" t="n">
+        <v>0.0005122950819671922</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -7771,6 +8395,12 @@
       <c r="V104" s="3" t="n">
         <v>-0.0006673340006672605</v>
       </c>
+      <c r="W104" s="1" t="n">
+        <v>2.996</v>
+      </c>
+      <c r="X104" s="2" t="n">
+        <v>0.0003338898163605642</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -7841,6 +8471,12 @@
       <c r="V105" s="3" t="n">
         <v>-0.0003072196620583106</v>
       </c>
+      <c r="W105" s="1" t="n">
+        <v>32.47</v>
+      </c>
+      <c r="X105" s="3" t="n">
+        <v>-0.002151198524892449</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -7911,6 +8547,12 @@
       <c r="V106" s="3" t="n">
         <v>-0.001800720288115214</v>
       </c>
+      <c r="W106" s="1" t="n">
+        <v>0.1661</v>
+      </c>
+      <c r="X106" s="3" t="n">
+        <v>-0.001202645820805807</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -7981,6 +8623,12 @@
       <c r="V107" s="2" t="n">
         <v>0.003225112878950766</v>
       </c>
+      <c r="W107" s="1" t="n">
+        <v>0.4644</v>
+      </c>
+      <c r="X107" s="3" t="n">
+        <v>-0.004714959279897204</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -8051,6 +8699,12 @@
       <c r="V108" s="2" t="n">
         <v>0.001191185229303191</v>
       </c>
+      <c r="W108" s="1" t="n">
+        <v>0.3359</v>
+      </c>
+      <c r="X108" s="3" t="n">
+        <v>-0.0008923259964307629</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -8121,6 +8775,12 @@
       <c r="V109" s="2" t="n">
         <v>0.004416961130742054</v>
       </c>
+      <c r="W109" s="1" t="n">
+        <v>0.2265</v>
+      </c>
+      <c r="X109" s="3" t="n">
+        <v>-0.00395778364116088</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -8191,6 +8851,12 @@
       <c r="V110" s="2" t="n">
         <v>0.003295978905734983</v>
       </c>
+      <c r="W110" s="1" t="n">
+        <v>0.01504</v>
+      </c>
+      <c r="X110" s="3" t="n">
+        <v>-0.01182654402102494</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -8261,6 +8927,12 @@
       <c r="V111" s="2" t="n">
         <v>0.001635768811341271</v>
       </c>
+      <c r="W111" s="1" t="n">
+        <v>1.837</v>
+      </c>
+      <c r="X111" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -8331,6 +9003,12 @@
       <c r="V112" s="3" t="n">
         <v>-0.001823391508205278</v>
       </c>
+      <c r="W112" s="1" t="n">
+        <v>0.03828</v>
+      </c>
+      <c r="X112" s="3" t="n">
+        <v>-0.001043841336116868</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -8401,6 +9079,12 @@
       <c r="V113" s="2" t="n">
         <v>0.0009313154831200111</v>
       </c>
+      <c r="W113" s="1" t="n">
+        <v>4.296</v>
+      </c>
+      <c r="X113" s="3" t="n">
+        <v>-0.0006978367062107731</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -8471,6 +9155,12 @@
       <c r="V114" s="2" t="n">
         <v>0.005679566767930327</v>
       </c>
+      <c r="W114" s="1" t="n">
+        <v>0.007535</v>
+      </c>
+      <c r="X114" s="3" t="n">
+        <v>-0.01037562385080117</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -8541,6 +9231,12 @@
       <c r="V115" s="2" t="n">
         <v>0.007054318250529136</v>
       </c>
+      <c r="W115" s="1" t="n">
+        <v>0.09958</v>
+      </c>
+      <c r="X115" s="3" t="n">
+        <v>-0.003502451716201372</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -8611,6 +9307,12 @@
       <c r="V116" s="3" t="n">
         <v>-0.000120423892100146</v>
       </c>
+      <c r="W116" s="1" t="n">
+        <v>0.08298</v>
+      </c>
+      <c r="X116" s="3" t="n">
+        <v>-0.0006021919788029431</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -8681,6 +9383,12 @@
       <c r="V117" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="W117" s="1" t="n">
+        <v>0.2989</v>
+      </c>
+      <c r="X117" s="3" t="n">
+        <v>-0.006646726487205057</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -8751,6 +9459,12 @@
       <c r="V118" s="3" t="n">
         <v>-0.0004422821760284414</v>
       </c>
+      <c r="W118" s="1" t="n">
+        <v>0.0226</v>
+      </c>
+      <c r="X118" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -8821,6 +9535,12 @@
       <c r="V119" s="3" t="n">
         <v>-0.002594033722438466</v>
       </c>
+      <c r="W119" s="1" t="n">
+        <v>0.1536</v>
+      </c>
+      <c r="X119" s="3" t="n">
+        <v>-0.001300390117035148</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -8891,6 +9611,12 @@
       <c r="V120" s="3" t="n">
         <v>-0.01116071428571422</v>
       </c>
+      <c r="W120" s="1" t="n">
+        <v>0.004526</v>
+      </c>
+      <c r="X120" s="2" t="n">
+        <v>0.02167042889390513</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -8961,6 +9687,12 @@
       <c r="V121" s="3" t="n">
         <v>-0.00523679417122033</v>
       </c>
+      <c r="W121" s="1" t="n">
+        <v>0.4354</v>
+      </c>
+      <c r="X121" s="3" t="n">
+        <v>-0.003433279926756698</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -9031,6 +9763,12 @@
       <c r="V122" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="W122" s="1" t="n">
+        <v>0.776</v>
+      </c>
+      <c r="X122" s="3" t="n">
+        <v>-0.002570694087403601</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -9101,6 +9839,12 @@
       <c r="V123" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="W123" s="1" t="n">
+        <v>0.0866</v>
+      </c>
+      <c r="X123" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -9171,6 +9915,12 @@
       <c r="V124" s="3" t="n">
         <v>-0.001619433198380501</v>
       </c>
+      <c r="W124" s="1" t="n">
+        <v>0.01227</v>
+      </c>
+      <c r="X124" s="3" t="n">
+        <v>-0.004866180048661883</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -9241,6 +9991,12 @@
       <c r="V125" s="3" t="n">
         <v>-0.0006145022531749743</v>
       </c>
+      <c r="W125" s="1" t="n">
+        <v>0.09748999999999999</v>
+      </c>
+      <c r="X125" s="3" t="n">
+        <v>-0.0009223201475712927</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -9311,6 +10067,12 @@
       <c r="V126" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="W126" s="1" t="n">
+        <v>0.04671</v>
+      </c>
+      <c r="X126" s="3" t="n">
+        <v>-0.002136295663319717</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -9381,6 +10143,12 @@
       <c r="V127" s="2" t="n">
         <v>0.003076923076923152</v>
       </c>
+      <c r="W127" s="1" t="n">
+        <v>3.24e-05</v>
+      </c>
+      <c r="X127" s="3" t="n">
+        <v>-0.006134969325153315</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -9451,6 +10219,12 @@
       <c r="V128" s="2" t="n">
         <v>0.001949317738791405</v>
       </c>
+      <c r="W128" s="1" t="n">
+        <v>0.5643</v>
+      </c>
+      <c r="X128" s="3" t="n">
+        <v>-0.001945525291828776</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -9521,6 +10295,12 @@
       <c r="V129" s="3" t="n">
         <v>-0.0006138735420503126</v>
       </c>
+      <c r="W129" s="1" t="n">
+        <v>0.06503</v>
+      </c>
+      <c r="X129" s="3" t="n">
+        <v>-0.001382063882063772</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -9591,6 +10371,12 @@
       <c r="V130" s="2" t="n">
         <v>0.007575757575757581</v>
       </c>
+      <c r="W130" s="1" t="n">
+        <v>0.0006136</v>
+      </c>
+      <c r="X130" s="2" t="n">
+        <v>0.002942137953579495</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -9661,6 +10447,12 @@
       <c r="V131" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="W131" s="1" t="n">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="X131" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -9731,6 +10523,12 @@
       <c r="V132" s="2" t="n">
         <v>0.001661681621801264</v>
       </c>
+      <c r="W132" s="1" t="n">
+        <v>0.301</v>
+      </c>
+      <c r="X132" s="3" t="n">
+        <v>-0.001327140013271438</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -9801,6 +10599,12 @@
       <c r="V133" s="2" t="n">
         <v>0.002673796791443844</v>
       </c>
+      <c r="W133" s="1" t="n">
+        <v>0.03411</v>
+      </c>
+      <c r="X133" s="2" t="n">
+        <v>0.01066666666666664</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -9871,6 +10675,12 @@
       <c r="V134" s="3" t="n">
         <v>-0.002838745413002795</v>
       </c>
+      <c r="W134" s="1" t="n">
+        <v>0.14358</v>
+      </c>
+      <c r="X134" s="3" t="n">
+        <v>-0.003055131231773337</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -9941,6 +10751,12 @@
       <c r="V135" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="W135" s="1" t="n">
+        <v>0.02966</v>
+      </c>
+      <c r="X135" s="3" t="n">
+        <v>-0.001346801346801409</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -10011,6 +10827,12 @@
       <c r="V136" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="W136" s="1" t="n">
+        <v>28.11</v>
+      </c>
+      <c r="X136" s="3" t="n">
+        <v>-0.004250797024442118</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -10081,6 +10903,12 @@
       <c r="V137" s="2" t="n">
         <v>0.002537485582468218</v>
       </c>
+      <c r="W137" s="1" t="n">
+        <v>0.0004343</v>
+      </c>
+      <c r="X137" s="3" t="n">
+        <v>-0.000690289921767159</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -10151,6 +10979,12 @@
       <c r="V138" s="2" t="n">
         <v>0.001629659808514953</v>
       </c>
+      <c r="W138" s="1" t="n">
+        <v>0.029521</v>
+      </c>
+      <c r="X138" s="2" t="n">
+        <v>0.0006440241339569584</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -10221,6 +11055,12 @@
       <c r="V139" s="2" t="n">
         <v>0.003014239684024515</v>
       </c>
+      <c r="W139" s="1" t="n">
+        <v>0.09608999999999999</v>
+      </c>
+      <c r="X139" s="3" t="n">
+        <v>-0.004248704663212513</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -10291,6 +11131,12 @@
       <c r="V140" s="3" t="n">
         <v>-0.0002763194252555651</v>
       </c>
+      <c r="W140" s="1" t="n">
+        <v>0.3588</v>
+      </c>
+      <c r="X140" s="3" t="n">
+        <v>-0.008291873963515762</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -10361,6 +11207,12 @@
       <c r="V141" s="3" t="n">
         <v>-0.0007598784194528566</v>
       </c>
+      <c r="W141" s="1" t="n">
+        <v>0.02639</v>
+      </c>
+      <c r="X141" s="2" t="n">
+        <v>0.003422053231939156</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -10431,6 +11283,12 @@
       <c r="V142" s="2" t="n">
         <v>0.00343555159689536</v>
       </c>
+      <c r="W142" s="1" t="n">
+        <v>0.07901</v>
+      </c>
+      <c r="X142" s="2" t="n">
+        <v>0.001902104996195756</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -10501,6 +11359,12 @@
       <c r="V143" s="3" t="n">
         <v>-0.001018099547511388</v>
       </c>
+      <c r="W143" s="1" t="n">
+        <v>0.08828999999999999</v>
+      </c>
+      <c r="X143" s="3" t="n">
+        <v>-0.0002264749179029116</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -10571,6 +11435,12 @@
       <c r="V144" s="2" t="n">
         <v>0.0009770395701027188</v>
       </c>
+      <c r="W144" s="1" t="n">
+        <v>0.02056</v>
+      </c>
+      <c r="X144" s="2" t="n">
+        <v>0.003416300634455693</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -10641,6 +11511,12 @@
       <c r="V145" s="2" t="n">
         <v>0.003054367745876631</v>
       </c>
+      <c r="W145" s="1" t="n">
+        <v>0.11471</v>
+      </c>
+      <c r="X145" s="3" t="n">
+        <v>-0.002001044022968454</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -10711,6 +11587,12 @@
       <c r="V146" s="3" t="n">
         <v>-0.0009878169245967152</v>
       </c>
+      <c r="W146" s="1" t="n">
+        <v>0.3014</v>
+      </c>
+      <c r="X146" s="3" t="n">
+        <v>-0.006591957811470013</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -10781,6 +11663,12 @@
       <c r="V147" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="W147" s="1" t="n">
+        <v>0.123</v>
+      </c>
+      <c r="X147" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -10851,6 +11739,12 @@
       <c r="V148" s="2" t="n">
         <v>0.00123108489356243</v>
       </c>
+      <c r="W148" s="1" t="n">
+        <v>1.9577</v>
+      </c>
+      <c r="X148" s="2" t="n">
+        <v>0.00297146370203393</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -10921,6 +11815,12 @@
       <c r="V149" s="3" t="n">
         <v>-0.0009708737864077274</v>
       </c>
+      <c r="W149" s="1" t="n">
+        <v>0.06172</v>
+      </c>
+      <c r="X149" s="3" t="n">
+        <v>-0.0003239390994494027</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -10991,6 +11891,12 @@
       <c r="V150" s="3" t="n">
         <v>-0.001220256253813167</v>
       </c>
+      <c r="W150" s="1" t="n">
+        <v>0.1619</v>
+      </c>
+      <c r="X150" s="3" t="n">
+        <v>-0.01099572388515592</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -11061,6 +11967,12 @@
       <c r="V151" s="2" t="n">
         <v>0.0008959235478571902</v>
       </c>
+      <c r="W151" s="1" t="n">
+        <v>6.69e-05</v>
+      </c>
+      <c r="X151" s="3" t="n">
+        <v>-0.001939430105922728</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -11131,6 +12043,12 @@
       <c r="V152" s="2" t="n">
         <v>0.006109979633401209</v>
       </c>
+      <c r="W152" s="1" t="n">
+        <v>0.01472</v>
+      </c>
+      <c r="X152" s="3" t="n">
+        <v>-0.006747638326585655</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -11201,6 +12119,12 @@
       <c r="V153" s="3" t="n">
         <v>-0.0004761904761904568</v>
       </c>
+      <c r="W153" s="1" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="X153" s="2" t="n">
+        <v>0.0004764173415912145</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -11271,6 +12195,12 @@
       <c r="V154" s="3" t="n">
         <v>-0.002513826043237778</v>
       </c>
+      <c r="W154" s="1" t="n">
+        <v>0.0005928</v>
+      </c>
+      <c r="X154" s="3" t="n">
+        <v>-0.004032258064516227</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -11341,6 +12271,12 @@
       <c r="V155" s="3" t="n">
         <v>-0.000497017892644115</v>
       </c>
+      <c r="W155" s="1" t="n">
+        <v>0.04012</v>
+      </c>
+      <c r="X155" s="3" t="n">
+        <v>-0.002486325211337542</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -11411,6 +12347,12 @@
       <c r="V156" s="3" t="n">
         <v>-0.001058761249338231</v>
       </c>
+      <c r="W156" s="1" t="n">
+        <v>0.01886</v>
+      </c>
+      <c r="X156" s="3" t="n">
+        <v>-0.0005299417064124569</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -11481,6 +12423,12 @@
       <c r="V157" s="2" t="n">
         <v>0.004147943311441401</v>
       </c>
+      <c r="W157" s="1" t="n">
+        <v>0.08723</v>
+      </c>
+      <c r="X157" s="2" t="n">
+        <v>0.0009179575444635311</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -11551,6 +12499,12 @@
       <c r="V158" s="3" t="n">
         <v>-0.0166626418739434</v>
       </c>
+      <c r="W158" s="1" t="n">
+        <v>0.008415000000000001</v>
+      </c>
+      <c r="X158" s="2" t="n">
+        <v>0.03327603143418473</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -11621,6 +12575,12 @@
       <c r="V159" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="W159" s="1" t="n">
+        <v>2.503</v>
+      </c>
+      <c r="X159" s="2" t="n">
+        <v>0.002402883460152274</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -11691,6 +12651,12 @@
       <c r="V160" s="2" t="n">
         <v>0.000233972859148313</v>
       </c>
+      <c r="W160" s="1" t="n">
+        <v>1.2806</v>
+      </c>
+      <c r="X160" s="3" t="n">
+        <v>-0.001481481481481491</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -11761,6 +12727,12 @@
       <c r="V161" s="3" t="n">
         <v>-0.0009322146757224746</v>
       </c>
+      <c r="W161" s="1" t="n">
+        <v>0.007491</v>
+      </c>
+      <c r="X161" s="3" t="n">
+        <v>-0.00146627565982401</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -11831,6 +12803,12 @@
       <c r="V162" s="2" t="n">
         <v>0.03645581844519558</v>
       </c>
+      <c r="W162" s="1" t="n">
+        <v>0.004183</v>
+      </c>
+      <c r="X162" s="3" t="n">
+        <v>-0.02562310738411364</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -11901,6 +12879,12 @@
       <c r="V163" s="2" t="n">
         <v>0.001039501039501069</v>
       </c>
+      <c r="W163" s="1" t="n">
+        <v>0.0961</v>
+      </c>
+      <c r="X163" s="3" t="n">
+        <v>-0.002076843198338441</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -11971,6 +12955,12 @@
       <c r="V164" s="3" t="n">
         <v>-0.0007220737959420261</v>
       </c>
+      <c r="W164" s="1" t="n">
+        <v>1.3817</v>
+      </c>
+      <c r="X164" s="3" t="n">
+        <v>-0.001589710239179117</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -12041,6 +13031,12 @@
       <c r="V165" s="3" t="n">
         <v>-4.247547041587733e-05</v>
       </c>
+      <c r="W165" s="1" t="n">
+        <v>0.023563</v>
+      </c>
+      <c r="X165" s="2" t="n">
+        <v>0.0008920227678192246</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -12111,6 +13107,12 @@
       <c r="V166" s="3" t="n">
         <v>-0.005233572397751524</v>
       </c>
+      <c r="W166" s="1" t="n">
+        <v>0.005101</v>
+      </c>
+      <c r="X166" s="3" t="n">
+        <v>-0.006040530007794358</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -12181,6 +13183,12 @@
       <c r="V167" s="3" t="n">
         <v>-0.01109445277361305</v>
       </c>
+      <c r="W167" s="1" t="n">
+        <v>0.06593</v>
+      </c>
+      <c r="X167" s="3" t="n">
+        <v>-0.0004548211036992457</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -12251,6 +13259,12 @@
       <c r="V168" s="2" t="n">
         <v>0.001053740779768207</v>
       </c>
+      <c r="W168" s="1" t="n">
+        <v>0.09520000000000001</v>
+      </c>
+      <c r="X168" s="2" t="n">
+        <v>0.002105263157894797</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -12321,6 +13335,12 @@
       <c r="V169" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="W169" s="1" t="n">
+        <v>0.03824</v>
+      </c>
+      <c r="X169" s="2" t="n">
+        <v>0.004993429697766168</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -12391,6 +13411,12 @@
       <c r="V170" s="2" t="n">
         <v>0.0001400168020162605</v>
       </c>
+      <c r="W170" s="1" t="n">
+        <v>0.007136</v>
+      </c>
+      <c r="X170" s="3" t="n">
+        <v>-0.0009799804003920009</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -12461,6 +13487,12 @@
       <c r="V171" s="2" t="n">
         <v>0.0002932551319647771</v>
       </c>
+      <c r="W171" s="1" t="n">
+        <v>0.3404</v>
+      </c>
+      <c r="X171" s="3" t="n">
+        <v>-0.002052184110231703</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -12531,6 +13563,12 @@
       <c r="V172" s="3" t="n">
         <v>-0.0009170946441672585</v>
       </c>
+      <c r="W172" s="1" t="n">
+        <v>5.43</v>
+      </c>
+      <c r="X172" s="3" t="n">
+        <v>-0.003120984027905333</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -12601,6 +13639,12 @@
       <c r="V173" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="W173" s="1" t="n">
+        <v>0.04552</v>
+      </c>
+      <c r="X173" s="3" t="n">
+        <v>-0.001973251479938606</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -12671,6 +13715,12 @@
       <c r="V174" s="2" t="n">
         <v>0.0007694280584765902</v>
       </c>
+      <c r="W174" s="1" t="n">
+        <v>0.03899</v>
+      </c>
+      <c r="X174" s="3" t="n">
+        <v>-0.0007688364941056445</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -12741,6 +13791,12 @@
       <c r="V175" s="3" t="n">
         <v>-0.002845962290999713</v>
       </c>
+      <c r="W175" s="1" t="n">
+        <v>0.005529</v>
+      </c>
+      <c r="X175" s="3" t="n">
+        <v>-0.0137352836246878</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -12811,6 +13867,12 @@
       <c r="V176" s="2" t="n">
         <v>0.001324503311258224</v>
       </c>
+      <c r="W176" s="1" t="n">
+        <v>0.00756</v>
+      </c>
+      <c r="X176" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -12881,6 +13943,12 @@
       <c r="V177" s="2" t="n">
         <v>0.003376477208778844</v>
       </c>
+      <c r="W177" s="1" t="n">
+        <v>1.776</v>
+      </c>
+      <c r="X177" s="3" t="n">
+        <v>-0.003925967470555186</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -12951,6 +14019,12 @@
       <c r="V178" s="2" t="n">
         <v>0.001977419149071926</v>
       </c>
+      <c r="W178" s="1" t="n">
+        <v>15.692</v>
+      </c>
+      <c r="X178" s="3" t="n">
+        <v>-0.001018589253883373</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -13021,6 +14095,12 @@
       <c r="V179" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="W179" s="1" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="X179" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -13091,6 +14171,12 @@
       <c r="V180" s="3" t="n">
         <v>-0.009903011740684009</v>
       </c>
+      <c r="W180" s="1" t="n">
+        <v>0.0968</v>
+      </c>
+      <c r="X180" s="3" t="n">
+        <v>-0.001856052794390592</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -13161,6 +14247,12 @@
       <c r="V181" s="2" t="n">
         <v>0.0005333333333332746</v>
       </c>
+      <c r="W181" s="1" t="n">
+        <v>0.1872</v>
+      </c>
+      <c r="X181" s="3" t="n">
+        <v>-0.002132196162046822</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -13231,6 +14323,12 @@
       <c r="V182" s="2" t="n">
         <v>0.0001689189189188534</v>
       </c>
+      <c r="W182" s="1" t="n">
+        <v>0.0592</v>
+      </c>
+      <c r="X182" s="3" t="n">
+        <v>-0.0001688903901367357</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -13301,6 +14399,12 @@
       <c r="V183" s="3" t="n">
         <v>-0.002493765586034955</v>
       </c>
+      <c r="W183" s="1" t="n">
+        <v>0.01197</v>
+      </c>
+      <c r="X183" s="3" t="n">
+        <v>-0.002500000000000043</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -13371,6 +14475,12 @@
       <c r="V184" s="3" t="n">
         <v>-0.00186480186480195</v>
       </c>
+      <c r="W184" s="1" t="n">
+        <v>0.02135</v>
+      </c>
+      <c r="X184" s="3" t="n">
+        <v>-0.002802428771601941</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -13441,6 +14551,12 @@
       <c r="V185" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="W185" s="1" t="n">
+        <v>0.366</v>
+      </c>
+      <c r="X185" s="2" t="n">
+        <v>0.002739726027397263</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -13511,6 +14627,12 @@
       <c r="V186" s="3" t="n">
         <v>-0.001568832527127824</v>
       </c>
+      <c r="W186" s="1" t="n">
+        <v>0.007625</v>
+      </c>
+      <c r="X186" s="3" t="n">
+        <v>-0.00157129762995939</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -13581,6 +14703,12 @@
       <c r="V187" s="2" t="n">
         <v>0.006336190831159281</v>
       </c>
+      <c r="W187" s="1" t="n">
+        <v>0.2691</v>
+      </c>
+      <c r="X187" s="3" t="n">
+        <v>-0.003333333333333377</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -13651,6 +14779,12 @@
       <c r="V188" s="3" t="n">
         <v>-0.0006086427267194613</v>
       </c>
+      <c r="W188" s="1" t="n">
+        <v>0.04917</v>
+      </c>
+      <c r="X188" s="3" t="n">
+        <v>-0.001827040194884283</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -13721,6 +14855,12 @@
       <c r="V189" s="2" t="n">
         <v>0.00273651290070359</v>
       </c>
+      <c r="W189" s="1" t="n">
+        <v>0.2556</v>
+      </c>
+      <c r="X189" s="3" t="n">
+        <v>-0.003508771929824608</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -13791,6 +14931,12 @@
       <c r="V190" s="3" t="n">
         <v>-0.00210785174776037</v>
       </c>
+      <c r="W190" s="1" t="n">
+        <v>0.5679999999999999</v>
+      </c>
+      <c r="X190" s="3" t="n">
+        <v>-0.0001760253476502376</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -13861,6 +15007,12 @@
       <c r="V191" s="2" t="n">
         <v>0.001656726308813896</v>
       </c>
+      <c r="W191" s="1" t="n">
+        <v>6.036</v>
+      </c>
+      <c r="X191" s="3" t="n">
+        <v>-0.001653986106516817</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -13931,6 +15083,12 @@
       <c r="V192" s="2" t="n">
         <v>0.003432494279176141</v>
       </c>
+      <c r="W192" s="1" t="n">
+        <v>0.3499</v>
+      </c>
+      <c r="X192" s="3" t="n">
+        <v>-0.002565564424173352</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -14001,6 +15159,12 @@
       <c r="V193" s="3" t="n">
         <v>-0.006240249609984361</v>
       </c>
+      <c r="W193" s="1" t="n">
+        <v>0.0636</v>
+      </c>
+      <c r="X193" s="3" t="n">
+        <v>-0.0015698587127159</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -14071,6 +15235,12 @@
       <c r="V194" s="3" t="n">
         <v>-0.004597701149425299</v>
       </c>
+      <c r="W194" s="1" t="n">
+        <v>0.01737</v>
+      </c>
+      <c r="X194" s="2" t="n">
+        <v>0.002886836027713709</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -14141,6 +15311,12 @@
       <c r="V195" s="3" t="n">
         <v>-0.006821121956956407</v>
       </c>
+      <c r="W195" s="1" t="n">
+        <v>0.0008456</v>
+      </c>
+      <c r="X195" s="2" t="n">
+        <v>0.001302545885139103</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -14211,6 +15387,12 @@
       <c r="V196" s="3" t="n">
         <v>-0.01189387008234217</v>
       </c>
+      <c r="W196" s="1" t="n">
+        <v>0.001055</v>
+      </c>
+      <c r="X196" s="3" t="n">
+        <v>-0.02314814814814821</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -14281,6 +15463,12 @@
       <c r="V197" s="3" t="n">
         <v>-0.001846153846153724</v>
       </c>
+      <c r="W197" s="1" t="n">
+        <v>0.0001615</v>
+      </c>
+      <c r="X197" s="3" t="n">
+        <v>-0.004315659679408243</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -14351,6 +15539,12 @@
       <c r="V198" s="3" t="n">
         <v>-0.00161216029479495</v>
       </c>
+      <c r="W198" s="1" t="n">
+        <v>4.329</v>
+      </c>
+      <c r="X198" s="3" t="n">
+        <v>-0.001384083044982751</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -14421,6 +15615,12 @@
       <c r="V199" s="3" t="n">
         <v>-0.001229256299938572</v>
       </c>
+      <c r="W199" s="1" t="n">
+        <v>0.1621</v>
+      </c>
+      <c r="X199" s="3" t="n">
+        <v>-0.002461538461538532</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -14491,6 +15691,12 @@
       <c r="V200" s="3" t="n">
         <v>-0.02418738861071039</v>
       </c>
+      <c r="W200" s="1" t="n">
+        <v>0.022806</v>
+      </c>
+      <c r="X200" s="3" t="n">
+        <v>-0.008262306488084849</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -14561,6 +15767,12 @@
       <c r="V201" s="3" t="n">
         <v>-0.0006479306714181318</v>
       </c>
+      <c r="W201" s="1" t="n">
+        <v>0.12393</v>
+      </c>
+      <c r="X201" s="2" t="n">
+        <v>0.00437636761487964</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -14631,6 +15843,12 @@
       <c r="V202" s="2" t="n">
         <v>0.003617945007235868</v>
       </c>
+      <c r="W202" s="1" t="n">
+        <v>0.01386</v>
+      </c>
+      <c r="X202" s="3" t="n">
+        <v>-0.0007209805335255654</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -14701,6 +15919,12 @@
       <c r="V203" s="2" t="n">
         <v>0.002190847127555984</v>
       </c>
+      <c r="W203" s="1" t="n">
+        <v>0.04119</v>
+      </c>
+      <c r="X203" s="2" t="n">
+        <v>0.0004857906242409324</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -14771,6 +15995,12 @@
       <c r="V204" s="3" t="n">
         <v>-0.0007748934521502978</v>
       </c>
+      <c r="W204" s="1" t="n">
+        <v>0.0258</v>
+      </c>
+      <c r="X204" s="2" t="n">
+        <v>0.0003877471888328652</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -14841,6 +16071,12 @@
       <c r="V205" s="3" t="n">
         <v>-0.0004627487274409486</v>
       </c>
+      <c r="W205" s="1" t="n">
+        <v>0.4312</v>
+      </c>
+      <c r="X205" s="3" t="n">
+        <v>-0.001851851851851776</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -14911,6 +16147,12 @@
       <c r="V206" s="3" t="n">
         <v>-0.00478677110530892</v>
       </c>
+      <c r="W206" s="1" t="n">
+        <v>0.02282</v>
+      </c>
+      <c r="X206" s="3" t="n">
+        <v>-0.002186270222999625</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -14981,6 +16223,12 @@
       <c r="V207" s="2" t="n">
         <v>0.001918465227817748</v>
       </c>
+      <c r="W207" s="1" t="n">
+        <v>4.174</v>
+      </c>
+      <c r="X207" s="3" t="n">
+        <v>-0.0009573958831975969</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -15051,6 +16299,12 @@
       <c r="V208" s="2" t="n">
         <v>0.0001356668023334164</v>
       </c>
+      <c r="W208" s="1" t="n">
+        <v>0.07364</v>
+      </c>
+      <c r="X208" s="3" t="n">
+        <v>-0.001085187194791057</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -15121,6 +16375,12 @@
       <c r="V209" s="3" t="n">
         <v>-0.00166191832858501</v>
       </c>
+      <c r="W209" s="1" t="n">
+        <v>0.04198</v>
+      </c>
+      <c r="X209" s="3" t="n">
+        <v>-0.001664684898929695</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -15191,6 +16451,12 @@
       <c r="V210" s="3" t="n">
         <v>-0.0005390835579514231</v>
       </c>
+      <c r="W210" s="1" t="n">
+        <v>0.1851</v>
+      </c>
+      <c r="X210" s="3" t="n">
+        <v>-0.001618122977346399</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -15261,6 +16527,12 @@
       <c r="V211" s="3" t="n">
         <v>-0.001697072549851437</v>
       </c>
+      <c r="W211" s="1" t="n">
+        <v>0.2354</v>
+      </c>
+      <c r="X211" s="2" t="n">
+        <v>0.0004249893752655715</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -15331,6 +16603,12 @@
       <c r="V212" s="2" t="n">
         <v>0.003373493975903644</v>
       </c>
+      <c r="W212" s="1" t="n">
+        <v>0.002087</v>
+      </c>
+      <c r="X212" s="2" t="n">
+        <v>0.002401536983669451</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -15401,6 +16679,12 @@
       <c r="V213" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="W213" s="1" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="X213" s="3" t="n">
+        <v>-0.003215434083601289</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -15471,6 +16755,12 @@
       <c r="V214" s="2" t="n">
         <v>0.00140080546314134</v>
       </c>
+      <c r="W214" s="1" t="n">
+        <v>0.0057</v>
+      </c>
+      <c r="X214" s="3" t="n">
+        <v>-0.00332225913621261</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -15541,6 +16831,12 @@
       <c r="V215" s="3" t="n">
         <v>-0.0007301935012779355</v>
       </c>
+      <c r="W215" s="1" t="n">
+        <v>0.05466</v>
+      </c>
+      <c r="X215" s="3" t="n">
+        <v>-0.001461454146876082</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -15611,6 +16907,12 @@
       <c r="V216" s="3" t="n">
         <v>-0.001579778830963491</v>
       </c>
+      <c r="W216" s="1" t="n">
+        <v>0.063</v>
+      </c>
+      <c r="X216" s="3" t="n">
+        <v>-0.003164556962025407</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -15681,6 +16983,12 @@
       <c r="V217" s="2" t="n">
         <v>0.001078748651564067</v>
       </c>
+      <c r="W217" s="1" t="n">
+        <v>0.09279999999999999</v>
+      </c>
+      <c r="X217" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -15751,6 +17059,12 @@
       <c r="V218" s="3" t="n">
         <v>-0.003242658980363941</v>
       </c>
+      <c r="W218" s="1" t="n">
+        <v>0.27754</v>
+      </c>
+      <c r="X218" s="2" t="n">
+        <v>0.003217061268751137</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -15821,6 +17135,12 @@
       <c r="V219" s="3" t="n">
         <v>-0.0003054367745877009</v>
       </c>
+      <c r="W219" s="1" t="n">
+        <v>0.003256</v>
+      </c>
+      <c r="X219" s="3" t="n">
+        <v>-0.005194011610143494</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -15891,6 +17211,12 @@
       <c r="V220" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="W220" s="1" t="n">
+        <v>0.999374</v>
+      </c>
+      <c r="X220" s="2" t="n">
+        <v>1.00062739340442e-06</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -15961,6 +17287,12 @@
       <c r="V221" s="3" t="n">
         <v>-0.001538856116953002</v>
       </c>
+      <c r="W221" s="1" t="n">
+        <v>0.03897</v>
+      </c>
+      <c r="X221" s="2" t="n">
+        <v>0.001027485229899778</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -16031,6 +17363,12 @@
       <c r="V222" s="2" t="n">
         <v>0.0004291845493562056</v>
       </c>
+      <c r="W222" s="1" t="n">
+        <v>0.04653</v>
+      </c>
+      <c r="X222" s="3" t="n">
+        <v>-0.001930501930501926</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -16101,6 +17439,12 @@
       <c r="V223" s="2" t="n">
         <v>0.000948766603415587</v>
       </c>
+      <c r="W223" s="1" t="n">
+        <v>0.1053</v>
+      </c>
+      <c r="X223" s="3" t="n">
+        <v>-0.001895734597156321</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -16171,6 +17515,12 @@
       <c r="V224" s="2" t="n">
         <v>0.001793492185498365</v>
       </c>
+      <c r="W224" s="1" t="n">
+        <v>3.909</v>
+      </c>
+      <c r="X224" s="3" t="n">
+        <v>-0.0002557544757034102</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -16241,6 +17591,12 @@
       <c r="V225" s="2" t="n">
         <v>0.001843417913684653</v>
       </c>
+      <c r="W225" s="1" t="n">
+        <v>0.0009214</v>
+      </c>
+      <c r="X225" s="3" t="n">
+        <v>-0.002705920554172537</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -16311,6 +17667,12 @@
       <c r="V226" s="3" t="n">
         <v>-0.0001174398120962144</v>
       </c>
+      <c r="W226" s="1" t="n">
+        <v>0.008554000000000001</v>
+      </c>
+      <c r="X226" s="2" t="n">
+        <v>0.004698144233027966</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -16381,6 +17743,12 @@
       <c r="V227" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="W227" s="1" t="n">
+        <v>0.04131</v>
+      </c>
+      <c r="X227" s="3" t="n">
+        <v>-0.0007256894049347423</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -16451,6 +17819,12 @@
       <c r="V228" s="3" t="n">
         <v>-0.0002805836139168385</v>
       </c>
+      <c r="W228" s="1" t="n">
+        <v>0.03542</v>
+      </c>
+      <c r="X228" s="3" t="n">
+        <v>-0.005893909626719109</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -16521,6 +17895,12 @@
       <c r="V229" s="2" t="n">
         <v>0.001945525291828714</v>
       </c>
+      <c r="W229" s="1" t="n">
+        <v>0.05153</v>
+      </c>
+      <c r="X229" s="2" t="n">
+        <v>0.0005825242718447038</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -16591,6 +17971,12 @@
       <c r="V230" s="3" t="n">
         <v>-0.005175388154111621</v>
       </c>
+      <c r="W230" s="1" t="n">
+        <v>0.001731</v>
+      </c>
+      <c r="X230" s="2" t="n">
+        <v>0.0005780346820808762</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -16661,6 +18047,12 @@
       <c r="V231" s="2" t="n">
         <v>0.001237113402061805</v>
       </c>
+      <c r="W231" s="1" t="n">
+        <v>0.04855</v>
+      </c>
+      <c r="X231" s="3" t="n">
+        <v>-0.0002059308072486846</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -16731,6 +18123,12 @@
       <c r="V232" s="2" t="n">
         <v>0.00323325635103929</v>
       </c>
+      <c r="W232" s="1" t="n">
+        <v>0.02178</v>
+      </c>
+      <c r="X232" s="2" t="n">
+        <v>0.002762430939226566</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -16801,6 +18199,12 @@
       <c r="V233" s="3" t="n">
         <v>-0.0001707941929973496</v>
       </c>
+      <c r="W233" s="1" t="n">
+        <v>0.000585</v>
+      </c>
+      <c r="X233" s="3" t="n">
+        <v>-0.0006832934745473347</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -16871,6 +18275,12 @@
       <c r="V234" s="3" t="n">
         <v>-0.008715491672370627</v>
       </c>
+      <c r="W234" s="1" t="n">
+        <v>0.21562</v>
+      </c>
+      <c r="X234" s="3" t="n">
+        <v>-0.00745719020438217</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -16941,6 +18351,12 @@
       <c r="V235" s="3" t="n">
         <v>-0.002141327623126375</v>
       </c>
+      <c r="W235" s="1" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="X235" s="2" t="n">
+        <v>0.00143061516452081</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -17011,6 +18427,12 @@
       <c r="V236" s="2" t="n">
         <v>0.002427184466019487</v>
       </c>
+      <c r="W236" s="1" t="n">
+        <v>0.0412</v>
+      </c>
+      <c r="X236" s="3" t="n">
+        <v>-0.002421307506053338</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -17081,6 +18503,12 @@
       <c r="V237" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="W237" s="1" t="n">
+        <v>0.00419</v>
+      </c>
+      <c r="X237" s="3" t="n">
+        <v>-0.002380952380952284</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -17151,6 +18579,12 @@
       <c r="V238" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="W238" s="1" t="n">
+        <v>0.0249</v>
+      </c>
+      <c r="X238" s="3" t="n">
+        <v>-0.004000000000000115</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -17221,6 +18655,12 @@
       <c r="V239" s="2" t="n">
         <v>0.00335345405767939</v>
       </c>
+      <c r="W239" s="1" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="X239" s="2" t="n">
+        <v>0.002673796791443857</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -17291,6 +18731,12 @@
       <c r="V240" s="2" t="n">
         <v>0.001020929045431367</v>
       </c>
+      <c r="W240" s="1" t="n">
+        <v>0.0003915</v>
+      </c>
+      <c r="X240" s="3" t="n">
+        <v>-0.001784803671596168</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -17361,6 +18807,12 @@
       <c r="V241" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="W241" s="1" t="n">
+        <v>0.268</v>
+      </c>
+      <c r="X241" s="3" t="n">
+        <v>-0.005565862708719856</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -17431,6 +18883,12 @@
       <c r="V242" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="W242" s="1" t="n">
+        <v>0.0759</v>
+      </c>
+      <c r="X242" s="3" t="n">
+        <v>-0.002103602419142879</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -17501,6 +18959,12 @@
       <c r="V243" s="2" t="n">
         <v>0.001517450682852921</v>
       </c>
+      <c r="W243" s="1" t="n">
+        <v>0.01986</v>
+      </c>
+      <c r="X243" s="2" t="n">
+        <v>0.003030303030302907</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -17571,6 +19035,12 @@
       <c r="V244" s="2" t="n">
         <v>0.001612903225806466</v>
       </c>
+      <c r="W244" s="1" t="n">
+        <v>0.08691</v>
+      </c>
+      <c r="X244" s="3" t="n">
+        <v>-0.0003450655624568926</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -17641,6 +19111,12 @@
       <c r="V245" s="2" t="n">
         <v>0.00425710098401842</v>
       </c>
+      <c r="W245" s="1" t="n">
+        <v>1.4405</v>
+      </c>
+      <c r="X245" s="2" t="n">
+        <v>0.001042390548992241</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -17711,6 +19187,12 @@
       <c r="V246" s="3" t="n">
         <v>-0.0005624296962879411</v>
       </c>
+      <c r="W246" s="1" t="n">
+        <v>0.01776</v>
+      </c>
+      <c r="X246" s="3" t="n">
+        <v>-0.0005627462014631172</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -17781,6 +19263,12 @@
       <c r="V247" s="3" t="n">
         <v>-0.0001510117789187757</v>
       </c>
+      <c r="W247" s="1" t="n">
+        <v>0.006593</v>
+      </c>
+      <c r="X247" s="3" t="n">
+        <v>-0.004228968433771371</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -17851,6 +19339,12 @@
       <c r="V248" s="3" t="n">
         <v>-0.01232227488151658</v>
       </c>
+      <c r="W248" s="1" t="n">
+        <v>0.004183</v>
+      </c>
+      <c r="X248" s="2" t="n">
+        <v>0.003598848368522135</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -17921,6 +19415,12 @@
       <c r="V249" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="W249" s="1" t="n">
+        <v>0.1096</v>
+      </c>
+      <c r="X249" s="3" t="n">
+        <v>-0.000911577028258914</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -17991,6 +19491,12 @@
       <c r="V250" s="3" t="n">
         <v>-0.002892681515764996</v>
       </c>
+      <c r="W250" s="1" t="n">
+        <v>0.03426</v>
+      </c>
+      <c r="X250" s="3" t="n">
+        <v>-0.006092254134029644</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -18061,6 +19567,12 @@
       <c r="V251" s="3" t="n">
         <v>-0.005315461058470096</v>
       </c>
+      <c r="W251" s="1" t="n">
+        <v>0.04292</v>
+      </c>
+      <c r="X251" s="3" t="n">
+        <v>-0.002788104089219378</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -18131,6 +19643,12 @@
       <c r="V252" s="3" t="n">
         <v>-0.001311690441055943</v>
       </c>
+      <c r="W252" s="1" t="n">
+        <v>0.006054</v>
+      </c>
+      <c r="X252" s="3" t="n">
+        <v>-0.006074536200952176</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -18201,6 +19719,12 @@
       <c r="V253" s="2" t="n">
         <v>0.01156737998843255</v>
       </c>
+      <c r="W253" s="1" t="n">
+        <v>0.01734</v>
+      </c>
+      <c r="X253" s="3" t="n">
+        <v>-0.008576329331046162</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -18271,6 +19795,12 @@
       <c r="V254" s="3" t="n">
         <v>-0.00230946882217086</v>
       </c>
+      <c r="W254" s="1" t="n">
+        <v>0.1293</v>
+      </c>
+      <c r="X254" s="3" t="n">
+        <v>-0.002314814814814774</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -18341,6 +19871,12 @@
       <c r="V255" s="3" t="n">
         <v>-0.008886810102899869</v>
       </c>
+      <c r="W255" s="1" t="n">
+        <v>0.02103</v>
+      </c>
+      <c r="X255" s="3" t="n">
+        <v>-0.007550731477111865</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -18411,6 +19947,12 @@
       <c r="V256" s="3" t="n">
         <v>-0.001423149905123446</v>
       </c>
+      <c r="W256" s="1" t="n">
+        <v>0.02104</v>
+      </c>
+      <c r="X256" s="3" t="n">
+        <v>-0.0004750593824227835</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -18481,6 +20023,12 @@
       <c r="V257" s="3" t="n">
         <v>-0.001976284584980157</v>
       </c>
+      <c r="W257" s="1" t="n">
+        <v>0.0252</v>
+      </c>
+      <c r="X257" s="3" t="n">
+        <v>-0.001980198019802037</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -18551,6 +20099,12 @@
       <c r="V258" s="2" t="n">
         <v>0.006143162393162421</v>
       </c>
+      <c r="W258" s="1" t="n">
+        <v>0.15071</v>
+      </c>
+      <c r="X258" s="2" t="n">
+        <v>0.0001990974250066515</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -18621,6 +20175,12 @@
       <c r="V259" s="3" t="n">
         <v>-0.001571400510705102</v>
       </c>
+      <c r="W259" s="1" t="n">
+        <v>0.05079</v>
+      </c>
+      <c r="X259" s="3" t="n">
+        <v>-0.0007869368483178905</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -18691,6 +20251,12 @@
       <c r="V260" s="3" t="n">
         <v>-0.002760441670667402</v>
       </c>
+      <c r="W260" s="1" t="n">
+        <v>0.08305999999999999</v>
+      </c>
+      <c r="X260" s="3" t="n">
+        <v>-0.0003610542784932272</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -18761,6 +20327,12 @@
       <c r="V261" s="2" t="n">
         <v>0.005638340716874798</v>
       </c>
+      <c r="W261" s="1" t="n">
+        <v>0.2541</v>
+      </c>
+      <c r="X261" s="2" t="n">
+        <v>0.01762114537444929</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -18831,6 +20403,12 @@
       <c r="V262" s="2" t="n">
         <v>0.004187020237264406</v>
       </c>
+      <c r="W262" s="1" t="n">
+        <v>0.1442</v>
+      </c>
+      <c r="X262" s="2" t="n">
+        <v>0.002084781097984675</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -18901,6 +20479,12 @@
       <c r="V263" s="2" t="n">
         <v>0.001040312093628227</v>
       </c>
+      <c r="W263" s="1" t="n">
+        <v>0.07685</v>
+      </c>
+      <c r="X263" s="3" t="n">
+        <v>-0.001688750324759744</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -18971,6 +20555,12 @@
       <c r="V264" s="3" t="n">
         <v>-0.007315842583249207</v>
       </c>
+      <c r="W264" s="1" t="n">
+        <v>0.03941</v>
+      </c>
+      <c r="X264" s="2" t="n">
+        <v>0.001524777636594601</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -19041,6 +20631,12 @@
       <c r="V265" s="3" t="n">
         <v>-0.0006531678641411709</v>
       </c>
+      <c r="W265" s="1" t="n">
+        <v>0.01528</v>
+      </c>
+      <c r="X265" s="3" t="n">
+        <v>-0.001307189542483607</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -19111,6 +20707,12 @@
       <c r="V266" s="2" t="n">
         <v>0.00151387720773765</v>
       </c>
+      <c r="W266" s="1" t="n">
+        <v>0.005991</v>
+      </c>
+      <c r="X266" s="2" t="n">
+        <v>0.00621430970775944</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -19181,6 +20783,12 @@
       <c r="V267" s="3" t="n">
         <v>-0.001337613697164112</v>
       </c>
+      <c r="W267" s="1" t="n">
+        <v>0.03717</v>
+      </c>
+      <c r="X267" s="3" t="n">
+        <v>-0.004286096972944024</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -19251,6 +20859,12 @@
       <c r="V268" s="3" t="n">
         <v>-0.0006523157208088449</v>
       </c>
+      <c r="W268" s="1" t="n">
+        <v>0.03055</v>
+      </c>
+      <c r="X268" s="3" t="n">
+        <v>-0.002937336814621403</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -19321,6 +20935,12 @@
       <c r="V269" s="2" t="n">
         <v>0.0008840560491535417</v>
       </c>
+      <c r="W269" s="1" t="n">
+        <v>0.22574</v>
+      </c>
+      <c r="X269" s="3" t="n">
+        <v>-0.00304729938612373</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -19391,6 +21011,12 @@
       <c r="V270" s="3" t="n">
         <v>-0.002157497303128373</v>
       </c>
+      <c r="W270" s="1" t="n">
+        <v>0.926</v>
+      </c>
+      <c r="X270" s="2" t="n">
+        <v>0.001081081081081082</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -19461,6 +21087,12 @@
       <c r="V271" s="2" t="n">
         <v>0.002312138728323616</v>
       </c>
+      <c r="W271" s="1" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="X271" s="3" t="n">
+        <v>-0.0003844675124951518</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -19531,6 +21163,12 @@
       <c r="V272" s="2" t="n">
         <v>0.000540540540540481</v>
       </c>
+      <c r="W272" s="1" t="n">
+        <v>0.185</v>
+      </c>
+      <c r="X272" s="3" t="n">
+        <v>-0.0005402485143165261</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -19601,6 +21239,12 @@
       <c r="V273" s="2" t="n">
         <v>0.0009680542110357786</v>
       </c>
+      <c r="W273" s="1" t="n">
+        <v>0.03105</v>
+      </c>
+      <c r="X273" s="2" t="n">
+        <v>0.0009671179883946566</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -19671,6 +21315,12 @@
       <c r="V274" s="2" t="n">
         <v>0.001563314226159575</v>
       </c>
+      <c r="W274" s="1" t="n">
+        <v>0.1907</v>
+      </c>
+      <c r="X274" s="3" t="n">
+        <v>-0.007804370447450579</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -19741,6 +21391,12 @@
       <c r="V275" s="2" t="n">
         <v>0.001014934029288105</v>
       </c>
+      <c r="W275" s="1" t="n">
+        <v>0.06915</v>
+      </c>
+      <c r="X275" s="2" t="n">
+        <v>0.001593279258400912</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -19811,6 +21467,12 @@
       <c r="V276" s="3" t="n">
         <v>-0.000373087924387542</v>
       </c>
+      <c r="W276" s="1" t="n">
+        <v>0.08032</v>
+      </c>
+      <c r="X276" s="3" t="n">
+        <v>-0.0007464543418759719</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -19881,6 +21543,12 @@
       <c r="V277" s="2" t="n">
         <v>0.001753946379353561</v>
       </c>
+      <c r="W277" s="1" t="n">
+        <v>0.003989</v>
+      </c>
+      <c r="X277" s="3" t="n">
+        <v>-0.002251125562781256</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -19951,6 +21619,12 @@
       <c r="V278" s="3" t="n">
         <v>-0.0006430868167201865</v>
       </c>
+      <c r="W278" s="1" t="n">
+        <v>1.552</v>
+      </c>
+      <c r="X278" s="3" t="n">
+        <v>-0.001287001287001288</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -20021,6 +21695,12 @@
       <c r="V279" s="3" t="n">
         <v>-0.0009066183136898996</v>
       </c>
+      <c r="W279" s="1" t="n">
+        <v>0.01102</v>
+      </c>
+      <c r="X279" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -20091,6 +21771,12 @@
       <c r="V280" s="2" t="n">
         <v>0.01790668348045403</v>
       </c>
+      <c r="W280" s="1" t="n">
+        <v>0.04043</v>
+      </c>
+      <c r="X280" s="2" t="n">
+        <v>0.001734390485629351</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -20161,6 +21847,12 @@
       <c r="V281" s="3" t="n">
         <v>-0.003447456015216341</v>
       </c>
+      <c r="W281" s="1" t="n">
+        <v>0.08373999999999999</v>
+      </c>
+      <c r="X281" s="3" t="n">
+        <v>-0.001073601336037299</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -20231,6 +21923,12 @@
       <c r="V282" s="2" t="n">
         <v>0.003759398496240709</v>
       </c>
+      <c r="W282" s="1" t="n">
+        <v>0.0266</v>
+      </c>
+      <c r="X282" s="3" t="n">
+        <v>-0.003745318352060032</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -20301,6 +21999,12 @@
       <c r="V283" s="2" t="n">
         <v>0.0028863815271582</v>
       </c>
+      <c r="W283" s="1" t="n">
+        <v>0.07618</v>
+      </c>
+      <c r="X283" s="3" t="n">
+        <v>-0.00340136054421764</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -20371,6 +22075,12 @@
       <c r="V284" s="3" t="n">
         <v>-0.001238390092879153</v>
       </c>
+      <c r="W284" s="1" t="n">
+        <v>0.001604</v>
+      </c>
+      <c r="X284" s="3" t="n">
+        <v>-0.005579665220086863</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -20441,6 +22151,12 @@
       <c r="V285" s="3" t="n">
         <v>-0.001480750246791682</v>
       </c>
+      <c r="W285" s="1" t="n">
+        <v>0.2021</v>
+      </c>
+      <c r="X285" s="3" t="n">
+        <v>-0.0009886307464162419</v>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -20511,6 +22227,12 @@
       <c r="V286" s="3" t="n">
         <v>-0.001493233784414312</v>
       </c>
+      <c r="W286" s="1" t="n">
+        <v>0.10675</v>
+      </c>
+      <c r="X286" s="3" t="n">
+        <v>-0.002243200299093411</v>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -20581,6 +22303,12 @@
       <c r="V287" s="2" t="n">
         <v>0.0005770340450086319</v>
       </c>
+      <c r="W287" s="1" t="n">
+        <v>0.01743</v>
+      </c>
+      <c r="X287" s="2" t="n">
+        <v>0.00519031141868511</v>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -20651,6 +22379,12 @@
       <c r="V288" s="3" t="n">
         <v>-0.003306878306878287</v>
       </c>
+      <c r="W288" s="1" t="n">
+        <v>0.01504</v>
+      </c>
+      <c r="X288" s="3" t="n">
+        <v>-0.001990710019907134</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -20721,6 +22455,12 @@
       <c r="V289" s="2" t="n">
         <v>0.001238390092879207</v>
       </c>
+      <c r="W289" s="1" t="n">
+        <v>0.01616</v>
+      </c>
+      <c r="X289" s="3" t="n">
+        <v>-0.0006184291898577361</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -20791,6 +22531,12 @@
       <c r="V290" s="2" t="n">
         <v>0.001323334803705388</v>
       </c>
+      <c r="W290" s="1" t="n">
+        <v>2.258</v>
+      </c>
+      <c r="X290" s="3" t="n">
+        <v>-0.005286343612334807</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -20861,6 +22607,12 @@
       <c r="V291" s="2" t="n">
         <v>0.002049180327868879</v>
       </c>
+      <c r="W291" s="1" t="n">
+        <v>0.4401</v>
+      </c>
+      <c r="X291" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -20931,6 +22683,12 @@
       <c r="V292" s="2" t="n">
         <v>0.002317497103128623</v>
       </c>
+      <c r="W292" s="1" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="X292" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -21001,6 +22759,12 @@
       <c r="V293" s="3" t="n">
         <v>-0.01168316831683169</v>
       </c>
+      <c r="W293" s="1" t="n">
+        <v>0.0499</v>
+      </c>
+      <c r="X293" s="3" t="n">
+        <v>-0.0002003606491685646</v>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -21071,6 +22835,12 @@
       <c r="V294" s="3" t="n">
         <v>-0.0006304176516944404</v>
       </c>
+      <c r="W294" s="1" t="n">
+        <v>0.06331000000000001</v>
+      </c>
+      <c r="X294" s="3" t="n">
+        <v>-0.001577038322031052</v>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -21141,6 +22911,12 @@
       <c r="V295" s="3" t="n">
         <v>-0.001924927815206976</v>
       </c>
+      <c r="W295" s="1" t="n">
+        <v>0.0004132</v>
+      </c>
+      <c r="X295" s="3" t="n">
+        <v>-0.003857280617164862</v>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -21211,6 +22987,12 @@
       <c r="V296" s="2" t="n">
         <v>0.001600256040966577</v>
       </c>
+      <c r="W296" s="1" t="n">
+        <v>62.47</v>
+      </c>
+      <c r="X296" s="3" t="n">
+        <v>-0.001917239175587227</v>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -21281,6 +23063,12 @@
       <c r="V297" s="3" t="n">
         <v>-0.001022494887525592</v>
       </c>
+      <c r="W297" s="1" t="n">
+        <v>0.0977</v>
+      </c>
+      <c r="X297" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -21351,6 +23139,12 @@
       <c r="V298" s="3" t="n">
         <v>-0.00104384133611694</v>
       </c>
+      <c r="W298" s="1" t="n">
+        <v>0.0956</v>
+      </c>
+      <c r="X298" s="3" t="n">
+        <v>-0.001044932079414723</v>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -21421,6 +23215,12 @@
       <c r="V299" s="2" t="n">
         <v>0.00342288144383374</v>
       </c>
+      <c r="W299" s="1" t="n">
+        <v>0.09594</v>
+      </c>
+      <c r="X299" s="3" t="n">
+        <v>-0.008269588587967841</v>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -21491,6 +23291,12 @@
       <c r="V300" s="2" t="n">
         <v>0.00213675213675205</v>
       </c>
+      <c r="W300" s="1" t="n">
+        <v>0.01875</v>
+      </c>
+      <c r="X300" s="3" t="n">
+        <v>-0.0005330490405117054</v>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -21561,6 +23367,12 @@
       <c r="V301" s="3" t="n">
         <v>-0.003734129947722287</v>
       </c>
+      <c r="W301" s="1" t="n">
+        <v>0.01332</v>
+      </c>
+      <c r="X301" s="3" t="n">
+        <v>-0.001499250374812533</v>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -21631,6 +23443,12 @@
       <c r="V302" s="3" t="n">
         <v>-0.0002291475710357774</v>
       </c>
+      <c r="W302" s="1" t="n">
+        <v>0.004375</v>
+      </c>
+      <c r="X302" s="2" t="n">
+        <v>0.002750401100160606</v>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -21701,6 +23519,12 @@
       <c r="V303" s="3" t="n">
         <v>-0.007518796992481269</v>
       </c>
+      <c r="W303" s="1" t="n">
+        <v>0.00923</v>
+      </c>
+      <c r="X303" s="3" t="n">
+        <v>-0.001082251082251038</v>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -21771,6 +23595,12 @@
       <c r="V304" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="W304" s="1" t="n">
+        <v>4.711</v>
+      </c>
+      <c r="X304" s="3" t="n">
+        <v>-0.0006364022061943388</v>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -21841,6 +23671,12 @@
       <c r="V305" s="2" t="n">
         <v>0.001696832579185517</v>
       </c>
+      <c r="W305" s="1" t="n">
+        <v>0.053</v>
+      </c>
+      <c r="X305" s="3" t="n">
+        <v>-0.002446828533785021</v>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -21911,6 +23747,12 @@
       <c r="V306" s="2" t="n">
         <v>0.0005154639175256925</v>
       </c>
+      <c r="W306" s="1" t="n">
+        <v>0.0582</v>
+      </c>
+      <c r="X306" s="3" t="n">
+        <v>-0.0005151983513651951</v>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -21981,6 +23823,12 @@
       <c r="V307" s="2" t="n">
         <v>0.0005733944954127809</v>
       </c>
+      <c r="W307" s="1" t="n">
+        <v>0.1741</v>
+      </c>
+      <c r="X307" s="3" t="n">
+        <v>-0.002292263610315093</v>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -22051,6 +23899,12 @@
       <c r="V308" s="3" t="n">
         <v>-0.01132975551580205</v>
       </c>
+      <c r="W308" s="1" t="n">
+        <v>0.04943</v>
+      </c>
+      <c r="X308" s="3" t="n">
+        <v>-0.006232408524326453</v>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -22121,6 +23975,12 @@
       <c r="V309" s="2" t="n">
         <v>0.002396313364055241</v>
       </c>
+      <c r="W309" s="1" t="n">
+        <v>0.5427</v>
+      </c>
+      <c r="X309" s="3" t="n">
+        <v>-0.002022802500919437</v>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -22191,6 +24051,12 @@
       <c r="V310" s="3" t="n">
         <v>-0.004098360655737716</v>
       </c>
+      <c r="W310" s="1" t="n">
+        <v>0.00243</v>
+      </c>
+      <c r="X310" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -22261,6 +24127,12 @@
       <c r="V311" s="3" t="n">
         <v>-0.0002821272393848533</v>
       </c>
+      <c r="W311" s="1" t="n">
+        <v>0.07077</v>
+      </c>
+      <c r="X311" s="3" t="n">
+        <v>-0.001411034288133242</v>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -22331,6 +24203,12 @@
       <c r="V312" s="3" t="n">
         <v>-0.001559193674128343</v>
       </c>
+      <c r="W312" s="1" t="n">
+        <v>0.008952999999999999</v>
+      </c>
+      <c r="X312" s="3" t="n">
+        <v>-0.001338538761851823</v>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -22401,6 +24279,12 @@
       <c r="V313" s="3" t="n">
         <v>-0.001083784910379396</v>
       </c>
+      <c r="W313" s="1" t="n">
+        <v>0.011999</v>
+      </c>
+      <c r="X313" s="2" t="n">
+        <v>0.001418794858955071</v>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -22471,6 +24355,12 @@
       <c r="V314" s="3" t="n">
         <v>-0.002135839384878319</v>
       </c>
+      <c r="W314" s="1" t="n">
+        <v>0.02335</v>
+      </c>
+      <c r="X314" s="3" t="n">
+        <v>-0.0004280821917808045</v>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -22541,6 +24431,12 @@
       <c r="V315" s="2" t="n">
         <v>0.002816901408450589</v>
       </c>
+      <c r="W315" s="1" t="n">
+        <v>0.0071</v>
+      </c>
+      <c r="X315" s="3" t="n">
+        <v>-0.00280898876404483</v>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -22611,6 +24507,12 @@
       <c r="V316" s="3" t="n">
         <v>-0.002301495972382008</v>
       </c>
+      <c r="W316" s="1" t="n">
+        <v>0.2598</v>
+      </c>
+      <c r="X316" s="3" t="n">
+        <v>-0.001153402537485669</v>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -22681,6 +24583,12 @@
       <c r="V317" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="W317" s="1" t="n">
+        <v>1.12e-05</v>
+      </c>
+      <c r="X317" s="2" t="n">
+        <v>0.009009009009008922</v>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -22751,6 +24659,12 @@
       <c r="V318" s="2" t="n">
         <v>0.001959068776628099</v>
       </c>
+      <c r="W318" s="1" t="n">
+        <v>0.052626</v>
+      </c>
+      <c r="X318" s="3" t="n">
+        <v>-0.00100609350974767</v>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -22821,6 +24735,12 @@
       <c r="V319" s="2" t="n">
         <v>0.0007847240387131114</v>
       </c>
+      <c r="W319" s="1" t="n">
+        <v>0.03824</v>
+      </c>
+      <c r="X319" s="3" t="n">
+        <v>-0.0005227391531625505</v>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -22891,6 +24811,12 @@
       <c r="V320" s="2" t="n">
         <v>0.001324698263173436</v>
       </c>
+      <c r="W320" s="1" t="n">
+        <v>0.006797</v>
+      </c>
+      <c r="X320" s="3" t="n">
+        <v>-0.0008819638394825707</v>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -22961,6 +24887,12 @@
       <c r="V321" s="3" t="n">
         <v>-0.001545595054095755</v>
       </c>
+      <c r="W321" s="1" t="n">
+        <v>4.519</v>
+      </c>
+      <c r="X321" s="3" t="n">
+        <v>-0.0006634232640424842</v>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -23031,6 +24963,12 @@
       <c r="V322" s="2" t="n">
         <v>0.0005192107995846895</v>
       </c>
+      <c r="W322" s="1" t="n">
+        <v>1.921</v>
+      </c>
+      <c r="X322" s="3" t="n">
+        <v>-0.003113648157758176</v>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -23101,6 +25039,12 @@
       <c r="V323" s="2" t="n">
         <v>0.0114422941093374</v>
       </c>
+      <c r="W323" s="1" t="n">
+        <v>0.007138</v>
+      </c>
+      <c r="X323" s="3" t="n">
+        <v>-0.003072625698323946</v>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -23171,6 +25115,12 @@
       <c r="V324" s="2" t="n">
         <v>0.002177463255307478</v>
       </c>
+      <c r="W324" s="1" t="n">
+        <v>0.01835</v>
+      </c>
+      <c r="X324" s="3" t="n">
+        <v>-0.003259098316132404</v>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -23241,6 +25191,12 @@
       <c r="V325" s="2" t="n">
         <v>0.001709401709401792</v>
       </c>
+      <c r="W325" s="1" t="n">
+        <v>0.4113</v>
+      </c>
+      <c r="X325" s="2" t="n">
+        <v>0.002681618722574329</v>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -23311,6 +25267,12 @@
       <c r="V326" s="3" t="n">
         <v>-0.0009715475364329209</v>
       </c>
+      <c r="W326" s="1" t="n">
+        <v>0.007177</v>
+      </c>
+      <c r="X326" s="3" t="n">
+        <v>-0.002917477076965849</v>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -23381,6 +25343,12 @@
       <c r="V327" s="2" t="n">
         <v>0.004721930745015803</v>
       </c>
+      <c r="W327" s="1" t="n">
+        <v>0.1906</v>
+      </c>
+      <c r="X327" s="3" t="n">
+        <v>-0.004699738903394318</v>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -23451,6 +25419,12 @@
       <c r="V328" s="2" t="n">
         <v>0.002351432235998268</v>
       </c>
+      <c r="W328" s="1" t="n">
+        <v>0.4673</v>
+      </c>
+      <c r="X328" s="3" t="n">
+        <v>-0.003412241416080167</v>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -23521,6 +25495,12 @@
       <c r="V329" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="W329" s="1" t="n">
+        <v>0.01342</v>
+      </c>
+      <c r="X329" s="3" t="n">
+        <v>-0.002230483271375503</v>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -23591,6 +25571,12 @@
       <c r="V330" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="W330" s="1" t="n">
+        <v>0.1132</v>
+      </c>
+      <c r="X330" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -23661,6 +25647,12 @@
       <c r="V331" s="3" t="n">
         <v>-0.002144860584061983</v>
       </c>
+      <c r="W331" s="1" t="n">
+        <v>0.6025</v>
+      </c>
+      <c r="X331" s="3" t="n">
+        <v>-0.003802910052910001</v>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -23731,6 +25723,12 @@
       <c r="V332" s="3" t="n">
         <v>-0.0009182736455463808</v>
       </c>
+      <c r="W332" s="1" t="n">
+        <v>0.30382</v>
+      </c>
+      <c r="X332" s="3" t="n">
+        <v>-0.002691701680672409</v>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -23801,6 +25799,12 @@
       <c r="V333" s="2" t="n">
         <v>0.002129774243930106</v>
       </c>
+      <c r="W333" s="1" t="n">
+        <v>0.07063999999999999</v>
+      </c>
+      <c r="X333" s="2" t="n">
+        <v>0.000850099178237328</v>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -23871,6 +25875,12 @@
       <c r="V334" s="3" t="n">
         <v>-0.002720998141757509</v>
       </c>
+      <c r="W334" s="1" t="n">
+        <v>0.15109</v>
+      </c>
+      <c r="X334" s="2" t="n">
+        <v>0.005456844346842452</v>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -23941,6 +25951,12 @@
       <c r="V335" s="3" t="n">
         <v>-0.0006381620931717724</v>
       </c>
+      <c r="W335" s="1" t="n">
+        <v>0.1565</v>
+      </c>
+      <c r="X335" s="3" t="n">
+        <v>-0.0006385696040867751</v>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -24011,6 +26027,12 @@
       <c r="V336" s="2" t="n">
         <v>0.001150747986190897</v>
       </c>
+      <c r="W336" s="1" t="n">
+        <v>0.1737</v>
+      </c>
+      <c r="X336" s="3" t="n">
+        <v>-0.001724137931034453</v>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -24081,6 +26103,12 @@
       <c r="V337" s="3" t="n">
         <v>-0.008639842014317358</v>
       </c>
+      <c r="W337" s="1" t="n">
+        <v>0.04016</v>
+      </c>
+      <c r="X337" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -24151,6 +26179,12 @@
       <c r="V338" s="2" t="n">
         <v>0.001702932828760705</v>
       </c>
+      <c r="W338" s="1" t="n">
+        <v>0.005274</v>
+      </c>
+      <c r="X338" s="3" t="n">
+        <v>-0.003777861730260682</v>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -24221,6 +26255,12 @@
       <c r="V339" s="2" t="n">
         <v>0.002325581395348877</v>
       </c>
+      <c r="W339" s="1" t="n">
+        <v>0.05143</v>
+      </c>
+      <c r="X339" s="3" t="n">
+        <v>-0.005607115235885645</v>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -24291,6 +26331,12 @@
       <c r="V340" s="3" t="n">
         <v>-0.001915202747325403</v>
       </c>
+      <c r="W340" s="1" t="n">
+        <v>0.15072</v>
+      </c>
+      <c r="X340" s="3" t="n">
+        <v>-0.002712896182094844</v>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -24361,6 +26407,12 @@
       <c r="V341" s="2" t="n">
         <v>0.002234490010515293</v>
       </c>
+      <c r="W341" s="1" t="n">
+        <v>7.62</v>
+      </c>
+      <c r="X341" s="3" t="n">
+        <v>-0.0006557377049180188</v>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -24431,6 +26483,12 @@
       <c r="V342" s="3" t="n">
         <v>-0.002132196162046843</v>
       </c>
+      <c r="W342" s="1" t="n">
+        <v>0.3288</v>
+      </c>
+      <c r="X342" s="2" t="n">
+        <v>0.003663003663003598</v>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -24501,6 +26559,12 @@
       <c r="V343" s="2" t="n">
         <v>0.005544354838709627</v>
       </c>
+      <c r="W343" s="1" t="n">
+        <v>0.01991</v>
+      </c>
+      <c r="X343" s="3" t="n">
+        <v>-0.002005012531328239</v>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -24571,6 +26635,12 @@
       <c r="V344" s="3" t="n">
         <v>-0.001376146788990878</v>
       </c>
+      <c r="W344" s="1" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="X344" s="3" t="n">
+        <v>-0.00321543408360134</v>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -24641,6 +26711,12 @@
       <c r="V345" s="3" t="n">
         <v>-0.002362204724409538</v>
       </c>
+      <c r="W345" s="1" t="n">
+        <v>1.264</v>
+      </c>
+      <c r="X345" s="3" t="n">
+        <v>-0.00236779794790836</v>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -24711,6 +26787,12 @@
       <c r="V346" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="W346" s="1" t="n">
+        <v>0.005161</v>
+      </c>
+      <c r="X346" s="3" t="n">
+        <v>-0.00212683681361187</v>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -24781,6 +26863,12 @@
       <c r="V347" s="2" t="n">
         <v>0.001747946163258222</v>
       </c>
+      <c r="W347" s="1" t="n">
+        <v>0.05723</v>
+      </c>
+      <c r="X347" s="3" t="n">
+        <v>-0.001395916942941838</v>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -24851,6 +26939,12 @@
       <c r="V348" s="2" t="n">
         <v>0.003144654088050186</v>
       </c>
+      <c r="W348" s="1" t="n">
+        <v>0.1273</v>
+      </c>
+      <c r="X348" s="3" t="n">
+        <v>-0.002351097178683345</v>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -24921,6 +27015,12 @@
       <c r="V349" s="3" t="n">
         <v>-0.001558381591857832</v>
       </c>
+      <c r="W349" s="1" t="n">
+        <v>5183.8</v>
+      </c>
+      <c r="X349" s="3" t="n">
+        <v>-0.00111761985509484</v>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -24991,6 +27091,12 @@
       <c r="V350" s="3" t="n">
         <v>-0.0010744985673352</v>
       </c>
+      <c r="W350" s="1" t="n">
+        <v>0.02789</v>
+      </c>
+      <c r="X350" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -25061,6 +27167,12 @@
       <c r="V351" s="3" t="n">
         <v>-0.002871500358937459</v>
       </c>
+      <c r="W351" s="1" t="n">
+        <v>0.001395</v>
+      </c>
+      <c r="X351" s="2" t="n">
+        <v>0.004319654427645737</v>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -25131,6 +27243,12 @@
       <c r="V352" s="3" t="n">
         <v>-0.0006361323155218233</v>
       </c>
+      <c r="W352" s="1" t="n">
+        <v>0.01571</v>
+      </c>
+      <c r="X352" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -25201,6 +27319,12 @@
       <c r="V353" s="2" t="n">
         <v>0.0004799232122859103</v>
       </c>
+      <c r="W353" s="1" t="n">
+        <v>6.289</v>
+      </c>
+      <c r="X353" s="2" t="n">
+        <v>0.005596418292292956</v>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -25271,6 +27395,12 @@
       <c r="V354" s="2" t="n">
         <v>0.0006968641114983746</v>
       </c>
+      <c r="W354" s="1" t="n">
+        <v>0.287</v>
+      </c>
+      <c r="X354" s="3" t="n">
+        <v>-0.000696378830083682</v>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -25341,6 +27471,12 @@
       <c r="V355" s="2" t="n">
         <v>0.0009636232233196428</v>
       </c>
+      <c r="W355" s="1" t="n">
+        <v>0.04148</v>
+      </c>
+      <c r="X355" s="3" t="n">
+        <v>-0.00168471720818276</v>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -25411,6 +27547,12 @@
       <c r="V356" s="3" t="n">
         <v>-0.0001768033946251083</v>
       </c>
+      <c r="W356" s="1" t="n">
+        <v>0.11337</v>
+      </c>
+      <c r="X356" s="2" t="n">
+        <v>0.002387267904509217</v>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -25481,6 +27623,12 @@
       <c r="V357" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="W357" s="1" t="n">
+        <v>0.005259</v>
+      </c>
+      <c r="X357" s="2" t="n">
+        <v>0.006122058542184792</v>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -25551,6 +27699,12 @@
       <c r="V358" s="3" t="n">
         <v>-0.003225806451612846</v>
       </c>
+      <c r="W358" s="1" t="n">
+        <v>0.1846</v>
+      </c>
+      <c r="X358" s="3" t="n">
+        <v>-0.004314994606256866</v>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -25621,6 +27775,12 @@
       <c r="V359" s="3" t="n">
         <v>-0.00122774708410054</v>
       </c>
+      <c r="W359" s="1" t="n">
+        <v>0.1626</v>
+      </c>
+      <c r="X359" s="3" t="n">
+        <v>-0.0006146281499693714</v>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -25691,6 +27851,12 @@
       <c r="V360" s="3" t="n">
         <v>-0.00117192077815543</v>
       </c>
+      <c r="W360" s="1" t="n">
+        <v>0.08511000000000001</v>
+      </c>
+      <c r="X360" s="3" t="n">
+        <v>-0.001407954945441689</v>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -25761,6 +27927,12 @@
       <c r="V361" s="3" t="n">
         <v>-0.002617801047120426</v>
       </c>
+      <c r="W361" s="1" t="n">
+        <v>0.00764</v>
+      </c>
+      <c r="X361" s="2" t="n">
+        <v>0.002624671916010506</v>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -25831,6 +28003,12 @@
       <c r="V362" s="2" t="n">
         <v>0.0004698144233027436</v>
       </c>
+      <c r="W362" s="1" t="n">
+        <v>0.4256</v>
+      </c>
+      <c r="X362" s="3" t="n">
+        <v>-0.0007043907020427858</v>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -25901,6 +28079,12 @@
       <c r="V363" s="3" t="n">
         <v>-0.004486671945104341</v>
       </c>
+      <c r="W363" s="1" t="n">
+        <v>3.773</v>
+      </c>
+      <c r="X363" s="2" t="n">
+        <v>0.0002651113467657301</v>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -25971,6 +28155,12 @@
       <c r="V364" s="2" t="n">
         <v>0.000908265213442288</v>
       </c>
+      <c r="W364" s="1" t="n">
+        <v>0.01098</v>
+      </c>
+      <c r="X364" s="3" t="n">
+        <v>-0.003629764065335763</v>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -26041,6 +28231,12 @@
       <c r="V365" s="2" t="n">
         <v>0.0001817190623295679</v>
       </c>
+      <c r="W365" s="1" t="n">
+        <v>0.05501</v>
+      </c>
+      <c r="X365" s="3" t="n">
+        <v>-0.0005450581395347985</v>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -26111,6 +28307,12 @@
       <c r="V366" s="3" t="n">
         <v>-0.01934651762682713</v>
       </c>
+      <c r="W366" s="1" t="n">
+        <v>0.02283</v>
+      </c>
+      <c r="X366" s="2" t="n">
+        <v>0.0008768084173607709</v>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -26181,6 +28383,12 @@
       <c r="V367" s="2" t="n">
         <v>0.007390983000739117</v>
       </c>
+      <c r="W367" s="1" t="n">
+        <v>0.001353</v>
+      </c>
+      <c r="X367" s="3" t="n">
+        <v>-0.007336757153338243</v>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -26251,6 +28459,12 @@
       <c r="V368" s="2" t="n">
         <v>0.0003490401396162112</v>
       </c>
+      <c r="W368" s="1" t="n">
+        <v>0.2865</v>
+      </c>
+      <c r="X368" s="3" t="n">
+        <v>-0.0003489183531055286</v>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -26321,6 +28535,12 @@
       <c r="V369" s="3" t="n">
         <v>-0.003765465303926876</v>
       </c>
+      <c r="W369" s="1" t="n">
+        <v>0.01857</v>
+      </c>
+      <c r="X369" s="2" t="n">
+        <v>0.002699784017278695</v>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -26391,6 +28611,12 @@
       <c r="V370" s="3" t="n">
         <v>-0.005239030779305755</v>
       </c>
+      <c r="W370" s="1" t="n">
+        <v>0.19676</v>
+      </c>
+      <c r="X370" s="3" t="n">
+        <v>-0.003595482858155751</v>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -26461,6 +28687,12 @@
       <c r="V371" s="2" t="n">
         <v>0.01333333333333335</v>
       </c>
+      <c r="W371" s="1" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="X371" s="3" t="n">
+        <v>-0.01315789473684212</v>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -26531,6 +28763,12 @@
       <c r="V372" s="3" t="n">
         <v>-0.0009505703422053504</v>
       </c>
+      <c r="W372" s="1" t="n">
+        <v>0.1048</v>
+      </c>
+      <c r="X372" s="3" t="n">
+        <v>-0.002854424357754469</v>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -26601,6 +28839,12 @@
       <c r="V373" s="2" t="n">
         <v>0.0009049773755656787</v>
       </c>
+      <c r="W373" s="1" t="n">
+        <v>0.06593</v>
+      </c>
+      <c r="X373" s="3" t="n">
+        <v>-0.006479807112718503</v>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -26671,6 +28915,12 @@
       <c r="V374" s="3" t="n">
         <v>-0.001575630252100936</v>
       </c>
+      <c r="W374" s="1" t="n">
+        <v>0.007588</v>
+      </c>
+      <c r="X374" s="3" t="n">
+        <v>-0.002104155707522294</v>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -26741,6 +28991,12 @@
       <c r="V375" s="3" t="n">
         <v>-0.0006289308176099936</v>
       </c>
+      <c r="W375" s="1" t="n">
+        <v>0.1587</v>
+      </c>
+      <c r="X375" s="3" t="n">
+        <v>-0.001258653241032132</v>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -26811,6 +29067,12 @@
       <c r="V376" s="3" t="n">
         <v>-0.0002936857562408613</v>
       </c>
+      <c r="W376" s="1" t="n">
+        <v>0.003408</v>
+      </c>
+      <c r="X376" s="2" t="n">
+        <v>0.001175088131609899</v>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -26881,6 +29143,12 @@
       <c r="V377" s="2" t="n">
         <v>0.01234567901234582</v>
       </c>
+      <c r="W377" s="1" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="X377" s="2" t="n">
+        <v>0.006097560975609719</v>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -26951,6 +29219,12 @@
       <c r="V378" s="3" t="n">
         <v>-0.01135371179039301</v>
       </c>
+      <c r="W378" s="1" t="n">
+        <v>0.01123</v>
+      </c>
+      <c r="X378" s="3" t="n">
+        <v>-0.007950530035335671</v>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -27021,6 +29295,12 @@
       <c r="V379" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="W379" s="1" t="n">
+        <v>0.0214</v>
+      </c>
+      <c r="X379" s="3" t="n">
+        <v>-0.0004670714619336569</v>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -27091,6 +29371,12 @@
       <c r="V380" s="2" t="n">
         <v>0.004259850905218143</v>
       </c>
+      <c r="W380" s="1" t="n">
+        <v>0.01879</v>
+      </c>
+      <c r="X380" s="3" t="n">
+        <v>-0.003711558854718831</v>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -27161,6 +29447,12 @@
       <c r="V381" s="3" t="n">
         <v>-0.001661129568106245</v>
       </c>
+      <c r="W381" s="1" t="n">
+        <v>0.1198</v>
+      </c>
+      <c r="X381" s="3" t="n">
+        <v>-0.003327787021630595</v>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -27231,6 +29523,12 @@
       <c r="V382" s="3" t="n">
         <v>-0.004721753794266367</v>
       </c>
+      <c r="W382" s="1" t="n">
+        <v>0.02961</v>
+      </c>
+      <c r="X382" s="2" t="n">
+        <v>0.003388681802778698</v>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -27301,6 +29599,12 @@
       <c r="V383" s="3" t="n">
         <v>-0.0007639419404124975</v>
       </c>
+      <c r="W383" s="1" t="n">
+        <v>0.006567</v>
+      </c>
+      <c r="X383" s="2" t="n">
+        <v>0.004128440366972495</v>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -27371,6 +29675,12 @@
       <c r="V384" s="3" t="n">
         <v>-0.001438159156279903</v>
       </c>
+      <c r="W384" s="1" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="X384" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -27441,6 +29751,12 @@
       <c r="V385" s="3" t="n">
         <v>-0.0003941663381947182</v>
       </c>
+      <c r="W385" s="1" t="n">
+        <v>2531</v>
+      </c>
+      <c r="X385" s="3" t="n">
+        <v>-0.001971608832807571</v>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -27511,6 +29827,12 @@
       <c r="V386" s="3" t="n">
         <v>-0.001510574018126862</v>
       </c>
+      <c r="W386" s="1" t="n">
+        <v>0.1983</v>
+      </c>
+      <c r="X386" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -27581,6 +29903,12 @@
       <c r="V387" s="3" t="n">
         <v>-0.0003529827038475379</v>
       </c>
+      <c r="W387" s="1" t="n">
+        <v>0.0848</v>
+      </c>
+      <c r="X387" s="3" t="n">
+        <v>-0.001883239171374688</v>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -27651,6 +29979,12 @@
       <c r="V388" s="3" t="n">
         <v>-0.003793929712460048</v>
       </c>
+      <c r="W388" s="1" t="n">
+        <v>0.004976</v>
+      </c>
+      <c r="X388" s="3" t="n">
+        <v>-0.002605732611745839</v>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -27721,6 +30055,12 @@
       <c r="V389" s="2" t="n">
         <v>0.00529801324503305</v>
       </c>
+      <c r="W389" s="1" t="n">
+        <v>0.02254</v>
+      </c>
+      <c r="X389" s="3" t="n">
+        <v>-0.01010101010100999</v>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -27791,6 +30131,12 @@
       <c r="V390" s="2" t="n">
         <v>0.0025778306563555</v>
       </c>
+      <c r="W390" s="1" t="n">
+        <v>0.5034</v>
+      </c>
+      <c r="X390" s="3" t="n">
+        <v>-0.004351265822784989</v>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -27861,6 +30207,12 @@
       <c r="V391" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="W391" s="1" t="n">
+        <v>0.000602</v>
+      </c>
+      <c r="X391" s="3" t="n">
+        <v>-0.003970880211780195</v>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -27931,6 +30283,12 @@
       <c r="V392" s="3" t="n">
         <v>-0.0008558712769599697</v>
       </c>
+      <c r="W392" s="1" t="n">
+        <v>0.05842</v>
+      </c>
+      <c r="X392" s="2" t="n">
+        <v>0.0008566044200788321</v>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -28001,6 +30359,12 @@
       <c r="V393" s="2" t="n">
         <v>0.002609019754006835</v>
       </c>
+      <c r="W393" s="1" t="n">
+        <v>0.2694</v>
+      </c>
+      <c r="X393" s="2" t="n">
+        <v>0.001486988847583479</v>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -28071,6 +30435,12 @@
       <c r="V394" s="3" t="n">
         <v>-0.0006081800212863815</v>
       </c>
+      <c r="W394" s="1" t="n">
+        <v>0.006667</v>
+      </c>
+      <c r="X394" s="2" t="n">
+        <v>0.01430092803894726</v>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -28141,6 +30511,12 @@
       <c r="V395" s="2" t="n">
         <v>0.0008710801393728472</v>
       </c>
+      <c r="W395" s="1" t="n">
+        <v>0.1146</v>
+      </c>
+      <c r="X395" s="3" t="n">
+        <v>-0.002610966057441328</v>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -28211,6 +30587,12 @@
       <c r="V396" s="3" t="n">
         <v>-0.002262443438913935</v>
       </c>
+      <c r="W396" s="1" t="n">
+        <v>0.03072</v>
+      </c>
+      <c r="X396" s="3" t="n">
+        <v>-0.00485908649173958</v>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -28281,6 +30663,12 @@
       <c r="V397" s="3" t="n">
         <v>-0.0006631299734747281</v>
       </c>
+      <c r="W397" s="1" t="n">
+        <v>0.1504</v>
+      </c>
+      <c r="X397" s="3" t="n">
+        <v>-0.001990710019907065</v>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -28351,6 +30739,12 @@
       <c r="V398" s="3" t="n">
         <v>-0.001210653753026664</v>
       </c>
+      <c r="W398" s="1" t="n">
+        <v>0.003302</v>
+      </c>
+      <c r="X398" s="2" t="n">
+        <v>0.0006060606060605551</v>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -28421,6 +30815,12 @@
       <c r="V399" s="2" t="n">
         <v>0.01738185768604024</v>
       </c>
+      <c r="W399" s="1" t="n">
+        <v>0.01848</v>
+      </c>
+      <c r="X399" s="3" t="n">
+        <v>-0.01334757074212494</v>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -28491,6 +30891,12 @@
       <c r="V400" s="3" t="n">
         <v>-0.01026811180832858</v>
       </c>
+      <c r="W400" s="1" t="n">
+        <v>0.006977</v>
+      </c>
+      <c r="X400" s="2" t="n">
+        <v>0.005331412103746355</v>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -28561,6 +30967,12 @@
       <c r="V401" s="2" t="n">
         <v>0.0008587376556461899</v>
       </c>
+      <c r="W401" s="1" t="n">
+        <v>0.006959</v>
+      </c>
+      <c r="X401" s="3" t="n">
+        <v>-0.004862004862004887</v>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -28631,6 +31043,12 @@
       <c r="V402" s="2" t="n">
         <v>0.0002500000000000332</v>
       </c>
+      <c r="W402" s="1" t="n">
+        <v>0.00801</v>
+      </c>
+      <c r="X402" s="2" t="n">
+        <v>0.0009997500624842949</v>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -28701,6 +31119,12 @@
       <c r="V403" s="3" t="n">
         <v>-0.003250050782043478</v>
       </c>
+      <c r="W403" s="1" t="n">
+        <v>0.04909</v>
+      </c>
+      <c r="X403" s="2" t="n">
+        <v>0.00040758100672507</v>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -28771,6 +31195,12 @@
       <c r="V404" s="2" t="n">
         <v>0.004454944313196043</v>
       </c>
+      <c r="W404" s="1" t="n">
+        <v>0.14852</v>
+      </c>
+      <c r="X404" s="3" t="n">
+        <v>-0.001948793763859853</v>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -28841,6 +31271,12 @@
       <c r="V405" s="3" t="n">
         <v>-0.003259604190919703</v>
       </c>
+      <c r="W405" s="1" t="n">
+        <v>0.0428</v>
+      </c>
+      <c r="X405" s="3" t="n">
+        <v>-0.0002335902826443135</v>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -28911,6 +31347,12 @@
       <c r="V406" s="3" t="n">
         <v>-0.0006265664160401472</v>
       </c>
+      <c r="W406" s="1" t="n">
+        <v>0.4778</v>
+      </c>
+      <c r="X406" s="3" t="n">
+        <v>-0.001462904911180728</v>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -28981,6 +31423,12 @@
       <c r="V407" s="2" t="n">
         <v>0.0002029632636493944</v>
       </c>
+      <c r="W407" s="1" t="n">
+        <v>0.0004934</v>
+      </c>
+      <c r="X407" s="2" t="n">
+        <v>0.001217532467532277</v>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -29051,6 +31499,12 @@
       <c r="V408" s="2" t="n">
         <v>0.0008103727714748454</v>
       </c>
+      <c r="W408" s="1" t="n">
+        <v>0.01237</v>
+      </c>
+      <c r="X408" s="2" t="n">
+        <v>0.001619433198380641</v>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -29121,6 +31575,12 @@
       <c r="V409" s="3" t="n">
         <v>-0.003460207612456715</v>
       </c>
+      <c r="W409" s="1" t="n">
+        <v>0.3185</v>
+      </c>
+      <c r="X409" s="2" t="n">
+        <v>0.00536616161616155</v>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -29191,6 +31651,12 @@
       <c r="V410" s="2" t="n">
         <v>0.002639788816894624</v>
       </c>
+      <c r="W410" s="1" t="n">
+        <v>0.04169</v>
+      </c>
+      <c r="X410" s="3" t="n">
+        <v>-0.002154140737194825</v>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -29261,6 +31727,12 @@
       <c r="V411" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="W411" s="1" t="n">
+        <v>0.02969</v>
+      </c>
+      <c r="X411" s="2" t="n">
+        <v>0.0003369272237196628</v>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
@@ -29331,6 +31803,12 @@
       <c r="V412" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="W412" s="1" t="n">
+        <v>0.004573</v>
+      </c>
+      <c r="X412" s="3" t="n">
+        <v>-0.0006555944055944926</v>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -29401,6 +31879,12 @@
       <c r="V413" s="2" t="n">
         <v>0.003191065017949832</v>
       </c>
+      <c r="W413" s="1" t="n">
+        <v>0.2508</v>
+      </c>
+      <c r="X413" s="3" t="n">
+        <v>-0.002783300198807071</v>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -29471,6 +31955,12 @@
       <c r="V414" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="W414" s="1" t="n">
+        <v>1.278</v>
+      </c>
+      <c r="X414" s="3" t="n">
+        <v>-0.0007818608287723924</v>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -29541,6 +32031,12 @@
       <c r="V415" s="2" t="n">
         <v>0.001834189288334517</v>
       </c>
+      <c r="W415" s="1" t="n">
+        <v>2.717</v>
+      </c>
+      <c r="X415" s="3" t="n">
+        <v>-0.005126327352618012</v>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -29611,6 +32107,12 @@
       <c r="V416" s="2" t="n">
         <v>0.004661280298321857</v>
       </c>
+      <c r="W416" s="1" t="n">
+        <v>0.03239</v>
+      </c>
+      <c r="X416" s="2" t="n">
+        <v>0.001855861429013439</v>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -29681,6 +32183,12 @@
       <c r="V417" s="3" t="n">
         <v>-0.006025608837559557</v>
       </c>
+      <c r="W417" s="1" t="n">
+        <v>0.03966</v>
+      </c>
+      <c r="X417" s="2" t="n">
+        <v>0.001768123263450382</v>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -29751,6 +32259,12 @@
       <c r="V418" s="2" t="n">
         <v>0.0009202050742737034</v>
       </c>
+      <c r="W418" s="1" t="n">
+        <v>0.07599</v>
+      </c>
+      <c r="X418" s="3" t="n">
+        <v>-0.001970055161544488</v>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -29821,6 +32335,12 @@
       <c r="V419" s="3" t="n">
         <v>-0.001508295625942623</v>
       </c>
+      <c r="W419" s="1" t="n">
+        <v>0.00661</v>
+      </c>
+      <c r="X419" s="3" t="n">
+        <v>-0.001510574018126827</v>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -29891,6 +32411,12 @@
       <c r="V420" s="3" t="n">
         <v>-0.003389830508474517</v>
       </c>
+      <c r="W420" s="1" t="n">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="X420" s="3" t="n">
+        <v>-0.00226757369614519</v>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -29961,6 +32487,12 @@
       <c r="V421" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="W421" s="1" t="n">
+        <v>0.2391</v>
+      </c>
+      <c r="X421" s="3" t="n">
+        <v>-0.002086811352253758</v>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
@@ -30031,6 +32563,12 @@
       <c r="V422" s="2" t="n">
         <v>0.005154639175257701</v>
       </c>
+      <c r="W422" s="1" t="n">
+        <v>0.0198</v>
+      </c>
+      <c r="X422" s="2" t="n">
+        <v>0.01538461538461547</v>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -30101,6 +32639,12 @@
       <c r="V423" s="2" t="n">
         <v>0.001325381047051065</v>
       </c>
+      <c r="W423" s="1" t="n">
+        <v>0.1507</v>
+      </c>
+      <c r="X423" s="3" t="n">
+        <v>-0.002647253474520261</v>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -30171,6 +32715,12 @@
       <c r="V424" s="2" t="n">
         <v>0.003358925143953887</v>
       </c>
+      <c r="W424" s="1" t="n">
+        <v>0.0002091</v>
+      </c>
+      <c r="X424" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -30241,6 +32791,12 @@
       <c r="V425" s="3" t="n">
         <v>-0.0008077544426493456</v>
       </c>
+      <c r="W425" s="1" t="n">
+        <v>1.239</v>
+      </c>
+      <c r="X425" s="2" t="n">
+        <v>0.001616814874696848</v>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
@@ -30311,6 +32867,12 @@
       <c r="V426" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="W426" s="1" t="n">
+        <v>1.413</v>
+      </c>
+      <c r="X426" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -30381,6 +32943,12 @@
       <c r="V427" s="3" t="n">
         <v>-0.0005141388174806988</v>
       </c>
+      <c r="W427" s="1" t="n">
+        <v>0.01943</v>
+      </c>
+      <c r="X427" s="3" t="n">
+        <v>-0.0005144032921810491</v>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
@@ -30451,6 +33019,12 @@
       <c r="V428" s="2" t="n">
         <v>0.002574977279612292</v>
       </c>
+      <c r="W428" s="1" t="n">
+        <v>0.066</v>
+      </c>
+      <c r="X428" s="3" t="n">
+        <v>-0.002870524248375823</v>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
@@ -30521,6 +33095,12 @@
       <c r="V429" s="3" t="n">
         <v>-0.001512859304084763</v>
       </c>
+      <c r="W429" s="1" t="n">
+        <v>0.1318</v>
+      </c>
+      <c r="X429" s="3" t="n">
+        <v>-0.001515151515151559</v>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
@@ -30591,6 +33171,12 @@
       <c r="V430" s="2" t="n">
         <v>0.0009072763563781158</v>
       </c>
+      <c r="W430" s="1" t="n">
+        <v>0.011036</v>
+      </c>
+      <c r="X430" s="2" t="n">
+        <v>0.0003625815808557406</v>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -30661,6 +33247,12 @@
       <c r="V431" s="3" t="n">
         <v>-0.01180811808118071</v>
       </c>
+      <c r="W431" s="1" t="n">
+        <v>0.006672</v>
+      </c>
+      <c r="X431" s="3" t="n">
+        <v>-0.003435399551904474</v>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
@@ -30731,6 +33323,12 @@
       <c r="V432" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="W432" s="1" t="n">
+        <v>0.001767</v>
+      </c>
+      <c r="X432" s="3" t="n">
+        <v>-0.0005656108597285819</v>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
@@ -30801,6 +33399,12 @@
       <c r="V433" s="2" t="n">
         <v>0.00665188470066511</v>
       </c>
+      <c r="W433" s="1" t="n">
+        <v>0.001363</v>
+      </c>
+      <c r="X433" s="2" t="n">
+        <v>0.0007342143906021533</v>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
@@ -30871,6 +33475,12 @@
       <c r="V434" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="W434" s="1" t="n">
+        <v>0.000412</v>
+      </c>
+      <c r="X434" s="2" t="n">
+        <v>0.004878048780487791</v>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
@@ -30941,6 +33551,12 @@
       <c r="V435" s="2" t="n">
         <v>0.0003162055335969348</v>
       </c>
+      <c r="W435" s="1" t="n">
+        <v>0.12646</v>
+      </c>
+      <c r="X435" s="3" t="n">
+        <v>-0.0006322111585271415</v>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -31011,6 +33627,12 @@
       <c r="V436" s="3" t="n">
         <v>-0.0005144694533761848</v>
       </c>
+      <c r="W436" s="1" t="n">
+        <v>0.07761999999999999</v>
+      </c>
+      <c r="X436" s="3" t="n">
+        <v>-0.001158152103976409</v>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
@@ -31081,6 +33703,12 @@
       <c r="V437" s="2" t="n">
         <v>0.0009537434430139007</v>
       </c>
+      <c r="W437" s="1" t="n">
+        <v>0.6274</v>
+      </c>
+      <c r="X437" s="3" t="n">
+        <v>-0.003652532952199587</v>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -31151,6 +33779,12 @@
       <c r="V438" s="3" t="n">
         <v>-0.001141813199360617</v>
       </c>
+      <c r="W438" s="1" t="n">
+        <v>0.04378</v>
+      </c>
+      <c r="X438" s="2" t="n">
+        <v>0.0009144947416551982</v>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
@@ -31221,6 +33855,12 @@
       <c r="V439" s="3" t="n">
         <v>-0.003981231337978139</v>
       </c>
+      <c r="W439" s="1" t="n">
+        <v>0.0699</v>
+      </c>
+      <c r="X439" s="3" t="n">
+        <v>-0.002141327623126301</v>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
@@ -31291,6 +33931,12 @@
       <c r="V440" s="2" t="n">
         <v>0.0006609385327164017</v>
       </c>
+      <c r="W440" s="1" t="n">
+        <v>0.001513</v>
+      </c>
+      <c r="X440" s="3" t="n">
+        <v>-0.000660501981505889</v>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -31361,6 +34007,12 @@
       <c r="V441" s="2" t="n">
         <v>0.001374643121497211</v>
       </c>
+      <c r="W441" s="1" t="n">
+        <v>0.009488999999999999</v>
+      </c>
+      <c r="X441" s="2" t="n">
+        <v>0.00200633579725448</v>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
@@ -31431,6 +34083,12 @@
       <c r="V442" s="3" t="n">
         <v>-0.00282220131702718</v>
       </c>
+      <c r="W442" s="1" t="n">
+        <v>1.049</v>
+      </c>
+      <c r="X442" s="3" t="n">
+        <v>-0.01037735849056615</v>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
@@ -31501,6 +34159,12 @@
       <c r="V443" s="3" t="n">
         <v>-0.002273760800363709</v>
       </c>
+      <c r="W443" s="1" t="n">
+        <v>0.02187</v>
+      </c>
+      <c r="X443" s="3" t="n">
+        <v>-0.003190519598906135</v>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
@@ -31571,6 +34235,12 @@
       <c r="V444" s="2" t="n">
         <v>0.001314405888538413</v>
       </c>
+      <c r="W444" s="1" t="n">
+        <v>0.000381</v>
+      </c>
+      <c r="X444" s="2" t="n">
+        <v>0.0002625360987135795</v>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
@@ -31641,6 +34311,12 @@
       <c r="V445" s="2" t="n">
         <v>0.002259887005649625</v>
       </c>
+      <c r="W445" s="1" t="n">
+        <v>0.03544</v>
+      </c>
+      <c r="X445" s="3" t="n">
+        <v>-0.001127395715896234</v>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
@@ -31711,6 +34387,12 @@
       <c r="V446" s="2" t="n">
         <v>0.0005853430110045467</v>
       </c>
+      <c r="W446" s="1" t="n">
+        <v>0.08522</v>
+      </c>
+      <c r="X446" s="3" t="n">
+        <v>-0.002925002925002927</v>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
@@ -31781,6 +34463,12 @@
       <c r="V447" s="3" t="n">
         <v>-0.0009126863401278107</v>
       </c>
+      <c r="W447" s="1" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="X447" s="3" t="n">
+        <v>-0.004263093788063273</v>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
@@ -31851,6 +34539,12 @@
       <c r="V448" s="2" t="n">
         <v>0.0007824726134586599</v>
       </c>
+      <c r="W448" s="1" t="n">
+        <v>0.06385</v>
+      </c>
+      <c r="X448" s="3" t="n">
+        <v>-0.001563721657545002</v>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
@@ -31921,6 +34615,12 @@
       <c r="V449" s="3" t="n">
         <v>-0.000821523926884394</v>
       </c>
+      <c r="W449" s="1" t="n">
+        <v>0.4861</v>
+      </c>
+      <c r="X449" s="3" t="n">
+        <v>-0.000822199383350486</v>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
@@ -31991,6 +34691,12 @@
       <c r="V450" s="2" t="n">
         <v>0.006164567140176738</v>
       </c>
+      <c r="W450" s="1" t="n">
+        <v>0.03765</v>
+      </c>
+      <c r="X450" s="2" t="n">
+        <v>0.002930207778369897</v>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -32061,6 +34767,12 @@
       <c r="V451" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="W451" s="1" t="n">
+        <v>0.00546</v>
+      </c>
+      <c r="X451" s="3" t="n">
+        <v>-0.00364963503649636</v>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
@@ -32131,6 +34843,12 @@
       <c r="V452" s="2" t="n">
         <v>0.00223041117145068</v>
       </c>
+      <c r="W452" s="1" t="n">
+        <v>0.10371</v>
+      </c>
+      <c r="X452" s="2" t="n">
+        <v>0.003483309143686495</v>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
@@ -32201,6 +34919,12 @@
       <c r="V453" s="2" t="n">
         <v>0.001244555071561866</v>
       </c>
+      <c r="W453" s="1" t="n">
+        <v>0.01606</v>
+      </c>
+      <c r="X453" s="3" t="n">
+        <v>-0.0018645121193287</v>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
@@ -32271,6 +34995,12 @@
       <c r="V454" s="2" t="n">
         <v>0.004165220409580011</v>
       </c>
+      <c r="W454" s="1" t="n">
+        <v>2.912</v>
+      </c>
+      <c r="X454" s="2" t="n">
+        <v>0.006567576909782278</v>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
@@ -32341,6 +35071,12 @@
       <c r="V455" s="2" t="n">
         <v>0.001118568232662193</v>
       </c>
+      <c r="W455" s="1" t="n">
+        <v>0.893</v>
+      </c>
+      <c r="X455" s="3" t="n">
+        <v>-0.002234636871508382</v>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
@@ -32411,6 +35147,12 @@
       <c r="V456" s="2" t="n">
         <v>0.00204081632653069</v>
       </c>
+      <c r="W456" s="1" t="n">
+        <v>2.946</v>
+      </c>
+      <c r="X456" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -32481,6 +35223,12 @@
       <c r="V457" s="3" t="n">
         <v>-0.001014198782961595</v>
       </c>
+      <c r="W457" s="1" t="n">
+        <v>0.009860000000000001</v>
+      </c>
+      <c r="X457" s="2" t="n">
+        <v>0.001015228426396074</v>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
@@ -32551,6 +35299,12 @@
       <c r="V458" s="2" t="n">
         <v>0.001613163413453717</v>
       </c>
+      <c r="W458" s="1" t="n">
+        <v>0.06222</v>
+      </c>
+      <c r="X458" s="2" t="n">
+        <v>0.002093734900950204</v>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
@@ -32621,6 +35375,12 @@
       <c r="V459" s="3" t="n">
         <v>-0.0006993006993006708</v>
       </c>
+      <c r="W459" s="1" t="n">
+        <v>0.01427</v>
+      </c>
+      <c r="X459" s="3" t="n">
+        <v>-0.001399580125962276</v>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
@@ -32691,6 +35451,12 @@
       <c r="V460" s="3" t="n">
         <v>-0.0002499062851431045</v>
       </c>
+      <c r="W460" s="1" t="n">
+        <v>0.015989</v>
+      </c>
+      <c r="X460" s="3" t="n">
+        <v>-0.0008123984501936711</v>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
@@ -32761,6 +35527,12 @@
       <c r="V461" s="2" t="n">
         <v>0.0006006006006005761</v>
       </c>
+      <c r="W461" s="1" t="n">
+        <v>0.01666</v>
+      </c>
+      <c r="X461" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
@@ -32831,6 +35603,12 @@
       <c r="V462" s="3" t="n">
         <v>-0.002382086707956227</v>
       </c>
+      <c r="W462" s="1" t="n">
+        <v>0.0002088</v>
+      </c>
+      <c r="X462" s="3" t="n">
+        <v>-0.002865329512893923</v>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
@@ -32901,6 +35679,12 @@
       <c r="V463" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="W463" s="1" t="n">
+        <v>0.0987</v>
+      </c>
+      <c r="X463" s="3" t="n">
+        <v>-0.002022244691607742</v>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
@@ -32971,6 +35755,12 @@
       <c r="V464" s="3" t="n">
         <v>-0.0007633587786260555</v>
       </c>
+      <c r="W464" s="1" t="n">
+        <v>0.02616</v>
+      </c>
+      <c r="X464" s="3" t="n">
+        <v>-0.0007639419404124975</v>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
@@ -33041,6 +35831,12 @@
       <c r="V465" s="3" t="n">
         <v>-0.00527704485488128</v>
       </c>
+      <c r="W465" s="1" t="n">
+        <v>0.01502</v>
+      </c>
+      <c r="X465" s="3" t="n">
+        <v>-0.00397877984084876</v>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
@@ -33111,6 +35907,12 @@
       <c r="V466" s="2" t="n">
         <v>0.001645639056500271</v>
       </c>
+      <c r="W466" s="1" t="n">
+        <v>0.05474</v>
+      </c>
+      <c r="X466" s="3" t="n">
+        <v>-0.0007301935012779355</v>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
@@ -33181,6 +35983,12 @@
       <c r="V467" s="3" t="n">
         <v>-0.003190255220417604</v>
       </c>
+      <c r="W467" s="1" t="n">
+        <v>0.0344</v>
+      </c>
+      <c r="X467" s="2" t="n">
+        <v>0.0008728542333430972</v>
+      </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
@@ -33251,6 +36059,12 @@
       <c r="V468" s="2" t="n">
         <v>0.002187386073641951</v>
       </c>
+      <c r="W468" s="1" t="n">
+        <v>27.42</v>
+      </c>
+      <c r="X468" s="3" t="n">
+        <v>-0.002546380502000609</v>
+      </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
@@ -33321,6 +36135,12 @@
       <c r="V469" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="W469" s="1" t="n">
+        <v>0.0007438</v>
+      </c>
+      <c r="X469" s="3" t="n">
+        <v>-0.004816697886004789</v>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
@@ -33391,6 +36211,12 @@
       <c r="V470" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="W470" s="1" t="n">
+        <v>0.882</v>
+      </c>
+      <c r="X470" s="3" t="n">
+        <v>-0.006756756756756762</v>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
@@ -33461,6 +36287,12 @@
       <c r="V471" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="W471" s="1" t="n">
+        <v>0.00988</v>
+      </c>
+      <c r="X471" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
@@ -33531,6 +36363,12 @@
       <c r="V472" s="3" t="n">
         <v>-0.0008596604341286333</v>
       </c>
+      <c r="W472" s="1" t="n">
+        <v>0.04644</v>
+      </c>
+      <c r="X472" s="3" t="n">
+        <v>-0.001075500107549892</v>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -33601,6 +36439,12 @@
       <c r="V473" s="3" t="n">
         <v>-0.001094491061656412</v>
       </c>
+      <c r="W473" s="1" t="n">
+        <v>0.274</v>
+      </c>
+      <c r="X473" s="2" t="n">
+        <v>0.0007304601899197717</v>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
@@ -33671,6 +36515,12 @@
       <c r="V474" s="3" t="n">
         <v>-0.002049180327868848</v>
       </c>
+      <c r="W474" s="1" t="n">
+        <v>0.04378</v>
+      </c>
+      <c r="X474" s="3" t="n">
+        <v>-0.001140771161305075</v>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
@@ -33741,6 +36591,12 @@
       <c r="V475" s="3" t="n">
         <v>-0.00177095631641079</v>
       </c>
+      <c r="W475" s="1" t="n">
+        <v>0.008448000000000001</v>
+      </c>
+      <c r="X475" s="3" t="n">
+        <v>-0.0008279124778237801</v>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
@@ -33811,6 +36667,12 @@
       <c r="V476" s="3" t="n">
         <v>-0.002320185614849305</v>
       </c>
+      <c r="W476" s="1" t="n">
+        <v>0.08155999999999999</v>
+      </c>
+      <c r="X476" s="3" t="n">
+        <v>-0.001713586291309685</v>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
@@ -33881,6 +36743,12 @@
       <c r="V477" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="W477" s="1" t="n">
+        <v>0.1355</v>
+      </c>
+      <c r="X477" s="3" t="n">
+        <v>-0.004408523144746432</v>
+      </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
@@ -33951,6 +36819,12 @@
       <c r="V478" s="3" t="n">
         <v>-0.0002520161290322303</v>
       </c>
+      <c r="W478" s="1" t="n">
+        <v>0.3962</v>
+      </c>
+      <c r="X478" s="3" t="n">
+        <v>-0.001260398285858332</v>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
@@ -34021,6 +36895,12 @@
       <c r="V479" s="3" t="n">
         <v>-0.004501904651968237</v>
       </c>
+      <c r="W479" s="1" t="n">
+        <v>0.008588</v>
+      </c>
+      <c r="X479" s="3" t="n">
+        <v>-0.004174397031539839</v>
+      </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
@@ -34091,6 +36971,12 @@
       <c r="V480" s="3" t="n">
         <v>-0.006203473945409392</v>
       </c>
+      <c r="W480" s="1" t="n">
+        <v>0.01588</v>
+      </c>
+      <c r="X480" s="3" t="n">
+        <v>-0.008739076154806569</v>
+      </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
@@ -34161,6 +37047,12 @@
       <c r="V481" s="3" t="n">
         <v>-0.003941011950165152</v>
       </c>
+      <c r="W481" s="1" t="n">
+        <v>0.07822</v>
+      </c>
+      <c r="X481" s="3" t="n">
+        <v>-0.001659221442246396</v>
+      </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
@@ -34231,6 +37123,12 @@
       <c r="V482" s="3" t="n">
         <v>-0.0005954743946010768</v>
       </c>
+      <c r="W482" s="1" t="n">
+        <v>0.05025</v>
+      </c>
+      <c r="X482" s="3" t="n">
+        <v>-0.001986097318768539</v>
+      </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
@@ -34301,6 +37199,12 @@
       <c r="V483" s="3" t="n">
         <v>-0.002057613168724196</v>
       </c>
+      <c r="W483" s="1" t="n">
+        <v>0.009690000000000001</v>
+      </c>
+      <c r="X483" s="3" t="n">
+        <v>-0.001030927835051504</v>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
@@ -34371,6 +37275,12 @@
       <c r="V484" s="2" t="n">
         <v>0.0002939015429831906</v>
       </c>
+      <c r="W484" s="1" t="n">
+        <v>0.06783</v>
+      </c>
+      <c r="X484" s="3" t="n">
+        <v>-0.003525782282944088</v>
+      </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
@@ -34441,6 +37351,12 @@
       <c r="V485" s="2" t="n">
         <v>0.0033400133600534</v>
       </c>
+      <c r="W485" s="1" t="n">
+        <v>0.0004517</v>
+      </c>
+      <c r="X485" s="2" t="n">
+        <v>0.002441189525077613</v>
+      </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
@@ -34511,6 +37427,12 @@
       <c r="V486" s="3" t="n">
         <v>-0.003271263210870613</v>
       </c>
+      <c r="W486" s="1" t="n">
+        <v>0.0793</v>
+      </c>
+      <c r="X486" s="2" t="n">
+        <v>0.00100984599848519</v>
+      </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
@@ -34581,6 +37503,12 @@
       <c r="V487" s="2" t="n">
         <v>0.002310803004043805</v>
       </c>
+      <c r="W487" s="1" t="n">
+        <v>0.0001732</v>
+      </c>
+      <c r="X487" s="3" t="n">
+        <v>-0.001729106628241961</v>
+      </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
@@ -34651,6 +37579,12 @@
       <c r="V488" s="2" t="n">
         <v>0.002892745883400048</v>
       </c>
+      <c r="W488" s="1" t="n">
+        <v>0.0898</v>
+      </c>
+      <c r="X488" s="3" t="n">
+        <v>-0.003771910361659564</v>
+      </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
@@ -34721,6 +37655,12 @@
       <c r="V489" s="2" t="n">
         <v>0.001885606536769323</v>
       </c>
+      <c r="W489" s="1" t="n">
+        <v>0.0477</v>
+      </c>
+      <c r="X489" s="3" t="n">
+        <v>-0.002509410288582226</v>
+      </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
@@ -34791,6 +37731,12 @@
       <c r="V490" s="3" t="n">
         <v>-0.006683804627249264</v>
       </c>
+      <c r="W490" s="1" t="n">
+        <v>0.03901</v>
+      </c>
+      <c r="X490" s="2" t="n">
+        <v>0.009575569358178113</v>
+      </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
@@ -34861,6 +37807,12 @@
       <c r="V491" s="2" t="n">
         <v>0.01111253033593046</v>
       </c>
+      <c r="W491" s="1" t="n">
+        <v>0.07869</v>
+      </c>
+      <c r="X491" s="3" t="n">
+        <v>-0.005937342091965617</v>
+      </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
@@ -34931,6 +37883,12 @@
       <c r="V492" s="3" t="n">
         <v>-0.0003151591553735601</v>
       </c>
+      <c r="W492" s="1" t="n">
+        <v>0.06315999999999999</v>
+      </c>
+      <c r="X492" s="3" t="n">
+        <v>-0.004413619167717568</v>
+      </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
@@ -35001,6 +37959,12 @@
       <c r="V493" s="3" t="n">
         <v>-0.007604562737642605</v>
       </c>
+      <c r="W493" s="1" t="n">
+        <v>0.00521</v>
+      </c>
+      <c r="X493" s="3" t="n">
+        <v>-0.001915708812260458</v>
+      </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
@@ -35071,6 +38035,12 @@
       <c r="V494" s="2" t="n">
         <v>0.0007259528130670706</v>
       </c>
+      <c r="W494" s="1" t="n">
+        <v>0.2751</v>
+      </c>
+      <c r="X494" s="3" t="n">
+        <v>-0.002176278563656109</v>
+      </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
@@ -35141,6 +38111,12 @@
       <c r="V495" s="3" t="n">
         <v>-0.0004705882352941529</v>
       </c>
+      <c r="W495" s="1" t="n">
+        <v>0.06374</v>
+      </c>
+      <c r="X495" s="2" t="n">
+        <v>0.0003138731952292236</v>
+      </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
@@ -35211,6 +38187,12 @@
       <c r="V496" s="3" t="n">
         <v>-0.0006821282401092547</v>
       </c>
+      <c r="W496" s="1" t="n">
+        <v>0.2934</v>
+      </c>
+      <c r="X496" s="2" t="n">
+        <v>0.001365187713310619</v>
+      </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
@@ -35281,6 +38263,12 @@
       <c r="V497" s="2" t="n">
         <v>0.02303557716918347</v>
       </c>
+      <c r="W497" s="1" t="n">
+        <v>0.07967</v>
+      </c>
+      <c r="X497" s="3" t="n">
+        <v>-0.003377533149862303</v>
+      </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
@@ -35351,6 +38339,12 @@
       <c r="V498" s="2" t="n">
         <v>0.0009689922480620432</v>
       </c>
+      <c r="W498" s="1" t="n">
+        <v>0.1028</v>
+      </c>
+      <c r="X498" s="3" t="n">
+        <v>-0.004840271055179094</v>
+      </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
@@ -35421,6 +38415,12 @@
       <c r="V499" s="2" t="n">
         <v>0.001919846412287105</v>
       </c>
+      <c r="W499" s="1" t="n">
+        <v>0.04175</v>
+      </c>
+      <c r="X499" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
@@ -35491,6 +38491,12 @@
       <c r="V500" s="3" t="n">
         <v>-0.003001500750375239</v>
       </c>
+      <c r="W500" s="1" t="n">
+        <v>0.04011</v>
+      </c>
+      <c r="X500" s="2" t="n">
+        <v>0.00627195183140994</v>
+      </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
@@ -35561,6 +38567,12 @@
       <c r="V501" s="3" t="n">
         <v>-0.001012145748987883</v>
       </c>
+      <c r="W501" s="1" t="n">
+        <v>0.0987</v>
+      </c>
+      <c r="X501" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
@@ -35631,6 +38643,12 @@
       <c r="V502" s="2" t="n">
         <v>0.001209555488358058</v>
       </c>
+      <c r="W502" s="1" t="n">
+        <v>0.003314</v>
+      </c>
+      <c r="X502" s="2" t="n">
+        <v>0.0009060706735125232</v>
+      </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
@@ -35701,6 +38719,12 @@
       <c r="V503" s="3" t="n">
         <v>-0.001094091903720058</v>
       </c>
+      <c r="W503" s="1" t="n">
+        <v>0.009129999999999999</v>
+      </c>
+      <c r="X503" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
@@ -35771,6 +38795,12 @@
       <c r="V504" s="3" t="n">
         <v>-0.0006277463904581857</v>
       </c>
+      <c r="W504" s="1" t="n">
+        <v>0.1587</v>
+      </c>
+      <c r="X504" s="3" t="n">
+        <v>-0.003140703517587942</v>
+      </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
@@ -35841,6 +38871,12 @@
       <c r="V505" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="W505" s="1" t="n">
+        <v>0.1312</v>
+      </c>
+      <c r="X505" s="2" t="n">
+        <v>0.0007627765064837281</v>
+      </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
@@ -35911,6 +38947,12 @@
       <c r="V506" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="W506" s="1" t="n">
+        <v>0.01687</v>
+      </c>
+      <c r="X506" s="3" t="n">
+        <v>-0.001184132622853711</v>
+      </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
@@ -35981,6 +39023,12 @@
       <c r="V507" s="3" t="n">
         <v>-0.004512322110378338</v>
       </c>
+      <c r="W507" s="1" t="n">
+        <v>0.002856</v>
+      </c>
+      <c r="X507" s="3" t="n">
+        <v>-0.004184100418409993</v>
+      </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
@@ -36051,6 +39099,12 @@
       <c r="V508" s="3" t="n">
         <v>-0.007210455159981981</v>
       </c>
+      <c r="W508" s="1" t="n">
+        <v>2.196</v>
+      </c>
+      <c r="X508" s="3" t="n">
+        <v>-0.003177485247389775</v>
+      </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
@@ -36121,6 +39175,12 @@
       <c r="V509" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="W509" s="1" t="n">
+        <v>0.05483</v>
+      </c>
+      <c r="X509" s="3" t="n">
+        <v>-0.0009110787172011923</v>
+      </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
@@ -36191,6 +39251,12 @@
       <c r="V510" s="2" t="n">
         <v>0.0006807351940095026</v>
       </c>
+      <c r="W510" s="1" t="n">
+        <v>0.02935</v>
+      </c>
+      <c r="X510" s="3" t="n">
+        <v>-0.001700680272108774</v>
+      </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
@@ -36261,6 +39327,12 @@
       <c r="V511" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="W511" s="1" t="n">
+        <v>0.04034</v>
+      </c>
+      <c r="X511" s="3" t="n">
+        <v>-0.0009905894006933722</v>
+      </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
@@ -36331,6 +39403,12 @@
       <c r="V512" s="3" t="n">
         <v>-0.01123595505617979</v>
       </c>
+      <c r="W512" s="1" t="n">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="X512" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
@@ -36401,6 +39479,12 @@
       <c r="V513" s="3" t="n">
         <v>-0.006792403059878703</v>
       </c>
+      <c r="W513" s="1" t="n">
+        <v>0.015001</v>
+      </c>
+      <c r="X513" s="3" t="n">
+        <v>-0.00398379921651944</v>
+      </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
@@ -36471,6 +39555,12 @@
       <c r="V514" s="2" t="n">
         <v>0.001727115716752992</v>
       </c>
+      <c r="W514" s="1" t="n">
+        <v>0.1741</v>
+      </c>
+      <c r="X514" s="2" t="n">
+        <v>0.0005747126436782572</v>
+      </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
@@ -36541,6 +39631,12 @@
       <c r="V515" s="3" t="n">
         <v>-0.0009285051067781138</v>
       </c>
+      <c r="W515" s="1" t="n">
+        <v>0.1075</v>
+      </c>
+      <c r="X515" s="3" t="n">
+        <v>-0.0009293680297398036</v>
+      </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
@@ -36611,6 +39707,12 @@
       <c r="V516" s="3" t="n">
         <v>-0.003745318352059935</v>
       </c>
+      <c r="W516" s="1" t="n">
+        <v>0.00267</v>
+      </c>
+      <c r="X516" s="2" t="n">
+        <v>0.003759398496240611</v>
+      </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
@@ -36681,6 +39783,12 @@
       <c r="V517" s="3" t="n">
         <v>-0.0002591680704937496</v>
       </c>
+      <c r="W517" s="1" t="n">
+        <v>0.007691</v>
+      </c>
+      <c r="X517" s="3" t="n">
+        <v>-0.003110823071937747</v>
+      </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
@@ -36751,6 +39859,12 @@
       <c r="V518" s="2" t="n">
         <v>0.01027617212588314</v>
       </c>
+      <c r="W518" s="1" t="n">
+        <v>0.01573</v>
+      </c>
+      <c r="X518" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
@@ -36821,6 +39935,12 @@
       <c r="V519" s="2" t="n">
         <v>0.00358166189111754</v>
       </c>
+      <c r="W519" s="1" t="n">
+        <v>0.004211</v>
+      </c>
+      <c r="X519" s="2" t="n">
+        <v>0.001903402331667903</v>
+      </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
@@ -36891,6 +40011,12 @@
       <c r="V520" s="2" t="n">
         <v>0.0008635578583766259</v>
       </c>
+      <c r="W520" s="1" t="n">
+        <v>0.001158</v>
+      </c>
+      <c r="X520" s="3" t="n">
+        <v>-0.0008628127696291049</v>
+      </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
@@ -36961,6 +40087,12 @@
       <c r="V521" s="2" t="n">
         <v>0.001502629601803094</v>
       </c>
+      <c r="W521" s="1" t="n">
+        <v>0.01333</v>
+      </c>
+      <c r="X521" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
@@ -37031,6 +40163,12 @@
       <c r="V522" s="2" t="n">
         <v>0.000583430571762058</v>
       </c>
+      <c r="W522" s="1" t="n">
+        <v>0.6873</v>
+      </c>
+      <c r="X522" s="2" t="n">
+        <v>0.001895043731778379</v>
+      </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
@@ -37101,6 +40239,12 @@
       <c r="V523" s="3" t="n">
         <v>-0.003562776115148927</v>
       </c>
+      <c r="W523" s="1" t="n">
+        <v>0.06974</v>
+      </c>
+      <c r="X523" s="3" t="n">
+        <v>-0.002574370709382145</v>
+      </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
@@ -37171,6 +40315,12 @@
       <c r="V524" s="2" t="n">
         <v>0.001713796058269145</v>
       </c>
+      <c r="W524" s="1" t="n">
+        <v>0.01167</v>
+      </c>
+      <c r="X524" s="3" t="n">
+        <v>-0.001710863986313167</v>
+      </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
@@ -37241,6 +40391,12 @@
       <c r="V525" s="3" t="n">
         <v>-0.001824817518248101</v>
       </c>
+      <c r="W525" s="1" t="n">
+        <v>0.01639</v>
+      </c>
+      <c r="X525" s="3" t="n">
+        <v>-0.001218769043266463</v>
+      </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
@@ -37311,6 +40467,12 @@
       <c r="V526" s="3" t="n">
         <v>-0.0005194034280627328</v>
       </c>
+      <c r="W526" s="1" t="n">
+        <v>0.13436</v>
+      </c>
+      <c r="X526" s="3" t="n">
+        <v>-0.002524127691165399</v>
+      </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
@@ -37381,6 +40543,12 @@
       <c r="V527" s="3" t="n">
         <v>-0.001626772019521279</v>
       </c>
+      <c r="W527" s="1" t="n">
+        <v>0.04292</v>
+      </c>
+      <c r="X527" s="3" t="n">
+        <v>-0.0009310986964617871</v>
+      </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
@@ -37451,6 +40619,12 @@
       <c r="V528" s="2" t="n">
         <v>0.003673769287288762</v>
       </c>
+      <c r="W528" s="1" t="n">
+        <v>0.2729</v>
+      </c>
+      <c r="X528" s="3" t="n">
+        <v>-0.001098096632503743</v>
+      </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
@@ -37521,6 +40695,12 @@
       <c r="V529" s="3" t="n">
         <v>-0.001933434608479539</v>
       </c>
+      <c r="W529" s="1" t="n">
+        <v>0.0007231</v>
+      </c>
+      <c r="X529" s="2" t="n">
+        <v>0.0005534800055348136</v>
+      </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
@@ -37591,6 +40771,12 @@
       <c r="V530" s="2" t="n">
         <v>0.001439884809215246</v>
       </c>
+      <c r="W530" s="1" t="n">
+        <v>0.004171</v>
+      </c>
+      <c r="X530" s="3" t="n">
+        <v>-0.0004792715073087463</v>
+      </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
@@ -37661,6 +40847,12 @@
       <c r="V531" s="2" t="n">
         <v>0.004573170731707321</v>
       </c>
+      <c r="W531" s="1" t="n">
+        <v>1.316</v>
+      </c>
+      <c r="X531" s="3" t="n">
+        <v>-0.001517450682852809</v>
+      </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
@@ -37731,6 +40923,12 @@
       <c r="V532" s="3" t="n">
         <v>-0.0008474576271185508</v>
       </c>
+      <c r="W532" s="1" t="n">
+        <v>0.1177</v>
+      </c>
+      <c r="X532" s="3" t="n">
+        <v>-0.001696352841391058</v>
+      </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
@@ -37801,6 +40999,12 @@
       <c r="V533" s="3" t="n">
         <v>-0.0003732736095557892</v>
       </c>
+      <c r="W533" s="1" t="n">
+        <v>0.05355</v>
+      </c>
+      <c r="X533" s="3" t="n">
+        <v>-0.0001867064973861662</v>
+      </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
@@ -37871,6 +41075,12 @@
       <c r="V534" s="2" t="n">
         <v>0.001333333333333372</v>
       </c>
+      <c r="W534" s="1" t="n">
+        <v>0.1499</v>
+      </c>
+      <c r="X534" s="3" t="n">
+        <v>-0.001997336884154426</v>
+      </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
@@ -37941,6 +41151,12 @@
       <c r="V535" s="2" t="n">
         <v>0.000586166471277819</v>
       </c>
+      <c r="W535" s="1" t="n">
+        <v>0.0171</v>
+      </c>
+      <c r="X535" s="2" t="n">
+        <v>0.001757469244288357</v>
+      </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
@@ -38011,6 +41227,12 @@
       <c r="V536" s="2" t="n">
         <v>0.001396926761125536</v>
       </c>
+      <c r="W536" s="1" t="n">
+        <v>0.005007</v>
+      </c>
+      <c r="X536" s="3" t="n">
+        <v>-0.002192108409724935</v>
+      </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
@@ -38081,6 +41303,12 @@
       <c r="V537" s="3" t="n">
         <v>-0.001711156741957565</v>
       </c>
+      <c r="W537" s="1" t="n">
+        <v>0.2913</v>
+      </c>
+      <c r="X537" s="3" t="n">
+        <v>-0.001371271854645223</v>
+      </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
@@ -38151,6 +41379,12 @@
       <c r="V538" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="W538" s="1" t="n">
+        <v>0.01327</v>
+      </c>
+      <c r="X538" s="3" t="n">
+        <v>-0.0007530120481927404</v>
+      </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
@@ -38221,6 +41455,12 @@
       <c r="V539" s="2" t="n">
         <v>0.001190476190476142</v>
       </c>
+      <c r="W539" s="1" t="n">
+        <v>0.02525</v>
+      </c>
+      <c r="X539" s="2" t="n">
+        <v>0.000792707094728603</v>
+      </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
@@ -38291,6 +41531,12 @@
       <c r="V540" s="2" t="n">
         <v>0.0008795074758135696</v>
       </c>
+      <c r="W540" s="1" t="n">
+        <v>0.05682</v>
+      </c>
+      <c r="X540" s="3" t="n">
+        <v>-0.001405975395430523</v>
+      </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
@@ -38361,6 +41607,12 @@
       <c r="V541" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="W541" s="1" t="n">
+        <v>0.0116</v>
+      </c>
+      <c r="X541" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
@@ -38431,6 +41683,12 @@
       <c r="V542" s="2" t="n">
         <v>0.009009009009008922</v>
       </c>
+      <c r="W542" s="1" t="n">
+        <v>1.11e-05</v>
+      </c>
+      <c r="X542" s="3" t="n">
+        <v>-0.008928571428571343</v>
+      </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
@@ -38500,6 +41758,12 @@
       </c>
       <c r="V543" s="3" t="n">
         <v>-0.004875406283856931</v>
+      </c>
+      <c r="W543" s="1" t="n">
+        <v>0.003673</v>
+      </c>
+      <c r="X543" s="3" t="n">
+        <v>-0.000272182906913482</v>
       </c>
     </row>
   </sheetData>

--- a/binance-usdt-perpetual-data/weeks/2026-03-09_2026-03-15/2026-03-12.xlsx
+++ b/binance-usdt-perpetual-data/weeks/2026-03-09_2026-03-15/2026-03-12.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X543"/>
+  <dimension ref="A1:Z543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -450,6 +450,8 @@
     <col width="18" customWidth="1" min="22" max="22"/>
     <col width="13" customWidth="1" min="23" max="23"/>
     <col width="18" customWidth="1" min="24" max="24"/>
+    <col width="13" customWidth="1" min="25" max="25"/>
+    <col width="18" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -573,6 +575,16 @@
           <t>change_02:45</t>
         </is>
       </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>price_03:00</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>change_03:00</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -649,6 +661,12 @@
       <c r="X2" s="3" t="n">
         <v>-0.002755163986737814</v>
       </c>
+      <c r="Y2" s="1" t="n">
+        <v>70578.89999999999</v>
+      </c>
+      <c r="Z2" s="2" t="n">
+        <v>0.001508387657046687</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -725,6 +743,12 @@
       <c r="X3" s="3" t="n">
         <v>-0.001756561771617954</v>
       </c>
+      <c r="Y3" s="1" t="n">
+        <v>2075.33</v>
+      </c>
+      <c r="Z3" s="2" t="n">
+        <v>0.003258258040500912</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -801,6 +825,12 @@
       <c r="X4" s="3" t="n">
         <v>-0.003539216805571438</v>
       </c>
+      <c r="Y4" s="1" t="n">
+        <v>87.77</v>
+      </c>
+      <c r="Z4" s="2" t="n">
+        <v>0.005614115490375744</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -877,6 +907,12 @@
       <c r="X5" s="2" t="n">
         <v>0.01135876553793395</v>
       </c>
+      <c r="Y5" s="1" t="n">
+        <v>0.014051</v>
+      </c>
+      <c r="Z5" s="3" t="n">
+        <v>-0.007487462032916592</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -953,6 +989,12 @@
       <c r="X6" s="3" t="n">
         <v>-0.001806012960798932</v>
       </c>
+      <c r="Y6" s="1" t="n">
+        <v>0.09433999999999999</v>
+      </c>
+      <c r="Z6" s="2" t="n">
+        <v>0.004044274159216597</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1029,6 +1071,12 @@
       <c r="X7" s="3" t="n">
         <v>-0.0007856020568489351</v>
       </c>
+      <c r="Y7" s="1" t="n">
+        <v>1.4036</v>
+      </c>
+      <c r="Z7" s="2" t="n">
+        <v>0.00321635337002355</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1105,6 +1153,12 @@
       <c r="X8" s="2" t="n">
         <v>0.002468998807113096</v>
       </c>
+      <c r="Y8" s="1" t="n">
+        <v>36.383</v>
+      </c>
+      <c r="Z8" s="2" t="n">
+        <v>0.00683528890856763</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1181,6 +1235,12 @@
       <c r="X9" s="3" t="n">
         <v>-0.001915562025898399</v>
       </c>
+      <c r="Y9" s="1" t="n">
+        <v>652.84</v>
+      </c>
+      <c r="Z9" s="2" t="n">
+        <v>0.002364501765699489</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1257,6 +1317,12 @@
       <c r="X10" s="2" t="n">
         <v>0.01626416954164612</v>
       </c>
+      <c r="Y10" s="1" t="n">
+        <v>14.337</v>
+      </c>
+      <c r="Z10" s="3" t="n">
+        <v>-0.006720243868643449</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1333,6 +1399,12 @@
       <c r="X11" s="3" t="n">
         <v>-0.004373589164785452</v>
       </c>
+      <c r="Y11" s="1" t="n">
+        <v>213.12</v>
+      </c>
+      <c r="Z11" s="2" t="n">
+        <v>0.006660053847243855</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1409,6 +1481,12 @@
       <c r="X12" s="3" t="n">
         <v>-2.966390792331093e-05</v>
       </c>
+      <c r="Y12" s="1" t="n">
+        <v>0.0033868</v>
+      </c>
+      <c r="Z12" s="2" t="n">
+        <v>0.004687036487689195</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1563,12 @@
       <c r="X13" s="2" t="n">
         <v>0.03006500541711809</v>
       </c>
+      <c r="Y13" s="1" t="n">
+        <v>0.03903</v>
+      </c>
+      <c r="Z13" s="2" t="n">
+        <v>0.0262950302392848</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1561,6 +1645,12 @@
       <c r="X14" s="2" t="n">
         <v>0.003079291762894537</v>
       </c>
+      <c r="Y14" s="1" t="n">
+        <v>2.627</v>
+      </c>
+      <c r="Z14" s="2" t="n">
+        <v>0.008058326937835729</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1637,6 +1727,12 @@
       <c r="X15" s="2" t="n">
         <v>0.001629161999796402</v>
       </c>
+      <c r="Y15" s="1" t="n">
+        <v>0.9915</v>
+      </c>
+      <c r="Z15" s="2" t="n">
+        <v>0.007929246721561482</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1713,6 +1809,12 @@
       <c r="X16" s="3" t="n">
         <v>-0.0003516174402250209</v>
       </c>
+      <c r="Y16" s="1" t="n">
+        <v>0.05697</v>
+      </c>
+      <c r="Z16" s="2" t="n">
+        <v>0.001934576151952145</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1789,6 +1891,12 @@
       <c r="X17" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" s="1" t="n">
+        <v>0.889</v>
+      </c>
+      <c r="Z17" s="2" t="n">
+        <v>0.004519774011299439</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1865,6 +1973,12 @@
       <c r="X18" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" s="1" t="n">
+        <v>0.2663</v>
+      </c>
+      <c r="Z18" s="2" t="n">
+        <v>0.003013182674199501</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1941,6 +2055,12 @@
       <c r="X19" s="2" t="n">
         <v>0.01532490511115546</v>
       </c>
+      <c r="Y19" s="1" t="n">
+        <v>0.35929</v>
+      </c>
+      <c r="Z19" s="2" t="n">
+        <v>0.009865647310135514</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2017,6 +2137,12 @@
       <c r="X20" s="3" t="n">
         <v>-0.001750051472102248</v>
       </c>
+      <c r="Y20" s="1" t="n">
+        <v>9.731</v>
+      </c>
+      <c r="Z20" s="2" t="n">
+        <v>0.003506239043003063</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2093,6 +2219,12 @@
       <c r="X21" s="2" t="n">
         <v>0.001208398368662105</v>
       </c>
+      <c r="Y21" s="1" t="n">
+        <v>200.85</v>
+      </c>
+      <c r="Z21" s="2" t="n">
+        <v>0.01005783253708826</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2169,6 +2301,12 @@
       <c r="X22" s="3" t="n">
         <v>-0.00600801068090793</v>
       </c>
+      <c r="Y22" s="1" t="n">
+        <v>0.0211</v>
+      </c>
+      <c r="Z22" s="2" t="n">
+        <v>0.01218459176820497</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2245,6 +2383,12 @@
       <c r="X23" s="3" t="n">
         <v>-0.001334704505174621</v>
       </c>
+      <c r="Y23" s="1" t="n">
+        <v>456.89</v>
+      </c>
+      <c r="Z23" s="2" t="n">
+        <v>0.001029753297401451</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2321,6 +2465,12 @@
       <c r="X24" s="3" t="n">
         <v>-6.955970638068725e-05</v>
       </c>
+      <c r="Y24" s="1" t="n">
+        <v>5170.8</v>
+      </c>
+      <c r="Z24" s="3" t="n">
+        <v>-0.0008212481038830543</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2397,6 +2547,12 @@
       <c r="X25" s="3" t="n">
         <v>-0.002311248073960026</v>
       </c>
+      <c r="Y25" s="1" t="n">
+        <v>9.090999999999999</v>
+      </c>
+      <c r="Z25" s="2" t="n">
+        <v>0.002868174296745703</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2473,6 +2629,12 @@
       <c r="X26" s="2" t="n">
         <v>0.005650656473325578</v>
       </c>
+      <c r="Y26" s="1" t="n">
+        <v>0.12266</v>
+      </c>
+      <c r="Z26" s="2" t="n">
+        <v>0.01355147909436459</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2549,6 +2711,12 @@
       <c r="X27" s="2" t="n">
         <v>0.01518987341772163</v>
       </c>
+      <c r="Y27" s="1" t="n">
+        <v>0.01185</v>
+      </c>
+      <c r="Z27" s="3" t="n">
+        <v>-0.01496259351620959</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2625,6 +2793,12 @@
       <c r="X28" s="3" t="n">
         <v>-0.003086419753086422</v>
       </c>
+      <c r="Y28" s="1" t="n">
+        <v>1.294</v>
+      </c>
+      <c r="Z28" s="2" t="n">
+        <v>0.001547987616099073</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2701,6 +2875,12 @@
       <c r="X29" s="2" t="n">
         <v>0.009480957737425683</v>
       </c>
+      <c r="Y29" s="1" t="n">
+        <v>0.05966</v>
+      </c>
+      <c r="Z29" s="3" t="n">
+        <v>-0.0503024514485833</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2777,6 +2957,12 @@
       <c r="X30" s="2" t="n">
         <v>0.00130633572828217</v>
       </c>
+      <c r="Y30" s="1" t="n">
+        <v>1.536</v>
+      </c>
+      <c r="Z30" s="2" t="n">
+        <v>0.001956947162426689</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2853,6 +3039,12 @@
       <c r="X31" s="3" t="n">
         <v>-0.007411067193676015</v>
       </c>
+      <c r="Y31" s="1" t="n">
+        <v>0.002026</v>
+      </c>
+      <c r="Z31" s="2" t="n">
+        <v>0.008461921353907461</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2929,6 +3121,12 @@
       <c r="X32" s="3" t="n">
         <v>-0.007658102766798535</v>
       </c>
+      <c r="Y32" s="1" t="n">
+        <v>0.04039</v>
+      </c>
+      <c r="Z32" s="2" t="n">
+        <v>0.005476723923325988</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3005,6 +3203,12 @@
       <c r="X33" s="3" t="n">
         <v>-0.004060913705583731</v>
       </c>
+      <c r="Y33" s="1" t="n">
+        <v>0.099</v>
+      </c>
+      <c r="Z33" s="2" t="n">
+        <v>0.009174311926605484</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3081,6 +3285,12 @@
       <c r="X34" s="2" t="n">
         <v>0.0009505703422053504</v>
       </c>
+      <c r="Y34" s="1" t="n">
+        <v>0.1057</v>
+      </c>
+      <c r="Z34" s="2" t="n">
+        <v>0.003798670465337109</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3157,6 +3367,12 @@
       <c r="X35" s="2" t="n">
         <v>0.02059496567505736</v>
       </c>
+      <c r="Y35" s="1" t="n">
+        <v>0.008959999999999999</v>
+      </c>
+      <c r="Z35" s="2" t="n">
+        <v>0.004484304932735243</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3233,6 +3449,12 @@
       <c r="X36" s="3" t="n">
         <v>-0.002509760178471713</v>
       </c>
+      <c r="Y36" s="1" t="n">
+        <v>0.3598</v>
+      </c>
+      <c r="Z36" s="2" t="n">
+        <v>0.005870841487279817</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3309,6 +3531,12 @@
       <c r="X37" s="3" t="n">
         <v>-0.002229080932784635</v>
       </c>
+      <c r="Y37" s="1" t="n">
+        <v>0.005835</v>
+      </c>
+      <c r="Z37" s="2" t="n">
+        <v>0.002749613335624596</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3385,6 +3613,12 @@
       <c r="X38" s="2" t="n">
         <v>0.0004201520186394675</v>
       </c>
+      <c r="Y38" s="1" t="n">
+        <v>0.2621</v>
+      </c>
+      <c r="Z38" s="2" t="n">
+        <v>0.0006872327428222873</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3461,6 +3695,12 @@
       <c r="X39" s="2" t="n">
         <v>0.005149534561299332</v>
       </c>
+      <c r="Y39" s="1" t="n">
+        <v>0.05092</v>
+      </c>
+      <c r="Z39" s="2" t="n">
+        <v>0.003349753694581212</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -3537,6 +3777,12 @@
       <c r="X40" s="3" t="n">
         <v>-0.008774823513887958</v>
       </c>
+      <c r="Y40" s="1" t="n">
+        <v>0.15082</v>
+      </c>
+      <c r="Z40" s="2" t="n">
+        <v>0.003860489882854081</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -3613,6 +3859,12 @@
       <c r="X41" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="Y41" s="1" t="n">
+        <v>0.1711</v>
+      </c>
+      <c r="Z41" s="2" t="n">
+        <v>0.005287896592244489</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -3689,6 +3941,12 @@
       <c r="X42" s="3" t="n">
         <v>-0.001782848992690344</v>
       </c>
+      <c r="Y42" s="1" t="n">
+        <v>112.41</v>
+      </c>
+      <c r="Z42" s="2" t="n">
+        <v>0.00383997142346841</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -3765,6 +4023,12 @@
       <c r="X43" s="3" t="n">
         <v>-0.07676988947525634</v>
       </c>
+      <c r="Y43" s="1" t="n">
+        <v>0.8724</v>
+      </c>
+      <c r="Z43" s="3" t="n">
+        <v>-0.05910267471958593</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -3841,6 +4105,12 @@
       <c r="X44" s="3" t="n">
         <v>-0.001633690324922915</v>
       </c>
+      <c r="Y44" s="1" t="n">
+        <v>55.1</v>
+      </c>
+      <c r="Z44" s="2" t="n">
+        <v>0.001818181818181844</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -3917,6 +4187,12 @@
       <c r="X45" s="3" t="n">
         <v>-0.003930332922317993</v>
       </c>
+      <c r="Y45" s="1" t="n">
+        <v>0.51903</v>
+      </c>
+      <c r="Z45" s="2" t="n">
+        <v>0.003926499032881965</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -3993,6 +4269,12 @@
       <c r="X46" s="3" t="n">
         <v>-0.001564722617354182</v>
       </c>
+      <c r="Y46" s="1" t="n">
+        <v>0.702</v>
+      </c>
+      <c r="Z46" s="2" t="n">
+        <v>0.0001424704373842271</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -4069,6 +4351,12 @@
       <c r="X47" s="3" t="n">
         <v>-0.002544529262086573</v>
       </c>
+      <c r="Y47" s="1" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="Z47" s="2" t="n">
+        <v>0.002551020408163324</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -4145,6 +4433,12 @@
       <c r="X48" s="3" t="n">
         <v>-0.001062300818596535</v>
       </c>
+      <c r="Y48" s="1" t="n">
+        <v>0.16077</v>
+      </c>
+      <c r="Z48" s="2" t="n">
+        <v>0.005692480920805668</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -4221,6 +4515,12 @@
       <c r="X49" s="2" t="n">
         <v>0.009828009828009882</v>
       </c>
+      <c r="Y49" s="1" t="n">
+        <v>0.06289</v>
+      </c>
+      <c r="Z49" s="2" t="n">
+        <v>0.02011354420113541</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -4297,6 +4597,12 @@
       <c r="X50" s="3" t="n">
         <v>-0.002583979328165269</v>
       </c>
+      <c r="Y50" s="1" t="n">
+        <v>0.0388</v>
+      </c>
+      <c r="Z50" s="2" t="n">
+        <v>0.005181347150259035</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -4373,6 +4679,12 @@
       <c r="X51" s="2" t="n">
         <v>0.01075482312452422</v>
       </c>
+      <c r="Y51" s="1" t="n">
+        <v>0.30444</v>
+      </c>
+      <c r="Z51" s="3" t="n">
+        <v>-0.003273965426925095</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -4449,6 +4761,12 @@
       <c r="X52" s="2" t="n">
         <v>0.002400548696844919</v>
       </c>
+      <c r="Y52" s="1" t="n">
+        <v>0.2912</v>
+      </c>
+      <c r="Z52" s="3" t="n">
+        <v>-0.003763256927813855</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -4525,6 +4843,12 @@
       <c r="X53" s="3" t="n">
         <v>-0.001257861635220162</v>
       </c>
+      <c r="Y53" s="1" t="n">
+        <v>0.1598</v>
+      </c>
+      <c r="Z53" s="2" t="n">
+        <v>0.006297229219143582</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -4601,6 +4925,12 @@
       <c r="X54" s="3" t="n">
         <v>-0.002786186020913517</v>
       </c>
+      <c r="Y54" s="1" t="n">
+        <v>0.2903</v>
+      </c>
+      <c r="Z54" s="2" t="n">
+        <v>0.001345245076058092</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -4677,6 +5007,12 @@
       <c r="X55" s="3" t="n">
         <v>-0.003631284916201115</v>
       </c>
+      <c r="Y55" s="1" t="n">
+        <v>0.00717</v>
+      </c>
+      <c r="Z55" s="2" t="n">
+        <v>0.005046257359125377</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -4753,6 +5089,12 @@
       <c r="X56" s="2" t="n">
         <v>0.002817893624515682</v>
       </c>
+      <c r="Y56" s="1" t="n">
+        <v>0.02843</v>
+      </c>
+      <c r="Z56" s="3" t="n">
+        <v>-0.001404987706357512</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -4829,6 +5171,12 @@
       <c r="X57" s="3" t="n">
         <v>-0.009011145364002807</v>
       </c>
+      <c r="Y57" s="1" t="n">
+        <v>0.04221</v>
+      </c>
+      <c r="Z57" s="2" t="n">
+        <v>0.01005025125628133</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -4905,6 +5253,12 @@
       <c r="X58" s="2" t="n">
         <v>0.01476835929597413</v>
       </c>
+      <c r="Y58" s="1" t="n">
+        <v>0.04909</v>
+      </c>
+      <c r="Z58" s="3" t="n">
+        <v>-0.02133173843700163</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -4981,6 +5335,12 @@
       <c r="X59" s="2" t="n">
         <v>0.001291989664082688</v>
       </c>
+      <c r="Y59" s="1" t="n">
+        <v>1.551</v>
+      </c>
+      <c r="Z59" s="2" t="n">
+        <v>0.0006451612903225095</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -5057,6 +5417,12 @@
       <c r="X60" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="Y60" s="1" t="n">
+        <v>0.00345</v>
+      </c>
+      <c r="Z60" s="2" t="n">
+        <v>0.002906976744186054</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -5133,6 +5499,12 @@
       <c r="X61" s="3" t="n">
         <v>-0.003861003861003971</v>
       </c>
+      <c r="Y61" s="1" t="n">
+        <v>0.156</v>
+      </c>
+      <c r="Z61" s="2" t="n">
+        <v>0.007751937984496167</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -5209,6 +5581,12 @@
       <c r="X62" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="Y62" s="1" t="n">
+        <v>1.147</v>
+      </c>
+      <c r="Z62" s="2" t="n">
+        <v>0.001746724890829696</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -5285,6 +5663,12 @@
       <c r="X63" s="3" t="n">
         <v>-0.002424761089716052</v>
       </c>
+      <c r="Y63" s="1" t="n">
+        <v>0.7032</v>
+      </c>
+      <c r="Z63" s="2" t="n">
+        <v>0.005433228481555656</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -5361,6 +5745,12 @@
       <c r="X64" s="3" t="n">
         <v>-0.001021450459652594</v>
       </c>
+      <c r="Y64" s="1" t="n">
+        <v>2.942</v>
+      </c>
+      <c r="Z64" s="2" t="n">
+        <v>0.002726653033401502</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -5437,6 +5827,12 @@
       <c r="X65" s="3" t="n">
         <v>-0.002937473772555628</v>
       </c>
+      <c r="Y65" s="1" t="n">
+        <v>0.02377</v>
+      </c>
+      <c r="Z65" s="2" t="n">
+        <v>0.0004208754208754037</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -5513,6 +5909,12 @@
       <c r="X66" s="3" t="n">
         <v>-0.0009842519685038286</v>
       </c>
+      <c r="Y66" s="1" t="n">
+        <v>0.1019</v>
+      </c>
+      <c r="Z66" s="2" t="n">
+        <v>0.003940886699507365</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -5589,6 +5991,12 @@
       <c r="X67" s="2" t="n">
         <v>0.004184100418410129</v>
       </c>
+      <c r="Y67" s="1" t="n">
+        <v>0.007379</v>
+      </c>
+      <c r="Z67" s="3" t="n">
+        <v>-0.008198924731182835</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -5665,6 +6073,12 @@
       <c r="X68" s="3" t="n">
         <v>-0.007265179034769101</v>
       </c>
+      <c r="Y68" s="1" t="n">
+        <v>18.38</v>
+      </c>
+      <c r="Z68" s="3" t="n">
+        <v>-0.03920543648719289</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -5741,6 +6155,12 @@
       <c r="X69" s="2" t="n">
         <v>0.001296056285872998</v>
       </c>
+      <c r="Y69" s="1" t="n">
+        <v>0.05436</v>
+      </c>
+      <c r="Z69" s="2" t="n">
+        <v>0.005177514792899325</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -5817,6 +6237,12 @@
       <c r="X70" s="3" t="n">
         <v>-0.01680672268907553</v>
       </c>
+      <c r="Y70" s="1" t="n">
+        <v>0.236</v>
+      </c>
+      <c r="Z70" s="2" t="n">
+        <v>0.008547008547008435</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -5893,6 +6319,12 @@
       <c r="X71" s="3" t="n">
         <v>-0.00676848316556746</v>
       </c>
+      <c r="Y71" s="1" t="n">
+        <v>5.741</v>
+      </c>
+      <c r="Z71" s="2" t="n">
+        <v>0.003145203564564004</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -5969,6 +6401,12 @@
       <c r="X72" s="3" t="n">
         <v>-0.002139037433155017</v>
       </c>
+      <c r="Y72" s="1" t="n">
+        <v>0.001826</v>
+      </c>
+      <c r="Z72" s="3" t="n">
+        <v>-0.02143622722400863</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -6045,6 +6483,12 @@
       <c r="X73" s="3" t="n">
         <v>-0.002228116710875322</v>
       </c>
+      <c r="Y73" s="1" t="n">
+        <v>0.9448</v>
+      </c>
+      <c r="Z73" s="2" t="n">
+        <v>0.004678860059549085</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -6121,6 +6565,12 @@
       <c r="X74" s="3" t="n">
         <v>-0.003316749585406282</v>
       </c>
+      <c r="Y74" s="1" t="n">
+        <v>0.1207</v>
+      </c>
+      <c r="Z74" s="2" t="n">
+        <v>0.004159733777038273</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -6197,6 +6647,12 @@
       <c r="X75" s="3" t="n">
         <v>-5.671184710496981e-05</v>
       </c>
+      <c r="Y75" s="1" t="n">
+        <v>354.1</v>
+      </c>
+      <c r="Z75" s="2" t="n">
+        <v>0.004140199637023697</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -6273,6 +6729,12 @@
       <c r="X76" s="2" t="n">
         <v>0.005012318409650898</v>
       </c>
+      <c r="Y76" s="1" t="n">
+        <v>0.11905</v>
+      </c>
+      <c r="Z76" s="2" t="n">
+        <v>0.00633981403212173</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -6349,6 +6811,12 @@
       <c r="X77" s="2" t="n">
         <v>0.001116249402009259</v>
       </c>
+      <c r="Y77" s="1" t="n">
+        <v>0.06307</v>
+      </c>
+      <c r="Z77" s="2" t="n">
+        <v>0.004619305511309311</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -6425,6 +6893,12 @@
       <c r="X78" s="2" t="n">
         <v>0.002646062658763762</v>
       </c>
+      <c r="Y78" s="1" t="n">
+        <v>0.09517</v>
+      </c>
+      <c r="Z78" s="2" t="n">
+        <v>0.004644779900770715</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -6501,6 +6975,12 @@
       <c r="X79" s="3" t="n">
         <v>-0.01434578283452875</v>
       </c>
+      <c r="Y79" s="1" t="n">
+        <v>0.3997</v>
+      </c>
+      <c r="Z79" s="2" t="n">
+        <v>0.003011292346298567</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -6577,6 +7057,12 @@
       <c r="X80" s="3" t="n">
         <v>-0.002158034528552455</v>
       </c>
+      <c r="Y80" s="1" t="n">
+        <v>0.006049</v>
+      </c>
+      <c r="Z80" s="2" t="n">
+        <v>0.006321743470304416</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -6653,6 +7139,12 @@
       <c r="X81" s="2" t="n">
         <v>0.004830917874396139</v>
       </c>
+      <c r="Y81" s="1" t="n">
+        <v>0.1033</v>
+      </c>
+      <c r="Z81" s="3" t="n">
+        <v>-0.006730769230769157</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -6729,6 +7221,12 @@
       <c r="X82" s="3" t="n">
         <v>-0.004906771344455352</v>
       </c>
+      <c r="Y82" s="1" t="n">
+        <v>0.1016</v>
+      </c>
+      <c r="Z82" s="2" t="n">
+        <v>0.001972386587771123</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -6805,6 +7303,12 @@
       <c r="X83" s="2" t="n">
         <v>0.007841855905897749</v>
       </c>
+      <c r="Y83" s="1" t="n">
+        <v>0.06254</v>
+      </c>
+      <c r="Z83" s="2" t="n">
+        <v>0.01377857027070832</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -6881,6 +7385,12 @@
       <c r="X84" s="3" t="n">
         <v>-0.003825282448180938</v>
       </c>
+      <c r="Y84" s="1" t="n">
+        <v>1.1232</v>
+      </c>
+      <c r="Z84" s="2" t="n">
+        <v>0.003036256474370486</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -6957,6 +7467,12 @@
       <c r="X85" s="3" t="n">
         <v>-0.0007651109410864264</v>
       </c>
+      <c r="Y85" s="1" t="n">
+        <v>0.01315</v>
+      </c>
+      <c r="Z85" s="2" t="n">
+        <v>0.006891271056661547</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -7033,6 +7549,12 @@
       <c r="X86" s="3" t="n">
         <v>-0.001190476190476142</v>
       </c>
+      <c r="Y86" s="1" t="n">
+        <v>0.01679</v>
+      </c>
+      <c r="Z86" s="2" t="n">
+        <v>0.0005959475566149936</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -7109,6 +7631,12 @@
       <c r="X87" s="3" t="n">
         <v>-0.0007204610951008919</v>
       </c>
+      <c r="Y87" s="1" t="n">
+        <v>8.351000000000001</v>
+      </c>
+      <c r="Z87" s="2" t="n">
+        <v>0.003484739245373912</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -7185,6 +7713,12 @@
       <c r="X88" s="3" t="n">
         <v>-0.004401779442753385</v>
       </c>
+      <c r="Y88" s="1" t="n">
+        <v>2.1369</v>
+      </c>
+      <c r="Z88" s="2" t="n">
+        <v>0.005079723437279384</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -7261,6 +7795,12 @@
       <c r="X89" s="3" t="n">
         <v>-0.001282965074839676</v>
       </c>
+      <c r="Y89" s="1" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="Z89" s="3" t="n">
+        <v>-0.0008564087924635925</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -7337,6 +7877,12 @@
       <c r="X90" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="Y90" s="1" t="n">
+        <v>15.31</v>
+      </c>
+      <c r="Z90" s="2" t="n">
+        <v>0.001963350785340389</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -7413,6 +7959,12 @@
       <c r="X91" s="3" t="n">
         <v>-0.004444444444444432</v>
       </c>
+      <c r="Y91" s="1" t="n">
+        <v>0.000224</v>
+      </c>
+      <c r="Z91" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -7489,6 +8041,12 @@
       <c r="X92" s="3" t="n">
         <v>-0.005934150076569769</v>
       </c>
+      <c r="Y92" s="1" t="n">
+        <v>0.05218</v>
+      </c>
+      <c r="Z92" s="2" t="n">
+        <v>0.004814172925091474</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -7565,6 +8123,12 @@
       <c r="X93" s="2" t="n">
         <v>0.00173584905660375</v>
       </c>
+      <c r="Y93" s="1" t="n">
+        <v>1.3261</v>
+      </c>
+      <c r="Z93" s="3" t="n">
+        <v>-0.0009040910118284245</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -7641,6 +8205,12 @@
       <c r="X94" s="3" t="n">
         <v>-0.008252818035426731</v>
       </c>
+      <c r="Y94" s="1" t="n">
+        <v>0.054251</v>
+      </c>
+      <c r="Z94" s="2" t="n">
+        <v>0.0009963651124600713</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -7717,6 +8287,12 @@
       <c r="X95" s="3" t="n">
         <v>-0.002487562189054683</v>
       </c>
+      <c r="Y95" s="1" t="n">
+        <v>0.2411</v>
+      </c>
+      <c r="Z95" s="2" t="n">
+        <v>0.002078137988362429</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -7793,6 +8369,12 @@
       <c r="X96" s="3" t="n">
         <v>-0.004095309009679783</v>
       </c>
+      <c r="Y96" s="1" t="n">
+        <v>1.0737</v>
+      </c>
+      <c r="Z96" s="2" t="n">
+        <v>0.003457943925233679</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -7869,6 +8451,12 @@
       <c r="X97" s="3" t="n">
         <v>-0.002331908278274347</v>
       </c>
+      <c r="Y97" s="1" t="n">
+        <v>0.2579</v>
+      </c>
+      <c r="Z97" s="2" t="n">
+        <v>0.004674717569146998</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -7945,6 +8533,12 @@
       <c r="X98" s="3" t="n">
         <v>-0.003442340791738385</v>
       </c>
+      <c r="Y98" s="1" t="n">
+        <v>0.5821</v>
+      </c>
+      <c r="Z98" s="2" t="n">
+        <v>0.005354058721934355</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -8021,6 +8615,12 @@
       <c r="X99" s="2" t="n">
         <v>0.001549701129068082</v>
       </c>
+      <c r="Y99" s="1" t="n">
+        <v>0.13645</v>
+      </c>
+      <c r="Z99" s="2" t="n">
+        <v>0.005378720895962133</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -8097,6 +8697,12 @@
       <c r="X100" s="2" t="n">
         <v>0.003906249999999954</v>
       </c>
+      <c r="Y100" s="1" t="n">
+        <v>0.03106</v>
+      </c>
+      <c r="Z100" s="2" t="n">
+        <v>0.007133592736705624</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -8173,6 +8779,12 @@
       <c r="X101" s="2" t="n">
         <v>0.00289017341040452</v>
       </c>
+      <c r="Y101" s="1" t="n">
+        <v>1.049</v>
+      </c>
+      <c r="Z101" s="2" t="n">
+        <v>0.007684918347742563</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -8249,6 +8861,12 @@
       <c r="X102" s="2" t="n">
         <v>0.0009062075215223917</v>
       </c>
+      <c r="Y102" s="1" t="n">
+        <v>0.02208</v>
+      </c>
+      <c r="Z102" s="3" t="n">
+        <v>-0.0004526935264825529</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -8325,6 +8943,12 @@
       <c r="X103" s="2" t="n">
         <v>0.0005122950819671922</v>
       </c>
+      <c r="Y103" s="1" t="n">
+        <v>0.01963</v>
+      </c>
+      <c r="Z103" s="2" t="n">
+        <v>0.005120327700973009</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -8401,6 +9025,12 @@
       <c r="X104" s="2" t="n">
         <v>0.0003338898163605642</v>
       </c>
+      <c r="Y104" s="1" t="n">
+        <v>3.016</v>
+      </c>
+      <c r="Z104" s="2" t="n">
+        <v>0.006675567423230981</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -8477,6 +9107,12 @@
       <c r="X105" s="3" t="n">
         <v>-0.002151198524892449</v>
       </c>
+      <c r="Y105" s="1" t="n">
+        <v>32.61</v>
+      </c>
+      <c r="Z105" s="2" t="n">
+        <v>0.004311672312904237</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -8553,6 +9189,12 @@
       <c r="X106" s="3" t="n">
         <v>-0.001202645820805807</v>
       </c>
+      <c r="Y106" s="1" t="n">
+        <v>0.1666</v>
+      </c>
+      <c r="Z106" s="2" t="n">
+        <v>0.003010234798314271</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -8629,6 +9271,12 @@
       <c r="X107" s="3" t="n">
         <v>-0.004714959279897204</v>
       </c>
+      <c r="Y107" s="1" t="n">
+        <v>0.4651</v>
+      </c>
+      <c r="Z107" s="2" t="n">
+        <v>0.001507321274763208</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -8705,6 +9353,12 @@
       <c r="X108" s="3" t="n">
         <v>-0.0008923259964307629</v>
       </c>
+      <c r="Y108" s="1" t="n">
+        <v>0.3381</v>
+      </c>
+      <c r="Z108" s="2" t="n">
+        <v>0.00654956832390603</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -8781,6 +9435,12 @@
       <c r="X109" s="3" t="n">
         <v>-0.00395778364116088</v>
       </c>
+      <c r="Y109" s="1" t="n">
+        <v>0.2277</v>
+      </c>
+      <c r="Z109" s="2" t="n">
+        <v>0.005298013245033142</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -8857,6 +9517,12 @@
       <c r="X110" s="3" t="n">
         <v>-0.01182654402102494</v>
       </c>
+      <c r="Y110" s="1" t="n">
+        <v>0.01505</v>
+      </c>
+      <c r="Z110" s="2" t="n">
+        <v>0.0006648936170212495</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -8933,6 +9599,12 @@
       <c r="X111" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="Y111" s="1" t="n">
+        <v>1.844</v>
+      </c>
+      <c r="Z111" s="2" t="n">
+        <v>0.003810560696788306</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -9009,6 +9681,12 @@
       <c r="X112" s="3" t="n">
         <v>-0.001043841336116868</v>
       </c>
+      <c r="Y112" s="1" t="n">
+        <v>0.03828</v>
+      </c>
+      <c r="Z112" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -9085,6 +9763,12 @@
       <c r="X113" s="3" t="n">
         <v>-0.0006978367062107731</v>
       </c>
+      <c r="Y113" s="1" t="n">
+        <v>4.304</v>
+      </c>
+      <c r="Z113" s="2" t="n">
+        <v>0.001862197392923651</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -9161,6 +9845,12 @@
       <c r="X114" s="3" t="n">
         <v>-0.01037562385080117</v>
       </c>
+      <c r="Y114" s="1" t="n">
+        <v>0.007508</v>
+      </c>
+      <c r="Z114" s="3" t="n">
+        <v>-0.003583278035832796</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -9237,6 +9927,12 @@
       <c r="X115" s="3" t="n">
         <v>-0.003502451716201372</v>
       </c>
+      <c r="Y115" s="1" t="n">
+        <v>0.10001</v>
+      </c>
+      <c r="Z115" s="2" t="n">
+        <v>0.004318136171922071</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -9313,6 +10009,12 @@
       <c r="X116" s="3" t="n">
         <v>-0.0006021919788029431</v>
       </c>
+      <c r="Y116" s="1" t="n">
+        <v>0.08332000000000001</v>
+      </c>
+      <c r="Z116" s="2" t="n">
+        <v>0.004097372860930429</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -9389,6 +10091,12 @@
       <c r="X117" s="3" t="n">
         <v>-0.006646726487205057</v>
       </c>
+      <c r="Y117" s="1" t="n">
+        <v>0.3004</v>
+      </c>
+      <c r="Z117" s="2" t="n">
+        <v>0.005018400802944133</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -9465,6 +10173,12 @@
       <c r="X118" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="Y118" s="1" t="n">
+        <v>0.02264</v>
+      </c>
+      <c r="Z118" s="2" t="n">
+        <v>0.00176991150442486</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -9541,6 +10255,12 @@
       <c r="X119" s="3" t="n">
         <v>-0.001300390117035148</v>
       </c>
+      <c r="Y119" s="1" t="n">
+        <v>0.1544</v>
+      </c>
+      <c r="Z119" s="2" t="n">
+        <v>0.005208333333333483</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -9617,6 +10337,12 @@
       <c r="X120" s="2" t="n">
         <v>0.02167042889390513</v>
       </c>
+      <c r="Y120" s="1" t="n">
+        <v>0.004425</v>
+      </c>
+      <c r="Z120" s="3" t="n">
+        <v>-0.02231551038444532</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -9693,6 +10419,12 @@
       <c r="X121" s="3" t="n">
         <v>-0.003433279926756698</v>
       </c>
+      <c r="Y121" s="1" t="n">
+        <v>0.4372</v>
+      </c>
+      <c r="Z121" s="2" t="n">
+        <v>0.004134129536058724</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -9769,6 +10501,12 @@
       <c r="X122" s="3" t="n">
         <v>-0.002570694087403601</v>
       </c>
+      <c r="Y122" s="1" t="n">
+        <v>0.778</v>
+      </c>
+      <c r="Z122" s="2" t="n">
+        <v>0.002577319587628868</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -9845,6 +10583,12 @@
       <c r="X123" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="Y123" s="1" t="n">
+        <v>0.0868</v>
+      </c>
+      <c r="Z123" s="2" t="n">
+        <v>0.002309468822170967</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -9921,6 +10665,12 @@
       <c r="X124" s="3" t="n">
         <v>-0.004866180048661883</v>
       </c>
+      <c r="Y124" s="1" t="n">
+        <v>0.01229</v>
+      </c>
+      <c r="Z124" s="2" t="n">
+        <v>0.001629991850040825</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -9997,6 +10747,12 @@
       <c r="X125" s="3" t="n">
         <v>-0.0009223201475712927</v>
       </c>
+      <c r="Y125" s="1" t="n">
+        <v>0.0979</v>
+      </c>
+      <c r="Z125" s="2" t="n">
+        <v>0.004205559544568751</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -10073,6 +10829,12 @@
       <c r="X126" s="3" t="n">
         <v>-0.002136295663319717</v>
       </c>
+      <c r="Y126" s="1" t="n">
+        <v>0.04684</v>
+      </c>
+      <c r="Z126" s="2" t="n">
+        <v>0.00278312995075997</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -10149,6 +10911,12 @@
       <c r="X127" s="3" t="n">
         <v>-0.006134969325153315</v>
       </c>
+      <c r="Y127" s="1" t="n">
+        <v>3.24e-05</v>
+      </c>
+      <c r="Z127" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -10225,6 +10993,12 @@
       <c r="X128" s="3" t="n">
         <v>-0.001945525291828776</v>
       </c>
+      <c r="Y128" s="1" t="n">
+        <v>0.5689</v>
+      </c>
+      <c r="Z128" s="2" t="n">
+        <v>0.008151692362218566</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -10301,6 +11075,12 @@
       <c r="X129" s="3" t="n">
         <v>-0.001382063882063772</v>
       </c>
+      <c r="Y129" s="1" t="n">
+        <v>0.0648</v>
+      </c>
+      <c r="Z129" s="3" t="n">
+        <v>-0.00353682915577438</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -10377,6 +11157,12 @@
       <c r="X130" s="2" t="n">
         <v>0.002942137953579495</v>
       </c>
+      <c r="Y130" s="1" t="n">
+        <v>0.0006115</v>
+      </c>
+      <c r="Z130" s="3" t="n">
+        <v>-0.003422425032594519</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -10453,6 +11239,12 @@
       <c r="X131" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="Y131" s="1" t="n">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="Z131" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -10529,6 +11321,12 @@
       <c r="X132" s="3" t="n">
         <v>-0.001327140013271438</v>
       </c>
+      <c r="Y132" s="1" t="n">
+        <v>0.3029</v>
+      </c>
+      <c r="Z132" s="2" t="n">
+        <v>0.00631229235880403</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -10605,6 +11403,12 @@
       <c r="X133" s="2" t="n">
         <v>0.01066666666666664</v>
       </c>
+      <c r="Y133" s="1" t="n">
+        <v>0.03393</v>
+      </c>
+      <c r="Z133" s="3" t="n">
+        <v>-0.005277044854881255</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -10681,6 +11485,12 @@
       <c r="X134" s="3" t="n">
         <v>-0.003055131231773337</v>
       </c>
+      <c r="Y134" s="1" t="n">
+        <v>0.14361</v>
+      </c>
+      <c r="Z134" s="2" t="n">
+        <v>0.0002089427496864082</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -10757,6 +11567,12 @@
       <c r="X135" s="3" t="n">
         <v>-0.001346801346801409</v>
       </c>
+      <c r="Y135" s="1" t="n">
+        <v>0.02982</v>
+      </c>
+      <c r="Z135" s="2" t="n">
+        <v>0.00539447066756576</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -10833,6 +11649,12 @@
       <c r="X136" s="3" t="n">
         <v>-0.004250797024442118</v>
       </c>
+      <c r="Y136" s="1" t="n">
+        <v>28.23</v>
+      </c>
+      <c r="Z136" s="2" t="n">
+        <v>0.004268943436499502</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -10909,6 +11731,12 @@
       <c r="X137" s="3" t="n">
         <v>-0.000690289921767159</v>
       </c>
+      <c r="Y137" s="1" t="n">
+        <v>0.0004401</v>
+      </c>
+      <c r="Z137" s="2" t="n">
+        <v>0.01335482385447855</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -10985,6 +11813,12 @@
       <c r="X138" s="2" t="n">
         <v>0.0006440241339569584</v>
       </c>
+      <c r="Y138" s="1" t="n">
+        <v>0.029487</v>
+      </c>
+      <c r="Z138" s="3" t="n">
+        <v>-0.001151722502625226</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -11061,6 +11895,12 @@
       <c r="X139" s="3" t="n">
         <v>-0.004248704663212513</v>
       </c>
+      <c r="Y139" s="1" t="n">
+        <v>0.09664</v>
+      </c>
+      <c r="Z139" s="2" t="n">
+        <v>0.005723800603600883</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -11137,6 +11977,12 @@
       <c r="X140" s="3" t="n">
         <v>-0.008291873963515762</v>
       </c>
+      <c r="Y140" s="1" t="n">
+        <v>0.3611</v>
+      </c>
+      <c r="Z140" s="2" t="n">
+        <v>0.006410256410256323</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -11213,6 +12059,12 @@
       <c r="X141" s="2" t="n">
         <v>0.003422053231939156</v>
       </c>
+      <c r="Y141" s="1" t="n">
+        <v>0.02635</v>
+      </c>
+      <c r="Z141" s="3" t="n">
+        <v>-0.001515725653656758</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -11289,6 +12141,12 @@
       <c r="X142" s="2" t="n">
         <v>0.001902104996195756</v>
       </c>
+      <c r="Y142" s="1" t="n">
+        <v>0.0794</v>
+      </c>
+      <c r="Z142" s="2" t="n">
+        <v>0.004936084039994956</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -11365,6 +12223,12 @@
       <c r="X143" s="3" t="n">
         <v>-0.0002264749179029116</v>
       </c>
+      <c r="Y143" s="1" t="n">
+        <v>0.08846999999999999</v>
+      </c>
+      <c r="Z143" s="2" t="n">
+        <v>0.002038735983690108</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -11441,6 +12305,12 @@
       <c r="X144" s="2" t="n">
         <v>0.003416300634455693</v>
       </c>
+      <c r="Y144" s="1" t="n">
+        <v>0.02064</v>
+      </c>
+      <c r="Z144" s="2" t="n">
+        <v>0.003891050583657598</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -11517,6 +12387,12 @@
       <c r="X145" s="3" t="n">
         <v>-0.002001044022968454</v>
       </c>
+      <c r="Y145" s="1" t="n">
+        <v>0.11476</v>
+      </c>
+      <c r="Z145" s="2" t="n">
+        <v>0.0004358817888588134</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -11593,6 +12469,12 @@
       <c r="X146" s="3" t="n">
         <v>-0.006591957811470013</v>
       </c>
+      <c r="Y146" s="1" t="n">
+        <v>0.3035</v>
+      </c>
+      <c r="Z146" s="2" t="n">
+        <v>0.00696748506967482</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -11669,6 +12551,12 @@
       <c r="X147" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="Y147" s="1" t="n">
+        <v>0.123</v>
+      </c>
+      <c r="Z147" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -11745,6 +12633,12 @@
       <c r="X148" s="2" t="n">
         <v>0.00297146370203393</v>
       </c>
+      <c r="Y148" s="1" t="n">
+        <v>1.9648</v>
+      </c>
+      <c r="Z148" s="2" t="n">
+        <v>0.003626704806660932</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -11821,6 +12715,12 @@
       <c r="X149" s="3" t="n">
         <v>-0.0003239390994494027</v>
       </c>
+      <c r="Y149" s="1" t="n">
+        <v>0.06168</v>
+      </c>
+      <c r="Z149" s="3" t="n">
+        <v>-0.0006480881399870119</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -11897,6 +12797,12 @@
       <c r="X150" s="3" t="n">
         <v>-0.01099572388515592</v>
       </c>
+      <c r="Y150" s="1" t="n">
+        <v>0.1619</v>
+      </c>
+      <c r="Z150" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -11973,6 +12879,12 @@
       <c r="X151" s="3" t="n">
         <v>-0.001939430105922728</v>
       </c>
+      <c r="Y151" s="1" t="n">
+        <v>6.732e-05</v>
+      </c>
+      <c r="Z151" s="2" t="n">
+        <v>0.006278026905829587</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -12049,6 +12961,12 @@
       <c r="X152" s="3" t="n">
         <v>-0.006747638326585655</v>
       </c>
+      <c r="Y152" s="1" t="n">
+        <v>0.01487</v>
+      </c>
+      <c r="Z152" s="2" t="n">
+        <v>0.01019021739130429</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -12125,6 +13043,12 @@
       <c r="X153" s="2" t="n">
         <v>0.0004764173415912145</v>
       </c>
+      <c r="Y153" s="1" t="n">
+        <v>0.02112</v>
+      </c>
+      <c r="Z153" s="2" t="n">
+        <v>0.005714285714285647</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -12201,6 +13125,12 @@
       <c r="X154" s="3" t="n">
         <v>-0.004032258064516227</v>
       </c>
+      <c r="Y154" s="1" t="n">
+        <v>0.000596</v>
+      </c>
+      <c r="Z154" s="2" t="n">
+        <v>0.005398110661268505</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -12277,6 +13207,12 @@
       <c r="X155" s="3" t="n">
         <v>-0.002486325211337542</v>
       </c>
+      <c r="Y155" s="1" t="n">
+        <v>0.04028</v>
+      </c>
+      <c r="Z155" s="2" t="n">
+        <v>0.003988035892323041</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -12353,6 +13289,12 @@
       <c r="X156" s="3" t="n">
         <v>-0.0005299417064124569</v>
       </c>
+      <c r="Y156" s="1" t="n">
+        <v>0.01898</v>
+      </c>
+      <c r="Z156" s="2" t="n">
+        <v>0.006362672322375507</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -12429,6 +13371,12 @@
       <c r="X157" s="2" t="n">
         <v>0.0009179575444635311</v>
       </c>
+      <c r="Y157" s="1" t="n">
+        <v>0.08782</v>
+      </c>
+      <c r="Z157" s="2" t="n">
+        <v>0.006763728075203408</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -12505,6 +13453,12 @@
       <c r="X158" s="2" t="n">
         <v>0.03327603143418473</v>
       </c>
+      <c r="Y158" s="1" t="n">
+        <v>0.008460000000000001</v>
+      </c>
+      <c r="Z158" s="2" t="n">
+        <v>0.005347593582887688</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -12581,6 +13535,12 @@
       <c r="X159" s="2" t="n">
         <v>0.002402883460152274</v>
       </c>
+      <c r="Y159" s="1" t="n">
+        <v>2.518</v>
+      </c>
+      <c r="Z159" s="2" t="n">
+        <v>0.005992808629644299</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -12657,6 +13617,12 @@
       <c r="X160" s="3" t="n">
         <v>-0.001481481481481491</v>
       </c>
+      <c r="Y160" s="1" t="n">
+        <v>1.2867</v>
+      </c>
+      <c r="Z160" s="2" t="n">
+        <v>0.004763392159925031</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -12733,6 +13699,12 @@
       <c r="X161" s="3" t="n">
         <v>-0.00146627565982401</v>
       </c>
+      <c r="Y161" s="1" t="n">
+        <v>0.007507</v>
+      </c>
+      <c r="Z161" s="2" t="n">
+        <v>0.002135896409024098</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -12809,6 +13781,12 @@
       <c r="X162" s="3" t="n">
         <v>-0.02562310738411364</v>
       </c>
+      <c r="Y162" s="1" t="n">
+        <v>0.004077</v>
+      </c>
+      <c r="Z162" s="3" t="n">
+        <v>-0.02534066459478847</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -12885,6 +13863,12 @@
       <c r="X163" s="3" t="n">
         <v>-0.002076843198338441</v>
       </c>
+      <c r="Y163" s="1" t="n">
+        <v>0.0965</v>
+      </c>
+      <c r="Z163" s="2" t="n">
+        <v>0.004162330905306946</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -12961,6 +13945,12 @@
       <c r="X164" s="3" t="n">
         <v>-0.001589710239179117</v>
       </c>
+      <c r="Y164" s="1" t="n">
+        <v>1.3875</v>
+      </c>
+      <c r="Z164" s="2" t="n">
+        <v>0.004197727437215045</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -13037,6 +14027,12 @@
       <c r="X165" s="2" t="n">
         <v>0.0008920227678192246</v>
       </c>
+      <c r="Y165" s="1" t="n">
+        <v>0.023805</v>
+      </c>
+      <c r="Z165" s="2" t="n">
+        <v>0.01027033909094764</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -13113,6 +14109,12 @@
       <c r="X166" s="3" t="n">
         <v>-0.006040530007794358</v>
       </c>
+      <c r="Y166" s="1" t="n">
+        <v>0.005139</v>
+      </c>
+      <c r="Z166" s="2" t="n">
+        <v>0.007449519702019351</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -13189,6 +14191,12 @@
       <c r="X167" s="3" t="n">
         <v>-0.0004548211036992457</v>
       </c>
+      <c r="Y167" s="1" t="n">
+        <v>0.06610000000000001</v>
+      </c>
+      <c r="Z167" s="2" t="n">
+        <v>0.002578492340361042</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -13265,6 +14273,12 @@
       <c r="X168" s="2" t="n">
         <v>0.002105263157894797</v>
       </c>
+      <c r="Y168" s="1" t="n">
+        <v>0.0959</v>
+      </c>
+      <c r="Z168" s="2" t="n">
+        <v>0.007352941176470507</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -13341,6 +14355,12 @@
       <c r="X169" s="2" t="n">
         <v>0.004993429697766168</v>
       </c>
+      <c r="Y169" s="1" t="n">
+        <v>0.03848</v>
+      </c>
+      <c r="Z169" s="2" t="n">
+        <v>0.006276150627614988</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -13417,6 +14437,12 @@
       <c r="X170" s="3" t="n">
         <v>-0.0009799804003920009</v>
       </c>
+      <c r="Y170" s="1" t="n">
+        <v>0.007159</v>
+      </c>
+      <c r="Z170" s="2" t="n">
+        <v>0.003223094170403651</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -13493,6 +14519,12 @@
       <c r="X171" s="3" t="n">
         <v>-0.002052184110231703</v>
       </c>
+      <c r="Y171" s="1" t="n">
+        <v>0.3414</v>
+      </c>
+      <c r="Z171" s="2" t="n">
+        <v>0.002937720329024679</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -13569,6 +14601,12 @@
       <c r="X172" s="3" t="n">
         <v>-0.003120984027905333</v>
       </c>
+      <c r="Y172" s="1" t="n">
+        <v>5.467</v>
+      </c>
+      <c r="Z172" s="2" t="n">
+        <v>0.006813996316758734</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -13645,6 +14683,12 @@
       <c r="X173" s="3" t="n">
         <v>-0.001973251479938606</v>
       </c>
+      <c r="Y173" s="1" t="n">
+        <v>0.0458</v>
+      </c>
+      <c r="Z173" s="2" t="n">
+        <v>0.006151142355008842</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -13721,6 +14765,12 @@
       <c r="X174" s="3" t="n">
         <v>-0.0007688364941056445</v>
       </c>
+      <c r="Y174" s="1" t="n">
+        <v>0.03921</v>
+      </c>
+      <c r="Z174" s="2" t="n">
+        <v>0.005642472428828031</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -13797,6 +14847,12 @@
       <c r="X175" s="3" t="n">
         <v>-0.0137352836246878</v>
       </c>
+      <c r="Y175" s="1" t="n">
+        <v>0.005606</v>
+      </c>
+      <c r="Z175" s="2" t="n">
+        <v>0.0139265689998191</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -13873,6 +14929,12 @@
       <c r="X176" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="Y176" s="1" t="n">
+        <v>0.00758</v>
+      </c>
+      <c r="Z176" s="2" t="n">
+        <v>0.002645502645502652</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -13949,6 +15011,12 @@
       <c r="X177" s="3" t="n">
         <v>-0.003925967470555186</v>
       </c>
+      <c r="Y177" s="1" t="n">
+        <v>1.783</v>
+      </c>
+      <c r="Z177" s="2" t="n">
+        <v>0.003941441441441382</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -14025,6 +15093,12 @@
       <c r="X178" s="3" t="n">
         <v>-0.001018589253883373</v>
       </c>
+      <c r="Y178" s="1" t="n">
+        <v>15.744</v>
+      </c>
+      <c r="Z178" s="2" t="n">
+        <v>0.00331379046647971</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -14101,6 +15175,12 @@
       <c r="X179" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="Y179" s="1" t="n">
+        <v>0.314</v>
+      </c>
+      <c r="Z179" s="2" t="n">
+        <v>0.006410256410256416</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -14177,6 +15257,12 @@
       <c r="X180" s="3" t="n">
         <v>-0.001856052794390592</v>
       </c>
+      <c r="Y180" s="1" t="n">
+        <v>0.09807</v>
+      </c>
+      <c r="Z180" s="2" t="n">
+        <v>0.01311983471074388</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -14253,6 +15339,12 @@
       <c r="X181" s="3" t="n">
         <v>-0.002132196162046822</v>
       </c>
+      <c r="Y181" s="1" t="n">
+        <v>0.1885</v>
+      </c>
+      <c r="Z181" s="2" t="n">
+        <v>0.006944444444444421</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -14329,6 +15421,12 @@
       <c r="X182" s="3" t="n">
         <v>-0.0001688903901367357</v>
       </c>
+      <c r="Y182" s="1" t="n">
+        <v>0.05932</v>
+      </c>
+      <c r="Z182" s="2" t="n">
+        <v>0.002027027027026944</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -14405,6 +15503,12 @@
       <c r="X183" s="3" t="n">
         <v>-0.002500000000000043</v>
       </c>
+      <c r="Y183" s="1" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="Z183" s="2" t="n">
+        <v>0.002506265664160444</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -14481,6 +15585,12 @@
       <c r="X184" s="3" t="n">
         <v>-0.002802428771601941</v>
       </c>
+      <c r="Y184" s="1" t="n">
+        <v>0.02148</v>
+      </c>
+      <c r="Z184" s="2" t="n">
+        <v>0.00608899297423879</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -14557,6 +15667,12 @@
       <c r="X185" s="2" t="n">
         <v>0.002739726027397263</v>
       </c>
+      <c r="Y185" s="1" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="Z185" s="2" t="n">
+        <v>0.005464480874316945</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -14633,6 +15749,12 @@
       <c r="X186" s="3" t="n">
         <v>-0.00157129762995939</v>
       </c>
+      <c r="Y186" s="1" t="n">
+        <v>0.007649</v>
+      </c>
+      <c r="Z186" s="2" t="n">
+        <v>0.003147540983606634</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -14709,6 +15831,12 @@
       <c r="X187" s="3" t="n">
         <v>-0.003333333333333377</v>
       </c>
+      <c r="Y187" s="1" t="n">
+        <v>0.2711</v>
+      </c>
+      <c r="Z187" s="2" t="n">
+        <v>0.00743218134522483</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -14785,6 +15913,12 @@
       <c r="X188" s="3" t="n">
         <v>-0.001827040194884283</v>
       </c>
+      <c r="Y188" s="1" t="n">
+        <v>0.04946</v>
+      </c>
+      <c r="Z188" s="2" t="n">
+        <v>0.005897905226764259</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -14861,6 +15995,12 @@
       <c r="X189" s="3" t="n">
         <v>-0.003508771929824608</v>
       </c>
+      <c r="Y189" s="1" t="n">
+        <v>0.2566</v>
+      </c>
+      <c r="Z189" s="2" t="n">
+        <v>0.003912363067292648</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -14937,6 +16077,12 @@
       <c r="X190" s="3" t="n">
         <v>-0.0001760253476502376</v>
       </c>
+      <c r="Y190" s="1" t="n">
+        <v>0.5703</v>
+      </c>
+      <c r="Z190" s="2" t="n">
+        <v>0.004049295774648029</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -15013,6 +16159,12 @@
       <c r="X191" s="3" t="n">
         <v>-0.001653986106516817</v>
       </c>
+      <c r="Y191" s="1" t="n">
+        <v>6.06</v>
+      </c>
+      <c r="Z191" s="2" t="n">
+        <v>0.003976143141153085</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -15089,6 +16241,12 @@
       <c r="X192" s="3" t="n">
         <v>-0.002565564424173352</v>
       </c>
+      <c r="Y192" s="1" t="n">
+        <v>0.3507</v>
+      </c>
+      <c r="Z192" s="2" t="n">
+        <v>0.002286367533581089</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -15165,6 +16323,12 @@
       <c r="X193" s="3" t="n">
         <v>-0.0015698587127159</v>
       </c>
+      <c r="Y193" s="1" t="n">
+        <v>0.0638</v>
+      </c>
+      <c r="Z193" s="2" t="n">
+        <v>0.003144654088050186</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -15241,6 +16405,12 @@
       <c r="X194" s="2" t="n">
         <v>0.002886836027713709</v>
       </c>
+      <c r="Y194" s="1" t="n">
+        <v>0.01727</v>
+      </c>
+      <c r="Z194" s="3" t="n">
+        <v>-0.005757052389176707</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -15317,6 +16487,12 @@
       <c r="X195" s="2" t="n">
         <v>0.001302545885139103</v>
       </c>
+      <c r="Y195" s="1" t="n">
+        <v>0.0008474</v>
+      </c>
+      <c r="Z195" s="2" t="n">
+        <v>0.002128666035950856</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -15393,6 +16569,12 @@
       <c r="X196" s="3" t="n">
         <v>-0.02314814814814821</v>
       </c>
+      <c r="Y196" s="1" t="n">
+        <v>0.001047</v>
+      </c>
+      <c r="Z196" s="3" t="n">
+        <v>-0.007582938388625572</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -15469,6 +16651,12 @@
       <c r="X197" s="3" t="n">
         <v>-0.004315659679408243</v>
       </c>
+      <c r="Y197" s="1" t="n">
+        <v>0.0001621</v>
+      </c>
+      <c r="Z197" s="2" t="n">
+        <v>0.003715170278637861</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -15545,6 +16733,12 @@
       <c r="X198" s="3" t="n">
         <v>-0.001384083044982751</v>
       </c>
+      <c r="Y198" s="1" t="n">
+        <v>4.338</v>
+      </c>
+      <c r="Z198" s="2" t="n">
+        <v>0.002079002079002158</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -15621,6 +16815,12 @@
       <c r="X199" s="3" t="n">
         <v>-0.002461538461538532</v>
       </c>
+      <c r="Y199" s="1" t="n">
+        <v>0.1631</v>
+      </c>
+      <c r="Z199" s="2" t="n">
+        <v>0.006169031462060462</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -15697,6 +16897,12 @@
       <c r="X200" s="3" t="n">
         <v>-0.008262306488084849</v>
       </c>
+      <c r="Y200" s="1" t="n">
+        <v>0.023026</v>
+      </c>
+      <c r="Z200" s="2" t="n">
+        <v>0.009646584232219655</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -15773,6 +16979,12 @@
       <c r="X201" s="2" t="n">
         <v>0.00437636761487964</v>
       </c>
+      <c r="Y201" s="1" t="n">
+        <v>0.12409</v>
+      </c>
+      <c r="Z201" s="2" t="n">
+        <v>0.001291051399983921</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -15849,6 +17061,12 @@
       <c r="X202" s="3" t="n">
         <v>-0.0007209805335255654</v>
       </c>
+      <c r="Y202" s="1" t="n">
+        <v>0.01394</v>
+      </c>
+      <c r="Z202" s="2" t="n">
+        <v>0.005772005772005662</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -15925,6 +17143,12 @@
       <c r="X203" s="2" t="n">
         <v>0.0004857906242409324</v>
       </c>
+      <c r="Y203" s="1" t="n">
+        <v>0.04123</v>
+      </c>
+      <c r="Z203" s="2" t="n">
+        <v>0.000971109492595419</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -16001,6 +17225,12 @@
       <c r="X204" s="2" t="n">
         <v>0.0003877471888328652</v>
       </c>
+      <c r="Y204" s="1" t="n">
+        <v>0.02596</v>
+      </c>
+      <c r="Z204" s="2" t="n">
+        <v>0.006201550387596916</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -16077,6 +17307,12 @@
       <c r="X205" s="3" t="n">
         <v>-0.001851851851851776</v>
       </c>
+      <c r="Y205" s="1" t="n">
+        <v>0.4317</v>
+      </c>
+      <c r="Z205" s="2" t="n">
+        <v>0.001159554730983175</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -16153,6 +17389,12 @@
       <c r="X206" s="3" t="n">
         <v>-0.002186270222999625</v>
       </c>
+      <c r="Y206" s="1" t="n">
+        <v>0.02291</v>
+      </c>
+      <c r="Z206" s="2" t="n">
+        <v>0.003943908851884303</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -16229,6 +17471,12 @@
       <c r="X207" s="3" t="n">
         <v>-0.0009573958831975969</v>
       </c>
+      <c r="Y207" s="1" t="n">
+        <v>4.192</v>
+      </c>
+      <c r="Z207" s="2" t="n">
+        <v>0.004312410158121656</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -16305,6 +17553,12 @@
       <c r="X208" s="3" t="n">
         <v>-0.001085187194791057</v>
       </c>
+      <c r="Y208" s="1" t="n">
+        <v>0.07378999999999999</v>
+      </c>
+      <c r="Z208" s="2" t="n">
+        <v>0.002036936447582799</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -16381,6 +17635,12 @@
       <c r="X209" s="3" t="n">
         <v>-0.001664684898929695</v>
       </c>
+      <c r="Y209" s="1" t="n">
+        <v>0.04212</v>
+      </c>
+      <c r="Z209" s="2" t="n">
+        <v>0.003334921391138501</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -16457,6 +17717,12 @@
       <c r="X210" s="3" t="n">
         <v>-0.001618122977346399</v>
       </c>
+      <c r="Y210" s="1" t="n">
+        <v>0.1857</v>
+      </c>
+      <c r="Z210" s="2" t="n">
+        <v>0.003241491085899607</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -16533,6 +17799,12 @@
       <c r="X211" s="2" t="n">
         <v>0.0004249893752655715</v>
       </c>
+      <c r="Y211" s="1" t="n">
+        <v>0.2359</v>
+      </c>
+      <c r="Z211" s="2" t="n">
+        <v>0.002124044180118948</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -16609,6 +17881,12 @@
       <c r="X212" s="2" t="n">
         <v>0.002401536983669451</v>
       </c>
+      <c r="Y212" s="1" t="n">
+        <v>0.002083</v>
+      </c>
+      <c r="Z212" s="3" t="n">
+        <v>-0.001916626736942819</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -16685,6 +17963,12 @@
       <c r="X213" s="3" t="n">
         <v>-0.003215434083601289</v>
       </c>
+      <c r="Y213" s="1" t="n">
+        <v>0.9330000000000001</v>
+      </c>
+      <c r="Z213" s="2" t="n">
+        <v>0.003225806451612906</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -16761,6 +18045,12 @@
       <c r="X214" s="3" t="n">
         <v>-0.00332225913621261</v>
       </c>
+      <c r="Y214" s="1" t="n">
+        <v>0.005718</v>
+      </c>
+      <c r="Z214" s="2" t="n">
+        <v>0.003157894736842068</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -16837,6 +18127,12 @@
       <c r="X215" s="3" t="n">
         <v>-0.001461454146876082</v>
       </c>
+      <c r="Y215" s="1" t="n">
+        <v>0.0548</v>
+      </c>
+      <c r="Z215" s="2" t="n">
+        <v>0.002561287961946602</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -16913,6 +18209,12 @@
       <c r="X216" s="3" t="n">
         <v>-0.003164556962025407</v>
       </c>
+      <c r="Y216" s="1" t="n">
+        <v>0.0633</v>
+      </c>
+      <c r="Z216" s="2" t="n">
+        <v>0.004761904761904678</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -16989,6 +18291,12 @@
       <c r="X217" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="Y217" s="1" t="n">
+        <v>0.093</v>
+      </c>
+      <c r="Z217" s="2" t="n">
+        <v>0.002155172413793165</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -17065,6 +18373,12 @@
       <c r="X218" s="2" t="n">
         <v>0.003217061268751137</v>
       </c>
+      <c r="Y218" s="1" t="n">
+        <v>0.27777</v>
+      </c>
+      <c r="Z218" s="2" t="n">
+        <v>0.0008287093752252215</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -17141,6 +18455,12 @@
       <c r="X219" s="3" t="n">
         <v>-0.005194011610143494</v>
       </c>
+      <c r="Y219" s="1" t="n">
+        <v>0.00328</v>
+      </c>
+      <c r="Z219" s="2" t="n">
+        <v>0.007371007371007284</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -17217,6 +18537,12 @@
       <c r="X220" s="2" t="n">
         <v>1.00062739340442e-06</v>
       </c>
+      <c r="Y220" s="1" t="n">
+        <v>0.999373</v>
+      </c>
+      <c r="Z220" s="3" t="n">
+        <v>-1.000626392150242e-06</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -17293,6 +18619,12 @@
       <c r="X221" s="2" t="n">
         <v>0.001027485229899778</v>
       </c>
+      <c r="Y221" s="1" t="n">
+        <v>0.0392</v>
+      </c>
+      <c r="Z221" s="2" t="n">
+        <v>0.005901975878881217</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -17369,6 +18701,12 @@
       <c r="X222" s="3" t="n">
         <v>-0.001930501930501926</v>
       </c>
+      <c r="Y222" s="1" t="n">
+        <v>0.0468</v>
+      </c>
+      <c r="Z222" s="2" t="n">
+        <v>0.005802707930367492</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -17445,6 +18783,12 @@
       <c r="X223" s="3" t="n">
         <v>-0.001895734597156321</v>
       </c>
+      <c r="Y223" s="1" t="n">
+        <v>0.106</v>
+      </c>
+      <c r="Z223" s="2" t="n">
+        <v>0.006647673314339907</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -17521,6 +18865,12 @@
       <c r="X224" s="3" t="n">
         <v>-0.0002557544757034102</v>
       </c>
+      <c r="Y224" s="1" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="Z224" s="2" t="n">
+        <v>0.002814018930672838</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -17597,6 +18947,12 @@
       <c r="X225" s="3" t="n">
         <v>-0.002705920554172537</v>
       </c>
+      <c r="Y225" s="1" t="n">
+        <v>0.0009259</v>
+      </c>
+      <c r="Z225" s="2" t="n">
+        <v>0.004883872368135506</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -17673,6 +19029,12 @@
       <c r="X226" s="2" t="n">
         <v>0.004698144233027966</v>
       </c>
+      <c r="Y226" s="1" t="n">
+        <v>0.008571</v>
+      </c>
+      <c r="Z226" s="2" t="n">
+        <v>0.001987374327799819</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -17749,6 +19111,12 @@
       <c r="X227" s="3" t="n">
         <v>-0.0007256894049347423</v>
       </c>
+      <c r="Y227" s="1" t="n">
+        <v>0.04149</v>
+      </c>
+      <c r="Z227" s="2" t="n">
+        <v>0.004357298474945525</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -17825,6 +19193,12 @@
       <c r="X228" s="3" t="n">
         <v>-0.005893909626719109</v>
       </c>
+      <c r="Y228" s="1" t="n">
+        <v>0.03565</v>
+      </c>
+      <c r="Z228" s="2" t="n">
+        <v>0.006493506493506523</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -17901,6 +19275,12 @@
       <c r="X229" s="2" t="n">
         <v>0.0005825242718447038</v>
       </c>
+      <c r="Y229" s="1" t="n">
+        <v>0.05191</v>
+      </c>
+      <c r="Z229" s="2" t="n">
+        <v>0.007374345041723237</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -17977,6 +19357,12 @@
       <c r="X230" s="2" t="n">
         <v>0.0005780346820808762</v>
       </c>
+      <c r="Y230" s="1" t="n">
+        <v>0.001745</v>
+      </c>
+      <c r="Z230" s="2" t="n">
+        <v>0.00808781051415374</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -18053,6 +19439,12 @@
       <c r="X231" s="3" t="n">
         <v>-0.0002059308072486846</v>
       </c>
+      <c r="Y231" s="1" t="n">
+        <v>0.04857</v>
+      </c>
+      <c r="Z231" s="2" t="n">
+        <v>0.0004119464469618782</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -18129,6 +19521,12 @@
       <c r="X232" s="2" t="n">
         <v>0.002762430939226566</v>
       </c>
+      <c r="Y232" s="1" t="n">
+        <v>0.0219</v>
+      </c>
+      <c r="Z232" s="2" t="n">
+        <v>0.005509641873278171</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -18205,6 +19603,12 @@
       <c r="X233" s="3" t="n">
         <v>-0.0006832934745473347</v>
       </c>
+      <c r="Y233" s="1" t="n">
+        <v>0.0005888999999999999</v>
+      </c>
+      <c r="Z233" s="2" t="n">
+        <v>0.006666666666666551</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -18281,6 +19685,12 @@
       <c r="X234" s="3" t="n">
         <v>-0.00745719020438217</v>
       </c>
+      <c r="Y234" s="1" t="n">
+        <v>0.21594</v>
+      </c>
+      <c r="Z234" s="2" t="n">
+        <v>0.00148409238475089</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -18357,6 +19767,12 @@
       <c r="X235" s="2" t="n">
         <v>0.00143061516452081</v>
       </c>
+      <c r="Y235" s="1" t="n">
+        <v>0.01407</v>
+      </c>
+      <c r="Z235" s="2" t="n">
+        <v>0.00499999999999992</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -18433,6 +19849,12 @@
       <c r="X236" s="3" t="n">
         <v>-0.002421307506053338</v>
       </c>
+      <c r="Y236" s="1" t="n">
+        <v>0.0415</v>
+      </c>
+      <c r="Z236" s="2" t="n">
+        <v>0.007281553398058293</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -18509,6 +19931,12 @@
       <c r="X237" s="3" t="n">
         <v>-0.002380952380952284</v>
       </c>
+      <c r="Y237" s="1" t="n">
+        <v>0.00419</v>
+      </c>
+      <c r="Z237" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -18585,6 +20013,12 @@
       <c r="X238" s="3" t="n">
         <v>-0.004000000000000115</v>
       </c>
+      <c r="Y238" s="1" t="n">
+        <v>0.0249</v>
+      </c>
+      <c r="Z238" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -18661,6 +20095,12 @@
       <c r="X239" s="2" t="n">
         <v>0.002673796791443857</v>
       </c>
+      <c r="Y239" s="1" t="n">
+        <v>0.01501</v>
+      </c>
+      <c r="Z239" s="2" t="n">
+        <v>0.0006666666666667552</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -18737,6 +20177,12 @@
       <c r="X240" s="3" t="n">
         <v>-0.001784803671596168</v>
       </c>
+      <c r="Y240" s="1" t="n">
+        <v>0.0003936</v>
+      </c>
+      <c r="Z240" s="2" t="n">
+        <v>0.005363984674329633</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -18813,6 +20259,12 @@
       <c r="X241" s="3" t="n">
         <v>-0.005565862708719856</v>
       </c>
+      <c r="Y241" s="1" t="n">
+        <v>0.2693</v>
+      </c>
+      <c r="Z241" s="2" t="n">
+        <v>0.004850746268656596</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -18889,6 +20341,12 @@
       <c r="X242" s="3" t="n">
         <v>-0.002103602419142879</v>
       </c>
+      <c r="Y242" s="1" t="n">
+        <v>0.07618999999999999</v>
+      </c>
+      <c r="Z242" s="2" t="n">
+        <v>0.003820816864295107</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -18965,6 +20423,12 @@
       <c r="X243" s="2" t="n">
         <v>0.003030303030302907</v>
       </c>
+      <c r="Y243" s="1" t="n">
+        <v>0.02006</v>
+      </c>
+      <c r="Z243" s="2" t="n">
+        <v>0.01007049345417937</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -19041,6 +20505,12 @@
       <c r="X244" s="3" t="n">
         <v>-0.0003450655624568926</v>
       </c>
+      <c r="Y244" s="1" t="n">
+        <v>0.08633</v>
+      </c>
+      <c r="Z244" s="3" t="n">
+        <v>-0.006673570360142644</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -19117,6 +20587,12 @@
       <c r="X245" s="2" t="n">
         <v>0.001042390548992241</v>
       </c>
+      <c r="Y245" s="1" t="n">
+        <v>1.4382</v>
+      </c>
+      <c r="Z245" s="3" t="n">
+        <v>-0.001596667823672314</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -19193,6 +20669,12 @@
       <c r="X246" s="3" t="n">
         <v>-0.0005627462014631172</v>
       </c>
+      <c r="Y246" s="1" t="n">
+        <v>0.01793</v>
+      </c>
+      <c r="Z246" s="2" t="n">
+        <v>0.009572072072072071</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -19269,6 +20751,12 @@
       <c r="X247" s="3" t="n">
         <v>-0.004228968433771371</v>
       </c>
+      <c r="Y247" s="1" t="n">
+        <v>0.00663</v>
+      </c>
+      <c r="Z247" s="2" t="n">
+        <v>0.005612012740785637</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -19345,6 +20833,12 @@
       <c r="X248" s="2" t="n">
         <v>0.003598848368522135</v>
       </c>
+      <c r="Y248" s="1" t="n">
+        <v>0.00414</v>
+      </c>
+      <c r="Z248" s="3" t="n">
+        <v>-0.01027970356203694</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -19421,6 +20915,12 @@
       <c r="X249" s="3" t="n">
         <v>-0.000911577028258914</v>
       </c>
+      <c r="Y249" s="1" t="n">
+        <v>0.1102</v>
+      </c>
+      <c r="Z249" s="2" t="n">
+        <v>0.005474452554744555</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -19497,6 +20997,12 @@
       <c r="X250" s="3" t="n">
         <v>-0.006092254134029644</v>
       </c>
+      <c r="Y250" s="1" t="n">
+        <v>0.03456</v>
+      </c>
+      <c r="Z250" s="2" t="n">
+        <v>0.008756567425569226</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -19573,6 +21079,12 @@
       <c r="X251" s="3" t="n">
         <v>-0.002788104089219378</v>
       </c>
+      <c r="Y251" s="1" t="n">
+        <v>0.04306</v>
+      </c>
+      <c r="Z251" s="2" t="n">
+        <v>0.003261882572227428</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -19649,6 +21161,12 @@
       <c r="X252" s="3" t="n">
         <v>-0.006074536200952176</v>
       </c>
+      <c r="Y252" s="1" t="n">
+        <v>0.006037</v>
+      </c>
+      <c r="Z252" s="3" t="n">
+        <v>-0.002808060786257106</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -19725,6 +21243,12 @@
       <c r="X253" s="3" t="n">
         <v>-0.008576329331046162</v>
       </c>
+      <c r="Y253" s="1" t="n">
+        <v>0.01723</v>
+      </c>
+      <c r="Z253" s="3" t="n">
+        <v>-0.006343713956170845</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -19801,6 +21325,12 @@
       <c r="X254" s="3" t="n">
         <v>-0.002314814814814774</v>
       </c>
+      <c r="Y254" s="1" t="n">
+        <v>0.1298</v>
+      </c>
+      <c r="Z254" s="2" t="n">
+        <v>0.00386697602474865</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -19877,6 +21407,12 @@
       <c r="X255" s="3" t="n">
         <v>-0.007550731477111865</v>
       </c>
+      <c r="Y255" s="1" t="n">
+        <v>0.02112</v>
+      </c>
+      <c r="Z255" s="2" t="n">
+        <v>0.0042796005706134</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -19953,6 +21489,12 @@
       <c r="X256" s="3" t="n">
         <v>-0.0004750593824227835</v>
       </c>
+      <c r="Y256" s="1" t="n">
+        <v>0.02111</v>
+      </c>
+      <c r="Z256" s="2" t="n">
+        <v>0.00332699619771866</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -20029,6 +21571,12 @@
       <c r="X257" s="3" t="n">
         <v>-0.001980198019802037</v>
       </c>
+      <c r="Y257" s="1" t="n">
+        <v>0.02526</v>
+      </c>
+      <c r="Z257" s="2" t="n">
+        <v>0.002380952380952421</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -20105,6 +21653,12 @@
       <c r="X258" s="2" t="n">
         <v>0.0001990974250066515</v>
       </c>
+      <c r="Y258" s="1" t="n">
+        <v>0.15066</v>
+      </c>
+      <c r="Z258" s="3" t="n">
+        <v>-0.0003317629885211482</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -20181,6 +21735,12 @@
       <c r="X259" s="3" t="n">
         <v>-0.0007869368483178905</v>
       </c>
+      <c r="Y259" s="1" t="n">
+        <v>0.05094</v>
+      </c>
+      <c r="Z259" s="2" t="n">
+        <v>0.002953337271116309</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -20257,6 +21817,12 @@
       <c r="X260" s="3" t="n">
         <v>-0.0003610542784932272</v>
       </c>
+      <c r="Y260" s="1" t="n">
+        <v>0.08384999999999999</v>
+      </c>
+      <c r="Z260" s="2" t="n">
+        <v>0.009511196725258839</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -20333,6 +21899,12 @@
       <c r="X261" s="2" t="n">
         <v>0.01762114537444929</v>
       </c>
+      <c r="Y261" s="1" t="n">
+        <v>0.2462</v>
+      </c>
+      <c r="Z261" s="3" t="n">
+        <v>-0.03109012199921287</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -20409,6 +21981,12 @@
       <c r="X262" s="2" t="n">
         <v>0.002084781097984675</v>
       </c>
+      <c r="Y262" s="1" t="n">
+        <v>0.1443</v>
+      </c>
+      <c r="Z262" s="2" t="n">
+        <v>0.000693481276005664</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -20485,6 +22063,12 @@
       <c r="X263" s="3" t="n">
         <v>-0.001688750324759744</v>
       </c>
+      <c r="Y263" s="1" t="n">
+        <v>0.07713</v>
+      </c>
+      <c r="Z263" s="2" t="n">
+        <v>0.003643461288223845</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -20561,6 +22145,12 @@
       <c r="X264" s="2" t="n">
         <v>0.001524777636594601</v>
       </c>
+      <c r="Y264" s="1" t="n">
+        <v>0.03935</v>
+      </c>
+      <c r="Z264" s="3" t="n">
+        <v>-0.001522456229383343</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -20637,6 +22227,12 @@
       <c r="X265" s="3" t="n">
         <v>-0.001307189542483607</v>
       </c>
+      <c r="Y265" s="1" t="n">
+        <v>0.01535</v>
+      </c>
+      <c r="Z265" s="2" t="n">
+        <v>0.004581151832460773</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -20713,6 +22309,12 @@
       <c r="X266" s="2" t="n">
         <v>0.00621430970775944</v>
       </c>
+      <c r="Y266" s="1" t="n">
+        <v>0.006025</v>
+      </c>
+      <c r="Z266" s="2" t="n">
+        <v>0.005675179435820426</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -20789,6 +22391,12 @@
       <c r="X267" s="3" t="n">
         <v>-0.004286096972944024</v>
       </c>
+      <c r="Y267" s="1" t="n">
+        <v>0.03731</v>
+      </c>
+      <c r="Z267" s="2" t="n">
+        <v>0.003766478342749562</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -20865,6 +22473,12 @@
       <c r="X268" s="3" t="n">
         <v>-0.002937336814621403</v>
       </c>
+      <c r="Y268" s="1" t="n">
+        <v>0.03062</v>
+      </c>
+      <c r="Z268" s="2" t="n">
+        <v>0.002291325695581035</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -20941,6 +22555,12 @@
       <c r="X269" s="3" t="n">
         <v>-0.00304729938612373</v>
       </c>
+      <c r="Y269" s="1" t="n">
+        <v>0.22661</v>
+      </c>
+      <c r="Z269" s="2" t="n">
+        <v>0.003853991317444891</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -21017,6 +22637,12 @@
       <c r="X270" s="2" t="n">
         <v>0.001081081081081082</v>
       </c>
+      <c r="Y270" s="1" t="n">
+        <v>0.9340000000000001</v>
+      </c>
+      <c r="Z270" s="2" t="n">
+        <v>0.008639308855291584</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -21093,6 +22719,12 @@
       <c r="X271" s="3" t="n">
         <v>-0.0003844675124951518</v>
       </c>
+      <c r="Y271" s="1" t="n">
+        <v>2.606</v>
+      </c>
+      <c r="Z271" s="2" t="n">
+        <v>0.002307692307692224</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -21169,6 +22801,12 @@
       <c r="X272" s="3" t="n">
         <v>-0.0005402485143165261</v>
       </c>
+      <c r="Y272" s="1" t="n">
+        <v>0.1861</v>
+      </c>
+      <c r="Z272" s="2" t="n">
+        <v>0.005945945945945891</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -21245,6 +22883,12 @@
       <c r="X273" s="2" t="n">
         <v>0.0009671179883946566</v>
       </c>
+      <c r="Y273" s="1" t="n">
+        <v>0.03116</v>
+      </c>
+      <c r="Z273" s="2" t="n">
+        <v>0.003542673107890467</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -21321,6 +22965,12 @@
       <c r="X274" s="3" t="n">
         <v>-0.007804370447450579</v>
       </c>
+      <c r="Y274" s="1" t="n">
+        <v>0.1917</v>
+      </c>
+      <c r="Z274" s="2" t="n">
+        <v>0.005243838489774519</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -21397,6 +23047,12 @@
       <c r="X275" s="2" t="n">
         <v>0.001593279258400912</v>
       </c>
+      <c r="Y275" s="1" t="n">
+        <v>0.06926</v>
+      </c>
+      <c r="Z275" s="2" t="n">
+        <v>0.001590744757772943</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -21473,6 +23129,12 @@
       <c r="X276" s="3" t="n">
         <v>-0.0007464543418759719</v>
       </c>
+      <c r="Y276" s="1" t="n">
+        <v>0.08055</v>
+      </c>
+      <c r="Z276" s="2" t="n">
+        <v>0.002863545816732994</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -21549,6 +23211,12 @@
       <c r="X277" s="3" t="n">
         <v>-0.002251125562781256</v>
       </c>
+      <c r="Y277" s="1" t="n">
+        <v>0.004032</v>
+      </c>
+      <c r="Z277" s="2" t="n">
+        <v>0.01077964402105782</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -21625,6 +23293,12 @@
       <c r="X278" s="3" t="n">
         <v>-0.001287001287001288</v>
       </c>
+      <c r="Y278" s="1" t="n">
+        <v>1.557</v>
+      </c>
+      <c r="Z278" s="2" t="n">
+        <v>0.003221649484536014</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -21701,6 +23375,12 @@
       <c r="X279" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="Y279" s="1" t="n">
+        <v>0.01107</v>
+      </c>
+      <c r="Z279" s="2" t="n">
+        <v>0.004537205081669664</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -21777,6 +23457,12 @@
       <c r="X280" s="2" t="n">
         <v>0.001734390485629351</v>
       </c>
+      <c r="Y280" s="1" t="n">
+        <v>0.04049</v>
+      </c>
+      <c r="Z280" s="2" t="n">
+        <v>0.00148404650012361</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -21853,6 +23539,12 @@
       <c r="X281" s="3" t="n">
         <v>-0.001073601336037299</v>
       </c>
+      <c r="Y281" s="1" t="n">
+        <v>0.08409</v>
+      </c>
+      <c r="Z281" s="2" t="n">
+        <v>0.004179603534750455</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -21929,6 +23621,12 @@
       <c r="X282" s="3" t="n">
         <v>-0.003745318352060032</v>
       </c>
+      <c r="Y282" s="1" t="n">
+        <v>0.0268</v>
+      </c>
+      <c r="Z282" s="2" t="n">
+        <v>0.007518796992481288</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -22005,6 +23703,12 @@
       <c r="X283" s="3" t="n">
         <v>-0.00340136054421764</v>
       </c>
+      <c r="Y283" s="1" t="n">
+        <v>0.07661999999999999</v>
+      </c>
+      <c r="Z283" s="2" t="n">
+        <v>0.005775794171698555</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -22081,6 +23785,12 @@
       <c r="X284" s="3" t="n">
         <v>-0.005579665220086863</v>
       </c>
+      <c r="Y284" s="1" t="n">
+        <v>0.00162</v>
+      </c>
+      <c r="Z284" s="2" t="n">
+        <v>0.009975062344139623</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -22157,6 +23867,12 @@
       <c r="X285" s="3" t="n">
         <v>-0.0009886307464162419</v>
       </c>
+      <c r="Y285" s="1" t="n">
+        <v>0.2029</v>
+      </c>
+      <c r="Z285" s="2" t="n">
+        <v>0.003958436417615018</v>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -22233,6 +23949,12 @@
       <c r="X286" s="3" t="n">
         <v>-0.002243200299093411</v>
       </c>
+      <c r="Y286" s="1" t="n">
+        <v>0.10708</v>
+      </c>
+      <c r="Z286" s="2" t="n">
+        <v>0.003091334894613555</v>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -22309,6 +24031,12 @@
       <c r="X287" s="2" t="n">
         <v>0.00519031141868511</v>
       </c>
+      <c r="Y287" s="1" t="n">
+        <v>0.01742</v>
+      </c>
+      <c r="Z287" s="3" t="n">
+        <v>-0.000573723465289707</v>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -22385,6 +24113,12 @@
       <c r="X288" s="3" t="n">
         <v>-0.001990710019907134</v>
       </c>
+      <c r="Y288" s="1" t="n">
+        <v>0.01509</v>
+      </c>
+      <c r="Z288" s="2" t="n">
+        <v>0.003324468085106363</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -22461,6 +24195,12 @@
       <c r="X289" s="3" t="n">
         <v>-0.0006184291898577361</v>
       </c>
+      <c r="Y289" s="1" t="n">
+        <v>0.01623</v>
+      </c>
+      <c r="Z289" s="2" t="n">
+        <v>0.004331683168316869</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -22537,6 +24277,12 @@
       <c r="X290" s="3" t="n">
         <v>-0.005286343612334807</v>
       </c>
+      <c r="Y290" s="1" t="n">
+        <v>2.266</v>
+      </c>
+      <c r="Z290" s="2" t="n">
+        <v>0.003542958370239153</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -22613,6 +24359,12 @@
       <c r="X291" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="Y291" s="1" t="n">
+        <v>0.4423</v>
+      </c>
+      <c r="Z291" s="2" t="n">
+        <v>0.004998863894569497</v>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -22689,6 +24441,12 @@
       <c r="X292" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="Y292" s="1" t="n">
+        <v>1.726</v>
+      </c>
+      <c r="Z292" s="3" t="n">
+        <v>-0.002312138728323701</v>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -22765,6 +24523,12 @@
       <c r="X293" s="3" t="n">
         <v>-0.0002003606491685646</v>
       </c>
+      <c r="Y293" s="1" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Z293" s="2" t="n">
+        <v>0.002004008016032122</v>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -22841,6 +24605,12 @@
       <c r="X294" s="3" t="n">
         <v>-0.001577038322031052</v>
       </c>
+      <c r="Y294" s="1" t="n">
+        <v>0.06349</v>
+      </c>
+      <c r="Z294" s="2" t="n">
+        <v>0.002843152740483329</v>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -22917,6 +24687,12 @@
       <c r="X295" s="3" t="n">
         <v>-0.003857280617164862</v>
       </c>
+      <c r="Y295" s="1" t="n">
+        <v>0.0004147</v>
+      </c>
+      <c r="Z295" s="2" t="n">
+        <v>0.003630203291384275</v>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -22993,6 +24769,12 @@
       <c r="X296" s="3" t="n">
         <v>-0.001917239175587227</v>
       </c>
+      <c r="Y296" s="1" t="n">
+        <v>62.63</v>
+      </c>
+      <c r="Z296" s="2" t="n">
+        <v>0.002561229390107311</v>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -23069,6 +24851,12 @@
       <c r="X297" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="Y297" s="1" t="n">
+        <v>0.0979</v>
+      </c>
+      <c r="Z297" s="2" t="n">
+        <v>0.002047082906857786</v>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -23145,6 +24933,12 @@
       <c r="X298" s="3" t="n">
         <v>-0.001044932079414723</v>
       </c>
+      <c r="Y298" s="1" t="n">
+        <v>0.0959</v>
+      </c>
+      <c r="Z298" s="2" t="n">
+        <v>0.003138075313807476</v>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -23221,6 +25015,12 @@
       <c r="X299" s="3" t="n">
         <v>-0.008269588587967841</v>
       </c>
+      <c r="Y299" s="1" t="n">
+        <v>0.09594999999999999</v>
+      </c>
+      <c r="Z299" s="2" t="n">
+        <v>0.0001042318115488443</v>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -23297,6 +25097,12 @@
       <c r="X300" s="3" t="n">
         <v>-0.0005330490405117054</v>
       </c>
+      <c r="Y300" s="1" t="n">
+        <v>0.01868</v>
+      </c>
+      <c r="Z300" s="3" t="n">
+        <v>-0.003733333333333366</v>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -23373,6 +25179,12 @@
       <c r="X301" s="3" t="n">
         <v>-0.001499250374812533</v>
       </c>
+      <c r="Y301" s="1" t="n">
+        <v>0.01344</v>
+      </c>
+      <c r="Z301" s="2" t="n">
+        <v>0.009009009009009033</v>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -23449,6 +25261,12 @@
       <c r="X302" s="2" t="n">
         <v>0.002750401100160606</v>
       </c>
+      <c r="Y302" s="1" t="n">
+        <v>0.004387</v>
+      </c>
+      <c r="Z302" s="2" t="n">
+        <v>0.00274285714285711</v>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -23525,6 +25343,12 @@
       <c r="X303" s="3" t="n">
         <v>-0.001082251082251038</v>
       </c>
+      <c r="Y303" s="1" t="n">
+        <v>0.00925</v>
+      </c>
+      <c r="Z303" s="2" t="n">
+        <v>0.002166847237269684</v>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -23601,6 +25425,12 @@
       <c r="X304" s="3" t="n">
         <v>-0.0006364022061943388</v>
       </c>
+      <c r="Y304" s="1" t="n">
+        <v>4.722</v>
+      </c>
+      <c r="Z304" s="2" t="n">
+        <v>0.002334960730205927</v>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -23677,6 +25507,12 @@
       <c r="X305" s="3" t="n">
         <v>-0.002446828533785021</v>
       </c>
+      <c r="Y305" s="1" t="n">
+        <v>0.05312</v>
+      </c>
+      <c r="Z305" s="2" t="n">
+        <v>0.002264150943396265</v>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -23753,6 +25589,12 @@
       <c r="X306" s="3" t="n">
         <v>-0.0005151983513651951</v>
       </c>
+      <c r="Y306" s="1" t="n">
+        <v>0.0584</v>
+      </c>
+      <c r="Z306" s="2" t="n">
+        <v>0.003436426116838467</v>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -23829,6 +25671,12 @@
       <c r="X307" s="3" t="n">
         <v>-0.002292263610315093</v>
       </c>
+      <c r="Y307" s="1" t="n">
+        <v>0.1744</v>
+      </c>
+      <c r="Z307" s="2" t="n">
+        <v>0.001723147616312434</v>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -23905,6 +25753,12 @@
       <c r="X308" s="3" t="n">
         <v>-0.006232408524326453</v>
       </c>
+      <c r="Y308" s="1" t="n">
+        <v>0.04971</v>
+      </c>
+      <c r="Z308" s="2" t="n">
+        <v>0.005664576168318745</v>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -23981,6 +25835,12 @@
       <c r="X309" s="3" t="n">
         <v>-0.002022802500919437</v>
       </c>
+      <c r="Y309" s="1" t="n">
+        <v>0.545</v>
+      </c>
+      <c r="Z309" s="2" t="n">
+        <v>0.004238068914685977</v>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -24057,6 +25917,12 @@
       <c r="X310" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="Y310" s="1" t="n">
+        <v>0.00244</v>
+      </c>
+      <c r="Z310" s="2" t="n">
+        <v>0.00411522633744857</v>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -24133,6 +25999,12 @@
       <c r="X311" s="3" t="n">
         <v>-0.001411034288133242</v>
       </c>
+      <c r="Y311" s="1" t="n">
+        <v>0.07106999999999999</v>
+      </c>
+      <c r="Z311" s="2" t="n">
+        <v>0.004239084357778645</v>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -24209,6 +26081,12 @@
       <c r="X312" s="3" t="n">
         <v>-0.001338538761851823</v>
       </c>
+      <c r="Y312" s="1" t="n">
+        <v>0.009001</v>
+      </c>
+      <c r="Z312" s="2" t="n">
+        <v>0.005361331397297126</v>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -24285,6 +26163,12 @@
       <c r="X313" s="2" t="n">
         <v>0.001418794858955071</v>
       </c>
+      <c r="Y313" s="1" t="n">
+        <v>0.012076</v>
+      </c>
+      <c r="Z313" s="2" t="n">
+        <v>0.006417201433452845</v>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -24361,6 +26245,12 @@
       <c r="X314" s="3" t="n">
         <v>-0.0004280821917808045</v>
       </c>
+      <c r="Y314" s="1" t="n">
+        <v>0.02361</v>
+      </c>
+      <c r="Z314" s="2" t="n">
+        <v>0.01113490364025695</v>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -24437,6 +26327,12 @@
       <c r="X315" s="3" t="n">
         <v>-0.00280898876404483</v>
       </c>
+      <c r="Y315" s="1" t="n">
+        <v>0.00712</v>
+      </c>
+      <c r="Z315" s="2" t="n">
+        <v>0.002816901408450589</v>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -24513,6 +26409,12 @@
       <c r="X316" s="3" t="n">
         <v>-0.001153402537485669</v>
       </c>
+      <c r="Y316" s="1" t="n">
+        <v>0.2616</v>
+      </c>
+      <c r="Z316" s="2" t="n">
+        <v>0.006928406466512794</v>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -24589,6 +26491,12 @@
       <c r="X317" s="2" t="n">
         <v>0.009009009009008922</v>
       </c>
+      <c r="Y317" s="1" t="n">
+        <v>1.12e-05</v>
+      </c>
+      <c r="Z317" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -24665,6 +26573,12 @@
       <c r="X318" s="3" t="n">
         <v>-0.00100609350974767</v>
       </c>
+      <c r="Y318" s="1" t="n">
+        <v>0.052711</v>
+      </c>
+      <c r="Z318" s="2" t="n">
+        <v>0.001615171208148097</v>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -24741,6 +26655,12 @@
       <c r="X319" s="3" t="n">
         <v>-0.0005227391531625505</v>
       </c>
+      <c r="Y319" s="1" t="n">
+        <v>0.03828</v>
+      </c>
+      <c r="Z319" s="2" t="n">
+        <v>0.001046025104602468</v>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -24817,6 +26737,12 @@
       <c r="X320" s="3" t="n">
         <v>-0.0008819638394825707</v>
       </c>
+      <c r="Y320" s="1" t="n">
+        <v>0.006836</v>
+      </c>
+      <c r="Z320" s="2" t="n">
+        <v>0.005737825511254961</v>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -24893,6 +26819,12 @@
       <c r="X321" s="3" t="n">
         <v>-0.0006634232640424842</v>
       </c>
+      <c r="Y321" s="1" t="n">
+        <v>4.541</v>
+      </c>
+      <c r="Z321" s="2" t="n">
+        <v>0.004868333702146546</v>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -24969,6 +26901,12 @@
       <c r="X322" s="3" t="n">
         <v>-0.003113648157758176</v>
       </c>
+      <c r="Y322" s="1" t="n">
+        <v>1.929</v>
+      </c>
+      <c r="Z322" s="2" t="n">
+        <v>0.004164497657470071</v>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -25045,6 +26983,12 @@
       <c r="X323" s="3" t="n">
         <v>-0.003072625698323946</v>
       </c>
+      <c r="Y323" s="1" t="n">
+        <v>0.007164</v>
+      </c>
+      <c r="Z323" s="2" t="n">
+        <v>0.003642476884281309</v>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -25121,6 +27065,12 @@
       <c r="X324" s="3" t="n">
         <v>-0.003259098316132404</v>
       </c>
+      <c r="Y324" s="1" t="n">
+        <v>0.01844</v>
+      </c>
+      <c r="Z324" s="2" t="n">
+        <v>0.004904632152588545</v>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -25197,6 +27147,12 @@
       <c r="X325" s="2" t="n">
         <v>0.002681618722574329</v>
       </c>
+      <c r="Y325" s="1" t="n">
+        <v>0.4139</v>
+      </c>
+      <c r="Z325" s="2" t="n">
+        <v>0.006321419888159473</v>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -25273,6 +27229,12 @@
       <c r="X326" s="3" t="n">
         <v>-0.002917477076965849</v>
       </c>
+      <c r="Y326" s="1" t="n">
+        <v>0.007233</v>
+      </c>
+      <c r="Z326" s="2" t="n">
+        <v>0.007802703079280984</v>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -25349,6 +27311,12 @@
       <c r="X327" s="3" t="n">
         <v>-0.004699738903394318</v>
       </c>
+      <c r="Y327" s="1" t="n">
+        <v>0.191</v>
+      </c>
+      <c r="Z327" s="2" t="n">
+        <v>0.002098635886673722</v>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -25425,6 +27393,12 @@
       <c r="X328" s="3" t="n">
         <v>-0.003412241416080167</v>
       </c>
+      <c r="Y328" s="1" t="n">
+        <v>0.4703</v>
+      </c>
+      <c r="Z328" s="2" t="n">
+        <v>0.006419858763107218</v>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -25501,6 +27475,12 @@
       <c r="X329" s="3" t="n">
         <v>-0.002230483271375503</v>
       </c>
+      <c r="Y329" s="1" t="n">
+        <v>0.01344</v>
+      </c>
+      <c r="Z329" s="2" t="n">
+        <v>0.00149031296572287</v>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -25577,6 +27557,12 @@
       <c r="X330" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="Y330" s="1" t="n">
+        <v>0.1135</v>
+      </c>
+      <c r="Z330" s="2" t="n">
+        <v>0.002650176678445306</v>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -25653,6 +27639,12 @@
       <c r="X331" s="3" t="n">
         <v>-0.003802910052910001</v>
       </c>
+      <c r="Y331" s="1" t="n">
+        <v>0.6064000000000001</v>
+      </c>
+      <c r="Z331" s="2" t="n">
+        <v>0.006473029045643178</v>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -25729,6 +27721,12 @@
       <c r="X332" s="3" t="n">
         <v>-0.002691701680672409</v>
       </c>
+      <c r="Y332" s="1" t="n">
+        <v>0.30474</v>
+      </c>
+      <c r="Z332" s="2" t="n">
+        <v>0.003028108748601251</v>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -25805,6 +27803,12 @@
       <c r="X333" s="2" t="n">
         <v>0.000850099178237328</v>
       </c>
+      <c r="Y333" s="1" t="n">
+        <v>0.07058</v>
+      </c>
+      <c r="Z333" s="3" t="n">
+        <v>-0.0008493771234426758</v>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -25881,6 +27885,12 @@
       <c r="X334" s="2" t="n">
         <v>0.005456844346842452</v>
       </c>
+      <c r="Y334" s="1" t="n">
+        <v>0.15107</v>
+      </c>
+      <c r="Z334" s="3" t="n">
+        <v>-0.0001323714342444387</v>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -25957,6 +27967,12 @@
       <c r="X335" s="3" t="n">
         <v>-0.0006385696040867751</v>
       </c>
+      <c r="Y335" s="1" t="n">
+        <v>0.1568</v>
+      </c>
+      <c r="Z335" s="2" t="n">
+        <v>0.001916932907348209</v>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -26033,6 +28049,12 @@
       <c r="X336" s="3" t="n">
         <v>-0.001724137931034453</v>
       </c>
+      <c r="Y336" s="1" t="n">
+        <v>0.1746</v>
+      </c>
+      <c r="Z336" s="2" t="n">
+        <v>0.005181347150259136</v>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -26109,6 +28131,12 @@
       <c r="X337" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="Y337" s="1" t="n">
+        <v>0.04006</v>
+      </c>
+      <c r="Z337" s="3" t="n">
+        <v>-0.002490039840637521</v>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -26185,6 +28213,12 @@
       <c r="X338" s="3" t="n">
         <v>-0.003777861730260682</v>
       </c>
+      <c r="Y338" s="1" t="n">
+        <v>0.005297</v>
+      </c>
+      <c r="Z338" s="2" t="n">
+        <v>0.004361016306408719</v>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -26261,6 +28295,12 @@
       <c r="X339" s="3" t="n">
         <v>-0.005607115235885645</v>
       </c>
+      <c r="Y339" s="1" t="n">
+        <v>0.05181</v>
+      </c>
+      <c r="Z339" s="2" t="n">
+        <v>0.007388683647676557</v>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -26337,6 +28377,12 @@
       <c r="X340" s="3" t="n">
         <v>-0.002712896182094844</v>
       </c>
+      <c r="Y340" s="1" t="n">
+        <v>0.15125</v>
+      </c>
+      <c r="Z340" s="2" t="n">
+        <v>0.003516454352441631</v>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -26413,6 +28459,12 @@
       <c r="X341" s="3" t="n">
         <v>-0.0006557377049180188</v>
       </c>
+      <c r="Y341" s="1" t="n">
+        <v>7.641</v>
+      </c>
+      <c r="Z341" s="2" t="n">
+        <v>0.002755905511811011</v>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -26489,6 +28541,12 @@
       <c r="X342" s="2" t="n">
         <v>0.003663003663003598</v>
       </c>
+      <c r="Y342" s="1" t="n">
+        <v>0.3286</v>
+      </c>
+      <c r="Z342" s="3" t="n">
+        <v>-0.0006082725060826581</v>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -26565,6 +28623,12 @@
       <c r="X343" s="3" t="n">
         <v>-0.002005012531328239</v>
       </c>
+      <c r="Y343" s="1" t="n">
+        <v>0.02015</v>
+      </c>
+      <c r="Z343" s="2" t="n">
+        <v>0.01205424409844302</v>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -26641,6 +28705,12 @@
       <c r="X344" s="3" t="n">
         <v>-0.00321543408360134</v>
       </c>
+      <c r="Y344" s="1" t="n">
+        <v>2.176</v>
+      </c>
+      <c r="Z344" s="2" t="n">
+        <v>0.002764976958525451</v>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -26717,6 +28787,12 @@
       <c r="X345" s="3" t="n">
         <v>-0.00236779794790836</v>
       </c>
+      <c r="Y345" s="1" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z345" s="2" t="n">
+        <v>0.004746835443037979</v>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -26793,6 +28869,12 @@
       <c r="X346" s="3" t="n">
         <v>-0.00212683681361187</v>
       </c>
+      <c r="Y346" s="1" t="n">
+        <v>0.005176</v>
+      </c>
+      <c r="Z346" s="2" t="n">
+        <v>0.002906413485758623</v>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -26869,6 +28951,12 @@
       <c r="X347" s="3" t="n">
         <v>-0.001395916942941838</v>
       </c>
+      <c r="Y347" s="1" t="n">
+        <v>0.05751</v>
+      </c>
+      <c r="Z347" s="2" t="n">
+        <v>0.00489253887821065</v>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -26945,6 +29033,12 @@
       <c r="X348" s="3" t="n">
         <v>-0.002351097178683345</v>
       </c>
+      <c r="Y348" s="1" t="n">
+        <v>0.1277</v>
+      </c>
+      <c r="Z348" s="2" t="n">
+        <v>0.003142183817753429</v>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -27021,6 +29115,12 @@
       <c r="X349" s="3" t="n">
         <v>-0.00111761985509484</v>
       </c>
+      <c r="Y349" s="1" t="n">
+        <v>5176.3</v>
+      </c>
+      <c r="Z349" s="3" t="n">
+        <v>-0.001446815077742197</v>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -27097,6 +29197,12 @@
       <c r="X350" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="Y350" s="1" t="n">
+        <v>0.02795</v>
+      </c>
+      <c r="Z350" s="2" t="n">
+        <v>0.002151308712800199</v>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -27173,6 +29279,12 @@
       <c r="X351" s="2" t="n">
         <v>0.004319654427645737</v>
       </c>
+      <c r="Y351" s="1" t="n">
+        <v>0.001397</v>
+      </c>
+      <c r="Z351" s="2" t="n">
+        <v>0.001433691756272436</v>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -27249,6 +29361,12 @@
       <c r="X352" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="Y352" s="1" t="n">
+        <v>0.0159</v>
+      </c>
+      <c r="Z352" s="2" t="n">
+        <v>0.01209420751113957</v>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -27325,6 +29443,12 @@
       <c r="X353" s="2" t="n">
         <v>0.005596418292292956</v>
       </c>
+      <c r="Y353" s="1" t="n">
+        <v>6.291</v>
+      </c>
+      <c r="Z353" s="2" t="n">
+        <v>0.0003180155827636617</v>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -27401,6 +29525,12 @@
       <c r="X354" s="3" t="n">
         <v>-0.000696378830083682</v>
       </c>
+      <c r="Y354" s="1" t="n">
+        <v>0.2876</v>
+      </c>
+      <c r="Z354" s="2" t="n">
+        <v>0.00209059233449493</v>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -27477,6 +29607,12 @@
       <c r="X355" s="3" t="n">
         <v>-0.00168471720818276</v>
       </c>
+      <c r="Y355" s="1" t="n">
+        <v>0.04152</v>
+      </c>
+      <c r="Z355" s="2" t="n">
+        <v>0.0009643201542911854</v>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -27553,6 +29689,12 @@
       <c r="X356" s="2" t="n">
         <v>0.002387267904509217</v>
       </c>
+      <c r="Y356" s="1" t="n">
+        <v>0.11383</v>
+      </c>
+      <c r="Z356" s="2" t="n">
+        <v>0.004057510805327707</v>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -27629,6 +29771,12 @@
       <c r="X357" s="2" t="n">
         <v>0.006122058542184792</v>
       </c>
+      <c r="Y357" s="1" t="n">
+        <v>0.005273</v>
+      </c>
+      <c r="Z357" s="2" t="n">
+        <v>0.002662103061418544</v>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -27705,6 +29853,12 @@
       <c r="X358" s="3" t="n">
         <v>-0.004314994606256866</v>
       </c>
+      <c r="Y358" s="1" t="n">
+        <v>0.1856</v>
+      </c>
+      <c r="Z358" s="2" t="n">
+        <v>0.005417118093174436</v>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -27781,6 +29935,12 @@
       <c r="X359" s="3" t="n">
         <v>-0.0006146281499693714</v>
       </c>
+      <c r="Y359" s="1" t="n">
+        <v>0.163</v>
+      </c>
+      <c r="Z359" s="2" t="n">
+        <v>0.002460024600246073</v>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -27857,6 +30017,12 @@
       <c r="X360" s="3" t="n">
         <v>-0.001407954945441689</v>
       </c>
+      <c r="Y360" s="1" t="n">
+        <v>0.08520999999999999</v>
+      </c>
+      <c r="Z360" s="2" t="n">
+        <v>0.001174950064622124</v>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -27933,6 +30099,12 @@
       <c r="X361" s="2" t="n">
         <v>0.002624671916010506</v>
       </c>
+      <c r="Y361" s="1" t="n">
+        <v>0.00765</v>
+      </c>
+      <c r="Z361" s="2" t="n">
+        <v>0.001308900523560156</v>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -28009,6 +30181,12 @@
       <c r="X362" s="3" t="n">
         <v>-0.0007043907020427858</v>
       </c>
+      <c r="Y362" s="1" t="n">
+        <v>0.426</v>
+      </c>
+      <c r="Z362" s="2" t="n">
+        <v>0.0009398496240601773</v>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -28085,6 +30263,12 @@
       <c r="X363" s="2" t="n">
         <v>0.0002651113467657301</v>
       </c>
+      <c r="Y363" s="1" t="n">
+        <v>3.788</v>
+      </c>
+      <c r="Z363" s="2" t="n">
+        <v>0.003975616220514095</v>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -28161,6 +30345,12 @@
       <c r="X364" s="3" t="n">
         <v>-0.003629764065335763</v>
       </c>
+      <c r="Y364" s="1" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="Z364" s="2" t="n">
+        <v>0.001821493624772239</v>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -28237,6 +30427,12 @@
       <c r="X365" s="3" t="n">
         <v>-0.0005450581395347985</v>
       </c>
+      <c r="Y365" s="1" t="n">
+        <v>0.05516</v>
+      </c>
+      <c r="Z365" s="2" t="n">
+        <v>0.002726776949645471</v>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -28313,6 +30509,12 @@
       <c r="X366" s="2" t="n">
         <v>0.0008768084173607709</v>
       </c>
+      <c r="Y366" s="1" t="n">
+        <v>0.02298</v>
+      </c>
+      <c r="Z366" s="2" t="n">
+        <v>0.006570302233902796</v>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -28389,6 +30591,12 @@
       <c r="X367" s="3" t="n">
         <v>-0.007336757153338243</v>
       </c>
+      <c r="Y367" s="1" t="n">
+        <v>0.001358</v>
+      </c>
+      <c r="Z367" s="2" t="n">
+        <v>0.003695491500369559</v>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -28465,6 +30673,12 @@
       <c r="X368" s="3" t="n">
         <v>-0.0003489183531055286</v>
       </c>
+      <c r="Y368" s="1" t="n">
+        <v>0.2884</v>
+      </c>
+      <c r="Z368" s="2" t="n">
+        <v>0.006631762652705106</v>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -28541,6 +30755,12 @@
       <c r="X369" s="2" t="n">
         <v>0.002699784017278695</v>
       </c>
+      <c r="Y369" s="1" t="n">
+        <v>0.01856</v>
+      </c>
+      <c r="Z369" s="3" t="n">
+        <v>-0.0005385029617662678</v>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -28617,6 +30837,12 @@
       <c r="X370" s="3" t="n">
         <v>-0.003595482858155751</v>
       </c>
+      <c r="Y370" s="1" t="n">
+        <v>0.19736</v>
+      </c>
+      <c r="Z370" s="2" t="n">
+        <v>0.003049400284610781</v>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -28693,6 +30919,12 @@
       <c r="X371" s="3" t="n">
         <v>-0.01315789473684212</v>
       </c>
+      <c r="Y371" s="1" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="Z371" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -28769,6 +31001,12 @@
       <c r="X372" s="3" t="n">
         <v>-0.002854424357754469</v>
       </c>
+      <c r="Y372" s="1" t="n">
+        <v>0.1054</v>
+      </c>
+      <c r="Z372" s="2" t="n">
+        <v>0.005725190839694555</v>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -28845,6 +31083,12 @@
       <c r="X373" s="3" t="n">
         <v>-0.006479807112718503</v>
       </c>
+      <c r="Y373" s="1" t="n">
+        <v>0.06610000000000001</v>
+      </c>
+      <c r="Z373" s="2" t="n">
+        <v>0.002578492340361042</v>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -28921,6 +31165,12 @@
       <c r="X374" s="3" t="n">
         <v>-0.002104155707522294</v>
       </c>
+      <c r="Y374" s="1" t="n">
+        <v>0.007617</v>
+      </c>
+      <c r="Z374" s="2" t="n">
+        <v>0.003821823932524975</v>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -28997,6 +31247,12 @@
       <c r="X375" s="3" t="n">
         <v>-0.001258653241032132</v>
       </c>
+      <c r="Y375" s="1" t="n">
+        <v>0.1596</v>
+      </c>
+      <c r="Z375" s="2" t="n">
+        <v>0.005671077504725798</v>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -29073,6 +31329,12 @@
       <c r="X376" s="2" t="n">
         <v>0.001175088131609899</v>
       </c>
+      <c r="Y376" s="1" t="n">
+        <v>0.003424</v>
+      </c>
+      <c r="Z376" s="2" t="n">
+        <v>0.004694835680751161</v>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -29149,6 +31411,12 @@
       <c r="X377" s="2" t="n">
         <v>0.006097560975609719</v>
       </c>
+      <c r="Y377" s="1" t="n">
+        <v>0.0166</v>
+      </c>
+      <c r="Z377" s="2" t="n">
+        <v>0.006060606060606023</v>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -29225,6 +31493,12 @@
       <c r="X378" s="3" t="n">
         <v>-0.007950530035335671</v>
       </c>
+      <c r="Y378" s="1" t="n">
+        <v>0.01115</v>
+      </c>
+      <c r="Z378" s="3" t="n">
+        <v>-0.007123775601068584</v>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -29301,6 +31575,12 @@
       <c r="X379" s="3" t="n">
         <v>-0.0004670714619336569</v>
       </c>
+      <c r="Y379" s="1" t="n">
+        <v>0.0215</v>
+      </c>
+      <c r="Z379" s="2" t="n">
+        <v>0.004672897196261654</v>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -29377,6 +31657,12 @@
       <c r="X380" s="3" t="n">
         <v>-0.003711558854718831</v>
       </c>
+      <c r="Y380" s="1" t="n">
+        <v>0.01885</v>
+      </c>
+      <c r="Z380" s="2" t="n">
+        <v>0.003193187865885979</v>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -29453,6 +31739,12 @@
       <c r="X381" s="3" t="n">
         <v>-0.003327787021630595</v>
       </c>
+      <c r="Y381" s="1" t="n">
+        <v>0.1203</v>
+      </c>
+      <c r="Z381" s="2" t="n">
+        <v>0.004173622704507516</v>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -29529,6 +31821,12 @@
       <c r="X382" s="2" t="n">
         <v>0.003388681802778698</v>
       </c>
+      <c r="Y382" s="1" t="n">
+        <v>0.02968</v>
+      </c>
+      <c r="Z382" s="2" t="n">
+        <v>0.002364066193853449</v>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -29605,6 +31903,12 @@
       <c r="X383" s="2" t="n">
         <v>0.004128440366972495</v>
       </c>
+      <c r="Y383" s="1" t="n">
+        <v>0.006565</v>
+      </c>
+      <c r="Z383" s="3" t="n">
+        <v>-0.0003045530683722043</v>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -29681,6 +31985,12 @@
       <c r="X384" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="Y384" s="1" t="n">
+        <v>0.02088</v>
+      </c>
+      <c r="Z384" s="2" t="n">
+        <v>0.002400384061449734</v>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -29757,6 +32067,12 @@
       <c r="X385" s="3" t="n">
         <v>-0.001971608832807571</v>
       </c>
+      <c r="Y385" s="1" t="n">
+        <v>2541</v>
+      </c>
+      <c r="Z385" s="2" t="n">
+        <v>0.003951007506914263</v>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -29833,6 +32149,12 @@
       <c r="X386" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="Y386" s="1" t="n">
+        <v>0.1989</v>
+      </c>
+      <c r="Z386" s="2" t="n">
+        <v>0.003025718608169387</v>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -29909,6 +32231,12 @@
       <c r="X387" s="3" t="n">
         <v>-0.001883239171374688</v>
       </c>
+      <c r="Y387" s="1" t="n">
+        <v>0.08513999999999999</v>
+      </c>
+      <c r="Z387" s="2" t="n">
+        <v>0.004009433962264069</v>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -29985,6 +32313,12 @@
       <c r="X388" s="3" t="n">
         <v>-0.002605732611745839</v>
       </c>
+      <c r="Y388" s="1" t="n">
+        <v>0.004986</v>
+      </c>
+      <c r="Z388" s="2" t="n">
+        <v>0.002009646302250722</v>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -30061,6 +32395,12 @@
       <c r="X389" s="3" t="n">
         <v>-0.01010101010100999</v>
       </c>
+      <c r="Y389" s="1" t="n">
+        <v>0.02249</v>
+      </c>
+      <c r="Z389" s="3" t="n">
+        <v>-0.002218278615794207</v>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -30137,6 +32477,12 @@
       <c r="X390" s="3" t="n">
         <v>-0.004351265822784989</v>
       </c>
+      <c r="Y390" s="1" t="n">
+        <v>0.5059</v>
+      </c>
+      <c r="Z390" s="2" t="n">
+        <v>0.004966229638458598</v>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -30213,6 +32559,12 @@
       <c r="X391" s="3" t="n">
         <v>-0.003970880211780195</v>
       </c>
+      <c r="Y391" s="1" t="n">
+        <v>0.0006073</v>
+      </c>
+      <c r="Z391" s="2" t="n">
+        <v>0.008803986710963399</v>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -30289,6 +32641,12 @@
       <c r="X392" s="2" t="n">
         <v>0.0008566044200788321</v>
       </c>
+      <c r="Y392" s="1" t="n">
+        <v>0.05869</v>
+      </c>
+      <c r="Z392" s="2" t="n">
+        <v>0.004621704895583694</v>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -30365,6 +32723,12 @@
       <c r="X393" s="2" t="n">
         <v>0.001486988847583479</v>
       </c>
+      <c r="Y393" s="1" t="n">
+        <v>0.2704</v>
+      </c>
+      <c r="Z393" s="2" t="n">
+        <v>0.00371195248700817</v>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -30441,6 +32805,12 @@
       <c r="X394" s="2" t="n">
         <v>0.01430092803894726</v>
       </c>
+      <c r="Y394" s="1" t="n">
+        <v>0.00668</v>
+      </c>
+      <c r="Z394" s="2" t="n">
+        <v>0.001949902504874755</v>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -30517,6 +32887,12 @@
       <c r="X395" s="3" t="n">
         <v>-0.002610966057441328</v>
       </c>
+      <c r="Y395" s="1" t="n">
+        <v>0.115</v>
+      </c>
+      <c r="Z395" s="2" t="n">
+        <v>0.003490401396160659</v>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -30593,6 +32969,12 @@
       <c r="X396" s="3" t="n">
         <v>-0.00485908649173958</v>
       </c>
+      <c r="Y396" s="1" t="n">
+        <v>0.03095</v>
+      </c>
+      <c r="Z396" s="2" t="n">
+        <v>0.007486979166666587</v>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -30669,6 +33051,12 @@
       <c r="X397" s="3" t="n">
         <v>-0.001990710019907065</v>
       </c>
+      <c r="Y397" s="1" t="n">
+        <v>0.1506</v>
+      </c>
+      <c r="Z397" s="2" t="n">
+        <v>0.001329787234042591</v>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -30745,6 +33133,12 @@
       <c r="X398" s="2" t="n">
         <v>0.0006060606060605551</v>
       </c>
+      <c r="Y398" s="1" t="n">
+        <v>0.003295</v>
+      </c>
+      <c r="Z398" s="3" t="n">
+        <v>-0.002119927316777598</v>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -30821,6 +33215,12 @@
       <c r="X399" s="3" t="n">
         <v>-0.01334757074212494</v>
       </c>
+      <c r="Y399" s="1" t="n">
+        <v>0.01859</v>
+      </c>
+      <c r="Z399" s="2" t="n">
+        <v>0.005952380952380897</v>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -30897,6 +33297,12 @@
       <c r="X400" s="2" t="n">
         <v>0.005331412103746355</v>
       </c>
+      <c r="Y400" s="1" t="n">
+        <v>0.006954</v>
+      </c>
+      <c r="Z400" s="3" t="n">
+        <v>-0.003296545793320852</v>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -30973,6 +33379,12 @@
       <c r="X401" s="3" t="n">
         <v>-0.004862004862004887</v>
       </c>
+      <c r="Y401" s="1" t="n">
+        <v>0.006973</v>
+      </c>
+      <c r="Z401" s="2" t="n">
+        <v>0.00201178330219861</v>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -31049,6 +33461,12 @@
       <c r="X402" s="2" t="n">
         <v>0.0009997500624842949</v>
       </c>
+      <c r="Y402" s="1" t="n">
+        <v>0.008037000000000001</v>
+      </c>
+      <c r="Z402" s="2" t="n">
+        <v>0.003370786516854055</v>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -31125,6 +33543,12 @@
       <c r="X403" s="2" t="n">
         <v>0.00040758100672507</v>
       </c>
+      <c r="Y403" s="1" t="n">
+        <v>0.04943</v>
+      </c>
+      <c r="Z403" s="2" t="n">
+        <v>0.006926054186188633</v>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -31201,6 +33625,12 @@
       <c r="X404" s="3" t="n">
         <v>-0.001948793763859853</v>
       </c>
+      <c r="Y404" s="1" t="n">
+        <v>0.14861</v>
+      </c>
+      <c r="Z404" s="2" t="n">
+        <v>0.0006059789927281105</v>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -31277,6 +33707,12 @@
       <c r="X405" s="3" t="n">
         <v>-0.0002335902826443135</v>
       </c>
+      <c r="Y405" s="1" t="n">
+        <v>0.04298</v>
+      </c>
+      <c r="Z405" s="2" t="n">
+        <v>0.004205607476635505</v>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -31353,6 +33789,12 @@
       <c r="X406" s="3" t="n">
         <v>-0.001462904911180728</v>
       </c>
+      <c r="Y406" s="1" t="n">
+        <v>0.4794</v>
+      </c>
+      <c r="Z406" s="2" t="n">
+        <v>0.003348681456676413</v>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -31429,6 +33871,12 @@
       <c r="X407" s="2" t="n">
         <v>0.001217532467532277</v>
       </c>
+      <c r="Y407" s="1" t="n">
+        <v>0.0004959</v>
+      </c>
+      <c r="Z407" s="2" t="n">
+        <v>0.005066882853668437</v>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -31505,6 +33953,12 @@
       <c r="X408" s="2" t="n">
         <v>0.001619433198380641</v>
       </c>
+      <c r="Y408" s="1" t="n">
+        <v>0.01245</v>
+      </c>
+      <c r="Z408" s="2" t="n">
+        <v>0.006467259498787265</v>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -31581,6 +34035,12 @@
       <c r="X409" s="2" t="n">
         <v>0.00536616161616155</v>
       </c>
+      <c r="Y409" s="1" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="Z409" s="2" t="n">
+        <v>0.001569858712715857</v>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -31657,6 +34117,12 @@
       <c r="X410" s="3" t="n">
         <v>-0.002154140737194825</v>
       </c>
+      <c r="Y410" s="1" t="n">
+        <v>0.04187</v>
+      </c>
+      <c r="Z410" s="2" t="n">
+        <v>0.004317582153993754</v>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -31733,6 +34199,12 @@
       <c r="X411" s="2" t="n">
         <v>0.0003369272237196628</v>
       </c>
+      <c r="Y411" s="1" t="n">
+        <v>0.02976</v>
+      </c>
+      <c r="Z411" s="2" t="n">
+        <v>0.002357696194004736</v>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
@@ -31809,6 +34281,12 @@
       <c r="X412" s="3" t="n">
         <v>-0.0006555944055944926</v>
       </c>
+      <c r="Y412" s="1" t="n">
+        <v>0.004581</v>
+      </c>
+      <c r="Z412" s="2" t="n">
+        <v>0.001749398644216093</v>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -31885,6 +34363,12 @@
       <c r="X413" s="3" t="n">
         <v>-0.002783300198807071</v>
       </c>
+      <c r="Y413" s="1" t="n">
+        <v>0.2527</v>
+      </c>
+      <c r="Z413" s="2" t="n">
+        <v>0.007575757575757405</v>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -31961,6 +34445,12 @@
       <c r="X414" s="3" t="n">
         <v>-0.0007818608287723924</v>
       </c>
+      <c r="Y414" s="1" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z414" s="2" t="n">
+        <v>0.001564945226917059</v>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -32037,6 +34527,12 @@
       <c r="X415" s="3" t="n">
         <v>-0.005126327352618012</v>
       </c>
+      <c r="Y415" s="1" t="n">
+        <v>2.745</v>
+      </c>
+      <c r="Z415" s="2" t="n">
+        <v>0.01030548398969452</v>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -32113,6 +34609,12 @@
       <c r="X416" s="2" t="n">
         <v>0.001855861429013439</v>
       </c>
+      <c r="Y416" s="1" t="n">
+        <v>0.03245</v>
+      </c>
+      <c r="Z416" s="2" t="n">
+        <v>0.001852423587526939</v>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -32189,6 +34691,12 @@
       <c r="X417" s="2" t="n">
         <v>0.001768123263450382</v>
       </c>
+      <c r="Y417" s="1" t="n">
+        <v>0.03983</v>
+      </c>
+      <c r="Z417" s="2" t="n">
+        <v>0.00428643469490662</v>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -32265,6 +34773,12 @@
       <c r="X418" s="3" t="n">
         <v>-0.001970055161544488</v>
       </c>
+      <c r="Y418" s="1" t="n">
+        <v>0.07618999999999999</v>
+      </c>
+      <c r="Z418" s="2" t="n">
+        <v>0.002631925253322698</v>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -32341,6 +34855,12 @@
       <c r="X419" s="3" t="n">
         <v>-0.001510574018126827</v>
       </c>
+      <c r="Y419" s="1" t="n">
+        <v>0.00665</v>
+      </c>
+      <c r="Z419" s="2" t="n">
+        <v>0.006051437216338764</v>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -32417,6 +34937,12 @@
       <c r="X420" s="3" t="n">
         <v>-0.00226757369614519</v>
       </c>
+      <c r="Y420" s="1" t="n">
+        <v>0.0882</v>
+      </c>
+      <c r="Z420" s="2" t="n">
+        <v>0.002272727272727338</v>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -32493,6 +35019,12 @@
       <c r="X421" s="3" t="n">
         <v>-0.002086811352253758</v>
       </c>
+      <c r="Y421" s="1" t="n">
+        <v>0.2409</v>
+      </c>
+      <c r="Z421" s="2" t="n">
+        <v>0.007528230865746533</v>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
@@ -32569,6 +35101,12 @@
       <c r="X422" s="2" t="n">
         <v>0.01538461538461547</v>
       </c>
+      <c r="Y422" s="1" t="n">
+        <v>0.0247</v>
+      </c>
+      <c r="Z422" s="2" t="n">
+        <v>0.2474747474747473</v>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -32645,6 +35183,12 @@
       <c r="X423" s="3" t="n">
         <v>-0.002647253474520261</v>
       </c>
+      <c r="Y423" s="1" t="n">
+        <v>0.1512</v>
+      </c>
+      <c r="Z423" s="2" t="n">
+        <v>0.003317850033178503</v>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -32721,6 +35265,12 @@
       <c r="X424" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="Y424" s="1" t="n">
+        <v>0.0002098</v>
+      </c>
+      <c r="Z424" s="2" t="n">
+        <v>0.003347680535628967</v>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -32797,6 +35347,12 @@
       <c r="X425" s="2" t="n">
         <v>0.001616814874696848</v>
       </c>
+      <c r="Y425" s="1" t="n">
+        <v>1.244</v>
+      </c>
+      <c r="Z425" s="2" t="n">
+        <v>0.004035512510088695</v>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
@@ -32873,6 +35429,12 @@
       <c r="X426" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="Y426" s="1" t="n">
+        <v>1.418</v>
+      </c>
+      <c r="Z426" s="2" t="n">
+        <v>0.003538570417551234</v>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -32949,6 +35511,12 @@
       <c r="X427" s="3" t="n">
         <v>-0.0005144032921810491</v>
       </c>
+      <c r="Y427" s="1" t="n">
+        <v>0.01949</v>
+      </c>
+      <c r="Z427" s="2" t="n">
+        <v>0.003088008234688679</v>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
@@ -33025,6 +35593,12 @@
       <c r="X428" s="3" t="n">
         <v>-0.002870524248375823</v>
       </c>
+      <c r="Y428" s="1" t="n">
+        <v>0.06619</v>
+      </c>
+      <c r="Z428" s="2" t="n">
+        <v>0.002878787878787814</v>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
@@ -33101,6 +35675,12 @@
       <c r="X429" s="3" t="n">
         <v>-0.001515151515151559</v>
       </c>
+      <c r="Y429" s="1" t="n">
+        <v>0.1324</v>
+      </c>
+      <c r="Z429" s="2" t="n">
+        <v>0.004552352048558341</v>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
@@ -33177,6 +35757,12 @@
       <c r="X430" s="2" t="n">
         <v>0.0003625815808557406</v>
       </c>
+      <c r="Y430" s="1" t="n">
+        <v>0.01105</v>
+      </c>
+      <c r="Z430" s="2" t="n">
+        <v>0.001268575570859018</v>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -33253,6 +35839,12 @@
       <c r="X431" s="3" t="n">
         <v>-0.003435399551904474</v>
       </c>
+      <c r="Y431" s="1" t="n">
+        <v>0.006696</v>
+      </c>
+      <c r="Z431" s="2" t="n">
+        <v>0.003597122302158231</v>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
@@ -33329,6 +35921,12 @@
       <c r="X432" s="3" t="n">
         <v>-0.0005656108597285819</v>
       </c>
+      <c r="Y432" s="1" t="n">
+        <v>0.001773</v>
+      </c>
+      <c r="Z432" s="2" t="n">
+        <v>0.003395585738539981</v>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
@@ -33405,6 +36003,12 @@
       <c r="X433" s="2" t="n">
         <v>0.0007342143906021533</v>
       </c>
+      <c r="Y433" s="1" t="n">
+        <v>0.00136</v>
+      </c>
+      <c r="Z433" s="3" t="n">
+        <v>-0.002201027146001441</v>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
@@ -33481,6 +36085,12 @@
       <c r="X434" s="2" t="n">
         <v>0.004878048780487791</v>
       </c>
+      <c r="Y434" s="1" t="n">
+        <v>0.000413</v>
+      </c>
+      <c r="Z434" s="2" t="n">
+        <v>0.002427184466019477</v>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
@@ -33557,6 +36167,12 @@
       <c r="X435" s="3" t="n">
         <v>-0.0006322111585271415</v>
       </c>
+      <c r="Y435" s="1" t="n">
+        <v>0.12705</v>
+      </c>
+      <c r="Z435" s="2" t="n">
+        <v>0.004665506879645795</v>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -33633,6 +36249,12 @@
       <c r="X436" s="3" t="n">
         <v>-0.001158152103976409</v>
       </c>
+      <c r="Y436" s="1" t="n">
+        <v>0.07813000000000001</v>
+      </c>
+      <c r="Z436" s="2" t="n">
+        <v>0.006570471527956847</v>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
@@ -33709,6 +36331,12 @@
       <c r="X437" s="3" t="n">
         <v>-0.003652532952199587</v>
       </c>
+      <c r="Y437" s="1" t="n">
+        <v>0.6282</v>
+      </c>
+      <c r="Z437" s="2" t="n">
+        <v>0.001275103602167713</v>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -33785,6 +36413,12 @@
       <c r="X438" s="2" t="n">
         <v>0.0009144947416551982</v>
       </c>
+      <c r="Y438" s="1" t="n">
+        <v>0.04391</v>
+      </c>
+      <c r="Z438" s="2" t="n">
+        <v>0.002969392416628556</v>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
@@ -33861,6 +36495,12 @@
       <c r="X439" s="3" t="n">
         <v>-0.002141327623126301</v>
       </c>
+      <c r="Y439" s="1" t="n">
+        <v>0.07013999999999999</v>
+      </c>
+      <c r="Z439" s="2" t="n">
+        <v>0.003433476394849645</v>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
@@ -33937,6 +36577,12 @@
       <c r="X440" s="3" t="n">
         <v>-0.000660501981505889</v>
       </c>
+      <c r="Y440" s="1" t="n">
+        <v>0.001519</v>
+      </c>
+      <c r="Z440" s="2" t="n">
+        <v>0.003965631196298698</v>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -34013,6 +36659,12 @@
       <c r="X441" s="2" t="n">
         <v>0.00200633579725448</v>
       </c>
+      <c r="Y441" s="1" t="n">
+        <v>0.00946</v>
+      </c>
+      <c r="Z441" s="3" t="n">
+        <v>-0.003056170302455424</v>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
@@ -34089,6 +36741,12 @@
       <c r="X442" s="3" t="n">
         <v>-0.01037735849056615</v>
       </c>
+      <c r="Y442" s="1" t="n">
+        <v>1.055</v>
+      </c>
+      <c r="Z442" s="2" t="n">
+        <v>0.005719733079122979</v>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
@@ -34165,6 +36823,12 @@
       <c r="X443" s="3" t="n">
         <v>-0.003190519598906135</v>
       </c>
+      <c r="Y443" s="1" t="n">
+        <v>0.02201</v>
+      </c>
+      <c r="Z443" s="2" t="n">
+        <v>0.006401463191586546</v>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
@@ -34241,6 +36905,12 @@
       <c r="X444" s="2" t="n">
         <v>0.0002625360987135795</v>
       </c>
+      <c r="Y444" s="1" t="n">
+        <v>0.0003823</v>
+      </c>
+      <c r="Z444" s="2" t="n">
+        <v>0.003412073490813732</v>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
@@ -34317,6 +36987,12 @@
       <c r="X445" s="3" t="n">
         <v>-0.001127395715896234</v>
       </c>
+      <c r="Y445" s="1" t="n">
+        <v>0.03557</v>
+      </c>
+      <c r="Z445" s="2" t="n">
+        <v>0.003668171557562025</v>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
@@ -34393,6 +37069,12 @@
       <c r="X446" s="3" t="n">
         <v>-0.002925002925002927</v>
       </c>
+      <c r="Y446" s="1" t="n">
+        <v>0.08593000000000001</v>
+      </c>
+      <c r="Z446" s="2" t="n">
+        <v>0.008331377610889489</v>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
@@ -34469,6 +37151,12 @@
       <c r="X447" s="3" t="n">
         <v>-0.004263093788063273</v>
       </c>
+      <c r="Y447" s="1" t="n">
+        <v>3.272</v>
+      </c>
+      <c r="Z447" s="2" t="n">
+        <v>0.0006116207951069663</v>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
@@ -34545,6 +37233,12 @@
       <c r="X448" s="3" t="n">
         <v>-0.001563721657545002</v>
       </c>
+      <c r="Y448" s="1" t="n">
+        <v>0.06401999999999999</v>
+      </c>
+      <c r="Z448" s="2" t="n">
+        <v>0.002662490211432883</v>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
@@ -34621,6 +37315,12 @@
       <c r="X449" s="3" t="n">
         <v>-0.000822199383350486</v>
       </c>
+      <c r="Y449" s="1" t="n">
+        <v>0.4877</v>
+      </c>
+      <c r="Z449" s="2" t="n">
+        <v>0.00329150380580137</v>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
@@ -34697,6 +37397,12 @@
       <c r="X450" s="2" t="n">
         <v>0.002930207778369897</v>
       </c>
+      <c r="Y450" s="1" t="n">
+        <v>0.03766</v>
+      </c>
+      <c r="Z450" s="2" t="n">
+        <v>0.0002656042496678917</v>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -34773,6 +37479,12 @@
       <c r="X451" s="3" t="n">
         <v>-0.00364963503649636</v>
       </c>
+      <c r="Y451" s="1" t="n">
+        <v>0.00548</v>
+      </c>
+      <c r="Z451" s="2" t="n">
+        <v>0.003663003663003673</v>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
@@ -34849,6 +37561,12 @@
       <c r="X452" s="2" t="n">
         <v>0.003483309143686495</v>
       </c>
+      <c r="Y452" s="1" t="n">
+        <v>0.10408</v>
+      </c>
+      <c r="Z452" s="2" t="n">
+        <v>0.003567640536110396</v>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
@@ -34925,6 +37643,12 @@
       <c r="X453" s="3" t="n">
         <v>-0.0018645121193287</v>
       </c>
+      <c r="Y453" s="1" t="n">
+        <v>0.01637</v>
+      </c>
+      <c r="Z453" s="2" t="n">
+        <v>0.01930261519302601</v>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
@@ -35001,6 +37725,12 @@
       <c r="X454" s="2" t="n">
         <v>0.006567576909782278</v>
       </c>
+      <c r="Y454" s="1" t="n">
+        <v>2.873</v>
+      </c>
+      <c r="Z454" s="3" t="n">
+        <v>-0.01339285714285704</v>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
@@ -35077,6 +37807,12 @@
       <c r="X455" s="3" t="n">
         <v>-0.002234636871508382</v>
       </c>
+      <c r="Y455" s="1" t="n">
+        <v>0.897</v>
+      </c>
+      <c r="Z455" s="2" t="n">
+        <v>0.004479283314669656</v>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
@@ -35153,6 +37889,12 @@
       <c r="X456" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="Y456" s="1" t="n">
+        <v>2.952</v>
+      </c>
+      <c r="Z456" s="2" t="n">
+        <v>0.002036659877800334</v>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -35229,6 +37971,12 @@
       <c r="X457" s="2" t="n">
         <v>0.001015228426396074</v>
       </c>
+      <c r="Y457" s="1" t="n">
+        <v>0.00988</v>
+      </c>
+      <c r="Z457" s="2" t="n">
+        <v>0.002028397565922838</v>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
@@ -35305,6 +38053,12 @@
       <c r="X458" s="2" t="n">
         <v>0.002093734900950204</v>
       </c>
+      <c r="Y458" s="1" t="n">
+        <v>0.06228</v>
+      </c>
+      <c r="Z458" s="2" t="n">
+        <v>0.0009643201542912969</v>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
@@ -35381,6 +38135,12 @@
       <c r="X459" s="3" t="n">
         <v>-0.001399580125962276</v>
       </c>
+      <c r="Y459" s="1" t="n">
+        <v>0.01432</v>
+      </c>
+      <c r="Z459" s="2" t="n">
+        <v>0.003503854239663609</v>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
@@ -35457,6 +38217,12 @@
       <c r="X460" s="3" t="n">
         <v>-0.0008123984501936711</v>
       </c>
+      <c r="Y460" s="1" t="n">
+        <v>0.016006</v>
+      </c>
+      <c r="Z460" s="2" t="n">
+        <v>0.001063230971292742</v>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
@@ -35533,6 +38299,12 @@
       <c r="X461" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="Y461" s="1" t="n">
+        <v>0.01671</v>
+      </c>
+      <c r="Z461" s="2" t="n">
+        <v>0.003001200480191954</v>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
@@ -35609,6 +38381,12 @@
       <c r="X462" s="3" t="n">
         <v>-0.002865329512893923</v>
       </c>
+      <c r="Y462" s="1" t="n">
+        <v>0.0002095</v>
+      </c>
+      <c r="Z462" s="2" t="n">
+        <v>0.00335249042145589</v>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
@@ -35685,6 +38463,12 @@
       <c r="X463" s="3" t="n">
         <v>-0.002022244691607742</v>
       </c>
+      <c r="Y463" s="1" t="n">
+        <v>0.09959999999999999</v>
+      </c>
+      <c r="Z463" s="2" t="n">
+        <v>0.009118541033434631</v>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
@@ -35761,6 +38545,12 @@
       <c r="X464" s="3" t="n">
         <v>-0.0007639419404124975</v>
       </c>
+      <c r="Y464" s="1" t="n">
+        <v>0.02645</v>
+      </c>
+      <c r="Z464" s="2" t="n">
+        <v>0.01108562691131506</v>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
@@ -35837,6 +38627,12 @@
       <c r="X465" s="3" t="n">
         <v>-0.00397877984084876</v>
       </c>
+      <c r="Y465" s="1" t="n">
+        <v>0.01499</v>
+      </c>
+      <c r="Z465" s="3" t="n">
+        <v>-0.001997336884154495</v>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
@@ -35913,6 +38709,12 @@
       <c r="X466" s="3" t="n">
         <v>-0.0007301935012779355</v>
       </c>
+      <c r="Y466" s="1" t="n">
+        <v>0.05477</v>
+      </c>
+      <c r="Z466" s="2" t="n">
+        <v>0.0005480453050785943</v>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
@@ -35989,6 +38791,12 @@
       <c r="X467" s="2" t="n">
         <v>0.0008728542333430972</v>
       </c>
+      <c r="Y467" s="1" t="n">
+        <v>0.03462</v>
+      </c>
+      <c r="Z467" s="2" t="n">
+        <v>0.006395348837209243</v>
+      </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
@@ -36065,6 +38873,12 @@
       <c r="X468" s="3" t="n">
         <v>-0.002546380502000609</v>
       </c>
+      <c r="Y468" s="1" t="n">
+        <v>27.39</v>
+      </c>
+      <c r="Z468" s="3" t="n">
+        <v>-0.001094091903719954</v>
+      </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
@@ -36141,6 +38955,12 @@
       <c r="X469" s="3" t="n">
         <v>-0.004816697886004789</v>
       </c>
+      <c r="Y469" s="1" t="n">
+        <v>0.0007485</v>
+      </c>
+      <c r="Z469" s="2" t="n">
+        <v>0.006318902930895483</v>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
@@ -36217,6 +39037,12 @@
       <c r="X470" s="3" t="n">
         <v>-0.006756756756756762</v>
       </c>
+      <c r="Y470" s="1" t="n">
+        <v>0.888</v>
+      </c>
+      <c r="Z470" s="2" t="n">
+        <v>0.00680272108843538</v>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
@@ -36293,6 +39119,12 @@
       <c r="X471" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="Y471" s="1" t="n">
+        <v>0.00991</v>
+      </c>
+      <c r="Z471" s="2" t="n">
+        <v>0.003036437246963615</v>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
@@ -36369,6 +39201,12 @@
       <c r="X472" s="3" t="n">
         <v>-0.001075500107549892</v>
       </c>
+      <c r="Y472" s="1" t="n">
+        <v>0.04668</v>
+      </c>
+      <c r="Z472" s="2" t="n">
+        <v>0.005167958656330688</v>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -36445,6 +39283,12 @@
       <c r="X473" s="2" t="n">
         <v>0.0007304601899197717</v>
       </c>
+      <c r="Y473" s="1" t="n">
+        <v>0.2747</v>
+      </c>
+      <c r="Z473" s="2" t="n">
+        <v>0.002554744525547366</v>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
@@ -36521,6 +39365,12 @@
       <c r="X474" s="3" t="n">
         <v>-0.001140771161305075</v>
       </c>
+      <c r="Y474" s="1" t="n">
+        <v>0.04384</v>
+      </c>
+      <c r="Z474" s="2" t="n">
+        <v>0.001370488807674681</v>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
@@ -36597,6 +39447,12 @@
       <c r="X475" s="3" t="n">
         <v>-0.0008279124778237801</v>
       </c>
+      <c r="Y475" s="1" t="n">
+        <v>0.008467000000000001</v>
+      </c>
+      <c r="Z475" s="2" t="n">
+        <v>0.00224905303030302</v>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
@@ -36673,6 +39529,12 @@
       <c r="X476" s="3" t="n">
         <v>-0.001713586291309685</v>
       </c>
+      <c r="Y476" s="1" t="n">
+        <v>0.0823</v>
+      </c>
+      <c r="Z476" s="2" t="n">
+        <v>0.009073075036782794</v>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
@@ -36749,6 +39611,12 @@
       <c r="X477" s="3" t="n">
         <v>-0.004408523144746432</v>
       </c>
+      <c r="Y477" s="1" t="n">
+        <v>0.1361</v>
+      </c>
+      <c r="Z477" s="2" t="n">
+        <v>0.004428044280442726</v>
+      </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
@@ -36825,6 +39693,12 @@
       <c r="X478" s="3" t="n">
         <v>-0.001260398285858332</v>
       </c>
+      <c r="Y478" s="1" t="n">
+        <v>0.3985</v>
+      </c>
+      <c r="Z478" s="2" t="n">
+        <v>0.005805148914689612</v>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
@@ -36901,6 +39775,12 @@
       <c r="X479" s="3" t="n">
         <v>-0.004174397031539839</v>
       </c>
+      <c r="Y479" s="1" t="n">
+        <v>0.008621</v>
+      </c>
+      <c r="Z479" s="2" t="n">
+        <v>0.003842571029343275</v>
+      </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
@@ -36977,6 +39857,12 @@
       <c r="X480" s="3" t="n">
         <v>-0.008739076154806569</v>
       </c>
+      <c r="Y480" s="1" t="n">
+        <v>0.01603</v>
+      </c>
+      <c r="Z480" s="2" t="n">
+        <v>0.009445843828715418</v>
+      </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
@@ -37053,6 +39939,12 @@
       <c r="X481" s="3" t="n">
         <v>-0.001659221442246396</v>
       </c>
+      <c r="Y481" s="1" t="n">
+        <v>0.07838000000000001</v>
+      </c>
+      <c r="Z481" s="2" t="n">
+        <v>0.002045512656609657</v>
+      </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
@@ -37129,6 +40021,12 @@
       <c r="X482" s="3" t="n">
         <v>-0.001986097318768539</v>
       </c>
+      <c r="Y482" s="1" t="n">
+        <v>0.05051</v>
+      </c>
+      <c r="Z482" s="2" t="n">
+        <v>0.005174129353233758</v>
+      </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
@@ -37205,6 +40103,12 @@
       <c r="X483" s="3" t="n">
         <v>-0.001030927835051504</v>
       </c>
+      <c r="Y483" s="1" t="n">
+        <v>0.00971</v>
+      </c>
+      <c r="Z483" s="2" t="n">
+        <v>0.002063983488132011</v>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
@@ -37281,6 +40185,12 @@
       <c r="X484" s="3" t="n">
         <v>-0.003525782282944088</v>
       </c>
+      <c r="Y484" s="1" t="n">
+        <v>0.06798999999999999</v>
+      </c>
+      <c r="Z484" s="2" t="n">
+        <v>0.002358838272150869</v>
+      </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
@@ -37357,6 +40267,12 @@
       <c r="X485" s="2" t="n">
         <v>0.002441189525077613</v>
       </c>
+      <c r="Y485" s="1" t="n">
+        <v>0.0004535</v>
+      </c>
+      <c r="Z485" s="2" t="n">
+        <v>0.00398494576046058</v>
+      </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
@@ -37433,6 +40349,12 @@
       <c r="X486" s="2" t="n">
         <v>0.00100984599848519</v>
       </c>
+      <c r="Y486" s="1" t="n">
+        <v>0.07929</v>
+      </c>
+      <c r="Z486" s="3" t="n">
+        <v>-0.0001261034047918805</v>
+      </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
@@ -37509,6 +40431,12 @@
       <c r="X487" s="3" t="n">
         <v>-0.001729106628241961</v>
       </c>
+      <c r="Y487" s="1" t="n">
+        <v>0.0001737</v>
+      </c>
+      <c r="Z487" s="2" t="n">
+        <v>0.002886836027713539</v>
+      </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
@@ -37585,6 +40513,12 @@
       <c r="X488" s="3" t="n">
         <v>-0.003771910361659564</v>
       </c>
+      <c r="Y488" s="1" t="n">
+        <v>0.08971</v>
+      </c>
+      <c r="Z488" s="3" t="n">
+        <v>-0.00100222717149228</v>
+      </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
@@ -37661,6 +40595,12 @@
       <c r="X489" s="3" t="n">
         <v>-0.002509410288582226</v>
       </c>
+      <c r="Y489" s="1" t="n">
+        <v>0.04797</v>
+      </c>
+      <c r="Z489" s="2" t="n">
+        <v>0.005660377358490554</v>
+      </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
@@ -37737,6 +40677,12 @@
       <c r="X490" s="2" t="n">
         <v>0.009575569358178113</v>
       </c>
+      <c r="Y490" s="1" t="n">
+        <v>0.0393</v>
+      </c>
+      <c r="Z490" s="2" t="n">
+        <v>0.007433991284286044</v>
+      </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
@@ -37813,6 +40759,12 @@
       <c r="X491" s="3" t="n">
         <v>-0.005937342091965617</v>
       </c>
+      <c r="Y491" s="1" t="n">
+        <v>0.08223999999999999</v>
+      </c>
+      <c r="Z491" s="2" t="n">
+        <v>0.0451137374507561</v>
+      </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
@@ -37889,6 +40841,12 @@
       <c r="X492" s="3" t="n">
         <v>-0.004413619167717568</v>
       </c>
+      <c r="Y492" s="1" t="n">
+        <v>0.06303</v>
+      </c>
+      <c r="Z492" s="3" t="n">
+        <v>-0.002058264724509045</v>
+      </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
@@ -37965,6 +40923,12 @@
       <c r="X493" s="3" t="n">
         <v>-0.001915708812260458</v>
       </c>
+      <c r="Y493" s="1" t="n">
+        <v>0.00523</v>
+      </c>
+      <c r="Z493" s="2" t="n">
+        <v>0.003838771593090221</v>
+      </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
@@ -38041,6 +41005,12 @@
       <c r="X494" s="3" t="n">
         <v>-0.002176278563656109</v>
       </c>
+      <c r="Y494" s="1" t="n">
+        <v>0.2755</v>
+      </c>
+      <c r="Z494" s="2" t="n">
+        <v>0.001454016721192335</v>
+      </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
@@ -38117,6 +41087,12 @@
       <c r="X495" s="2" t="n">
         <v>0.0003138731952292236</v>
       </c>
+      <c r="Y495" s="1" t="n">
+        <v>0.06398</v>
+      </c>
+      <c r="Z495" s="2" t="n">
+        <v>0.003765296517100568</v>
+      </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
@@ -38193,6 +41169,12 @@
       <c r="X496" s="2" t="n">
         <v>0.001365187713310619</v>
       </c>
+      <c r="Y496" s="1" t="n">
+        <v>0.2938</v>
+      </c>
+      <c r="Z496" s="2" t="n">
+        <v>0.001363326516700789</v>
+      </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
@@ -38269,6 +41251,12 @@
       <c r="X497" s="3" t="n">
         <v>-0.003377533149862303</v>
       </c>
+      <c r="Y497" s="1" t="n">
+        <v>0.07965</v>
+      </c>
+      <c r="Z497" s="3" t="n">
+        <v>-0.0002510355215263728</v>
+      </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
@@ -38345,6 +41333,12 @@
       <c r="X498" s="3" t="n">
         <v>-0.004840271055179094</v>
       </c>
+      <c r="Y498" s="1" t="n">
+        <v>0.1033</v>
+      </c>
+      <c r="Z498" s="2" t="n">
+        <v>0.004863813229571989</v>
+      </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
@@ -38421,6 +41415,12 @@
       <c r="X499" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="Y499" s="1" t="n">
+        <v>0.04195</v>
+      </c>
+      <c r="Z499" s="2" t="n">
+        <v>0.004790419161676617</v>
+      </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
@@ -38497,6 +41497,12 @@
       <c r="X500" s="2" t="n">
         <v>0.00627195183140994</v>
       </c>
+      <c r="Y500" s="1" t="n">
+        <v>0.04032</v>
+      </c>
+      <c r="Z500" s="2" t="n">
+        <v>0.005235602094240884</v>
+      </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
@@ -38573,6 +41579,12 @@
       <c r="X501" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="Y501" s="1" t="n">
+        <v>0.0993</v>
+      </c>
+      <c r="Z501" s="2" t="n">
+        <v>0.006079027355623134</v>
+      </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
@@ -38649,6 +41661,12 @@
       <c r="X502" s="2" t="n">
         <v>0.0009060706735125232</v>
       </c>
+      <c r="Y502" s="1" t="n">
+        <v>0.003311</v>
+      </c>
+      <c r="Z502" s="3" t="n">
+        <v>-0.0009052504526252155</v>
+      </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
@@ -38725,6 +41743,12 @@
       <c r="X503" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="Y503" s="1" t="n">
+        <v>0.00916</v>
+      </c>
+      <c r="Z503" s="2" t="n">
+        <v>0.00328587075575033</v>
+      </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
@@ -38801,6 +41825,12 @@
       <c r="X504" s="3" t="n">
         <v>-0.003140703517587942</v>
       </c>
+      <c r="Y504" s="1" t="n">
+        <v>0.1596</v>
+      </c>
+      <c r="Z504" s="2" t="n">
+        <v>0.005671077504725798</v>
+      </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
@@ -38877,6 +41907,12 @@
       <c r="X505" s="2" t="n">
         <v>0.0007627765064837281</v>
       </c>
+      <c r="Y505" s="1" t="n">
+        <v>0.1317</v>
+      </c>
+      <c r="Z505" s="2" t="n">
+        <v>0.003810975609756101</v>
+      </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
@@ -38953,6 +41989,12 @@
       <c r="X506" s="3" t="n">
         <v>-0.001184132622853711</v>
       </c>
+      <c r="Y506" s="1" t="n">
+        <v>0.01706</v>
+      </c>
+      <c r="Z506" s="2" t="n">
+        <v>0.01126259632483694</v>
+      </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
@@ -39029,6 +42071,12 @@
       <c r="X507" s="3" t="n">
         <v>-0.004184100418409993</v>
       </c>
+      <c r="Y507" s="1" t="n">
+        <v>0.002854</v>
+      </c>
+      <c r="Z507" s="3" t="n">
+        <v>-0.0007002801120447591</v>
+      </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
@@ -39105,6 +42153,12 @@
       <c r="X508" s="3" t="n">
         <v>-0.003177485247389775</v>
       </c>
+      <c r="Y508" s="1" t="n">
+        <v>2.207</v>
+      </c>
+      <c r="Z508" s="2" t="n">
+        <v>0.005009107468123714</v>
+      </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
@@ -39181,6 +42235,12 @@
       <c r="X509" s="3" t="n">
         <v>-0.0009110787172011923</v>
       </c>
+      <c r="Y509" s="1" t="n">
+        <v>0.0551</v>
+      </c>
+      <c r="Z509" s="2" t="n">
+        <v>0.004924311508298492</v>
+      </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
@@ -39257,6 +42317,12 @@
       <c r="X510" s="3" t="n">
         <v>-0.001700680272108774</v>
       </c>
+      <c r="Y510" s="1" t="n">
+        <v>0.02943</v>
+      </c>
+      <c r="Z510" s="2" t="n">
+        <v>0.002725724020442937</v>
+      </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
@@ -39333,6 +42399,12 @@
       <c r="X511" s="3" t="n">
         <v>-0.0009905894006933722</v>
       </c>
+      <c r="Y511" s="1" t="n">
+        <v>0.04042</v>
+      </c>
+      <c r="Z511" s="2" t="n">
+        <v>0.001983143282102051</v>
+      </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
@@ -39409,6 +42481,12 @@
       <c r="X512" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="Y512" s="1" t="n">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="Z512" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
@@ -39485,6 +42563,12 @@
       <c r="X513" s="3" t="n">
         <v>-0.00398379921651944</v>
       </c>
+      <c r="Y513" s="1" t="n">
+        <v>0.014895</v>
+      </c>
+      <c r="Z513" s="3" t="n">
+        <v>-0.007066195586960882</v>
+      </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
@@ -39561,6 +42645,12 @@
       <c r="X514" s="2" t="n">
         <v>0.0005747126436782572</v>
       </c>
+      <c r="Y514" s="1" t="n">
+        <v>0.1752</v>
+      </c>
+      <c r="Z514" s="2" t="n">
+        <v>0.006318207926478977</v>
+      </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
@@ -39637,6 +42727,12 @@
       <c r="X515" s="3" t="n">
         <v>-0.0009293680297398036</v>
       </c>
+      <c r="Y515" s="1" t="n">
+        <v>0.108</v>
+      </c>
+      <c r="Z515" s="2" t="n">
+        <v>0.004651162790697679</v>
+      </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
@@ -39713,6 +42809,12 @@
       <c r="X516" s="2" t="n">
         <v>0.003759398496240611</v>
       </c>
+      <c r="Y516" s="1" t="n">
+        <v>0.00269</v>
+      </c>
+      <c r="Z516" s="2" t="n">
+        <v>0.007490636704119869</v>
+      </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
@@ -39789,6 +42891,12 @@
       <c r="X517" s="3" t="n">
         <v>-0.003110823071937747</v>
       </c>
+      <c r="Y517" s="1" t="n">
+        <v>0.007732</v>
+      </c>
+      <c r="Z517" s="2" t="n">
+        <v>0.005330906254063222</v>
+      </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
@@ -39865,6 +42973,12 @@
       <c r="X518" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="Y518" s="1" t="n">
+        <v>0.01688</v>
+      </c>
+      <c r="Z518" s="2" t="n">
+        <v>0.07310870947234573</v>
+      </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
@@ -39941,6 +43055,12 @@
       <c r="X519" s="2" t="n">
         <v>0.001903402331667903</v>
       </c>
+      <c r="Y519" s="1" t="n">
+        <v>0.004204</v>
+      </c>
+      <c r="Z519" s="3" t="n">
+        <v>-0.001662312989788663</v>
+      </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
@@ -40017,6 +43137,12 @@
       <c r="X520" s="3" t="n">
         <v>-0.0008628127696291049</v>
       </c>
+      <c r="Y520" s="1" t="n">
+        <v>0.001163</v>
+      </c>
+      <c r="Z520" s="2" t="n">
+        <v>0.004317789291882567</v>
+      </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
@@ -40093,6 +43219,12 @@
       <c r="X521" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="Y521" s="1" t="n">
+        <v>0.01337</v>
+      </c>
+      <c r="Z521" s="2" t="n">
+        <v>0.003000750187546895</v>
+      </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
@@ -40169,6 +43301,12 @@
       <c r="X522" s="2" t="n">
         <v>0.001895043731778379</v>
       </c>
+      <c r="Y522" s="1" t="n">
+        <v>0.6876</v>
+      </c>
+      <c r="Z522" s="2" t="n">
+        <v>0.0004364906154517197</v>
+      </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
@@ -40245,6 +43383,12 @@
       <c r="X523" s="3" t="n">
         <v>-0.002574370709382145</v>
       </c>
+      <c r="Y523" s="1" t="n">
+        <v>0.07006</v>
+      </c>
+      <c r="Z523" s="2" t="n">
+        <v>0.004588471465443086</v>
+      </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
@@ -40321,6 +43465,12 @@
       <c r="X524" s="3" t="n">
         <v>-0.001710863986313167</v>
       </c>
+      <c r="Y524" s="1" t="n">
+        <v>0.0117</v>
+      </c>
+      <c r="Z524" s="2" t="n">
+        <v>0.002570694087403643</v>
+      </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
@@ -40397,6 +43547,12 @@
       <c r="X525" s="3" t="n">
         <v>-0.001218769043266463</v>
       </c>
+      <c r="Y525" s="1" t="n">
+        <v>0.01644</v>
+      </c>
+      <c r="Z525" s="2" t="n">
+        <v>0.00305064063453334</v>
+      </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
@@ -40473,6 +43629,12 @@
       <c r="X526" s="3" t="n">
         <v>-0.002524127691165399</v>
       </c>
+      <c r="Y526" s="1" t="n">
+        <v>0.13446</v>
+      </c>
+      <c r="Z526" s="2" t="n">
+        <v>0.0007442691277165003</v>
+      </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
@@ -40549,6 +43711,12 @@
       <c r="X527" s="3" t="n">
         <v>-0.0009310986964617871</v>
       </c>
+      <c r="Y527" s="1" t="n">
+        <v>0.04304</v>
+      </c>
+      <c r="Z527" s="2" t="n">
+        <v>0.002795899347623533</v>
+      </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
@@ -40625,6 +43793,12 @@
       <c r="X528" s="3" t="n">
         <v>-0.001098096632503743</v>
       </c>
+      <c r="Y528" s="1" t="n">
+        <v>0.2738</v>
+      </c>
+      <c r="Z528" s="2" t="n">
+        <v>0.003297911322828919</v>
+      </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
@@ -40701,6 +43875,12 @@
       <c r="X529" s="2" t="n">
         <v>0.0005534800055348136</v>
       </c>
+      <c r="Y529" s="1" t="n">
+        <v>0.0007277</v>
+      </c>
+      <c r="Z529" s="2" t="n">
+        <v>0.006361499101092524</v>
+      </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
@@ -40777,6 +43957,12 @@
       <c r="X530" s="3" t="n">
         <v>-0.0004792715073087463</v>
       </c>
+      <c r="Y530" s="1" t="n">
+        <v>0.004181</v>
+      </c>
+      <c r="Z530" s="2" t="n">
+        <v>0.002397506593143033</v>
+      </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
@@ -40853,6 +44039,12 @@
       <c r="X531" s="3" t="n">
         <v>-0.001517450682852809</v>
       </c>
+      <c r="Y531" s="1" t="n">
+        <v>1.317</v>
+      </c>
+      <c r="Z531" s="2" t="n">
+        <v>0.0007598784194528038</v>
+      </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
@@ -40929,6 +44121,12 @@
       <c r="X532" s="3" t="n">
         <v>-0.001696352841391058</v>
       </c>
+      <c r="Y532" s="1" t="n">
+        <v>0.1181</v>
+      </c>
+      <c r="Z532" s="2" t="n">
+        <v>0.003398470688190294</v>
+      </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
@@ -41005,6 +44203,12 @@
       <c r="X533" s="3" t="n">
         <v>-0.0001867064973861662</v>
       </c>
+      <c r="Y533" s="1" t="n">
+        <v>0.05371</v>
+      </c>
+      <c r="Z533" s="2" t="n">
+        <v>0.002987861811391231</v>
+      </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
@@ -41081,6 +44285,12 @@
       <c r="X534" s="3" t="n">
         <v>-0.001997336884154426</v>
       </c>
+      <c r="Y534" s="1" t="n">
+        <v>0.1504</v>
+      </c>
+      <c r="Z534" s="2" t="n">
+        <v>0.003335557038025353</v>
+      </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
@@ -41157,6 +44367,12 @@
       <c r="X535" s="2" t="n">
         <v>0.001757469244288357</v>
       </c>
+      <c r="Y535" s="1" t="n">
+        <v>0.01724</v>
+      </c>
+      <c r="Z535" s="2" t="n">
+        <v>0.008187134502923845</v>
+      </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
@@ -41233,6 +44449,12 @@
       <c r="X536" s="3" t="n">
         <v>-0.002192108409724935</v>
       </c>
+      <c r="Y536" s="1" t="n">
+        <v>0.005011</v>
+      </c>
+      <c r="Z536" s="2" t="n">
+        <v>0.0007988815658078017</v>
+      </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
@@ -41309,6 +44531,12 @@
       <c r="X537" s="3" t="n">
         <v>-0.001371271854645223</v>
       </c>
+      <c r="Y537" s="1" t="n">
+        <v>0.2929</v>
+      </c>
+      <c r="Z537" s="2" t="n">
+        <v>0.005492619292825233</v>
+      </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
@@ -41385,6 +44613,12 @@
       <c r="X538" s="3" t="n">
         <v>-0.0007530120481927404</v>
       </c>
+      <c r="Y538" s="1" t="n">
+        <v>0.01335</v>
+      </c>
+      <c r="Z538" s="2" t="n">
+        <v>0.006028636021100242</v>
+      </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
@@ -41461,6 +44695,12 @@
       <c r="X539" s="2" t="n">
         <v>0.000792707094728603</v>
       </c>
+      <c r="Y539" s="1" t="n">
+        <v>0.02525</v>
+      </c>
+      <c r="Z539" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
@@ -41537,6 +44777,12 @@
       <c r="X540" s="3" t="n">
         <v>-0.001405975395430523</v>
       </c>
+      <c r="Y540" s="1" t="n">
+        <v>0.05682</v>
+      </c>
+      <c r="Z540" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
@@ -41613,6 +44859,12 @@
       <c r="X541" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="Y541" s="1" t="n">
+        <v>0.0116</v>
+      </c>
+      <c r="Z541" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
@@ -41689,6 +44941,12 @@
       <c r="X542" s="3" t="n">
         <v>-0.008928571428571343</v>
       </c>
+      <c r="Y542" s="1" t="n">
+        <v>1.12e-05</v>
+      </c>
+      <c r="Z542" s="2" t="n">
+        <v>0.009009009009008922</v>
+      </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
@@ -41764,6 +45022,12 @@
       </c>
       <c r="X543" s="3" t="n">
         <v>-0.000272182906913482</v>
+      </c>
+      <c r="Y543" s="1" t="n">
+        <v>0.003681</v>
+      </c>
+      <c r="Z543" s="2" t="n">
+        <v>0.002178056084944122</v>
       </c>
     </row>
   </sheetData>

--- a/binance-usdt-perpetual-data/weeks/2026-03-09_2026-03-15/2026-03-12.xlsx
+++ b/binance-usdt-perpetual-data/weeks/2026-03-09_2026-03-15/2026-03-12.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z543"/>
+  <dimension ref="A1:AB543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -452,6 +452,8 @@
     <col width="18" customWidth="1" min="24" max="24"/>
     <col width="13" customWidth="1" min="25" max="25"/>
     <col width="18" customWidth="1" min="26" max="26"/>
+    <col width="13" customWidth="1" min="27" max="27"/>
+    <col width="18" customWidth="1" min="28" max="28"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -585,6 +587,16 @@
           <t>change_03:00</t>
         </is>
       </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>price_03:15</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>change_03:15</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -667,6 +679,12 @@
       <c r="Z2" s="2" t="n">
         <v>0.001508387657046687</v>
       </c>
+      <c r="AA2" s="1" t="n">
+        <v>70434.10000000001</v>
+      </c>
+      <c r="AB2" s="3" t="n">
+        <v>-0.002051604658049196</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -749,6 +767,12 @@
       <c r="Z3" s="2" t="n">
         <v>0.003258258040500912</v>
       </c>
+      <c r="AA3" s="1" t="n">
+        <v>2070.48</v>
+      </c>
+      <c r="AB3" s="3" t="n">
+        <v>-0.002336977733661591</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -831,6 +855,12 @@
       <c r="Z4" s="2" t="n">
         <v>0.005614115490375744</v>
       </c>
+      <c r="AA4" s="1" t="n">
+        <v>87.29000000000001</v>
+      </c>
+      <c r="AB4" s="3" t="n">
+        <v>-0.005468839011051496</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -913,6 +943,12 @@
       <c r="Z5" s="3" t="n">
         <v>-0.007487462032916592</v>
       </c>
+      <c r="AA5" s="1" t="n">
+        <v>0.013837</v>
+      </c>
+      <c r="AB5" s="3" t="n">
+        <v>-0.01523023272364949</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -995,6 +1031,12 @@
       <c r="Z6" s="2" t="n">
         <v>0.004044274159216597</v>
       </c>
+      <c r="AA6" s="1" t="n">
+        <v>0.09429999999999999</v>
+      </c>
+      <c r="AB6" s="3" t="n">
+        <v>-0.0004239983040067667</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1077,6 +1119,12 @@
       <c r="Z7" s="2" t="n">
         <v>0.00321635337002355</v>
       </c>
+      <c r="AA7" s="1" t="n">
+        <v>1.3965</v>
+      </c>
+      <c r="AB7" s="3" t="n">
+        <v>-0.005058421202621747</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1159,6 +1207,12 @@
       <c r="Z8" s="2" t="n">
         <v>0.00683528890856763</v>
       </c>
+      <c r="AA8" s="1" t="n">
+        <v>36.102</v>
+      </c>
+      <c r="AB8" s="3" t="n">
+        <v>-0.007723387296264901</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1241,6 +1295,12 @@
       <c r="Z9" s="2" t="n">
         <v>0.002364501765699489</v>
       </c>
+      <c r="AA9" s="1" t="n">
+        <v>651.84</v>
+      </c>
+      <c r="AB9" s="3" t="n">
+        <v>-0.001531768886710373</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1323,6 +1383,12 @@
       <c r="Z10" s="3" t="n">
         <v>-0.006720243868643449</v>
       </c>
+      <c r="AA10" s="1" t="n">
+        <v>14.15</v>
+      </c>
+      <c r="AB10" s="3" t="n">
+        <v>-0.0130431750017437</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1405,6 +1471,12 @@
       <c r="Z11" s="2" t="n">
         <v>0.006660053847243855</v>
       </c>
+      <c r="AA11" s="1" t="n">
+        <v>212.52</v>
+      </c>
+      <c r="AB11" s="3" t="n">
+        <v>-0.002815315315315289</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1487,6 +1559,12 @@
       <c r="Z12" s="2" t="n">
         <v>0.004687036487689195</v>
       </c>
+      <c r="AA12" s="1" t="n">
+        <v>0.0033736</v>
+      </c>
+      <c r="AB12" s="3" t="n">
+        <v>-0.003897484351009833</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1569,6 +1647,12 @@
       <c r="Z13" s="2" t="n">
         <v>0.0262950302392848</v>
       </c>
+      <c r="AA13" s="1" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AB13" s="2" t="n">
+        <v>0.02485267742761974</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1651,6 +1735,12 @@
       <c r="Z14" s="2" t="n">
         <v>0.008058326937835729</v>
       </c>
+      <c r="AA14" s="1" t="n">
+        <v>2.641</v>
+      </c>
+      <c r="AB14" s="2" t="n">
+        <v>0.005329272934906828</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1733,6 +1823,12 @@
       <c r="Z15" s="2" t="n">
         <v>0.007929246721561482</v>
       </c>
+      <c r="AA15" s="1" t="n">
+        <v>0.9881</v>
+      </c>
+      <c r="AB15" s="3" t="n">
+        <v>-0.003429147755925436</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1815,6 +1911,12 @@
       <c r="Z16" s="2" t="n">
         <v>0.001934576151952145</v>
       </c>
+      <c r="AA16" s="1" t="n">
+        <v>0.05684</v>
+      </c>
+      <c r="AB16" s="3" t="n">
+        <v>-0.002281902755836373</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1897,6 +1999,12 @@
       <c r="Z17" s="2" t="n">
         <v>0.004519774011299439</v>
       </c>
+      <c r="AA17" s="1" t="n">
+        <v>0.889</v>
+      </c>
+      <c r="AB17" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1979,6 +2087,12 @@
       <c r="Z18" s="2" t="n">
         <v>0.003013182674199501</v>
       </c>
+      <c r="AA18" s="1" t="n">
+        <v>0.2659</v>
+      </c>
+      <c r="AB18" s="3" t="n">
+        <v>-0.001502065339842118</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2061,6 +2175,12 @@
       <c r="Z19" s="2" t="n">
         <v>0.009865647310135514</v>
       </c>
+      <c r="AA19" s="1" t="n">
+        <v>0.36352</v>
+      </c>
+      <c r="AB19" s="2" t="n">
+        <v>0.01177321940493755</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2143,6 +2263,12 @@
       <c r="Z20" s="2" t="n">
         <v>0.003506239043003063</v>
       </c>
+      <c r="AA20" s="1" t="n">
+        <v>9.706</v>
+      </c>
+      <c r="AB20" s="3" t="n">
+        <v>-0.002569109032987397</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2225,6 +2351,12 @@
       <c r="Z21" s="2" t="n">
         <v>0.01005783253708826</v>
       </c>
+      <c r="AA21" s="1" t="n">
+        <v>200.53</v>
+      </c>
+      <c r="AB21" s="3" t="n">
+        <v>-0.001593228777694763</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2307,6 +2439,12 @@
       <c r="Z22" s="2" t="n">
         <v>0.01218459176820497</v>
       </c>
+      <c r="AA22" s="1" t="n">
+        <v>0.020575</v>
+      </c>
+      <c r="AB22" s="3" t="n">
+        <v>-0.02488151658767778</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2389,6 +2527,12 @@
       <c r="Z23" s="2" t="n">
         <v>0.001029753297401451</v>
       </c>
+      <c r="AA23" s="1" t="n">
+        <v>456.27</v>
+      </c>
+      <c r="AB23" s="3" t="n">
+        <v>-0.00135700059095188</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2471,6 +2615,12 @@
       <c r="Z24" s="3" t="n">
         <v>-0.0008212481038830543</v>
       </c>
+      <c r="AA24" s="1" t="n">
+        <v>5171.33</v>
+      </c>
+      <c r="AB24" s="2" t="n">
+        <v>0.0001024986462442456</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2553,6 +2703,12 @@
       <c r="Z25" s="2" t="n">
         <v>0.002868174296745703</v>
       </c>
+      <c r="AA25" s="1" t="n">
+        <v>9.067</v>
+      </c>
+      <c r="AB25" s="3" t="n">
+        <v>-0.002639973600263902</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2635,6 +2791,12 @@
       <c r="Z26" s="2" t="n">
         <v>0.01355147909436459</v>
       </c>
+      <c r="AA26" s="1" t="n">
+        <v>0.11953</v>
+      </c>
+      <c r="AB26" s="3" t="n">
+        <v>-0.02551769117886848</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2717,6 +2879,12 @@
       <c r="Z27" s="3" t="n">
         <v>-0.01496259351620959</v>
       </c>
+      <c r="AA27" s="1" t="n">
+        <v>0.0118</v>
+      </c>
+      <c r="AB27" s="3" t="n">
+        <v>-0.004219409282700396</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2799,6 +2967,12 @@
       <c r="Z28" s="2" t="n">
         <v>0.001547987616099073</v>
       </c>
+      <c r="AA28" s="1" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AB28" s="3" t="n">
+        <v>-0.003091190108191656</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2881,6 +3055,12 @@
       <c r="Z29" s="3" t="n">
         <v>-0.0503024514485833</v>
       </c>
+      <c r="AA29" s="1" t="n">
+        <v>0.0592</v>
+      </c>
+      <c r="AB29" s="3" t="n">
+        <v>-0.00771035869929593</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2963,6 +3143,12 @@
       <c r="Z30" s="2" t="n">
         <v>0.001956947162426689</v>
       </c>
+      <c r="AA30" s="1" t="n">
+        <v>1.535</v>
+      </c>
+      <c r="AB30" s="3" t="n">
+        <v>-0.0006510416666667395</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3045,6 +3231,12 @@
       <c r="Z31" s="2" t="n">
         <v>0.008461921353907461</v>
       </c>
+      <c r="AA31" s="1" t="n">
+        <v>0.002012</v>
+      </c>
+      <c r="AB31" s="3" t="n">
+        <v>-0.006910167818361364</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3127,6 +3319,12 @@
       <c r="Z32" s="2" t="n">
         <v>0.005476723923325988</v>
       </c>
+      <c r="AA32" s="1" t="n">
+        <v>0.04034</v>
+      </c>
+      <c r="AB32" s="3" t="n">
+        <v>-0.001237930180737842</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3209,6 +3407,12 @@
       <c r="Z33" s="2" t="n">
         <v>0.009174311926605484</v>
       </c>
+      <c r="AA33" s="1" t="n">
+        <v>0.0987</v>
+      </c>
+      <c r="AB33" s="3" t="n">
+        <v>-0.003030303030303117</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3291,6 +3495,12 @@
       <c r="Z34" s="2" t="n">
         <v>0.003798670465337109</v>
       </c>
+      <c r="AA34" s="1" t="n">
+        <v>0.1054</v>
+      </c>
+      <c r="AB34" s="3" t="n">
+        <v>-0.00283822138126782</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3373,6 +3583,12 @@
       <c r="Z35" s="2" t="n">
         <v>0.004484304932735243</v>
       </c>
+      <c r="AA35" s="1" t="n">
+        <v>0.009090000000000001</v>
+      </c>
+      <c r="AB35" s="2" t="n">
+        <v>0.01450892857142876</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3455,6 +3671,12 @@
       <c r="Z36" s="2" t="n">
         <v>0.005870841487279817</v>
       </c>
+      <c r="AA36" s="1" t="n">
+        <v>0.3581</v>
+      </c>
+      <c r="AB36" s="3" t="n">
+        <v>-0.004724847137298596</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3537,6 +3759,12 @@
       <c r="Z37" s="2" t="n">
         <v>0.002749613335624596</v>
       </c>
+      <c r="AA37" s="1" t="n">
+        <v>0.005818</v>
+      </c>
+      <c r="AB37" s="3" t="n">
+        <v>-0.002913453299057353</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3619,6 +3847,12 @@
       <c r="Z38" s="2" t="n">
         <v>0.0006872327428222873</v>
       </c>
+      <c r="AA38" s="1" t="n">
+        <v>0.25972</v>
+      </c>
+      <c r="AB38" s="3" t="n">
+        <v>-0.009080503624570749</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3701,6 +3935,12 @@
       <c r="Z39" s="2" t="n">
         <v>0.003349753694581212</v>
       </c>
+      <c r="AA39" s="1" t="n">
+        <v>0.05077</v>
+      </c>
+      <c r="AB39" s="3" t="n">
+        <v>-0.002945797329143703</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -3783,6 +4023,12 @@
       <c r="Z40" s="2" t="n">
         <v>0.003860489882854081</v>
       </c>
+      <c r="AA40" s="1" t="n">
+        <v>0.14929</v>
+      </c>
+      <c r="AB40" s="3" t="n">
+        <v>-0.01014454316403662</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -3865,6 +4111,12 @@
       <c r="Z41" s="2" t="n">
         <v>0.005287896592244489</v>
       </c>
+      <c r="AA41" s="1" t="n">
+        <v>0.1694</v>
+      </c>
+      <c r="AB41" s="3" t="n">
+        <v>-0.009935710111046213</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -3947,6 +4199,12 @@
       <c r="Z42" s="2" t="n">
         <v>0.00383997142346841</v>
       </c>
+      <c r="AA42" s="1" t="n">
+        <v>111.97</v>
+      </c>
+      <c r="AB42" s="3" t="n">
+        <v>-0.003914242505115183</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -4029,6 +4287,12 @@
       <c r="Z43" s="3" t="n">
         <v>-0.05910267471958593</v>
       </c>
+      <c r="AA43" s="1" t="n">
+        <v>0.8922</v>
+      </c>
+      <c r="AB43" s="2" t="n">
+        <v>0.02269601100412659</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -4111,6 +4375,12 @@
       <c r="Z44" s="2" t="n">
         <v>0.001818181818181844</v>
       </c>
+      <c r="AA44" s="1" t="n">
+        <v>54.96</v>
+      </c>
+      <c r="AB44" s="3" t="n">
+        <v>-0.002540834845735038</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -4193,6 +4463,12 @@
       <c r="Z45" s="2" t="n">
         <v>0.003926499032881965</v>
       </c>
+      <c r="AA45" s="1" t="n">
+        <v>0.51925</v>
+      </c>
+      <c r="AB45" s="2" t="n">
+        <v>0.0004238675991753809</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -4275,6 +4551,12 @@
       <c r="Z46" s="2" t="n">
         <v>0.0001424704373842271</v>
       </c>
+      <c r="AA46" s="1" t="n">
+        <v>0.6977</v>
+      </c>
+      <c r="AB46" s="3" t="n">
+        <v>-0.006125356125356083</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -4357,6 +4639,12 @@
       <c r="Z47" s="2" t="n">
         <v>0.002551020408163324</v>
       </c>
+      <c r="AA47" s="1" t="n">
+        <v>3.921</v>
+      </c>
+      <c r="AB47" s="3" t="n">
+        <v>-0.002290076335877949</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -4439,6 +4727,12 @@
       <c r="Z48" s="2" t="n">
         <v>0.005692480920805668</v>
       </c>
+      <c r="AA48" s="1" t="n">
+        <v>0.16023</v>
+      </c>
+      <c r="AB48" s="3" t="n">
+        <v>-0.003358835603657305</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -4521,6 +4815,12 @@
       <c r="Z49" s="2" t="n">
         <v>0.02011354420113541</v>
       </c>
+      <c r="AA49" s="1" t="n">
+        <v>0.06174</v>
+      </c>
+      <c r="AB49" s="3" t="n">
+        <v>-0.01828589600890441</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -4603,6 +4903,12 @@
       <c r="Z50" s="2" t="n">
         <v>0.005181347150259035</v>
       </c>
+      <c r="AA50" s="1" t="n">
+        <v>0.0389</v>
+      </c>
+      <c r="AB50" s="2" t="n">
+        <v>0.002577319587628761</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -4685,6 +4991,12 @@
       <c r="Z51" s="3" t="n">
         <v>-0.003273965426925095</v>
       </c>
+      <c r="AA51" s="1" t="n">
+        <v>0.29015</v>
+      </c>
+      <c r="AB51" s="3" t="n">
+        <v>-0.04693864144002093</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -4767,6 +5079,12 @@
       <c r="Z52" s="3" t="n">
         <v>-0.003763256927813855</v>
       </c>
+      <c r="AA52" s="1" t="n">
+        <v>0.2922</v>
+      </c>
+      <c r="AB52" s="2" t="n">
+        <v>0.003434065934065937</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -4849,6 +5167,12 @@
       <c r="Z53" s="2" t="n">
         <v>0.006297229219143582</v>
       </c>
+      <c r="AA53" s="1" t="n">
+        <v>0.1591</v>
+      </c>
+      <c r="AB53" s="3" t="n">
+        <v>-0.004380475594493155</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -4931,6 +5255,12 @@
       <c r="Z54" s="2" t="n">
         <v>0.001345245076058092</v>
       </c>
+      <c r="AA54" s="1" t="n">
+        <v>0.28985</v>
+      </c>
+      <c r="AB54" s="3" t="n">
+        <v>-0.001550120564932849</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -5013,6 +5343,12 @@
       <c r="Z55" s="2" t="n">
         <v>0.005046257359125377</v>
       </c>
+      <c r="AA55" s="1" t="n">
+        <v>0.007142</v>
+      </c>
+      <c r="AB55" s="3" t="n">
+        <v>-0.003905160390516073</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -5095,6 +5431,12 @@
       <c r="Z56" s="3" t="n">
         <v>-0.001404987706357512</v>
       </c>
+      <c r="AA56" s="1" t="n">
+        <v>0.02834</v>
+      </c>
+      <c r="AB56" s="3" t="n">
+        <v>-0.003165670066830805</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -5177,6 +5519,12 @@
       <c r="Z57" s="2" t="n">
         <v>0.01005025125628133</v>
       </c>
+      <c r="AA57" s="1" t="n">
+        <v>0.04185</v>
+      </c>
+      <c r="AB57" s="3" t="n">
+        <v>-0.008528784648187616</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -5259,6 +5607,12 @@
       <c r="Z58" s="3" t="n">
         <v>-0.02133173843700163</v>
       </c>
+      <c r="AA58" s="1" t="n">
+        <v>0.0486</v>
+      </c>
+      <c r="AB58" s="3" t="n">
+        <v>-0.009981666327154293</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -5341,6 +5695,12 @@
       <c r="Z59" s="2" t="n">
         <v>0.0006451612903225095</v>
       </c>
+      <c r="AA59" s="1" t="n">
+        <v>1.542</v>
+      </c>
+      <c r="AB59" s="3" t="n">
+        <v>-0.005802707930367438</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -5423,6 +5783,12 @@
       <c r="Z60" s="2" t="n">
         <v>0.002906976744186054</v>
       </c>
+      <c r="AA60" s="1" t="n">
+        <v>0.00342</v>
+      </c>
+      <c r="AB60" s="3" t="n">
+        <v>-0.008695652173913066</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -5505,6 +5871,12 @@
       <c r="Z61" s="2" t="n">
         <v>0.007751937984496167</v>
       </c>
+      <c r="AA61" s="1" t="n">
+        <v>0.1554</v>
+      </c>
+      <c r="AB61" s="3" t="n">
+        <v>-0.003846153846153778</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -5587,6 +5959,12 @@
       <c r="Z62" s="2" t="n">
         <v>0.001746724890829696</v>
       </c>
+      <c r="AA62" s="1" t="n">
+        <v>1.144</v>
+      </c>
+      <c r="AB62" s="3" t="n">
+        <v>-0.002615518744551102</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -5669,6 +6047,12 @@
       <c r="Z63" s="2" t="n">
         <v>0.005433228481555656</v>
       </c>
+      <c r="AA63" s="1" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AB63" s="3" t="n">
+        <v>-0.004550625711035397</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -5751,6 +6135,12 @@
       <c r="Z64" s="2" t="n">
         <v>0.002726653033401502</v>
       </c>
+      <c r="AA64" s="1" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AB64" s="3" t="n">
+        <v>-0.0006798096532971529</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -5833,6 +6223,12 @@
       <c r="Z65" s="2" t="n">
         <v>0.0004208754208754037</v>
       </c>
+      <c r="AA65" s="1" t="n">
+        <v>0.02367</v>
+      </c>
+      <c r="AB65" s="3" t="n">
+        <v>-0.004206983592763963</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -5915,6 +6311,12 @@
       <c r="Z66" s="2" t="n">
         <v>0.003940886699507365</v>
       </c>
+      <c r="AA66" s="1" t="n">
+        <v>0.1013</v>
+      </c>
+      <c r="AB66" s="3" t="n">
+        <v>-0.00588812561334645</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -5997,6 +6399,12 @@
       <c r="Z67" s="3" t="n">
         <v>-0.008198924731182835</v>
       </c>
+      <c r="AA67" s="1" t="n">
+        <v>0.007376</v>
+      </c>
+      <c r="AB67" s="3" t="n">
+        <v>-0.0004065591543570129</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -6079,6 +6487,12 @@
       <c r="Z68" s="3" t="n">
         <v>-0.03920543648719289</v>
       </c>
+      <c r="AA68" s="1" t="n">
+        <v>18.35</v>
+      </c>
+      <c r="AB68" s="3" t="n">
+        <v>-0.00163220892274198</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -6161,6 +6575,12 @@
       <c r="Z69" s="2" t="n">
         <v>0.005177514792899325</v>
       </c>
+      <c r="AA69" s="1" t="n">
+        <v>0.05419</v>
+      </c>
+      <c r="AB69" s="3" t="n">
+        <v>-0.003127299484915315</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -6243,6 +6663,12 @@
       <c r="Z70" s="2" t="n">
         <v>0.008547008547008435</v>
       </c>
+      <c r="AA70" s="1" t="n">
+        <v>0.235</v>
+      </c>
+      <c r="AB70" s="3" t="n">
+        <v>-0.004237288135593225</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -6325,6 +6751,12 @@
       <c r="Z71" s="2" t="n">
         <v>0.003145203564564004</v>
       </c>
+      <c r="AA71" s="1" t="n">
+        <v>5.712</v>
+      </c>
+      <c r="AB71" s="3" t="n">
+        <v>-0.005051384776171384</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -6407,6 +6839,12 @@
       <c r="Z72" s="3" t="n">
         <v>-0.02143622722400863</v>
       </c>
+      <c r="AA72" s="1" t="n">
+        <v>0.001779</v>
+      </c>
+      <c r="AB72" s="3" t="n">
+        <v>-0.02573932092004378</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -6489,6 +6927,12 @@
       <c r="Z73" s="2" t="n">
         <v>0.004678860059549085</v>
       </c>
+      <c r="AA73" s="1" t="n">
+        <v>0.9419</v>
+      </c>
+      <c r="AB73" s="3" t="n">
+        <v>-0.003069432684165976</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -6571,6 +7015,12 @@
       <c r="Z74" s="2" t="n">
         <v>0.004159733777038273</v>
       </c>
+      <c r="AA74" s="1" t="n">
+        <v>0.1204</v>
+      </c>
+      <c r="AB74" s="3" t="n">
+        <v>-0.002485501242750693</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -6653,6 +7103,12 @@
       <c r="Z75" s="2" t="n">
         <v>0.004140199637023697</v>
       </c>
+      <c r="AA75" s="1" t="n">
+        <v>354.98</v>
+      </c>
+      <c r="AB75" s="2" t="n">
+        <v>0.00248517367975147</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -6735,6 +7191,12 @@
       <c r="Z76" s="2" t="n">
         <v>0.00633981403212173</v>
       </c>
+      <c r="AA76" s="1" t="n">
+        <v>0.11851</v>
+      </c>
+      <c r="AB76" s="3" t="n">
+        <v>-0.004535909281814353</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -6817,6 +7279,12 @@
       <c r="Z77" s="2" t="n">
         <v>0.004619305511309311</v>
       </c>
+      <c r="AA77" s="1" t="n">
+        <v>0.06299</v>
+      </c>
+      <c r="AB77" s="3" t="n">
+        <v>-0.00126843190106226</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -6899,6 +7367,12 @@
       <c r="Z78" s="2" t="n">
         <v>0.004644779900770715</v>
       </c>
+      <c r="AA78" s="1" t="n">
+        <v>0.09493</v>
+      </c>
+      <c r="AB78" s="3" t="n">
+        <v>-0.002521803089208827</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -6981,6 +7455,12 @@
       <c r="Z79" s="2" t="n">
         <v>0.003011292346298567</v>
       </c>
+      <c r="AA79" s="1" t="n">
+        <v>0.4014</v>
+      </c>
+      <c r="AB79" s="2" t="n">
+        <v>0.004253189892419263</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -7063,6 +7543,12 @@
       <c r="Z80" s="2" t="n">
         <v>0.006321743470304416</v>
       </c>
+      <c r="AA80" s="1" t="n">
+        <v>0.00602</v>
+      </c>
+      <c r="AB80" s="3" t="n">
+        <v>-0.00479418085633981</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -7145,6 +7631,12 @@
       <c r="Z81" s="3" t="n">
         <v>-0.006730769230769157</v>
       </c>
+      <c r="AA81" s="1" t="n">
+        <v>0.1038</v>
+      </c>
+      <c r="AB81" s="2" t="n">
+        <v>0.004840271055179094</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -7227,6 +7719,12 @@
       <c r="Z82" s="2" t="n">
         <v>0.001972386587771123</v>
       </c>
+      <c r="AA82" s="1" t="n">
+        <v>0.1014</v>
+      </c>
+      <c r="AB82" s="3" t="n">
+        <v>-0.001968503937007794</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -7309,6 +7807,12 @@
       <c r="Z83" s="2" t="n">
         <v>0.01377857027070832</v>
       </c>
+      <c r="AA83" s="1" t="n">
+        <v>0.06231</v>
+      </c>
+      <c r="AB83" s="3" t="n">
+        <v>-0.003677646306363944</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -7391,6 +7895,12 @@
       <c r="Z84" s="2" t="n">
         <v>0.003036256474370486</v>
       </c>
+      <c r="AA84" s="1" t="n">
+        <v>1.1182</v>
+      </c>
+      <c r="AB84" s="3" t="n">
+        <v>-0.004451566951566857</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -7473,6 +7983,12 @@
       <c r="Z85" s="2" t="n">
         <v>0.006891271056661547</v>
       </c>
+      <c r="AA85" s="1" t="n">
+        <v>0.01308</v>
+      </c>
+      <c r="AB85" s="3" t="n">
+        <v>-0.005323193916349857</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -7555,6 +8071,12 @@
       <c r="Z86" s="2" t="n">
         <v>0.0005959475566149936</v>
       </c>
+      <c r="AA86" s="1" t="n">
+        <v>0.01669</v>
+      </c>
+      <c r="AB86" s="3" t="n">
+        <v>-0.005955926146515748</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -7637,6 +8159,12 @@
       <c r="Z87" s="2" t="n">
         <v>0.003484739245373912</v>
       </c>
+      <c r="AA87" s="1" t="n">
+        <v>8.315</v>
+      </c>
+      <c r="AB87" s="3" t="n">
+        <v>-0.004310860974733727</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -7719,6 +8247,12 @@
       <c r="Z88" s="2" t="n">
         <v>0.005079723437279384</v>
       </c>
+      <c r="AA88" s="1" t="n">
+        <v>2.1363</v>
+      </c>
+      <c r="AB88" s="3" t="n">
+        <v>-0.0002807805699845262</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -7801,6 +8335,12 @@
       <c r="Z89" s="3" t="n">
         <v>-0.0008564087924635925</v>
       </c>
+      <c r="AA89" s="1" t="n">
+        <v>0.006954</v>
+      </c>
+      <c r="AB89" s="3" t="n">
+        <v>-0.006571428571428576</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -7883,6 +8423,12 @@
       <c r="Z90" s="2" t="n">
         <v>0.001963350785340389</v>
       </c>
+      <c r="AA90" s="1" t="n">
+        <v>15.28</v>
+      </c>
+      <c r="AB90" s="3" t="n">
+        <v>-0.001959503592423327</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -7965,6 +8511,12 @@
       <c r="Z91" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AA91" s="1" t="n">
+        <v>0.000223</v>
+      </c>
+      <c r="AB91" s="3" t="n">
+        <v>-0.004464285714285702</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -8047,6 +8599,12 @@
       <c r="Z92" s="2" t="n">
         <v>0.004814172925091474</v>
       </c>
+      <c r="AA92" s="1" t="n">
+        <v>0.05239</v>
+      </c>
+      <c r="AB92" s="2" t="n">
+        <v>0.004024530471445034</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -8129,6 +8687,12 @@
       <c r="Z93" s="3" t="n">
         <v>-0.0009040910118284245</v>
       </c>
+      <c r="AA93" s="1" t="n">
+        <v>1.3274</v>
+      </c>
+      <c r="AB93" s="2" t="n">
+        <v>0.0009803182263779932</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -8211,6 +8775,12 @@
       <c r="Z94" s="2" t="n">
         <v>0.0009963651124600713</v>
       </c>
+      <c r="AA94" s="1" t="n">
+        <v>0.054134</v>
+      </c>
+      <c r="AB94" s="3" t="n">
+        <v>-0.002156642273875118</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -8293,6 +8863,12 @@
       <c r="Z95" s="2" t="n">
         <v>0.002078137988362429</v>
       </c>
+      <c r="AA95" s="1" t="n">
+        <v>0.2399</v>
+      </c>
+      <c r="AB95" s="3" t="n">
+        <v>-0.004977187888842831</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -8375,6 +8951,12 @@
       <c r="Z96" s="2" t="n">
         <v>0.003457943925233679</v>
       </c>
+      <c r="AA96" s="1" t="n">
+        <v>1.0792</v>
+      </c>
+      <c r="AB96" s="2" t="n">
+        <v>0.005122473689112264</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -8457,6 +9039,12 @@
       <c r="Z97" s="2" t="n">
         <v>0.004674717569146998</v>
       </c>
+      <c r="AA97" s="1" t="n">
+        <v>0.2574</v>
+      </c>
+      <c r="AB97" s="3" t="n">
+        <v>-0.001938735944164406</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -8539,6 +9127,12 @@
       <c r="Z98" s="2" t="n">
         <v>0.005354058721934355</v>
       </c>
+      <c r="AA98" s="1" t="n">
+        <v>0.5787</v>
+      </c>
+      <c r="AB98" s="3" t="n">
+        <v>-0.005840920803985499</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -8621,6 +9215,12 @@
       <c r="Z99" s="2" t="n">
         <v>0.005378720895962133</v>
       </c>
+      <c r="AA99" s="1" t="n">
+        <v>0.13585</v>
+      </c>
+      <c r="AB99" s="3" t="n">
+        <v>-0.00439721509710509</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -8703,6 +9303,12 @@
       <c r="Z100" s="2" t="n">
         <v>0.007133592736705624</v>
       </c>
+      <c r="AA100" s="1" t="n">
+        <v>0.03107</v>
+      </c>
+      <c r="AB100" s="2" t="n">
+        <v>0.0003219575016097744</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -8785,6 +9391,12 @@
       <c r="Z101" s="2" t="n">
         <v>0.007684918347742563</v>
       </c>
+      <c r="AA101" s="1" t="n">
+        <v>1.049</v>
+      </c>
+      <c r="AB101" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -8867,6 +9479,12 @@
       <c r="Z102" s="3" t="n">
         <v>-0.0004526935264825529</v>
       </c>
+      <c r="AA102" s="1" t="n">
+        <v>0.02216</v>
+      </c>
+      <c r="AB102" s="2" t="n">
+        <v>0.003623188405797111</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -8949,6 +9567,12 @@
       <c r="Z103" s="2" t="n">
         <v>0.005120327700973009</v>
       </c>
+      <c r="AA103" s="1" t="n">
+        <v>0.01963</v>
+      </c>
+      <c r="AB103" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -9031,6 +9655,12 @@
       <c r="Z104" s="2" t="n">
         <v>0.006675567423230981</v>
       </c>
+      <c r="AA104" s="1" t="n">
+        <v>3.001</v>
+      </c>
+      <c r="AB104" s="3" t="n">
+        <v>-0.004973474801061049</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -9113,6 +9743,12 @@
       <c r="Z105" s="2" t="n">
         <v>0.004311672312904237</v>
       </c>
+      <c r="AA105" s="1" t="n">
+        <v>32.55</v>
+      </c>
+      <c r="AB105" s="3" t="n">
+        <v>-0.001839926402943952</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -9195,6 +9831,12 @@
       <c r="Z106" s="2" t="n">
         <v>0.003010234798314271</v>
       </c>
+      <c r="AA106" s="1" t="n">
+        <v>0.1654</v>
+      </c>
+      <c r="AB106" s="3" t="n">
+        <v>-0.007202881152461024</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -9277,6 +9919,12 @@
       <c r="Z107" s="2" t="n">
         <v>0.001507321274763208</v>
       </c>
+      <c r="AA107" s="1" t="n">
+        <v>0.4597</v>
+      </c>
+      <c r="AB107" s="3" t="n">
+        <v>-0.01161040636422278</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -9359,6 +10007,12 @@
       <c r="Z108" s="2" t="n">
         <v>0.00654956832390603</v>
       </c>
+      <c r="AA108" s="1" t="n">
+        <v>0.3362</v>
+      </c>
+      <c r="AB108" s="3" t="n">
+        <v>-0.005619639160011868</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -9441,6 +10095,12 @@
       <c r="Z109" s="2" t="n">
         <v>0.005298013245033142</v>
       </c>
+      <c r="AA109" s="1" t="n">
+        <v>0.2266</v>
+      </c>
+      <c r="AB109" s="3" t="n">
+        <v>-0.004830917874396212</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -9523,6 +10183,12 @@
       <c r="Z110" s="2" t="n">
         <v>0.0006648936170212495</v>
       </c>
+      <c r="AA110" s="1" t="n">
+        <v>0.01507</v>
+      </c>
+      <c r="AB110" s="2" t="n">
+        <v>0.001328903654485111</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -9605,6 +10271,12 @@
       <c r="Z111" s="2" t="n">
         <v>0.003810560696788306</v>
       </c>
+      <c r="AA111" s="1" t="n">
+        <v>1.838</v>
+      </c>
+      <c r="AB111" s="3" t="n">
+        <v>-0.003253796095444688</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -9687,6 +10359,12 @@
       <c r="Z112" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AA112" s="1" t="n">
+        <v>0.03815</v>
+      </c>
+      <c r="AB112" s="3" t="n">
+        <v>-0.003396029258098176</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -9769,6 +10447,12 @@
       <c r="Z113" s="2" t="n">
         <v>0.001862197392923651</v>
       </c>
+      <c r="AA113" s="1" t="n">
+        <v>4.297</v>
+      </c>
+      <c r="AB113" s="3" t="n">
+        <v>-0.00162639405204474</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -9851,6 +10535,12 @@
       <c r="Z114" s="3" t="n">
         <v>-0.003583278035832796</v>
       </c>
+      <c r="AA114" s="1" t="n">
+        <v>0.0076</v>
+      </c>
+      <c r="AB114" s="2" t="n">
+        <v>0.01225359616409165</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -9933,6 +10623,12 @@
       <c r="Z115" s="2" t="n">
         <v>0.004318136171922071</v>
       </c>
+      <c r="AA115" s="1" t="n">
+        <v>0.10031</v>
+      </c>
+      <c r="AB115" s="2" t="n">
+        <v>0.002999700029996947</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -10015,6 +10711,12 @@
       <c r="Z116" s="2" t="n">
         <v>0.004097372860930429</v>
       </c>
+      <c r="AA116" s="1" t="n">
+        <v>0.08302</v>
+      </c>
+      <c r="AB116" s="3" t="n">
+        <v>-0.003600576092174851</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -10097,6 +10799,12 @@
       <c r="Z117" s="2" t="n">
         <v>0.005018400802944133</v>
       </c>
+      <c r="AA117" s="1" t="n">
+        <v>0.2993</v>
+      </c>
+      <c r="AB117" s="3" t="n">
+        <v>-0.003661784287616477</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -10179,6 +10887,12 @@
       <c r="Z118" s="2" t="n">
         <v>0.00176991150442486</v>
       </c>
+      <c r="AA118" s="1" t="n">
+        <v>0.02252</v>
+      </c>
+      <c r="AB118" s="3" t="n">
+        <v>-0.00530035335689055</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -10261,6 +10975,12 @@
       <c r="Z119" s="2" t="n">
         <v>0.005208333333333483</v>
       </c>
+      <c r="AA119" s="1" t="n">
+        <v>0.1537</v>
+      </c>
+      <c r="AB119" s="3" t="n">
+        <v>-0.004533678756476723</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -10343,6 +11063,12 @@
       <c r="Z120" s="3" t="n">
         <v>-0.02231551038444532</v>
       </c>
+      <c r="AA120" s="1" t="n">
+        <v>0.004405</v>
+      </c>
+      <c r="AB120" s="3" t="n">
+        <v>-0.004519774011299446</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -10425,6 +11151,12 @@
       <c r="Z121" s="2" t="n">
         <v>0.004134129536058724</v>
       </c>
+      <c r="AA121" s="1" t="n">
+        <v>0.4393</v>
+      </c>
+      <c r="AB121" s="2" t="n">
+        <v>0.004803293687099832</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -10507,6 +11239,12 @@
       <c r="Z122" s="2" t="n">
         <v>0.002577319587628868</v>
       </c>
+      <c r="AA122" s="1" t="n">
+        <v>0.776</v>
+      </c>
+      <c r="AB122" s="3" t="n">
+        <v>-0.002570694087403601</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -10589,6 +11327,12 @@
       <c r="Z123" s="2" t="n">
         <v>0.002309468822170967</v>
       </c>
+      <c r="AA123" s="1" t="n">
+        <v>0.0864</v>
+      </c>
+      <c r="AB123" s="3" t="n">
+        <v>-0.004608294930875548</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -10671,6 +11415,12 @@
       <c r="Z124" s="2" t="n">
         <v>0.001629991850040825</v>
       </c>
+      <c r="AA124" s="1" t="n">
+        <v>0.01228</v>
+      </c>
+      <c r="AB124" s="3" t="n">
+        <v>-0.0008136696501221584</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -10753,6 +11503,12 @@
       <c r="Z125" s="2" t="n">
         <v>0.004205559544568751</v>
       </c>
+      <c r="AA125" s="1" t="n">
+        <v>0.0977</v>
+      </c>
+      <c r="AB125" s="3" t="n">
+        <v>-0.002042900919305472</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -10835,6 +11591,12 @@
       <c r="Z126" s="2" t="n">
         <v>0.00278312995075997</v>
       </c>
+      <c r="AA126" s="1" t="n">
+        <v>0.04695</v>
+      </c>
+      <c r="AB126" s="2" t="n">
+        <v>0.002348420153714752</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -10917,6 +11679,12 @@
       <c r="Z127" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AA127" s="1" t="n">
+        <v>3.23e-05</v>
+      </c>
+      <c r="AB127" s="3" t="n">
+        <v>-0.003086419753086495</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -10999,6 +11767,12 @@
       <c r="Z128" s="2" t="n">
         <v>0.008151692362218566</v>
       </c>
+      <c r="AA128" s="1" t="n">
+        <v>0.5673</v>
+      </c>
+      <c r="AB128" s="3" t="n">
+        <v>-0.002812445069432123</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -11081,6 +11855,12 @@
       <c r="Z129" s="3" t="n">
         <v>-0.00353682915577438</v>
       </c>
+      <c r="AA129" s="1" t="n">
+        <v>0.06475</v>
+      </c>
+      <c r="AB129" s="3" t="n">
+        <v>-0.00077160493827152</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -11163,6 +11943,12 @@
       <c r="Z130" s="3" t="n">
         <v>-0.003422425032594519</v>
       </c>
+      <c r="AA130" s="1" t="n">
+        <v>0.00061</v>
+      </c>
+      <c r="AB130" s="3" t="n">
+        <v>-0.002452984464431696</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -11245,6 +12031,12 @@
       <c r="Z131" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AA131" s="1" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="AB131" s="3" t="n">
+        <v>-0.01136363636363637</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -11327,6 +12119,12 @@
       <c r="Z132" s="2" t="n">
         <v>0.00631229235880403</v>
       </c>
+      <c r="AA132" s="1" t="n">
+        <v>0.3014</v>
+      </c>
+      <c r="AB132" s="3" t="n">
+        <v>-0.004952129415648734</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -11409,6 +12207,12 @@
       <c r="Z133" s="3" t="n">
         <v>-0.005277044854881255</v>
       </c>
+      <c r="AA133" s="1" t="n">
+        <v>0.03376</v>
+      </c>
+      <c r="AB133" s="3" t="n">
+        <v>-0.005010315355143044</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -11491,6 +12295,12 @@
       <c r="Z134" s="2" t="n">
         <v>0.0002089427496864082</v>
       </c>
+      <c r="AA134" s="1" t="n">
+        <v>0.14389</v>
+      </c>
+      <c r="AB134" s="2" t="n">
+        <v>0.001949724949516068</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -11573,6 +12383,12 @@
       <c r="Z135" s="2" t="n">
         <v>0.00539447066756576</v>
       </c>
+      <c r="AA135" s="1" t="n">
+        <v>0.02965</v>
+      </c>
+      <c r="AB135" s="3" t="n">
+        <v>-0.005700871898054997</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -11655,6 +12471,12 @@
       <c r="Z136" s="2" t="n">
         <v>0.004268943436499502</v>
       </c>
+      <c r="AA136" s="1" t="n">
+        <v>28.16</v>
+      </c>
+      <c r="AB136" s="3" t="n">
+        <v>-0.002479631597591225</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -11737,6 +12559,12 @@
       <c r="Z137" s="2" t="n">
         <v>0.01335482385447855</v>
       </c>
+      <c r="AA137" s="1" t="n">
+        <v>0.0004385</v>
+      </c>
+      <c r="AB137" s="3" t="n">
+        <v>-0.003635537377868754</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -11819,6 +12647,12 @@
       <c r="Z138" s="3" t="n">
         <v>-0.001151722502625226</v>
       </c>
+      <c r="AA138" s="1" t="n">
+        <v>0.029102</v>
+      </c>
+      <c r="AB138" s="3" t="n">
+        <v>-0.01305660121409434</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -11901,6 +12735,12 @@
       <c r="Z139" s="2" t="n">
         <v>0.005723800603600883</v>
       </c>
+      <c r="AA139" s="1" t="n">
+        <v>0.09626999999999999</v>
+      </c>
+      <c r="AB139" s="3" t="n">
+        <v>-0.003828642384106055</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -11983,6 +12823,12 @@
       <c r="Z140" s="2" t="n">
         <v>0.006410256410256323</v>
       </c>
+      <c r="AA140" s="1" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AB140" s="3" t="n">
+        <v>-0.003046247576848491</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -12065,6 +12911,12 @@
       <c r="Z141" s="3" t="n">
         <v>-0.001515725653656758</v>
       </c>
+      <c r="AA141" s="1" t="n">
+        <v>0.02634</v>
+      </c>
+      <c r="AB141" s="3" t="n">
+        <v>-0.0003795066413662085</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -12147,6 +12999,12 @@
       <c r="Z142" s="2" t="n">
         <v>0.004936084039994956</v>
       </c>
+      <c r="AA142" s="1" t="n">
+        <v>0.07942</v>
+      </c>
+      <c r="AB142" s="2" t="n">
+        <v>0.0002518891687658202</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -12229,6 +13087,12 @@
       <c r="Z143" s="2" t="n">
         <v>0.002038735983690108</v>
       </c>
+      <c r="AA143" s="1" t="n">
+        <v>0.08785999999999999</v>
+      </c>
+      <c r="AB143" s="3" t="n">
+        <v>-0.006894992652876675</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -12311,6 +13175,12 @@
       <c r="Z144" s="2" t="n">
         <v>0.003891050583657598</v>
       </c>
+      <c r="AA144" s="1" t="n">
+        <v>0.02066</v>
+      </c>
+      <c r="AB144" s="2" t="n">
+        <v>0.0009689922480621442</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -12393,6 +13263,12 @@
       <c r="Z145" s="2" t="n">
         <v>0.0004358817888588134</v>
       </c>
+      <c r="AA145" s="1" t="n">
+        <v>0.11491</v>
+      </c>
+      <c r="AB145" s="2" t="n">
+        <v>0.00130707563611012</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -12475,6 +13351,12 @@
       <c r="Z146" s="2" t="n">
         <v>0.00696748506967482</v>
       </c>
+      <c r="AA146" s="1" t="n">
+        <v>0.3027</v>
+      </c>
+      <c r="AB146" s="3" t="n">
+        <v>-0.002635914332784077</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -12557,6 +13439,12 @@
       <c r="Z147" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AA147" s="1" t="n">
+        <v>0.124</v>
+      </c>
+      <c r="AB147" s="2" t="n">
+        <v>0.008130081300813016</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -12639,6 +13527,12 @@
       <c r="Z148" s="2" t="n">
         <v>0.003626704806660932</v>
       </c>
+      <c r="AA148" s="1" t="n">
+        <v>1.9629</v>
+      </c>
+      <c r="AB148" s="3" t="n">
+        <v>-0.0009670195439739479</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -12721,6 +13615,12 @@
       <c r="Z149" s="3" t="n">
         <v>-0.0006480881399870119</v>
       </c>
+      <c r="AA149" s="1" t="n">
+        <v>0.06166</v>
+      </c>
+      <c r="AB149" s="3" t="n">
+        <v>-0.0003242542153047858</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -12803,6 +13703,12 @@
       <c r="Z150" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AA150" s="1" t="n">
+        <v>0.1621</v>
+      </c>
+      <c r="AB150" s="2" t="n">
+        <v>0.00123533045089565</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -12885,6 +13791,12 @@
       <c r="Z151" s="2" t="n">
         <v>0.006278026905829587</v>
       </c>
+      <c r="AA151" s="1" t="n">
+        <v>6.711999999999999e-05</v>
+      </c>
+      <c r="AB151" s="3" t="n">
+        <v>-0.002970885323826573</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -12967,6 +13879,12 @@
       <c r="Z152" s="2" t="n">
         <v>0.01019021739130429</v>
       </c>
+      <c r="AA152" s="1" t="n">
+        <v>0.01477</v>
+      </c>
+      <c r="AB152" s="3" t="n">
+        <v>-0.006724949562878238</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -13049,6 +13967,12 @@
       <c r="Z153" s="2" t="n">
         <v>0.005714285714285647</v>
       </c>
+      <c r="AA153" s="1" t="n">
+        <v>0.02103</v>
+      </c>
+      <c r="AB153" s="3" t="n">
+        <v>-0.004261363636363627</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -13131,6 +14055,12 @@
       <c r="Z154" s="2" t="n">
         <v>0.005398110661268505</v>
       </c>
+      <c r="AA154" s="1" t="n">
+        <v>0.000594</v>
+      </c>
+      <c r="AB154" s="3" t="n">
+        <v>-0.003355704697986477</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -13213,6 +14143,12 @@
       <c r="Z155" s="2" t="n">
         <v>0.003988035892323041</v>
       </c>
+      <c r="AA155" s="1" t="n">
+        <v>0.04015</v>
+      </c>
+      <c r="AB155" s="3" t="n">
+        <v>-0.003227408142999134</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -13295,6 +14231,12 @@
       <c r="Z156" s="2" t="n">
         <v>0.006362672322375507</v>
       </c>
+      <c r="AA156" s="1" t="n">
+        <v>0.01899</v>
+      </c>
+      <c r="AB156" s="2" t="n">
+        <v>0.000526870389884067</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -13377,6 +14319,12 @@
       <c r="Z157" s="2" t="n">
         <v>0.006763728075203408</v>
       </c>
+      <c r="AA157" s="1" t="n">
+        <v>0.08738</v>
+      </c>
+      <c r="AB157" s="3" t="n">
+        <v>-0.005010248235026145</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -13459,6 +14407,12 @@
       <c r="Z158" s="2" t="n">
         <v>0.005347593582887688</v>
       </c>
+      <c r="AA158" s="1" t="n">
+        <v>0.008395</v>
+      </c>
+      <c r="AB158" s="3" t="n">
+        <v>-0.007683215130023738</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -13541,6 +14495,12 @@
       <c r="Z159" s="2" t="n">
         <v>0.005992808629644299</v>
       </c>
+      <c r="AA159" s="1" t="n">
+        <v>2.509</v>
+      </c>
+      <c r="AB159" s="3" t="n">
+        <v>-0.003574265289912588</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -13623,6 +14583,12 @@
       <c r="Z160" s="2" t="n">
         <v>0.004763392159925031</v>
       </c>
+      <c r="AA160" s="1" t="n">
+        <v>1.2838</v>
+      </c>
+      <c r="AB160" s="3" t="n">
+        <v>-0.002253827621046011</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -13705,6 +14671,12 @@
       <c r="Z161" s="2" t="n">
         <v>0.002135896409024098</v>
       </c>
+      <c r="AA161" s="1" t="n">
+        <v>0.00751</v>
+      </c>
+      <c r="AB161" s="2" t="n">
+        <v>0.0003996270147862526</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -13787,6 +14759,12 @@
       <c r="Z162" s="3" t="n">
         <v>-0.02534066459478847</v>
       </c>
+      <c r="AA162" s="1" t="n">
+        <v>0.004073</v>
+      </c>
+      <c r="AB162" s="3" t="n">
+        <v>-0.0009811135638949384</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -13869,6 +14847,12 @@
       <c r="Z163" s="2" t="n">
         <v>0.004162330905306946</v>
       </c>
+      <c r="AA163" s="1" t="n">
+        <v>0.0961</v>
+      </c>
+      <c r="AB163" s="3" t="n">
+        <v>-0.004145077720207229</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -13951,6 +14935,12 @@
       <c r="Z164" s="2" t="n">
         <v>0.004197727437215045</v>
       </c>
+      <c r="AA164" s="1" t="n">
+        <v>1.3829</v>
+      </c>
+      <c r="AB164" s="3" t="n">
+        <v>-0.003315315315315271</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -14033,6 +15023,12 @@
       <c r="Z165" s="2" t="n">
         <v>0.01027033909094764</v>
       </c>
+      <c r="AA165" s="1" t="n">
+        <v>0.023731</v>
+      </c>
+      <c r="AB165" s="3" t="n">
+        <v>-0.00310859063222017</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -14115,6 +15111,12 @@
       <c r="Z166" s="2" t="n">
         <v>0.007449519702019351</v>
       </c>
+      <c r="AA166" s="1" t="n">
+        <v>0.005152</v>
+      </c>
+      <c r="AB166" s="2" t="n">
+        <v>0.002529675034053316</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -14197,6 +15199,12 @@
       <c r="Z167" s="2" t="n">
         <v>0.002578492340361042</v>
       </c>
+      <c r="AA167" s="1" t="n">
+        <v>0.06562</v>
+      </c>
+      <c r="AB167" s="3" t="n">
+        <v>-0.00726172465960678</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -14279,6 +15287,12 @@
       <c r="Z168" s="2" t="n">
         <v>0.007352941176470507</v>
       </c>
+      <c r="AA168" s="1" t="n">
+        <v>0.0958</v>
+      </c>
+      <c r="AB168" s="3" t="n">
+        <v>-0.001042752867570416</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -14361,6 +15375,12 @@
       <c r="Z169" s="2" t="n">
         <v>0.006276150627614988</v>
       </c>
+      <c r="AA169" s="1" t="n">
+        <v>0.03866</v>
+      </c>
+      <c r="AB169" s="2" t="n">
+        <v>0.004677754677754668</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -14443,6 +15463,12 @@
       <c r="Z170" s="2" t="n">
         <v>0.003223094170403651</v>
       </c>
+      <c r="AA170" s="1" t="n">
+        <v>0.007134</v>
+      </c>
+      <c r="AB170" s="3" t="n">
+        <v>-0.003492107836290084</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -14525,6 +15551,12 @@
       <c r="Z171" s="2" t="n">
         <v>0.002937720329024679</v>
       </c>
+      <c r="AA171" s="1" t="n">
+        <v>0.3403</v>
+      </c>
+      <c r="AB171" s="3" t="n">
+        <v>-0.003222026947861716</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -14607,6 +15639,12 @@
       <c r="Z172" s="2" t="n">
         <v>0.006813996316758734</v>
       </c>
+      <c r="AA172" s="1" t="n">
+        <v>5.46</v>
+      </c>
+      <c r="AB172" s="3" t="n">
+        <v>-0.001280409731113897</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -14689,6 +15727,12 @@
       <c r="Z173" s="2" t="n">
         <v>0.006151142355008842</v>
       </c>
+      <c r="AA173" s="1" t="n">
+        <v>0.04566</v>
+      </c>
+      <c r="AB173" s="3" t="n">
+        <v>-0.003056768558951992</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -14771,6 +15815,12 @@
       <c r="Z174" s="2" t="n">
         <v>0.005642472428828031</v>
       </c>
+      <c r="AA174" s="1" t="n">
+        <v>0.03915</v>
+      </c>
+      <c r="AB174" s="3" t="n">
+        <v>-0.00153022188217303</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -14853,6 +15903,12 @@
       <c r="Z175" s="2" t="n">
         <v>0.0139265689998191</v>
       </c>
+      <c r="AA175" s="1" t="n">
+        <v>0.00564</v>
+      </c>
+      <c r="AB175" s="2" t="n">
+        <v>0.006064930431680374</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -14935,6 +15991,12 @@
       <c r="Z176" s="2" t="n">
         <v>0.002645502645502652</v>
       </c>
+      <c r="AA176" s="1" t="n">
+        <v>0.00755</v>
+      </c>
+      <c r="AB176" s="3" t="n">
+        <v>-0.003957783641160903</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -15017,6 +16079,12 @@
       <c r="Z177" s="2" t="n">
         <v>0.003941441441441382</v>
       </c>
+      <c r="AA177" s="1" t="n">
+        <v>1.786</v>
+      </c>
+      <c r="AB177" s="2" t="n">
+        <v>0.001682557487380883</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -15099,6 +16167,12 @@
       <c r="Z178" s="2" t="n">
         <v>0.00331379046647971</v>
       </c>
+      <c r="AA178" s="1" t="n">
+        <v>15.679</v>
+      </c>
+      <c r="AB178" s="3" t="n">
+        <v>-0.004128556910569074</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -15181,6 +16255,12 @@
       <c r="Z179" s="2" t="n">
         <v>0.006410256410256416</v>
       </c>
+      <c r="AA179" s="1" t="n">
+        <v>0.314</v>
+      </c>
+      <c r="AB179" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -15263,6 +16343,12 @@
       <c r="Z180" s="2" t="n">
         <v>0.01311983471074388</v>
       </c>
+      <c r="AA180" s="1" t="n">
+        <v>0.09891999999999999</v>
+      </c>
+      <c r="AB180" s="2" t="n">
+        <v>0.008667278474558882</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -15345,6 +16431,12 @@
       <c r="Z181" s="2" t="n">
         <v>0.006944444444444421</v>
       </c>
+      <c r="AA181" s="1" t="n">
+        <v>0.1876</v>
+      </c>
+      <c r="AB181" s="3" t="n">
+        <v>-0.004774535809018631</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -15427,6 +16519,12 @@
       <c r="Z182" s="2" t="n">
         <v>0.002027027027026944</v>
       </c>
+      <c r="AA182" s="1" t="n">
+        <v>0.05926</v>
+      </c>
+      <c r="AB182" s="3" t="n">
+        <v>-0.001011463250168536</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -15509,6 +16607,12 @@
       <c r="Z183" s="2" t="n">
         <v>0.002506265664160444</v>
       </c>
+      <c r="AA183" s="1" t="n">
+        <v>0.01199</v>
+      </c>
+      <c r="AB183" s="3" t="n">
+        <v>-0.0008333333333332993</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -15591,6 +16695,12 @@
       <c r="Z184" s="2" t="n">
         <v>0.00608899297423879</v>
       </c>
+      <c r="AA184" s="1" t="n">
+        <v>0.02148</v>
+      </c>
+      <c r="AB184" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -15673,6 +16783,12 @@
       <c r="Z185" s="2" t="n">
         <v>0.005464480874316945</v>
       </c>
+      <c r="AA185" s="1" t="n">
+        <v>0.366</v>
+      </c>
+      <c r="AB185" s="3" t="n">
+        <v>-0.005434782608695657</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -15755,6 +16871,12 @@
       <c r="Z186" s="2" t="n">
         <v>0.003147540983606634</v>
       </c>
+      <c r="AA186" s="1" t="n">
+        <v>0.007629</v>
+      </c>
+      <c r="AB186" s="3" t="n">
+        <v>-0.002614720878546222</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -15837,6 +16959,12 @@
       <c r="Z187" s="2" t="n">
         <v>0.00743218134522483</v>
       </c>
+      <c r="AA187" s="1" t="n">
+        <v>0.2694</v>
+      </c>
+      <c r="AB187" s="3" t="n">
+        <v>-0.006270748801180504</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -15919,6 +17047,12 @@
       <c r="Z188" s="2" t="n">
         <v>0.005897905226764259</v>
       </c>
+      <c r="AA188" s="1" t="n">
+        <v>0.04922</v>
+      </c>
+      <c r="AB188" s="3" t="n">
+        <v>-0.00485240598463399</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -16001,6 +17135,12 @@
       <c r="Z189" s="2" t="n">
         <v>0.003912363067292648</v>
       </c>
+      <c r="AA189" s="1" t="n">
+        <v>0.255</v>
+      </c>
+      <c r="AB189" s="3" t="n">
+        <v>-0.006235385814497235</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -16083,6 +17223,12 @@
       <c r="Z190" s="2" t="n">
         <v>0.004049295774648029</v>
       </c>
+      <c r="AA190" s="1" t="n">
+        <v>0.5723</v>
+      </c>
+      <c r="AB190" s="2" t="n">
+        <v>0.003506926179203931</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -16165,6 +17311,12 @@
       <c r="Z191" s="2" t="n">
         <v>0.003976143141153085</v>
       </c>
+      <c r="AA191" s="1" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="AB191" s="3" t="n">
+        <v>-0.004950495049504846</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -16247,6 +17399,12 @@
       <c r="Z192" s="2" t="n">
         <v>0.002286367533581089</v>
       </c>
+      <c r="AA192" s="1" t="n">
+        <v>0.349</v>
+      </c>
+      <c r="AB192" s="3" t="n">
+        <v>-0.004847447961220515</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -16329,6 +17487,12 @@
       <c r="Z193" s="2" t="n">
         <v>0.003144654088050186</v>
       </c>
+      <c r="AA193" s="1" t="n">
+        <v>0.0638</v>
+      </c>
+      <c r="AB193" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -16411,6 +17575,12 @@
       <c r="Z194" s="3" t="n">
         <v>-0.005757052389176707</v>
       </c>
+      <c r="AA194" s="1" t="n">
+        <v>0.01727</v>
+      </c>
+      <c r="AB194" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -16493,6 +17663,12 @@
       <c r="Z195" s="2" t="n">
         <v>0.002128666035950856</v>
       </c>
+      <c r="AA195" s="1" t="n">
+        <v>0.0008481</v>
+      </c>
+      <c r="AB195" s="2" t="n">
+        <v>0.0008260561718196398</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -16575,6 +17751,12 @@
       <c r="Z196" s="3" t="n">
         <v>-0.007582938388625572</v>
       </c>
+      <c r="AA196" s="1" t="n">
+        <v>0.001033</v>
+      </c>
+      <c r="AB196" s="3" t="n">
+        <v>-0.0133715377268385</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -16657,6 +17839,12 @@
       <c r="Z197" s="2" t="n">
         <v>0.003715170278637861</v>
       </c>
+      <c r="AA197" s="1" t="n">
+        <v>0.0001617</v>
+      </c>
+      <c r="AB197" s="3" t="n">
+        <v>-0.002467612584824243</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -16739,6 +17927,12 @@
       <c r="Z198" s="2" t="n">
         <v>0.002079002079002158</v>
       </c>
+      <c r="AA198" s="1" t="n">
+        <v>4.334</v>
+      </c>
+      <c r="AB198" s="3" t="n">
+        <v>-0.00092208390963588</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -16821,6 +18015,12 @@
       <c r="Z199" s="2" t="n">
         <v>0.006169031462060462</v>
       </c>
+      <c r="AA199" s="1" t="n">
+        <v>0.1626</v>
+      </c>
+      <c r="AB199" s="3" t="n">
+        <v>-0.003065603923973025</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -16903,6 +18103,12 @@
       <c r="Z200" s="2" t="n">
         <v>0.009646584232219655</v>
       </c>
+      <c r="AA200" s="1" t="n">
+        <v>0.02301</v>
+      </c>
+      <c r="AB200" s="3" t="n">
+        <v>-0.0006948666724573145</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -16985,6 +18191,12 @@
       <c r="Z201" s="2" t="n">
         <v>0.001291051399983921</v>
       </c>
+      <c r="AA201" s="1" t="n">
+        <v>0.12355</v>
+      </c>
+      <c r="AB201" s="3" t="n">
+        <v>-0.004351680232089715</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -17067,6 +18279,12 @@
       <c r="Z202" s="2" t="n">
         <v>0.005772005772005662</v>
       </c>
+      <c r="AA202" s="1" t="n">
+        <v>0.01397</v>
+      </c>
+      <c r="AB202" s="2" t="n">
+        <v>0.002152080344332892</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -17149,6 +18367,12 @@
       <c r="Z203" s="2" t="n">
         <v>0.000971109492595419</v>
       </c>
+      <c r="AA203" s="1" t="n">
+        <v>0.04102</v>
+      </c>
+      <c r="AB203" s="3" t="n">
+        <v>-0.005093378607809892</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -17231,6 +18455,12 @@
       <c r="Z204" s="2" t="n">
         <v>0.006201550387596916</v>
       </c>
+      <c r="AA204" s="1" t="n">
+        <v>0.02582</v>
+      </c>
+      <c r="AB204" s="3" t="n">
+        <v>-0.005392912172573237</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -17313,6 +18543,12 @@
       <c r="Z205" s="2" t="n">
         <v>0.001159554730983175</v>
       </c>
+      <c r="AA205" s="1" t="n">
+        <v>0.4303</v>
+      </c>
+      <c r="AB205" s="3" t="n">
+        <v>-0.00324299281908723</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -17395,6 +18631,12 @@
       <c r="Z206" s="2" t="n">
         <v>0.003943908851884303</v>
       </c>
+      <c r="AA206" s="1" t="n">
+        <v>0.02269</v>
+      </c>
+      <c r="AB206" s="3" t="n">
+        <v>-0.009602793539938955</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -17477,6 +18719,12 @@
       <c r="Z207" s="2" t="n">
         <v>0.004312410158121656</v>
       </c>
+      <c r="AA207" s="1" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="AB207" s="3" t="n">
+        <v>-0.002862595419847437</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -17559,6 +18807,12 @@
       <c r="Z208" s="2" t="n">
         <v>0.002036936447582799</v>
       </c>
+      <c r="AA208" s="1" t="n">
+        <v>0.07364999999999999</v>
+      </c>
+      <c r="AB208" s="3" t="n">
+        <v>-0.001897276053665825</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -17641,6 +18895,12 @@
       <c r="Z209" s="2" t="n">
         <v>0.003334921391138501</v>
       </c>
+      <c r="AA209" s="1" t="n">
+        <v>0.04218</v>
+      </c>
+      <c r="AB209" s="2" t="n">
+        <v>0.001424501424501531</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -17723,6 +18983,12 @@
       <c r="Z210" s="2" t="n">
         <v>0.003241491085899607</v>
       </c>
+      <c r="AA210" s="1" t="n">
+        <v>0.185</v>
+      </c>
+      <c r="AB210" s="3" t="n">
+        <v>-0.003769520732364061</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -17805,6 +19071,12 @@
       <c r="Z211" s="2" t="n">
         <v>0.002124044180118948</v>
       </c>
+      <c r="AA211" s="1" t="n">
+        <v>0.2362</v>
+      </c>
+      <c r="AB211" s="2" t="n">
+        <v>0.001271725307333593</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -17887,6 +19159,12 @@
       <c r="Z212" s="3" t="n">
         <v>-0.001916626736942819</v>
       </c>
+      <c r="AA212" s="1" t="n">
+        <v>0.002078</v>
+      </c>
+      <c r="AB212" s="3" t="n">
+        <v>-0.002400384061449942</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -17969,6 +19247,12 @@
       <c r="Z213" s="2" t="n">
         <v>0.003225806451612906</v>
       </c>
+      <c r="AA213" s="1" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="AB213" s="3" t="n">
+        <v>-0.003215434083601289</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -18051,6 +19335,12 @@
       <c r="Z214" s="2" t="n">
         <v>0.003157894736842068</v>
       </c>
+      <c r="AA214" s="1" t="n">
+        <v>0.005707</v>
+      </c>
+      <c r="AB214" s="3" t="n">
+        <v>-0.001923749562784142</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -18133,6 +19423,12 @@
       <c r="Z215" s="2" t="n">
         <v>0.002561287961946602</v>
       </c>
+      <c r="AA215" s="1" t="n">
+        <v>0.05464</v>
+      </c>
+      <c r="AB215" s="3" t="n">
+        <v>-0.002919708029197088</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -18215,6 +19511,12 @@
       <c r="Z216" s="2" t="n">
         <v>0.004761904761904678</v>
       </c>
+      <c r="AA216" s="1" t="n">
+        <v>0.0631</v>
+      </c>
+      <c r="AB216" s="3" t="n">
+        <v>-0.003159557661927202</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -18297,6 +19599,12 @@
       <c r="Z217" s="2" t="n">
         <v>0.002155172413793165</v>
       </c>
+      <c r="AA217" s="1" t="n">
+        <v>0.09279999999999999</v>
+      </c>
+      <c r="AB217" s="3" t="n">
+        <v>-0.002150537634408664</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -18379,6 +19687,12 @@
       <c r="Z218" s="2" t="n">
         <v>0.0008287093752252215</v>
       </c>
+      <c r="AA218" s="1" t="n">
+        <v>0.27863</v>
+      </c>
+      <c r="AB218" s="2" t="n">
+        <v>0.003096086690427231</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -18461,6 +19775,12 @@
       <c r="Z219" s="2" t="n">
         <v>0.007371007371007284</v>
       </c>
+      <c r="AA219" s="1" t="n">
+        <v>0.003269</v>
+      </c>
+      <c r="AB219" s="3" t="n">
+        <v>-0.003353658536585282</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -18543,6 +19863,12 @@
       <c r="Z220" s="3" t="n">
         <v>-1.000626392150242e-06</v>
       </c>
+      <c r="AA220" s="1" t="n">
+        <v>0.999374</v>
+      </c>
+      <c r="AB220" s="2" t="n">
+        <v>1.00062739340442e-06</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -18625,6 +19951,12 @@
       <c r="Z221" s="2" t="n">
         <v>0.005901975878881217</v>
       </c>
+      <c r="AA221" s="1" t="n">
+        <v>0.03865</v>
+      </c>
+      <c r="AB221" s="3" t="n">
+        <v>-0.01403061224489801</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -18707,6 +20039,12 @@
       <c r="Z222" s="2" t="n">
         <v>0.005802707930367492</v>
       </c>
+      <c r="AA222" s="1" t="n">
+        <v>0.04664</v>
+      </c>
+      <c r="AB222" s="3" t="n">
+        <v>-0.003418803418803427</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -18789,6 +20127,12 @@
       <c r="Z223" s="2" t="n">
         <v>0.006647673314339907</v>
       </c>
+      <c r="AA223" s="1" t="n">
+        <v>0.1058</v>
+      </c>
+      <c r="AB223" s="3" t="n">
+        <v>-0.001886792452830112</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -18871,6 +20215,12 @@
       <c r="Z224" s="2" t="n">
         <v>0.002814018930672838</v>
       </c>
+      <c r="AA224" s="1" t="n">
+        <v>3.949</v>
+      </c>
+      <c r="AB224" s="2" t="n">
+        <v>0.007397959183673448</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -18953,6 +20303,12 @@
       <c r="Z225" s="2" t="n">
         <v>0.004883872368135506</v>
       </c>
+      <c r="AA225" s="1" t="n">
+        <v>0.0009266</v>
+      </c>
+      <c r="AB225" s="2" t="n">
+        <v>0.0007560211685926805</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -19035,6 +20391,12 @@
       <c r="Z226" s="2" t="n">
         <v>0.001987374327799819</v>
       </c>
+      <c r="AA226" s="1" t="n">
+        <v>0.008491</v>
+      </c>
+      <c r="AB226" s="3" t="n">
+        <v>-0.009333800023334523</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -19117,6 +20479,12 @@
       <c r="Z227" s="2" t="n">
         <v>0.004357298474945525</v>
       </c>
+      <c r="AA227" s="1" t="n">
+        <v>0.04142</v>
+      </c>
+      <c r="AB227" s="3" t="n">
+        <v>-0.001687153530971333</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -19199,6 +20567,12 @@
       <c r="Z228" s="2" t="n">
         <v>0.006493506493506523</v>
       </c>
+      <c r="AA228" s="1" t="n">
+        <v>0.03554</v>
+      </c>
+      <c r="AB228" s="3" t="n">
+        <v>-0.003085553997194923</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -19281,6 +20655,12 @@
       <c r="Z229" s="2" t="n">
         <v>0.007374345041723237</v>
       </c>
+      <c r="AA229" s="1" t="n">
+        <v>0.05169</v>
+      </c>
+      <c r="AB229" s="3" t="n">
+        <v>-0.004238104411481371</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -19363,6 +20743,12 @@
       <c r="Z230" s="2" t="n">
         <v>0.00808781051415374</v>
       </c>
+      <c r="AA230" s="1" t="n">
+        <v>0.001741</v>
+      </c>
+      <c r="AB230" s="3" t="n">
+        <v>-0.002292263610315242</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -19445,6 +20831,12 @@
       <c r="Z231" s="2" t="n">
         <v>0.0004119464469618782</v>
       </c>
+      <c r="AA231" s="1" t="n">
+        <v>0.04878</v>
+      </c>
+      <c r="AB231" s="2" t="n">
+        <v>0.004323656578134546</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -19527,6 +20919,12 @@
       <c r="Z232" s="2" t="n">
         <v>0.005509641873278171</v>
       </c>
+      <c r="AA232" s="1" t="n">
+        <v>0.02181</v>
+      </c>
+      <c r="AB232" s="3" t="n">
+        <v>-0.004109589041095881</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -19609,6 +21007,12 @@
       <c r="Z233" s="2" t="n">
         <v>0.006666666666666551</v>
       </c>
+      <c r="AA233" s="1" t="n">
+        <v>0.0005894</v>
+      </c>
+      <c r="AB233" s="2" t="n">
+        <v>0.0008490405841400346</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -19691,6 +21095,12 @@
       <c r="Z234" s="2" t="n">
         <v>0.00148409238475089</v>
       </c>
+      <c r="AA234" s="1" t="n">
+        <v>0.21466</v>
+      </c>
+      <c r="AB234" s="3" t="n">
+        <v>-0.005927572473835341</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -19773,6 +21183,12 @@
       <c r="Z235" s="2" t="n">
         <v>0.00499999999999992</v>
       </c>
+      <c r="AA235" s="1" t="n">
+        <v>0.01433</v>
+      </c>
+      <c r="AB235" s="2" t="n">
+        <v>0.01847903340440665</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -19855,6 +21271,12 @@
       <c r="Z236" s="2" t="n">
         <v>0.007281553398058293</v>
       </c>
+      <c r="AA236" s="1" t="n">
+        <v>0.0415</v>
+      </c>
+      <c r="AB236" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -19937,6 +21359,12 @@
       <c r="Z237" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AA237" s="1" t="n">
+        <v>0.00417</v>
+      </c>
+      <c r="AB237" s="3" t="n">
+        <v>-0.004773269689737483</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -20019,6 +21447,12 @@
       <c r="Z238" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AA238" s="1" t="n">
+        <v>0.0251</v>
+      </c>
+      <c r="AB238" s="2" t="n">
+        <v>0.008032128514056316</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -20101,6 +21535,12 @@
       <c r="Z239" s="2" t="n">
         <v>0.0006666666666667552</v>
       </c>
+      <c r="AA239" s="1" t="n">
+        <v>0.01503</v>
+      </c>
+      <c r="AB239" s="2" t="n">
+        <v>0.001332445036642184</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -20183,6 +21623,12 @@
       <c r="Z240" s="2" t="n">
         <v>0.005363984674329633</v>
       </c>
+      <c r="AA240" s="1" t="n">
+        <v>0.0003951</v>
+      </c>
+      <c r="AB240" s="2" t="n">
+        <v>0.003810975609756052</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -20265,6 +21711,12 @@
       <c r="Z241" s="2" t="n">
         <v>0.004850746268656596</v>
       </c>
+      <c r="AA241" s="1" t="n">
+        <v>0.2703</v>
+      </c>
+      <c r="AB241" s="2" t="n">
+        <v>0.003713330857779432</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -20347,6 +21799,12 @@
       <c r="Z242" s="2" t="n">
         <v>0.003820816864295107</v>
       </c>
+      <c r="AA242" s="1" t="n">
+        <v>0.07665</v>
+      </c>
+      <c r="AB242" s="2" t="n">
+        <v>0.006037537734610869</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -20429,6 +21887,12 @@
       <c r="Z243" s="2" t="n">
         <v>0.01007049345417937</v>
       </c>
+      <c r="AA243" s="1" t="n">
+        <v>0.01993</v>
+      </c>
+      <c r="AB243" s="3" t="n">
+        <v>-0.006480558325025007</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -20511,6 +21975,12 @@
       <c r="Z244" s="3" t="n">
         <v>-0.006673570360142644</v>
       </c>
+      <c r="AA244" s="1" t="n">
+        <v>0.08558</v>
+      </c>
+      <c r="AB244" s="3" t="n">
+        <v>-0.008687594115602926</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -20593,6 +22063,12 @@
       <c r="Z245" s="3" t="n">
         <v>-0.001596667823672314</v>
       </c>
+      <c r="AA245" s="1" t="n">
+        <v>1.4373</v>
+      </c>
+      <c r="AB245" s="3" t="n">
+        <v>-0.000625782227784662</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -20675,6 +22151,12 @@
       <c r="Z246" s="2" t="n">
         <v>0.009572072072072071</v>
       </c>
+      <c r="AA246" s="1" t="n">
+        <v>0.01785</v>
+      </c>
+      <c r="AB246" s="3" t="n">
+        <v>-0.004461795872838829</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -20757,6 +22239,12 @@
       <c r="Z247" s="2" t="n">
         <v>0.005612012740785637</v>
       </c>
+      <c r="AA247" s="1" t="n">
+        <v>0.006601</v>
+      </c>
+      <c r="AB247" s="3" t="n">
+        <v>-0.004374057315233712</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -20839,6 +22327,12 @@
       <c r="Z248" s="3" t="n">
         <v>-0.01027970356203694</v>
       </c>
+      <c r="AA248" s="1" t="n">
+        <v>0.004099</v>
+      </c>
+      <c r="AB248" s="3" t="n">
+        <v>-0.009903381642511927</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -20921,6 +22415,12 @@
       <c r="Z249" s="2" t="n">
         <v>0.005474452554744555</v>
       </c>
+      <c r="AA249" s="1" t="n">
+        <v>0.1103</v>
+      </c>
+      <c r="AB249" s="2" t="n">
+        <v>0.0009074410163338383</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -21003,6 +22503,12 @@
       <c r="Z250" s="2" t="n">
         <v>0.008756567425569226</v>
       </c>
+      <c r="AA250" s="1" t="n">
+        <v>0.03454</v>
+      </c>
+      <c r="AB250" s="3" t="n">
+        <v>-0.0005787037037036801</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -21085,6 +22591,12 @@
       <c r="Z251" s="2" t="n">
         <v>0.003261882572227428</v>
       </c>
+      <c r="AA251" s="1" t="n">
+        <v>0.04286</v>
+      </c>
+      <c r="AB251" s="3" t="n">
+        <v>-0.00464468183929398</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -21167,6 +22679,12 @@
       <c r="Z252" s="3" t="n">
         <v>-0.002808060786257106</v>
       </c>
+      <c r="AA252" s="1" t="n">
+        <v>0.005968</v>
+      </c>
+      <c r="AB252" s="3" t="n">
+        <v>-0.01142951797250284</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -21249,6 +22767,12 @@
       <c r="Z253" s="3" t="n">
         <v>-0.006343713956170845</v>
       </c>
+      <c r="AA253" s="1" t="n">
+        <v>0.01719</v>
+      </c>
+      <c r="AB253" s="3" t="n">
+        <v>-0.002321532211259337</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -21331,6 +22855,12 @@
       <c r="Z254" s="2" t="n">
         <v>0.00386697602474865</v>
       </c>
+      <c r="AA254" s="1" t="n">
+        <v>0.1291</v>
+      </c>
+      <c r="AB254" s="3" t="n">
+        <v>-0.005392912172573238</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -21413,6 +22943,12 @@
       <c r="Z255" s="2" t="n">
         <v>0.0042796005706134</v>
       </c>
+      <c r="AA255" s="1" t="n">
+        <v>0.02121</v>
+      </c>
+      <c r="AB255" s="2" t="n">
+        <v>0.004261363636363627</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -21495,6 +23031,12 @@
       <c r="Z256" s="2" t="n">
         <v>0.00332699619771866</v>
       </c>
+      <c r="AA256" s="1" t="n">
+        <v>0.02103</v>
+      </c>
+      <c r="AB256" s="3" t="n">
+        <v>-0.003789673140691625</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -21577,6 +23119,12 @@
       <c r="Z257" s="2" t="n">
         <v>0.002380952380952421</v>
       </c>
+      <c r="AA257" s="1" t="n">
+        <v>0.02552</v>
+      </c>
+      <c r="AB257" s="2" t="n">
+        <v>0.01029295328582739</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -21659,6 +23207,12 @@
       <c r="Z258" s="3" t="n">
         <v>-0.0003317629885211482</v>
       </c>
+      <c r="AA258" s="1" t="n">
+        <v>0.15059</v>
+      </c>
+      <c r="AB258" s="3" t="n">
+        <v>-0.0004646223284215236</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -21741,6 +23295,12 @@
       <c r="Z259" s="2" t="n">
         <v>0.002953337271116309</v>
       </c>
+      <c r="AA259" s="1" t="n">
+        <v>0.05091</v>
+      </c>
+      <c r="AB259" s="3" t="n">
+        <v>-0.0005889281507656507</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -21823,6 +23383,12 @@
       <c r="Z260" s="2" t="n">
         <v>0.009511196725258839</v>
       </c>
+      <c r="AA260" s="1" t="n">
+        <v>0.08394</v>
+      </c>
+      <c r="AB260" s="2" t="n">
+        <v>0.001073345259391851</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -21905,6 +23471,12 @@
       <c r="Z261" s="3" t="n">
         <v>-0.03109012199921287</v>
       </c>
+      <c r="AA261" s="1" t="n">
+        <v>0.2454</v>
+      </c>
+      <c r="AB261" s="3" t="n">
+        <v>-0.003249390739236374</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -21987,6 +23559,12 @@
       <c r="Z262" s="2" t="n">
         <v>0.000693481276005664</v>
       </c>
+      <c r="AA262" s="1" t="n">
+        <v>0.1444</v>
+      </c>
+      <c r="AB262" s="2" t="n">
+        <v>0.0006930006930006167</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -22069,6 +23647,12 @@
       <c r="Z263" s="2" t="n">
         <v>0.003643461288223845</v>
       </c>
+      <c r="AA263" s="1" t="n">
+        <v>0.07653</v>
+      </c>
+      <c r="AB263" s="3" t="n">
+        <v>-0.007779074290159513</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -22151,6 +23735,12 @@
       <c r="Z264" s="3" t="n">
         <v>-0.001522456229383343</v>
       </c>
+      <c r="AA264" s="1" t="n">
+        <v>0.03938</v>
+      </c>
+      <c r="AB264" s="2" t="n">
+        <v>0.0007623888182972123</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -22233,6 +23823,12 @@
       <c r="Z265" s="2" t="n">
         <v>0.004581151832460773</v>
       </c>
+      <c r="AA265" s="1" t="n">
+        <v>0.01537</v>
+      </c>
+      <c r="AB265" s="2" t="n">
+        <v>0.001302931596091152</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -22315,6 +23911,12 @@
       <c r="Z266" s="2" t="n">
         <v>0.005675179435820426</v>
       </c>
+      <c r="AA266" s="1" t="n">
+        <v>0.005995</v>
+      </c>
+      <c r="AB266" s="3" t="n">
+        <v>-0.004979253112033136</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -22397,6 +23999,12 @@
       <c r="Z267" s="2" t="n">
         <v>0.003766478342749562</v>
       </c>
+      <c r="AA267" s="1" t="n">
+        <v>0.03725</v>
+      </c>
+      <c r="AB267" s="3" t="n">
+        <v>-0.001608147949611485</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -22479,6 +24087,12 @@
       <c r="Z268" s="2" t="n">
         <v>0.002291325695581035</v>
       </c>
+      <c r="AA268" s="1" t="n">
+        <v>0.03058</v>
+      </c>
+      <c r="AB268" s="3" t="n">
+        <v>-0.001306335728282229</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -22561,6 +24175,12 @@
       <c r="Z269" s="2" t="n">
         <v>0.003853991317444891</v>
       </c>
+      <c r="AA269" s="1" t="n">
+        <v>0.22567</v>
+      </c>
+      <c r="AB269" s="3" t="n">
+        <v>-0.004148095847491268</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -22643,6 +24263,12 @@
       <c r="Z270" s="2" t="n">
         <v>0.008639308855291584</v>
       </c>
+      <c r="AA270" s="1" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="AB270" s="3" t="n">
+        <v>-0.00428265524625268</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -22725,6 +24351,12 @@
       <c r="Z271" s="2" t="n">
         <v>0.002307692307692224</v>
       </c>
+      <c r="AA271" s="1" t="n">
+        <v>2.593</v>
+      </c>
+      <c r="AB271" s="3" t="n">
+        <v>-0.004988488104374482</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -22807,6 +24439,12 @@
       <c r="Z272" s="2" t="n">
         <v>0.005945945945945891</v>
       </c>
+      <c r="AA272" s="1" t="n">
+        <v>0.1864</v>
+      </c>
+      <c r="AB272" s="2" t="n">
+        <v>0.001612036539495016</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -22889,6 +24527,12 @@
       <c r="Z273" s="2" t="n">
         <v>0.003542673107890467</v>
       </c>
+      <c r="AA273" s="1" t="n">
+        <v>0.03095</v>
+      </c>
+      <c r="AB273" s="3" t="n">
+        <v>-0.006739409499358211</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -22971,6 +24615,12 @@
       <c r="Z274" s="2" t="n">
         <v>0.005243838489774519</v>
       </c>
+      <c r="AA274" s="1" t="n">
+        <v>0.1912</v>
+      </c>
+      <c r="AB274" s="3" t="n">
+        <v>-0.002608242044861766</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -23053,6 +24703,12 @@
       <c r="Z275" s="2" t="n">
         <v>0.001590744757772943</v>
       </c>
+      <c r="AA275" s="1" t="n">
+        <v>0.06920999999999999</v>
+      </c>
+      <c r="AB275" s="3" t="n">
+        <v>-0.0007219174126481139</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -23135,6 +24791,12 @@
       <c r="Z276" s="2" t="n">
         <v>0.002863545816732994</v>
       </c>
+      <c r="AA276" s="1" t="n">
+        <v>0.0803</v>
+      </c>
+      <c r="AB276" s="3" t="n">
+        <v>-0.003103662321539419</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -23217,6 +24879,12 @@
       <c r="Z277" s="2" t="n">
         <v>0.01077964402105782</v>
       </c>
+      <c r="AA277" s="1" t="n">
+        <v>0.003992</v>
+      </c>
+      <c r="AB277" s="3" t="n">
+        <v>-0.009920634920634946</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -23299,6 +24967,12 @@
       <c r="Z278" s="2" t="n">
         <v>0.003221649484536014</v>
       </c>
+      <c r="AA278" s="1" t="n">
+        <v>1.554</v>
+      </c>
+      <c r="AB278" s="3" t="n">
+        <v>-0.001926782273603013</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -23381,6 +25055,12 @@
       <c r="Z279" s="2" t="n">
         <v>0.004537205081669664</v>
       </c>
+      <c r="AA279" s="1" t="n">
+        <v>0.01104</v>
+      </c>
+      <c r="AB279" s="3" t="n">
+        <v>-0.002710027100271049</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -23463,6 +25143,12 @@
       <c r="Z280" s="2" t="n">
         <v>0.00148404650012361</v>
       </c>
+      <c r="AA280" s="1" t="n">
+        <v>0.04019</v>
+      </c>
+      <c r="AB280" s="3" t="n">
+        <v>-0.007409236848604635</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -23545,6 +25231,12 @@
       <c r="Z281" s="2" t="n">
         <v>0.004179603534750455</v>
       </c>
+      <c r="AA281" s="1" t="n">
+        <v>0.08393</v>
+      </c>
+      <c r="AB281" s="3" t="n">
+        <v>-0.001902723272683952</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -23627,6 +25319,12 @@
       <c r="Z282" s="2" t="n">
         <v>0.007518796992481288</v>
       </c>
+      <c r="AA282" s="1" t="n">
+        <v>0.0268</v>
+      </c>
+      <c r="AB282" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -23709,6 +25407,12 @@
       <c r="Z283" s="2" t="n">
         <v>0.005775794171698555</v>
       </c>
+      <c r="AA283" s="1" t="n">
+        <v>0.07630000000000001</v>
+      </c>
+      <c r="AB283" s="3" t="n">
+        <v>-0.004176455233620295</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -23791,6 +25495,12 @@
       <c r="Z284" s="2" t="n">
         <v>0.009975062344139623</v>
       </c>
+      <c r="AA284" s="1" t="n">
+        <v>0.001609</v>
+      </c>
+      <c r="AB284" s="3" t="n">
+        <v>-0.006790123456790088</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -23873,6 +25583,12 @@
       <c r="Z285" s="2" t="n">
         <v>0.003958436417615018</v>
       </c>
+      <c r="AA285" s="1" t="n">
+        <v>0.2024</v>
+      </c>
+      <c r="AB285" s="3" t="n">
+        <v>-0.002464268112370628</v>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -23955,6 +25671,12 @@
       <c r="Z286" s="2" t="n">
         <v>0.003091334894613555</v>
       </c>
+      <c r="AA286" s="1" t="n">
+        <v>0.10679</v>
+      </c>
+      <c r="AB286" s="3" t="n">
+        <v>-0.002708255509899128</v>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -24037,6 +25759,12 @@
       <c r="Z287" s="3" t="n">
         <v>-0.000573723465289707</v>
       </c>
+      <c r="AA287" s="1" t="n">
+        <v>0.01739</v>
+      </c>
+      <c r="AB287" s="3" t="n">
+        <v>-0.001722158438576478</v>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -24119,6 +25847,12 @@
       <c r="Z288" s="2" t="n">
         <v>0.003324468085106363</v>
       </c>
+      <c r="AA288" s="1" t="n">
+        <v>0.01507</v>
+      </c>
+      <c r="AB288" s="3" t="n">
+        <v>-0.001325381047050973</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -24201,6 +25935,12 @@
       <c r="Z289" s="2" t="n">
         <v>0.004331683168316869</v>
       </c>
+      <c r="AA289" s="1" t="n">
+        <v>0.01631</v>
+      </c>
+      <c r="AB289" s="2" t="n">
+        <v>0.004929143561306235</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -24283,6 +26023,12 @@
       <c r="Z290" s="2" t="n">
         <v>0.003542958370239153</v>
       </c>
+      <c r="AA290" s="1" t="n">
+        <v>2.252</v>
+      </c>
+      <c r="AB290" s="3" t="n">
+        <v>-0.006178287731685893</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -24365,6 +26111,12 @@
       <c r="Z291" s="2" t="n">
         <v>0.004998863894569497</v>
       </c>
+      <c r="AA291" s="1" t="n">
+        <v>0.4419</v>
+      </c>
+      <c r="AB291" s="3" t="n">
+        <v>-0.0009043635541487936</v>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -24447,6 +26199,12 @@
       <c r="Z292" s="3" t="n">
         <v>-0.002312138728323701</v>
       </c>
+      <c r="AA292" s="1" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AB292" s="2" t="n">
+        <v>0.002317497103128623</v>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -24529,6 +26287,12 @@
       <c r="Z293" s="2" t="n">
         <v>0.002004008016032122</v>
       </c>
+      <c r="AA293" s="1" t="n">
+        <v>0.04995</v>
+      </c>
+      <c r="AB293" s="3" t="n">
+        <v>-0.001000000000000029</v>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -24611,6 +26375,12 @@
       <c r="Z294" s="2" t="n">
         <v>0.002843152740483329</v>
       </c>
+      <c r="AA294" s="1" t="n">
+        <v>0.06337</v>
+      </c>
+      <c r="AB294" s="3" t="n">
+        <v>-0.001890061426996519</v>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -24693,6 +26463,12 @@
       <c r="Z295" s="2" t="n">
         <v>0.003630203291384275</v>
       </c>
+      <c r="AA295" s="1" t="n">
+        <v>0.0004131</v>
+      </c>
+      <c r="AB295" s="3" t="n">
+        <v>-0.003858210754762442</v>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -24775,6 +26551,12 @@
       <c r="Z296" s="2" t="n">
         <v>0.002561229390107311</v>
       </c>
+      <c r="AA296" s="1" t="n">
+        <v>62.43</v>
+      </c>
+      <c r="AB296" s="3" t="n">
+        <v>-0.003193357815743299</v>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -24857,6 +26639,12 @@
       <c r="Z297" s="2" t="n">
         <v>0.002047082906857786</v>
       </c>
+      <c r="AA297" s="1" t="n">
+        <v>0.0975</v>
+      </c>
+      <c r="AB297" s="3" t="n">
+        <v>-0.004085801838610802</v>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -24939,6 +26727,12 @@
       <c r="Z298" s="2" t="n">
         <v>0.003138075313807476</v>
       </c>
+      <c r="AA298" s="1" t="n">
+        <v>0.0954</v>
+      </c>
+      <c r="AB298" s="3" t="n">
+        <v>-0.005213764337851934</v>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -25021,6 +26815,12 @@
       <c r="Z299" s="2" t="n">
         <v>0.0001042318115488443</v>
       </c>
+      <c r="AA299" s="1" t="n">
+        <v>0.09601999999999999</v>
+      </c>
+      <c r="AB299" s="2" t="n">
+        <v>0.0007295466388744202</v>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -25103,6 +26903,12 @@
       <c r="Z300" s="3" t="n">
         <v>-0.003733333333333366</v>
       </c>
+      <c r="AA300" s="1" t="n">
+        <v>0.01863</v>
+      </c>
+      <c r="AB300" s="3" t="n">
+        <v>-0.002676659528907814</v>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -25185,6 +26991,12 @@
       <c r="Z301" s="2" t="n">
         <v>0.009009009009009033</v>
       </c>
+      <c r="AA301" s="1" t="n">
+        <v>0.01343</v>
+      </c>
+      <c r="AB301" s="3" t="n">
+        <v>-0.0007440476190477178</v>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -25267,6 +27079,12 @@
       <c r="Z302" s="2" t="n">
         <v>0.00274285714285711</v>
       </c>
+      <c r="AA302" s="1" t="n">
+        <v>0.004391</v>
+      </c>
+      <c r="AB302" s="2" t="n">
+        <v>0.0009117848187826905</v>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -25349,6 +27167,12 @@
       <c r="Z303" s="2" t="n">
         <v>0.002166847237269684</v>
       </c>
+      <c r="AA303" s="1" t="n">
+        <v>0.00923</v>
+      </c>
+      <c r="AB303" s="3" t="n">
+        <v>-0.002162162162162074</v>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -25431,6 +27255,12 @@
       <c r="Z304" s="2" t="n">
         <v>0.002334960730205927</v>
       </c>
+      <c r="AA304" s="1" t="n">
+        <v>4.712</v>
+      </c>
+      <c r="AB304" s="3" t="n">
+        <v>-0.002117746717492731</v>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -25513,6 +27343,12 @@
       <c r="Z305" s="2" t="n">
         <v>0.002264150943396265</v>
       </c>
+      <c r="AA305" s="1" t="n">
+        <v>0.05316</v>
+      </c>
+      <c r="AB305" s="2" t="n">
+        <v>0.0007530120481927404</v>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -25595,6 +27431,12 @@
       <c r="Z306" s="2" t="n">
         <v>0.003436426116838467</v>
       </c>
+      <c r="AA306" s="1" t="n">
+        <v>0.05844</v>
+      </c>
+      <c r="AB306" s="2" t="n">
+        <v>0.0006849315068492871</v>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -25677,6 +27519,12 @@
       <c r="Z307" s="2" t="n">
         <v>0.001723147616312434</v>
       </c>
+      <c r="AA307" s="1" t="n">
+        <v>0.1746</v>
+      </c>
+      <c r="AB307" s="2" t="n">
+        <v>0.001146788990825721</v>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -25759,6 +27607,12 @@
       <c r="Z308" s="2" t="n">
         <v>0.005664576168318745</v>
       </c>
+      <c r="AA308" s="1" t="n">
+        <v>0.04978</v>
+      </c>
+      <c r="AB308" s="2" t="n">
+        <v>0.001408167370750365</v>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -25841,6 +27695,12 @@
       <c r="Z309" s="2" t="n">
         <v>0.004238068914685977</v>
       </c>
+      <c r="AA309" s="1" t="n">
+        <v>0.547</v>
+      </c>
+      <c r="AB309" s="2" t="n">
+        <v>0.003669724770642205</v>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -25923,6 +27783,12 @@
       <c r="Z310" s="2" t="n">
         <v>0.00411522633744857</v>
       </c>
+      <c r="AA310" s="1" t="n">
+        <v>0.00244</v>
+      </c>
+      <c r="AB310" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -26005,6 +27871,12 @@
       <c r="Z311" s="2" t="n">
         <v>0.004239084357778645</v>
       </c>
+      <c r="AA311" s="1" t="n">
+        <v>0.07104000000000001</v>
+      </c>
+      <c r="AB311" s="3" t="n">
+        <v>-0.0004221190375684307</v>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -26087,6 +27959,12 @@
       <c r="Z312" s="2" t="n">
         <v>0.005361331397297126</v>
       </c>
+      <c r="AA312" s="1" t="n">
+        <v>0.008940999999999999</v>
+      </c>
+      <c r="AB312" s="3" t="n">
+        <v>-0.006665926008221423</v>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -26169,6 +28047,12 @@
       <c r="Z313" s="2" t="n">
         <v>0.006417201433452845</v>
       </c>
+      <c r="AA313" s="1" t="n">
+        <v>0.012068</v>
+      </c>
+      <c r="AB313" s="3" t="n">
+        <v>-0.0006624710168929552</v>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -26251,6 +28135,12 @@
       <c r="Z314" s="2" t="n">
         <v>0.01113490364025695</v>
       </c>
+      <c r="AA314" s="1" t="n">
+        <v>0.02372</v>
+      </c>
+      <c r="AB314" s="2" t="n">
+        <v>0.004659042778483798</v>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -26333,6 +28223,12 @@
       <c r="Z315" s="2" t="n">
         <v>0.002816901408450589</v>
       </c>
+      <c r="AA315" s="1" t="n">
+        <v>0.00713</v>
+      </c>
+      <c r="AB315" s="2" t="n">
+        <v>0.001404494382022536</v>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -26415,6 +28311,12 @@
       <c r="Z316" s="2" t="n">
         <v>0.006928406466512794</v>
       </c>
+      <c r="AA316" s="1" t="n">
+        <v>0.2608</v>
+      </c>
+      <c r="AB316" s="3" t="n">
+        <v>-0.003058103975535256</v>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -26497,6 +28399,12 @@
       <c r="Z317" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AA317" s="1" t="n">
+        <v>1.12e-05</v>
+      </c>
+      <c r="AB317" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -26579,6 +28487,12 @@
       <c r="Z318" s="2" t="n">
         <v>0.001615171208148097</v>
       </c>
+      <c r="AA318" s="1" t="n">
+        <v>0.052723</v>
+      </c>
+      <c r="AB318" s="2" t="n">
+        <v>0.0002276564663921785</v>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -26661,6 +28575,12 @@
       <c r="Z319" s="2" t="n">
         <v>0.001046025104602468</v>
       </c>
+      <c r="AA319" s="1" t="n">
+        <v>0.03832</v>
+      </c>
+      <c r="AB319" s="2" t="n">
+        <v>0.001044932079414795</v>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -26743,6 +28663,12 @@
       <c r="Z320" s="2" t="n">
         <v>0.005737825511254961</v>
       </c>
+      <c r="AA320" s="1" t="n">
+        <v>0.006825</v>
+      </c>
+      <c r="AB320" s="3" t="n">
+        <v>-0.001609128145114062</v>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -26825,6 +28751,12 @@
       <c r="Z321" s="2" t="n">
         <v>0.004868333702146546</v>
       </c>
+      <c r="AA321" s="1" t="n">
+        <v>4.539</v>
+      </c>
+      <c r="AB321" s="3" t="n">
+        <v>-0.0004404316229906778</v>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -26907,6 +28839,12 @@
       <c r="Z322" s="2" t="n">
         <v>0.004164497657470071</v>
       </c>
+      <c r="AA322" s="1" t="n">
+        <v>1.925</v>
+      </c>
+      <c r="AB322" s="3" t="n">
+        <v>-0.002073613271124937</v>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -26989,6 +28927,12 @@
       <c r="Z323" s="2" t="n">
         <v>0.003642476884281309</v>
       </c>
+      <c r="AA323" s="1" t="n">
+        <v>0.007121</v>
+      </c>
+      <c r="AB323" s="3" t="n">
+        <v>-0.006002233389168133</v>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -27071,6 +29015,12 @@
       <c r="Z324" s="2" t="n">
         <v>0.004904632152588545</v>
       </c>
+      <c r="AA324" s="1" t="n">
+        <v>0.01835</v>
+      </c>
+      <c r="AB324" s="3" t="n">
+        <v>-0.004880694143167017</v>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -27153,6 +29103,12 @@
       <c r="Z325" s="2" t="n">
         <v>0.006321419888159473</v>
       </c>
+      <c r="AA325" s="1" t="n">
+        <v>0.4122</v>
+      </c>
+      <c r="AB325" s="3" t="n">
+        <v>-0.004107272287992219</v>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -27235,6 +29191,12 @@
       <c r="Z326" s="2" t="n">
         <v>0.007802703079280984</v>
       </c>
+      <c r="AA326" s="1" t="n">
+        <v>0.007203</v>
+      </c>
+      <c r="AB326" s="3" t="n">
+        <v>-0.004147656574035621</v>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -27317,6 +29279,12 @@
       <c r="Z327" s="2" t="n">
         <v>0.002098635886673722</v>
       </c>
+      <c r="AA327" s="1" t="n">
+        <v>0.192</v>
+      </c>
+      <c r="AB327" s="2" t="n">
+        <v>0.005235602094240842</v>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -27399,6 +29367,12 @@
       <c r="Z328" s="2" t="n">
         <v>0.006419858763107218</v>
       </c>
+      <c r="AA328" s="1" t="n">
+        <v>0.4687</v>
+      </c>
+      <c r="AB328" s="3" t="n">
+        <v>-0.003402083776312971</v>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -27481,6 +29455,12 @@
       <c r="Z329" s="2" t="n">
         <v>0.00149031296572287</v>
       </c>
+      <c r="AA329" s="1" t="n">
+        <v>0.01343</v>
+      </c>
+      <c r="AB329" s="3" t="n">
+        <v>-0.0007440476190477178</v>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -27563,6 +29543,12 @@
       <c r="Z330" s="2" t="n">
         <v>0.002650176678445306</v>
       </c>
+      <c r="AA330" s="1" t="n">
+        <v>0.1131</v>
+      </c>
+      <c r="AB330" s="3" t="n">
+        <v>-0.003524229074889846</v>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -27645,6 +29631,12 @@
       <c r="Z331" s="2" t="n">
         <v>0.006473029045643178</v>
       </c>
+      <c r="AA331" s="1" t="n">
+        <v>0.6028</v>
+      </c>
+      <c r="AB331" s="3" t="n">
+        <v>-0.005936675461741502</v>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -27727,6 +29719,12 @@
       <c r="Z332" s="2" t="n">
         <v>0.003028108748601251</v>
       </c>
+      <c r="AA332" s="1" t="n">
+        <v>0.30468</v>
+      </c>
+      <c r="AB332" s="3" t="n">
+        <v>-0.0001968891514077722</v>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -27809,6 +29807,12 @@
       <c r="Z333" s="3" t="n">
         <v>-0.0008493771234426758</v>
       </c>
+      <c r="AA333" s="1" t="n">
+        <v>0.07049</v>
+      </c>
+      <c r="AB333" s="3" t="n">
+        <v>-0.001275148767356287</v>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -27891,6 +29895,12 @@
       <c r="Z334" s="3" t="n">
         <v>-0.0001323714342444387</v>
       </c>
+      <c r="AA334" s="1" t="n">
+        <v>0.15107</v>
+      </c>
+      <c r="AB334" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -27973,6 +29983,12 @@
       <c r="Z335" s="2" t="n">
         <v>0.001916932907348209</v>
       </c>
+      <c r="AA335" s="1" t="n">
+        <v>0.1567</v>
+      </c>
+      <c r="AB335" s="3" t="n">
+        <v>-0.0006377551020407461</v>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -28055,6 +30071,12 @@
       <c r="Z336" s="2" t="n">
         <v>0.005181347150259136</v>
       </c>
+      <c r="AA336" s="1" t="n">
+        <v>0.1743</v>
+      </c>
+      <c r="AB336" s="3" t="n">
+        <v>-0.001718213058419214</v>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -28137,6 +30159,12 @@
       <c r="Z337" s="3" t="n">
         <v>-0.002490039840637521</v>
       </c>
+      <c r="AA337" s="1" t="n">
+        <v>0.04008</v>
+      </c>
+      <c r="AB337" s="2" t="n">
+        <v>0.0004992511233150071</v>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -28219,6 +30247,12 @@
       <c r="Z338" s="2" t="n">
         <v>0.004361016306408719</v>
       </c>
+      <c r="AA338" s="1" t="n">
+        <v>0.005284</v>
+      </c>
+      <c r="AB338" s="3" t="n">
+        <v>-0.002454219369454406</v>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -28301,6 +30335,12 @@
       <c r="Z339" s="2" t="n">
         <v>0.007388683647676557</v>
       </c>
+      <c r="AA339" s="1" t="n">
+        <v>0.0516</v>
+      </c>
+      <c r="AB339" s="3" t="n">
+        <v>-0.004053271569195172</v>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -28383,6 +30423,12 @@
       <c r="Z340" s="2" t="n">
         <v>0.003516454352441631</v>
       </c>
+      <c r="AA340" s="1" t="n">
+        <v>0.15061</v>
+      </c>
+      <c r="AB340" s="3" t="n">
+        <v>-0.004231404958677697</v>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -28465,6 +30511,12 @@
       <c r="Z341" s="2" t="n">
         <v>0.002755905511811011</v>
       </c>
+      <c r="AA341" s="1" t="n">
+        <v>7.635</v>
+      </c>
+      <c r="AB341" s="3" t="n">
+        <v>-0.0007852375343541718</v>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -28547,6 +30599,12 @@
       <c r="Z342" s="3" t="n">
         <v>-0.0006082725060826581</v>
       </c>
+      <c r="AA342" s="1" t="n">
+        <v>0.3296</v>
+      </c>
+      <c r="AB342" s="2" t="n">
+        <v>0.003043213633597081</v>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -28629,6 +30687,12 @@
       <c r="Z343" s="2" t="n">
         <v>0.01205424409844302</v>
       </c>
+      <c r="AA343" s="1" t="n">
+        <v>0.02009</v>
+      </c>
+      <c r="AB343" s="3" t="n">
+        <v>-0.002977667493796577</v>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -28711,6 +30775,12 @@
       <c r="Z344" s="2" t="n">
         <v>0.002764976958525451</v>
       </c>
+      <c r="AA344" s="1" t="n">
+        <v>2.178</v>
+      </c>
+      <c r="AB344" s="2" t="n">
+        <v>0.0009191176470587223</v>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -28793,6 +30863,12 @@
       <c r="Z345" s="2" t="n">
         <v>0.004746835443037979</v>
       </c>
+      <c r="AA345" s="1" t="n">
+        <v>1.265</v>
+      </c>
+      <c r="AB345" s="3" t="n">
+        <v>-0.003937007874015839</v>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -28875,6 +30951,12 @@
       <c r="Z346" s="2" t="n">
         <v>0.002906413485758623</v>
       </c>
+      <c r="AA346" s="1" t="n">
+        <v>0.005165</v>
+      </c>
+      <c r="AB346" s="3" t="n">
+        <v>-0.002125193199381709</v>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -28957,6 +31039,12 @@
       <c r="Z347" s="2" t="n">
         <v>0.00489253887821065</v>
       </c>
+      <c r="AA347" s="1" t="n">
+        <v>0.05716</v>
+      </c>
+      <c r="AB347" s="3" t="n">
+        <v>-0.006085898104677381</v>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -29039,6 +31127,12 @@
       <c r="Z348" s="2" t="n">
         <v>0.003142183817753429</v>
       </c>
+      <c r="AA348" s="1" t="n">
+        <v>0.1273</v>
+      </c>
+      <c r="AB348" s="3" t="n">
+        <v>-0.003132341425215438</v>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -29121,6 +31215,12 @@
       <c r="Z349" s="3" t="n">
         <v>-0.001446815077742197</v>
       </c>
+      <c r="AA349" s="1" t="n">
+        <v>5180.2</v>
+      </c>
+      <c r="AB349" s="2" t="n">
+        <v>0.0007534339199813836</v>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -29203,6 +31303,12 @@
       <c r="Z350" s="2" t="n">
         <v>0.002151308712800199</v>
       </c>
+      <c r="AA350" s="1" t="n">
+        <v>0.0278</v>
+      </c>
+      <c r="AB350" s="3" t="n">
+        <v>-0.005366726296958885</v>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -29285,6 +31391,12 @@
       <c r="Z351" s="2" t="n">
         <v>0.001433691756272436</v>
       </c>
+      <c r="AA351" s="1" t="n">
+        <v>0.001389</v>
+      </c>
+      <c r="AB351" s="3" t="n">
+        <v>-0.005726556907659254</v>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -29367,6 +31479,12 @@
       <c r="Z352" s="2" t="n">
         <v>0.01209420751113957</v>
       </c>
+      <c r="AA352" s="1" t="n">
+        <v>0.01653</v>
+      </c>
+      <c r="AB352" s="2" t="n">
+        <v>0.03962264150943387</v>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -29449,6 +31567,12 @@
       <c r="Z353" s="2" t="n">
         <v>0.0003180155827636617</v>
       </c>
+      <c r="AA353" s="1" t="n">
+        <v>6.309</v>
+      </c>
+      <c r="AB353" s="2" t="n">
+        <v>0.002861230329041455</v>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -29531,6 +31655,12 @@
       <c r="Z354" s="2" t="n">
         <v>0.00209059233449493</v>
       </c>
+      <c r="AA354" s="1" t="n">
+        <v>0.2874</v>
+      </c>
+      <c r="AB354" s="3" t="n">
+        <v>-0.0006954102920724391</v>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -29613,6 +31743,12 @@
       <c r="Z355" s="2" t="n">
         <v>0.0009643201542911854</v>
       </c>
+      <c r="AA355" s="1" t="n">
+        <v>0.04158</v>
+      </c>
+      <c r="AB355" s="2" t="n">
+        <v>0.001445086705202253</v>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -29695,6 +31831,12 @@
       <c r="Z356" s="2" t="n">
         <v>0.004057510805327707</v>
       </c>
+      <c r="AA356" s="1" t="n">
+        <v>0.11339</v>
+      </c>
+      <c r="AB356" s="3" t="n">
+        <v>-0.003865413335675973</v>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -29777,6 +31919,12 @@
       <c r="Z357" s="2" t="n">
         <v>0.002662103061418544</v>
       </c>
+      <c r="AA357" s="1" t="n">
+        <v>0.005284</v>
+      </c>
+      <c r="AB357" s="2" t="n">
+        <v>0.002086098994879523</v>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -29859,6 +32007,12 @@
       <c r="Z358" s="2" t="n">
         <v>0.005417118093174436</v>
       </c>
+      <c r="AA358" s="1" t="n">
+        <v>0.1853</v>
+      </c>
+      <c r="AB358" s="3" t="n">
+        <v>-0.001616379310344799</v>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -29941,6 +32095,12 @@
       <c r="Z359" s="2" t="n">
         <v>0.002460024600246073</v>
       </c>
+      <c r="AA359" s="1" t="n">
+        <v>0.1638</v>
+      </c>
+      <c r="AB359" s="2" t="n">
+        <v>0.004907975460122669</v>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -30023,6 +32183,12 @@
       <c r="Z360" s="2" t="n">
         <v>0.001174950064622124</v>
       </c>
+      <c r="AA360" s="1" t="n">
+        <v>0.08505</v>
+      </c>
+      <c r="AB360" s="3" t="n">
+        <v>-0.001877713883346949</v>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -30105,6 +32271,12 @@
       <c r="Z361" s="2" t="n">
         <v>0.001308900523560156</v>
       </c>
+      <c r="AA361" s="1" t="n">
+        <v>0.00763</v>
+      </c>
+      <c r="AB361" s="3" t="n">
+        <v>-0.002614379084967327</v>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -30187,6 +32359,12 @@
       <c r="Z362" s="2" t="n">
         <v>0.0009398496240601773</v>
       </c>
+      <c r="AA362" s="1" t="n">
+        <v>0.4261</v>
+      </c>
+      <c r="AB362" s="2" t="n">
+        <v>0.0002347417840375328</v>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -30269,6 +32447,12 @@
       <c r="Z363" s="2" t="n">
         <v>0.003975616220514095</v>
       </c>
+      <c r="AA363" s="1" t="n">
+        <v>3.795</v>
+      </c>
+      <c r="AB363" s="2" t="n">
+        <v>0.001847940865892322</v>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -30351,6 +32535,12 @@
       <c r="Z364" s="2" t="n">
         <v>0.001821493624772239</v>
       </c>
+      <c r="AA364" s="1" t="n">
+        <v>0.01101</v>
+      </c>
+      <c r="AB364" s="2" t="n">
+        <v>0.0009090909090910298</v>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -30433,6 +32623,12 @@
       <c r="Z365" s="2" t="n">
         <v>0.002726776949645471</v>
       </c>
+      <c r="AA365" s="1" t="n">
+        <v>0.05517</v>
+      </c>
+      <c r="AB365" s="2" t="n">
+        <v>0.000181290790427776</v>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -30515,6 +32711,12 @@
       <c r="Z366" s="2" t="n">
         <v>0.006570302233902796</v>
       </c>
+      <c r="AA366" s="1" t="n">
+        <v>0.02297</v>
+      </c>
+      <c r="AB366" s="3" t="n">
+        <v>-0.0004351610095735245</v>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -30597,6 +32799,12 @@
       <c r="Z367" s="2" t="n">
         <v>0.003695491500369559</v>
       </c>
+      <c r="AA367" s="1" t="n">
+        <v>0.001347</v>
+      </c>
+      <c r="AB367" s="3" t="n">
+        <v>-0.008100147275404965</v>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -30679,6 +32887,12 @@
       <c r="Z368" s="2" t="n">
         <v>0.006631762652705106</v>
       </c>
+      <c r="AA368" s="1" t="n">
+        <v>0.2885</v>
+      </c>
+      <c r="AB368" s="2" t="n">
+        <v>0.0003467406380027358</v>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -30761,6 +32975,12 @@
       <c r="Z369" s="3" t="n">
         <v>-0.0005385029617662678</v>
       </c>
+      <c r="AA369" s="1" t="n">
+        <v>0.01859</v>
+      </c>
+      <c r="AB369" s="2" t="n">
+        <v>0.001616379310344762</v>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -30843,6 +33063,12 @@
       <c r="Z370" s="2" t="n">
         <v>0.003049400284610781</v>
       </c>
+      <c r="AA370" s="1" t="n">
+        <v>0.19703</v>
+      </c>
+      <c r="AB370" s="3" t="n">
+        <v>-0.001672071341710564</v>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -30925,6 +33151,12 @@
       <c r="Z371" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AA371" s="1" t="n">
+        <v>0.076</v>
+      </c>
+      <c r="AB371" s="2" t="n">
+        <v>0.01333333333333335</v>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -31007,6 +33239,12 @@
       <c r="Z372" s="2" t="n">
         <v>0.005725190839694555</v>
       </c>
+      <c r="AA372" s="1" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="AB372" s="3" t="n">
+        <v>-0.003795066413662216</v>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -31089,6 +33327,12 @@
       <c r="Z373" s="2" t="n">
         <v>0.002578492340361042</v>
       </c>
+      <c r="AA373" s="1" t="n">
+        <v>0.06603000000000001</v>
+      </c>
+      <c r="AB373" s="3" t="n">
+        <v>-0.001059001512859313</v>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -31171,6 +33415,12 @@
       <c r="Z374" s="2" t="n">
         <v>0.003821823932524975</v>
       </c>
+      <c r="AA374" s="1" t="n">
+        <v>0.007598</v>
+      </c>
+      <c r="AB374" s="3" t="n">
+        <v>-0.002494420375475899</v>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -31253,6 +33503,12 @@
       <c r="Z375" s="2" t="n">
         <v>0.005671077504725798</v>
       </c>
+      <c r="AA375" s="1" t="n">
+        <v>0.1603</v>
+      </c>
+      <c r="AB375" s="2" t="n">
+        <v>0.004385964912280741</v>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -31335,6 +33591,12 @@
       <c r="Z376" s="2" t="n">
         <v>0.004694835680751161</v>
       </c>
+      <c r="AA376" s="1" t="n">
+        <v>0.003403</v>
+      </c>
+      <c r="AB376" s="3" t="n">
+        <v>-0.006133177570093386</v>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -31417,6 +33679,12 @@
       <c r="Z377" s="2" t="n">
         <v>0.006060606060606023</v>
       </c>
+      <c r="AA377" s="1" t="n">
+        <v>0.0175</v>
+      </c>
+      <c r="AB377" s="2" t="n">
+        <v>0.05421686746987961</v>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -31499,6 +33767,12 @@
       <c r="Z378" s="3" t="n">
         <v>-0.007123775601068584</v>
       </c>
+      <c r="AA378" s="1" t="n">
+        <v>0.01116</v>
+      </c>
+      <c r="AB378" s="2" t="n">
+        <v>0.0008968609865470487</v>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -31581,6 +33855,12 @@
       <c r="Z379" s="2" t="n">
         <v>0.004672897196261654</v>
       </c>
+      <c r="AA379" s="1" t="n">
+        <v>0.02165</v>
+      </c>
+      <c r="AB379" s="2" t="n">
+        <v>0.006976744186046551</v>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -31663,6 +33943,12 @@
       <c r="Z380" s="2" t="n">
         <v>0.003193187865885979</v>
       </c>
+      <c r="AA380" s="1" t="n">
+        <v>0.01878</v>
+      </c>
+      <c r="AB380" s="3" t="n">
+        <v>-0.003713527851458735</v>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -31745,6 +34031,12 @@
       <c r="Z381" s="2" t="n">
         <v>0.004173622704507516</v>
       </c>
+      <c r="AA381" s="1" t="n">
+        <v>0.1197</v>
+      </c>
+      <c r="AB381" s="3" t="n">
+        <v>-0.004987531172069853</v>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -31827,6 +34119,12 @@
       <c r="Z382" s="2" t="n">
         <v>0.002364066193853449</v>
       </c>
+      <c r="AA382" s="1" t="n">
+        <v>0.02935</v>
+      </c>
+      <c r="AB382" s="3" t="n">
+        <v>-0.01111859838274934</v>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -31909,6 +34207,12 @@
       <c r="Z383" s="3" t="n">
         <v>-0.0003045530683722043</v>
       </c>
+      <c r="AA383" s="1" t="n">
+        <v>0.006559</v>
+      </c>
+      <c r="AB383" s="3" t="n">
+        <v>-0.0009139375476009032</v>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -31991,6 +34295,12 @@
       <c r="Z384" s="2" t="n">
         <v>0.002400384061449734</v>
       </c>
+      <c r="AA384" s="1" t="n">
+        <v>0.02093</v>
+      </c>
+      <c r="AB384" s="2" t="n">
+        <v>0.002394636015325739</v>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -32073,6 +34383,12 @@
       <c r="Z385" s="2" t="n">
         <v>0.003951007506914263</v>
       </c>
+      <c r="AA385" s="1" t="n">
+        <v>2536</v>
+      </c>
+      <c r="AB385" s="3" t="n">
+        <v>-0.001967729240456513</v>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -32155,6 +34471,12 @@
       <c r="Z386" s="2" t="n">
         <v>0.003025718608169387</v>
       </c>
+      <c r="AA386" s="1" t="n">
+        <v>0.1984</v>
+      </c>
+      <c r="AB386" s="3" t="n">
+        <v>-0.00251382604323781</v>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -32237,6 +34559,12 @@
       <c r="Z387" s="2" t="n">
         <v>0.004009433962264069</v>
       </c>
+      <c r="AA387" s="1" t="n">
+        <v>0.08536000000000001</v>
+      </c>
+      <c r="AB387" s="2" t="n">
+        <v>0.002583979328165514</v>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -32319,6 +34647,12 @@
       <c r="Z388" s="2" t="n">
         <v>0.002009646302250722</v>
       </c>
+      <c r="AA388" s="1" t="n">
+        <v>0.004986</v>
+      </c>
+      <c r="AB388" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -32401,6 +34735,12 @@
       <c r="Z389" s="3" t="n">
         <v>-0.002218278615794207</v>
       </c>
+      <c r="AA389" s="1" t="n">
+        <v>0.02246</v>
+      </c>
+      <c r="AB389" s="3" t="n">
+        <v>-0.001333926189417465</v>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -32483,6 +34823,12 @@
       <c r="Z390" s="2" t="n">
         <v>0.004966229638458598</v>
       </c>
+      <c r="AA390" s="1" t="n">
+        <v>0.5024999999999999</v>
+      </c>
+      <c r="AB390" s="3" t="n">
+        <v>-0.006720695789681892</v>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -32565,6 +34911,12 @@
       <c r="Z391" s="2" t="n">
         <v>0.008803986710963399</v>
       </c>
+      <c r="AA391" s="1" t="n">
+        <v>0.0006057</v>
+      </c>
+      <c r="AB391" s="3" t="n">
+        <v>-0.002634612218014047</v>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -32647,6 +34999,12 @@
       <c r="Z392" s="2" t="n">
         <v>0.004621704895583694</v>
       </c>
+      <c r="AA392" s="1" t="n">
+        <v>0.05845</v>
+      </c>
+      <c r="AB392" s="3" t="n">
+        <v>-0.004089282671664631</v>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -32729,6 +35087,12 @@
       <c r="Z393" s="2" t="n">
         <v>0.00371195248700817</v>
       </c>
+      <c r="AA393" s="1" t="n">
+        <v>0.2692</v>
+      </c>
+      <c r="AB393" s="3" t="n">
+        <v>-0.004437869822485129</v>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -32811,6 +35175,12 @@
       <c r="Z394" s="2" t="n">
         <v>0.001949902504874755</v>
       </c>
+      <c r="AA394" s="1" t="n">
+        <v>0.006636</v>
+      </c>
+      <c r="AB394" s="3" t="n">
+        <v>-0.006586826347305354</v>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -32893,6 +35263,12 @@
       <c r="Z395" s="2" t="n">
         <v>0.003490401396160659</v>
       </c>
+      <c r="AA395" s="1" t="n">
+        <v>0.1152</v>
+      </c>
+      <c r="AB395" s="2" t="n">
+        <v>0.001739130434782538</v>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -32975,6 +35351,12 @@
       <c r="Z396" s="2" t="n">
         <v>0.007486979166666587</v>
       </c>
+      <c r="AA396" s="1" t="n">
+        <v>0.03088</v>
+      </c>
+      <c r="AB396" s="3" t="n">
+        <v>-0.002261712439418325</v>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -33057,6 +35439,12 @@
       <c r="Z397" s="2" t="n">
         <v>0.001329787234042591</v>
       </c>
+      <c r="AA397" s="1" t="n">
+        <v>0.151</v>
+      </c>
+      <c r="AB397" s="2" t="n">
+        <v>0.002656042496679838</v>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -33139,6 +35527,12 @@
       <c r="Z398" s="3" t="n">
         <v>-0.002119927316777598</v>
       </c>
+      <c r="AA398" s="1" t="n">
+        <v>0.003297</v>
+      </c>
+      <c r="AB398" s="2" t="n">
+        <v>0.0006069802731410718</v>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -33221,6 +35615,12 @@
       <c r="Z399" s="2" t="n">
         <v>0.005952380952380897</v>
       </c>
+      <c r="AA399" s="1" t="n">
+        <v>0.01854</v>
+      </c>
+      <c r="AB399" s="3" t="n">
+        <v>-0.002689618074233349</v>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -33303,6 +35703,12 @@
       <c r="Z400" s="3" t="n">
         <v>-0.003296545793320852</v>
       </c>
+      <c r="AA400" s="1" t="n">
+        <v>0.006935</v>
+      </c>
+      <c r="AB400" s="3" t="n">
+        <v>-0.002732240437158458</v>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -33385,6 +35791,12 @@
       <c r="Z401" s="2" t="n">
         <v>0.00201178330219861</v>
       </c>
+      <c r="AA401" s="1" t="n">
+        <v>0.006958</v>
+      </c>
+      <c r="AB401" s="3" t="n">
+        <v>-0.002151154452889754</v>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -33467,6 +35879,12 @@
       <c r="Z402" s="2" t="n">
         <v>0.003370786516854055</v>
       </c>
+      <c r="AA402" s="1" t="n">
+        <v>0.008007999999999999</v>
+      </c>
+      <c r="AB402" s="3" t="n">
+        <v>-0.003608311559039597</v>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -33549,6 +35967,12 @@
       <c r="Z403" s="2" t="n">
         <v>0.006926054186188633</v>
       </c>
+      <c r="AA403" s="1" t="n">
+        <v>0.04929</v>
+      </c>
+      <c r="AB403" s="3" t="n">
+        <v>-0.002832288084159442</v>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -33631,6 +36055,12 @@
       <c r="Z404" s="2" t="n">
         <v>0.0006059789927281105</v>
       </c>
+      <c r="AA404" s="1" t="n">
+        <v>0.14818</v>
+      </c>
+      <c r="AB404" s="3" t="n">
+        <v>-0.002893479577417307</v>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -33713,6 +36143,12 @@
       <c r="Z405" s="2" t="n">
         <v>0.004205607476635505</v>
       </c>
+      <c r="AA405" s="1" t="n">
+        <v>0.04267</v>
+      </c>
+      <c r="AB405" s="3" t="n">
+        <v>-0.007212657049790549</v>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -33795,6 +36231,12 @@
       <c r="Z406" s="2" t="n">
         <v>0.003348681456676413</v>
       </c>
+      <c r="AA406" s="1" t="n">
+        <v>0.4787</v>
+      </c>
+      <c r="AB406" s="3" t="n">
+        <v>-0.00146015853149766</v>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -33877,6 +36319,12 @@
       <c r="Z407" s="2" t="n">
         <v>0.005066882853668437</v>
       </c>
+      <c r="AA407" s="1" t="n">
+        <v>0.000496</v>
+      </c>
+      <c r="AB407" s="2" t="n">
+        <v>0.0002016535591854339</v>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -33959,6 +36407,12 @@
       <c r="Z408" s="2" t="n">
         <v>0.006467259498787265</v>
       </c>
+      <c r="AA408" s="1" t="n">
+        <v>0.01238</v>
+      </c>
+      <c r="AB408" s="3" t="n">
+        <v>-0.005622489959839268</v>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -34041,6 +36495,12 @@
       <c r="Z409" s="2" t="n">
         <v>0.001569858712715857</v>
       </c>
+      <c r="AA409" s="1" t="n">
+        <v>0.3187</v>
+      </c>
+      <c r="AB409" s="3" t="n">
+        <v>-0.0009404388714734246</v>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -34123,6 +36583,12 @@
       <c r="Z410" s="2" t="n">
         <v>0.004317582153993754</v>
       </c>
+      <c r="AA410" s="1" t="n">
+        <v>0.04185</v>
+      </c>
+      <c r="AB410" s="3" t="n">
+        <v>-0.0004776689754000283</v>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -34205,6 +36671,12 @@
       <c r="Z411" s="2" t="n">
         <v>0.002357696194004736</v>
       </c>
+      <c r="AA411" s="1" t="n">
+        <v>0.02974</v>
+      </c>
+      <c r="AB411" s="3" t="n">
+        <v>-0.0006720430107527773</v>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
@@ -34287,6 +36759,12 @@
       <c r="Z412" s="2" t="n">
         <v>0.001749398644216093</v>
       </c>
+      <c r="AA412" s="1" t="n">
+        <v>0.00457</v>
+      </c>
+      <c r="AB412" s="3" t="n">
+        <v>-0.002401222440515112</v>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -34369,6 +36847,12 @@
       <c r="Z413" s="2" t="n">
         <v>0.007575757575757405</v>
       </c>
+      <c r="AA413" s="1" t="n">
+        <v>0.2517</v>
+      </c>
+      <c r="AB413" s="3" t="n">
+        <v>-0.00395726157499011</v>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -34451,6 +36935,12 @@
       <c r="Z414" s="2" t="n">
         <v>0.001564945226917059</v>
       </c>
+      <c r="AA414" s="1" t="n">
+        <v>1.283</v>
+      </c>
+      <c r="AB414" s="2" t="n">
+        <v>0.002343749999999915</v>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -34533,6 +37023,12 @@
       <c r="Z415" s="2" t="n">
         <v>0.01030548398969452</v>
       </c>
+      <c r="AA415" s="1" t="n">
+        <v>2.757</v>
+      </c>
+      <c r="AB415" s="2" t="n">
+        <v>0.004371584699453555</v>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -34615,6 +37111,12 @@
       <c r="Z416" s="2" t="n">
         <v>0.001852423587526939</v>
       </c>
+      <c r="AA416" s="1" t="n">
+        <v>0.03248</v>
+      </c>
+      <c r="AB416" s="2" t="n">
+        <v>0.0009244992295840446</v>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -34697,6 +37199,12 @@
       <c r="Z417" s="2" t="n">
         <v>0.00428643469490662</v>
       </c>
+      <c r="AA417" s="1" t="n">
+        <v>0.03974</v>
+      </c>
+      <c r="AB417" s="3" t="n">
+        <v>-0.002259603314084856</v>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -34779,6 +37287,12 @@
       <c r="Z418" s="2" t="n">
         <v>0.002631925253322698</v>
       </c>
+      <c r="AA418" s="1" t="n">
+        <v>0.07625</v>
+      </c>
+      <c r="AB418" s="2" t="n">
+        <v>0.000787504921905821</v>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -34861,6 +37375,12 @@
       <c r="Z419" s="2" t="n">
         <v>0.006051437216338764</v>
       </c>
+      <c r="AA419" s="1" t="n">
+        <v>0.00664</v>
+      </c>
+      <c r="AB419" s="3" t="n">
+        <v>-0.001503759398496179</v>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -34943,6 +37463,12 @@
       <c r="Z420" s="2" t="n">
         <v>0.002272727272727338</v>
       </c>
+      <c r="AA420" s="1" t="n">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="AB420" s="3" t="n">
+        <v>-0.00226757369614519</v>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -35025,6 +37551,12 @@
       <c r="Z421" s="2" t="n">
         <v>0.007528230865746533</v>
       </c>
+      <c r="AA421" s="1" t="n">
+        <v>0.2414</v>
+      </c>
+      <c r="AB421" s="2" t="n">
+        <v>0.002075550020755502</v>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
@@ -35107,6 +37639,12 @@
       <c r="Z422" s="2" t="n">
         <v>0.2474747474747473</v>
       </c>
+      <c r="AA422" s="1" t="n">
+        <v>0.0263</v>
+      </c>
+      <c r="AB422" s="2" t="n">
+        <v>0.0647773279352227</v>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -35189,6 +37727,12 @@
       <c r="Z423" s="2" t="n">
         <v>0.003317850033178503</v>
       </c>
+      <c r="AA423" s="1" t="n">
+        <v>0.1514</v>
+      </c>
+      <c r="AB423" s="2" t="n">
+        <v>0.001322751322751361</v>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -35271,6 +37815,12 @@
       <c r="Z424" s="2" t="n">
         <v>0.003347680535628967</v>
       </c>
+      <c r="AA424" s="1" t="n">
+        <v>0.0002101</v>
+      </c>
+      <c r="AB424" s="2" t="n">
+        <v>0.001429933269780778</v>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -35353,6 +37903,12 @@
       <c r="Z425" s="2" t="n">
         <v>0.004035512510088695</v>
       </c>
+      <c r="AA425" s="1" t="n">
+        <v>1.243</v>
+      </c>
+      <c r="AB425" s="3" t="n">
+        <v>-0.0008038585209002331</v>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
@@ -35435,6 +37991,12 @@
       <c r="Z426" s="2" t="n">
         <v>0.003538570417551234</v>
       </c>
+      <c r="AA426" s="1" t="n">
+        <v>1.414</v>
+      </c>
+      <c r="AB426" s="3" t="n">
+        <v>-0.002820874471086039</v>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -35517,6 +38079,12 @@
       <c r="Z427" s="2" t="n">
         <v>0.003088008234688679</v>
       </c>
+      <c r="AA427" s="1" t="n">
+        <v>0.0195</v>
+      </c>
+      <c r="AB427" s="2" t="n">
+        <v>0.0005130836326320981</v>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
@@ -35599,6 +38167,12 @@
       <c r="Z428" s="2" t="n">
         <v>0.002878787878787814</v>
       </c>
+      <c r="AA428" s="1" t="n">
+        <v>0.06580999999999999</v>
+      </c>
+      <c r="AB428" s="3" t="n">
+        <v>-0.005741048496751856</v>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
@@ -35681,6 +38255,12 @@
       <c r="Z429" s="2" t="n">
         <v>0.004552352048558341</v>
       </c>
+      <c r="AA429" s="1" t="n">
+        <v>0.1322</v>
+      </c>
+      <c r="AB429" s="3" t="n">
+        <v>-0.001510574018126722</v>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
@@ -35763,6 +38343,12 @@
       <c r="Z430" s="2" t="n">
         <v>0.001268575570859018</v>
       </c>
+      <c r="AA430" s="1" t="n">
+        <v>0.011064</v>
+      </c>
+      <c r="AB430" s="2" t="n">
+        <v>0.001266968325791709</v>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -35845,6 +38431,12 @@
       <c r="Z431" s="2" t="n">
         <v>0.003597122302158231</v>
       </c>
+      <c r="AA431" s="1" t="n">
+        <v>0.006699</v>
+      </c>
+      <c r="AB431" s="2" t="n">
+        <v>0.0004480286738351849</v>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
@@ -35927,6 +38519,12 @@
       <c r="Z432" s="2" t="n">
         <v>0.003395585738539981</v>
       </c>
+      <c r="AA432" s="1" t="n">
+        <v>0.001772</v>
+      </c>
+      <c r="AB432" s="3" t="n">
+        <v>-0.0005640157924422632</v>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
@@ -36009,6 +38607,12 @@
       <c r="Z433" s="3" t="n">
         <v>-0.002201027146001441</v>
       </c>
+      <c r="AA433" s="1" t="n">
+        <v>0.00136</v>
+      </c>
+      <c r="AB433" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
@@ -36091,6 +38695,12 @@
       <c r="Z434" s="2" t="n">
         <v>0.002427184466019477</v>
       </c>
+      <c r="AA434" s="1" t="n">
+        <v>0.000414</v>
+      </c>
+      <c r="AB434" s="2" t="n">
+        <v>0.002421307506053196</v>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
@@ -36173,6 +38783,12 @@
       <c r="Z435" s="2" t="n">
         <v>0.004665506879645795</v>
       </c>
+      <c r="AA435" s="1" t="n">
+        <v>0.12662</v>
+      </c>
+      <c r="AB435" s="3" t="n">
+        <v>-0.003384494293585092</v>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -36255,6 +38871,12 @@
       <c r="Z436" s="2" t="n">
         <v>0.006570471527956847</v>
       </c>
+      <c r="AA436" s="1" t="n">
+        <v>0.07778</v>
+      </c>
+      <c r="AB436" s="3" t="n">
+        <v>-0.004479713298348945</v>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
@@ -36337,6 +38959,12 @@
       <c r="Z437" s="2" t="n">
         <v>0.001275103602167713</v>
       </c>
+      <c r="AA437" s="1" t="n">
+        <v>0.6269</v>
+      </c>
+      <c r="AB437" s="3" t="n">
+        <v>-0.002069404648201158</v>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -36419,6 +39047,12 @@
       <c r="Z438" s="2" t="n">
         <v>0.002969392416628556</v>
       </c>
+      <c r="AA438" s="1" t="n">
+        <v>0.04384</v>
+      </c>
+      <c r="AB438" s="3" t="n">
+        <v>-0.001594169892962893</v>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
@@ -36501,6 +39135,12 @@
       <c r="Z439" s="2" t="n">
         <v>0.003433476394849645</v>
       </c>
+      <c r="AA439" s="1" t="n">
+        <v>0.07035</v>
+      </c>
+      <c r="AB439" s="2" t="n">
+        <v>0.002994011976047931</v>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
@@ -36583,6 +39223,12 @@
       <c r="Z440" s="2" t="n">
         <v>0.003965631196298698</v>
       </c>
+      <c r="AA440" s="1" t="n">
+        <v>0.001516</v>
+      </c>
+      <c r="AB440" s="3" t="n">
+        <v>-0.001974983541803795</v>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -36665,6 +39311,12 @@
       <c r="Z441" s="3" t="n">
         <v>-0.003056170302455424</v>
       </c>
+      <c r="AA441" s="1" t="n">
+        <v>0.009469</v>
+      </c>
+      <c r="AB441" s="2" t="n">
+        <v>0.0009513742071881953</v>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
@@ -36747,6 +39399,12 @@
       <c r="Z442" s="2" t="n">
         <v>0.005719733079122979</v>
       </c>
+      <c r="AA442" s="1" t="n">
+        <v>1.052</v>
+      </c>
+      <c r="AB442" s="3" t="n">
+        <v>-0.002843601895734495</v>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
@@ -36829,6 +39487,12 @@
       <c r="Z443" s="2" t="n">
         <v>0.006401463191586546</v>
       </c>
+      <c r="AA443" s="1" t="n">
+        <v>0.02196</v>
+      </c>
+      <c r="AB443" s="3" t="n">
+        <v>-0.002271694684234347</v>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
@@ -36911,6 +39575,12 @@
       <c r="Z444" s="2" t="n">
         <v>0.003412073490813732</v>
       </c>
+      <c r="AA444" s="1" t="n">
+        <v>0.0003822</v>
+      </c>
+      <c r="AB444" s="3" t="n">
+        <v>-0.0002615746795710238</v>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
@@ -36993,6 +39663,12 @@
       <c r="Z445" s="2" t="n">
         <v>0.003668171557562025</v>
       </c>
+      <c r="AA445" s="1" t="n">
+        <v>0.03554</v>
+      </c>
+      <c r="AB445" s="3" t="n">
+        <v>-0.0008434073657575291</v>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
@@ -37075,6 +39751,12 @@
       <c r="Z446" s="2" t="n">
         <v>0.008331377610889489</v>
       </c>
+      <c r="AA446" s="1" t="n">
+        <v>0.08605</v>
+      </c>
+      <c r="AB446" s="2" t="n">
+        <v>0.001396485511462762</v>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
@@ -37157,6 +39839,12 @@
       <c r="Z447" s="2" t="n">
         <v>0.0006116207951069663</v>
       </c>
+      <c r="AA447" s="1" t="n">
+        <v>3.269</v>
+      </c>
+      <c r="AB447" s="3" t="n">
+        <v>-0.0009168704156478208</v>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
@@ -37239,6 +39927,12 @@
       <c r="Z448" s="2" t="n">
         <v>0.002662490211432883</v>
       </c>
+      <c r="AA448" s="1" t="n">
+        <v>0.06407</v>
+      </c>
+      <c r="AB448" s="2" t="n">
+        <v>0.0007810059356452417</v>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
@@ -37321,6 +40015,12 @@
       <c r="Z449" s="2" t="n">
         <v>0.00329150380580137</v>
       </c>
+      <c r="AA449" s="1" t="n">
+        <v>0.4892</v>
+      </c>
+      <c r="AB449" s="2" t="n">
+        <v>0.003075661267172445</v>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
@@ -37403,6 +40103,12 @@
       <c r="Z450" s="2" t="n">
         <v>0.0002656042496678917</v>
       </c>
+      <c r="AA450" s="1" t="n">
+        <v>0.03773</v>
+      </c>
+      <c r="AB450" s="2" t="n">
+        <v>0.00185873605947957</v>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -37485,6 +40191,12 @@
       <c r="Z451" s="2" t="n">
         <v>0.003663003663003673</v>
       </c>
+      <c r="AA451" s="1" t="n">
+        <v>0.00549</v>
+      </c>
+      <c r="AB451" s="2" t="n">
+        <v>0.001824817518248259</v>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
@@ -37567,6 +40279,12 @@
       <c r="Z452" s="2" t="n">
         <v>0.003567640536110396</v>
       </c>
+      <c r="AA452" s="1" t="n">
+        <v>0.10424</v>
+      </c>
+      <c r="AB452" s="2" t="n">
+        <v>0.001537279016141367</v>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
@@ -37649,6 +40367,12 @@
       <c r="Z453" s="2" t="n">
         <v>0.01930261519302601</v>
       </c>
+      <c r="AA453" s="1" t="n">
+        <v>0.01624</v>
+      </c>
+      <c r="AB453" s="3" t="n">
+        <v>-0.007941356139279057</v>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
@@ -37731,6 +40455,12 @@
       <c r="Z454" s="3" t="n">
         <v>-0.01339285714285704</v>
       </c>
+      <c r="AA454" s="1" t="n">
+        <v>2.869</v>
+      </c>
+      <c r="AB454" s="3" t="n">
+        <v>-0.001392272885485556</v>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
@@ -37813,6 +40543,12 @@
       <c r="Z455" s="2" t="n">
         <v>0.004479283314669656</v>
       </c>
+      <c r="AA455" s="1" t="n">
+        <v>0.894</v>
+      </c>
+      <c r="AB455" s="3" t="n">
+        <v>-0.003344481605351174</v>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
@@ -37895,6 +40631,12 @@
       <c r="Z456" s="2" t="n">
         <v>0.002036659877800334</v>
       </c>
+      <c r="AA456" s="1" t="n">
+        <v>2.951</v>
+      </c>
+      <c r="AB456" s="3" t="n">
+        <v>-0.000338753387533838</v>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -37977,6 +40719,12 @@
       <c r="Z457" s="2" t="n">
         <v>0.002028397565922838</v>
       </c>
+      <c r="AA457" s="1" t="n">
+        <v>0.00988</v>
+      </c>
+      <c r="AB457" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
@@ -38059,6 +40807,12 @@
       <c r="Z458" s="2" t="n">
         <v>0.0009643201542912969</v>
       </c>
+      <c r="AA458" s="1" t="n">
+        <v>0.06233</v>
+      </c>
+      <c r="AB458" s="2" t="n">
+        <v>0.0008028259473346408</v>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
@@ -38141,6 +40895,12 @@
       <c r="Z459" s="2" t="n">
         <v>0.003503854239663609</v>
       </c>
+      <c r="AA459" s="1" t="n">
+        <v>0.01436</v>
+      </c>
+      <c r="AB459" s="2" t="n">
+        <v>0.002793296089385482</v>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
@@ -38223,6 +40983,12 @@
       <c r="Z460" s="2" t="n">
         <v>0.001063230971292742</v>
       </c>
+      <c r="AA460" s="1" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="AB460" s="3" t="n">
+        <v>-0.0003748594277145484</v>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
@@ -38305,6 +41071,12 @@
       <c r="Z461" s="2" t="n">
         <v>0.003001200480191954</v>
       </c>
+      <c r="AA461" s="1" t="n">
+        <v>0.01672</v>
+      </c>
+      <c r="AB461" s="2" t="n">
+        <v>0.0005984440454817232</v>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
@@ -38387,6 +41159,12 @@
       <c r="Z462" s="2" t="n">
         <v>0.00335249042145589</v>
       </c>
+      <c r="AA462" s="1" t="n">
+        <v>0.0002087</v>
+      </c>
+      <c r="AB462" s="3" t="n">
+        <v>-0.00381861575178994</v>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
@@ -38469,6 +41247,12 @@
       <c r="Z463" s="2" t="n">
         <v>0.009118541033434631</v>
       </c>
+      <c r="AA463" s="1" t="n">
+        <v>0.1004</v>
+      </c>
+      <c r="AB463" s="2" t="n">
+        <v>0.008032128514056316</v>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
@@ -38551,6 +41335,12 @@
       <c r="Z464" s="2" t="n">
         <v>0.01108562691131506</v>
       </c>
+      <c r="AA464" s="1" t="n">
+        <v>0.0265</v>
+      </c>
+      <c r="AB464" s="2" t="n">
+        <v>0.001890359168241889</v>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
@@ -38633,6 +41423,12 @@
       <c r="Z465" s="3" t="n">
         <v>-0.001997336884154495</v>
       </c>
+      <c r="AA465" s="1" t="n">
+        <v>0.01501</v>
+      </c>
+      <c r="AB465" s="2" t="n">
+        <v>0.001334222815210202</v>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
@@ -38715,6 +41511,12 @@
       <c r="Z466" s="2" t="n">
         <v>0.0005480453050785943</v>
       </c>
+      <c r="AA466" s="1" t="n">
+        <v>0.05471</v>
+      </c>
+      <c r="AB466" s="3" t="n">
+        <v>-0.001095490231878721</v>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
@@ -38797,6 +41599,12 @@
       <c r="Z467" s="2" t="n">
         <v>0.006395348837209243</v>
       </c>
+      <c r="AA467" s="1" t="n">
+        <v>0.03449</v>
+      </c>
+      <c r="AB467" s="3" t="n">
+        <v>-0.003755054881571294</v>
+      </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
@@ -38879,6 +41687,12 @@
       <c r="Z468" s="3" t="n">
         <v>-0.001094091903719954</v>
       </c>
+      <c r="AA468" s="1" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="AB468" s="2" t="n">
+        <v>0.0003650967506388467</v>
+      </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
@@ -38961,6 +41775,12 @@
       <c r="Z469" s="2" t="n">
         <v>0.006318902930895483</v>
       </c>
+      <c r="AA469" s="1" t="n">
+        <v>0.0007487</v>
+      </c>
+      <c r="AB469" s="2" t="n">
+        <v>0.0002672010688042817</v>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
@@ -39043,6 +41863,12 @@
       <c r="Z470" s="2" t="n">
         <v>0.00680272108843538</v>
       </c>
+      <c r="AA470" s="1" t="n">
+        <v>0.887</v>
+      </c>
+      <c r="AB470" s="3" t="n">
+        <v>-0.001126126126126127</v>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
@@ -39125,6 +41951,12 @@
       <c r="Z471" s="2" t="n">
         <v>0.003036437246963615</v>
       </c>
+      <c r="AA471" s="1" t="n">
+        <v>0.00992</v>
+      </c>
+      <c r="AB471" s="2" t="n">
+        <v>0.001009081735620544</v>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
@@ -39207,6 +42039,12 @@
       <c r="Z472" s="2" t="n">
         <v>0.005167958656330688</v>
       </c>
+      <c r="AA472" s="1" t="n">
+        <v>0.04674</v>
+      </c>
+      <c r="AB472" s="2" t="n">
+        <v>0.001285347043701747</v>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -39289,6 +42127,12 @@
       <c r="Z473" s="2" t="n">
         <v>0.002554744525547366</v>
       </c>
+      <c r="AA473" s="1" t="n">
+        <v>0.274</v>
+      </c>
+      <c r="AB473" s="3" t="n">
+        <v>-0.002548234437568178</v>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
@@ -39371,6 +42215,12 @@
       <c r="Z474" s="2" t="n">
         <v>0.001370488807674681</v>
       </c>
+      <c r="AA474" s="1" t="n">
+        <v>0.04388</v>
+      </c>
+      <c r="AB474" s="2" t="n">
+        <v>0.0009124087591242088</v>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
@@ -39453,6 +42303,12 @@
       <c r="Z475" s="2" t="n">
         <v>0.00224905303030302</v>
       </c>
+      <c r="AA475" s="1" t="n">
+        <v>0.008446</v>
+      </c>
+      <c r="AB475" s="3" t="n">
+        <v>-0.002480217314278987</v>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
@@ -39535,6 +42391,12 @@
       <c r="Z476" s="2" t="n">
         <v>0.009073075036782794</v>
       </c>
+      <c r="AA476" s="1" t="n">
+        <v>0.08195</v>
+      </c>
+      <c r="AB476" s="3" t="n">
+        <v>-0.004252733900364558</v>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
@@ -39617,6 +42479,12 @@
       <c r="Z477" s="2" t="n">
         <v>0.004428044280442726</v>
       </c>
+      <c r="AA477" s="1" t="n">
+        <v>0.1357</v>
+      </c>
+      <c r="AB477" s="3" t="n">
+        <v>-0.002939015429831091</v>
+      </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
@@ -39699,6 +42567,12 @@
       <c r="Z478" s="2" t="n">
         <v>0.005805148914689612</v>
       </c>
+      <c r="AA478" s="1" t="n">
+        <v>0.4006</v>
+      </c>
+      <c r="AB478" s="2" t="n">
+        <v>0.005269761606022562</v>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
@@ -39781,6 +42655,12 @@
       <c r="Z479" s="2" t="n">
         <v>0.003842571029343275</v>
       </c>
+      <c r="AA479" s="1" t="n">
+        <v>0.008425999999999999</v>
+      </c>
+      <c r="AB479" s="3" t="n">
+        <v>-0.02261918570931455</v>
+      </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
@@ -39863,6 +42743,12 @@
       <c r="Z480" s="2" t="n">
         <v>0.009445843828715418</v>
       </c>
+      <c r="AA480" s="1" t="n">
+        <v>0.0167</v>
+      </c>
+      <c r="AB480" s="2" t="n">
+        <v>0.041796631316282</v>
+      </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
@@ -39945,6 +42831,12 @@
       <c r="Z481" s="2" t="n">
         <v>0.002045512656609657</v>
       </c>
+      <c r="AA481" s="1" t="n">
+        <v>0.07825</v>
+      </c>
+      <c r="AB481" s="3" t="n">
+        <v>-0.001658586374075084</v>
+      </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
@@ -40027,6 +42919,12 @@
       <c r="Z482" s="2" t="n">
         <v>0.005174129353233758</v>
       </c>
+      <c r="AA482" s="1" t="n">
+        <v>0.05031</v>
+      </c>
+      <c r="AB482" s="3" t="n">
+        <v>-0.003959611958028089</v>
+      </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
@@ -40109,6 +43007,12 @@
       <c r="Z483" s="2" t="n">
         <v>0.002063983488132011</v>
       </c>
+      <c r="AA483" s="1" t="n">
+        <v>0.00966</v>
+      </c>
+      <c r="AB483" s="3" t="n">
+        <v>-0.005149330587023656</v>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
@@ -40191,6 +43095,12 @@
       <c r="Z484" s="2" t="n">
         <v>0.002358838272150869</v>
       </c>
+      <c r="AA484" s="1" t="n">
+        <v>0.06787</v>
+      </c>
+      <c r="AB484" s="3" t="n">
+        <v>-0.001764965436093471</v>
+      </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
@@ -40273,6 +43183,12 @@
       <c r="Z485" s="2" t="n">
         <v>0.00398494576046058</v>
       </c>
+      <c r="AA485" s="1" t="n">
+        <v>0.0004497</v>
+      </c>
+      <c r="AB485" s="3" t="n">
+        <v>-0.00837927232635069</v>
+      </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
@@ -40355,6 +43271,12 @@
       <c r="Z486" s="3" t="n">
         <v>-0.0001261034047918805</v>
       </c>
+      <c r="AA486" s="1" t="n">
+        <v>0.07926</v>
+      </c>
+      <c r="AB486" s="3" t="n">
+        <v>-0.0003783579265985906</v>
+      </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
@@ -40437,6 +43359,12 @@
       <c r="Z487" s="2" t="n">
         <v>0.002886836027713539</v>
       </c>
+      <c r="AA487" s="1" t="n">
+        <v>0.0001737</v>
+      </c>
+      <c r="AB487" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
@@ -40519,6 +43447,12 @@
       <c r="Z488" s="3" t="n">
         <v>-0.00100222717149228</v>
       </c>
+      <c r="AA488" s="1" t="n">
+        <v>0.09007</v>
+      </c>
+      <c r="AB488" s="2" t="n">
+        <v>0.004012930554007348</v>
+      </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
@@ -40601,6 +43535,12 @@
       <c r="Z489" s="2" t="n">
         <v>0.005660377358490554</v>
       </c>
+      <c r="AA489" s="1" t="n">
+        <v>0.04821</v>
+      </c>
+      <c r="AB489" s="2" t="n">
+        <v>0.005003126954346552</v>
+      </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
@@ -40683,6 +43623,12 @@
       <c r="Z490" s="2" t="n">
         <v>0.007433991284286044</v>
       </c>
+      <c r="AA490" s="1" t="n">
+        <v>0.03969</v>
+      </c>
+      <c r="AB490" s="2" t="n">
+        <v>0.009923664122137441</v>
+      </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
@@ -40765,6 +43711,12 @@
       <c r="Z491" s="2" t="n">
         <v>0.0451137374507561</v>
       </c>
+      <c r="AA491" s="1" t="n">
+        <v>0.08043</v>
+      </c>
+      <c r="AB491" s="3" t="n">
+        <v>-0.02200875486381314</v>
+      </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
@@ -40847,6 +43799,12 @@
       <c r="Z492" s="3" t="n">
         <v>-0.002058264724509045</v>
       </c>
+      <c r="AA492" s="1" t="n">
+        <v>0.06331000000000001</v>
+      </c>
+      <c r="AB492" s="2" t="n">
+        <v>0.004442329049658932</v>
+      </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
@@ -40929,6 +43887,12 @@
       <c r="Z493" s="2" t="n">
         <v>0.003838771593090221</v>
       </c>
+      <c r="AA493" s="1" t="n">
+        <v>0.00522</v>
+      </c>
+      <c r="AB493" s="3" t="n">
+        <v>-0.001912045889101426</v>
+      </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
@@ -41011,6 +43975,12 @@
       <c r="Z494" s="2" t="n">
         <v>0.001454016721192335</v>
       </c>
+      <c r="AA494" s="1" t="n">
+        <v>0.2746</v>
+      </c>
+      <c r="AB494" s="3" t="n">
+        <v>-0.003266787658802221</v>
+      </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
@@ -41093,6 +44063,12 @@
       <c r="Z495" s="2" t="n">
         <v>0.003765296517100568</v>
       </c>
+      <c r="AA495" s="1" t="n">
+        <v>0.0638</v>
+      </c>
+      <c r="AB495" s="3" t="n">
+        <v>-0.002813379180994055</v>
+      </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
@@ -41175,6 +44151,12 @@
       <c r="Z496" s="2" t="n">
         <v>0.001363326516700789</v>
       </c>
+      <c r="AA496" s="1" t="n">
+        <v>0.2934</v>
+      </c>
+      <c r="AB496" s="3" t="n">
+        <v>-0.0013614703880191</v>
+      </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
@@ -41257,6 +44239,12 @@
       <c r="Z497" s="3" t="n">
         <v>-0.0002510355215263728</v>
       </c>
+      <c r="AA497" s="1" t="n">
+        <v>0.0785</v>
+      </c>
+      <c r="AB497" s="3" t="n">
+        <v>-0.01443816698053984</v>
+      </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
@@ -41339,6 +44327,12 @@
       <c r="Z498" s="2" t="n">
         <v>0.004863813229571989</v>
       </c>
+      <c r="AA498" s="1" t="n">
+        <v>0.1029</v>
+      </c>
+      <c r="AB498" s="3" t="n">
+        <v>-0.003872216844143248</v>
+      </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
@@ -41421,6 +44415,12 @@
       <c r="Z499" s="2" t="n">
         <v>0.004790419161676617</v>
       </c>
+      <c r="AA499" s="1" t="n">
+        <v>0.04182</v>
+      </c>
+      <c r="AB499" s="3" t="n">
+        <v>-0.003098927294398049</v>
+      </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
@@ -41503,6 +44503,12 @@
       <c r="Z500" s="2" t="n">
         <v>0.005235602094240884</v>
       </c>
+      <c r="AA500" s="1" t="n">
+        <v>0.04016</v>
+      </c>
+      <c r="AB500" s="3" t="n">
+        <v>-0.003968253968253978</v>
+      </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
@@ -41585,6 +44591,12 @@
       <c r="Z501" s="2" t="n">
         <v>0.006079027355623134</v>
       </c>
+      <c r="AA501" s="1" t="n">
+        <v>0.0992</v>
+      </c>
+      <c r="AB501" s="3" t="n">
+        <v>-0.001007049345417954</v>
+      </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
@@ -41667,6 +44679,12 @@
       <c r="Z502" s="3" t="n">
         <v>-0.0009052504526252155</v>
       </c>
+      <c r="AA502" s="1" t="n">
+        <v>0.003319</v>
+      </c>
+      <c r="AB502" s="2" t="n">
+        <v>0.002416188462700018</v>
+      </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
@@ -41749,6 +44767,12 @@
       <c r="Z503" s="2" t="n">
         <v>0.00328587075575033</v>
       </c>
+      <c r="AA503" s="1" t="n">
+        <v>0.009129999999999999</v>
+      </c>
+      <c r="AB503" s="3" t="n">
+        <v>-0.003275109170305733</v>
+      </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
@@ -41831,6 +44855,12 @@
       <c r="Z504" s="2" t="n">
         <v>0.005671077504725798</v>
       </c>
+      <c r="AA504" s="1" t="n">
+        <v>0.1594</v>
+      </c>
+      <c r="AB504" s="3" t="n">
+        <v>-0.001253132832080236</v>
+      </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
@@ -41913,6 +44943,12 @@
       <c r="Z505" s="2" t="n">
         <v>0.003810975609756101</v>
       </c>
+      <c r="AA505" s="1" t="n">
+        <v>0.1317</v>
+      </c>
+      <c r="AB505" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
@@ -41995,6 +45031,12 @@
       <c r="Z506" s="2" t="n">
         <v>0.01126259632483694</v>
       </c>
+      <c r="AA506" s="1" t="n">
+        <v>0.01714</v>
+      </c>
+      <c r="AB506" s="2" t="n">
+        <v>0.004689331770222756</v>
+      </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
@@ -42077,6 +45119,12 @@
       <c r="Z507" s="3" t="n">
         <v>-0.0007002801120447591</v>
       </c>
+      <c r="AA507" s="1" t="n">
+        <v>0.00286</v>
+      </c>
+      <c r="AB507" s="2" t="n">
+        <v>0.002102312543798153</v>
+      </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
@@ -42159,6 +45207,12 @@
       <c r="Z508" s="2" t="n">
         <v>0.005009107468123714</v>
       </c>
+      <c r="AA508" s="1" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AB508" s="2" t="n">
+        <v>0.001359311282283695</v>
+      </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
@@ -42241,6 +45295,12 @@
       <c r="Z509" s="2" t="n">
         <v>0.004924311508298492</v>
       </c>
+      <c r="AA509" s="1" t="n">
+        <v>0.05498</v>
+      </c>
+      <c r="AB509" s="3" t="n">
+        <v>-0.002177858439201489</v>
+      </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
@@ -42323,6 +45383,12 @@
       <c r="Z510" s="2" t="n">
         <v>0.002725724020442937</v>
       </c>
+      <c r="AA510" s="1" t="n">
+        <v>0.02936</v>
+      </c>
+      <c r="AB510" s="3" t="n">
+        <v>-0.002378525314305152</v>
+      </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
@@ -42405,6 +45471,12 @@
       <c r="Z511" s="2" t="n">
         <v>0.001983143282102051</v>
       </c>
+      <c r="AA511" s="1" t="n">
+        <v>0.04036</v>
+      </c>
+      <c r="AB511" s="3" t="n">
+        <v>-0.00148441365660558</v>
+      </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
@@ -42487,6 +45559,12 @@
       <c r="Z512" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AA512" s="1" t="n">
+        <v>0.092</v>
+      </c>
+      <c r="AB512" s="2" t="n">
+        <v>0.0454545454545455</v>
+      </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
@@ -42569,6 +45647,12 @@
       <c r="Z513" s="3" t="n">
         <v>-0.007066195586960882</v>
       </c>
+      <c r="AA513" s="1" t="n">
+        <v>0.014996</v>
+      </c>
+      <c r="AB513" s="2" t="n">
+        <v>0.006780798925814058</v>
+      </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
@@ -42651,6 +45735,12 @@
       <c r="Z514" s="2" t="n">
         <v>0.006318207926478977</v>
       </c>
+      <c r="AA514" s="1" t="n">
+        <v>0.1747</v>
+      </c>
+      <c r="AB514" s="3" t="n">
+        <v>-0.002853881278538815</v>
+      </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
@@ -42733,6 +45823,12 @@
       <c r="Z515" s="2" t="n">
         <v>0.004651162790697679</v>
       </c>
+      <c r="AA515" s="1" t="n">
+        <v>0.1076</v>
+      </c>
+      <c r="AB515" s="3" t="n">
+        <v>-0.003703703703703681</v>
+      </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
@@ -42815,6 +45911,12 @@
       <c r="Z516" s="2" t="n">
         <v>0.007490636704119869</v>
       </c>
+      <c r="AA516" s="1" t="n">
+        <v>0.00267</v>
+      </c>
+      <c r="AB516" s="3" t="n">
+        <v>-0.007434944237918235</v>
+      </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
@@ -42897,6 +45999,12 @@
       <c r="Z517" s="2" t="n">
         <v>0.005330906254063222</v>
       </c>
+      <c r="AA517" s="1" t="n">
+        <v>0.007674</v>
+      </c>
+      <c r="AB517" s="3" t="n">
+        <v>-0.007501293326435578</v>
+      </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
@@ -42979,6 +46087,12 @@
       <c r="Z518" s="2" t="n">
         <v>0.07310870947234573</v>
       </c>
+      <c r="AA518" s="1" t="n">
+        <v>0.01641</v>
+      </c>
+      <c r="AB518" s="3" t="n">
+        <v>-0.02784360189573449</v>
+      </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
@@ -43061,6 +46175,12 @@
       <c r="Z519" s="3" t="n">
         <v>-0.001662312989788663</v>
       </c>
+      <c r="AA519" s="1" t="n">
+        <v>0.004213</v>
+      </c>
+      <c r="AB519" s="2" t="n">
+        <v>0.002140818268315761</v>
+      </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
@@ -43143,6 +46263,12 @@
       <c r="Z520" s="2" t="n">
         <v>0.004317789291882567</v>
       </c>
+      <c r="AA520" s="1" t="n">
+        <v>0.001162</v>
+      </c>
+      <c r="AB520" s="3" t="n">
+        <v>-0.0008598452278589131</v>
+      </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
@@ -43225,6 +46351,12 @@
       <c r="Z521" s="2" t="n">
         <v>0.003000750187546895</v>
       </c>
+      <c r="AA521" s="1" t="n">
+        <v>0.01332</v>
+      </c>
+      <c r="AB521" s="3" t="n">
+        <v>-0.003739715781600576</v>
+      </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
@@ -43307,6 +46439,12 @@
       <c r="Z522" s="2" t="n">
         <v>0.0004364906154517197</v>
       </c>
+      <c r="AA522" s="1" t="n">
+        <v>0.6868</v>
+      </c>
+      <c r="AB522" s="3" t="n">
+        <v>-0.001163467132053553</v>
+      </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
@@ -43389,6 +46527,12 @@
       <c r="Z523" s="2" t="n">
         <v>0.004588471465443086</v>
       </c>
+      <c r="AA523" s="1" t="n">
+        <v>0.0701</v>
+      </c>
+      <c r="AB523" s="2" t="n">
+        <v>0.0005709391949757118</v>
+      </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
@@ -43471,6 +46615,12 @@
       <c r="Z524" s="2" t="n">
         <v>0.002570694087403643</v>
       </c>
+      <c r="AA524" s="1" t="n">
+        <v>0.01174</v>
+      </c>
+      <c r="AB524" s="2" t="n">
+        <v>0.003418803418803427</v>
+      </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
@@ -43553,6 +46703,12 @@
       <c r="Z525" s="2" t="n">
         <v>0.00305064063453334</v>
       </c>
+      <c r="AA525" s="1" t="n">
+        <v>0.01646</v>
+      </c>
+      <c r="AB525" s="2" t="n">
+        <v>0.0012165450121654</v>
+      </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
@@ -43635,6 +46791,12 @@
       <c r="Z526" s="2" t="n">
         <v>0.0007442691277165003</v>
       </c>
+      <c r="AA526" s="1" t="n">
+        <v>0.13417</v>
+      </c>
+      <c r="AB526" s="3" t="n">
+        <v>-0.002156775249144613</v>
+      </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
@@ -43717,6 +46879,12 @@
       <c r="Z527" s="2" t="n">
         <v>0.002795899347623533</v>
       </c>
+      <c r="AA527" s="1" t="n">
+        <v>0.04298</v>
+      </c>
+      <c r="AB527" s="3" t="n">
+        <v>-0.00139405204460977</v>
+      </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
@@ -43799,6 +46967,12 @@
       <c r="Z528" s="2" t="n">
         <v>0.003297911322828919</v>
       </c>
+      <c r="AA528" s="1" t="n">
+        <v>0.274</v>
+      </c>
+      <c r="AB528" s="2" t="n">
+        <v>0.0007304601899197717</v>
+      </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
@@ -43881,6 +47055,12 @@
       <c r="Z529" s="2" t="n">
         <v>0.006361499101092524</v>
       </c>
+      <c r="AA529" s="1" t="n">
+        <v>0.0007265</v>
+      </c>
+      <c r="AB529" s="3" t="n">
+        <v>-0.001649031194173314</v>
+      </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
@@ -43963,6 +47143,12 @@
       <c r="Z530" s="2" t="n">
         <v>0.002397506593143033</v>
       </c>
+      <c r="AA530" s="1" t="n">
+        <v>0.004176</v>
+      </c>
+      <c r="AB530" s="3" t="n">
+        <v>-0.001195886151638315</v>
+      </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
@@ -44045,6 +47231,12 @@
       <c r="Z531" s="2" t="n">
         <v>0.0007598784194528038</v>
       </c>
+      <c r="AA531" s="1" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="AB531" s="3" t="n">
+        <v>-0.003796507213363625</v>
+      </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
@@ -44127,6 +47319,12 @@
       <c r="Z532" s="2" t="n">
         <v>0.003398470688190294</v>
       </c>
+      <c r="AA532" s="1" t="n">
+        <v>0.118</v>
+      </c>
+      <c r="AB532" s="3" t="n">
+        <v>-0.0008467400508044273</v>
+      </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
@@ -44209,6 +47407,12 @@
       <c r="Z533" s="2" t="n">
         <v>0.002987861811391231</v>
       </c>
+      <c r="AA533" s="1" t="n">
+        <v>0.05341</v>
+      </c>
+      <c r="AB533" s="3" t="n">
+        <v>-0.005585552038726525</v>
+      </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
@@ -44291,6 +47495,12 @@
       <c r="Z534" s="2" t="n">
         <v>0.003335557038025353</v>
       </c>
+      <c r="AA534" s="1" t="n">
+        <v>0.1504</v>
+      </c>
+      <c r="AB534" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
@@ -44373,6 +47583,12 @@
       <c r="Z535" s="2" t="n">
         <v>0.008187134502923845</v>
       </c>
+      <c r="AA535" s="1" t="n">
+        <v>0.01732</v>
+      </c>
+      <c r="AB535" s="2" t="n">
+        <v>0.004640371229698389</v>
+      </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
@@ -44455,6 +47671,12 @@
       <c r="Z536" s="2" t="n">
         <v>0.0007988815658078017</v>
       </c>
+      <c r="AA536" s="1" t="n">
+        <v>0.005004</v>
+      </c>
+      <c r="AB536" s="3" t="n">
+        <v>-0.001396926761125536</v>
+      </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
@@ -44537,6 +47759,12 @@
       <c r="Z537" s="2" t="n">
         <v>0.005492619292825233</v>
       </c>
+      <c r="AA537" s="1" t="n">
+        <v>0.2919</v>
+      </c>
+      <c r="AB537" s="3" t="n">
+        <v>-0.003414134516899969</v>
+      </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
@@ -44619,6 +47847,12 @@
       <c r="Z538" s="2" t="n">
         <v>0.006028636021100242</v>
       </c>
+      <c r="AA538" s="1" t="n">
+        <v>0.01328</v>
+      </c>
+      <c r="AB538" s="3" t="n">
+        <v>-0.005243445692883941</v>
+      </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
@@ -44701,6 +47935,12 @@
       <c r="Z539" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AA539" s="1" t="n">
+        <v>0.02517</v>
+      </c>
+      <c r="AB539" s="3" t="n">
+        <v>-0.003168316831683176</v>
+      </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
@@ -44783,6 +48023,12 @@
       <c r="Z540" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AA540" s="1" t="n">
+        <v>0.05683</v>
+      </c>
+      <c r="AB540" s="2" t="n">
+        <v>0.00017599436818015</v>
+      </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
@@ -44865,6 +48111,12 @@
       <c r="Z541" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AA541" s="1" t="n">
+        <v>0.0116</v>
+      </c>
+      <c r="AB541" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
@@ -44947,6 +48199,12 @@
       <c r="Z542" s="2" t="n">
         <v>0.009009009009008922</v>
       </c>
+      <c r="AA542" s="1" t="n">
+        <v>1.11e-05</v>
+      </c>
+      <c r="AB542" s="3" t="n">
+        <v>-0.008928571428571343</v>
+      </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
@@ -45028,6 +48286,12 @@
       </c>
       <c r="Z543" s="2" t="n">
         <v>0.002178056084944122</v>
+      </c>
+      <c r="AA543" s="1" t="n">
+        <v>0.003679</v>
+      </c>
+      <c r="AB543" s="3" t="n">
+        <v>-0.0005433306166802043</v>
       </c>
     </row>
   </sheetData>

--- a/binance-usdt-perpetual-data/weeks/2026-03-09_2026-03-15/2026-03-12.xlsx
+++ b/binance-usdt-perpetual-data/weeks/2026-03-09_2026-03-15/2026-03-12.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD543"/>
+  <dimension ref="A1:AF543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -456,6 +456,8 @@
     <col width="18" customWidth="1" min="28" max="28"/>
     <col width="13" customWidth="1" min="29" max="29"/>
     <col width="18" customWidth="1" min="30" max="30"/>
+    <col width="13" customWidth="1" min="31" max="31"/>
+    <col width="18" customWidth="1" min="32" max="32"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -609,6 +611,16 @@
           <t>change_03:30</t>
         </is>
       </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>price_03:45</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>change_03:45</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -703,6 +715,12 @@
       <c r="AD2" s="2" t="n">
         <v>0.0007467973609372628</v>
       </c>
+      <c r="AE2" s="1" t="n">
+        <v>70644.60000000001</v>
+      </c>
+      <c r="AF2" s="2" t="n">
+        <v>0.002240138919824715</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -797,6 +815,12 @@
       <c r="AD3" s="2" t="n">
         <v>0.0003235964607241185</v>
       </c>
+      <c r="AE3" s="1" t="n">
+        <v>2073.57</v>
+      </c>
+      <c r="AF3" s="2" t="n">
+        <v>0.001168432996161588</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -891,6 +915,12 @@
       <c r="AD4" s="3" t="n">
         <v>-0.001260167258563403</v>
       </c>
+      <c r="AE4" s="1" t="n">
+        <v>87.26000000000001</v>
+      </c>
+      <c r="AF4" s="2" t="n">
+        <v>0.0009176416609313866</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -985,6 +1015,12 @@
       <c r="AD5" s="3" t="n">
         <v>-0.002890800028908008</v>
       </c>
+      <c r="AE5" s="1" t="n">
+        <v>0.01379</v>
+      </c>
+      <c r="AF5" s="3" t="n">
+        <v>-0.0005073566717402378</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1079,6 +1115,12 @@
       <c r="AD6" s="3" t="n">
         <v>-0.003499469777306437</v>
       </c>
+      <c r="AE6" s="1" t="n">
+        <v>0.09385</v>
+      </c>
+      <c r="AF6" s="3" t="n">
+        <v>-0.001277003298925137</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1173,6 +1215,12 @@
       <c r="AD7" s="3" t="n">
         <v>-0.003150733977801777</v>
       </c>
+      <c r="AE7" s="1" t="n">
+        <v>1.3913</v>
+      </c>
+      <c r="AF7" s="3" t="n">
+        <v>-0.0005746713598160419</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1267,6 +1315,12 @@
       <c r="AD8" s="2" t="n">
         <v>0.001107971857514993</v>
       </c>
+      <c r="AE8" s="1" t="n">
+        <v>36.189</v>
+      </c>
+      <c r="AF8" s="2" t="n">
+        <v>0.001300426097061508</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1361,6 +1415,12 @@
       <c r="AD9" s="3" t="n">
         <v>-0.0001073883161512795</v>
       </c>
+      <c r="AE9" s="1" t="n">
+        <v>653.3</v>
+      </c>
+      <c r="AF9" s="2" t="n">
+        <v>0.002347453856421702</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1455,6 +1515,12 @@
       <c r="AD10" s="3" t="n">
         <v>-0.007137809187279213</v>
       </c>
+      <c r="AE10" s="1" t="n">
+        <v>14.128</v>
+      </c>
+      <c r="AF10" s="2" t="n">
+        <v>0.005623176026763516</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1549,6 +1615,12 @@
       <c r="AD11" s="2" t="n">
         <v>0.005081874647091963</v>
       </c>
+      <c r="AE11" s="1" t="n">
+        <v>214.33</v>
+      </c>
+      <c r="AF11" s="2" t="n">
+        <v>0.003417602996254767</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1643,6 +1715,12 @@
       <c r="AD12" s="3" t="n">
         <v>-0.002371354043158701</v>
       </c>
+      <c r="AE12" s="1" t="n">
+        <v>0.0033682</v>
+      </c>
+      <c r="AF12" s="2" t="n">
+        <v>0.0007725219871643011</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1737,6 +1815,12 @@
       <c r="AD13" s="2" t="n">
         <v>0.001999999999999919</v>
       </c>
+      <c r="AE13" s="1" t="n">
+        <v>0.04016</v>
+      </c>
+      <c r="AF13" s="2" t="n">
+        <v>0.001996007984032028</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1831,6 +1915,12 @@
       <c r="AD14" s="2" t="n">
         <v>0.003407800075728851</v>
       </c>
+      <c r="AE14" s="1" t="n">
+        <v>2.656</v>
+      </c>
+      <c r="AF14" s="2" t="n">
+        <v>0.002264150943396312</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1925,6 +2015,12 @@
       <c r="AD15" s="2" t="n">
         <v>0.005667442566541898</v>
       </c>
+      <c r="AE15" s="1" t="n">
+        <v>0.9976</v>
+      </c>
+      <c r="AF15" s="2" t="n">
+        <v>0.00392472577236592</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2019,6 +2115,12 @@
       <c r="AD16" s="3" t="n">
         <v>-0.009324419422941637</v>
       </c>
+      <c r="AE16" s="1" t="n">
+        <v>0.05632</v>
+      </c>
+      <c r="AF16" s="2" t="n">
+        <v>0.000177588350204281</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2113,6 +2215,12 @@
       <c r="AD17" s="2" t="n">
         <v>0.002249718785151858</v>
       </c>
+      <c r="AE17" s="1" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AF17" s="3" t="n">
+        <v>-0.00112233445566779</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2207,6 +2315,12 @@
       <c r="AD18" s="3" t="n">
         <v>-0.001504324934185827</v>
       </c>
+      <c r="AE18" s="1" t="n">
+        <v>0.2658</v>
+      </c>
+      <c r="AF18" s="2" t="n">
+        <v>0.001129943502824734</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2301,6 +2415,12 @@
       <c r="AD19" s="3" t="n">
         <v>-0.01848591549295776</v>
       </c>
+      <c r="AE19" s="1" t="n">
+        <v>0.35522</v>
+      </c>
+      <c r="AF19" s="3" t="n">
+        <v>-0.004428251121076305</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2395,6 +2515,12 @@
       <c r="AD20" s="2" t="n">
         <v>0.0001030290541934084</v>
       </c>
+      <c r="AE20" s="1" t="n">
+        <v>9.706</v>
+      </c>
+      <c r="AF20" s="3" t="n">
+        <v>-0.0001030184403009397</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2489,6 +2615,12 @@
       <c r="AD21" s="2" t="n">
         <v>0.004887049319303794</v>
       </c>
+      <c r="AE21" s="1" t="n">
+        <v>202.88</v>
+      </c>
+      <c r="AF21" s="2" t="n">
+        <v>0.006798670041189046</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2583,6 +2715,12 @@
       <c r="AD22" s="2" t="n">
         <v>0.01078979343863912</v>
       </c>
+      <c r="AE22" s="1" t="n">
+        <v>0.020447</v>
+      </c>
+      <c r="AF22" s="3" t="n">
+        <v>-0.01682935038707504</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2677,6 +2815,12 @@
       <c r="AD23" s="2" t="n">
         <v>0.001556096171126825</v>
       </c>
+      <c r="AE23" s="1" t="n">
+        <v>457.84</v>
+      </c>
+      <c r="AF23" s="2" t="n">
+        <v>0.001881920434154573</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2771,6 +2915,12 @@
       <c r="AD24" s="2" t="n">
         <v>0.0007560917597600336</v>
       </c>
+      <c r="AE24" s="1" t="n">
+        <v>5177.71</v>
+      </c>
+      <c r="AF24" s="2" t="n">
+        <v>0.0004772725516111822</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2865,6 +3015,12 @@
       <c r="AD25" s="2" t="n">
         <v>0.0009926105657880602</v>
       </c>
+      <c r="AE25" s="1" t="n">
+        <v>9.093</v>
+      </c>
+      <c r="AF25" s="2" t="n">
+        <v>0.001873071837813955</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2959,6 +3115,12 @@
       <c r="AD26" s="2" t="n">
         <v>0.007278507487659966</v>
       </c>
+      <c r="AE26" s="1" t="n">
+        <v>0.11931</v>
+      </c>
+      <c r="AF26" s="3" t="n">
+        <v>-0.009053156146179351</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3053,6 +3215,12 @@
       <c r="AD27" s="3" t="n">
         <v>-0.01101694915254237</v>
       </c>
+      <c r="AE27" s="1" t="n">
+        <v>0.01162</v>
+      </c>
+      <c r="AF27" s="3" t="n">
+        <v>-0.004284490145672639</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3147,6 +3315,12 @@
       <c r="AD28" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AE28" s="1" t="n">
+        <v>1.296</v>
+      </c>
+      <c r="AF28" s="2" t="n">
+        <v>0.004651162790697679</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3241,6 +3415,12 @@
       <c r="AD29" s="3" t="n">
         <v>-0.007601351351351452</v>
       </c>
+      <c r="AE29" s="1" t="n">
+        <v>0.05831</v>
+      </c>
+      <c r="AF29" s="3" t="n">
+        <v>-0.007489361702127591</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3335,6 +3515,12 @@
       <c r="AD30" s="2" t="n">
         <v>0.002605863192182413</v>
       </c>
+      <c r="AE30" s="1" t="n">
+        <v>1.544</v>
+      </c>
+      <c r="AF30" s="2" t="n">
+        <v>0.00324886289798578</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3429,6 +3615,12 @@
       <c r="AD31" s="3" t="n">
         <v>-0.0004970178926439856</v>
       </c>
+      <c r="AE31" s="1" t="n">
+        <v>0.002024</v>
+      </c>
+      <c r="AF31" s="2" t="n">
+        <v>0.006464445549477866</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3523,6 +3715,12 @@
       <c r="AD32" s="3" t="n">
         <v>-0.002974714923153249</v>
       </c>
+      <c r="AE32" s="1" t="n">
+        <v>0.04024</v>
+      </c>
+      <c r="AF32" s="2" t="n">
+        <v>0.0004972650422675084</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3617,6 +3815,12 @@
       <c r="AD33" s="3" t="n">
         <v>-0.001013171225937213</v>
       </c>
+      <c r="AE33" s="1" t="n">
+        <v>0.0985</v>
+      </c>
+      <c r="AF33" s="3" t="n">
+        <v>-0.001014198782961349</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3711,6 +3915,12 @@
       <c r="AD34" s="3" t="n">
         <v>-0.0009487666034154554</v>
       </c>
+      <c r="AE34" s="1" t="n">
+        <v>0.1057</v>
+      </c>
+      <c r="AF34" s="2" t="n">
+        <v>0.003798670465337109</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3805,6 +4015,12 @@
       <c r="AD35" s="3" t="n">
         <v>-0.005500550055005658</v>
       </c>
+      <c r="AE35" s="1" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="AF35" s="3" t="n">
+        <v>-0.004424778761061959</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3899,6 +4115,12 @@
       <c r="AD36" s="2" t="n">
         <v>0.000279251605696857</v>
       </c>
+      <c r="AE36" s="1" t="n">
+        <v>0.3589</v>
+      </c>
+      <c r="AF36" s="2" t="n">
+        <v>0.001954215522054658</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3993,6 +4215,12 @@
       <c r="AD37" s="3" t="n">
         <v>-0.001031282227569599</v>
       </c>
+      <c r="AE37" s="1" t="n">
+        <v>0.005808</v>
+      </c>
+      <c r="AF37" s="3" t="n">
+        <v>-0.000688231245698646</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -4087,6 +4315,12 @@
       <c r="AD38" s="3" t="n">
         <v>-0.001540120129370135</v>
       </c>
+      <c r="AE38" s="1" t="n">
+        <v>0.25983</v>
+      </c>
+      <c r="AF38" s="2" t="n">
+        <v>0.001966682091624288</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -4181,6 +4415,12 @@
       <c r="AD39" s="3" t="n">
         <v>-0.004333267677762554</v>
       </c>
+      <c r="AE39" s="1" t="n">
+        <v>0.05059</v>
+      </c>
+      <c r="AF39" s="2" t="n">
+        <v>0.0007912957467854661</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -4275,6 +4515,12 @@
       <c r="AD40" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AE40" s="1" t="n">
+        <v>0.14943</v>
+      </c>
+      <c r="AF40" s="2" t="n">
+        <v>0.0009377721213745142</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -4369,6 +4615,12 @@
       <c r="AD41" s="2" t="n">
         <v>0.0005903187721370528</v>
       </c>
+      <c r="AE41" s="1" t="n">
+        <v>0.1697</v>
+      </c>
+      <c r="AF41" s="2" t="n">
+        <v>0.001179941002949722</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -4463,6 +4715,12 @@
       <c r="AD42" s="2" t="n">
         <v>0.00232205054925431</v>
       </c>
+      <c r="AE42" s="1" t="n">
+        <v>112.49</v>
+      </c>
+      <c r="AF42" s="2" t="n">
+        <v>0.002316671121803358</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -4557,6 +4815,12 @@
       <c r="AD43" s="3" t="n">
         <v>-0.02219233355749837</v>
       </c>
+      <c r="AE43" s="1" t="n">
+        <v>0.8626</v>
+      </c>
+      <c r="AF43" s="3" t="n">
+        <v>-0.01123337918386052</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -4651,6 +4915,12 @@
       <c r="AD44" s="2" t="n">
         <v>0.0010917030567686</v>
       </c>
+      <c r="AE44" s="1" t="n">
+        <v>55.04</v>
+      </c>
+      <c r="AF44" s="2" t="n">
+        <v>0.0003635041802980011</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -4745,6 +5015,12 @@
       <c r="AD45" s="2" t="n">
         <v>0.005084256138661485</v>
       </c>
+      <c r="AE45" s="1" t="n">
+        <v>0.5260899999999999</v>
+      </c>
+      <c r="AF45" s="2" t="n">
+        <v>0.008047672881258468</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -4839,6 +5115,12 @@
       <c r="AD46" s="2" t="n">
         <v>0.003153217715350408</v>
       </c>
+      <c r="AE46" s="1" t="n">
+        <v>0.6997</v>
+      </c>
+      <c r="AF46" s="3" t="n">
+        <v>-0.0002857551078725217</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -4933,6 +5215,12 @@
       <c r="AD47" s="2" t="n">
         <v>0.002295332823259459</v>
       </c>
+      <c r="AE47" s="1" t="n">
+        <v>3.936</v>
+      </c>
+      <c r="AF47" s="2" t="n">
+        <v>0.001526717557251853</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -5027,6 +5315,12 @@
       <c r="AD48" s="3" t="n">
         <v>-0.001248205704300104</v>
       </c>
+      <c r="AE48" s="1" t="n">
+        <v>0.15995</v>
+      </c>
+      <c r="AF48" s="3" t="n">
+        <v>-0.0004999062675748094</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -5121,6 +5415,12 @@
       <c r="AD49" s="3" t="n">
         <v>-0.005992873339812152</v>
       </c>
+      <c r="AE49" s="1" t="n">
+        <v>0.06124</v>
+      </c>
+      <c r="AF49" s="3" t="n">
+        <v>-0.00211829884308291</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -5215,6 +5515,12 @@
       <c r="AD50" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AE50" s="1" t="n">
+        <v>0.039</v>
+      </c>
+      <c r="AF50" s="2" t="n">
+        <v>0.002570694087403673</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -5309,6 +5615,12 @@
       <c r="AD51" s="2" t="n">
         <v>0.008719627778735056</v>
       </c>
+      <c r="AE51" s="1" t="n">
+        <v>0.28494</v>
+      </c>
+      <c r="AF51" s="3" t="n">
+        <v>-0.02644526445264442</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -5403,6 +5715,12 @@
       <c r="AD52" s="2" t="n">
         <v>0.006160164271047119</v>
       </c>
+      <c r="AE52" s="1" t="n">
+        <v>0.2941</v>
+      </c>
+      <c r="AF52" s="2" t="n">
+        <v>0.0003401360544217313</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -5497,6 +5815,12 @@
       <c r="AD53" s="2" t="n">
         <v>0.0006285355122565478</v>
       </c>
+      <c r="AE53" s="1" t="n">
+        <v>0.1604</v>
+      </c>
+      <c r="AF53" s="2" t="n">
+        <v>0.007537688442210922</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -5591,6 +5915,12 @@
       <c r="AD54" s="2" t="n">
         <v>0.0002070036225634104</v>
       </c>
+      <c r="AE54" s="1" t="n">
+        <v>0.28999</v>
+      </c>
+      <c r="AF54" s="2" t="n">
+        <v>0.0002759477079094357</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -5685,6 +6015,12 @@
       <c r="AD55" s="3" t="n">
         <v>-0.0009801176141137023</v>
       </c>
+      <c r="AE55" s="1" t="n">
+        <v>0.007144</v>
+      </c>
+      <c r="AF55" s="2" t="n">
+        <v>0.001261387526278953</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -5779,6 +6115,12 @@
       <c r="AD56" s="3" t="n">
         <v>-0.004940014114326085</v>
       </c>
+      <c r="AE56" s="1" t="n">
+        <v>0.02897</v>
+      </c>
+      <c r="AF56" s="2" t="n">
+        <v>0.02730496453900709</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -5873,6 +6215,12 @@
       <c r="AD57" s="2" t="n">
         <v>0.005734767025089704</v>
       </c>
+      <c r="AE57" s="1" t="n">
+        <v>0.04191</v>
+      </c>
+      <c r="AF57" s="3" t="n">
+        <v>-0.004276550249465422</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -5967,6 +6315,12 @@
       <c r="AD58" s="3" t="n">
         <v>-0.0002057613168723482</v>
       </c>
+      <c r="AE58" s="1" t="n">
+        <v>0.04865</v>
+      </c>
+      <c r="AF58" s="2" t="n">
+        <v>0.001234821979831191</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -6061,6 +6415,12 @@
       <c r="AD59" s="2" t="n">
         <v>0.00324254215304792</v>
       </c>
+      <c r="AE59" s="1" t="n">
+        <v>1.548</v>
+      </c>
+      <c r="AF59" s="2" t="n">
+        <v>0.0006464124111183659</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -6155,6 +6515,12 @@
       <c r="AD60" s="2" t="n">
         <v>0.005847953216374284</v>
       </c>
+      <c r="AE60" s="1" t="n">
+        <v>0.00343</v>
+      </c>
+      <c r="AF60" s="3" t="n">
+        <v>-0.002906976744186054</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -6249,6 +6615,12 @@
       <c r="AD61" s="2" t="n">
         <v>0.001287001287001145</v>
       </c>
+      <c r="AE61" s="1" t="n">
+        <v>0.1562</v>
+      </c>
+      <c r="AF61" s="2" t="n">
+        <v>0.003856041131105509</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -6343,6 +6715,12 @@
       <c r="AD62" s="3" t="n">
         <v>-0.000874125874125778</v>
       </c>
+      <c r="AE62" s="1" t="n">
+        <v>1.142</v>
+      </c>
+      <c r="AF62" s="3" t="n">
+        <v>-0.0008748906386702642</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -6437,6 +6815,12 @@
       <c r="AD63" s="2" t="n">
         <v>0.002285714285714351</v>
       </c>
+      <c r="AE63" s="1" t="n">
+        <v>0.7036</v>
+      </c>
+      <c r="AF63" s="2" t="n">
+        <v>0.002850627137970356</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -6531,6 +6915,12 @@
       <c r="AD64" s="3" t="n">
         <v>-0.001020408163265345</v>
       </c>
+      <c r="AE64" s="1" t="n">
+        <v>2.932</v>
+      </c>
+      <c r="AF64" s="3" t="n">
+        <v>-0.001702417432754475</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -6625,6 +7015,12 @@
       <c r="AD65" s="3" t="n">
         <v>-0.002957329953527698</v>
       </c>
+      <c r="AE65" s="1" t="n">
+        <v>0.02366</v>
+      </c>
+      <c r="AF65" s="2" t="n">
+        <v>0.002542372881355976</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -6719,6 +7115,12 @@
       <c r="AD66" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AE66" s="1" t="n">
+        <v>0.1014</v>
+      </c>
+      <c r="AF66" s="2" t="n">
+        <v>0.0009871668311945002</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -6813,6 +7215,12 @@
       <c r="AD67" s="3" t="n">
         <v>-0.005016268980477184</v>
       </c>
+      <c r="AE67" s="1" t="n">
+        <v>0.007305</v>
+      </c>
+      <c r="AF67" s="3" t="n">
+        <v>-0.004632783758005202</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -6907,6 +7315,12 @@
       <c r="AD68" s="2" t="n">
         <v>0.0032697547683923</v>
       </c>
+      <c r="AE68" s="1" t="n">
+        <v>18.43</v>
+      </c>
+      <c r="AF68" s="2" t="n">
+        <v>0.001086366105377489</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -7001,6 +7415,12 @@
       <c r="AD69" s="2" t="n">
         <v>0.004797933198006945</v>
       </c>
+      <c r="AE69" s="1" t="n">
+        <v>0.05448</v>
+      </c>
+      <c r="AF69" s="2" t="n">
+        <v>0.0005509641873278649</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -7095,6 +7515,12 @@
       <c r="AD70" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AE70" s="1" t="n">
+        <v>0.236</v>
+      </c>
+      <c r="AF70" s="2" t="n">
+        <v>0.004255319148936175</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -7189,6 +7615,12 @@
       <c r="AD71" s="3" t="n">
         <v>-0.003676470588235278</v>
       </c>
+      <c r="AE71" s="1" t="n">
+        <v>5.742</v>
+      </c>
+      <c r="AF71" s="2" t="n">
+        <v>0.008961518186610465</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -7283,6 +7715,12 @@
       <c r="AD72" s="2" t="n">
         <v>0.00112422709387299</v>
       </c>
+      <c r="AE72" s="1" t="n">
+        <v>0.001779</v>
+      </c>
+      <c r="AF72" s="3" t="n">
+        <v>-0.001122964626614289</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -7377,6 +7815,12 @@
       <c r="AD73" s="2" t="n">
         <v>0.000318505149166661</v>
       </c>
+      <c r="AE73" s="1" t="n">
+        <v>0.9458</v>
+      </c>
+      <c r="AF73" s="2" t="n">
+        <v>0.003820844831245953</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -7471,6 +7915,12 @@
       <c r="AD74" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AE74" s="1" t="n">
+        <v>0.1208</v>
+      </c>
+      <c r="AF74" s="2" t="n">
+        <v>0.00332225913621272</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -7565,6 +8015,12 @@
       <c r="AD75" s="3" t="n">
         <v>-0.001859259676601569</v>
       </c>
+      <c r="AE75" s="1" t="n">
+        <v>354.82</v>
+      </c>
+      <c r="AF75" s="2" t="n">
+        <v>0.001411153759313615</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -7659,6 +8115,12 @@
       <c r="AD76" s="3" t="n">
         <v>-0.005653531347565639</v>
       </c>
+      <c r="AE76" s="1" t="n">
+        <v>0.1178</v>
+      </c>
+      <c r="AF76" s="3" t="n">
+        <v>-0.0003394433129667207</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -7753,6 +8215,12 @@
       <c r="AD77" s="3" t="n">
         <v>-0.0006350214319733032</v>
       </c>
+      <c r="AE77" s="1" t="n">
+        <v>0.06313000000000001</v>
+      </c>
+      <c r="AF77" s="2" t="n">
+        <v>0.002859412231930097</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -7847,6 +8315,12 @@
       <c r="AD78" s="3" t="n">
         <v>-0.003897608764352632</v>
       </c>
+      <c r="AE78" s="1" t="n">
+        <v>0.09504</v>
+      </c>
+      <c r="AF78" s="2" t="n">
+        <v>0.005076142131979635</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -7941,6 +8415,12 @@
       <c r="AD79" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AE79" s="1" t="n">
+        <v>0.402</v>
+      </c>
+      <c r="AF79" s="2" t="n">
+        <v>0.001494768310911921</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -8035,6 +8515,12 @@
       <c r="AD80" s="3" t="n">
         <v>-0.001661129568106389</v>
       </c>
+      <c r="AE80" s="1" t="n">
+        <v>0.006009</v>
+      </c>
+      <c r="AF80" s="3" t="n">
+        <v>-0.0001663893510815529</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -8129,6 +8615,12 @@
       <c r="AD81" s="3" t="n">
         <v>-0.00578034682080928</v>
       </c>
+      <c r="AE81" s="1" t="n">
+        <v>0.1022</v>
+      </c>
+      <c r="AF81" s="3" t="n">
+        <v>-0.009689922480620164</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -8223,6 +8715,12 @@
       <c r="AD82" s="2" t="n">
         <v>0.0009861932938856298</v>
       </c>
+      <c r="AE82" s="1" t="n">
+        <v>0.1014</v>
+      </c>
+      <c r="AF82" s="3" t="n">
+        <v>-0.0009852216748768754</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -8317,6 +8815,12 @@
       <c r="AD83" s="3" t="n">
         <v>-0.01316000641951524</v>
       </c>
+      <c r="AE83" s="1" t="n">
+        <v>0.06153</v>
+      </c>
+      <c r="AF83" s="2" t="n">
+        <v>0.0006505122784192287</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -8411,6 +8915,12 @@
       <c r="AD84" s="3" t="n">
         <v>-0.000715435521373756</v>
       </c>
+      <c r="AE84" s="1" t="n">
+        <v>1.1176</v>
+      </c>
+      <c r="AF84" s="2" t="n">
+        <v>0.0001789869339538017</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -8505,6 +9015,12 @@
       <c r="AD85" s="3" t="n">
         <v>-0.003058103975535176</v>
       </c>
+      <c r="AE85" s="1" t="n">
+        <v>0.01308</v>
+      </c>
+      <c r="AF85" s="2" t="n">
+        <v>0.003067484662576695</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -8599,6 +9115,12 @@
       <c r="AD86" s="2" t="n">
         <v>0.002396644697423509</v>
       </c>
+      <c r="AE86" s="1" t="n">
+        <v>0.01674</v>
+      </c>
+      <c r="AF86" s="2" t="n">
+        <v>0.0005977286312016176</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -8693,6 +9215,12 @@
       <c r="AD87" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AE87" s="1" t="n">
+        <v>8.331</v>
+      </c>
+      <c r="AF87" s="2" t="n">
+        <v>0.001924233313289238</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -8787,6 +9315,12 @@
       <c r="AD88" s="2" t="n">
         <v>0.003744792398071435</v>
       </c>
+      <c r="AE88" s="1" t="n">
+        <v>2.148</v>
+      </c>
+      <c r="AF88" s="2" t="n">
+        <v>0.001725504826750109</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -8881,6 +9415,12 @@
       <c r="AD89" s="2" t="n">
         <v>0.009059534081104355</v>
       </c>
+      <c r="AE89" s="1" t="n">
+        <v>0.007016</v>
+      </c>
+      <c r="AF89" s="3" t="n">
+        <v>-0.0001425110446059759</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -8975,6 +9515,12 @@
       <c r="AD90" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AE90" s="1" t="n">
+        <v>15.27</v>
+      </c>
+      <c r="AF90" s="3" t="n">
+        <v>-0.0006544502617800908</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -9069,6 +9615,12 @@
       <c r="AD91" s="3" t="n">
         <v>-0.004484304932735414</v>
       </c>
+      <c r="AE91" s="1" t="n">
+        <v>0.000222</v>
+      </c>
+      <c r="AF91" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -9163,6 +9715,12 @@
       <c r="AD92" s="2" t="n">
         <v>0.003054017942355419</v>
       </c>
+      <c r="AE92" s="1" t="n">
+        <v>0.05281</v>
+      </c>
+      <c r="AF92" s="2" t="n">
+        <v>0.004947668886774563</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -9257,6 +9815,12 @@
       <c r="AD93" s="2" t="n">
         <v>0.001130028627391937</v>
       </c>
+      <c r="AE93" s="1" t="n">
+        <v>1.3332</v>
+      </c>
+      <c r="AF93" s="2" t="n">
+        <v>0.003235758898336948</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -9351,6 +9915,12 @@
       <c r="AD94" s="2" t="n">
         <v>0.001570177707171126</v>
       </c>
+      <c r="AE94" s="1" t="n">
+        <v>0.05417</v>
+      </c>
+      <c r="AF94" s="3" t="n">
+        <v>-0.0009037422305833827</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -9445,6 +10015,12 @@
       <c r="AD95" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AE95" s="1" t="n">
+        <v>0.2397</v>
+      </c>
+      <c r="AF95" s="3" t="n">
+        <v>-0.0008336807002918121</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -9539,6 +10115,12 @@
       <c r="AD96" s="2" t="n">
         <v>0.000555967383246994</v>
       </c>
+      <c r="AE96" s="1" t="n">
+        <v>1.0753</v>
+      </c>
+      <c r="AF96" s="3" t="n">
+        <v>-0.004167438414521365</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -9633,6 +10215,12 @@
       <c r="AD97" s="2" t="n">
         <v>0.001554001554001383</v>
       </c>
+      <c r="AE97" s="1" t="n">
+        <v>0.2578</v>
+      </c>
+      <c r="AF97" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -9727,6 +10315,12 @@
       <c r="AD98" s="2" t="n">
         <v>0.004838430965958225</v>
       </c>
+      <c r="AE98" s="1" t="n">
+        <v>0.579</v>
+      </c>
+      <c r="AF98" s="3" t="n">
+        <v>-0.004299226139295026</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -9821,6 +10415,12 @@
       <c r="AD99" s="3" t="n">
         <v>-0.00404858299595138</v>
       </c>
+      <c r="AE99" s="1" t="n">
+        <v>0.13394</v>
+      </c>
+      <c r="AF99" s="3" t="n">
+        <v>-0.01005173688100517</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -9915,6 +10515,12 @@
       <c r="AD100" s="2" t="n">
         <v>0.00643707756678464</v>
       </c>
+      <c r="AE100" s="1" t="n">
+        <v>0.03128</v>
+      </c>
+      <c r="AF100" s="2" t="n">
+        <v>0.0003197953309882655</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -10009,6 +10615,12 @@
       <c r="AD101" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AE101" s="1" t="n">
+        <v>1.053</v>
+      </c>
+      <c r="AF101" s="2" t="n">
+        <v>0.003813155386081987</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -10103,6 +10715,12 @@
       <c r="AD102" s="2" t="n">
         <v>0.001805054151624632</v>
       </c>
+      <c r="AE102" s="1" t="n">
+        <v>0.02217</v>
+      </c>
+      <c r="AF102" s="3" t="n">
+        <v>-0.001351351351351452</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -10197,6 +10815,12 @@
       <c r="AD103" s="3" t="n">
         <v>-0.001018848700968041</v>
       </c>
+      <c r="AE103" s="1" t="n">
+        <v>0.01962</v>
+      </c>
+      <c r="AF103" s="2" t="n">
+        <v>0.0005099439061703005</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -10291,6 +10915,12 @@
       <c r="AD104" s="2" t="n">
         <v>0.001332889036987672</v>
       </c>
+      <c r="AE104" s="1" t="n">
+        <v>3.008</v>
+      </c>
+      <c r="AF104" s="2" t="n">
+        <v>0.0009983361064892227</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -10385,6 +11015,12 @@
       <c r="AD105" s="3" t="n">
         <v>-0.001228878648233461</v>
       </c>
+      <c r="AE105" s="1" t="n">
+        <v>32.56</v>
+      </c>
+      <c r="AF105" s="2" t="n">
+        <v>0.001537988311288965</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -10479,6 +11115,12 @@
       <c r="AD106" s="3" t="n">
         <v>-0.001209189842805187</v>
       </c>
+      <c r="AE106" s="1" t="n">
+        <v>0.1655</v>
+      </c>
+      <c r="AF106" s="2" t="n">
+        <v>0.001815980629539919</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -10573,6 +11215,12 @@
       <c r="AD107" s="3" t="n">
         <v>-0.01392212312377641</v>
       </c>
+      <c r="AE107" s="1" t="n">
+        <v>0.4528</v>
+      </c>
+      <c r="AF107" s="3" t="n">
+        <v>-0.001103022281050078</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -10667,6 +11315,12 @@
       <c r="AD108" s="2" t="n">
         <v>0.00208209399167156</v>
       </c>
+      <c r="AE108" s="1" t="n">
+        <v>0.3369</v>
+      </c>
+      <c r="AF108" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -10761,6 +11415,12 @@
       <c r="AD109" s="2" t="n">
         <v>0.006178287731685845</v>
       </c>
+      <c r="AE109" s="1" t="n">
+        <v>0.2261</v>
+      </c>
+      <c r="AF109" s="3" t="n">
+        <v>-0.008333333333333389</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -10855,6 +11515,12 @@
       <c r="AD110" s="2" t="n">
         <v>0.002654280026542807</v>
       </c>
+      <c r="AE110" s="1" t="n">
+        <v>0.0151</v>
+      </c>
+      <c r="AF110" s="3" t="n">
+        <v>-0.0006618133686300193</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -10949,6 +11615,12 @@
       <c r="AD111" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AE111" s="1" t="n">
+        <v>1.836</v>
+      </c>
+      <c r="AF111" s="3" t="n">
+        <v>-0.001088139281828075</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -11043,6 +11715,12 @@
       <c r="AD112" s="3" t="n">
         <v>-0.0005242463958061893</v>
       </c>
+      <c r="AE112" s="1" t="n">
+        <v>0.03812</v>
+      </c>
+      <c r="AF112" s="3" t="n">
+        <v>-0.0002622606871228986</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -11137,6 +11815,12 @@
       <c r="AD113" s="3" t="n">
         <v>-0.006050733069583384</v>
       </c>
+      <c r="AE113" s="1" t="n">
+        <v>4.266</v>
+      </c>
+      <c r="AF113" s="3" t="n">
+        <v>-0.001170686022008872</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -11231,6 +11915,12 @@
       <c r="AD114" s="3" t="n">
         <v>-0.001052631578947394</v>
       </c>
+      <c r="AE114" s="1" t="n">
+        <v>0.007512</v>
+      </c>
+      <c r="AF114" s="3" t="n">
+        <v>-0.0105374077976818</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -11325,6 +12015,12 @@
       <c r="AD115" s="2" t="n">
         <v>0.00328980161499349</v>
       </c>
+      <c r="AE115" s="1" t="n">
+        <v>0.10054</v>
+      </c>
+      <c r="AF115" s="3" t="n">
+        <v>-0.0009936406995229431</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -11419,6 +12115,12 @@
       <c r="AD116" s="2" t="n">
         <v>0.001204529029149637</v>
       </c>
+      <c r="AE116" s="1" t="n">
+        <v>0.08313</v>
+      </c>
+      <c r="AF116" s="2" t="n">
+        <v>0.0001203079884503865</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -11513,6 +12215,12 @@
       <c r="AD117" s="2" t="n">
         <v>0.00200467758102235</v>
       </c>
+      <c r="AE117" s="1" t="n">
+        <v>0.3003</v>
+      </c>
+      <c r="AF117" s="2" t="n">
+        <v>0.001333777925975363</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -11607,6 +12315,12 @@
       <c r="AD118" s="3" t="n">
         <v>-0.001776198934280567</v>
       </c>
+      <c r="AE118" s="1" t="n">
+        <v>0.02249</v>
+      </c>
+      <c r="AF118" s="2" t="n">
+        <v>0.0004448398576512274</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -11701,6 +12415,12 @@
       <c r="AD119" s="3" t="n">
         <v>-0.009759271307742364</v>
       </c>
+      <c r="AE119" s="1" t="n">
+        <v>0.1527</v>
+      </c>
+      <c r="AF119" s="2" t="n">
+        <v>0.003285151116951383</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -11795,6 +12515,12 @@
       <c r="AD120" s="2" t="n">
         <v>0.03110102156640181</v>
       </c>
+      <c r="AE120" s="1" t="n">
+        <v>0.004409</v>
+      </c>
+      <c r="AF120" s="3" t="n">
+        <v>-0.02928225451343027</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -11889,6 +12615,12 @@
       <c r="AD121" s="3" t="n">
         <v>-0.01001593444115642</v>
       </c>
+      <c r="AE121" s="1" t="n">
+        <v>0.4353</v>
+      </c>
+      <c r="AF121" s="2" t="n">
+        <v>0.0009197516670499229</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -11983,6 +12715,12 @@
       <c r="AD122" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AE122" s="1" t="n">
+        <v>0.775</v>
+      </c>
+      <c r="AF122" s="3" t="n">
+        <v>-0.001288659793814434</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -12077,6 +12815,12 @@
       <c r="AD123" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AE123" s="1" t="n">
+        <v>0.08649999999999999</v>
+      </c>
+      <c r="AF123" s="2" t="n">
+        <v>0.00115740740740728</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -12171,6 +12915,12 @@
       <c r="AD124" s="2" t="n">
         <v>0.003257328990228022</v>
       </c>
+      <c r="AE124" s="1" t="n">
+        <v>0.01226</v>
+      </c>
+      <c r="AF124" s="3" t="n">
+        <v>-0.004870129870129813</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -12265,6 +13015,12 @@
       <c r="AD125" s="2" t="n">
         <v>0.0008188331627431998</v>
       </c>
+      <c r="AE125" s="1" t="n">
+        <v>0.09801</v>
+      </c>
+      <c r="AF125" s="2" t="n">
+        <v>0.002352219267743854</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -12359,6 +13115,12 @@
       <c r="AD126" s="3" t="n">
         <v>-0.001916932907348239</v>
       </c>
+      <c r="AE126" s="1" t="n">
+        <v>0.04647</v>
+      </c>
+      <c r="AF126" s="3" t="n">
+        <v>-0.008322663252240748</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -12453,6 +13215,12 @@
       <c r="AD127" s="3" t="n">
         <v>-0.006191950464396225</v>
       </c>
+      <c r="AE127" s="1" t="n">
+        <v>3.19e-05</v>
+      </c>
+      <c r="AF127" s="3" t="n">
+        <v>-0.006230529595015516</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -12547,6 +13315,12 @@
       <c r="AD128" s="3" t="n">
         <v>-0.0008813678829544437</v>
       </c>
+      <c r="AE128" s="1" t="n">
+        <v>0.5663</v>
+      </c>
+      <c r="AF128" s="3" t="n">
+        <v>-0.0008821453775581245</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -12641,6 +13415,12 @@
       <c r="AD129" s="3" t="n">
         <v>-0.001544401544401589</v>
       </c>
+      <c r="AE129" s="1" t="n">
+        <v>0.06467000000000001</v>
+      </c>
+      <c r="AF129" s="2" t="n">
+        <v>0.0003093580819799865</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -12735,6 +13515,12 @@
       <c r="AD130" s="3" t="n">
         <v>-0.003442622950819667</v>
       </c>
+      <c r="AE130" s="1" t="n">
+        <v>0.0006114</v>
+      </c>
+      <c r="AF130" s="2" t="n">
+        <v>0.005757525908866641</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -12829,6 +13615,12 @@
       <c r="AD131" s="2" t="n">
         <v>0.01149425287356323</v>
       </c>
+      <c r="AE131" s="1" t="n">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="AF131" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -12923,6 +13715,12 @@
       <c r="AD132" s="3" t="n">
         <v>-0.002654280026542876</v>
       </c>
+      <c r="AE132" s="1" t="n">
+        <v>0.3005</v>
+      </c>
+      <c r="AF132" s="3" t="n">
+        <v>-0.0003326679973386194</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -13017,6 +13815,12 @@
       <c r="AD133" s="2" t="n">
         <v>0.00325829383886253</v>
       </c>
+      <c r="AE133" s="1" t="n">
+        <v>0.03387</v>
+      </c>
+      <c r="AF133" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -13111,6 +13915,12 @@
       <c r="AD134" s="2" t="n">
         <v>0.002015428452290031</v>
       </c>
+      <c r="AE134" s="1" t="n">
+        <v>0.14358</v>
+      </c>
+      <c r="AF134" s="3" t="n">
+        <v>-0.004161464835622066</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -13205,6 +14015,12 @@
       <c r="AD135" s="3" t="n">
         <v>-0.000337268128161875</v>
       </c>
+      <c r="AE135" s="1" t="n">
+        <v>0.02963</v>
+      </c>
+      <c r="AF135" s="3" t="n">
+        <v>-0.000337381916329271</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -13299,6 +14115,12 @@
       <c r="AD136" s="2" t="n">
         <v>0.00284090909090903</v>
       </c>
+      <c r="AE136" s="1" t="n">
+        <v>28.17</v>
+      </c>
+      <c r="AF136" s="3" t="n">
+        <v>-0.002478753541076372</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -13393,6 +14215,12 @@
       <c r="AD137" s="3" t="n">
         <v>-0.002964652223489116</v>
       </c>
+      <c r="AE137" s="1" t="n">
+        <v>0.0004357</v>
+      </c>
+      <c r="AF137" s="3" t="n">
+        <v>-0.003430924062214049</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -13487,6 +14315,12 @@
       <c r="AD138" s="3" t="n">
         <v>-0.004123427943096646</v>
       </c>
+      <c r="AE138" s="1" t="n">
+        <v>0.028765</v>
+      </c>
+      <c r="AF138" s="3" t="n">
+        <v>-0.007487405976123177</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -13581,6 +14415,12 @@
       <c r="AD139" s="2" t="n">
         <v>0.002700737509089127</v>
       </c>
+      <c r="AE139" s="1" t="n">
+        <v>0.09644</v>
+      </c>
+      <c r="AF139" s="3" t="n">
+        <v>-0.0009323526364861363</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -13675,6 +14515,12 @@
       <c r="AD140" s="2" t="n">
         <v>0.003611111111111176</v>
       </c>
+      <c r="AE140" s="1" t="n">
+        <v>0.3597</v>
+      </c>
+      <c r="AF140" s="3" t="n">
+        <v>-0.004428452809299724</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -13769,6 +14615,12 @@
       <c r="AD141" s="2" t="n">
         <v>0.005315110098709235</v>
       </c>
+      <c r="AE141" s="1" t="n">
+        <v>0.02652</v>
+      </c>
+      <c r="AF141" s="2" t="n">
+        <v>0.001510574018126827</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -13863,6 +14715,12 @@
       <c r="AD142" s="2" t="n">
         <v>0.0002518257365901819</v>
       </c>
+      <c r="AE142" s="1" t="n">
+        <v>0.07948</v>
+      </c>
+      <c r="AF142" s="2" t="n">
+        <v>0.0005035246727089422</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -13957,6 +14815,12 @@
       <c r="AD143" s="2" t="n">
         <v>0.002390166173457795</v>
       </c>
+      <c r="AE143" s="1" t="n">
+        <v>0.08823</v>
+      </c>
+      <c r="AF143" s="2" t="n">
+        <v>0.001816736686726551</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -14051,6 +14915,12 @@
       <c r="AD144" s="3" t="n">
         <v>-0.0091965150048404</v>
       </c>
+      <c r="AE144" s="1" t="n">
+        <v>0.02068</v>
+      </c>
+      <c r="AF144" s="2" t="n">
+        <v>0.01025891548607728</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -14145,6 +15015,12 @@
       <c r="AD145" s="3" t="n">
         <v>-0.005134453050213152</v>
       </c>
+      <c r="AE145" s="1" t="n">
+        <v>0.1142</v>
+      </c>
+      <c r="AF145" s="3" t="n">
+        <v>-0.001049685094471737</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -14239,6 +15115,12 @@
       <c r="AD146" s="3" t="n">
         <v>-0.0003303600925009729</v>
       </c>
+      <c r="AE146" s="1" t="n">
+        <v>0.3046</v>
+      </c>
+      <c r="AF146" s="2" t="n">
+        <v>0.00660938532716458</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -14333,6 +15215,12 @@
       <c r="AD147" s="3" t="n">
         <v>-0.008064516129032265</v>
       </c>
+      <c r="AE147" s="1" t="n">
+        <v>0.123</v>
+      </c>
+      <c r="AF147" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -14427,6 +15315,12 @@
       <c r="AD148" s="2" t="n">
         <v>0.001069845636558149</v>
       </c>
+      <c r="AE148" s="1" t="n">
+        <v>1.9595</v>
+      </c>
+      <c r="AF148" s="3" t="n">
+        <v>-0.002798982188295196</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -14521,6 +15415,12 @@
       <c r="AD149" s="2" t="n">
         <v>0.001621796951021778</v>
       </c>
+      <c r="AE149" s="1" t="n">
+        <v>0.06172</v>
+      </c>
+      <c r="AF149" s="3" t="n">
+        <v>-0.0006476683937824693</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -14615,6 +15515,12 @@
       <c r="AD150" s="2" t="n">
         <v>0.005552128315854485</v>
       </c>
+      <c r="AE150" s="1" t="n">
+        <v>0.1627</v>
+      </c>
+      <c r="AF150" s="3" t="n">
+        <v>-0.00184049079754598</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -14709,6 +15615,12 @@
       <c r="AD151" s="2" t="n">
         <v>0.001191895113230024</v>
       </c>
+      <c r="AE151" s="1" t="n">
+        <v>6.714e-05</v>
+      </c>
+      <c r="AF151" s="3" t="n">
+        <v>-0.000892857142857084</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -14803,6 +15715,12 @@
       <c r="AD152" s="3" t="n">
         <v>-0.006770480704129952</v>
       </c>
+      <c r="AE152" s="1" t="n">
+        <v>0.01461</v>
+      </c>
+      <c r="AF152" s="3" t="n">
+        <v>-0.004089979550102319</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -14897,6 +15815,12 @@
       <c r="AD153" s="2" t="n">
         <v>0.001902044698050327</v>
       </c>
+      <c r="AE153" s="1" t="n">
+        <v>0.02112</v>
+      </c>
+      <c r="AF153" s="2" t="n">
+        <v>0.002373042240151943</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -14991,6 +15915,12 @@
       <c r="AD154" s="2" t="n">
         <v>0.000505050505050426</v>
       </c>
+      <c r="AE154" s="1" t="n">
+        <v>0.000595</v>
+      </c>
+      <c r="AF154" s="2" t="n">
+        <v>0.001177856301531333</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -15085,6 +16015,12 @@
       <c r="AD155" s="2" t="n">
         <v>0.001494396014944072</v>
       </c>
+      <c r="AE155" s="1" t="n">
+        <v>0.04024</v>
+      </c>
+      <c r="AF155" s="2" t="n">
+        <v>0.0007460830639143324</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -15179,6 +16115,12 @@
       <c r="AD156" s="3" t="n">
         <v>-0.002106371774618135</v>
       </c>
+      <c r="AE156" s="1" t="n">
+        <v>0.01901</v>
+      </c>
+      <c r="AF156" s="2" t="n">
+        <v>0.003166226912928631</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -15273,6 +16215,12 @@
       <c r="AD157" s="3" t="n">
         <v>-0.004806591897459416</v>
       </c>
+      <c r="AE157" s="1" t="n">
+        <v>0.08791</v>
+      </c>
+      <c r="AF157" s="2" t="n">
+        <v>0.01092456301747938</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -15367,6 +16315,12 @@
       <c r="AD158" s="2" t="n">
         <v>0.002025014889815325</v>
       </c>
+      <c r="AE158" s="1" t="n">
+        <v>0.008358000000000001</v>
+      </c>
+      <c r="AF158" s="3" t="n">
+        <v>-0.006419400855919935</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -15461,6 +16415,12 @@
       <c r="AD159" s="2" t="n">
         <v>0.001992825827022676</v>
       </c>
+      <c r="AE159" s="1" t="n">
+        <v>2.515</v>
+      </c>
+      <c r="AF159" s="2" t="n">
+        <v>0.0003977724741449221</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -15555,6 +16515,12 @@
       <c r="AD160" s="3" t="n">
         <v>-0.0003115750116840286</v>
       </c>
+      <c r="AE160" s="1" t="n">
+        <v>1.288</v>
+      </c>
+      <c r="AF160" s="2" t="n">
+        <v>0.003584229390680955</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -15649,6 +16615,12 @@
       <c r="AD161" s="2" t="n">
         <v>0.003728362183755026</v>
       </c>
+      <c r="AE161" s="1" t="n">
+        <v>0.007525</v>
+      </c>
+      <c r="AF161" s="3" t="n">
+        <v>-0.001724595383390934</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -15743,6 +16715,12 @@
       <c r="AD162" s="2" t="n">
         <v>0.008593174564203152</v>
       </c>
+      <c r="AE162" s="1" t="n">
+        <v>0.004107</v>
+      </c>
+      <c r="AF162" s="3" t="n">
+        <v>-0.0002434274586171532</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -15837,6 +16815,12 @@
       <c r="AD163" s="2" t="n">
         <v>0.006243496357960347</v>
       </c>
+      <c r="AE163" s="1" t="n">
+        <v>0.09669999999999999</v>
+      </c>
+      <c r="AF163" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -15931,6 +16915,12 @@
       <c r="AD164" s="3" t="n">
         <v>-0.0005784944681465846</v>
       </c>
+      <c r="AE164" s="1" t="n">
+        <v>1.3849</v>
+      </c>
+      <c r="AF164" s="2" t="n">
+        <v>0.002025902611967233</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -16025,6 +17015,12 @@
       <c r="AD165" s="3" t="n">
         <v>-0.005225232817833177</v>
       </c>
+      <c r="AE165" s="1" t="n">
+        <v>0.023418</v>
+      </c>
+      <c r="AF165" s="3" t="n">
+        <v>-0.008006099885627069</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -16119,6 +17115,12 @@
       <c r="AD166" s="3" t="n">
         <v>-0.0005822981366460399</v>
       </c>
+      <c r="AE166" s="1" t="n">
+        <v>0.005125</v>
+      </c>
+      <c r="AF166" s="3" t="n">
+        <v>-0.004661099242571318</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -16213,6 +17215,12 @@
       <c r="AD167" s="3" t="n">
         <v>-0.0003047851264857093</v>
       </c>
+      <c r="AE167" s="1" t="n">
+        <v>0.0655</v>
+      </c>
+      <c r="AF167" s="3" t="n">
+        <v>-0.001524390243902483</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -16307,6 +17315,12 @@
       <c r="AD168" s="3" t="n">
         <v>-0.002087682672233736</v>
       </c>
+      <c r="AE168" s="1" t="n">
+        <v>0.0956</v>
+      </c>
+      <c r="AF168" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -16401,6 +17415,12 @@
       <c r="AD169" s="3" t="n">
         <v>-0.003879979306776962</v>
       </c>
+      <c r="AE169" s="1" t="n">
+        <v>0.03858</v>
+      </c>
+      <c r="AF169" s="2" t="n">
+        <v>0.001817709685795913</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -16495,6 +17515,12 @@
       <c r="AD170" s="2" t="n">
         <v>0.0001401738155312774</v>
       </c>
+      <c r="AE170" s="1" t="n">
+        <v>0.007148</v>
+      </c>
+      <c r="AF170" s="2" t="n">
+        <v>0.001822004204625086</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -16589,6 +17615,12 @@
       <c r="AD171" s="3" t="n">
         <v>-0.00146929180135175</v>
       </c>
+      <c r="AE171" s="1" t="n">
+        <v>0.3412</v>
+      </c>
+      <c r="AF171" s="2" t="n">
+        <v>0.004120070629782261</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -16683,6 +17715,12 @@
       <c r="AD172" s="2" t="n">
         <v>0.001831501831501792</v>
       </c>
+      <c r="AE172" s="1" t="n">
+        <v>5.469</v>
+      </c>
+      <c r="AF172" s="3" t="n">
+        <v>-0.0001828153564898438</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -16777,6 +17815,12 @@
       <c r="AD173" s="2" t="n">
         <v>0.001314060446780498</v>
       </c>
+      <c r="AE173" s="1" t="n">
+        <v>0.04566</v>
+      </c>
+      <c r="AF173" s="3" t="n">
+        <v>-0.001312335958005196</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -16871,6 +17915,12 @@
       <c r="AD174" s="2" t="n">
         <v>0.001277139208173728</v>
       </c>
+      <c r="AE174" s="1" t="n">
+        <v>0.03918</v>
+      </c>
+      <c r="AF174" s="3" t="n">
+        <v>-0.0005102040816326323</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -16965,6 +18015,12 @@
       <c r="AD175" s="3" t="n">
         <v>-0.007978723404255301</v>
       </c>
+      <c r="AE175" s="1" t="n">
+        <v>0.005534</v>
+      </c>
+      <c r="AF175" s="3" t="n">
+        <v>-0.01090259159964259</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -17059,6 +18115,12 @@
       <c r="AD176" s="3" t="n">
         <v>-0.001324503311258339</v>
       </c>
+      <c r="AE176" s="1" t="n">
+        <v>0.00753</v>
+      </c>
+      <c r="AF176" s="3" t="n">
+        <v>-0.001326259946949548</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -17153,6 +18215,12 @@
       <c r="AD177" s="2" t="n">
         <v>0.01063829787234037</v>
       </c>
+      <c r="AE177" s="1" t="n">
+        <v>1.804</v>
+      </c>
+      <c r="AF177" s="3" t="n">
+        <v>-0.000554016620498554</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -17247,6 +18315,12 @@
       <c r="AD178" s="2" t="n">
         <v>0.00325275846673896</v>
       </c>
+      <c r="AE178" s="1" t="n">
+        <v>15.779</v>
+      </c>
+      <c r="AF178" s="2" t="n">
+        <v>0.003115066751430355</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -17341,6 +18415,12 @@
       <c r="AD179" s="2" t="n">
         <v>0.003184713375796181</v>
       </c>
+      <c r="AE179" s="1" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="AF179" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -17435,6 +18515,12 @@
       <c r="AD180" s="3" t="n">
         <v>-0.008896077638495673</v>
       </c>
+      <c r="AE180" s="1" t="n">
+        <v>0.09915</v>
+      </c>
+      <c r="AF180" s="2" t="n">
+        <v>0.0113219094247246</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -17529,6 +18615,12 @@
       <c r="AD181" s="2" t="n">
         <v>0.002665245202558638</v>
       </c>
+      <c r="AE181" s="1" t="n">
+        <v>0.1883</v>
+      </c>
+      <c r="AF181" s="2" t="n">
+        <v>0.001063264221158988</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -17623,6 +18715,12 @@
       <c r="AD182" s="2" t="n">
         <v>0.004556193047586895</v>
       </c>
+      <c r="AE182" s="1" t="n">
+        <v>0.0593</v>
+      </c>
+      <c r="AF182" s="3" t="n">
+        <v>-0.003863598185788695</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -17717,6 +18815,12 @@
       <c r="AD183" s="2" t="n">
         <v>0.002502085070892308</v>
       </c>
+      <c r="AE183" s="1" t="n">
+        <v>0.01207</v>
+      </c>
+      <c r="AF183" s="2" t="n">
+        <v>0.004159733777038389</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -17811,6 +18915,12 @@
       <c r="AD184" s="3" t="n">
         <v>-0.0004655493482308936</v>
       </c>
+      <c r="AE184" s="1" t="n">
+        <v>0.02154</v>
+      </c>
+      <c r="AF184" s="2" t="n">
+        <v>0.003260363297624621</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -17905,6 +19015,12 @@
       <c r="AD185" s="2" t="n">
         <v>0.002732240437158473</v>
       </c>
+      <c r="AE185" s="1" t="n">
+        <v>0.367</v>
+      </c>
+      <c r="AF185" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -17999,6 +19115,12 @@
       <c r="AD186" s="3" t="n">
         <v>-0.0009175514484205088</v>
       </c>
+      <c r="AE186" s="1" t="n">
+        <v>0.007622</v>
+      </c>
+      <c r="AF186" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -18093,6 +19215,12 @@
       <c r="AD187" s="2" t="n">
         <v>0.002227171492205067</v>
       </c>
+      <c r="AE187" s="1" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="AF187" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -18187,6 +19315,12 @@
       <c r="AD188" s="2" t="n">
         <v>0.001219016659894302</v>
       </c>
+      <c r="AE188" s="1" t="n">
+        <v>0.04935</v>
+      </c>
+      <c r="AF188" s="2" t="n">
+        <v>0.001420454545454558</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -18281,6 +19415,12 @@
       <c r="AD189" s="2" t="n">
         <v>0.001960784313725492</v>
       </c>
+      <c r="AE189" s="1" t="n">
+        <v>0.256</v>
+      </c>
+      <c r="AF189" s="2" t="n">
+        <v>0.001956947162426616</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -18375,6 +19515,12 @@
       <c r="AD190" s="3" t="n">
         <v>-0.001397868250917391</v>
       </c>
+      <c r="AE190" s="1" t="n">
+        <v>0.5693</v>
+      </c>
+      <c r="AF190" s="3" t="n">
+        <v>-0.003849518810148696</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -18469,6 +19615,12 @@
       <c r="AD191" s="2" t="n">
         <v>0.001658374792703115</v>
       </c>
+      <c r="AE191" s="1" t="n">
+        <v>6.045</v>
+      </c>
+      <c r="AF191" s="2" t="n">
+        <v>0.0008278145695364062</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -18563,6 +19715,12 @@
       <c r="AD192" s="2" t="n">
         <v>0.0005730659025788926</v>
       </c>
+      <c r="AE192" s="1" t="n">
+        <v>0.3498</v>
+      </c>
+      <c r="AF192" s="2" t="n">
+        <v>0.001718213058419214</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -18657,6 +19815,12 @@
       <c r="AD193" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AE193" s="1" t="n">
+        <v>0.0641</v>
+      </c>
+      <c r="AF193" s="2" t="n">
+        <v>0.004702194357366906</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -18751,6 +19915,12 @@
       <c r="AD194" s="3" t="n">
         <v>-0.00347423277359589</v>
       </c>
+      <c r="AE194" s="1" t="n">
+        <v>0.01717</v>
+      </c>
+      <c r="AF194" s="3" t="n">
+        <v>-0.002324230098779685</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -18845,6 +20015,12 @@
       <c r="AD195" s="2" t="n">
         <v>0.004834335573635239</v>
       </c>
+      <c r="AE195" s="1" t="n">
+        <v>0.0008508</v>
+      </c>
+      <c r="AF195" s="3" t="n">
+        <v>-0.001642806852851483</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -18939,6 +20115,12 @@
       <c r="AD196" s="2" t="n">
         <v>0.004840271055179103</v>
       </c>
+      <c r="AE196" s="1" t="n">
+        <v>0.001042</v>
+      </c>
+      <c r="AF196" s="2" t="n">
+        <v>0.00385356454720605</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -19033,6 +20215,12 @@
       <c r="AD197" s="2" t="n">
         <v>0.002473716759431105</v>
       </c>
+      <c r="AE197" s="1" t="n">
+        <v>0.0001619</v>
+      </c>
+      <c r="AF197" s="3" t="n">
+        <v>-0.001233806292412121</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -19127,6 +20315,12 @@
       <c r="AD198" s="2" t="n">
         <v>0.0002307337332718814</v>
       </c>
+      <c r="AE198" s="1" t="n">
+        <v>4.323</v>
+      </c>
+      <c r="AF198" s="3" t="n">
+        <v>-0.002768166089965298</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -19221,6 +20415,12 @@
       <c r="AD199" s="2" t="n">
         <v>0.004920049200491976</v>
       </c>
+      <c r="AE199" s="1" t="n">
+        <v>0.1634</v>
+      </c>
+      <c r="AF199" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -19315,6 +20515,12 @@
       <c r="AD200" s="2" t="n">
         <v>0.00617122990004345</v>
       </c>
+      <c r="AE200" s="1" t="n">
+        <v>0.023077</v>
+      </c>
+      <c r="AF200" s="3" t="n">
+        <v>-0.003239460953697248</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -19409,6 +20615,12 @@
       <c r="AD201" s="2" t="n">
         <v>0.0008903278025092098</v>
       </c>
+      <c r="AE201" s="1" t="n">
+        <v>0.1238</v>
+      </c>
+      <c r="AF201" s="2" t="n">
+        <v>0.00113213650331544</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -19503,6 +20715,12 @@
       <c r="AD202" s="3" t="n">
         <v>-0.005010737294201905</v>
       </c>
+      <c r="AE202" s="1" t="n">
+        <v>0.01397</v>
+      </c>
+      <c r="AF202" s="2" t="n">
+        <v>0.005035971223021627</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -19597,6 +20815,12 @@
       <c r="AD203" s="3" t="n">
         <v>-0.0004875670404680445</v>
       </c>
+      <c r="AE203" s="1" t="n">
+        <v>0.04083</v>
+      </c>
+      <c r="AF203" s="3" t="n">
+        <v>-0.004146341463414718</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -19691,6 +20915,12 @@
       <c r="AD204" s="2" t="n">
         <v>0.003098373353989164</v>
       </c>
+      <c r="AE204" s="1" t="n">
+        <v>0.02591</v>
+      </c>
+      <c r="AF204" s="2" t="n">
+        <v>0.0003861003861003704</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -19785,6 +21015,12 @@
       <c r="AD205" s="2" t="n">
         <v>0.002556356030676249</v>
       </c>
+      <c r="AE205" s="1" t="n">
+        <v>0.4328</v>
+      </c>
+      <c r="AF205" s="2" t="n">
+        <v>0.003245248029670868</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -19879,6 +21115,12 @@
       <c r="AD206" s="2" t="n">
         <v>0.00132216835610411</v>
       </c>
+      <c r="AE206" s="1" t="n">
+        <v>0.0228</v>
+      </c>
+      <c r="AF206" s="2" t="n">
+        <v>0.003521126760563389</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -19973,6 +21215,12 @@
       <c r="AD207" s="2" t="n">
         <v>0.002392344497607817</v>
       </c>
+      <c r="AE207" s="1" t="n">
+        <v>4.184</v>
+      </c>
+      <c r="AF207" s="3" t="n">
+        <v>-0.001431980906921295</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -20067,6 +21315,12 @@
       <c r="AD208" s="2" t="n">
         <v>0.0005431093007469416</v>
       </c>
+      <c r="AE208" s="1" t="n">
+        <v>0.07373</v>
+      </c>
+      <c r="AF208" s="2" t="n">
+        <v>0.0005428144931469449</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -20161,6 +21415,12 @@
       <c r="AD209" s="2" t="n">
         <v>0.0007112375533427052</v>
       </c>
+      <c r="AE209" s="1" t="n">
+        <v>0.0421</v>
+      </c>
+      <c r="AF209" s="3" t="n">
+        <v>-0.002606017531390642</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -20255,6 +21515,12 @@
       <c r="AD210" s="2" t="n">
         <v>0.001621621621621593</v>
       </c>
+      <c r="AE210" s="1" t="n">
+        <v>0.1854</v>
+      </c>
+      <c r="AF210" s="2" t="n">
+        <v>0.000539665407447473</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -20349,6 +21615,12 @@
       <c r="AD211" s="2" t="n">
         <v>0.005503810330228601</v>
       </c>
+      <c r="AE211" s="1" t="n">
+        <v>0.2384</v>
+      </c>
+      <c r="AF211" s="2" t="n">
+        <v>0.003789473684210576</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -20443,6 +21715,12 @@
       <c r="AD212" s="2" t="n">
         <v>0.02406159769008669</v>
       </c>
+      <c r="AE212" s="1" t="n">
+        <v>0.002125</v>
+      </c>
+      <c r="AF212" s="3" t="n">
+        <v>-0.001409774436090209</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -20537,6 +21815,12 @@
       <c r="AD213" s="3" t="n">
         <v>-0.001075268817204302</v>
       </c>
+      <c r="AE213" s="1" t="n">
+        <v>0.929</v>
+      </c>
+      <c r="AF213" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -20631,6 +21915,12 @@
       <c r="AD214" s="2" t="n">
         <v>0.006132819344664349</v>
       </c>
+      <c r="AE214" s="1" t="n">
+        <v>0.005735</v>
+      </c>
+      <c r="AF214" s="3" t="n">
+        <v>-0.001219087425983989</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -20725,6 +22015,12 @@
       <c r="AD215" s="2" t="n">
         <v>0.0007320644216690771</v>
       </c>
+      <c r="AE215" s="1" t="n">
+        <v>0.05463</v>
+      </c>
+      <c r="AF215" s="3" t="n">
+        <v>-0.0009144111192392362</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -20819,6 +22115,12 @@
       <c r="AD216" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AE216" s="1" t="n">
+        <v>0.06320000000000001</v>
+      </c>
+      <c r="AF216" s="2" t="n">
+        <v>0.001584786053882771</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -20913,6 +22215,12 @@
       <c r="AD217" s="2" t="n">
         <v>0.002155172413793165</v>
       </c>
+      <c r="AE217" s="1" t="n">
+        <v>0.09279999999999999</v>
+      </c>
+      <c r="AF217" s="3" t="n">
+        <v>-0.002150537634408664</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -21007,6 +22315,12 @@
       <c r="AD218" s="2" t="n">
         <v>0.001722714711265966</v>
       </c>
+      <c r="AE218" s="1" t="n">
+        <v>0.27922</v>
+      </c>
+      <c r="AF218" s="2" t="n">
+        <v>0.0003941098491634086</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -21101,6 +22415,12 @@
       <c r="AD219" s="2" t="n">
         <v>0.004282655246252581</v>
       </c>
+      <c r="AE219" s="1" t="n">
+        <v>0.003272</v>
+      </c>
+      <c r="AF219" s="3" t="n">
+        <v>-0.003350593968930772</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -21195,6 +22515,12 @@
       <c r="AD220" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AE220" s="1" t="n">
+        <v>0.999373</v>
+      </c>
+      <c r="AF220" s="3" t="n">
+        <v>-1.000626392150242e-06</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -21289,6 +22615,12 @@
       <c r="AD221" s="2" t="n">
         <v>0.002328589909443721</v>
       </c>
+      <c r="AE221" s="1" t="n">
+        <v>0.03882</v>
+      </c>
+      <c r="AF221" s="2" t="n">
+        <v>0.002065049044914912</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -21383,6 +22715,12 @@
       <c r="AD222" s="2" t="n">
         <v>0.002787307032590012</v>
       </c>
+      <c r="AE222" s="1" t="n">
+        <v>0.04675</v>
+      </c>
+      <c r="AF222" s="3" t="n">
+        <v>-0.0004276245456489028</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -21477,6 +22815,12 @@
       <c r="AD223" s="2" t="n">
         <v>0.003780718336483909</v>
       </c>
+      <c r="AE223" s="1" t="n">
+        <v>0.1064</v>
+      </c>
+      <c r="AF223" s="2" t="n">
+        <v>0.001883239171374688</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -21571,6 +22915,12 @@
       <c r="AD224" s="3" t="n">
         <v>-0.000759685996454715</v>
       </c>
+      <c r="AE224" s="1" t="n">
+        <v>3.941</v>
+      </c>
+      <c r="AF224" s="3" t="n">
+        <v>-0.001267105930055838</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -21665,6 +23015,12 @@
       <c r="AD225" s="2" t="n">
         <v>0.0006475285991798128</v>
       </c>
+      <c r="AE225" s="1" t="n">
+        <v>0.0009253</v>
+      </c>
+      <c r="AF225" s="3" t="n">
+        <v>-0.002049180327868844</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -21759,6 +23115,12 @@
       <c r="AD226" s="2" t="n">
         <v>0.0005888587916617355</v>
       </c>
+      <c r="AE226" s="1" t="n">
+        <v>0.008477999999999999</v>
+      </c>
+      <c r="AF226" s="3" t="n">
+        <v>-0.002118644067796687</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -21853,6 +23215,12 @@
       <c r="AD227" s="3" t="n">
         <v>-0.004828585224529184</v>
       </c>
+      <c r="AE227" s="1" t="n">
+        <v>0.04118</v>
+      </c>
+      <c r="AF227" s="3" t="n">
+        <v>-0.0009704027171275685</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -21947,6 +23315,12 @@
       <c r="AD228" s="2" t="n">
         <v>0.001969611705121008</v>
       </c>
+      <c r="AE228" s="1" t="n">
+        <v>0.03567</v>
+      </c>
+      <c r="AF228" s="2" t="n">
+        <v>0.001684919966301532</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -22041,6 +23415,12 @@
       <c r="AD229" s="2" t="n">
         <v>0.00309537628167925</v>
       </c>
+      <c r="AE229" s="1" t="n">
+        <v>0.05189</v>
+      </c>
+      <c r="AF229" s="2" t="n">
+        <v>0.0007714561234329483</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -22135,6 +23515,12 @@
       <c r="AD230" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AE230" s="1" t="n">
+        <v>0.001726</v>
+      </c>
+      <c r="AF230" s="3" t="n">
+        <v>-0.008615738081562218</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -22229,6 +23615,12 @@
       <c r="AD231" s="3" t="n">
         <v>-0.002050020500204919</v>
       </c>
+      <c r="AE231" s="1" t="n">
+        <v>0.04879</v>
+      </c>
+      <c r="AF231" s="2" t="n">
+        <v>0.002259654889071466</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -22323,6 +23715,12 @@
       <c r="AD232" s="3" t="n">
         <v>-0.003668042182485108</v>
       </c>
+      <c r="AE232" s="1" t="n">
+        <v>0.02179</v>
+      </c>
+      <c r="AF232" s="2" t="n">
+        <v>0.002761159687068616</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -22417,6 +23815,12 @@
       <c r="AD233" s="2" t="n">
         <v>0.0008483203257549337</v>
       </c>
+      <c r="AE233" s="1" t="n">
+        <v>0.000588</v>
+      </c>
+      <c r="AF233" s="3" t="n">
+        <v>-0.003220884895745028</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -22511,6 +23915,12 @@
       <c r="AD234" s="3" t="n">
         <v>-0.003260970837603552</v>
       </c>
+      <c r="AE234" s="1" t="n">
+        <v>0.21463</v>
+      </c>
+      <c r="AF234" s="2" t="n">
+        <v>0.003131426434847524</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -22605,6 +24015,12 @@
       <c r="AD235" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AE235" s="1" t="n">
+        <v>0.01416</v>
+      </c>
+      <c r="AF235" s="3" t="n">
+        <v>-0.01186322400558269</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -22699,6 +24115,12 @@
       <c r="AD236" s="2" t="n">
         <v>0.002409638554216769</v>
       </c>
+      <c r="AE236" s="1" t="n">
+        <v>0.0415</v>
+      </c>
+      <c r="AF236" s="3" t="n">
+        <v>-0.002403846153846056</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -22793,6 +24215,12 @@
       <c r="AD237" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AE237" s="1" t="n">
+        <v>0.00418</v>
+      </c>
+      <c r="AF237" s="2" t="n">
+        <v>0.002398081534772085</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -22887,6 +24315,12 @@
       <c r="AD238" s="2" t="n">
         <v>0.003984063745019896</v>
       </c>
+      <c r="AE238" s="1" t="n">
+        <v>0.0253</v>
+      </c>
+      <c r="AF238" s="2" t="n">
+        <v>0.003968253968253945</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -22981,6 +24415,12 @@
       <c r="AD239" s="2" t="n">
         <v>0.00332667997338654</v>
       </c>
+      <c r="AE239" s="1" t="n">
+        <v>0.01508</v>
+      </c>
+      <c r="AF239" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -23075,6 +24515,12 @@
       <c r="AD240" s="3" t="n">
         <v>-0.0007593014426727595</v>
       </c>
+      <c r="AE240" s="1" t="n">
+        <v>0.0003943</v>
+      </c>
+      <c r="AF240" s="3" t="n">
+        <v>-0.00126646403242151</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -23169,6 +24615,12 @@
       <c r="AD241" s="2" t="n">
         <v>0.004809470958194686</v>
       </c>
+      <c r="AE241" s="1" t="n">
+        <v>0.2722</v>
+      </c>
+      <c r="AF241" s="2" t="n">
+        <v>0.002209131075110417</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -23263,6 +24715,12 @@
       <c r="AD242" s="3" t="n">
         <v>-0.001826484018264856</v>
       </c>
+      <c r="AE242" s="1" t="n">
+        <v>0.07650999999999999</v>
+      </c>
+      <c r="AF242" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -23357,6 +24815,12 @@
       <c r="AD243" s="2" t="n">
         <v>0.001003512293025549</v>
       </c>
+      <c r="AE243" s="1" t="n">
+        <v>0.01992</v>
+      </c>
+      <c r="AF243" s="3" t="n">
+        <v>-0.001503759398496179</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -23451,6 +24915,12 @@
       <c r="AD244" s="3" t="n">
         <v>-0.003622341668614217</v>
       </c>
+      <c r="AE244" s="1" t="n">
+        <v>0.08512</v>
+      </c>
+      <c r="AF244" s="3" t="n">
+        <v>-0.001759118095461444</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -23545,6 +25015,12 @@
       <c r="AD245" s="3" t="n">
         <v>-0.003617894663605436</v>
       </c>
+      <c r="AE245" s="1" t="n">
+        <v>1.4287</v>
+      </c>
+      <c r="AF245" s="3" t="n">
+        <v>-0.002374135884365511</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -23639,6 +25115,12 @@
       <c r="AD246" s="3" t="n">
         <v>-0.0005602240896358314</v>
       </c>
+      <c r="AE246" s="1" t="n">
+        <v>0.01786</v>
+      </c>
+      <c r="AF246" s="2" t="n">
+        <v>0.001121076233183811</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -23733,6 +25215,12 @@
       <c r="AD247" s="2" t="n">
         <v>0.001969398575973336</v>
       </c>
+      <c r="AE247" s="1" t="n">
+        <v>0.006622</v>
+      </c>
+      <c r="AF247" s="2" t="n">
+        <v>0.001209555488358058</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -23827,6 +25315,12 @@
       <c r="AD248" s="3" t="n">
         <v>-0.004635276896804079</v>
       </c>
+      <c r="AE248" s="1" t="n">
+        <v>0.004091</v>
+      </c>
+      <c r="AF248" s="2" t="n">
+        <v>0.002696078431372481</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -23921,6 +25415,12 @@
       <c r="AD249" s="2" t="n">
         <v>0.00362647325475985</v>
       </c>
+      <c r="AE249" s="1" t="n">
+        <v>0.1104</v>
+      </c>
+      <c r="AF249" s="3" t="n">
+        <v>-0.00271002710027108</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -24015,6 +25515,12 @@
       <c r="AD250" s="2" t="n">
         <v>0.002316155182397126</v>
       </c>
+      <c r="AE250" s="1" t="n">
+        <v>0.03464</v>
+      </c>
+      <c r="AF250" s="2" t="n">
+        <v>0.0005777007510109528</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -24109,6 +25615,12 @@
       <c r="AD251" s="3" t="n">
         <v>-0.003033131124591813</v>
       </c>
+      <c r="AE251" s="1" t="n">
+        <v>0.04279</v>
+      </c>
+      <c r="AF251" s="2" t="n">
+        <v>0.001404165691551708</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -24203,6 +25715,12 @@
       <c r="AD252" s="3" t="n">
         <v>-0.01926943699731912</v>
       </c>
+      <c r="AE252" s="1" t="n">
+        <v>0.005883</v>
+      </c>
+      <c r="AF252" s="2" t="n">
+        <v>0.005125576627370667</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -24297,6 +25815,12 @@
       <c r="AD253" s="3" t="n">
         <v>-0.002326934264107146</v>
       </c>
+      <c r="AE253" s="1" t="n">
+        <v>0.01711</v>
+      </c>
+      <c r="AF253" s="3" t="n">
+        <v>-0.00233236151603489</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -24391,6 +25915,12 @@
       <c r="AD254" s="2" t="n">
         <v>0.0007745933384974186</v>
       </c>
+      <c r="AE254" s="1" t="n">
+        <v>0.1292</v>
+      </c>
+      <c r="AF254" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -24485,6 +26015,12 @@
       <c r="AD255" s="2" t="n">
         <v>0.002357378595002425</v>
       </c>
+      <c r="AE255" s="1" t="n">
+        <v>0.02173</v>
+      </c>
+      <c r="AF255" s="2" t="n">
+        <v>0.02210724365004695</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -24579,6 +26115,12 @@
       <c r="AD256" s="2" t="n">
         <v>0.004755111745125982</v>
       </c>
+      <c r="AE256" s="1" t="n">
+        <v>0.02118</v>
+      </c>
+      <c r="AF256" s="2" t="n">
+        <v>0.002366303833412278</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -24673,6 +26215,12 @@
       <c r="AD257" s="3" t="n">
         <v>-0.0007836990595612325</v>
       </c>
+      <c r="AE257" s="1" t="n">
+        <v>0.02537</v>
+      </c>
+      <c r="AF257" s="3" t="n">
+        <v>-0.005098039215686203</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -24767,6 +26315,12 @@
       <c r="AD258" s="2" t="n">
         <v>0.00411713925227445</v>
       </c>
+      <c r="AE258" s="1" t="n">
+        <v>0.15137</v>
+      </c>
+      <c r="AF258" s="2" t="n">
+        <v>0.001058131075986995</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -24861,6 +26415,12 @@
       <c r="AD259" s="2" t="n">
         <v>0.0007857002553526873</v>
       </c>
+      <c r="AE259" s="1" t="n">
+        <v>0.0509</v>
+      </c>
+      <c r="AF259" s="3" t="n">
+        <v>-0.0009813542688910978</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -24955,6 +26515,12 @@
       <c r="AD260" s="2" t="n">
         <v>0.01167500595663563</v>
       </c>
+      <c r="AE260" s="1" t="n">
+        <v>0.08473</v>
+      </c>
+      <c r="AF260" s="3" t="n">
+        <v>-0.002237399905793638</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -25049,6 +26615,12 @@
       <c r="AD261" s="2" t="n">
         <v>0.01263243683781578</v>
       </c>
+      <c r="AE261" s="1" t="n">
+        <v>0.2471</v>
+      </c>
+      <c r="AF261" s="3" t="n">
+        <v>-0.005633802816901458</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -25143,6 +26715,12 @@
       <c r="AD262" s="2" t="n">
         <v>0.007617728531855886</v>
       </c>
+      <c r="AE262" s="1" t="n">
+        <v>0.1455</v>
+      </c>
+      <c r="AF262" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -25237,6 +26815,12 @@
       <c r="AD263" s="2" t="n">
         <v>0.0001306677120083121</v>
       </c>
+      <c r="AE263" s="1" t="n">
+        <v>0.07658</v>
+      </c>
+      <c r="AF263" s="2" t="n">
+        <v>0.0005226025607525264</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -25331,6 +26915,12 @@
       <c r="AD264" s="3" t="n">
         <v>-0.002793296089385449</v>
       </c>
+      <c r="AE264" s="1" t="n">
+        <v>0.0389</v>
+      </c>
+      <c r="AF264" s="3" t="n">
+        <v>-0.009421950598421245</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -25425,6 +27015,12 @@
       <c r="AD265" s="2" t="n">
         <v>0.001951854261548504</v>
       </c>
+      <c r="AE265" s="1" t="n">
+        <v>0.01543</v>
+      </c>
+      <c r="AF265" s="2" t="n">
+        <v>0.001948051948051869</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -25519,6 +27115,12 @@
       <c r="AD266" s="3" t="n">
         <v>-0.001334445371142651</v>
       </c>
+      <c r="AE266" s="1" t="n">
+        <v>0.005977</v>
+      </c>
+      <c r="AF266" s="3" t="n">
+        <v>-0.001670285618840899</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -25613,6 +27215,12 @@
       <c r="AD267" s="2" t="n">
         <v>0.002684563758389339</v>
       </c>
+      <c r="AE267" s="1" t="n">
+        <v>0.03735</v>
+      </c>
+      <c r="AF267" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -25707,6 +27315,12 @@
       <c r="AD268" s="2" t="n">
         <v>0.0006540222367560231</v>
       </c>
+      <c r="AE268" s="1" t="n">
+        <v>0.03057</v>
+      </c>
+      <c r="AF268" s="3" t="n">
+        <v>-0.0009803921568627052</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -25801,6 +27415,12 @@
       <c r="AD269" s="2" t="n">
         <v>0.0001329374750742334</v>
       </c>
+      <c r="AE269" s="1" t="n">
+        <v>0.22633</v>
+      </c>
+      <c r="AF269" s="2" t="n">
+        <v>0.002791315906069967</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -25895,6 +27515,12 @@
       <c r="AD270" s="2" t="n">
         <v>0.001075268817204302</v>
       </c>
+      <c r="AE270" s="1" t="n">
+        <v>0.931</v>
+      </c>
+      <c r="AF270" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -25989,6 +27615,12 @@
       <c r="AD271" s="2" t="n">
         <v>0.0007713073659854315</v>
       </c>
+      <c r="AE271" s="1" t="n">
+        <v>2.594</v>
+      </c>
+      <c r="AF271" s="3" t="n">
+        <v>-0.0003853564547207452</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -26083,6 +27715,12 @@
       <c r="AD272" s="2" t="n">
         <v>0.004828326180257425</v>
       </c>
+      <c r="AE272" s="1" t="n">
+        <v>0.1863</v>
+      </c>
+      <c r="AF272" s="3" t="n">
+        <v>-0.005339028296849979</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -26177,6 +27815,12 @@
       <c r="AD273" s="2" t="n">
         <v>0.006138933764135789</v>
       </c>
+      <c r="AE273" s="1" t="n">
+        <v>0.03139</v>
+      </c>
+      <c r="AF273" s="2" t="n">
+        <v>0.008028259473346185</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -26271,6 +27915,12 @@
       <c r="AD274" s="2" t="n">
         <v>0.004184100418410016</v>
       </c>
+      <c r="AE274" s="1" t="n">
+        <v>0.192</v>
+      </c>
+      <c r="AF274" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -26365,6 +28015,12 @@
       <c r="AD275" s="3" t="n">
         <v>-0.0002889755815632459</v>
       </c>
+      <c r="AE275" s="1" t="n">
+        <v>0.06895999999999999</v>
+      </c>
+      <c r="AF275" s="3" t="n">
+        <v>-0.003324179794768145</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -26459,6 +28115,12 @@
       <c r="AD276" s="2" t="n">
         <v>0.001120797011208054</v>
       </c>
+      <c r="AE276" s="1" t="n">
+        <v>0.08036</v>
+      </c>
+      <c r="AF276" s="3" t="n">
+        <v>-0.0003731807438736441</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -26553,6 +28215,12 @@
       <c r="AD277" s="3" t="n">
         <v>-0.0142785571142284</v>
       </c>
+      <c r="AE277" s="1" t="n">
+        <v>0.003889</v>
+      </c>
+      <c r="AF277" s="3" t="n">
+        <v>-0.01168996188055909</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -26647,6 +28315,12 @@
       <c r="AD278" s="3" t="n">
         <v>-0.0006435006435007155</v>
       </c>
+      <c r="AE278" s="1" t="n">
+        <v>1.553</v>
+      </c>
+      <c r="AF278" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -26741,6 +28415,12 @@
       <c r="AD279" s="2" t="n">
         <v>0.0009057971014493956</v>
       </c>
+      <c r="AE279" s="1" t="n">
+        <v>0.01104</v>
+      </c>
+      <c r="AF279" s="3" t="n">
+        <v>-0.0009049773755657309</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -26835,6 +28515,12 @@
       <c r="AD280" s="3" t="n">
         <v>-0.001990544911669489</v>
       </c>
+      <c r="AE280" s="1" t="n">
+        <v>0.04009</v>
+      </c>
+      <c r="AF280" s="3" t="n">
+        <v>-0.0004986287708800594</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -26929,6 +28615,12 @@
       <c r="AD281" s="2" t="n">
         <v>0.002502085070892432</v>
       </c>
+      <c r="AE281" s="1" t="n">
+        <v>0.08418</v>
+      </c>
+      <c r="AF281" s="2" t="n">
+        <v>0.0004753981459472114</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -27023,6 +28715,12 @@
       <c r="AD282" s="2" t="n">
         <v>0.01865671641791046</v>
       </c>
+      <c r="AE282" s="1" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="AF282" s="3" t="n">
+        <v>-0.01098901098901105</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -27117,6 +28815,12 @@
       <c r="AD283" s="2" t="n">
         <v>0.002228047182175486</v>
       </c>
+      <c r="AE283" s="1" t="n">
+        <v>0.07642</v>
+      </c>
+      <c r="AF283" s="3" t="n">
+        <v>-0.0006538511834705701</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -27211,6 +28915,12 @@
       <c r="AD284" s="2" t="n">
         <v>0.001243008079552547</v>
       </c>
+      <c r="AE284" s="1" t="n">
+        <v>0.001609</v>
+      </c>
+      <c r="AF284" s="3" t="n">
+        <v>-0.001241464928615797</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -27305,6 +29015,12 @@
       <c r="AD285" s="2" t="n">
         <v>0.002470355731225299</v>
       </c>
+      <c r="AE285" s="1" t="n">
+        <v>0.2032</v>
+      </c>
+      <c r="AF285" s="2" t="n">
+        <v>0.00147856086742235</v>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -27399,6 +29115,12 @@
       <c r="AD286" s="3" t="n">
         <v>-0.003371102163123881</v>
       </c>
+      <c r="AE286" s="1" t="n">
+        <v>0.10664</v>
+      </c>
+      <c r="AF286" s="2" t="n">
+        <v>0.001973127877478172</v>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -27493,6 +29215,12 @@
       <c r="AD287" s="2" t="n">
         <v>0.001725129384703982</v>
       </c>
+      <c r="AE287" s="1" t="n">
+        <v>0.01739</v>
+      </c>
+      <c r="AF287" s="3" t="n">
+        <v>-0.001722158438576478</v>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -27587,6 +29315,12 @@
       <c r="AD288" s="2" t="n">
         <v>0.001990710019907134</v>
       </c>
+      <c r="AE288" s="1" t="n">
+        <v>0.01514</v>
+      </c>
+      <c r="AF288" s="2" t="n">
+        <v>0.002649006622516563</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -27681,6 +29415,12 @@
       <c r="AD289" s="3" t="n">
         <v>-0.00735744941753538</v>
       </c>
+      <c r="AE289" s="1" t="n">
+        <v>0.01618</v>
+      </c>
+      <c r="AF289" s="3" t="n">
+        <v>-0.0006176652254477822</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -27775,6 +29515,12 @@
       <c r="AD290" s="2" t="n">
         <v>0.002220248667850949</v>
       </c>
+      <c r="AE290" s="1" t="n">
+        <v>2.262</v>
+      </c>
+      <c r="AF290" s="2" t="n">
+        <v>0.002215330084182496</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -27869,6 +29615,12 @@
       <c r="AD291" s="2" t="n">
         <v>0.000905182167911318</v>
       </c>
+      <c r="AE291" s="1" t="n">
+        <v>0.4414</v>
+      </c>
+      <c r="AF291" s="3" t="n">
+        <v>-0.002034817996834754</v>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -27963,6 +29715,12 @@
       <c r="AD292" s="3" t="n">
         <v>-0.002312138728323701</v>
       </c>
+      <c r="AE292" s="1" t="n">
+        <v>1.728</v>
+      </c>
+      <c r="AF292" s="2" t="n">
+        <v>0.001158748551564312</v>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -28057,6 +29815,12 @@
       <c r="AD293" s="2" t="n">
         <v>0.01921921921921913</v>
       </c>
+      <c r="AE293" s="1" t="n">
+        <v>0.05081</v>
+      </c>
+      <c r="AF293" s="3" t="n">
+        <v>-0.001964250638381378</v>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -28151,6 +29915,12 @@
       <c r="AD294" s="3" t="n">
         <v>-0.001420230392930296</v>
       </c>
+      <c r="AE294" s="1" t="n">
+        <v>0.06315999999999999</v>
+      </c>
+      <c r="AF294" s="3" t="n">
+        <v>-0.001896333754740976</v>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -28245,6 +30015,12 @@
       <c r="AD295" s="2" t="n">
         <v>0.0012103606874849</v>
       </c>
+      <c r="AE295" s="1" t="n">
+        <v>0.0004134</v>
+      </c>
+      <c r="AF295" s="3" t="n">
+        <v>-0.0004835589941973038</v>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -28339,6 +30115,12 @@
       <c r="AD296" s="2" t="n">
         <v>0.0009610764055742796</v>
       </c>
+      <c r="AE296" s="1" t="n">
+        <v>62.46</v>
+      </c>
+      <c r="AF296" s="3" t="n">
+        <v>-0.0004800768122899846</v>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -28433,6 +30215,12 @@
       <c r="AD297" s="2" t="n">
         <v>0.005128205128205133</v>
       </c>
+      <c r="AE297" s="1" t="n">
+        <v>0.0982</v>
+      </c>
+      <c r="AF297" s="2" t="n">
+        <v>0.002040816326530529</v>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -28527,6 +30315,12 @@
       <c r="AD298" s="2" t="n">
         <v>0.003144654088050259</v>
       </c>
+      <c r="AE298" s="1" t="n">
+        <v>0.0959</v>
+      </c>
+      <c r="AF298" s="2" t="n">
+        <v>0.002089864158829736</v>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -28621,6 +30415,12 @@
       <c r="AD299" s="2" t="n">
         <v>0.001770464486565335</v>
       </c>
+      <c r="AE299" s="1" t="n">
+        <v>0.09593</v>
+      </c>
+      <c r="AF299" s="3" t="n">
+        <v>-0.002702983678136983</v>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -28715,6 +30515,12 @@
       <c r="AD300" s="2" t="n">
         <v>0.00107353730542132</v>
       </c>
+      <c r="AE300" s="1" t="n">
+        <v>0.01867</v>
+      </c>
+      <c r="AF300" s="2" t="n">
+        <v>0.00107238605898119</v>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -28809,6 +30615,12 @@
       <c r="AD301" s="2" t="n">
         <v>0.001489203276247276</v>
       </c>
+      <c r="AE301" s="1" t="n">
+        <v>0.01341</v>
+      </c>
+      <c r="AF301" s="3" t="n">
+        <v>-0.002973977695167294</v>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -28903,6 +30715,12 @@
       <c r="AD302" s="2" t="n">
         <v>0.004327032566613509</v>
       </c>
+      <c r="AE302" s="1" t="n">
+        <v>0.004417</v>
+      </c>
+      <c r="AF302" s="2" t="n">
+        <v>0.001587301587301601</v>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -28997,6 +30815,12 @@
       <c r="AD303" s="2" t="n">
         <v>0.002166847237269684</v>
       </c>
+      <c r="AE303" s="1" t="n">
+        <v>0.00927</v>
+      </c>
+      <c r="AF303" s="2" t="n">
+        <v>0.002162162162162262</v>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -29091,6 +30915,12 @@
       <c r="AD304" s="2" t="n">
         <v>0.001910016977928765</v>
       </c>
+      <c r="AE304" s="1" t="n">
+        <v>4.725</v>
+      </c>
+      <c r="AF304" s="2" t="n">
+        <v>0.0008472781190424824</v>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -29185,6 +31015,12 @@
       <c r="AD305" s="2" t="n">
         <v>0.003762227238525184</v>
       </c>
+      <c r="AE305" s="1" t="n">
+        <v>0.05344</v>
+      </c>
+      <c r="AF305" s="2" t="n">
+        <v>0.001499250374812663</v>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -29279,6 +31115,12 @@
       <c r="AD306" s="2" t="n">
         <v>0.002224503764544801</v>
       </c>
+      <c r="AE306" s="1" t="n">
+        <v>0.05856</v>
+      </c>
+      <c r="AF306" s="3" t="n">
+        <v>-0.0001707358716065584</v>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -29373,6 +31215,12 @@
       <c r="AD307" s="2" t="n">
         <v>0.001718213058419214</v>
       </c>
+      <c r="AE307" s="1" t="n">
+        <v>0.1747</v>
+      </c>
+      <c r="AF307" s="3" t="n">
+        <v>-0.001143510577472874</v>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -29467,6 +31315,12 @@
       <c r="AD308" s="3" t="n">
         <v>-0.0032141422257935</v>
       </c>
+      <c r="AE308" s="1" t="n">
+        <v>0.04945</v>
+      </c>
+      <c r="AF308" s="3" t="n">
+        <v>-0.003426037887948338</v>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -29561,6 +31415,12 @@
       <c r="AD309" s="2" t="n">
         <v>0.002925045703839003</v>
       </c>
+      <c r="AE309" s="1" t="n">
+        <v>0.551</v>
+      </c>
+      <c r="AF309" s="2" t="n">
+        <v>0.004374772147284121</v>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -29655,6 +31515,12 @@
       <c r="AD310" s="2" t="n">
         <v>0.004098360655737716</v>
       </c>
+      <c r="AE310" s="1" t="n">
+        <v>0.00246</v>
+      </c>
+      <c r="AF310" s="2" t="n">
+        <v>0.004081632653061235</v>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -29749,6 +31615,12 @@
       <c r="AD311" s="3" t="n">
         <v>-0.00760135135135153</v>
       </c>
+      <c r="AE311" s="1" t="n">
+        <v>0.07062</v>
+      </c>
+      <c r="AF311" s="2" t="n">
+        <v>0.001702127659574596</v>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -29843,6 +31715,12 @@
       <c r="AD312" s="3" t="n">
         <v>-0.002572419192483919</v>
       </c>
+      <c r="AE312" s="1" t="n">
+        <v>0.00891</v>
+      </c>
+      <c r="AF312" s="3" t="n">
+        <v>-0.0008970621215520365</v>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -29937,6 +31815,12 @@
       <c r="AD313" s="2" t="n">
         <v>0.003977461054027132</v>
       </c>
+      <c r="AE313" s="1" t="n">
+        <v>0.012177</v>
+      </c>
+      <c r="AF313" s="2" t="n">
+        <v>0.005034664905909565</v>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -30031,6 +31915,12 @@
       <c r="AD314" s="2" t="n">
         <v>0.0008431703204046873</v>
       </c>
+      <c r="AE314" s="1" t="n">
+        <v>0.0237</v>
+      </c>
+      <c r="AF314" s="3" t="n">
+        <v>-0.001684919966301678</v>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -30125,6 +32015,12 @@
       <c r="AD315" s="3" t="n">
         <v>-0.001402524544179588</v>
       </c>
+      <c r="AE315" s="1" t="n">
+        <v>0.00712</v>
+      </c>
+      <c r="AF315" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -30219,6 +32115,12 @@
       <c r="AD316" s="2" t="n">
         <v>0.004217791411043119</v>
       </c>
+      <c r="AE316" s="1" t="n">
+        <v>0.2621</v>
+      </c>
+      <c r="AF316" s="2" t="n">
+        <v>0.0007636502481862465</v>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -30313,6 +32215,12 @@
       <c r="AD317" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AE317" s="1" t="n">
+        <v>1.11e-05</v>
+      </c>
+      <c r="AF317" s="3" t="n">
+        <v>-0.008928571428571343</v>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -30407,6 +32315,12 @@
       <c r="AD318" s="2" t="n">
         <v>0.0001896705422681384</v>
       </c>
+      <c r="AE318" s="1" t="n">
+        <v>0.052927</v>
+      </c>
+      <c r="AF318" s="2" t="n">
+        <v>0.00367891073900593</v>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -30501,6 +32415,12 @@
       <c r="AD319" s="2" t="n">
         <v>0.003131524008350784</v>
       </c>
+      <c r="AE319" s="1" t="n">
+        <v>0.03836</v>
+      </c>
+      <c r="AF319" s="3" t="n">
+        <v>-0.002081165452653582</v>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -30595,6 +32515,12 @@
       <c r="AD320" s="3" t="n">
         <v>-0.002197802197802235</v>
       </c>
+      <c r="AE320" s="1" t="n">
+        <v>0.006808</v>
+      </c>
+      <c r="AF320" s="3" t="n">
+        <v>-0.0002936857562408613</v>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -30689,6 +32615,12 @@
       <c r="AD321" s="2" t="n">
         <v>0.00220312844238834</v>
       </c>
+      <c r="AE321" s="1" t="n">
+        <v>4.548</v>
+      </c>
+      <c r="AF321" s="3" t="n">
+        <v>-0.0002198285337437533</v>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -30783,6 +32715,12 @@
       <c r="AD322" s="2" t="n">
         <v>0.005714285714285661</v>
       </c>
+      <c r="AE322" s="1" t="n">
+        <v>1.939</v>
+      </c>
+      <c r="AF322" s="2" t="n">
+        <v>0.001549586776859563</v>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -30877,6 +32815,12 @@
       <c r="AD323" s="3" t="n">
         <v>-0.003089453728408854</v>
       </c>
+      <c r="AE323" s="1" t="n">
+        <v>0.007115</v>
+      </c>
+      <c r="AF323" s="2" t="n">
+        <v>0.002253838568812441</v>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -30971,6 +32915,12 @@
       <c r="AD324" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AE324" s="1" t="n">
+        <v>0.01837</v>
+      </c>
+      <c r="AF324" s="2" t="n">
+        <v>0.001089918256130746</v>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -31065,6 +33015,12 @@
       <c r="AD325" s="2" t="n">
         <v>0.005579815623483669</v>
       </c>
+      <c r="AE325" s="1" t="n">
+        <v>0.4165</v>
+      </c>
+      <c r="AF325" s="2" t="n">
+        <v>0.004825090470446326</v>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -31159,6 +33115,12 @@
       <c r="AD326" s="2" t="n">
         <v>0.0004164931278633251</v>
       </c>
+      <c r="AE326" s="1" t="n">
+        <v>0.00722</v>
+      </c>
+      <c r="AF326" s="2" t="n">
+        <v>0.001942825423258413</v>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -31253,6 +33215,12 @@
       <c r="AD327" s="2" t="n">
         <v>0.003124999999999945</v>
       </c>
+      <c r="AE327" s="1" t="n">
+        <v>0.1922</v>
+      </c>
+      <c r="AF327" s="3" t="n">
+        <v>-0.002076843198338441</v>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -31347,6 +33315,12 @@
       <c r="AD328" s="2" t="n">
         <v>0.0002133560913163836</v>
       </c>
+      <c r="AE328" s="1" t="n">
+        <v>0.4682</v>
+      </c>
+      <c r="AF328" s="3" t="n">
+        <v>-0.001279863481228646</v>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -31441,6 +33415,12 @@
       <c r="AD329" s="2" t="n">
         <v>0.002978406552494423</v>
       </c>
+      <c r="AE329" s="1" t="n">
+        <v>0.0135</v>
+      </c>
+      <c r="AF329" s="2" t="n">
+        <v>0.002227171492204938</v>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -31535,6 +33515,12 @@
       <c r="AD330" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AE330" s="1" t="n">
+        <v>0.1131</v>
+      </c>
+      <c r="AF330" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -31629,6 +33615,12 @@
       <c r="AD331" s="3" t="n">
         <v>-0.0003317850033178135</v>
       </c>
+      <c r="AE331" s="1" t="n">
+        <v>0.6035</v>
+      </c>
+      <c r="AF331" s="2" t="n">
+        <v>0.001493528045137756</v>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -31723,6 +33715,12 @@
       <c r="AD332" s="2" t="n">
         <v>0.0003938558487593836</v>
       </c>
+      <c r="AE332" s="1" t="n">
+        <v>0.30561</v>
+      </c>
+      <c r="AF332" s="2" t="n">
+        <v>0.002657480314960556</v>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -31817,6 +33815,12 @@
       <c r="AD333" s="2" t="n">
         <v>0.003972194637537275</v>
       </c>
+      <c r="AE333" s="1" t="n">
+        <v>0.07063999999999999</v>
+      </c>
+      <c r="AF333" s="3" t="n">
+        <v>-0.001836936555037517</v>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -31911,6 +33915,12 @@
       <c r="AD334" s="3" t="n">
         <v>-0.001853445422651767</v>
       </c>
+      <c r="AE334" s="1" t="n">
+        <v>0.14981</v>
+      </c>
+      <c r="AF334" s="3" t="n">
+        <v>-0.006499104715166845</v>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -32005,6 +34015,12 @@
       <c r="AD335" s="3" t="n">
         <v>-0.001276324186343368</v>
       </c>
+      <c r="AE335" s="1" t="n">
+        <v>0.1568</v>
+      </c>
+      <c r="AF335" s="2" t="n">
+        <v>0.001916932907348209</v>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -32099,6 +34115,12 @@
       <c r="AD336" s="2" t="n">
         <v>0.001721170395869161</v>
       </c>
+      <c r="AE336" s="1" t="n">
+        <v>0.1748</v>
+      </c>
+      <c r="AF336" s="2" t="n">
+        <v>0.001145475372279529</v>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -32193,6 +34215,12 @@
       <c r="AD337" s="2" t="n">
         <v>0.003992015968063883</v>
       </c>
+      <c r="AE337" s="1" t="n">
+        <v>0.04022</v>
+      </c>
+      <c r="AF337" s="3" t="n">
+        <v>-0.000497017892644115</v>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -32287,6 +34315,12 @@
       <c r="AD338" s="2" t="n">
         <v>0.0007570022710069135</v>
       </c>
+      <c r="AE338" s="1" t="n">
+        <v>0.005291</v>
+      </c>
+      <c r="AF338" s="2" t="n">
+        <v>0.0005673222390316813</v>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -32381,6 +34415,12 @@
       <c r="AD339" s="2" t="n">
         <v>0.001744186046511624</v>
       </c>
+      <c r="AE339" s="1" t="n">
+        <v>0.05162</v>
+      </c>
+      <c r="AF339" s="3" t="n">
+        <v>-0.00135422712323468</v>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -32475,6 +34515,12 @@
       <c r="AD340" s="2" t="n">
         <v>0.001859106301042444</v>
       </c>
+      <c r="AE340" s="1" t="n">
+        <v>0.1508</v>
+      </c>
+      <c r="AF340" s="3" t="n">
+        <v>-0.0005964609980781148</v>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -32569,6 +34615,12 @@
       <c r="AD341" s="2" t="n">
         <v>0.000785854616895904</v>
       </c>
+      <c r="AE341" s="1" t="n">
+        <v>7.641</v>
+      </c>
+      <c r="AF341" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -32663,6 +34715,12 @@
       <c r="AD342" s="3" t="n">
         <v>-0.004550970873786412</v>
       </c>
+      <c r="AE342" s="1" t="n">
+        <v>0.3282</v>
+      </c>
+      <c r="AF342" s="2" t="n">
+        <v>0.0003047851264857939</v>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -32757,6 +34815,12 @@
       <c r="AD343" s="2" t="n">
         <v>0.009457441513190602</v>
       </c>
+      <c r="AE343" s="1" t="n">
+        <v>0.02014</v>
+      </c>
+      <c r="AF343" s="3" t="n">
+        <v>-0.006903353057199101</v>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -32851,6 +34915,12 @@
       <c r="AD344" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AE344" s="1" t="n">
+        <v>2.179</v>
+      </c>
+      <c r="AF344" s="2" t="n">
+        <v>0.0004591368227731359</v>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -32945,6 +35015,12 @@
       <c r="AD345" s="2" t="n">
         <v>0.003952569169960566</v>
       </c>
+      <c r="AE345" s="1" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AF345" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -33039,6 +35115,12 @@
       <c r="AD346" s="2" t="n">
         <v>0.0009680542110357785</v>
       </c>
+      <c r="AE346" s="1" t="n">
+        <v>0.005175</v>
+      </c>
+      <c r="AF346" s="2" t="n">
+        <v>0.0009671179883945447</v>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -33133,6 +35215,12 @@
       <c r="AD347" s="3" t="n">
         <v>-0.001924422673198144</v>
       </c>
+      <c r="AE347" s="1" t="n">
+        <v>0.05688</v>
+      </c>
+      <c r="AF347" s="3" t="n">
+        <v>-0.002979842243645864</v>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -33227,6 +35315,12 @@
       <c r="AD348" s="2" t="n">
         <v>0.0007855459544384662</v>
       </c>
+      <c r="AE348" s="1" t="n">
+        <v>0.127</v>
+      </c>
+      <c r="AF348" s="3" t="n">
+        <v>-0.003139717425431801</v>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -33321,6 +35415,12 @@
       <c r="AD349" s="2" t="n">
         <v>0.00102312652021161</v>
       </c>
+      <c r="AE349" s="1" t="n">
+        <v>5190.2</v>
+      </c>
+      <c r="AF349" s="2" t="n">
+        <v>0.0009063735416063674</v>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -33415,6 +35515,12 @@
       <c r="AD350" s="2" t="n">
         <v>0.001079136690647563</v>
       </c>
+      <c r="AE350" s="1" t="n">
+        <v>0.02779</v>
+      </c>
+      <c r="AF350" s="3" t="n">
+        <v>-0.001437297879985693</v>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -33509,6 +35615,12 @@
       <c r="AD351" s="2" t="n">
         <v>0.01223902087832964</v>
       </c>
+      <c r="AE351" s="1" t="n">
+        <v>0.001391</v>
+      </c>
+      <c r="AF351" s="3" t="n">
+        <v>-0.01066856330014212</v>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -33603,6 +35715,12 @@
       <c r="AD352" s="2" t="n">
         <v>0.04113732607380521</v>
       </c>
+      <c r="AE352" s="1" t="n">
+        <v>0.01627</v>
+      </c>
+      <c r="AF352" s="3" t="n">
+        <v>-0.0546194073213248</v>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -33697,6 +35815,12 @@
       <c r="AD353" s="2" t="n">
         <v>0.001585037248375303</v>
       </c>
+      <c r="AE353" s="1" t="n">
+        <v>6.302</v>
+      </c>
+      <c r="AF353" s="3" t="n">
+        <v>-0.002690299097958593</v>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -33791,6 +35915,12 @@
       <c r="AD354" s="2" t="n">
         <v>0.01043841336116911</v>
       </c>
+      <c r="AE354" s="1" t="n">
+        <v>0.2909</v>
+      </c>
+      <c r="AF354" s="2" t="n">
+        <v>0.001721763085399451</v>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -33885,6 +36015,12 @@
       <c r="AD355" s="2" t="n">
         <v>0.004088504088504172</v>
       </c>
+      <c r="AE355" s="1" t="n">
+        <v>0.04178</v>
+      </c>
+      <c r="AF355" s="2" t="n">
+        <v>0.0007185628742513846</v>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -33979,6 +36115,12 @@
       <c r="AD356" s="3" t="n">
         <v>-0.00405679513184586</v>
       </c>
+      <c r="AE356" s="1" t="n">
+        <v>0.11256</v>
+      </c>
+      <c r="AF356" s="3" t="n">
+        <v>-0.00327636589037465</v>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -34073,6 +36215,12 @@
       <c r="AD357" s="3" t="n">
         <v>-0.003406510219530619</v>
       </c>
+      <c r="AE357" s="1" t="n">
+        <v>0.005337</v>
+      </c>
+      <c r="AF357" s="2" t="n">
+        <v>0.01348271933156094</v>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -34167,6 +36315,12 @@
       <c r="AD358" s="2" t="n">
         <v>0.002698327037236916</v>
       </c>
+      <c r="AE358" s="1" t="n">
+        <v>0.1864</v>
+      </c>
+      <c r="AF358" s="2" t="n">
+        <v>0.003229278794402676</v>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -34261,6 +36415,12 @@
       <c r="AD359" s="2" t="n">
         <v>0.01282051282051276</v>
       </c>
+      <c r="AE359" s="1" t="n">
+        <v>0.1668</v>
+      </c>
+      <c r="AF359" s="2" t="n">
+        <v>0.005424954792043472</v>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -34355,6 +36515,12 @@
       <c r="AD360" s="2" t="n">
         <v>0.00141093474426802</v>
       </c>
+      <c r="AE360" s="1" t="n">
+        <v>0.08509</v>
+      </c>
+      <c r="AF360" s="3" t="n">
+        <v>-0.0009392978748385199</v>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -34449,6 +36615,12 @@
       <c r="AD361" s="3" t="n">
         <v>-0.001310615989515019</v>
       </c>
+      <c r="AE361" s="1" t="n">
+        <v>0.00763</v>
+      </c>
+      <c r="AF361" s="2" t="n">
+        <v>0.001312335958005196</v>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -34543,6 +36715,12 @@
       <c r="AD362" s="3" t="n">
         <v>-0.001642806852851393</v>
       </c>
+      <c r="AE362" s="1" t="n">
+        <v>0.426</v>
+      </c>
+      <c r="AF362" s="2" t="n">
+        <v>0.001410437235542994</v>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -34637,6 +36815,12 @@
       <c r="AD363" s="3" t="n">
         <v>-0.007905138339920898</v>
       </c>
+      <c r="AE363" s="1" t="n">
+        <v>3.742</v>
+      </c>
+      <c r="AF363" s="3" t="n">
+        <v>-0.006108897742363913</v>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -34731,6 +36915,12 @@
       <c r="AD364" s="2" t="n">
         <v>0.007266121707538462</v>
       </c>
+      <c r="AE364" s="1" t="n">
+        <v>0.01108</v>
+      </c>
+      <c r="AF364" s="3" t="n">
+        <v>-0.0009017132551848145</v>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -34825,6 +37015,12 @@
       <c r="AD365" s="2" t="n">
         <v>0.002718868950516663</v>
       </c>
+      <c r="AE365" s="1" t="n">
+        <v>0.05521</v>
+      </c>
+      <c r="AF365" s="3" t="n">
+        <v>-0.001988430947216178</v>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -34919,6 +37115,12 @@
       <c r="AD366" s="3" t="n">
         <v>-0.005224205485415849</v>
       </c>
+      <c r="AE366" s="1" t="n">
+        <v>0.02273</v>
+      </c>
+      <c r="AF366" s="3" t="n">
+        <v>-0.005251641137855518</v>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -35013,6 +37215,12 @@
       <c r="AD367" s="2" t="n">
         <v>0.003711952487008015</v>
       </c>
+      <c r="AE367" s="1" t="n">
+        <v>0.001346</v>
+      </c>
+      <c r="AF367" s="3" t="n">
+        <v>-0.004437869822485155</v>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -35107,6 +37315,12 @@
       <c r="AD368" s="2" t="n">
         <v>0.003812824956672601</v>
       </c>
+      <c r="AE368" s="1" t="n">
+        <v>0.2896</v>
+      </c>
+      <c r="AF368" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -35201,6 +37415,12 @@
       <c r="AD369" s="2" t="n">
         <v>0.002689618074233536</v>
       </c>
+      <c r="AE369" s="1" t="n">
+        <v>0.01863</v>
+      </c>
+      <c r="AF369" s="3" t="n">
+        <v>-0.0005364806866952571</v>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -35295,6 +37515,12 @@
       <c r="AD370" s="2" t="n">
         <v>0.002842206770542441</v>
       </c>
+      <c r="AE370" s="1" t="n">
+        <v>0.19773</v>
+      </c>
+      <c r="AF370" s="2" t="n">
+        <v>0.0007085378814717407</v>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -35389,6 +37615,12 @@
       <c r="AD371" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AE371" s="1" t="n">
+        <v>0.076</v>
+      </c>
+      <c r="AF371" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -35483,6 +37715,12 @@
       <c r="AD372" s="2" t="n">
         <v>0.002857142857142939</v>
       </c>
+      <c r="AE372" s="1" t="n">
+        <v>0.1054</v>
+      </c>
+      <c r="AF372" s="2" t="n">
+        <v>0.0009496676163341783</v>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -35577,6 +37815,12 @@
       <c r="AD373" s="3" t="n">
         <v>-0.005149174617598166</v>
       </c>
+      <c r="AE373" s="1" t="n">
+        <v>0.06568</v>
+      </c>
+      <c r="AF373" s="3" t="n">
+        <v>-0.0001522301720200354</v>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -35671,6 +37915,12 @@
       <c r="AD374" s="2" t="n">
         <v>0.003685180310608088</v>
       </c>
+      <c r="AE374" s="1" t="n">
+        <v>0.007637</v>
+      </c>
+      <c r="AF374" s="2" t="n">
+        <v>0.001442433779176465</v>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -35765,6 +38015,12 @@
       <c r="AD375" s="3" t="n">
         <v>-0.0006238303181533935</v>
       </c>
+      <c r="AE375" s="1" t="n">
+        <v>0.161</v>
+      </c>
+      <c r="AF375" s="2" t="n">
+        <v>0.004993757802746536</v>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -35859,6 +38115,12 @@
       <c r="AD376" s="2" t="n">
         <v>0.0002938583602702612</v>
       </c>
+      <c r="AE376" s="1" t="n">
+        <v>0.003408</v>
+      </c>
+      <c r="AF376" s="2" t="n">
+        <v>0.001175088131609899</v>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -35953,6 +38215,12 @@
       <c r="AD377" s="3" t="n">
         <v>-0.04000000000000015</v>
       </c>
+      <c r="AE377" s="1" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="AF377" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -36047,6 +38315,12 @@
       <c r="AD378" s="2" t="n">
         <v>0.01612903225806448</v>
       </c>
+      <c r="AE378" s="1" t="n">
+        <v>0.01125</v>
+      </c>
+      <c r="AF378" s="3" t="n">
+        <v>-0.007936507936507919</v>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -36141,6 +38415,12 @@
       <c r="AD379" s="3" t="n">
         <v>-0.001847575057736645</v>
       </c>
+      <c r="AE379" s="1" t="n">
+        <v>0.02161</v>
+      </c>
+      <c r="AF379" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -36235,6 +38515,12 @@
       <c r="AD380" s="2" t="n">
         <v>0.003194888178913608</v>
       </c>
+      <c r="AE380" s="1" t="n">
+        <v>0.01882</v>
+      </c>
+      <c r="AF380" s="3" t="n">
+        <v>-0.00106157112526535</v>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -36329,6 +38615,12 @@
       <c r="AD381" s="2" t="n">
         <v>0.001670843776106982</v>
       </c>
+      <c r="AE381" s="1" t="n">
+        <v>0.1199</v>
+      </c>
+      <c r="AF381" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -36423,6 +38715,12 @@
       <c r="AD382" s="3" t="n">
         <v>-0.002725724020442937</v>
       </c>
+      <c r="AE382" s="1" t="n">
+        <v>0.02921</v>
+      </c>
+      <c r="AF382" s="3" t="n">
+        <v>-0.002049880423641989</v>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -36517,6 +38815,12 @@
       <c r="AD383" s="2" t="n">
         <v>0.003049245311785341</v>
       </c>
+      <c r="AE383" s="1" t="n">
+        <v>0.006554</v>
+      </c>
+      <c r="AF383" s="3" t="n">
+        <v>-0.003799969600243175</v>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -36611,6 +38915,12 @@
       <c r="AD384" s="3" t="n">
         <v>-0.002866698518872481</v>
       </c>
+      <c r="AE384" s="1" t="n">
+        <v>0.02085</v>
+      </c>
+      <c r="AF384" s="3" t="n">
+        <v>-0.0009583133684714512</v>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -36705,6 +39015,12 @@
       <c r="AD385" s="2" t="n">
         <v>0.003548895899053628</v>
       </c>
+      <c r="AE385" s="1" t="n">
+        <v>2543</v>
+      </c>
+      <c r="AF385" s="3" t="n">
+        <v>-0.0007858546168958742</v>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -36799,6 +39115,12 @@
       <c r="AD386" s="2" t="n">
         <v>0.007560483870967749</v>
       </c>
+      <c r="AE386" s="1" t="n">
+        <v>0.2004</v>
+      </c>
+      <c r="AF386" s="2" t="n">
+        <v>0.002501250625312658</v>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -36893,6 +39215,12 @@
       <c r="AD387" s="3" t="n">
         <v>-0.003280224929709495</v>
       </c>
+      <c r="AE387" s="1" t="n">
+        <v>0.0849</v>
+      </c>
+      <c r="AF387" s="3" t="n">
+        <v>-0.002115655853314523</v>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -36987,6 +39315,12 @@
       <c r="AD388" s="2" t="n">
         <v>0.002406738868832703</v>
       </c>
+      <c r="AE388" s="1" t="n">
+        <v>0.005005</v>
+      </c>
+      <c r="AF388" s="2" t="n">
+        <v>0.001400560224089648</v>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -37081,6 +39415,12 @@
       <c r="AD389" s="2" t="n">
         <v>0.01424755120213717</v>
       </c>
+      <c r="AE389" s="1" t="n">
+        <v>0.02278</v>
+      </c>
+      <c r="AF389" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -37175,6 +39515,12 @@
       <c r="AD390" s="2" t="n">
         <v>0.002985074626865785</v>
       </c>
+      <c r="AE390" s="1" t="n">
+        <v>0.5054999999999999</v>
+      </c>
+      <c r="AF390" s="2" t="n">
+        <v>0.002976190476190368</v>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -37269,6 +39615,12 @@
       <c r="AD391" s="2" t="n">
         <v>0.003136866435529127</v>
       </c>
+      <c r="AE391" s="1" t="n">
+        <v>0.0006071</v>
+      </c>
+      <c r="AF391" s="3" t="n">
+        <v>-0.0008229098090850335</v>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -37363,6 +39715,12 @@
       <c r="AD392" s="2" t="n">
         <v>0.002566295979469587</v>
       </c>
+      <c r="AE392" s="1" t="n">
+        <v>0.05846</v>
+      </c>
+      <c r="AF392" s="3" t="n">
+        <v>-0.002389078498293536</v>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -37457,6 +39815,12 @@
       <c r="AD393" s="3" t="n">
         <v>-0.0003714710252599888</v>
       </c>
+      <c r="AE393" s="1" t="n">
+        <v>0.2697</v>
+      </c>
+      <c r="AF393" s="2" t="n">
+        <v>0.002229654403567408</v>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -37551,6 +39915,12 @@
       <c r="AD394" s="2" t="n">
         <v>0.002260397830017991</v>
       </c>
+      <c r="AE394" s="1" t="n">
+        <v>0.006621</v>
+      </c>
+      <c r="AF394" s="3" t="n">
+        <v>-0.004510599909787949</v>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -37645,6 +40015,12 @@
       <c r="AD395" s="2" t="n">
         <v>0.0008680555555555804</v>
       </c>
+      <c r="AE395" s="1" t="n">
+        <v>0.1154</v>
+      </c>
+      <c r="AF395" s="2" t="n">
+        <v>0.0008673026886383596</v>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -37739,6 +40115,12 @@
       <c r="AD396" s="2" t="n">
         <v>0.01619170984455949</v>
       </c>
+      <c r="AE396" s="1" t="n">
+        <v>0.03146</v>
+      </c>
+      <c r="AF396" s="2" t="n">
+        <v>0.002549394518801902</v>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -37833,6 +40215,12 @@
       <c r="AD397" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AE397" s="1" t="n">
+        <v>0.1508</v>
+      </c>
+      <c r="AF397" s="3" t="n">
+        <v>-0.001324503311258316</v>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -37927,6 +40315,12 @@
       <c r="AD398" s="2" t="n">
         <v>0.005762814680012108</v>
       </c>
+      <c r="AE398" s="1" t="n">
+        <v>0.003306</v>
+      </c>
+      <c r="AF398" s="3" t="n">
+        <v>-0.003015681544028959</v>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -38021,6 +40415,12 @@
       <c r="AD399" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AE399" s="1" t="n">
+        <v>0.01837</v>
+      </c>
+      <c r="AF399" s="3" t="n">
+        <v>-0.009169363538295578</v>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -38115,6 +40515,12 @@
       <c r="AD400" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AE400" s="1" t="n">
+        <v>0.006989</v>
+      </c>
+      <c r="AF400" s="2" t="n">
+        <v>0.007786589762076457</v>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -38209,6 +40615,12 @@
       <c r="AD401" s="2" t="n">
         <v>0.001149755676918683</v>
       </c>
+      <c r="AE401" s="1" t="n">
+        <v>0.006965</v>
+      </c>
+      <c r="AF401" s="3" t="n">
+        <v>-0.0001435544071203177</v>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -38303,6 +40715,12 @@
       <c r="AD402" s="3" t="n">
         <v>-0.0008741258741258819</v>
       </c>
+      <c r="AE402" s="1" t="n">
+        <v>0.008015</v>
+      </c>
+      <c r="AF402" s="2" t="n">
+        <v>0.001749781277340348</v>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -38397,6 +40815,12 @@
       <c r="AD403" s="2" t="n">
         <v>0.006492189085007117</v>
       </c>
+      <c r="AE403" s="1" t="n">
+        <v>0.04965</v>
+      </c>
+      <c r="AF403" s="2" t="n">
+        <v>0.0008062890546260506</v>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -38491,6 +40915,12 @@
       <c r="AD404" s="3" t="n">
         <v>-0.0002024564718585656</v>
       </c>
+      <c r="AE404" s="1" t="n">
+        <v>0.14762</v>
+      </c>
+      <c r="AF404" s="3" t="n">
+        <v>-0.003577455281808996</v>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -38585,6 +41015,12 @@
       <c r="AD405" s="2" t="n">
         <v>0.002812280290602345</v>
       </c>
+      <c r="AE405" s="1" t="n">
+        <v>0.04291</v>
+      </c>
+      <c r="AF405" s="2" t="n">
+        <v>0.002804393549894721</v>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -38679,6 +41115,12 @@
       <c r="AD406" s="2" t="n">
         <v>0.001462293712136993</v>
       </c>
+      <c r="AE406" s="1" t="n">
+        <v>0.4791</v>
+      </c>
+      <c r="AF406" s="3" t="n">
+        <v>-0.000625782227784662</v>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -38773,6 +41215,12 @@
       <c r="AD407" s="2" t="n">
         <v>0.000201612903225702</v>
       </c>
+      <c r="AE407" s="1" t="n">
+        <v>0.0004935</v>
+      </c>
+      <c r="AF407" s="3" t="n">
+        <v>-0.005240878855069452</v>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -38867,6 +41315,12 @@
       <c r="AD408" s="3" t="n">
         <v>-0.004038772213247149</v>
       </c>
+      <c r="AE408" s="1" t="n">
+        <v>0.0123</v>
+      </c>
+      <c r="AF408" s="3" t="n">
+        <v>-0.002433090024330942</v>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -38961,6 +41415,12 @@
       <c r="AD409" s="3" t="n">
         <v>-0.001882648258550328</v>
       </c>
+      <c r="AE409" s="1" t="n">
+        <v>0.3168</v>
+      </c>
+      <c r="AF409" s="3" t="n">
+        <v>-0.004086765168186004</v>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -39055,6 +41515,12 @@
       <c r="AD410" s="2" t="n">
         <v>0.001433691756272509</v>
       </c>
+      <c r="AE410" s="1" t="n">
+        <v>0.04188</v>
+      </c>
+      <c r="AF410" s="3" t="n">
+        <v>-0.0007158196134574623</v>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -39149,6 +41615,12 @@
       <c r="AD411" s="2" t="n">
         <v>0.0006724949562879172</v>
       </c>
+      <c r="AE411" s="1" t="n">
+        <v>0.02982</v>
+      </c>
+      <c r="AF411" s="2" t="n">
+        <v>0.002016129032257982</v>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
@@ -39243,6 +41715,12 @@
       <c r="AD412" s="3" t="n">
         <v>-0.0002188183807440115</v>
       </c>
+      <c r="AE412" s="1" t="n">
+        <v>0.004572</v>
+      </c>
+      <c r="AF412" s="2" t="n">
+        <v>0.0006565988181220247</v>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -39337,6 +41815,12 @@
       <c r="AD413" s="2" t="n">
         <v>0.001191895113230125</v>
       </c>
+      <c r="AE413" s="1" t="n">
+        <v>0.2522</v>
+      </c>
+      <c r="AF413" s="2" t="n">
+        <v>0.0007936507936507063</v>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -39431,6 +41915,12 @@
       <c r="AD414" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AE414" s="1" t="n">
+        <v>1.287</v>
+      </c>
+      <c r="AF414" s="2" t="n">
+        <v>0.003117692907248639</v>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -39525,6 +42015,12 @@
       <c r="AD415" s="2" t="n">
         <v>0.009793253536452554</v>
       </c>
+      <c r="AE415" s="1" t="n">
+        <v>2.779</v>
+      </c>
+      <c r="AF415" s="3" t="n">
+        <v>-0.001795977011494215</v>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -39619,6 +42115,12 @@
       <c r="AD416" s="2" t="n">
         <v>0.001847290640394013</v>
       </c>
+      <c r="AE416" s="1" t="n">
+        <v>0.03284</v>
+      </c>
+      <c r="AF416" s="2" t="n">
+        <v>0.00921942224953908</v>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -39713,6 +42215,12 @@
       <c r="AD417" s="3" t="n">
         <v>-0.001761449421238063</v>
       </c>
+      <c r="AE417" s="1" t="n">
+        <v>0.03979</v>
+      </c>
+      <c r="AF417" s="2" t="n">
+        <v>0.003024955886060047</v>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -39807,6 +42315,12 @@
       <c r="AD418" s="2" t="n">
         <v>0.001836065573770508</v>
       </c>
+      <c r="AE418" s="1" t="n">
+        <v>0.07643999999999999</v>
+      </c>
+      <c r="AF418" s="2" t="n">
+        <v>0.0006545359340227058</v>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -39901,6 +42415,12 @@
       <c r="AD419" s="2" t="n">
         <v>0.004518072289156573</v>
       </c>
+      <c r="AE419" s="1" t="n">
+        <v>0.00666</v>
+      </c>
+      <c r="AF419" s="3" t="n">
+        <v>-0.001499250374812533</v>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -39995,6 +42515,12 @@
       <c r="AD420" s="2" t="n">
         <v>0.002272727272727338</v>
       </c>
+      <c r="AE420" s="1" t="n">
+        <v>0.0882</v>
+      </c>
+      <c r="AF420" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -40089,6 +42615,12 @@
       <c r="AD421" s="3" t="n">
         <v>-0.001242750621375289</v>
       </c>
+      <c r="AE421" s="1" t="n">
+        <v>0.2402</v>
+      </c>
+      <c r="AF421" s="3" t="n">
+        <v>-0.003732890916632152</v>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
@@ -40183,6 +42715,12 @@
       <c r="AD422" s="2" t="n">
         <v>0.02281368821292775</v>
       </c>
+      <c r="AE422" s="1" t="n">
+        <v>0.0271</v>
+      </c>
+      <c r="AF422" s="2" t="n">
+        <v>0.00743494423791817</v>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -40277,6 +42815,12 @@
       <c r="AD423" s="2" t="n">
         <v>0.001981505944517799</v>
       </c>
+      <c r="AE423" s="1" t="n">
+        <v>0.1519</v>
+      </c>
+      <c r="AF423" s="2" t="n">
+        <v>0.001318391562294039</v>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -40371,6 +42915,12 @@
       <c r="AD424" s="3" t="n">
         <v>-0.003807710613993429</v>
       </c>
+      <c r="AE424" s="1" t="n">
+        <v>0.0002094</v>
+      </c>
+      <c r="AF424" s="2" t="n">
+        <v>0.0004777830864787503</v>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -40465,6 +43015,12 @@
       <c r="AD425" s="2" t="n">
         <v>0.003218020917135964</v>
       </c>
+      <c r="AE425" s="1" t="n">
+        <v>1.248</v>
+      </c>
+      <c r="AF425" s="2" t="n">
+        <v>0.0008019246190857176</v>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
@@ -40559,6 +43115,12 @@
       <c r="AD426" s="2" t="n">
         <v>0.001414427157001416</v>
       </c>
+      <c r="AE426" s="1" t="n">
+        <v>1.418</v>
+      </c>
+      <c r="AF426" s="2" t="n">
+        <v>0.001412429378531075</v>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -40653,6 +43215,12 @@
       <c r="AD427" s="2" t="n">
         <v>0.001025641025640984</v>
       </c>
+      <c r="AE427" s="1" t="n">
+        <v>0.01951</v>
+      </c>
+      <c r="AF427" s="3" t="n">
+        <v>-0.0005122950819671922</v>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
@@ -40747,6 +43315,12 @@
       <c r="AD428" s="2" t="n">
         <v>0.0009117155447501064</v>
       </c>
+      <c r="AE428" s="1" t="n">
+        <v>0.06593</v>
+      </c>
+      <c r="AF428" s="2" t="n">
+        <v>0.0009108850766662289</v>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
@@ -40841,6 +43415,12 @@
       <c r="AD429" s="2" t="n">
         <v>0.00226928895612704</v>
       </c>
+      <c r="AE429" s="1" t="n">
+        <v>0.1323</v>
+      </c>
+      <c r="AF429" s="3" t="n">
+        <v>-0.001509433962264194</v>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
@@ -40935,6 +43515,12 @@
       <c r="AD430" s="2" t="n">
         <v>0.0002711496746205048</v>
       </c>
+      <c r="AE430" s="1" t="n">
+        <v>0.011066</v>
+      </c>
+      <c r="AF430" s="3" t="n">
+        <v>-9.035872413490558e-05</v>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -41029,6 +43615,12 @@
       <c r="AD431" s="3" t="n">
         <v>-0.001492760113449837</v>
       </c>
+      <c r="AE431" s="1" t="n">
+        <v>0.00669</v>
+      </c>
+      <c r="AF431" s="2" t="n">
+        <v>0.0001494991777545422</v>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
@@ -41123,6 +43715,12 @@
       <c r="AD432" s="2" t="n">
         <v>0.000564334085778856</v>
       </c>
+      <c r="AE432" s="1" t="n">
+        <v>0.001772</v>
+      </c>
+      <c r="AF432" s="3" t="n">
+        <v>-0.0005640157924422632</v>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
@@ -41217,6 +43815,12 @@
       <c r="AD433" s="2" t="n">
         <v>0.00220588235294115</v>
       </c>
+      <c r="AE433" s="1" t="n">
+        <v>0.00137</v>
+      </c>
+      <c r="AF433" s="2" t="n">
+        <v>0.005135730007336643</v>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
@@ -41311,6 +43915,12 @@
       <c r="AD434" s="2" t="n">
         <v>0.007246376811594248</v>
       </c>
+      <c r="AE434" s="1" t="n">
+        <v>0.000413</v>
+      </c>
+      <c r="AF434" s="3" t="n">
+        <v>-0.009592326139088702</v>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
@@ -41405,6 +44015,12 @@
       <c r="AD435" s="2" t="n">
         <v>0.001974411625335651</v>
       </c>
+      <c r="AE435" s="1" t="n">
+        <v>0.12721</v>
+      </c>
+      <c r="AF435" s="2" t="n">
+        <v>0.002679908567825169</v>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -41499,6 +44115,12 @@
       <c r="AD436" s="2" t="n">
         <v>0.003085626124967911</v>
       </c>
+      <c r="AE436" s="1" t="n">
+        <v>0.07829999999999999</v>
+      </c>
+      <c r="AF436" s="2" t="n">
+        <v>0.00358882337862072</v>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
@@ -41593,6 +44215,12 @@
       <c r="AD437" s="2" t="n">
         <v>0.002871271335141209</v>
       </c>
+      <c r="AE437" s="1" t="n">
+        <v>0.6294999999999999</v>
+      </c>
+      <c r="AF437" s="2" t="n">
+        <v>0.001272466995387167</v>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -41687,6 +44315,12 @@
       <c r="AD438" s="3" t="n">
         <v>-0.0002281021897809335</v>
       </c>
+      <c r="AE438" s="1" t="n">
+        <v>0.04406</v>
+      </c>
+      <c r="AF438" s="2" t="n">
+        <v>0.005247547342003217</v>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
@@ -41781,6 +44415,12 @@
       <c r="AD439" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AE439" s="1" t="n">
+        <v>0.07023</v>
+      </c>
+      <c r="AF439" s="3" t="n">
+        <v>-0.001705756929637457</v>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
@@ -41875,6 +44515,12 @@
       <c r="AD440" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AE440" s="1" t="n">
+        <v>0.001515</v>
+      </c>
+      <c r="AF440" s="3" t="n">
+        <v>-0.0006596306068601029</v>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -41969,6 +44615,12 @@
       <c r="AD441" s="3" t="n">
         <v>-0.00232337100010555</v>
       </c>
+      <c r="AE441" s="1" t="n">
+        <v>0.009534000000000001</v>
+      </c>
+      <c r="AF441" s="2" t="n">
+        <v>0.009209272785011142</v>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
@@ -42063,6 +44715,12 @@
       <c r="AD442" s="2" t="n">
         <v>0.007604562737642592</v>
       </c>
+      <c r="AE442" s="1" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AF442" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
@@ -42157,6 +44815,12 @@
       <c r="AD443" s="2" t="n">
         <v>0.003187613843351576</v>
       </c>
+      <c r="AE443" s="1" t="n">
+        <v>0.02206</v>
+      </c>
+      <c r="AF443" s="2" t="n">
+        <v>0.001361779391738483</v>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
@@ -42251,6 +44915,12 @@
       <c r="AD444" s="2" t="n">
         <v>0.002093144950287716</v>
       </c>
+      <c r="AE444" s="1" t="n">
+        <v>0.0003817</v>
+      </c>
+      <c r="AF444" s="3" t="n">
+        <v>-0.00339425587467357</v>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
@@ -42345,6 +45015,12 @@
       <c r="AD445" s="2" t="n">
         <v>0.001406865503657695</v>
       </c>
+      <c r="AE445" s="1" t="n">
+        <v>0.03569</v>
+      </c>
+      <c r="AF445" s="2" t="n">
+        <v>0.002809778027535906</v>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
@@ -42439,6 +45115,12 @@
       <c r="AD446" s="2" t="n">
         <v>0.006159209761766446</v>
       </c>
+      <c r="AE446" s="1" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="AF446" s="2" t="n">
+        <v>0.004851004851004734</v>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
@@ -42533,6 +45215,12 @@
       <c r="AD447" s="2" t="n">
         <v>0.001223615784643623</v>
       </c>
+      <c r="AE447" s="1" t="n">
+        <v>3.268</v>
+      </c>
+      <c r="AF447" s="3" t="n">
+        <v>-0.00152765047357175</v>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
@@ -42627,6 +45315,12 @@
       <c r="AD448" s="2" t="n">
         <v>0.001560792882784499</v>
       </c>
+      <c r="AE448" s="1" t="n">
+        <v>0.06418</v>
+      </c>
+      <c r="AF448" s="2" t="n">
+        <v>0.000155836060464331</v>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
@@ -42721,6 +45415,12 @@
       <c r="AD449" s="2" t="n">
         <v>0.001226492232215841</v>
       </c>
+      <c r="AE449" s="1" t="n">
+        <v>0.4904</v>
+      </c>
+      <c r="AF449" s="2" t="n">
+        <v>0.001224989791751714</v>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
@@ -42815,6 +45515,12 @@
       <c r="AD450" s="3" t="n">
         <v>-0.0007951232441028955</v>
       </c>
+      <c r="AE450" s="1" t="n">
+        <v>0.03761</v>
+      </c>
+      <c r="AF450" s="3" t="n">
+        <v>-0.002387267904509279</v>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -42909,6 +45615,12 @@
       <c r="AD451" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AE451" s="1" t="n">
+        <v>0.0055</v>
+      </c>
+      <c r="AF451" s="2" t="n">
+        <v>0.001821493624772239</v>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
@@ -43003,6 +45715,12 @@
       <c r="AD452" s="2" t="n">
         <v>0.001438986953184932</v>
       </c>
+      <c r="AE452" s="1" t="n">
+        <v>0.10452</v>
+      </c>
+      <c r="AF452" s="2" t="n">
+        <v>0.001245330012453349</v>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
@@ -43097,6 +45815,12 @@
       <c r="AD453" s="3" t="n">
         <v>-0.00369458128078824</v>
       </c>
+      <c r="AE453" s="1" t="n">
+        <v>0.0161</v>
+      </c>
+      <c r="AF453" s="3" t="n">
+        <v>-0.004944375772558727</v>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
@@ -43191,6 +45915,12 @@
       <c r="AD454" s="2" t="n">
         <v>0.003485535029626973</v>
       </c>
+      <c r="AE454" s="1" t="n">
+        <v>2.874</v>
+      </c>
+      <c r="AF454" s="3" t="n">
+        <v>-0.001736714136853037</v>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
@@ -43285,6 +46015,12 @@
       <c r="AD455" s="2" t="n">
         <v>0.002237136465324387</v>
       </c>
+      <c r="AE455" s="1" t="n">
+        <v>0.895</v>
+      </c>
+      <c r="AF455" s="3" t="n">
+        <v>-0.00111607142857143</v>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
@@ -43379,6 +46115,12 @@
       <c r="AD456" s="3" t="n">
         <v>-0.0006777363605558196</v>
       </c>
+      <c r="AE456" s="1" t="n">
+        <v>2.952</v>
+      </c>
+      <c r="AF456" s="2" t="n">
+        <v>0.001017293997965451</v>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -43473,6 +46215,12 @@
       <c r="AD457" s="2" t="n">
         <v>0.001012145748987813</v>
       </c>
+      <c r="AE457" s="1" t="n">
+        <v>0.009849999999999999</v>
+      </c>
+      <c r="AF457" s="3" t="n">
+        <v>-0.00404448938321538</v>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
@@ -43567,6 +46315,12 @@
       <c r="AD458" s="2" t="n">
         <v>0.004171346061286752</v>
       </c>
+      <c r="AE458" s="1" t="n">
+        <v>0.06264</v>
+      </c>
+      <c r="AF458" s="2" t="n">
+        <v>0.0007988496564945597</v>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
@@ -43661,6 +46415,12 @@
       <c r="AD459" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AE459" s="1" t="n">
+        <v>0.01435</v>
+      </c>
+      <c r="AF459" s="3" t="n">
+        <v>-0.0006963788300835371</v>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
@@ -43755,6 +46515,12 @@
       <c r="AD460" s="2" t="n">
         <v>0.000562499999999912</v>
       </c>
+      <c r="AE460" s="1" t="n">
+        <v>0.016017</v>
+      </c>
+      <c r="AF460" s="2" t="n">
+        <v>0.0004997189081142521</v>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
@@ -43849,6 +46615,12 @@
       <c r="AD461" s="2" t="n">
         <v>0.001196172248803987</v>
       </c>
+      <c r="AE461" s="1" t="n">
+        <v>0.01671</v>
+      </c>
+      <c r="AF461" s="3" t="n">
+        <v>-0.001792114695340636</v>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
@@ -43943,6 +46715,12 @@
       <c r="AD462" s="3" t="n">
         <v>-0.00143747005270727</v>
       </c>
+      <c r="AE462" s="1" t="n">
+        <v>0.0002085</v>
+      </c>
+      <c r="AF462" s="2" t="n">
+        <v>0.0004798464491362881</v>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
@@ -44037,6 +46815,12 @@
       <c r="AD463" s="3" t="n">
         <v>-0.004980079681274905</v>
       </c>
+      <c r="AE463" s="1" t="n">
+        <v>0.0992</v>
+      </c>
+      <c r="AF463" s="3" t="n">
+        <v>-0.007007007007007069</v>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
@@ -44131,6 +46915,12 @@
       <c r="AD464" s="2" t="n">
         <v>0.02528301886792455</v>
       </c>
+      <c r="AE464" s="1" t="n">
+        <v>0.02628</v>
+      </c>
+      <c r="AF464" s="3" t="n">
+        <v>-0.03275671696724323</v>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
@@ -44225,6 +47015,12 @@
       <c r="AD465" s="2" t="n">
         <v>0.007994670219853336</v>
       </c>
+      <c r="AE465" s="1" t="n">
+        <v>0.01504</v>
+      </c>
+      <c r="AF465" s="3" t="n">
+        <v>-0.005948446794448103</v>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
@@ -44319,6 +47115,12 @@
       <c r="AD466" s="2" t="n">
         <v>0.001279473588009516</v>
       </c>
+      <c r="AE466" s="1" t="n">
+        <v>0.05488</v>
+      </c>
+      <c r="AF466" s="2" t="n">
+        <v>0.001825483753194522</v>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
@@ -44413,6 +47215,12 @@
       <c r="AD467" s="2" t="n">
         <v>0.006958538706871475</v>
       </c>
+      <c r="AE467" s="1" t="n">
+        <v>0.03432</v>
+      </c>
+      <c r="AF467" s="3" t="n">
+        <v>-0.01180535560034534</v>
+      </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
@@ -44507,6 +47315,12 @@
       <c r="AD468" s="3" t="n">
         <v>-0.00328467153284671</v>
       </c>
+      <c r="AE468" s="1" t="n">
+        <v>27.31</v>
+      </c>
+      <c r="AF468" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
@@ -44601,6 +47415,12 @@
       <c r="AD469" s="2" t="n">
         <v>0.0009349539201281725</v>
       </c>
+      <c r="AE469" s="1" t="n">
+        <v>0.000752</v>
+      </c>
+      <c r="AF469" s="2" t="n">
+        <v>0.003469442220442961</v>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
@@ -44695,6 +47515,12 @@
       <c r="AD470" s="2" t="n">
         <v>0.02029312288613305</v>
       </c>
+      <c r="AE470" s="1" t="n">
+        <v>0.891</v>
+      </c>
+      <c r="AF470" s="3" t="n">
+        <v>-0.01546961325966852</v>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
@@ -44789,6 +47615,12 @@
       <c r="AD471" s="2" t="n">
         <v>0.005040322580645131</v>
       </c>
+      <c r="AE471" s="1" t="n">
+        <v>0.00992</v>
+      </c>
+      <c r="AF471" s="3" t="n">
+        <v>-0.005015045135406188</v>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
@@ -44883,6 +47715,12 @@
       <c r="AD472" s="2" t="n">
         <v>0.003851091142490513</v>
       </c>
+      <c r="AE472" s="1" t="n">
+        <v>0.04683</v>
+      </c>
+      <c r="AF472" s="3" t="n">
+        <v>-0.00191815856777508</v>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -44977,6 +47815,12 @@
       <c r="AD473" s="2" t="n">
         <v>0.001459854014598379</v>
       </c>
+      <c r="AE473" s="1" t="n">
+        <v>0.2741</v>
+      </c>
+      <c r="AF473" s="3" t="n">
+        <v>-0.001093294460641279</v>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
@@ -45071,6 +47915,12 @@
       <c r="AD474" s="2" t="n">
         <v>0.002051048313582493</v>
       </c>
+      <c r="AE474" s="1" t="n">
+        <v>0.04393</v>
+      </c>
+      <c r="AF474" s="3" t="n">
+        <v>-0.000909711166704692</v>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
@@ -45165,6 +48015,12 @@
       <c r="AD475" s="2" t="n">
         <v>0.002012787118162403</v>
       </c>
+      <c r="AE475" s="1" t="n">
+        <v>0.008459</v>
+      </c>
+      <c r="AF475" s="3" t="n">
+        <v>-0.0004726456339360192</v>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
@@ -45259,6 +48115,12 @@
       <c r="AD476" s="3" t="n">
         <v>-0.002562538133007955</v>
       </c>
+      <c r="AE476" s="1" t="n">
+        <v>0.08179</v>
+      </c>
+      <c r="AF476" s="2" t="n">
+        <v>0.0006116956202594614</v>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
@@ -45353,6 +48215,12 @@
       <c r="AD477" s="2" t="n">
         <v>0.001473839351510728</v>
       </c>
+      <c r="AE477" s="1" t="n">
+        <v>0.1359</v>
+      </c>
+      <c r="AF477" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
@@ -45447,6 +48315,12 @@
       <c r="AD478" s="2" t="n">
         <v>0.002246630054917653</v>
       </c>
+      <c r="AE478" s="1" t="n">
+        <v>0.3993</v>
+      </c>
+      <c r="AF478" s="3" t="n">
+        <v>-0.005479452054794608</v>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
@@ -45541,6 +48415,12 @@
       <c r="AD479" s="2" t="n">
         <v>0.004509850462853055</v>
       </c>
+      <c r="AE479" s="1" t="n">
+        <v>0.008428</v>
+      </c>
+      <c r="AF479" s="3" t="n">
+        <v>-0.004253308128544374</v>
+      </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
@@ -45635,6 +48515,12 @@
       <c r="AD480" s="2" t="n">
         <v>0.2640718562874252</v>
       </c>
+      <c r="AE480" s="1" t="n">
+        <v>0.01947</v>
+      </c>
+      <c r="AF480" s="3" t="n">
+        <v>-0.07768829938417807</v>
+      </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
@@ -45729,6 +48615,12 @@
       <c r="AD481" s="3" t="n">
         <v>-0.008051118210862691</v>
       </c>
+      <c r="AE481" s="1" t="n">
+        <v>0.07768</v>
+      </c>
+      <c r="AF481" s="2" t="n">
+        <v>0.0007729966503479065</v>
+      </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
@@ -45823,6 +48715,12 @@
       <c r="AD482" s="3" t="n">
         <v>-0.002186444046909143</v>
       </c>
+      <c r="AE482" s="1" t="n">
+        <v>0.05025</v>
+      </c>
+      <c r="AF482" s="2" t="n">
+        <v>0.0009960159362550087</v>
+      </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
@@ -45917,6 +48815,12 @@
       <c r="AD483" s="2" t="n">
         <v>0.001035196687370558</v>
       </c>
+      <c r="AE483" s="1" t="n">
+        <v>0.0097</v>
+      </c>
+      <c r="AF483" s="2" t="n">
+        <v>0.003102378490175855</v>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
@@ -46011,6 +48915,12 @@
       <c r="AD484" s="2" t="n">
         <v>0.003536172093708621</v>
       </c>
+      <c r="AE484" s="1" t="n">
+        <v>0.06814000000000001</v>
+      </c>
+      <c r="AF484" s="2" t="n">
+        <v>0.0004404639553663522</v>
+      </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
@@ -46105,6 +49015,12 @@
       <c r="AD485" s="2" t="n">
         <v>0.003335557038025432</v>
       </c>
+      <c r="AE485" s="1" t="n">
+        <v>0.0004514</v>
+      </c>
+      <c r="AF485" s="2" t="n">
+        <v>0.0004432624113475285</v>
+      </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
@@ -46199,6 +49115,12 @@
       <c r="AD486" s="3" t="n">
         <v>-0.0007570022710066946</v>
       </c>
+      <c r="AE486" s="1" t="n">
+        <v>0.07913000000000001</v>
+      </c>
+      <c r="AF486" s="3" t="n">
+        <v>-0.0008838383838383916</v>
+      </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
@@ -46293,6 +49215,12 @@
       <c r="AD487" s="2" t="n">
         <v>0.01151410477835345</v>
       </c>
+      <c r="AE487" s="1" t="n">
+        <v>0.0001754</v>
+      </c>
+      <c r="AF487" s="3" t="n">
+        <v>-0.00170745589072271</v>
+      </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
@@ -46387,6 +49315,12 @@
       <c r="AD488" s="3" t="n">
         <v>-0.002886643721549865</v>
       </c>
+      <c r="AE488" s="1" t="n">
+        <v>0.08943</v>
+      </c>
+      <c r="AF488" s="3" t="n">
+        <v>-0.004231154659837494</v>
+      </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
@@ -46481,6 +49415,12 @@
       <c r="AD489" s="2" t="n">
         <v>0.002281684297863493</v>
       </c>
+      <c r="AE489" s="1" t="n">
+        <v>0.04817</v>
+      </c>
+      <c r="AF489" s="3" t="n">
+        <v>-0.003104304635761678</v>
+      </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
@@ -46575,6 +49515,12 @@
       <c r="AD490" s="3" t="n">
         <v>-0.01486520534139582</v>
       </c>
+      <c r="AE490" s="1" t="n">
+        <v>0.03887</v>
+      </c>
+      <c r="AF490" s="3" t="n">
+        <v>-0.005882352941176497</v>
+      </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
@@ -46669,6 +49615,12 @@
       <c r="AD491" s="2" t="n">
         <v>0.01529280119358442</v>
       </c>
+      <c r="AE491" s="1" t="n">
+        <v>0.08371000000000001</v>
+      </c>
+      <c r="AF491" s="2" t="n">
+        <v>0.02510409012980664</v>
+      </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
@@ -46763,6 +49715,12 @@
       <c r="AD492" s="3" t="n">
         <v>-0.0009477175801611829</v>
       </c>
+      <c r="AE492" s="1" t="n">
+        <v>0.06304999999999999</v>
+      </c>
+      <c r="AF492" s="3" t="n">
+        <v>-0.00316205533596847</v>
+      </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
@@ -46857,6 +49815,12 @@
       <c r="AD493" s="2" t="n">
         <v>0.001915708812260625</v>
       </c>
+      <c r="AE493" s="1" t="n">
+        <v>0.00524</v>
+      </c>
+      <c r="AF493" s="2" t="n">
+        <v>0.001912045889101261</v>
+      </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
@@ -46951,6 +49915,12 @@
       <c r="AD494" s="2" t="n">
         <v>0.0007283321194463874</v>
       </c>
+      <c r="AE494" s="1" t="n">
+        <v>0.2748</v>
+      </c>
+      <c r="AF494" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
@@ -47045,6 +50015,12 @@
       <c r="AD495" s="2" t="n">
         <v>0.003134796238244604</v>
       </c>
+      <c r="AE495" s="1" t="n">
+        <v>0.06396</v>
+      </c>
+      <c r="AF495" s="3" t="n">
+        <v>-0.0006249999999999745</v>
+      </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
@@ -47139,6 +50115,12 @@
       <c r="AD496" s="2" t="n">
         <v>0.0003408316291751499</v>
       </c>
+      <c r="AE496" s="1" t="n">
+        <v>0.2932</v>
+      </c>
+      <c r="AF496" s="3" t="n">
+        <v>-0.001022146507665986</v>
+      </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
@@ -47233,6 +50215,12 @@
       <c r="AD497" s="2" t="n">
         <v>0.002420382165605041</v>
       </c>
+      <c r="AE497" s="1" t="n">
+        <v>0.07929</v>
+      </c>
+      <c r="AF497" s="2" t="n">
+        <v>0.007624857033930657</v>
+      </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
@@ -47327,6 +50315,12 @@
       <c r="AD498" s="2" t="n">
         <v>0.0009718172983478035</v>
       </c>
+      <c r="AE498" s="1" t="n">
+        <v>0.103</v>
+      </c>
+      <c r="AF498" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
@@ -47421,6 +50415,12 @@
       <c r="AD499" s="2" t="n">
         <v>0.006695361071257664</v>
       </c>
+      <c r="AE499" s="1" t="n">
+        <v>0.04192</v>
+      </c>
+      <c r="AF499" s="3" t="n">
+        <v>-0.004275534441805217</v>
+      </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
@@ -47515,6 +50515,12 @@
       <c r="AD500" s="3" t="n">
         <v>-0.003735059760956282</v>
       </c>
+      <c r="AE500" s="1" t="n">
+        <v>0.04012</v>
+      </c>
+      <c r="AF500" s="2" t="n">
+        <v>0.00274931267183219</v>
+      </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
@@ -47609,6 +50615,12 @@
       <c r="AD501" s="2" t="n">
         <v>0.003024193548387183</v>
       </c>
+      <c r="AE501" s="1" t="n">
+        <v>0.0998</v>
+      </c>
+      <c r="AF501" s="2" t="n">
+        <v>0.003015075376884369</v>
+      </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
@@ -47703,6 +50715,12 @@
       <c r="AD502" s="2" t="n">
         <v>0.001506477854775604</v>
       </c>
+      <c r="AE502" s="1" t="n">
+        <v>0.003324</v>
+      </c>
+      <c r="AF502" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
@@ -47797,6 +50815,12 @@
       <c r="AD503" s="3" t="n">
         <v>-0.001095290251916713</v>
       </c>
+      <c r="AE503" s="1" t="n">
+        <v>0.009129999999999999</v>
+      </c>
+      <c r="AF503" s="2" t="n">
+        <v>0.001096491228070131</v>
+      </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
@@ -47891,6 +50915,12 @@
       <c r="AD504" s="2" t="n">
         <v>0.002509410288582255</v>
       </c>
+      <c r="AE504" s="1" t="n">
+        <v>0.1597</v>
+      </c>
+      <c r="AF504" s="3" t="n">
+        <v>-0.000625782227784662</v>
+      </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
@@ -47985,6 +51015,12 @@
       <c r="AD505" s="2" t="n">
         <v>0.002277904328018183</v>
       </c>
+      <c r="AE505" s="1" t="n">
+        <v>0.132</v>
+      </c>
+      <c r="AF505" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
@@ -48079,6 +51115,12 @@
       <c r="AD506" s="2" t="n">
         <v>0.0005834305717619366</v>
       </c>
+      <c r="AE506" s="1" t="n">
+        <v>0.01704</v>
+      </c>
+      <c r="AF506" s="3" t="n">
+        <v>-0.006413994169096151</v>
+      </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
@@ -48173,6 +51215,12 @@
       <c r="AD507" s="2" t="n">
         <v>0.0003496503496502444</v>
       </c>
+      <c r="AE507" s="1" t="n">
+        <v>0.002877</v>
+      </c>
+      <c r="AF507" s="2" t="n">
+        <v>0.00559245019224046</v>
+      </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
@@ -48267,6 +51315,12 @@
       <c r="AD508" s="3" t="n">
         <v>-0.001357466063348468</v>
       </c>
+      <c r="AE508" s="1" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AF508" s="3" t="n">
+        <v>-0.003171726325328353</v>
+      </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
@@ -48361,6 +51415,12 @@
       <c r="AD509" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AE509" s="1" t="n">
+        <v>0.05502</v>
+      </c>
+      <c r="AF509" s="2" t="n">
+        <v>0.0007275372862858925</v>
+      </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
@@ -48455,6 +51515,12 @@
       <c r="AD510" s="3" t="n">
         <v>-0.002384196185286124</v>
       </c>
+      <c r="AE510" s="1" t="n">
+        <v>0.02965</v>
+      </c>
+      <c r="AF510" s="2" t="n">
+        <v>0.01229088426083985</v>
+      </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
@@ -48549,6 +51615,12 @@
       <c r="AD511" s="2" t="n">
         <v>0.002725470763131788</v>
       </c>
+      <c r="AE511" s="1" t="n">
+        <v>0.04049</v>
+      </c>
+      <c r="AF511" s="2" t="n">
+        <v>0.000494193229552735</v>
+      </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
@@ -48643,6 +51715,12 @@
       <c r="AD512" s="3" t="n">
         <v>-0.02173913043478263</v>
       </c>
+      <c r="AE512" s="1" t="n">
+        <v>0.093</v>
+      </c>
+      <c r="AF512" s="2" t="n">
+        <v>0.03333333333333337</v>
+      </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
@@ -48737,6 +51815,12 @@
       <c r="AD513" s="2" t="n">
         <v>0.002067217924779926</v>
       </c>
+      <c r="AE513" s="1" t="n">
+        <v>0.01497</v>
+      </c>
+      <c r="AF513" s="3" t="n">
+        <v>-0.003793172289878203</v>
+      </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
@@ -48831,6 +51915,12 @@
       <c r="AD514" s="2" t="n">
         <v>0.001144819690898716</v>
       </c>
+      <c r="AE514" s="1" t="n">
+        <v>0.1747</v>
+      </c>
+      <c r="AF514" s="3" t="n">
+        <v>-0.001143510577472874</v>
+      </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
@@ -48925,6 +52015,12 @@
       <c r="AD515" s="2" t="n">
         <v>0.001858736059479607</v>
       </c>
+      <c r="AE515" s="1" t="n">
+        <v>0.1075</v>
+      </c>
+      <c r="AF515" s="3" t="n">
+        <v>-0.002782931354360006</v>
+      </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
@@ -49019,6 +52115,12 @@
       <c r="AD516" s="2" t="n">
         <v>0.01498127340823974</v>
       </c>
+      <c r="AE516" s="1" t="n">
+        <v>0.00268</v>
+      </c>
+      <c r="AF516" s="3" t="n">
+        <v>-0.01107011070110704</v>
+      </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
@@ -49113,6 +52215,12 @@
       <c r="AD517" s="2" t="n">
         <v>0.005473025801407285</v>
       </c>
+      <c r="AE517" s="1" t="n">
+        <v>0.00771</v>
+      </c>
+      <c r="AF517" s="3" t="n">
+        <v>-0.0007776049766718415</v>
+      </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
@@ -49207,6 +52315,12 @@
       <c r="AD518" s="3" t="n">
         <v>-0.03900060938452173</v>
       </c>
+      <c r="AE518" s="1" t="n">
+        <v>0.01583</v>
+      </c>
+      <c r="AF518" s="2" t="n">
+        <v>0.003804692454026698</v>
+      </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
@@ -49301,6 +52415,12 @@
       <c r="AD519" s="3" t="n">
         <v>-0.005459292665558886</v>
       </c>
+      <c r="AE519" s="1" t="n">
+        <v>0.004212</v>
+      </c>
+      <c r="AF519" s="2" t="n">
+        <v>0.005250596658711086</v>
+      </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
@@ -49395,6 +52515,12 @@
       <c r="AD520" s="2" t="n">
         <v>0.0008605851979345231</v>
       </c>
+      <c r="AE520" s="1" t="n">
+        <v>0.001162</v>
+      </c>
+      <c r="AF520" s="3" t="n">
+        <v>-0.0008598452278589131</v>
+      </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
@@ -49489,6 +52615,12 @@
       <c r="AD521" s="2" t="n">
         <v>0.0007507507507507202</v>
       </c>
+      <c r="AE521" s="1" t="n">
+        <v>0.01334</v>
+      </c>
+      <c r="AF521" s="2" t="n">
+        <v>0.0007501875468866911</v>
+      </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
@@ -49583,6 +52715,12 @@
       <c r="AD522" s="2" t="n">
         <v>0.00189283634245789</v>
       </c>
+      <c r="AE522" s="1" t="n">
+        <v>0.6878</v>
+      </c>
+      <c r="AF522" s="3" t="n">
+        <v>-0.0004359831419852899</v>
+      </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
@@ -49677,6 +52815,12 @@
       <c r="AD523" s="2" t="n">
         <v>0.00741797432239667</v>
       </c>
+      <c r="AE523" s="1" t="n">
+        <v>0.07054000000000001</v>
+      </c>
+      <c r="AF523" s="3" t="n">
+        <v>-0.001132823562730059</v>
+      </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
@@ -49771,6 +52915,12 @@
       <c r="AD524" s="2" t="n">
         <v>0.0008517887563883809</v>
       </c>
+      <c r="AE524" s="1" t="n">
+        <v>0.01177</v>
+      </c>
+      <c r="AF524" s="2" t="n">
+        <v>0.001702127659574399</v>
+      </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
@@ -49865,6 +53015,12 @@
       <c r="AD525" s="3" t="n">
         <v>-0.0006075334143377639</v>
       </c>
+      <c r="AE525" s="1" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="AF525" s="2" t="n">
+        <v>0.003039513677811637</v>
+      </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
@@ -49959,6 +53115,12 @@
       <c r="AD526" s="3" t="n">
         <v>-0.00372661548781397</v>
       </c>
+      <c r="AE526" s="1" t="n">
+        <v>0.13386</v>
+      </c>
+      <c r="AF526" s="2" t="n">
+        <v>0.001421410937383076</v>
+      </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
@@ -50053,6 +53215,12 @@
       <c r="AD527" s="3" t="n">
         <v>-0.0006979990693344651</v>
       </c>
+      <c r="AE527" s="1" t="n">
+        <v>0.04298</v>
+      </c>
+      <c r="AF527" s="2" t="n">
+        <v>0.0006984866123398209</v>
+      </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
@@ -50147,6 +53315,12 @@
       <c r="AD528" s="2" t="n">
         <v>0.004379562043795543</v>
       </c>
+      <c r="AE528" s="1" t="n">
+        <v>0.2752</v>
+      </c>
+      <c r="AF528" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
@@ -50241,6 +53415,12 @@
       <c r="AD529" s="2" t="n">
         <v>0.0001376462491396397</v>
       </c>
+      <c r="AE529" s="1" t="n">
+        <v>0.0007266</v>
+      </c>
+      <c r="AF529" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
@@ -50335,6 +53515,12 @@
       <c r="AD530" s="2" t="n">
         <v>0.004310344827586156</v>
       </c>
+      <c r="AE530" s="1" t="n">
+        <v>0.0042</v>
+      </c>
+      <c r="AF530" s="2" t="n">
+        <v>0.001430615164520727</v>
+      </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
@@ -50429,6 +53615,12 @@
       <c r="AD531" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AE531" s="1" t="n">
+        <v>1.313</v>
+      </c>
+      <c r="AF531" s="2" t="n">
+        <v>0.0007621951219511355</v>
+      </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
@@ -50523,6 +53715,12 @@
       <c r="AD532" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AE532" s="1" t="n">
+        <v>0.118</v>
+      </c>
+      <c r="AF532" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
@@ -50617,6 +53815,12 @@
       <c r="AD533" s="2" t="n">
         <v>0.002808462834675235</v>
       </c>
+      <c r="AE533" s="1" t="n">
+        <v>0.05352</v>
+      </c>
+      <c r="AF533" s="3" t="n">
+        <v>-0.0007468259895445352</v>
+      </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
@@ -50711,6 +53915,12 @@
       <c r="AD534" s="2" t="n">
         <v>0.0006648936170212034</v>
       </c>
+      <c r="AE534" s="1" t="n">
+        <v>0.1505</v>
+      </c>
+      <c r="AF534" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
@@ -50805,6 +54015,12 @@
       <c r="AD535" s="2" t="n">
         <v>0.008660508083140925</v>
       </c>
+      <c r="AE535" s="1" t="n">
+        <v>0.01742</v>
+      </c>
+      <c r="AF535" s="3" t="n">
+        <v>-0.002862049227246592</v>
+      </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
@@ -50899,6 +54115,12 @@
       <c r="AD536" s="2" t="n">
         <v>0.00199840127897691</v>
       </c>
+      <c r="AE536" s="1" t="n">
+        <v>0.004997</v>
+      </c>
+      <c r="AF536" s="3" t="n">
+        <v>-0.003390506581571703</v>
+      </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
@@ -50993,6 +54215,12 @@
       <c r="AD537" s="2" t="n">
         <v>0.00205549845837612</v>
       </c>
+      <c r="AE537" s="1" t="n">
+        <v>0.2928</v>
+      </c>
+      <c r="AF537" s="2" t="n">
+        <v>0.001025641025641103</v>
+      </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
@@ -51087,6 +54315,12 @@
       <c r="AD538" s="3" t="n">
         <v>-0.0007530120481927404</v>
       </c>
+      <c r="AE538" s="1" t="n">
+        <v>0.01329</v>
+      </c>
+      <c r="AF538" s="2" t="n">
+        <v>0.001507159005274995</v>
+      </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
@@ -51181,6 +54415,12 @@
       <c r="AD539" s="2" t="n">
         <v>0.001191895113229987</v>
       </c>
+      <c r="AE539" s="1" t="n">
+        <v>0.02518</v>
+      </c>
+      <c r="AF539" s="3" t="n">
+        <v>-0.0007936507936507613</v>
+      </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
@@ -51275,6 +54515,12 @@
       <c r="AD540" s="2" t="n">
         <v>0.004575048389934951</v>
       </c>
+      <c r="AE540" s="1" t="n">
+        <v>0.05719</v>
+      </c>
+      <c r="AF540" s="2" t="n">
+        <v>0.001751620248730004</v>
+      </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
@@ -51369,6 +54615,12 @@
       <c r="AD541" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AE541" s="1" t="n">
+        <v>0.0115</v>
+      </c>
+      <c r="AF541" s="3" t="n">
+        <v>-0.008620689655172362</v>
+      </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
@@ -51463,6 +54715,12 @@
       <c r="AD542" s="2" t="n">
         <v>0.009009009009008922</v>
       </c>
+      <c r="AE542" s="1" t="n">
+        <v>1.12e-05</v>
+      </c>
+      <c r="AF542" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
@@ -51556,6 +54814,12 @@
       </c>
       <c r="AD543" s="2" t="n">
         <v>0.001087251970644223</v>
+      </c>
+      <c r="AE543" s="1" t="n">
+        <v>0.003688</v>
+      </c>
+      <c r="AF543" s="2" t="n">
+        <v>0.001357588922074341</v>
       </c>
     </row>
   </sheetData>

--- a/binance-usdt-perpetual-data/weeks/2026-03-09_2026-03-15/2026-03-12.xlsx
+++ b/binance-usdt-perpetual-data/weeks/2026-03-09_2026-03-15/2026-03-12.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF543"/>
+  <dimension ref="A1:AH543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -458,6 +458,8 @@
     <col width="18" customWidth="1" min="30" max="30"/>
     <col width="13" customWidth="1" min="31" max="31"/>
     <col width="18" customWidth="1" min="32" max="32"/>
+    <col width="13" customWidth="1" min="33" max="33"/>
+    <col width="18" customWidth="1" min="34" max="34"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -621,6 +623,16 @@
           <t>change_03:45</t>
         </is>
       </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>price_04:00</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>change_04:00</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -721,6 +733,12 @@
       <c r="AF2" s="2" t="n">
         <v>0.002240138919824715</v>
       </c>
+      <c r="AG2" s="1" t="n">
+        <v>70610</v>
+      </c>
+      <c r="AH2" s="3" t="n">
+        <v>-0.000489775580865428</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -821,6 +839,12 @@
       <c r="AF3" s="2" t="n">
         <v>0.001168432996161588</v>
       </c>
+      <c r="AG3" s="1" t="n">
+        <v>2075.57</v>
+      </c>
+      <c r="AH3" s="2" t="n">
+        <v>0.0009645201271237527</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -921,6 +945,12 @@
       <c r="AF4" s="2" t="n">
         <v>0.0009176416609313866</v>
       </c>
+      <c r="AG4" s="1" t="n">
+        <v>87.22</v>
+      </c>
+      <c r="AH4" s="3" t="n">
+        <v>-0.000458400183360145</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1021,6 +1051,12 @@
       <c r="AF5" s="3" t="n">
         <v>-0.0005073566717402378</v>
       </c>
+      <c r="AG5" s="1" t="n">
+        <v>0.013707</v>
+      </c>
+      <c r="AH5" s="3" t="n">
+        <v>-0.006018854242204478</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1121,6 +1157,12 @@
       <c r="AF6" s="3" t="n">
         <v>-0.001277003298925137</v>
       </c>
+      <c r="AG6" s="1" t="n">
+        <v>0.09382</v>
+      </c>
+      <c r="AH6" s="3" t="n">
+        <v>-0.0003196590303676318</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1221,6 +1263,12 @@
       <c r="AF7" s="3" t="n">
         <v>-0.0005746713598160419</v>
       </c>
+      <c r="AG7" s="1" t="n">
+        <v>1.3891</v>
+      </c>
+      <c r="AH7" s="3" t="n">
+        <v>-0.001581254941421677</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1321,6 +1369,12 @@
       <c r="AF8" s="2" t="n">
         <v>0.001300426097061508</v>
       </c>
+      <c r="AG8" s="1" t="n">
+        <v>36.326</v>
+      </c>
+      <c r="AH8" s="2" t="n">
+        <v>0.003785680731714069</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1421,6 +1475,12 @@
       <c r="AF9" s="2" t="n">
         <v>0.002347453856421702</v>
       </c>
+      <c r="AG9" s="1" t="n">
+        <v>653.37</v>
+      </c>
+      <c r="AH9" s="2" t="n">
+        <v>0.0001071483238941528</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1521,6 +1581,12 @@
       <c r="AF10" s="2" t="n">
         <v>0.005623176026763516</v>
       </c>
+      <c r="AG10" s="1" t="n">
+        <v>14.015</v>
+      </c>
+      <c r="AH10" s="3" t="n">
+        <v>-0.007998301245753082</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1621,6 +1687,12 @@
       <c r="AF11" s="2" t="n">
         <v>0.003417602996254767</v>
       </c>
+      <c r="AG11" s="1" t="n">
+        <v>213.82</v>
+      </c>
+      <c r="AH11" s="3" t="n">
+        <v>-0.002379508234964864</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1721,6 +1793,12 @@
       <c r="AF12" s="2" t="n">
         <v>0.0007725219871643011</v>
       </c>
+      <c r="AG12" s="1" t="n">
+        <v>0.0033661</v>
+      </c>
+      <c r="AH12" s="3" t="n">
+        <v>-0.0006234784157710662</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1821,6 +1899,12 @@
       <c r="AF13" s="2" t="n">
         <v>0.001996007984032028</v>
       </c>
+      <c r="AG13" s="1" t="n">
+        <v>0.04004</v>
+      </c>
+      <c r="AH13" s="3" t="n">
+        <v>-0.002988047808764991</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1921,6 +2005,12 @@
       <c r="AF14" s="2" t="n">
         <v>0.002264150943396312</v>
       </c>
+      <c r="AG14" s="1" t="n">
+        <v>2.654</v>
+      </c>
+      <c r="AH14" s="3" t="n">
+        <v>-0.0007530120481928554</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2021,6 +2111,12 @@
       <c r="AF15" s="2" t="n">
         <v>0.00392472577236592</v>
       </c>
+      <c r="AG15" s="1" t="n">
+        <v>0.9917</v>
+      </c>
+      <c r="AH15" s="3" t="n">
+        <v>-0.005914194065757835</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2121,6 +2217,12 @@
       <c r="AF16" s="2" t="n">
         <v>0.000177588350204281</v>
       </c>
+      <c r="AG16" s="1" t="n">
+        <v>0.05615</v>
+      </c>
+      <c r="AH16" s="3" t="n">
+        <v>-0.003018465909090971</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2221,6 +2323,12 @@
       <c r="AF17" s="3" t="n">
         <v>-0.00112233445566779</v>
       </c>
+      <c r="AG17" s="1" t="n">
+        <v>0.886</v>
+      </c>
+      <c r="AH17" s="3" t="n">
+        <v>-0.004494382022471914</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2321,6 +2429,12 @@
       <c r="AF18" s="2" t="n">
         <v>0.001129943502824734</v>
       </c>
+      <c r="AG18" s="1" t="n">
+        <v>0.2652</v>
+      </c>
+      <c r="AH18" s="3" t="n">
+        <v>-0.002257336343115084</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2421,6 +2535,12 @@
       <c r="AF19" s="3" t="n">
         <v>-0.004428251121076305</v>
       </c>
+      <c r="AG19" s="1" t="n">
+        <v>0.35787</v>
+      </c>
+      <c r="AH19" s="2" t="n">
+        <v>0.007460165531220205</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2521,6 +2641,12 @@
       <c r="AF20" s="3" t="n">
         <v>-0.0001030184403009397</v>
       </c>
+      <c r="AG20" s="1" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="AH20" s="3" t="n">
+        <v>-0.0006181743251597185</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2621,6 +2747,12 @@
       <c r="AF21" s="2" t="n">
         <v>0.006798670041189046</v>
       </c>
+      <c r="AG21" s="1" t="n">
+        <v>201.64</v>
+      </c>
+      <c r="AH21" s="3" t="n">
+        <v>-0.006111987381703515</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2721,6 +2853,12 @@
       <c r="AF22" s="3" t="n">
         <v>-0.01682935038707504</v>
       </c>
+      <c r="AG22" s="1" t="n">
+        <v>0.020502</v>
+      </c>
+      <c r="AH22" s="2" t="n">
+        <v>0.002689881156159803</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2821,6 +2959,12 @@
       <c r="AF23" s="2" t="n">
         <v>0.001881920434154573</v>
       </c>
+      <c r="AG23" s="1" t="n">
+        <v>457.55</v>
+      </c>
+      <c r="AH23" s="3" t="n">
+        <v>-0.0006334090511968453</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2921,6 +3065,12 @@
       <c r="AF24" s="2" t="n">
         <v>0.0004772725516111822</v>
       </c>
+      <c r="AG24" s="1" t="n">
+        <v>5181.4</v>
+      </c>
+      <c r="AH24" s="2" t="n">
+        <v>0.000712670273151567</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3021,6 +3171,12 @@
       <c r="AF25" s="2" t="n">
         <v>0.001873071837813955</v>
       </c>
+      <c r="AG25" s="1" t="n">
+        <v>9.083</v>
+      </c>
+      <c r="AH25" s="3" t="n">
+        <v>-0.001099747058176596</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3121,6 +3277,12 @@
       <c r="AF26" s="3" t="n">
         <v>-0.009053156146179351</v>
       </c>
+      <c r="AG26" s="1" t="n">
+        <v>0.11856</v>
+      </c>
+      <c r="AH26" s="3" t="n">
+        <v>-0.006286145335680167</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3221,6 +3383,12 @@
       <c r="AF27" s="3" t="n">
         <v>-0.004284490145672639</v>
       </c>
+      <c r="AG27" s="1" t="n">
+        <v>0.01165</v>
+      </c>
+      <c r="AH27" s="2" t="n">
+        <v>0.002581755593803831</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3321,6 +3489,12 @@
       <c r="AF28" s="2" t="n">
         <v>0.004651162790697679</v>
       </c>
+      <c r="AG28" s="1" t="n">
+        <v>1.295</v>
+      </c>
+      <c r="AH28" s="3" t="n">
+        <v>-0.0007716049382716913</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3421,6 +3595,12 @@
       <c r="AF29" s="3" t="n">
         <v>-0.007489361702127591</v>
       </c>
+      <c r="AG29" s="1" t="n">
+        <v>0.05749</v>
+      </c>
+      <c r="AH29" s="3" t="n">
+        <v>-0.01406276796432861</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3521,6 +3701,12 @@
       <c r="AF30" s="2" t="n">
         <v>0.00324886289798578</v>
       </c>
+      <c r="AG30" s="1" t="n">
+        <v>1.538</v>
+      </c>
+      <c r="AH30" s="3" t="n">
+        <v>-0.003886010362694304</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3621,6 +3807,12 @@
       <c r="AF31" s="2" t="n">
         <v>0.006464445549477866</v>
       </c>
+      <c r="AG31" s="1" t="n">
+        <v>0.002018</v>
+      </c>
+      <c r="AH31" s="3" t="n">
+        <v>-0.002964426877470535</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3721,6 +3913,12 @@
       <c r="AF32" s="2" t="n">
         <v>0.0004972650422675084</v>
       </c>
+      <c r="AG32" s="1" t="n">
+        <v>0.04009</v>
+      </c>
+      <c r="AH32" s="3" t="n">
+        <v>-0.003727634194830948</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3821,6 +4019,12 @@
       <c r="AF33" s="3" t="n">
         <v>-0.001014198782961349</v>
       </c>
+      <c r="AG33" s="1" t="n">
+        <v>0.0985</v>
+      </c>
+      <c r="AH33" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3921,6 +4125,12 @@
       <c r="AF34" s="2" t="n">
         <v>0.003798670465337109</v>
       </c>
+      <c r="AG34" s="1" t="n">
+        <v>0.1056</v>
+      </c>
+      <c r="AH34" s="3" t="n">
+        <v>-0.0009460737937559401</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -4021,6 +4231,12 @@
       <c r="AF35" s="3" t="n">
         <v>-0.004424778761061959</v>
       </c>
+      <c r="AG35" s="1" t="n">
+        <v>0.008869999999999999</v>
+      </c>
+      <c r="AH35" s="3" t="n">
+        <v>-0.01444444444444444</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -4121,6 +4337,12 @@
       <c r="AF36" s="2" t="n">
         <v>0.001954215522054658</v>
       </c>
+      <c r="AG36" s="1" t="n">
+        <v>0.3588</v>
+      </c>
+      <c r="AH36" s="3" t="n">
+        <v>-0.0002786291446084954</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -4221,6 +4443,12 @@
       <c r="AF37" s="3" t="n">
         <v>-0.000688231245698646</v>
       </c>
+      <c r="AG37" s="1" t="n">
+        <v>0.005797</v>
+      </c>
+      <c r="AH37" s="3" t="n">
+        <v>-0.001893939393939347</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -4321,6 +4549,12 @@
       <c r="AF38" s="2" t="n">
         <v>0.001966682091624288</v>
       </c>
+      <c r="AG38" s="1" t="n">
+        <v>0.26011</v>
+      </c>
+      <c r="AH38" s="2" t="n">
+        <v>0.001077627679636695</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -4421,6 +4655,12 @@
       <c r="AF39" s="2" t="n">
         <v>0.0007912957467854661</v>
       </c>
+      <c r="AG39" s="1" t="n">
+        <v>0.05042</v>
+      </c>
+      <c r="AH39" s="3" t="n">
+        <v>-0.003360347894840946</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -4521,6 +4761,12 @@
       <c r="AF40" s="2" t="n">
         <v>0.0009377721213745142</v>
       </c>
+      <c r="AG40" s="1" t="n">
+        <v>0.14893</v>
+      </c>
+      <c r="AH40" s="3" t="n">
+        <v>-0.0033460483169377</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -4621,6 +4867,12 @@
       <c r="AF41" s="2" t="n">
         <v>0.001179941002949722</v>
       </c>
+      <c r="AG41" s="1" t="n">
+        <v>0.1693</v>
+      </c>
+      <c r="AH41" s="3" t="n">
+        <v>-0.002357100766057653</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -4721,6 +4973,12 @@
       <c r="AF42" s="2" t="n">
         <v>0.002316671121803358</v>
       </c>
+      <c r="AG42" s="1" t="n">
+        <v>112.19</v>
+      </c>
+      <c r="AH42" s="3" t="n">
+        <v>-0.00266690372477551</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -4821,6 +5079,12 @@
       <c r="AF43" s="3" t="n">
         <v>-0.01123337918386052</v>
       </c>
+      <c r="AG43" s="1" t="n">
+        <v>0.8519</v>
+      </c>
+      <c r="AH43" s="3" t="n">
+        <v>-0.01240435891490847</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -4921,6 +5185,12 @@
       <c r="AF44" s="2" t="n">
         <v>0.0003635041802980011</v>
       </c>
+      <c r="AG44" s="1" t="n">
+        <v>55.02</v>
+      </c>
+      <c r="AH44" s="3" t="n">
+        <v>-0.0003633720930231835</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -5021,6 +5291,12 @@
       <c r="AF45" s="2" t="n">
         <v>0.008047672881258468</v>
       </c>
+      <c r="AG45" s="1" t="n">
+        <v>0.52501</v>
+      </c>
+      <c r="AH45" s="3" t="n">
+        <v>-0.002052880685814157</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -5121,6 +5397,12 @@
       <c r="AF46" s="3" t="n">
         <v>-0.0002857551078725217</v>
       </c>
+      <c r="AG46" s="1" t="n">
+        <v>0.6991000000000001</v>
+      </c>
+      <c r="AH46" s="3" t="n">
+        <v>-0.0008575103615834414</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -5221,6 +5503,12 @@
       <c r="AF47" s="2" t="n">
         <v>0.001526717557251853</v>
       </c>
+      <c r="AG47" s="1" t="n">
+        <v>3.924</v>
+      </c>
+      <c r="AH47" s="3" t="n">
+        <v>-0.003048780487804881</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -5321,6 +5609,12 @@
       <c r="AF48" s="3" t="n">
         <v>-0.0004999062675748094</v>
       </c>
+      <c r="AG48" s="1" t="n">
+        <v>0.15992</v>
+      </c>
+      <c r="AH48" s="3" t="n">
+        <v>-0.0001875586120662847</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -5421,6 +5715,12 @@
       <c r="AF49" s="3" t="n">
         <v>-0.00211829884308291</v>
       </c>
+      <c r="AG49" s="1" t="n">
+        <v>0.06196</v>
+      </c>
+      <c r="AH49" s="2" t="n">
+        <v>0.01175702155453949</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -5521,6 +5821,12 @@
       <c r="AF50" s="2" t="n">
         <v>0.002570694087403673</v>
       </c>
+      <c r="AG50" s="1" t="n">
+        <v>0.039</v>
+      </c>
+      <c r="AH50" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -5621,6 +5927,12 @@
       <c r="AF51" s="3" t="n">
         <v>-0.02644526445264442</v>
       </c>
+      <c r="AG51" s="1" t="n">
+        <v>0.28157</v>
+      </c>
+      <c r="AH51" s="3" t="n">
+        <v>-0.01182705130904766</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -5721,6 +6033,12 @@
       <c r="AF52" s="2" t="n">
         <v>0.0003401360544217313</v>
       </c>
+      <c r="AG52" s="1" t="n">
+        <v>0.2933</v>
+      </c>
+      <c r="AH52" s="3" t="n">
+        <v>-0.002720163209792477</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -5821,6 +6139,12 @@
       <c r="AF53" s="2" t="n">
         <v>0.007537688442210922</v>
       </c>
+      <c r="AG53" s="1" t="n">
+        <v>0.1601</v>
+      </c>
+      <c r="AH53" s="3" t="n">
+        <v>-0.001870324189526152</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -5921,6 +6245,12 @@
       <c r="AF54" s="2" t="n">
         <v>0.0002759477079094357</v>
       </c>
+      <c r="AG54" s="1" t="n">
+        <v>0.29015</v>
+      </c>
+      <c r="AH54" s="2" t="n">
+        <v>0.0005517431635573415</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -6021,6 +6351,12 @@
       <c r="AF55" s="2" t="n">
         <v>0.001261387526278953</v>
       </c>
+      <c r="AG55" s="1" t="n">
+        <v>0.007135</v>
+      </c>
+      <c r="AH55" s="3" t="n">
+        <v>-0.001259798432250886</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -6121,6 +6457,12 @@
       <c r="AF56" s="2" t="n">
         <v>0.02730496453900709</v>
       </c>
+      <c r="AG56" s="1" t="n">
+        <v>0.02909</v>
+      </c>
+      <c r="AH56" s="2" t="n">
+        <v>0.00414221608560587</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -6221,6 +6563,12 @@
       <c r="AF57" s="3" t="n">
         <v>-0.004276550249465422</v>
       </c>
+      <c r="AG57" s="1" t="n">
+        <v>0.04211</v>
+      </c>
+      <c r="AH57" s="2" t="n">
+        <v>0.004772130756382695</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -6321,6 +6669,12 @@
       <c r="AF58" s="2" t="n">
         <v>0.001234821979831191</v>
       </c>
+      <c r="AG58" s="1" t="n">
+        <v>0.04863</v>
+      </c>
+      <c r="AH58" s="3" t="n">
+        <v>-0.0004110996916752145</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -6421,6 +6775,12 @@
       <c r="AF59" s="2" t="n">
         <v>0.0006464124111183659</v>
       </c>
+      <c r="AG59" s="1" t="n">
+        <v>1.545</v>
+      </c>
+      <c r="AH59" s="3" t="n">
+        <v>-0.001937984496124104</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -6521,6 +6881,12 @@
       <c r="AF60" s="3" t="n">
         <v>-0.002906976744186054</v>
       </c>
+      <c r="AG60" s="1" t="n">
+        <v>0.00343</v>
+      </c>
+      <c r="AH60" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -6621,6 +6987,12 @@
       <c r="AF61" s="2" t="n">
         <v>0.003856041131105509</v>
       </c>
+      <c r="AG61" s="1" t="n">
+        <v>0.1556</v>
+      </c>
+      <c r="AH61" s="3" t="n">
+        <v>-0.003841229193341979</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -6721,6 +7093,12 @@
       <c r="AF62" s="3" t="n">
         <v>-0.0008748906386702642</v>
       </c>
+      <c r="AG62" s="1" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AH62" s="3" t="n">
+        <v>-0.001751313485113837</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -6821,6 +7199,12 @@
       <c r="AF63" s="2" t="n">
         <v>0.002850627137970356</v>
       </c>
+      <c r="AG63" s="1" t="n">
+        <v>0.7017</v>
+      </c>
+      <c r="AH63" s="3" t="n">
+        <v>-0.002700397953382622</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -6921,6 +7305,12 @@
       <c r="AF64" s="3" t="n">
         <v>-0.001702417432754475</v>
       </c>
+      <c r="AG64" s="1" t="n">
+        <v>2.929</v>
+      </c>
+      <c r="AH64" s="3" t="n">
+        <v>-0.00102319236016375</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -7021,6 +7411,12 @@
       <c r="AF65" s="2" t="n">
         <v>0.002542372881355976</v>
       </c>
+      <c r="AG65" s="1" t="n">
+        <v>0.02359</v>
+      </c>
+      <c r="AH65" s="3" t="n">
+        <v>-0.002958579881656831</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -7121,6 +7517,12 @@
       <c r="AF66" s="2" t="n">
         <v>0.0009871668311945002</v>
       </c>
+      <c r="AG66" s="1" t="n">
+        <v>0.1012</v>
+      </c>
+      <c r="AH66" s="3" t="n">
+        <v>-0.00197238658777126</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -7221,6 +7623,12 @@
       <c r="AF67" s="3" t="n">
         <v>-0.004632783758005202</v>
       </c>
+      <c r="AG67" s="1" t="n">
+        <v>0.007254</v>
+      </c>
+      <c r="AH67" s="3" t="n">
+        <v>-0.006981519507186835</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -7321,6 +7729,12 @@
       <c r="AF68" s="2" t="n">
         <v>0.001086366105377489</v>
       </c>
+      <c r="AG68" s="1" t="n">
+        <v>18.42</v>
+      </c>
+      <c r="AH68" s="3" t="n">
+        <v>-0.0005425935973954428</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -7421,6 +7835,12 @@
       <c r="AF69" s="2" t="n">
         <v>0.0005509641873278649</v>
       </c>
+      <c r="AG69" s="1" t="n">
+        <v>0.05432</v>
+      </c>
+      <c r="AH69" s="3" t="n">
+        <v>-0.002936857562408231</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -7521,6 +7941,12 @@
       <c r="AF70" s="2" t="n">
         <v>0.004255319148936175</v>
       </c>
+      <c r="AG70" s="1" t="n">
+        <v>0.235</v>
+      </c>
+      <c r="AH70" s="3" t="n">
+        <v>-0.004237288135593225</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -7621,6 +8047,12 @@
       <c r="AF71" s="2" t="n">
         <v>0.008961518186610465</v>
       </c>
+      <c r="AG71" s="1" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AH71" s="3" t="n">
+        <v>-0.007314524555903834</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -7721,6 +8153,12 @@
       <c r="AF72" s="3" t="n">
         <v>-0.001122964626614289</v>
       </c>
+      <c r="AG72" s="1" t="n">
+        <v>0.001744</v>
+      </c>
+      <c r="AH72" s="3" t="n">
+        <v>-0.01967397414277677</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -7821,6 +8259,12 @@
       <c r="AF73" s="2" t="n">
         <v>0.003820844831245953</v>
       </c>
+      <c r="AG73" s="1" t="n">
+        <v>0.9422</v>
+      </c>
+      <c r="AH73" s="3" t="n">
+        <v>-0.00380630154366667</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -7921,6 +8365,12 @@
       <c r="AF74" s="2" t="n">
         <v>0.00332225913621272</v>
       </c>
+      <c r="AG74" s="1" t="n">
+        <v>0.1205</v>
+      </c>
+      <c r="AH74" s="3" t="n">
+        <v>-0.002483443708609343</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -8021,6 +8471,12 @@
       <c r="AF75" s="2" t="n">
         <v>0.001411153759313615</v>
       </c>
+      <c r="AG75" s="1" t="n">
+        <v>355.26</v>
+      </c>
+      <c r="AH75" s="2" t="n">
+        <v>0.001240065385265762</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -8121,6 +8577,12 @@
       <c r="AF76" s="3" t="n">
         <v>-0.0003394433129667207</v>
       </c>
+      <c r="AG76" s="1" t="n">
+        <v>0.11696</v>
+      </c>
+      <c r="AH76" s="3" t="n">
+        <v>-0.007130730050933849</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -8221,6 +8683,12 @@
       <c r="AF77" s="2" t="n">
         <v>0.002859412231930097</v>
       </c>
+      <c r="AG77" s="1" t="n">
+        <v>0.06288000000000001</v>
+      </c>
+      <c r="AH77" s="3" t="n">
+        <v>-0.003960082369713293</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -8321,6 +8789,12 @@
       <c r="AF78" s="2" t="n">
         <v>0.005076142131979635</v>
       </c>
+      <c r="AG78" s="1" t="n">
+        <v>0.09485</v>
+      </c>
+      <c r="AH78" s="3" t="n">
+        <v>-0.001999158249158204</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -8421,6 +8895,12 @@
       <c r="AF79" s="2" t="n">
         <v>0.001494768310911921</v>
       </c>
+      <c r="AG79" s="1" t="n">
+        <v>0.4043</v>
+      </c>
+      <c r="AH79" s="2" t="n">
+        <v>0.005721393034825792</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -8521,6 +9001,12 @@
       <c r="AF80" s="3" t="n">
         <v>-0.0001663893510815529</v>
       </c>
+      <c r="AG80" s="1" t="n">
+        <v>0.005997</v>
+      </c>
+      <c r="AH80" s="3" t="n">
+        <v>-0.001997004493260086</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -8621,6 +9107,12 @@
       <c r="AF81" s="3" t="n">
         <v>-0.009689922480620164</v>
       </c>
+      <c r="AG81" s="1" t="n">
+        <v>0.102</v>
+      </c>
+      <c r="AH81" s="3" t="n">
+        <v>-0.001956947162426671</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -8721,6 +9213,12 @@
       <c r="AF82" s="3" t="n">
         <v>-0.0009852216748768754</v>
       </c>
+      <c r="AG82" s="1" t="n">
+        <v>0.1013</v>
+      </c>
+      <c r="AH82" s="3" t="n">
+        <v>-0.0009861932938856298</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -8821,6 +9319,12 @@
       <c r="AF83" s="2" t="n">
         <v>0.0006505122784192287</v>
       </c>
+      <c r="AG83" s="1" t="n">
+        <v>0.06192</v>
+      </c>
+      <c r="AH83" s="2" t="n">
+        <v>0.00633837152608486</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -8921,6 +9425,12 @@
       <c r="AF84" s="2" t="n">
         <v>0.0001789869339538017</v>
       </c>
+      <c r="AG84" s="1" t="n">
+        <v>1.1092</v>
+      </c>
+      <c r="AH84" s="3" t="n">
+        <v>-0.007516105941302759</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -9021,6 +9531,12 @@
       <c r="AF85" s="2" t="n">
         <v>0.003067484662576695</v>
       </c>
+      <c r="AG85" s="1" t="n">
+        <v>0.01292</v>
+      </c>
+      <c r="AH85" s="3" t="n">
+        <v>-0.01223241590214071</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -9121,6 +9637,12 @@
       <c r="AF86" s="2" t="n">
         <v>0.0005977286312016176</v>
       </c>
+      <c r="AG86" s="1" t="n">
+        <v>0.01674</v>
+      </c>
+      <c r="AH86" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -9221,6 +9743,12 @@
       <c r="AF87" s="2" t="n">
         <v>0.001924233313289238</v>
       </c>
+      <c r="AG87" s="1" t="n">
+        <v>8.321999999999999</v>
+      </c>
+      <c r="AH87" s="3" t="n">
+        <v>-0.001080302484695756</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -9321,6 +9849,12 @@
       <c r="AF88" s="2" t="n">
         <v>0.001725504826750109</v>
       </c>
+      <c r="AG88" s="1" t="n">
+        <v>2.1451</v>
+      </c>
+      <c r="AH88" s="3" t="n">
+        <v>-0.001350093109869808</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -9421,6 +9955,12 @@
       <c r="AF89" s="3" t="n">
         <v>-0.0001425110446059759</v>
       </c>
+      <c r="AG89" s="1" t="n">
+        <v>0.007012</v>
+      </c>
+      <c r="AH89" s="3" t="n">
+        <v>-0.0005701254275940228</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -9521,6 +10061,12 @@
       <c r="AF90" s="3" t="n">
         <v>-0.0006544502617800908</v>
       </c>
+      <c r="AG90" s="1" t="n">
+        <v>15.26</v>
+      </c>
+      <c r="AH90" s="3" t="n">
+        <v>-0.0006548788474132146</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -9621,6 +10167,12 @@
       <c r="AF91" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AG91" s="1" t="n">
+        <v>0.000222</v>
+      </c>
+      <c r="AH91" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -9721,6 +10273,12 @@
       <c r="AF92" s="2" t="n">
         <v>0.004947668886774563</v>
       </c>
+      <c r="AG92" s="1" t="n">
+        <v>0.05207</v>
+      </c>
+      <c r="AH92" s="3" t="n">
+        <v>-0.01401249763302413</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -9821,6 +10379,12 @@
       <c r="AF93" s="2" t="n">
         <v>0.003235758898336948</v>
       </c>
+      <c r="AG93" s="1" t="n">
+        <v>1.3318</v>
+      </c>
+      <c r="AH93" s="3" t="n">
+        <v>-0.001050105010500935</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -9921,6 +10485,12 @@
       <c r="AF94" s="3" t="n">
         <v>-0.0009037422305833827</v>
       </c>
+      <c r="AG94" s="1" t="n">
+        <v>0.054259</v>
+      </c>
+      <c r="AH94" s="2" t="n">
+        <v>0.001642975816872786</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -10021,6 +10591,12 @@
       <c r="AF95" s="3" t="n">
         <v>-0.0008336807002918121</v>
       </c>
+      <c r="AG95" s="1" t="n">
+        <v>0.2401</v>
+      </c>
+      <c r="AH95" s="2" t="n">
+        <v>0.001668752607425997</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -10121,6 +10697,12 @@
       <c r="AF96" s="3" t="n">
         <v>-0.004167438414521365</v>
       </c>
+      <c r="AG96" s="1" t="n">
+        <v>1.0731</v>
+      </c>
+      <c r="AH96" s="3" t="n">
+        <v>-0.002045940667720618</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -10221,6 +10803,12 @@
       <c r="AF97" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AG97" s="1" t="n">
+        <v>0.2579</v>
+      </c>
+      <c r="AH97" s="2" t="n">
+        <v>0.0003878975950350834</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -10321,6 +10909,12 @@
       <c r="AF98" s="3" t="n">
         <v>-0.004299226139295026</v>
       </c>
+      <c r="AG98" s="1" t="n">
+        <v>0.5775</v>
+      </c>
+      <c r="AH98" s="3" t="n">
+        <v>-0.00259067357512944</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -10421,6 +11015,12 @@
       <c r="AF99" s="3" t="n">
         <v>-0.01005173688100517</v>
       </c>
+      <c r="AG99" s="1" t="n">
+        <v>0.13353</v>
+      </c>
+      <c r="AH99" s="3" t="n">
+        <v>-0.003061072121845556</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -10521,6 +11121,12 @@
       <c r="AF100" s="2" t="n">
         <v>0.0003197953309882655</v>
       </c>
+      <c r="AG100" s="1" t="n">
+        <v>0.03133</v>
+      </c>
+      <c r="AH100" s="2" t="n">
+        <v>0.001598465473145604</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -10621,6 +11227,12 @@
       <c r="AF101" s="2" t="n">
         <v>0.003813155386081987</v>
       </c>
+      <c r="AG101" s="1" t="n">
+        <v>1.047</v>
+      </c>
+      <c r="AH101" s="3" t="n">
+        <v>-0.005698005698005703</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -10721,6 +11333,12 @@
       <c r="AF102" s="3" t="n">
         <v>-0.001351351351351452</v>
       </c>
+      <c r="AG102" s="1" t="n">
+        <v>0.02205</v>
+      </c>
+      <c r="AH102" s="3" t="n">
+        <v>-0.005412719891745538</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -10821,6 +11439,12 @@
       <c r="AF103" s="2" t="n">
         <v>0.0005099439061703005</v>
       </c>
+      <c r="AG103" s="1" t="n">
+        <v>0.01955</v>
+      </c>
+      <c r="AH103" s="3" t="n">
+        <v>-0.003567787971457551</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -10921,6 +11545,12 @@
       <c r="AF104" s="2" t="n">
         <v>0.0009983361064892227</v>
       </c>
+      <c r="AG104" s="1" t="n">
+        <v>3.005</v>
+      </c>
+      <c r="AH104" s="3" t="n">
+        <v>-0.0009973404255319528</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -11021,6 +11651,12 @@
       <c r="AF105" s="2" t="n">
         <v>0.001537988311288965</v>
       </c>
+      <c r="AG105" s="1" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="AH105" s="3" t="n">
+        <v>-0.001842751842751912</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -11121,6 +11757,12 @@
       <c r="AF106" s="2" t="n">
         <v>0.001815980629539919</v>
       </c>
+      <c r="AG106" s="1" t="n">
+        <v>0.1656</v>
+      </c>
+      <c r="AH106" s="2" t="n">
+        <v>0.0006042296072506887</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -11221,6 +11863,12 @@
       <c r="AF107" s="3" t="n">
         <v>-0.001103022281050078</v>
       </c>
+      <c r="AG107" s="1" t="n">
+        <v>0.4487</v>
+      </c>
+      <c r="AH107" s="3" t="n">
+        <v>-0.009054770318021186</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -11321,6 +11969,12 @@
       <c r="AF108" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AG108" s="1" t="n">
+        <v>0.3366</v>
+      </c>
+      <c r="AH108" s="3" t="n">
+        <v>-0.0008904719501334728</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -11421,6 +12075,12 @@
       <c r="AF109" s="3" t="n">
         <v>-0.008333333333333389</v>
       </c>
+      <c r="AG109" s="1" t="n">
+        <v>0.2263</v>
+      </c>
+      <c r="AH109" s="2" t="n">
+        <v>0.0008845643520566374</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -11521,6 +12181,12 @@
       <c r="AF110" s="3" t="n">
         <v>-0.0006618133686300193</v>
       </c>
+      <c r="AG110" s="1" t="n">
+        <v>0.01508</v>
+      </c>
+      <c r="AH110" s="3" t="n">
+        <v>-0.001324503311258339</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -11621,6 +12287,12 @@
       <c r="AF111" s="3" t="n">
         <v>-0.001088139281828075</v>
       </c>
+      <c r="AG111" s="1" t="n">
+        <v>1.836</v>
+      </c>
+      <c r="AH111" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -11721,6 +12393,12 @@
       <c r="AF112" s="3" t="n">
         <v>-0.0002622606871228986</v>
       </c>
+      <c r="AG112" s="1" t="n">
+        <v>0.03822</v>
+      </c>
+      <c r="AH112" s="2" t="n">
+        <v>0.002623294858341971</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -11821,6 +12499,12 @@
       <c r="AF113" s="3" t="n">
         <v>-0.001170686022008872</v>
       </c>
+      <c r="AG113" s="1" t="n">
+        <v>4.264</v>
+      </c>
+      <c r="AH113" s="3" t="n">
+        <v>-0.0004688232536333286</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -11921,6 +12605,12 @@
       <c r="AF114" s="3" t="n">
         <v>-0.0105374077976818</v>
       </c>
+      <c r="AG114" s="1" t="n">
+        <v>0.007571</v>
+      </c>
+      <c r="AH114" s="2" t="n">
+        <v>0.007854100106496276</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -12021,6 +12711,12 @@
       <c r="AF115" s="3" t="n">
         <v>-0.0009936406995229431</v>
       </c>
+      <c r="AG115" s="1" t="n">
+        <v>0.10023</v>
+      </c>
+      <c r="AH115" s="3" t="n">
+        <v>-0.003083349910483436</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -12121,6 +12817,12 @@
       <c r="AF116" s="2" t="n">
         <v>0.0001203079884503865</v>
       </c>
+      <c r="AG116" s="1" t="n">
+        <v>0.08302</v>
+      </c>
+      <c r="AH116" s="3" t="n">
+        <v>-0.001323228677974245</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -12221,6 +12923,12 @@
       <c r="AF117" s="2" t="n">
         <v>0.001333777925975363</v>
       </c>
+      <c r="AG117" s="1" t="n">
+        <v>0.3001</v>
+      </c>
+      <c r="AH117" s="3" t="n">
+        <v>-0.0006660006660007775</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -12321,6 +13029,12 @@
       <c r="AF118" s="2" t="n">
         <v>0.0004448398576512274</v>
       </c>
+      <c r="AG118" s="1" t="n">
+        <v>0.02244</v>
+      </c>
+      <c r="AH118" s="3" t="n">
+        <v>-0.002223210315695774</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -12421,6 +13135,12 @@
       <c r="AF119" s="2" t="n">
         <v>0.003285151116951383</v>
       </c>
+      <c r="AG119" s="1" t="n">
+        <v>0.1515</v>
+      </c>
+      <c r="AH119" s="3" t="n">
+        <v>-0.007858546168958785</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -12521,6 +13241,12 @@
       <c r="AF120" s="3" t="n">
         <v>-0.02928225451343027</v>
       </c>
+      <c r="AG120" s="1" t="n">
+        <v>0.004272</v>
+      </c>
+      <c r="AH120" s="3" t="n">
+        <v>-0.03107280562485824</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -12621,6 +13347,12 @@
       <c r="AF121" s="2" t="n">
         <v>0.0009197516670499229</v>
       </c>
+      <c r="AG121" s="1" t="n">
+        <v>0.4326</v>
+      </c>
+      <c r="AH121" s="3" t="n">
+        <v>-0.006202618883528683</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -12721,6 +13453,12 @@
       <c r="AF122" s="3" t="n">
         <v>-0.001288659793814434</v>
       </c>
+      <c r="AG122" s="1" t="n">
+        <v>0.775</v>
+      </c>
+      <c r="AH122" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -12821,6 +13559,12 @@
       <c r="AF123" s="2" t="n">
         <v>0.00115740740740728</v>
       </c>
+      <c r="AG123" s="1" t="n">
+        <v>0.08649999999999999</v>
+      </c>
+      <c r="AH123" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -12921,6 +13665,12 @@
       <c r="AF124" s="3" t="n">
         <v>-0.004870129870129813</v>
       </c>
+      <c r="AG124" s="1" t="n">
+        <v>0.01222</v>
+      </c>
+      <c r="AH124" s="3" t="n">
+        <v>-0.003262642740619911</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -13021,6 +13771,12 @@
       <c r="AF125" s="2" t="n">
         <v>0.002352219267743854</v>
       </c>
+      <c r="AG125" s="1" t="n">
+        <v>0.09797</v>
+      </c>
+      <c r="AH125" s="3" t="n">
+        <v>-0.0004081216202428157</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -13121,6 +13877,12 @@
       <c r="AF126" s="3" t="n">
         <v>-0.008322663252240748</v>
       </c>
+      <c r="AG126" s="1" t="n">
+        <v>0.04666</v>
+      </c>
+      <c r="AH126" s="2" t="n">
+        <v>0.004088659350118413</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -13221,6 +13983,12 @@
       <c r="AF127" s="3" t="n">
         <v>-0.006230529595015516</v>
       </c>
+      <c r="AG127" s="1" t="n">
+        <v>3.2e-05</v>
+      </c>
+      <c r="AH127" s="2" t="n">
+        <v>0.003134796238244378</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -13321,6 +14089,12 @@
       <c r="AF128" s="3" t="n">
         <v>-0.0008821453775581245</v>
       </c>
+      <c r="AG128" s="1" t="n">
+        <v>0.5671</v>
+      </c>
+      <c r="AH128" s="2" t="n">
+        <v>0.001412678792159673</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -13421,6 +14195,12 @@
       <c r="AF129" s="2" t="n">
         <v>0.0003093580819799865</v>
       </c>
+      <c r="AG129" s="1" t="n">
+        <v>0.06463000000000001</v>
+      </c>
+      <c r="AH129" s="3" t="n">
+        <v>-0.0006185248183083094</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -13521,6 +14301,12 @@
       <c r="AF130" s="2" t="n">
         <v>0.005757525908866641</v>
       </c>
+      <c r="AG130" s="1" t="n">
+        <v>0.0006108</v>
+      </c>
+      <c r="AH130" s="3" t="n">
+        <v>-0.0009813542688910935</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -13621,6 +14407,12 @@
       <c r="AF131" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AG131" s="1" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="AH131" s="3" t="n">
+        <v>-0.01136363636363637</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -13721,6 +14513,12 @@
       <c r="AF132" s="3" t="n">
         <v>-0.0003326679973386194</v>
       </c>
+      <c r="AG132" s="1" t="n">
+        <v>0.3002</v>
+      </c>
+      <c r="AH132" s="3" t="n">
+        <v>-0.0009983361064890748</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -13821,6 +14619,12 @@
       <c r="AF133" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AG133" s="1" t="n">
+        <v>0.03406</v>
+      </c>
+      <c r="AH133" s="2" t="n">
+        <v>0.005609684086212066</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -13921,6 +14725,12 @@
       <c r="AF134" s="3" t="n">
         <v>-0.004161464835622066</v>
       </c>
+      <c r="AG134" s="1" t="n">
+        <v>0.14446</v>
+      </c>
+      <c r="AH134" s="2" t="n">
+        <v>0.006128987324139796</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -14021,6 +14831,12 @@
       <c r="AF135" s="3" t="n">
         <v>-0.000337381916329271</v>
       </c>
+      <c r="AG135" s="1" t="n">
+        <v>0.02957</v>
+      </c>
+      <c r="AH135" s="3" t="n">
+        <v>-0.002024974687816437</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -14121,6 +14937,12 @@
       <c r="AF136" s="3" t="n">
         <v>-0.002478753541076372</v>
       </c>
+      <c r="AG136" s="1" t="n">
+        <v>28.07</v>
+      </c>
+      <c r="AH136" s="3" t="n">
+        <v>-0.003549875754348648</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -14221,6 +15043,12 @@
       <c r="AF137" s="3" t="n">
         <v>-0.003430924062214049</v>
       </c>
+      <c r="AG137" s="1" t="n">
+        <v>0.0004342</v>
+      </c>
+      <c r="AH137" s="3" t="n">
+        <v>-0.003442735827404261</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -14321,6 +15149,12 @@
       <c r="AF138" s="3" t="n">
         <v>-0.007487405976123177</v>
       </c>
+      <c r="AG138" s="1" t="n">
+        <v>0.028693</v>
+      </c>
+      <c r="AH138" s="3" t="n">
+        <v>-0.002503041891187177</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -14421,6 +15255,12 @@
       <c r="AF139" s="3" t="n">
         <v>-0.0009323526364861363</v>
       </c>
+      <c r="AG139" s="1" t="n">
+        <v>0.09651999999999999</v>
+      </c>
+      <c r="AH139" s="2" t="n">
+        <v>0.0008295313148071002</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -14521,6 +15361,12 @@
       <c r="AF140" s="3" t="n">
         <v>-0.004428452809299724</v>
       </c>
+      <c r="AG140" s="1" t="n">
+        <v>0.3611</v>
+      </c>
+      <c r="AH140" s="2" t="n">
+        <v>0.003892132332499185</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -14621,6 +15467,12 @@
       <c r="AF141" s="2" t="n">
         <v>0.001510574018126827</v>
       </c>
+      <c r="AG141" s="1" t="n">
+        <v>0.02651</v>
+      </c>
+      <c r="AH141" s="3" t="n">
+        <v>-0.0003770739064856559</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -14721,6 +15573,12 @@
       <c r="AF142" s="2" t="n">
         <v>0.0005035246727089422</v>
       </c>
+      <c r="AG142" s="1" t="n">
+        <v>0.07967</v>
+      </c>
+      <c r="AH142" s="2" t="n">
+        <v>0.002390538500251756</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -14821,6 +15679,12 @@
       <c r="AF143" s="2" t="n">
         <v>0.001816736686726551</v>
       </c>
+      <c r="AG143" s="1" t="n">
+        <v>0.08827</v>
+      </c>
+      <c r="AH143" s="2" t="n">
+        <v>0.0004533605349654128</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -14921,6 +15785,12 @@
       <c r="AF144" s="2" t="n">
         <v>0.01025891548607728</v>
       </c>
+      <c r="AG144" s="1" t="n">
+        <v>0.02061</v>
+      </c>
+      <c r="AH144" s="3" t="n">
+        <v>-0.003384912959381074</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -15021,6 +15891,12 @@
       <c r="AF145" s="3" t="n">
         <v>-0.001049685094471737</v>
       </c>
+      <c r="AG145" s="1" t="n">
+        <v>0.1142</v>
+      </c>
+      <c r="AH145" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -15121,6 +15997,12 @@
       <c r="AF146" s="2" t="n">
         <v>0.00660938532716458</v>
       </c>
+      <c r="AG146" s="1" t="n">
+        <v>0.3045</v>
+      </c>
+      <c r="AH146" s="3" t="n">
+        <v>-0.0003282994090610276</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -15221,6 +16103,12 @@
       <c r="AF147" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AG147" s="1" t="n">
+        <v>0.124</v>
+      </c>
+      <c r="AH147" s="2" t="n">
+        <v>0.008130081300813016</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -15321,6 +16209,12 @@
       <c r="AF148" s="3" t="n">
         <v>-0.002798982188295196</v>
       </c>
+      <c r="AG148" s="1" t="n">
+        <v>1.9568</v>
+      </c>
+      <c r="AH148" s="3" t="n">
+        <v>-0.001377902526154593</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -15421,6 +16315,12 @@
       <c r="AF149" s="3" t="n">
         <v>-0.0006476683937824693</v>
       </c>
+      <c r="AG149" s="1" t="n">
+        <v>0.06172</v>
+      </c>
+      <c r="AH149" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -15521,6 +16421,12 @@
       <c r="AF150" s="3" t="n">
         <v>-0.00184049079754598</v>
       </c>
+      <c r="AG150" s="1" t="n">
+        <v>0.1625</v>
+      </c>
+      <c r="AH150" s="3" t="n">
+        <v>-0.001229256299938572</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -15621,6 +16527,12 @@
       <c r="AF151" s="3" t="n">
         <v>-0.000892857142857084</v>
       </c>
+      <c r="AG151" s="1" t="n">
+        <v>6.709e-05</v>
+      </c>
+      <c r="AH151" s="3" t="n">
+        <v>-0.0007447125409592079</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -15721,6 +16633,12 @@
       <c r="AF152" s="3" t="n">
         <v>-0.004089979550102319</v>
       </c>
+      <c r="AG152" s="1" t="n">
+        <v>0.01458</v>
+      </c>
+      <c r="AH152" s="3" t="n">
+        <v>-0.002053388090349111</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -15821,6 +16739,12 @@
       <c r="AF153" s="2" t="n">
         <v>0.002373042240151943</v>
       </c>
+      <c r="AG153" s="1" t="n">
+        <v>0.02109</v>
+      </c>
+      <c r="AH153" s="3" t="n">
+        <v>-0.001420454545454488</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -15921,6 +16845,12 @@
       <c r="AF154" s="2" t="n">
         <v>0.001177856301531333</v>
       </c>
+      <c r="AG154" s="1" t="n">
+        <v>0.0005934</v>
+      </c>
+      <c r="AH154" s="3" t="n">
+        <v>-0.002689075630252166</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -16021,6 +16951,12 @@
       <c r="AF155" s="2" t="n">
         <v>0.0007460830639143324</v>
       </c>
+      <c r="AG155" s="1" t="n">
+        <v>0.04022</v>
+      </c>
+      <c r="AH155" s="3" t="n">
+        <v>-0.000497017892644115</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -16121,6 +17057,12 @@
       <c r="AF156" s="2" t="n">
         <v>0.003166226912928631</v>
       </c>
+      <c r="AG156" s="1" t="n">
+        <v>0.01899</v>
+      </c>
+      <c r="AH156" s="3" t="n">
+        <v>-0.001052077853761136</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -16221,6 +17163,12 @@
       <c r="AF157" s="2" t="n">
         <v>0.01092456301747938</v>
       </c>
+      <c r="AG157" s="1" t="n">
+        <v>0.08748</v>
+      </c>
+      <c r="AH157" s="3" t="n">
+        <v>-0.004891366169946535</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -16321,6 +17269,12 @@
       <c r="AF158" s="3" t="n">
         <v>-0.006419400855919935</v>
       </c>
+      <c r="AG158" s="1" t="n">
+        <v>0.008411</v>
+      </c>
+      <c r="AH158" s="2" t="n">
+        <v>0.006341229959320319</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -16421,6 +17375,12 @@
       <c r="AF159" s="2" t="n">
         <v>0.0003977724741449221</v>
       </c>
+      <c r="AG159" s="1" t="n">
+        <v>2.515</v>
+      </c>
+      <c r="AH159" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -16521,6 +17481,12 @@
       <c r="AF160" s="2" t="n">
         <v>0.003584229390680955</v>
       </c>
+      <c r="AG160" s="1" t="n">
+        <v>1.2877</v>
+      </c>
+      <c r="AH160" s="3" t="n">
+        <v>-0.0002329192546583594</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -16621,6 +17587,12 @@
       <c r="AF161" s="3" t="n">
         <v>-0.001724595383390934</v>
       </c>
+      <c r="AG161" s="1" t="n">
+        <v>0.007525</v>
+      </c>
+      <c r="AH161" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -16721,6 +17693,12 @@
       <c r="AF162" s="3" t="n">
         <v>-0.0002434274586171532</v>
       </c>
+      <c r="AG162" s="1" t="n">
+        <v>0.004097</v>
+      </c>
+      <c r="AH162" s="3" t="n">
+        <v>-0.002434867299732276</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -16821,6 +17799,12 @@
       <c r="AF163" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AG163" s="1" t="n">
+        <v>0.09669999999999999</v>
+      </c>
+      <c r="AH163" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -16921,6 +17905,12 @@
       <c r="AF164" s="2" t="n">
         <v>0.002025902611967233</v>
       </c>
+      <c r="AG164" s="1" t="n">
+        <v>1.3842</v>
+      </c>
+      <c r="AH164" s="3" t="n">
+        <v>-0.000505451657159306</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -17021,6 +18011,12 @@
       <c r="AF165" s="3" t="n">
         <v>-0.008006099885627069</v>
       </c>
+      <c r="AG165" s="1" t="n">
+        <v>0.023437</v>
+      </c>
+      <c r="AH165" s="2" t="n">
+        <v>0.0008113417029634547</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -17121,6 +18117,12 @@
       <c r="AF166" s="3" t="n">
         <v>-0.004661099242571318</v>
       </c>
+      <c r="AG166" s="1" t="n">
+        <v>0.005155</v>
+      </c>
+      <c r="AH166" s="2" t="n">
+        <v>0.005853658536585296</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -17221,6 +18223,12 @@
       <c r="AF167" s="3" t="n">
         <v>-0.001524390243902483</v>
       </c>
+      <c r="AG167" s="1" t="n">
+        <v>0.06607</v>
+      </c>
+      <c r="AH167" s="2" t="n">
+        <v>0.008702290076335894</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -17321,6 +18329,12 @@
       <c r="AF168" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AG168" s="1" t="n">
+        <v>0.0956</v>
+      </c>
+      <c r="AH168" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -17421,6 +18435,12 @@
       <c r="AF169" s="2" t="n">
         <v>0.001817709685795913</v>
       </c>
+      <c r="AG169" s="1" t="n">
+        <v>0.03864</v>
+      </c>
+      <c r="AH169" s="2" t="n">
+        <v>0.001555209953343638</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -17521,6 +18541,12 @@
       <c r="AF170" s="2" t="n">
         <v>0.001822004204625086</v>
       </c>
+      <c r="AG170" s="1" t="n">
+        <v>0.007147</v>
+      </c>
+      <c r="AH170" s="3" t="n">
+        <v>-0.0001398992725238015</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -17621,6 +18647,12 @@
       <c r="AF171" s="2" t="n">
         <v>0.004120070629782261</v>
       </c>
+      <c r="AG171" s="1" t="n">
+        <v>0.3416</v>
+      </c>
+      <c r="AH171" s="2" t="n">
+        <v>0.001172332942555719</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -17721,6 +18753,12 @@
       <c r="AF172" s="3" t="n">
         <v>-0.0001828153564898438</v>
       </c>
+      <c r="AG172" s="1" t="n">
+        <v>5.466</v>
+      </c>
+      <c r="AH172" s="3" t="n">
+        <v>-0.0005485463521667788</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -17821,6 +18859,12 @@
       <c r="AF173" s="3" t="n">
         <v>-0.001312335958005196</v>
       </c>
+      <c r="AG173" s="1" t="n">
+        <v>0.04566</v>
+      </c>
+      <c r="AH173" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -17921,6 +18965,12 @@
       <c r="AF174" s="3" t="n">
         <v>-0.0005102040816326323</v>
       </c>
+      <c r="AG174" s="1" t="n">
+        <v>0.03913</v>
+      </c>
+      <c r="AH174" s="3" t="n">
+        <v>-0.001276161306789215</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -18021,6 +19071,12 @@
       <c r="AF175" s="3" t="n">
         <v>-0.01090259159964259</v>
       </c>
+      <c r="AG175" s="1" t="n">
+        <v>0.00563</v>
+      </c>
+      <c r="AH175" s="2" t="n">
+        <v>0.01734730755330678</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -18121,6 +19177,12 @@
       <c r="AF176" s="3" t="n">
         <v>-0.001326259946949548</v>
       </c>
+      <c r="AG176" s="1" t="n">
+        <v>0.00756</v>
+      </c>
+      <c r="AH176" s="2" t="n">
+        <v>0.003984063745019873</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -18221,6 +19283,12 @@
       <c r="AF177" s="3" t="n">
         <v>-0.000554016620498554</v>
       </c>
+      <c r="AG177" s="1" t="n">
+        <v>1.795</v>
+      </c>
+      <c r="AH177" s="3" t="n">
+        <v>-0.004988913525498957</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -18321,6 +19389,12 @@
       <c r="AF178" s="2" t="n">
         <v>0.003115066751430355</v>
       </c>
+      <c r="AG178" s="1" t="n">
+        <v>15.778</v>
+      </c>
+      <c r="AH178" s="3" t="n">
+        <v>-6.337537233027732e-05</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -18421,6 +19495,12 @@
       <c r="AF179" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AG179" s="1" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="AH179" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -18521,6 +19601,12 @@
       <c r="AF180" s="2" t="n">
         <v>0.0113219094247246</v>
       </c>
+      <c r="AG180" s="1" t="n">
+        <v>0.09787</v>
+      </c>
+      <c r="AH180" s="3" t="n">
+        <v>-0.01290973272818965</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -18621,6 +19707,12 @@
       <c r="AF181" s="2" t="n">
         <v>0.001063264221158988</v>
       </c>
+      <c r="AG181" s="1" t="n">
+        <v>0.1883</v>
+      </c>
+      <c r="AH181" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -18721,6 +19813,12 @@
       <c r="AF182" s="3" t="n">
         <v>-0.003863598185788695</v>
       </c>
+      <c r="AG182" s="1" t="n">
+        <v>0.05977</v>
+      </c>
+      <c r="AH182" s="2" t="n">
+        <v>0.007925801011804354</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -18821,6 +19919,12 @@
       <c r="AF183" s="2" t="n">
         <v>0.004159733777038389</v>
       </c>
+      <c r="AG183" s="1" t="n">
+        <v>0.01203</v>
+      </c>
+      <c r="AH183" s="3" t="n">
+        <v>-0.003314001657000837</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -18921,6 +20025,12 @@
       <c r="AF184" s="2" t="n">
         <v>0.003260363297624621</v>
       </c>
+      <c r="AG184" s="1" t="n">
+        <v>0.0215</v>
+      </c>
+      <c r="AH184" s="3" t="n">
+        <v>-0.00185701021355626</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -19021,6 +20131,12 @@
       <c r="AF185" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AG185" s="1" t="n">
+        <v>0.367</v>
+      </c>
+      <c r="AH185" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -19121,6 +20237,12 @@
       <c r="AF186" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AG186" s="1" t="n">
+        <v>0.007612</v>
+      </c>
+      <c r="AH186" s="3" t="n">
+        <v>-0.0013119916032538</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -19221,6 +20343,12 @@
       <c r="AF187" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AG187" s="1" t="n">
+        <v>0.2689</v>
+      </c>
+      <c r="AH187" s="3" t="n">
+        <v>-0.004074074074074242</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -19321,6 +20449,12 @@
       <c r="AF188" s="2" t="n">
         <v>0.001420454545454558</v>
       </c>
+      <c r="AG188" s="1" t="n">
+        <v>0.04925</v>
+      </c>
+      <c r="AH188" s="3" t="n">
+        <v>-0.002026342451874284</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -19421,6 +20555,12 @@
       <c r="AF189" s="2" t="n">
         <v>0.001956947162426616</v>
       </c>
+      <c r="AG189" s="1" t="n">
+        <v>0.2554</v>
+      </c>
+      <c r="AH189" s="3" t="n">
+        <v>-0.002343749999999959</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -19521,6 +20661,12 @@
       <c r="AF190" s="3" t="n">
         <v>-0.003849518810148696</v>
       </c>
+      <c r="AG190" s="1" t="n">
+        <v>0.5702</v>
+      </c>
+      <c r="AH190" s="2" t="n">
+        <v>0.001580888810820326</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -19621,6 +20767,12 @@
       <c r="AF191" s="2" t="n">
         <v>0.0008278145695364062</v>
       </c>
+      <c r="AG191" s="1" t="n">
+        <v>6.045</v>
+      </c>
+      <c r="AH191" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -19721,6 +20873,12 @@
       <c r="AF192" s="2" t="n">
         <v>0.001718213058419214</v>
       </c>
+      <c r="AG192" s="1" t="n">
+        <v>0.3492</v>
+      </c>
+      <c r="AH192" s="3" t="n">
+        <v>-0.001715265866209232</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -19821,6 +20979,12 @@
       <c r="AF193" s="2" t="n">
         <v>0.004702194357366906</v>
       </c>
+      <c r="AG193" s="1" t="n">
+        <v>0.0641</v>
+      </c>
+      <c r="AH193" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -19921,6 +21085,12 @@
       <c r="AF194" s="3" t="n">
         <v>-0.002324230098779685</v>
       </c>
+      <c r="AG194" s="1" t="n">
+        <v>0.01715</v>
+      </c>
+      <c r="AH194" s="3" t="n">
+        <v>-0.001164822364589555</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -20021,6 +21191,12 @@
       <c r="AF195" s="3" t="n">
         <v>-0.001642806852851483</v>
       </c>
+      <c r="AG195" s="1" t="n">
+        <v>0.0008573</v>
+      </c>
+      <c r="AH195" s="2" t="n">
+        <v>0.007639868359191344</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -20121,6 +21297,12 @@
       <c r="AF196" s="2" t="n">
         <v>0.00385356454720605</v>
       </c>
+      <c r="AG196" s="1" t="n">
+        <v>0.001036</v>
+      </c>
+      <c r="AH196" s="3" t="n">
+        <v>-0.005758157389635248</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -20221,6 +21403,12 @@
       <c r="AF197" s="3" t="n">
         <v>-0.001233806292412121</v>
       </c>
+      <c r="AG197" s="1" t="n">
+        <v>0.0001618</v>
+      </c>
+      <c r="AH197" s="3" t="n">
+        <v>-0.0006176652254478223</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -20321,6 +21509,12 @@
       <c r="AF198" s="3" t="n">
         <v>-0.002768166089965298</v>
       </c>
+      <c r="AG198" s="1" t="n">
+        <v>4.327</v>
+      </c>
+      <c r="AH198" s="2" t="n">
+        <v>0.0009252833680313576</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -20421,6 +21615,12 @@
       <c r="AF199" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AG199" s="1" t="n">
+        <v>0.1633</v>
+      </c>
+      <c r="AH199" s="3" t="n">
+        <v>-0.0006119951040391003</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -20521,6 +21721,12 @@
       <c r="AF200" s="3" t="n">
         <v>-0.003239460953697248</v>
       </c>
+      <c r="AG200" s="1" t="n">
+        <v>0.023018</v>
+      </c>
+      <c r="AH200" s="3" t="n">
+        <v>-0.002556658144472853</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -20621,6 +21827,12 @@
       <c r="AF201" s="2" t="n">
         <v>0.00113213650331544</v>
       </c>
+      <c r="AG201" s="1" t="n">
+        <v>0.12364</v>
+      </c>
+      <c r="AH201" s="3" t="n">
+        <v>-0.001292407108239043</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -20721,6 +21933,12 @@
       <c r="AF202" s="2" t="n">
         <v>0.005035971223021627</v>
       </c>
+      <c r="AG202" s="1" t="n">
+        <v>0.01398</v>
+      </c>
+      <c r="AH202" s="2" t="n">
+        <v>0.0007158196134573795</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -20821,6 +22039,12 @@
       <c r="AF203" s="3" t="n">
         <v>-0.004146341463414718</v>
       </c>
+      <c r="AG203" s="1" t="n">
+        <v>0.04082</v>
+      </c>
+      <c r="AH203" s="3" t="n">
+        <v>-0.0002449179524858223</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -20921,6 +22145,12 @@
       <c r="AF204" s="2" t="n">
         <v>0.0003861003861003704</v>
       </c>
+      <c r="AG204" s="1" t="n">
+        <v>0.0259</v>
+      </c>
+      <c r="AH204" s="3" t="n">
+        <v>-0.0003859513701273482</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -21021,6 +22251,12 @@
       <c r="AF205" s="2" t="n">
         <v>0.003245248029670868</v>
       </c>
+      <c r="AG205" s="1" t="n">
+        <v>0.433</v>
+      </c>
+      <c r="AH205" s="2" t="n">
+        <v>0.0004621072088724075</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -21121,6 +22357,12 @@
       <c r="AF206" s="2" t="n">
         <v>0.003521126760563389</v>
       </c>
+      <c r="AG206" s="1" t="n">
+        <v>0.02284</v>
+      </c>
+      <c r="AH206" s="2" t="n">
+        <v>0.001754385964912209</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -21221,6 +22463,12 @@
       <c r="AF207" s="3" t="n">
         <v>-0.001431980906921295</v>
       </c>
+      <c r="AG207" s="1" t="n">
+        <v>4.182</v>
+      </c>
+      <c r="AH207" s="3" t="n">
+        <v>-0.000478011472275282</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -21321,6 +22569,12 @@
       <c r="AF208" s="2" t="n">
         <v>0.0005428144931469449</v>
       </c>
+      <c r="AG208" s="1" t="n">
+        <v>0.07371999999999999</v>
+      </c>
+      <c r="AH208" s="3" t="n">
+        <v>-0.0001356300013564356</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -21421,6 +22675,12 @@
       <c r="AF209" s="3" t="n">
         <v>-0.002606017531390642</v>
       </c>
+      <c r="AG209" s="1" t="n">
+        <v>0.0421</v>
+      </c>
+      <c r="AH209" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -21521,6 +22781,12 @@
       <c r="AF210" s="2" t="n">
         <v>0.000539665407447473</v>
       </c>
+      <c r="AG210" s="1" t="n">
+        <v>0.1851</v>
+      </c>
+      <c r="AH210" s="3" t="n">
+        <v>-0.001618122977346399</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -21621,6 +22887,12 @@
       <c r="AF211" s="2" t="n">
         <v>0.003789473684210576</v>
       </c>
+      <c r="AG211" s="1" t="n">
+        <v>0.2373</v>
+      </c>
+      <c r="AH211" s="3" t="n">
+        <v>-0.004614093959731501</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -21721,6 +22993,12 @@
       <c r="AF212" s="3" t="n">
         <v>-0.001409774436090209</v>
       </c>
+      <c r="AG212" s="1" t="n">
+        <v>0.002106</v>
+      </c>
+      <c r="AH212" s="3" t="n">
+        <v>-0.0089411764705884</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -21821,6 +23099,12 @@
       <c r="AF213" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AG213" s="1" t="n">
+        <v>0.929</v>
+      </c>
+      <c r="AH213" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -21921,6 +23205,12 @@
       <c r="AF214" s="3" t="n">
         <v>-0.001219087425983989</v>
       </c>
+      <c r="AG214" s="1" t="n">
+        <v>0.005735</v>
+      </c>
+      <c r="AH214" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -22021,6 +23311,12 @@
       <c r="AF215" s="3" t="n">
         <v>-0.0009144111192392362</v>
       </c>
+      <c r="AG215" s="1" t="n">
+        <v>0.05465</v>
+      </c>
+      <c r="AH215" s="2" t="n">
+        <v>0.0003660992128866774</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -22121,6 +23417,12 @@
       <c r="AF216" s="2" t="n">
         <v>0.001584786053882771</v>
       </c>
+      <c r="AG216" s="1" t="n">
+        <v>0.063</v>
+      </c>
+      <c r="AH216" s="3" t="n">
+        <v>-0.003164556962025407</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -22221,6 +23523,12 @@
       <c r="AF217" s="3" t="n">
         <v>-0.002150537634408664</v>
       </c>
+      <c r="AG217" s="1" t="n">
+        <v>0.0927</v>
+      </c>
+      <c r="AH217" s="3" t="n">
+        <v>-0.001077586206896433</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -22321,6 +23629,12 @@
       <c r="AF218" s="2" t="n">
         <v>0.0003941098491634086</v>
       </c>
+      <c r="AG218" s="1" t="n">
+        <v>0.27935</v>
+      </c>
+      <c r="AH218" s="2" t="n">
+        <v>0.0004655826946492496</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -22421,6 +23735,12 @@
       <c r="AF219" s="3" t="n">
         <v>-0.003350593968930772</v>
       </c>
+      <c r="AG219" s="1" t="n">
+        <v>0.003269</v>
+      </c>
+      <c r="AH219" s="3" t="n">
+        <v>-0.0009168704156479109</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -22521,6 +23841,12 @@
       <c r="AF220" s="3" t="n">
         <v>-1.000626392150242e-06</v>
       </c>
+      <c r="AG220" s="1" t="n">
+        <v>0.999374</v>
+      </c>
+      <c r="AH220" s="2" t="n">
+        <v>1.00062739340442e-06</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -22621,6 +23947,12 @@
       <c r="AF221" s="2" t="n">
         <v>0.002065049044914912</v>
       </c>
+      <c r="AG221" s="1" t="n">
+        <v>0.03868</v>
+      </c>
+      <c r="AH221" s="3" t="n">
+        <v>-0.003606388459556961</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -22721,6 +24053,12 @@
       <c r="AF222" s="3" t="n">
         <v>-0.0004276245456489028</v>
       </c>
+      <c r="AG222" s="1" t="n">
+        <v>0.04669</v>
+      </c>
+      <c r="AH222" s="3" t="n">
+        <v>-0.001283422459892996</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -22821,6 +24159,12 @@
       <c r="AF223" s="2" t="n">
         <v>0.001883239171374688</v>
       </c>
+      <c r="AG223" s="1" t="n">
+        <v>0.1064</v>
+      </c>
+      <c r="AH223" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -22921,6 +24265,12 @@
       <c r="AF224" s="3" t="n">
         <v>-0.001267105930055838</v>
       </c>
+      <c r="AG224" s="1" t="n">
+        <v>3.951</v>
+      </c>
+      <c r="AH224" s="2" t="n">
+        <v>0.002537427048972401</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -23021,6 +24371,12 @@
       <c r="AF225" s="3" t="n">
         <v>-0.002049180327868844</v>
       </c>
+      <c r="AG225" s="1" t="n">
+        <v>0.0009241</v>
+      </c>
+      <c r="AH225" s="3" t="n">
+        <v>-0.001296876688641553</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -23121,6 +24477,12 @@
       <c r="AF226" s="3" t="n">
         <v>-0.002118644067796687</v>
       </c>
+      <c r="AG226" s="1" t="n">
+        <v>0.008453</v>
+      </c>
+      <c r="AH226" s="3" t="n">
+        <v>-0.002948808681292638</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -23221,6 +24583,12 @@
       <c r="AF227" s="3" t="n">
         <v>-0.0009704027171275685</v>
       </c>
+      <c r="AG227" s="1" t="n">
+        <v>0.04113</v>
+      </c>
+      <c r="AH227" s="3" t="n">
+        <v>-0.001214181641573614</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -23321,6 +24689,12 @@
       <c r="AF228" s="2" t="n">
         <v>0.001684919966301532</v>
       </c>
+      <c r="AG228" s="1" t="n">
+        <v>0.03574</v>
+      </c>
+      <c r="AH228" s="2" t="n">
+        <v>0.00196243341743764</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -23421,6 +24795,12 @@
       <c r="AF229" s="2" t="n">
         <v>0.0007714561234329483</v>
       </c>
+      <c r="AG229" s="1" t="n">
+        <v>0.05193</v>
+      </c>
+      <c r="AH229" s="2" t="n">
+        <v>0.0007708614376565499</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -23521,6 +24901,12 @@
       <c r="AF230" s="3" t="n">
         <v>-0.008615738081562218</v>
       </c>
+      <c r="AG230" s="1" t="n">
+        <v>0.001715</v>
+      </c>
+      <c r="AH230" s="3" t="n">
+        <v>-0.0063731170336038</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -23621,6 +25007,12 @@
       <c r="AF231" s="2" t="n">
         <v>0.002259654889071466</v>
       </c>
+      <c r="AG231" s="1" t="n">
+        <v>0.04859</v>
+      </c>
+      <c r="AH231" s="3" t="n">
+        <v>-0.00409920065587208</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -23721,6 +25113,12 @@
       <c r="AF232" s="2" t="n">
         <v>0.002761159687068616</v>
       </c>
+      <c r="AG232" s="1" t="n">
+        <v>0.02176</v>
+      </c>
+      <c r="AH232" s="3" t="n">
+        <v>-0.001376778338687415</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -23821,6 +25219,12 @@
       <c r="AF233" s="3" t="n">
         <v>-0.003220884895745028</v>
       </c>
+      <c r="AG233" s="1" t="n">
+        <v>0.0005874</v>
+      </c>
+      <c r="AH233" s="3" t="n">
+        <v>-0.001020408163265331</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -23921,6 +25325,12 @@
       <c r="AF234" s="2" t="n">
         <v>0.003131426434847524</v>
       </c>
+      <c r="AG234" s="1" t="n">
+        <v>0.21297</v>
+      </c>
+      <c r="AH234" s="3" t="n">
+        <v>-0.007734240320551623</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -24021,6 +25431,12 @@
       <c r="AF235" s="3" t="n">
         <v>-0.01186322400558269</v>
       </c>
+      <c r="AG235" s="1" t="n">
+        <v>0.01416</v>
+      </c>
+      <c r="AH235" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -24121,6 +25537,12 @@
       <c r="AF236" s="3" t="n">
         <v>-0.002403846153846056</v>
       </c>
+      <c r="AG236" s="1" t="n">
+        <v>0.0416</v>
+      </c>
+      <c r="AH236" s="2" t="n">
+        <v>0.002409638554216769</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -24221,6 +25643,12 @@
       <c r="AF237" s="2" t="n">
         <v>0.002398081534772085</v>
       </c>
+      <c r="AG237" s="1" t="n">
+        <v>0.00417</v>
+      </c>
+      <c r="AH237" s="3" t="n">
+        <v>-0.002392344497607558</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -24321,6 +25749,12 @@
       <c r="AF238" s="2" t="n">
         <v>0.003968253968253945</v>
       </c>
+      <c r="AG238" s="1" t="n">
+        <v>0.0255</v>
+      </c>
+      <c r="AH238" s="2" t="n">
+        <v>0.007905138339920901</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -24421,6 +25855,12 @@
       <c r="AF239" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AG239" s="1" t="n">
+        <v>0.01505</v>
+      </c>
+      <c r="AH239" s="3" t="n">
+        <v>-0.001989389920424437</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -24521,6 +25961,12 @@
       <c r="AF240" s="3" t="n">
         <v>-0.00126646403242151</v>
       </c>
+      <c r="AG240" s="1" t="n">
+        <v>0.000392</v>
+      </c>
+      <c r="AH240" s="3" t="n">
+        <v>-0.00583312198833376</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -24621,6 +26067,12 @@
       <c r="AF241" s="2" t="n">
         <v>0.002209131075110417</v>
       </c>
+      <c r="AG241" s="1" t="n">
+        <v>0.2712</v>
+      </c>
+      <c r="AH241" s="3" t="n">
+        <v>-0.003673769287288762</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -24721,6 +26173,12 @@
       <c r="AF242" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AG242" s="1" t="n">
+        <v>0.07675999999999999</v>
+      </c>
+      <c r="AH242" s="2" t="n">
+        <v>0.003267546725918184</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -24821,6 +26279,12 @@
       <c r="AF243" s="3" t="n">
         <v>-0.001503759398496179</v>
       </c>
+      <c r="AG243" s="1" t="n">
+        <v>0.01994</v>
+      </c>
+      <c r="AH243" s="2" t="n">
+        <v>0.001004016064256987</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -24921,6 +26385,12 @@
       <c r="AF244" s="3" t="n">
         <v>-0.001759118095461444</v>
       </c>
+      <c r="AG244" s="1" t="n">
+        <v>0.08585</v>
+      </c>
+      <c r="AH244" s="2" t="n">
+        <v>0.008576127819548808</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -25021,6 +26491,12 @@
       <c r="AF245" s="3" t="n">
         <v>-0.002374135884365511</v>
       </c>
+      <c r="AG245" s="1" t="n">
+        <v>1.4299</v>
+      </c>
+      <c r="AH245" s="2" t="n">
+        <v>0.0008399244068032952</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -25121,6 +26597,12 @@
       <c r="AF246" s="2" t="n">
         <v>0.001121076233183811</v>
       </c>
+      <c r="AG246" s="1" t="n">
+        <v>0.01785</v>
+      </c>
+      <c r="AH246" s="3" t="n">
+        <v>-0.0005599104143336837</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -25221,6 +26703,12 @@
       <c r="AF247" s="2" t="n">
         <v>0.001209555488358058</v>
       </c>
+      <c r="AG247" s="1" t="n">
+        <v>0.006641</v>
+      </c>
+      <c r="AH247" s="2" t="n">
+        <v>0.002869223799456345</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -25321,6 +26809,12 @@
       <c r="AF248" s="2" t="n">
         <v>0.002696078431372481</v>
       </c>
+      <c r="AG248" s="1" t="n">
+        <v>0.004068</v>
+      </c>
+      <c r="AH248" s="3" t="n">
+        <v>-0.005622097286727072</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -25421,6 +26915,12 @@
       <c r="AF249" s="3" t="n">
         <v>-0.00271002710027108</v>
       </c>
+      <c r="AG249" s="1" t="n">
+        <v>0.1108</v>
+      </c>
+      <c r="AH249" s="2" t="n">
+        <v>0.003623188405797079</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -25521,6 +27021,12 @@
       <c r="AF250" s="2" t="n">
         <v>0.0005777007510109528</v>
       </c>
+      <c r="AG250" s="1" t="n">
+        <v>0.03453</v>
+      </c>
+      <c r="AH250" s="3" t="n">
+        <v>-0.003175519630484959</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -25621,6 +27127,12 @@
       <c r="AF251" s="2" t="n">
         <v>0.001404165691551708</v>
       </c>
+      <c r="AG251" s="1" t="n">
+        <v>0.04244</v>
+      </c>
+      <c r="AH251" s="3" t="n">
+        <v>-0.008179481187193341</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -25721,6 +27233,12 @@
       <c r="AF252" s="2" t="n">
         <v>0.005125576627370667</v>
       </c>
+      <c r="AG252" s="1" t="n">
+        <v>0.005943</v>
+      </c>
+      <c r="AH252" s="2" t="n">
+        <v>0.01019887812340645</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -25821,6 +27339,12 @@
       <c r="AF253" s="3" t="n">
         <v>-0.00233236151603489</v>
       </c>
+      <c r="AG253" s="1" t="n">
+        <v>0.01682</v>
+      </c>
+      <c r="AH253" s="3" t="n">
+        <v>-0.0169491525423728</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -25921,6 +27445,12 @@
       <c r="AF254" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AG254" s="1" t="n">
+        <v>0.1291</v>
+      </c>
+      <c r="AH254" s="3" t="n">
+        <v>-0.0007739938080496651</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -26021,6 +27551,12 @@
       <c r="AF255" s="2" t="n">
         <v>0.02210724365004695</v>
       </c>
+      <c r="AG255" s="1" t="n">
+        <v>0.02162</v>
+      </c>
+      <c r="AH255" s="3" t="n">
+        <v>-0.005062126092958997</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -26121,6 +27657,12 @@
       <c r="AF256" s="2" t="n">
         <v>0.002366303833412278</v>
       </c>
+      <c r="AG256" s="1" t="n">
+        <v>0.02116</v>
+      </c>
+      <c r="AH256" s="3" t="n">
+        <v>-0.0009442870632671947</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -26221,6 +27763,12 @@
       <c r="AF257" s="3" t="n">
         <v>-0.005098039215686203</v>
       </c>
+      <c r="AG257" s="1" t="n">
+        <v>0.02533</v>
+      </c>
+      <c r="AH257" s="3" t="n">
+        <v>-0.001576665352778945</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -26321,6 +27869,12 @@
       <c r="AF258" s="2" t="n">
         <v>0.001058131075986995</v>
       </c>
+      <c r="AG258" s="1" t="n">
+        <v>0.15146</v>
+      </c>
+      <c r="AH258" s="2" t="n">
+        <v>0.0005945695976746168</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -26421,6 +27975,12 @@
       <c r="AF259" s="3" t="n">
         <v>-0.0009813542688910978</v>
       </c>
+      <c r="AG259" s="1" t="n">
+        <v>0.05088</v>
+      </c>
+      <c r="AH259" s="3" t="n">
+        <v>-0.0003929273084479211</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -26521,6 +28081,12 @@
       <c r="AF260" s="3" t="n">
         <v>-0.002237399905793638</v>
       </c>
+      <c r="AG260" s="1" t="n">
+        <v>0.08418</v>
+      </c>
+      <c r="AH260" s="3" t="n">
+        <v>-0.00649120736456975</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -26621,6 +28187,12 @@
       <c r="AF261" s="3" t="n">
         <v>-0.005633802816901458</v>
       </c>
+      <c r="AG261" s="1" t="n">
+        <v>0.2437</v>
+      </c>
+      <c r="AH261" s="3" t="n">
+        <v>-0.01375961149332249</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -26721,6 +28293,12 @@
       <c r="AF262" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AG262" s="1" t="n">
+        <v>0.1448</v>
+      </c>
+      <c r="AH262" s="3" t="n">
+        <v>-0.004810996563573735</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -26821,6 +28399,12 @@
       <c r="AF263" s="2" t="n">
         <v>0.0005226025607525264</v>
       </c>
+      <c r="AG263" s="1" t="n">
+        <v>0.0765</v>
+      </c>
+      <c r="AH263" s="3" t="n">
+        <v>-0.001044659179942501</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -26921,6 +28505,12 @@
       <c r="AF264" s="3" t="n">
         <v>-0.009421950598421245</v>
       </c>
+      <c r="AG264" s="1" t="n">
+        <v>0.03904</v>
+      </c>
+      <c r="AH264" s="2" t="n">
+        <v>0.00359897172236507</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -27021,6 +28611,12 @@
       <c r="AF265" s="2" t="n">
         <v>0.001948051948051869</v>
       </c>
+      <c r="AG265" s="1" t="n">
+        <v>0.0154</v>
+      </c>
+      <c r="AH265" s="3" t="n">
+        <v>-0.001944264419961036</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -27121,6 +28717,12 @@
       <c r="AF266" s="3" t="n">
         <v>-0.001670285618840899</v>
       </c>
+      <c r="AG266" s="1" t="n">
+        <v>0.005978</v>
+      </c>
+      <c r="AH266" s="2" t="n">
+        <v>0.0001673080140538954</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -27221,6 +28823,12 @@
       <c r="AF267" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AG267" s="1" t="n">
+        <v>0.0372</v>
+      </c>
+      <c r="AH267" s="3" t="n">
+        <v>-0.004016064257028227</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -27321,6 +28929,12 @@
       <c r="AF268" s="3" t="n">
         <v>-0.0009803921568627052</v>
       </c>
+      <c r="AG268" s="1" t="n">
+        <v>0.03059</v>
+      </c>
+      <c r="AH268" s="2" t="n">
+        <v>0.0006542361792606865</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -27421,6 +29035,12 @@
       <c r="AF269" s="2" t="n">
         <v>0.002791315906069967</v>
       </c>
+      <c r="AG269" s="1" t="n">
+        <v>0.22625</v>
+      </c>
+      <c r="AH269" s="3" t="n">
+        <v>-0.0003534661777051064</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -27521,6 +29141,12 @@
       <c r="AF270" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AG270" s="1" t="n">
+        <v>0.9320000000000001</v>
+      </c>
+      <c r="AH270" s="2" t="n">
+        <v>0.001074113856068744</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -27621,6 +29247,12 @@
       <c r="AF271" s="3" t="n">
         <v>-0.0003853564547207452</v>
       </c>
+      <c r="AG271" s="1" t="n">
+        <v>2.591</v>
+      </c>
+      <c r="AH271" s="3" t="n">
+        <v>-0.001156515034695324</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -27721,6 +29353,12 @@
       <c r="AF272" s="3" t="n">
         <v>-0.005339028296849979</v>
       </c>
+      <c r="AG272" s="1" t="n">
+        <v>0.1861</v>
+      </c>
+      <c r="AH272" s="3" t="n">
+        <v>-0.001073537305421394</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -27821,6 +29459,12 @@
       <c r="AF273" s="2" t="n">
         <v>0.008028259473346185</v>
       </c>
+      <c r="AG273" s="1" t="n">
+        <v>0.0312</v>
+      </c>
+      <c r="AH273" s="3" t="n">
+        <v>-0.006052883083784729</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -27921,6 +29565,12 @@
       <c r="AF274" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AG274" s="1" t="n">
+        <v>0.1915</v>
+      </c>
+      <c r="AH274" s="3" t="n">
+        <v>-0.002604166666666669</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -28021,6 +29671,12 @@
       <c r="AF275" s="3" t="n">
         <v>-0.003324179794768145</v>
       </c>
+      <c r="AG275" s="1" t="n">
+        <v>0.06908</v>
+      </c>
+      <c r="AH275" s="2" t="n">
+        <v>0.001740139211137021</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -28121,6 +29777,12 @@
       <c r="AF276" s="3" t="n">
         <v>-0.0003731807438736441</v>
       </c>
+      <c r="AG276" s="1" t="n">
+        <v>0.08044999999999999</v>
+      </c>
+      <c r="AH276" s="2" t="n">
+        <v>0.00111996017919354</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -28221,6 +29883,12 @@
       <c r="AF277" s="3" t="n">
         <v>-0.01168996188055909</v>
       </c>
+      <c r="AG277" s="1" t="n">
+        <v>0.003841</v>
+      </c>
+      <c r="AH277" s="3" t="n">
+        <v>-0.01234250449987151</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -28321,6 +29989,12 @@
       <c r="AF278" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AG278" s="1" t="n">
+        <v>1.553</v>
+      </c>
+      <c r="AH278" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -28421,6 +30095,12 @@
       <c r="AF279" s="3" t="n">
         <v>-0.0009049773755657309</v>
       </c>
+      <c r="AG279" s="1" t="n">
+        <v>0.01104</v>
+      </c>
+      <c r="AH279" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -28521,6 +30201,12 @@
       <c r="AF280" s="3" t="n">
         <v>-0.0004986287708800594</v>
       </c>
+      <c r="AG280" s="1" t="n">
+        <v>0.04022</v>
+      </c>
+      <c r="AH280" s="2" t="n">
+        <v>0.00324270391618853</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -28621,6 +30307,12 @@
       <c r="AF281" s="2" t="n">
         <v>0.0004753981459472114</v>
       </c>
+      <c r="AG281" s="1" t="n">
+        <v>0.08400000000000001</v>
+      </c>
+      <c r="AH281" s="3" t="n">
+        <v>-0.002138275124732711</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -28721,6 +30413,12 @@
       <c r="AF282" s="3" t="n">
         <v>-0.01098901098901105</v>
       </c>
+      <c r="AG282" s="1" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="AH282" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -28821,6 +30519,12 @@
       <c r="AF283" s="3" t="n">
         <v>-0.0006538511834705701</v>
       </c>
+      <c r="AG283" s="1" t="n">
+        <v>0.07633</v>
+      </c>
+      <c r="AH283" s="3" t="n">
+        <v>-0.001177702172206317</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -28921,6 +30625,12 @@
       <c r="AF284" s="3" t="n">
         <v>-0.001241464928615797</v>
       </c>
+      <c r="AG284" s="1" t="n">
+        <v>0.00161</v>
+      </c>
+      <c r="AH284" s="2" t="n">
+        <v>0.000621504039776341</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -29021,6 +30731,12 @@
       <c r="AF285" s="2" t="n">
         <v>0.00147856086742235</v>
       </c>
+      <c r="AG285" s="1" t="n">
+        <v>0.2033</v>
+      </c>
+      <c r="AH285" s="2" t="n">
+        <v>0.0004921259842520509</v>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -29121,6 +30837,12 @@
       <c r="AF286" s="2" t="n">
         <v>0.001973127877478172</v>
       </c>
+      <c r="AG286" s="1" t="n">
+        <v>0.10642</v>
+      </c>
+      <c r="AH286" s="3" t="n">
+        <v>-0.002063015753938466</v>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -29221,6 +30943,12 @@
       <c r="AF287" s="3" t="n">
         <v>-0.001722158438576478</v>
       </c>
+      <c r="AG287" s="1" t="n">
+        <v>0.01735</v>
+      </c>
+      <c r="AH287" s="3" t="n">
+        <v>-0.002300172512938377</v>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -29321,6 +31049,12 @@
       <c r="AF288" s="2" t="n">
         <v>0.002649006622516563</v>
       </c>
+      <c r="AG288" s="1" t="n">
+        <v>0.01513</v>
+      </c>
+      <c r="AH288" s="3" t="n">
+        <v>-0.0006605019815060321</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -29421,6 +31155,12 @@
       <c r="AF289" s="3" t="n">
         <v>-0.0006176652254477822</v>
       </c>
+      <c r="AG289" s="1" t="n">
+        <v>0.01621</v>
+      </c>
+      <c r="AH289" s="2" t="n">
+        <v>0.001854140914709442</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -29521,6 +31261,12 @@
       <c r="AF290" s="2" t="n">
         <v>0.002215330084182496</v>
       </c>
+      <c r="AG290" s="1" t="n">
+        <v>2.265</v>
+      </c>
+      <c r="AH290" s="2" t="n">
+        <v>0.001326259946949652</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -29621,6 +31367,12 @@
       <c r="AF291" s="3" t="n">
         <v>-0.002034817996834754</v>
       </c>
+      <c r="AG291" s="1" t="n">
+        <v>0.4413</v>
+      </c>
+      <c r="AH291" s="3" t="n">
+        <v>-0.0002265518803805822</v>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -29721,6 +31473,12 @@
       <c r="AF292" s="2" t="n">
         <v>0.001158748551564312</v>
       </c>
+      <c r="AG292" s="1" t="n">
+        <v>1.729</v>
+      </c>
+      <c r="AH292" s="2" t="n">
+        <v>0.0005787037037037685</v>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -29821,6 +31579,12 @@
       <c r="AF293" s="3" t="n">
         <v>-0.001964250638381378</v>
       </c>
+      <c r="AG293" s="1" t="n">
+        <v>0.05085</v>